--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/91fa87361a894c12/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="8_{BBB43D32-B953-4799-B724-336D98AD9DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EAD1B58-6E5A-424D-938E-3AFA1BE27CA1}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="8_{BBB43D32-B953-4799-B724-336D98AD9DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFAABF7B-4221-402B-AAAD-46B08D02DDB2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -3756,7 +3756,9 @@
       <c r="K3" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="9"/>
+      <c r="L3" s="64">
+        <v>46232</v>
+      </c>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="64">
@@ -3811,7 +3813,9 @@
       <c r="K4" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="L4" s="9"/>
+      <c r="L4" s="64">
+        <v>46235</v>
+      </c>
       <c r="M4" s="9"/>
       <c r="N4" s="9"/>
       <c r="O4" s="9"/>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/91fa87361a894c12/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="8_{BBB43D32-B953-4799-B724-336D98AD9DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFAABF7B-4221-402B-AAAD-46B08D02DDB2}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="8_{BBB43D32-B953-4799-B724-336D98AD9DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09BF8A79-0F12-4B26-87C5-86363BD596CC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -2614,9 +2614,6 @@
     <t>PLS BAH</t>
   </si>
   <si>
-    <t>ASIF BHAI</t>
-  </si>
-  <si>
     <t>SULTAN</t>
   </si>
   <si>
@@ -2771,6 +2768,9 @@
   </si>
   <si>
     <t>RECEIVED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASIF </t>
   </si>
 </sst>
 </file>
@@ -3696,7 +3696,7 @@
         <v>12</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>859</v>
+        <v>911</v>
       </c>
       <c r="K2" s="49" t="s">
         <v>21</v>
@@ -4497,7 +4497,7 @@
         <v>12</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K17" s="49" t="s">
         <v>21</v>
@@ -4554,7 +4554,7 @@
         <v>12</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K18" s="49" t="s">
         <v>21</v>
@@ -4607,7 +4607,7 @@
         <v>12</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K19" s="49" t="s">
         <v>21</v>
@@ -4664,7 +4664,7 @@
         <v>12</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K20" s="49" t="s">
         <v>21</v>
@@ -4675,7 +4675,7 @@
       <c r="O20" s="9"/>
       <c r="P20" s="9"/>
       <c r="Q20" s="13" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="R20" s="60" t="s">
         <v>25</v>
@@ -4719,7 +4719,7 @@
         <v>12</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K21" s="49" t="s">
         <v>21</v>
@@ -4774,7 +4774,7 @@
         <v>12</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K22" s="49" t="s">
         <v>21</v>
@@ -4831,7 +4831,7 @@
         <v>12</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K23" s="49" t="s">
         <v>21</v>
@@ -4888,7 +4888,7 @@
         <v>12</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K24" s="49" t="s">
         <v>21</v>
@@ -4943,7 +4943,7 @@
         <v>12</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K25" s="49" t="s">
         <v>21</v>
@@ -4998,7 +4998,7 @@
         <v>12</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K26" s="49" t="s">
         <v>21</v>
@@ -5057,7 +5057,7 @@
         <v>12</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K27" s="49" t="s">
         <v>21</v>
@@ -5116,7 +5116,7 @@
         <v>12</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K28" s="49" t="s">
         <v>21</v>
@@ -5160,7 +5160,7 @@
         <v>12</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K29" s="49" t="s">
         <v>21</v>
@@ -5204,7 +5204,7 @@
         <v>12</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K30" s="49" t="s">
         <v>21</v>
@@ -5250,7 +5250,7 @@
         <v>12</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K31" s="49" t="s">
         <v>21</v>
@@ -5294,7 +5294,7 @@
         <v>12</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K32" s="49" t="s">
         <v>21</v>
@@ -5338,7 +5338,7 @@
         <v>12</v>
       </c>
       <c r="J33" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K33" s="49" t="s">
         <v>21</v>
@@ -5382,7 +5382,7 @@
         <v>12</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K34" s="49" t="s">
         <v>21</v>
@@ -5426,7 +5426,7 @@
         <v>12</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K35" s="49" t="s">
         <v>21</v>
@@ -5470,7 +5470,7 @@
         <v>12</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K36" s="49" t="s">
         <v>21</v>
@@ -5514,7 +5514,7 @@
         <v>12</v>
       </c>
       <c r="J37" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K37" s="49" t="s">
         <v>21</v>
@@ -5558,7 +5558,7 @@
         <v>12</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K38" s="49" t="s">
         <v>21</v>
@@ -5602,7 +5602,7 @@
         <v>12</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K39" s="49" t="s">
         <v>21</v>
@@ -5646,7 +5646,7 @@
         <v>12</v>
       </c>
       <c r="J40" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K40" s="49" t="s">
         <v>21</v>
@@ -5690,7 +5690,7 @@
         <v>12</v>
       </c>
       <c r="J41" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K41" s="49" t="s">
         <v>21</v>
@@ -5734,7 +5734,7 @@
         <v>12</v>
       </c>
       <c r="J42" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K42" s="49" t="s">
         <v>21</v>
@@ -5780,7 +5780,7 @@
         <v>12</v>
       </c>
       <c r="J43" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K43" s="49" t="s">
         <v>21</v>
@@ -5824,7 +5824,7 @@
         <v>12</v>
       </c>
       <c r="J44" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K44" s="49" t="s">
         <v>21</v>
@@ -5868,7 +5868,7 @@
         <v>12</v>
       </c>
       <c r="J45" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K45" s="49" t="s">
         <v>21</v>
@@ -5912,7 +5912,7 @@
         <v>12</v>
       </c>
       <c r="J46" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K46" s="49" t="s">
         <v>21</v>
@@ -5956,7 +5956,7 @@
         <v>12</v>
       </c>
       <c r="J47" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K47" s="49" t="s">
         <v>21</v>
@@ -6000,7 +6000,7 @@
         <v>12</v>
       </c>
       <c r="J48" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K48" s="49" t="s">
         <v>21</v>
@@ -6044,7 +6044,7 @@
         <v>12</v>
       </c>
       <c r="J49" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K49" s="49" t="s">
         <v>21</v>
@@ -6088,7 +6088,7 @@
         <v>12</v>
       </c>
       <c r="J50" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K50" s="49" t="s">
         <v>21</v>
@@ -6099,7 +6099,7 @@
       <c r="O50" s="9"/>
       <c r="P50" s="9"/>
       <c r="Q50" s="13" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="R50" s="60" t="s">
         <v>25</v>
@@ -6134,7 +6134,7 @@
         <v>856</v>
       </c>
       <c r="J51" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K51" s="49" t="s">
         <v>21</v>
@@ -6148,7 +6148,7 @@
         <v>90956441</v>
       </c>
       <c r="R51" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="52" spans="1:18" ht="15" thickBot="1">
@@ -6178,7 +6178,7 @@
         <v>12</v>
       </c>
       <c r="J52" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K52" s="49" t="s">
         <v>21</v>
@@ -6222,7 +6222,7 @@
         <v>12</v>
       </c>
       <c r="J53" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K53" s="49" t="s">
         <v>21</v>
@@ -6264,7 +6264,7 @@
         <v>12</v>
       </c>
       <c r="J54" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K54" s="49" t="s">
         <v>21</v>
@@ -6308,7 +6308,7 @@
         <v>12</v>
       </c>
       <c r="J55" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K55" s="49" t="s">
         <v>21</v>
@@ -6350,7 +6350,7 @@
         <v>12</v>
       </c>
       <c r="J56" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K56" s="49" t="s">
         <v>21</v>
@@ -6394,7 +6394,7 @@
         <v>12</v>
       </c>
       <c r="J57" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K57" s="49" t="s">
         <v>21</v>
@@ -6438,7 +6438,7 @@
         <v>12</v>
       </c>
       <c r="J58" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K58" s="49" t="s">
         <v>21</v>
@@ -6449,7 +6449,7 @@
       <c r="O58" s="9"/>
       <c r="P58" s="9"/>
       <c r="Q58" s="13" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="R58" s="60" t="s">
         <v>25</v>
@@ -6482,7 +6482,7 @@
         <v>12</v>
       </c>
       <c r="J59" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K59" s="49" t="s">
         <v>21</v>
@@ -6526,7 +6526,7 @@
         <v>12</v>
       </c>
       <c r="J60" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K60" s="49" t="s">
         <v>21</v>
@@ -6570,7 +6570,7 @@
         <v>12</v>
       </c>
       <c r="J61" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K61" s="49" t="s">
         <v>21</v>
@@ -6612,7 +6612,7 @@
         <v>12</v>
       </c>
       <c r="J62" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K62" s="49" t="s">
         <v>21</v>
@@ -6654,7 +6654,7 @@
         <v>12</v>
       </c>
       <c r="J63" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K63" s="49" t="s">
         <v>21</v>
@@ -6696,7 +6696,7 @@
         <v>12</v>
       </c>
       <c r="J64" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K64" s="49" t="s">
         <v>21</v>
@@ -6738,7 +6738,7 @@
         <v>12</v>
       </c>
       <c r="J65" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K65" s="49" t="s">
         <v>21</v>
@@ -6780,7 +6780,7 @@
         <v>12</v>
       </c>
       <c r="J66" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K66" s="49" t="s">
         <v>21</v>
@@ -6822,7 +6822,7 @@
         <v>12</v>
       </c>
       <c r="J67" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K67" s="49" t="s">
         <v>21</v>
@@ -6915,7 +6915,7 @@
       <c r="O69" s="9"/>
       <c r="P69" s="9"/>
       <c r="Q69" s="13" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="R69" s="60" t="s">
         <v>25</v>
@@ -6950,7 +6950,7 @@
         <v>858</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="K70" s="49" t="s">
         <v>21</v>
@@ -6962,7 +6962,7 @@
       <c r="P70" s="9"/>
       <c r="Q70" s="9"/>
       <c r="R70" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="71" spans="1:18" ht="28.2" thickBot="1">
@@ -6994,7 +6994,7 @@
         <v>858</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="K71" s="49" t="s">
         <v>21</v>
@@ -7008,7 +7008,7 @@
       <c r="P71" s="9"/>
       <c r="Q71" s="9"/>
       <c r="R71" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="72" spans="1:18" ht="28.2" thickBot="1">
@@ -7040,7 +7040,7 @@
         <v>858</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="K72" s="49" t="s">
         <v>21</v>
@@ -7052,7 +7052,7 @@
       <c r="P72" s="9"/>
       <c r="Q72" s="9"/>
       <c r="R72" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="73" spans="1:18" ht="28.2" thickBot="1">
@@ -7084,7 +7084,7 @@
         <v>858</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="K73" s="49" t="s">
         <v>21</v>
@@ -7096,7 +7096,7 @@
       <c r="P73" s="9"/>
       <c r="Q73" s="9"/>
       <c r="R73" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="74" spans="1:18" ht="15" thickBot="1">
@@ -7128,7 +7128,7 @@
         <v>12</v>
       </c>
       <c r="J74" s="14" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K74" s="49" t="s">
         <v>21</v>
@@ -7172,10 +7172,10 @@
         <v>12</v>
       </c>
       <c r="J75" s="14" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K75" s="23" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="L75" s="52"/>
       <c r="M75" s="52"/>
@@ -7216,7 +7216,7 @@
         <v>12</v>
       </c>
       <c r="J76" s="14" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K76" s="49" t="s">
         <v>21</v>
@@ -7260,7 +7260,7 @@
         <v>12</v>
       </c>
       <c r="J77" s="14" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K77" s="49" t="s">
         <v>21</v>
@@ -7304,7 +7304,7 @@
         <v>12</v>
       </c>
       <c r="J78" s="14" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K78" s="49" t="s">
         <v>21</v>
@@ -7348,7 +7348,7 @@
         <v>12</v>
       </c>
       <c r="J79" s="14" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K79" s="49" t="s">
         <v>21</v>
@@ -7392,7 +7392,7 @@
         <v>12</v>
       </c>
       <c r="J80" s="14" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="K80" s="49" t="s">
         <v>21</v>
@@ -7436,7 +7436,7 @@
         <v>12</v>
       </c>
       <c r="J81" s="14" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="K81" s="49" t="s">
         <v>21</v>
@@ -7480,7 +7480,7 @@
         <v>12</v>
       </c>
       <c r="J82" s="14" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="K82" s="49" t="s">
         <v>21</v>
@@ -7524,7 +7524,7 @@
         <v>12</v>
       </c>
       <c r="J83" s="14" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="K83" s="49" t="s">
         <v>21</v>
@@ -7568,7 +7568,7 @@
         <v>12</v>
       </c>
       <c r="J84" s="14" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="K84" s="49" t="s">
         <v>21</v>
@@ -7612,7 +7612,7 @@
         <v>12</v>
       </c>
       <c r="J85" s="14" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="K85" s="49" t="s">
         <v>21</v>
@@ -7656,7 +7656,7 @@
         <v>12</v>
       </c>
       <c r="J86" s="14" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="K86" s="49" t="s">
         <v>21</v>
@@ -7700,7 +7700,7 @@
         <v>12</v>
       </c>
       <c r="J87" s="14" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="K87" s="49" t="s">
         <v>21</v>
@@ -7742,7 +7742,7 @@
         <v>12</v>
       </c>
       <c r="J88" s="14" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="K88" s="49" t="s">
         <v>21</v>
@@ -7788,7 +7788,7 @@
         <v>12</v>
       </c>
       <c r="J89" s="14" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="K89" s="49" t="s">
         <v>21</v>
@@ -7832,7 +7832,7 @@
         <v>12</v>
       </c>
       <c r="J90" s="14" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="K90" s="49" t="s">
         <v>21</v>
@@ -7876,7 +7876,7 @@
         <v>12</v>
       </c>
       <c r="J91" s="14" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="K91" s="49" t="s">
         <v>21</v>
@@ -7922,7 +7922,7 @@
         <v>12</v>
       </c>
       <c r="J92" s="14" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="K92" s="49" t="s">
         <v>21</v>
@@ -7966,7 +7966,7 @@
         <v>12</v>
       </c>
       <c r="J93" s="14" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="K93" s="49" t="s">
         <v>21</v>
@@ -8012,7 +8012,7 @@
         <v>12</v>
       </c>
       <c r="J94" s="14" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="K94" s="49" t="s">
         <v>21</v>
@@ -8056,7 +8056,7 @@
         <v>12</v>
       </c>
       <c r="J95" s="14" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="K95" s="49" t="s">
         <v>21</v>
@@ -8100,7 +8100,7 @@
         <v>12</v>
       </c>
       <c r="J96" s="14" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="K96" s="49" t="s">
         <v>21</v>
@@ -8144,7 +8144,7 @@
         <v>12</v>
       </c>
       <c r="J97" s="14" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="K97" s="49" t="s">
         <v>21</v>
@@ -8188,7 +8188,7 @@
         <v>12</v>
       </c>
       <c r="J98" s="14" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="K98" s="49" t="s">
         <v>21</v>
@@ -8234,7 +8234,7 @@
         <v>12</v>
       </c>
       <c r="J99" s="14" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="K99" s="49" t="s">
         <v>21</v>
@@ -8276,10 +8276,10 @@
         <v>12</v>
       </c>
       <c r="J100" s="14" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="K100" s="49" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="L100" s="9"/>
       <c r="M100" s="9"/>
@@ -8320,7 +8320,7 @@
         <v>856</v>
       </c>
       <c r="J101" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K101" s="49" t="s">
         <v>21</v>
@@ -8334,7 +8334,7 @@
         <v>96897095513</v>
       </c>
       <c r="R101" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="102" spans="1:18" ht="15" thickBot="1">
@@ -8366,7 +8366,7 @@
         <v>856</v>
       </c>
       <c r="J102" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K102" s="49" t="s">
         <v>21</v>
@@ -8380,7 +8380,7 @@
         <v>94542937</v>
       </c>
       <c r="R102" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="103" spans="1:18" ht="15" thickBot="1">
@@ -8412,7 +8412,7 @@
         <v>856</v>
       </c>
       <c r="J103" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K103" s="49" t="s">
         <v>21</v>
@@ -8426,7 +8426,7 @@
         <v>971547128897</v>
       </c>
       <c r="R103" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="104" spans="1:18" ht="15" thickBot="1">
@@ -8458,7 +8458,7 @@
         <v>856</v>
       </c>
       <c r="J104" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K104" s="49" t="s">
         <v>21</v>
@@ -8472,7 +8472,7 @@
         <v>77136723</v>
       </c>
       <c r="R104" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="105" spans="1:18" ht="15" thickBot="1">
@@ -8504,7 +8504,7 @@
         <v>856</v>
       </c>
       <c r="J105" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K105" s="49" t="s">
         <v>21</v>
@@ -8518,7 +8518,7 @@
         <v>96876683087</v>
       </c>
       <c r="R105" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="106" spans="1:18" ht="15" thickBot="1">
@@ -8550,7 +8550,7 @@
         <v>856</v>
       </c>
       <c r="J106" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K106" s="49" t="s">
         <v>21</v>
@@ -8566,7 +8566,7 @@
         <v>77005352</v>
       </c>
       <c r="R106" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="107" spans="1:18" ht="15" thickBot="1">
@@ -8596,7 +8596,7 @@
         <v>856</v>
       </c>
       <c r="J107" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K107" s="49" t="s">
         <v>21</v>
@@ -8610,7 +8610,7 @@
         <v>77825143</v>
       </c>
       <c r="R107" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="108" spans="1:18" ht="15" thickBot="1">
@@ -8642,7 +8642,7 @@
         <v>856</v>
       </c>
       <c r="J108" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K108" s="49" t="s">
         <v>21</v>
@@ -8656,7 +8656,7 @@
         <v>77560153</v>
       </c>
       <c r="R108" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="109" spans="1:18" ht="15" thickBot="1">
@@ -8688,7 +8688,7 @@
         <v>856</v>
       </c>
       <c r="J109" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K109" s="49" t="s">
         <v>21</v>
@@ -8702,7 +8702,7 @@
         <v>77078394</v>
       </c>
       <c r="R109" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="110" spans="1:18" ht="15" thickBot="1">
@@ -8734,7 +8734,7 @@
         <v>856</v>
       </c>
       <c r="J110" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K110" s="49" t="s">
         <v>21</v>
@@ -8748,7 +8748,7 @@
         <v>569370083</v>
       </c>
       <c r="R110" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="111" spans="1:18" ht="15" thickBot="1">
@@ -8780,7 +8780,7 @@
         <v>856</v>
       </c>
       <c r="J111" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K111" s="49" t="s">
         <v>21</v>
@@ -8794,7 +8794,7 @@
         <v>95775986</v>
       </c>
       <c r="R111" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="112" spans="1:18" ht="15" thickBot="1">
@@ -8826,7 +8826,7 @@
         <v>856</v>
       </c>
       <c r="J112" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K112" s="49" t="s">
         <v>21</v>
@@ -8840,7 +8840,7 @@
         <v>527491452</v>
       </c>
       <c r="R112" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="113" spans="1:18" ht="15" thickBot="1">
@@ -8872,7 +8872,7 @@
         <v>856</v>
       </c>
       <c r="J113" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K113" s="49" t="s">
         <v>21</v>
@@ -8886,7 +8886,7 @@
         <v>523113475</v>
       </c>
       <c r="R113" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="114" spans="1:18" ht="15" thickBot="1">
@@ -8918,7 +8918,7 @@
         <v>856</v>
       </c>
       <c r="J114" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K114" s="49" t="s">
         <v>21</v>
@@ -8934,7 +8934,7 @@
         <v>71576737</v>
       </c>
       <c r="R114" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="115" spans="1:18" ht="15" thickBot="1">
@@ -8966,7 +8966,7 @@
         <v>856</v>
       </c>
       <c r="J115" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K115" s="49" t="s">
         <v>21</v>
@@ -8980,7 +8980,7 @@
         <v>99138916</v>
       </c>
       <c r="R115" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="116" spans="1:18" ht="15" thickBot="1">
@@ -9012,7 +9012,7 @@
         <v>856</v>
       </c>
       <c r="J116" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K116" s="49" t="s">
         <v>21</v>
@@ -9026,7 +9026,7 @@
         <v>76784205</v>
       </c>
       <c r="R116" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="117" spans="1:18" ht="15" thickBot="1">
@@ -9058,7 +9058,7 @@
         <v>856</v>
       </c>
       <c r="J117" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K117" s="49" t="s">
         <v>21</v>
@@ -9072,7 +9072,7 @@
         <v>77454348</v>
       </c>
       <c r="R117" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="118" spans="1:18" ht="15" thickBot="1">
@@ -9104,7 +9104,7 @@
         <v>856</v>
       </c>
       <c r="J118" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K118" s="49" t="s">
         <v>21</v>
@@ -9118,7 +9118,7 @@
         <v>76646912</v>
       </c>
       <c r="R118" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="119" spans="1:18" ht="15" thickBot="1">
@@ -9150,7 +9150,7 @@
         <v>856</v>
       </c>
       <c r="J119" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K119" s="49" t="s">
         <v>21</v>
@@ -9164,7 +9164,7 @@
         <v>96895691746</v>
       </c>
       <c r="R119" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="120" spans="1:18" ht="15" thickBot="1">
@@ -9196,7 +9196,7 @@
         <v>856</v>
       </c>
       <c r="J120" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K120" s="49" t="s">
         <v>21</v>
@@ -9210,7 +9210,7 @@
         <v>95613236</v>
       </c>
       <c r="R120" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="121" spans="1:18" ht="15" thickBot="1">
@@ -9242,7 +9242,7 @@
         <v>856</v>
       </c>
       <c r="J121" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K121" s="49" t="s">
         <v>21</v>
@@ -9256,7 +9256,7 @@
         <v>77113476</v>
       </c>
       <c r="R121" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="122" spans="1:18" ht="15" thickBot="1">
@@ -9288,7 +9288,7 @@
         <v>856</v>
       </c>
       <c r="J122" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K122" s="49" t="s">
         <v>21</v>
@@ -9302,7 +9302,7 @@
         <v>77843600</v>
       </c>
       <c r="R122" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="123" spans="1:18" ht="15" thickBot="1">
@@ -9334,7 +9334,7 @@
         <v>856</v>
       </c>
       <c r="J123" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K123" s="49" t="s">
         <v>21</v>
@@ -9348,7 +9348,7 @@
         <v>77847478</v>
       </c>
       <c r="R123" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="124" spans="1:18" ht="15" thickBot="1">
@@ -9380,7 +9380,7 @@
         <v>856</v>
       </c>
       <c r="J124" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K124" s="49" t="s">
         <v>21</v>
@@ -9394,7 +9394,7 @@
         <v>96895572588</v>
       </c>
       <c r="R124" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="125" spans="1:18" ht="15" thickBot="1">
@@ -9426,7 +9426,7 @@
         <v>856</v>
       </c>
       <c r="J125" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K125" s="49" t="s">
         <v>21</v>
@@ -9440,7 +9440,7 @@
         <v>76927610</v>
       </c>
       <c r="R125" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="126" spans="1:18" ht="15" thickBot="1">
@@ -9472,7 +9472,7 @@
         <v>856</v>
       </c>
       <c r="J126" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K126" s="49" t="s">
         <v>21</v>
@@ -9486,7 +9486,7 @@
         <v>96891242027</v>
       </c>
       <c r="R126" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="127" spans="1:18" ht="15" thickBot="1">
@@ -9518,7 +9518,7 @@
         <v>856</v>
       </c>
       <c r="J127" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K127" s="49" t="s">
         <v>21</v>
@@ -9532,7 +9532,7 @@
         <v>94549929</v>
       </c>
       <c r="R127" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="128" spans="1:18" ht="15" thickBot="1">
@@ -9564,7 +9564,7 @@
         <v>856</v>
       </c>
       <c r="J128" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K128" s="49" t="s">
         <v>21</v>
@@ -9578,7 +9578,7 @@
         <v>77402729</v>
       </c>
       <c r="R128" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="129" spans="1:18" ht="15" thickBot="1">
@@ -9610,7 +9610,7 @@
         <v>856</v>
       </c>
       <c r="J129" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K129" s="49" t="s">
         <v>21</v>
@@ -9624,7 +9624,7 @@
         <v>94553287</v>
       </c>
       <c r="R129" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="130" spans="1:18" ht="15" thickBot="1">
@@ -9656,7 +9656,7 @@
         <v>856</v>
       </c>
       <c r="J130" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K130" s="49" t="s">
         <v>21</v>
@@ -9670,7 +9670,7 @@
         <v>96895756374</v>
       </c>
       <c r="R130" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="131" spans="1:18" ht="15" thickBot="1">
@@ -9702,7 +9702,7 @@
         <v>856</v>
       </c>
       <c r="J131" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K131" s="49" t="s">
         <v>21</v>
@@ -9716,7 +9716,7 @@
         <v>76800630</v>
       </c>
       <c r="R131" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="132" spans="1:18" ht="15" thickBot="1">
@@ -9748,7 +9748,7 @@
         <v>856</v>
       </c>
       <c r="J132" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K132" s="49" t="s">
         <v>21</v>
@@ -9762,7 +9762,7 @@
         <v>77598659</v>
       </c>
       <c r="R132" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="133" spans="1:18" ht="15" thickBot="1">
@@ -9794,7 +9794,7 @@
         <v>856</v>
       </c>
       <c r="J133" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K133" s="49" t="s">
         <v>21</v>
@@ -9808,7 +9808,7 @@
         <v>96427254</v>
       </c>
       <c r="R133" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="134" spans="1:18" ht="15" thickBot="1">
@@ -9840,7 +9840,7 @@
         <v>856</v>
       </c>
       <c r="J134" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K134" s="49" t="s">
         <v>21</v>
@@ -9854,7 +9854,7 @@
         <v>504703168</v>
       </c>
       <c r="R134" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="135" spans="1:18" ht="15" thickBot="1">
@@ -9886,7 +9886,7 @@
         <v>856</v>
       </c>
       <c r="J135" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K135" s="49" t="s">
         <v>21</v>
@@ -9900,7 +9900,7 @@
         <v>77587531</v>
       </c>
       <c r="R135" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="136" spans="1:18" ht="15" thickBot="1">
@@ -9932,7 +9932,7 @@
         <v>856</v>
       </c>
       <c r="J136" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K136" s="49" t="s">
         <v>21</v>
@@ -9946,7 +9946,7 @@
         <v>95753271</v>
       </c>
       <c r="R136" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="137" spans="1:18" ht="15" thickBot="1">
@@ -9978,7 +9978,7 @@
         <v>856</v>
       </c>
       <c r="J137" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K137" s="49" t="s">
         <v>21</v>
@@ -9989,10 +9989,10 @@
       <c r="O137" s="9"/>
       <c r="P137" s="9"/>
       <c r="Q137" s="13" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="R137" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="138" spans="1:18" ht="15" thickBot="1">
@@ -10024,7 +10024,7 @@
         <v>856</v>
       </c>
       <c r="J138" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K138" s="49" t="s">
         <v>21</v>
@@ -10038,7 +10038,7 @@
         <v>524910916</v>
       </c>
       <c r="R138" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="139" spans="1:18" ht="15" thickBot="1">
@@ -10070,7 +10070,7 @@
         <v>856</v>
       </c>
       <c r="J139" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K139" s="49" t="s">
         <v>21</v>
@@ -10084,7 +10084,7 @@
         <v>76904367</v>
       </c>
       <c r="R139" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="140" spans="1:18" ht="15" thickBot="1">
@@ -10116,7 +10116,7 @@
         <v>856</v>
       </c>
       <c r="J140" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K140" s="49" t="s">
         <v>21</v>
@@ -10130,7 +10130,7 @@
         <v>76814187</v>
       </c>
       <c r="R140" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="141" spans="1:18" ht="28.2" thickBot="1">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="J147" s="9"/>
       <c r="K147" s="50" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L147" s="9"/>
       <c r="M147" s="9"/>
@@ -10471,7 +10471,7 @@
       </c>
       <c r="J148" s="9"/>
       <c r="K148" s="50" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L148" s="9"/>
       <c r="M148" s="9"/>
@@ -10688,7 +10688,7 @@
         <v>856</v>
       </c>
       <c r="J153" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K153" s="49" t="s">
         <v>21</v>
@@ -10702,7 +10702,7 @@
         <v>95837339</v>
       </c>
       <c r="R153" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="154" spans="1:18" ht="15" thickBot="1">
@@ -10734,7 +10734,7 @@
         <v>856</v>
       </c>
       <c r="J154" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K154" s="49" t="s">
         <v>21</v>
@@ -10748,7 +10748,7 @@
         <v>71317145</v>
       </c>
       <c r="R154" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="155" spans="1:18" ht="15" thickBot="1">
@@ -10780,7 +10780,7 @@
         <v>856</v>
       </c>
       <c r="J155" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K155" s="49" t="s">
         <v>21</v>
@@ -10794,7 +10794,7 @@
         <v>72093508</v>
       </c>
       <c r="R155" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="156" spans="1:18" ht="15" thickBot="1">
@@ -10826,7 +10826,7 @@
         <v>856</v>
       </c>
       <c r="J156" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K156" s="49" t="s">
         <v>21</v>
@@ -10840,7 +10840,7 @@
         <v>95813276</v>
       </c>
       <c r="R156" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="157" spans="1:18" ht="15" thickBot="1">
@@ -10872,7 +10872,7 @@
         <v>856</v>
       </c>
       <c r="J157" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K157" s="49" t="s">
         <v>21</v>
@@ -10886,7 +10886,7 @@
         <v>95684365</v>
       </c>
       <c r="R157" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="158" spans="1:18" ht="28.2" thickBot="1">
@@ -10916,10 +10916,10 @@
         <v>858</v>
       </c>
       <c r="J158" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="K158" s="50" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L158" s="54">
         <v>46232</v>
@@ -10930,7 +10930,7 @@
       <c r="P158" s="9"/>
       <c r="Q158" s="9"/>
       <c r="R158" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="159" spans="1:18" ht="28.2" thickBot="1">
@@ -10962,10 +10962,10 @@
         <v>858</v>
       </c>
       <c r="J159" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="K159" s="50" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L159" s="54">
         <v>46232</v>
@@ -10976,7 +10976,7 @@
       <c r="P159" s="9"/>
       <c r="Q159" s="9"/>
       <c r="R159" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="160" spans="1:18" ht="28.2" thickBot="1">
@@ -11008,10 +11008,10 @@
         <v>858</v>
       </c>
       <c r="J160" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="K160" s="50" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L160" s="54">
         <v>46232</v>
@@ -11022,7 +11022,7 @@
       <c r="P160" s="9"/>
       <c r="Q160" s="9"/>
       <c r="R160" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="161" spans="1:18" ht="28.2" thickBot="1">
@@ -11054,10 +11054,10 @@
         <v>858</v>
       </c>
       <c r="J161" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="K161" s="50" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L161" s="54">
         <v>46232</v>
@@ -11068,7 +11068,7 @@
       <c r="P161" s="9"/>
       <c r="Q161" s="9"/>
       <c r="R161" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="162" spans="1:18" ht="28.2" thickBot="1">
@@ -11100,10 +11100,10 @@
         <v>858</v>
       </c>
       <c r="J162" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="K162" s="50" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L162" s="54">
         <v>46232</v>
@@ -11114,7 +11114,7 @@
       <c r="P162" s="9"/>
       <c r="Q162" s="9"/>
       <c r="R162" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="163" spans="1:18" ht="28.2" thickBot="1">
@@ -11146,7 +11146,7 @@
         <v>858</v>
       </c>
       <c r="J163" s="7" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="K163" s="49" t="s">
         <v>21</v>
@@ -11160,7 +11160,7 @@
       <c r="P163" s="9"/>
       <c r="Q163" s="9"/>
       <c r="R163" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="164" spans="1:18" ht="28.2" thickBot="1">
@@ -11192,10 +11192,10 @@
         <v>858</v>
       </c>
       <c r="J164" s="7" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="K164" s="50" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L164" s="54">
         <v>46232</v>
@@ -11206,7 +11206,7 @@
       <c r="P164" s="9"/>
       <c r="Q164" s="9"/>
       <c r="R164" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="165" spans="1:18" ht="28.2" thickBot="1">
@@ -11238,10 +11238,10 @@
         <v>858</v>
       </c>
       <c r="J165" s="7" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="K165" s="50" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L165" s="54">
         <v>46232</v>
@@ -11252,7 +11252,7 @@
       <c r="P165" s="9"/>
       <c r="Q165" s="9"/>
       <c r="R165" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="166" spans="1:18" ht="28.2" thickBot="1">
@@ -11284,7 +11284,7 @@
         <v>858</v>
       </c>
       <c r="J166" s="7" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="K166" s="49" t="s">
         <v>21</v>
@@ -11296,7 +11296,7 @@
       <c r="P166" s="9"/>
       <c r="Q166" s="9"/>
       <c r="R166" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="167" spans="1:18" ht="28.2" thickBot="1">
@@ -11328,10 +11328,10 @@
         <v>858</v>
       </c>
       <c r="J167" s="7" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="K167" s="50" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L167" s="54">
         <v>46232</v>
@@ -11342,7 +11342,7 @@
       <c r="P167" s="9"/>
       <c r="Q167" s="9"/>
       <c r="R167" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="168" spans="1:18" ht="28.2" thickBot="1">
@@ -11374,7 +11374,7 @@
         <v>858</v>
       </c>
       <c r="J168" s="7" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="K168" s="49" t="s">
         <v>21</v>
@@ -11386,7 +11386,7 @@
       <c r="P168" s="9"/>
       <c r="Q168" s="9"/>
       <c r="R168" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="169" spans="1:18" ht="28.2" thickBot="1">
@@ -11460,7 +11460,7 @@
         <v>856</v>
       </c>
       <c r="J170" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K170" s="49" t="s">
         <v>21</v>
@@ -11474,7 +11474,7 @@
         <v>77030605</v>
       </c>
       <c r="R170" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="171" spans="1:18" ht="15" thickBot="1">
@@ -11506,7 +11506,7 @@
         <v>856</v>
       </c>
       <c r="J171" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K171" s="49" t="s">
         <v>21</v>
@@ -11520,7 +11520,7 @@
         <v>94557560</v>
       </c>
       <c r="R171" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="172" spans="1:18" ht="15" thickBot="1">
@@ -11552,7 +11552,7 @@
         <v>856</v>
       </c>
       <c r="J172" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K172" s="49" t="s">
         <v>21</v>
@@ -11566,7 +11566,7 @@
         <v>95712792</v>
       </c>
       <c r="R172" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="173" spans="1:18" ht="15" thickBot="1">
@@ -11598,7 +11598,7 @@
         <v>856</v>
       </c>
       <c r="J173" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K173" s="49" t="s">
         <v>21</v>
@@ -11612,7 +11612,7 @@
         <v>77376182</v>
       </c>
       <c r="R173" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="174" spans="1:18" ht="15" thickBot="1">
@@ -11644,7 +11644,7 @@
         <v>856</v>
       </c>
       <c r="J174" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K174" s="49" t="s">
         <v>21</v>
@@ -11658,7 +11658,7 @@
         <v>93325795</v>
       </c>
       <c r="R174" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="175" spans="1:18" ht="15" thickBot="1">
@@ -11690,7 +11690,7 @@
         <v>856</v>
       </c>
       <c r="J175" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K175" s="49" t="s">
         <v>21</v>
@@ -11704,7 +11704,7 @@
         <v>971554547960</v>
       </c>
       <c r="R175" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="176" spans="1:18" ht="15" thickBot="1">
@@ -11736,7 +11736,7 @@
         <v>856</v>
       </c>
       <c r="J176" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K176" s="49" t="s">
         <v>21</v>
@@ -11750,7 +11750,7 @@
         <v>77201572</v>
       </c>
       <c r="R176" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="177" spans="1:18" ht="15" thickBot="1">
@@ -11782,7 +11782,7 @@
         <v>856</v>
       </c>
       <c r="J177" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K177" s="49" t="s">
         <v>21</v>
@@ -11796,7 +11796,7 @@
         <v>96895127824</v>
       </c>
       <c r="R177" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="178" spans="1:18" ht="15" thickBot="1">
@@ -11828,7 +11828,7 @@
         <v>856</v>
       </c>
       <c r="J178" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K178" s="49" t="s">
         <v>21</v>
@@ -11842,7 +11842,7 @@
         <v>95775821</v>
       </c>
       <c r="R178" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="179" spans="1:18" ht="15" thickBot="1">
@@ -11874,7 +11874,7 @@
         <v>856</v>
       </c>
       <c r="J179" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K179" s="49" t="s">
         <v>21</v>
@@ -11888,7 +11888,7 @@
         <v>521811752</v>
       </c>
       <c r="R179" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="180" spans="1:18" ht="15" thickBot="1">
@@ -11920,7 +11920,7 @@
         <v>856</v>
       </c>
       <c r="J180" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K180" s="49" t="s">
         <v>21</v>
@@ -11934,7 +11934,7 @@
         <v>77489256</v>
       </c>
       <c r="R180" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="181" spans="1:18" ht="15" thickBot="1">
@@ -11966,7 +11966,7 @@
         <v>856</v>
       </c>
       <c r="J181" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K181" s="49" t="s">
         <v>21</v>
@@ -11980,7 +11980,7 @@
         <v>76892940</v>
       </c>
       <c r="R181" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="182" spans="1:18" ht="15" thickBot="1">
@@ -12012,7 +12012,7 @@
         <v>856</v>
       </c>
       <c r="J182" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K182" s="49" t="s">
         <v>21</v>
@@ -12026,7 +12026,7 @@
         <v>971559767232</v>
       </c>
       <c r="R182" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="183" spans="1:18" ht="28.2" thickBot="1">
@@ -12056,7 +12056,7 @@
         <v>858</v>
       </c>
       <c r="J183" s="3" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="K183" s="49" t="s">
         <v>21</v>
@@ -12070,7 +12070,7 @@
         <v>95827351</v>
       </c>
       <c r="R183" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="184" spans="1:18" ht="28.2" thickBot="1">
@@ -12102,7 +12102,7 @@
         <v>858</v>
       </c>
       <c r="J184" s="3" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="K184" s="49" t="s">
         <v>21</v>
@@ -12114,7 +12114,7 @@
       <c r="P184" s="9"/>
       <c r="Q184" s="9"/>
       <c r="R184" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="185" spans="1:18" ht="28.2" thickBot="1">
@@ -12146,7 +12146,7 @@
         <v>858</v>
       </c>
       <c r="J185" s="3" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="K185" s="49" t="s">
         <v>21</v>
@@ -12160,7 +12160,7 @@
         <v>77659893</v>
       </c>
       <c r="R185" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="186" spans="1:18" ht="28.2" thickBot="1">
@@ -12192,7 +12192,7 @@
         <v>858</v>
       </c>
       <c r="J186" s="3" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="K186" s="49" t="s">
         <v>21</v>
@@ -12206,7 +12206,7 @@
         <v>971558394793</v>
       </c>
       <c r="R186" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="187" spans="1:18" ht="28.2" thickBot="1">
@@ -12238,7 +12238,7 @@
         <v>858</v>
       </c>
       <c r="J187" s="3" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="K187" s="49" t="s">
         <v>21</v>
@@ -12249,10 +12249,10 @@
       <c r="O187" s="9"/>
       <c r="P187" s="9"/>
       <c r="Q187" s="13" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="R187" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="188" spans="1:18" ht="28.2" thickBot="1">
@@ -12284,7 +12284,7 @@
         <v>858</v>
       </c>
       <c r="J188" s="3" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="K188" s="49" t="s">
         <v>21</v>
@@ -12298,7 +12298,7 @@
         <v>77124080</v>
       </c>
       <c r="R188" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="189" spans="1:18" ht="28.2" thickBot="1">
@@ -12330,7 +12330,7 @@
         <v>858</v>
       </c>
       <c r="J189" s="3" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="K189" s="49" t="s">
         <v>21</v>
@@ -12344,7 +12344,7 @@
         <v>93825952</v>
       </c>
       <c r="R189" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="190" spans="1:18" ht="28.2" thickBot="1">
@@ -12376,7 +12376,7 @@
         <v>858</v>
       </c>
       <c r="J190" s="3" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="K190" s="49" t="s">
         <v>21</v>
@@ -12388,7 +12388,7 @@
       <c r="P190" s="9"/>
       <c r="Q190" s="9"/>
       <c r="R190" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="191" spans="1:18" ht="28.2" thickBot="1">
@@ -12420,7 +12420,7 @@
         <v>858</v>
       </c>
       <c r="J191" s="3" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="K191" s="49" t="s">
         <v>21</v>
@@ -12434,7 +12434,7 @@
         <v>95832714</v>
       </c>
       <c r="R191" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="192" spans="1:18" ht="28.2" thickBot="1">
@@ -12508,7 +12508,7 @@
         <v>12</v>
       </c>
       <c r="J193" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K193" s="49" t="s">
         <v>21</v>
@@ -12554,7 +12554,7 @@
         <v>12</v>
       </c>
       <c r="J194" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K194" s="49" t="s">
         <v>21</v>
@@ -12600,7 +12600,7 @@
         <v>12</v>
       </c>
       <c r="J195" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K195" s="49" t="s">
         <v>21</v>
@@ -12646,7 +12646,7 @@
         <v>12</v>
       </c>
       <c r="J196" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K196" s="49" t="s">
         <v>21</v>
@@ -12692,7 +12692,7 @@
         <v>12</v>
       </c>
       <c r="J197" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K197" s="49" t="s">
         <v>21</v>
@@ -12736,7 +12736,7 @@
         <v>12</v>
       </c>
       <c r="J198" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K198" s="49" t="s">
         <v>21</v>
@@ -12782,7 +12782,7 @@
         <v>12</v>
       </c>
       <c r="J199" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K199" s="49" t="s">
         <v>21</v>
@@ -12793,7 +12793,7 @@
       <c r="O199" s="9"/>
       <c r="P199" s="9"/>
       <c r="Q199" s="13" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="R199" s="60" t="s">
         <v>25</v>
@@ -12828,7 +12828,7 @@
         <v>12</v>
       </c>
       <c r="J200" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K200" s="49" t="s">
         <v>21</v>
@@ -12874,7 +12874,7 @@
         <v>12</v>
       </c>
       <c r="J201" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K201" s="49" t="s">
         <v>21</v>
@@ -12920,7 +12920,7 @@
         <v>12</v>
       </c>
       <c r="J202" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K202" s="49" t="s">
         <v>21</v>
@@ -12966,7 +12966,7 @@
         <v>12</v>
       </c>
       <c r="J203" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K203" s="9"/>
       <c r="L203" s="9"/>
@@ -13010,7 +13010,7 @@
         <v>12</v>
       </c>
       <c r="J204" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K204" s="9"/>
       <c r="L204" s="9"/>
@@ -13054,7 +13054,7 @@
         <v>12</v>
       </c>
       <c r="J205" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K205" s="9"/>
       <c r="L205" s="9"/>
@@ -13098,7 +13098,7 @@
         <v>12</v>
       </c>
       <c r="J206" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K206" s="9"/>
       <c r="L206" s="9"/>
@@ -13142,7 +13142,7 @@
         <v>12</v>
       </c>
       <c r="J207" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K207" s="9"/>
       <c r="L207" s="9"/>
@@ -13186,7 +13186,7 @@
         <v>12</v>
       </c>
       <c r="J208" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K208" s="49" t="s">
         <v>21</v>
@@ -13232,7 +13232,7 @@
         <v>12</v>
       </c>
       <c r="J209" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K209" s="49" t="s">
         <v>21</v>
@@ -13278,7 +13278,7 @@
         <v>12</v>
       </c>
       <c r="J210" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K210" s="49" t="s">
         <v>21</v>
@@ -13324,7 +13324,7 @@
         <v>12</v>
       </c>
       <c r="J211" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K211" s="49" t="s">
         <v>21</v>
@@ -13370,7 +13370,7 @@
         <v>12</v>
       </c>
       <c r="J212" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K212" s="49" t="s">
         <v>21</v>
@@ -13417,7 +13417,7 @@
       </c>
       <c r="J213" s="9"/>
       <c r="K213" s="50" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L213" s="54">
         <v>46232</v>
@@ -13461,7 +13461,7 @@
       </c>
       <c r="J214" s="9"/>
       <c r="K214" s="20" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="L214" s="9"/>
       <c r="M214" s="9"/>
@@ -13503,7 +13503,7 @@
       </c>
       <c r="J215" s="9"/>
       <c r="K215" s="50" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L215" s="54">
         <v>46231</v>
@@ -13588,7 +13588,7 @@
         <v>858</v>
       </c>
       <c r="J217" s="14" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="K217" s="49" t="s">
         <v>21</v>
@@ -13634,7 +13634,7 @@
         <v>858</v>
       </c>
       <c r="J218" s="14" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="K218" s="49" t="s">
         <v>21</v>
@@ -13680,7 +13680,7 @@
         <v>12</v>
       </c>
       <c r="J219" s="14" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K219" s="49" t="s">
         <v>21</v>
@@ -13726,7 +13726,7 @@
         <v>12</v>
       </c>
       <c r="J220" s="14" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K220" s="49" t="s">
         <v>21</v>
@@ -13772,10 +13772,10 @@
         <v>858</v>
       </c>
       <c r="J221" s="14" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="K221" s="49" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="L221" s="9"/>
       <c r="M221" s="9"/>
@@ -13865,14 +13865,14 @@
         <v>28</v>
       </c>
       <c r="K223" s="20" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="L223" s="9"/>
       <c r="M223" s="9"/>
       <c r="N223" s="9"/>
       <c r="O223" s="9"/>
       <c r="P223" s="56" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="Q223" s="9"/>
       <c r="R223" s="61" t="s">
@@ -13916,7 +13916,7 @@
       <c r="N224" s="37"/>
       <c r="O224" s="37"/>
       <c r="P224" s="57" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="Q224" s="37"/>
       <c r="R224" s="63" t="s">
@@ -14042,7 +14042,7 @@
         <v>858</v>
       </c>
       <c r="J227" s="14" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="K227" s="49" t="s">
         <v>21</v>
@@ -14088,7 +14088,7 @@
         <v>12</v>
       </c>
       <c r="J228" s="14" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="K228" s="49" t="s">
         <v>21</v>
@@ -14134,7 +14134,7 @@
         <v>12</v>
       </c>
       <c r="J229" s="14" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="K229" s="49" t="s">
         <v>21</v>
@@ -14178,7 +14178,7 @@
         <v>12</v>
       </c>
       <c r="J230" s="14" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="K230" s="49" t="s">
         <v>21</v>
@@ -14220,7 +14220,7 @@
         <v>12</v>
       </c>
       <c r="J231" s="14" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="K231" s="49" t="s">
         <v>21</v>
@@ -14266,7 +14266,7 @@
         <v>12</v>
       </c>
       <c r="J232" s="14" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="K232" s="9"/>
       <c r="L232" s="9"/>
@@ -14308,10 +14308,10 @@
         <v>12</v>
       </c>
       <c r="J233" s="14" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="K233" s="50" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L233" s="54">
         <v>46232</v>
@@ -14354,7 +14354,7 @@
         <v>12</v>
       </c>
       <c r="J234" s="14" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="K234" s="9"/>
       <c r="L234" s="9"/>
@@ -14396,7 +14396,7 @@
         <v>12</v>
       </c>
       <c r="J235" s="14" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="K235" s="9"/>
       <c r="L235" s="9"/>
@@ -14438,7 +14438,7 @@
         <v>12</v>
       </c>
       <c r="J236" s="14" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="K236" s="9"/>
       <c r="L236" s="9"/>
@@ -14480,10 +14480,10 @@
         <v>12</v>
       </c>
       <c r="J237" s="14" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="K237" s="50" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L237" s="54">
         <v>46232</v>
@@ -14526,7 +14526,7 @@
         <v>12</v>
       </c>
       <c r="J238" s="14" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="K238" s="9"/>
       <c r="L238" s="9"/>
@@ -14570,7 +14570,7 @@
         <v>12</v>
       </c>
       <c r="J239" s="14" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="K239" s="9"/>
       <c r="L239" s="9"/>
@@ -14614,7 +14614,7 @@
         <v>12</v>
       </c>
       <c r="J240" s="14" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="K240" s="9"/>
       <c r="L240" s="9"/>
@@ -14658,7 +14658,7 @@
         <v>12</v>
       </c>
       <c r="J241" s="14" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="K241" s="9"/>
       <c r="L241" s="9"/>
@@ -14702,7 +14702,7 @@
         <v>12</v>
       </c>
       <c r="J242" s="14" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="K242" s="9"/>
       <c r="L242" s="9"/>
@@ -14746,7 +14746,7 @@
         <v>12</v>
       </c>
       <c r="J243" s="14" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="K243" s="9"/>
       <c r="L243" s="9"/>
@@ -14790,7 +14790,7 @@
         <v>12</v>
       </c>
       <c r="J244" s="14" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="K244" s="9"/>
       <c r="L244" s="9"/>
@@ -14834,7 +14834,7 @@
         <v>12</v>
       </c>
       <c r="J245" s="14" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="K245" s="9"/>
       <c r="L245" s="9"/>
@@ -14876,7 +14876,7 @@
         <v>12</v>
       </c>
       <c r="J246" s="14" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="K246" s="9"/>
       <c r="L246" s="9"/>
@@ -14920,7 +14920,7 @@
         <v>12</v>
       </c>
       <c r="J247" s="14" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="K247" s="9"/>
       <c r="L247" s="9"/>
@@ -14964,7 +14964,7 @@
         <v>12</v>
       </c>
       <c r="J248" s="14" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="K248" s="9"/>
       <c r="L248" s="9"/>
@@ -15008,7 +15008,7 @@
         <v>12</v>
       </c>
       <c r="J249" s="14" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="K249" s="9"/>
       <c r="L249" s="9"/>
@@ -15052,7 +15052,7 @@
         <v>12</v>
       </c>
       <c r="J250" s="14" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="K250" s="9"/>
       <c r="L250" s="9"/>
@@ -15094,7 +15094,7 @@
         <v>12</v>
       </c>
       <c r="J251" s="14" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="K251" s="9"/>
       <c r="L251" s="9"/>
@@ -15136,7 +15136,7 @@
         <v>858</v>
       </c>
       <c r="J252" s="14" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="K252" s="9"/>
       <c r="L252" s="9"/>
@@ -15180,7 +15180,7 @@
         <v>858</v>
       </c>
       <c r="J253" s="14" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="K253" s="9"/>
       <c r="L253" s="9"/>
@@ -15224,7 +15224,7 @@
         <v>12</v>
       </c>
       <c r="J254" s="14" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="K254" s="9"/>
       <c r="L254" s="9"/>
@@ -15354,7 +15354,7 @@
         <v>858</v>
       </c>
       <c r="J257" s="14" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="K257" s="9"/>
       <c r="L257" s="9"/>
@@ -15398,7 +15398,7 @@
         <v>858</v>
       </c>
       <c r="J258" s="14" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="K258" s="9"/>
       <c r="L258" s="9"/>
@@ -15440,7 +15440,7 @@
         <v>858</v>
       </c>
       <c r="J259" s="14" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="K259" s="9"/>
       <c r="L259" s="9"/>
@@ -15484,7 +15484,7 @@
         <v>858</v>
       </c>
       <c r="J260" s="14" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="K260" s="9"/>
       <c r="L260" s="9"/>
@@ -15528,7 +15528,7 @@
         <v>858</v>
       </c>
       <c r="J261" s="14" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="K261" s="9"/>
       <c r="L261" s="9"/>
@@ -15572,7 +15572,7 @@
         <v>858</v>
       </c>
       <c r="J262" s="14" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="K262" s="52"/>
       <c r="L262" s="52"/>
@@ -15614,7 +15614,7 @@
         <v>858</v>
       </c>
       <c r="J263" s="14" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="K263" s="52"/>
       <c r="L263" s="52"/>
@@ -15658,7 +15658,7 @@
         <v>858</v>
       </c>
       <c r="J264" s="14" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="K264" s="52"/>
       <c r="L264" s="52"/>
@@ -15702,7 +15702,7 @@
         <v>12</v>
       </c>
       <c r="J265" s="14" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="K265" s="9"/>
       <c r="L265" s="9"/>
@@ -15744,7 +15744,7 @@
         <v>12</v>
       </c>
       <c r="J266" s="14" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="K266" s="9"/>
       <c r="L266" s="9"/>
@@ -15788,7 +15788,7 @@
         <v>12</v>
       </c>
       <c r="J267" s="14" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="K267" s="9"/>
       <c r="L267" s="9"/>
@@ -15874,7 +15874,7 @@
         <v>12</v>
       </c>
       <c r="J269" s="14" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="K269" s="52"/>
       <c r="L269" s="52"/>
@@ -15916,7 +15916,7 @@
         <v>12</v>
       </c>
       <c r="J270" s="14" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="K270" s="9"/>
       <c r="L270" s="9"/>
@@ -15958,7 +15958,7 @@
         <v>12</v>
       </c>
       <c r="J271" s="14" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="K271" s="9"/>
       <c r="L271" s="9"/>
@@ -16000,7 +16000,7 @@
         <v>12</v>
       </c>
       <c r="J272" s="14" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="K272" s="9"/>
       <c r="L272" s="9"/>
@@ -16042,7 +16042,7 @@
         <v>12</v>
       </c>
       <c r="J273" s="14" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="K273" s="9"/>
       <c r="L273" s="9"/>
@@ -16086,7 +16086,7 @@
         <v>12</v>
       </c>
       <c r="J274" s="14" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="K274" s="9"/>
       <c r="L274" s="9"/>
@@ -16128,7 +16128,7 @@
         <v>12</v>
       </c>
       <c r="J275" s="14" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="K275" s="9"/>
       <c r="L275" s="9"/>
@@ -16170,7 +16170,7 @@
         <v>12</v>
       </c>
       <c r="J276" s="14" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="K276" s="9"/>
       <c r="L276" s="9"/>
@@ -16212,7 +16212,7 @@
         <v>12</v>
       </c>
       <c r="J277" s="14" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="K277" s="9"/>
       <c r="L277" s="9"/>
@@ -16254,7 +16254,7 @@
         <v>12</v>
       </c>
       <c r="J278" s="14" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="K278" s="9"/>
       <c r="L278" s="9"/>
@@ -16296,7 +16296,7 @@
         <v>12</v>
       </c>
       <c r="J279" s="14" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="K279" s="9"/>
       <c r="L279" s="9"/>
@@ -16340,7 +16340,7 @@
         <v>12</v>
       </c>
       <c r="J280" s="14" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="K280" s="9"/>
       <c r="L280" s="9"/>
@@ -16382,7 +16382,7 @@
         <v>12</v>
       </c>
       <c r="J281" s="14" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="K281" s="9"/>
       <c r="L281" s="9"/>
@@ -16426,7 +16426,7 @@
         <v>12</v>
       </c>
       <c r="J282" s="14" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="K282" s="9"/>
       <c r="L282" s="9"/>
@@ -16470,7 +16470,7 @@
         <v>12</v>
       </c>
       <c r="J283" s="14" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="K283" s="9"/>
       <c r="L283" s="9"/>
@@ -16512,7 +16512,7 @@
         <v>12</v>
       </c>
       <c r="J284" s="14" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="K284" s="9"/>
       <c r="L284" s="9"/>
@@ -16556,7 +16556,7 @@
         <v>12</v>
       </c>
       <c r="J285" s="14" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="K285" s="9"/>
       <c r="L285" s="9"/>
@@ -16600,7 +16600,7 @@
         <v>12</v>
       </c>
       <c r="J286" s="14" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="K286" s="9"/>
       <c r="L286" s="9"/>
@@ -16644,7 +16644,7 @@
         <v>12</v>
       </c>
       <c r="J287" s="14" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="K287" s="9"/>
       <c r="L287" s="9"/>
@@ -16688,7 +16688,7 @@
         <v>12</v>
       </c>
       <c r="J288" s="14" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="K288" s="9"/>
       <c r="L288" s="9"/>
@@ -16732,7 +16732,7 @@
         <v>12</v>
       </c>
       <c r="J289" s="14" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="K289" s="9"/>
       <c r="L289" s="9"/>
@@ -16774,7 +16774,7 @@
         <v>12</v>
       </c>
       <c r="J290" s="14" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="K290" s="9"/>
       <c r="L290" s="9"/>
@@ -16816,7 +16816,7 @@
         <v>858</v>
       </c>
       <c r="J291" s="14" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="K291" s="9"/>
       <c r="L291" s="9"/>
@@ -16860,7 +16860,7 @@
         <v>858</v>
       </c>
       <c r="J292" s="14" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="K292" s="9"/>
       <c r="L292" s="9"/>
@@ -16902,7 +16902,7 @@
         <v>12</v>
       </c>
       <c r="J293" s="14" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="K293" s="9"/>
       <c r="L293" s="9"/>
@@ -16946,7 +16946,7 @@
         <v>12</v>
       </c>
       <c r="J294" s="14" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="K294" s="9"/>
       <c r="L294" s="9"/>
@@ -16990,7 +16990,7 @@
         <v>12</v>
       </c>
       <c r="J295" s="14" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="K295" s="9"/>
       <c r="L295" s="9"/>
@@ -17120,10 +17120,10 @@
         <v>12</v>
       </c>
       <c r="J298" s="14" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="K298" s="50" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L298" s="54">
         <v>46234</v>
@@ -17166,7 +17166,7 @@
         <v>12</v>
       </c>
       <c r="J299" s="14" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="K299" s="9"/>
       <c r="L299" s="9"/>
@@ -17210,7 +17210,7 @@
         <v>12</v>
       </c>
       <c r="J300" s="14" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="K300" s="9"/>
       <c r="L300" s="9"/>
@@ -17254,7 +17254,7 @@
         <v>12</v>
       </c>
       <c r="J301" s="14" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="K301" s="9"/>
       <c r="L301" s="9"/>
@@ -17263,7 +17263,7 @@
       <c r="O301" s="9"/>
       <c r="P301" s="9"/>
       <c r="Q301" s="13" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="R301" s="61" t="s">
         <v>13</v>
@@ -17298,10 +17298,10 @@
         <v>12</v>
       </c>
       <c r="J302" s="14" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="K302" s="50" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L302" s="54">
         <v>46232</v>
@@ -17346,7 +17346,7 @@
         <v>858</v>
       </c>
       <c r="J303" s="14" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="K303" s="9"/>
       <c r="L303" s="9"/>
@@ -17388,7 +17388,7 @@
         <v>12</v>
       </c>
       <c r="J304" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K304" s="49" t="s">
         <v>21</v>
@@ -17400,7 +17400,7 @@
       <c r="P304" s="9"/>
       <c r="Q304" s="9"/>
       <c r="R304" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="305" spans="1:18" ht="15" thickBot="1">
@@ -17432,7 +17432,7 @@
         <v>12</v>
       </c>
       <c r="J305" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K305" s="49" t="s">
         <v>21</v>
@@ -17444,7 +17444,7 @@
       <c r="P305" s="9"/>
       <c r="Q305" s="9"/>
       <c r="R305" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="306" spans="1:18" ht="15" thickBot="1">
@@ -17476,7 +17476,7 @@
         <v>12</v>
       </c>
       <c r="J306" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K306" s="49" t="s">
         <v>21</v>
@@ -17488,7 +17488,7 @@
       <c r="P306" s="9"/>
       <c r="Q306" s="9"/>
       <c r="R306" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="307" spans="1:18" ht="15" thickBot="1">
@@ -17520,7 +17520,7 @@
         <v>12</v>
       </c>
       <c r="J307" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K307" s="49" t="s">
         <v>21</v>
@@ -17532,7 +17532,7 @@
       <c r="P307" s="9"/>
       <c r="Q307" s="9"/>
       <c r="R307" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="308" spans="1:18" ht="15" thickBot="1">
@@ -17564,7 +17564,7 @@
         <v>12</v>
       </c>
       <c r="J308" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K308" s="49" t="s">
         <v>21</v>
@@ -17576,7 +17576,7 @@
       <c r="P308" s="9"/>
       <c r="Q308" s="9"/>
       <c r="R308" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="309" spans="1:18" ht="15" thickBot="1">
@@ -17608,7 +17608,7 @@
         <v>12</v>
       </c>
       <c r="J309" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K309" s="49" t="s">
         <v>21</v>
@@ -17620,7 +17620,7 @@
       <c r="P309" s="9"/>
       <c r="Q309" s="9"/>
       <c r="R309" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="310" spans="1:18" ht="15" thickBot="1">
@@ -17652,7 +17652,7 @@
         <v>12</v>
       </c>
       <c r="J310" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K310" s="49" t="s">
         <v>21</v>
@@ -17664,7 +17664,7 @@
       <c r="P310" s="9"/>
       <c r="Q310" s="9"/>
       <c r="R310" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="311" spans="1:18" ht="15" thickBot="1">
@@ -17696,7 +17696,7 @@
         <v>12</v>
       </c>
       <c r="J311" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K311" s="49" t="s">
         <v>21</v>
@@ -17708,7 +17708,7 @@
       <c r="P311" s="9"/>
       <c r="Q311" s="9"/>
       <c r="R311" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="312" spans="1:18" ht="15" thickBot="1">
@@ -17740,7 +17740,7 @@
         <v>12</v>
       </c>
       <c r="J312" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K312" s="49" t="s">
         <v>21</v>
@@ -17752,7 +17752,7 @@
       <c r="P312" s="9"/>
       <c r="Q312" s="9"/>
       <c r="R312" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="313" spans="1:18" ht="15" thickBot="1">
@@ -17784,7 +17784,7 @@
         <v>12</v>
       </c>
       <c r="J313" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K313" s="49" t="s">
         <v>21</v>
@@ -17796,7 +17796,7 @@
       <c r="P313" s="9"/>
       <c r="Q313" s="9"/>
       <c r="R313" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="314" spans="1:18" ht="15" thickBot="1">
@@ -17828,7 +17828,7 @@
         <v>12</v>
       </c>
       <c r="J314" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K314" s="49" t="s">
         <v>21</v>
@@ -17840,7 +17840,7 @@
       <c r="P314" s="9"/>
       <c r="Q314" s="9"/>
       <c r="R314" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="315" spans="1:18" ht="15" thickBot="1">
@@ -17872,7 +17872,7 @@
         <v>12</v>
       </c>
       <c r="J315" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K315" s="49" t="s">
         <v>21</v>
@@ -17884,7 +17884,7 @@
       <c r="P315" s="9"/>
       <c r="Q315" s="9"/>
       <c r="R315" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="316" spans="1:18" ht="15" thickBot="1">
@@ -17916,7 +17916,7 @@
         <v>12</v>
       </c>
       <c r="J316" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K316" s="49" t="s">
         <v>21</v>
@@ -17928,7 +17928,7 @@
       <c r="P316" s="9"/>
       <c r="Q316" s="9"/>
       <c r="R316" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="317" spans="1:18" ht="15" thickBot="1">
@@ -17960,10 +17960,10 @@
         <v>12</v>
       </c>
       <c r="J317" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K317" s="49" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="L317" s="9"/>
       <c r="M317" s="9"/>
@@ -17972,7 +17972,7 @@
       <c r="P317" s="9"/>
       <c r="Q317" s="9"/>
       <c r="R317" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="318" spans="1:18" ht="15" thickBot="1">
@@ -18004,10 +18004,10 @@
         <v>12</v>
       </c>
       <c r="J318" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K318" s="49" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="L318" s="9"/>
       <c r="M318" s="9"/>
@@ -18016,7 +18016,7 @@
       <c r="P318" s="9"/>
       <c r="Q318" s="9"/>
       <c r="R318" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="319" spans="1:18" ht="15" thickBot="1">
@@ -18046,10 +18046,10 @@
         <v>12</v>
       </c>
       <c r="J319" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K319" s="49" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="L319" s="64">
         <v>46235</v>
@@ -18060,7 +18060,7 @@
       <c r="P319" s="9"/>
       <c r="Q319" s="9"/>
       <c r="R319" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="320" spans="1:18" ht="15" thickBot="1">
@@ -18092,7 +18092,7 @@
         <v>12</v>
       </c>
       <c r="J320" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K320" s="49" t="s">
         <v>21</v>
@@ -18104,7 +18104,7 @@
       <c r="P320" s="9"/>
       <c r="Q320" s="9"/>
       <c r="R320" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="321" spans="1:18" ht="15" thickBot="1">
@@ -18136,7 +18136,7 @@
         <v>12</v>
       </c>
       <c r="J321" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K321" s="49" t="s">
         <v>21</v>
@@ -18148,7 +18148,7 @@
       <c r="P321" s="9"/>
       <c r="Q321" s="9"/>
       <c r="R321" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="322" spans="1:18" ht="15" thickBot="1">
@@ -18180,7 +18180,7 @@
         <v>12</v>
       </c>
       <c r="J322" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K322" s="49" t="s">
         <v>21</v>
@@ -18194,7 +18194,7 @@
       <c r="P322" s="9"/>
       <c r="Q322" s="9"/>
       <c r="R322" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="323" spans="1:18" ht="15" thickBot="1">
@@ -18226,7 +18226,7 @@
         <v>12</v>
       </c>
       <c r="J323" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K323" s="49" t="s">
         <v>21</v>
@@ -18238,7 +18238,7 @@
       <c r="P323" s="9"/>
       <c r="Q323" s="9"/>
       <c r="R323" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="324" spans="1:18" ht="15" thickBot="1">
@@ -18270,7 +18270,7 @@
         <v>12</v>
       </c>
       <c r="J324" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K324" s="49" t="s">
         <v>21</v>
@@ -18282,7 +18282,7 @@
       <c r="P324" s="9"/>
       <c r="Q324" s="9"/>
       <c r="R324" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="325" spans="1:18" ht="15" thickBot="1">
@@ -18314,7 +18314,7 @@
         <v>12</v>
       </c>
       <c r="J325" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K325" s="49" t="s">
         <v>21</v>
@@ -18326,7 +18326,7 @@
       <c r="P325" s="9"/>
       <c r="Q325" s="9"/>
       <c r="R325" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="326" spans="1:18" ht="15" thickBot="1">
@@ -18358,7 +18358,7 @@
         <v>12</v>
       </c>
       <c r="J326" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K326" s="49" t="s">
         <v>21</v>
@@ -18370,7 +18370,7 @@
       <c r="P326" s="9"/>
       <c r="Q326" s="9"/>
       <c r="R326" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="327" spans="1:18" ht="15" thickBot="1">
@@ -18402,7 +18402,7 @@
         <v>12</v>
       </c>
       <c r="J327" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K327" s="49" t="s">
         <v>21</v>
@@ -18414,7 +18414,7 @@
       <c r="P327" s="9"/>
       <c r="Q327" s="9"/>
       <c r="R327" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="328" spans="1:18" ht="15" thickBot="1">
@@ -18446,7 +18446,7 @@
         <v>12</v>
       </c>
       <c r="J328" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K328" s="49" t="s">
         <v>21</v>
@@ -18458,7 +18458,7 @@
       <c r="P328" s="9"/>
       <c r="Q328" s="9"/>
       <c r="R328" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="329" spans="1:18" ht="15" thickBot="1">
@@ -18490,7 +18490,7 @@
         <v>12</v>
       </c>
       <c r="J329" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K329" s="49" t="s">
         <v>21</v>
@@ -18502,7 +18502,7 @@
       <c r="P329" s="9"/>
       <c r="Q329" s="9"/>
       <c r="R329" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="330" spans="1:18" ht="15" thickBot="1">
@@ -18534,7 +18534,7 @@
         <v>12</v>
       </c>
       <c r="J330" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K330" s="49" t="s">
         <v>21</v>
@@ -18548,7 +18548,7 @@
       <c r="P330" s="9"/>
       <c r="Q330" s="9"/>
       <c r="R330" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="331" spans="1:18" ht="15" thickBot="1">
@@ -18580,7 +18580,7 @@
         <v>12</v>
       </c>
       <c r="J331" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K331" s="49" t="s">
         <v>21</v>
@@ -18592,7 +18592,7 @@
       <c r="P331" s="9"/>
       <c r="Q331" s="9"/>
       <c r="R331" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="332" spans="1:18" ht="15" thickBot="1">
@@ -18624,7 +18624,7 @@
         <v>12</v>
       </c>
       <c r="J332" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K332" s="49" t="s">
         <v>21</v>
@@ -18636,7 +18636,7 @@
       <c r="P332" s="9"/>
       <c r="Q332" s="9"/>
       <c r="R332" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="333" spans="1:18" ht="15" thickBot="1">
@@ -18668,7 +18668,7 @@
         <v>12</v>
       </c>
       <c r="J333" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K333" s="49" t="s">
         <v>21</v>
@@ -18680,7 +18680,7 @@
       <c r="P333" s="9"/>
       <c r="Q333" s="9"/>
       <c r="R333" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="334" spans="1:18" ht="15" thickBot="1">
@@ -18712,7 +18712,7 @@
         <v>12</v>
       </c>
       <c r="J334" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K334" s="49" t="s">
         <v>21</v>
@@ -18724,7 +18724,7 @@
       <c r="P334" s="9"/>
       <c r="Q334" s="9"/>
       <c r="R334" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="335" spans="1:18" ht="15" thickBot="1">
@@ -18756,7 +18756,7 @@
         <v>12</v>
       </c>
       <c r="J335" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K335" s="49" t="s">
         <v>21</v>
@@ -18768,7 +18768,7 @@
       <c r="P335" s="9"/>
       <c r="Q335" s="9"/>
       <c r="R335" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="336" spans="1:18" ht="15" thickBot="1">
@@ -18800,7 +18800,7 @@
         <v>12</v>
       </c>
       <c r="J336" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K336" s="49" t="s">
         <v>21</v>
@@ -18812,7 +18812,7 @@
       <c r="P336" s="9"/>
       <c r="Q336" s="9"/>
       <c r="R336" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="337" spans="1:18" ht="15" thickBot="1">
@@ -18844,7 +18844,7 @@
         <v>12</v>
       </c>
       <c r="J337" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K337" s="49" t="s">
         <v>21</v>
@@ -18856,7 +18856,7 @@
       <c r="P337" s="9"/>
       <c r="Q337" s="9"/>
       <c r="R337" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="338" spans="1:18" ht="15" thickBot="1">
@@ -18888,7 +18888,7 @@
         <v>12</v>
       </c>
       <c r="J338" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K338" s="49" t="s">
         <v>21</v>
@@ -18900,7 +18900,7 @@
       <c r="P338" s="9"/>
       <c r="Q338" s="9"/>
       <c r="R338" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="339" spans="1:18" ht="15" thickBot="1">
@@ -18932,7 +18932,7 @@
         <v>12</v>
       </c>
       <c r="J339" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K339" s="49" t="s">
         <v>21</v>
@@ -18944,7 +18944,7 @@
       <c r="P339" s="9"/>
       <c r="Q339" s="9"/>
       <c r="R339" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="340" spans="1:18" ht="15" thickBot="1">
@@ -18976,7 +18976,7 @@
         <v>12</v>
       </c>
       <c r="J340" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K340" s="49" t="s">
         <v>21</v>
@@ -18988,7 +18988,7 @@
       <c r="P340" s="9"/>
       <c r="Q340" s="9"/>
       <c r="R340" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="341" spans="1:18" ht="15" thickBot="1">
@@ -19020,7 +19020,7 @@
         <v>12</v>
       </c>
       <c r="J341" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K341" s="49" t="s">
         <v>21</v>
@@ -19032,7 +19032,7 @@
       <c r="P341" s="9"/>
       <c r="Q341" s="9"/>
       <c r="R341" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="342" spans="1:18" ht="15" thickBot="1">
@@ -19064,7 +19064,7 @@
         <v>12</v>
       </c>
       <c r="J342" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K342" s="49" t="s">
         <v>21</v>
@@ -19076,7 +19076,7 @@
       <c r="P342" s="9"/>
       <c r="Q342" s="9"/>
       <c r="R342" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="343" spans="1:18" ht="15" thickBot="1">
@@ -19108,7 +19108,7 @@
         <v>12</v>
       </c>
       <c r="J343" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K343" s="49" t="s">
         <v>21</v>
@@ -19120,7 +19120,7 @@
       <c r="P343" s="9"/>
       <c r="Q343" s="9"/>
       <c r="R343" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="344" spans="1:18" ht="15" thickBot="1">
@@ -19152,7 +19152,7 @@
         <v>12</v>
       </c>
       <c r="J344" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K344" s="49" t="s">
         <v>21</v>
@@ -19164,7 +19164,7 @@
       <c r="P344" s="9"/>
       <c r="Q344" s="9"/>
       <c r="R344" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="345" spans="1:18" ht="15" thickBot="1">
@@ -19196,7 +19196,7 @@
         <v>12</v>
       </c>
       <c r="J345" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K345" s="49" t="s">
         <v>21</v>
@@ -19208,7 +19208,7 @@
       <c r="P345" s="9"/>
       <c r="Q345" s="9"/>
       <c r="R345" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="346" spans="1:18" ht="15" thickBot="1">
@@ -19240,7 +19240,7 @@
         <v>12</v>
       </c>
       <c r="J346" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K346" s="49" t="s">
         <v>21</v>
@@ -19252,7 +19252,7 @@
       <c r="P346" s="9"/>
       <c r="Q346" s="9"/>
       <c r="R346" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="347" spans="1:18" ht="15" thickBot="1">
@@ -19284,7 +19284,7 @@
         <v>12</v>
       </c>
       <c r="J347" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K347" s="49" t="s">
         <v>21</v>
@@ -19296,7 +19296,7 @@
       <c r="P347" s="9"/>
       <c r="Q347" s="9"/>
       <c r="R347" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="348" spans="1:18" ht="15" thickBot="1">
@@ -19328,7 +19328,7 @@
         <v>12</v>
       </c>
       <c r="J348" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K348" s="49" t="s">
         <v>21</v>
@@ -19340,7 +19340,7 @@
       <c r="P348" s="9"/>
       <c r="Q348" s="9"/>
       <c r="R348" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="349" spans="1:18" ht="15" thickBot="1">
@@ -19372,7 +19372,7 @@
         <v>12</v>
       </c>
       <c r="J349" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K349" s="49" t="s">
         <v>21</v>
@@ -19384,7 +19384,7 @@
       <c r="P349" s="9"/>
       <c r="Q349" s="9"/>
       <c r="R349" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="350" spans="1:18" ht="15" thickBot="1">
@@ -19416,7 +19416,7 @@
         <v>12</v>
       </c>
       <c r="J350" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K350" s="49" t="s">
         <v>21</v>
@@ -19428,7 +19428,7 @@
       <c r="P350" s="9"/>
       <c r="Q350" s="9"/>
       <c r="R350" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="351" spans="1:18" ht="15" thickBot="1">
@@ -19460,7 +19460,7 @@
         <v>12</v>
       </c>
       <c r="J351" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K351" s="49" t="s">
         <v>21</v>
@@ -19472,7 +19472,7 @@
       <c r="P351" s="9"/>
       <c r="Q351" s="9"/>
       <c r="R351" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="352" spans="1:18" ht="15" thickBot="1">
@@ -19504,7 +19504,7 @@
         <v>12</v>
       </c>
       <c r="J352" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K352" s="49" t="s">
         <v>21</v>
@@ -19516,7 +19516,7 @@
       <c r="P352" s="9"/>
       <c r="Q352" s="9"/>
       <c r="R352" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="353" spans="1:18" ht="15" thickBot="1">
@@ -19548,7 +19548,7 @@
         <v>12</v>
       </c>
       <c r="J353" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K353" s="49" t="s">
         <v>21</v>
@@ -19560,7 +19560,7 @@
       <c r="P353" s="9"/>
       <c r="Q353" s="9"/>
       <c r="R353" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="354" spans="1:18" ht="15" thickBot="1">
@@ -19592,7 +19592,7 @@
         <v>12</v>
       </c>
       <c r="J354" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K354" s="49" t="s">
         <v>21</v>
@@ -19604,7 +19604,7 @@
       <c r="P354" s="9"/>
       <c r="Q354" s="9"/>
       <c r="R354" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="355" spans="1:18" ht="15" thickBot="1">
@@ -19636,7 +19636,7 @@
         <v>12</v>
       </c>
       <c r="J355" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K355" s="49" t="s">
         <v>21</v>
@@ -19648,7 +19648,7 @@
       <c r="P355" s="9"/>
       <c r="Q355" s="9"/>
       <c r="R355" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="356" spans="1:18" ht="15" thickBot="1">
@@ -19680,7 +19680,7 @@
         <v>12</v>
       </c>
       <c r="J356" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K356" s="49" t="s">
         <v>21</v>
@@ -19692,7 +19692,7 @@
       <c r="P356" s="9"/>
       <c r="Q356" s="9"/>
       <c r="R356" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="357" spans="1:18" ht="15" thickBot="1">
@@ -19724,7 +19724,7 @@
         <v>12</v>
       </c>
       <c r="J357" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K357" s="49" t="s">
         <v>21</v>
@@ -19736,7 +19736,7 @@
       <c r="P357" s="9"/>
       <c r="Q357" s="9"/>
       <c r="R357" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="358" spans="1:18" ht="15" thickBot="1">
@@ -19768,7 +19768,7 @@
         <v>12</v>
       </c>
       <c r="J358" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K358" s="49" t="s">
         <v>21</v>
@@ -19780,7 +19780,7 @@
       <c r="P358" s="9"/>
       <c r="Q358" s="9"/>
       <c r="R358" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="359" spans="1:18" ht="15" thickBot="1">
@@ -19812,7 +19812,7 @@
         <v>12</v>
       </c>
       <c r="J359" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K359" s="49" t="s">
         <v>21</v>
@@ -19824,7 +19824,7 @@
       <c r="P359" s="9"/>
       <c r="Q359" s="9"/>
       <c r="R359" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="360" spans="1:18" ht="15" thickBot="1">
@@ -19856,7 +19856,7 @@
         <v>12</v>
       </c>
       <c r="J360" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K360" s="49" t="s">
         <v>21</v>
@@ -19868,7 +19868,7 @@
       <c r="P360" s="9"/>
       <c r="Q360" s="9"/>
       <c r="R360" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="361" spans="1:18" ht="23.4" thickBot="1">
@@ -19900,7 +19900,7 @@
         <v>12</v>
       </c>
       <c r="J361" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K361" s="49" t="s">
         <v>21</v>
@@ -19912,7 +19912,7 @@
       <c r="P361" s="9"/>
       <c r="Q361" s="9"/>
       <c r="R361" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="362" spans="1:18" ht="15" thickBot="1">
@@ -19944,7 +19944,7 @@
         <v>12</v>
       </c>
       <c r="J362" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K362" s="49" t="s">
         <v>21</v>
@@ -19956,7 +19956,7 @@
       <c r="P362" s="9"/>
       <c r="Q362" s="9"/>
       <c r="R362" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="363" spans="1:18" ht="23.4" thickBot="1">
@@ -19988,7 +19988,7 @@
         <v>12</v>
       </c>
       <c r="J363" s="48" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K363" s="49" t="s">
         <v>21</v>
@@ -20000,7 +20000,7 @@
       <c r="P363" s="9"/>
       <c r="Q363" s="9"/>
       <c r="R363" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="364" spans="1:18" ht="15" thickBot="1">
@@ -20032,7 +20032,7 @@
         <v>12</v>
       </c>
       <c r="J364" s="14" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="K364" s="49" t="s">
         <v>21</v>
@@ -20078,7 +20078,7 @@
         <v>12</v>
       </c>
       <c r="J365" s="14" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="K365" s="49" t="s">
         <v>21</v>
@@ -20124,7 +20124,7 @@
         <v>12</v>
       </c>
       <c r="J366" s="14" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="K366" s="49" t="s">
         <v>21</v>
@@ -20170,7 +20170,7 @@
         <v>12</v>
       </c>
       <c r="J367" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K367" s="49" t="s">
         <v>21</v>
@@ -20214,7 +20214,7 @@
         <v>858</v>
       </c>
       <c r="J368" s="3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="K368" s="9"/>
       <c r="L368" s="9"/>
@@ -20226,7 +20226,7 @@
         <v>94319762</v>
       </c>
       <c r="R368" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="369" spans="1:18" ht="28.2" thickBot="1">
@@ -20258,7 +20258,7 @@
         <v>858</v>
       </c>
       <c r="J369" s="3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="K369" s="9"/>
       <c r="L369" s="9"/>
@@ -20270,7 +20270,7 @@
         <v>94232210</v>
       </c>
       <c r="R369" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="370" spans="1:18" ht="28.2" thickBot="1">
@@ -20302,7 +20302,7 @@
         <v>858</v>
       </c>
       <c r="J370" s="3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="K370" s="9"/>
       <c r="L370" s="9"/>
@@ -20314,7 +20314,7 @@
         <v>94081942</v>
       </c>
       <c r="R370" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="371" spans="1:18" ht="28.2" thickBot="1">
@@ -20346,7 +20346,7 @@
         <v>858</v>
       </c>
       <c r="J371" s="3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="K371" s="9"/>
       <c r="L371" s="9"/>
@@ -20358,7 +20358,7 @@
         <v>97076719</v>
       </c>
       <c r="R371" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="372" spans="1:18" ht="28.2" thickBot="1">
@@ -20390,7 +20390,7 @@
         <v>858</v>
       </c>
       <c r="J372" s="3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="K372" s="9"/>
       <c r="L372" s="9"/>
@@ -20402,7 +20402,7 @@
         <v>96034267</v>
       </c>
       <c r="R372" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="373" spans="1:18" ht="28.2" thickBot="1">
@@ -20434,7 +20434,7 @@
         <v>858</v>
       </c>
       <c r="J373" s="3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="K373" s="9"/>
       <c r="L373" s="9"/>
@@ -20446,7 +20446,7 @@
         <v>501168949</v>
       </c>
       <c r="R373" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="374" spans="1:18" ht="28.2" thickBot="1">
@@ -20476,7 +20476,7 @@
         <v>858</v>
       </c>
       <c r="J374" s="3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="K374" s="9"/>
       <c r="L374" s="9"/>
@@ -20488,7 +20488,7 @@
         <v>96895764851</v>
       </c>
       <c r="R374" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="375" spans="1:18" ht="15" thickBot="1">
@@ -20520,7 +20520,7 @@
         <v>856</v>
       </c>
       <c r="J375" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K375" s="9"/>
       <c r="L375" s="9"/>
@@ -20532,7 +20532,7 @@
         <v>94572081</v>
       </c>
       <c r="R375" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="376" spans="1:18" ht="15" thickBot="1">
@@ -20564,7 +20564,7 @@
         <v>856</v>
       </c>
       <c r="J376" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K376" s="9"/>
       <c r="L376" s="9"/>
@@ -20576,7 +20576,7 @@
         <v>94572081</v>
       </c>
       <c r="R376" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="377" spans="1:18" ht="15" thickBot="1">
@@ -20608,7 +20608,7 @@
         <v>856</v>
       </c>
       <c r="J377" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K377" s="9"/>
       <c r="L377" s="9"/>
@@ -20620,7 +20620,7 @@
         <v>76802749</v>
       </c>
       <c r="R377" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="378" spans="1:18" ht="15" thickBot="1">
@@ -20652,7 +20652,7 @@
         <v>856</v>
       </c>
       <c r="J378" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K378" s="9"/>
       <c r="L378" s="9"/>
@@ -20664,7 +20664,7 @@
         <v>96895644081</v>
       </c>
       <c r="R378" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="379" spans="1:18" ht="15" thickBot="1">
@@ -20696,7 +20696,7 @@
         <v>856</v>
       </c>
       <c r="J379" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K379" s="9"/>
       <c r="L379" s="9"/>
@@ -20708,7 +20708,7 @@
         <v>96894464618</v>
       </c>
       <c r="R379" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="380" spans="1:18" ht="15" thickBot="1">
@@ -20740,7 +20740,7 @@
         <v>856</v>
       </c>
       <c r="J380" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K380" s="9"/>
       <c r="L380" s="9"/>
@@ -20752,7 +20752,7 @@
         <v>79103588</v>
       </c>
       <c r="R380" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="381" spans="1:18" ht="15" thickBot="1">
@@ -20784,7 +20784,7 @@
         <v>856</v>
       </c>
       <c r="J381" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K381" s="9"/>
       <c r="L381" s="9"/>
@@ -20796,7 +20796,7 @@
         <v>94907844</v>
       </c>
       <c r="R381" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="382" spans="1:18" ht="15" thickBot="1">
@@ -20828,7 +20828,7 @@
         <v>856</v>
       </c>
       <c r="J382" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K382" s="9"/>
       <c r="L382" s="9"/>
@@ -20840,7 +20840,7 @@
         <v>97007985</v>
       </c>
       <c r="R382" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="383" spans="1:18" ht="15" thickBot="1">
@@ -20872,7 +20872,7 @@
         <v>856</v>
       </c>
       <c r="J383" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K383" s="9"/>
       <c r="L383" s="9"/>
@@ -20884,7 +20884,7 @@
         <v>98363420</v>
       </c>
       <c r="R383" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="384" spans="1:18" ht="15" thickBot="1">
@@ -20916,7 +20916,7 @@
         <v>856</v>
       </c>
       <c r="J384" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K384" s="9"/>
       <c r="L384" s="9"/>
@@ -20928,7 +20928,7 @@
         <v>67602067</v>
       </c>
       <c r="R384" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="385" spans="1:18" ht="15" thickBot="1">
@@ -20960,7 +20960,7 @@
         <v>856</v>
       </c>
       <c r="J385" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K385" s="9"/>
       <c r="L385" s="9"/>
@@ -20972,7 +20972,7 @@
         <v>94978894</v>
       </c>
       <c r="R385" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="386" spans="1:18" ht="15" thickBot="1">
@@ -21004,7 +21004,7 @@
         <v>856</v>
       </c>
       <c r="J386" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K386" s="9"/>
       <c r="L386" s="9"/>
@@ -21016,7 +21016,7 @@
         <v>92902600</v>
       </c>
       <c r="R386" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="387" spans="1:18" ht="15" thickBot="1">
@@ -21048,7 +21048,7 @@
         <v>856</v>
       </c>
       <c r="J387" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K387" s="9"/>
       <c r="L387" s="9"/>
@@ -21060,7 +21060,7 @@
         <v>79164015</v>
       </c>
       <c r="R387" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="388" spans="1:18" ht="15" thickBot="1">
@@ -21092,7 +21092,7 @@
         <v>856</v>
       </c>
       <c r="J388" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K388" s="9"/>
       <c r="L388" s="9"/>
@@ -21104,7 +21104,7 @@
         <v>96954720</v>
       </c>
       <c r="R388" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="389" spans="1:18" ht="15" thickBot="1">
@@ -21136,7 +21136,7 @@
         <v>856</v>
       </c>
       <c r="J389" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K389" s="9"/>
       <c r="L389" s="9"/>
@@ -21148,7 +21148,7 @@
         <v>94245786</v>
       </c>
       <c r="R389" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="390" spans="1:18" ht="15" thickBot="1">
@@ -21180,7 +21180,7 @@
         <v>856</v>
       </c>
       <c r="J390" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K390" s="9"/>
       <c r="L390" s="9"/>
@@ -21192,7 +21192,7 @@
         <v>76643273</v>
       </c>
       <c r="R390" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="391" spans="1:18" ht="15" thickBot="1">
@@ -21222,7 +21222,7 @@
         <v>856</v>
       </c>
       <c r="J391" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K391" s="9"/>
       <c r="L391" s="9"/>
@@ -21232,7 +21232,7 @@
       <c r="P391" s="9"/>
       <c r="Q391" s="9"/>
       <c r="R391" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="392" spans="1:18" ht="15" thickBot="1">
@@ -21264,7 +21264,7 @@
         <v>856</v>
       </c>
       <c r="J392" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K392" s="9"/>
       <c r="L392" s="9"/>
@@ -21276,7 +21276,7 @@
         <v>78937592</v>
       </c>
       <c r="R392" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="393" spans="1:18" ht="15" thickBot="1">
@@ -21308,7 +21308,7 @@
         <v>856</v>
       </c>
       <c r="J393" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K393" s="9"/>
       <c r="L393" s="9"/>
@@ -21320,7 +21320,7 @@
         <v>95171005</v>
       </c>
       <c r="R393" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="394" spans="1:18" ht="15" thickBot="1">
@@ -21352,7 +21352,7 @@
         <v>856</v>
       </c>
       <c r="J394" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K394" s="9"/>
       <c r="L394" s="9"/>
@@ -21364,7 +21364,7 @@
         <v>77805015</v>
       </c>
       <c r="R394" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="395" spans="1:18" ht="15" thickBot="1">
@@ -21396,7 +21396,7 @@
         <v>856</v>
       </c>
       <c r="J395" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K395" s="9"/>
       <c r="L395" s="9"/>
@@ -21408,7 +21408,7 @@
         <v>97155215</v>
       </c>
       <c r="R395" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="396" spans="1:18" ht="15" thickBot="1">
@@ -21440,7 +21440,7 @@
         <v>856</v>
       </c>
       <c r="J396" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K396" s="9"/>
       <c r="L396" s="9"/>
@@ -21452,7 +21452,7 @@
         <v>95637364</v>
       </c>
       <c r="R396" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="397" spans="1:18" ht="15" thickBot="1">
@@ -21484,7 +21484,7 @@
         <v>856</v>
       </c>
       <c r="J397" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K397" s="9"/>
       <c r="L397" s="9"/>
@@ -21496,7 +21496,7 @@
         <v>555875734</v>
       </c>
       <c r="R397" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="398" spans="1:18" ht="15" thickBot="1">
@@ -21528,7 +21528,7 @@
         <v>856</v>
       </c>
       <c r="J398" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K398" s="9"/>
       <c r="L398" s="9"/>
@@ -21540,7 +21540,7 @@
         <v>96899193792</v>
       </c>
       <c r="R398" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="399" spans="1:18" ht="15" thickBot="1">
@@ -21572,7 +21572,7 @@
         <v>856</v>
       </c>
       <c r="J399" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K399" s="9"/>
       <c r="L399" s="9"/>
@@ -21582,7 +21582,7 @@
       <c r="P399" s="9"/>
       <c r="Q399" s="9"/>
       <c r="R399" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="400" spans="1:18" ht="15" thickBot="1">
@@ -21614,7 +21614,7 @@
         <v>856</v>
       </c>
       <c r="J400" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K400" s="9"/>
       <c r="L400" s="9"/>
@@ -21624,7 +21624,7 @@
       <c r="P400" s="9"/>
       <c r="Q400" s="9"/>
       <c r="R400" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="401" spans="1:18" ht="15" thickBot="1">
@@ -21656,7 +21656,7 @@
         <v>856</v>
       </c>
       <c r="J401" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K401" s="9"/>
       <c r="L401" s="9"/>
@@ -21668,7 +21668,7 @@
         <v>557183305</v>
       </c>
       <c r="R401" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="402" spans="1:18" ht="15" thickBot="1">
@@ -21700,7 +21700,7 @@
         <v>856</v>
       </c>
       <c r="J402" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K402" s="9"/>
       <c r="L402" s="9"/>
@@ -21712,7 +21712,7 @@
         <v>96898175353</v>
       </c>
       <c r="R402" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="403" spans="1:18" ht="15" thickBot="1">
@@ -21744,7 +21744,7 @@
         <v>856</v>
       </c>
       <c r="J403" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K403" s="9"/>
       <c r="L403" s="9"/>
@@ -21756,7 +21756,7 @@
         <v>96897168086</v>
       </c>
       <c r="R403" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="404" spans="1:18" ht="15" thickBot="1">
@@ -21788,7 +21788,7 @@
         <v>856</v>
       </c>
       <c r="J404" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K404" s="9"/>
       <c r="L404" s="9"/>
@@ -21800,7 +21800,7 @@
         <v>78495141</v>
       </c>
       <c r="R404" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="405" spans="1:18" ht="15" thickBot="1">
@@ -21832,7 +21832,7 @@
         <v>856</v>
       </c>
       <c r="J405" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K405" s="9"/>
       <c r="L405" s="9"/>
@@ -21844,7 +21844,7 @@
         <v>96879631381</v>
       </c>
       <c r="R405" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="406" spans="1:18" ht="15" thickBot="1">
@@ -21876,7 +21876,7 @@
         <v>856</v>
       </c>
       <c r="J406" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K406" s="9"/>
       <c r="L406" s="9"/>
@@ -21888,7 +21888,7 @@
         <v>545772756</v>
       </c>
       <c r="R406" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="407" spans="1:18" ht="15" thickBot="1">
@@ -21920,7 +21920,7 @@
         <v>856</v>
       </c>
       <c r="J407" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K407" s="9"/>
       <c r="L407" s="9"/>
@@ -21932,7 +21932,7 @@
         <v>95743527</v>
       </c>
       <c r="R407" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="408" spans="1:18" ht="15" thickBot="1">
@@ -21964,7 +21964,7 @@
         <v>856</v>
       </c>
       <c r="J408" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K408" s="9"/>
       <c r="L408" s="9"/>
@@ -21976,7 +21976,7 @@
         <v>95743527</v>
       </c>
       <c r="R408" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="409" spans="1:18" ht="15" thickBot="1">
@@ -22008,7 +22008,7 @@
         <v>856</v>
       </c>
       <c r="J409" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K409" s="9"/>
       <c r="L409" s="9"/>
@@ -22020,7 +22020,7 @@
         <v>90770149</v>
       </c>
       <c r="R409" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="410" spans="1:18" ht="15" thickBot="1">
@@ -22052,7 +22052,7 @@
         <v>856</v>
       </c>
       <c r="J410" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K410" s="9"/>
       <c r="L410" s="9"/>
@@ -22064,7 +22064,7 @@
         <v>99084824</v>
       </c>
       <c r="R410" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="411" spans="1:18" ht="15" thickBot="1">
@@ -22096,7 +22096,7 @@
         <v>856</v>
       </c>
       <c r="J411" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K411" s="9"/>
       <c r="L411" s="9"/>
@@ -22108,7 +22108,7 @@
         <v>537729524</v>
       </c>
       <c r="R411" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="412" spans="1:18" ht="15" thickBot="1">
@@ -22140,7 +22140,7 @@
         <v>856</v>
       </c>
       <c r="J412" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K412" s="9"/>
       <c r="L412" s="9"/>
@@ -22152,7 +22152,7 @@
         <v>79227545</v>
       </c>
       <c r="R412" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="413" spans="1:18" ht="15" thickBot="1">
@@ -22184,7 +22184,7 @@
         <v>856</v>
       </c>
       <c r="J413" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K413" s="9"/>
       <c r="L413" s="9"/>
@@ -22196,7 +22196,7 @@
         <v>96876745617</v>
       </c>
       <c r="R413" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="414" spans="1:18" ht="23.4" thickBot="1">
@@ -22228,7 +22228,7 @@
         <v>12</v>
       </c>
       <c r="J414" s="14" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="K414" s="49" t="s">
         <v>21</v>
@@ -22274,7 +22274,7 @@
         <v>12</v>
       </c>
       <c r="J415" s="14" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="K415" s="49" t="s">
         <v>21</v>
@@ -22318,7 +22318,7 @@
         <v>12</v>
       </c>
       <c r="J416" s="14" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="K416" s="49" t="s">
         <v>21</v>
@@ -22640,7 +22640,7 @@
         <v>12</v>
       </c>
       <c r="J423" s="14" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="K423" s="49" t="s">
         <v>21</v>
@@ -22730,23 +22730,23 @@
         <v>858</v>
       </c>
       <c r="J425" s="3" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="K425" s="20" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="L425" s="9"/>
       <c r="M425" s="9"/>
       <c r="N425" s="9"/>
       <c r="O425" s="9"/>
       <c r="P425" s="56" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="Q425" s="13">
         <v>95735940</v>
       </c>
       <c r="R425" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="426" spans="1:18" ht="28.2" thickBot="1">
@@ -22778,7 +22778,7 @@
         <v>858</v>
       </c>
       <c r="J426" s="3" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="K426" s="9"/>
       <c r="L426" s="9"/>
@@ -22790,7 +22790,7 @@
         <v>95215829</v>
       </c>
       <c r="R426" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="427" spans="1:18" ht="28.2" thickBot="1">
@@ -22822,7 +22822,7 @@
         <v>858</v>
       </c>
       <c r="J427" s="3" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="K427" s="9"/>
       <c r="L427" s="9"/>
@@ -22834,7 +22834,7 @@
         <v>95706502</v>
       </c>
       <c r="R427" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="428" spans="1:18" ht="28.2" thickBot="1">
@@ -22866,7 +22866,7 @@
         <v>858</v>
       </c>
       <c r="J428" s="3" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="K428" s="9"/>
       <c r="L428" s="9"/>
@@ -22878,7 +22878,7 @@
         <v>95736230</v>
       </c>
       <c r="R428" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="429" spans="1:18" ht="28.2" thickBot="1">
@@ -23774,7 +23774,7 @@
         <v>858</v>
       </c>
       <c r="J449" s="14" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="K449" s="9"/>
       <c r="L449" s="9"/>
@@ -23814,7 +23814,7 @@
         <v>12</v>
       </c>
       <c r="J450" s="14" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K450" s="9"/>
       <c r="L450" s="9"/>
@@ -23854,7 +23854,7 @@
         <v>12</v>
       </c>
       <c r="J451" s="14" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K451" s="9"/>
       <c r="L451" s="9"/>
@@ -23894,7 +23894,7 @@
         <v>12</v>
       </c>
       <c r="J452" s="14" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K452" s="9"/>
       <c r="L452" s="9"/>
@@ -24018,7 +24018,7 @@
         <v>12</v>
       </c>
       <c r="J455" s="14" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="K455" s="9"/>
       <c r="L455" s="9"/>
@@ -24060,10 +24060,10 @@
         <v>12</v>
       </c>
       <c r="J456" s="14" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="K456" s="50" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L456" s="54">
         <v>46232</v>
@@ -24106,10 +24106,10 @@
         <v>12</v>
       </c>
       <c r="J457" s="14" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="K457" s="50" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L457" s="54">
         <v>46232</v>
@@ -24150,10 +24150,10 @@
         <v>12</v>
       </c>
       <c r="J458" s="14" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="K458" s="50" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L458" s="54">
         <v>46232</v>
@@ -24194,10 +24194,10 @@
         <v>12</v>
       </c>
       <c r="J459" s="14" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="K459" s="50" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L459" s="54">
         <v>46232</v>
@@ -24236,10 +24236,10 @@
         <v>12</v>
       </c>
       <c r="J460" s="14" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="K460" s="50" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L460" s="54">
         <v>46232</v>
@@ -24280,7 +24280,7 @@
         <v>12</v>
       </c>
       <c r="J461" s="14" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="K461" s="9"/>
       <c r="L461" s="9"/>
@@ -24320,17 +24320,17 @@
         <v>12</v>
       </c>
       <c r="J462" s="14" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="K462" s="20" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="L462" s="9"/>
       <c r="M462" s="9"/>
       <c r="N462" s="9"/>
       <c r="O462" s="9"/>
       <c r="P462" s="56" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="Q462" s="9"/>
       <c r="R462" s="61" t="s">
@@ -24364,7 +24364,7 @@
         <v>12</v>
       </c>
       <c r="J463" s="14" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="K463" s="9"/>
       <c r="L463" s="9"/>
@@ -24372,7 +24372,7 @@
       <c r="N463" s="9"/>
       <c r="O463" s="9"/>
       <c r="P463" s="56" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="Q463" s="9"/>
       <c r="R463" s="61" t="s">
@@ -24406,17 +24406,17 @@
         <v>12</v>
       </c>
       <c r="J464" s="14" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="K464" s="20" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="L464" s="9"/>
       <c r="M464" s="9"/>
       <c r="N464" s="9"/>
       <c r="O464" s="9"/>
       <c r="P464" s="56" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="Q464" s="9"/>
       <c r="R464" s="61" t="s">
@@ -24450,7 +24450,7 @@
         <v>12</v>
       </c>
       <c r="J465" s="14" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="K465" s="9"/>
       <c r="L465" s="9"/>
@@ -24490,7 +24490,7 @@
         <v>12</v>
       </c>
       <c r="J466" s="14" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="K466" s="9"/>
       <c r="L466" s="9"/>
@@ -24530,7 +24530,7 @@
         <v>12</v>
       </c>
       <c r="J467" s="14" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="K467" s="9"/>
       <c r="L467" s="9"/>
@@ -24570,7 +24570,7 @@
         <v>12</v>
       </c>
       <c r="J468" s="14" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="K468" s="9"/>
       <c r="L468" s="9"/>
@@ -24692,7 +24692,7 @@
         <v>12</v>
       </c>
       <c r="J471" s="14" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="K471" s="49" t="s">
         <v>21</v>
@@ -24736,7 +24736,7 @@
         <v>12</v>
       </c>
       <c r="J472" s="14" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="K472" s="49" t="s">
         <v>21</v>
@@ -24780,7 +24780,7 @@
         <v>858</v>
       </c>
       <c r="J473" s="14" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="K473" s="9"/>
       <c r="L473" s="9"/>
@@ -24792,7 +24792,7 @@
         <v>95746236</v>
       </c>
       <c r="R473" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="474" spans="1:18" ht="28.2" thickBot="1">
@@ -24822,7 +24822,7 @@
         <v>858</v>
       </c>
       <c r="J474" s="14" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="K474" s="9"/>
       <c r="L474" s="9"/>
@@ -24834,7 +24834,7 @@
         <v>90453715</v>
       </c>
       <c r="R474" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="475" spans="1:18" ht="28.2" thickBot="1">
@@ -24864,7 +24864,7 @@
         <v>858</v>
       </c>
       <c r="J475" s="14" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="K475" s="9"/>
       <c r="L475" s="9"/>
@@ -24876,7 +24876,7 @@
         <v>95746253</v>
       </c>
       <c r="R475" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="476" spans="1:18" ht="28.2" thickBot="1">
@@ -24906,7 +24906,7 @@
         <v>858</v>
       </c>
       <c r="J476" s="14" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="K476" s="9"/>
       <c r="L476" s="9"/>
@@ -24918,7 +24918,7 @@
         <v>551582495</v>
       </c>
       <c r="R476" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="477" spans="1:18" ht="28.2" thickBot="1">
@@ -24948,10 +24948,10 @@
         <v>858</v>
       </c>
       <c r="J477" s="14" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="K477" s="50" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L477" s="9"/>
       <c r="M477" s="9"/>
@@ -24960,7 +24960,7 @@
       <c r="P477" s="9"/>
       <c r="Q477" s="9"/>
       <c r="R477" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="478" spans="1:18" ht="28.2" thickBot="1">
@@ -24990,10 +24990,10 @@
         <v>858</v>
       </c>
       <c r="J478" s="14" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="K478" s="50" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L478" s="9"/>
       <c r="M478" s="9"/>
@@ -25002,7 +25002,7 @@
       <c r="P478" s="9"/>
       <c r="Q478" s="9"/>
       <c r="R478" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="479" spans="1:18" ht="15" thickBot="1">
@@ -25032,7 +25032,7 @@
         <v>856</v>
       </c>
       <c r="J479" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K479" s="9"/>
       <c r="L479" s="9"/>
@@ -25044,7 +25044,7 @@
         <v>96139476</v>
       </c>
       <c r="R479" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="480" spans="1:18" ht="15" thickBot="1">
@@ -25074,7 +25074,7 @@
         <v>856</v>
       </c>
       <c r="J480" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K480" s="9"/>
       <c r="L480" s="9"/>
@@ -25086,7 +25086,7 @@
         <v>96877385621</v>
       </c>
       <c r="R480" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="481" spans="1:18" ht="15" thickBot="1">
@@ -25116,7 +25116,7 @@
         <v>856</v>
       </c>
       <c r="J481" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K481" s="9"/>
       <c r="L481" s="9"/>
@@ -25128,7 +25128,7 @@
         <v>95187492</v>
       </c>
       <c r="R481" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="482" spans="1:18" ht="15" thickBot="1">
@@ -25158,7 +25158,7 @@
         <v>856</v>
       </c>
       <c r="J482" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K482" s="9"/>
       <c r="L482" s="9"/>
@@ -25170,7 +25170,7 @@
         <v>96894182149</v>
       </c>
       <c r="R482" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="483" spans="1:18" ht="15" thickBot="1">
@@ -25200,7 +25200,7 @@
         <v>856</v>
       </c>
       <c r="J483" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K483" s="9"/>
       <c r="L483" s="9"/>
@@ -25212,7 +25212,7 @@
         <v>98504360</v>
       </c>
       <c r="R483" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="484" spans="1:18" ht="15" thickBot="1">
@@ -25242,7 +25242,7 @@
         <v>856</v>
       </c>
       <c r="J484" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K484" s="9"/>
       <c r="L484" s="9"/>
@@ -25254,7 +25254,7 @@
         <v>95432531</v>
       </c>
       <c r="R484" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="485" spans="1:18" ht="15" thickBot="1">
@@ -25284,7 +25284,7 @@
         <v>856</v>
       </c>
       <c r="J485" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K485" s="9"/>
       <c r="L485" s="9"/>
@@ -25296,7 +25296,7 @@
         <v>99532737</v>
       </c>
       <c r="R485" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="486" spans="1:18" ht="15" thickBot="1">
@@ -25326,7 +25326,7 @@
         <v>856</v>
       </c>
       <c r="J486" s="47" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K486" s="9"/>
       <c r="L486" s="9"/>
@@ -25338,7 +25338,7 @@
         <v>96708583</v>
       </c>
       <c r="R486" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="487" spans="1:18" ht="28.2" thickBot="1">
@@ -25368,7 +25368,7 @@
         <v>858</v>
       </c>
       <c r="J487" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="K487" s="9"/>
       <c r="L487" s="9"/>
@@ -25380,7 +25380,7 @@
         <v>97571414</v>
       </c>
       <c r="R487" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="488" spans="1:18" ht="28.2" thickBot="1">
@@ -25410,7 +25410,7 @@
         <v>858</v>
       </c>
       <c r="J488" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="K488" s="9"/>
       <c r="L488" s="9"/>
@@ -25422,7 +25422,7 @@
         <v>77178016</v>
       </c>
       <c r="R488" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="489" spans="1:18" ht="28.2" thickBot="1">
@@ -25452,7 +25452,7 @@
         <v>858</v>
       </c>
       <c r="J489" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="K489" s="9"/>
       <c r="L489" s="9"/>
@@ -25464,7 +25464,7 @@
         <v>98013058</v>
       </c>
       <c r="R489" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="490" spans="1:18" ht="28.2" thickBot="1">
@@ -25494,7 +25494,7 @@
         <v>858</v>
       </c>
       <c r="J490" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="K490" s="9"/>
       <c r="L490" s="9"/>
@@ -25506,7 +25506,7 @@
         <v>71713470</v>
       </c>
       <c r="R490" s="44" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
   </sheetData>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/91fa87361a894c12/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="256" documentId="8_{BBB43D32-B953-4799-B724-336D98AD9DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E33C435C-EA0A-4FDA-9FD8-A4F598D1C8EE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53851D80-F1BB-4751-8AA2-F80F6842B5EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7466" uniqueCount="1620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7467" uniqueCount="1621">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -4895,6 +4895,9 @@
   </si>
   <si>
     <t>OMAN VISA TOMORW</t>
+  </si>
+  <si>
+    <t>SUB</t>
   </si>
 </sst>
 </file>
@@ -5632,10 +5635,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -5974,7 +5973,9 @@
       <c r="I1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="1"/>
+      <c r="J1" s="1" t="s">
+        <v>1620</v>
+      </c>
       <c r="K1" s="1" t="s">
         <v>4</v>
       </c>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53851D80-F1BB-4751-8AA2-F80F6842B5EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F9FE00-C423-439E-9221-4F787044BEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -5295,7 +5295,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5617,6 +5617,9 @@
     </xf>
     <xf numFmtId="0" fontId="29" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -50741,7 +50744,9 @@
       </c>
       <c r="M982" s="8"/>
       <c r="N982" s="8"/>
-      <c r="O982" s="8"/>
+      <c r="O982" s="108">
+        <v>46231</v>
+      </c>
       <c r="P982" s="8"/>
       <c r="Q982" s="8"/>
       <c r="R982" s="55" t="s">

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/91fa87361a894c12/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="331" documentId="8_{BBB43D32-B953-4799-B724-336D98AD9DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33B35C66-EE6B-4E85-9B26-3F05FBC648D6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B778826-1D43-41A7-B59A-7FE10EE23987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
+    <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8350" uniqueCount="1820">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8351" uniqueCount="1821">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -5495,6 +5495,9 @@
   </si>
   <si>
     <t>BT5985375</t>
+  </si>
+  <si>
+    <t>applied 4last vessal</t>
   </si>
 </sst>
 </file>
@@ -5913,7 +5916,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6236,36 +6239,6 @@
     <xf numFmtId="0" fontId="38" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6281,10 +6254,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6662,7 +6631,7 @@
       <c r="AB1" s="4"/>
       <c r="AC1" s="4"/>
     </row>
-    <row r="2" spans="1:29" ht="15" thickBot="1">
+    <row r="2" spans="1:29" ht="42" thickBot="1">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -6704,7 +6673,9 @@
       <c r="O2" s="24">
         <v>46231</v>
       </c>
-      <c r="P2" s="23"/>
+      <c r="P2" s="23" t="s">
+        <v>1820</v>
+      </c>
       <c r="Q2" s="19">
         <v>563491256</v>
       </c>
@@ -6764,7 +6735,9 @@
       <c r="N3" s="19">
         <v>298</v>
       </c>
-      <c r="O3" s="22"/>
+      <c r="O3" s="27">
+        <v>46232</v>
+      </c>
       <c r="P3" s="22"/>
       <c r="Q3" s="15">
         <v>77207946</v>
@@ -6825,7 +6798,9 @@
       <c r="N4" s="19">
         <v>296</v>
       </c>
-      <c r="O4" s="22"/>
+      <c r="O4" s="27">
+        <v>46232</v>
+      </c>
       <c r="P4" s="22"/>
       <c r="Q4" s="15">
         <v>77637230</v>
@@ -7541,7 +7516,9 @@
       <c r="N16" s="19">
         <v>318</v>
       </c>
-      <c r="O16" s="22"/>
+      <c r="O16" s="27">
+        <v>46232</v>
+      </c>
       <c r="P16" s="22"/>
       <c r="Q16" s="15">
         <v>94988270</v>
@@ -7669,17 +7646,6 @@
       <c r="R18" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="S18" s="5"/>
-      <c r="T18" s="5"/>
-      <c r="U18" s="5"/>
-      <c r="V18" s="5"/>
-      <c r="W18" s="5"/>
-      <c r="X18" s="5"/>
-      <c r="Y18" s="5"/>
-      <c r="Z18" s="5"/>
-      <c r="AA18" s="5"/>
-      <c r="AB18" s="5"/>
-      <c r="AC18" s="5"/>
     </row>
     <row r="19" spans="1:29" ht="15" thickBot="1">
       <c r="A19" s="7">
@@ -7770,7 +7736,9 @@
       <c r="N20" s="19">
         <v>327</v>
       </c>
-      <c r="O20" s="22"/>
+      <c r="O20" s="27">
+        <v>46232</v>
+      </c>
       <c r="P20" s="22"/>
       <c r="Q20" s="15" t="s">
         <v>892</v>
@@ -7818,7 +7786,9 @@
       <c r="N21" s="19">
         <v>326</v>
       </c>
-      <c r="O21" s="22"/>
+      <c r="O21" s="27">
+        <v>46232</v>
+      </c>
       <c r="P21" s="22"/>
       <c r="Q21" s="15">
         <v>95859428</v>
@@ -7866,7 +7836,9 @@
       <c r="N22" s="19">
         <v>319</v>
       </c>
-      <c r="O22" s="22"/>
+      <c r="O22" s="27">
+        <v>46232</v>
+      </c>
       <c r="P22" s="22"/>
       <c r="Q22" s="15">
         <v>92631925</v>
@@ -7914,7 +7886,9 @@
       <c r="N23" s="19">
         <v>321</v>
       </c>
-      <c r="O23" s="22"/>
+      <c r="O23" s="27">
+        <v>46232</v>
+      </c>
       <c r="P23" s="22"/>
       <c r="Q23" s="15">
         <v>529380494</v>
@@ -7962,7 +7936,9 @@
       <c r="N24" s="19">
         <v>322</v>
       </c>
-      <c r="O24" s="22"/>
+      <c r="O24" s="27">
+        <v>46232</v>
+      </c>
       <c r="P24" s="22"/>
       <c r="Q24" s="15">
         <v>502502279</v>
@@ -9054,7 +9030,9 @@
       <c r="N47" s="19">
         <v>241</v>
       </c>
-      <c r="O47" s="22"/>
+      <c r="O47" s="27">
+        <v>46232</v>
+      </c>
       <c r="P47" s="22"/>
       <c r="Q47" s="15">
         <v>77574192</v>
@@ -10016,7 +9994,9 @@
       <c r="N67" s="19">
         <v>325</v>
       </c>
-      <c r="O67" s="22"/>
+      <c r="O67" s="27">
+        <v>46232</v>
+      </c>
       <c r="P67" s="22"/>
       <c r="Q67" s="22"/>
       <c r="R67" s="28" t="s">
@@ -11050,7 +11030,9 @@
       <c r="N89" s="19">
         <v>349</v>
       </c>
-      <c r="O89" s="22"/>
+      <c r="O89" s="27">
+        <v>46232</v>
+      </c>
       <c r="P89" s="22"/>
       <c r="Q89" s="22"/>
       <c r="R89" s="43" t="s">
@@ -11098,7 +11080,9 @@
       <c r="N90" s="19">
         <v>348</v>
       </c>
-      <c r="O90" s="22"/>
+      <c r="O90" s="27">
+        <v>46232</v>
+      </c>
       <c r="P90" s="22"/>
       <c r="Q90" s="22"/>
       <c r="R90" s="43" t="s">
@@ -11382,7 +11366,9 @@
       <c r="N96" s="19">
         <v>678</v>
       </c>
-      <c r="O96" s="22"/>
+      <c r="O96" s="27">
+        <v>46232</v>
+      </c>
       <c r="P96" s="22"/>
       <c r="Q96" s="22"/>
       <c r="R96" s="25" t="s">
@@ -11430,7 +11416,9 @@
       <c r="N97" s="19">
         <v>679</v>
       </c>
-      <c r="O97" s="22"/>
+      <c r="O97" s="27">
+        <v>46232</v>
+      </c>
       <c r="P97" s="22"/>
       <c r="Q97" s="22"/>
       <c r="R97" s="25" t="s">
@@ -11478,7 +11466,9 @@
       <c r="N98" s="19">
         <v>347</v>
       </c>
-      <c r="O98" s="22"/>
+      <c r="O98" s="27">
+        <v>46232</v>
+      </c>
       <c r="P98" s="22"/>
       <c r="Q98" s="15">
         <v>95725624</v>
@@ -11528,7 +11518,9 @@
       <c r="N99" s="19">
         <v>350</v>
       </c>
-      <c r="O99" s="22"/>
+      <c r="O99" s="27">
+        <v>46232</v>
+      </c>
       <c r="P99" s="22"/>
       <c r="Q99" s="22"/>
       <c r="R99" s="25" t="s">
@@ -11874,7 +11866,9 @@
       <c r="N106" s="19">
         <v>340</v>
       </c>
-      <c r="O106" s="22"/>
+      <c r="O106" s="27">
+        <v>46232</v>
+      </c>
       <c r="P106" s="22"/>
       <c r="Q106" s="15">
         <v>77005352</v>
@@ -12068,7 +12062,9 @@
       <c r="N110" s="19">
         <v>256</v>
       </c>
-      <c r="O110" s="22"/>
+      <c r="O110" s="27">
+        <v>46232</v>
+      </c>
       <c r="P110" s="22"/>
       <c r="Q110" s="15">
         <v>569370083</v>
@@ -12316,7 +12312,9 @@
       <c r="N115" s="19">
         <v>355</v>
       </c>
-      <c r="O115" s="22"/>
+      <c r="O115" s="27">
+        <v>46232</v>
+      </c>
       <c r="P115" s="22"/>
       <c r="Q115" s="15">
         <v>99138916</v>
@@ -13436,7 +13434,9 @@
       <c r="N138" s="19">
         <v>394</v>
       </c>
-      <c r="O138" s="22"/>
+      <c r="O138" s="27">
+        <v>46232</v>
+      </c>
       <c r="P138" s="22"/>
       <c r="Q138" s="15">
         <v>524910916</v>
@@ -13484,7 +13484,9 @@
       <c r="N139" s="19">
         <v>401</v>
       </c>
-      <c r="O139" s="22"/>
+      <c r="O139" s="27">
+        <v>46232</v>
+      </c>
       <c r="P139" s="22"/>
       <c r="Q139" s="15">
         <v>76904367</v>
@@ -13532,7 +13534,9 @@
       <c r="N140" s="19">
         <v>399</v>
       </c>
-      <c r="O140" s="22"/>
+      <c r="O140" s="27">
+        <v>46232</v>
+      </c>
       <c r="P140" s="22"/>
       <c r="Q140" s="15">
         <v>76814187</v>
@@ -14580,7 +14584,9 @@
       <c r="N162" s="19">
         <v>271</v>
       </c>
-      <c r="O162" s="22"/>
+      <c r="O162" s="27">
+        <v>46232</v>
+      </c>
       <c r="P162" s="22"/>
       <c r="Q162" s="22"/>
       <c r="R162" s="34" t="s">
@@ -14618,11 +14624,11 @@
       <c r="J163" s="61" t="s">
         <v>860</v>
       </c>
-      <c r="K163" s="21" t="s">
-        <v>20</v>
+      <c r="K163" s="26" t="s">
+        <v>1291</v>
       </c>
       <c r="L163" s="27">
-        <v>46229</v>
+        <v>46237</v>
       </c>
       <c r="M163" s="22"/>
       <c r="N163" s="19">
@@ -14960,10 +14966,12 @@
       <c r="J170" s="33" t="s">
         <v>854</v>
       </c>
-      <c r="K170" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L170" s="22"/>
+      <c r="K170" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L170" s="27">
+        <v>46237</v>
+      </c>
       <c r="M170" s="22"/>
       <c r="N170" s="22"/>
       <c r="O170" s="22"/>
@@ -15052,15 +15060,19 @@
       <c r="J172" s="33" t="s">
         <v>854</v>
       </c>
-      <c r="K172" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L172" s="22"/>
+      <c r="K172" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L172" s="27">
+        <v>46237</v>
+      </c>
       <c r="M172" s="22"/>
       <c r="N172" s="19">
         <v>346</v>
       </c>
-      <c r="O172" s="22"/>
+      <c r="O172" s="27">
+        <v>46232</v>
+      </c>
       <c r="P172" s="22"/>
       <c r="Q172" s="15">
         <v>95712792</v>
@@ -15100,10 +15112,12 @@
       <c r="J173" s="33" t="s">
         <v>854</v>
       </c>
-      <c r="K173" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L173" s="22"/>
+      <c r="K173" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L173" s="27">
+        <v>46237</v>
+      </c>
       <c r="M173" s="22"/>
       <c r="N173" s="19">
         <v>338</v>
@@ -15148,10 +15162,12 @@
       <c r="J174" s="33" t="s">
         <v>854</v>
       </c>
-      <c r="K174" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L174" s="22"/>
+      <c r="K174" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L174" s="27">
+        <v>46237</v>
+      </c>
       <c r="M174" s="22"/>
       <c r="N174" s="19">
         <v>180</v>
@@ -15246,15 +15262,19 @@
       <c r="J176" s="33" t="s">
         <v>854</v>
       </c>
-      <c r="K176" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L176" s="22"/>
+      <c r="K176" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L176" s="27">
+        <v>46237</v>
+      </c>
       <c r="M176" s="22"/>
       <c r="N176" s="19">
         <v>307</v>
       </c>
-      <c r="O176" s="22"/>
+      <c r="O176" s="27">
+        <v>46232</v>
+      </c>
       <c r="P176" s="22"/>
       <c r="Q176" s="15">
         <v>77201572</v>
@@ -15294,10 +15314,12 @@
       <c r="J177" s="33" t="s">
         <v>854</v>
       </c>
-      <c r="K177" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L177" s="22"/>
+      <c r="K177" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L177" s="27">
+        <v>46237</v>
+      </c>
       <c r="M177" s="22"/>
       <c r="N177" s="19">
         <v>306</v>
@@ -15342,15 +15364,19 @@
       <c r="J178" s="33" t="s">
         <v>854</v>
       </c>
-      <c r="K178" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L178" s="22"/>
+      <c r="K178" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L178" s="27">
+        <v>46237</v>
+      </c>
       <c r="M178" s="22"/>
       <c r="N178" s="19">
         <v>308</v>
       </c>
-      <c r="O178" s="22"/>
+      <c r="O178" s="27">
+        <v>46232</v>
+      </c>
       <c r="P178" s="22"/>
       <c r="Q178" s="15">
         <v>95775821</v>
@@ -15390,10 +15416,12 @@
       <c r="J179" s="33" t="s">
         <v>854</v>
       </c>
-      <c r="K179" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L179" s="22"/>
+      <c r="K179" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L179" s="27">
+        <v>46237</v>
+      </c>
       <c r="M179" s="22"/>
       <c r="N179" s="19">
         <v>133</v>
@@ -15438,10 +15466,12 @@
       <c r="J180" s="33" t="s">
         <v>854</v>
       </c>
-      <c r="K180" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L180" s="22"/>
+      <c r="K180" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L180" s="27">
+        <v>46237</v>
+      </c>
       <c r="M180" s="22"/>
       <c r="N180" s="19">
         <v>4</v>
@@ -15536,11 +15566,11 @@
       <c r="J182" s="31" t="s">
         <v>854</v>
       </c>
-      <c r="K182" s="55" t="s">
-        <v>887</v>
+      <c r="K182" s="69" t="s">
+        <v>1291</v>
       </c>
       <c r="L182" s="56">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="M182" s="54"/>
       <c r="N182" s="31" t="s">
@@ -15588,11 +15618,11 @@
       <c r="J183" s="23" t="s">
         <v>861</v>
       </c>
-      <c r="K183" s="46" t="s">
-        <v>887</v>
+      <c r="K183" s="26" t="s">
+        <v>1291</v>
       </c>
       <c r="L183" s="27">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="M183" s="22"/>
       <c r="N183" s="19">
@@ -15640,11 +15670,11 @@
       <c r="J184" s="23" t="s">
         <v>861</v>
       </c>
-      <c r="K184" s="46" t="s">
-        <v>887</v>
+      <c r="K184" s="26" t="s">
+        <v>1291</v>
       </c>
       <c r="L184" s="27">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="M184" s="22"/>
       <c r="N184" s="19">
@@ -15690,11 +15720,11 @@
       <c r="J185" s="23" t="s">
         <v>861</v>
       </c>
-      <c r="K185" s="46" t="s">
-        <v>887</v>
+      <c r="K185" s="26" t="s">
+        <v>1291</v>
       </c>
       <c r="L185" s="27">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="M185" s="22"/>
       <c r="N185" s="19">
@@ -15742,10 +15772,12 @@
       <c r="J186" s="23" t="s">
         <v>861</v>
       </c>
-      <c r="K186" s="46" t="s">
-        <v>887</v>
-      </c>
-      <c r="L186" s="22"/>
+      <c r="K186" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L186" s="27">
+        <v>46237</v>
+      </c>
       <c r="M186" s="22"/>
       <c r="N186" s="19">
         <v>105</v>
@@ -15792,10 +15824,12 @@
       <c r="J187" s="23" t="s">
         <v>861</v>
       </c>
-      <c r="K187" s="46" t="s">
-        <v>887</v>
-      </c>
-      <c r="L187" s="22"/>
+      <c r="K187" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L187" s="27">
+        <v>46237</v>
+      </c>
       <c r="M187" s="22"/>
       <c r="N187" s="19">
         <v>104</v>
@@ -15842,11 +15876,11 @@
       <c r="J188" s="23" t="s">
         <v>861</v>
       </c>
-      <c r="K188" s="46" t="s">
-        <v>887</v>
+      <c r="K188" s="26" t="s">
+        <v>1291</v>
       </c>
       <c r="L188" s="27">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="M188" s="22"/>
       <c r="N188" s="19">
@@ -15892,10 +15926,12 @@
       <c r="J189" s="23" t="s">
         <v>861</v>
       </c>
-      <c r="K189" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L189" s="22"/>
+      <c r="K189" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L189" s="27">
+        <v>46237</v>
+      </c>
       <c r="M189" s="22"/>
       <c r="N189" s="19">
         <v>453</v>
@@ -15940,10 +15976,12 @@
       <c r="J190" s="23" t="s">
         <v>861</v>
       </c>
-      <c r="K190" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L190" s="22"/>
+      <c r="K190" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L190" s="27">
+        <v>46236</v>
+      </c>
       <c r="M190" s="22"/>
       <c r="N190" s="19">
         <v>427</v>
@@ -15986,10 +16024,12 @@
       <c r="J191" s="23" t="s">
         <v>861</v>
       </c>
-      <c r="K191" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L191" s="22"/>
+      <c r="K191" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L191" s="27">
+        <v>46237</v>
+      </c>
       <c r="M191" s="22"/>
       <c r="N191" s="22"/>
       <c r="O191" s="22"/>
@@ -17218,10 +17258,12 @@
         <v>851</v>
       </c>
       <c r="J216" s="22"/>
-      <c r="K216" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L216" s="22"/>
+      <c r="K216" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L216" s="27">
+        <v>46237</v>
+      </c>
       <c r="M216" s="22"/>
       <c r="N216" s="22"/>
       <c r="O216" s="22"/>
@@ -17746,7 +17788,9 @@
       <c r="N227" s="19">
         <v>488</v>
       </c>
-      <c r="O227" s="22"/>
+      <c r="O227" s="27">
+        <v>46232</v>
+      </c>
       <c r="P227" s="22"/>
       <c r="Q227" s="15">
         <v>94784990</v>
@@ -18924,7 +18968,9 @@
       <c r="N251" s="19">
         <v>358</v>
       </c>
-      <c r="O251" s="22"/>
+      <c r="O251" s="27">
+        <v>46232</v>
+      </c>
       <c r="P251" s="22"/>
       <c r="Q251" s="22"/>
       <c r="R251" s="25" t="s">
@@ -19598,7 +19644,9 @@
       <c r="N265" s="19">
         <v>364</v>
       </c>
-      <c r="O265" s="22"/>
+      <c r="O265" s="27">
+        <v>46232</v>
+      </c>
       <c r="P265" s="22"/>
       <c r="Q265" s="22"/>
       <c r="R265" s="25" t="s">
@@ -20316,10 +20364,12 @@
       <c r="J280" s="19" t="s">
         <v>870</v>
       </c>
-      <c r="K280" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L280" s="22"/>
+      <c r="K280" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L280" s="27">
+        <v>46237</v>
+      </c>
       <c r="M280" s="22"/>
       <c r="N280" s="22"/>
       <c r="O280" s="22"/>
@@ -20512,7 +20562,9 @@
       <c r="N284" s="19">
         <v>354</v>
       </c>
-      <c r="O284" s="22"/>
+      <c r="O284" s="27">
+        <v>46232</v>
+      </c>
       <c r="P284" s="22"/>
       <c r="Q284" s="15">
         <v>79900411</v>
@@ -20562,7 +20614,9 @@
       <c r="N285" s="19">
         <v>351</v>
       </c>
-      <c r="O285" s="22"/>
+      <c r="O285" s="27">
+        <v>46232</v>
+      </c>
       <c r="P285" s="22"/>
       <c r="Q285" s="15">
         <v>95199535</v>
@@ -20612,7 +20666,9 @@
       <c r="N286" s="19">
         <v>353</v>
       </c>
-      <c r="O286" s="22"/>
+      <c r="O286" s="27">
+        <v>46232</v>
+      </c>
       <c r="P286" s="22"/>
       <c r="Q286" s="15">
         <v>96894609416</v>
@@ -20944,7 +21000,9 @@
       <c r="N293" s="19">
         <v>417</v>
       </c>
-      <c r="O293" s="22"/>
+      <c r="O293" s="27">
+        <v>46232</v>
+      </c>
       <c r="P293" s="22"/>
       <c r="Q293" s="15">
         <v>94389684</v>
@@ -22402,7 +22460,9 @@
       <c r="N324" s="19">
         <v>383</v>
       </c>
-      <c r="O324" s="22"/>
+      <c r="O324" s="27">
+        <v>46232</v>
+      </c>
       <c r="P324" s="22"/>
       <c r="Q324" s="22"/>
       <c r="R324" s="34" t="s">
@@ -23166,10 +23226,12 @@
       <c r="J340" s="74" t="s">
         <v>875</v>
       </c>
-      <c r="K340" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L340" s="22"/>
+      <c r="K340" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L340" s="27">
+        <v>46236</v>
+      </c>
       <c r="M340" s="22"/>
       <c r="N340" s="19">
         <v>612</v>
@@ -26452,7 +26514,9 @@
       <c r="N408" s="19">
         <v>413</v>
       </c>
-      <c r="O408" s="22"/>
+      <c r="O408" s="27">
+        <v>46232</v>
+      </c>
       <c r="P408" s="22"/>
       <c r="Q408" s="15">
         <v>99084824</v>
@@ -28494,10 +28558,12 @@
       <c r="J451" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="K451" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L451" s="22"/>
+      <c r="K451" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L451" s="27">
+        <v>46237</v>
+      </c>
       <c r="M451" s="22"/>
       <c r="N451" s="19">
         <v>137</v>
@@ -28934,10 +29000,12 @@
       <c r="J460" s="19" t="s">
         <v>881</v>
       </c>
-      <c r="K460" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L460" s="22"/>
+      <c r="K460" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L460" s="27">
+        <v>46237</v>
+      </c>
       <c r="M460" s="22"/>
       <c r="N460" s="22"/>
       <c r="O460" s="22"/>
@@ -29026,10 +29094,12 @@
       <c r="J462" s="19" t="s">
         <v>881</v>
       </c>
-      <c r="K462" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L462" s="22"/>
+      <c r="K462" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L462" s="27">
+        <v>46237</v>
+      </c>
       <c r="M462" s="22"/>
       <c r="N462" s="22"/>
       <c r="O462" s="22"/>
@@ -29848,10 +29918,12 @@
       <c r="J479" s="19" t="s">
         <v>1199</v>
       </c>
-      <c r="K479" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L479" s="22"/>
+      <c r="K479" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L479" s="27">
+        <v>46237</v>
+      </c>
       <c r="M479" s="22"/>
       <c r="N479" s="19">
         <v>673</v>
@@ -29896,10 +29968,12 @@
       <c r="J480" s="19" t="s">
         <v>864</v>
       </c>
-      <c r="K480" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L480" s="22"/>
+      <c r="K480" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L480" s="27">
+        <v>46237</v>
+      </c>
       <c r="M480" s="22"/>
       <c r="N480" s="22"/>
       <c r="O480" s="22"/>
@@ -29942,10 +30016,12 @@
       <c r="J481" s="19" t="s">
         <v>864</v>
       </c>
-      <c r="K481" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L481" s="22"/>
+      <c r="K481" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L481" s="27">
+        <v>46237</v>
+      </c>
       <c r="M481" s="22"/>
       <c r="N481" s="22"/>
       <c r="O481" s="22"/>
@@ -30034,10 +30110,12 @@
       <c r="J483" s="19" t="s">
         <v>864</v>
       </c>
-      <c r="K483" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L483" s="22"/>
+      <c r="K483" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L483" s="27">
+        <v>46237</v>
+      </c>
       <c r="M483" s="22"/>
       <c r="N483" s="19">
         <v>563</v>
@@ -30082,10 +30160,12 @@
       <c r="J484" s="19" t="s">
         <v>864</v>
       </c>
-      <c r="K484" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L484" s="22"/>
+      <c r="K484" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L484" s="27">
+        <v>46237</v>
+      </c>
       <c r="M484" s="22"/>
       <c r="N484" s="19">
         <v>559</v>
@@ -30180,10 +30260,12 @@
       <c r="J486" s="19" t="s">
         <v>872</v>
       </c>
-      <c r="K486" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L486" s="22"/>
+      <c r="K486" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L486" s="27">
+        <v>46237</v>
+      </c>
       <c r="M486" s="22"/>
       <c r="N486" s="22"/>
       <c r="O486" s="22"/>
@@ -30226,10 +30308,12 @@
       <c r="J487" s="19" t="s">
         <v>872</v>
       </c>
-      <c r="K487" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L487" s="22"/>
+      <c r="K487" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L487" s="27">
+        <v>46237</v>
+      </c>
       <c r="M487" s="22"/>
       <c r="N487" s="22"/>
       <c r="O487" s="22"/>
@@ -30272,10 +30356,12 @@
       <c r="J488" s="19" t="s">
         <v>864</v>
       </c>
-      <c r="K488" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L488" s="22"/>
+      <c r="K488" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L488" s="27">
+        <v>46237</v>
+      </c>
       <c r="M488" s="22"/>
       <c r="N488" s="22"/>
       <c r="O488" s="22"/>
@@ -30316,10 +30402,12 @@
       <c r="J489" s="19" t="s">
         <v>868</v>
       </c>
-      <c r="K489" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L489" s="22"/>
+      <c r="K489" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L489" s="27">
+        <v>46237</v>
+      </c>
       <c r="M489" s="22"/>
       <c r="N489" s="19">
         <v>486</v>
@@ -30362,10 +30450,12 @@
       <c r="J490" s="19" t="s">
         <v>1200</v>
       </c>
-      <c r="K490" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L490" s="22"/>
+      <c r="K490" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L490" s="27">
+        <v>46237</v>
+      </c>
       <c r="M490" s="22"/>
       <c r="N490" s="19">
         <v>522</v>
@@ -32090,10 +32180,12 @@
         <v>851</v>
       </c>
       <c r="J526" s="22"/>
-      <c r="K526" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L526" s="22"/>
+      <c r="K526" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L526" s="27">
+        <v>46237</v>
+      </c>
       <c r="M526" s="22"/>
       <c r="N526" s="22"/>
       <c r="O526" s="22"/>
@@ -32134,10 +32226,12 @@
         <v>851</v>
       </c>
       <c r="J527" s="22"/>
-      <c r="K527" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L527" s="22"/>
+      <c r="K527" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L527" s="27">
+        <v>46237</v>
+      </c>
       <c r="M527" s="22"/>
       <c r="N527" s="22"/>
       <c r="O527" s="22"/>
@@ -32178,10 +32272,12 @@
         <v>851</v>
       </c>
       <c r="J528" s="22"/>
-      <c r="K528" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L528" s="22"/>
+      <c r="K528" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L528" s="27">
+        <v>46237</v>
+      </c>
       <c r="M528" s="22"/>
       <c r="N528" s="22"/>
       <c r="O528" s="22"/>
@@ -32225,7 +32321,9 @@
       <c r="K529" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="L529" s="22"/>
+      <c r="L529" s="27">
+        <v>46236</v>
+      </c>
       <c r="M529" s="22"/>
       <c r="N529" s="22"/>
       <c r="O529" s="22"/>
@@ -32266,10 +32364,12 @@
         <v>851</v>
       </c>
       <c r="J530" s="22"/>
-      <c r="K530" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L530" s="22"/>
+      <c r="K530" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L530" s="27">
+        <v>46236</v>
+      </c>
       <c r="M530" s="22"/>
       <c r="N530" s="22"/>
       <c r="O530" s="22"/>
@@ -32310,10 +32410,12 @@
         <v>851</v>
       </c>
       <c r="J531" s="22"/>
-      <c r="K531" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L531" s="22"/>
+      <c r="K531" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L531" s="27">
+        <v>46237</v>
+      </c>
       <c r="M531" s="22"/>
       <c r="N531" s="19">
         <v>648</v>
@@ -32356,10 +32458,12 @@
         <v>851</v>
       </c>
       <c r="J532" s="22"/>
-      <c r="K532" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L532" s="22"/>
+      <c r="K532" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L532" s="27">
+        <v>46237</v>
+      </c>
       <c r="M532" s="22"/>
       <c r="N532" s="19">
         <v>649</v>
@@ -32402,10 +32506,12 @@
         <v>851</v>
       </c>
       <c r="J533" s="22"/>
-      <c r="K533" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L533" s="22"/>
+      <c r="K533" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L533" s="27">
+        <v>46237</v>
+      </c>
       <c r="M533" s="22"/>
       <c r="N533" s="22"/>
       <c r="O533" s="22"/>
@@ -32592,10 +32698,12 @@
       <c r="J537" s="19" t="s">
         <v>853</v>
       </c>
-      <c r="K537" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L537" s="22"/>
+      <c r="K537" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L537" s="27">
+        <v>46237</v>
+      </c>
       <c r="M537" s="22"/>
       <c r="N537" s="22"/>
       <c r="O537" s="22"/>
@@ -32794,7 +32902,9 @@
       <c r="N541" s="19">
         <v>320</v>
       </c>
-      <c r="O541" s="22"/>
+      <c r="O541" s="27">
+        <v>46232</v>
+      </c>
       <c r="P541" s="22"/>
       <c r="Q541" s="15">
         <v>77552346</v>
@@ -32844,7 +32954,9 @@
       <c r="N542" s="19">
         <v>360</v>
       </c>
-      <c r="O542" s="22"/>
+      <c r="O542" s="27">
+        <v>46232</v>
+      </c>
       <c r="P542" s="22"/>
       <c r="Q542" s="15">
         <v>95709215</v>
@@ -32894,7 +33006,9 @@
       <c r="N543" s="19">
         <v>357</v>
       </c>
-      <c r="O543" s="22"/>
+      <c r="O543" s="27">
+        <v>46232</v>
+      </c>
       <c r="P543" s="22"/>
       <c r="Q543" s="15">
         <v>95913528</v>
@@ -34342,7 +34456,9 @@
       </c>
       <c r="M573" s="22"/>
       <c r="N573" s="22"/>
-      <c r="O573" s="22"/>
+      <c r="O573" s="27">
+        <v>46232</v>
+      </c>
       <c r="P573" s="22"/>
       <c r="Q573" s="15">
         <v>96139476</v>
@@ -34392,7 +34508,9 @@
       <c r="N574" s="19">
         <v>315</v>
       </c>
-      <c r="O574" s="22"/>
+      <c r="O574" s="27">
+        <v>46232</v>
+      </c>
       <c r="P574" s="22"/>
       <c r="Q574" s="15">
         <v>96877385621</v>
@@ -34442,7 +34560,9 @@
       <c r="N575" s="19">
         <v>709</v>
       </c>
-      <c r="O575" s="22"/>
+      <c r="O575" s="27">
+        <v>46232</v>
+      </c>
       <c r="P575" s="22"/>
       <c r="Q575" s="15">
         <v>95187492</v>
@@ -34640,7 +34760,9 @@
       <c r="N579" s="19">
         <v>388</v>
       </c>
-      <c r="O579" s="22"/>
+      <c r="O579" s="27">
+        <v>46232</v>
+      </c>
       <c r="P579" s="22"/>
       <c r="Q579" s="15">
         <v>99532737</v>
@@ -36664,7 +36786,9 @@
       <c r="N622" s="19">
         <v>405</v>
       </c>
-      <c r="O622" s="22"/>
+      <c r="O622" s="27">
+        <v>46232</v>
+      </c>
       <c r="P622" s="22"/>
       <c r="Q622" s="22"/>
       <c r="R622" s="34" t="s">
@@ -36712,7 +36836,9 @@
       <c r="N623" s="19">
         <v>404</v>
       </c>
-      <c r="O623" s="22"/>
+      <c r="O623" s="27">
+        <v>46232</v>
+      </c>
       <c r="P623" s="22"/>
       <c r="Q623" s="22"/>
       <c r="R623" s="34" t="s">
@@ -36760,7 +36886,9 @@
       <c r="N624" s="19">
         <v>403</v>
       </c>
-      <c r="O624" s="22"/>
+      <c r="O624" s="27">
+        <v>46232</v>
+      </c>
       <c r="P624" s="22"/>
       <c r="Q624" s="22"/>
       <c r="R624" s="34" t="s">
@@ -37456,7 +37584,9 @@
       <c r="N639" s="19">
         <v>476</v>
       </c>
-      <c r="O639" s="22"/>
+      <c r="O639" s="27">
+        <v>46232</v>
+      </c>
       <c r="P639" s="22"/>
       <c r="Q639" s="15">
         <v>93317831</v>
@@ -37550,7 +37680,9 @@
       </c>
       <c r="M641" s="22"/>
       <c r="N641" s="22"/>
-      <c r="O641" s="22"/>
+      <c r="O641" s="27">
+        <v>46232</v>
+      </c>
       <c r="P641" s="22"/>
       <c r="Q641" s="22"/>
       <c r="R641" s="34" t="s">
@@ -38244,7 +38376,9 @@
         <v>448</v>
       </c>
       <c r="N655" s="88"/>
-      <c r="O655" s="22"/>
+      <c r="O655" s="27">
+        <v>46232</v>
+      </c>
       <c r="P655" s="22"/>
       <c r="Q655" s="22"/>
       <c r="R655" s="34" t="s">
@@ -38672,10 +38806,12 @@
       <c r="J664" s="33" t="s">
         <v>854</v>
       </c>
-      <c r="K664" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L664" s="22"/>
+      <c r="K664" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L664" s="27">
+        <v>46236</v>
+      </c>
       <c r="M664" s="22"/>
       <c r="N664" s="19">
         <v>379</v>
@@ -39988,7 +40124,9 @@
       <c r="L692" s="22"/>
       <c r="M692" s="22"/>
       <c r="N692" s="22"/>
-      <c r="O692" s="22"/>
+      <c r="O692" s="27">
+        <v>46232</v>
+      </c>
       <c r="P692" s="22"/>
       <c r="Q692" s="22"/>
       <c r="R692" s="20" t="s">
@@ -40030,7 +40168,9 @@
       <c r="L693" s="22"/>
       <c r="M693" s="22"/>
       <c r="N693" s="22"/>
-      <c r="O693" s="22"/>
+      <c r="O693" s="27">
+        <v>46232</v>
+      </c>
       <c r="P693" s="22"/>
       <c r="Q693" s="22"/>
       <c r="R693" s="20" t="s">
@@ -40574,10 +40714,12 @@
       <c r="J706" s="23" t="s">
         <v>1289</v>
       </c>
-      <c r="K706" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L706" s="22"/>
+      <c r="K706" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L706" s="27">
+        <v>46237</v>
+      </c>
       <c r="M706" s="22"/>
       <c r="N706" s="22"/>
       <c r="O706" s="22"/>
@@ -40618,11 +40760,11 @@
       <c r="J707" s="23" t="s">
         <v>1289</v>
       </c>
-      <c r="K707" s="46" t="s">
-        <v>887</v>
+      <c r="K707" s="26" t="s">
+        <v>1291</v>
       </c>
       <c r="L707" s="27">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="M707" s="22"/>
       <c r="N707" s="19">
@@ -40666,17 +40808,19 @@
       <c r="J708" s="23" t="s">
         <v>1289</v>
       </c>
-      <c r="K708" s="46" t="s">
-        <v>887</v>
+      <c r="K708" s="26" t="s">
+        <v>1291</v>
       </c>
       <c r="L708" s="27">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="M708" s="22"/>
       <c r="N708" s="19">
         <v>368</v>
       </c>
-      <c r="O708" s="22"/>
+      <c r="O708" s="27">
+        <v>46232</v>
+      </c>
       <c r="P708" s="22"/>
       <c r="Q708" s="22"/>
       <c r="R708" s="34" t="s">
@@ -40714,10 +40858,12 @@
       <c r="J709" s="23" t="s">
         <v>1289</v>
       </c>
-      <c r="K709" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L709" s="22"/>
+      <c r="K709" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L709" s="27">
+        <v>46237</v>
+      </c>
       <c r="M709" s="22"/>
       <c r="N709" s="22"/>
       <c r="O709" s="22"/>
@@ -40758,10 +40904,12 @@
       <c r="J710" s="23" t="s">
         <v>1289</v>
       </c>
-      <c r="K710" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L710" s="22"/>
+      <c r="K710" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L710" s="27">
+        <v>46237</v>
+      </c>
       <c r="M710" s="22"/>
       <c r="N710" s="22"/>
       <c r="O710" s="22"/>
@@ -40802,10 +40950,12 @@
       <c r="J711" s="23" t="s">
         <v>1289</v>
       </c>
-      <c r="K711" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L711" s="22"/>
+      <c r="K711" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L711" s="27">
+        <v>46237</v>
+      </c>
       <c r="M711" s="22"/>
       <c r="N711" s="22"/>
       <c r="O711" s="22"/>
@@ -40846,10 +40996,12 @@
       <c r="J712" s="23" t="s">
         <v>1289</v>
       </c>
-      <c r="K712" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L712" s="22"/>
+      <c r="K712" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L712" s="27">
+        <v>46237</v>
+      </c>
       <c r="M712" s="22"/>
       <c r="N712" s="19">
         <v>587</v>
@@ -40940,10 +41092,12 @@
       <c r="J714" s="23" t="s">
         <v>1289</v>
       </c>
-      <c r="K714" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L714" s="22"/>
+      <c r="K714" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L714" s="27">
+        <v>46237</v>
+      </c>
       <c r="M714" s="22"/>
       <c r="N714" s="22"/>
       <c r="O714" s="22"/>
@@ -40984,10 +41138,12 @@
       <c r="J715" s="23" t="s">
         <v>1289</v>
       </c>
-      <c r="K715" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L715" s="22"/>
+      <c r="K715" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L715" s="27">
+        <v>46237</v>
+      </c>
       <c r="M715" s="22"/>
       <c r="N715" s="22"/>
       <c r="O715" s="22"/>
@@ -41028,10 +41184,12 @@
       <c r="J716" s="23" t="s">
         <v>1289</v>
       </c>
-      <c r="K716" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L716" s="22"/>
+      <c r="K716" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L716" s="27">
+        <v>46237</v>
+      </c>
       <c r="M716" s="22"/>
       <c r="N716" s="22"/>
       <c r="O716" s="22"/>
@@ -41072,10 +41230,12 @@
       <c r="J717" s="23" t="s">
         <v>1289</v>
       </c>
-      <c r="K717" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L717" s="22"/>
+      <c r="K717" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L717" s="27">
+        <v>46237</v>
+      </c>
       <c r="M717" s="22"/>
       <c r="N717" s="22"/>
       <c r="O717" s="22"/>
@@ -41166,10 +41326,12 @@
       <c r="J719" s="23" t="s">
         <v>1289</v>
       </c>
-      <c r="K719" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L719" s="22"/>
+      <c r="K719" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L719" s="27">
+        <v>46237</v>
+      </c>
       <c r="M719" s="22"/>
       <c r="N719" s="19">
         <v>578</v>
@@ -41212,10 +41374,12 @@
       <c r="J720" s="23" t="s">
         <v>1289</v>
       </c>
-      <c r="K720" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L720" s="22"/>
+      <c r="K720" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L720" s="27">
+        <v>46237</v>
+      </c>
       <c r="M720" s="22"/>
       <c r="N720" s="19">
         <v>605</v>
@@ -41258,10 +41422,12 @@
       <c r="J721" s="23" t="s">
         <v>1289</v>
       </c>
-      <c r="K721" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L721" s="22"/>
+      <c r="K721" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L721" s="27">
+        <v>46237</v>
+      </c>
       <c r="M721" s="22"/>
       <c r="N721" s="19">
         <v>606</v>
@@ -41304,11 +41470,11 @@
       <c r="J722" s="23" t="s">
         <v>1289</v>
       </c>
-      <c r="K722" s="46" t="s">
-        <v>887</v>
+      <c r="K722" s="26" t="s">
+        <v>1291</v>
       </c>
       <c r="L722" s="27">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="M722" s="22"/>
       <c r="N722" s="19">
@@ -41352,10 +41518,12 @@
       <c r="J723" s="23" t="s">
         <v>1289</v>
       </c>
-      <c r="K723" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L723" s="22"/>
+      <c r="K723" s="26" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L723" s="27">
+        <v>46237</v>
+      </c>
       <c r="M723" s="22"/>
       <c r="N723" s="22"/>
       <c r="O723" s="22"/>
@@ -42473,7 +42641,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="748" spans="1:18" ht="28.8" thickBot="1">
+    <row r="748" spans="1:18" ht="45" customHeight="1" thickBot="1">
       <c r="A748" s="3">
         <v>3</v>
       </c>
@@ -42508,7 +42676,9 @@
       <c r="L748" s="22"/>
       <c r="M748" s="22"/>
       <c r="N748" s="22"/>
-      <c r="O748" s="22"/>
+      <c r="O748" s="27">
+        <v>46232</v>
+      </c>
       <c r="P748" s="22"/>
       <c r="Q748" s="22"/>
       <c r="R748" s="20" t="s">
@@ -42641,7 +42811,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="752" spans="1:18" ht="45" customHeight="1" thickBot="1">
+    <row r="752" spans="1:18" ht="15" thickBot="1">
       <c r="A752" s="3">
         <v>7</v>
       </c>
@@ -45036,7 +45206,9 @@
       <c r="L803" s="22"/>
       <c r="M803" s="22"/>
       <c r="N803" s="22"/>
-      <c r="O803" s="22"/>
+      <c r="O803" s="27">
+        <v>46232</v>
+      </c>
       <c r="P803" s="22"/>
       <c r="Q803" s="22"/>
       <c r="R803" s="25" t="s">
@@ -45700,7 +45872,9 @@
       <c r="N817" s="19">
         <v>514</v>
       </c>
-      <c r="O817" s="22"/>
+      <c r="O817" s="27">
+        <v>46232</v>
+      </c>
       <c r="P817" s="22"/>
       <c r="Q817" s="22"/>
       <c r="R817" s="25" t="s">
@@ -47858,7 +48032,9 @@
       <c r="L864" s="22"/>
       <c r="M864" s="22"/>
       <c r="N864" s="22"/>
-      <c r="O864" s="22"/>
+      <c r="O864" s="27">
+        <v>46232</v>
+      </c>
       <c r="P864" s="22"/>
       <c r="Q864" s="22"/>
       <c r="R864" s="20" t="s">
@@ -48702,7 +48878,9 @@
       <c r="N883" s="19">
         <v>100</v>
       </c>
-      <c r="O883" s="22"/>
+      <c r="O883" s="27">
+        <v>46232</v>
+      </c>
       <c r="P883" s="22"/>
       <c r="Q883" s="22"/>
       <c r="R883" s="34" t="s">
@@ -50542,7 +50720,9 @@
       </c>
       <c r="M923" s="22"/>
       <c r="N923" s="22"/>
-      <c r="O923" s="22"/>
+      <c r="O923" s="27">
+        <v>46232</v>
+      </c>
       <c r="P923" s="22"/>
       <c r="Q923" s="22"/>
       <c r="R923" s="34" t="s">
@@ -53920,7 +54100,9 @@
       <c r="L996" s="22"/>
       <c r="M996" s="22"/>
       <c r="N996" s="22"/>
-      <c r="O996" s="22"/>
+      <c r="O996" s="27">
+        <v>46232</v>
+      </c>
       <c r="P996" s="22"/>
       <c r="Q996" s="22"/>
       <c r="R996" s="34" t="s">
@@ -54008,7 +54190,9 @@
       <c r="L998" s="22"/>
       <c r="M998" s="22"/>
       <c r="N998" s="22"/>
-      <c r="O998" s="22"/>
+      <c r="O998" s="27">
+        <v>46232</v>
+      </c>
       <c r="P998" s="22"/>
       <c r="Q998" s="22"/>
       <c r="R998" s="34" t="s">
@@ -57116,7 +57300,9 @@
       <c r="L1068" s="22"/>
       <c r="M1068" s="22"/>
       <c r="N1068" s="22"/>
-      <c r="O1068" s="22"/>
+      <c r="O1068" s="27">
+        <v>46232</v>
+      </c>
       <c r="P1068" s="22"/>
       <c r="Q1068" s="22"/>
       <c r="R1068" s="34" t="s">
@@ -58958,7 +59144,9 @@
       <c r="L1110" s="22"/>
       <c r="M1110" s="22"/>
       <c r="N1110" s="22"/>
-      <c r="O1110" s="22"/>
+      <c r="O1110" s="27">
+        <v>46232</v>
+      </c>
       <c r="P1110" s="22"/>
       <c r="Q1110" s="22"/>
       <c r="R1110" s="34" t="s">
@@ -59191,43 +59379,43 @@
       <c r="A1116" s="3">
         <v>69</v>
       </c>
-      <c r="B1116" s="108">
+      <c r="B1116" s="14">
         <v>46232</v>
       </c>
-      <c r="C1116" s="109" t="s">
+      <c r="C1116" s="15" t="s">
         <v>1816</v>
       </c>
-      <c r="D1116" s="109" t="s">
+      <c r="D1116" s="15" t="s">
         <v>1817</v>
       </c>
-      <c r="E1116" s="110" t="s">
-        <v>47</v>
-      </c>
-      <c r="F1116" s="111" t="s">
-        <v>48</v>
-      </c>
-      <c r="G1116" s="112">
+      <c r="E1116" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1116" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1116" s="18">
         <v>3921</v>
       </c>
-      <c r="H1116" s="113">
+      <c r="H1116" s="19">
         <v>19183</v>
       </c>
-      <c r="I1116" s="113" t="s">
+      <c r="I1116" s="19" t="s">
         <v>852</v>
       </c>
-      <c r="J1116" s="114" t="s">
+      <c r="J1116" s="23" t="s">
         <v>855</v>
       </c>
-      <c r="K1116" s="115" t="s">
+      <c r="K1116" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="L1116" s="116"/>
-      <c r="M1116" s="116"/>
-      <c r="N1116" s="116"/>
-      <c r="O1116" s="116"/>
-      <c r="P1116" s="116"/>
-      <c r="Q1116" s="116"/>
-      <c r="R1116" s="117" t="s">
+      <c r="L1116" s="22"/>
+      <c r="M1116" s="22"/>
+      <c r="N1116" s="22"/>
+      <c r="O1116" s="22"/>
+      <c r="P1116" s="22"/>
+      <c r="Q1116" s="22"/>
+      <c r="R1116" s="34" t="s">
         <v>900</v>
       </c>
     </row>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B778826-1D43-41A7-B59A-7FE10EE23987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3480259F-0078-4CB7-89E9-47C2032CBE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -56304,7 +56304,9 @@
       <c r="F1046" s="20" t="s">
         <v>847</v>
       </c>
-      <c r="G1046" s="18"/>
+      <c r="G1046" s="18">
+        <v>9262</v>
+      </c>
       <c r="H1046" s="19">
         <v>8278</v>
       </c>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F522A372-D41C-4C05-B5A4-204D74D25463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C99DF33-D18B-484F-A4EC-8D3CCB84F942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8650" uniqueCount="1887">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8683" uniqueCount="1897">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -5696,6 +5696,36 @@
   </si>
   <si>
     <t>SAQALIN</t>
+  </si>
+  <si>
+    <t>554/919</t>
+  </si>
+  <si>
+    <t>832/888</t>
+  </si>
+  <si>
+    <t>234/918</t>
+  </si>
+  <si>
+    <t>EISA SALEH ABDALLAH</t>
+  </si>
+  <si>
+    <t>SALEM SAID SALIM</t>
+  </si>
+  <si>
+    <t>AHMED ABDULLAH</t>
+  </si>
+  <si>
+    <t>8429-</t>
+  </si>
+  <si>
+    <t>SHAHZAD CHEEMA</t>
+  </si>
+  <si>
+    <t>4668-</t>
+  </si>
+  <si>
+    <t>RECEIVED</t>
   </si>
 </sst>
 </file>
@@ -6733,7 +6763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1157"/>
+  <dimension ref="A1:R1161"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -6832,7 +6862,7 @@
         <v>1171</v>
       </c>
       <c r="K2" s="18" t="s">
-        <v>20</v>
+        <v>860</v>
       </c>
       <c r="L2" s="19"/>
       <c r="M2" s="19"/>
@@ -6884,7 +6914,7 @@
         <v>32</v>
       </c>
       <c r="K3" s="23" t="s">
-        <v>1264</v>
+        <v>1896</v>
       </c>
       <c r="L3" s="24">
         <v>46236</v>
@@ -7980,7 +8010,9 @@
         <v>46236</v>
       </c>
       <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
+      <c r="N25" s="16">
+        <v>746</v>
+      </c>
       <c r="O25" s="19"/>
       <c r="P25" s="19"/>
       <c r="Q25" s="12">
@@ -8936,7 +8968,9 @@
         <v>46236</v>
       </c>
       <c r="M45" s="19"/>
-      <c r="N45" s="19"/>
+      <c r="N45" s="16">
+        <v>897</v>
+      </c>
       <c r="O45" s="19"/>
       <c r="P45" s="19"/>
       <c r="Q45" s="12">
@@ -9128,7 +9162,9 @@
         <v>46236</v>
       </c>
       <c r="M49" s="19"/>
-      <c r="N49" s="19"/>
+      <c r="N49" s="16">
+        <v>895</v>
+      </c>
       <c r="O49" s="19"/>
       <c r="P49" s="19"/>
       <c r="Q49" s="12">
@@ -10232,7 +10268,9 @@
       </c>
       <c r="L72" s="19"/>
       <c r="M72" s="19"/>
-      <c r="N72" s="19"/>
+      <c r="N72" s="16">
+        <v>732</v>
+      </c>
       <c r="O72" s="19"/>
       <c r="P72" s="19"/>
       <c r="Q72" s="19"/>
@@ -11184,7 +11222,9 @@
         <v>46236</v>
       </c>
       <c r="M92" s="19"/>
-      <c r="N92" s="19"/>
+      <c r="N92" s="16">
+        <v>738</v>
+      </c>
       <c r="O92" s="19"/>
       <c r="P92" s="19"/>
       <c r="Q92" s="12">
@@ -11324,7 +11364,9 @@
         <v>46236</v>
       </c>
       <c r="M95" s="19"/>
-      <c r="N95" s="19"/>
+      <c r="N95" s="16">
+        <v>740</v>
+      </c>
       <c r="O95" s="19"/>
       <c r="P95" s="19"/>
       <c r="Q95" s="19"/>
@@ -13914,7 +13956,9 @@
         <v>46236</v>
       </c>
       <c r="M147" s="19"/>
-      <c r="N147" s="19"/>
+      <c r="N147" s="16">
+        <v>883</v>
+      </c>
       <c r="O147" s="19"/>
       <c r="P147" s="19"/>
       <c r="Q147" s="12">
@@ -13960,8 +14004,8 @@
         <v>46236</v>
       </c>
       <c r="M148" s="19"/>
-      <c r="N148" s="16">
-        <v>554</v>
+      <c r="N148" s="16" t="s">
+        <v>1887</v>
       </c>
       <c r="O148" s="19"/>
       <c r="P148" s="19"/>
@@ -17376,7 +17420,9 @@
         <v>46236</v>
       </c>
       <c r="M217" s="19"/>
-      <c r="N217" s="19"/>
+      <c r="N217" s="16">
+        <v>730</v>
+      </c>
       <c r="O217" s="19"/>
       <c r="P217" s="19"/>
       <c r="Q217" s="12">
@@ -17424,7 +17470,9 @@
         <v>46236</v>
       </c>
       <c r="M218" s="19"/>
-      <c r="N218" s="19"/>
+      <c r="N218" s="16">
+        <v>729</v>
+      </c>
       <c r="O218" s="19"/>
       <c r="P218" s="19"/>
       <c r="Q218" s="12">
@@ -19618,7 +19666,9 @@
         <v>46236</v>
       </c>
       <c r="M263" s="39"/>
-      <c r="N263" s="19"/>
+      <c r="N263" s="16">
+        <v>923</v>
+      </c>
       <c r="O263" s="39"/>
       <c r="P263" s="39"/>
       <c r="Q263" s="12">
@@ -21238,7 +21288,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="297" spans="1:18" ht="23.4" thickBot="1">
+    <row r="297" spans="1:18" ht="15" thickBot="1">
       <c r="A297" s="4">
         <v>140</v>
       </c>
@@ -23190,7 +23240,9 @@
         <v>46236</v>
       </c>
       <c r="M337" s="19"/>
-      <c r="N337" s="19"/>
+      <c r="N337" s="16">
+        <v>910</v>
+      </c>
       <c r="O337" s="19"/>
       <c r="P337" s="19"/>
       <c r="Q337" s="19"/>
@@ -23236,7 +23288,9 @@
         <v>46236</v>
       </c>
       <c r="M338" s="19"/>
-      <c r="N338" s="19"/>
+      <c r="N338" s="16">
+        <v>909</v>
+      </c>
       <c r="O338" s="19"/>
       <c r="P338" s="19"/>
       <c r="Q338" s="19"/>
@@ -23792,7 +23846,9 @@
         <v>46236</v>
       </c>
       <c r="M350" s="19"/>
-      <c r="N350" s="19"/>
+      <c r="N350" s="16">
+        <v>728</v>
+      </c>
       <c r="O350" s="19"/>
       <c r="P350" s="19"/>
       <c r="Q350" s="12">
@@ -23840,7 +23896,9 @@
         <v>46236</v>
       </c>
       <c r="M351" s="19"/>
-      <c r="N351" s="19"/>
+      <c r="N351" s="16">
+        <v>735</v>
+      </c>
       <c r="O351" s="19"/>
       <c r="P351" s="19"/>
       <c r="Q351" s="12">
@@ -23984,7 +24042,9 @@
         <v>46236</v>
       </c>
       <c r="M354" s="19"/>
-      <c r="N354" s="19"/>
+      <c r="N354" s="16">
+        <v>714</v>
+      </c>
       <c r="O354" s="19"/>
       <c r="P354" s="19"/>
       <c r="Q354" s="12">
@@ -25210,7 +25270,9 @@
         <v>46236</v>
       </c>
       <c r="M379" s="19"/>
-      <c r="N379" s="19"/>
+      <c r="N379" s="16">
+        <v>724</v>
+      </c>
       <c r="O379" s="19"/>
       <c r="P379" s="19"/>
       <c r="Q379" s="12">
@@ -26596,7 +26658,9 @@
         <v>46236</v>
       </c>
       <c r="M407" s="19"/>
-      <c r="N407" s="19"/>
+      <c r="N407" s="16">
+        <v>736</v>
+      </c>
       <c r="O407" s="19"/>
       <c r="P407" s="19"/>
       <c r="Q407" s="12">
@@ -27362,7 +27426,9 @@
         <v>46236</v>
       </c>
       <c r="M423" s="19"/>
-      <c r="N423" s="19"/>
+      <c r="N423" s="16">
+        <v>906</v>
+      </c>
       <c r="O423" s="19"/>
       <c r="P423" s="19"/>
       <c r="Q423" s="12">
@@ -28928,7 +28994,9 @@
         <v>46237</v>
       </c>
       <c r="M456" s="19"/>
-      <c r="N456" s="19"/>
+      <c r="N456" s="16">
+        <v>719</v>
+      </c>
       <c r="O456" s="19"/>
       <c r="P456" s="19"/>
       <c r="Q456" s="12">
@@ -29424,7 +29492,9 @@
         <v>46237</v>
       </c>
       <c r="M466" s="19"/>
-      <c r="N466" s="19"/>
+      <c r="N466" s="16">
+        <v>725</v>
+      </c>
       <c r="O466" s="19"/>
       <c r="P466" s="19"/>
       <c r="Q466" s="12">
@@ -30316,7 +30386,9 @@
         <v>46237</v>
       </c>
       <c r="M484" s="19"/>
-      <c r="N484" s="19"/>
+      <c r="N484" s="16">
+        <v>727</v>
+      </c>
       <c r="O484" s="19"/>
       <c r="P484" s="19"/>
       <c r="Q484" s="12">
@@ -31100,7 +31172,9 @@
         <v>46237</v>
       </c>
       <c r="M500" s="19"/>
-      <c r="N500" s="19"/>
+      <c r="N500" s="16">
+        <v>911</v>
+      </c>
       <c r="O500" s="19"/>
       <c r="P500" s="19"/>
       <c r="Q500" s="19"/>
@@ -31330,7 +31404,9 @@
       </c>
       <c r="L505" s="19"/>
       <c r="M505" s="19"/>
-      <c r="N505" s="19"/>
+      <c r="N505" s="16">
+        <v>924</v>
+      </c>
       <c r="O505" s="19"/>
       <c r="P505" s="19"/>
       <c r="Q505" s="19"/>
@@ -32836,7 +32912,9 @@
         <v>46236</v>
       </c>
       <c r="M536" s="19"/>
-      <c r="N536" s="19"/>
+      <c r="N536" s="16">
+        <v>894</v>
+      </c>
       <c r="O536" s="19"/>
       <c r="P536" s="19"/>
       <c r="Q536" s="12">
@@ -34450,7 +34528,9 @@
         <v>46236</v>
       </c>
       <c r="M569" s="19"/>
-      <c r="N569" s="19"/>
+      <c r="N569" s="16">
+        <v>902</v>
+      </c>
       <c r="O569" s="19"/>
       <c r="P569" s="19"/>
       <c r="Q569" s="12">
@@ -34498,7 +34578,9 @@
         <v>46236</v>
       </c>
       <c r="M570" s="19"/>
-      <c r="N570" s="19"/>
+      <c r="N570" s="16">
+        <v>901</v>
+      </c>
       <c r="O570" s="19"/>
       <c r="P570" s="19"/>
       <c r="Q570" s="12">
@@ -35338,8 +35420,8 @@
         <v>46236</v>
       </c>
       <c r="M588" s="19"/>
-      <c r="N588" s="16">
-        <v>832</v>
+      <c r="N588" s="16" t="s">
+        <v>1888</v>
       </c>
       <c r="O588" s="19"/>
       <c r="P588" s="19"/>
@@ -35530,7 +35612,9 @@
         <v>46236</v>
       </c>
       <c r="M592" s="19"/>
-      <c r="N592" s="19"/>
+      <c r="N592" s="16">
+        <v>884</v>
+      </c>
       <c r="O592" s="19"/>
       <c r="P592" s="19"/>
       <c r="Q592" s="19"/>
@@ -35576,7 +35660,9 @@
         <v>46232</v>
       </c>
       <c r="M593" s="19"/>
-      <c r="N593" s="19"/>
+      <c r="N593" s="16">
+        <v>892</v>
+      </c>
       <c r="O593" s="19"/>
       <c r="P593" s="19"/>
       <c r="Q593" s="19"/>
@@ -35622,7 +35708,9 @@
         <v>46236</v>
       </c>
       <c r="M594" s="16"/>
-      <c r="N594" s="19"/>
+      <c r="N594" s="16">
+        <v>896</v>
+      </c>
       <c r="O594" s="19"/>
       <c r="P594" s="19"/>
       <c r="Q594" s="19"/>
@@ -37434,7 +37522,9 @@
         <v>46236</v>
       </c>
       <c r="M632" s="19"/>
-      <c r="N632" s="19"/>
+      <c r="N632" s="16">
+        <v>743</v>
+      </c>
       <c r="O632" s="24">
         <v>46231</v>
       </c>
@@ -37484,7 +37574,9 @@
         <v>46236</v>
       </c>
       <c r="M633" s="19"/>
-      <c r="N633" s="19"/>
+      <c r="N633" s="16">
+        <v>744</v>
+      </c>
       <c r="O633" s="19"/>
       <c r="P633" s="19"/>
       <c r="Q633" s="12">
@@ -39128,7 +39220,9 @@
         <v>46237</v>
       </c>
       <c r="M667" s="19"/>
-      <c r="N667" s="19"/>
+      <c r="N667" s="16">
+        <v>723</v>
+      </c>
       <c r="O667" s="19"/>
       <c r="P667" s="19"/>
       <c r="Q667" s="19"/>
@@ -39270,7 +39364,9 @@
         <v>46237</v>
       </c>
       <c r="M670" s="19"/>
-      <c r="N670" s="19"/>
+      <c r="N670" s="16">
+        <v>737</v>
+      </c>
       <c r="O670" s="19"/>
       <c r="P670" s="19"/>
       <c r="Q670" s="19"/>
@@ -39608,7 +39704,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="678" spans="1:18" ht="40.799999999999997" thickBot="1">
+    <row r="678" spans="1:18" ht="27.6" thickBot="1">
       <c r="A678" s="4">
         <v>246</v>
       </c>
@@ -39780,7 +39876,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="682" spans="1:18" ht="27.6" thickBot="1">
+    <row r="682" spans="1:18" ht="15" thickBot="1">
       <c r="A682" s="4">
         <v>250</v>
       </c>
@@ -40620,7 +40716,9 @@
         <v>46237</v>
       </c>
       <c r="M700" s="19"/>
-      <c r="N700" s="19"/>
+      <c r="N700" s="16">
+        <v>928</v>
+      </c>
       <c r="O700" s="19"/>
       <c r="P700" s="19"/>
       <c r="Q700" s="19"/>
@@ -40758,7 +40856,9 @@
         <v>46237</v>
       </c>
       <c r="M703" s="19"/>
-      <c r="N703" s="19"/>
+      <c r="N703" s="16">
+        <v>929</v>
+      </c>
       <c r="O703" s="19"/>
       <c r="P703" s="19"/>
       <c r="Q703" s="19"/>
@@ -42248,7 +42348,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="736" spans="1:18" ht="28.8" thickBot="1">
+    <row r="736" spans="1:18" ht="45" customHeight="1" thickBot="1">
       <c r="A736" s="2">
         <v>5</v>
       </c>
@@ -42418,7 +42518,9 @@
         <v>46237</v>
       </c>
       <c r="M739" s="19"/>
-      <c r="N739" s="19"/>
+      <c r="N739" s="16">
+        <v>898</v>
+      </c>
       <c r="O739" s="19"/>
       <c r="P739" s="19"/>
       <c r="Q739" s="19"/>
@@ -42426,7 +42528,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="740" spans="1:18" ht="45" customHeight="1" thickBot="1">
+    <row r="740" spans="1:18" ht="15" thickBot="1">
       <c r="A740" s="2">
         <v>9</v>
       </c>
@@ -42462,7 +42564,9 @@
         <v>46237</v>
       </c>
       <c r="M740" s="19"/>
-      <c r="N740" s="19"/>
+      <c r="N740" s="16">
+        <v>899</v>
+      </c>
       <c r="O740" s="19"/>
       <c r="P740" s="19"/>
       <c r="Q740" s="19"/>
@@ -43100,7 +43204,9 @@
         <v>46237</v>
       </c>
       <c r="M754" s="19"/>
-      <c r="N754" s="19"/>
+      <c r="N754" s="16">
+        <v>726</v>
+      </c>
       <c r="O754" s="19"/>
       <c r="P754" s="19"/>
       <c r="Q754" s="12" t="s">
@@ -44088,7 +44194,9 @@
         <v>46237</v>
       </c>
       <c r="M775" s="19"/>
-      <c r="N775" s="19"/>
+      <c r="N775" s="16">
+        <v>731</v>
+      </c>
       <c r="O775" s="19"/>
       <c r="P775" s="19"/>
       <c r="Q775" s="12">
@@ -44828,7 +44936,9 @@
         <v>46237</v>
       </c>
       <c r="M791" s="19"/>
-      <c r="N791" s="19"/>
+      <c r="N791" s="16">
+        <v>718</v>
+      </c>
       <c r="O791" s="19"/>
       <c r="P791" s="19"/>
       <c r="Q791" s="19"/>
@@ -45208,7 +45318,9 @@
         <v>46237</v>
       </c>
       <c r="M799" s="19"/>
-      <c r="N799" s="19"/>
+      <c r="N799" s="16">
+        <v>734</v>
+      </c>
       <c r="O799" s="19"/>
       <c r="P799" s="19"/>
       <c r="Q799" s="12">
@@ -45256,7 +45368,9 @@
         <v>46237</v>
       </c>
       <c r="M800" s="19"/>
-      <c r="N800" s="19"/>
+      <c r="N800" s="16">
+        <v>733</v>
+      </c>
       <c r="O800" s="19"/>
       <c r="P800" s="19"/>
       <c r="Q800" s="19"/>
@@ -47182,7 +47296,9 @@
       </c>
       <c r="L841" s="19"/>
       <c r="M841" s="19"/>
-      <c r="N841" s="19"/>
+      <c r="N841" s="16">
+        <v>717</v>
+      </c>
       <c r="O841" s="19"/>
       <c r="P841" s="19"/>
       <c r="Q841" s="19"/>
@@ -47968,7 +48084,9 @@
       </c>
       <c r="L859" s="19"/>
       <c r="M859" s="19"/>
-      <c r="N859" s="19"/>
+      <c r="N859" s="16">
+        <v>905</v>
+      </c>
       <c r="O859" s="19"/>
       <c r="P859" s="19"/>
       <c r="Q859" s="19"/>
@@ -48050,7 +48168,9 @@
         <v>46237</v>
       </c>
       <c r="M861" s="19"/>
-      <c r="N861" s="19"/>
+      <c r="N861" s="16">
+        <v>904</v>
+      </c>
       <c r="O861" s="19"/>
       <c r="P861" s="19"/>
       <c r="Q861" s="19"/>
@@ -48092,7 +48212,9 @@
         <v>46238</v>
       </c>
       <c r="M862" s="19"/>
-      <c r="N862" s="19"/>
+      <c r="N862" s="16">
+        <v>915</v>
+      </c>
       <c r="O862" s="19"/>
       <c r="P862" s="19"/>
       <c r="Q862" s="19"/>
@@ -49108,7 +49230,9 @@
         <v>46237</v>
       </c>
       <c r="M884" s="19"/>
-      <c r="N884" s="19"/>
+      <c r="N884" s="16">
+        <v>887</v>
+      </c>
       <c r="O884" s="19"/>
       <c r="P884" s="19"/>
       <c r="Q884" s="19"/>
@@ -49894,7 +50018,9 @@
         <v>46237</v>
       </c>
       <c r="M901" s="19"/>
-      <c r="N901" s="19"/>
+      <c r="N901" s="16">
+        <v>886</v>
+      </c>
       <c r="O901" s="19"/>
       <c r="P901" s="19"/>
       <c r="Q901" s="19"/>
@@ -50908,8 +51034,8 @@
         <v>46237</v>
       </c>
       <c r="M923" s="19"/>
-      <c r="N923" s="16">
-        <v>234</v>
+      <c r="N923" s="16" t="s">
+        <v>1889</v>
       </c>
       <c r="O923" s="19"/>
       <c r="P923" s="19"/>
@@ -51514,7 +51640,9 @@
         <v>46237</v>
       </c>
       <c r="M936" s="19"/>
-      <c r="N936" s="19"/>
+      <c r="N936" s="16">
+        <v>893</v>
+      </c>
       <c r="O936" s="19"/>
       <c r="P936" s="19"/>
       <c r="Q936" s="19"/>
@@ -51560,7 +51688,9 @@
         <v>46237</v>
       </c>
       <c r="M937" s="19"/>
-      <c r="N937" s="19"/>
+      <c r="N937" s="16">
+        <v>890</v>
+      </c>
       <c r="O937" s="19"/>
       <c r="P937" s="19"/>
       <c r="Q937" s="19"/>
@@ -51606,7 +51736,9 @@
         <v>46237</v>
       </c>
       <c r="M938" s="19"/>
-      <c r="N938" s="19"/>
+      <c r="N938" s="16">
+        <v>891</v>
+      </c>
       <c r="O938" s="19"/>
       <c r="P938" s="19"/>
       <c r="Q938" s="19"/>
@@ -51942,7 +52074,9 @@
         <v>46232</v>
       </c>
       <c r="M945" s="19"/>
-      <c r="N945" s="19"/>
+      <c r="N945" s="16">
+        <v>741</v>
+      </c>
       <c r="O945" s="19"/>
       <c r="P945" s="19"/>
       <c r="Q945" s="19"/>
@@ -56398,7 +56532,9 @@
       </c>
       <c r="L1042" s="19"/>
       <c r="M1042" s="19"/>
-      <c r="N1042" s="19"/>
+      <c r="N1042" s="16">
+        <v>889</v>
+      </c>
       <c r="O1042" s="19"/>
       <c r="P1042" s="19"/>
       <c r="Q1042" s="19"/>
@@ -56440,7 +56576,9 @@
       </c>
       <c r="L1043" s="19"/>
       <c r="M1043" s="19"/>
-      <c r="N1043" s="19"/>
+      <c r="N1043" s="16">
+        <v>885</v>
+      </c>
       <c r="O1043" s="19"/>
       <c r="P1043" s="19"/>
       <c r="Q1043" s="19"/>
@@ -57718,7 +57856,9 @@
       </c>
       <c r="L1071" s="19"/>
       <c r="M1071" s="19"/>
-      <c r="N1071" s="19"/>
+      <c r="N1071" s="16">
+        <v>908</v>
+      </c>
       <c r="O1071" s="19"/>
       <c r="P1071" s="19"/>
       <c r="Q1071" s="12">
@@ -57762,7 +57902,9 @@
       </c>
       <c r="L1072" s="19"/>
       <c r="M1072" s="19"/>
-      <c r="N1072" s="19"/>
+      <c r="N1072" s="16">
+        <v>907</v>
+      </c>
       <c r="O1072" s="19"/>
       <c r="P1072" s="19"/>
       <c r="Q1072" s="12">
@@ -58358,7 +58500,9 @@
         <v>46238</v>
       </c>
       <c r="M1085" s="19"/>
-      <c r="N1085" s="19"/>
+      <c r="N1085" s="16">
+        <v>900</v>
+      </c>
       <c r="O1085" s="19"/>
       <c r="P1085" s="19"/>
       <c r="Q1085" s="19"/>
@@ -58404,7 +58548,9 @@
         <v>46238</v>
       </c>
       <c r="M1086" s="19"/>
-      <c r="N1086" s="19"/>
+      <c r="N1086" s="16">
+        <v>926</v>
+      </c>
       <c r="O1086" s="19"/>
       <c r="P1086" s="19"/>
       <c r="Q1086" s="19"/>
@@ -58448,7 +58594,9 @@
         <v>46238</v>
       </c>
       <c r="M1087" s="19"/>
-      <c r="N1087" s="19"/>
+      <c r="N1087" s="16">
+        <v>925</v>
+      </c>
       <c r="O1087" s="19"/>
       <c r="P1087" s="19"/>
       <c r="Q1087" s="19"/>
@@ -58494,7 +58642,9 @@
         <v>46238</v>
       </c>
       <c r="M1088" s="19"/>
-      <c r="N1088" s="19"/>
+      <c r="N1088" s="16">
+        <v>927</v>
+      </c>
       <c r="O1088" s="19"/>
       <c r="P1088" s="19"/>
       <c r="Q1088" s="19"/>
@@ -60148,7 +60298,9 @@
       </c>
       <c r="L1125" s="19"/>
       <c r="M1125" s="19"/>
-      <c r="N1125" s="19"/>
+      <c r="N1125" s="16">
+        <v>716</v>
+      </c>
       <c r="O1125" s="19"/>
       <c r="P1125" s="19"/>
       <c r="Q1125" s="19"/>
@@ -60192,7 +60344,9 @@
       </c>
       <c r="L1126" s="19"/>
       <c r="M1126" s="19"/>
-      <c r="N1126" s="19"/>
+      <c r="N1126" s="16">
+        <v>715</v>
+      </c>
       <c r="O1126" s="19"/>
       <c r="P1126" s="19"/>
       <c r="Q1126" s="19"/>
@@ -60588,7 +60742,9 @@
       </c>
       <c r="L1135" s="19"/>
       <c r="M1135" s="19"/>
-      <c r="N1135" s="19"/>
+      <c r="N1135" s="16">
+        <v>917</v>
+      </c>
       <c r="O1135" s="19"/>
       <c r="P1135" s="19"/>
       <c r="Q1135" s="19"/>
@@ -60974,7 +61130,9 @@
       </c>
       <c r="L1144" s="19"/>
       <c r="M1144" s="19"/>
-      <c r="N1144" s="19"/>
+      <c r="N1144" s="16">
+        <v>930</v>
+      </c>
       <c r="O1144" s="19"/>
       <c r="P1144" s="19"/>
       <c r="Q1144" s="19"/>
@@ -61018,7 +61176,9 @@
       </c>
       <c r="L1145" s="19"/>
       <c r="M1145" s="19"/>
-      <c r="N1145" s="19"/>
+      <c r="N1145" s="16">
+        <v>913</v>
+      </c>
       <c r="O1145" s="19"/>
       <c r="P1145" s="19"/>
       <c r="Q1145" s="19"/>
@@ -61062,7 +61222,9 @@
       </c>
       <c r="L1146" s="19"/>
       <c r="M1146" s="19"/>
-      <c r="N1146" s="19"/>
+      <c r="N1146" s="16">
+        <v>912</v>
+      </c>
       <c r="O1146" s="19"/>
       <c r="P1146" s="19"/>
       <c r="Q1146" s="19"/>
@@ -61106,7 +61268,9 @@
       </c>
       <c r="L1147" s="19"/>
       <c r="M1147" s="19"/>
-      <c r="N1147" s="19"/>
+      <c r="N1147" s="16">
+        <v>914</v>
+      </c>
       <c r="O1147" s="19"/>
       <c r="P1147" s="19"/>
       <c r="Q1147" s="19"/>
@@ -61148,7 +61312,9 @@
       </c>
       <c r="L1148" s="19"/>
       <c r="M1148" s="19"/>
-      <c r="N1148" s="19"/>
+      <c r="N1148" s="16">
+        <v>931</v>
+      </c>
       <c r="O1148" s="19"/>
       <c r="P1148" s="19"/>
       <c r="Q1148" s="19"/>
@@ -61236,7 +61402,9 @@
       </c>
       <c r="L1150" s="19"/>
       <c r="M1150" s="19"/>
-      <c r="N1150" s="19"/>
+      <c r="N1150" s="16">
+        <v>921</v>
+      </c>
       <c r="O1150" s="19"/>
       <c r="P1150" s="19"/>
       <c r="Q1150" s="19"/>
@@ -61280,7 +61448,9 @@
       </c>
       <c r="L1151" s="19"/>
       <c r="M1151" s="19"/>
-      <c r="N1151" s="19"/>
+      <c r="N1151" s="16">
+        <v>916</v>
+      </c>
       <c r="O1151" s="19"/>
       <c r="P1151" s="19"/>
       <c r="Q1151" s="19"/>
@@ -61324,7 +61494,9 @@
       </c>
       <c r="L1152" s="19"/>
       <c r="M1152" s="19"/>
-      <c r="N1152" s="19"/>
+      <c r="N1152" s="16">
+        <v>922</v>
+      </c>
       <c r="O1152" s="19"/>
       <c r="P1152" s="19"/>
       <c r="Q1152" s="19"/>
@@ -61368,7 +61540,9 @@
       </c>
       <c r="L1153" s="19"/>
       <c r="M1153" s="19"/>
-      <c r="N1153" s="19"/>
+      <c r="N1153" s="16">
+        <v>920</v>
+      </c>
       <c r="O1153" s="19"/>
       <c r="P1153" s="19"/>
       <c r="Q1153" s="19"/>
@@ -61546,6 +61720,180 @@
         <v>1183</v>
       </c>
     </row>
+    <row r="1158" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1158" s="2">
+        <v>54</v>
+      </c>
+      <c r="B1158" s="11">
+        <v>46233</v>
+      </c>
+      <c r="C1158" s="12" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D1158" s="12">
+        <v>19112022</v>
+      </c>
+      <c r="E1158" s="76" t="s">
+        <v>819</v>
+      </c>
+      <c r="F1158" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="G1158" s="15">
+        <v>1670</v>
+      </c>
+      <c r="H1158" s="19"/>
+      <c r="I1158" s="16" t="s">
+        <v>825</v>
+      </c>
+      <c r="J1158" s="20" t="s">
+        <v>858</v>
+      </c>
+      <c r="K1158" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1158" s="19"/>
+      <c r="M1158" s="19"/>
+      <c r="N1158" s="19"/>
+      <c r="O1158" s="19"/>
+      <c r="P1158" s="19"/>
+      <c r="Q1158" s="19"/>
+      <c r="R1158" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1159" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1159" s="11">
+        <v>46233</v>
+      </c>
+      <c r="C1159" s="12" t="s">
+        <v>1891</v>
+      </c>
+      <c r="D1159" s="12">
+        <v>19627498</v>
+      </c>
+      <c r="E1159" s="76" t="s">
+        <v>819</v>
+      </c>
+      <c r="F1159" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="G1159" s="15">
+        <v>5720</v>
+      </c>
+      <c r="H1159" s="16">
+        <v>1805</v>
+      </c>
+      <c r="I1159" s="16" t="s">
+        <v>825</v>
+      </c>
+      <c r="J1159" s="20" t="s">
+        <v>858</v>
+      </c>
+      <c r="K1159" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1159" s="19"/>
+      <c r="M1159" s="19"/>
+      <c r="N1159" s="19"/>
+      <c r="O1159" s="19"/>
+      <c r="P1159" s="19"/>
+      <c r="Q1159" s="19"/>
+      <c r="R1159" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1160" s="2">
+        <v>56</v>
+      </c>
+      <c r="B1160" s="11">
+        <v>46233</v>
+      </c>
+      <c r="C1160" s="12" t="s">
+        <v>1892</v>
+      </c>
+      <c r="D1160" s="12">
+        <v>13681887</v>
+      </c>
+      <c r="E1160" s="76" t="s">
+        <v>819</v>
+      </c>
+      <c r="F1160" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="G1160" s="15">
+        <v>281</v>
+      </c>
+      <c r="H1160" s="16" t="s">
+        <v>1893</v>
+      </c>
+      <c r="I1160" s="16" t="s">
+        <v>825</v>
+      </c>
+      <c r="J1160" s="20" t="s">
+        <v>1409</v>
+      </c>
+      <c r="K1160" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1160" s="19"/>
+      <c r="M1160" s="19"/>
+      <c r="N1160" s="19"/>
+      <c r="O1160" s="19"/>
+      <c r="P1160" s="19"/>
+      <c r="Q1160" s="19"/>
+      <c r="R1160" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:18" ht="15" thickBot="1">
+      <c r="A1161" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1161" s="11">
+        <v>46233</v>
+      </c>
+      <c r="C1161" s="12" t="s">
+        <v>1894</v>
+      </c>
+      <c r="D1161" s="12">
+        <v>102315974</v>
+      </c>
+      <c r="E1161" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1161" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="G1161" s="15">
+        <v>3633</v>
+      </c>
+      <c r="H1161" s="16" t="s">
+        <v>1895</v>
+      </c>
+      <c r="I1161" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1161" s="71" t="s">
+        <v>848</v>
+      </c>
+      <c r="K1161" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1161" s="19"/>
+      <c r="M1161" s="19"/>
+      <c r="N1161" s="19"/>
+      <c r="O1161" s="19"/>
+      <c r="P1161" s="19"/>
+      <c r="Q1161" s="19"/>
+      <c r="R1161" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2240C9D-4457-41CA-BFE6-E43D54F8D4B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0012D5-9C03-467C-8BC4-6A2D5EB334C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$K$1:$K$1180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$K$1:$K$1174</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9263" uniqueCount="1993">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9504" uniqueCount="2040">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -6017,6 +6017,147 @@
   </si>
   <si>
     <t>R/NIYAS ALI</t>
+  </si>
+  <si>
+    <t>R/AKASH</t>
+  </si>
+  <si>
+    <t>SHAHEN SHEH</t>
+  </si>
+  <si>
+    <t>KHAN ATTAULLAH</t>
+  </si>
+  <si>
+    <t>DP4139137</t>
+  </si>
+  <si>
+    <t>USMAN MUHAMMAD</t>
+  </si>
+  <si>
+    <t>BT2853836</t>
+  </si>
+  <si>
+    <t>BK1201855</t>
+  </si>
+  <si>
+    <t>ABBAS ZAHEER</t>
+  </si>
+  <si>
+    <t>HA1016504</t>
+  </si>
+  <si>
+    <t>FIAZMINHAS</t>
+  </si>
+  <si>
+    <t>AMIR ZEB</t>
+  </si>
+  <si>
+    <t>ZEDRAZA</t>
+  </si>
+  <si>
+    <t>AMIN AFTAB</t>
+  </si>
+  <si>
+    <t>EF1204823</t>
+  </si>
+  <si>
+    <t>HAIDER ZEESHAN</t>
+  </si>
+  <si>
+    <t>ES6975432</t>
+  </si>
+  <si>
+    <t>LP1223643</t>
+  </si>
+  <si>
+    <t>ARIF HUSIAN</t>
+  </si>
+  <si>
+    <t>ALI MURTAZA</t>
+  </si>
+  <si>
+    <t>USMAN RASOOL</t>
+  </si>
+  <si>
+    <t>Z5217183</t>
+  </si>
+  <si>
+    <t>SALMAN KHAN</t>
+  </si>
+  <si>
+    <t>ZA452264</t>
+  </si>
+  <si>
+    <t>22013-</t>
+  </si>
+  <si>
+    <t>NAEEM AKRAM</t>
+  </si>
+  <si>
+    <t>IQRAR HASSAN</t>
+  </si>
+  <si>
+    <t>ZEESHAN KHAN</t>
+  </si>
+  <si>
+    <t>P9442114</t>
+  </si>
+  <si>
+    <t>VANSH</t>
+  </si>
+  <si>
+    <t>B9155696</t>
+  </si>
+  <si>
+    <t>JOBANPREET</t>
+  </si>
+  <si>
+    <t>Z5409968</t>
+  </si>
+  <si>
+    <t>53457-</t>
+  </si>
+  <si>
+    <t>AWAIS HABIB</t>
+  </si>
+  <si>
+    <t>BQ6032723</t>
+  </si>
+  <si>
+    <t>ARSLAN ALI</t>
+  </si>
+  <si>
+    <t>MW1815653</t>
+  </si>
+  <si>
+    <t>LW9895383</t>
+  </si>
+  <si>
+    <t>AFZAL</t>
+  </si>
+  <si>
+    <t>6432-</t>
+  </si>
+  <si>
+    <t>LIAQAT KHAN</t>
+  </si>
+  <si>
+    <t>MUHAMMAD JAMIL KHAN</t>
+  </si>
+  <si>
+    <t>ABDULLAH JAMDAD KHAN</t>
+  </si>
+  <si>
+    <t>RASHID MAHMOOD</t>
+  </si>
+  <si>
+    <t>HF0154283</t>
+  </si>
+  <si>
+    <t>ASIF HUSSAIN CORAYA</t>
+  </si>
+  <si>
+    <t>EH6179654</t>
   </si>
 </sst>
 </file>
@@ -6420,7 +6561,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6746,6 +6887,21 @@
     <xf numFmtId="0" fontId="29" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7060,7 +7216,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1234"/>
+  <dimension ref="A1:R1268"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -7128,9 +7284,7 @@
       <c r="R1" s="5"/>
     </row>
     <row r="2" spans="1:18" ht="28.2" thickBot="1">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
+      <c r="A2" s="2"/>
       <c r="B2" s="11">
         <v>46227</v>
       </c>
@@ -23721,9 +23875,7 @@
       <c r="G338" s="15">
         <v>425</v>
       </c>
-      <c r="H338" s="16">
-        <v>3418</v>
-      </c>
+      <c r="H338" s="19"/>
       <c r="I338" s="17" t="s">
         <v>11</v>
       </c>
@@ -26714,7 +26866,7 @@
         <v>421</v>
       </c>
       <c r="D399" s="12">
-        <v>111637321</v>
+        <v>11163</v>
       </c>
       <c r="E399" s="13" t="s">
         <v>47</v>
@@ -32307,7 +32459,7 @@
       <c r="O513" s="19"/>
       <c r="P513" s="19"/>
       <c r="Q513" s="12">
-        <v>78473214</v>
+        <v>7844</v>
       </c>
       <c r="R513" s="25" t="s">
         <v>24</v>
@@ -38925,7 +39077,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="650" spans="1:18" ht="15" thickBot="1">
+    <row r="650" spans="1:18" ht="28.2" thickBot="1">
       <c r="A650" s="4">
         <v>219</v>
       </c>
@@ -38950,11 +39102,11 @@
       <c r="H650" s="16">
         <v>67714</v>
       </c>
-      <c r="I650" s="31" t="s">
-        <v>823</v>
-      </c>
-      <c r="J650" s="30" t="s">
-        <v>827</v>
+      <c r="I650" s="16" t="s">
+        <v>825</v>
+      </c>
+      <c r="J650" s="16" t="s">
+        <v>1993</v>
       </c>
       <c r="K650" s="23" t="s">
         <v>1262</v>
@@ -38973,7 +39125,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="651" spans="1:18" ht="15" thickBot="1">
+    <row r="651" spans="1:18" ht="28.2" thickBot="1">
       <c r="A651" s="4">
         <v>220</v>
       </c>
@@ -38998,11 +39150,11 @@
       <c r="H651" s="16">
         <v>74584</v>
       </c>
-      <c r="I651" s="31" t="s">
-        <v>823</v>
-      </c>
-      <c r="J651" s="30" t="s">
-        <v>827</v>
+      <c r="I651" s="16" t="s">
+        <v>825</v>
+      </c>
+      <c r="J651" s="16" t="s">
+        <v>1993</v>
       </c>
       <c r="K651" s="23" t="s">
         <v>1262</v>
@@ -39021,7 +39173,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="652" spans="1:18" ht="15" thickBot="1">
+    <row r="652" spans="1:18" ht="28.2" thickBot="1">
       <c r="A652" s="4">
         <v>221</v>
       </c>
@@ -39046,11 +39198,11 @@
       <c r="H652" s="16">
         <v>74584</v>
       </c>
-      <c r="I652" s="31" t="s">
-        <v>823</v>
-      </c>
-      <c r="J652" s="30" t="s">
-        <v>827</v>
+      <c r="I652" s="16" t="s">
+        <v>825</v>
+      </c>
+      <c r="J652" s="16" t="s">
+        <v>1993</v>
       </c>
       <c r="K652" s="23" t="s">
         <v>1262</v>
@@ -42391,7 +42543,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="723" spans="1:18" ht="15" thickBot="1">
+    <row r="723" spans="1:18" ht="45" customHeight="1" thickBot="1">
       <c r="A723" s="4">
         <v>292</v>
       </c>
@@ -42523,7 +42675,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="726" spans="1:18" ht="45" customHeight="1" thickBot="1">
+    <row r="726" spans="1:18" ht="15" thickBot="1">
       <c r="A726" s="4">
         <v>295</v>
       </c>
@@ -47884,7 +48036,7 @@
         <v>1357</v>
       </c>
       <c r="D839" s="94">
-        <v>73212693</v>
+        <v>2693</v>
       </c>
       <c r="E839" s="76" t="s">
         <v>819</v>
@@ -60470,8 +60622,8 @@
       <c r="J1109" s="16" t="s">
         <v>1796</v>
       </c>
-      <c r="K1109" s="18" t="s">
-        <v>20</v>
+      <c r="K1109" s="42" t="s">
+        <v>1520</v>
       </c>
       <c r="L1109" s="19"/>
       <c r="M1109" s="19"/>
@@ -65381,7 +65533,9 @@
       <c r="O1217" s="19"/>
       <c r="P1217" s="19"/>
       <c r="Q1217" s="19"/>
-      <c r="R1217" s="19"/>
+      <c r="R1217" s="22" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="1218" spans="1:18" ht="15" thickBot="1">
       <c r="A1218" s="2">
@@ -65391,40 +65545,40 @@
         <v>46234</v>
       </c>
       <c r="C1218" s="12" t="s">
-        <v>1947</v>
+        <v>1994</v>
       </c>
       <c r="D1218" s="12">
-        <v>113961322</v>
-      </c>
-      <c r="E1218" s="44" t="s">
-        <v>815</v>
+        <v>71572946</v>
+      </c>
+      <c r="E1218" s="13" t="s">
+        <v>47</v>
       </c>
       <c r="F1218" s="17" t="s">
         <v>820</v>
       </c>
       <c r="G1218" s="15">
-        <v>6707</v>
+        <v>2872</v>
       </c>
       <c r="H1218" s="16">
-        <v>3130</v>
+        <v>4158</v>
       </c>
       <c r="I1218" s="17" t="s">
         <v>11</v>
       </c>
       <c r="J1218" s="16" t="s">
-        <v>1259</v>
-      </c>
-      <c r="K1218" s="19"/>
+        <v>845</v>
+      </c>
+      <c r="K1218" s="18" t="s">
+        <v>20</v>
+      </c>
       <c r="L1218" s="19"/>
       <c r="M1218" s="19"/>
       <c r="N1218" s="19"/>
       <c r="O1218" s="19"/>
-      <c r="P1218" s="59" t="s">
-        <v>1948</v>
-      </c>
+      <c r="P1218" s="19"/>
       <c r="Q1218" s="19"/>
-      <c r="R1218" s="25" t="s">
-        <v>24</v>
+      <c r="R1218" s="22" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="1219" spans="1:18" ht="28.2" thickBot="1">
@@ -65435,38 +65589,42 @@
         <v>46234</v>
       </c>
       <c r="C1219" s="12" t="s">
-        <v>1949</v>
-      </c>
-      <c r="D1219" s="12">
-        <v>121436929</v>
+        <v>1995</v>
+      </c>
+      <c r="D1219" s="12" t="s">
+        <v>1996</v>
       </c>
       <c r="E1219" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="F1219" s="17" t="s">
-        <v>820</v>
+      <c r="F1219" s="14" t="s">
+        <v>48</v>
       </c>
       <c r="G1219" s="15">
-        <v>227</v>
+        <v>53599</v>
       </c>
       <c r="H1219" s="16">
-        <v>7508</v>
-      </c>
-      <c r="I1219" s="16" t="s">
-        <v>825</v>
-      </c>
-      <c r="J1219" s="19"/>
-      <c r="K1219" s="43" t="s">
-        <v>860</v>
+        <v>29656</v>
+      </c>
+      <c r="I1219" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1219" s="16" t="s">
+        <v>1406</v>
+      </c>
+      <c r="K1219" s="18" t="s">
+        <v>20</v>
       </c>
       <c r="L1219" s="19"/>
       <c r="M1219" s="19"/>
       <c r="N1219" s="19"/>
       <c r="O1219" s="19"/>
       <c r="P1219" s="19"/>
-      <c r="Q1219" s="19"/>
-      <c r="R1219" s="31" t="s">
-        <v>873</v>
+      <c r="Q1219" s="12">
+        <v>525986225</v>
+      </c>
+      <c r="R1219" s="22" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="1220" spans="1:18" ht="28.2" thickBot="1">
@@ -65477,29 +65635,31 @@
         <v>46234</v>
       </c>
       <c r="C1220" s="12" t="s">
-        <v>1634</v>
-      </c>
-      <c r="D1220" s="12">
-        <v>77733982</v>
+        <v>1997</v>
+      </c>
+      <c r="D1220" s="12" t="s">
+        <v>1998</v>
       </c>
       <c r="E1220" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="F1220" s="17" t="s">
-        <v>820</v>
+      <c r="F1220" s="14" t="s">
+        <v>48</v>
       </c>
       <c r="G1220" s="15">
-        <v>4513</v>
+        <v>19947</v>
       </c>
       <c r="H1220" s="16">
-        <v>2267</v>
-      </c>
-      <c r="I1220" s="16" t="s">
-        <v>825</v>
-      </c>
-      <c r="J1220" s="19"/>
-      <c r="K1220" s="43" t="s">
-        <v>860</v>
+        <v>39550</v>
+      </c>
+      <c r="I1220" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1220" s="16" t="s">
+        <v>1406</v>
+      </c>
+      <c r="K1220" s="18" t="s">
+        <v>20</v>
       </c>
       <c r="L1220" s="19"/>
       <c r="M1220" s="19"/>
@@ -65507,8 +65667,8 @@
       <c r="O1220" s="19"/>
       <c r="P1220" s="19"/>
       <c r="Q1220" s="19"/>
-      <c r="R1220" s="31" t="s">
-        <v>873</v>
+      <c r="R1220" s="22" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="1221" spans="1:18" ht="28.2" thickBot="1">
@@ -65519,40 +65679,40 @@
         <v>46234</v>
       </c>
       <c r="C1221" s="12" t="s">
-        <v>1950</v>
-      </c>
-      <c r="D1221" s="12">
-        <v>101365433</v>
+        <v>77</v>
+      </c>
+      <c r="D1221" s="12" t="s">
+        <v>1999</v>
       </c>
       <c r="E1221" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="F1221" s="17" t="s">
-        <v>820</v>
+      <c r="F1221" s="14" t="s">
+        <v>48</v>
       </c>
       <c r="G1221" s="15">
-        <v>5463</v>
-      </c>
-      <c r="H1221" s="16">
-        <v>2363</v>
-      </c>
-      <c r="I1221" s="16" t="s">
-        <v>825</v>
-      </c>
-      <c r="J1221" s="20" t="s">
-        <v>1951</v>
-      </c>
-      <c r="K1221" s="43" t="s">
-        <v>860</v>
+        <v>63226</v>
+      </c>
+      <c r="H1221" s="19"/>
+      <c r="I1221" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1221" s="16" t="s">
+        <v>1406</v>
+      </c>
+      <c r="K1221" s="18" t="s">
+        <v>20</v>
       </c>
       <c r="L1221" s="19"/>
       <c r="M1221" s="19"/>
       <c r="N1221" s="19"/>
       <c r="O1221" s="19"/>
       <c r="P1221" s="19"/>
-      <c r="Q1221" s="19"/>
-      <c r="R1221" s="31" t="s">
-        <v>873</v>
+      <c r="Q1221" s="12">
+        <v>971527752054</v>
+      </c>
+      <c r="R1221" s="22" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="1222" spans="1:18" ht="28.2" thickBot="1">
@@ -65563,10 +65723,10 @@
         <v>46234</v>
       </c>
       <c r="C1222" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="D1222" s="12">
-        <v>100418408</v>
+        <v>2000</v>
+      </c>
+      <c r="D1222" s="12" t="s">
+        <v>2001</v>
       </c>
       <c r="E1222" s="13" t="s">
         <v>47</v>
@@ -65575,19 +65735,19 @@
         <v>820</v>
       </c>
       <c r="G1222" s="15">
-        <v>4859</v>
+        <v>3246</v>
       </c>
       <c r="H1222" s="16">
-        <v>8915</v>
-      </c>
-      <c r="I1222" s="16" t="s">
-        <v>825</v>
-      </c>
-      <c r="J1222" s="20" t="s">
-        <v>1951</v>
-      </c>
-      <c r="K1222" s="43" t="s">
-        <v>860</v>
+        <v>-3247</v>
+      </c>
+      <c r="I1222" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1222" s="16" t="s">
+        <v>2002</v>
+      </c>
+      <c r="K1222" s="18" t="s">
+        <v>20</v>
       </c>
       <c r="L1222" s="19"/>
       <c r="M1222" s="19"/>
@@ -65595,11 +65755,11 @@
       <c r="O1222" s="19"/>
       <c r="P1222" s="19"/>
       <c r="Q1222" s="19"/>
-      <c r="R1222" s="31" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="1223" spans="1:18" ht="28.2" thickBot="1">
+      <c r="R1222" s="22" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:18" ht="15" thickBot="1">
       <c r="A1223" s="2">
         <v>32</v>
       </c>
@@ -65607,10 +65767,10 @@
         <v>46234</v>
       </c>
       <c r="C1223" s="12" t="s">
-        <v>1952</v>
+        <v>2003</v>
       </c>
       <c r="D1223" s="12">
-        <v>117980276</v>
+        <v>102591188</v>
       </c>
       <c r="E1223" s="13" t="s">
         <v>47</v>
@@ -65619,19 +65779,19 @@
         <v>820</v>
       </c>
       <c r="G1223" s="15">
-        <v>4141</v>
+        <v>4994</v>
       </c>
       <c r="H1223" s="16">
-        <v>2995</v>
-      </c>
-      <c r="I1223" s="16" t="s">
-        <v>825</v>
-      </c>
-      <c r="J1223" s="20" t="s">
-        <v>1951</v>
-      </c>
-      <c r="K1223" s="43" t="s">
-        <v>860</v>
+        <v>4392</v>
+      </c>
+      <c r="I1223" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1223" s="16" t="s">
+        <v>2004</v>
+      </c>
+      <c r="K1223" s="18" t="s">
+        <v>20</v>
       </c>
       <c r="L1223" s="19"/>
       <c r="M1223" s="19"/>
@@ -65639,8 +65799,8 @@
       <c r="O1223" s="19"/>
       <c r="P1223" s="19"/>
       <c r="Q1223" s="19"/>
-      <c r="R1223" s="31" t="s">
-        <v>873</v>
+      <c r="R1223" s="22" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="1224" spans="1:18" ht="15" thickBot="1">
@@ -65651,40 +65811,40 @@
         <v>46234</v>
       </c>
       <c r="C1224" s="12" t="s">
-        <v>1953</v>
+        <v>2005</v>
       </c>
       <c r="D1224" s="12" t="s">
-        <v>1954</v>
-      </c>
-      <c r="E1224" s="44" t="s">
-        <v>815</v>
-      </c>
-      <c r="F1224" s="14" t="s">
-        <v>48</v>
+        <v>2006</v>
+      </c>
+      <c r="E1224" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1224" s="17" t="s">
+        <v>820</v>
       </c>
       <c r="G1224" s="15">
-        <v>84545</v>
+        <v>41051</v>
       </c>
       <c r="H1224" s="16">
-        <v>90931</v>
+        <v>57445</v>
       </c>
       <c r="I1224" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="J1224" s="71" t="s">
-        <v>848</v>
-      </c>
-      <c r="K1224" s="43" t="s">
-        <v>860</v>
-      </c>
+      <c r="J1224" s="16" t="s">
+        <v>1962</v>
+      </c>
+      <c r="K1224" s="19"/>
       <c r="L1224" s="19"/>
       <c r="M1224" s="19"/>
       <c r="N1224" s="19"/>
       <c r="O1224" s="19"/>
       <c r="P1224" s="19"/>
-      <c r="Q1224" s="19"/>
-      <c r="R1224" s="31" t="s">
-        <v>873</v>
+      <c r="Q1224" s="12">
+        <v>96878452324</v>
+      </c>
+      <c r="R1224" s="22" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="1225" spans="1:18" ht="15" thickBot="1">
@@ -65695,40 +65855,40 @@
         <v>46234</v>
       </c>
       <c r="C1225" s="12" t="s">
-        <v>1955</v>
+        <v>2007</v>
       </c>
       <c r="D1225" s="12" t="s">
-        <v>1956</v>
-      </c>
-      <c r="E1225" s="44" t="s">
-        <v>815</v>
+        <v>2008</v>
+      </c>
+      <c r="E1225" s="13" t="s">
+        <v>47</v>
       </c>
       <c r="F1225" s="14" t="s">
         <v>48</v>
       </c>
       <c r="G1225" s="15">
-        <v>83079</v>
+        <v>32182</v>
       </c>
       <c r="H1225" s="16">
-        <v>66372</v>
+        <v>84933</v>
       </c>
       <c r="I1225" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="J1225" s="71" t="s">
-        <v>848</v>
-      </c>
-      <c r="K1225" s="43" t="s">
-        <v>860</v>
-      </c>
+      <c r="J1225" s="16" t="s">
+        <v>1962</v>
+      </c>
+      <c r="K1225" s="19"/>
       <c r="L1225" s="19"/>
       <c r="M1225" s="19"/>
       <c r="N1225" s="19"/>
       <c r="O1225" s="19"/>
       <c r="P1225" s="19"/>
-      <c r="Q1225" s="19"/>
-      <c r="R1225" s="31" t="s">
-        <v>873</v>
+      <c r="Q1225" s="12">
+        <v>95710874</v>
+      </c>
+      <c r="R1225" s="22" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="1226" spans="1:18" ht="15" thickBot="1">
@@ -65739,45 +65899,43 @@
         <v>46234</v>
       </c>
       <c r="C1226" s="12" t="s">
-        <v>1957</v>
-      </c>
-      <c r="D1226" s="12">
-        <v>130981461</v>
+        <v>131</v>
+      </c>
+      <c r="D1226" s="12" t="s">
+        <v>2009</v>
       </c>
       <c r="E1226" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="F1226" s="17" t="s">
-        <v>820</v>
+      <c r="F1226" s="14" t="s">
+        <v>48</v>
       </c>
       <c r="G1226" s="15">
-        <v>4597</v>
+        <v>88736</v>
       </c>
       <c r="H1226" s="16">
-        <v>2823</v>
+        <v>15749</v>
       </c>
       <c r="I1226" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="J1226" s="71" t="s">
-        <v>848</v>
-      </c>
-      <c r="K1226" s="43" t="s">
-        <v>860</v>
-      </c>
+      <c r="J1226" s="16" t="s">
+        <v>1962</v>
+      </c>
+      <c r="K1226" s="19"/>
       <c r="L1226" s="19"/>
       <c r="M1226" s="19"/>
-      <c r="N1226" s="16">
-        <v>969</v>
-      </c>
+      <c r="N1226" s="19"/>
       <c r="O1226" s="19"/>
       <c r="P1226" s="19"/>
-      <c r="Q1226" s="19"/>
-      <c r="R1226" s="31" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="1227" spans="1:18" ht="28.2" thickBot="1">
+      <c r="Q1226" s="12">
+        <v>96895726274</v>
+      </c>
+      <c r="R1226" s="22" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:18" ht="15" thickBot="1">
       <c r="A1227" s="2">
         <v>36</v>
       </c>
@@ -65785,10 +65943,10 @@
         <v>46234</v>
       </c>
       <c r="C1227" s="12" t="s">
-        <v>1981</v>
+        <v>2010</v>
       </c>
       <c r="D1227" s="12">
-        <v>133456021</v>
+        <v>107296805</v>
       </c>
       <c r="E1227" s="13" t="s">
         <v>47</v>
@@ -65797,28 +65955,26 @@
         <v>820</v>
       </c>
       <c r="G1227" s="15">
-        <v>3867</v>
-      </c>
-      <c r="H1227" s="16">
-        <v>4489</v>
-      </c>
-      <c r="I1227" s="16" t="s">
-        <v>825</v>
-      </c>
-      <c r="J1227" s="20" t="s">
-        <v>1982</v>
-      </c>
-      <c r="K1227" s="43" t="s">
-        <v>860</v>
-      </c>
+        <v>2385</v>
+      </c>
+      <c r="H1227" s="19"/>
+      <c r="I1227" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1227" s="16" t="s">
+        <v>1962</v>
+      </c>
+      <c r="K1227" s="19"/>
       <c r="L1227" s="19"/>
       <c r="M1227" s="19"/>
       <c r="N1227" s="19"/>
       <c r="O1227" s="19"/>
       <c r="P1227" s="19"/>
-      <c r="Q1227" s="19"/>
-      <c r="R1227" s="31" t="s">
-        <v>873</v>
+      <c r="Q1227" s="12">
+        <v>95771582</v>
+      </c>
+      <c r="R1227" s="22" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="1228" spans="1:18" ht="15" thickBot="1">
@@ -65829,10 +65985,10 @@
         <v>46234</v>
       </c>
       <c r="C1228" s="12" t="s">
-        <v>838</v>
+        <v>2011</v>
       </c>
       <c r="D1228" s="12">
-        <v>137462763</v>
+        <v>134687944</v>
       </c>
       <c r="E1228" s="13" t="s">
         <v>47</v>
@@ -65841,29 +65997,25 @@
         <v>820</v>
       </c>
       <c r="G1228" s="15">
-        <v>9203</v>
-      </c>
-      <c r="H1228" s="16" t="s">
-        <v>1983</v>
-      </c>
-      <c r="I1228" s="31" t="s">
-        <v>823</v>
-      </c>
-      <c r="J1228" s="20" t="s">
-        <v>1260</v>
-      </c>
-      <c r="K1228" s="43" t="s">
-        <v>860</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="H1228" s="16">
+        <v>1956</v>
+      </c>
+      <c r="I1228" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1228" s="16" t="s">
+        <v>1962</v>
+      </c>
+      <c r="K1228" s="19"/>
       <c r="L1228" s="19"/>
       <c r="M1228" s="19"/>
       <c r="N1228" s="19"/>
       <c r="O1228" s="19"/>
       <c r="P1228" s="19"/>
       <c r="Q1228" s="19"/>
-      <c r="R1228" s="31" t="s">
-        <v>873</v>
-      </c>
+      <c r="R1228" s="19"/>
     </row>
     <row r="1229" spans="1:18" ht="15" thickBot="1">
       <c r="A1229" s="2">
@@ -65873,43 +66025,39 @@
         <v>46234</v>
       </c>
       <c r="C1229" s="12" t="s">
-        <v>1984</v>
-      </c>
-      <c r="D1229" s="12" t="s">
-        <v>1985</v>
+        <v>2012</v>
+      </c>
+      <c r="D1229" s="12">
+        <v>107092728</v>
       </c>
       <c r="E1229" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="F1229" s="14" t="s">
-        <v>48</v>
+      <c r="F1229" s="17" t="s">
+        <v>820</v>
       </c>
       <c r="G1229" s="15">
-        <v>85542</v>
+        <v>7321</v>
       </c>
       <c r="H1229" s="16">
-        <v>33771</v>
-      </c>
-      <c r="I1229" s="31" t="s">
-        <v>823</v>
-      </c>
-      <c r="J1229" s="20" t="s">
-        <v>1260</v>
-      </c>
-      <c r="K1229" s="43" t="s">
-        <v>860</v>
-      </c>
+        <v>632</v>
+      </c>
+      <c r="I1229" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1229" s="16" t="s">
+        <v>1962</v>
+      </c>
+      <c r="K1229" s="19"/>
       <c r="L1229" s="19"/>
       <c r="M1229" s="19"/>
       <c r="N1229" s="19"/>
       <c r="O1229" s="19"/>
       <c r="P1229" s="19"/>
       <c r="Q1229" s="19"/>
-      <c r="R1229" s="31" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="1230" spans="1:18" ht="28.2" thickBot="1">
+      <c r="R1229" s="19"/>
+    </row>
+    <row r="1230" spans="1:18" ht="15" thickBot="1">
       <c r="A1230" s="2">
         <v>39</v>
       </c>
@@ -65917,40 +66065,40 @@
         <v>46234</v>
       </c>
       <c r="C1230" s="12" t="s">
-        <v>1986</v>
-      </c>
-      <c r="D1230" s="12" t="s">
-        <v>1987</v>
-      </c>
-      <c r="E1230" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="F1230" s="14" t="s">
-        <v>48</v>
+        <v>1947</v>
+      </c>
+      <c r="D1230" s="12">
+        <v>113961322</v>
+      </c>
+      <c r="E1230" s="44" t="s">
+        <v>815</v>
+      </c>
+      <c r="F1230" s="17" t="s">
+        <v>820</v>
       </c>
       <c r="G1230" s="15">
-        <v>53695</v>
+        <v>6707</v>
       </c>
       <c r="H1230" s="16">
-        <v>47102</v>
-      </c>
-      <c r="I1230" s="16" t="s">
-        <v>825</v>
-      </c>
-      <c r="J1230" s="20" t="s">
+        <v>3130</v>
+      </c>
+      <c r="I1230" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1230" s="16" t="s">
         <v>1259</v>
       </c>
-      <c r="K1230" s="43" t="s">
-        <v>860</v>
-      </c>
+      <c r="K1230" s="19"/>
       <c r="L1230" s="19"/>
       <c r="M1230" s="19"/>
       <c r="N1230" s="19"/>
       <c r="O1230" s="19"/>
-      <c r="P1230" s="19"/>
+      <c r="P1230" s="59" t="s">
+        <v>1948</v>
+      </c>
       <c r="Q1230" s="19"/>
-      <c r="R1230" s="31" t="s">
-        <v>873</v>
+      <c r="R1230" s="25" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="1231" spans="1:18" ht="28.2" thickBot="1">
@@ -65961,10 +66109,10 @@
         <v>46234</v>
       </c>
       <c r="C1231" s="12" t="s">
-        <v>1988</v>
+        <v>1949</v>
       </c>
       <c r="D1231" s="12">
-        <v>90614152</v>
+        <v>121436929</v>
       </c>
       <c r="E1231" s="13" t="s">
         <v>47</v>
@@ -65973,17 +66121,15 @@
         <v>820</v>
       </c>
       <c r="G1231" s="15">
-        <v>3315</v>
+        <v>227</v>
       </c>
       <c r="H1231" s="16">
-        <v>7442</v>
+        <v>7508</v>
       </c>
       <c r="I1231" s="16" t="s">
         <v>825</v>
       </c>
-      <c r="J1231" s="20" t="s">
-        <v>1407</v>
-      </c>
+      <c r="J1231" s="19"/>
       <c r="K1231" s="43" t="s">
         <v>860</v>
       </c>
@@ -66005,10 +66151,10 @@
         <v>46234</v>
       </c>
       <c r="C1232" s="12" t="s">
-        <v>1989</v>
+        <v>1634</v>
       </c>
       <c r="D1232" s="12">
-        <v>143012774</v>
+        <v>77733982</v>
       </c>
       <c r="E1232" s="13" t="s">
         <v>47</v>
@@ -66017,17 +66163,15 @@
         <v>820</v>
       </c>
       <c r="G1232" s="15">
-        <v>2806</v>
+        <v>4513</v>
       </c>
       <c r="H1232" s="16">
-        <v>4054</v>
+        <v>2267</v>
       </c>
       <c r="I1232" s="16" t="s">
         <v>825</v>
       </c>
-      <c r="J1232" s="20" t="s">
-        <v>1407</v>
-      </c>
+      <c r="J1232" s="19"/>
       <c r="K1232" s="43" t="s">
         <v>860</v>
       </c>
@@ -66049,10 +66193,10 @@
         <v>46234</v>
       </c>
       <c r="C1233" s="12" t="s">
-        <v>56</v>
+        <v>1950</v>
       </c>
       <c r="D1233" s="12">
-        <v>76637533</v>
+        <v>101365433</v>
       </c>
       <c r="E1233" s="13" t="s">
         <v>47</v>
@@ -66061,16 +66205,16 @@
         <v>820</v>
       </c>
       <c r="G1233" s="15">
-        <v>1027</v>
+        <v>5463</v>
       </c>
       <c r="H1233" s="16">
-        <v>512</v>
+        <v>2363</v>
       </c>
       <c r="I1233" s="16" t="s">
         <v>825</v>
       </c>
       <c r="J1233" s="20" t="s">
-        <v>1261</v>
+        <v>1951</v>
       </c>
       <c r="K1233" s="43" t="s">
         <v>860</v>
@@ -66079,9 +66223,7 @@
       <c r="M1233" s="19"/>
       <c r="N1233" s="19"/>
       <c r="O1233" s="19"/>
-      <c r="P1233" s="59" t="s">
-        <v>1990</v>
-      </c>
+      <c r="P1233" s="19"/>
       <c r="Q1233" s="19"/>
       <c r="R1233" s="31" t="s">
         <v>873</v>
@@ -66095,10 +66237,10 @@
         <v>46234</v>
       </c>
       <c r="C1234" s="12" t="s">
-        <v>1991</v>
+        <v>273</v>
       </c>
       <c r="D1234" s="12">
-        <v>82483279</v>
+        <v>100418408</v>
       </c>
       <c r="E1234" s="13" t="s">
         <v>47</v>
@@ -66107,16 +66249,16 @@
         <v>820</v>
       </c>
       <c r="G1234" s="15">
-        <v>9487</v>
+        <v>4859</v>
       </c>
       <c r="H1234" s="16">
-        <v>4662</v>
+        <v>8915</v>
       </c>
       <c r="I1234" s="16" t="s">
         <v>825</v>
       </c>
       <c r="J1234" s="20" t="s">
-        <v>1992</v>
+        <v>1951</v>
       </c>
       <c r="K1234" s="43" t="s">
         <v>860</v>
@@ -66131,6 +66273,1500 @@
         <v>873</v>
       </c>
     </row>
+    <row r="1235" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1235" s="2">
+        <v>44</v>
+      </c>
+      <c r="B1235" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1235" s="12" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D1235" s="12">
+        <v>117980276</v>
+      </c>
+      <c r="E1235" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1235" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="G1235" s="15">
+        <v>4141</v>
+      </c>
+      <c r="H1235" s="16">
+        <v>2995</v>
+      </c>
+      <c r="I1235" s="16" t="s">
+        <v>825</v>
+      </c>
+      <c r="J1235" s="20" t="s">
+        <v>1951</v>
+      </c>
+      <c r="K1235" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1235" s="19"/>
+      <c r="M1235" s="19"/>
+      <c r="N1235" s="19"/>
+      <c r="O1235" s="19"/>
+      <c r="P1235" s="19"/>
+      <c r="Q1235" s="19"/>
+      <c r="R1235" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:18" ht="15" thickBot="1">
+      <c r="A1236" s="2">
+        <v>45</v>
+      </c>
+      <c r="B1236" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1236" s="12" t="s">
+        <v>1953</v>
+      </c>
+      <c r="D1236" s="12" t="s">
+        <v>1954</v>
+      </c>
+      <c r="E1236" s="44" t="s">
+        <v>815</v>
+      </c>
+      <c r="F1236" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1236" s="15">
+        <v>84545</v>
+      </c>
+      <c r="H1236" s="16">
+        <v>90931</v>
+      </c>
+      <c r="I1236" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1236" s="71" t="s">
+        <v>848</v>
+      </c>
+      <c r="K1236" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1236" s="19"/>
+      <c r="M1236" s="19"/>
+      <c r="N1236" s="19"/>
+      <c r="O1236" s="19"/>
+      <c r="P1236" s="19"/>
+      <c r="Q1236" s="19"/>
+      <c r="R1236" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:18" ht="15" thickBot="1">
+      <c r="A1237" s="2">
+        <v>46</v>
+      </c>
+      <c r="B1237" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1237" s="12" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D1237" s="12" t="s">
+        <v>1956</v>
+      </c>
+      <c r="E1237" s="44" t="s">
+        <v>815</v>
+      </c>
+      <c r="F1237" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1237" s="15">
+        <v>83079</v>
+      </c>
+      <c r="H1237" s="16">
+        <v>66372</v>
+      </c>
+      <c r="I1237" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1237" s="71" t="s">
+        <v>848</v>
+      </c>
+      <c r="K1237" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1237" s="19"/>
+      <c r="M1237" s="19"/>
+      <c r="N1237" s="19"/>
+      <c r="O1237" s="19"/>
+      <c r="P1237" s="19"/>
+      <c r="Q1237" s="19"/>
+      <c r="R1237" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:18" ht="15" thickBot="1">
+      <c r="A1238" s="2">
+        <v>47</v>
+      </c>
+      <c r="B1238" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1238" s="12" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D1238" s="12">
+        <v>130981461</v>
+      </c>
+      <c r="E1238" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1238" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="G1238" s="15">
+        <v>4597</v>
+      </c>
+      <c r="H1238" s="16">
+        <v>2823</v>
+      </c>
+      <c r="I1238" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1238" s="71" t="s">
+        <v>848</v>
+      </c>
+      <c r="K1238" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1238" s="19"/>
+      <c r="M1238" s="19"/>
+      <c r="N1238" s="16">
+        <v>969</v>
+      </c>
+      <c r="O1238" s="19"/>
+      <c r="P1238" s="19"/>
+      <c r="Q1238" s="19"/>
+      <c r="R1238" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1239" s="2">
+        <v>48</v>
+      </c>
+      <c r="B1239" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1239" s="12" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D1239" s="12">
+        <v>133456021</v>
+      </c>
+      <c r="E1239" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1239" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="G1239" s="15">
+        <v>3867</v>
+      </c>
+      <c r="H1239" s="16">
+        <v>4489</v>
+      </c>
+      <c r="I1239" s="16" t="s">
+        <v>825</v>
+      </c>
+      <c r="J1239" s="20" t="s">
+        <v>1982</v>
+      </c>
+      <c r="K1239" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1239" s="19"/>
+      <c r="M1239" s="19"/>
+      <c r="N1239" s="19"/>
+      <c r="O1239" s="19"/>
+      <c r="P1239" s="19"/>
+      <c r="Q1239" s="19"/>
+      <c r="R1239" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:18" ht="15" thickBot="1">
+      <c r="A1240" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1240" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1240" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="D1240" s="12">
+        <v>137462763</v>
+      </c>
+      <c r="E1240" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1240" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="G1240" s="15">
+        <v>9203</v>
+      </c>
+      <c r="H1240" s="16" t="s">
+        <v>1983</v>
+      </c>
+      <c r="I1240" s="31" t="s">
+        <v>823</v>
+      </c>
+      <c r="J1240" s="20" t="s">
+        <v>1260</v>
+      </c>
+      <c r="K1240" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1240" s="19"/>
+      <c r="M1240" s="19"/>
+      <c r="N1240" s="19"/>
+      <c r="O1240" s="19"/>
+      <c r="P1240" s="19"/>
+      <c r="Q1240" s="19"/>
+      <c r="R1240" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:18" ht="15" thickBot="1">
+      <c r="A1241" s="2">
+        <v>50</v>
+      </c>
+      <c r="B1241" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1241" s="12" t="s">
+        <v>1984</v>
+      </c>
+      <c r="D1241" s="12" t="s">
+        <v>1985</v>
+      </c>
+      <c r="E1241" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1241" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1241" s="15">
+        <v>85542</v>
+      </c>
+      <c r="H1241" s="16">
+        <v>33771</v>
+      </c>
+      <c r="I1241" s="31" t="s">
+        <v>823</v>
+      </c>
+      <c r="J1241" s="20" t="s">
+        <v>1260</v>
+      </c>
+      <c r="K1241" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1241" s="19"/>
+      <c r="M1241" s="19"/>
+      <c r="N1241" s="19"/>
+      <c r="O1241" s="19"/>
+      <c r="P1241" s="19"/>
+      <c r="Q1241" s="19"/>
+      <c r="R1241" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1242" s="2">
+        <v>51</v>
+      </c>
+      <c r="B1242" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1242" s="12" t="s">
+        <v>1986</v>
+      </c>
+      <c r="D1242" s="12" t="s">
+        <v>1987</v>
+      </c>
+      <c r="E1242" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1242" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1242" s="15">
+        <v>53695</v>
+      </c>
+      <c r="H1242" s="16">
+        <v>47102</v>
+      </c>
+      <c r="I1242" s="16" t="s">
+        <v>825</v>
+      </c>
+      <c r="J1242" s="20" t="s">
+        <v>1259</v>
+      </c>
+      <c r="K1242" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1242" s="19"/>
+      <c r="M1242" s="19"/>
+      <c r="N1242" s="19"/>
+      <c r="O1242" s="19"/>
+      <c r="P1242" s="19"/>
+      <c r="Q1242" s="19"/>
+      <c r="R1242" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1243" s="2">
+        <v>52</v>
+      </c>
+      <c r="B1243" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1243" s="12" t="s">
+        <v>1988</v>
+      </c>
+      <c r="D1243" s="12">
+        <v>90614152</v>
+      </c>
+      <c r="E1243" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1243" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="G1243" s="15">
+        <v>3315</v>
+      </c>
+      <c r="H1243" s="16">
+        <v>7442</v>
+      </c>
+      <c r="I1243" s="16" t="s">
+        <v>825</v>
+      </c>
+      <c r="J1243" s="20" t="s">
+        <v>1407</v>
+      </c>
+      <c r="K1243" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1243" s="19"/>
+      <c r="M1243" s="19"/>
+      <c r="N1243" s="19"/>
+      <c r="O1243" s="19"/>
+      <c r="P1243" s="19"/>
+      <c r="Q1243" s="19"/>
+      <c r="R1243" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1244" s="2">
+        <v>53</v>
+      </c>
+      <c r="B1244" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1244" s="12" t="s">
+        <v>1989</v>
+      </c>
+      <c r="D1244" s="12">
+        <v>143012774</v>
+      </c>
+      <c r="E1244" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1244" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="G1244" s="15">
+        <v>2806</v>
+      </c>
+      <c r="H1244" s="16">
+        <v>4054</v>
+      </c>
+      <c r="I1244" s="16" t="s">
+        <v>825</v>
+      </c>
+      <c r="J1244" s="20" t="s">
+        <v>1407</v>
+      </c>
+      <c r="K1244" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1244" s="19"/>
+      <c r="M1244" s="19"/>
+      <c r="N1244" s="19"/>
+      <c r="O1244" s="19"/>
+      <c r="P1244" s="19"/>
+      <c r="Q1244" s="19"/>
+      <c r="R1244" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1245" s="2">
+        <v>54</v>
+      </c>
+      <c r="B1245" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1245" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1245" s="12">
+        <v>76637533</v>
+      </c>
+      <c r="E1245" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1245" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="G1245" s="15">
+        <v>1027</v>
+      </c>
+      <c r="H1245" s="16">
+        <v>512</v>
+      </c>
+      <c r="I1245" s="16" t="s">
+        <v>825</v>
+      </c>
+      <c r="J1245" s="20" t="s">
+        <v>1261</v>
+      </c>
+      <c r="K1245" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1245" s="19"/>
+      <c r="M1245" s="19"/>
+      <c r="N1245" s="19"/>
+      <c r="O1245" s="19"/>
+      <c r="P1245" s="59" t="s">
+        <v>1990</v>
+      </c>
+      <c r="Q1245" s="19"/>
+      <c r="R1245" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1246" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1246" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1246" s="12" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D1246" s="12">
+        <v>82483279</v>
+      </c>
+      <c r="E1246" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1246" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="G1246" s="15">
+        <v>9487</v>
+      </c>
+      <c r="H1246" s="16">
+        <v>4662</v>
+      </c>
+      <c r="I1246" s="16" t="s">
+        <v>825</v>
+      </c>
+      <c r="J1246" s="20" t="s">
+        <v>1992</v>
+      </c>
+      <c r="K1246" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1246" s="19"/>
+      <c r="M1246" s="19"/>
+      <c r="N1246" s="19"/>
+      <c r="O1246" s="19"/>
+      <c r="P1246" s="19"/>
+      <c r="Q1246" s="19"/>
+      <c r="R1246" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:18" ht="15" thickBot="1">
+      <c r="A1247" s="2">
+        <v>56</v>
+      </c>
+      <c r="B1247" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1247" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="D1247" s="12" t="s">
+        <v>2013</v>
+      </c>
+      <c r="E1247" s="44" t="s">
+        <v>815</v>
+      </c>
+      <c r="F1247" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1247" s="15">
+        <v>34101</v>
+      </c>
+      <c r="H1247" s="16">
+        <v>48514</v>
+      </c>
+      <c r="I1247" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1247" s="71" t="s">
+        <v>848</v>
+      </c>
+      <c r="K1247" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1247" s="19"/>
+      <c r="M1247" s="19"/>
+      <c r="N1247" s="19"/>
+      <c r="O1247" s="19"/>
+      <c r="P1247" s="19"/>
+      <c r="Q1247" s="19"/>
+      <c r="R1247" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:18" ht="15" thickBot="1">
+      <c r="A1248" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1248" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1248" s="12" t="s">
+        <v>2014</v>
+      </c>
+      <c r="D1248" s="12" t="s">
+        <v>2015</v>
+      </c>
+      <c r="E1248" s="44" t="s">
+        <v>815</v>
+      </c>
+      <c r="F1248" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1248" s="15">
+        <v>65229</v>
+      </c>
+      <c r="H1248" s="16" t="s">
+        <v>2016</v>
+      </c>
+      <c r="I1248" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1248" s="71" t="s">
+        <v>848</v>
+      </c>
+      <c r="K1248" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1248" s="19"/>
+      <c r="M1248" s="19"/>
+      <c r="N1248" s="19"/>
+      <c r="O1248" s="19"/>
+      <c r="P1248" s="19"/>
+      <c r="Q1248" s="19"/>
+      <c r="R1248" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:18" ht="15" thickBot="1">
+      <c r="A1249" s="2">
+        <v>58</v>
+      </c>
+      <c r="B1249" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1249" s="12" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D1249" s="12">
+        <v>109781891</v>
+      </c>
+      <c r="E1249" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1249" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="G1249" s="15">
+        <v>8109</v>
+      </c>
+      <c r="H1249" s="16">
+        <v>6640</v>
+      </c>
+      <c r="I1249" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1249" s="71" t="s">
+        <v>848</v>
+      </c>
+      <c r="K1249" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1249" s="19"/>
+      <c r="M1249" s="19"/>
+      <c r="N1249" s="19"/>
+      <c r="O1249" s="19"/>
+      <c r="P1249" s="19"/>
+      <c r="Q1249" s="19"/>
+      <c r="R1249" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:18" ht="15" thickBot="1">
+      <c r="A1250" s="2">
+        <v>59</v>
+      </c>
+      <c r="B1250" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1250" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="D1250" s="12">
+        <v>116958115</v>
+      </c>
+      <c r="E1250" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1250" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="G1250" s="15">
+        <v>1499</v>
+      </c>
+      <c r="H1250" s="16">
+        <v>7165</v>
+      </c>
+      <c r="I1250" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1250" s="71" t="s">
+        <v>848</v>
+      </c>
+      <c r="K1250" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1250" s="19"/>
+      <c r="M1250" s="19"/>
+      <c r="N1250" s="19"/>
+      <c r="O1250" s="19"/>
+      <c r="P1250" s="19"/>
+      <c r="Q1250" s="19"/>
+      <c r="R1250" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:18" ht="15" thickBot="1">
+      <c r="A1251" s="2">
+        <v>60</v>
+      </c>
+      <c r="B1251" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1251" s="27" t="s">
+        <v>2018</v>
+      </c>
+      <c r="D1251" s="27">
+        <v>135210905</v>
+      </c>
+      <c r="E1251" s="109" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1251" s="110" t="s">
+        <v>820</v>
+      </c>
+      <c r="G1251" s="88">
+        <v>4821</v>
+      </c>
+      <c r="H1251" s="89">
+        <v>1058</v>
+      </c>
+      <c r="I1251" s="110" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1251" s="111" t="s">
+        <v>848</v>
+      </c>
+      <c r="K1251" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1251" s="19"/>
+      <c r="M1251" s="19"/>
+      <c r="N1251" s="19"/>
+      <c r="O1251" s="19"/>
+      <c r="P1251" s="19"/>
+      <c r="Q1251" s="19"/>
+      <c r="R1251" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:18" ht="15" thickBot="1">
+      <c r="A1252" s="2">
+        <v>61</v>
+      </c>
+      <c r="B1252" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1252" s="27" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D1252" s="27" t="s">
+        <v>2020</v>
+      </c>
+      <c r="E1252" s="112" t="s">
+        <v>815</v>
+      </c>
+      <c r="F1252" s="113" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1252" s="88">
+        <v>25509</v>
+      </c>
+      <c r="H1252" s="89">
+        <v>8620</v>
+      </c>
+      <c r="I1252" s="110" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1252" s="111" t="s">
+        <v>848</v>
+      </c>
+      <c r="K1252" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1252" s="19"/>
+      <c r="M1252" s="19"/>
+      <c r="N1252" s="19"/>
+      <c r="O1252" s="19"/>
+      <c r="P1252" s="19"/>
+      <c r="Q1252" s="19"/>
+      <c r="R1252" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:18" ht="15" thickBot="1">
+      <c r="A1253" s="2">
+        <v>62</v>
+      </c>
+      <c r="B1253" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1253" s="27" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D1253" s="27" t="s">
+        <v>2022</v>
+      </c>
+      <c r="E1253" s="112" t="s">
+        <v>815</v>
+      </c>
+      <c r="F1253" s="113" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1253" s="88">
+        <v>79775</v>
+      </c>
+      <c r="H1253" s="89">
+        <v>27573</v>
+      </c>
+      <c r="I1253" s="110" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1253" s="111" t="s">
+        <v>848</v>
+      </c>
+      <c r="K1253" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1253" s="19"/>
+      <c r="M1253" s="19"/>
+      <c r="N1253" s="19"/>
+      <c r="O1253" s="19"/>
+      <c r="P1253" s="19"/>
+      <c r="Q1253" s="19"/>
+      <c r="R1253" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:18" ht="15" thickBot="1">
+      <c r="A1254" s="2">
+        <v>63</v>
+      </c>
+      <c r="B1254" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1254" s="27" t="s">
+        <v>2023</v>
+      </c>
+      <c r="D1254" s="27" t="s">
+        <v>2024</v>
+      </c>
+      <c r="E1254" s="112" t="s">
+        <v>815</v>
+      </c>
+      <c r="F1254" s="113" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1254" s="88">
+        <v>54265</v>
+      </c>
+      <c r="H1254" s="89">
+        <v>27573</v>
+      </c>
+      <c r="I1254" s="110" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1254" s="111" t="s">
+        <v>848</v>
+      </c>
+      <c r="K1254" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1254" s="19"/>
+      <c r="M1254" s="19"/>
+      <c r="N1254" s="19"/>
+      <c r="O1254" s="19"/>
+      <c r="P1254" s="19"/>
+      <c r="Q1254" s="19"/>
+      <c r="R1254" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:18" ht="15" thickBot="1">
+      <c r="A1255" s="2">
+        <v>64</v>
+      </c>
+      <c r="B1255" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1255" s="27" t="s">
+        <v>335</v>
+      </c>
+      <c r="D1255" s="27" t="s">
+        <v>708</v>
+      </c>
+      <c r="E1255" s="112" t="s">
+        <v>815</v>
+      </c>
+      <c r="F1255" s="113" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1255" s="88">
+        <v>67105</v>
+      </c>
+      <c r="H1255" s="89" t="s">
+        <v>2025</v>
+      </c>
+      <c r="I1255" s="110" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1255" s="111" t="s">
+        <v>848</v>
+      </c>
+      <c r="K1255" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1255" s="19"/>
+      <c r="M1255" s="19"/>
+      <c r="N1255" s="19"/>
+      <c r="O1255" s="19"/>
+      <c r="P1255" s="19"/>
+      <c r="Q1255" s="19"/>
+      <c r="R1255" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:18" ht="15" thickBot="1">
+      <c r="A1256" s="2">
+        <v>65</v>
+      </c>
+      <c r="B1256" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1256" s="27" t="s">
+        <v>2026</v>
+      </c>
+      <c r="D1256" s="27" t="s">
+        <v>2027</v>
+      </c>
+      <c r="E1256" s="109" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1256" s="113" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1256" s="88">
+        <v>39243</v>
+      </c>
+      <c r="H1256" s="89">
+        <v>82527</v>
+      </c>
+      <c r="I1256" s="110" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1256" s="111" t="s">
+        <v>848</v>
+      </c>
+      <c r="K1256" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1256" s="19"/>
+      <c r="M1256" s="19"/>
+      <c r="N1256" s="19"/>
+      <c r="O1256" s="19"/>
+      <c r="P1256" s="19"/>
+      <c r="Q1256" s="19"/>
+      <c r="R1256" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:18" ht="15" thickBot="1">
+      <c r="A1257" s="2">
+        <v>66</v>
+      </c>
+      <c r="B1257" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1257" s="27" t="s">
+        <v>2028</v>
+      </c>
+      <c r="D1257" s="27" t="s">
+        <v>2029</v>
+      </c>
+      <c r="E1257" s="109" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1257" s="113" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1257" s="88">
+        <v>73261</v>
+      </c>
+      <c r="H1257" s="89">
+        <v>19106</v>
+      </c>
+      <c r="I1257" s="110" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1257" s="111" t="s">
+        <v>848</v>
+      </c>
+      <c r="K1257" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1257" s="19"/>
+      <c r="M1257" s="19"/>
+      <c r="N1257" s="19"/>
+      <c r="O1257" s="19"/>
+      <c r="P1257" s="19"/>
+      <c r="Q1257" s="19"/>
+      <c r="R1257" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:18" ht="15" thickBot="1">
+      <c r="A1258" s="2">
+        <v>67</v>
+      </c>
+      <c r="B1258" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1258" s="27" t="s">
+        <v>1738</v>
+      </c>
+      <c r="D1258" s="27" t="s">
+        <v>2030</v>
+      </c>
+      <c r="E1258" s="109" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1258" s="113" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1258" s="91">
+        <v>58574</v>
+      </c>
+      <c r="H1258" s="89">
+        <v>26677</v>
+      </c>
+      <c r="I1258" s="110" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1258" s="111" t="s">
+        <v>848</v>
+      </c>
+      <c r="K1258" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1258" s="19"/>
+      <c r="M1258" s="19"/>
+      <c r="N1258" s="19"/>
+      <c r="O1258" s="19"/>
+      <c r="P1258" s="19"/>
+      <c r="Q1258" s="19"/>
+      <c r="R1258" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:18" ht="15" thickBot="1">
+      <c r="A1259" s="2">
+        <v>68</v>
+      </c>
+      <c r="B1259" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1259" s="12" t="s">
+        <v>2031</v>
+      </c>
+      <c r="D1259" s="12">
+        <v>126958851</v>
+      </c>
+      <c r="E1259" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1259" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="G1259" s="91">
+        <v>4983</v>
+      </c>
+      <c r="H1259" s="16" t="s">
+        <v>2032</v>
+      </c>
+      <c r="I1259" s="31" t="s">
+        <v>823</v>
+      </c>
+      <c r="J1259" s="20" t="s">
+        <v>1260</v>
+      </c>
+      <c r="K1259" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1259" s="19"/>
+      <c r="M1259" s="19"/>
+      <c r="N1259" s="19"/>
+      <c r="O1259" s="19"/>
+      <c r="P1259" s="19"/>
+      <c r="Q1259" s="19"/>
+      <c r="R1259" s="31" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1260" s="2">
+        <v>69</v>
+      </c>
+      <c r="B1260" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1260" s="12" t="s">
+        <v>2033</v>
+      </c>
+      <c r="D1260" s="12">
+        <v>123757652</v>
+      </c>
+      <c r="E1260" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1260" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="G1260" s="56">
+        <v>7264</v>
+      </c>
+      <c r="H1260" s="16">
+        <v>-7760</v>
+      </c>
+      <c r="I1260" s="45" t="s">
+        <v>824</v>
+      </c>
+      <c r="J1260" s="19"/>
+      <c r="K1260" s="43" t="s">
+        <v>860</v>
+      </c>
+      <c r="L1260" s="24">
+        <v>46236</v>
+      </c>
+      <c r="M1260" s="19"/>
+      <c r="N1260" s="19"/>
+      <c r="O1260" s="19"/>
+      <c r="P1260" s="19"/>
+      <c r="Q1260" s="12">
+        <v>78804403</v>
+      </c>
+      <c r="R1260" s="25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1261" s="2">
+        <v>70</v>
+      </c>
+      <c r="B1261" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1261" s="12" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D1261" s="12">
+        <v>94006643</v>
+      </c>
+      <c r="E1261" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1261" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="G1261" s="56">
+        <v>906</v>
+      </c>
+      <c r="H1261" s="16">
+        <v>1029</v>
+      </c>
+      <c r="I1261" s="45" t="s">
+        <v>824</v>
+      </c>
+      <c r="J1261" s="19"/>
+      <c r="K1261" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1261" s="19"/>
+      <c r="M1261" s="19"/>
+      <c r="N1261" s="19"/>
+      <c r="O1261" s="19"/>
+      <c r="P1261" s="19"/>
+      <c r="Q1261" s="12">
+        <v>94535329</v>
+      </c>
+      <c r="R1261" s="25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1262" s="2">
+        <v>71</v>
+      </c>
+      <c r="B1262" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1262" s="12" t="s">
+        <v>1626</v>
+      </c>
+      <c r="D1262" s="12">
+        <v>126179269</v>
+      </c>
+      <c r="E1262" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1262" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="G1262" s="15">
+        <v>7888</v>
+      </c>
+      <c r="H1262" s="16">
+        <v>5504</v>
+      </c>
+      <c r="I1262" s="45" t="s">
+        <v>824</v>
+      </c>
+      <c r="J1262" s="19"/>
+      <c r="K1262" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1262" s="19"/>
+      <c r="M1262" s="19"/>
+      <c r="N1262" s="19"/>
+      <c r="O1262" s="19"/>
+      <c r="P1262" s="19"/>
+      <c r="Q1262" s="12">
+        <v>96949016</v>
+      </c>
+      <c r="R1262" s="25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1263" s="2">
+        <v>72</v>
+      </c>
+      <c r="B1263" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1263" s="12" t="s">
+        <v>2034</v>
+      </c>
+      <c r="D1263" s="12">
+        <v>90039233</v>
+      </c>
+      <c r="E1263" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1263" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="G1263" s="15">
+        <v>4467</v>
+      </c>
+      <c r="H1263" s="16">
+        <v>2766</v>
+      </c>
+      <c r="I1263" s="45" t="s">
+        <v>824</v>
+      </c>
+      <c r="J1263" s="19"/>
+      <c r="K1263" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1263" s="19"/>
+      <c r="M1263" s="19"/>
+      <c r="N1263" s="19"/>
+      <c r="O1263" s="19"/>
+      <c r="P1263" s="19"/>
+      <c r="Q1263" s="12">
+        <v>94247434</v>
+      </c>
+      <c r="R1263" s="25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1264" s="2">
+        <v>73</v>
+      </c>
+      <c r="B1264" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1264" s="12" t="s">
+        <v>2035</v>
+      </c>
+      <c r="D1264" s="12">
+        <v>135109456</v>
+      </c>
+      <c r="E1264" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1264" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="G1264" s="15">
+        <v>8980</v>
+      </c>
+      <c r="H1264" s="16">
+        <v>9304</v>
+      </c>
+      <c r="I1264" s="45" t="s">
+        <v>824</v>
+      </c>
+      <c r="J1264" s="19"/>
+      <c r="K1264" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1264" s="19"/>
+      <c r="M1264" s="19"/>
+      <c r="N1264" s="19"/>
+      <c r="O1264" s="19"/>
+      <c r="P1264" s="19"/>
+      <c r="Q1264" s="12">
+        <v>94966894</v>
+      </c>
+      <c r="R1264" s="25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1265" s="2">
+        <v>74</v>
+      </c>
+      <c r="B1265" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1265" s="12" t="s">
+        <v>2036</v>
+      </c>
+      <c r="D1265" s="12" t="s">
+        <v>2037</v>
+      </c>
+      <c r="E1265" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1265" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1265" s="15">
+        <v>37285</v>
+      </c>
+      <c r="H1265" s="16">
+        <v>56579</v>
+      </c>
+      <c r="I1265" s="45" t="s">
+        <v>824</v>
+      </c>
+      <c r="J1265" s="19"/>
+      <c r="K1265" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1265" s="19"/>
+      <c r="M1265" s="19"/>
+      <c r="N1265" s="19"/>
+      <c r="O1265" s="19"/>
+      <c r="P1265" s="19"/>
+      <c r="Q1265" s="12">
+        <v>95697183</v>
+      </c>
+      <c r="R1265" s="25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1266" s="2">
+        <v>75</v>
+      </c>
+      <c r="B1266" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1266" s="12" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D1266" s="12">
+        <v>102033848</v>
+      </c>
+      <c r="E1266" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1266" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="G1266" s="15">
+        <v>8850</v>
+      </c>
+      <c r="H1266" s="16">
+        <v>239</v>
+      </c>
+      <c r="I1266" s="45" t="s">
+        <v>824</v>
+      </c>
+      <c r="J1266" s="19"/>
+      <c r="K1266" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1266" s="19"/>
+      <c r="M1266" s="19"/>
+      <c r="N1266" s="19"/>
+      <c r="O1266" s="19"/>
+      <c r="P1266" s="19"/>
+      <c r="Q1266" s="12">
+        <v>94709965</v>
+      </c>
+      <c r="R1266" s="25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:18" ht="15" thickBot="1">
+      <c r="A1267" s="2">
+        <v>76</v>
+      </c>
+      <c r="B1267" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1267" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="D1267" s="12" t="s">
+        <v>2039</v>
+      </c>
+      <c r="E1267" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1267" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1267" s="15">
+        <v>66749</v>
+      </c>
+      <c r="H1267" s="16">
+        <v>22214</v>
+      </c>
+      <c r="I1267" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1267" s="20" t="s">
+        <v>826</v>
+      </c>
+      <c r="K1267" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1267" s="19"/>
+      <c r="M1267" s="19"/>
+      <c r="N1267" s="19"/>
+      <c r="O1267" s="19"/>
+      <c r="P1267" s="19"/>
+      <c r="Q1267" s="12">
+        <v>77427297</v>
+      </c>
+      <c r="R1267" s="25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:18" ht="15" thickBot="1">
+      <c r="A1268" s="2">
+        <v>77</v>
+      </c>
+      <c r="B1268" s="11">
+        <v>46234</v>
+      </c>
+      <c r="C1268" s="19"/>
+      <c r="D1268" s="19"/>
+      <c r="E1268" s="19"/>
+      <c r="F1268" s="19"/>
+      <c r="G1268" s="15">
+        <v>8201</v>
+      </c>
+      <c r="H1268" s="16">
+        <v>2269</v>
+      </c>
+      <c r="I1268" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1268" s="20" t="s">
+        <v>826</v>
+      </c>
+      <c r="K1268" s="19"/>
+      <c r="L1268" s="19"/>
+      <c r="M1268" s="19"/>
+      <c r="N1268" s="19"/>
+      <c r="O1268" s="19"/>
+      <c r="P1268" s="19"/>
+      <c r="Q1268" s="19"/>
+      <c r="R1268" s="25" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F56EE23B-CAD1-4246-9C39-CC116A7F54DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{054E8D66-A081-4468-B0D9-C30EE434B6BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10743" uniqueCount="2254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10750" uniqueCount="2255">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -6801,6 +6801,9 @@
   </si>
   <si>
     <t>YASIR IQBAL MALIKLI LIAQAT ALI</t>
+  </si>
+  <si>
+    <t>FAUD AHMED</t>
   </si>
 </sst>
 </file>
@@ -7210,7 +7213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7578,6 +7581,30 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7892,7 +7919,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1439"/>
+  <dimension ref="A1:R1440"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -77118,6 +77145,50 @@
         <v>24</v>
       </c>
     </row>
+    <row r="1440" spans="1:18" ht="15" thickBot="1">
+      <c r="A1440" s="2">
+        <v>30</v>
+      </c>
+      <c r="B1440" s="11">
+        <v>46236</v>
+      </c>
+      <c r="C1440" s="124" t="s">
+        <v>2254</v>
+      </c>
+      <c r="D1440" s="124">
+        <v>11290069</v>
+      </c>
+      <c r="E1440" s="125" t="s">
+        <v>818</v>
+      </c>
+      <c r="F1440" s="126" t="s">
+        <v>819</v>
+      </c>
+      <c r="G1440" s="127">
+        <v>4912</v>
+      </c>
+      <c r="H1440" s="128">
+        <v>4706</v>
+      </c>
+      <c r="I1440" s="126" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1440" s="128" t="s">
+        <v>1916</v>
+      </c>
+      <c r="K1440" s="129" t="s">
+        <v>859</v>
+      </c>
+      <c r="L1440" s="123"/>
+      <c r="M1440" s="123"/>
+      <c r="N1440" s="130"/>
+      <c r="O1440" s="123"/>
+      <c r="P1440" s="123"/>
+      <c r="Q1440" s="123"/>
+      <c r="R1440" s="22" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{054E8D66-A081-4468-B0D9-C30EE434B6BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7B02DDD-BBE2-4AB9-BFEE-DE772946E49D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10750" uniqueCount="2255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10764" uniqueCount="2257">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -6804,6 +6804,12 @@
   </si>
   <si>
     <t>FAUD AHMED</t>
+  </si>
+  <si>
+    <t>SAID RASHID</t>
+  </si>
+  <si>
+    <t>KHALID KHAMIS</t>
   </si>
 </sst>
 </file>
@@ -7213,7 +7219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7605,6 +7611,15 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7919,7 +7934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1440"/>
+  <dimension ref="A1:R1442"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -77189,6 +77204,94 @@
         <v>12</v>
       </c>
     </row>
+    <row r="1441" spans="1:18" ht="15" thickBot="1">
+      <c r="A1441" s="131">
+        <v>34</v>
+      </c>
+      <c r="B1441" s="132">
+        <v>46236</v>
+      </c>
+      <c r="C1441" s="124" t="s">
+        <v>2255</v>
+      </c>
+      <c r="D1441" s="124">
+        <v>19626369</v>
+      </c>
+      <c r="E1441" s="125" t="s">
+        <v>818</v>
+      </c>
+      <c r="F1441" s="126" t="s">
+        <v>819</v>
+      </c>
+      <c r="G1441" s="127">
+        <v>9372</v>
+      </c>
+      <c r="H1441" s="128">
+        <v>7029</v>
+      </c>
+      <c r="I1441" s="126" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1441" s="128" t="s">
+        <v>1916</v>
+      </c>
+      <c r="K1441" s="129" t="s">
+        <v>859</v>
+      </c>
+      <c r="L1441" s="123"/>
+      <c r="M1441" s="123"/>
+      <c r="N1441" s="130"/>
+      <c r="O1441" s="123"/>
+      <c r="P1441" s="123"/>
+      <c r="Q1441" s="123"/>
+      <c r="R1441" s="133" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:18" ht="15" thickBot="1">
+      <c r="A1442" s="2">
+        <v>35</v>
+      </c>
+      <c r="B1442" s="11">
+        <v>46236</v>
+      </c>
+      <c r="C1442" s="12" t="s">
+        <v>2256</v>
+      </c>
+      <c r="D1442" s="12">
+        <v>12463573</v>
+      </c>
+      <c r="E1442" s="75" t="s">
+        <v>818</v>
+      </c>
+      <c r="F1442" s="17" t="s">
+        <v>819</v>
+      </c>
+      <c r="G1442" s="15">
+        <v>-3270</v>
+      </c>
+      <c r="H1442" s="16">
+        <v>6440</v>
+      </c>
+      <c r="I1442" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1442" s="16" t="s">
+        <v>1916</v>
+      </c>
+      <c r="K1442" s="42" t="s">
+        <v>859</v>
+      </c>
+      <c r="L1442" s="19"/>
+      <c r="M1442" s="19"/>
+      <c r="N1442" s="112"/>
+      <c r="O1442" s="19"/>
+      <c r="P1442" s="19"/>
+      <c r="Q1442" s="19"/>
+      <c r="R1442" s="22" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{832BB6F8-B7FB-4BF8-9883-5AD0EC15C97B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E705F7-CBF2-4974-8F53-CE2ADD973BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9111" uniqueCount="1884">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9283" uniqueCount="1917">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -5665,9 +5665,6 @@
     <t>KHALID BASHIR</t>
   </si>
   <si>
-    <t>CD3847255</t>
-  </si>
-  <si>
     <t>SAFDAR IQBAL</t>
   </si>
   <si>
@@ -5690,6 +5687,108 @@
   </si>
   <si>
     <t>ZM1790254</t>
+  </si>
+  <si>
+    <t>TRUCK CHANGED</t>
+  </si>
+  <si>
+    <t>ZUBAIR</t>
+  </si>
+  <si>
+    <t>AMIR</t>
+  </si>
+  <si>
+    <t>SOYAB KHAN</t>
+  </si>
+  <si>
+    <t>R8013574</t>
+  </si>
+  <si>
+    <t>KAMEEL</t>
+  </si>
+  <si>
+    <t>N00310592</t>
+  </si>
+  <si>
+    <t>ZAMAN</t>
+  </si>
+  <si>
+    <t>SARFRAZ</t>
+  </si>
+  <si>
+    <t>SAAD HASAN</t>
+  </si>
+  <si>
+    <t>SAEED ABDUL</t>
+  </si>
+  <si>
+    <t>ALI AHMED</t>
+  </si>
+  <si>
+    <t>SHAHZAD AKHTAR</t>
+  </si>
+  <si>
+    <t>KHAN SHAFI ULLAH</t>
+  </si>
+  <si>
+    <t>SC4144883</t>
+  </si>
+  <si>
+    <t>KALEEM BAI</t>
+  </si>
+  <si>
+    <t>AZHAR ADNAN</t>
+  </si>
+  <si>
+    <t>HL1840633</t>
+  </si>
+  <si>
+    <t>WASEEM MUHAMMAED</t>
+  </si>
+  <si>
+    <t>CX6854163</t>
+  </si>
+  <si>
+    <t>CHAND MAM</t>
+  </si>
+  <si>
+    <t>ZA064801</t>
+  </si>
+  <si>
+    <t>VIKAS</t>
+  </si>
+  <si>
+    <t>DAYA RAM JIT</t>
+  </si>
+  <si>
+    <t>ZA376408</t>
+  </si>
+  <si>
+    <t>98751-</t>
+  </si>
+  <si>
+    <t>MOHID MUHAMMAD</t>
+  </si>
+  <si>
+    <t>BD0174891</t>
+  </si>
+  <si>
+    <t>MANNE VENKATESWARLU</t>
+  </si>
+  <si>
+    <t>Z3852990</t>
+  </si>
+  <si>
+    <t>NAEEM</t>
+  </si>
+  <si>
+    <t>R/IMRAN</t>
+  </si>
+  <si>
+    <t>JABAR</t>
+  </si>
+  <si>
+    <t>198-</t>
   </si>
 </sst>
 </file>
@@ -5994,7 +6093,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -6062,78 +6161,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6357,22 +6389,42 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6687,7 +6739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1234"/>
+  <dimension ref="A1:R1254"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -56719,7 +56771,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="1080" spans="1:18" ht="15" thickBot="1">
+    <row r="1080" spans="1:18" ht="21" thickBot="1">
       <c r="A1080" s="2">
         <v>1079</v>
       </c>
@@ -56739,7 +56791,7 @@
         <v>123</v>
       </c>
       <c r="G1080" s="57">
-        <v>4806</v>
+        <v>7100</v>
       </c>
       <c r="H1080" s="15">
         <v>8078</v>
@@ -56750,14 +56802,16 @@
       <c r="J1080" s="15" t="s">
         <v>1673</v>
       </c>
-      <c r="K1080" s="17" t="s">
-        <v>13</v>
+      <c r="K1080" s="68" t="s">
+        <v>1286</v>
       </c>
       <c r="L1080" s="18"/>
       <c r="M1080" s="18"/>
       <c r="N1080" s="40"/>
       <c r="O1080" s="18"/>
-      <c r="P1080" s="18"/>
+      <c r="P1080" s="50" t="s">
+        <v>1883</v>
+      </c>
       <c r="Q1080" s="18"/>
       <c r="R1080" s="22" t="s">
         <v>132</v>
@@ -61727,7 +61781,7 @@
       <c r="K1197" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="L1197" s="78"/>
+      <c r="L1197" s="18"/>
       <c r="M1197" s="18"/>
       <c r="N1197" s="55">
         <v>353</v>
@@ -61774,9 +61828,11 @@
       <c r="J1198" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1198" s="75"/>
-      <c r="L1198" s="80"/>
-      <c r="M1198" s="77"/>
+      <c r="K1198" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1198" s="18"/>
+      <c r="M1198" s="18"/>
       <c r="N1198" s="40"/>
       <c r="O1198" s="18"/>
       <c r="P1198" s="18"/>
@@ -61818,9 +61874,11 @@
       <c r="J1199" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1199" s="75"/>
-      <c r="L1199" s="80"/>
-      <c r="M1199" s="77"/>
+      <c r="K1199" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1199" s="18"/>
+      <c r="M1199" s="18"/>
       <c r="N1199" s="40"/>
       <c r="O1199" s="18"/>
       <c r="P1199" s="18"/>
@@ -61862,11 +61920,11 @@
       <c r="J1200" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1200" s="76" t="s">
+      <c r="K1200" s="30" t="s">
         <v>1597</v>
       </c>
-      <c r="L1200" s="80"/>
-      <c r="M1200" s="77"/>
+      <c r="L1200" s="18"/>
+      <c r="M1200" s="18"/>
       <c r="N1200" s="40"/>
       <c r="O1200" s="18"/>
       <c r="P1200" s="18"/>
@@ -61908,9 +61966,11 @@
       <c r="J1201" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1201" s="75"/>
-      <c r="L1201" s="80"/>
-      <c r="M1201" s="77"/>
+      <c r="K1201" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1201" s="18"/>
+      <c r="M1201" s="18"/>
       <c r="N1201" s="40"/>
       <c r="O1201" s="18"/>
       <c r="P1201" s="18"/>
@@ -61952,9 +62012,11 @@
       <c r="J1202" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1202" s="75"/>
-      <c r="L1202" s="80"/>
-      <c r="M1202" s="77"/>
+      <c r="K1202" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1202" s="18"/>
+      <c r="M1202" s="18"/>
       <c r="N1202" s="40"/>
       <c r="O1202" s="18"/>
       <c r="P1202" s="18"/>
@@ -61996,9 +62058,11 @@
       <c r="J1203" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1203" s="75"/>
-      <c r="L1203" s="80"/>
-      <c r="M1203" s="77"/>
+      <c r="K1203" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1203" s="18"/>
+      <c r="M1203" s="18"/>
       <c r="N1203" s="40"/>
       <c r="O1203" s="18"/>
       <c r="P1203" s="18"/>
@@ -62040,9 +62104,11 @@
       <c r="J1204" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1204" s="75"/>
-      <c r="L1204" s="80"/>
-      <c r="M1204" s="77"/>
+      <c r="K1204" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1204" s="18"/>
+      <c r="M1204" s="18"/>
       <c r="N1204" s="40"/>
       <c r="O1204" s="18"/>
       <c r="P1204" s="18"/>
@@ -62084,9 +62150,11 @@
       <c r="J1205" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1205" s="75"/>
-      <c r="L1205" s="80"/>
-      <c r="M1205" s="77"/>
+      <c r="K1205" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1205" s="18"/>
+      <c r="M1205" s="18"/>
       <c r="N1205" s="40"/>
       <c r="O1205" s="18"/>
       <c r="P1205" s="18"/>
@@ -62128,9 +62196,11 @@
       <c r="J1206" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1206" s="75"/>
-      <c r="L1206" s="80"/>
-      <c r="M1206" s="77"/>
+      <c r="K1206" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1206" s="18"/>
+      <c r="M1206" s="18"/>
       <c r="N1206" s="40"/>
       <c r="O1206" s="18"/>
       <c r="P1206" s="18"/>
@@ -62172,9 +62242,11 @@
       <c r="J1207" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1207" s="75"/>
-      <c r="L1207" s="80"/>
-      <c r="M1207" s="77"/>
+      <c r="K1207" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1207" s="18"/>
+      <c r="M1207" s="18"/>
       <c r="N1207" s="40"/>
       <c r="O1207" s="18"/>
       <c r="P1207" s="18"/>
@@ -62216,9 +62288,11 @@
       <c r="J1208" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1208" s="75"/>
-      <c r="L1208" s="80"/>
-      <c r="M1208" s="77"/>
+      <c r="K1208" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1208" s="18"/>
+      <c r="M1208" s="18"/>
       <c r="N1208" s="55">
         <v>322</v>
       </c>
@@ -62254,9 +62328,9 @@
       <c r="J1209" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1209" s="75"/>
-      <c r="L1209" s="80"/>
-      <c r="M1209" s="77"/>
+      <c r="K1209" s="18"/>
+      <c r="L1209" s="18"/>
+      <c r="M1209" s="18"/>
       <c r="N1209" s="40"/>
       <c r="O1209" s="18"/>
       <c r="P1209" s="18"/>
@@ -62296,9 +62370,11 @@
       <c r="J1210" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1210" s="75"/>
-      <c r="L1210" s="80"/>
-      <c r="M1210" s="77"/>
+      <c r="K1210" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1210" s="18"/>
+      <c r="M1210" s="18"/>
       <c r="N1210" s="40"/>
       <c r="O1210" s="18"/>
       <c r="P1210" s="18"/>
@@ -62340,9 +62416,11 @@
       <c r="J1211" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1211" s="75"/>
-      <c r="L1211" s="80"/>
-      <c r="M1211" s="77"/>
+      <c r="K1211" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1211" s="18"/>
+      <c r="M1211" s="18"/>
       <c r="N1211" s="40"/>
       <c r="O1211" s="18"/>
       <c r="P1211" s="18"/>
@@ -62376,9 +62454,9 @@
       <c r="J1212" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1212" s="75"/>
-      <c r="L1212" s="80"/>
-      <c r="M1212" s="77"/>
+      <c r="K1212" s="18"/>
+      <c r="L1212" s="18"/>
+      <c r="M1212" s="18"/>
       <c r="N1212" s="40"/>
       <c r="O1212" s="18"/>
       <c r="P1212" s="18"/>
@@ -62418,9 +62496,11 @@
       <c r="J1213" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1213" s="75"/>
-      <c r="L1213" s="80"/>
-      <c r="M1213" s="77"/>
+      <c r="K1213" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1213" s="18"/>
+      <c r="M1213" s="18"/>
       <c r="N1213" s="40"/>
       <c r="O1213" s="18"/>
       <c r="P1213" s="18"/>
@@ -62462,9 +62542,11 @@
       <c r="J1214" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1214" s="75"/>
-      <c r="L1214" s="80"/>
-      <c r="M1214" s="77"/>
+      <c r="K1214" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1214" s="18"/>
+      <c r="M1214" s="18"/>
       <c r="N1214" s="40"/>
       <c r="O1214" s="18"/>
       <c r="P1214" s="18"/>
@@ -62498,11 +62580,11 @@
       <c r="J1215" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1215" s="76" t="s">
+      <c r="K1215" s="30" t="s">
         <v>1597</v>
       </c>
-      <c r="L1215" s="80"/>
-      <c r="M1215" s="77"/>
+      <c r="L1215" s="18"/>
+      <c r="M1215" s="18"/>
       <c r="N1215" s="40"/>
       <c r="O1215" s="18"/>
       <c r="P1215" s="18"/>
@@ -62542,9 +62624,11 @@
       <c r="J1216" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1216" s="75"/>
-      <c r="L1216" s="80"/>
-      <c r="M1216" s="77"/>
+      <c r="K1216" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1216" s="18"/>
+      <c r="M1216" s="18"/>
       <c r="N1216" s="40"/>
       <c r="O1216" s="18"/>
       <c r="P1216" s="18"/>
@@ -62586,9 +62670,11 @@
       <c r="J1217" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1217" s="75"/>
-      <c r="L1217" s="80"/>
-      <c r="M1217" s="77"/>
+      <c r="K1217" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1217" s="18"/>
+      <c r="M1217" s="18"/>
       <c r="N1217" s="40"/>
       <c r="O1217" s="18"/>
       <c r="P1217" s="18"/>
@@ -62630,9 +62716,11 @@
       <c r="J1218" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1218" s="75"/>
-      <c r="L1218" s="80"/>
-      <c r="M1218" s="77"/>
+      <c r="K1218" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1218" s="18"/>
+      <c r="M1218" s="18"/>
       <c r="N1218" s="40"/>
       <c r="O1218" s="18"/>
       <c r="P1218" s="18"/>
@@ -62674,9 +62762,11 @@
       <c r="J1219" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1219" s="75"/>
-      <c r="L1219" s="80"/>
-      <c r="M1219" s="77"/>
+      <c r="K1219" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1219" s="18"/>
+      <c r="M1219" s="18"/>
       <c r="N1219" s="40"/>
       <c r="O1219" s="18"/>
       <c r="P1219" s="18"/>
@@ -62718,9 +62808,11 @@
       <c r="J1220" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1220" s="75"/>
-      <c r="L1220" s="80"/>
-      <c r="M1220" s="77"/>
+      <c r="K1220" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1220" s="18"/>
+      <c r="M1220" s="18"/>
       <c r="N1220" s="55">
         <v>321</v>
       </c>
@@ -62759,7 +62851,7 @@
       <c r="K1221" s="30" t="s">
         <v>1597</v>
       </c>
-      <c r="L1221" s="79"/>
+      <c r="L1221" s="18"/>
       <c r="M1221" s="18"/>
       <c r="N1221" s="55">
         <v>358</v>
@@ -62817,10 +62909,12 @@
       <c r="C1223" s="56" t="s">
         <v>1874</v>
       </c>
-      <c r="D1223" s="56" t="s">
-        <v>1875</v>
-      </c>
-      <c r="E1223" s="18"/>
+      <c r="D1223" s="56">
+        <v>101198406</v>
+      </c>
+      <c r="E1223" s="12" t="s">
+        <v>22</v>
+      </c>
       <c r="F1223" s="16" t="s">
         <v>123</v>
       </c>
@@ -62836,13 +62930,17 @@
       <c r="J1223" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1223" s="18"/>
+      <c r="K1223" s="17" t="s">
+        <v>13</v>
+      </c>
       <c r="L1223" s="18"/>
       <c r="M1223" s="18"/>
       <c r="N1223" s="40"/>
       <c r="O1223" s="18"/>
       <c r="P1223" s="18"/>
-      <c r="Q1223" s="18"/>
+      <c r="Q1223" s="15">
+        <v>96709596</v>
+      </c>
       <c r="R1223" s="22" t="s">
         <v>132</v>
       </c>
@@ -62870,7 +62968,9 @@
       <c r="J1224" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1224" s="18"/>
+      <c r="K1224" s="30" t="s">
+        <v>1597</v>
+      </c>
       <c r="L1224" s="18"/>
       <c r="M1224" s="18"/>
       <c r="N1224" s="40"/>
@@ -62904,7 +63004,9 @@
       <c r="J1225" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1225" s="18"/>
+      <c r="K1225" s="30" t="s">
+        <v>1597</v>
+      </c>
       <c r="L1225" s="18"/>
       <c r="M1225" s="18"/>
       <c r="N1225" s="40"/>
@@ -62922,9 +63024,15 @@
       <c r="B1226" s="10">
         <v>46244</v>
       </c>
-      <c r="C1226" s="38"/>
-      <c r="D1226" s="38"/>
-      <c r="E1226" s="18"/>
+      <c r="C1226" s="56" t="s">
+        <v>433</v>
+      </c>
+      <c r="D1226" s="56">
+        <v>94734526</v>
+      </c>
+      <c r="E1226" s="12" t="s">
+        <v>22</v>
+      </c>
       <c r="F1226" s="16" t="s">
         <v>123</v>
       </c>
@@ -62940,13 +63048,17 @@
       <c r="J1226" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="K1226" s="18"/>
+      <c r="K1226" s="17" t="s">
+        <v>13</v>
+      </c>
       <c r="L1226" s="18"/>
       <c r="M1226" s="18"/>
       <c r="N1226" s="40"/>
       <c r="O1226" s="18"/>
       <c r="P1226" s="18"/>
-      <c r="Q1226" s="18"/>
+      <c r="Q1226" s="15">
+        <v>77454348</v>
+      </c>
       <c r="R1226" s="22" t="s">
         <v>132</v>
       </c>
@@ -62959,10 +63071,10 @@
         <v>46244</v>
       </c>
       <c r="C1227" s="56" t="s">
-        <v>1876</v>
+        <v>1884</v>
       </c>
       <c r="D1227" s="56">
-        <v>112067329</v>
+        <v>116911156</v>
       </c>
       <c r="E1227" s="12" t="s">
         <v>22</v>
@@ -62971,29 +63083,33 @@
         <v>123</v>
       </c>
       <c r="G1227" s="57">
-        <v>2968</v>
+        <v>4479</v>
       </c>
       <c r="H1227" s="15">
-        <v>5613</v>
-      </c>
-      <c r="I1227" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1227" s="15" t="s">
-        <v>840</v>
-      </c>
-      <c r="K1227" s="18"/>
+        <v>3757</v>
+      </c>
+      <c r="I1227" s="22" t="s">
+        <v>564</v>
+      </c>
+      <c r="J1227" s="51" t="s">
+        <v>565</v>
+      </c>
+      <c r="K1227" s="17" t="s">
+        <v>13</v>
+      </c>
       <c r="L1227" s="18"/>
       <c r="M1227" s="18"/>
       <c r="N1227" s="40"/>
       <c r="O1227" s="18"/>
       <c r="P1227" s="18"/>
-      <c r="Q1227" s="18"/>
-      <c r="R1227" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="1228" spans="1:18" ht="27.6" thickBot="1">
+      <c r="Q1227" s="15">
+        <v>96894139420</v>
+      </c>
+      <c r="R1227" s="22" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:18" ht="15" thickBot="1">
       <c r="A1228" s="2">
         <v>1227</v>
       </c>
@@ -63001,10 +63117,10 @@
         <v>46244</v>
       </c>
       <c r="C1228" s="56" t="s">
-        <v>1877</v>
+        <v>1885</v>
       </c>
       <c r="D1228" s="56">
-        <v>116806083</v>
+        <v>85817633</v>
       </c>
       <c r="E1228" s="12" t="s">
         <v>22</v>
@@ -63013,29 +63129,27 @@
         <v>123</v>
       </c>
       <c r="G1228" s="57">
-        <v>442</v>
+        <v>9082</v>
       </c>
       <c r="H1228" s="15">
-        <v>7536</v>
-      </c>
-      <c r="I1228" s="16" t="s">
-        <v>11</v>
+        <v>3546</v>
+      </c>
+      <c r="I1228" s="22" t="s">
+        <v>564</v>
       </c>
       <c r="J1228" s="15" t="s">
-        <v>951</v>
-      </c>
-      <c r="K1228" s="18"/>
+        <v>1673</v>
+      </c>
+      <c r="K1228" s="17" t="s">
+        <v>13</v>
+      </c>
       <c r="L1228" s="18"/>
       <c r="M1228" s="18"/>
       <c r="N1228" s="40"/>
       <c r="O1228" s="18"/>
       <c r="P1228" s="18"/>
-      <c r="Q1228" s="11">
-        <v>79997138</v>
-      </c>
-      <c r="R1228" s="20" t="s">
-        <v>12</v>
-      </c>
+      <c r="Q1228" s="18"/>
+      <c r="R1228" s="18"/>
     </row>
     <row r="1229" spans="1:18" ht="15" thickBot="1">
       <c r="A1229" s="2">
@@ -63045,41 +63159,41 @@
         <v>46244</v>
       </c>
       <c r="C1229" s="56" t="s">
-        <v>1878</v>
-      </c>
-      <c r="D1229" s="56">
-        <v>113458078</v>
+        <v>1886</v>
+      </c>
+      <c r="D1229" s="56" t="s">
+        <v>1887</v>
       </c>
       <c r="E1229" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F1229" s="16" t="s">
-        <v>123</v>
+      <c r="F1229" s="13" t="s">
+        <v>23</v>
       </c>
       <c r="G1229" s="57">
-        <v>5913</v>
+        <v>81144</v>
       </c>
       <c r="H1229" s="15">
-        <v>1154</v>
-      </c>
-      <c r="I1229" s="16" t="s">
-        <v>11</v>
+        <v>55344</v>
+      </c>
+      <c r="I1229" s="22" t="s">
+        <v>564</v>
       </c>
       <c r="J1229" s="15" t="s">
-        <v>951</v>
-      </c>
-      <c r="K1229" s="18"/>
+        <v>1673</v>
+      </c>
+      <c r="K1229" s="17" t="s">
+        <v>13</v>
+      </c>
       <c r="L1229" s="18"/>
       <c r="M1229" s="18"/>
       <c r="N1229" s="40"/>
       <c r="O1229" s="18"/>
       <c r="P1229" s="18"/>
       <c r="Q1229" s="18"/>
-      <c r="R1229" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="1230" spans="1:18" ht="27.6" thickBot="1">
+      <c r="R1229" s="18"/>
+    </row>
+    <row r="1230" spans="1:18" ht="15" thickBot="1">
       <c r="A1230" s="2">
         <v>1229</v>
       </c>
@@ -63087,41 +63201,41 @@
         <v>46244</v>
       </c>
       <c r="C1230" s="56" t="s">
-        <v>639</v>
-      </c>
-      <c r="D1230" s="56">
-        <v>122952217</v>
-      </c>
-      <c r="E1230" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1230" s="16" t="s">
-        <v>123</v>
+        <v>1888</v>
+      </c>
+      <c r="D1230" s="56" t="s">
+        <v>1889</v>
+      </c>
+      <c r="E1230" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1230" s="13" t="s">
+        <v>23</v>
       </c>
       <c r="G1230" s="57">
-        <v>4581</v>
+        <v>15562</v>
       </c>
       <c r="H1230" s="15">
-        <v>-8325</v>
+        <v>74553</v>
       </c>
       <c r="I1230" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="J1230" s="15" t="s">
-        <v>951</v>
-      </c>
-      <c r="K1230" s="18"/>
-      <c r="L1230" s="18"/>
+      <c r="J1230" s="52" t="s">
+        <v>777</v>
+      </c>
+      <c r="K1230" s="61" t="s">
+        <v>1190</v>
+      </c>
+      <c r="L1230" s="15">
+        <v>566209290</v>
+      </c>
       <c r="M1230" s="18"/>
       <c r="N1230" s="40"/>
       <c r="O1230" s="18"/>
       <c r="P1230" s="18"/>
-      <c r="Q1230" s="11" t="s">
-        <v>1879</v>
-      </c>
-      <c r="R1230" s="20" t="s">
-        <v>12</v>
-      </c>
+      <c r="Q1230" s="18"/>
+      <c r="R1230" s="18"/>
     </row>
     <row r="1231" spans="1:18" ht="15" thickBot="1">
       <c r="A1231" s="2">
@@ -63131,10 +63245,10 @@
         <v>46244</v>
       </c>
       <c r="C1231" s="56" t="s">
-        <v>1880</v>
+        <v>1890</v>
       </c>
       <c r="D1231" s="56">
-        <v>126214395</v>
+        <v>107948231</v>
       </c>
       <c r="E1231" s="12" t="s">
         <v>22</v>
@@ -63143,29 +63257,31 @@
         <v>123</v>
       </c>
       <c r="G1231" s="57">
-        <v>355</v>
+        <v>1602</v>
       </c>
       <c r="H1231" s="15">
-        <v>2278</v>
+        <v>1099</v>
       </c>
       <c r="I1231" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="J1231" s="15" t="s">
-        <v>951</v>
-      </c>
-      <c r="K1231" s="18"/>
-      <c r="L1231" s="18"/>
+      <c r="J1231" s="52" t="s">
+        <v>777</v>
+      </c>
+      <c r="K1231" s="61" t="s">
+        <v>1190</v>
+      </c>
+      <c r="L1231" s="15">
+        <v>96892448478</v>
+      </c>
       <c r="M1231" s="18"/>
       <c r="N1231" s="40"/>
       <c r="O1231" s="18"/>
       <c r="P1231" s="18"/>
       <c r="Q1231" s="18"/>
-      <c r="R1231" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="1232" spans="1:18" ht="28.2" thickBot="1">
+      <c r="R1231" s="18"/>
+    </row>
+    <row r="1232" spans="1:18" ht="15" thickBot="1">
       <c r="A1232" s="2">
         <v>1231</v>
       </c>
@@ -63173,43 +63289,43 @@
         <v>46244</v>
       </c>
       <c r="C1232" s="56" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1232" s="56" t="s">
-        <v>1881</v>
+        <v>1891</v>
+      </c>
+      <c r="D1232" s="56">
+        <v>76217672</v>
       </c>
       <c r="E1232" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F1232" s="13" t="s">
-        <v>23</v>
+      <c r="F1232" s="16" t="s">
+        <v>123</v>
       </c>
       <c r="G1232" s="57">
-        <v>33404</v>
+        <v>4465</v>
       </c>
       <c r="H1232" s="15">
-        <v>89137</v>
+        <v>8001</v>
       </c>
       <c r="I1232" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="J1232" s="15" t="s">
-        <v>1882</v>
-      </c>
-      <c r="K1232" s="18"/>
-      <c r="L1232" s="18"/>
+      <c r="J1232" s="52" t="s">
+        <v>777</v>
+      </c>
+      <c r="K1232" s="61" t="s">
+        <v>1190</v>
+      </c>
+      <c r="L1232" s="15">
+        <v>93317831</v>
+      </c>
       <c r="M1232" s="18"/>
       <c r="N1232" s="40"/>
       <c r="O1232" s="18"/>
       <c r="P1232" s="18"/>
-      <c r="Q1232" s="11">
-        <v>95643750</v>
-      </c>
-      <c r="R1232" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="1233" spans="1:18" ht="28.2" thickBot="1">
+      <c r="Q1232" s="18"/>
+      <c r="R1232" s="18"/>
+    </row>
+    <row r="1233" spans="1:18" ht="15" thickBot="1">
       <c r="A1233" s="2">
         <v>1232</v>
       </c>
@@ -63217,43 +63333,41 @@
         <v>46244</v>
       </c>
       <c r="C1233" s="56" t="s">
-        <v>505</v>
-      </c>
-      <c r="D1233" s="56" t="s">
-        <v>1883</v>
+        <v>1892</v>
+      </c>
+      <c r="D1233" s="56">
+        <v>113802138</v>
       </c>
       <c r="E1233" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F1233" s="13" t="s">
-        <v>23</v>
+      <c r="F1233" s="16" t="s">
+        <v>123</v>
       </c>
       <c r="G1233" s="57">
-        <v>7606</v>
+        <v>1777</v>
       </c>
       <c r="H1233" s="15">
-        <v>66793</v>
+        <v>9472</v>
       </c>
       <c r="I1233" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="J1233" s="15" t="s">
-        <v>1882</v>
-      </c>
-      <c r="K1233" s="18"/>
+      <c r="J1233" s="52" t="s">
+        <v>777</v>
+      </c>
+      <c r="K1233" s="61" t="s">
+        <v>1190</v>
+      </c>
       <c r="L1233" s="18"/>
       <c r="M1233" s="18"/>
       <c r="N1233" s="40"/>
       <c r="O1233" s="18"/>
       <c r="P1233" s="18"/>
-      <c r="Q1233" s="11">
-        <v>501924525</v>
-      </c>
-      <c r="R1233" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="1234" spans="1:18" ht="27.6" thickBot="1">
+      <c r="Q1233" s="18"/>
+      <c r="R1233" s="18"/>
+    </row>
+    <row r="1234" spans="1:18" ht="15" thickBot="1">
       <c r="A1234" s="2">
         <v>1233</v>
       </c>
@@ -63261,10 +63375,10 @@
         <v>46244</v>
       </c>
       <c r="C1234" s="56" t="s">
-        <v>907</v>
+        <v>1893</v>
       </c>
       <c r="D1234" s="56">
-        <v>128333109</v>
+        <v>77396496</v>
       </c>
       <c r="E1234" s="12" t="s">
         <v>22</v>
@@ -63273,28 +63387,922 @@
         <v>123</v>
       </c>
       <c r="G1234" s="57">
-        <v>4900</v>
+        <v>3536</v>
       </c>
       <c r="H1234" s="15">
-        <v>-6338</v>
+        <v>9212</v>
       </c>
       <c r="I1234" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="J1234" s="15" t="s">
-        <v>891</v>
-      </c>
-      <c r="K1234" s="18"/>
+      <c r="J1234" s="52" t="s">
+        <v>777</v>
+      </c>
+      <c r="K1234" s="17" t="s">
+        <v>13</v>
+      </c>
       <c r="L1234" s="18"/>
       <c r="M1234" s="18"/>
       <c r="N1234" s="40"/>
       <c r="O1234" s="18"/>
       <c r="P1234" s="18"/>
-      <c r="Q1234" s="11">
+      <c r="Q1234" s="18"/>
+      <c r="R1234" s="18"/>
+    </row>
+    <row r="1235" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1235" s="2">
+        <v>1234</v>
+      </c>
+      <c r="B1235" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1235" s="56" t="s">
+        <v>1894</v>
+      </c>
+      <c r="D1235" s="56">
+        <v>131422754</v>
+      </c>
+      <c r="E1235" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1235" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1235" s="57">
+        <v>3097</v>
+      </c>
+      <c r="H1235" s="15">
+        <v>3993</v>
+      </c>
+      <c r="I1235" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="J1235" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="K1235" s="18"/>
+      <c r="L1235" s="15">
+        <v>78615034</v>
+      </c>
+      <c r="M1235" s="18"/>
+      <c r="N1235" s="40"/>
+      <c r="O1235" s="18"/>
+      <c r="P1235" s="18"/>
+      <c r="Q1235" s="18"/>
+      <c r="R1235" s="18"/>
+    </row>
+    <row r="1236" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1236" s="2">
+        <v>1235</v>
+      </c>
+      <c r="B1236" s="75">
+        <v>46244</v>
+      </c>
+      <c r="C1236" s="76" t="s">
+        <v>1913</v>
+      </c>
+      <c r="D1236" s="76">
+        <v>109499244</v>
+      </c>
+      <c r="E1236" s="86" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1236" s="78" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1236" s="79">
+        <v>6018</v>
+      </c>
+      <c r="H1236" s="80">
+        <v>8793</v>
+      </c>
+      <c r="I1236" s="80" t="s">
+        <v>124</v>
+      </c>
+      <c r="J1236" s="80" t="s">
+        <v>1914</v>
+      </c>
+      <c r="K1236" s="82"/>
+      <c r="L1236" s="80">
+        <v>78735597</v>
+      </c>
+      <c r="M1236" s="82"/>
+      <c r="N1236" s="83"/>
+      <c r="O1236" s="82"/>
+      <c r="P1236" s="82"/>
+      <c r="Q1236" s="82"/>
+      <c r="R1236" s="82"/>
+    </row>
+    <row r="1237" spans="1:18" ht="15" thickBot="1">
+      <c r="A1237" s="2">
+        <v>1236</v>
+      </c>
+      <c r="B1237" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1237" s="56" t="s">
+        <v>1875</v>
+      </c>
+      <c r="D1237" s="56">
+        <v>112067329</v>
+      </c>
+      <c r="E1237" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1237" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1237" s="57">
+        <v>2968</v>
+      </c>
+      <c r="H1237" s="15">
+        <v>5613</v>
+      </c>
+      <c r="I1237" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1237" s="15" t="s">
+        <v>840</v>
+      </c>
+      <c r="K1237" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1237" s="18"/>
+      <c r="M1237" s="18"/>
+      <c r="N1237" s="40"/>
+      <c r="O1237" s="18"/>
+      <c r="P1237" s="18"/>
+      <c r="Q1237" s="18"/>
+      <c r="R1237" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1238" s="2">
+        <v>1237</v>
+      </c>
+      <c r="B1238" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1238" s="56" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D1238" s="56">
+        <v>116806083</v>
+      </c>
+      <c r="E1238" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1238" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1238" s="57">
+        <v>442</v>
+      </c>
+      <c r="H1238" s="15">
+        <v>7536</v>
+      </c>
+      <c r="I1238" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1238" s="15" t="s">
+        <v>951</v>
+      </c>
+      <c r="K1238" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1238" s="18"/>
+      <c r="M1238" s="18"/>
+      <c r="N1238" s="40"/>
+      <c r="O1238" s="18"/>
+      <c r="P1238" s="18"/>
+      <c r="Q1238" s="11">
+        <v>79997138</v>
+      </c>
+      <c r="R1238" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:18" ht="15" thickBot="1">
+      <c r="A1239" s="2">
+        <v>1238</v>
+      </c>
+      <c r="B1239" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1239" s="56" t="s">
+        <v>1877</v>
+      </c>
+      <c r="D1239" s="56">
+        <v>113458078</v>
+      </c>
+      <c r="E1239" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1239" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1239" s="57">
+        <v>5913</v>
+      </c>
+      <c r="H1239" s="15">
+        <v>1154</v>
+      </c>
+      <c r="I1239" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1239" s="15" t="s">
+        <v>951</v>
+      </c>
+      <c r="K1239" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1239" s="18"/>
+      <c r="M1239" s="18"/>
+      <c r="N1239" s="40"/>
+      <c r="O1239" s="18"/>
+      <c r="P1239" s="18"/>
+      <c r="Q1239" s="18"/>
+      <c r="R1239" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1240" s="2">
+        <v>1239</v>
+      </c>
+      <c r="B1240" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1240" s="56" t="s">
+        <v>639</v>
+      </c>
+      <c r="D1240" s="56">
+        <v>122952217</v>
+      </c>
+      <c r="E1240" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1240" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1240" s="57">
+        <v>4581</v>
+      </c>
+      <c r="H1240" s="15">
+        <v>-8325</v>
+      </c>
+      <c r="I1240" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1240" s="15" t="s">
+        <v>951</v>
+      </c>
+      <c r="K1240" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1240" s="18"/>
+      <c r="M1240" s="18"/>
+      <c r="N1240" s="40"/>
+      <c r="O1240" s="18"/>
+      <c r="P1240" s="18"/>
+      <c r="Q1240" s="11" t="s">
+        <v>1878</v>
+      </c>
+      <c r="R1240" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:18" ht="15" thickBot="1">
+      <c r="A1241" s="2">
+        <v>1240</v>
+      </c>
+      <c r="B1241" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1241" s="56" t="s">
+        <v>1879</v>
+      </c>
+      <c r="D1241" s="56">
+        <v>126214395</v>
+      </c>
+      <c r="E1241" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1241" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1241" s="57">
+        <v>355</v>
+      </c>
+      <c r="H1241" s="15">
+        <v>2278</v>
+      </c>
+      <c r="I1241" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1241" s="15" t="s">
+        <v>951</v>
+      </c>
+      <c r="K1241" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1241" s="18"/>
+      <c r="M1241" s="18"/>
+      <c r="N1241" s="40"/>
+      <c r="O1241" s="18"/>
+      <c r="P1241" s="18"/>
+      <c r="Q1241" s="18"/>
+      <c r="R1241" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1242" s="2">
+        <v>1241</v>
+      </c>
+      <c r="B1242" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1242" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1242" s="56" t="s">
+        <v>1880</v>
+      </c>
+      <c r="E1242" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1242" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1242" s="57">
+        <v>33404</v>
+      </c>
+      <c r="H1242" s="15">
+        <v>89137</v>
+      </c>
+      <c r="I1242" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1242" s="15" t="s">
+        <v>1881</v>
+      </c>
+      <c r="K1242" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1242" s="18"/>
+      <c r="M1242" s="18"/>
+      <c r="N1242" s="40"/>
+      <c r="O1242" s="18"/>
+      <c r="P1242" s="18"/>
+      <c r="Q1242" s="11">
+        <v>95643750</v>
+      </c>
+      <c r="R1242" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1243" s="2">
+        <v>1242</v>
+      </c>
+      <c r="B1243" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1243" s="56" t="s">
+        <v>505</v>
+      </c>
+      <c r="D1243" s="56" t="s">
+        <v>1882</v>
+      </c>
+      <c r="E1243" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1243" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1243" s="57">
+        <v>7606</v>
+      </c>
+      <c r="H1243" s="15">
+        <v>66793</v>
+      </c>
+      <c r="I1243" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1243" s="15" t="s">
+        <v>1881</v>
+      </c>
+      <c r="K1243" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1243" s="18"/>
+      <c r="M1243" s="18"/>
+      <c r="N1243" s="40"/>
+      <c r="O1243" s="18"/>
+      <c r="P1243" s="18"/>
+      <c r="Q1243" s="11">
+        <v>501924525</v>
+      </c>
+      <c r="R1243" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1244" s="2">
+        <v>1243</v>
+      </c>
+      <c r="B1244" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1244" s="56" t="s">
+        <v>907</v>
+      </c>
+      <c r="D1244" s="56">
+        <v>128333109</v>
+      </c>
+      <c r="E1244" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1244" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1244" s="57">
+        <v>4900</v>
+      </c>
+      <c r="H1244" s="15">
+        <v>-6338</v>
+      </c>
+      <c r="I1244" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1244" s="15" t="s">
+        <v>891</v>
+      </c>
+      <c r="K1244" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1244" s="18"/>
+      <c r="M1244" s="18"/>
+      <c r="N1244" s="40"/>
+      <c r="O1244" s="18"/>
+      <c r="P1244" s="18"/>
+      <c r="Q1244" s="11">
         <v>95609530</v>
       </c>
-      <c r="R1234" s="20" t="s">
+      <c r="R1244" s="20" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:18" ht="15" thickBot="1">
+      <c r="A1245" s="2">
+        <v>1244</v>
+      </c>
+      <c r="B1245" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1245" s="56" t="s">
+        <v>1895</v>
+      </c>
+      <c r="D1245" s="56">
+        <v>116033629</v>
+      </c>
+      <c r="E1245" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1245" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1245" s="57">
+        <v>1702</v>
+      </c>
+      <c r="H1245" s="15">
+        <v>5164</v>
+      </c>
+      <c r="I1245" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1245" s="15" t="s">
+        <v>951</v>
+      </c>
+      <c r="K1245" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1245" s="18"/>
+      <c r="M1245" s="18"/>
+      <c r="N1245" s="40"/>
+      <c r="O1245" s="18"/>
+      <c r="P1245" s="18"/>
+      <c r="Q1245" s="11">
+        <v>94250210</v>
+      </c>
+      <c r="R1245" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1246" s="2">
+        <v>1245</v>
+      </c>
+      <c r="B1246" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1246" s="56" t="s">
+        <v>1896</v>
+      </c>
+      <c r="D1246" s="56" t="s">
+        <v>1897</v>
+      </c>
+      <c r="E1246" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1246" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1246" s="57">
+        <v>21668</v>
+      </c>
+      <c r="H1246" s="15">
+        <v>75184</v>
+      </c>
+      <c r="I1246" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1246" s="15" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K1246" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1246" s="18"/>
+      <c r="M1246" s="18"/>
+      <c r="N1246" s="40"/>
+      <c r="O1246" s="18"/>
+      <c r="P1246" s="18"/>
+      <c r="Q1246" s="11">
+        <v>557824163</v>
+      </c>
+      <c r="R1246" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1247" s="2">
+        <v>1246</v>
+      </c>
+      <c r="B1247" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1247" s="56" t="s">
+        <v>1899</v>
+      </c>
+      <c r="D1247" s="56" t="s">
+        <v>1900</v>
+      </c>
+      <c r="E1247" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1247" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1247" s="57">
+        <v>9215</v>
+      </c>
+      <c r="H1247" s="15">
+        <v>10278</v>
+      </c>
+      <c r="I1247" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1247" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="K1247" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1247" s="18"/>
+      <c r="M1247" s="18"/>
+      <c r="N1247" s="40"/>
+      <c r="O1247" s="18"/>
+      <c r="P1247" s="18"/>
+      <c r="Q1247" s="18"/>
+      <c r="R1247" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1248" s="2">
+        <v>1247</v>
+      </c>
+      <c r="B1248" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1248" s="56" t="s">
+        <v>1901</v>
+      </c>
+      <c r="D1248" s="56" t="s">
+        <v>1902</v>
+      </c>
+      <c r="E1248" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1248" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1248" s="57">
+        <v>53578</v>
+      </c>
+      <c r="H1248" s="15">
+        <v>46411</v>
+      </c>
+      <c r="I1248" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1248" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="K1248" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1248" s="18"/>
+      <c r="M1248" s="18"/>
+      <c r="N1248" s="40"/>
+      <c r="O1248" s="18"/>
+      <c r="P1248" s="18"/>
+      <c r="Q1248" s="18"/>
+      <c r="R1248" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:18" ht="15" thickBot="1">
+      <c r="A1249" s="2">
+        <v>1248</v>
+      </c>
+      <c r="B1249" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1249" s="56" t="s">
+        <v>1903</v>
+      </c>
+      <c r="D1249" s="56" t="s">
+        <v>1904</v>
+      </c>
+      <c r="E1249" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1249" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1249" s="57">
+        <v>68833</v>
+      </c>
+      <c r="H1249" s="15">
+        <v>78793</v>
+      </c>
+      <c r="I1249" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1249" s="15" t="s">
+        <v>1905</v>
+      </c>
+      <c r="K1249" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1249" s="18"/>
+      <c r="M1249" s="18"/>
+      <c r="N1249" s="40"/>
+      <c r="O1249" s="18"/>
+      <c r="P1249" s="18"/>
+      <c r="Q1249" s="11">
+        <v>554186760</v>
+      </c>
+      <c r="R1249" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:18" ht="15" thickBot="1">
+      <c r="A1250" s="2">
+        <v>1249</v>
+      </c>
+      <c r="B1250" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1250" s="56" t="s">
+        <v>1906</v>
+      </c>
+      <c r="D1250" s="56" t="s">
+        <v>1907</v>
+      </c>
+      <c r="E1250" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1250" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1250" s="57">
+        <v>56757</v>
+      </c>
+      <c r="H1250" s="15" t="s">
+        <v>1908</v>
+      </c>
+      <c r="I1250" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1250" s="15" t="s">
+        <v>1905</v>
+      </c>
+      <c r="K1250" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1250" s="18"/>
+      <c r="M1250" s="18"/>
+      <c r="N1250" s="40"/>
+      <c r="O1250" s="18"/>
+      <c r="P1250" s="18"/>
+      <c r="Q1250" s="11">
+        <v>76969759</v>
+      </c>
+      <c r="R1250" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1251" s="2">
+        <v>1250</v>
+      </c>
+      <c r="B1251" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1251" s="56" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D1251" s="56" t="s">
+        <v>1910</v>
+      </c>
+      <c r="E1251" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1251" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1251" s="57">
+        <v>61918</v>
+      </c>
+      <c r="H1251" s="15">
+        <v>19939</v>
+      </c>
+      <c r="I1251" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1251" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="K1251" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1251" s="18"/>
+      <c r="M1251" s="18"/>
+      <c r="N1251" s="40"/>
+      <c r="O1251" s="18"/>
+      <c r="P1251" s="18"/>
+      <c r="Q1251" s="18"/>
+      <c r="R1251" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1252" s="2">
+        <v>1251</v>
+      </c>
+      <c r="B1252" s="75">
+        <v>46244</v>
+      </c>
+      <c r="C1252" s="76" t="s">
+        <v>1911</v>
+      </c>
+      <c r="D1252" s="76" t="s">
+        <v>1912</v>
+      </c>
+      <c r="E1252" s="77" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1252" s="78" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1252" s="79">
+        <v>8490</v>
+      </c>
+      <c r="H1252" s="80">
+        <v>8101</v>
+      </c>
+      <c r="I1252" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1252" s="80" t="s">
+        <v>203</v>
+      </c>
+      <c r="K1252" s="81" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1252" s="82"/>
+      <c r="M1252" s="82"/>
+      <c r="N1252" s="83"/>
+      <c r="O1252" s="82"/>
+      <c r="P1252" s="82"/>
+      <c r="Q1252" s="84">
+        <v>98705284</v>
+      </c>
+      <c r="R1252" s="85" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1253" s="2">
+        <v>1252</v>
+      </c>
+      <c r="B1253" s="75">
+        <v>46244</v>
+      </c>
+      <c r="C1253" s="76" t="s">
+        <v>1915</v>
+      </c>
+      <c r="D1253" s="76">
+        <v>110877972</v>
+      </c>
+      <c r="E1253" s="86" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1253" s="78" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1253" s="79">
+        <v>5734</v>
+      </c>
+      <c r="H1253" s="80">
+        <v>235</v>
+      </c>
+      <c r="I1253" s="80" t="s">
+        <v>124</v>
+      </c>
+      <c r="J1253" s="80" t="s">
+        <v>1914</v>
+      </c>
+      <c r="K1253" s="82"/>
+      <c r="L1253" s="80">
+        <v>79031527</v>
+      </c>
+      <c r="M1253" s="82"/>
+      <c r="N1253" s="83"/>
+      <c r="O1253" s="82"/>
+      <c r="P1253" s="82"/>
+      <c r="Q1253" s="82"/>
+      <c r="R1253" s="22" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1254" s="2">
+        <v>1253</v>
+      </c>
+      <c r="B1254" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1254" s="56" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D1254" s="56">
+        <v>124842182</v>
+      </c>
+      <c r="E1254" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1254" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1254" s="57">
+        <v>9340</v>
+      </c>
+      <c r="H1254" s="15" t="s">
+        <v>1916</v>
+      </c>
+      <c r="I1254" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="J1254" s="15" t="s">
+        <v>1914</v>
+      </c>
+      <c r="K1254" s="18"/>
+      <c r="L1254" s="15">
+        <v>98172901</v>
+      </c>
+      <c r="M1254" s="18"/>
+      <c r="N1254" s="40"/>
+      <c r="O1254" s="18"/>
+      <c r="P1254" s="18"/>
+      <c r="Q1254" s="18"/>
+      <c r="R1254" s="22" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47AC62B1-1BD4-42EC-B7A3-FE9EC92E52C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8801E9E7-4691-4CEA-949B-47100BDD291A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9319" uniqueCount="1926">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9505" uniqueCount="1950">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -5812,10 +5812,82 @@
     <t>POD</t>
   </si>
   <si>
-    <t>JEBAL ALI</t>
-  </si>
-  <si>
-    <t>HEMARIYA</t>
+    <t>MULKIYA TILL 12TH</t>
+  </si>
+  <si>
+    <t>TAMIM HAMOON</t>
+  </si>
+  <si>
+    <t>HILAL HAMED</t>
+  </si>
+  <si>
+    <t>IBRAHIM SAID</t>
+  </si>
+  <si>
+    <t>YOUSUF JAMIL</t>
+  </si>
+  <si>
+    <t>JUMA KHADIM</t>
+  </si>
+  <si>
+    <t>SYED TAIMOUR</t>
+  </si>
+  <si>
+    <t>SOHAIL AHMAD</t>
+  </si>
+  <si>
+    <t>AQEEL</t>
+  </si>
+  <si>
+    <t>2180-</t>
+  </si>
+  <si>
+    <t>UMAIR HUSSAIN</t>
+  </si>
+  <si>
+    <t>3757-</t>
+  </si>
+  <si>
+    <t>41738-</t>
+  </si>
+  <si>
+    <t>HUMAYON BUTT</t>
+  </si>
+  <si>
+    <t>AK6039396</t>
+  </si>
+  <si>
+    <t>ALI SHAN</t>
+  </si>
+  <si>
+    <t>AM5106836</t>
+  </si>
+  <si>
+    <t>ATTIQUE</t>
+  </si>
+  <si>
+    <t>YV1157475</t>
+  </si>
+  <si>
+    <t>FAIZAN AKRAM</t>
+  </si>
+  <si>
+    <t>FR1325962</t>
+  </si>
+  <si>
+    <t>FQ1884802</t>
+  </si>
+  <si>
+    <t>YASIR ALI</t>
+  </si>
+  <si>
+    <t>JEETENDAR SINGH</t>
+  </si>
+  <si>
+    <t>Z6399010</t>
+  </si>
+  <si>
+    <t>FAROOQ UMAR</t>
   </si>
 </sst>
 </file>
@@ -6192,7 +6264,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6414,48 +6486,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6772,7 +6802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1258"/>
+  <dimension ref="A1:R1286"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -6839,7 +6869,9 @@
       <c r="Q1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="4"/>
+      <c r="R1" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2" spans="1:18" ht="28.2" thickBot="1">
       <c r="A2" s="2">
@@ -6872,18 +6904,18 @@
       <c r="J2" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="K2" s="37" t="s">
-        <v>175</v>
+      <c r="K2" s="68" t="s">
+        <v>1285</v>
       </c>
       <c r="L2" s="18"/>
-      <c r="M2" s="18" t="s">
-        <v>1924</v>
-      </c>
+      <c r="M2" s="18"/>
       <c r="N2" s="55">
         <v>97</v>
       </c>
       <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
+      <c r="P2" s="50" t="s">
+        <v>1924</v>
+      </c>
       <c r="Q2" s="18"/>
       <c r="R2" s="20" t="s">
         <v>11</v>
@@ -6926,9 +6958,7 @@
       <c r="L3" s="54">
         <v>46247</v>
       </c>
-      <c r="M3" s="18" t="s">
-        <v>1925</v>
-      </c>
+      <c r="M3" s="18"/>
       <c r="N3" s="55">
         <v>91</v>
       </c>
@@ -7260,7 +7290,7 @@
       <c r="L10" s="54">
         <v>46247</v>
       </c>
-      <c r="M10" s="28"/>
+      <c r="M10" s="18"/>
       <c r="N10" s="48"/>
       <c r="O10" s="28"/>
       <c r="P10" s="28"/>
@@ -7640,7 +7670,7 @@
         <v>12</v>
       </c>
       <c r="L18" s="28"/>
-      <c r="M18" s="28"/>
+      <c r="M18" s="18"/>
       <c r="N18" s="55">
         <v>331</v>
       </c>
@@ -8254,7 +8284,7 @@
       <c r="L31" s="66">
         <v>46247</v>
       </c>
-      <c r="M31" s="28"/>
+      <c r="M31" s="18"/>
       <c r="N31" s="60">
         <v>103</v>
       </c>
@@ -20660,14 +20690,16 @@
       <c r="J295" s="15" t="s">
         <v>382</v>
       </c>
-      <c r="K295" s="37" t="s">
-        <v>175</v>
+      <c r="K295" s="68" t="s">
+        <v>1285</v>
       </c>
       <c r="L295" s="18"/>
       <c r="M295" s="18"/>
       <c r="N295" s="40"/>
       <c r="O295" s="18"/>
-      <c r="P295" s="18"/>
+      <c r="P295" s="71">
+        <v>46244</v>
+      </c>
       <c r="Q295" s="11">
         <v>97970749</v>
       </c>
@@ -43374,7 +43406,9 @@
       <c r="J785" s="15" t="s">
         <v>968</v>
       </c>
-      <c r="K785" s="18"/>
+      <c r="K785" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L785" s="18"/>
       <c r="M785" s="18"/>
       <c r="N785" s="40"/>
@@ -43416,7 +43450,9 @@
       <c r="J786" s="15" t="s">
         <v>1653</v>
       </c>
-      <c r="K786" s="18"/>
+      <c r="K786" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L786" s="18"/>
       <c r="M786" s="18"/>
       <c r="N786" s="40"/>
@@ -47473,7 +47509,9 @@
       <c r="A876" s="2">
         <v>875</v>
       </c>
-      <c r="B876" s="18"/>
+      <c r="B876" s="10">
+        <v>46243</v>
+      </c>
       <c r="C876" s="56" t="s">
         <v>1789</v>
       </c>
@@ -47498,7 +47536,9 @@
       <c r="J876" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="K876" s="18"/>
+      <c r="K876" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L876" s="18"/>
       <c r="M876" s="18"/>
       <c r="N876" s="40"/>
@@ -50825,8 +50865,8 @@
       <c r="C950" s="56" t="s">
         <v>1365</v>
       </c>
-      <c r="D950" s="56">
-        <v>107499595</v>
+      <c r="D950" s="56" t="s">
+        <v>1364</v>
       </c>
       <c r="E950" s="12" t="s">
         <v>21</v>
@@ -61793,7 +61833,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1197" spans="1:18" ht="15" thickBot="1">
+    <row r="1197" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1197" s="2">
         <v>1196</v>
       </c>
@@ -61801,49 +61841,43 @@
         <v>46244</v>
       </c>
       <c r="C1197" s="56" t="s">
-        <v>1843</v>
+        <v>1925</v>
       </c>
       <c r="D1197" s="56">
-        <v>12175744</v>
-      </c>
-      <c r="E1197" s="12" t="s">
-        <v>21</v>
+        <v>7382202</v>
+      </c>
+      <c r="E1197" s="37" t="s">
+        <v>121</v>
       </c>
       <c r="F1197" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1197" s="57">
-        <v>2168</v>
+        <v>1879</v>
       </c>
       <c r="H1197" s="15">
-        <v>2168</v>
-      </c>
-      <c r="I1197" s="22" t="s">
-        <v>563</v>
-      </c>
-      <c r="J1197" s="51" t="s">
-        <v>564</v>
-      </c>
-      <c r="K1197" s="17" t="s">
-        <v>12</v>
+        <v>6223</v>
+      </c>
+      <c r="I1197" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1197" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1197" s="61" t="s">
+        <v>1189</v>
       </c>
       <c r="L1197" s="18"/>
       <c r="M1197" s="18"/>
-      <c r="N1197" s="55">
-        <v>353</v>
-      </c>
+      <c r="N1197" s="40"/>
       <c r="O1197" s="18"/>
-      <c r="P1197" s="50" t="s">
-        <v>1844</v>
-      </c>
-      <c r="Q1197" s="11">
-        <v>98504360</v>
-      </c>
-      <c r="R1197" s="22" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="1198" spans="1:18" ht="15" thickBot="1">
+      <c r="P1197" s="18"/>
+      <c r="Q1197" s="18"/>
+      <c r="R1197" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1198" s="2">
         <v>1197</v>
       </c>
@@ -61851,45 +61885,43 @@
         <v>46244</v>
       </c>
       <c r="C1198" s="56" t="s">
-        <v>1845</v>
-      </c>
-      <c r="D1198" s="56" t="s">
-        <v>1846</v>
-      </c>
-      <c r="E1198" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1198" s="13" t="s">
-        <v>22</v>
+        <v>1926</v>
+      </c>
+      <c r="D1198" s="56">
+        <v>21531852</v>
+      </c>
+      <c r="E1198" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1198" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1198" s="57">
-        <v>71359</v>
+        <v>6160</v>
       </c>
       <c r="H1198" s="15">
-        <v>88489</v>
-      </c>
-      <c r="I1198" s="22" t="s">
-        <v>563</v>
-      </c>
-      <c r="J1198" s="51" t="s">
-        <v>564</v>
-      </c>
-      <c r="K1198" s="17" t="s">
-        <v>12</v>
+        <v>102</v>
+      </c>
+      <c r="I1198" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1198" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1198" s="61" t="s">
+        <v>1189</v>
       </c>
       <c r="L1198" s="18"/>
       <c r="M1198" s="18"/>
       <c r="N1198" s="40"/>
       <c r="O1198" s="18"/>
       <c r="P1198" s="18"/>
-      <c r="Q1198" s="15">
-        <v>77391393</v>
-      </c>
-      <c r="R1198" s="22" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="1199" spans="1:18" ht="15" thickBot="1">
+      <c r="Q1198" s="18"/>
+      <c r="R1198" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1199" s="2">
         <v>1198</v>
       </c>
@@ -61897,45 +61929,43 @@
         <v>46244</v>
       </c>
       <c r="C1199" s="56" t="s">
-        <v>1847</v>
-      </c>
-      <c r="D1199" s="56" t="s">
-        <v>1848</v>
-      </c>
-      <c r="E1199" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1199" s="13" t="s">
-        <v>22</v>
+        <v>1927</v>
+      </c>
+      <c r="D1199" s="56">
+        <v>9133766</v>
+      </c>
+      <c r="E1199" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1199" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1199" s="57">
-        <v>64626</v>
+        <v>-2846</v>
       </c>
       <c r="H1199" s="15">
-        <v>66431</v>
-      </c>
-      <c r="I1199" s="22" t="s">
-        <v>563</v>
-      </c>
-      <c r="J1199" s="51" t="s">
-        <v>564</v>
-      </c>
-      <c r="K1199" s="17" t="s">
-        <v>12</v>
+        <v>8728</v>
+      </c>
+      <c r="I1199" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1199" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1199" s="61" t="s">
+        <v>1189</v>
       </c>
       <c r="L1199" s="18"/>
       <c r="M1199" s="18"/>
       <c r="N1199" s="40"/>
       <c r="O1199" s="18"/>
       <c r="P1199" s="18"/>
-      <c r="Q1199" s="15">
-        <v>96877836595</v>
-      </c>
-      <c r="R1199" s="22" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="1200" spans="1:18" ht="15" thickBot="1">
+      <c r="Q1199" s="18"/>
+      <c r="R1199" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1200" s="2">
         <v>1199</v>
       </c>
@@ -61943,45 +61973,43 @@
         <v>46244</v>
       </c>
       <c r="C1200" s="56" t="s">
-        <v>789</v>
-      </c>
-      <c r="D1200" s="56" t="s">
-        <v>1849</v>
-      </c>
-      <c r="E1200" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1200" s="13" t="s">
-        <v>22</v>
+        <v>1928</v>
+      </c>
+      <c r="D1200" s="56">
+        <v>5374489</v>
+      </c>
+      <c r="E1200" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1200" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1200" s="57">
-        <v>71507</v>
+        <v>1630</v>
       </c>
       <c r="H1200" s="15">
-        <v>81670</v>
-      </c>
-      <c r="I1200" s="22" t="s">
-        <v>563</v>
-      </c>
-      <c r="J1200" s="51" t="s">
-        <v>564</v>
-      </c>
-      <c r="K1200" s="30" t="s">
-        <v>1596</v>
+        <v>8176</v>
+      </c>
+      <c r="I1200" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1200" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1200" s="61" t="s">
+        <v>1189</v>
       </c>
       <c r="L1200" s="18"/>
       <c r="M1200" s="18"/>
       <c r="N1200" s="40"/>
       <c r="O1200" s="18"/>
       <c r="P1200" s="18"/>
-      <c r="Q1200" s="15">
-        <v>77548862</v>
-      </c>
-      <c r="R1200" s="22" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="1201" spans="1:18" ht="15" thickBot="1">
+      <c r="Q1200" s="18"/>
+      <c r="R1200" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1201" s="2">
         <v>1200</v>
       </c>
@@ -61989,42 +62017,40 @@
         <v>46244</v>
       </c>
       <c r="C1201" s="56" t="s">
-        <v>1850</v>
-      </c>
-      <c r="D1201" s="56" t="s">
-        <v>1851</v>
-      </c>
-      <c r="E1201" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1201" s="13" t="s">
-        <v>22</v>
+        <v>1929</v>
+      </c>
+      <c r="D1201" s="56">
+        <v>14465845</v>
+      </c>
+      <c r="E1201" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1201" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1201" s="57">
-        <v>44366</v>
+        <v>7020</v>
       </c>
       <c r="H1201" s="15">
-        <v>98082</v>
-      </c>
-      <c r="I1201" s="22" t="s">
-        <v>563</v>
-      </c>
-      <c r="J1201" s="51" t="s">
-        <v>564</v>
-      </c>
-      <c r="K1201" s="17" t="s">
-        <v>12</v>
+        <v>1700</v>
+      </c>
+      <c r="I1201" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1201" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1201" s="61" t="s">
+        <v>1189</v>
       </c>
       <c r="L1201" s="18"/>
       <c r="M1201" s="18"/>
       <c r="N1201" s="40"/>
       <c r="O1201" s="18"/>
       <c r="P1201" s="18"/>
-      <c r="Q1201" s="15">
-        <v>589621226</v>
-      </c>
-      <c r="R1201" s="22" t="s">
-        <v>131</v>
+      <c r="Q1201" s="18"/>
+      <c r="R1201" s="21" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="1202" spans="1:18" ht="15" thickBot="1">
@@ -62035,22 +62061,22 @@
         <v>46244</v>
       </c>
       <c r="C1202" s="56" t="s">
-        <v>1852</v>
-      </c>
-      <c r="D1202" s="56" t="s">
-        <v>1853</v>
+        <v>1843</v>
+      </c>
+      <c r="D1202" s="56">
+        <v>12175744</v>
       </c>
       <c r="E1202" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1202" s="13" t="s">
-        <v>22</v>
+      <c r="F1202" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1202" s="57">
-        <v>4576</v>
+        <v>2168</v>
       </c>
       <c r="H1202" s="15">
-        <v>55234</v>
+        <v>2168</v>
       </c>
       <c r="I1202" s="22" t="s">
         <v>563</v>
@@ -62063,11 +62089,15 @@
       </c>
       <c r="L1202" s="18"/>
       <c r="M1202" s="18"/>
-      <c r="N1202" s="40"/>
+      <c r="N1202" s="55">
+        <v>353</v>
+      </c>
       <c r="O1202" s="18"/>
-      <c r="P1202" s="18"/>
-      <c r="Q1202" s="15">
-        <v>502405112</v>
+      <c r="P1202" s="50" t="s">
+        <v>1844</v>
+      </c>
+      <c r="Q1202" s="11">
+        <v>98504360</v>
       </c>
       <c r="R1202" s="22" t="s">
         <v>131</v>
@@ -62081,10 +62111,10 @@
         <v>46244</v>
       </c>
       <c r="C1203" s="56" t="s">
-        <v>1854</v>
+        <v>1845</v>
       </c>
       <c r="D1203" s="56" t="s">
-        <v>1855</v>
+        <v>1846</v>
       </c>
       <c r="E1203" s="12" t="s">
         <v>21</v>
@@ -62093,10 +62123,10 @@
         <v>22</v>
       </c>
       <c r="G1203" s="57">
-        <v>39669</v>
+        <v>71359</v>
       </c>
       <c r="H1203" s="15">
-        <v>53385</v>
+        <v>88489</v>
       </c>
       <c r="I1203" s="22" t="s">
         <v>563</v>
@@ -62113,7 +62143,7 @@
       <c r="O1203" s="18"/>
       <c r="P1203" s="18"/>
       <c r="Q1203" s="15">
-        <v>71713093</v>
+        <v>77391393</v>
       </c>
       <c r="R1203" s="22" t="s">
         <v>131</v>
@@ -62127,10 +62157,10 @@
         <v>46244</v>
       </c>
       <c r="C1204" s="56" t="s">
-        <v>1856</v>
+        <v>1847</v>
       </c>
       <c r="D1204" s="56" t="s">
-        <v>1857</v>
+        <v>1848</v>
       </c>
       <c r="E1204" s="12" t="s">
         <v>21</v>
@@ -62139,10 +62169,10 @@
         <v>22</v>
       </c>
       <c r="G1204" s="57">
-        <v>23875</v>
+        <v>64626</v>
       </c>
       <c r="H1204" s="15">
-        <v>53385</v>
+        <v>66431</v>
       </c>
       <c r="I1204" s="22" t="s">
         <v>563</v>
@@ -62159,13 +62189,13 @@
       <c r="O1204" s="18"/>
       <c r="P1204" s="18"/>
       <c r="Q1204" s="15">
-        <v>96890683052</v>
+        <v>96877836595</v>
       </c>
       <c r="R1204" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1205" spans="1:18" ht="27.6" thickBot="1">
+    <row r="1205" spans="1:18" ht="15" thickBot="1">
       <c r="A1205" s="2">
         <v>1204</v>
       </c>
@@ -62173,10 +62203,10 @@
         <v>46244</v>
       </c>
       <c r="C1205" s="56" t="s">
-        <v>1858</v>
+        <v>789</v>
       </c>
       <c r="D1205" s="56" t="s">
-        <v>1859</v>
+        <v>1849</v>
       </c>
       <c r="E1205" s="12" t="s">
         <v>21</v>
@@ -62185,10 +62215,10 @@
         <v>22</v>
       </c>
       <c r="G1205" s="57">
-        <v>31663</v>
+        <v>71507</v>
       </c>
       <c r="H1205" s="15">
-        <v>66670</v>
+        <v>81670</v>
       </c>
       <c r="I1205" s="22" t="s">
         <v>563</v>
@@ -62196,8 +62226,8 @@
       <c r="J1205" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1205" s="17" t="s">
-        <v>12</v>
+      <c r="K1205" s="30" t="s">
+        <v>1596</v>
       </c>
       <c r="L1205" s="18"/>
       <c r="M1205" s="18"/>
@@ -62205,13 +62235,13 @@
       <c r="O1205" s="18"/>
       <c r="P1205" s="18"/>
       <c r="Q1205" s="15">
-        <v>96876789204</v>
+        <v>77548862</v>
       </c>
       <c r="R1205" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1206" spans="1:18" ht="27.6" thickBot="1">
+    <row r="1206" spans="1:18" ht="15" thickBot="1">
       <c r="A1206" s="2">
         <v>1205</v>
       </c>
@@ -62219,10 +62249,10 @@
         <v>46244</v>
       </c>
       <c r="C1206" s="56" t="s">
-        <v>37</v>
+        <v>1850</v>
       </c>
       <c r="D1206" s="56" t="s">
-        <v>1860</v>
+        <v>1851</v>
       </c>
       <c r="E1206" s="12" t="s">
         <v>21</v>
@@ -62231,10 +62261,10 @@
         <v>22</v>
       </c>
       <c r="G1206" s="57">
-        <v>56846</v>
+        <v>44366</v>
       </c>
       <c r="H1206" s="15">
-        <v>74554</v>
+        <v>98082</v>
       </c>
       <c r="I1206" s="22" t="s">
         <v>563</v>
@@ -62251,7 +62281,7 @@
       <c r="O1206" s="18"/>
       <c r="P1206" s="18"/>
       <c r="Q1206" s="15">
-        <v>971506743142</v>
+        <v>589621226</v>
       </c>
       <c r="R1206" s="22" t="s">
         <v>131</v>
@@ -62265,10 +62295,10 @@
         <v>46244</v>
       </c>
       <c r="C1207" s="56" t="s">
-        <v>56</v>
+        <v>1852</v>
       </c>
       <c r="D1207" s="56" t="s">
-        <v>1861</v>
+        <v>1853</v>
       </c>
       <c r="E1207" s="12" t="s">
         <v>21</v>
@@ -62277,10 +62307,10 @@
         <v>22</v>
       </c>
       <c r="G1207" s="57">
-        <v>43021</v>
+        <v>4576</v>
       </c>
       <c r="H1207" s="15">
-        <v>24348</v>
+        <v>55234</v>
       </c>
       <c r="I1207" s="22" t="s">
         <v>563</v>
@@ -62297,7 +62327,7 @@
       <c r="O1207" s="18"/>
       <c r="P1207" s="18"/>
       <c r="Q1207" s="15">
-        <v>96877058642</v>
+        <v>502405112</v>
       </c>
       <c r="R1207" s="22" t="s">
         <v>131</v>
@@ -62311,10 +62341,10 @@
         <v>46244</v>
       </c>
       <c r="C1208" s="56" t="s">
-        <v>1862</v>
+        <v>1854</v>
       </c>
       <c r="D1208" s="56" t="s">
-        <v>1863</v>
+        <v>1855</v>
       </c>
       <c r="E1208" s="12" t="s">
         <v>21</v>
@@ -62323,10 +62353,10 @@
         <v>22</v>
       </c>
       <c r="G1208" s="57">
-        <v>21267</v>
+        <v>39669</v>
       </c>
       <c r="H1208" s="15">
-        <v>38336</v>
+        <v>53385</v>
       </c>
       <c r="I1208" s="22" t="s">
         <v>563</v>
@@ -62339,13 +62369,11 @@
       </c>
       <c r="L1208" s="18"/>
       <c r="M1208" s="18"/>
-      <c r="N1208" s="55">
-        <v>322</v>
-      </c>
+      <c r="N1208" s="40"/>
       <c r="O1208" s="18"/>
       <c r="P1208" s="18"/>
       <c r="Q1208" s="15">
-        <v>525399766</v>
+        <v>71713093</v>
       </c>
       <c r="R1208" s="22" t="s">
         <v>131</v>
@@ -62358,34 +62386,46 @@
       <c r="B1209" s="10">
         <v>46244</v>
       </c>
-      <c r="C1209" s="38"/>
-      <c r="D1209" s="38"/>
-      <c r="E1209" s="18"/>
+      <c r="C1209" s="56" t="s">
+        <v>1856</v>
+      </c>
+      <c r="D1209" s="56" t="s">
+        <v>1857</v>
+      </c>
+      <c r="E1209" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="F1209" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1209" s="57">
-        <v>24960</v>
-      </c>
-      <c r="H1209" s="18"/>
+        <v>23875</v>
+      </c>
+      <c r="H1209" s="15">
+        <v>53385</v>
+      </c>
       <c r="I1209" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1209" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1209" s="18"/>
+      <c r="K1209" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1209" s="18"/>
       <c r="M1209" s="18"/>
       <c r="N1209" s="40"/>
       <c r="O1209" s="18"/>
       <c r="P1209" s="18"/>
-      <c r="Q1209" s="18"/>
+      <c r="Q1209" s="15">
+        <v>96890683052</v>
+      </c>
       <c r="R1209" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1210" spans="1:18" ht="15" thickBot="1">
+    <row r="1210" spans="1:18" ht="27.6" thickBot="1">
       <c r="A1210" s="2">
         <v>1209</v>
       </c>
@@ -62393,10 +62433,10 @@
         <v>46244</v>
       </c>
       <c r="C1210" s="56" t="s">
-        <v>1137</v>
+        <v>1858</v>
       </c>
       <c r="D1210" s="56" t="s">
-        <v>1864</v>
+        <v>1859</v>
       </c>
       <c r="E1210" s="12" t="s">
         <v>21</v>
@@ -62405,10 +62445,10 @@
         <v>22</v>
       </c>
       <c r="G1210" s="57">
-        <v>36008</v>
+        <v>31663</v>
       </c>
       <c r="H1210" s="15">
-        <v>9102</v>
+        <v>66670</v>
       </c>
       <c r="I1210" s="22" t="s">
         <v>563</v>
@@ -62425,13 +62465,13 @@
       <c r="O1210" s="18"/>
       <c r="P1210" s="18"/>
       <c r="Q1210" s="15">
-        <v>94789315</v>
+        <v>96876789204</v>
       </c>
       <c r="R1210" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1211" spans="1:18" ht="15" thickBot="1">
+    <row r="1211" spans="1:18" ht="27.6" thickBot="1">
       <c r="A1211" s="2">
         <v>1210</v>
       </c>
@@ -62439,22 +62479,22 @@
         <v>46244</v>
       </c>
       <c r="C1211" s="56" t="s">
-        <v>1865</v>
-      </c>
-      <c r="D1211" s="56">
-        <v>138838184</v>
+        <v>37</v>
+      </c>
+      <c r="D1211" s="56" t="s">
+        <v>1860</v>
       </c>
       <c r="E1211" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1211" s="16" t="s">
-        <v>122</v>
+      <c r="F1211" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1211" s="57">
-        <v>2233</v>
+        <v>56846</v>
       </c>
       <c r="H1211" s="15">
-        <v>198</v>
+        <v>74554</v>
       </c>
       <c r="I1211" s="22" t="s">
         <v>563</v>
@@ -62471,7 +62511,7 @@
       <c r="O1211" s="18"/>
       <c r="P1211" s="18"/>
       <c r="Q1211" s="15">
-        <v>76249681</v>
+        <v>971506743142</v>
       </c>
       <c r="R1211" s="22" t="s">
         <v>131</v>
@@ -62484,29 +62524,41 @@
       <c r="B1212" s="10">
         <v>46244</v>
       </c>
-      <c r="C1212" s="38"/>
-      <c r="D1212" s="38"/>
-      <c r="E1212" s="18"/>
-      <c r="F1212" s="16" t="s">
-        <v>122</v>
+      <c r="C1212" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1212" s="56" t="s">
+        <v>1861</v>
+      </c>
+      <c r="E1212" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1212" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1212" s="57">
-        <v>4202</v>
-      </c>
-      <c r="H1212" s="18"/>
+        <v>43021</v>
+      </c>
+      <c r="H1212" s="15">
+        <v>24348</v>
+      </c>
       <c r="I1212" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1212" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1212" s="18"/>
+      <c r="K1212" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1212" s="18"/>
       <c r="M1212" s="18"/>
       <c r="N1212" s="40"/>
       <c r="O1212" s="18"/>
       <c r="P1212" s="18"/>
-      <c r="Q1212" s="18"/>
+      <c r="Q1212" s="15">
+        <v>96877058642</v>
+      </c>
       <c r="R1212" s="22" t="s">
         <v>131</v>
       </c>
@@ -62519,22 +62571,22 @@
         <v>46244</v>
       </c>
       <c r="C1213" s="56" t="s">
-        <v>1866</v>
-      </c>
-      <c r="D1213" s="56">
-        <v>95388683</v>
+        <v>1862</v>
+      </c>
+      <c r="D1213" s="56" t="s">
+        <v>1863</v>
       </c>
       <c r="E1213" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1213" s="16" t="s">
-        <v>122</v>
+      <c r="F1213" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1213" s="57">
-        <v>5961</v>
+        <v>21267</v>
       </c>
       <c r="H1213" s="15">
-        <v>9283</v>
+        <v>38336</v>
       </c>
       <c r="I1213" s="22" t="s">
         <v>563</v>
@@ -62547,11 +62599,13 @@
       </c>
       <c r="L1213" s="18"/>
       <c r="M1213" s="18"/>
-      <c r="N1213" s="40"/>
+      <c r="N1213" s="55">
+        <v>322</v>
+      </c>
       <c r="O1213" s="18"/>
       <c r="P1213" s="18"/>
       <c r="Q1213" s="15">
-        <v>71025778</v>
+        <v>525399766</v>
       </c>
       <c r="R1213" s="22" t="s">
         <v>131</v>
@@ -62564,41 +62618,29 @@
       <c r="B1214" s="10">
         <v>46244</v>
       </c>
-      <c r="C1214" s="56" t="s">
-        <v>1867</v>
-      </c>
-      <c r="D1214" s="56">
-        <v>78746152</v>
-      </c>
-      <c r="E1214" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1214" s="16" t="s">
-        <v>122</v>
+      <c r="C1214" s="38"/>
+      <c r="D1214" s="38"/>
+      <c r="E1214" s="18"/>
+      <c r="F1214" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1214" s="57">
-        <v>1834</v>
-      </c>
-      <c r="H1214" s="15">
-        <v>3623</v>
-      </c>
+        <v>24960</v>
+      </c>
+      <c r="H1214" s="18"/>
       <c r="I1214" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1214" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1214" s="17" t="s">
-        <v>12</v>
-      </c>
+      <c r="K1214" s="18"/>
       <c r="L1214" s="18"/>
       <c r="M1214" s="18"/>
       <c r="N1214" s="40"/>
       <c r="O1214" s="18"/>
       <c r="P1214" s="18"/>
-      <c r="Q1214" s="15">
-        <v>96895952892</v>
-      </c>
+      <c r="Q1214" s="18"/>
       <c r="R1214" s="22" t="s">
         <v>131</v>
       </c>
@@ -62610,31 +62652,41 @@
       <c r="B1215" s="10">
         <v>46244</v>
       </c>
-      <c r="C1215" s="38"/>
-      <c r="D1215" s="38"/>
-      <c r="E1215" s="18"/>
-      <c r="F1215" s="16" t="s">
-        <v>122</v>
+      <c r="C1215" s="56" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D1215" s="56" t="s">
+        <v>1864</v>
+      </c>
+      <c r="E1215" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1215" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1215" s="57">
-        <v>249</v>
-      </c>
-      <c r="H1215" s="18"/>
+        <v>36008</v>
+      </c>
+      <c r="H1215" s="15">
+        <v>9102</v>
+      </c>
       <c r="I1215" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1215" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1215" s="30" t="s">
-        <v>1596</v>
+      <c r="K1215" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1215" s="18"/>
       <c r="M1215" s="18"/>
       <c r="N1215" s="40"/>
       <c r="O1215" s="18"/>
       <c r="P1215" s="18"/>
-      <c r="Q1215" s="18"/>
+      <c r="Q1215" s="15">
+        <v>94789315</v>
+      </c>
       <c r="R1215" s="22" t="s">
         <v>131</v>
       </c>
@@ -62647,10 +62699,10 @@
         <v>46244</v>
       </c>
       <c r="C1216" s="56" t="s">
-        <v>1542</v>
+        <v>1865</v>
       </c>
       <c r="D1216" s="56">
-        <v>119318055</v>
+        <v>138838184</v>
       </c>
       <c r="E1216" s="12" t="s">
         <v>21</v>
@@ -62659,10 +62711,10 @@
         <v>122</v>
       </c>
       <c r="G1216" s="57">
-        <v>3638</v>
+        <v>2233</v>
       </c>
       <c r="H1216" s="15">
-        <v>4122</v>
+        <v>198</v>
       </c>
       <c r="I1216" s="22" t="s">
         <v>563</v>
@@ -62679,7 +62731,7 @@
       <c r="O1216" s="18"/>
       <c r="P1216" s="18"/>
       <c r="Q1216" s="15">
-        <v>78528125</v>
+        <v>76249681</v>
       </c>
       <c r="R1216" s="22" t="s">
         <v>131</v>
@@ -62692,41 +62744,29 @@
       <c r="B1217" s="10">
         <v>46244</v>
       </c>
-      <c r="C1217" s="56" t="s">
-        <v>1868</v>
-      </c>
-      <c r="D1217" s="56">
-        <v>91086972</v>
-      </c>
-      <c r="E1217" s="12" t="s">
-        <v>21</v>
-      </c>
+      <c r="C1217" s="38"/>
+      <c r="D1217" s="38"/>
+      <c r="E1217" s="18"/>
       <c r="F1217" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1217" s="57">
-        <v>1856</v>
-      </c>
-      <c r="H1217" s="15">
-        <v>9607</v>
-      </c>
+        <v>4202</v>
+      </c>
+      <c r="H1217" s="18"/>
       <c r="I1217" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1217" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1217" s="17" t="s">
-        <v>12</v>
-      </c>
+      <c r="K1217" s="18"/>
       <c r="L1217" s="18"/>
       <c r="M1217" s="18"/>
       <c r="N1217" s="40"/>
       <c r="O1217" s="18"/>
       <c r="P1217" s="18"/>
-      <c r="Q1217" s="15">
-        <v>95918065</v>
-      </c>
+      <c r="Q1217" s="18"/>
       <c r="R1217" s="22" t="s">
         <v>131</v>
       </c>
@@ -62739,10 +62779,10 @@
         <v>46244</v>
       </c>
       <c r="C1218" s="56" t="s">
-        <v>1869</v>
+        <v>1866</v>
       </c>
       <c r="D1218" s="56">
-        <v>121149924</v>
+        <v>95388683</v>
       </c>
       <c r="E1218" s="12" t="s">
         <v>21</v>
@@ -62751,10 +62791,10 @@
         <v>122</v>
       </c>
       <c r="G1218" s="57">
-        <v>3785</v>
+        <v>5961</v>
       </c>
       <c r="H1218" s="15">
-        <v>9062</v>
+        <v>9283</v>
       </c>
       <c r="I1218" s="22" t="s">
         <v>563</v>
@@ -62771,7 +62811,7 @@
       <c r="O1218" s="18"/>
       <c r="P1218" s="18"/>
       <c r="Q1218" s="15">
-        <v>95881870</v>
+        <v>71025778</v>
       </c>
       <c r="R1218" s="22" t="s">
         <v>131</v>
@@ -62785,10 +62825,10 @@
         <v>46244</v>
       </c>
       <c r="C1219" s="56" t="s">
-        <v>317</v>
+        <v>1867</v>
       </c>
       <c r="D1219" s="56">
-        <v>96363803</v>
+        <v>78746152</v>
       </c>
       <c r="E1219" s="12" t="s">
         <v>21</v>
@@ -62797,10 +62837,10 @@
         <v>122</v>
       </c>
       <c r="G1219" s="57">
-        <v>3367</v>
-      </c>
-      <c r="H1219" s="15" t="s">
-        <v>1870</v>
+        <v>1834</v>
+      </c>
+      <c r="H1219" s="15">
+        <v>3623</v>
       </c>
       <c r="I1219" s="22" t="s">
         <v>563</v>
@@ -62817,7 +62857,7 @@
       <c r="O1219" s="18"/>
       <c r="P1219" s="18"/>
       <c r="Q1219" s="15">
-        <v>96363803</v>
+        <v>96895952892</v>
       </c>
       <c r="R1219" s="22" t="s">
         <v>131</v>
@@ -62830,43 +62870,31 @@
       <c r="B1220" s="10">
         <v>46244</v>
       </c>
-      <c r="C1220" s="56" t="s">
-        <v>1871</v>
-      </c>
-      <c r="D1220" s="56" t="s">
-        <v>1872</v>
-      </c>
-      <c r="E1220" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1220" s="13" t="s">
-        <v>22</v>
+      <c r="C1220" s="38"/>
+      <c r="D1220" s="38"/>
+      <c r="E1220" s="18"/>
+      <c r="F1220" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1220" s="57">
-        <v>71968</v>
-      </c>
-      <c r="H1220" s="15">
-        <v>13188</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="H1220" s="18"/>
       <c r="I1220" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1220" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1220" s="17" t="s">
-        <v>12</v>
+      <c r="K1220" s="30" t="s">
+        <v>1596</v>
       </c>
       <c r="L1220" s="18"/>
       <c r="M1220" s="18"/>
-      <c r="N1220" s="55">
-        <v>321</v>
-      </c>
+      <c r="N1220" s="40"/>
       <c r="O1220" s="18"/>
       <c r="P1220" s="18"/>
-      <c r="Q1220" s="15">
-        <v>77245341</v>
-      </c>
+      <c r="Q1220" s="18"/>
       <c r="R1220" s="22" t="s">
         <v>131</v>
       </c>
@@ -62878,33 +62906,41 @@
       <c r="B1221" s="10">
         <v>46244</v>
       </c>
-      <c r="C1221" s="38"/>
-      <c r="D1221" s="38"/>
-      <c r="E1221" s="18"/>
+      <c r="C1221" s="56" t="s">
+        <v>1542</v>
+      </c>
+      <c r="D1221" s="56">
+        <v>119318055</v>
+      </c>
+      <c r="E1221" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="F1221" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1221" s="57">
-        <v>5195</v>
-      </c>
-      <c r="H1221" s="18"/>
+        <v>3638</v>
+      </c>
+      <c r="H1221" s="15">
+        <v>4122</v>
+      </c>
       <c r="I1221" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1221" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1221" s="30" t="s">
-        <v>1596</v>
+      <c r="K1221" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1221" s="18"/>
       <c r="M1221" s="18"/>
-      <c r="N1221" s="55">
-        <v>358</v>
-      </c>
+      <c r="N1221" s="40"/>
       <c r="O1221" s="18"/>
       <c r="P1221" s="18"/>
-      <c r="Q1221" s="18"/>
+      <c r="Q1221" s="15">
+        <v>78528125</v>
+      </c>
       <c r="R1221" s="22" t="s">
         <v>131</v>
       </c>
@@ -62916,31 +62952,41 @@
       <c r="B1222" s="10">
         <v>46244</v>
       </c>
-      <c r="C1222" s="38"/>
-      <c r="D1222" s="38"/>
-      <c r="E1222" s="18"/>
+      <c r="C1222" s="56" t="s">
+        <v>1868</v>
+      </c>
+      <c r="D1222" s="56">
+        <v>91086972</v>
+      </c>
+      <c r="E1222" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="F1222" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1222" s="57">
-        <v>7347</v>
-      </c>
-      <c r="H1222" s="18"/>
+        <v>1856</v>
+      </c>
+      <c r="H1222" s="15">
+        <v>9607</v>
+      </c>
       <c r="I1222" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1222" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1222" s="30" t="s">
-        <v>1596</v>
+      <c r="K1222" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1222" s="18"/>
       <c r="M1222" s="18"/>
       <c r="N1222" s="40"/>
       <c r="O1222" s="18"/>
       <c r="P1222" s="18"/>
-      <c r="Q1222" s="18"/>
+      <c r="Q1222" s="15">
+        <v>95918065</v>
+      </c>
       <c r="R1222" s="22" t="s">
         <v>131</v>
       </c>
@@ -62953,10 +62999,10 @@
         <v>46244</v>
       </c>
       <c r="C1223" s="56" t="s">
-        <v>1873</v>
+        <v>1869</v>
       </c>
       <c r="D1223" s="56">
-        <v>101198406</v>
+        <v>121149924</v>
       </c>
       <c r="E1223" s="12" t="s">
         <v>21</v>
@@ -62965,10 +63011,10 @@
         <v>122</v>
       </c>
       <c r="G1223" s="57">
-        <v>6330</v>
+        <v>3785</v>
       </c>
       <c r="H1223" s="15">
-        <v>7507</v>
+        <v>9062</v>
       </c>
       <c r="I1223" s="22" t="s">
         <v>563</v>
@@ -62985,7 +63031,7 @@
       <c r="O1223" s="18"/>
       <c r="P1223" s="18"/>
       <c r="Q1223" s="15">
-        <v>96709596</v>
+        <v>95881870</v>
       </c>
       <c r="R1223" s="22" t="s">
         <v>131</v>
@@ -62998,31 +63044,41 @@
       <c r="B1224" s="10">
         <v>46244</v>
       </c>
-      <c r="C1224" s="38"/>
-      <c r="D1224" s="38"/>
-      <c r="E1224" s="18"/>
-      <c r="F1224" s="13" t="s">
-        <v>22</v>
+      <c r="C1224" s="56" t="s">
+        <v>317</v>
+      </c>
+      <c r="D1224" s="56">
+        <v>96363803</v>
+      </c>
+      <c r="E1224" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1224" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1224" s="57">
-        <v>35455</v>
-      </c>
-      <c r="H1224" s="18"/>
+        <v>3367</v>
+      </c>
+      <c r="H1224" s="15" t="s">
+        <v>1870</v>
+      </c>
       <c r="I1224" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1224" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1224" s="30" t="s">
-        <v>1596</v>
+      <c r="K1224" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1224" s="18"/>
       <c r="M1224" s="18"/>
       <c r="N1224" s="40"/>
       <c r="O1224" s="18"/>
       <c r="P1224" s="18"/>
-      <c r="Q1224" s="18"/>
+      <c r="Q1224" s="15">
+        <v>96363803</v>
+      </c>
       <c r="R1224" s="22" t="s">
         <v>131</v>
       </c>
@@ -63034,31 +63090,43 @@
       <c r="B1225" s="10">
         <v>46244</v>
       </c>
-      <c r="C1225" s="38"/>
-      <c r="D1225" s="38"/>
-      <c r="E1225" s="18"/>
+      <c r="C1225" s="56" t="s">
+        <v>1871</v>
+      </c>
+      <c r="D1225" s="56" t="s">
+        <v>1872</v>
+      </c>
+      <c r="E1225" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="F1225" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1225" s="57">
-        <v>72129</v>
-      </c>
-      <c r="H1225" s="18"/>
+        <v>71968</v>
+      </c>
+      <c r="H1225" s="15">
+        <v>13188</v>
+      </c>
       <c r="I1225" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1225" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1225" s="30" t="s">
-        <v>1596</v>
+      <c r="K1225" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1225" s="18"/>
       <c r="M1225" s="18"/>
-      <c r="N1225" s="40"/>
+      <c r="N1225" s="55">
+        <v>321</v>
+      </c>
       <c r="O1225" s="18"/>
       <c r="P1225" s="18"/>
-      <c r="Q1225" s="18"/>
+      <c r="Q1225" s="15">
+        <v>77245341</v>
+      </c>
       <c r="R1225" s="22" t="s">
         <v>131</v>
       </c>
@@ -63070,41 +63138,33 @@
       <c r="B1226" s="10">
         <v>46244</v>
       </c>
-      <c r="C1226" s="56" t="s">
-        <v>432</v>
-      </c>
-      <c r="D1226" s="56">
-        <v>94734526</v>
-      </c>
-      <c r="E1226" s="12" t="s">
-        <v>21</v>
-      </c>
+      <c r="C1226" s="38"/>
+      <c r="D1226" s="38"/>
+      <c r="E1226" s="18"/>
       <c r="F1226" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1226" s="57">
-        <v>2535</v>
-      </c>
-      <c r="H1226" s="15">
-        <v>4261</v>
-      </c>
+        <v>5195</v>
+      </c>
+      <c r="H1226" s="18"/>
       <c r="I1226" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1226" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1226" s="17" t="s">
-        <v>12</v>
+      <c r="K1226" s="30" t="s">
+        <v>1596</v>
       </c>
       <c r="L1226" s="18"/>
       <c r="M1226" s="18"/>
-      <c r="N1226" s="40"/>
+      <c r="N1226" s="55">
+        <v>358</v>
+      </c>
       <c r="O1226" s="18"/>
       <c r="P1226" s="18"/>
-      <c r="Q1226" s="15">
-        <v>77454348</v>
-      </c>
+      <c r="Q1226" s="18"/>
       <c r="R1226" s="22" t="s">
         <v>131</v>
       </c>
@@ -63116,41 +63176,31 @@
       <c r="B1227" s="10">
         <v>46244</v>
       </c>
-      <c r="C1227" s="56" t="s">
-        <v>1883</v>
-      </c>
-      <c r="D1227" s="56">
-        <v>116911156</v>
-      </c>
-      <c r="E1227" s="12" t="s">
-        <v>21</v>
-      </c>
+      <c r="C1227" s="38"/>
+      <c r="D1227" s="38"/>
+      <c r="E1227" s="18"/>
       <c r="F1227" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1227" s="57">
-        <v>4479</v>
-      </c>
-      <c r="H1227" s="15">
-        <v>3757</v>
-      </c>
+        <v>7347</v>
+      </c>
+      <c r="H1227" s="18"/>
       <c r="I1227" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1227" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1227" s="17" t="s">
-        <v>12</v>
+      <c r="K1227" s="30" t="s">
+        <v>1596</v>
       </c>
       <c r="L1227" s="18"/>
       <c r="M1227" s="18"/>
       <c r="N1227" s="40"/>
       <c r="O1227" s="18"/>
       <c r="P1227" s="18"/>
-      <c r="Q1227" s="15">
-        <v>96894139420</v>
-      </c>
+      <c r="Q1227" s="18"/>
       <c r="R1227" s="22" t="s">
         <v>131</v>
       </c>
@@ -63163,10 +63213,10 @@
         <v>46244</v>
       </c>
       <c r="C1228" s="56" t="s">
-        <v>1884</v>
+        <v>1873</v>
       </c>
       <c r="D1228" s="56">
-        <v>85817633</v>
+        <v>101198406</v>
       </c>
       <c r="E1228" s="12" t="s">
         <v>21</v>
@@ -63175,16 +63225,16 @@
         <v>122</v>
       </c>
       <c r="G1228" s="57">
-        <v>9082</v>
+        <v>6330</v>
       </c>
       <c r="H1228" s="15">
-        <v>3546</v>
+        <v>7507</v>
       </c>
       <c r="I1228" s="22" t="s">
         <v>563</v>
       </c>
-      <c r="J1228" s="15" t="s">
-        <v>1672</v>
+      <c r="J1228" s="51" t="s">
+        <v>564</v>
       </c>
       <c r="K1228" s="17" t="s">
         <v>12</v>
@@ -63194,8 +63244,12 @@
       <c r="N1228" s="40"/>
       <c r="O1228" s="18"/>
       <c r="P1228" s="18"/>
-      <c r="Q1228" s="18"/>
-      <c r="R1228" s="18"/>
+      <c r="Q1228" s="15">
+        <v>96709596</v>
+      </c>
+      <c r="R1228" s="22" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="1229" spans="1:18" ht="15" thickBot="1">
       <c r="A1229" s="2">
@@ -63204,32 +63258,24 @@
       <c r="B1229" s="10">
         <v>46244</v>
       </c>
-      <c r="C1229" s="56" t="s">
-        <v>1885</v>
-      </c>
-      <c r="D1229" s="56" t="s">
-        <v>1886</v>
-      </c>
-      <c r="E1229" s="12" t="s">
-        <v>21</v>
-      </c>
+      <c r="C1229" s="38"/>
+      <c r="D1229" s="38"/>
+      <c r="E1229" s="18"/>
       <c r="F1229" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1229" s="57">
-        <v>81144</v>
-      </c>
-      <c r="H1229" s="15">
-        <v>55344</v>
-      </c>
+        <v>35455</v>
+      </c>
+      <c r="H1229" s="18"/>
       <c r="I1229" s="22" t="s">
         <v>563</v>
       </c>
-      <c r="J1229" s="15" t="s">
-        <v>1672</v>
-      </c>
-      <c r="K1229" s="17" t="s">
-        <v>12</v>
+      <c r="J1229" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1229" s="30" t="s">
+        <v>1596</v>
       </c>
       <c r="L1229" s="18"/>
       <c r="M1229" s="18"/>
@@ -63237,7 +63283,9 @@
       <c r="O1229" s="18"/>
       <c r="P1229" s="18"/>
       <c r="Q1229" s="18"/>
-      <c r="R1229" s="18"/>
+      <c r="R1229" s="22" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="1230" spans="1:18" ht="15" thickBot="1">
       <c r="A1230" s="2">
@@ -63246,42 +63294,34 @@
       <c r="B1230" s="10">
         <v>46244</v>
       </c>
-      <c r="C1230" s="56" t="s">
-        <v>1887</v>
-      </c>
-      <c r="D1230" s="56" t="s">
-        <v>1888</v>
-      </c>
-      <c r="E1230" s="35" t="s">
-        <v>120</v>
-      </c>
+      <c r="C1230" s="38"/>
+      <c r="D1230" s="38"/>
+      <c r="E1230" s="18"/>
       <c r="F1230" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1230" s="57">
-        <v>15562</v>
-      </c>
-      <c r="H1230" s="15">
-        <v>74553</v>
-      </c>
-      <c r="I1230" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1230" s="52" t="s">
-        <v>776</v>
-      </c>
-      <c r="K1230" s="61" t="s">
-        <v>1189</v>
-      </c>
-      <c r="L1230" s="15">
-        <v>566209290</v>
-      </c>
+        <v>72129</v>
+      </c>
+      <c r="H1230" s="18"/>
+      <c r="I1230" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1230" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1230" s="30" t="s">
+        <v>1596</v>
+      </c>
+      <c r="L1230" s="18"/>
       <c r="M1230" s="18"/>
       <c r="N1230" s="40"/>
       <c r="O1230" s="18"/>
       <c r="P1230" s="18"/>
       <c r="Q1230" s="18"/>
-      <c r="R1230" s="18"/>
+      <c r="R1230" s="22" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="1231" spans="1:18" ht="15" thickBot="1">
       <c r="A1231" s="2">
@@ -63291,10 +63331,10 @@
         <v>46244</v>
       </c>
       <c r="C1231" s="56" t="s">
-        <v>1889</v>
+        <v>432</v>
       </c>
       <c r="D1231" s="56">
-        <v>107948231</v>
+        <v>94734526</v>
       </c>
       <c r="E1231" s="12" t="s">
         <v>21</v>
@@ -63303,29 +63343,31 @@
         <v>122</v>
       </c>
       <c r="G1231" s="57">
-        <v>1602</v>
+        <v>2535</v>
       </c>
       <c r="H1231" s="15">
-        <v>1099</v>
-      </c>
-      <c r="I1231" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1231" s="52" t="s">
-        <v>776</v>
-      </c>
-      <c r="K1231" s="61" t="s">
-        <v>1189</v>
-      </c>
-      <c r="L1231" s="15">
-        <v>96892448478</v>
-      </c>
+        <v>4261</v>
+      </c>
+      <c r="I1231" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1231" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1231" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1231" s="18"/>
       <c r="M1231" s="18"/>
       <c r="N1231" s="40"/>
       <c r="O1231" s="18"/>
       <c r="P1231" s="18"/>
-      <c r="Q1231" s="18"/>
-      <c r="R1231" s="18"/>
+      <c r="Q1231" s="15">
+        <v>77454348</v>
+      </c>
+      <c r="R1231" s="22" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="1232" spans="1:18" ht="15" thickBot="1">
       <c r="A1232" s="2">
@@ -63335,10 +63377,10 @@
         <v>46244</v>
       </c>
       <c r="C1232" s="56" t="s">
-        <v>1890</v>
+        <v>1883</v>
       </c>
       <c r="D1232" s="56">
-        <v>76217672</v>
+        <v>116911156</v>
       </c>
       <c r="E1232" s="12" t="s">
         <v>21</v>
@@ -63347,29 +63389,31 @@
         <v>122</v>
       </c>
       <c r="G1232" s="57">
-        <v>4465</v>
+        <v>4479</v>
       </c>
       <c r="H1232" s="15">
-        <v>8001</v>
-      </c>
-      <c r="I1232" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1232" s="52" t="s">
-        <v>776</v>
-      </c>
-      <c r="K1232" s="61" t="s">
-        <v>1189</v>
-      </c>
-      <c r="L1232" s="15">
-        <v>93317831</v>
-      </c>
+        <v>3757</v>
+      </c>
+      <c r="I1232" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1232" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1232" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1232" s="18"/>
       <c r="M1232" s="18"/>
       <c r="N1232" s="40"/>
       <c r="O1232" s="18"/>
       <c r="P1232" s="18"/>
-      <c r="Q1232" s="18"/>
-      <c r="R1232" s="18"/>
+      <c r="Q1232" s="15">
+        <v>96894139420</v>
+      </c>
+      <c r="R1232" s="22" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="1233" spans="1:18" ht="15" thickBot="1">
       <c r="A1233" s="2">
@@ -63379,10 +63423,10 @@
         <v>46244</v>
       </c>
       <c r="C1233" s="56" t="s">
-        <v>1891</v>
+        <v>1884</v>
       </c>
       <c r="D1233" s="56">
-        <v>113802138</v>
+        <v>85817633</v>
       </c>
       <c r="E1233" s="12" t="s">
         <v>21</v>
@@ -63391,19 +63435,19 @@
         <v>122</v>
       </c>
       <c r="G1233" s="57">
-        <v>1777</v>
+        <v>9082</v>
       </c>
       <c r="H1233" s="15">
-        <v>9472</v>
-      </c>
-      <c r="I1233" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1233" s="52" t="s">
-        <v>776</v>
-      </c>
-      <c r="K1233" s="61" t="s">
-        <v>1189</v>
+        <v>3546</v>
+      </c>
+      <c r="I1233" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1233" s="15" t="s">
+        <v>1672</v>
+      </c>
+      <c r="K1233" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1233" s="18"/>
       <c r="M1233" s="18"/>
@@ -63411,7 +63455,9 @@
       <c r="O1233" s="18"/>
       <c r="P1233" s="18"/>
       <c r="Q1233" s="18"/>
-      <c r="R1233" s="18"/>
+      <c r="R1233" s="22" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="1234" spans="1:18" ht="15" thickBot="1">
       <c r="A1234" s="2">
@@ -63421,28 +63467,28 @@
         <v>46244</v>
       </c>
       <c r="C1234" s="56" t="s">
-        <v>1892</v>
-      </c>
-      <c r="D1234" s="56">
-        <v>77396496</v>
+        <v>1885</v>
+      </c>
+      <c r="D1234" s="56" t="s">
+        <v>1886</v>
       </c>
       <c r="E1234" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1234" s="16" t="s">
-        <v>122</v>
+      <c r="F1234" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1234" s="57">
-        <v>3536</v>
+        <v>81144</v>
       </c>
       <c r="H1234" s="15">
-        <v>9212</v>
-      </c>
-      <c r="I1234" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1234" s="52" t="s">
-        <v>776</v>
+        <v>55344</v>
+      </c>
+      <c r="I1234" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1234" s="15" t="s">
+        <v>1672</v>
       </c>
       <c r="K1234" s="17" t="s">
         <v>12</v>
@@ -63453,9 +63499,11 @@
       <c r="O1234" s="18"/>
       <c r="P1234" s="18"/>
       <c r="Q1234" s="18"/>
-      <c r="R1234" s="18"/>
-    </row>
-    <row r="1235" spans="1:18" ht="28.2" thickBot="1">
+      <c r="R1234" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:18" ht="15" thickBot="1">
       <c r="A1235" s="2">
         <v>1234</v>
       </c>
@@ -63463,81 +63511,89 @@
         <v>46244</v>
       </c>
       <c r="C1235" s="56" t="s">
-        <v>1893</v>
-      </c>
-      <c r="D1235" s="56">
-        <v>131422754</v>
-      </c>
-      <c r="E1235" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1235" s="16" t="s">
-        <v>122</v>
+        <v>1887</v>
+      </c>
+      <c r="D1235" s="56" t="s">
+        <v>1888</v>
+      </c>
+      <c r="E1235" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1235" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1235" s="57">
-        <v>3097</v>
+        <v>15562</v>
       </c>
       <c r="H1235" s="15">
-        <v>3993</v>
-      </c>
-      <c r="I1235" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="J1235" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="K1235" s="18"/>
-      <c r="L1235" s="15">
-        <v>78615034</v>
-      </c>
+        <v>74553</v>
+      </c>
+      <c r="I1235" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1235" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1235" s="61" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1235" s="18"/>
       <c r="M1235" s="18"/>
       <c r="N1235" s="40"/>
       <c r="O1235" s="18"/>
       <c r="P1235" s="18"/>
-      <c r="Q1235" s="18"/>
-      <c r="R1235" s="18"/>
-    </row>
-    <row r="1236" spans="1:18" ht="28.2" thickBot="1">
+      <c r="Q1235" s="15">
+        <v>566209290</v>
+      </c>
+      <c r="R1235" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:18" ht="15" thickBot="1">
       <c r="A1236" s="2">
         <v>1235</v>
       </c>
-      <c r="B1236" s="75">
+      <c r="B1236" s="10">
         <v>46244</v>
       </c>
-      <c r="C1236" s="76" t="s">
-        <v>1912</v>
-      </c>
-      <c r="D1236" s="76">
-        <v>109499244</v>
-      </c>
-      <c r="E1236" s="86" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1236" s="78" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1236" s="79">
-        <v>6018</v>
-      </c>
-      <c r="H1236" s="80">
-        <v>8793</v>
-      </c>
-      <c r="I1236" s="80" t="s">
-        <v>123</v>
-      </c>
-      <c r="J1236" s="80" t="s">
-        <v>1913</v>
-      </c>
-      <c r="K1236" s="82"/>
-      <c r="L1236" s="80">
-        <v>78735597</v>
-      </c>
-      <c r="M1236" s="82"/>
-      <c r="N1236" s="83"/>
-      <c r="O1236" s="82"/>
-      <c r="P1236" s="82"/>
-      <c r="Q1236" s="82"/>
-      <c r="R1236" s="82"/>
+      <c r="C1236" s="56" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D1236" s="56">
+        <v>107948231</v>
+      </c>
+      <c r="E1236" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1236" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1236" s="57">
+        <v>1602</v>
+      </c>
+      <c r="H1236" s="15">
+        <v>1099</v>
+      </c>
+      <c r="I1236" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1236" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1236" s="61" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1236" s="18"/>
+      <c r="M1236" s="18"/>
+      <c r="N1236" s="40"/>
+      <c r="O1236" s="18"/>
+      <c r="P1236" s="18"/>
+      <c r="Q1236" s="15">
+        <v>96892448478</v>
+      </c>
+      <c r="R1236" s="22" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="1237" spans="1:18" ht="15" thickBot="1">
       <c r="A1237" s="2">
@@ -63547,10 +63603,10 @@
         <v>46244</v>
       </c>
       <c r="C1237" s="56" t="s">
-        <v>1874</v>
+        <v>1890</v>
       </c>
       <c r="D1237" s="56">
-        <v>112067329</v>
+        <v>76217672</v>
       </c>
       <c r="E1237" s="12" t="s">
         <v>21</v>
@@ -63559,31 +63615,33 @@
         <v>122</v>
       </c>
       <c r="G1237" s="57">
-        <v>2968</v>
+        <v>4465</v>
       </c>
       <c r="H1237" s="15">
-        <v>5613</v>
+        <v>8001</v>
       </c>
       <c r="I1237" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J1237" s="15" t="s">
-        <v>839</v>
-      </c>
-      <c r="K1237" s="17" t="s">
-        <v>12</v>
+      <c r="J1237" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1237" s="61" t="s">
+        <v>1189</v>
       </c>
       <c r="L1237" s="18"/>
       <c r="M1237" s="18"/>
       <c r="N1237" s="40"/>
       <c r="O1237" s="18"/>
       <c r="P1237" s="18"/>
-      <c r="Q1237" s="18"/>
-      <c r="R1237" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1238" spans="1:18" ht="27.6" thickBot="1">
+      <c r="Q1237" s="15">
+        <v>93317831</v>
+      </c>
+      <c r="R1237" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:18" ht="15" thickBot="1">
       <c r="A1238" s="2">
         <v>1237</v>
       </c>
@@ -63591,10 +63649,10 @@
         <v>46244</v>
       </c>
       <c r="C1238" s="56" t="s">
-        <v>1875</v>
+        <v>1891</v>
       </c>
       <c r="D1238" s="56">
-        <v>116806083</v>
+        <v>113802138</v>
       </c>
       <c r="E1238" s="12" t="s">
         <v>21</v>
@@ -63603,30 +63661,28 @@
         <v>122</v>
       </c>
       <c r="G1238" s="57">
-        <v>442</v>
+        <v>1777</v>
       </c>
       <c r="H1238" s="15">
-        <v>7536</v>
+        <v>9472</v>
       </c>
       <c r="I1238" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J1238" s="15" t="s">
-        <v>950</v>
-      </c>
-      <c r="K1238" s="17" t="s">
-        <v>12</v>
+      <c r="J1238" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1238" s="61" t="s">
+        <v>1189</v>
       </c>
       <c r="L1238" s="18"/>
       <c r="M1238" s="18"/>
       <c r="N1238" s="40"/>
       <c r="O1238" s="18"/>
       <c r="P1238" s="18"/>
-      <c r="Q1238" s="11">
-        <v>79997138</v>
-      </c>
-      <c r="R1238" s="20" t="s">
-        <v>11</v>
+      <c r="Q1238" s="18"/>
+      <c r="R1238" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="1239" spans="1:18" ht="15" thickBot="1">
@@ -63637,10 +63693,10 @@
         <v>46244</v>
       </c>
       <c r="C1239" s="56" t="s">
-        <v>1876</v>
+        <v>1892</v>
       </c>
       <c r="D1239" s="56">
-        <v>113458078</v>
+        <v>77396496</v>
       </c>
       <c r="E1239" s="12" t="s">
         <v>21</v>
@@ -63649,16 +63705,16 @@
         <v>122</v>
       </c>
       <c r="G1239" s="57">
-        <v>5913</v>
+        <v>3536</v>
       </c>
       <c r="H1239" s="15">
-        <v>1154</v>
+        <v>9212</v>
       </c>
       <c r="I1239" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J1239" s="15" t="s">
-        <v>950</v>
+      <c r="J1239" s="52" t="s">
+        <v>776</v>
       </c>
       <c r="K1239" s="17" t="s">
         <v>12</v>
@@ -63669,11 +63725,11 @@
       <c r="O1239" s="18"/>
       <c r="P1239" s="18"/>
       <c r="Q1239" s="18"/>
-      <c r="R1239" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1240" spans="1:18" ht="27.6" thickBot="1">
+      <c r="R1239" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1240" s="2">
         <v>1239</v>
       </c>
@@ -63681,10 +63737,10 @@
         <v>46244</v>
       </c>
       <c r="C1240" s="56" t="s">
-        <v>638</v>
+        <v>1893</v>
       </c>
       <c r="D1240" s="56">
-        <v>122952217</v>
+        <v>131422754</v>
       </c>
       <c r="E1240" s="12" t="s">
         <v>21</v>
@@ -63693,16 +63749,16 @@
         <v>122</v>
       </c>
       <c r="G1240" s="57">
-        <v>4581</v>
+        <v>3097</v>
       </c>
       <c r="H1240" s="15">
-        <v>-8325</v>
-      </c>
-      <c r="I1240" s="16" t="s">
-        <v>10</v>
+        <v>3993</v>
+      </c>
+      <c r="I1240" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="J1240" s="15" t="s">
-        <v>950</v>
+        <v>174</v>
       </c>
       <c r="K1240" s="17" t="s">
         <v>12</v>
@@ -63712,14 +63768,14 @@
       <c r="N1240" s="40"/>
       <c r="O1240" s="18"/>
       <c r="P1240" s="18"/>
-      <c r="Q1240" s="11" t="s">
-        <v>1877</v>
-      </c>
-      <c r="R1240" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1241" spans="1:18" ht="15" thickBot="1">
+      <c r="Q1240" s="15">
+        <v>78615034</v>
+      </c>
+      <c r="R1240" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1241" s="2">
         <v>1240</v>
       </c>
@@ -63727,10 +63783,10 @@
         <v>46244</v>
       </c>
       <c r="C1241" s="56" t="s">
-        <v>1878</v>
+        <v>1912</v>
       </c>
       <c r="D1241" s="56">
-        <v>126214395</v>
+        <v>109499244</v>
       </c>
       <c r="E1241" s="12" t="s">
         <v>21</v>
@@ -63739,16 +63795,16 @@
         <v>122</v>
       </c>
       <c r="G1241" s="57">
-        <v>355</v>
+        <v>6018</v>
       </c>
       <c r="H1241" s="15">
-        <v>2278</v>
-      </c>
-      <c r="I1241" s="16" t="s">
-        <v>10</v>
+        <v>8793</v>
+      </c>
+      <c r="I1241" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="J1241" s="15" t="s">
-        <v>950</v>
+        <v>1913</v>
       </c>
       <c r="K1241" s="17" t="s">
         <v>12</v>
@@ -63758,9 +63814,11 @@
       <c r="N1241" s="40"/>
       <c r="O1241" s="18"/>
       <c r="P1241" s="18"/>
-      <c r="Q1241" s="18"/>
-      <c r="R1241" s="20" t="s">
-        <v>11</v>
+      <c r="Q1241" s="15">
+        <v>78735597</v>
+      </c>
+      <c r="R1241" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="1242" spans="1:18" ht="28.2" thickBot="1">
@@ -63771,28 +63829,28 @@
         <v>46244</v>
       </c>
       <c r="C1242" s="56" t="s">
-        <v>47</v>
-      </c>
-      <c r="D1242" s="56" t="s">
-        <v>1879</v>
+        <v>1914</v>
+      </c>
+      <c r="D1242" s="56">
+        <v>110877972</v>
       </c>
       <c r="E1242" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1242" s="13" t="s">
-        <v>22</v>
+      <c r="F1242" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1242" s="57">
-        <v>33404</v>
+        <v>5734</v>
       </c>
       <c r="H1242" s="15">
-        <v>89137</v>
-      </c>
-      <c r="I1242" s="16" t="s">
-        <v>10</v>
+        <v>235</v>
+      </c>
+      <c r="I1242" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="J1242" s="15" t="s">
-        <v>1880</v>
+        <v>1913</v>
       </c>
       <c r="K1242" s="17" t="s">
         <v>12</v>
@@ -63802,11 +63860,11 @@
       <c r="N1242" s="40"/>
       <c r="O1242" s="18"/>
       <c r="P1242" s="18"/>
-      <c r="Q1242" s="11">
-        <v>95643750</v>
-      </c>
-      <c r="R1242" s="20" t="s">
-        <v>11</v>
+      <c r="Q1242" s="15">
+        <v>79031527</v>
+      </c>
+      <c r="R1242" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="1243" spans="1:18" ht="28.2" thickBot="1">
@@ -63817,28 +63875,28 @@
         <v>46244</v>
       </c>
       <c r="C1243" s="56" t="s">
-        <v>504</v>
-      </c>
-      <c r="D1243" s="56" t="s">
-        <v>1881</v>
+        <v>1149</v>
+      </c>
+      <c r="D1243" s="56">
+        <v>124842182</v>
       </c>
       <c r="E1243" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1243" s="13" t="s">
-        <v>22</v>
+      <c r="F1243" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1243" s="57">
-        <v>7606</v>
-      </c>
-      <c r="H1243" s="15">
-        <v>66793</v>
-      </c>
-      <c r="I1243" s="16" t="s">
-        <v>10</v>
+        <v>9340</v>
+      </c>
+      <c r="H1243" s="15" t="s">
+        <v>1915</v>
+      </c>
+      <c r="I1243" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="J1243" s="15" t="s">
-        <v>1880</v>
+        <v>1913</v>
       </c>
       <c r="K1243" s="17" t="s">
         <v>12</v>
@@ -63848,14 +63906,14 @@
       <c r="N1243" s="40"/>
       <c r="O1243" s="18"/>
       <c r="P1243" s="18"/>
-      <c r="Q1243" s="11">
-        <v>501924525</v>
-      </c>
-      <c r="R1243" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1244" spans="1:18" ht="27.6" thickBot="1">
+      <c r="Q1243" s="15">
+        <v>98172901</v>
+      </c>
+      <c r="R1243" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1244" s="2">
         <v>1243</v>
       </c>
@@ -63863,28 +63921,28 @@
         <v>46244</v>
       </c>
       <c r="C1244" s="56" t="s">
-        <v>906</v>
-      </c>
-      <c r="D1244" s="56">
-        <v>128333109</v>
+        <v>1916</v>
+      </c>
+      <c r="D1244" s="56" t="s">
+        <v>1917</v>
       </c>
       <c r="E1244" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1244" s="16" t="s">
-        <v>122</v>
+      <c r="F1244" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1244" s="57">
-        <v>4900</v>
+        <v>16853</v>
       </c>
       <c r="H1244" s="15">
-        <v>-6338</v>
-      </c>
-      <c r="I1244" s="16" t="s">
-        <v>10</v>
+        <v>76548</v>
+      </c>
+      <c r="I1244" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="J1244" s="15" t="s">
-        <v>890</v>
+        <v>1913</v>
       </c>
       <c r="K1244" s="17" t="s">
         <v>12</v>
@@ -63894,14 +63952,14 @@
       <c r="N1244" s="40"/>
       <c r="O1244" s="18"/>
       <c r="P1244" s="18"/>
-      <c r="Q1244" s="11">
-        <v>95609530</v>
-      </c>
-      <c r="R1244" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1245" spans="1:18" ht="15" thickBot="1">
+      <c r="Q1244" s="15">
+        <v>95596076</v>
+      </c>
+      <c r="R1244" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1245" s="2">
         <v>1244</v>
       </c>
@@ -63909,28 +63967,28 @@
         <v>46244</v>
       </c>
       <c r="C1245" s="56" t="s">
-        <v>1894</v>
-      </c>
-      <c r="D1245" s="56">
-        <v>116033629</v>
+        <v>1918</v>
+      </c>
+      <c r="D1245" s="56" t="s">
+        <v>1919</v>
       </c>
       <c r="E1245" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1245" s="16" t="s">
-        <v>122</v>
+      <c r="F1245" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1245" s="57">
-        <v>1702</v>
+        <v>55729</v>
       </c>
       <c r="H1245" s="15">
-        <v>5164</v>
-      </c>
-      <c r="I1245" s="16" t="s">
-        <v>10</v>
+        <v>21874</v>
+      </c>
+      <c r="I1245" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="J1245" s="15" t="s">
-        <v>950</v>
+        <v>1913</v>
       </c>
       <c r="K1245" s="17" t="s">
         <v>12</v>
@@ -63940,14 +63998,14 @@
       <c r="N1245" s="40"/>
       <c r="O1245" s="18"/>
       <c r="P1245" s="18"/>
-      <c r="Q1245" s="11">
-        <v>94250210</v>
-      </c>
-      <c r="R1245" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1246" spans="1:18" ht="27.6" thickBot="1">
+      <c r="Q1245" s="15">
+        <v>77821958</v>
+      </c>
+      <c r="R1245" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1246" s="2">
         <v>1245</v>
       </c>
@@ -63955,10 +64013,10 @@
         <v>46244</v>
       </c>
       <c r="C1246" s="56" t="s">
-        <v>1895</v>
+        <v>1920</v>
       </c>
       <c r="D1246" s="56" t="s">
-        <v>1896</v>
+        <v>1921</v>
       </c>
       <c r="E1246" s="12" t="s">
         <v>21</v>
@@ -63967,16 +64025,16 @@
         <v>22</v>
       </c>
       <c r="G1246" s="57">
-        <v>21668</v>
+        <v>24788</v>
       </c>
       <c r="H1246" s="15">
-        <v>75184</v>
-      </c>
-      <c r="I1246" s="16" t="s">
-        <v>10</v>
+        <v>81726</v>
+      </c>
+      <c r="I1246" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="J1246" s="15" t="s">
-        <v>1897</v>
+        <v>1913</v>
       </c>
       <c r="K1246" s="17" t="s">
         <v>12</v>
@@ -63986,11 +64044,11 @@
       <c r="N1246" s="40"/>
       <c r="O1246" s="18"/>
       <c r="P1246" s="18"/>
-      <c r="Q1246" s="11">
-        <v>557824163</v>
-      </c>
-      <c r="R1246" s="20" t="s">
-        <v>11</v>
+      <c r="Q1246" s="15">
+        <v>555524049</v>
+      </c>
+      <c r="R1246" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="1247" spans="1:18" ht="28.2" thickBot="1">
@@ -64001,28 +64059,28 @@
         <v>46244</v>
       </c>
       <c r="C1247" s="56" t="s">
-        <v>1898</v>
-      </c>
-      <c r="D1247" s="56" t="s">
-        <v>1899</v>
+        <v>1922</v>
+      </c>
+      <c r="D1247" s="56">
+        <v>133589295</v>
       </c>
       <c r="E1247" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1247" s="13" t="s">
-        <v>22</v>
+      <c r="F1247" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1247" s="57">
-        <v>9215</v>
+        <v>4317</v>
       </c>
       <c r="H1247" s="15">
-        <v>10278</v>
-      </c>
-      <c r="I1247" s="16" t="s">
-        <v>10</v>
+        <v>9901</v>
+      </c>
+      <c r="I1247" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="J1247" s="15" t="s">
-        <v>49</v>
+        <v>174</v>
       </c>
       <c r="K1247" s="17" t="s">
         <v>12</v>
@@ -64032,9 +64090,11 @@
       <c r="N1247" s="40"/>
       <c r="O1247" s="18"/>
       <c r="P1247" s="18"/>
-      <c r="Q1247" s="18"/>
-      <c r="R1247" s="20" t="s">
-        <v>11</v>
+      <c r="Q1247" s="11">
+        <v>96877336001</v>
+      </c>
+      <c r="R1247" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="1248" spans="1:18" ht="28.2" thickBot="1">
@@ -64045,28 +64105,28 @@
         <v>46244</v>
       </c>
       <c r="C1248" s="56" t="s">
-        <v>1900</v>
-      </c>
-      <c r="D1248" s="56" t="s">
-        <v>1901</v>
+        <v>771</v>
+      </c>
+      <c r="D1248" s="56">
+        <v>121398708</v>
       </c>
       <c r="E1248" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1248" s="13" t="s">
-        <v>22</v>
+      <c r="F1248" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1248" s="57">
-        <v>53578</v>
+        <v>9244</v>
       </c>
       <c r="H1248" s="15">
-        <v>46411</v>
-      </c>
-      <c r="I1248" s="16" t="s">
-        <v>10</v>
+        <v>9611</v>
+      </c>
+      <c r="I1248" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="J1248" s="15" t="s">
-        <v>49</v>
+        <v>174</v>
       </c>
       <c r="K1248" s="17" t="s">
         <v>12</v>
@@ -64076,12 +64136,14 @@
       <c r="N1248" s="40"/>
       <c r="O1248" s="18"/>
       <c r="P1248" s="18"/>
-      <c r="Q1248" s="18"/>
-      <c r="R1248" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1249" spans="1:18" ht="15" thickBot="1">
+      <c r="Q1248" s="11">
+        <v>71382892</v>
+      </c>
+      <c r="R1248" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1249" s="2">
         <v>1248</v>
       </c>
@@ -64089,28 +64151,28 @@
         <v>46244</v>
       </c>
       <c r="C1249" s="56" t="s">
-        <v>1902</v>
-      </c>
-      <c r="D1249" s="56" t="s">
-        <v>1903</v>
-      </c>
-      <c r="E1249" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="F1249" s="13" t="s">
-        <v>22</v>
+        <v>1930</v>
+      </c>
+      <c r="D1249" s="56">
+        <v>123092622</v>
+      </c>
+      <c r="E1249" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1249" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1249" s="57">
-        <v>68833</v>
+        <v>8269</v>
       </c>
       <c r="H1249" s="15">
-        <v>78793</v>
-      </c>
-      <c r="I1249" s="16" t="s">
-        <v>10</v>
+        <v>8963</v>
+      </c>
+      <c r="I1249" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="J1249" s="15" t="s">
-        <v>1904</v>
+        <v>174</v>
       </c>
       <c r="K1249" s="17" t="s">
         <v>12</v>
@@ -64121,13 +64183,13 @@
       <c r="O1249" s="18"/>
       <c r="P1249" s="18"/>
       <c r="Q1249" s="11">
-        <v>554186760</v>
-      </c>
-      <c r="R1249" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1250" spans="1:18" ht="15" thickBot="1">
+        <v>98560324</v>
+      </c>
+      <c r="R1249" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1250" s="2">
         <v>1249</v>
       </c>
@@ -64135,45 +64197,45 @@
         <v>46244</v>
       </c>
       <c r="C1250" s="56" t="s">
-        <v>1905</v>
-      </c>
-      <c r="D1250" s="56" t="s">
-        <v>1906</v>
-      </c>
-      <c r="E1250" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="F1250" s="13" t="s">
-        <v>22</v>
+        <v>1931</v>
+      </c>
+      <c r="D1250" s="56">
+        <v>136802631</v>
+      </c>
+      <c r="E1250" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1250" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1250" s="57">
-        <v>56757</v>
-      </c>
-      <c r="H1250" s="15" t="s">
-        <v>1907</v>
-      </c>
-      <c r="I1250" s="16" t="s">
-        <v>10</v>
+        <v>1474</v>
+      </c>
+      <c r="H1250" s="15">
+        <v>3475</v>
+      </c>
+      <c r="I1250" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="J1250" s="15" t="s">
-        <v>1904</v>
-      </c>
-      <c r="K1250" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1250" s="18"/>
+        <v>1913</v>
+      </c>
+      <c r="K1250" s="18"/>
+      <c r="L1250" s="15">
+        <v>94317092</v>
+      </c>
       <c r="M1250" s="18"/>
       <c r="N1250" s="40"/>
       <c r="O1250" s="18"/>
       <c r="P1250" s="18"/>
-      <c r="Q1250" s="11">
-        <v>76969759</v>
-      </c>
-      <c r="R1250" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1251" spans="1:18" ht="27.6" thickBot="1">
+      <c r="Q1250" s="15">
+        <v>94317092</v>
+      </c>
+      <c r="R1250" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1251" s="2">
         <v>1250</v>
       </c>
@@ -64181,128 +64243,128 @@
         <v>46244</v>
       </c>
       <c r="C1251" s="56" t="s">
-        <v>1908</v>
-      </c>
-      <c r="D1251" s="56" t="s">
-        <v>1909</v>
+        <v>1932</v>
+      </c>
+      <c r="D1251" s="56">
+        <v>136393574</v>
       </c>
       <c r="E1251" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1251" s="13" t="s">
-        <v>22</v>
+      <c r="F1251" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1251" s="57">
-        <v>61918</v>
-      </c>
-      <c r="H1251" s="15">
-        <v>19939</v>
-      </c>
-      <c r="I1251" s="16" t="s">
-        <v>10</v>
+        <v>8580</v>
+      </c>
+      <c r="H1251" s="15" t="s">
+        <v>1933</v>
+      </c>
+      <c r="I1251" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="J1251" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="K1251" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1251" s="18"/>
+        <v>1913</v>
+      </c>
+      <c r="K1251" s="18"/>
+      <c r="L1251" s="15">
+        <v>94526230</v>
+      </c>
       <c r="M1251" s="18"/>
       <c r="N1251" s="40"/>
       <c r="O1251" s="18"/>
       <c r="P1251" s="18"/>
-      <c r="Q1251" s="18"/>
-      <c r="R1251" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1252" spans="1:18" ht="27.6" thickBot="1">
+      <c r="Q1251" s="15">
+        <v>94526230</v>
+      </c>
+      <c r="R1251" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1252" s="2">
         <v>1251</v>
       </c>
-      <c r="B1252" s="75">
+      <c r="B1252" s="10">
         <v>46244</v>
       </c>
-      <c r="C1252" s="76" t="s">
-        <v>1910</v>
-      </c>
-      <c r="D1252" s="76" t="s">
-        <v>1911</v>
-      </c>
-      <c r="E1252" s="77" t="s">
-        <v>119</v>
-      </c>
-      <c r="F1252" s="78" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1252" s="79">
-        <v>8490</v>
-      </c>
-      <c r="H1252" s="80">
-        <v>8101</v>
-      </c>
-      <c r="I1252" s="78" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1252" s="80" t="s">
-        <v>202</v>
-      </c>
-      <c r="K1252" s="81" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1252" s="82"/>
-      <c r="M1252" s="82"/>
-      <c r="N1252" s="83"/>
-      <c r="O1252" s="82"/>
-      <c r="P1252" s="82"/>
-      <c r="Q1252" s="84">
-        <v>98705284</v>
-      </c>
-      <c r="R1252" s="85" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1253" spans="1:18" ht="28.2" thickBot="1">
+      <c r="C1252" s="56" t="s">
+        <v>1934</v>
+      </c>
+      <c r="D1252" s="56">
+        <v>101540233</v>
+      </c>
+      <c r="E1252" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1252" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1252" s="57">
+        <v>5126</v>
+      </c>
+      <c r="H1252" s="15" t="s">
+        <v>1935</v>
+      </c>
+      <c r="I1252" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1252" s="15" t="s">
+        <v>1913</v>
+      </c>
+      <c r="K1252" s="18"/>
+      <c r="L1252" s="18"/>
+      <c r="M1252" s="18"/>
+      <c r="N1252" s="40"/>
+      <c r="O1252" s="18"/>
+      <c r="P1252" s="18"/>
+      <c r="Q1252" s="18"/>
+      <c r="R1252" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:18" ht="31.2" thickBot="1">
       <c r="A1253" s="2">
         <v>1252</v>
       </c>
-      <c r="B1253" s="75">
+      <c r="B1253" s="10">
         <v>46244</v>
       </c>
-      <c r="C1253" s="76" t="s">
-        <v>1914</v>
-      </c>
-      <c r="D1253" s="76">
-        <v>110877972</v>
-      </c>
-      <c r="E1253" s="86" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1253" s="78" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1253" s="79">
-        <v>5734</v>
-      </c>
-      <c r="H1253" s="80">
-        <v>235</v>
-      </c>
-      <c r="I1253" s="80" t="s">
+      <c r="C1253" s="56" t="s">
+        <v>279</v>
+      </c>
+      <c r="D1253" s="56" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1253" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1253" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1253" s="57" t="s">
+        <v>1936</v>
+      </c>
+      <c r="H1253" s="15">
+        <v>48752</v>
+      </c>
+      <c r="I1253" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="J1253" s="80" t="s">
+      <c r="J1253" s="15" t="s">
         <v>1913</v>
       </c>
-      <c r="K1253" s="82"/>
-      <c r="L1253" s="80">
-        <v>79031527</v>
-      </c>
-      <c r="M1253" s="82"/>
-      <c r="N1253" s="83"/>
-      <c r="O1253" s="82"/>
-      <c r="P1253" s="82"/>
-      <c r="Q1253" s="82"/>
+      <c r="K1253" s="30" t="s">
+        <v>1596</v>
+      </c>
+      <c r="L1253" s="18"/>
+      <c r="M1253" s="18"/>
+      <c r="N1253" s="40"/>
+      <c r="O1253" s="18"/>
+      <c r="P1253" s="50" t="s">
+        <v>1803</v>
+      </c>
+      <c r="Q1253" s="18"/>
       <c r="R1253" s="22" t="s">
         <v>131</v>
       </c>
@@ -64315,10 +64377,10 @@
         <v>46244</v>
       </c>
       <c r="C1254" s="56" t="s">
-        <v>1149</v>
+        <v>1937</v>
       </c>
       <c r="D1254" s="56">
-        <v>124842182</v>
+        <v>76637533</v>
       </c>
       <c r="E1254" s="12" t="s">
         <v>21</v>
@@ -64327,21 +64389,21 @@
         <v>122</v>
       </c>
       <c r="G1254" s="57">
-        <v>9340</v>
-      </c>
-      <c r="H1254" s="15" t="s">
-        <v>1915</v>
+        <v>1027</v>
+      </c>
+      <c r="H1254" s="15">
+        <v>512</v>
       </c>
       <c r="I1254" s="15" t="s">
         <v>123</v>
       </c>
       <c r="J1254" s="15" t="s">
-        <v>1913</v>
-      </c>
-      <c r="K1254" s="18"/>
-      <c r="L1254" s="15">
-        <v>98172901</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="K1254" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1254" s="18"/>
       <c r="M1254" s="18"/>
       <c r="N1254" s="40"/>
       <c r="O1254" s="18"/>
@@ -64351,174 +64413,130 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1255" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1255" spans="1:18" ht="15" thickBot="1">
       <c r="A1255" s="2">
         <v>1254</v>
       </c>
-      <c r="B1255" s="75">
+      <c r="B1255" s="10">
         <v>46244</v>
       </c>
-      <c r="C1255" s="76" t="s">
-        <v>1916</v>
-      </c>
-      <c r="D1255" s="76" t="s">
-        <v>1917</v>
-      </c>
-      <c r="E1255" s="86" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1255" s="87" t="s">
+      <c r="C1255" s="38"/>
+      <c r="D1255" s="38"/>
+      <c r="E1255" s="18"/>
+      <c r="F1255" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="G1255" s="79">
-        <v>16853</v>
-      </c>
-      <c r="H1255" s="80">
-        <v>76548</v>
-      </c>
-      <c r="I1255" s="80" t="s">
-        <v>123</v>
-      </c>
-      <c r="J1255" s="80" t="s">
-        <v>1913</v>
-      </c>
-      <c r="K1255" s="81" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1255" s="82"/>
-      <c r="M1255" s="82"/>
-      <c r="N1255" s="83"/>
-      <c r="O1255" s="82"/>
-      <c r="P1255" s="82"/>
-      <c r="Q1255" s="80">
-        <v>95596076</v>
-      </c>
-      <c r="R1255" s="88" t="s">
+      <c r="G1255" s="57">
+        <v>78112</v>
+      </c>
+      <c r="H1255" s="18"/>
+      <c r="I1255" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1255" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1255" s="18"/>
+      <c r="L1255" s="18"/>
+      <c r="M1255" s="18"/>
+      <c r="N1255" s="40"/>
+      <c r="O1255" s="18"/>
+      <c r="P1255" s="18"/>
+      <c r="Q1255" s="18"/>
+      <c r="R1255" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1256" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1256" spans="1:18" ht="15" thickBot="1">
       <c r="A1256" s="2">
         <v>1255</v>
       </c>
       <c r="B1256" s="10">
         <v>46244</v>
       </c>
-      <c r="C1256" s="56" t="s">
-        <v>1918</v>
-      </c>
-      <c r="D1256" s="56" t="s">
-        <v>1919</v>
-      </c>
-      <c r="E1256" s="12" t="s">
-        <v>21</v>
-      </c>
+      <c r="C1256" s="38"/>
+      <c r="D1256" s="38"/>
+      <c r="E1256" s="18"/>
       <c r="F1256" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1256" s="57">
-        <v>55729</v>
-      </c>
-      <c r="H1256" s="15">
-        <v>21874</v>
-      </c>
-      <c r="I1256" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="J1256" s="15" t="s">
-        <v>1913</v>
-      </c>
-      <c r="K1256" s="17" t="s">
-        <v>12</v>
-      </c>
+        <v>20380</v>
+      </c>
+      <c r="H1256" s="18"/>
+      <c r="I1256" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1256" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1256" s="18"/>
       <c r="L1256" s="18"/>
       <c r="M1256" s="18"/>
       <c r="N1256" s="40"/>
       <c r="O1256" s="18"/>
       <c r="P1256" s="18"/>
-      <c r="Q1256" s="15">
-        <v>77821958</v>
-      </c>
+      <c r="Q1256" s="18"/>
       <c r="R1256" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1257" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1257" spans="1:18" ht="15" thickBot="1">
       <c r="A1257" s="2">
         <v>1256</v>
       </c>
       <c r="B1257" s="10">
         <v>46244</v>
       </c>
-      <c r="C1257" s="56" t="s">
-        <v>1920</v>
-      </c>
-      <c r="D1257" s="56" t="s">
-        <v>1921</v>
-      </c>
-      <c r="E1257" s="12" t="s">
-        <v>21</v>
-      </c>
+      <c r="C1257" s="38"/>
+      <c r="D1257" s="38"/>
+      <c r="E1257" s="18"/>
       <c r="F1257" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1257" s="57">
-        <v>24788</v>
-      </c>
-      <c r="H1257" s="15">
-        <v>81726</v>
-      </c>
-      <c r="I1257" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="J1257" s="15" t="s">
-        <v>1913</v>
-      </c>
-      <c r="K1257" s="17" t="s">
-        <v>12</v>
-      </c>
+        <v>40255</v>
+      </c>
+      <c r="H1257" s="18"/>
+      <c r="I1257" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1257" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1257" s="18"/>
       <c r="L1257" s="18"/>
       <c r="M1257" s="18"/>
       <c r="N1257" s="40"/>
       <c r="O1257" s="18"/>
       <c r="P1257" s="18"/>
-      <c r="Q1257" s="15">
-        <v>555524049</v>
-      </c>
+      <c r="Q1257" s="18"/>
       <c r="R1257" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1258" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1258" spans="1:18" ht="15" thickBot="1">
       <c r="A1258" s="2">
         <v>1257</v>
       </c>
       <c r="B1258" s="10">
         <v>46244</v>
       </c>
-      <c r="C1258" s="56" t="s">
-        <v>1922</v>
-      </c>
-      <c r="D1258" s="56">
-        <v>133589295</v>
-      </c>
-      <c r="E1258" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1258" s="16" t="s">
-        <v>122</v>
+      <c r="C1258" s="38"/>
+      <c r="D1258" s="38"/>
+      <c r="E1258" s="18"/>
+      <c r="F1258" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1258" s="57">
-        <v>4317</v>
-      </c>
-      <c r="H1258" s="15">
-        <v>9901</v>
-      </c>
-      <c r="I1258" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="J1258" s="15" t="s">
-        <v>174</v>
+        <v>78295</v>
+      </c>
+      <c r="H1258" s="18"/>
+      <c r="I1258" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1258" s="52" t="s">
+        <v>776</v>
       </c>
       <c r="K1258" s="18"/>
       <c r="L1258" s="18"/>
@@ -64526,11 +64544,1193 @@
       <c r="N1258" s="40"/>
       <c r="O1258" s="18"/>
       <c r="P1258" s="18"/>
-      <c r="Q1258" s="11">
-        <v>96877336001</v>
-      </c>
+      <c r="Q1258" s="18"/>
       <c r="R1258" s="22" t="s">
         <v>131</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:18" ht="15" thickBot="1">
+      <c r="A1259" s="2">
+        <v>1258</v>
+      </c>
+      <c r="B1259" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1259" s="38"/>
+      <c r="D1259" s="38"/>
+      <c r="E1259" s="18"/>
+      <c r="F1259" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1259" s="57">
+        <v>43916</v>
+      </c>
+      <c r="H1259" s="18"/>
+      <c r="I1259" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1259" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1259" s="18"/>
+      <c r="L1259" s="18"/>
+      <c r="M1259" s="18"/>
+      <c r="N1259" s="40"/>
+      <c r="O1259" s="18"/>
+      <c r="P1259" s="18"/>
+      <c r="Q1259" s="18"/>
+      <c r="R1259" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:18" ht="15" thickBot="1">
+      <c r="A1260" s="2">
+        <v>1259</v>
+      </c>
+      <c r="B1260" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1260" s="38"/>
+      <c r="D1260" s="38"/>
+      <c r="E1260" s="18"/>
+      <c r="F1260" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1260" s="57">
+        <v>18439</v>
+      </c>
+      <c r="H1260" s="18"/>
+      <c r="I1260" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1260" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1260" s="18"/>
+      <c r="L1260" s="18"/>
+      <c r="M1260" s="18"/>
+      <c r="N1260" s="40"/>
+      <c r="O1260" s="18"/>
+      <c r="P1260" s="18"/>
+      <c r="Q1260" s="18"/>
+      <c r="R1260" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:18" ht="15" thickBot="1">
+      <c r="A1261" s="2">
+        <v>1260</v>
+      </c>
+      <c r="B1261" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1261" s="38"/>
+      <c r="D1261" s="38"/>
+      <c r="E1261" s="18"/>
+      <c r="F1261" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1261" s="57">
+        <v>85929</v>
+      </c>
+      <c r="H1261" s="18"/>
+      <c r="I1261" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1261" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1261" s="18"/>
+      <c r="L1261" s="18"/>
+      <c r="M1261" s="18"/>
+      <c r="N1261" s="40"/>
+      <c r="O1261" s="18"/>
+      <c r="P1261" s="18"/>
+      <c r="Q1261" s="18"/>
+      <c r="R1261" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:18" ht="15" thickBot="1">
+      <c r="A1262" s="2">
+        <v>1261</v>
+      </c>
+      <c r="B1262" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1262" s="38"/>
+      <c r="D1262" s="38"/>
+      <c r="E1262" s="18"/>
+      <c r="F1262" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1262" s="57">
+        <v>28434</v>
+      </c>
+      <c r="H1262" s="18"/>
+      <c r="I1262" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1262" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1262" s="18"/>
+      <c r="L1262" s="18"/>
+      <c r="M1262" s="18"/>
+      <c r="N1262" s="40"/>
+      <c r="O1262" s="18"/>
+      <c r="P1262" s="18"/>
+      <c r="Q1262" s="18"/>
+      <c r="R1262" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:18" ht="15" thickBot="1">
+      <c r="A1263" s="2">
+        <v>1262</v>
+      </c>
+      <c r="B1263" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1263" s="56" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D1263" s="56" t="s">
+        <v>1938</v>
+      </c>
+      <c r="E1263" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1263" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1263" s="57">
+        <v>13349</v>
+      </c>
+      <c r="H1263" s="15">
+        <v>43281</v>
+      </c>
+      <c r="I1263" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1263" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1263" s="18"/>
+      <c r="L1263" s="18"/>
+      <c r="M1263" s="18"/>
+      <c r="N1263" s="40"/>
+      <c r="O1263" s="18"/>
+      <c r="P1263" s="18"/>
+      <c r="Q1263" s="18"/>
+      <c r="R1263" s="18"/>
+    </row>
+    <row r="1264" spans="1:18" ht="15" thickBot="1">
+      <c r="A1264" s="2">
+        <v>1263</v>
+      </c>
+      <c r="B1264" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1264" s="56" t="s">
+        <v>1939</v>
+      </c>
+      <c r="D1264" s="56" t="s">
+        <v>1940</v>
+      </c>
+      <c r="E1264" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1264" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1264" s="57">
+        <v>48418</v>
+      </c>
+      <c r="H1264" s="15">
+        <v>62782</v>
+      </c>
+      <c r="I1264" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1264" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1264" s="18"/>
+      <c r="L1264" s="18"/>
+      <c r="M1264" s="18"/>
+      <c r="N1264" s="40"/>
+      <c r="O1264" s="18"/>
+      <c r="P1264" s="18"/>
+      <c r="Q1264" s="18"/>
+      <c r="R1264" s="18"/>
+    </row>
+    <row r="1265" spans="1:18" ht="15" thickBot="1">
+      <c r="A1265" s="2">
+        <v>1264</v>
+      </c>
+      <c r="B1265" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1265" s="56" t="s">
+        <v>1941</v>
+      </c>
+      <c r="D1265" s="56" t="s">
+        <v>1942</v>
+      </c>
+      <c r="E1265" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1265" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1265" s="57">
+        <v>51661</v>
+      </c>
+      <c r="H1265" s="15">
+        <v>40394</v>
+      </c>
+      <c r="I1265" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1265" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1265" s="18"/>
+      <c r="L1265" s="18"/>
+      <c r="M1265" s="18"/>
+      <c r="N1265" s="40"/>
+      <c r="O1265" s="18"/>
+      <c r="P1265" s="18"/>
+      <c r="Q1265" s="18"/>
+      <c r="R1265" s="18"/>
+    </row>
+    <row r="1266" spans="1:18" ht="15" thickBot="1">
+      <c r="A1266" s="2">
+        <v>1265</v>
+      </c>
+      <c r="B1266" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1266" s="56" t="s">
+        <v>1943</v>
+      </c>
+      <c r="D1266" s="56" t="s">
+        <v>1944</v>
+      </c>
+      <c r="E1266" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1266" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1266" s="57">
+        <v>84554</v>
+      </c>
+      <c r="H1266" s="15">
+        <v>21501</v>
+      </c>
+      <c r="I1266" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1266" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1266" s="18"/>
+      <c r="L1266" s="18"/>
+      <c r="M1266" s="18"/>
+      <c r="N1266" s="40"/>
+      <c r="O1266" s="18"/>
+      <c r="P1266" s="18"/>
+      <c r="Q1266" s="18"/>
+      <c r="R1266" s="18"/>
+    </row>
+    <row r="1267" spans="1:18" ht="15" thickBot="1">
+      <c r="A1267" s="2">
+        <v>1266</v>
+      </c>
+      <c r="B1267" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1267" s="56" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D1267" s="56" t="s">
+        <v>1945</v>
+      </c>
+      <c r="E1267" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1267" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1267" s="57">
+        <v>41504</v>
+      </c>
+      <c r="H1267" s="18"/>
+      <c r="I1267" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1267" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1267" s="18"/>
+      <c r="L1267" s="18"/>
+      <c r="M1267" s="18"/>
+      <c r="N1267" s="40"/>
+      <c r="O1267" s="18"/>
+      <c r="P1267" s="18"/>
+      <c r="Q1267" s="18"/>
+      <c r="R1267" s="18"/>
+    </row>
+    <row r="1268" spans="1:18" ht="15" thickBot="1">
+      <c r="A1268" s="2">
+        <v>1267</v>
+      </c>
+      <c r="B1268" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1268" s="56" t="s">
+        <v>1946</v>
+      </c>
+      <c r="D1268" s="38"/>
+      <c r="E1268" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1268" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1268" s="57">
+        <v>17443</v>
+      </c>
+      <c r="H1268" s="15">
+        <v>20106</v>
+      </c>
+      <c r="I1268" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1268" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1268" s="18"/>
+      <c r="L1268" s="18"/>
+      <c r="M1268" s="18"/>
+      <c r="N1268" s="40"/>
+      <c r="O1268" s="18"/>
+      <c r="P1268" s="18"/>
+      <c r="Q1268" s="18"/>
+      <c r="R1268" s="18"/>
+    </row>
+    <row r="1269" spans="1:18" ht="15" thickBot="1">
+      <c r="A1269" s="2">
+        <v>1268</v>
+      </c>
+      <c r="B1269" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1269" s="56" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D1269" s="56">
+        <v>112067329</v>
+      </c>
+      <c r="E1269" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1269" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1269" s="57">
+        <v>2968</v>
+      </c>
+      <c r="H1269" s="15">
+        <v>5613</v>
+      </c>
+      <c r="I1269" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1269" s="15" t="s">
+        <v>839</v>
+      </c>
+      <c r="K1269" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1269" s="18"/>
+      <c r="M1269" s="18"/>
+      <c r="N1269" s="40"/>
+      <c r="O1269" s="18"/>
+      <c r="P1269" s="18"/>
+      <c r="Q1269" s="18"/>
+      <c r="R1269" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1270" s="2">
+        <v>1269</v>
+      </c>
+      <c r="B1270" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1270" s="56" t="s">
+        <v>1875</v>
+      </c>
+      <c r="D1270" s="56">
+        <v>116806083</v>
+      </c>
+      <c r="E1270" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1270" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1270" s="57">
+        <v>442</v>
+      </c>
+      <c r="H1270" s="15">
+        <v>7536</v>
+      </c>
+      <c r="I1270" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1270" s="15" t="s">
+        <v>950</v>
+      </c>
+      <c r="K1270" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1270" s="18"/>
+      <c r="M1270" s="18"/>
+      <c r="N1270" s="40"/>
+      <c r="O1270" s="18"/>
+      <c r="P1270" s="18"/>
+      <c r="Q1270" s="11">
+        <v>79997138</v>
+      </c>
+      <c r="R1270" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:18" ht="15" thickBot="1">
+      <c r="A1271" s="2">
+        <v>1270</v>
+      </c>
+      <c r="B1271" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1271" s="56" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D1271" s="56">
+        <v>113458078</v>
+      </c>
+      <c r="E1271" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1271" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1271" s="57">
+        <v>5913</v>
+      </c>
+      <c r="H1271" s="15">
+        <v>1154</v>
+      </c>
+      <c r="I1271" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1271" s="15" t="s">
+        <v>950</v>
+      </c>
+      <c r="K1271" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1271" s="18"/>
+      <c r="M1271" s="18"/>
+      <c r="N1271" s="40"/>
+      <c r="O1271" s="18"/>
+      <c r="P1271" s="18"/>
+      <c r="Q1271" s="18"/>
+      <c r="R1271" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1272" s="2">
+        <v>1271</v>
+      </c>
+      <c r="B1272" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1272" s="56" t="s">
+        <v>638</v>
+      </c>
+      <c r="D1272" s="56">
+        <v>122952217</v>
+      </c>
+      <c r="E1272" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1272" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1272" s="57">
+        <v>4581</v>
+      </c>
+      <c r="H1272" s="15">
+        <v>-8325</v>
+      </c>
+      <c r="I1272" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1272" s="15" t="s">
+        <v>950</v>
+      </c>
+      <c r="K1272" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1272" s="18"/>
+      <c r="M1272" s="18"/>
+      <c r="N1272" s="40"/>
+      <c r="O1272" s="18"/>
+      <c r="P1272" s="18"/>
+      <c r="Q1272" s="11" t="s">
+        <v>1877</v>
+      </c>
+      <c r="R1272" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:18" ht="15" thickBot="1">
+      <c r="A1273" s="2">
+        <v>1272</v>
+      </c>
+      <c r="B1273" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1273" s="56" t="s">
+        <v>1878</v>
+      </c>
+      <c r="D1273" s="56">
+        <v>126214395</v>
+      </c>
+      <c r="E1273" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1273" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1273" s="57">
+        <v>355</v>
+      </c>
+      <c r="H1273" s="15">
+        <v>2278</v>
+      </c>
+      <c r="I1273" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1273" s="15" t="s">
+        <v>950</v>
+      </c>
+      <c r="K1273" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1273" s="18"/>
+      <c r="M1273" s="18"/>
+      <c r="N1273" s="40"/>
+      <c r="O1273" s="18"/>
+      <c r="P1273" s="18"/>
+      <c r="Q1273" s="18"/>
+      <c r="R1273" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1274" s="2">
+        <v>1273</v>
+      </c>
+      <c r="B1274" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1274" s="56" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1274" s="56" t="s">
+        <v>1879</v>
+      </c>
+      <c r="E1274" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1274" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1274" s="57">
+        <v>33404</v>
+      </c>
+      <c r="H1274" s="15">
+        <v>89137</v>
+      </c>
+      <c r="I1274" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1274" s="15" t="s">
+        <v>1880</v>
+      </c>
+      <c r="K1274" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1274" s="18"/>
+      <c r="M1274" s="18"/>
+      <c r="N1274" s="40"/>
+      <c r="O1274" s="18"/>
+      <c r="P1274" s="18"/>
+      <c r="Q1274" s="11">
+        <v>95643750</v>
+      </c>
+      <c r="R1274" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1275" s="2">
+        <v>1274</v>
+      </c>
+      <c r="B1275" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1275" s="56" t="s">
+        <v>504</v>
+      </c>
+      <c r="D1275" s="56" t="s">
+        <v>1881</v>
+      </c>
+      <c r="E1275" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1275" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1275" s="57">
+        <v>7606</v>
+      </c>
+      <c r="H1275" s="15">
+        <v>66793</v>
+      </c>
+      <c r="I1275" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1275" s="15" t="s">
+        <v>1880</v>
+      </c>
+      <c r="K1275" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1275" s="18"/>
+      <c r="M1275" s="18"/>
+      <c r="N1275" s="40"/>
+      <c r="O1275" s="18"/>
+      <c r="P1275" s="18"/>
+      <c r="Q1275" s="11">
+        <v>501924525</v>
+      </c>
+      <c r="R1275" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1276" s="2">
+        <v>1275</v>
+      </c>
+      <c r="B1276" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1276" s="56" t="s">
+        <v>906</v>
+      </c>
+      <c r="D1276" s="56">
+        <v>128333109</v>
+      </c>
+      <c r="E1276" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1276" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1276" s="57">
+        <v>4900</v>
+      </c>
+      <c r="H1276" s="15">
+        <v>-6338</v>
+      </c>
+      <c r="I1276" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1276" s="15" t="s">
+        <v>890</v>
+      </c>
+      <c r="K1276" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1276" s="18"/>
+      <c r="M1276" s="18"/>
+      <c r="N1276" s="40"/>
+      <c r="O1276" s="18"/>
+      <c r="P1276" s="18"/>
+      <c r="Q1276" s="11">
+        <v>95609530</v>
+      </c>
+      <c r="R1276" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:18" ht="15" thickBot="1">
+      <c r="A1277" s="2">
+        <v>1276</v>
+      </c>
+      <c r="B1277" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1277" s="56" t="s">
+        <v>1894</v>
+      </c>
+      <c r="D1277" s="56">
+        <v>116033629</v>
+      </c>
+      <c r="E1277" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1277" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1277" s="57">
+        <v>1702</v>
+      </c>
+      <c r="H1277" s="15">
+        <v>5164</v>
+      </c>
+      <c r="I1277" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1277" s="15" t="s">
+        <v>950</v>
+      </c>
+      <c r="K1277" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1277" s="18"/>
+      <c r="M1277" s="18"/>
+      <c r="N1277" s="40"/>
+      <c r="O1277" s="18"/>
+      <c r="P1277" s="18"/>
+      <c r="Q1277" s="11">
+        <v>94250210</v>
+      </c>
+      <c r="R1277" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1278" s="2">
+        <v>1277</v>
+      </c>
+      <c r="B1278" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1278" s="56" t="s">
+        <v>1895</v>
+      </c>
+      <c r="D1278" s="56" t="s">
+        <v>1896</v>
+      </c>
+      <c r="E1278" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1278" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1278" s="57">
+        <v>21668</v>
+      </c>
+      <c r="H1278" s="15">
+        <v>75184</v>
+      </c>
+      <c r="I1278" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1278" s="15" t="s">
+        <v>1897</v>
+      </c>
+      <c r="K1278" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1278" s="18"/>
+      <c r="M1278" s="18"/>
+      <c r="N1278" s="40"/>
+      <c r="O1278" s="18"/>
+      <c r="P1278" s="18"/>
+      <c r="Q1278" s="11">
+        <v>557824163</v>
+      </c>
+      <c r="R1278" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1279" s="2">
+        <v>1278</v>
+      </c>
+      <c r="B1279" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1279" s="56" t="s">
+        <v>1898</v>
+      </c>
+      <c r="D1279" s="56" t="s">
+        <v>1899</v>
+      </c>
+      <c r="E1279" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1279" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1279" s="57">
+        <v>9215</v>
+      </c>
+      <c r="H1279" s="15">
+        <v>10278</v>
+      </c>
+      <c r="I1279" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1279" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1279" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1279" s="18"/>
+      <c r="M1279" s="18"/>
+      <c r="N1279" s="40"/>
+      <c r="O1279" s="18"/>
+      <c r="P1279" s="18"/>
+      <c r="Q1279" s="18"/>
+      <c r="R1279" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1280" s="2">
+        <v>1279</v>
+      </c>
+      <c r="B1280" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1280" s="56" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D1280" s="56" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E1280" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1280" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1280" s="57">
+        <v>53578</v>
+      </c>
+      <c r="H1280" s="15">
+        <v>46411</v>
+      </c>
+      <c r="I1280" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1280" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1280" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1280" s="18"/>
+      <c r="M1280" s="18"/>
+      <c r="N1280" s="40"/>
+      <c r="O1280" s="18"/>
+      <c r="P1280" s="18"/>
+      <c r="Q1280" s="18"/>
+      <c r="R1280" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:18" ht="15" thickBot="1">
+      <c r="A1281" s="2">
+        <v>1280</v>
+      </c>
+      <c r="B1281" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1281" s="56" t="s">
+        <v>1902</v>
+      </c>
+      <c r="D1281" s="56" t="s">
+        <v>1903</v>
+      </c>
+      <c r="E1281" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1281" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1281" s="57">
+        <v>68833</v>
+      </c>
+      <c r="H1281" s="15">
+        <v>78793</v>
+      </c>
+      <c r="I1281" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1281" s="15" t="s">
+        <v>1904</v>
+      </c>
+      <c r="K1281" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1281" s="18"/>
+      <c r="M1281" s="18"/>
+      <c r="N1281" s="40"/>
+      <c r="O1281" s="18"/>
+      <c r="P1281" s="18"/>
+      <c r="Q1281" s="11">
+        <v>554186760</v>
+      </c>
+      <c r="R1281" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:18" ht="15" thickBot="1">
+      <c r="A1282" s="2">
+        <v>1281</v>
+      </c>
+      <c r="B1282" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1282" s="56" t="s">
+        <v>1905</v>
+      </c>
+      <c r="D1282" s="56" t="s">
+        <v>1906</v>
+      </c>
+      <c r="E1282" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1282" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1282" s="57">
+        <v>56757</v>
+      </c>
+      <c r="H1282" s="15" t="s">
+        <v>1907</v>
+      </c>
+      <c r="I1282" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1282" s="15" t="s">
+        <v>1904</v>
+      </c>
+      <c r="K1282" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1282" s="18"/>
+      <c r="M1282" s="18"/>
+      <c r="N1282" s="40"/>
+      <c r="O1282" s="18"/>
+      <c r="P1282" s="18"/>
+      <c r="Q1282" s="11">
+        <v>76969759</v>
+      </c>
+      <c r="R1282" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1283" s="2">
+        <v>1282</v>
+      </c>
+      <c r="B1283" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1283" s="56" t="s">
+        <v>1908</v>
+      </c>
+      <c r="D1283" s="56" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1283" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1283" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1283" s="57">
+        <v>61918</v>
+      </c>
+      <c r="H1283" s="15">
+        <v>19939</v>
+      </c>
+      <c r="I1283" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1283" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K1283" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1283" s="18"/>
+      <c r="M1283" s="18"/>
+      <c r="N1283" s="40"/>
+      <c r="O1283" s="18"/>
+      <c r="P1283" s="18"/>
+      <c r="Q1283" s="18"/>
+      <c r="R1283" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1284" s="2">
+        <v>1283</v>
+      </c>
+      <c r="B1284" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1284" s="56" t="s">
+        <v>1910</v>
+      </c>
+      <c r="D1284" s="56" t="s">
+        <v>1911</v>
+      </c>
+      <c r="E1284" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1284" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1284" s="57">
+        <v>8490</v>
+      </c>
+      <c r="H1284" s="15">
+        <v>8101</v>
+      </c>
+      <c r="I1284" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1284" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="K1284" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1284" s="18"/>
+      <c r="M1284" s="18"/>
+      <c r="N1284" s="40"/>
+      <c r="O1284" s="18"/>
+      <c r="P1284" s="18"/>
+      <c r="Q1284" s="11">
+        <v>98705284</v>
+      </c>
+      <c r="R1284" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1285" s="2">
+        <v>1284</v>
+      </c>
+      <c r="B1285" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1285" s="56" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D1285" s="56" t="s">
+        <v>1948</v>
+      </c>
+      <c r="E1285" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1285" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1285" s="57">
+        <v>18552</v>
+      </c>
+      <c r="H1285" s="15">
+        <v>36476</v>
+      </c>
+      <c r="I1285" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1285" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1285" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1285" s="18"/>
+      <c r="M1285" s="18"/>
+      <c r="N1285" s="40"/>
+      <c r="O1285" s="18"/>
+      <c r="P1285" s="18"/>
+      <c r="Q1285" s="18"/>
+      <c r="R1285" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:18" ht="15" thickBot="1">
+      <c r="A1286" s="2">
+        <v>1285</v>
+      </c>
+      <c r="B1286" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1286" s="56" t="s">
+        <v>1949</v>
+      </c>
+      <c r="D1286" s="56">
+        <v>132109131</v>
+      </c>
+      <c r="E1286" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1286" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1286" s="57">
+        <v>1052</v>
+      </c>
+      <c r="H1286" s="15">
+        <v>2979</v>
+      </c>
+      <c r="I1286" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1286" s="15" t="s">
+        <v>715</v>
+      </c>
+      <c r="K1286" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1286" s="18"/>
+      <c r="M1286" s="18"/>
+      <c r="N1286" s="40"/>
+      <c r="O1286" s="18"/>
+      <c r="P1286" s="18"/>
+      <c r="Q1286" s="18"/>
+      <c r="R1286" s="20" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8801E9E7-4691-4CEA-949B-47100BDD291A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C59FBB-0CFD-492F-A85E-F97210E92ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9505" uniqueCount="1950">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9573" uniqueCount="1964">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -5888,6 +5888,48 @@
   </si>
   <si>
     <t>FAROOQ UMAR</t>
+  </si>
+  <si>
+    <t>IMRAN AFZAL</t>
+  </si>
+  <si>
+    <t>EN1510024</t>
+  </si>
+  <si>
+    <t>AQEEL KHAN</t>
+  </si>
+  <si>
+    <t>WM4119283</t>
+  </si>
+  <si>
+    <t>AHMAD CHAUDHRY</t>
+  </si>
+  <si>
+    <t>XF1152086</t>
+  </si>
+  <si>
+    <t>SALUM ALLY</t>
+  </si>
+  <si>
+    <t>SALIM SULTAN</t>
+  </si>
+  <si>
+    <t>SAIF NASSER</t>
+  </si>
+  <si>
+    <t>BARGASH</t>
+  </si>
+  <si>
+    <t>SULTAN RASHID</t>
+  </si>
+  <si>
+    <t>YUSUF SLEYUM</t>
+  </si>
+  <si>
+    <t>IQBAL FAISAL</t>
+  </si>
+  <si>
+    <t>NC1333693</t>
   </si>
 </sst>
 </file>
@@ -6264,7 +6306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6487,6 +6529,54 @@
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6802,7 +6892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1286"/>
+  <dimension ref="A1:R1298"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -65733,6 +65823,494 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1287" spans="1:18" ht="15" thickBot="1">
+      <c r="A1287" s="2">
+        <v>1286</v>
+      </c>
+      <c r="B1287" s="75">
+        <v>46244</v>
+      </c>
+      <c r="C1287" s="76" t="s">
+        <v>1950</v>
+      </c>
+      <c r="D1287" s="76" t="s">
+        <v>1951</v>
+      </c>
+      <c r="E1287" s="85" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1287" s="86" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1287" s="78">
+        <v>20603</v>
+      </c>
+      <c r="H1287" s="79">
+        <v>11429</v>
+      </c>
+      <c r="I1287" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1287" s="79" t="s">
+        <v>130</v>
+      </c>
+      <c r="K1287" s="80" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1287" s="81"/>
+      <c r="M1287" s="81"/>
+      <c r="N1287" s="82"/>
+      <c r="O1287" s="81"/>
+      <c r="P1287" s="81"/>
+      <c r="Q1287" s="81"/>
+      <c r="R1287" s="81"/>
+    </row>
+    <row r="1288" spans="1:18" ht="15" thickBot="1">
+      <c r="A1288" s="2">
+        <v>1287</v>
+      </c>
+      <c r="B1288" s="75">
+        <v>46244</v>
+      </c>
+      <c r="C1288" s="76" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D1288" s="76" t="s">
+        <v>1953</v>
+      </c>
+      <c r="E1288" s="85" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1288" s="86" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1288" s="78">
+        <v>82557</v>
+      </c>
+      <c r="H1288" s="79">
+        <v>23835</v>
+      </c>
+      <c r="I1288" s="87" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1288" s="88" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1288" s="81"/>
+      <c r="L1288" s="81"/>
+      <c r="M1288" s="81"/>
+      <c r="N1288" s="82"/>
+      <c r="O1288" s="81"/>
+      <c r="P1288" s="81"/>
+      <c r="Q1288" s="81"/>
+      <c r="R1288" s="81"/>
+    </row>
+    <row r="1289" spans="1:18" ht="15" thickBot="1">
+      <c r="A1289" s="2">
+        <v>1288</v>
+      </c>
+      <c r="B1289" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1289" s="56" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D1289" s="56">
+        <v>107774476</v>
+      </c>
+      <c r="E1289" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1289" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1289" s="57">
+        <v>3561</v>
+      </c>
+      <c r="H1289" s="15">
+        <v>5702</v>
+      </c>
+      <c r="I1289" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1289" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1289" s="18"/>
+      <c r="L1289" s="18"/>
+      <c r="M1289" s="18"/>
+      <c r="N1289" s="40"/>
+      <c r="O1289" s="18"/>
+      <c r="P1289" s="18"/>
+      <c r="Q1289" s="18"/>
+      <c r="R1289" s="18"/>
+    </row>
+    <row r="1290" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1290" s="2">
+        <v>1289</v>
+      </c>
+      <c r="B1290" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1290" s="56" t="s">
+        <v>1954</v>
+      </c>
+      <c r="D1290" s="56" t="s">
+        <v>1955</v>
+      </c>
+      <c r="E1290" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1290" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1290" s="57">
+        <v>22319</v>
+      </c>
+      <c r="H1290" s="15">
+        <v>19801</v>
+      </c>
+      <c r="I1290" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1290" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1290" s="18"/>
+      <c r="L1290" s="18"/>
+      <c r="M1290" s="18"/>
+      <c r="N1290" s="40"/>
+      <c r="O1290" s="18"/>
+      <c r="P1290" s="18"/>
+      <c r="Q1290" s="18"/>
+      <c r="R1290" s="18"/>
+    </row>
+    <row r="1291" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1291" s="2">
+        <v>1290</v>
+      </c>
+      <c r="B1291" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1291" s="56" t="s">
+        <v>1956</v>
+      </c>
+      <c r="D1291" s="56">
+        <v>36336406</v>
+      </c>
+      <c r="E1291" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1291" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1291" s="57">
+        <v>1965</v>
+      </c>
+      <c r="H1291" s="15">
+        <v>826</v>
+      </c>
+      <c r="I1291" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1291" s="15" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K1291" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1291" s="18"/>
+      <c r="M1291" s="18"/>
+      <c r="N1291" s="40"/>
+      <c r="O1291" s="18"/>
+      <c r="P1291" s="18"/>
+      <c r="Q1291" s="18"/>
+      <c r="R1291" s="18"/>
+    </row>
+    <row r="1292" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1292" s="2">
+        <v>1291</v>
+      </c>
+      <c r="B1292" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1292" s="56" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D1292" s="56">
+        <v>17065948</v>
+      </c>
+      <c r="E1292" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1292" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1292" s="57">
+        <v>5788</v>
+      </c>
+      <c r="H1292" s="15">
+        <v>9112</v>
+      </c>
+      <c r="I1292" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1292" s="15" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K1292" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1292" s="18"/>
+      <c r="M1292" s="18"/>
+      <c r="N1292" s="40"/>
+      <c r="O1292" s="18"/>
+      <c r="P1292" s="18"/>
+      <c r="Q1292" s="18"/>
+      <c r="R1292" s="18"/>
+    </row>
+    <row r="1293" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1293" s="2">
+        <v>1292</v>
+      </c>
+      <c r="B1293" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1293" s="56" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D1293" s="56">
+        <v>3084818</v>
+      </c>
+      <c r="E1293" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1293" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1293" s="57">
+        <v>6300</v>
+      </c>
+      <c r="H1293" s="15">
+        <v>8487</v>
+      </c>
+      <c r="I1293" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1293" s="15" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K1293" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1293" s="18"/>
+      <c r="M1293" s="18"/>
+      <c r="N1293" s="40"/>
+      <c r="O1293" s="18"/>
+      <c r="P1293" s="18"/>
+      <c r="Q1293" s="18"/>
+      <c r="R1293" s="18"/>
+    </row>
+    <row r="1294" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1294" s="2">
+        <v>1293</v>
+      </c>
+      <c r="B1294" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1294" s="56" t="s">
+        <v>1959</v>
+      </c>
+      <c r="D1294" s="56">
+        <v>2144791</v>
+      </c>
+      <c r="E1294" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1294" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1294" s="57">
+        <v>1598</v>
+      </c>
+      <c r="H1294" s="15">
+        <v>3380</v>
+      </c>
+      <c r="I1294" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1294" s="15" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K1294" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1294" s="18"/>
+      <c r="M1294" s="18"/>
+      <c r="N1294" s="40"/>
+      <c r="O1294" s="18"/>
+      <c r="P1294" s="18"/>
+      <c r="Q1294" s="18"/>
+      <c r="R1294" s="18"/>
+    </row>
+    <row r="1295" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1295" s="2">
+        <v>1294</v>
+      </c>
+      <c r="B1295" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1295" s="56" t="s">
+        <v>1960</v>
+      </c>
+      <c r="D1295" s="56">
+        <v>12571732</v>
+      </c>
+      <c r="E1295" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1295" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1295" s="57">
+        <v>8884</v>
+      </c>
+      <c r="H1295" s="15">
+        <v>8169</v>
+      </c>
+      <c r="I1295" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1295" s="15" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K1295" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1295" s="18"/>
+      <c r="M1295" s="18"/>
+      <c r="N1295" s="40"/>
+      <c r="O1295" s="18"/>
+      <c r="P1295" s="18"/>
+      <c r="Q1295" s="18"/>
+      <c r="R1295" s="18"/>
+    </row>
+    <row r="1296" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1296" s="2">
+        <v>1295</v>
+      </c>
+      <c r="B1296" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1296" s="56" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D1296" s="56">
+        <v>96995164</v>
+      </c>
+      <c r="E1296" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1296" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1296" s="57">
+        <v>8884</v>
+      </c>
+      <c r="H1296" s="15">
+        <v>8169</v>
+      </c>
+      <c r="I1296" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1296" s="15" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K1296" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1296" s="18"/>
+      <c r="M1296" s="18"/>
+      <c r="N1296" s="40"/>
+      <c r="O1296" s="18"/>
+      <c r="P1296" s="18"/>
+      <c r="Q1296" s="18"/>
+      <c r="R1296" s="18"/>
+    </row>
+    <row r="1297" spans="1:18" ht="15" thickBot="1">
+      <c r="A1297" s="2">
+        <v>1296</v>
+      </c>
+      <c r="B1297" s="75">
+        <v>46244</v>
+      </c>
+      <c r="C1297" s="76" t="s">
+        <v>1962</v>
+      </c>
+      <c r="D1297" s="76" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E1297" s="85" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1297" s="86" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1297" s="78">
+        <v>71861</v>
+      </c>
+      <c r="H1297" s="79">
+        <v>38386</v>
+      </c>
+      <c r="I1297" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1297" s="79" t="s">
+        <v>127</v>
+      </c>
+      <c r="K1297" s="89" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1297" s="81"/>
+      <c r="M1297" s="81"/>
+      <c r="N1297" s="82"/>
+      <c r="O1297" s="81"/>
+      <c r="P1297" s="81"/>
+      <c r="Q1297" s="83">
+        <v>77439516</v>
+      </c>
+      <c r="R1297" s="84" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:18" ht="15" thickBot="1">
+      <c r="A1298" s="2">
+        <v>1297</v>
+      </c>
+      <c r="B1298" s="75">
+        <v>46244</v>
+      </c>
+      <c r="C1298" s="90"/>
+      <c r="D1298" s="90"/>
+      <c r="E1298" s="81"/>
+      <c r="F1298" s="81"/>
+      <c r="G1298" s="78">
+        <v>9125</v>
+      </c>
+      <c r="H1298" s="79">
+        <v>988</v>
+      </c>
+      <c r="I1298" s="81"/>
+      <c r="J1298" s="81"/>
+      <c r="K1298" s="81"/>
+      <c r="L1298" s="81"/>
+      <c r="M1298" s="81"/>
+      <c r="N1298" s="82"/>
+      <c r="O1298" s="81"/>
+      <c r="P1298" s="81"/>
+      <c r="Q1298" s="81"/>
+      <c r="R1298" s="81"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C59FBB-0CFD-492F-A85E-F97210E92ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D85D26A-9233-43B7-A3AD-4E0FDEE167AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
+    <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9573" uniqueCount="1964">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9749" uniqueCount="2006">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -5930,6 +5930,132 @@
   </si>
   <si>
     <t>NC1333693</t>
+  </si>
+  <si>
+    <t>BLOCKED BY PORT</t>
+  </si>
+  <si>
+    <t>ABDUL REHMAN</t>
+  </si>
+  <si>
+    <t>BW8911814</t>
+  </si>
+  <si>
+    <t>JABRAN ALI</t>
+  </si>
+  <si>
+    <t>MU1802704</t>
+  </si>
+  <si>
+    <t>WARIS</t>
+  </si>
+  <si>
+    <t>AP6910976</t>
+  </si>
+  <si>
+    <t>AY8675314</t>
+  </si>
+  <si>
+    <t>MD ASIF</t>
+  </si>
+  <si>
+    <t>W5147719</t>
+  </si>
+  <si>
+    <t>SAIF KHAN</t>
+  </si>
+  <si>
+    <t>U9585850</t>
+  </si>
+  <si>
+    <t>ADIL KHAN</t>
+  </si>
+  <si>
+    <t>B682075</t>
+  </si>
+  <si>
+    <t>UMESH KUMAR</t>
+  </si>
+  <si>
+    <t>ZA453540</t>
+  </si>
+  <si>
+    <t>SH1799956</t>
+  </si>
+  <si>
+    <t>AMJAD</t>
+  </si>
+  <si>
+    <t>JAHAN ZAIB</t>
+  </si>
+  <si>
+    <t>ZULFIKER ALI</t>
+  </si>
+  <si>
+    <t>Z5557363</t>
+  </si>
+  <si>
+    <t>GHOUSE</t>
+  </si>
+  <si>
+    <t>C4765134</t>
+  </si>
+  <si>
+    <t>MERAJ ALAM</t>
+  </si>
+  <si>
+    <t>Z4921588</t>
+  </si>
+  <si>
+    <t>JAVED AKHTAR</t>
+  </si>
+  <si>
+    <t>Z6434333</t>
+  </si>
+  <si>
+    <t>FIROZ AHMAD</t>
+  </si>
+  <si>
+    <t>ZA453519</t>
+  </si>
+  <si>
+    <t>MAHBOOB ALAM</t>
+  </si>
+  <si>
+    <t>Z6458504</t>
+  </si>
+  <si>
+    <t>DANNY JOSEPH</t>
+  </si>
+  <si>
+    <t>Z6706856</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>HAMZA MANSOOR</t>
+  </si>
+  <si>
+    <t>JEBAL ALI</t>
+  </si>
+  <si>
+    <t>ALI ASHGAR</t>
+  </si>
+  <si>
+    <t>MUHAMMED SOHAIL</t>
+  </si>
+  <si>
+    <t>AAMIR RASHID</t>
+  </si>
+  <si>
+    <t>SAID SALMAN</t>
+  </si>
+  <si>
+    <t>KHALFAN</t>
+  </si>
+  <si>
+    <t>ZAID HUSSAIN</t>
   </si>
 </sst>
 </file>
@@ -6306,7 +6432,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6530,53 +6656,11 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6892,7 +6976,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1298"/>
+  <dimension ref="A1:R1312"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -6959,9 +7043,7 @@
       <c r="Q1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="R1" s="4"/>
     </row>
     <row r="2" spans="1:18" ht="28.2" thickBot="1">
       <c r="A2" s="2">
@@ -30903,7 +30985,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="513" spans="1:18" ht="15" thickBot="1">
+    <row r="513" spans="1:18" ht="21" thickBot="1">
       <c r="A513" s="2">
         <v>512</v>
       </c>
@@ -30934,14 +31016,16 @@
       <c r="J513" s="15" t="s">
         <v>961</v>
       </c>
-      <c r="K513" s="17" t="s">
-        <v>12</v>
+      <c r="K513" s="37" t="s">
+        <v>175</v>
       </c>
       <c r="L513" s="18"/>
       <c r="M513" s="18"/>
       <c r="N513" s="40"/>
       <c r="O513" s="18"/>
-      <c r="P513" s="18"/>
+      <c r="P513" s="50" t="s">
+        <v>1964</v>
+      </c>
       <c r="Q513" s="11">
         <v>90122897</v>
       </c>
@@ -61732,7 +61816,9 @@
       <c r="J1192" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="K1192" s="18"/>
+      <c r="K1192" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1192" s="18"/>
       <c r="M1192" s="18"/>
       <c r="N1192" s="40"/>
@@ -61776,7 +61862,9 @@
       <c r="J1193" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="K1193" s="18"/>
+      <c r="K1193" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1193" s="18"/>
       <c r="M1193" s="18"/>
       <c r="N1193" s="40"/>
@@ -61820,7 +61908,9 @@
       <c r="J1194" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="K1194" s="18"/>
+      <c r="K1194" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1194" s="18"/>
       <c r="M1194" s="18"/>
       <c r="N1194" s="40"/>
@@ -61864,7 +61954,9 @@
       <c r="J1195" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="K1195" s="18"/>
+      <c r="K1195" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1195" s="18"/>
       <c r="M1195" s="18"/>
       <c r="N1195" s="40"/>
@@ -62151,47 +62243,39 @@
         <v>46244</v>
       </c>
       <c r="C1202" s="56" t="s">
-        <v>1843</v>
-      </c>
-      <c r="D1202" s="56">
-        <v>12175744</v>
+        <v>1950</v>
+      </c>
+      <c r="D1202" s="56" t="s">
+        <v>1951</v>
       </c>
       <c r="E1202" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1202" s="16" t="s">
-        <v>122</v>
+      <c r="F1202" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1202" s="57">
-        <v>2168</v>
+        <v>20603</v>
       </c>
       <c r="H1202" s="15">
-        <v>2168</v>
-      </c>
-      <c r="I1202" s="22" t="s">
-        <v>563</v>
-      </c>
-      <c r="J1202" s="51" t="s">
-        <v>564</v>
+        <v>11429</v>
+      </c>
+      <c r="I1202" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1202" s="15" t="s">
+        <v>130</v>
       </c>
       <c r="K1202" s="17" t="s">
         <v>12</v>
       </c>
       <c r="L1202" s="18"/>
       <c r="M1202" s="18"/>
-      <c r="N1202" s="55">
-        <v>353</v>
-      </c>
+      <c r="N1202" s="40"/>
       <c r="O1202" s="18"/>
-      <c r="P1202" s="50" t="s">
-        <v>1844</v>
-      </c>
-      <c r="Q1202" s="11">
-        <v>98504360</v>
-      </c>
-      <c r="R1202" s="22" t="s">
-        <v>131</v>
-      </c>
+      <c r="P1202" s="18"/>
+      <c r="Q1202" s="18"/>
+      <c r="R1202" s="18"/>
     </row>
     <row r="1203" spans="1:18" ht="15" thickBot="1">
       <c r="A1203" s="2">
@@ -62201,22 +62285,22 @@
         <v>46244</v>
       </c>
       <c r="C1203" s="56" t="s">
-        <v>1845</v>
-      </c>
-      <c r="D1203" s="56" t="s">
-        <v>1846</v>
+        <v>1843</v>
+      </c>
+      <c r="D1203" s="56">
+        <v>12175744</v>
       </c>
       <c r="E1203" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1203" s="13" t="s">
-        <v>22</v>
+      <c r="F1203" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1203" s="57">
-        <v>71359</v>
+        <v>2168</v>
       </c>
       <c r="H1203" s="15">
-        <v>88489</v>
+        <v>2168</v>
       </c>
       <c r="I1203" s="22" t="s">
         <v>563</v>
@@ -62229,11 +62313,15 @@
       </c>
       <c r="L1203" s="18"/>
       <c r="M1203" s="18"/>
-      <c r="N1203" s="40"/>
+      <c r="N1203" s="55">
+        <v>353</v>
+      </c>
       <c r="O1203" s="18"/>
-      <c r="P1203" s="18"/>
-      <c r="Q1203" s="15">
-        <v>77391393</v>
+      <c r="P1203" s="50" t="s">
+        <v>1844</v>
+      </c>
+      <c r="Q1203" s="11">
+        <v>98504360</v>
       </c>
       <c r="R1203" s="22" t="s">
         <v>131</v>
@@ -62247,10 +62335,10 @@
         <v>46244</v>
       </c>
       <c r="C1204" s="56" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="D1204" s="56" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
       <c r="E1204" s="12" t="s">
         <v>21</v>
@@ -62259,10 +62347,10 @@
         <v>22</v>
       </c>
       <c r="G1204" s="57">
-        <v>64626</v>
+        <v>71359</v>
       </c>
       <c r="H1204" s="15">
-        <v>66431</v>
+        <v>88489</v>
       </c>
       <c r="I1204" s="22" t="s">
         <v>563</v>
@@ -62279,7 +62367,7 @@
       <c r="O1204" s="18"/>
       <c r="P1204" s="18"/>
       <c r="Q1204" s="15">
-        <v>96877836595</v>
+        <v>77391393</v>
       </c>
       <c r="R1204" s="22" t="s">
         <v>131</v>
@@ -62293,10 +62381,10 @@
         <v>46244</v>
       </c>
       <c r="C1205" s="56" t="s">
-        <v>789</v>
+        <v>1847</v>
       </c>
       <c r="D1205" s="56" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="E1205" s="12" t="s">
         <v>21</v>
@@ -62305,10 +62393,10 @@
         <v>22</v>
       </c>
       <c r="G1205" s="57">
-        <v>71507</v>
+        <v>64626</v>
       </c>
       <c r="H1205" s="15">
-        <v>81670</v>
+        <v>66431</v>
       </c>
       <c r="I1205" s="22" t="s">
         <v>563</v>
@@ -62316,8 +62404,8 @@
       <c r="J1205" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1205" s="30" t="s">
-        <v>1596</v>
+      <c r="K1205" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1205" s="18"/>
       <c r="M1205" s="18"/>
@@ -62325,7 +62413,7 @@
       <c r="O1205" s="18"/>
       <c r="P1205" s="18"/>
       <c r="Q1205" s="15">
-        <v>77548862</v>
+        <v>96877836595</v>
       </c>
       <c r="R1205" s="22" t="s">
         <v>131</v>
@@ -62339,10 +62427,10 @@
         <v>46244</v>
       </c>
       <c r="C1206" s="56" t="s">
-        <v>1850</v>
+        <v>789</v>
       </c>
       <c r="D1206" s="56" t="s">
-        <v>1851</v>
+        <v>1849</v>
       </c>
       <c r="E1206" s="12" t="s">
         <v>21</v>
@@ -62351,10 +62439,10 @@
         <v>22</v>
       </c>
       <c r="G1206" s="57">
-        <v>44366</v>
+        <v>71507</v>
       </c>
       <c r="H1206" s="15">
-        <v>98082</v>
+        <v>81670</v>
       </c>
       <c r="I1206" s="22" t="s">
         <v>563</v>
@@ -62362,8 +62450,8 @@
       <c r="J1206" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1206" s="17" t="s">
-        <v>12</v>
+      <c r="K1206" s="30" t="s">
+        <v>1596</v>
       </c>
       <c r="L1206" s="18"/>
       <c r="M1206" s="18"/>
@@ -62371,7 +62459,7 @@
       <c r="O1206" s="18"/>
       <c r="P1206" s="18"/>
       <c r="Q1206" s="15">
-        <v>589621226</v>
+        <v>77548862</v>
       </c>
       <c r="R1206" s="22" t="s">
         <v>131</v>
@@ -62385,10 +62473,10 @@
         <v>46244</v>
       </c>
       <c r="C1207" s="56" t="s">
-        <v>1852</v>
+        <v>1850</v>
       </c>
       <c r="D1207" s="56" t="s">
-        <v>1853</v>
+        <v>1851</v>
       </c>
       <c r="E1207" s="12" t="s">
         <v>21</v>
@@ -62397,10 +62485,10 @@
         <v>22</v>
       </c>
       <c r="G1207" s="57">
-        <v>4576</v>
+        <v>44366</v>
       </c>
       <c r="H1207" s="15">
-        <v>55234</v>
+        <v>98082</v>
       </c>
       <c r="I1207" s="22" t="s">
         <v>563</v>
@@ -62417,7 +62505,7 @@
       <c r="O1207" s="18"/>
       <c r="P1207" s="18"/>
       <c r="Q1207" s="15">
-        <v>502405112</v>
+        <v>589621226</v>
       </c>
       <c r="R1207" s="22" t="s">
         <v>131</v>
@@ -62431,10 +62519,10 @@
         <v>46244</v>
       </c>
       <c r="C1208" s="56" t="s">
-        <v>1854</v>
+        <v>1852</v>
       </c>
       <c r="D1208" s="56" t="s">
-        <v>1855</v>
+        <v>1853</v>
       </c>
       <c r="E1208" s="12" t="s">
         <v>21</v>
@@ -62443,10 +62531,10 @@
         <v>22</v>
       </c>
       <c r="G1208" s="57">
-        <v>39669</v>
+        <v>4576</v>
       </c>
       <c r="H1208" s="15">
-        <v>53385</v>
+        <v>55234</v>
       </c>
       <c r="I1208" s="22" t="s">
         <v>563</v>
@@ -62463,7 +62551,7 @@
       <c r="O1208" s="18"/>
       <c r="P1208" s="18"/>
       <c r="Q1208" s="15">
-        <v>71713093</v>
+        <v>502405112</v>
       </c>
       <c r="R1208" s="22" t="s">
         <v>131</v>
@@ -62477,10 +62565,10 @@
         <v>46244</v>
       </c>
       <c r="C1209" s="56" t="s">
-        <v>1856</v>
+        <v>1854</v>
       </c>
       <c r="D1209" s="56" t="s">
-        <v>1857</v>
+        <v>1855</v>
       </c>
       <c r="E1209" s="12" t="s">
         <v>21</v>
@@ -62489,7 +62577,7 @@
         <v>22</v>
       </c>
       <c r="G1209" s="57">
-        <v>23875</v>
+        <v>39669</v>
       </c>
       <c r="H1209" s="15">
         <v>53385</v>
@@ -62509,13 +62597,13 @@
       <c r="O1209" s="18"/>
       <c r="P1209" s="18"/>
       <c r="Q1209" s="15">
-        <v>96890683052</v>
+        <v>71713093</v>
       </c>
       <c r="R1209" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1210" spans="1:18" ht="27.6" thickBot="1">
+    <row r="1210" spans="1:18" ht="15" thickBot="1">
       <c r="A1210" s="2">
         <v>1209</v>
       </c>
@@ -62523,10 +62611,10 @@
         <v>46244</v>
       </c>
       <c r="C1210" s="56" t="s">
-        <v>1858</v>
+        <v>1856</v>
       </c>
       <c r="D1210" s="56" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="E1210" s="12" t="s">
         <v>21</v>
@@ -62535,10 +62623,10 @@
         <v>22</v>
       </c>
       <c r="G1210" s="57">
-        <v>31663</v>
+        <v>23875</v>
       </c>
       <c r="H1210" s="15">
-        <v>66670</v>
+        <v>53385</v>
       </c>
       <c r="I1210" s="22" t="s">
         <v>563</v>
@@ -62555,7 +62643,7 @@
       <c r="O1210" s="18"/>
       <c r="P1210" s="18"/>
       <c r="Q1210" s="15">
-        <v>96876789204</v>
+        <v>96890683052</v>
       </c>
       <c r="R1210" s="22" t="s">
         <v>131</v>
@@ -62569,10 +62657,10 @@
         <v>46244</v>
       </c>
       <c r="C1211" s="56" t="s">
-        <v>37</v>
+        <v>1858</v>
       </c>
       <c r="D1211" s="56" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="E1211" s="12" t="s">
         <v>21</v>
@@ -62581,10 +62669,10 @@
         <v>22</v>
       </c>
       <c r="G1211" s="57">
-        <v>56846</v>
+        <v>31663</v>
       </c>
       <c r="H1211" s="15">
-        <v>74554</v>
+        <v>66670</v>
       </c>
       <c r="I1211" s="22" t="s">
         <v>563</v>
@@ -62601,13 +62689,13 @@
       <c r="O1211" s="18"/>
       <c r="P1211" s="18"/>
       <c r="Q1211" s="15">
-        <v>971506743142</v>
+        <v>96876789204</v>
       </c>
       <c r="R1211" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1212" spans="1:18" ht="15" thickBot="1">
+    <row r="1212" spans="1:18" ht="27.6" thickBot="1">
       <c r="A1212" s="2">
         <v>1211</v>
       </c>
@@ -62615,10 +62703,10 @@
         <v>46244</v>
       </c>
       <c r="C1212" s="56" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="D1212" s="56" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="E1212" s="12" t="s">
         <v>21</v>
@@ -62627,10 +62715,10 @@
         <v>22</v>
       </c>
       <c r="G1212" s="57">
-        <v>43021</v>
+        <v>56846</v>
       </c>
       <c r="H1212" s="15">
-        <v>24348</v>
+        <v>74554</v>
       </c>
       <c r="I1212" s="22" t="s">
         <v>563</v>
@@ -62647,7 +62735,7 @@
       <c r="O1212" s="18"/>
       <c r="P1212" s="18"/>
       <c r="Q1212" s="15">
-        <v>96877058642</v>
+        <v>971506743142</v>
       </c>
       <c r="R1212" s="22" t="s">
         <v>131</v>
@@ -62661,10 +62749,10 @@
         <v>46244</v>
       </c>
       <c r="C1213" s="56" t="s">
-        <v>1862</v>
+        <v>56</v>
       </c>
       <c r="D1213" s="56" t="s">
-        <v>1863</v>
+        <v>1861</v>
       </c>
       <c r="E1213" s="12" t="s">
         <v>21</v>
@@ -62673,10 +62761,10 @@
         <v>22</v>
       </c>
       <c r="G1213" s="57">
-        <v>21267</v>
+        <v>43021</v>
       </c>
       <c r="H1213" s="15">
-        <v>38336</v>
+        <v>24348</v>
       </c>
       <c r="I1213" s="22" t="s">
         <v>563</v>
@@ -62689,13 +62777,11 @@
       </c>
       <c r="L1213" s="18"/>
       <c r="M1213" s="18"/>
-      <c r="N1213" s="55">
-        <v>322</v>
-      </c>
+      <c r="N1213" s="40"/>
       <c r="O1213" s="18"/>
       <c r="P1213" s="18"/>
       <c r="Q1213" s="15">
-        <v>525399766</v>
+        <v>96877058642</v>
       </c>
       <c r="R1213" s="22" t="s">
         <v>131</v>
@@ -62708,29 +62794,43 @@
       <c r="B1214" s="10">
         <v>46244</v>
       </c>
-      <c r="C1214" s="38"/>
-      <c r="D1214" s="38"/>
-      <c r="E1214" s="18"/>
+      <c r="C1214" s="56" t="s">
+        <v>1862</v>
+      </c>
+      <c r="D1214" s="56" t="s">
+        <v>1863</v>
+      </c>
+      <c r="E1214" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="F1214" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1214" s="57">
-        <v>24960</v>
-      </c>
-      <c r="H1214" s="18"/>
+        <v>21267</v>
+      </c>
+      <c r="H1214" s="15">
+        <v>38336</v>
+      </c>
       <c r="I1214" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1214" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1214" s="18"/>
+      <c r="K1214" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1214" s="18"/>
       <c r="M1214" s="18"/>
-      <c r="N1214" s="40"/>
+      <c r="N1214" s="55">
+        <v>322</v>
+      </c>
       <c r="O1214" s="18"/>
       <c r="P1214" s="18"/>
-      <c r="Q1214" s="18"/>
+      <c r="Q1214" s="15">
+        <v>525399766</v>
+      </c>
       <c r="R1214" s="22" t="s">
         <v>131</v>
       </c>
@@ -62742,41 +62842,29 @@
       <c r="B1215" s="10">
         <v>46244</v>
       </c>
-      <c r="C1215" s="56" t="s">
-        <v>1137</v>
-      </c>
-      <c r="D1215" s="56" t="s">
-        <v>1864</v>
-      </c>
-      <c r="E1215" s="12" t="s">
-        <v>21</v>
-      </c>
+      <c r="C1215" s="38"/>
+      <c r="D1215" s="38"/>
+      <c r="E1215" s="18"/>
       <c r="F1215" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1215" s="57">
-        <v>36008</v>
-      </c>
-      <c r="H1215" s="15">
-        <v>9102</v>
-      </c>
+        <v>24960</v>
+      </c>
+      <c r="H1215" s="18"/>
       <c r="I1215" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1215" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1215" s="17" t="s">
-        <v>12</v>
-      </c>
+      <c r="K1215" s="18"/>
       <c r="L1215" s="18"/>
       <c r="M1215" s="18"/>
       <c r="N1215" s="40"/>
       <c r="O1215" s="18"/>
       <c r="P1215" s="18"/>
-      <c r="Q1215" s="15">
-        <v>94789315</v>
-      </c>
+      <c r="Q1215" s="18"/>
       <c r="R1215" s="22" t="s">
         <v>131</v>
       </c>
@@ -62789,22 +62877,22 @@
         <v>46244</v>
       </c>
       <c r="C1216" s="56" t="s">
-        <v>1865</v>
-      </c>
-      <c r="D1216" s="56">
-        <v>138838184</v>
+        <v>1137</v>
+      </c>
+      <c r="D1216" s="56" t="s">
+        <v>1864</v>
       </c>
       <c r="E1216" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1216" s="16" t="s">
-        <v>122</v>
+      <c r="F1216" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1216" s="57">
-        <v>2233</v>
+        <v>36008</v>
       </c>
       <c r="H1216" s="15">
-        <v>198</v>
+        <v>9102</v>
       </c>
       <c r="I1216" s="22" t="s">
         <v>563</v>
@@ -62821,7 +62909,7 @@
       <c r="O1216" s="18"/>
       <c r="P1216" s="18"/>
       <c r="Q1216" s="15">
-        <v>76249681</v>
+        <v>94789315</v>
       </c>
       <c r="R1216" s="22" t="s">
         <v>131</v>
@@ -62834,29 +62922,41 @@
       <c r="B1217" s="10">
         <v>46244</v>
       </c>
-      <c r="C1217" s="38"/>
-      <c r="D1217" s="38"/>
-      <c r="E1217" s="18"/>
+      <c r="C1217" s="56" t="s">
+        <v>1865</v>
+      </c>
+      <c r="D1217" s="56">
+        <v>138838184</v>
+      </c>
+      <c r="E1217" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="F1217" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1217" s="57">
-        <v>4202</v>
-      </c>
-      <c r="H1217" s="18"/>
+        <v>2233</v>
+      </c>
+      <c r="H1217" s="15">
+        <v>198</v>
+      </c>
       <c r="I1217" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1217" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1217" s="18"/>
+      <c r="K1217" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1217" s="18"/>
       <c r="M1217" s="18"/>
       <c r="N1217" s="40"/>
       <c r="O1217" s="18"/>
       <c r="P1217" s="18"/>
-      <c r="Q1217" s="18"/>
+      <c r="Q1217" s="15">
+        <v>76249681</v>
+      </c>
       <c r="R1217" s="22" t="s">
         <v>131</v>
       </c>
@@ -62868,41 +62968,29 @@
       <c r="B1218" s="10">
         <v>46244</v>
       </c>
-      <c r="C1218" s="56" t="s">
-        <v>1866</v>
-      </c>
-      <c r="D1218" s="56">
-        <v>95388683</v>
-      </c>
-      <c r="E1218" s="12" t="s">
-        <v>21</v>
-      </c>
+      <c r="C1218" s="38"/>
+      <c r="D1218" s="38"/>
+      <c r="E1218" s="18"/>
       <c r="F1218" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1218" s="57">
-        <v>5961</v>
-      </c>
-      <c r="H1218" s="15">
-        <v>9283</v>
-      </c>
+        <v>4202</v>
+      </c>
+      <c r="H1218" s="18"/>
       <c r="I1218" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1218" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1218" s="17" t="s">
-        <v>12</v>
-      </c>
+      <c r="K1218" s="18"/>
       <c r="L1218" s="18"/>
       <c r="M1218" s="18"/>
       <c r="N1218" s="40"/>
       <c r="O1218" s="18"/>
       <c r="P1218" s="18"/>
-      <c r="Q1218" s="15">
-        <v>71025778</v>
-      </c>
+      <c r="Q1218" s="18"/>
       <c r="R1218" s="22" t="s">
         <v>131</v>
       </c>
@@ -62915,10 +63003,10 @@
         <v>46244</v>
       </c>
       <c r="C1219" s="56" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="D1219" s="56">
-        <v>78746152</v>
+        <v>95388683</v>
       </c>
       <c r="E1219" s="12" t="s">
         <v>21</v>
@@ -62927,10 +63015,10 @@
         <v>122</v>
       </c>
       <c r="G1219" s="57">
-        <v>1834</v>
+        <v>5961</v>
       </c>
       <c r="H1219" s="15">
-        <v>3623</v>
+        <v>9283</v>
       </c>
       <c r="I1219" s="22" t="s">
         <v>563</v>
@@ -62947,7 +63035,7 @@
       <c r="O1219" s="18"/>
       <c r="P1219" s="18"/>
       <c r="Q1219" s="15">
-        <v>96895952892</v>
+        <v>71025778</v>
       </c>
       <c r="R1219" s="22" t="s">
         <v>131</v>
@@ -62960,31 +63048,41 @@
       <c r="B1220" s="10">
         <v>46244</v>
       </c>
-      <c r="C1220" s="38"/>
-      <c r="D1220" s="38"/>
-      <c r="E1220" s="18"/>
+      <c r="C1220" s="56" t="s">
+        <v>1867</v>
+      </c>
+      <c r="D1220" s="56">
+        <v>78746152</v>
+      </c>
+      <c r="E1220" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="F1220" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1220" s="57">
-        <v>249</v>
-      </c>
-      <c r="H1220" s="18"/>
+        <v>1834</v>
+      </c>
+      <c r="H1220" s="15">
+        <v>3623</v>
+      </c>
       <c r="I1220" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1220" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1220" s="30" t="s">
-        <v>1596</v>
+      <c r="K1220" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1220" s="18"/>
       <c r="M1220" s="18"/>
       <c r="N1220" s="40"/>
       <c r="O1220" s="18"/>
       <c r="P1220" s="18"/>
-      <c r="Q1220" s="18"/>
+      <c r="Q1220" s="15">
+        <v>96895952892</v>
+      </c>
       <c r="R1220" s="22" t="s">
         <v>131</v>
       </c>
@@ -62996,41 +63094,31 @@
       <c r="B1221" s="10">
         <v>46244</v>
       </c>
-      <c r="C1221" s="56" t="s">
-        <v>1542</v>
-      </c>
-      <c r="D1221" s="56">
-        <v>119318055</v>
-      </c>
-      <c r="E1221" s="12" t="s">
-        <v>21</v>
-      </c>
+      <c r="C1221" s="38"/>
+      <c r="D1221" s="38"/>
+      <c r="E1221" s="18"/>
       <c r="F1221" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1221" s="57">
-        <v>3638</v>
-      </c>
-      <c r="H1221" s="15">
-        <v>4122</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="H1221" s="18"/>
       <c r="I1221" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1221" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1221" s="17" t="s">
-        <v>12</v>
+      <c r="K1221" s="30" t="s">
+        <v>1596</v>
       </c>
       <c r="L1221" s="18"/>
       <c r="M1221" s="18"/>
       <c r="N1221" s="40"/>
       <c r="O1221" s="18"/>
       <c r="P1221" s="18"/>
-      <c r="Q1221" s="15">
-        <v>78528125</v>
-      </c>
+      <c r="Q1221" s="18"/>
       <c r="R1221" s="22" t="s">
         <v>131</v>
       </c>
@@ -63043,10 +63131,10 @@
         <v>46244</v>
       </c>
       <c r="C1222" s="56" t="s">
-        <v>1868</v>
+        <v>1542</v>
       </c>
       <c r="D1222" s="56">
-        <v>91086972</v>
+        <v>119318055</v>
       </c>
       <c r="E1222" s="12" t="s">
         <v>21</v>
@@ -63055,10 +63143,10 @@
         <v>122</v>
       </c>
       <c r="G1222" s="57">
-        <v>1856</v>
+        <v>3638</v>
       </c>
       <c r="H1222" s="15">
-        <v>9607</v>
+        <v>4122</v>
       </c>
       <c r="I1222" s="22" t="s">
         <v>563</v>
@@ -63075,7 +63163,7 @@
       <c r="O1222" s="18"/>
       <c r="P1222" s="18"/>
       <c r="Q1222" s="15">
-        <v>95918065</v>
+        <v>78528125</v>
       </c>
       <c r="R1222" s="22" t="s">
         <v>131</v>
@@ -63089,10 +63177,10 @@
         <v>46244</v>
       </c>
       <c r="C1223" s="56" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="D1223" s="56">
-        <v>121149924</v>
+        <v>91086972</v>
       </c>
       <c r="E1223" s="12" t="s">
         <v>21</v>
@@ -63101,10 +63189,10 @@
         <v>122</v>
       </c>
       <c r="G1223" s="57">
-        <v>3785</v>
+        <v>1856</v>
       </c>
       <c r="H1223" s="15">
-        <v>9062</v>
+        <v>9607</v>
       </c>
       <c r="I1223" s="22" t="s">
         <v>563</v>
@@ -63121,7 +63209,7 @@
       <c r="O1223" s="18"/>
       <c r="P1223" s="18"/>
       <c r="Q1223" s="15">
-        <v>95881870</v>
+        <v>95918065</v>
       </c>
       <c r="R1223" s="22" t="s">
         <v>131</v>
@@ -63135,10 +63223,10 @@
         <v>46244</v>
       </c>
       <c r="C1224" s="56" t="s">
-        <v>317</v>
+        <v>1869</v>
       </c>
       <c r="D1224" s="56">
-        <v>96363803</v>
+        <v>121149924</v>
       </c>
       <c r="E1224" s="12" t="s">
         <v>21</v>
@@ -63147,10 +63235,10 @@
         <v>122</v>
       </c>
       <c r="G1224" s="57">
-        <v>3367</v>
-      </c>
-      <c r="H1224" s="15" t="s">
-        <v>1870</v>
+        <v>3785</v>
+      </c>
+      <c r="H1224" s="15">
+        <v>9062</v>
       </c>
       <c r="I1224" s="22" t="s">
         <v>563</v>
@@ -63167,7 +63255,7 @@
       <c r="O1224" s="18"/>
       <c r="P1224" s="18"/>
       <c r="Q1224" s="15">
-        <v>96363803</v>
+        <v>95881870</v>
       </c>
       <c r="R1224" s="22" t="s">
         <v>131</v>
@@ -63181,22 +63269,22 @@
         <v>46244</v>
       </c>
       <c r="C1225" s="56" t="s">
-        <v>1871</v>
-      </c>
-      <c r="D1225" s="56" t="s">
-        <v>1872</v>
+        <v>317</v>
+      </c>
+      <c r="D1225" s="56">
+        <v>96363803</v>
       </c>
       <c r="E1225" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1225" s="13" t="s">
-        <v>22</v>
+      <c r="F1225" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1225" s="57">
-        <v>71968</v>
-      </c>
-      <c r="H1225" s="15">
-        <v>13188</v>
+        <v>3367</v>
+      </c>
+      <c r="H1225" s="15" t="s">
+        <v>1870</v>
       </c>
       <c r="I1225" s="22" t="s">
         <v>563</v>
@@ -63209,13 +63297,11 @@
       </c>
       <c r="L1225" s="18"/>
       <c r="M1225" s="18"/>
-      <c r="N1225" s="55">
-        <v>321</v>
-      </c>
+      <c r="N1225" s="40"/>
       <c r="O1225" s="18"/>
       <c r="P1225" s="18"/>
       <c r="Q1225" s="15">
-        <v>77245341</v>
+        <v>96363803</v>
       </c>
       <c r="R1225" s="22" t="s">
         <v>131</v>
@@ -63228,33 +63314,43 @@
       <c r="B1226" s="10">
         <v>46244</v>
       </c>
-      <c r="C1226" s="38"/>
-      <c r="D1226" s="38"/>
-      <c r="E1226" s="18"/>
-      <c r="F1226" s="16" t="s">
-        <v>122</v>
+      <c r="C1226" s="56" t="s">
+        <v>1871</v>
+      </c>
+      <c r="D1226" s="56" t="s">
+        <v>1872</v>
+      </c>
+      <c r="E1226" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1226" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1226" s="57">
-        <v>5195</v>
-      </c>
-      <c r="H1226" s="18"/>
+        <v>71968</v>
+      </c>
+      <c r="H1226" s="15">
+        <v>13188</v>
+      </c>
       <c r="I1226" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1226" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1226" s="30" t="s">
-        <v>1596</v>
+      <c r="K1226" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1226" s="18"/>
       <c r="M1226" s="18"/>
       <c r="N1226" s="55">
-        <v>358</v>
+        <v>321</v>
       </c>
       <c r="O1226" s="18"/>
       <c r="P1226" s="18"/>
-      <c r="Q1226" s="18"/>
+      <c r="Q1226" s="15">
+        <v>77245341</v>
+      </c>
       <c r="R1226" s="22" t="s">
         <v>131</v>
       </c>
@@ -63273,7 +63369,7 @@
         <v>122</v>
       </c>
       <c r="G1227" s="57">
-        <v>7347</v>
+        <v>5195</v>
       </c>
       <c r="H1227" s="18"/>
       <c r="I1227" s="22" t="s">
@@ -63287,7 +63383,9 @@
       </c>
       <c r="L1227" s="18"/>
       <c r="M1227" s="18"/>
-      <c r="N1227" s="40"/>
+      <c r="N1227" s="55">
+        <v>358</v>
+      </c>
       <c r="O1227" s="18"/>
       <c r="P1227" s="18"/>
       <c r="Q1227" s="18"/>
@@ -63302,41 +63400,31 @@
       <c r="B1228" s="10">
         <v>46244</v>
       </c>
-      <c r="C1228" s="56" t="s">
-        <v>1873</v>
-      </c>
-      <c r="D1228" s="56">
-        <v>101198406</v>
-      </c>
-      <c r="E1228" s="12" t="s">
-        <v>21</v>
-      </c>
+      <c r="C1228" s="38"/>
+      <c r="D1228" s="38"/>
+      <c r="E1228" s="18"/>
       <c r="F1228" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1228" s="57">
-        <v>6330</v>
-      </c>
-      <c r="H1228" s="15">
-        <v>7507</v>
-      </c>
+        <v>7347</v>
+      </c>
+      <c r="H1228" s="18"/>
       <c r="I1228" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1228" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1228" s="17" t="s">
-        <v>12</v>
+      <c r="K1228" s="30" t="s">
+        <v>1596</v>
       </c>
       <c r="L1228" s="18"/>
       <c r="M1228" s="18"/>
       <c r="N1228" s="40"/>
       <c r="O1228" s="18"/>
       <c r="P1228" s="18"/>
-      <c r="Q1228" s="15">
-        <v>96709596</v>
-      </c>
+      <c r="Q1228" s="18"/>
       <c r="R1228" s="22" t="s">
         <v>131</v>
       </c>
@@ -63348,31 +63436,41 @@
       <c r="B1229" s="10">
         <v>46244</v>
       </c>
-      <c r="C1229" s="38"/>
-      <c r="D1229" s="38"/>
-      <c r="E1229" s="18"/>
-      <c r="F1229" s="13" t="s">
-        <v>22</v>
+      <c r="C1229" s="56" t="s">
+        <v>1873</v>
+      </c>
+      <c r="D1229" s="56">
+        <v>101198406</v>
+      </c>
+      <c r="E1229" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1229" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1229" s="57">
-        <v>35455</v>
-      </c>
-      <c r="H1229" s="18"/>
+        <v>6330</v>
+      </c>
+      <c r="H1229" s="15">
+        <v>7507</v>
+      </c>
       <c r="I1229" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1229" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1229" s="30" t="s">
-        <v>1596</v>
+      <c r="K1229" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1229" s="18"/>
       <c r="M1229" s="18"/>
       <c r="N1229" s="40"/>
       <c r="O1229" s="18"/>
       <c r="P1229" s="18"/>
-      <c r="Q1229" s="18"/>
+      <c r="Q1229" s="15">
+        <v>96709596</v>
+      </c>
       <c r="R1229" s="22" t="s">
         <v>131</v>
       </c>
@@ -63391,7 +63489,7 @@
         <v>22</v>
       </c>
       <c r="G1230" s="57">
-        <v>72129</v>
+        <v>35455</v>
       </c>
       <c r="H1230" s="18"/>
       <c r="I1230" s="22" t="s">
@@ -63420,41 +63518,31 @@
       <c r="B1231" s="10">
         <v>46244</v>
       </c>
-      <c r="C1231" s="56" t="s">
-        <v>432</v>
-      </c>
-      <c r="D1231" s="56">
-        <v>94734526</v>
-      </c>
-      <c r="E1231" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1231" s="16" t="s">
-        <v>122</v>
+      <c r="C1231" s="38"/>
+      <c r="D1231" s="38"/>
+      <c r="E1231" s="18"/>
+      <c r="F1231" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1231" s="57">
-        <v>2535</v>
-      </c>
-      <c r="H1231" s="15">
-        <v>4261</v>
-      </c>
+        <v>72129</v>
+      </c>
+      <c r="H1231" s="18"/>
       <c r="I1231" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1231" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1231" s="17" t="s">
-        <v>12</v>
+      <c r="K1231" s="30" t="s">
+        <v>1596</v>
       </c>
       <c r="L1231" s="18"/>
       <c r="M1231" s="18"/>
       <c r="N1231" s="40"/>
       <c r="O1231" s="18"/>
       <c r="P1231" s="18"/>
-      <c r="Q1231" s="15">
-        <v>77454348</v>
-      </c>
+      <c r="Q1231" s="18"/>
       <c r="R1231" s="22" t="s">
         <v>131</v>
       </c>
@@ -63467,10 +63555,10 @@
         <v>46244</v>
       </c>
       <c r="C1232" s="56" t="s">
-        <v>1883</v>
+        <v>432</v>
       </c>
       <c r="D1232" s="56">
-        <v>116911156</v>
+        <v>94734526</v>
       </c>
       <c r="E1232" s="12" t="s">
         <v>21</v>
@@ -63479,10 +63567,10 @@
         <v>122</v>
       </c>
       <c r="G1232" s="57">
-        <v>4479</v>
+        <v>2535</v>
       </c>
       <c r="H1232" s="15">
-        <v>3757</v>
+        <v>4261</v>
       </c>
       <c r="I1232" s="22" t="s">
         <v>563</v>
@@ -63499,7 +63587,7 @@
       <c r="O1232" s="18"/>
       <c r="P1232" s="18"/>
       <c r="Q1232" s="15">
-        <v>96894139420</v>
+        <v>77454348</v>
       </c>
       <c r="R1232" s="22" t="s">
         <v>131</v>
@@ -63513,10 +63601,10 @@
         <v>46244</v>
       </c>
       <c r="C1233" s="56" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="D1233" s="56">
-        <v>85817633</v>
+        <v>116911156</v>
       </c>
       <c r="E1233" s="12" t="s">
         <v>21</v>
@@ -63525,16 +63613,16 @@
         <v>122</v>
       </c>
       <c r="G1233" s="57">
-        <v>9082</v>
+        <v>4479</v>
       </c>
       <c r="H1233" s="15">
-        <v>3546</v>
+        <v>3757</v>
       </c>
       <c r="I1233" s="22" t="s">
         <v>563</v>
       </c>
-      <c r="J1233" s="15" t="s">
-        <v>1672</v>
+      <c r="J1233" s="51" t="s">
+        <v>564</v>
       </c>
       <c r="K1233" s="17" t="s">
         <v>12</v>
@@ -63544,7 +63632,9 @@
       <c r="N1233" s="40"/>
       <c r="O1233" s="18"/>
       <c r="P1233" s="18"/>
-      <c r="Q1233" s="18"/>
+      <c r="Q1233" s="15">
+        <v>96894139420</v>
+      </c>
       <c r="R1233" s="22" t="s">
         <v>131</v>
       </c>
@@ -63557,22 +63647,22 @@
         <v>46244</v>
       </c>
       <c r="C1234" s="56" t="s">
-        <v>1885</v>
-      </c>
-      <c r="D1234" s="56" t="s">
-        <v>1886</v>
+        <v>1884</v>
+      </c>
+      <c r="D1234" s="56">
+        <v>85817633</v>
       </c>
       <c r="E1234" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1234" s="13" t="s">
-        <v>22</v>
+      <c r="F1234" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1234" s="57">
-        <v>81144</v>
+        <v>9082</v>
       </c>
       <c r="H1234" s="15">
-        <v>55344</v>
+        <v>3546</v>
       </c>
       <c r="I1234" s="22" t="s">
         <v>563</v>
@@ -63601,40 +63691,38 @@
         <v>46244</v>
       </c>
       <c r="C1235" s="56" t="s">
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="D1235" s="56" t="s">
-        <v>1888</v>
-      </c>
-      <c r="E1235" s="35" t="s">
-        <v>120</v>
+        <v>1886</v>
+      </c>
+      <c r="E1235" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="F1235" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1235" s="57">
-        <v>15562</v>
+        <v>81144</v>
       </c>
       <c r="H1235" s="15">
-        <v>74553</v>
-      </c>
-      <c r="I1235" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1235" s="52" t="s">
-        <v>776</v>
-      </c>
-      <c r="K1235" s="61" t="s">
-        <v>1189</v>
+        <v>55344</v>
+      </c>
+      <c r="I1235" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1235" s="15" t="s">
+        <v>1672</v>
+      </c>
+      <c r="K1235" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1235" s="18"/>
       <c r="M1235" s="18"/>
       <c r="N1235" s="40"/>
       <c r="O1235" s="18"/>
       <c r="P1235" s="18"/>
-      <c r="Q1235" s="15">
-        <v>566209290</v>
-      </c>
+      <c r="Q1235" s="18"/>
       <c r="R1235" s="22" t="s">
         <v>131</v>
       </c>
@@ -63647,22 +63735,22 @@
         <v>46244</v>
       </c>
       <c r="C1236" s="56" t="s">
-        <v>1889</v>
-      </c>
-      <c r="D1236" s="56">
-        <v>107948231</v>
-      </c>
-      <c r="E1236" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1236" s="16" t="s">
-        <v>122</v>
+        <v>1887</v>
+      </c>
+      <c r="D1236" s="56" t="s">
+        <v>1888</v>
+      </c>
+      <c r="E1236" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1236" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1236" s="57">
-        <v>1602</v>
+        <v>15562</v>
       </c>
       <c r="H1236" s="15">
-        <v>1099</v>
+        <v>74553</v>
       </c>
       <c r="I1236" s="16" t="s">
         <v>10</v>
@@ -63679,7 +63767,7 @@
       <c r="O1236" s="18"/>
       <c r="P1236" s="18"/>
       <c r="Q1236" s="15">
-        <v>96892448478</v>
+        <v>566209290</v>
       </c>
       <c r="R1236" s="22" t="s">
         <v>131</v>
@@ -63693,10 +63781,10 @@
         <v>46244</v>
       </c>
       <c r="C1237" s="56" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="D1237" s="56">
-        <v>76217672</v>
+        <v>107948231</v>
       </c>
       <c r="E1237" s="12" t="s">
         <v>21</v>
@@ -63705,10 +63793,10 @@
         <v>122</v>
       </c>
       <c r="G1237" s="57">
-        <v>4465</v>
+        <v>1602</v>
       </c>
       <c r="H1237" s="15">
-        <v>8001</v>
+        <v>1099</v>
       </c>
       <c r="I1237" s="16" t="s">
         <v>10</v>
@@ -63725,7 +63813,7 @@
       <c r="O1237" s="18"/>
       <c r="P1237" s="18"/>
       <c r="Q1237" s="15">
-        <v>93317831</v>
+        <v>96892448478</v>
       </c>
       <c r="R1237" s="22" t="s">
         <v>131</v>
@@ -63739,10 +63827,10 @@
         <v>46244</v>
       </c>
       <c r="C1238" s="56" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="D1238" s="56">
-        <v>113802138</v>
+        <v>76217672</v>
       </c>
       <c r="E1238" s="12" t="s">
         <v>21</v>
@@ -63751,10 +63839,10 @@
         <v>122</v>
       </c>
       <c r="G1238" s="57">
-        <v>1777</v>
+        <v>4465</v>
       </c>
       <c r="H1238" s="15">
-        <v>9472</v>
+        <v>8001</v>
       </c>
       <c r="I1238" s="16" t="s">
         <v>10</v>
@@ -63770,7 +63858,9 @@
       <c r="N1238" s="40"/>
       <c r="O1238" s="18"/>
       <c r="P1238" s="18"/>
-      <c r="Q1238" s="18"/>
+      <c r="Q1238" s="15">
+        <v>93317831</v>
+      </c>
       <c r="R1238" s="22" t="s">
         <v>131</v>
       </c>
@@ -63783,10 +63873,10 @@
         <v>46244</v>
       </c>
       <c r="C1239" s="56" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="D1239" s="56">
-        <v>77396496</v>
+        <v>113802138</v>
       </c>
       <c r="E1239" s="12" t="s">
         <v>21</v>
@@ -63795,10 +63885,10 @@
         <v>122</v>
       </c>
       <c r="G1239" s="57">
-        <v>3536</v>
+        <v>1777</v>
       </c>
       <c r="H1239" s="15">
-        <v>9212</v>
+        <v>9472</v>
       </c>
       <c r="I1239" s="16" t="s">
         <v>10</v>
@@ -63806,8 +63896,8 @@
       <c r="J1239" s="52" t="s">
         <v>776</v>
       </c>
-      <c r="K1239" s="17" t="s">
-        <v>12</v>
+      <c r="K1239" s="61" t="s">
+        <v>1189</v>
       </c>
       <c r="L1239" s="18"/>
       <c r="M1239" s="18"/>
@@ -63819,7 +63909,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1240" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1240" spans="1:18" ht="15" thickBot="1">
       <c r="A1240" s="2">
         <v>1239</v>
       </c>
@@ -63827,10 +63917,10 @@
         <v>46244</v>
       </c>
       <c r="C1240" s="56" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="D1240" s="56">
-        <v>131422754</v>
+        <v>77396496</v>
       </c>
       <c r="E1240" s="12" t="s">
         <v>21</v>
@@ -63839,16 +63929,16 @@
         <v>122</v>
       </c>
       <c r="G1240" s="57">
-        <v>3097</v>
+        <v>3536</v>
       </c>
       <c r="H1240" s="15">
-        <v>3993</v>
-      </c>
-      <c r="I1240" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="J1240" s="15" t="s">
-        <v>174</v>
+        <v>9212</v>
+      </c>
+      <c r="I1240" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1240" s="52" t="s">
+        <v>776</v>
       </c>
       <c r="K1240" s="17" t="s">
         <v>12</v>
@@ -63858,9 +63948,7 @@
       <c r="N1240" s="40"/>
       <c r="O1240" s="18"/>
       <c r="P1240" s="18"/>
-      <c r="Q1240" s="15">
-        <v>78615034</v>
-      </c>
+      <c r="Q1240" s="18"/>
       <c r="R1240" s="22" t="s">
         <v>131</v>
       </c>
@@ -63873,10 +63961,10 @@
         <v>46244</v>
       </c>
       <c r="C1241" s="56" t="s">
-        <v>1912</v>
+        <v>1893</v>
       </c>
       <c r="D1241" s="56">
-        <v>109499244</v>
+        <v>131422754</v>
       </c>
       <c r="E1241" s="12" t="s">
         <v>21</v>
@@ -63885,16 +63973,16 @@
         <v>122</v>
       </c>
       <c r="G1241" s="57">
-        <v>6018</v>
+        <v>3097</v>
       </c>
       <c r="H1241" s="15">
-        <v>8793</v>
+        <v>3993</v>
       </c>
       <c r="I1241" s="15" t="s">
         <v>123</v>
       </c>
       <c r="J1241" s="15" t="s">
-        <v>1913</v>
+        <v>174</v>
       </c>
       <c r="K1241" s="17" t="s">
         <v>12</v>
@@ -63905,7 +63993,7 @@
       <c r="O1241" s="18"/>
       <c r="P1241" s="18"/>
       <c r="Q1241" s="15">
-        <v>78735597</v>
+        <v>78615034</v>
       </c>
       <c r="R1241" s="22" t="s">
         <v>131</v>
@@ -63919,10 +64007,10 @@
         <v>46244</v>
       </c>
       <c r="C1242" s="56" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="D1242" s="56">
-        <v>110877972</v>
+        <v>109499244</v>
       </c>
       <c r="E1242" s="12" t="s">
         <v>21</v>
@@ -63931,10 +64019,10 @@
         <v>122</v>
       </c>
       <c r="G1242" s="57">
-        <v>5734</v>
+        <v>6018</v>
       </c>
       <c r="H1242" s="15">
-        <v>235</v>
+        <v>8793</v>
       </c>
       <c r="I1242" s="15" t="s">
         <v>123</v>
@@ -63951,7 +64039,7 @@
       <c r="O1242" s="18"/>
       <c r="P1242" s="18"/>
       <c r="Q1242" s="15">
-        <v>79031527</v>
+        <v>78735597</v>
       </c>
       <c r="R1242" s="22" t="s">
         <v>131</v>
@@ -63965,10 +64053,10 @@
         <v>46244</v>
       </c>
       <c r="C1243" s="56" t="s">
-        <v>1149</v>
+        <v>1914</v>
       </c>
       <c r="D1243" s="56">
-        <v>124842182</v>
+        <v>110877972</v>
       </c>
       <c r="E1243" s="12" t="s">
         <v>21</v>
@@ -63977,10 +64065,10 @@
         <v>122</v>
       </c>
       <c r="G1243" s="57">
-        <v>9340</v>
-      </c>
-      <c r="H1243" s="15" t="s">
-        <v>1915</v>
+        <v>5734</v>
+      </c>
+      <c r="H1243" s="15">
+        <v>235</v>
       </c>
       <c r="I1243" s="15" t="s">
         <v>123</v>
@@ -63997,7 +64085,7 @@
       <c r="O1243" s="18"/>
       <c r="P1243" s="18"/>
       <c r="Q1243" s="15">
-        <v>98172901</v>
+        <v>79031527</v>
       </c>
       <c r="R1243" s="22" t="s">
         <v>131</v>
@@ -64011,22 +64099,22 @@
         <v>46244</v>
       </c>
       <c r="C1244" s="56" t="s">
-        <v>1916</v>
-      </c>
-      <c r="D1244" s="56" t="s">
-        <v>1917</v>
+        <v>1149</v>
+      </c>
+      <c r="D1244" s="56">
+        <v>124842182</v>
       </c>
       <c r="E1244" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1244" s="13" t="s">
-        <v>22</v>
+      <c r="F1244" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1244" s="57">
-        <v>16853</v>
-      </c>
-      <c r="H1244" s="15">
-        <v>76548</v>
+        <v>9340</v>
+      </c>
+      <c r="H1244" s="15" t="s">
+        <v>1915</v>
       </c>
       <c r="I1244" s="15" t="s">
         <v>123</v>
@@ -64043,7 +64131,7 @@
       <c r="O1244" s="18"/>
       <c r="P1244" s="18"/>
       <c r="Q1244" s="15">
-        <v>95596076</v>
+        <v>98172901</v>
       </c>
       <c r="R1244" s="22" t="s">
         <v>131</v>
@@ -64057,10 +64145,10 @@
         <v>46244</v>
       </c>
       <c r="C1245" s="56" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="D1245" s="56" t="s">
-        <v>1919</v>
+        <v>1917</v>
       </c>
       <c r="E1245" s="12" t="s">
         <v>21</v>
@@ -64069,10 +64157,10 @@
         <v>22</v>
       </c>
       <c r="G1245" s="57">
-        <v>55729</v>
+        <v>16853</v>
       </c>
       <c r="H1245" s="15">
-        <v>21874</v>
+        <v>76548</v>
       </c>
       <c r="I1245" s="15" t="s">
         <v>123</v>
@@ -64089,7 +64177,7 @@
       <c r="O1245" s="18"/>
       <c r="P1245" s="18"/>
       <c r="Q1245" s="15">
-        <v>77821958</v>
+        <v>95596076</v>
       </c>
       <c r="R1245" s="22" t="s">
         <v>131</v>
@@ -64103,10 +64191,10 @@
         <v>46244</v>
       </c>
       <c r="C1246" s="56" t="s">
-        <v>1920</v>
+        <v>1918</v>
       </c>
       <c r="D1246" s="56" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="E1246" s="12" t="s">
         <v>21</v>
@@ -64115,10 +64203,10 @@
         <v>22</v>
       </c>
       <c r="G1246" s="57">
-        <v>24788</v>
+        <v>55729</v>
       </c>
       <c r="H1246" s="15">
-        <v>81726</v>
+        <v>21874</v>
       </c>
       <c r="I1246" s="15" t="s">
         <v>123</v>
@@ -64135,7 +64223,7 @@
       <c r="O1246" s="18"/>
       <c r="P1246" s="18"/>
       <c r="Q1246" s="15">
-        <v>555524049</v>
+        <v>77821958</v>
       </c>
       <c r="R1246" s="22" t="s">
         <v>131</v>
@@ -64149,28 +64237,28 @@
         <v>46244</v>
       </c>
       <c r="C1247" s="56" t="s">
-        <v>1922</v>
-      </c>
-      <c r="D1247" s="56">
-        <v>133589295</v>
+        <v>1920</v>
+      </c>
+      <c r="D1247" s="56" t="s">
+        <v>1921</v>
       </c>
       <c r="E1247" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1247" s="16" t="s">
-        <v>122</v>
+      <c r="F1247" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1247" s="57">
-        <v>4317</v>
+        <v>24788</v>
       </c>
       <c r="H1247" s="15">
-        <v>9901</v>
+        <v>81726</v>
       </c>
       <c r="I1247" s="15" t="s">
         <v>123</v>
       </c>
       <c r="J1247" s="15" t="s">
-        <v>174</v>
+        <v>1913</v>
       </c>
       <c r="K1247" s="17" t="s">
         <v>12</v>
@@ -64180,8 +64268,8 @@
       <c r="N1247" s="40"/>
       <c r="O1247" s="18"/>
       <c r="P1247" s="18"/>
-      <c r="Q1247" s="11">
-        <v>96877336001</v>
+      <c r="Q1247" s="15">
+        <v>555524049</v>
       </c>
       <c r="R1247" s="22" t="s">
         <v>131</v>
@@ -64195,10 +64283,10 @@
         <v>46244</v>
       </c>
       <c r="C1248" s="56" t="s">
-        <v>771</v>
+        <v>1922</v>
       </c>
       <c r="D1248" s="56">
-        <v>121398708</v>
+        <v>133589295</v>
       </c>
       <c r="E1248" s="12" t="s">
         <v>21</v>
@@ -64207,10 +64295,10 @@
         <v>122</v>
       </c>
       <c r="G1248" s="57">
-        <v>9244</v>
+        <v>4317</v>
       </c>
       <c r="H1248" s="15">
-        <v>9611</v>
+        <v>9901</v>
       </c>
       <c r="I1248" s="15" t="s">
         <v>123</v>
@@ -64227,7 +64315,7 @@
       <c r="O1248" s="18"/>
       <c r="P1248" s="18"/>
       <c r="Q1248" s="11">
-        <v>71382892</v>
+        <v>96877336001</v>
       </c>
       <c r="R1248" s="22" t="s">
         <v>131</v>
@@ -64241,10 +64329,10 @@
         <v>46244</v>
       </c>
       <c r="C1249" s="56" t="s">
-        <v>1930</v>
+        <v>771</v>
       </c>
       <c r="D1249" s="56">
-        <v>123092622</v>
+        <v>121398708</v>
       </c>
       <c r="E1249" s="12" t="s">
         <v>21</v>
@@ -64253,10 +64341,10 @@
         <v>122</v>
       </c>
       <c r="G1249" s="57">
-        <v>8269</v>
+        <v>9244</v>
       </c>
       <c r="H1249" s="15">
-        <v>8963</v>
+        <v>9611</v>
       </c>
       <c r="I1249" s="15" t="s">
         <v>123</v>
@@ -64273,7 +64361,7 @@
       <c r="O1249" s="18"/>
       <c r="P1249" s="18"/>
       <c r="Q1249" s="11">
-        <v>98560324</v>
+        <v>71382892</v>
       </c>
       <c r="R1249" s="22" t="s">
         <v>131</v>
@@ -64287,10 +64375,10 @@
         <v>46244</v>
       </c>
       <c r="C1250" s="56" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="D1250" s="56">
-        <v>136802631</v>
+        <v>123092622</v>
       </c>
       <c r="E1250" s="12" t="s">
         <v>21</v>
@@ -64299,27 +64387,27 @@
         <v>122</v>
       </c>
       <c r="G1250" s="57">
-        <v>1474</v>
+        <v>8269</v>
       </c>
       <c r="H1250" s="15">
-        <v>3475</v>
+        <v>8963</v>
       </c>
       <c r="I1250" s="15" t="s">
         <v>123</v>
       </c>
       <c r="J1250" s="15" t="s">
-        <v>1913</v>
-      </c>
-      <c r="K1250" s="18"/>
-      <c r="L1250" s="15">
-        <v>94317092</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="K1250" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1250" s="18"/>
       <c r="M1250" s="18"/>
       <c r="N1250" s="40"/>
       <c r="O1250" s="18"/>
       <c r="P1250" s="18"/>
-      <c r="Q1250" s="15">
-        <v>94317092</v>
+      <c r="Q1250" s="11">
+        <v>98560324</v>
       </c>
       <c r="R1250" s="22" t="s">
         <v>131</v>
@@ -64333,10 +64421,10 @@
         <v>46244</v>
       </c>
       <c r="C1251" s="56" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="D1251" s="56">
-        <v>136393574</v>
+        <v>136802631</v>
       </c>
       <c r="E1251" s="12" t="s">
         <v>21</v>
@@ -64345,10 +64433,10 @@
         <v>122</v>
       </c>
       <c r="G1251" s="57">
-        <v>8580</v>
-      </c>
-      <c r="H1251" s="15" t="s">
-        <v>1933</v>
+        <v>1474</v>
+      </c>
+      <c r="H1251" s="15">
+        <v>3475</v>
       </c>
       <c r="I1251" s="15" t="s">
         <v>123</v>
@@ -64356,16 +64444,16 @@
       <c r="J1251" s="15" t="s">
         <v>1913</v>
       </c>
-      <c r="K1251" s="18"/>
-      <c r="L1251" s="15">
-        <v>94526230</v>
-      </c>
+      <c r="K1251" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1251" s="18"/>
       <c r="M1251" s="18"/>
       <c r="N1251" s="40"/>
       <c r="O1251" s="18"/>
       <c r="P1251" s="18"/>
       <c r="Q1251" s="15">
-        <v>94526230</v>
+        <v>94317092</v>
       </c>
       <c r="R1251" s="22" t="s">
         <v>131</v>
@@ -64379,10 +64467,10 @@
         <v>46244</v>
       </c>
       <c r="C1252" s="56" t="s">
-        <v>1934</v>
+        <v>1932</v>
       </c>
       <c r="D1252" s="56">
-        <v>101540233</v>
+        <v>136393574</v>
       </c>
       <c r="E1252" s="12" t="s">
         <v>21</v>
@@ -64391,10 +64479,10 @@
         <v>122</v>
       </c>
       <c r="G1252" s="57">
-        <v>5126</v>
+        <v>8580</v>
       </c>
       <c r="H1252" s="15" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="I1252" s="15" t="s">
         <v>123</v>
@@ -64402,18 +64490,22 @@
       <c r="J1252" s="15" t="s">
         <v>1913</v>
       </c>
-      <c r="K1252" s="18"/>
+      <c r="K1252" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1252" s="18"/>
       <c r="M1252" s="18"/>
       <c r="N1252" s="40"/>
       <c r="O1252" s="18"/>
       <c r="P1252" s="18"/>
-      <c r="Q1252" s="18"/>
+      <c r="Q1252" s="15">
+        <v>94526230</v>
+      </c>
       <c r="R1252" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1253" spans="1:18" ht="31.2" thickBot="1">
+    <row r="1253" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1253" s="2">
         <v>1252</v>
       </c>
@@ -64421,22 +64513,22 @@
         <v>46244</v>
       </c>
       <c r="C1253" s="56" t="s">
-        <v>279</v>
-      </c>
-      <c r="D1253" s="56" t="s">
-        <v>280</v>
+        <v>1934</v>
+      </c>
+      <c r="D1253" s="56">
+        <v>101540233</v>
       </c>
       <c r="E1253" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1253" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1253" s="57" t="s">
-        <v>1936</v>
-      </c>
-      <c r="H1253" s="15">
-        <v>48752</v>
+      <c r="F1253" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1253" s="57">
+        <v>5126</v>
+      </c>
+      <c r="H1253" s="15" t="s">
+        <v>1935</v>
       </c>
       <c r="I1253" s="15" t="s">
         <v>123</v>
@@ -64444,22 +64536,20 @@
       <c r="J1253" s="15" t="s">
         <v>1913</v>
       </c>
-      <c r="K1253" s="30" t="s">
-        <v>1596</v>
+      <c r="K1253" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1253" s="18"/>
       <c r="M1253" s="18"/>
       <c r="N1253" s="40"/>
       <c r="O1253" s="18"/>
-      <c r="P1253" s="50" t="s">
-        <v>1803</v>
-      </c>
+      <c r="P1253" s="18"/>
       <c r="Q1253" s="18"/>
       <c r="R1253" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1254" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1254" spans="1:18" ht="31.2" thickBot="1">
       <c r="A1254" s="2">
         <v>1253</v>
       </c>
@@ -64467,66 +64557,78 @@
         <v>46244</v>
       </c>
       <c r="C1254" s="56" t="s">
-        <v>1937</v>
-      </c>
-      <c r="D1254" s="56">
-        <v>76637533</v>
+        <v>279</v>
+      </c>
+      <c r="D1254" s="56" t="s">
+        <v>280</v>
       </c>
       <c r="E1254" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1254" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1254" s="57">
-        <v>1027</v>
+      <c r="F1254" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1254" s="57" t="s">
+        <v>1936</v>
       </c>
       <c r="H1254" s="15">
-        <v>512</v>
+        <v>48752</v>
       </c>
       <c r="I1254" s="15" t="s">
         <v>123</v>
       </c>
       <c r="J1254" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="K1254" s="17" t="s">
-        <v>12</v>
+        <v>1913</v>
+      </c>
+      <c r="K1254" s="30" t="s">
+        <v>1596</v>
       </c>
       <c r="L1254" s="18"/>
       <c r="M1254" s="18"/>
       <c r="N1254" s="40"/>
       <c r="O1254" s="18"/>
-      <c r="P1254" s="18"/>
+      <c r="P1254" s="50" t="s">
+        <v>1803</v>
+      </c>
       <c r="Q1254" s="18"/>
       <c r="R1254" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1255" spans="1:18" ht="15" thickBot="1">
+    <row r="1255" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1255" s="2">
         <v>1254</v>
       </c>
       <c r="B1255" s="10">
         <v>46244</v>
       </c>
-      <c r="C1255" s="38"/>
-      <c r="D1255" s="38"/>
-      <c r="E1255" s="18"/>
-      <c r="F1255" s="13" t="s">
-        <v>22</v>
+      <c r="C1255" s="56" t="s">
+        <v>1937</v>
+      </c>
+      <c r="D1255" s="56">
+        <v>76637533</v>
+      </c>
+      <c r="E1255" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1255" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1255" s="57">
-        <v>78112</v>
-      </c>
-      <c r="H1255" s="18"/>
-      <c r="I1255" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1255" s="52" t="s">
-        <v>776</v>
-      </c>
-      <c r="K1255" s="18"/>
+        <v>1027</v>
+      </c>
+      <c r="H1255" s="15">
+        <v>512</v>
+      </c>
+      <c r="I1255" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1255" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1255" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1255" s="18"/>
       <c r="M1255" s="18"/>
       <c r="N1255" s="40"/>
@@ -64544,23 +64646,33 @@
       <c r="B1256" s="10">
         <v>46244</v>
       </c>
-      <c r="C1256" s="38"/>
-      <c r="D1256" s="38"/>
-      <c r="E1256" s="18"/>
+      <c r="C1256" s="56" t="s">
+        <v>1965</v>
+      </c>
+      <c r="D1256" s="56" t="s">
+        <v>1966</v>
+      </c>
+      <c r="E1256" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="F1256" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1256" s="57">
-        <v>20380</v>
-      </c>
-      <c r="H1256" s="18"/>
+        <v>78112</v>
+      </c>
+      <c r="H1256" s="15">
+        <v>19848</v>
+      </c>
       <c r="I1256" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1256" s="52" t="s">
         <v>776</v>
       </c>
-      <c r="K1256" s="18"/>
+      <c r="K1256" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1256" s="18"/>
       <c r="M1256" s="18"/>
       <c r="N1256" s="40"/>
@@ -64578,23 +64690,33 @@
       <c r="B1257" s="10">
         <v>46244</v>
       </c>
-      <c r="C1257" s="38"/>
-      <c r="D1257" s="38"/>
-      <c r="E1257" s="18"/>
+      <c r="C1257" s="56" t="s">
+        <v>1967</v>
+      </c>
+      <c r="D1257" s="56" t="s">
+        <v>1968</v>
+      </c>
+      <c r="E1257" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="F1257" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1257" s="57">
-        <v>40255</v>
-      </c>
-      <c r="H1257" s="18"/>
+        <v>20380</v>
+      </c>
+      <c r="H1257" s="15">
+        <v>23939</v>
+      </c>
       <c r="I1257" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1257" s="52" t="s">
         <v>776</v>
       </c>
-      <c r="K1257" s="18"/>
+      <c r="K1257" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1257" s="18"/>
       <c r="M1257" s="18"/>
       <c r="N1257" s="40"/>
@@ -64612,23 +64734,33 @@
       <c r="B1258" s="10">
         <v>46244</v>
       </c>
-      <c r="C1258" s="38"/>
-      <c r="D1258" s="38"/>
-      <c r="E1258" s="18"/>
+      <c r="C1258" s="56" t="s">
+        <v>1969</v>
+      </c>
+      <c r="D1258" s="56" t="s">
+        <v>1970</v>
+      </c>
+      <c r="E1258" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="F1258" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1258" s="57">
-        <v>78295</v>
-      </c>
-      <c r="H1258" s="18"/>
+        <v>40255</v>
+      </c>
+      <c r="H1258" s="15">
+        <v>39156</v>
+      </c>
       <c r="I1258" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1258" s="52" t="s">
         <v>776</v>
       </c>
-      <c r="K1258" s="18"/>
+      <c r="K1258" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1258" s="18"/>
       <c r="M1258" s="18"/>
       <c r="N1258" s="40"/>
@@ -64646,23 +64778,33 @@
       <c r="B1259" s="10">
         <v>46244</v>
       </c>
-      <c r="C1259" s="38"/>
-      <c r="D1259" s="38"/>
-      <c r="E1259" s="18"/>
+      <c r="C1259" s="56" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1259" s="56" t="s">
+        <v>1971</v>
+      </c>
+      <c r="E1259" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="F1259" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1259" s="57">
-        <v>43916</v>
-      </c>
-      <c r="H1259" s="18"/>
+        <v>78295</v>
+      </c>
+      <c r="H1259" s="15">
+        <v>91055</v>
+      </c>
       <c r="I1259" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1259" s="52" t="s">
         <v>776</v>
       </c>
-      <c r="K1259" s="18"/>
+      <c r="K1259" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1259" s="18"/>
       <c r="M1259" s="18"/>
       <c r="N1259" s="40"/>
@@ -64680,23 +64822,33 @@
       <c r="B1260" s="10">
         <v>46244</v>
       </c>
-      <c r="C1260" s="38"/>
-      <c r="D1260" s="38"/>
-      <c r="E1260" s="18"/>
+      <c r="C1260" s="56" t="s">
+        <v>1972</v>
+      </c>
+      <c r="D1260" s="56" t="s">
+        <v>1973</v>
+      </c>
+      <c r="E1260" s="30" t="s">
+        <v>119</v>
+      </c>
       <c r="F1260" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1260" s="57">
-        <v>18439</v>
-      </c>
-      <c r="H1260" s="18"/>
+        <v>43916</v>
+      </c>
+      <c r="H1260" s="15">
+        <v>63018</v>
+      </c>
       <c r="I1260" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1260" s="52" t="s">
         <v>776</v>
       </c>
-      <c r="K1260" s="18"/>
+      <c r="K1260" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1260" s="18"/>
       <c r="M1260" s="18"/>
       <c r="N1260" s="40"/>
@@ -64714,23 +64866,33 @@
       <c r="B1261" s="10">
         <v>46244</v>
       </c>
-      <c r="C1261" s="38"/>
-      <c r="D1261" s="38"/>
-      <c r="E1261" s="18"/>
+      <c r="C1261" s="56" t="s">
+        <v>1974</v>
+      </c>
+      <c r="D1261" s="56" t="s">
+        <v>1975</v>
+      </c>
+      <c r="E1261" s="30" t="s">
+        <v>119</v>
+      </c>
       <c r="F1261" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1261" s="57">
-        <v>85929</v>
-      </c>
-      <c r="H1261" s="18"/>
+        <v>18439</v>
+      </c>
+      <c r="H1261" s="15">
+        <v>28485</v>
+      </c>
       <c r="I1261" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1261" s="52" t="s">
         <v>776</v>
       </c>
-      <c r="K1261" s="18"/>
+      <c r="K1261" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1261" s="18"/>
       <c r="M1261" s="18"/>
       <c r="N1261" s="40"/>
@@ -64748,23 +64910,33 @@
       <c r="B1262" s="10">
         <v>46244</v>
       </c>
-      <c r="C1262" s="38"/>
-      <c r="D1262" s="38"/>
-      <c r="E1262" s="18"/>
+      <c r="C1262" s="56" t="s">
+        <v>1976</v>
+      </c>
+      <c r="D1262" s="56" t="s">
+        <v>1977</v>
+      </c>
+      <c r="E1262" s="30" t="s">
+        <v>119</v>
+      </c>
       <c r="F1262" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1262" s="57">
-        <v>28434</v>
-      </c>
-      <c r="H1262" s="18"/>
+        <v>85929</v>
+      </c>
+      <c r="H1262" s="15">
+        <v>13193</v>
+      </c>
       <c r="I1262" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1262" s="52" t="s">
         <v>776</v>
       </c>
-      <c r="K1262" s="18"/>
+      <c r="K1262" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1262" s="18"/>
       <c r="M1262" s="18"/>
       <c r="N1262" s="40"/>
@@ -64783,37 +64955,41 @@
         <v>46244</v>
       </c>
       <c r="C1263" s="56" t="s">
-        <v>1349</v>
+        <v>1978</v>
       </c>
       <c r="D1263" s="56" t="s">
-        <v>1938</v>
-      </c>
-      <c r="E1263" s="12" t="s">
-        <v>21</v>
+        <v>1979</v>
+      </c>
+      <c r="E1263" s="30" t="s">
+        <v>119</v>
       </c>
       <c r="F1263" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1263" s="57">
-        <v>13349</v>
+        <v>28434</v>
       </c>
       <c r="H1263" s="15">
-        <v>43281</v>
-      </c>
-      <c r="I1263" s="22" t="s">
-        <v>563</v>
-      </c>
-      <c r="J1263" s="51" t="s">
-        <v>564</v>
-      </c>
-      <c r="K1263" s="18"/>
+        <v>10962</v>
+      </c>
+      <c r="I1263" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1263" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1263" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1263" s="18"/>
       <c r="M1263" s="18"/>
       <c r="N1263" s="40"/>
       <c r="O1263" s="18"/>
       <c r="P1263" s="18"/>
       <c r="Q1263" s="18"/>
-      <c r="R1263" s="18"/>
+      <c r="R1263" s="22" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="1264" spans="1:18" ht="15" thickBot="1">
       <c r="A1264" s="2">
@@ -64823,10 +64999,10 @@
         <v>46244</v>
       </c>
       <c r="C1264" s="56" t="s">
-        <v>1939</v>
+        <v>1349</v>
       </c>
       <c r="D1264" s="56" t="s">
-        <v>1940</v>
+        <v>1938</v>
       </c>
       <c r="E1264" s="12" t="s">
         <v>21</v>
@@ -64835,10 +65011,10 @@
         <v>22</v>
       </c>
       <c r="G1264" s="57">
-        <v>48418</v>
+        <v>13349</v>
       </c>
       <c r="H1264" s="15">
-        <v>62782</v>
+        <v>43281</v>
       </c>
       <c r="I1264" s="22" t="s">
         <v>563</v>
@@ -64846,14 +65022,18 @@
       <c r="J1264" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1264" s="18"/>
+      <c r="K1264" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1264" s="18"/>
       <c r="M1264" s="18"/>
       <c r="N1264" s="40"/>
       <c r="O1264" s="18"/>
       <c r="P1264" s="18"/>
       <c r="Q1264" s="18"/>
-      <c r="R1264" s="18"/>
+      <c r="R1264" s="22" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="1265" spans="1:18" ht="15" thickBot="1">
       <c r="A1265" s="2">
@@ -64863,10 +65043,10 @@
         <v>46244</v>
       </c>
       <c r="C1265" s="56" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="D1265" s="56" t="s">
-        <v>1942</v>
+        <v>1940</v>
       </c>
       <c r="E1265" s="12" t="s">
         <v>21</v>
@@ -64875,10 +65055,10 @@
         <v>22</v>
       </c>
       <c r="G1265" s="57">
-        <v>51661</v>
+        <v>48418</v>
       </c>
       <c r="H1265" s="15">
-        <v>40394</v>
+        <v>62782</v>
       </c>
       <c r="I1265" s="22" t="s">
         <v>563</v>
@@ -64886,14 +65066,18 @@
       <c r="J1265" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1265" s="18"/>
+      <c r="K1265" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1265" s="18"/>
       <c r="M1265" s="18"/>
       <c r="N1265" s="40"/>
       <c r="O1265" s="18"/>
       <c r="P1265" s="18"/>
       <c r="Q1265" s="18"/>
-      <c r="R1265" s="18"/>
+      <c r="R1265" s="22" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="1266" spans="1:18" ht="15" thickBot="1">
       <c r="A1266" s="2">
@@ -64903,10 +65087,10 @@
         <v>46244</v>
       </c>
       <c r="C1266" s="56" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="D1266" s="56" t="s">
-        <v>1944</v>
+        <v>1942</v>
       </c>
       <c r="E1266" s="12" t="s">
         <v>21</v>
@@ -64915,10 +65099,10 @@
         <v>22</v>
       </c>
       <c r="G1266" s="57">
-        <v>84554</v>
+        <v>51661</v>
       </c>
       <c r="H1266" s="15">
-        <v>21501</v>
+        <v>40394</v>
       </c>
       <c r="I1266" s="22" t="s">
         <v>563</v>
@@ -64926,14 +65110,18 @@
       <c r="J1266" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1266" s="18"/>
+      <c r="K1266" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1266" s="18"/>
       <c r="M1266" s="18"/>
       <c r="N1266" s="40"/>
       <c r="O1266" s="18"/>
       <c r="P1266" s="18"/>
       <c r="Q1266" s="18"/>
-      <c r="R1266" s="18"/>
+      <c r="R1266" s="22" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="1267" spans="1:18" ht="15" thickBot="1">
       <c r="A1267" s="2">
@@ -64943,10 +65131,10 @@
         <v>46244</v>
       </c>
       <c r="C1267" s="56" t="s">
-        <v>1137</v>
+        <v>1943</v>
       </c>
       <c r="D1267" s="56" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="E1267" s="12" t="s">
         <v>21</v>
@@ -64955,23 +65143,29 @@
         <v>22</v>
       </c>
       <c r="G1267" s="57">
-        <v>41504</v>
-      </c>
-      <c r="H1267" s="18"/>
+        <v>84554</v>
+      </c>
+      <c r="H1267" s="15">
+        <v>21501</v>
+      </c>
       <c r="I1267" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1267" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1267" s="18"/>
+      <c r="K1267" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1267" s="18"/>
       <c r="M1267" s="18"/>
       <c r="N1267" s="40"/>
       <c r="O1267" s="18"/>
       <c r="P1267" s="18"/>
       <c r="Q1267" s="18"/>
-      <c r="R1267" s="18"/>
+      <c r="R1267" s="22" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="1268" spans="1:18" ht="15" thickBot="1">
       <c r="A1268" s="2">
@@ -64981,9 +65175,11 @@
         <v>46244</v>
       </c>
       <c r="C1268" s="56" t="s">
-        <v>1946</v>
-      </c>
-      <c r="D1268" s="38"/>
+        <v>1137</v>
+      </c>
+      <c r="D1268" s="56" t="s">
+        <v>1945</v>
+      </c>
       <c r="E1268" s="12" t="s">
         <v>21</v>
       </c>
@@ -64991,25 +65187,27 @@
         <v>22</v>
       </c>
       <c r="G1268" s="57">
-        <v>17443</v>
-      </c>
-      <c r="H1268" s="15">
-        <v>20106</v>
-      </c>
+        <v>41504</v>
+      </c>
+      <c r="H1268" s="18"/>
       <c r="I1268" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1268" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1268" s="18"/>
+      <c r="K1268" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1268" s="18"/>
       <c r="M1268" s="18"/>
       <c r="N1268" s="40"/>
       <c r="O1268" s="18"/>
       <c r="P1268" s="18"/>
       <c r="Q1268" s="18"/>
-      <c r="R1268" s="18"/>
+      <c r="R1268" s="22" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="1269" spans="1:18" ht="15" thickBot="1">
       <c r="A1269" s="2">
@@ -65019,28 +65217,28 @@
         <v>46244</v>
       </c>
       <c r="C1269" s="56" t="s">
-        <v>1874</v>
-      </c>
-      <c r="D1269" s="56">
-        <v>112067329</v>
+        <v>1946</v>
+      </c>
+      <c r="D1269" s="56" t="s">
+        <v>1980</v>
       </c>
       <c r="E1269" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1269" s="16" t="s">
-        <v>122</v>
+      <c r="F1269" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1269" s="57">
-        <v>2968</v>
+        <v>17443</v>
       </c>
       <c r="H1269" s="15">
-        <v>5613</v>
-      </c>
-      <c r="I1269" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1269" s="15" t="s">
-        <v>839</v>
+        <v>20106</v>
+      </c>
+      <c r="I1269" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1269" s="51" t="s">
+        <v>564</v>
       </c>
       <c r="K1269" s="17" t="s">
         <v>12</v>
@@ -65051,11 +65249,11 @@
       <c r="O1269" s="18"/>
       <c r="P1269" s="18"/>
       <c r="Q1269" s="18"/>
-      <c r="R1269" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1270" spans="1:18" ht="27.6" thickBot="1">
+      <c r="R1269" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:18" ht="15" thickBot="1">
       <c r="A1270" s="2">
         <v>1269</v>
       </c>
@@ -65063,28 +65261,28 @@
         <v>46244</v>
       </c>
       <c r="C1270" s="56" t="s">
-        <v>1875</v>
-      </c>
-      <c r="D1270" s="56">
-        <v>116806083</v>
+        <v>1952</v>
+      </c>
+      <c r="D1270" s="56" t="s">
+        <v>1953</v>
       </c>
       <c r="E1270" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1270" s="16" t="s">
-        <v>122</v>
+      <c r="F1270" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1270" s="57">
-        <v>442</v>
+        <v>82557</v>
       </c>
       <c r="H1270" s="15">
-        <v>7536</v>
-      </c>
-      <c r="I1270" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1270" s="15" t="s">
-        <v>950</v>
+        <v>23835</v>
+      </c>
+      <c r="I1270" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1270" s="51" t="s">
+        <v>564</v>
       </c>
       <c r="K1270" s="17" t="s">
         <v>12</v>
@@ -65094,11 +65292,9 @@
       <c r="N1270" s="40"/>
       <c r="O1270" s="18"/>
       <c r="P1270" s="18"/>
-      <c r="Q1270" s="11">
-        <v>79997138</v>
-      </c>
-      <c r="R1270" s="20" t="s">
-        <v>11</v>
+      <c r="Q1270" s="18"/>
+      <c r="R1270" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="1271" spans="1:18" ht="15" thickBot="1">
@@ -65109,10 +65305,10 @@
         <v>46244</v>
       </c>
       <c r="C1271" s="56" t="s">
-        <v>1876</v>
+        <v>1102</v>
       </c>
       <c r="D1271" s="56">
-        <v>113458078</v>
+        <v>107774476</v>
       </c>
       <c r="E1271" s="12" t="s">
         <v>21</v>
@@ -65121,16 +65317,16 @@
         <v>122</v>
       </c>
       <c r="G1271" s="57">
-        <v>5913</v>
+        <v>3561</v>
       </c>
       <c r="H1271" s="15">
-        <v>1154</v>
-      </c>
-      <c r="I1271" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1271" s="15" t="s">
-        <v>950</v>
+        <v>5702</v>
+      </c>
+      <c r="I1271" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1271" s="51" t="s">
+        <v>564</v>
       </c>
       <c r="K1271" s="17" t="s">
         <v>12</v>
@@ -65141,8 +65337,8 @@
       <c r="O1271" s="18"/>
       <c r="P1271" s="18"/>
       <c r="Q1271" s="18"/>
-      <c r="R1271" s="20" t="s">
-        <v>11</v>
+      <c r="R1271" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="1272" spans="1:18" ht="27.6" thickBot="1">
@@ -65153,28 +65349,28 @@
         <v>46244</v>
       </c>
       <c r="C1272" s="56" t="s">
-        <v>638</v>
-      </c>
-      <c r="D1272" s="56">
-        <v>122952217</v>
+        <v>1954</v>
+      </c>
+      <c r="D1272" s="56" t="s">
+        <v>1955</v>
       </c>
       <c r="E1272" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1272" s="16" t="s">
-        <v>122</v>
+      <c r="F1272" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1272" s="57">
-        <v>4581</v>
+        <v>22319</v>
       </c>
       <c r="H1272" s="15">
-        <v>-8325</v>
-      </c>
-      <c r="I1272" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1272" s="15" t="s">
-        <v>950</v>
+        <v>19801</v>
+      </c>
+      <c r="I1272" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1272" s="51" t="s">
+        <v>564</v>
       </c>
       <c r="K1272" s="17" t="s">
         <v>12</v>
@@ -65184,14 +65380,12 @@
       <c r="N1272" s="40"/>
       <c r="O1272" s="18"/>
       <c r="P1272" s="18"/>
-      <c r="Q1272" s="11" t="s">
-        <v>1877</v>
-      </c>
-      <c r="R1272" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1273" spans="1:18" ht="15" thickBot="1">
+      <c r="Q1272" s="18"/>
+      <c r="R1272" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1273" s="2">
         <v>1272</v>
       </c>
@@ -65199,28 +65393,28 @@
         <v>46244</v>
       </c>
       <c r="C1273" s="56" t="s">
-        <v>1878</v>
+        <v>1956</v>
       </c>
       <c r="D1273" s="56">
-        <v>126214395</v>
-      </c>
-      <c r="E1273" s="12" t="s">
-        <v>21</v>
+        <v>36336406</v>
+      </c>
+      <c r="E1273" s="37" t="s">
+        <v>121</v>
       </c>
       <c r="F1273" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1273" s="57">
-        <v>355</v>
+        <v>1965</v>
       </c>
       <c r="H1273" s="15">
-        <v>2278</v>
-      </c>
-      <c r="I1273" s="16" t="s">
-        <v>10</v>
+        <v>826</v>
+      </c>
+      <c r="I1273" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="J1273" s="15" t="s">
-        <v>950</v>
+        <v>1058</v>
       </c>
       <c r="K1273" s="17" t="s">
         <v>12</v>
@@ -65231,8 +65425,8 @@
       <c r="O1273" s="18"/>
       <c r="P1273" s="18"/>
       <c r="Q1273" s="18"/>
-      <c r="R1273" s="20" t="s">
-        <v>11</v>
+      <c r="R1273" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="1274" spans="1:18" ht="28.2" thickBot="1">
@@ -65243,28 +65437,28 @@
         <v>46244</v>
       </c>
       <c r="C1274" s="56" t="s">
-        <v>47</v>
-      </c>
-      <c r="D1274" s="56" t="s">
-        <v>1879</v>
-      </c>
-      <c r="E1274" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1274" s="13" t="s">
-        <v>22</v>
+        <v>1957</v>
+      </c>
+      <c r="D1274" s="56">
+        <v>17065948</v>
+      </c>
+      <c r="E1274" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1274" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1274" s="57">
-        <v>33404</v>
+        <v>5788</v>
       </c>
       <c r="H1274" s="15">
-        <v>89137</v>
-      </c>
-      <c r="I1274" s="16" t="s">
-        <v>10</v>
+        <v>9112</v>
+      </c>
+      <c r="I1274" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="J1274" s="15" t="s">
-        <v>1880</v>
+        <v>1058</v>
       </c>
       <c r="K1274" s="17" t="s">
         <v>12</v>
@@ -65274,11 +65468,9 @@
       <c r="N1274" s="40"/>
       <c r="O1274" s="18"/>
       <c r="P1274" s="18"/>
-      <c r="Q1274" s="11">
-        <v>95643750</v>
-      </c>
-      <c r="R1274" s="20" t="s">
-        <v>11</v>
+      <c r="Q1274" s="18"/>
+      <c r="R1274" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="1275" spans="1:18" ht="28.2" thickBot="1">
@@ -65289,28 +65481,28 @@
         <v>46244</v>
       </c>
       <c r="C1275" s="56" t="s">
-        <v>504</v>
-      </c>
-      <c r="D1275" s="56" t="s">
-        <v>1881</v>
-      </c>
-      <c r="E1275" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1275" s="13" t="s">
-        <v>22</v>
+        <v>1958</v>
+      </c>
+      <c r="D1275" s="56">
+        <v>3084818</v>
+      </c>
+      <c r="E1275" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1275" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1275" s="57">
-        <v>7606</v>
+        <v>6300</v>
       </c>
       <c r="H1275" s="15">
-        <v>66793</v>
-      </c>
-      <c r="I1275" s="16" t="s">
-        <v>10</v>
+        <v>8487</v>
+      </c>
+      <c r="I1275" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="J1275" s="15" t="s">
-        <v>1880</v>
+        <v>1058</v>
       </c>
       <c r="K1275" s="17" t="s">
         <v>12</v>
@@ -65320,14 +65512,12 @@
       <c r="N1275" s="40"/>
       <c r="O1275" s="18"/>
       <c r="P1275" s="18"/>
-      <c r="Q1275" s="11">
-        <v>501924525</v>
-      </c>
-      <c r="R1275" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1276" spans="1:18" ht="27.6" thickBot="1">
+      <c r="Q1275" s="18"/>
+      <c r="R1275" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1276" s="2">
         <v>1275</v>
       </c>
@@ -65335,28 +65525,28 @@
         <v>46244</v>
       </c>
       <c r="C1276" s="56" t="s">
-        <v>906</v>
+        <v>1959</v>
       </c>
       <c r="D1276" s="56">
-        <v>128333109</v>
-      </c>
-      <c r="E1276" s="12" t="s">
-        <v>21</v>
+        <v>2144791</v>
+      </c>
+      <c r="E1276" s="37" t="s">
+        <v>121</v>
       </c>
       <c r="F1276" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1276" s="57">
-        <v>4900</v>
+        <v>1598</v>
       </c>
       <c r="H1276" s="15">
-        <v>-6338</v>
-      </c>
-      <c r="I1276" s="16" t="s">
-        <v>10</v>
+        <v>3380</v>
+      </c>
+      <c r="I1276" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="J1276" s="15" t="s">
-        <v>890</v>
+        <v>1058</v>
       </c>
       <c r="K1276" s="17" t="s">
         <v>12</v>
@@ -65366,14 +65556,12 @@
       <c r="N1276" s="40"/>
       <c r="O1276" s="18"/>
       <c r="P1276" s="18"/>
-      <c r="Q1276" s="11">
-        <v>95609530</v>
-      </c>
-      <c r="R1276" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1277" spans="1:18" ht="15" thickBot="1">
+      <c r="Q1276" s="18"/>
+      <c r="R1276" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1277" s="2">
         <v>1276</v>
       </c>
@@ -65381,28 +65569,28 @@
         <v>46244</v>
       </c>
       <c r="C1277" s="56" t="s">
-        <v>1894</v>
+        <v>1960</v>
       </c>
       <c r="D1277" s="56">
-        <v>116033629</v>
-      </c>
-      <c r="E1277" s="12" t="s">
-        <v>21</v>
+        <v>12571732</v>
+      </c>
+      <c r="E1277" s="37" t="s">
+        <v>121</v>
       </c>
       <c r="F1277" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1277" s="57">
-        <v>1702</v>
+        <v>8884</v>
       </c>
       <c r="H1277" s="15">
-        <v>5164</v>
-      </c>
-      <c r="I1277" s="16" t="s">
-        <v>10</v>
+        <v>8169</v>
+      </c>
+      <c r="I1277" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="J1277" s="15" t="s">
-        <v>950</v>
+        <v>1058</v>
       </c>
       <c r="K1277" s="17" t="s">
         <v>12</v>
@@ -65412,14 +65600,12 @@
       <c r="N1277" s="40"/>
       <c r="O1277" s="18"/>
       <c r="P1277" s="18"/>
-      <c r="Q1277" s="11">
-        <v>94250210</v>
-      </c>
-      <c r="R1277" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1278" spans="1:18" ht="27.6" thickBot="1">
+      <c r="Q1277" s="18"/>
+      <c r="R1277" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1278" s="2">
         <v>1277</v>
       </c>
@@ -65427,28 +65613,28 @@
         <v>46244</v>
       </c>
       <c r="C1278" s="56" t="s">
-        <v>1895</v>
-      </c>
-      <c r="D1278" s="56" t="s">
-        <v>1896</v>
-      </c>
-      <c r="E1278" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1278" s="13" t="s">
-        <v>22</v>
+        <v>1961</v>
+      </c>
+      <c r="D1278" s="56">
+        <v>96995164</v>
+      </c>
+      <c r="E1278" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1278" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1278" s="57">
-        <v>21668</v>
+        <v>8884</v>
       </c>
       <c r="H1278" s="15">
-        <v>75184</v>
-      </c>
-      <c r="I1278" s="16" t="s">
-        <v>10</v>
+        <v>8169</v>
+      </c>
+      <c r="I1278" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="J1278" s="15" t="s">
-        <v>1897</v>
+        <v>1058</v>
       </c>
       <c r="K1278" s="17" t="s">
         <v>12</v>
@@ -65458,14 +65644,12 @@
       <c r="N1278" s="40"/>
       <c r="O1278" s="18"/>
       <c r="P1278" s="18"/>
-      <c r="Q1278" s="11">
-        <v>557824163</v>
-      </c>
-      <c r="R1278" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1279" spans="1:18" ht="28.2" thickBot="1">
+      <c r="Q1278" s="18"/>
+      <c r="R1278" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:18" ht="15" thickBot="1">
       <c r="A1279" s="2">
         <v>1278</v>
       </c>
@@ -65473,28 +65657,28 @@
         <v>46244</v>
       </c>
       <c r="C1279" s="56" t="s">
-        <v>1898</v>
-      </c>
-      <c r="D1279" s="56" t="s">
-        <v>1899</v>
-      </c>
-      <c r="E1279" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1279" s="13" t="s">
-        <v>22</v>
+        <v>1981</v>
+      </c>
+      <c r="D1279" s="56">
+        <v>76532221</v>
+      </c>
+      <c r="E1279" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1279" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1279" s="57">
-        <v>9215</v>
+        <v>9125</v>
       </c>
       <c r="H1279" s="15">
-        <v>10278</v>
-      </c>
-      <c r="I1279" s="16" t="s">
-        <v>10</v>
+        <v>988</v>
+      </c>
+      <c r="I1279" s="22" t="s">
+        <v>563</v>
       </c>
       <c r="J1279" s="15" t="s">
-        <v>49</v>
+        <v>1672</v>
       </c>
       <c r="K1279" s="17" t="s">
         <v>12</v>
@@ -65505,11 +65689,11 @@
       <c r="O1279" s="18"/>
       <c r="P1279" s="18"/>
       <c r="Q1279" s="18"/>
-      <c r="R1279" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1280" spans="1:18" ht="28.2" thickBot="1">
+      <c r="R1279" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:18" ht="15" thickBot="1">
       <c r="A1280" s="2">
         <v>1279</v>
       </c>
@@ -65517,28 +65701,28 @@
         <v>46244</v>
       </c>
       <c r="C1280" s="56" t="s">
-        <v>1900</v>
-      </c>
-      <c r="D1280" s="56" t="s">
-        <v>1901</v>
+        <v>1982</v>
+      </c>
+      <c r="D1280" s="56">
+        <v>86125495</v>
       </c>
       <c r="E1280" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1280" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1280" s="57">
-        <v>53578</v>
+      <c r="F1280" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1280" s="75">
+        <v>9181</v>
       </c>
       <c r="H1280" s="15">
-        <v>46411</v>
-      </c>
-      <c r="I1280" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1280" s="15" t="s">
-        <v>49</v>
+        <v>1776</v>
+      </c>
+      <c r="I1280" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1280" s="51" t="s">
+        <v>564</v>
       </c>
       <c r="K1280" s="17" t="s">
         <v>12</v>
@@ -65549,8 +65733,8 @@
       <c r="O1280" s="18"/>
       <c r="P1280" s="18"/>
       <c r="Q1280" s="18"/>
-      <c r="R1280" s="20" t="s">
-        <v>11</v>
+      <c r="R1280" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="1281" spans="1:18" ht="15" thickBot="1">
@@ -65561,10 +65745,10 @@
         <v>46244</v>
       </c>
       <c r="C1281" s="56" t="s">
-        <v>1902</v>
+        <v>1983</v>
       </c>
       <c r="D1281" s="56" t="s">
-        <v>1903</v>
+        <v>1984</v>
       </c>
       <c r="E1281" s="30" t="s">
         <v>119</v>
@@ -65572,17 +65756,17 @@
       <c r="F1281" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="G1281" s="57">
-        <v>68833</v>
+      <c r="G1281" s="75">
+        <v>62966</v>
       </c>
       <c r="H1281" s="15">
-        <v>78793</v>
+        <v>78304</v>
       </c>
       <c r="I1281" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J1281" s="15" t="s">
-        <v>1904</v>
+      <c r="J1281" s="52" t="s">
+        <v>776</v>
       </c>
       <c r="K1281" s="17" t="s">
         <v>12</v>
@@ -65592,11 +65776,9 @@
       <c r="N1281" s="40"/>
       <c r="O1281" s="18"/>
       <c r="P1281" s="18"/>
-      <c r="Q1281" s="11">
-        <v>554186760</v>
-      </c>
-      <c r="R1281" s="20" t="s">
-        <v>11</v>
+      <c r="Q1281" s="18"/>
+      <c r="R1281" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="1282" spans="1:18" ht="15" thickBot="1">
@@ -65607,10 +65789,10 @@
         <v>46244</v>
       </c>
       <c r="C1282" s="56" t="s">
-        <v>1905</v>
+        <v>1985</v>
       </c>
       <c r="D1282" s="56" t="s">
-        <v>1906</v>
+        <v>1986</v>
       </c>
       <c r="E1282" s="30" t="s">
         <v>119</v>
@@ -65618,17 +65800,15 @@
       <c r="F1282" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="G1282" s="57">
-        <v>56757</v>
-      </c>
-      <c r="H1282" s="15" t="s">
-        <v>1907</v>
-      </c>
+      <c r="G1282" s="75">
+        <v>69727</v>
+      </c>
+      <c r="H1282" s="18"/>
       <c r="I1282" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J1282" s="15" t="s">
-        <v>1904</v>
+      <c r="J1282" s="52" t="s">
+        <v>776</v>
       </c>
       <c r="K1282" s="17" t="s">
         <v>12</v>
@@ -65638,14 +65818,12 @@
       <c r="N1282" s="40"/>
       <c r="O1282" s="18"/>
       <c r="P1282" s="18"/>
-      <c r="Q1282" s="11">
-        <v>76969759</v>
-      </c>
-      <c r="R1282" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1283" spans="1:18" ht="27.6" thickBot="1">
+      <c r="Q1282" s="18"/>
+      <c r="R1282" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:18" ht="15" thickBot="1">
       <c r="A1283" s="2">
         <v>1282</v>
       </c>
@@ -65653,28 +65831,28 @@
         <v>46244</v>
       </c>
       <c r="C1283" s="56" t="s">
-        <v>1908</v>
+        <v>1987</v>
       </c>
       <c r="D1283" s="56" t="s">
-        <v>1909</v>
-      </c>
-      <c r="E1283" s="12" t="s">
-        <v>21</v>
+        <v>1988</v>
+      </c>
+      <c r="E1283" s="30" t="s">
+        <v>119</v>
       </c>
       <c r="F1283" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="G1283" s="57">
-        <v>61918</v>
+      <c r="G1283" s="75">
+        <v>88240</v>
       </c>
       <c r="H1283" s="15">
-        <v>19939</v>
+        <v>35031</v>
       </c>
       <c r="I1283" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J1283" s="15" t="s">
-        <v>46</v>
+      <c r="J1283" s="52" t="s">
+        <v>776</v>
       </c>
       <c r="K1283" s="17" t="s">
         <v>12</v>
@@ -65685,11 +65863,11 @@
       <c r="O1283" s="18"/>
       <c r="P1283" s="18"/>
       <c r="Q1283" s="18"/>
-      <c r="R1283" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1284" spans="1:18" ht="27.6" thickBot="1">
+      <c r="R1283" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:18" ht="15" thickBot="1">
       <c r="A1284" s="2">
         <v>1283</v>
       </c>
@@ -65697,28 +65875,28 @@
         <v>46244</v>
       </c>
       <c r="C1284" s="56" t="s">
-        <v>1910</v>
+        <v>1989</v>
       </c>
       <c r="D1284" s="56" t="s">
-        <v>1911</v>
+        <v>1990</v>
       </c>
       <c r="E1284" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="F1284" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1284" s="57">
-        <v>8490</v>
+      <c r="F1284" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1284" s="75">
+        <v>28971</v>
       </c>
       <c r="H1284" s="15">
-        <v>8101</v>
+        <v>31344</v>
       </c>
       <c r="I1284" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J1284" s="15" t="s">
-        <v>202</v>
+      <c r="J1284" s="52" t="s">
+        <v>776</v>
       </c>
       <c r="K1284" s="17" t="s">
         <v>12</v>
@@ -65728,14 +65906,12 @@
       <c r="N1284" s="40"/>
       <c r="O1284" s="18"/>
       <c r="P1284" s="18"/>
-      <c r="Q1284" s="11">
-        <v>98705284</v>
-      </c>
-      <c r="R1284" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1285" spans="1:18" ht="28.2" thickBot="1">
+      <c r="Q1284" s="18"/>
+      <c r="R1284" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:18" ht="15" thickBot="1">
       <c r="A1285" s="2">
         <v>1284</v>
       </c>
@@ -65743,10 +65919,10 @@
         <v>46244</v>
       </c>
       <c r="C1285" s="56" t="s">
-        <v>1947</v>
+        <v>1991</v>
       </c>
       <c r="D1285" s="56" t="s">
-        <v>1948</v>
+        <v>1992</v>
       </c>
       <c r="E1285" s="30" t="s">
         <v>119</v>
@@ -65754,17 +65930,17 @@
       <c r="F1285" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="G1285" s="57">
-        <v>18552</v>
+      <c r="G1285" s="75">
+        <v>19055</v>
       </c>
       <c r="H1285" s="15">
-        <v>36476</v>
+        <v>83425</v>
       </c>
       <c r="I1285" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J1285" s="15" t="s">
-        <v>49</v>
+      <c r="J1285" s="52" t="s">
+        <v>776</v>
       </c>
       <c r="K1285" s="17" t="s">
         <v>12</v>
@@ -65775,8 +65951,8 @@
       <c r="O1285" s="18"/>
       <c r="P1285" s="18"/>
       <c r="Q1285" s="18"/>
-      <c r="R1285" s="20" t="s">
-        <v>11</v>
+      <c r="R1285" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="1286" spans="1:18" ht="15" thickBot="1">
@@ -65787,28 +65963,28 @@
         <v>46244</v>
       </c>
       <c r="C1286" s="56" t="s">
-        <v>1949</v>
-      </c>
-      <c r="D1286" s="56">
-        <v>132109131</v>
-      </c>
-      <c r="E1286" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1286" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1286" s="57">
-        <v>1052</v>
+        <v>1993</v>
+      </c>
+      <c r="D1286" s="56" t="s">
+        <v>1994</v>
+      </c>
+      <c r="E1286" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1286" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1286" s="75">
+        <v>38691</v>
       </c>
       <c r="H1286" s="15">
-        <v>2979</v>
+        <v>57004</v>
       </c>
       <c r="I1286" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J1286" s="15" t="s">
-        <v>715</v>
+      <c r="J1286" s="52" t="s">
+        <v>776</v>
       </c>
       <c r="K1286" s="17" t="s">
         <v>12</v>
@@ -65819,93 +65995,101 @@
       <c r="O1286" s="18"/>
       <c r="P1286" s="18"/>
       <c r="Q1286" s="18"/>
-      <c r="R1286" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1287" spans="1:18" ht="15" thickBot="1">
+      <c r="R1286" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1287" s="2">
         <v>1286</v>
       </c>
-      <c r="B1287" s="75">
+      <c r="B1287" s="10">
         <v>46244</v>
       </c>
-      <c r="C1287" s="76" t="s">
-        <v>1950</v>
-      </c>
-      <c r="D1287" s="76" t="s">
-        <v>1951</v>
-      </c>
-      <c r="E1287" s="85" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1287" s="86" t="s">
+      <c r="C1287" s="56" t="s">
+        <v>1995</v>
+      </c>
+      <c r="D1287" s="56" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E1287" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1287" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="G1287" s="78">
-        <v>20603</v>
-      </c>
-      <c r="H1287" s="79">
-        <v>11429</v>
-      </c>
-      <c r="I1287" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1287" s="79" t="s">
-        <v>130</v>
-      </c>
-      <c r="K1287" s="80" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1287" s="81"/>
-      <c r="M1287" s="81"/>
-      <c r="N1287" s="82"/>
-      <c r="O1287" s="81"/>
-      <c r="P1287" s="81"/>
-      <c r="Q1287" s="81"/>
-      <c r="R1287" s="81"/>
+      <c r="G1287" s="75">
+        <v>27098</v>
+      </c>
+      <c r="H1287" s="15">
+        <v>25544</v>
+      </c>
+      <c r="I1287" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1287" s="15" t="s">
+        <v>1997</v>
+      </c>
+      <c r="K1287" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1287" s="18"/>
+      <c r="M1287" s="18"/>
+      <c r="N1287" s="40"/>
+      <c r="O1287" s="18"/>
+      <c r="P1287" s="18"/>
+      <c r="Q1287" s="11">
+        <v>95691585</v>
+      </c>
+      <c r="R1287" s="22" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="1288" spans="1:18" ht="15" thickBot="1">
       <c r="A1288" s="2">
         <v>1287</v>
       </c>
-      <c r="B1288" s="75">
+      <c r="B1288" s="10">
         <v>46244</v>
       </c>
-      <c r="C1288" s="76" t="s">
-        <v>1952</v>
-      </c>
-      <c r="D1288" s="76" t="s">
-        <v>1953</v>
-      </c>
-      <c r="E1288" s="85" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1288" s="86" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1288" s="78">
-        <v>82557</v>
-      </c>
-      <c r="H1288" s="79">
-        <v>23835</v>
-      </c>
-      <c r="I1288" s="87" t="s">
-        <v>563</v>
-      </c>
-      <c r="J1288" s="88" t="s">
-        <v>564</v>
-      </c>
-      <c r="K1288" s="81"/>
-      <c r="L1288" s="81"/>
-      <c r="M1288" s="81"/>
-      <c r="N1288" s="82"/>
-      <c r="O1288" s="81"/>
-      <c r="P1288" s="81"/>
-      <c r="Q1288" s="81"/>
-      <c r="R1288" s="81"/>
-    </row>
-    <row r="1289" spans="1:18" ht="15" thickBot="1">
+      <c r="C1288" s="56" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D1288" s="56">
+        <v>112067329</v>
+      </c>
+      <c r="E1288" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1288" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1288" s="57">
+        <v>2968</v>
+      </c>
+      <c r="H1288" s="15">
+        <v>5613</v>
+      </c>
+      <c r="I1288" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1288" s="15" t="s">
+        <v>839</v>
+      </c>
+      <c r="K1288" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1288" s="18"/>
+      <c r="M1288" s="18"/>
+      <c r="N1288" s="40"/>
+      <c r="O1288" s="18"/>
+      <c r="P1288" s="18"/>
+      <c r="Q1288" s="18"/>
+      <c r="R1288" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:18" ht="27.6" thickBot="1">
       <c r="A1289" s="2">
         <v>1288</v>
       </c>
@@ -65913,10 +66097,10 @@
         <v>46244</v>
       </c>
       <c r="C1289" s="56" t="s">
-        <v>1102</v>
+        <v>1875</v>
       </c>
       <c r="D1289" s="56">
-        <v>107774476</v>
+        <v>116806083</v>
       </c>
       <c r="E1289" s="12" t="s">
         <v>21</v>
@@ -65925,27 +66109,33 @@
         <v>122</v>
       </c>
       <c r="G1289" s="57">
-        <v>3561</v>
+        <v>442</v>
       </c>
       <c r="H1289" s="15">
-        <v>5702</v>
-      </c>
-      <c r="I1289" s="22" t="s">
-        <v>563</v>
-      </c>
-      <c r="J1289" s="51" t="s">
-        <v>564</v>
-      </c>
-      <c r="K1289" s="18"/>
+        <v>7536</v>
+      </c>
+      <c r="I1289" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1289" s="15" t="s">
+        <v>950</v>
+      </c>
+      <c r="K1289" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1289" s="18"/>
       <c r="M1289" s="18"/>
       <c r="N1289" s="40"/>
       <c r="O1289" s="18"/>
       <c r="P1289" s="18"/>
-      <c r="Q1289" s="18"/>
-      <c r="R1289" s="18"/>
-    </row>
-    <row r="1290" spans="1:18" ht="27.6" thickBot="1">
+      <c r="Q1289" s="11">
+        <v>79997138</v>
+      </c>
+      <c r="R1289" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:18" ht="15" thickBot="1">
       <c r="A1290" s="2">
         <v>1289</v>
       </c>
@@ -65953,39 +66143,43 @@
         <v>46244</v>
       </c>
       <c r="C1290" s="56" t="s">
-        <v>1954</v>
-      </c>
-      <c r="D1290" s="56" t="s">
-        <v>1955</v>
+        <v>1876</v>
+      </c>
+      <c r="D1290" s="56">
+        <v>113458078</v>
       </c>
       <c r="E1290" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1290" s="13" t="s">
-        <v>22</v>
+      <c r="F1290" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1290" s="57">
-        <v>22319</v>
+        <v>5913</v>
       </c>
       <c r="H1290" s="15">
-        <v>19801</v>
-      </c>
-      <c r="I1290" s="22" t="s">
-        <v>563</v>
-      </c>
-      <c r="J1290" s="51" t="s">
-        <v>564</v>
-      </c>
-      <c r="K1290" s="18"/>
+        <v>1154</v>
+      </c>
+      <c r="I1290" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1290" s="15" t="s">
+        <v>950</v>
+      </c>
+      <c r="K1290" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1290" s="18"/>
       <c r="M1290" s="18"/>
       <c r="N1290" s="40"/>
       <c r="O1290" s="18"/>
       <c r="P1290" s="18"/>
       <c r="Q1290" s="18"/>
-      <c r="R1290" s="18"/>
-    </row>
-    <row r="1291" spans="1:18" ht="28.2" thickBot="1">
+      <c r="R1290" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:18" ht="27.6" thickBot="1">
       <c r="A1291" s="2">
         <v>1290</v>
       </c>
@@ -65993,28 +66187,28 @@
         <v>46244</v>
       </c>
       <c r="C1291" s="56" t="s">
-        <v>1956</v>
+        <v>638</v>
       </c>
       <c r="D1291" s="56">
-        <v>36336406</v>
-      </c>
-      <c r="E1291" s="37" t="s">
-        <v>121</v>
+        <v>122952217</v>
+      </c>
+      <c r="E1291" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="F1291" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1291" s="57">
-        <v>1965</v>
+        <v>4581</v>
       </c>
       <c r="H1291" s="15">
-        <v>826</v>
-      </c>
-      <c r="I1291" s="15" t="s">
-        <v>123</v>
+        <v>-8325</v>
+      </c>
+      <c r="I1291" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="J1291" s="15" t="s">
-        <v>1058</v>
+        <v>950</v>
       </c>
       <c r="K1291" s="17" t="s">
         <v>12</v>
@@ -66024,10 +66218,14 @@
       <c r="N1291" s="40"/>
       <c r="O1291" s="18"/>
       <c r="P1291" s="18"/>
-      <c r="Q1291" s="18"/>
-      <c r="R1291" s="18"/>
-    </row>
-    <row r="1292" spans="1:18" ht="28.2" thickBot="1">
+      <c r="Q1291" s="11" t="s">
+        <v>1877</v>
+      </c>
+      <c r="R1291" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:18" ht="15" thickBot="1">
       <c r="A1292" s="2">
         <v>1291</v>
       </c>
@@ -66035,28 +66233,28 @@
         <v>46244</v>
       </c>
       <c r="C1292" s="56" t="s">
-        <v>1957</v>
+        <v>1878</v>
       </c>
       <c r="D1292" s="56">
-        <v>17065948</v>
-      </c>
-      <c r="E1292" s="37" t="s">
-        <v>121</v>
+        <v>126214395</v>
+      </c>
+      <c r="E1292" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="F1292" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1292" s="57">
-        <v>5788</v>
+        <v>355</v>
       </c>
       <c r="H1292" s="15">
-        <v>9112</v>
-      </c>
-      <c r="I1292" s="15" t="s">
-        <v>123</v>
+        <v>2278</v>
+      </c>
+      <c r="I1292" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="J1292" s="15" t="s">
-        <v>1058</v>
+        <v>950</v>
       </c>
       <c r="K1292" s="17" t="s">
         <v>12</v>
@@ -66067,7 +66265,9 @@
       <c r="O1292" s="18"/>
       <c r="P1292" s="18"/>
       <c r="Q1292" s="18"/>
-      <c r="R1292" s="18"/>
+      <c r="R1292" s="20" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1293" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1293" s="2">
@@ -66077,28 +66277,28 @@
         <v>46244</v>
       </c>
       <c r="C1293" s="56" t="s">
-        <v>1958</v>
-      </c>
-      <c r="D1293" s="56">
-        <v>3084818</v>
-      </c>
-      <c r="E1293" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="F1293" s="16" t="s">
-        <v>122</v>
+        <v>47</v>
+      </c>
+      <c r="D1293" s="56" t="s">
+        <v>1879</v>
+      </c>
+      <c r="E1293" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1293" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1293" s="57">
-        <v>6300</v>
+        <v>33404</v>
       </c>
       <c r="H1293" s="15">
-        <v>8487</v>
-      </c>
-      <c r="I1293" s="15" t="s">
-        <v>123</v>
+        <v>89137</v>
+      </c>
+      <c r="I1293" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="J1293" s="15" t="s">
-        <v>1058</v>
+        <v>1880</v>
       </c>
       <c r="K1293" s="17" t="s">
         <v>12</v>
@@ -66108,8 +66308,12 @@
       <c r="N1293" s="40"/>
       <c r="O1293" s="18"/>
       <c r="P1293" s="18"/>
-      <c r="Q1293" s="18"/>
-      <c r="R1293" s="18"/>
+      <c r="Q1293" s="11">
+        <v>95643750</v>
+      </c>
+      <c r="R1293" s="20" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1294" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1294" s="2">
@@ -66119,28 +66323,28 @@
         <v>46244</v>
       </c>
       <c r="C1294" s="56" t="s">
-        <v>1959</v>
-      </c>
-      <c r="D1294" s="56">
-        <v>2144791</v>
-      </c>
-      <c r="E1294" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="F1294" s="16" t="s">
-        <v>122</v>
+        <v>504</v>
+      </c>
+      <c r="D1294" s="56" t="s">
+        <v>1881</v>
+      </c>
+      <c r="E1294" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1294" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1294" s="57">
-        <v>1598</v>
+        <v>7606</v>
       </c>
       <c r="H1294" s="15">
-        <v>3380</v>
-      </c>
-      <c r="I1294" s="15" t="s">
-        <v>123</v>
+        <v>66793</v>
+      </c>
+      <c r="I1294" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="J1294" s="15" t="s">
-        <v>1058</v>
+        <v>1880</v>
       </c>
       <c r="K1294" s="17" t="s">
         <v>12</v>
@@ -66150,10 +66354,14 @@
       <c r="N1294" s="40"/>
       <c r="O1294" s="18"/>
       <c r="P1294" s="18"/>
-      <c r="Q1294" s="18"/>
-      <c r="R1294" s="18"/>
-    </row>
-    <row r="1295" spans="1:18" ht="28.2" thickBot="1">
+      <c r="Q1294" s="11">
+        <v>501924525</v>
+      </c>
+      <c r="R1294" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:18" ht="27.6" thickBot="1">
       <c r="A1295" s="2">
         <v>1294</v>
       </c>
@@ -66161,28 +66369,28 @@
         <v>46244</v>
       </c>
       <c r="C1295" s="56" t="s">
-        <v>1960</v>
+        <v>906</v>
       </c>
       <c r="D1295" s="56">
-        <v>12571732</v>
-      </c>
-      <c r="E1295" s="37" t="s">
-        <v>121</v>
+        <v>128333109</v>
+      </c>
+      <c r="E1295" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="F1295" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1295" s="57">
-        <v>8884</v>
+        <v>4900</v>
       </c>
       <c r="H1295" s="15">
-        <v>8169</v>
-      </c>
-      <c r="I1295" s="15" t="s">
-        <v>123</v>
+        <v>-6338</v>
+      </c>
+      <c r="I1295" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="J1295" s="15" t="s">
-        <v>1058</v>
+        <v>890</v>
       </c>
       <c r="K1295" s="17" t="s">
         <v>12</v>
@@ -66192,10 +66400,14 @@
       <c r="N1295" s="40"/>
       <c r="O1295" s="18"/>
       <c r="P1295" s="18"/>
-      <c r="Q1295" s="18"/>
-      <c r="R1295" s="18"/>
-    </row>
-    <row r="1296" spans="1:18" ht="28.2" thickBot="1">
+      <c r="Q1295" s="11">
+        <v>95609530</v>
+      </c>
+      <c r="R1295" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:18" ht="15" thickBot="1">
       <c r="A1296" s="2">
         <v>1295</v>
       </c>
@@ -66203,28 +66415,28 @@
         <v>46244</v>
       </c>
       <c r="C1296" s="56" t="s">
-        <v>1961</v>
+        <v>1894</v>
       </c>
       <c r="D1296" s="56">
-        <v>96995164</v>
-      </c>
-      <c r="E1296" s="37" t="s">
-        <v>121</v>
+        <v>116033629</v>
+      </c>
+      <c r="E1296" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="F1296" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1296" s="57">
-        <v>8884</v>
+        <v>1702</v>
       </c>
       <c r="H1296" s="15">
-        <v>8169</v>
-      </c>
-      <c r="I1296" s="15" t="s">
-        <v>123</v>
+        <v>5164</v>
+      </c>
+      <c r="I1296" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="J1296" s="15" t="s">
-        <v>1058</v>
+        <v>950</v>
       </c>
       <c r="K1296" s="17" t="s">
         <v>12</v>
@@ -66234,82 +66446,730 @@
       <c r="N1296" s="40"/>
       <c r="O1296" s="18"/>
       <c r="P1296" s="18"/>
-      <c r="Q1296" s="18"/>
-      <c r="R1296" s="18"/>
-    </row>
-    <row r="1297" spans="1:18" ht="15" thickBot="1">
+      <c r="Q1296" s="11">
+        <v>94250210</v>
+      </c>
+      <c r="R1296" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:18" ht="27.6" thickBot="1">
       <c r="A1297" s="2">
         <v>1296</v>
       </c>
-      <c r="B1297" s="75">
+      <c r="B1297" s="10">
         <v>46244</v>
       </c>
-      <c r="C1297" s="76" t="s">
-        <v>1962</v>
-      </c>
-      <c r="D1297" s="76" t="s">
-        <v>1963</v>
-      </c>
-      <c r="E1297" s="85" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1297" s="86" t="s">
+      <c r="C1297" s="56" t="s">
+        <v>1895</v>
+      </c>
+      <c r="D1297" s="56" t="s">
+        <v>1896</v>
+      </c>
+      <c r="E1297" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1297" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="G1297" s="78">
-        <v>71861</v>
-      </c>
-      <c r="H1297" s="79">
-        <v>38386</v>
-      </c>
-      <c r="I1297" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1297" s="79" t="s">
-        <v>127</v>
-      </c>
-      <c r="K1297" s="89" t="s">
-        <v>1189</v>
-      </c>
-      <c r="L1297" s="81"/>
-      <c r="M1297" s="81"/>
-      <c r="N1297" s="82"/>
-      <c r="O1297" s="81"/>
-      <c r="P1297" s="81"/>
-      <c r="Q1297" s="83">
-        <v>77439516</v>
-      </c>
-      <c r="R1297" s="84" t="s">
+      <c r="G1297" s="57">
+        <v>21668</v>
+      </c>
+      <c r="H1297" s="15">
+        <v>75184</v>
+      </c>
+      <c r="I1297" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1297" s="15" t="s">
+        <v>1897</v>
+      </c>
+      <c r="K1297" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1297" s="18"/>
+      <c r="M1297" s="18"/>
+      <c r="N1297" s="40"/>
+      <c r="O1297" s="18"/>
+      <c r="P1297" s="18"/>
+      <c r="Q1297" s="11">
+        <v>557824163</v>
+      </c>
+      <c r="R1297" s="20" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="1298" spans="1:18" ht="15" thickBot="1">
+    <row r="1298" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1298" s="2">
         <v>1297</v>
       </c>
-      <c r="B1298" s="75">
+      <c r="B1298" s="10">
         <v>46244</v>
       </c>
-      <c r="C1298" s="90"/>
-      <c r="D1298" s="90"/>
-      <c r="E1298" s="81"/>
-      <c r="F1298" s="81"/>
-      <c r="G1298" s="78">
-        <v>9125</v>
-      </c>
-      <c r="H1298" s="79">
-        <v>988</v>
-      </c>
-      <c r="I1298" s="81"/>
-      <c r="J1298" s="81"/>
-      <c r="K1298" s="81"/>
-      <c r="L1298" s="81"/>
-      <c r="M1298" s="81"/>
-      <c r="N1298" s="82"/>
-      <c r="O1298" s="81"/>
-      <c r="P1298" s="81"/>
-      <c r="Q1298" s="81"/>
-      <c r="R1298" s="81"/>
+      <c r="C1298" s="56" t="s">
+        <v>1898</v>
+      </c>
+      <c r="D1298" s="56" t="s">
+        <v>1899</v>
+      </c>
+      <c r="E1298" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1298" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1298" s="57">
+        <v>9215</v>
+      </c>
+      <c r="H1298" s="15">
+        <v>10278</v>
+      </c>
+      <c r="I1298" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1298" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1298" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1298" s="18"/>
+      <c r="M1298" s="18"/>
+      <c r="N1298" s="40"/>
+      <c r="O1298" s="18"/>
+      <c r="P1298" s="18"/>
+      <c r="Q1298" s="18"/>
+      <c r="R1298" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1299" s="2">
+        <v>1298</v>
+      </c>
+      <c r="B1299" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1299" s="56" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D1299" s="56" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E1299" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1299" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1299" s="57">
+        <v>53578</v>
+      </c>
+      <c r="H1299" s="15">
+        <v>46411</v>
+      </c>
+      <c r="I1299" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1299" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1299" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1299" s="18"/>
+      <c r="M1299" s="18"/>
+      <c r="N1299" s="40"/>
+      <c r="O1299" s="18"/>
+      <c r="P1299" s="18"/>
+      <c r="Q1299" s="18"/>
+      <c r="R1299" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:18" ht="15" thickBot="1">
+      <c r="A1300" s="2">
+        <v>1299</v>
+      </c>
+      <c r="B1300" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1300" s="56" t="s">
+        <v>1902</v>
+      </c>
+      <c r="D1300" s="56" t="s">
+        <v>1903</v>
+      </c>
+      <c r="E1300" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1300" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1300" s="57">
+        <v>68833</v>
+      </c>
+      <c r="H1300" s="15">
+        <v>78793</v>
+      </c>
+      <c r="I1300" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1300" s="15" t="s">
+        <v>1904</v>
+      </c>
+      <c r="K1300" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1300" s="18"/>
+      <c r="M1300" s="18"/>
+      <c r="N1300" s="40"/>
+      <c r="O1300" s="18"/>
+      <c r="P1300" s="18"/>
+      <c r="Q1300" s="11">
+        <v>554186760</v>
+      </c>
+      <c r="R1300" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:18" ht="15" thickBot="1">
+      <c r="A1301" s="2">
+        <v>1300</v>
+      </c>
+      <c r="B1301" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1301" s="56" t="s">
+        <v>1905</v>
+      </c>
+      <c r="D1301" s="56" t="s">
+        <v>1906</v>
+      </c>
+      <c r="E1301" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1301" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1301" s="57">
+        <v>56757</v>
+      </c>
+      <c r="H1301" s="15" t="s">
+        <v>1907</v>
+      </c>
+      <c r="I1301" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1301" s="15" t="s">
+        <v>1904</v>
+      </c>
+      <c r="K1301" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1301" s="18"/>
+      <c r="M1301" s="18"/>
+      <c r="N1301" s="40"/>
+      <c r="O1301" s="18"/>
+      <c r="P1301" s="18"/>
+      <c r="Q1301" s="11">
+        <v>76969759</v>
+      </c>
+      <c r="R1301" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1302" s="2">
+        <v>1301</v>
+      </c>
+      <c r="B1302" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1302" s="56" t="s">
+        <v>1908</v>
+      </c>
+      <c r="D1302" s="56" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1302" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1302" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1302" s="57">
+        <v>61918</v>
+      </c>
+      <c r="H1302" s="15">
+        <v>19939</v>
+      </c>
+      <c r="I1302" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1302" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K1302" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1302" s="18"/>
+      <c r="M1302" s="18"/>
+      <c r="N1302" s="40"/>
+      <c r="O1302" s="18"/>
+      <c r="P1302" s="18"/>
+      <c r="Q1302" s="18"/>
+      <c r="R1302" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1303" s="2">
+        <v>1302</v>
+      </c>
+      <c r="B1303" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1303" s="56" t="s">
+        <v>1910</v>
+      </c>
+      <c r="D1303" s="56" t="s">
+        <v>1911</v>
+      </c>
+      <c r="E1303" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1303" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1303" s="57">
+        <v>8490</v>
+      </c>
+      <c r="H1303" s="15">
+        <v>8101</v>
+      </c>
+      <c r="I1303" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1303" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="K1303" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1303" s="18"/>
+      <c r="M1303" s="18"/>
+      <c r="N1303" s="40"/>
+      <c r="O1303" s="18"/>
+      <c r="P1303" s="18"/>
+      <c r="Q1303" s="11">
+        <v>98705284</v>
+      </c>
+      <c r="R1303" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1304" s="2">
+        <v>1303</v>
+      </c>
+      <c r="B1304" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1304" s="56" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D1304" s="56" t="s">
+        <v>1948</v>
+      </c>
+      <c r="E1304" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1304" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1304" s="57">
+        <v>18552</v>
+      </c>
+      <c r="H1304" s="15">
+        <v>36476</v>
+      </c>
+      <c r="I1304" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1304" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1304" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1304" s="18"/>
+      <c r="M1304" s="18"/>
+      <c r="N1304" s="40"/>
+      <c r="O1304" s="18"/>
+      <c r="P1304" s="18"/>
+      <c r="Q1304" s="18"/>
+      <c r="R1304" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:18" ht="15" thickBot="1">
+      <c r="A1305" s="2">
+        <v>1304</v>
+      </c>
+      <c r="B1305" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1305" s="56" t="s">
+        <v>1949</v>
+      </c>
+      <c r="D1305" s="56">
+        <v>132109131</v>
+      </c>
+      <c r="E1305" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1305" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1305" s="57">
+        <v>1052</v>
+      </c>
+      <c r="H1305" s="15">
+        <v>2979</v>
+      </c>
+      <c r="I1305" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1305" s="15" t="s">
+        <v>715</v>
+      </c>
+      <c r="K1305" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1305" s="18"/>
+      <c r="M1305" s="18"/>
+      <c r="N1305" s="40"/>
+      <c r="O1305" s="18"/>
+      <c r="P1305" s="18"/>
+      <c r="Q1305" s="18"/>
+      <c r="R1305" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:18" ht="15" thickBot="1">
+      <c r="A1306" s="2">
+        <v>1305</v>
+      </c>
+      <c r="B1306" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1306" s="56" t="s">
+        <v>1962</v>
+      </c>
+      <c r="D1306" s="56" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E1306" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1306" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1306" s="57">
+        <v>71861</v>
+      </c>
+      <c r="H1306" s="15">
+        <v>38386</v>
+      </c>
+      <c r="I1306" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1306" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="K1306" s="61" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1306" s="18"/>
+      <c r="M1306" s="18"/>
+      <c r="N1306" s="40"/>
+      <c r="O1306" s="18"/>
+      <c r="P1306" s="18"/>
+      <c r="Q1306" s="11">
+        <v>77439516</v>
+      </c>
+      <c r="R1306" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:18" ht="15" thickBot="1">
+      <c r="A1307" s="2">
+        <v>1306</v>
+      </c>
+      <c r="B1307" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1307" s="56" t="s">
+        <v>1998</v>
+      </c>
+      <c r="D1307" s="56">
+        <v>105256785</v>
+      </c>
+      <c r="E1307" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1307" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1307" s="57">
+        <v>587</v>
+      </c>
+      <c r="H1307" s="15">
+        <v>-9022</v>
+      </c>
+      <c r="I1307" s="59" t="s">
+        <v>1177</v>
+      </c>
+      <c r="J1307" s="18"/>
+      <c r="K1307" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1307" s="18"/>
+      <c r="M1307" s="16" t="s">
+        <v>1999</v>
+      </c>
+      <c r="N1307" s="40"/>
+      <c r="O1307" s="18"/>
+      <c r="P1307" s="18"/>
+      <c r="Q1307" s="18"/>
+      <c r="R1307" s="16" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:18" ht="15" thickBot="1">
+      <c r="A1308" s="2">
+        <v>1307</v>
+      </c>
+      <c r="B1308" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1308" s="56" t="s">
+        <v>2000</v>
+      </c>
+      <c r="D1308" s="56">
+        <v>65444142</v>
+      </c>
+      <c r="E1308" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1308" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1308" s="57">
+        <v>2227</v>
+      </c>
+      <c r="H1308" s="15">
+        <v>-9283</v>
+      </c>
+      <c r="I1308" s="59" t="s">
+        <v>1177</v>
+      </c>
+      <c r="J1308" s="18"/>
+      <c r="K1308" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1308" s="18"/>
+      <c r="M1308" s="16" t="s">
+        <v>1999</v>
+      </c>
+      <c r="N1308" s="40"/>
+      <c r="O1308" s="18"/>
+      <c r="P1308" s="18"/>
+      <c r="Q1308" s="18"/>
+      <c r="R1308" s="16" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1309" s="2">
+        <v>1308</v>
+      </c>
+      <c r="B1309" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1309" s="56" t="s">
+        <v>2001</v>
+      </c>
+      <c r="D1309" s="56">
+        <v>99086357</v>
+      </c>
+      <c r="E1309" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1309" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1309" s="57">
+        <v>9268</v>
+      </c>
+      <c r="H1309" s="15">
+        <v>477</v>
+      </c>
+      <c r="I1309" s="59" t="s">
+        <v>1177</v>
+      </c>
+      <c r="J1309" s="18"/>
+      <c r="K1309" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1309" s="18"/>
+      <c r="M1309" s="16" t="s">
+        <v>1999</v>
+      </c>
+      <c r="N1309" s="40"/>
+      <c r="O1309" s="18"/>
+      <c r="P1309" s="18"/>
+      <c r="Q1309" s="18"/>
+      <c r="R1309" s="16" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:18" ht="15" thickBot="1">
+      <c r="A1310" s="2">
+        <v>1309</v>
+      </c>
+      <c r="B1310" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1310" s="56" t="s">
+        <v>2002</v>
+      </c>
+      <c r="D1310" s="56">
+        <v>68572777</v>
+      </c>
+      <c r="E1310" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1310" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1310" s="57">
+        <v>2295</v>
+      </c>
+      <c r="H1310" s="15">
+        <v>970</v>
+      </c>
+      <c r="I1310" s="59" t="s">
+        <v>1177</v>
+      </c>
+      <c r="J1310" s="18"/>
+      <c r="K1310" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1310" s="18"/>
+      <c r="M1310" s="16" t="s">
+        <v>1999</v>
+      </c>
+      <c r="N1310" s="40"/>
+      <c r="O1310" s="18"/>
+      <c r="P1310" s="18"/>
+      <c r="Q1310" s="18"/>
+      <c r="R1310" s="16" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1311" s="2">
+        <v>1310</v>
+      </c>
+      <c r="B1311" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1311" s="56" t="s">
+        <v>2003</v>
+      </c>
+      <c r="D1311" s="56">
+        <v>2232021</v>
+      </c>
+      <c r="E1311" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1311" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1311" s="75">
+        <v>8606</v>
+      </c>
+      <c r="H1311" s="76">
+        <v>9540</v>
+      </c>
+      <c r="I1311" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1311" s="15" t="s">
+        <v>2004</v>
+      </c>
+      <c r="K1311" s="61" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1311" s="18"/>
+      <c r="M1311" s="18"/>
+      <c r="N1311" s="40"/>
+      <c r="O1311" s="18"/>
+      <c r="P1311" s="18"/>
+      <c r="Q1311" s="11">
+        <v>99727424</v>
+      </c>
+      <c r="R1311" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1312" s="2">
+        <v>1311</v>
+      </c>
+      <c r="B1312" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1312" s="56" t="s">
+        <v>2005</v>
+      </c>
+      <c r="D1312" s="56">
+        <v>75278541</v>
+      </c>
+      <c r="E1312" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1312" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1312" s="75">
+        <v>1802</v>
+      </c>
+      <c r="H1312" s="76">
+        <v>7412</v>
+      </c>
+      <c r="I1312" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1312" s="15" t="s">
+        <v>2004</v>
+      </c>
+      <c r="K1312" s="61" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1312" s="18"/>
+      <c r="M1312" s="18"/>
+      <c r="N1312" s="40"/>
+      <c r="O1312" s="18"/>
+      <c r="P1312" s="18"/>
+      <c r="Q1312" s="11">
+        <v>79294748</v>
+      </c>
+      <c r="R1312" s="20" t="s">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D85D26A-9233-43B7-A3AD-4E0FDEE167AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAAC3FBA-21A9-45E9-BC77-87BCA0849890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9749" uniqueCount="2006">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10058" uniqueCount="2061">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -6056,6 +6056,171 @@
   </si>
   <si>
     <t>ZAID HUSSAIN</t>
+  </si>
+  <si>
+    <t>MAJID SULAIMAN</t>
+  </si>
+  <si>
+    <t>ABDULLAH SAIF</t>
+  </si>
+  <si>
+    <t>KHALIFA MOHAMMED</t>
+  </si>
+  <si>
+    <t>OMER SALIM</t>
+  </si>
+  <si>
+    <t>HAMOOD MOHAMMED</t>
+  </si>
+  <si>
+    <t>SOHAIL FURQAN</t>
+  </si>
+  <si>
+    <t>DU5193745</t>
+  </si>
+  <si>
+    <t>QADIR</t>
+  </si>
+  <si>
+    <t>AT4429465</t>
+  </si>
+  <si>
+    <t>AJMAL</t>
+  </si>
+  <si>
+    <t>AF1554574</t>
+  </si>
+  <si>
+    <t>25323-</t>
+  </si>
+  <si>
+    <t>SAJAWAL KHAN</t>
+  </si>
+  <si>
+    <t>RK4115355</t>
+  </si>
+  <si>
+    <t>ABRAR AHMED</t>
+  </si>
+  <si>
+    <t>FP1159426</t>
+  </si>
+  <si>
+    <t>ADIL ARSHID</t>
+  </si>
+  <si>
+    <t>ABY SUFYAN</t>
+  </si>
+  <si>
+    <t>ZAIN RAFAQAT</t>
+  </si>
+  <si>
+    <t>ADEEL IQBAL</t>
+  </si>
+  <si>
+    <t>IMRAN ASMAT</t>
+  </si>
+  <si>
+    <t>ALI HUSNAIN</t>
+  </si>
+  <si>
+    <t>5549-</t>
+  </si>
+  <si>
+    <t>AMIR KHAN</t>
+  </si>
+  <si>
+    <t>EP4146523</t>
+  </si>
+  <si>
+    <t>AYUUB</t>
+  </si>
+  <si>
+    <t>IBRAR HUSAIN</t>
+  </si>
+  <si>
+    <t>DR6891897</t>
+  </si>
+  <si>
+    <t>ANAM AMAN</t>
+  </si>
+  <si>
+    <t>GE1200132</t>
+  </si>
+  <si>
+    <t>MAJID HUSSAIN</t>
+  </si>
+  <si>
+    <t>SHAHZAB</t>
+  </si>
+  <si>
+    <t>978-</t>
+  </si>
+  <si>
+    <t>MUKHTAR</t>
+  </si>
+  <si>
+    <t>KAMRAN MASIH</t>
+  </si>
+  <si>
+    <t>IRFAN ABDUL</t>
+  </si>
+  <si>
+    <t>UMAER</t>
+  </si>
+  <si>
+    <t>8872-</t>
+  </si>
+  <si>
+    <t>YOUSUF</t>
+  </si>
+  <si>
+    <t>3547-</t>
+  </si>
+  <si>
+    <t>RAMEEZ AFZAL</t>
+  </si>
+  <si>
+    <t>HASEEB SADIQ</t>
+  </si>
+  <si>
+    <t>DW5464204</t>
+  </si>
+  <si>
+    <t>ZAHID</t>
+  </si>
+  <si>
+    <t>DF5178594</t>
+  </si>
+  <si>
+    <t>MUSHTAQ</t>
+  </si>
+  <si>
+    <t>JUNAID KHALID</t>
+  </si>
+  <si>
+    <t>9754-</t>
+  </si>
+  <si>
+    <t>USMAN SAQIB</t>
+  </si>
+  <si>
+    <t>AZMAT ALI</t>
+  </si>
+  <si>
+    <t>ANEES</t>
+  </si>
+  <si>
+    <t>RAFIQUE</t>
+  </si>
+  <si>
+    <t>RAJA ZAHID</t>
+  </si>
+  <si>
+    <t>NASIR HAMEED</t>
+  </si>
+  <si>
+    <t>SADDAM</t>
   </si>
 </sst>
 </file>
@@ -6432,7 +6597,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6661,6 +6826,30 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6976,7 +7165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1312"/>
+  <dimension ref="A1:R1361"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -16170,10 +16359,12 @@
       <c r="J193" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="K193" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L193" s="18"/>
+      <c r="K193" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L193" s="54">
+        <v>46250</v>
+      </c>
       <c r="M193" s="18"/>
       <c r="N193" s="40"/>
       <c r="O193" s="18"/>
@@ -17002,10 +17193,12 @@
       <c r="J211" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="K211" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L211" s="18"/>
+      <c r="K211" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L211" s="54">
+        <v>46250</v>
+      </c>
       <c r="M211" s="18"/>
       <c r="N211" s="40"/>
       <c r="O211" s="18"/>
@@ -17048,10 +17241,12 @@
       <c r="J212" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="K212" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L212" s="18"/>
+      <c r="K212" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L212" s="54">
+        <v>46250</v>
+      </c>
       <c r="M212" s="18"/>
       <c r="N212" s="40"/>
       <c r="O212" s="18"/>
@@ -17094,10 +17289,12 @@
       <c r="J213" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="K213" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L213" s="18"/>
+      <c r="K213" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L213" s="54">
+        <v>46250</v>
+      </c>
       <c r="M213" s="18"/>
       <c r="N213" s="40"/>
       <c r="O213" s="18"/>
@@ -17140,10 +17337,12 @@
       <c r="J214" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="K214" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L214" s="18"/>
+      <c r="K214" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L214" s="54">
+        <v>46250</v>
+      </c>
       <c r="M214" s="18"/>
       <c r="N214" s="55">
         <v>54</v>
@@ -17236,10 +17435,12 @@
       <c r="J216" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="K216" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L216" s="18"/>
+      <c r="K216" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L216" s="54">
+        <v>46250</v>
+      </c>
       <c r="M216" s="18"/>
       <c r="N216" s="55">
         <v>57</v>
@@ -17332,10 +17533,12 @@
       <c r="J218" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="K218" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L218" s="18"/>
+      <c r="K218" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L218" s="54">
+        <v>46248</v>
+      </c>
       <c r="M218" s="18"/>
       <c r="N218" s="40"/>
       <c r="O218" s="18"/>
@@ -17378,10 +17581,12 @@
       <c r="J219" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="K219" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L219" s="18"/>
+      <c r="K219" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L219" s="54">
+        <v>46248</v>
+      </c>
       <c r="M219" s="18"/>
       <c r="N219" s="55">
         <v>229</v>
@@ -17820,10 +18025,12 @@
         <v>485</v>
       </c>
       <c r="J229" s="18"/>
-      <c r="K229" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L229" s="18"/>
+      <c r="K229" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L229" s="54">
+        <v>46250</v>
+      </c>
       <c r="M229" s="18"/>
       <c r="N229" s="40"/>
       <c r="O229" s="18"/>
@@ -17864,10 +18071,12 @@
         <v>485</v>
       </c>
       <c r="J230" s="18"/>
-      <c r="K230" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L230" s="18"/>
+      <c r="K230" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L230" s="54">
+        <v>46250</v>
+      </c>
       <c r="M230" s="18"/>
       <c r="N230" s="40"/>
       <c r="O230" s="18"/>
@@ -17906,10 +18115,12 @@
         <v>485</v>
       </c>
       <c r="J231" s="18"/>
-      <c r="K231" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L231" s="18"/>
+      <c r="K231" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L231" s="54">
+        <v>46250</v>
+      </c>
       <c r="M231" s="18"/>
       <c r="N231" s="40"/>
       <c r="O231" s="18"/>
@@ -17950,10 +18161,12 @@
         <v>485</v>
       </c>
       <c r="J232" s="18"/>
-      <c r="K232" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L232" s="18"/>
+      <c r="K232" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L232" s="54">
+        <v>46250</v>
+      </c>
       <c r="M232" s="18"/>
       <c r="N232" s="40"/>
       <c r="O232" s="18"/>
@@ -22718,10 +22931,12 @@
       <c r="J334" s="15" t="s">
         <v>549</v>
       </c>
-      <c r="K334" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L334" s="18"/>
+      <c r="K334" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L334" s="54">
+        <v>46250</v>
+      </c>
       <c r="M334" s="18"/>
       <c r="N334" s="40"/>
       <c r="O334" s="18"/>
@@ -24338,10 +24553,12 @@
       <c r="J369" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="K369" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L369" s="28"/>
+      <c r="K369" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L369" s="66">
+        <v>46250</v>
+      </c>
       <c r="M369" s="28"/>
       <c r="N369" s="28"/>
       <c r="O369" s="28"/>
@@ -26228,10 +26445,12 @@
       <c r="J409" s="15" t="s">
         <v>562</v>
       </c>
-      <c r="K409" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L409" s="18"/>
+      <c r="K409" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L409" s="54">
+        <v>46250</v>
+      </c>
       <c r="M409" s="18"/>
       <c r="N409" s="55">
         <v>41</v>
@@ -26276,10 +26495,12 @@
       <c r="J410" s="15" t="s">
         <v>562</v>
       </c>
-      <c r="K410" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L410" s="18"/>
+      <c r="K410" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L410" s="54">
+        <v>46250</v>
+      </c>
       <c r="M410" s="18"/>
       <c r="N410" s="55">
         <v>18</v>
@@ -27056,10 +27277,12 @@
       <c r="J427" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="K427" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L427" s="18"/>
+      <c r="K427" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L427" s="54">
+        <v>46250</v>
+      </c>
       <c r="M427" s="18"/>
       <c r="N427" s="55">
         <v>98</v>
@@ -27482,10 +27705,12 @@
       <c r="J436" s="15" t="s">
         <v>848</v>
       </c>
-      <c r="K436" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L436" s="18"/>
+      <c r="K436" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L436" s="54">
+        <v>46250</v>
+      </c>
       <c r="M436" s="18"/>
       <c r="N436" s="55">
         <v>130</v>
@@ -27530,10 +27755,12 @@
       <c r="J437" s="15" t="s">
         <v>848</v>
       </c>
-      <c r="K437" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L437" s="18"/>
+      <c r="K437" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L437" s="54">
+        <v>46250</v>
+      </c>
       <c r="M437" s="18"/>
       <c r="N437" s="55">
         <v>131</v>
@@ -27624,10 +27851,12 @@
       <c r="J439" s="15" t="s">
         <v>848</v>
       </c>
-      <c r="K439" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L439" s="18"/>
+      <c r="K439" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L439" s="54">
+        <v>46250</v>
+      </c>
       <c r="M439" s="18"/>
       <c r="N439" s="55">
         <v>349</v>
@@ -27718,10 +27947,12 @@
       <c r="J441" s="15" t="s">
         <v>848</v>
       </c>
-      <c r="K441" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L441" s="18"/>
+      <c r="K441" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L441" s="54">
+        <v>46250</v>
+      </c>
       <c r="M441" s="18"/>
       <c r="N441" s="55">
         <v>133</v>
@@ -27766,10 +27997,12 @@
       <c r="J442" s="15" t="s">
         <v>848</v>
       </c>
-      <c r="K442" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L442" s="18"/>
+      <c r="K442" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L442" s="54">
+        <v>46250</v>
+      </c>
       <c r="M442" s="18"/>
       <c r="N442" s="55">
         <v>129</v>
@@ -27814,10 +28047,12 @@
       <c r="J443" s="15" t="s">
         <v>848</v>
       </c>
-      <c r="K443" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L443" s="18"/>
+      <c r="K443" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L443" s="54">
+        <v>46250</v>
+      </c>
       <c r="M443" s="18"/>
       <c r="N443" s="55">
         <v>175</v>
@@ -27862,10 +28097,12 @@
       <c r="J444" s="15" t="s">
         <v>848</v>
       </c>
-      <c r="K444" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L444" s="18"/>
+      <c r="K444" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L444" s="54">
+        <v>46250</v>
+      </c>
       <c r="M444" s="18"/>
       <c r="N444" s="40"/>
       <c r="O444" s="18"/>
@@ -27908,10 +28145,12 @@
       <c r="J445" s="15" t="s">
         <v>848</v>
       </c>
-      <c r="K445" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L445" s="18"/>
+      <c r="K445" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L445" s="54">
+        <v>46250</v>
+      </c>
       <c r="M445" s="18"/>
       <c r="N445" s="40"/>
       <c r="O445" s="18"/>
@@ -27954,10 +28193,12 @@
       <c r="J446" s="15" t="s">
         <v>848</v>
       </c>
-      <c r="K446" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L446" s="18"/>
+      <c r="K446" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L446" s="54">
+        <v>46250</v>
+      </c>
       <c r="M446" s="18"/>
       <c r="N446" s="40"/>
       <c r="O446" s="18"/>
@@ -28000,10 +28241,12 @@
       <c r="J447" s="15" t="s">
         <v>848</v>
       </c>
-      <c r="K447" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L447" s="18"/>
+      <c r="K447" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L447" s="54">
+        <v>46250</v>
+      </c>
       <c r="M447" s="18"/>
       <c r="N447" s="40"/>
       <c r="O447" s="18"/>
@@ -28046,10 +28289,12 @@
       <c r="J448" s="15" t="s">
         <v>848</v>
       </c>
-      <c r="K448" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L448" s="18"/>
+      <c r="K448" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L448" s="54">
+        <v>46250</v>
+      </c>
       <c r="M448" s="18"/>
       <c r="N448" s="40"/>
       <c r="O448" s="18"/>
@@ -28092,10 +28337,12 @@
       <c r="J449" s="15" t="s">
         <v>848</v>
       </c>
-      <c r="K449" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L449" s="18"/>
+      <c r="K449" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L449" s="54">
+        <v>46250</v>
+      </c>
       <c r="M449" s="18"/>
       <c r="N449" s="40"/>
       <c r="O449" s="18"/>
@@ -28136,10 +28383,12 @@
       <c r="J450" s="15" t="s">
         <v>848</v>
       </c>
-      <c r="K450" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L450" s="18"/>
+      <c r="K450" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L450" s="54">
+        <v>46250</v>
+      </c>
       <c r="M450" s="18"/>
       <c r="N450" s="40"/>
       <c r="O450" s="18"/>
@@ -28228,10 +28477,12 @@
       <c r="J452" s="15" t="s">
         <v>848</v>
       </c>
-      <c r="K452" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L452" s="18"/>
+      <c r="K452" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L452" s="54">
+        <v>46250</v>
+      </c>
       <c r="M452" s="18"/>
       <c r="N452" s="40"/>
       <c r="O452" s="18"/>
@@ -28464,10 +28715,12 @@
       <c r="J457" s="15" t="s">
         <v>881</v>
       </c>
-      <c r="K457" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L457" s="18"/>
+      <c r="K457" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L457" s="54">
+        <v>46250</v>
+      </c>
       <c r="M457" s="18"/>
       <c r="N457" s="55">
         <v>346</v>
@@ -28512,10 +28765,12 @@
       <c r="J458" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="K458" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L458" s="18"/>
+      <c r="K458" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L458" s="54">
+        <v>46250</v>
+      </c>
       <c r="M458" s="18"/>
       <c r="N458" s="40"/>
       <c r="O458" s="18"/>
@@ -28558,10 +28813,12 @@
       <c r="J459" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="K459" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L459" s="18"/>
+      <c r="K459" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L459" s="54">
+        <v>46250</v>
+      </c>
       <c r="M459" s="18"/>
       <c r="N459" s="55">
         <v>336</v>
@@ -28606,10 +28863,12 @@
       <c r="J460" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="K460" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L460" s="18"/>
+      <c r="K460" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L460" s="54">
+        <v>46250</v>
+      </c>
       <c r="M460" s="18"/>
       <c r="N460" s="55">
         <v>350</v>
@@ -29418,10 +29677,12 @@
       <c r="J478" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="K478" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L478" s="18"/>
+      <c r="K478" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L478" s="54">
+        <v>46247</v>
+      </c>
       <c r="M478" s="18"/>
       <c r="N478" s="40"/>
       <c r="O478" s="18"/>
@@ -33886,10 +34147,12 @@
       <c r="J576" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K576" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L576" s="18"/>
+      <c r="K576" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L576" s="54">
+        <v>46250</v>
+      </c>
       <c r="M576" s="18"/>
       <c r="N576" s="40"/>
       <c r="O576" s="18"/>
@@ -33932,10 +34195,12 @@
       <c r="J577" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K577" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L577" s="18"/>
+      <c r="K577" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L577" s="54">
+        <v>46250</v>
+      </c>
       <c r="M577" s="18"/>
       <c r="N577" s="55">
         <v>128</v>
@@ -33980,10 +34245,12 @@
       <c r="J578" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K578" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L578" s="18"/>
+      <c r="K578" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L578" s="54">
+        <v>46250</v>
+      </c>
       <c r="M578" s="18"/>
       <c r="N578" s="40"/>
       <c r="O578" s="18"/>
@@ -34118,10 +34385,12 @@
       <c r="J581" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K581" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L581" s="18"/>
+      <c r="K581" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L581" s="54">
+        <v>46250</v>
+      </c>
       <c r="M581" s="18"/>
       <c r="N581" s="40"/>
       <c r="O581" s="18"/>
@@ -34210,10 +34479,12 @@
       <c r="J583" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K583" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L583" s="18"/>
+      <c r="K583" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L583" s="54">
+        <v>46250</v>
+      </c>
       <c r="M583" s="18"/>
       <c r="N583" s="40"/>
       <c r="O583" s="18"/>
@@ -34304,10 +34575,12 @@
       <c r="J585" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K585" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L585" s="18"/>
+      <c r="K585" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L585" s="54">
+        <v>46250</v>
+      </c>
       <c r="M585" s="18"/>
       <c r="N585" s="55">
         <v>200</v>
@@ -34352,10 +34625,12 @@
       <c r="J586" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K586" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L586" s="18"/>
+      <c r="K586" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L586" s="54">
+        <v>46250</v>
+      </c>
       <c r="M586" s="18"/>
       <c r="N586" s="40"/>
       <c r="O586" s="18"/>
@@ -34396,10 +34671,12 @@
       <c r="J587" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K587" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L587" s="18"/>
+      <c r="K587" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L587" s="54">
+        <v>46250</v>
+      </c>
       <c r="M587" s="18"/>
       <c r="N587" s="55">
         <v>51</v>
@@ -34444,10 +34721,12 @@
       <c r="J588" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K588" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L588" s="18"/>
+      <c r="K588" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L588" s="54">
+        <v>46250</v>
+      </c>
       <c r="M588" s="18"/>
       <c r="N588" s="40"/>
       <c r="O588" s="18"/>
@@ -34490,10 +34769,12 @@
       <c r="J589" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K589" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L589" s="18"/>
+      <c r="K589" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L589" s="54">
+        <v>46250</v>
+      </c>
       <c r="M589" s="18"/>
       <c r="N589" s="40"/>
       <c r="O589" s="18"/>
@@ -34536,10 +34817,12 @@
       <c r="J590" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K590" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L590" s="18"/>
+      <c r="K590" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L590" s="54">
+        <v>46250</v>
+      </c>
       <c r="M590" s="18"/>
       <c r="N590" s="55">
         <v>266</v>
@@ -34584,10 +34867,12 @@
       <c r="J591" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K591" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L591" s="18"/>
+      <c r="K591" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L591" s="54">
+        <v>46250</v>
+      </c>
       <c r="M591" s="18"/>
       <c r="N591" s="40"/>
       <c r="O591" s="18"/>
@@ -34630,10 +34915,12 @@
       <c r="J592" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K592" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L592" s="18"/>
+      <c r="K592" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L592" s="54">
+        <v>46250</v>
+      </c>
       <c r="M592" s="18"/>
       <c r="N592" s="55">
         <v>337</v>
@@ -34768,10 +35055,12 @@
       <c r="J595" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K595" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L595" s="18"/>
+      <c r="K595" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L595" s="54">
+        <v>46250</v>
+      </c>
       <c r="M595" s="18"/>
       <c r="N595" s="55">
         <v>50</v>
@@ -35766,10 +36055,12 @@
       <c r="J616" s="15" t="s">
         <v>382</v>
       </c>
-      <c r="K616" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L616" s="18"/>
+      <c r="K616" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L616" s="54">
+        <v>46250</v>
+      </c>
       <c r="M616" s="18"/>
       <c r="N616" s="40"/>
       <c r="O616" s="18"/>
@@ -38648,10 +38939,12 @@
       <c r="J678" s="15" t="s">
         <v>832</v>
       </c>
-      <c r="K678" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L678" s="18"/>
+      <c r="K678" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L678" s="54">
+        <v>46250</v>
+      </c>
       <c r="M678" s="18"/>
       <c r="N678" s="55">
         <v>216</v>
@@ -38696,10 +38989,12 @@
       <c r="J679" s="15" t="s">
         <v>832</v>
       </c>
-      <c r="K679" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L679" s="18"/>
+      <c r="K679" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L679" s="54">
+        <v>46250</v>
+      </c>
       <c r="M679" s="18"/>
       <c r="N679" s="40"/>
       <c r="O679" s="18"/>
@@ -38740,10 +39035,12 @@
       <c r="J680" s="15" t="s">
         <v>832</v>
       </c>
-      <c r="K680" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L680" s="18"/>
+      <c r="K680" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L680" s="54">
+        <v>46250</v>
+      </c>
       <c r="M680" s="18"/>
       <c r="N680" s="55">
         <v>217</v>
@@ -40568,10 +40865,12 @@
       <c r="J720" s="15" t="s">
         <v>1058</v>
       </c>
-      <c r="K720" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L720" s="18"/>
+      <c r="K720" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L720" s="54">
+        <v>46250</v>
+      </c>
       <c r="M720" s="18"/>
       <c r="N720" s="40"/>
       <c r="O720" s="18"/>
@@ -42978,10 +43277,12 @@
       <c r="J772" s="15" t="s">
         <v>1207</v>
       </c>
-      <c r="K772" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L772" s="18"/>
+      <c r="K772" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L772" s="54">
+        <v>46249</v>
+      </c>
       <c r="M772" s="18"/>
       <c r="N772" s="40"/>
       <c r="O772" s="18"/>
@@ -43072,10 +43373,12 @@
       <c r="J774" s="15" t="s">
         <v>1207</v>
       </c>
-      <c r="K774" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L774" s="18"/>
+      <c r="K774" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L774" s="54">
+        <v>46249</v>
+      </c>
       <c r="M774" s="18"/>
       <c r="N774" s="40"/>
       <c r="O774" s="18"/>
@@ -43118,10 +43421,12 @@
       <c r="J775" s="15" t="s">
         <v>1207</v>
       </c>
-      <c r="K775" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L775" s="18"/>
+      <c r="K775" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L775" s="54">
+        <v>46250</v>
+      </c>
       <c r="M775" s="18"/>
       <c r="N775" s="40"/>
       <c r="O775" s="18"/>
@@ -43164,10 +43469,12 @@
       <c r="J776" s="15" t="s">
         <v>1207</v>
       </c>
-      <c r="K776" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L776" s="18"/>
+      <c r="K776" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L776" s="54">
+        <v>46249</v>
+      </c>
       <c r="M776" s="18"/>
       <c r="N776" s="40"/>
       <c r="O776" s="18"/>
@@ -43958,10 +44265,12 @@
       <c r="J793" s="15" t="s">
         <v>1236</v>
       </c>
-      <c r="K793" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L793" s="18"/>
+      <c r="K793" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L793" s="54">
+        <v>46250</v>
+      </c>
       <c r="M793" s="18"/>
       <c r="N793" s="40"/>
       <c r="O793" s="18"/>
@@ -49554,10 +49863,12 @@
       <c r="J917" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="K917" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L917" s="18"/>
+      <c r="K917" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L917" s="54">
+        <v>46250</v>
+      </c>
       <c r="M917" s="18"/>
       <c r="N917" s="40"/>
       <c r="O917" s="18"/>
@@ -61816,10 +62127,12 @@
       <c r="J1192" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="K1192" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1192" s="18"/>
+      <c r="K1192" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1192" s="54">
+        <v>46250</v>
+      </c>
       <c r="M1192" s="18"/>
       <c r="N1192" s="40"/>
       <c r="O1192" s="18"/>
@@ -61954,10 +62267,12 @@
       <c r="J1195" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="K1195" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1195" s="18"/>
+      <c r="K1195" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1195" s="54">
+        <v>46250</v>
+      </c>
       <c r="M1195" s="18"/>
       <c r="N1195" s="40"/>
       <c r="O1195" s="18"/>
@@ -62000,10 +62315,12 @@
       <c r="J1196" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="K1196" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1196" s="18"/>
+      <c r="K1196" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1196" s="54">
+        <v>46250</v>
+      </c>
       <c r="M1196" s="18"/>
       <c r="N1196" s="40"/>
       <c r="O1196" s="18"/>
@@ -62275,9 +62592,11 @@
       <c r="O1202" s="18"/>
       <c r="P1202" s="18"/>
       <c r="Q1202" s="18"/>
-      <c r="R1202" s="18"/>
-    </row>
-    <row r="1203" spans="1:18" ht="15" thickBot="1">
+      <c r="R1202" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1203" s="2">
         <v>1202</v>
       </c>
@@ -62285,49 +62604,43 @@
         <v>46244</v>
       </c>
       <c r="C1203" s="56" t="s">
-        <v>1843</v>
+        <v>2006</v>
       </c>
       <c r="D1203" s="56">
-        <v>12175744</v>
-      </c>
-      <c r="E1203" s="12" t="s">
-        <v>21</v>
+        <v>14821612</v>
+      </c>
+      <c r="E1203" s="37" t="s">
+        <v>121</v>
       </c>
       <c r="F1203" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1203" s="57">
-        <v>2168</v>
+        <v>769</v>
       </c>
       <c r="H1203" s="15">
-        <v>2168</v>
-      </c>
-      <c r="I1203" s="22" t="s">
-        <v>563</v>
-      </c>
-      <c r="J1203" s="51" t="s">
-        <v>564</v>
-      </c>
-      <c r="K1203" s="17" t="s">
-        <v>12</v>
+        <v>2409</v>
+      </c>
+      <c r="I1203" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1203" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1203" s="61" t="s">
+        <v>1189</v>
       </c>
       <c r="L1203" s="18"/>
       <c r="M1203" s="18"/>
-      <c r="N1203" s="55">
-        <v>353</v>
-      </c>
+      <c r="N1203" s="40"/>
       <c r="O1203" s="18"/>
-      <c r="P1203" s="50" t="s">
-        <v>1844</v>
-      </c>
-      <c r="Q1203" s="11">
-        <v>98504360</v>
-      </c>
-      <c r="R1203" s="22" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="1204" spans="1:18" ht="15" thickBot="1">
+      <c r="P1203" s="18"/>
+      <c r="Q1203" s="18"/>
+      <c r="R1203" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1204" s="2">
         <v>1203</v>
       </c>
@@ -62335,45 +62648,43 @@
         <v>46244</v>
       </c>
       <c r="C1204" s="56" t="s">
-        <v>1845</v>
-      </c>
-      <c r="D1204" s="56" t="s">
-        <v>1846</v>
-      </c>
-      <c r="E1204" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1204" s="13" t="s">
-        <v>22</v>
+        <v>2007</v>
+      </c>
+      <c r="D1204" s="56">
+        <v>14666696</v>
+      </c>
+      <c r="E1204" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1204" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1204" s="57">
-        <v>71359</v>
+        <v>-639</v>
       </c>
       <c r="H1204" s="15">
-        <v>88489</v>
-      </c>
-      <c r="I1204" s="22" t="s">
-        <v>563</v>
-      </c>
-      <c r="J1204" s="51" t="s">
-        <v>564</v>
-      </c>
-      <c r="K1204" s="17" t="s">
-        <v>12</v>
+        <v>6070</v>
+      </c>
+      <c r="I1204" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1204" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1204" s="61" t="s">
+        <v>1189</v>
       </c>
       <c r="L1204" s="18"/>
       <c r="M1204" s="18"/>
       <c r="N1204" s="40"/>
       <c r="O1204" s="18"/>
       <c r="P1204" s="18"/>
-      <c r="Q1204" s="15">
-        <v>77391393</v>
-      </c>
-      <c r="R1204" s="22" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="1205" spans="1:18" ht="15" thickBot="1">
+      <c r="Q1204" s="18"/>
+      <c r="R1204" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1205" s="2">
         <v>1204</v>
       </c>
@@ -62381,45 +62692,43 @@
         <v>46244</v>
       </c>
       <c r="C1205" s="56" t="s">
-        <v>1847</v>
-      </c>
-      <c r="D1205" s="56" t="s">
-        <v>1848</v>
-      </c>
-      <c r="E1205" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1205" s="13" t="s">
-        <v>22</v>
+        <v>2008</v>
+      </c>
+      <c r="D1205" s="56">
+        <v>13556728</v>
+      </c>
+      <c r="E1205" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1205" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1205" s="57">
-        <v>64626</v>
+        <v>5257</v>
       </c>
       <c r="H1205" s="15">
-        <v>66431</v>
-      </c>
-      <c r="I1205" s="22" t="s">
-        <v>563</v>
-      </c>
-      <c r="J1205" s="51" t="s">
-        <v>564</v>
-      </c>
-      <c r="K1205" s="17" t="s">
-        <v>12</v>
+        <v>5093</v>
+      </c>
+      <c r="I1205" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1205" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1205" s="61" t="s">
+        <v>1189</v>
       </c>
       <c r="L1205" s="18"/>
       <c r="M1205" s="18"/>
       <c r="N1205" s="40"/>
       <c r="O1205" s="18"/>
       <c r="P1205" s="18"/>
-      <c r="Q1205" s="15">
-        <v>96877836595</v>
-      </c>
-      <c r="R1205" s="22" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="1206" spans="1:18" ht="15" thickBot="1">
+      <c r="Q1205" s="18"/>
+      <c r="R1205" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1206" s="2">
         <v>1205</v>
       </c>
@@ -62427,45 +62736,43 @@
         <v>46244</v>
       </c>
       <c r="C1206" s="56" t="s">
-        <v>789</v>
-      </c>
-      <c r="D1206" s="56" t="s">
-        <v>1849</v>
-      </c>
-      <c r="E1206" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1206" s="13" t="s">
-        <v>22</v>
+        <v>2009</v>
+      </c>
+      <c r="D1206" s="56">
+        <v>15529953</v>
+      </c>
+      <c r="E1206" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1206" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1206" s="57">
-        <v>71507</v>
+        <v>2469</v>
       </c>
       <c r="H1206" s="15">
-        <v>81670</v>
-      </c>
-      <c r="I1206" s="22" t="s">
-        <v>563</v>
-      </c>
-      <c r="J1206" s="51" t="s">
-        <v>564</v>
-      </c>
-      <c r="K1206" s="30" t="s">
-        <v>1596</v>
+        <v>-4907</v>
+      </c>
+      <c r="I1206" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1206" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1206" s="61" t="s">
+        <v>1189</v>
       </c>
       <c r="L1206" s="18"/>
       <c r="M1206" s="18"/>
       <c r="N1206" s="40"/>
       <c r="O1206" s="18"/>
       <c r="P1206" s="18"/>
-      <c r="Q1206" s="15">
-        <v>77548862</v>
-      </c>
-      <c r="R1206" s="22" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="1207" spans="1:18" ht="15" thickBot="1">
+      <c r="Q1206" s="18"/>
+      <c r="R1206" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1207" s="2">
         <v>1206</v>
       </c>
@@ -62473,42 +62780,40 @@
         <v>46244</v>
       </c>
       <c r="C1207" s="56" t="s">
-        <v>1850</v>
-      </c>
-      <c r="D1207" s="56" t="s">
-        <v>1851</v>
-      </c>
-      <c r="E1207" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1207" s="13" t="s">
-        <v>22</v>
+        <v>2010</v>
+      </c>
+      <c r="D1207" s="56">
+        <v>1897229</v>
+      </c>
+      <c r="E1207" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1207" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1207" s="57">
-        <v>44366</v>
+        <v>9246</v>
       </c>
       <c r="H1207" s="15">
-        <v>98082</v>
-      </c>
-      <c r="I1207" s="22" t="s">
-        <v>563</v>
-      </c>
-      <c r="J1207" s="51" t="s">
-        <v>564</v>
-      </c>
-      <c r="K1207" s="17" t="s">
-        <v>12</v>
+        <v>9030</v>
+      </c>
+      <c r="I1207" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1207" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1207" s="61" t="s">
+        <v>1189</v>
       </c>
       <c r="L1207" s="18"/>
       <c r="M1207" s="18"/>
       <c r="N1207" s="40"/>
       <c r="O1207" s="18"/>
       <c r="P1207" s="18"/>
-      <c r="Q1207" s="15">
-        <v>589621226</v>
-      </c>
-      <c r="R1207" s="22" t="s">
-        <v>131</v>
+      <c r="Q1207" s="18"/>
+      <c r="R1207" s="21" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="1208" spans="1:18" ht="15" thickBot="1">
@@ -62519,22 +62824,22 @@
         <v>46244</v>
       </c>
       <c r="C1208" s="56" t="s">
-        <v>1852</v>
-      </c>
-      <c r="D1208" s="56" t="s">
-        <v>1853</v>
+        <v>1843</v>
+      </c>
+      <c r="D1208" s="56">
+        <v>12175744</v>
       </c>
       <c r="E1208" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1208" s="13" t="s">
-        <v>22</v>
+      <c r="F1208" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1208" s="57">
-        <v>4576</v>
+        <v>2168</v>
       </c>
       <c r="H1208" s="15">
-        <v>55234</v>
+        <v>2168</v>
       </c>
       <c r="I1208" s="22" t="s">
         <v>563</v>
@@ -62547,11 +62852,15 @@
       </c>
       <c r="L1208" s="18"/>
       <c r="M1208" s="18"/>
-      <c r="N1208" s="40"/>
+      <c r="N1208" s="55">
+        <v>353</v>
+      </c>
       <c r="O1208" s="18"/>
-      <c r="P1208" s="18"/>
-      <c r="Q1208" s="15">
-        <v>502405112</v>
+      <c r="P1208" s="50" t="s">
+        <v>1844</v>
+      </c>
+      <c r="Q1208" s="11">
+        <v>98504360</v>
       </c>
       <c r="R1208" s="22" t="s">
         <v>131</v>
@@ -62565,10 +62874,10 @@
         <v>46244</v>
       </c>
       <c r="C1209" s="56" t="s">
-        <v>1854</v>
+        <v>1845</v>
       </c>
       <c r="D1209" s="56" t="s">
-        <v>1855</v>
+        <v>1846</v>
       </c>
       <c r="E1209" s="12" t="s">
         <v>21</v>
@@ -62577,10 +62886,10 @@
         <v>22</v>
       </c>
       <c r="G1209" s="57">
-        <v>39669</v>
+        <v>71359</v>
       </c>
       <c r="H1209" s="15">
-        <v>53385</v>
+        <v>88489</v>
       </c>
       <c r="I1209" s="22" t="s">
         <v>563</v>
@@ -62597,7 +62906,7 @@
       <c r="O1209" s="18"/>
       <c r="P1209" s="18"/>
       <c r="Q1209" s="15">
-        <v>71713093</v>
+        <v>77391393</v>
       </c>
       <c r="R1209" s="22" t="s">
         <v>131</v>
@@ -62611,10 +62920,10 @@
         <v>46244</v>
       </c>
       <c r="C1210" s="56" t="s">
-        <v>1856</v>
+        <v>1847</v>
       </c>
       <c r="D1210" s="56" t="s">
-        <v>1857</v>
+        <v>1848</v>
       </c>
       <c r="E1210" s="12" t="s">
         <v>21</v>
@@ -62623,10 +62932,10 @@
         <v>22</v>
       </c>
       <c r="G1210" s="57">
-        <v>23875</v>
+        <v>64626</v>
       </c>
       <c r="H1210" s="15">
-        <v>53385</v>
+        <v>66431</v>
       </c>
       <c r="I1210" s="22" t="s">
         <v>563</v>
@@ -62643,13 +62952,13 @@
       <c r="O1210" s="18"/>
       <c r="P1210" s="18"/>
       <c r="Q1210" s="15">
-        <v>96890683052</v>
+        <v>96877836595</v>
       </c>
       <c r="R1210" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1211" spans="1:18" ht="27.6" thickBot="1">
+    <row r="1211" spans="1:18" ht="15" thickBot="1">
       <c r="A1211" s="2">
         <v>1210</v>
       </c>
@@ -62657,10 +62966,10 @@
         <v>46244</v>
       </c>
       <c r="C1211" s="56" t="s">
-        <v>1858</v>
+        <v>789</v>
       </c>
       <c r="D1211" s="56" t="s">
-        <v>1859</v>
+        <v>1849</v>
       </c>
       <c r="E1211" s="12" t="s">
         <v>21</v>
@@ -62669,10 +62978,10 @@
         <v>22</v>
       </c>
       <c r="G1211" s="57">
-        <v>31663</v>
+        <v>71507</v>
       </c>
       <c r="H1211" s="15">
-        <v>66670</v>
+        <v>81670</v>
       </c>
       <c r="I1211" s="22" t="s">
         <v>563</v>
@@ -62680,8 +62989,8 @@
       <c r="J1211" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1211" s="17" t="s">
-        <v>12</v>
+      <c r="K1211" s="30" t="s">
+        <v>1596</v>
       </c>
       <c r="L1211" s="18"/>
       <c r="M1211" s="18"/>
@@ -62689,13 +62998,13 @@
       <c r="O1211" s="18"/>
       <c r="P1211" s="18"/>
       <c r="Q1211" s="15">
-        <v>96876789204</v>
+        <v>77548862</v>
       </c>
       <c r="R1211" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1212" spans="1:18" ht="27.6" thickBot="1">
+    <row r="1212" spans="1:18" ht="15" thickBot="1">
       <c r="A1212" s="2">
         <v>1211</v>
       </c>
@@ -62703,10 +63012,10 @@
         <v>46244</v>
       </c>
       <c r="C1212" s="56" t="s">
-        <v>37</v>
+        <v>1850</v>
       </c>
       <c r="D1212" s="56" t="s">
-        <v>1860</v>
+        <v>1851</v>
       </c>
       <c r="E1212" s="12" t="s">
         <v>21</v>
@@ -62715,10 +63024,10 @@
         <v>22</v>
       </c>
       <c r="G1212" s="57">
-        <v>56846</v>
+        <v>44366</v>
       </c>
       <c r="H1212" s="15">
-        <v>74554</v>
+        <v>98082</v>
       </c>
       <c r="I1212" s="22" t="s">
         <v>563</v>
@@ -62735,7 +63044,7 @@
       <c r="O1212" s="18"/>
       <c r="P1212" s="18"/>
       <c r="Q1212" s="15">
-        <v>971506743142</v>
+        <v>589621226</v>
       </c>
       <c r="R1212" s="22" t="s">
         <v>131</v>
@@ -62749,10 +63058,10 @@
         <v>46244</v>
       </c>
       <c r="C1213" s="56" t="s">
-        <v>56</v>
+        <v>1852</v>
       </c>
       <c r="D1213" s="56" t="s">
-        <v>1861</v>
+        <v>1853</v>
       </c>
       <c r="E1213" s="12" t="s">
         <v>21</v>
@@ -62761,10 +63070,10 @@
         <v>22</v>
       </c>
       <c r="G1213" s="57">
-        <v>43021</v>
+        <v>4576</v>
       </c>
       <c r="H1213" s="15">
-        <v>24348</v>
+        <v>55234</v>
       </c>
       <c r="I1213" s="22" t="s">
         <v>563</v>
@@ -62781,7 +63090,7 @@
       <c r="O1213" s="18"/>
       <c r="P1213" s="18"/>
       <c r="Q1213" s="15">
-        <v>96877058642</v>
+        <v>502405112</v>
       </c>
       <c r="R1213" s="22" t="s">
         <v>131</v>
@@ -62795,10 +63104,10 @@
         <v>46244</v>
       </c>
       <c r="C1214" s="56" t="s">
-        <v>1862</v>
+        <v>1854</v>
       </c>
       <c r="D1214" s="56" t="s">
-        <v>1863</v>
+        <v>1855</v>
       </c>
       <c r="E1214" s="12" t="s">
         <v>21</v>
@@ -62807,10 +63116,10 @@
         <v>22</v>
       </c>
       <c r="G1214" s="57">
-        <v>21267</v>
+        <v>39669</v>
       </c>
       <c r="H1214" s="15">
-        <v>38336</v>
+        <v>53385</v>
       </c>
       <c r="I1214" s="22" t="s">
         <v>563</v>
@@ -62823,13 +63132,11 @@
       </c>
       <c r="L1214" s="18"/>
       <c r="M1214" s="18"/>
-      <c r="N1214" s="55">
-        <v>322</v>
-      </c>
+      <c r="N1214" s="40"/>
       <c r="O1214" s="18"/>
       <c r="P1214" s="18"/>
       <c r="Q1214" s="15">
-        <v>525399766</v>
+        <v>71713093</v>
       </c>
       <c r="R1214" s="22" t="s">
         <v>131</v>
@@ -62842,34 +63149,46 @@
       <c r="B1215" s="10">
         <v>46244</v>
       </c>
-      <c r="C1215" s="38"/>
-      <c r="D1215" s="38"/>
-      <c r="E1215" s="18"/>
+      <c r="C1215" s="56" t="s">
+        <v>1856</v>
+      </c>
+      <c r="D1215" s="56" t="s">
+        <v>1857</v>
+      </c>
+      <c r="E1215" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="F1215" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1215" s="57">
-        <v>24960</v>
-      </c>
-      <c r="H1215" s="18"/>
+        <v>23875</v>
+      </c>
+      <c r="H1215" s="15">
+        <v>53385</v>
+      </c>
       <c r="I1215" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1215" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1215" s="18"/>
+      <c r="K1215" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1215" s="18"/>
       <c r="M1215" s="18"/>
       <c r="N1215" s="40"/>
       <c r="O1215" s="18"/>
       <c r="P1215" s="18"/>
-      <c r="Q1215" s="18"/>
+      <c r="Q1215" s="15">
+        <v>96890683052</v>
+      </c>
       <c r="R1215" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1216" spans="1:18" ht="15" thickBot="1">
+    <row r="1216" spans="1:18" ht="27.6" thickBot="1">
       <c r="A1216" s="2">
         <v>1215</v>
       </c>
@@ -62877,10 +63196,10 @@
         <v>46244</v>
       </c>
       <c r="C1216" s="56" t="s">
-        <v>1137</v>
+        <v>1858</v>
       </c>
       <c r="D1216" s="56" t="s">
-        <v>1864</v>
+        <v>1859</v>
       </c>
       <c r="E1216" s="12" t="s">
         <v>21</v>
@@ -62889,10 +63208,10 @@
         <v>22</v>
       </c>
       <c r="G1216" s="57">
-        <v>36008</v>
+        <v>31663</v>
       </c>
       <c r="H1216" s="15">
-        <v>9102</v>
+        <v>66670</v>
       </c>
       <c r="I1216" s="22" t="s">
         <v>563</v>
@@ -62909,13 +63228,13 @@
       <c r="O1216" s="18"/>
       <c r="P1216" s="18"/>
       <c r="Q1216" s="15">
-        <v>94789315</v>
+        <v>96876789204</v>
       </c>
       <c r="R1216" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1217" spans="1:18" ht="15" thickBot="1">
+    <row r="1217" spans="1:18" ht="27.6" thickBot="1">
       <c r="A1217" s="2">
         <v>1216</v>
       </c>
@@ -62923,22 +63242,22 @@
         <v>46244</v>
       </c>
       <c r="C1217" s="56" t="s">
-        <v>1865</v>
-      </c>
-      <c r="D1217" s="56">
-        <v>138838184</v>
+        <v>37</v>
+      </c>
+      <c r="D1217" s="56" t="s">
+        <v>1860</v>
       </c>
       <c r="E1217" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1217" s="16" t="s">
-        <v>122</v>
+      <c r="F1217" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1217" s="57">
-        <v>2233</v>
+        <v>56846</v>
       </c>
       <c r="H1217" s="15">
-        <v>198</v>
+        <v>74554</v>
       </c>
       <c r="I1217" s="22" t="s">
         <v>563</v>
@@ -62955,7 +63274,7 @@
       <c r="O1217" s="18"/>
       <c r="P1217" s="18"/>
       <c r="Q1217" s="15">
-        <v>76249681</v>
+        <v>971506743142</v>
       </c>
       <c r="R1217" s="22" t="s">
         <v>131</v>
@@ -62968,29 +63287,41 @@
       <c r="B1218" s="10">
         <v>46244</v>
       </c>
-      <c r="C1218" s="38"/>
-      <c r="D1218" s="38"/>
-      <c r="E1218" s="18"/>
-      <c r="F1218" s="16" t="s">
-        <v>122</v>
+      <c r="C1218" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1218" s="56" t="s">
+        <v>1861</v>
+      </c>
+      <c r="E1218" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1218" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1218" s="57">
-        <v>4202</v>
-      </c>
-      <c r="H1218" s="18"/>
+        <v>43021</v>
+      </c>
+      <c r="H1218" s="15">
+        <v>24348</v>
+      </c>
       <c r="I1218" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1218" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1218" s="18"/>
+      <c r="K1218" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1218" s="18"/>
       <c r="M1218" s="18"/>
       <c r="N1218" s="40"/>
       <c r="O1218" s="18"/>
       <c r="P1218" s="18"/>
-      <c r="Q1218" s="18"/>
+      <c r="Q1218" s="15">
+        <v>96877058642</v>
+      </c>
       <c r="R1218" s="22" t="s">
         <v>131</v>
       </c>
@@ -63003,22 +63334,22 @@
         <v>46244</v>
       </c>
       <c r="C1219" s="56" t="s">
-        <v>1866</v>
-      </c>
-      <c r="D1219" s="56">
-        <v>95388683</v>
+        <v>1862</v>
+      </c>
+      <c r="D1219" s="56" t="s">
+        <v>1863</v>
       </c>
       <c r="E1219" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1219" s="16" t="s">
-        <v>122</v>
+      <c r="F1219" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1219" s="57">
-        <v>5961</v>
+        <v>21267</v>
       </c>
       <c r="H1219" s="15">
-        <v>9283</v>
+        <v>38336</v>
       </c>
       <c r="I1219" s="22" t="s">
         <v>563</v>
@@ -63031,11 +63362,13 @@
       </c>
       <c r="L1219" s="18"/>
       <c r="M1219" s="18"/>
-      <c r="N1219" s="40"/>
+      <c r="N1219" s="55">
+        <v>322</v>
+      </c>
       <c r="O1219" s="18"/>
       <c r="P1219" s="18"/>
       <c r="Q1219" s="15">
-        <v>71025778</v>
+        <v>525399766</v>
       </c>
       <c r="R1219" s="22" t="s">
         <v>131</v>
@@ -63048,41 +63381,29 @@
       <c r="B1220" s="10">
         <v>46244</v>
       </c>
-      <c r="C1220" s="56" t="s">
-        <v>1867</v>
-      </c>
-      <c r="D1220" s="56">
-        <v>78746152</v>
-      </c>
-      <c r="E1220" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1220" s="16" t="s">
-        <v>122</v>
+      <c r="C1220" s="38"/>
+      <c r="D1220" s="38"/>
+      <c r="E1220" s="18"/>
+      <c r="F1220" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1220" s="57">
-        <v>1834</v>
-      </c>
-      <c r="H1220" s="15">
-        <v>3623</v>
-      </c>
+        <v>24960</v>
+      </c>
+      <c r="H1220" s="18"/>
       <c r="I1220" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1220" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1220" s="17" t="s">
-        <v>12</v>
-      </c>
+      <c r="K1220" s="18"/>
       <c r="L1220" s="18"/>
       <c r="M1220" s="18"/>
       <c r="N1220" s="40"/>
       <c r="O1220" s="18"/>
       <c r="P1220" s="18"/>
-      <c r="Q1220" s="15">
-        <v>96895952892</v>
-      </c>
+      <c r="Q1220" s="18"/>
       <c r="R1220" s="22" t="s">
         <v>131</v>
       </c>
@@ -63094,31 +63415,41 @@
       <c r="B1221" s="10">
         <v>46244</v>
       </c>
-      <c r="C1221" s="38"/>
-      <c r="D1221" s="38"/>
-      <c r="E1221" s="18"/>
-      <c r="F1221" s="16" t="s">
-        <v>122</v>
+      <c r="C1221" s="56" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D1221" s="56" t="s">
+        <v>1864</v>
+      </c>
+      <c r="E1221" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1221" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1221" s="57">
-        <v>249</v>
-      </c>
-      <c r="H1221" s="18"/>
+        <v>36008</v>
+      </c>
+      <c r="H1221" s="15">
+        <v>9102</v>
+      </c>
       <c r="I1221" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1221" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1221" s="30" t="s">
-        <v>1596</v>
+      <c r="K1221" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1221" s="18"/>
       <c r="M1221" s="18"/>
       <c r="N1221" s="40"/>
       <c r="O1221" s="18"/>
       <c r="P1221" s="18"/>
-      <c r="Q1221" s="18"/>
+      <c r="Q1221" s="15">
+        <v>94789315</v>
+      </c>
       <c r="R1221" s="22" t="s">
         <v>131</v>
       </c>
@@ -63131,10 +63462,10 @@
         <v>46244</v>
       </c>
       <c r="C1222" s="56" t="s">
-        <v>1542</v>
+        <v>1865</v>
       </c>
       <c r="D1222" s="56">
-        <v>119318055</v>
+        <v>138838184</v>
       </c>
       <c r="E1222" s="12" t="s">
         <v>21</v>
@@ -63143,10 +63474,10 @@
         <v>122</v>
       </c>
       <c r="G1222" s="57">
-        <v>3638</v>
+        <v>2233</v>
       </c>
       <c r="H1222" s="15">
-        <v>4122</v>
+        <v>198</v>
       </c>
       <c r="I1222" s="22" t="s">
         <v>563</v>
@@ -63163,7 +63494,7 @@
       <c r="O1222" s="18"/>
       <c r="P1222" s="18"/>
       <c r="Q1222" s="15">
-        <v>78528125</v>
+        <v>76249681</v>
       </c>
       <c r="R1222" s="22" t="s">
         <v>131</v>
@@ -63176,41 +63507,29 @@
       <c r="B1223" s="10">
         <v>46244</v>
       </c>
-      <c r="C1223" s="56" t="s">
-        <v>1868</v>
-      </c>
-      <c r="D1223" s="56">
-        <v>91086972</v>
-      </c>
-      <c r="E1223" s="12" t="s">
-        <v>21</v>
-      </c>
+      <c r="C1223" s="38"/>
+      <c r="D1223" s="38"/>
+      <c r="E1223" s="18"/>
       <c r="F1223" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1223" s="57">
-        <v>1856</v>
-      </c>
-      <c r="H1223" s="15">
-        <v>9607</v>
-      </c>
+        <v>4202</v>
+      </c>
+      <c r="H1223" s="18"/>
       <c r="I1223" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1223" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1223" s="17" t="s">
-        <v>12</v>
-      </c>
+      <c r="K1223" s="18"/>
       <c r="L1223" s="18"/>
       <c r="M1223" s="18"/>
       <c r="N1223" s="40"/>
       <c r="O1223" s="18"/>
       <c r="P1223" s="18"/>
-      <c r="Q1223" s="15">
-        <v>95918065</v>
-      </c>
+      <c r="Q1223" s="18"/>
       <c r="R1223" s="22" t="s">
         <v>131</v>
       </c>
@@ -63223,10 +63542,10 @@
         <v>46244</v>
       </c>
       <c r="C1224" s="56" t="s">
-        <v>1869</v>
+        <v>1866</v>
       </c>
       <c r="D1224" s="56">
-        <v>121149924</v>
+        <v>95388683</v>
       </c>
       <c r="E1224" s="12" t="s">
         <v>21</v>
@@ -63235,10 +63554,10 @@
         <v>122</v>
       </c>
       <c r="G1224" s="57">
-        <v>3785</v>
+        <v>5961</v>
       </c>
       <c r="H1224" s="15">
-        <v>9062</v>
+        <v>9283</v>
       </c>
       <c r="I1224" s="22" t="s">
         <v>563</v>
@@ -63255,7 +63574,7 @@
       <c r="O1224" s="18"/>
       <c r="P1224" s="18"/>
       <c r="Q1224" s="15">
-        <v>95881870</v>
+        <v>71025778</v>
       </c>
       <c r="R1224" s="22" t="s">
         <v>131</v>
@@ -63269,10 +63588,10 @@
         <v>46244</v>
       </c>
       <c r="C1225" s="56" t="s">
-        <v>317</v>
+        <v>1867</v>
       </c>
       <c r="D1225" s="56">
-        <v>96363803</v>
+        <v>78746152</v>
       </c>
       <c r="E1225" s="12" t="s">
         <v>21</v>
@@ -63281,10 +63600,10 @@
         <v>122</v>
       </c>
       <c r="G1225" s="57">
-        <v>3367</v>
-      </c>
-      <c r="H1225" s="15" t="s">
-        <v>1870</v>
+        <v>1834</v>
+      </c>
+      <c r="H1225" s="15">
+        <v>3623</v>
       </c>
       <c r="I1225" s="22" t="s">
         <v>563</v>
@@ -63301,7 +63620,7 @@
       <c r="O1225" s="18"/>
       <c r="P1225" s="18"/>
       <c r="Q1225" s="15">
-        <v>96363803</v>
+        <v>96895952892</v>
       </c>
       <c r="R1225" s="22" t="s">
         <v>131</v>
@@ -63314,43 +63633,31 @@
       <c r="B1226" s="10">
         <v>46244</v>
       </c>
-      <c r="C1226" s="56" t="s">
-        <v>1871</v>
-      </c>
-      <c r="D1226" s="56" t="s">
-        <v>1872</v>
-      </c>
-      <c r="E1226" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1226" s="13" t="s">
-        <v>22</v>
+      <c r="C1226" s="38"/>
+      <c r="D1226" s="38"/>
+      <c r="E1226" s="18"/>
+      <c r="F1226" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1226" s="57">
-        <v>71968</v>
-      </c>
-      <c r="H1226" s="15">
-        <v>13188</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="H1226" s="18"/>
       <c r="I1226" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1226" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1226" s="17" t="s">
-        <v>12</v>
+      <c r="K1226" s="30" t="s">
+        <v>1596</v>
       </c>
       <c r="L1226" s="18"/>
       <c r="M1226" s="18"/>
-      <c r="N1226" s="55">
-        <v>321</v>
-      </c>
+      <c r="N1226" s="40"/>
       <c r="O1226" s="18"/>
       <c r="P1226" s="18"/>
-      <c r="Q1226" s="15">
-        <v>77245341</v>
-      </c>
+      <c r="Q1226" s="18"/>
       <c r="R1226" s="22" t="s">
         <v>131</v>
       </c>
@@ -63362,33 +63669,41 @@
       <c r="B1227" s="10">
         <v>46244</v>
       </c>
-      <c r="C1227" s="38"/>
-      <c r="D1227" s="38"/>
-      <c r="E1227" s="18"/>
+      <c r="C1227" s="56" t="s">
+        <v>1542</v>
+      </c>
+      <c r="D1227" s="56">
+        <v>119318055</v>
+      </c>
+      <c r="E1227" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="F1227" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1227" s="57">
-        <v>5195</v>
-      </c>
-      <c r="H1227" s="18"/>
+        <v>3638</v>
+      </c>
+      <c r="H1227" s="15">
+        <v>4122</v>
+      </c>
       <c r="I1227" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1227" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1227" s="30" t="s">
-        <v>1596</v>
+      <c r="K1227" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1227" s="18"/>
       <c r="M1227" s="18"/>
-      <c r="N1227" s="55">
-        <v>358</v>
-      </c>
+      <c r="N1227" s="40"/>
       <c r="O1227" s="18"/>
       <c r="P1227" s="18"/>
-      <c r="Q1227" s="18"/>
+      <c r="Q1227" s="15">
+        <v>78528125</v>
+      </c>
       <c r="R1227" s="22" t="s">
         <v>131</v>
       </c>
@@ -63400,31 +63715,41 @@
       <c r="B1228" s="10">
         <v>46244</v>
       </c>
-      <c r="C1228" s="38"/>
-      <c r="D1228" s="38"/>
-      <c r="E1228" s="18"/>
+      <c r="C1228" s="56" t="s">
+        <v>1868</v>
+      </c>
+      <c r="D1228" s="56">
+        <v>91086972</v>
+      </c>
+      <c r="E1228" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="F1228" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1228" s="57">
-        <v>7347</v>
-      </c>
-      <c r="H1228" s="18"/>
+        <v>1856</v>
+      </c>
+      <c r="H1228" s="15">
+        <v>9607</v>
+      </c>
       <c r="I1228" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1228" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1228" s="30" t="s">
-        <v>1596</v>
+      <c r="K1228" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1228" s="18"/>
       <c r="M1228" s="18"/>
       <c r="N1228" s="40"/>
       <c r="O1228" s="18"/>
       <c r="P1228" s="18"/>
-      <c r="Q1228" s="18"/>
+      <c r="Q1228" s="15">
+        <v>95918065</v>
+      </c>
       <c r="R1228" s="22" t="s">
         <v>131</v>
       </c>
@@ -63437,10 +63762,10 @@
         <v>46244</v>
       </c>
       <c r="C1229" s="56" t="s">
-        <v>1873</v>
+        <v>1869</v>
       </c>
       <c r="D1229" s="56">
-        <v>101198406</v>
+        <v>121149924</v>
       </c>
       <c r="E1229" s="12" t="s">
         <v>21</v>
@@ -63449,10 +63774,10 @@
         <v>122</v>
       </c>
       <c r="G1229" s="57">
-        <v>6330</v>
+        <v>3785</v>
       </c>
       <c r="H1229" s="15">
-        <v>7507</v>
+        <v>9062</v>
       </c>
       <c r="I1229" s="22" t="s">
         <v>563</v>
@@ -63469,7 +63794,7 @@
       <c r="O1229" s="18"/>
       <c r="P1229" s="18"/>
       <c r="Q1229" s="15">
-        <v>96709596</v>
+        <v>95881870</v>
       </c>
       <c r="R1229" s="22" t="s">
         <v>131</v>
@@ -63482,31 +63807,41 @@
       <c r="B1230" s="10">
         <v>46244</v>
       </c>
-      <c r="C1230" s="38"/>
-      <c r="D1230" s="38"/>
-      <c r="E1230" s="18"/>
-      <c r="F1230" s="13" t="s">
-        <v>22</v>
+      <c r="C1230" s="56" t="s">
+        <v>317</v>
+      </c>
+      <c r="D1230" s="56">
+        <v>96363803</v>
+      </c>
+      <c r="E1230" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1230" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1230" s="57">
-        <v>35455</v>
-      </c>
-      <c r="H1230" s="18"/>
+        <v>3367</v>
+      </c>
+      <c r="H1230" s="15" t="s">
+        <v>1870</v>
+      </c>
       <c r="I1230" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1230" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1230" s="30" t="s">
-        <v>1596</v>
+      <c r="K1230" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1230" s="18"/>
       <c r="M1230" s="18"/>
       <c r="N1230" s="40"/>
       <c r="O1230" s="18"/>
       <c r="P1230" s="18"/>
-      <c r="Q1230" s="18"/>
+      <c r="Q1230" s="15">
+        <v>96363803</v>
+      </c>
       <c r="R1230" s="22" t="s">
         <v>131</v>
       </c>
@@ -63518,31 +63853,43 @@
       <c r="B1231" s="10">
         <v>46244</v>
       </c>
-      <c r="C1231" s="38"/>
-      <c r="D1231" s="38"/>
-      <c r="E1231" s="18"/>
+      <c r="C1231" s="56" t="s">
+        <v>1871</v>
+      </c>
+      <c r="D1231" s="56" t="s">
+        <v>1872</v>
+      </c>
+      <c r="E1231" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="F1231" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1231" s="57">
-        <v>72129</v>
-      </c>
-      <c r="H1231" s="18"/>
+        <v>71968</v>
+      </c>
+      <c r="H1231" s="15">
+        <v>13188</v>
+      </c>
       <c r="I1231" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1231" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1231" s="30" t="s">
-        <v>1596</v>
+      <c r="K1231" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1231" s="18"/>
       <c r="M1231" s="18"/>
-      <c r="N1231" s="40"/>
+      <c r="N1231" s="55">
+        <v>321</v>
+      </c>
       <c r="O1231" s="18"/>
       <c r="P1231" s="18"/>
-      <c r="Q1231" s="18"/>
+      <c r="Q1231" s="15">
+        <v>77245341</v>
+      </c>
       <c r="R1231" s="22" t="s">
         <v>131</v>
       </c>
@@ -63554,41 +63901,33 @@
       <c r="B1232" s="10">
         <v>46244</v>
       </c>
-      <c r="C1232" s="56" t="s">
-        <v>432</v>
-      </c>
-      <c r="D1232" s="56">
-        <v>94734526</v>
-      </c>
-      <c r="E1232" s="12" t="s">
-        <v>21</v>
-      </c>
+      <c r="C1232" s="38"/>
+      <c r="D1232" s="38"/>
+      <c r="E1232" s="18"/>
       <c r="F1232" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1232" s="57">
-        <v>2535</v>
-      </c>
-      <c r="H1232" s="15">
-        <v>4261</v>
-      </c>
+        <v>5195</v>
+      </c>
+      <c r="H1232" s="18"/>
       <c r="I1232" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1232" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1232" s="17" t="s">
-        <v>12</v>
+      <c r="K1232" s="30" t="s">
+        <v>1596</v>
       </c>
       <c r="L1232" s="18"/>
       <c r="M1232" s="18"/>
-      <c r="N1232" s="40"/>
+      <c r="N1232" s="55">
+        <v>358</v>
+      </c>
       <c r="O1232" s="18"/>
       <c r="P1232" s="18"/>
-      <c r="Q1232" s="15">
-        <v>77454348</v>
-      </c>
+      <c r="Q1232" s="18"/>
       <c r="R1232" s="22" t="s">
         <v>131</v>
       </c>
@@ -63600,41 +63939,31 @@
       <c r="B1233" s="10">
         <v>46244</v>
       </c>
-      <c r="C1233" s="56" t="s">
-        <v>1883</v>
-      </c>
-      <c r="D1233" s="56">
-        <v>116911156</v>
-      </c>
-      <c r="E1233" s="12" t="s">
-        <v>21</v>
-      </c>
+      <c r="C1233" s="38"/>
+      <c r="D1233" s="38"/>
+      <c r="E1233" s="18"/>
       <c r="F1233" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1233" s="57">
-        <v>4479</v>
-      </c>
-      <c r="H1233" s="15">
-        <v>3757</v>
-      </c>
+        <v>7347</v>
+      </c>
+      <c r="H1233" s="18"/>
       <c r="I1233" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J1233" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1233" s="17" t="s">
-        <v>12</v>
+      <c r="K1233" s="30" t="s">
+        <v>1596</v>
       </c>
       <c r="L1233" s="18"/>
       <c r="M1233" s="18"/>
       <c r="N1233" s="40"/>
       <c r="O1233" s="18"/>
       <c r="P1233" s="18"/>
-      <c r="Q1233" s="15">
-        <v>96894139420</v>
-      </c>
+      <c r="Q1233" s="18"/>
       <c r="R1233" s="22" t="s">
         <v>131</v>
       </c>
@@ -63647,10 +63976,10 @@
         <v>46244</v>
       </c>
       <c r="C1234" s="56" t="s">
-        <v>1884</v>
+        <v>1873</v>
       </c>
       <c r="D1234" s="56">
-        <v>85817633</v>
+        <v>101198406</v>
       </c>
       <c r="E1234" s="12" t="s">
         <v>21</v>
@@ -63659,16 +63988,16 @@
         <v>122</v>
       </c>
       <c r="G1234" s="57">
-        <v>9082</v>
+        <v>6330</v>
       </c>
       <c r="H1234" s="15">
-        <v>3546</v>
+        <v>7507</v>
       </c>
       <c r="I1234" s="22" t="s">
         <v>563</v>
       </c>
-      <c r="J1234" s="15" t="s">
-        <v>1672</v>
+      <c r="J1234" s="51" t="s">
+        <v>564</v>
       </c>
       <c r="K1234" s="17" t="s">
         <v>12</v>
@@ -63678,7 +64007,9 @@
       <c r="N1234" s="40"/>
       <c r="O1234" s="18"/>
       <c r="P1234" s="18"/>
-      <c r="Q1234" s="18"/>
+      <c r="Q1234" s="15">
+        <v>96709596</v>
+      </c>
       <c r="R1234" s="22" t="s">
         <v>131</v>
       </c>
@@ -63690,32 +64021,24 @@
       <c r="B1235" s="10">
         <v>46244</v>
       </c>
-      <c r="C1235" s="56" t="s">
-        <v>1885</v>
-      </c>
-      <c r="D1235" s="56" t="s">
-        <v>1886</v>
-      </c>
-      <c r="E1235" s="12" t="s">
-        <v>21</v>
-      </c>
+      <c r="C1235" s="38"/>
+      <c r="D1235" s="38"/>
+      <c r="E1235" s="18"/>
       <c r="F1235" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1235" s="57">
-        <v>81144</v>
-      </c>
-      <c r="H1235" s="15">
-        <v>55344</v>
-      </c>
+        <v>35455</v>
+      </c>
+      <c r="H1235" s="18"/>
       <c r="I1235" s="22" t="s">
         <v>563</v>
       </c>
-      <c r="J1235" s="15" t="s">
-        <v>1672</v>
-      </c>
-      <c r="K1235" s="17" t="s">
-        <v>12</v>
+      <c r="J1235" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1235" s="30" t="s">
+        <v>1596</v>
       </c>
       <c r="L1235" s="18"/>
       <c r="M1235" s="18"/>
@@ -63734,41 +64057,31 @@
       <c r="B1236" s="10">
         <v>46244</v>
       </c>
-      <c r="C1236" s="56" t="s">
-        <v>1887</v>
-      </c>
-      <c r="D1236" s="56" t="s">
-        <v>1888</v>
-      </c>
-      <c r="E1236" s="35" t="s">
-        <v>120</v>
-      </c>
+      <c r="C1236" s="38"/>
+      <c r="D1236" s="38"/>
+      <c r="E1236" s="18"/>
       <c r="F1236" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1236" s="57">
-        <v>15562</v>
-      </c>
-      <c r="H1236" s="15">
-        <v>74553</v>
-      </c>
-      <c r="I1236" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1236" s="52" t="s">
-        <v>776</v>
-      </c>
-      <c r="K1236" s="61" t="s">
-        <v>1189</v>
+        <v>72129</v>
+      </c>
+      <c r="H1236" s="18"/>
+      <c r="I1236" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1236" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1236" s="30" t="s">
+        <v>1596</v>
       </c>
       <c r="L1236" s="18"/>
       <c r="M1236" s="18"/>
       <c r="N1236" s="40"/>
       <c r="O1236" s="18"/>
       <c r="P1236" s="18"/>
-      <c r="Q1236" s="15">
-        <v>566209290</v>
-      </c>
+      <c r="Q1236" s="18"/>
       <c r="R1236" s="22" t="s">
         <v>131</v>
       </c>
@@ -63781,10 +64094,10 @@
         <v>46244</v>
       </c>
       <c r="C1237" s="56" t="s">
-        <v>1889</v>
+        <v>432</v>
       </c>
       <c r="D1237" s="56">
-        <v>107948231</v>
+        <v>94734526</v>
       </c>
       <c r="E1237" s="12" t="s">
         <v>21</v>
@@ -63793,19 +64106,19 @@
         <v>122</v>
       </c>
       <c r="G1237" s="57">
-        <v>1602</v>
+        <v>2535</v>
       </c>
       <c r="H1237" s="15">
-        <v>1099</v>
-      </c>
-      <c r="I1237" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1237" s="52" t="s">
-        <v>776</v>
-      </c>
-      <c r="K1237" s="61" t="s">
-        <v>1189</v>
+        <v>4261</v>
+      </c>
+      <c r="I1237" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1237" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1237" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1237" s="18"/>
       <c r="M1237" s="18"/>
@@ -63813,7 +64126,7 @@
       <c r="O1237" s="18"/>
       <c r="P1237" s="18"/>
       <c r="Q1237" s="15">
-        <v>96892448478</v>
+        <v>77454348</v>
       </c>
       <c r="R1237" s="22" t="s">
         <v>131</v>
@@ -63827,10 +64140,10 @@
         <v>46244</v>
       </c>
       <c r="C1238" s="56" t="s">
-        <v>1890</v>
+        <v>1883</v>
       </c>
       <c r="D1238" s="56">
-        <v>76217672</v>
+        <v>116911156</v>
       </c>
       <c r="E1238" s="12" t="s">
         <v>21</v>
@@ -63839,19 +64152,19 @@
         <v>122</v>
       </c>
       <c r="G1238" s="57">
-        <v>4465</v>
+        <v>4479</v>
       </c>
       <c r="H1238" s="15">
-        <v>8001</v>
-      </c>
-      <c r="I1238" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1238" s="52" t="s">
-        <v>776</v>
-      </c>
-      <c r="K1238" s="61" t="s">
-        <v>1189</v>
+        <v>3757</v>
+      </c>
+      <c r="I1238" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1238" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1238" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1238" s="18"/>
       <c r="M1238" s="18"/>
@@ -63859,7 +64172,7 @@
       <c r="O1238" s="18"/>
       <c r="P1238" s="18"/>
       <c r="Q1238" s="15">
-        <v>93317831</v>
+        <v>96894139420</v>
       </c>
       <c r="R1238" s="22" t="s">
         <v>131</v>
@@ -63873,10 +64186,10 @@
         <v>46244</v>
       </c>
       <c r="C1239" s="56" t="s">
-        <v>1891</v>
+        <v>1884</v>
       </c>
       <c r="D1239" s="56">
-        <v>113802138</v>
+        <v>85817633</v>
       </c>
       <c r="E1239" s="12" t="s">
         <v>21</v>
@@ -63885,19 +64198,19 @@
         <v>122</v>
       </c>
       <c r="G1239" s="57">
-        <v>1777</v>
+        <v>9082</v>
       </c>
       <c r="H1239" s="15">
-        <v>9472</v>
-      </c>
-      <c r="I1239" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1239" s="52" t="s">
-        <v>776</v>
-      </c>
-      <c r="K1239" s="61" t="s">
-        <v>1189</v>
+        <v>3546</v>
+      </c>
+      <c r="I1239" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1239" s="15" t="s">
+        <v>1672</v>
+      </c>
+      <c r="K1239" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1239" s="18"/>
       <c r="M1239" s="18"/>
@@ -63917,28 +64230,28 @@
         <v>46244</v>
       </c>
       <c r="C1240" s="56" t="s">
-        <v>1892</v>
-      </c>
-      <c r="D1240" s="56">
-        <v>77396496</v>
+        <v>1885</v>
+      </c>
+      <c r="D1240" s="56" t="s">
+        <v>1886</v>
       </c>
       <c r="E1240" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1240" s="16" t="s">
-        <v>122</v>
+      <c r="F1240" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1240" s="57">
-        <v>3536</v>
+        <v>81144</v>
       </c>
       <c r="H1240" s="15">
-        <v>9212</v>
-      </c>
-      <c r="I1240" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1240" s="52" t="s">
-        <v>776</v>
+        <v>55344</v>
+      </c>
+      <c r="I1240" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1240" s="15" t="s">
+        <v>1672</v>
       </c>
       <c r="K1240" s="17" t="s">
         <v>12</v>
@@ -63953,7 +64266,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1241" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1241" spans="1:18" ht="15" thickBot="1">
       <c r="A1241" s="2">
         <v>1240</v>
       </c>
@@ -63961,31 +64274,31 @@
         <v>46244</v>
       </c>
       <c r="C1241" s="56" t="s">
-        <v>1893</v>
-      </c>
-      <c r="D1241" s="56">
-        <v>131422754</v>
-      </c>
-      <c r="E1241" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1241" s="16" t="s">
-        <v>122</v>
+        <v>1887</v>
+      </c>
+      <c r="D1241" s="56" t="s">
+        <v>1888</v>
+      </c>
+      <c r="E1241" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1241" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1241" s="57">
-        <v>3097</v>
+        <v>15562</v>
       </c>
       <c r="H1241" s="15">
-        <v>3993</v>
-      </c>
-      <c r="I1241" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="J1241" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="K1241" s="17" t="s">
-        <v>12</v>
+        <v>74553</v>
+      </c>
+      <c r="I1241" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1241" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1241" s="61" t="s">
+        <v>1189</v>
       </c>
       <c r="L1241" s="18"/>
       <c r="M1241" s="18"/>
@@ -63993,13 +64306,13 @@
       <c r="O1241" s="18"/>
       <c r="P1241" s="18"/>
       <c r="Q1241" s="15">
-        <v>78615034</v>
+        <v>566209290</v>
       </c>
       <c r="R1241" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1242" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1242" spans="1:18" ht="15" thickBot="1">
       <c r="A1242" s="2">
         <v>1241</v>
       </c>
@@ -64007,10 +64320,10 @@
         <v>46244</v>
       </c>
       <c r="C1242" s="56" t="s">
-        <v>1912</v>
+        <v>1889</v>
       </c>
       <c r="D1242" s="56">
-        <v>109499244</v>
+        <v>107948231</v>
       </c>
       <c r="E1242" s="12" t="s">
         <v>21</v>
@@ -64019,19 +64332,19 @@
         <v>122</v>
       </c>
       <c r="G1242" s="57">
-        <v>6018</v>
+        <v>1602</v>
       </c>
       <c r="H1242" s="15">
-        <v>8793</v>
-      </c>
-      <c r="I1242" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="J1242" s="15" t="s">
-        <v>1913</v>
-      </c>
-      <c r="K1242" s="17" t="s">
-        <v>12</v>
+        <v>1099</v>
+      </c>
+      <c r="I1242" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1242" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1242" s="61" t="s">
+        <v>1189</v>
       </c>
       <c r="L1242" s="18"/>
       <c r="M1242" s="18"/>
@@ -64039,13 +64352,13 @@
       <c r="O1242" s="18"/>
       <c r="P1242" s="18"/>
       <c r="Q1242" s="15">
-        <v>78735597</v>
+        <v>96892448478</v>
       </c>
       <c r="R1242" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1243" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1243" spans="1:18" ht="15" thickBot="1">
       <c r="A1243" s="2">
         <v>1242</v>
       </c>
@@ -64053,10 +64366,10 @@
         <v>46244</v>
       </c>
       <c r="C1243" s="56" t="s">
-        <v>1914</v>
+        <v>1890</v>
       </c>
       <c r="D1243" s="56">
-        <v>110877972</v>
+        <v>76217672</v>
       </c>
       <c r="E1243" s="12" t="s">
         <v>21</v>
@@ -64065,19 +64378,19 @@
         <v>122</v>
       </c>
       <c r="G1243" s="57">
-        <v>5734</v>
+        <v>4465</v>
       </c>
       <c r="H1243" s="15">
-        <v>235</v>
-      </c>
-      <c r="I1243" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="J1243" s="15" t="s">
-        <v>1913</v>
-      </c>
-      <c r="K1243" s="17" t="s">
-        <v>12</v>
+        <v>8001</v>
+      </c>
+      <c r="I1243" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1243" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1243" s="61" t="s">
+        <v>1189</v>
       </c>
       <c r="L1243" s="18"/>
       <c r="M1243" s="18"/>
@@ -64085,13 +64398,13 @@
       <c r="O1243" s="18"/>
       <c r="P1243" s="18"/>
       <c r="Q1243" s="15">
-        <v>79031527</v>
+        <v>93317831</v>
       </c>
       <c r="R1243" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1244" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1244" spans="1:18" ht="15" thickBot="1">
       <c r="A1244" s="2">
         <v>1243</v>
       </c>
@@ -64099,10 +64412,10 @@
         <v>46244</v>
       </c>
       <c r="C1244" s="56" t="s">
-        <v>1149</v>
+        <v>1891</v>
       </c>
       <c r="D1244" s="56">
-        <v>124842182</v>
+        <v>113802138</v>
       </c>
       <c r="E1244" s="12" t="s">
         <v>21</v>
@@ -64111,33 +64424,31 @@
         <v>122</v>
       </c>
       <c r="G1244" s="57">
-        <v>9340</v>
-      </c>
-      <c r="H1244" s="15" t="s">
-        <v>1915</v>
-      </c>
-      <c r="I1244" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="J1244" s="15" t="s">
-        <v>1913</v>
-      </c>
-      <c r="K1244" s="17" t="s">
-        <v>12</v>
+        <v>1777</v>
+      </c>
+      <c r="H1244" s="15">
+        <v>9472</v>
+      </c>
+      <c r="I1244" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1244" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1244" s="61" t="s">
+        <v>1189</v>
       </c>
       <c r="L1244" s="18"/>
       <c r="M1244" s="18"/>
       <c r="N1244" s="40"/>
       <c r="O1244" s="18"/>
       <c r="P1244" s="18"/>
-      <c r="Q1244" s="15">
-        <v>98172901</v>
-      </c>
+      <c r="Q1244" s="18"/>
       <c r="R1244" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1245" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1245" spans="1:18" ht="15" thickBot="1">
       <c r="A1245" s="2">
         <v>1244</v>
       </c>
@@ -64145,28 +64456,28 @@
         <v>46244</v>
       </c>
       <c r="C1245" s="56" t="s">
-        <v>1916</v>
-      </c>
-      <c r="D1245" s="56" t="s">
-        <v>1917</v>
+        <v>1892</v>
+      </c>
+      <c r="D1245" s="56">
+        <v>77396496</v>
       </c>
       <c r="E1245" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1245" s="13" t="s">
-        <v>22</v>
+      <c r="F1245" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1245" s="57">
-        <v>16853</v>
+        <v>3536</v>
       </c>
       <c r="H1245" s="15">
-        <v>76548</v>
-      </c>
-      <c r="I1245" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="J1245" s="15" t="s">
-        <v>1913</v>
+        <v>9212</v>
+      </c>
+      <c r="I1245" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1245" s="52" t="s">
+        <v>776</v>
       </c>
       <c r="K1245" s="17" t="s">
         <v>12</v>
@@ -64176,9 +64487,7 @@
       <c r="N1245" s="40"/>
       <c r="O1245" s="18"/>
       <c r="P1245" s="18"/>
-      <c r="Q1245" s="15">
-        <v>95596076</v>
-      </c>
+      <c r="Q1245" s="18"/>
       <c r="R1245" s="22" t="s">
         <v>131</v>
       </c>
@@ -64191,28 +64500,28 @@
         <v>46244</v>
       </c>
       <c r="C1246" s="56" t="s">
-        <v>1918</v>
-      </c>
-      <c r="D1246" s="56" t="s">
-        <v>1919</v>
+        <v>1893</v>
+      </c>
+      <c r="D1246" s="56">
+        <v>131422754</v>
       </c>
       <c r="E1246" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1246" s="13" t="s">
-        <v>22</v>
+      <c r="F1246" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1246" s="57">
-        <v>55729</v>
+        <v>3097</v>
       </c>
       <c r="H1246" s="15">
-        <v>21874</v>
+        <v>3993</v>
       </c>
       <c r="I1246" s="15" t="s">
         <v>123</v>
       </c>
       <c r="J1246" s="15" t="s">
-        <v>1913</v>
+        <v>174</v>
       </c>
       <c r="K1246" s="17" t="s">
         <v>12</v>
@@ -64223,7 +64532,7 @@
       <c r="O1246" s="18"/>
       <c r="P1246" s="18"/>
       <c r="Q1246" s="15">
-        <v>77821958</v>
+        <v>78615034</v>
       </c>
       <c r="R1246" s="22" t="s">
         <v>131</v>
@@ -64237,22 +64546,22 @@
         <v>46244</v>
       </c>
       <c r="C1247" s="56" t="s">
-        <v>1920</v>
-      </c>
-      <c r="D1247" s="56" t="s">
-        <v>1921</v>
+        <v>1912</v>
+      </c>
+      <c r="D1247" s="56">
+        <v>109499244</v>
       </c>
       <c r="E1247" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1247" s="13" t="s">
-        <v>22</v>
+      <c r="F1247" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1247" s="57">
-        <v>24788</v>
+        <v>6018</v>
       </c>
       <c r="H1247" s="15">
-        <v>81726</v>
+        <v>8793</v>
       </c>
       <c r="I1247" s="15" t="s">
         <v>123</v>
@@ -64269,7 +64578,7 @@
       <c r="O1247" s="18"/>
       <c r="P1247" s="18"/>
       <c r="Q1247" s="15">
-        <v>555524049</v>
+        <v>78735597</v>
       </c>
       <c r="R1247" s="22" t="s">
         <v>131</v>
@@ -64283,10 +64592,10 @@
         <v>46244</v>
       </c>
       <c r="C1248" s="56" t="s">
-        <v>1922</v>
+        <v>1914</v>
       </c>
       <c r="D1248" s="56">
-        <v>133589295</v>
+        <v>110877972</v>
       </c>
       <c r="E1248" s="12" t="s">
         <v>21</v>
@@ -64295,16 +64604,16 @@
         <v>122</v>
       </c>
       <c r="G1248" s="57">
-        <v>4317</v>
+        <v>5734</v>
       </c>
       <c r="H1248" s="15">
-        <v>9901</v>
+        <v>235</v>
       </c>
       <c r="I1248" s="15" t="s">
         <v>123</v>
       </c>
       <c r="J1248" s="15" t="s">
-        <v>174</v>
+        <v>1913</v>
       </c>
       <c r="K1248" s="17" t="s">
         <v>12</v>
@@ -64314,8 +64623,8 @@
       <c r="N1248" s="40"/>
       <c r="O1248" s="18"/>
       <c r="P1248" s="18"/>
-      <c r="Q1248" s="11">
-        <v>96877336001</v>
+      <c r="Q1248" s="15">
+        <v>79031527</v>
       </c>
       <c r="R1248" s="22" t="s">
         <v>131</v>
@@ -64329,10 +64638,10 @@
         <v>46244</v>
       </c>
       <c r="C1249" s="56" t="s">
-        <v>771</v>
+        <v>1149</v>
       </c>
       <c r="D1249" s="56">
-        <v>121398708</v>
+        <v>124842182</v>
       </c>
       <c r="E1249" s="12" t="s">
         <v>21</v>
@@ -64341,16 +64650,16 @@
         <v>122</v>
       </c>
       <c r="G1249" s="57">
-        <v>9244</v>
-      </c>
-      <c r="H1249" s="15">
-        <v>9611</v>
+        <v>9340</v>
+      </c>
+      <c r="H1249" s="15" t="s">
+        <v>1915</v>
       </c>
       <c r="I1249" s="15" t="s">
         <v>123</v>
       </c>
       <c r="J1249" s="15" t="s">
-        <v>174</v>
+        <v>1913</v>
       </c>
       <c r="K1249" s="17" t="s">
         <v>12</v>
@@ -64360,8 +64669,8 @@
       <c r="N1249" s="40"/>
       <c r="O1249" s="18"/>
       <c r="P1249" s="18"/>
-      <c r="Q1249" s="11">
-        <v>71382892</v>
+      <c r="Q1249" s="15">
+        <v>98172901</v>
       </c>
       <c r="R1249" s="22" t="s">
         <v>131</v>
@@ -64375,28 +64684,28 @@
         <v>46244</v>
       </c>
       <c r="C1250" s="56" t="s">
-        <v>1930</v>
-      </c>
-      <c r="D1250" s="56">
-        <v>123092622</v>
+        <v>1916</v>
+      </c>
+      <c r="D1250" s="56" t="s">
+        <v>1917</v>
       </c>
       <c r="E1250" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1250" s="16" t="s">
-        <v>122</v>
+      <c r="F1250" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1250" s="57">
-        <v>8269</v>
+        <v>16853</v>
       </c>
       <c r="H1250" s="15">
-        <v>8963</v>
+        <v>76548</v>
       </c>
       <c r="I1250" s="15" t="s">
         <v>123</v>
       </c>
       <c r="J1250" s="15" t="s">
-        <v>174</v>
+        <v>1913</v>
       </c>
       <c r="K1250" s="17" t="s">
         <v>12</v>
@@ -64406,8 +64715,8 @@
       <c r="N1250" s="40"/>
       <c r="O1250" s="18"/>
       <c r="P1250" s="18"/>
-      <c r="Q1250" s="11">
-        <v>98560324</v>
+      <c r="Q1250" s="15">
+        <v>95596076</v>
       </c>
       <c r="R1250" s="22" t="s">
         <v>131</v>
@@ -64421,22 +64730,22 @@
         <v>46244</v>
       </c>
       <c r="C1251" s="56" t="s">
-        <v>1931</v>
-      </c>
-      <c r="D1251" s="56">
-        <v>136802631</v>
+        <v>1918</v>
+      </c>
+      <c r="D1251" s="56" t="s">
+        <v>1919</v>
       </c>
       <c r="E1251" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1251" s="16" t="s">
-        <v>122</v>
+      <c r="F1251" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1251" s="57">
-        <v>1474</v>
+        <v>55729</v>
       </c>
       <c r="H1251" s="15">
-        <v>3475</v>
+        <v>21874</v>
       </c>
       <c r="I1251" s="15" t="s">
         <v>123</v>
@@ -64453,7 +64762,7 @@
       <c r="O1251" s="18"/>
       <c r="P1251" s="18"/>
       <c r="Q1251" s="15">
-        <v>94317092</v>
+        <v>77821958</v>
       </c>
       <c r="R1251" s="22" t="s">
         <v>131</v>
@@ -64467,22 +64776,22 @@
         <v>46244</v>
       </c>
       <c r="C1252" s="56" t="s">
-        <v>1932</v>
-      </c>
-      <c r="D1252" s="56">
-        <v>136393574</v>
+        <v>1920</v>
+      </c>
+      <c r="D1252" s="56" t="s">
+        <v>1921</v>
       </c>
       <c r="E1252" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1252" s="16" t="s">
-        <v>122</v>
+      <c r="F1252" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1252" s="57">
-        <v>8580</v>
-      </c>
-      <c r="H1252" s="15" t="s">
-        <v>1933</v>
+        <v>24788</v>
+      </c>
+      <c r="H1252" s="15">
+        <v>81726</v>
       </c>
       <c r="I1252" s="15" t="s">
         <v>123</v>
@@ -64499,7 +64808,7 @@
       <c r="O1252" s="18"/>
       <c r="P1252" s="18"/>
       <c r="Q1252" s="15">
-        <v>94526230</v>
+        <v>555524049</v>
       </c>
       <c r="R1252" s="22" t="s">
         <v>131</v>
@@ -64513,10 +64822,10 @@
         <v>46244</v>
       </c>
       <c r="C1253" s="56" t="s">
-        <v>1934</v>
+        <v>1922</v>
       </c>
       <c r="D1253" s="56">
-        <v>101540233</v>
+        <v>133589295</v>
       </c>
       <c r="E1253" s="12" t="s">
         <v>21</v>
@@ -64525,16 +64834,16 @@
         <v>122</v>
       </c>
       <c r="G1253" s="57">
-        <v>5126</v>
-      </c>
-      <c r="H1253" s="15" t="s">
-        <v>1935</v>
+        <v>4317</v>
+      </c>
+      <c r="H1253" s="15">
+        <v>9901</v>
       </c>
       <c r="I1253" s="15" t="s">
         <v>123</v>
       </c>
       <c r="J1253" s="15" t="s">
-        <v>1913</v>
+        <v>174</v>
       </c>
       <c r="K1253" s="17" t="s">
         <v>12</v>
@@ -64544,12 +64853,14 @@
       <c r="N1253" s="40"/>
       <c r="O1253" s="18"/>
       <c r="P1253" s="18"/>
-      <c r="Q1253" s="18"/>
+      <c r="Q1253" s="11">
+        <v>96877336001</v>
+      </c>
       <c r="R1253" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1254" spans="1:18" ht="31.2" thickBot="1">
+    <row r="1254" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1254" s="2">
         <v>1253</v>
       </c>
@@ -64557,40 +64868,40 @@
         <v>46244</v>
       </c>
       <c r="C1254" s="56" t="s">
-        <v>279</v>
-      </c>
-      <c r="D1254" s="56" t="s">
-        <v>280</v>
+        <v>771</v>
+      </c>
+      <c r="D1254" s="56">
+        <v>121398708</v>
       </c>
       <c r="E1254" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1254" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1254" s="57" t="s">
-        <v>1936</v>
+      <c r="F1254" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1254" s="57">
+        <v>9244</v>
       </c>
       <c r="H1254" s="15">
-        <v>48752</v>
+        <v>9611</v>
       </c>
       <c r="I1254" s="15" t="s">
         <v>123</v>
       </c>
       <c r="J1254" s="15" t="s">
-        <v>1913</v>
-      </c>
-      <c r="K1254" s="30" t="s">
-        <v>1596</v>
+        <v>174</v>
+      </c>
+      <c r="K1254" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1254" s="18"/>
       <c r="M1254" s="18"/>
       <c r="N1254" s="40"/>
       <c r="O1254" s="18"/>
-      <c r="P1254" s="50" t="s">
-        <v>1803</v>
-      </c>
-      <c r="Q1254" s="18"/>
+      <c r="P1254" s="18"/>
+      <c r="Q1254" s="11">
+        <v>71382892</v>
+      </c>
       <c r="R1254" s="22" t="s">
         <v>131</v>
       </c>
@@ -64603,10 +64914,10 @@
         <v>46244</v>
       </c>
       <c r="C1255" s="56" t="s">
-        <v>1937</v>
+        <v>1930</v>
       </c>
       <c r="D1255" s="56">
-        <v>76637533</v>
+        <v>123092622</v>
       </c>
       <c r="E1255" s="12" t="s">
         <v>21</v>
@@ -64615,10 +64926,10 @@
         <v>122</v>
       </c>
       <c r="G1255" s="57">
-        <v>1027</v>
+        <v>8269</v>
       </c>
       <c r="H1255" s="15">
-        <v>512</v>
+        <v>8963</v>
       </c>
       <c r="I1255" s="15" t="s">
         <v>123</v>
@@ -64634,12 +64945,14 @@
       <c r="N1255" s="40"/>
       <c r="O1255" s="18"/>
       <c r="P1255" s="18"/>
-      <c r="Q1255" s="18"/>
+      <c r="Q1255" s="11">
+        <v>98560324</v>
+      </c>
       <c r="R1255" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1256" spans="1:18" ht="15" thickBot="1">
+    <row r="1256" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1256" s="2">
         <v>1255</v>
       </c>
@@ -64647,28 +64960,28 @@
         <v>46244</v>
       </c>
       <c r="C1256" s="56" t="s">
-        <v>1965</v>
-      </c>
-      <c r="D1256" s="56" t="s">
-        <v>1966</v>
+        <v>1931</v>
+      </c>
+      <c r="D1256" s="56">
+        <v>136802631</v>
       </c>
       <c r="E1256" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1256" s="13" t="s">
-        <v>22</v>
+      <c r="F1256" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1256" s="57">
-        <v>78112</v>
+        <v>1474</v>
       </c>
       <c r="H1256" s="15">
-        <v>19848</v>
-      </c>
-      <c r="I1256" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1256" s="52" t="s">
-        <v>776</v>
+        <v>3475</v>
+      </c>
+      <c r="I1256" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1256" s="15" t="s">
+        <v>1913</v>
       </c>
       <c r="K1256" s="17" t="s">
         <v>12</v>
@@ -64678,12 +64991,14 @@
       <c r="N1256" s="40"/>
       <c r="O1256" s="18"/>
       <c r="P1256" s="18"/>
-      <c r="Q1256" s="18"/>
+      <c r="Q1256" s="15">
+        <v>94317092</v>
+      </c>
       <c r="R1256" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1257" spans="1:18" ht="15" thickBot="1">
+    <row r="1257" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1257" s="2">
         <v>1256</v>
       </c>
@@ -64691,28 +65006,28 @@
         <v>46244</v>
       </c>
       <c r="C1257" s="56" t="s">
-        <v>1967</v>
-      </c>
-      <c r="D1257" s="56" t="s">
-        <v>1968</v>
+        <v>1932</v>
+      </c>
+      <c r="D1257" s="56">
+        <v>136393574</v>
       </c>
       <c r="E1257" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1257" s="13" t="s">
-        <v>22</v>
+      <c r="F1257" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1257" s="57">
-        <v>20380</v>
-      </c>
-      <c r="H1257" s="15">
-        <v>23939</v>
-      </c>
-      <c r="I1257" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1257" s="52" t="s">
-        <v>776</v>
+        <v>8580</v>
+      </c>
+      <c r="H1257" s="15" t="s">
+        <v>1933</v>
+      </c>
+      <c r="I1257" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1257" s="15" t="s">
+        <v>1913</v>
       </c>
       <c r="K1257" s="17" t="s">
         <v>12</v>
@@ -64722,12 +65037,14 @@
       <c r="N1257" s="40"/>
       <c r="O1257" s="18"/>
       <c r="P1257" s="18"/>
-      <c r="Q1257" s="18"/>
+      <c r="Q1257" s="15">
+        <v>94526230</v>
+      </c>
       <c r="R1257" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1258" spans="1:18" ht="15" thickBot="1">
+    <row r="1258" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1258" s="2">
         <v>1257</v>
       </c>
@@ -64735,28 +65052,28 @@
         <v>46244</v>
       </c>
       <c r="C1258" s="56" t="s">
-        <v>1969</v>
-      </c>
-      <c r="D1258" s="56" t="s">
-        <v>1970</v>
+        <v>1934</v>
+      </c>
+      <c r="D1258" s="56">
+        <v>101540233</v>
       </c>
       <c r="E1258" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1258" s="13" t="s">
-        <v>22</v>
+      <c r="F1258" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1258" s="57">
-        <v>40255</v>
-      </c>
-      <c r="H1258" s="15">
-        <v>39156</v>
-      </c>
-      <c r="I1258" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1258" s="52" t="s">
-        <v>776</v>
+        <v>5126</v>
+      </c>
+      <c r="H1258" s="15" t="s">
+        <v>1935</v>
+      </c>
+      <c r="I1258" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1258" s="15" t="s">
+        <v>1913</v>
       </c>
       <c r="K1258" s="17" t="s">
         <v>12</v>
@@ -64771,7 +65088,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1259" spans="1:18" ht="15" thickBot="1">
+    <row r="1259" spans="1:18" ht="31.2" thickBot="1">
       <c r="A1259" s="2">
         <v>1258</v>
       </c>
@@ -64779,10 +65096,10 @@
         <v>46244</v>
       </c>
       <c r="C1259" s="56" t="s">
-        <v>27</v>
+        <v>279</v>
       </c>
       <c r="D1259" s="56" t="s">
-        <v>1971</v>
+        <v>280</v>
       </c>
       <c r="E1259" s="12" t="s">
         <v>21</v>
@@ -64790,32 +65107,34 @@
       <c r="F1259" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="G1259" s="57">
-        <v>78295</v>
+      <c r="G1259" s="57" t="s">
+        <v>1936</v>
       </c>
       <c r="H1259" s="15">
-        <v>91055</v>
-      </c>
-      <c r="I1259" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1259" s="52" t="s">
-        <v>776</v>
-      </c>
-      <c r="K1259" s="17" t="s">
-        <v>12</v>
+        <v>48752</v>
+      </c>
+      <c r="I1259" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1259" s="15" t="s">
+        <v>1913</v>
+      </c>
+      <c r="K1259" s="30" t="s">
+        <v>1596</v>
       </c>
       <c r="L1259" s="18"/>
       <c r="M1259" s="18"/>
       <c r="N1259" s="40"/>
       <c r="O1259" s="18"/>
-      <c r="P1259" s="18"/>
+      <c r="P1259" s="50" t="s">
+        <v>1803</v>
+      </c>
       <c r="Q1259" s="18"/>
       <c r="R1259" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1260" spans="1:18" ht="15" thickBot="1">
+    <row r="1260" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1260" s="2">
         <v>1259</v>
       </c>
@@ -64823,28 +65142,28 @@
         <v>46244</v>
       </c>
       <c r="C1260" s="56" t="s">
-        <v>1972</v>
-      </c>
-      <c r="D1260" s="56" t="s">
-        <v>1973</v>
-      </c>
-      <c r="E1260" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="F1260" s="13" t="s">
-        <v>22</v>
+        <v>1937</v>
+      </c>
+      <c r="D1260" s="56">
+        <v>76637533</v>
+      </c>
+      <c r="E1260" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1260" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1260" s="57">
-        <v>43916</v>
+        <v>1027</v>
       </c>
       <c r="H1260" s="15">
-        <v>63018</v>
-      </c>
-      <c r="I1260" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1260" s="52" t="s">
-        <v>776</v>
+        <v>512</v>
+      </c>
+      <c r="I1260" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1260" s="15" t="s">
+        <v>174</v>
       </c>
       <c r="K1260" s="17" t="s">
         <v>12</v>
@@ -64867,22 +65186,22 @@
         <v>46244</v>
       </c>
       <c r="C1261" s="56" t="s">
-        <v>1974</v>
+        <v>1965</v>
       </c>
       <c r="D1261" s="56" t="s">
-        <v>1975</v>
-      </c>
-      <c r="E1261" s="30" t="s">
-        <v>119</v>
+        <v>1966</v>
+      </c>
+      <c r="E1261" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="F1261" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1261" s="57">
-        <v>18439</v>
+        <v>78112</v>
       </c>
       <c r="H1261" s="15">
-        <v>28485</v>
+        <v>19848</v>
       </c>
       <c r="I1261" s="16" t="s">
         <v>10</v>
@@ -64911,22 +65230,22 @@
         <v>46244</v>
       </c>
       <c r="C1262" s="56" t="s">
-        <v>1976</v>
+        <v>1967</v>
       </c>
       <c r="D1262" s="56" t="s">
-        <v>1977</v>
-      </c>
-      <c r="E1262" s="30" t="s">
-        <v>119</v>
+        <v>1968</v>
+      </c>
+      <c r="E1262" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="F1262" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1262" s="57">
-        <v>85929</v>
+        <v>20380</v>
       </c>
       <c r="H1262" s="15">
-        <v>13193</v>
+        <v>23939</v>
       </c>
       <c r="I1262" s="16" t="s">
         <v>10</v>
@@ -64955,22 +65274,22 @@
         <v>46244</v>
       </c>
       <c r="C1263" s="56" t="s">
-        <v>1978</v>
+        <v>1969</v>
       </c>
       <c r="D1263" s="56" t="s">
-        <v>1979</v>
-      </c>
-      <c r="E1263" s="30" t="s">
-        <v>119</v>
+        <v>1970</v>
+      </c>
+      <c r="E1263" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="F1263" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1263" s="57">
-        <v>28434</v>
+        <v>40255</v>
       </c>
       <c r="H1263" s="15">
-        <v>10962</v>
+        <v>39156</v>
       </c>
       <c r="I1263" s="16" t="s">
         <v>10</v>
@@ -64999,10 +65318,10 @@
         <v>46244</v>
       </c>
       <c r="C1264" s="56" t="s">
-        <v>1349</v>
+        <v>27</v>
       </c>
       <c r="D1264" s="56" t="s">
-        <v>1938</v>
+        <v>1971</v>
       </c>
       <c r="E1264" s="12" t="s">
         <v>21</v>
@@ -65011,16 +65330,16 @@
         <v>22</v>
       </c>
       <c r="G1264" s="57">
-        <v>13349</v>
+        <v>78295</v>
       </c>
       <c r="H1264" s="15">
-        <v>43281</v>
-      </c>
-      <c r="I1264" s="22" t="s">
-        <v>563</v>
-      </c>
-      <c r="J1264" s="51" t="s">
-        <v>564</v>
+        <v>91055</v>
+      </c>
+      <c r="I1264" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1264" s="52" t="s">
+        <v>776</v>
       </c>
       <c r="K1264" s="17" t="s">
         <v>12</v>
@@ -65043,28 +65362,28 @@
         <v>46244</v>
       </c>
       <c r="C1265" s="56" t="s">
-        <v>1939</v>
+        <v>1972</v>
       </c>
       <c r="D1265" s="56" t="s">
-        <v>1940</v>
-      </c>
-      <c r="E1265" s="12" t="s">
-        <v>21</v>
+        <v>1973</v>
+      </c>
+      <c r="E1265" s="30" t="s">
+        <v>119</v>
       </c>
       <c r="F1265" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1265" s="57">
-        <v>48418</v>
+        <v>43916</v>
       </c>
       <c r="H1265" s="15">
-        <v>62782</v>
-      </c>
-      <c r="I1265" s="22" t="s">
-        <v>563</v>
-      </c>
-      <c r="J1265" s="51" t="s">
-        <v>564</v>
+        <v>63018</v>
+      </c>
+      <c r="I1265" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1265" s="52" t="s">
+        <v>776</v>
       </c>
       <c r="K1265" s="17" t="s">
         <v>12</v>
@@ -65087,28 +65406,28 @@
         <v>46244</v>
       </c>
       <c r="C1266" s="56" t="s">
-        <v>1941</v>
+        <v>1974</v>
       </c>
       <c r="D1266" s="56" t="s">
-        <v>1942</v>
-      </c>
-      <c r="E1266" s="12" t="s">
-        <v>21</v>
+        <v>1975</v>
+      </c>
+      <c r="E1266" s="30" t="s">
+        <v>119</v>
       </c>
       <c r="F1266" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1266" s="57">
-        <v>51661</v>
+        <v>18439</v>
       </c>
       <c r="H1266" s="15">
-        <v>40394</v>
-      </c>
-      <c r="I1266" s="22" t="s">
-        <v>563</v>
-      </c>
-      <c r="J1266" s="51" t="s">
-        <v>564</v>
+        <v>28485</v>
+      </c>
+      <c r="I1266" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1266" s="52" t="s">
+        <v>776</v>
       </c>
       <c r="K1266" s="17" t="s">
         <v>12</v>
@@ -65131,28 +65450,28 @@
         <v>46244</v>
       </c>
       <c r="C1267" s="56" t="s">
-        <v>1943</v>
+        <v>1976</v>
       </c>
       <c r="D1267" s="56" t="s">
-        <v>1944</v>
-      </c>
-      <c r="E1267" s="12" t="s">
-        <v>21</v>
+        <v>1977</v>
+      </c>
+      <c r="E1267" s="30" t="s">
+        <v>119</v>
       </c>
       <c r="F1267" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1267" s="57">
-        <v>84554</v>
+        <v>85929</v>
       </c>
       <c r="H1267" s="15">
-        <v>21501</v>
-      </c>
-      <c r="I1267" s="22" t="s">
-        <v>563</v>
-      </c>
-      <c r="J1267" s="51" t="s">
-        <v>564</v>
+        <v>13193</v>
+      </c>
+      <c r="I1267" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1267" s="52" t="s">
+        <v>776</v>
       </c>
       <c r="K1267" s="17" t="s">
         <v>12</v>
@@ -65175,26 +65494,28 @@
         <v>46244</v>
       </c>
       <c r="C1268" s="56" t="s">
-        <v>1137</v>
+        <v>1978</v>
       </c>
       <c r="D1268" s="56" t="s">
-        <v>1945</v>
-      </c>
-      <c r="E1268" s="12" t="s">
-        <v>21</v>
+        <v>1979</v>
+      </c>
+      <c r="E1268" s="30" t="s">
+        <v>119</v>
       </c>
       <c r="F1268" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1268" s="57">
-        <v>41504</v>
-      </c>
-      <c r="H1268" s="18"/>
-      <c r="I1268" s="22" t="s">
-        <v>563</v>
-      </c>
-      <c r="J1268" s="51" t="s">
-        <v>564</v>
+        <v>28434</v>
+      </c>
+      <c r="H1268" s="15">
+        <v>10962</v>
+      </c>
+      <c r="I1268" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1268" s="52" t="s">
+        <v>776</v>
       </c>
       <c r="K1268" s="17" t="s">
         <v>12</v>
@@ -65217,10 +65538,10 @@
         <v>46244</v>
       </c>
       <c r="C1269" s="56" t="s">
-        <v>1946</v>
+        <v>1349</v>
       </c>
       <c r="D1269" s="56" t="s">
-        <v>1980</v>
+        <v>1938</v>
       </c>
       <c r="E1269" s="12" t="s">
         <v>21</v>
@@ -65229,10 +65550,10 @@
         <v>22</v>
       </c>
       <c r="G1269" s="57">
-        <v>17443</v>
+        <v>13349</v>
       </c>
       <c r="H1269" s="15">
-        <v>20106</v>
+        <v>43281</v>
       </c>
       <c r="I1269" s="22" t="s">
         <v>563</v>
@@ -65261,10 +65582,10 @@
         <v>46244</v>
       </c>
       <c r="C1270" s="56" t="s">
-        <v>1952</v>
+        <v>1939</v>
       </c>
       <c r="D1270" s="56" t="s">
-        <v>1953</v>
+        <v>1940</v>
       </c>
       <c r="E1270" s="12" t="s">
         <v>21</v>
@@ -65273,10 +65594,10 @@
         <v>22</v>
       </c>
       <c r="G1270" s="57">
-        <v>82557</v>
+        <v>48418</v>
       </c>
       <c r="H1270" s="15">
-        <v>23835</v>
+        <v>62782</v>
       </c>
       <c r="I1270" s="22" t="s">
         <v>563</v>
@@ -65305,22 +65626,22 @@
         <v>46244</v>
       </c>
       <c r="C1271" s="56" t="s">
-        <v>1102</v>
-      </c>
-      <c r="D1271" s="56">
-        <v>107774476</v>
+        <v>1941</v>
+      </c>
+      <c r="D1271" s="56" t="s">
+        <v>1942</v>
       </c>
       <c r="E1271" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1271" s="16" t="s">
-        <v>122</v>
+      <c r="F1271" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1271" s="57">
-        <v>3561</v>
+        <v>51661</v>
       </c>
       <c r="H1271" s="15">
-        <v>5702</v>
+        <v>40394</v>
       </c>
       <c r="I1271" s="22" t="s">
         <v>563</v>
@@ -65341,7 +65662,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1272" spans="1:18" ht="27.6" thickBot="1">
+    <row r="1272" spans="1:18" ht="15" thickBot="1">
       <c r="A1272" s="2">
         <v>1271</v>
       </c>
@@ -65349,10 +65670,10 @@
         <v>46244</v>
       </c>
       <c r="C1272" s="56" t="s">
-        <v>1954</v>
+        <v>1943</v>
       </c>
       <c r="D1272" s="56" t="s">
-        <v>1955</v>
+        <v>1944</v>
       </c>
       <c r="E1272" s="12" t="s">
         <v>21</v>
@@ -65361,10 +65682,10 @@
         <v>22</v>
       </c>
       <c r="G1272" s="57">
-        <v>22319</v>
+        <v>84554</v>
       </c>
       <c r="H1272" s="15">
-        <v>19801</v>
+        <v>21501</v>
       </c>
       <c r="I1272" s="22" t="s">
         <v>563</v>
@@ -65385,7 +65706,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1273" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1273" spans="1:18" ht="15" thickBot="1">
       <c r="A1273" s="2">
         <v>1272</v>
       </c>
@@ -65393,28 +65714,26 @@
         <v>46244</v>
       </c>
       <c r="C1273" s="56" t="s">
-        <v>1956</v>
-      </c>
-      <c r="D1273" s="56">
-        <v>36336406</v>
-      </c>
-      <c r="E1273" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="F1273" s="16" t="s">
-        <v>122</v>
+        <v>1137</v>
+      </c>
+      <c r="D1273" s="56" t="s">
+        <v>1945</v>
+      </c>
+      <c r="E1273" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1273" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1273" s="57">
-        <v>1965</v>
-      </c>
-      <c r="H1273" s="15">
-        <v>826</v>
-      </c>
-      <c r="I1273" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="J1273" s="15" t="s">
-        <v>1058</v>
+        <v>41504</v>
+      </c>
+      <c r="H1273" s="18"/>
+      <c r="I1273" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1273" s="51" t="s">
+        <v>564</v>
       </c>
       <c r="K1273" s="17" t="s">
         <v>12</v>
@@ -65429,7 +65748,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1274" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1274" spans="1:18" ht="15" thickBot="1">
       <c r="A1274" s="2">
         <v>1273</v>
       </c>
@@ -65437,28 +65756,28 @@
         <v>46244</v>
       </c>
       <c r="C1274" s="56" t="s">
-        <v>1957</v>
-      </c>
-      <c r="D1274" s="56">
-        <v>17065948</v>
-      </c>
-      <c r="E1274" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="F1274" s="16" t="s">
-        <v>122</v>
+        <v>1946</v>
+      </c>
+      <c r="D1274" s="56" t="s">
+        <v>1980</v>
+      </c>
+      <c r="E1274" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1274" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1274" s="57">
-        <v>5788</v>
+        <v>17443</v>
       </c>
       <c r="H1274" s="15">
-        <v>9112</v>
-      </c>
-      <c r="I1274" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="J1274" s="15" t="s">
-        <v>1058</v>
+        <v>20106</v>
+      </c>
+      <c r="I1274" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1274" s="51" t="s">
+        <v>564</v>
       </c>
       <c r="K1274" s="17" t="s">
         <v>12</v>
@@ -65473,7 +65792,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1275" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1275" spans="1:18" ht="15" thickBot="1">
       <c r="A1275" s="2">
         <v>1274</v>
       </c>
@@ -65481,28 +65800,28 @@
         <v>46244</v>
       </c>
       <c r="C1275" s="56" t="s">
-        <v>1958</v>
-      </c>
-      <c r="D1275" s="56">
-        <v>3084818</v>
-      </c>
-      <c r="E1275" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="F1275" s="16" t="s">
-        <v>122</v>
+        <v>1952</v>
+      </c>
+      <c r="D1275" s="56" t="s">
+        <v>1953</v>
+      </c>
+      <c r="E1275" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1275" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1275" s="57">
-        <v>6300</v>
+        <v>82557</v>
       </c>
       <c r="H1275" s="15">
-        <v>8487</v>
-      </c>
-      <c r="I1275" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="J1275" s="15" t="s">
-        <v>1058</v>
+        <v>23835</v>
+      </c>
+      <c r="I1275" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1275" s="51" t="s">
+        <v>564</v>
       </c>
       <c r="K1275" s="17" t="s">
         <v>12</v>
@@ -65517,7 +65836,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1276" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1276" spans="1:18" ht="15" thickBot="1">
       <c r="A1276" s="2">
         <v>1275</v>
       </c>
@@ -65525,28 +65844,28 @@
         <v>46244</v>
       </c>
       <c r="C1276" s="56" t="s">
-        <v>1959</v>
+        <v>1102</v>
       </c>
       <c r="D1276" s="56">
-        <v>2144791</v>
-      </c>
-      <c r="E1276" s="37" t="s">
-        <v>121</v>
+        <v>107774476</v>
+      </c>
+      <c r="E1276" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="F1276" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1276" s="57">
-        <v>1598</v>
+        <v>3561</v>
       </c>
       <c r="H1276" s="15">
-        <v>3380</v>
-      </c>
-      <c r="I1276" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="J1276" s="15" t="s">
-        <v>1058</v>
+        <v>5702</v>
+      </c>
+      <c r="I1276" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1276" s="51" t="s">
+        <v>564</v>
       </c>
       <c r="K1276" s="17" t="s">
         <v>12</v>
@@ -65561,7 +65880,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1277" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1277" spans="1:18" ht="27.6" thickBot="1">
       <c r="A1277" s="2">
         <v>1276</v>
       </c>
@@ -65569,28 +65888,28 @@
         <v>46244</v>
       </c>
       <c r="C1277" s="56" t="s">
-        <v>1960</v>
-      </c>
-      <c r="D1277" s="56">
-        <v>12571732</v>
-      </c>
-      <c r="E1277" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="F1277" s="16" t="s">
-        <v>122</v>
+        <v>1954</v>
+      </c>
+      <c r="D1277" s="56" t="s">
+        <v>1955</v>
+      </c>
+      <c r="E1277" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1277" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1277" s="57">
-        <v>8884</v>
+        <v>22319</v>
       </c>
       <c r="H1277" s="15">
-        <v>8169</v>
-      </c>
-      <c r="I1277" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="J1277" s="15" t="s">
-        <v>1058</v>
+        <v>19801</v>
+      </c>
+      <c r="I1277" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1277" s="51" t="s">
+        <v>564</v>
       </c>
       <c r="K1277" s="17" t="s">
         <v>12</v>
@@ -65613,10 +65932,10 @@
         <v>46244</v>
       </c>
       <c r="C1278" s="56" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="D1278" s="56">
-        <v>96995164</v>
+        <v>36336406</v>
       </c>
       <c r="E1278" s="37" t="s">
         <v>121</v>
@@ -65625,10 +65944,10 @@
         <v>122</v>
       </c>
       <c r="G1278" s="57">
-        <v>8884</v>
+        <v>1965</v>
       </c>
       <c r="H1278" s="15">
-        <v>8169</v>
+        <v>826</v>
       </c>
       <c r="I1278" s="15" t="s">
         <v>123</v>
@@ -65649,7 +65968,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1279" spans="1:18" ht="15" thickBot="1">
+    <row r="1279" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1279" s="2">
         <v>1278</v>
       </c>
@@ -65657,10 +65976,10 @@
         <v>46244</v>
       </c>
       <c r="C1279" s="56" t="s">
-        <v>1981</v>
+        <v>1957</v>
       </c>
       <c r="D1279" s="56">
-        <v>76532221</v>
+        <v>17065948</v>
       </c>
       <c r="E1279" s="37" t="s">
         <v>121</v>
@@ -65669,16 +65988,16 @@
         <v>122</v>
       </c>
       <c r="G1279" s="57">
-        <v>9125</v>
+        <v>5788</v>
       </c>
       <c r="H1279" s="15">
-        <v>988</v>
-      </c>
-      <c r="I1279" s="22" t="s">
-        <v>563</v>
+        <v>9112</v>
+      </c>
+      <c r="I1279" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="J1279" s="15" t="s">
-        <v>1672</v>
+        <v>1058</v>
       </c>
       <c r="K1279" s="17" t="s">
         <v>12</v>
@@ -65693,7 +66012,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1280" spans="1:18" ht="15" thickBot="1">
+    <row r="1280" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1280" s="2">
         <v>1279</v>
       </c>
@@ -65701,28 +66020,28 @@
         <v>46244</v>
       </c>
       <c r="C1280" s="56" t="s">
-        <v>1982</v>
+        <v>1958</v>
       </c>
       <c r="D1280" s="56">
-        <v>86125495</v>
-      </c>
-      <c r="E1280" s="12" t="s">
-        <v>21</v>
+        <v>3084818</v>
+      </c>
+      <c r="E1280" s="37" t="s">
+        <v>121</v>
       </c>
       <c r="F1280" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="G1280" s="75">
-        <v>9181</v>
+      <c r="G1280" s="57">
+        <v>6300</v>
       </c>
       <c r="H1280" s="15">
-        <v>1776</v>
-      </c>
-      <c r="I1280" s="22" t="s">
-        <v>563</v>
-      </c>
-      <c r="J1280" s="51" t="s">
-        <v>564</v>
+        <v>8487</v>
+      </c>
+      <c r="I1280" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1280" s="15" t="s">
+        <v>1058</v>
       </c>
       <c r="K1280" s="17" t="s">
         <v>12</v>
@@ -65737,7 +66056,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1281" spans="1:18" ht="15" thickBot="1">
+    <row r="1281" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1281" s="2">
         <v>1280</v>
       </c>
@@ -65745,28 +66064,28 @@
         <v>46244</v>
       </c>
       <c r="C1281" s="56" t="s">
-        <v>1983</v>
-      </c>
-      <c r="D1281" s="56" t="s">
-        <v>1984</v>
-      </c>
-      <c r="E1281" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="F1281" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1281" s="75">
-        <v>62966</v>
+        <v>1959</v>
+      </c>
+      <c r="D1281" s="56">
+        <v>2144791</v>
+      </c>
+      <c r="E1281" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1281" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1281" s="57">
+        <v>1598</v>
       </c>
       <c r="H1281" s="15">
-        <v>78304</v>
-      </c>
-      <c r="I1281" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1281" s="52" t="s">
-        <v>776</v>
+        <v>3380</v>
+      </c>
+      <c r="I1281" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1281" s="15" t="s">
+        <v>1058</v>
       </c>
       <c r="K1281" s="17" t="s">
         <v>12</v>
@@ -65781,7 +66100,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1282" spans="1:18" ht="15" thickBot="1">
+    <row r="1282" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1282" s="2">
         <v>1281</v>
       </c>
@@ -65789,26 +66108,28 @@
         <v>46244</v>
       </c>
       <c r="C1282" s="56" t="s">
-        <v>1985</v>
-      </c>
-      <c r="D1282" s="56" t="s">
-        <v>1986</v>
-      </c>
-      <c r="E1282" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="F1282" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1282" s="75">
-        <v>69727</v>
-      </c>
-      <c r="H1282" s="18"/>
-      <c r="I1282" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1282" s="52" t="s">
-        <v>776</v>
+        <v>1960</v>
+      </c>
+      <c r="D1282" s="56">
+        <v>12571732</v>
+      </c>
+      <c r="E1282" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1282" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1282" s="57">
+        <v>8884</v>
+      </c>
+      <c r="H1282" s="15">
+        <v>8169</v>
+      </c>
+      <c r="I1282" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1282" s="15" t="s">
+        <v>1058</v>
       </c>
       <c r="K1282" s="17" t="s">
         <v>12</v>
@@ -65823,7 +66144,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1283" spans="1:18" ht="15" thickBot="1">
+    <row r="1283" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1283" s="2">
         <v>1282</v>
       </c>
@@ -65831,28 +66152,28 @@
         <v>46244</v>
       </c>
       <c r="C1283" s="56" t="s">
-        <v>1987</v>
-      </c>
-      <c r="D1283" s="56" t="s">
-        <v>1988</v>
-      </c>
-      <c r="E1283" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="F1283" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1283" s="75">
-        <v>88240</v>
+        <v>1961</v>
+      </c>
+      <c r="D1283" s="56">
+        <v>96995164</v>
+      </c>
+      <c r="E1283" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1283" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1283" s="57">
+        <v>8884</v>
       </c>
       <c r="H1283" s="15">
-        <v>35031</v>
-      </c>
-      <c r="I1283" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1283" s="52" t="s">
-        <v>776</v>
+        <v>8169</v>
+      </c>
+      <c r="I1283" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1283" s="15" t="s">
+        <v>1058</v>
       </c>
       <c r="K1283" s="17" t="s">
         <v>12</v>
@@ -65875,28 +66196,28 @@
         <v>46244</v>
       </c>
       <c r="C1284" s="56" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D1284" s="56" t="s">
-        <v>1990</v>
-      </c>
-      <c r="E1284" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="F1284" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1284" s="75">
-        <v>28971</v>
+        <v>1981</v>
+      </c>
+      <c r="D1284" s="56">
+        <v>76532221</v>
+      </c>
+      <c r="E1284" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1284" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1284" s="57">
+        <v>9125</v>
       </c>
       <c r="H1284" s="15">
-        <v>31344</v>
-      </c>
-      <c r="I1284" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1284" s="52" t="s">
-        <v>776</v>
+        <v>988</v>
+      </c>
+      <c r="I1284" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1284" s="15" t="s">
+        <v>1672</v>
       </c>
       <c r="K1284" s="17" t="s">
         <v>12</v>
@@ -65919,28 +66240,28 @@
         <v>46244</v>
       </c>
       <c r="C1285" s="56" t="s">
-        <v>1991</v>
-      </c>
-      <c r="D1285" s="56" t="s">
-        <v>1992</v>
-      </c>
-      <c r="E1285" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="F1285" s="13" t="s">
-        <v>22</v>
+        <v>1982</v>
+      </c>
+      <c r="D1285" s="56">
+        <v>86125495</v>
+      </c>
+      <c r="E1285" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1285" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1285" s="75">
-        <v>19055</v>
+        <v>9181</v>
       </c>
       <c r="H1285" s="15">
-        <v>83425</v>
-      </c>
-      <c r="I1285" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1285" s="52" t="s">
-        <v>776</v>
+        <v>1776</v>
+      </c>
+      <c r="I1285" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1285" s="51" t="s">
+        <v>564</v>
       </c>
       <c r="K1285" s="17" t="s">
         <v>12</v>
@@ -65963,10 +66284,10 @@
         <v>46244</v>
       </c>
       <c r="C1286" s="56" t="s">
-        <v>1993</v>
+        <v>1983</v>
       </c>
       <c r="D1286" s="56" t="s">
-        <v>1994</v>
+        <v>1984</v>
       </c>
       <c r="E1286" s="30" t="s">
         <v>119</v>
@@ -65975,10 +66296,10 @@
         <v>22</v>
       </c>
       <c r="G1286" s="75">
-        <v>38691</v>
+        <v>62966</v>
       </c>
       <c r="H1286" s="15">
-        <v>57004</v>
+        <v>78304</v>
       </c>
       <c r="I1286" s="16" t="s">
         <v>10</v>
@@ -65999,7 +66320,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1287" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1287" spans="1:18" ht="15" thickBot="1">
       <c r="A1287" s="2">
         <v>1286</v>
       </c>
@@ -66007,10 +66328,10 @@
         <v>46244</v>
       </c>
       <c r="C1287" s="56" t="s">
-        <v>1995</v>
+        <v>1985</v>
       </c>
       <c r="D1287" s="56" t="s">
-        <v>1996</v>
+        <v>1986</v>
       </c>
       <c r="E1287" s="30" t="s">
         <v>119</v>
@@ -66019,16 +66340,14 @@
         <v>22</v>
       </c>
       <c r="G1287" s="75">
-        <v>27098</v>
-      </c>
-      <c r="H1287" s="15">
-        <v>25544</v>
-      </c>
-      <c r="I1287" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="J1287" s="15" t="s">
-        <v>1997</v>
+        <v>69727</v>
+      </c>
+      <c r="H1287" s="18"/>
+      <c r="I1287" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1287" s="52" t="s">
+        <v>776</v>
       </c>
       <c r="K1287" s="17" t="s">
         <v>12</v>
@@ -66038,9 +66357,7 @@
       <c r="N1287" s="40"/>
       <c r="O1287" s="18"/>
       <c r="P1287" s="18"/>
-      <c r="Q1287" s="11">
-        <v>95691585</v>
-      </c>
+      <c r="Q1287" s="18"/>
       <c r="R1287" s="22" t="s">
         <v>131</v>
       </c>
@@ -66053,28 +66370,28 @@
         <v>46244</v>
       </c>
       <c r="C1288" s="56" t="s">
-        <v>1874</v>
-      </c>
-      <c r="D1288" s="56">
-        <v>112067329</v>
-      </c>
-      <c r="E1288" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1288" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1288" s="57">
-        <v>2968</v>
+        <v>1987</v>
+      </c>
+      <c r="D1288" s="56" t="s">
+        <v>1988</v>
+      </c>
+      <c r="E1288" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1288" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1288" s="75">
+        <v>88240</v>
       </c>
       <c r="H1288" s="15">
-        <v>5613</v>
+        <v>35031</v>
       </c>
       <c r="I1288" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J1288" s="15" t="s">
-        <v>839</v>
+      <c r="J1288" s="52" t="s">
+        <v>776</v>
       </c>
       <c r="K1288" s="17" t="s">
         <v>12</v>
@@ -66085,11 +66402,11 @@
       <c r="O1288" s="18"/>
       <c r="P1288" s="18"/>
       <c r="Q1288" s="18"/>
-      <c r="R1288" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1289" spans="1:18" ht="27.6" thickBot="1">
+      <c r="R1288" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:18" ht="15" thickBot="1">
       <c r="A1289" s="2">
         <v>1288</v>
       </c>
@@ -66097,28 +66414,28 @@
         <v>46244</v>
       </c>
       <c r="C1289" s="56" t="s">
-        <v>1875</v>
-      </c>
-      <c r="D1289" s="56">
-        <v>116806083</v>
-      </c>
-      <c r="E1289" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1289" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1289" s="57">
-        <v>442</v>
+        <v>1989</v>
+      </c>
+      <c r="D1289" s="56" t="s">
+        <v>1990</v>
+      </c>
+      <c r="E1289" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1289" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1289" s="75">
+        <v>28971</v>
       </c>
       <c r="H1289" s="15">
-        <v>7536</v>
+        <v>31344</v>
       </c>
       <c r="I1289" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J1289" s="15" t="s">
-        <v>950</v>
+      <c r="J1289" s="52" t="s">
+        <v>776</v>
       </c>
       <c r="K1289" s="17" t="s">
         <v>12</v>
@@ -66128,11 +66445,9 @@
       <c r="N1289" s="40"/>
       <c r="O1289" s="18"/>
       <c r="P1289" s="18"/>
-      <c r="Q1289" s="11">
-        <v>79997138</v>
-      </c>
-      <c r="R1289" s="20" t="s">
-        <v>11</v>
+      <c r="Q1289" s="18"/>
+      <c r="R1289" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="1290" spans="1:18" ht="15" thickBot="1">
@@ -66143,28 +66458,28 @@
         <v>46244</v>
       </c>
       <c r="C1290" s="56" t="s">
-        <v>1876</v>
-      </c>
-      <c r="D1290" s="56">
-        <v>113458078</v>
-      </c>
-      <c r="E1290" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1290" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1290" s="57">
-        <v>5913</v>
+        <v>1991</v>
+      </c>
+      <c r="D1290" s="56" t="s">
+        <v>1992</v>
+      </c>
+      <c r="E1290" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1290" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1290" s="75">
+        <v>19055</v>
       </c>
       <c r="H1290" s="15">
-        <v>1154</v>
+        <v>83425</v>
       </c>
       <c r="I1290" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J1290" s="15" t="s">
-        <v>950</v>
+      <c r="J1290" s="52" t="s">
+        <v>776</v>
       </c>
       <c r="K1290" s="17" t="s">
         <v>12</v>
@@ -66175,11 +66490,11 @@
       <c r="O1290" s="18"/>
       <c r="P1290" s="18"/>
       <c r="Q1290" s="18"/>
-      <c r="R1290" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1291" spans="1:18" ht="27.6" thickBot="1">
+      <c r="R1290" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:18" ht="15" thickBot="1">
       <c r="A1291" s="2">
         <v>1290</v>
       </c>
@@ -66187,28 +66502,28 @@
         <v>46244</v>
       </c>
       <c r="C1291" s="56" t="s">
-        <v>638</v>
-      </c>
-      <c r="D1291" s="56">
-        <v>122952217</v>
-      </c>
-      <c r="E1291" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1291" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1291" s="57">
-        <v>4581</v>
+        <v>1993</v>
+      </c>
+      <c r="D1291" s="56" t="s">
+        <v>1994</v>
+      </c>
+      <c r="E1291" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1291" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1291" s="75">
+        <v>38691</v>
       </c>
       <c r="H1291" s="15">
-        <v>-8325</v>
+        <v>57004</v>
       </c>
       <c r="I1291" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J1291" s="15" t="s">
-        <v>950</v>
+      <c r="J1291" s="52" t="s">
+        <v>776</v>
       </c>
       <c r="K1291" s="17" t="s">
         <v>12</v>
@@ -66218,14 +66533,12 @@
       <c r="N1291" s="40"/>
       <c r="O1291" s="18"/>
       <c r="P1291" s="18"/>
-      <c r="Q1291" s="11" t="s">
-        <v>1877</v>
-      </c>
-      <c r="R1291" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1292" spans="1:18" ht="15" thickBot="1">
+      <c r="Q1291" s="18"/>
+      <c r="R1291" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1292" s="2">
         <v>1291</v>
       </c>
@@ -66233,28 +66546,28 @@
         <v>46244</v>
       </c>
       <c r="C1292" s="56" t="s">
-        <v>1878</v>
-      </c>
-      <c r="D1292" s="56">
-        <v>126214395</v>
-      </c>
-      <c r="E1292" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1292" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1292" s="57">
-        <v>355</v>
+        <v>1995</v>
+      </c>
+      <c r="D1292" s="56" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E1292" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1292" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1292" s="75">
+        <v>27098</v>
       </c>
       <c r="H1292" s="15">
-        <v>2278</v>
-      </c>
-      <c r="I1292" s="16" t="s">
-        <v>10</v>
+        <v>25544</v>
+      </c>
+      <c r="I1292" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="J1292" s="15" t="s">
-        <v>950</v>
+        <v>1997</v>
       </c>
       <c r="K1292" s="17" t="s">
         <v>12</v>
@@ -66264,148 +66577,108 @@
       <c r="N1292" s="40"/>
       <c r="O1292" s="18"/>
       <c r="P1292" s="18"/>
-      <c r="Q1292" s="18"/>
-      <c r="R1292" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1293" spans="1:18" ht="28.2" thickBot="1">
+      <c r="Q1292" s="11">
+        <v>95691585</v>
+      </c>
+      <c r="R1292" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:18" ht="15" thickBot="1">
       <c r="A1293" s="2">
         <v>1292</v>
       </c>
       <c r="B1293" s="10">
         <v>46244</v>
       </c>
-      <c r="C1293" s="56" t="s">
-        <v>47</v>
-      </c>
-      <c r="D1293" s="56" t="s">
-        <v>1879</v>
-      </c>
-      <c r="E1293" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1293" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1293" s="57">
-        <v>33404</v>
-      </c>
-      <c r="H1293" s="15">
-        <v>89137</v>
-      </c>
+      <c r="C1293" s="38"/>
+      <c r="D1293" s="38"/>
+      <c r="E1293" s="18"/>
+      <c r="F1293" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1293" s="75">
+        <v>4872</v>
+      </c>
+      <c r="H1293" s="18"/>
       <c r="I1293" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J1293" s="15" t="s">
-        <v>1880</v>
-      </c>
-      <c r="K1293" s="17" t="s">
-        <v>12</v>
-      </c>
+      <c r="J1293" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1293" s="18"/>
       <c r="L1293" s="18"/>
       <c r="M1293" s="18"/>
       <c r="N1293" s="40"/>
       <c r="O1293" s="18"/>
       <c r="P1293" s="18"/>
-      <c r="Q1293" s="11">
-        <v>95643750</v>
-      </c>
-      <c r="R1293" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1294" spans="1:18" ht="28.2" thickBot="1">
+      <c r="Q1293" s="18"/>
+      <c r="R1293" s="18"/>
+    </row>
+    <row r="1294" spans="1:18" ht="15" thickBot="1">
       <c r="A1294" s="2">
         <v>1293</v>
       </c>
       <c r="B1294" s="10">
         <v>46244</v>
       </c>
-      <c r="C1294" s="56" t="s">
-        <v>504</v>
-      </c>
-      <c r="D1294" s="56" t="s">
-        <v>1881</v>
-      </c>
-      <c r="E1294" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1294" s="13" t="s">
-        <v>22</v>
+      <c r="C1294" s="38"/>
+      <c r="D1294" s="38"/>
+      <c r="E1294" s="18"/>
+      <c r="F1294" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1294" s="57">
-        <v>7606</v>
-      </c>
-      <c r="H1294" s="15">
-        <v>66793</v>
-      </c>
+        <v>7876</v>
+      </c>
+      <c r="H1294" s="18"/>
       <c r="I1294" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J1294" s="15" t="s">
-        <v>1880</v>
-      </c>
-      <c r="K1294" s="17" t="s">
-        <v>12</v>
-      </c>
+      <c r="J1294" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1294" s="18"/>
       <c r="L1294" s="18"/>
       <c r="M1294" s="18"/>
       <c r="N1294" s="40"/>
       <c r="O1294" s="18"/>
       <c r="P1294" s="18"/>
-      <c r="Q1294" s="11">
-        <v>501924525</v>
-      </c>
-      <c r="R1294" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1295" spans="1:18" ht="27.6" thickBot="1">
+      <c r="Q1294" s="18"/>
+      <c r="R1294" s="18"/>
+    </row>
+    <row r="1295" spans="1:18" ht="15" thickBot="1">
       <c r="A1295" s="2">
         <v>1294</v>
       </c>
       <c r="B1295" s="10">
         <v>46244</v>
       </c>
-      <c r="C1295" s="56" t="s">
-        <v>906</v>
-      </c>
-      <c r="D1295" s="56">
-        <v>128333109</v>
-      </c>
-      <c r="E1295" s="12" t="s">
-        <v>21</v>
-      </c>
+      <c r="C1295" s="38"/>
+      <c r="D1295" s="38"/>
+      <c r="E1295" s="18"/>
       <c r="F1295" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1295" s="57">
-        <v>4900</v>
-      </c>
-      <c r="H1295" s="15">
-        <v>-6338</v>
-      </c>
+        <v>2328</v>
+      </c>
+      <c r="H1295" s="18"/>
       <c r="I1295" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J1295" s="15" t="s">
-        <v>890</v>
-      </c>
-      <c r="K1295" s="17" t="s">
-        <v>12</v>
-      </c>
+      <c r="J1295" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1295" s="18"/>
       <c r="L1295" s="18"/>
       <c r="M1295" s="18"/>
       <c r="N1295" s="40"/>
       <c r="O1295" s="18"/>
       <c r="P1295" s="18"/>
-      <c r="Q1295" s="11">
-        <v>95609530</v>
-      </c>
-      <c r="R1295" s="20" t="s">
-        <v>11</v>
-      </c>
+      <c r="Q1295" s="18"/>
+      <c r="R1295" s="18"/>
     </row>
     <row r="1296" spans="1:18" ht="15" thickBot="1">
       <c r="A1296" s="2">
@@ -66415,10 +66688,10 @@
         <v>46244</v>
       </c>
       <c r="C1296" s="56" t="s">
-        <v>1894</v>
+        <v>1874</v>
       </c>
       <c r="D1296" s="56">
-        <v>116033629</v>
+        <v>112067329</v>
       </c>
       <c r="E1296" s="12" t="s">
         <v>21</v>
@@ -66427,16 +66700,16 @@
         <v>122</v>
       </c>
       <c r="G1296" s="57">
-        <v>1702</v>
+        <v>2968</v>
       </c>
       <c r="H1296" s="15">
-        <v>5164</v>
+        <v>5613</v>
       </c>
       <c r="I1296" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1296" s="15" t="s">
-        <v>950</v>
+        <v>839</v>
       </c>
       <c r="K1296" s="17" t="s">
         <v>12</v>
@@ -66446,9 +66719,7 @@
       <c r="N1296" s="40"/>
       <c r="O1296" s="18"/>
       <c r="P1296" s="18"/>
-      <c r="Q1296" s="11">
-        <v>94250210</v>
-      </c>
+      <c r="Q1296" s="18"/>
       <c r="R1296" s="20" t="s">
         <v>11</v>
       </c>
@@ -66461,28 +66732,28 @@
         <v>46244</v>
       </c>
       <c r="C1297" s="56" t="s">
-        <v>1895</v>
-      </c>
-      <c r="D1297" s="56" t="s">
-        <v>1896</v>
+        <v>1875</v>
+      </c>
+      <c r="D1297" s="56">
+        <v>116806083</v>
       </c>
       <c r="E1297" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1297" s="13" t="s">
-        <v>22</v>
+      <c r="F1297" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1297" s="57">
-        <v>21668</v>
+        <v>442</v>
       </c>
       <c r="H1297" s="15">
-        <v>75184</v>
+        <v>7536</v>
       </c>
       <c r="I1297" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1297" s="15" t="s">
-        <v>1897</v>
+        <v>950</v>
       </c>
       <c r="K1297" s="17" t="s">
         <v>12</v>
@@ -66493,13 +66764,13 @@
       <c r="O1297" s="18"/>
       <c r="P1297" s="18"/>
       <c r="Q1297" s="11">
-        <v>557824163</v>
+        <v>79997138</v>
       </c>
       <c r="R1297" s="20" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="1298" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1298" spans="1:18" ht="15" thickBot="1">
       <c r="A1298" s="2">
         <v>1297</v>
       </c>
@@ -66507,28 +66778,28 @@
         <v>46244</v>
       </c>
       <c r="C1298" s="56" t="s">
-        <v>1898</v>
-      </c>
-      <c r="D1298" s="56" t="s">
-        <v>1899</v>
+        <v>1876</v>
+      </c>
+      <c r="D1298" s="56">
+        <v>113458078</v>
       </c>
       <c r="E1298" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1298" s="13" t="s">
-        <v>22</v>
+      <c r="F1298" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1298" s="57">
-        <v>9215</v>
+        <v>5913</v>
       </c>
       <c r="H1298" s="15">
-        <v>10278</v>
+        <v>1154</v>
       </c>
       <c r="I1298" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1298" s="15" t="s">
-        <v>49</v>
+        <v>950</v>
       </c>
       <c r="K1298" s="17" t="s">
         <v>12</v>
@@ -66543,7 +66814,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1299" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1299" spans="1:18" ht="27.6" thickBot="1">
       <c r="A1299" s="2">
         <v>1298</v>
       </c>
@@ -66551,28 +66822,28 @@
         <v>46244</v>
       </c>
       <c r="C1299" s="56" t="s">
-        <v>1900</v>
-      </c>
-      <c r="D1299" s="56" t="s">
-        <v>1901</v>
+        <v>638</v>
+      </c>
+      <c r="D1299" s="56">
+        <v>122952217</v>
       </c>
       <c r="E1299" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1299" s="13" t="s">
-        <v>22</v>
+      <c r="F1299" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1299" s="57">
-        <v>53578</v>
+        <v>4581</v>
       </c>
       <c r="H1299" s="15">
-        <v>46411</v>
+        <v>-8325</v>
       </c>
       <c r="I1299" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1299" s="15" t="s">
-        <v>49</v>
+        <v>950</v>
       </c>
       <c r="K1299" s="17" t="s">
         <v>12</v>
@@ -66582,7 +66853,9 @@
       <c r="N1299" s="40"/>
       <c r="O1299" s="18"/>
       <c r="P1299" s="18"/>
-      <c r="Q1299" s="18"/>
+      <c r="Q1299" s="11" t="s">
+        <v>1877</v>
+      </c>
       <c r="R1299" s="20" t="s">
         <v>11</v>
       </c>
@@ -66595,28 +66868,28 @@
         <v>46244</v>
       </c>
       <c r="C1300" s="56" t="s">
-        <v>1902</v>
-      </c>
-      <c r="D1300" s="56" t="s">
-        <v>1903</v>
-      </c>
-      <c r="E1300" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="F1300" s="13" t="s">
-        <v>22</v>
+        <v>1878</v>
+      </c>
+      <c r="D1300" s="56">
+        <v>126214395</v>
+      </c>
+      <c r="E1300" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1300" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1300" s="57">
-        <v>68833</v>
+        <v>355</v>
       </c>
       <c r="H1300" s="15">
-        <v>78793</v>
+        <v>2278</v>
       </c>
       <c r="I1300" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1300" s="15" t="s">
-        <v>1904</v>
+        <v>950</v>
       </c>
       <c r="K1300" s="17" t="s">
         <v>12</v>
@@ -66626,14 +66899,12 @@
       <c r="N1300" s="40"/>
       <c r="O1300" s="18"/>
       <c r="P1300" s="18"/>
-      <c r="Q1300" s="11">
-        <v>554186760</v>
-      </c>
+      <c r="Q1300" s="18"/>
       <c r="R1300" s="20" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="1301" spans="1:18" ht="15" thickBot="1">
+    <row r="1301" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1301" s="2">
         <v>1300</v>
       </c>
@@ -66641,28 +66912,28 @@
         <v>46244</v>
       </c>
       <c r="C1301" s="56" t="s">
-        <v>1905</v>
+        <v>47</v>
       </c>
       <c r="D1301" s="56" t="s">
-        <v>1906</v>
-      </c>
-      <c r="E1301" s="30" t="s">
-        <v>119</v>
+        <v>1879</v>
+      </c>
+      <c r="E1301" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="F1301" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1301" s="57">
-        <v>56757</v>
-      </c>
-      <c r="H1301" s="15" t="s">
-        <v>1907</v>
+        <v>33404</v>
+      </c>
+      <c r="H1301" s="15">
+        <v>89137</v>
       </c>
       <c r="I1301" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1301" s="15" t="s">
-        <v>1904</v>
+        <v>1880</v>
       </c>
       <c r="K1301" s="17" t="s">
         <v>12</v>
@@ -66673,13 +66944,13 @@
       <c r="O1301" s="18"/>
       <c r="P1301" s="18"/>
       <c r="Q1301" s="11">
-        <v>76969759</v>
+        <v>95643750</v>
       </c>
       <c r="R1301" s="20" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="1302" spans="1:18" ht="27.6" thickBot="1">
+    <row r="1302" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1302" s="2">
         <v>1301</v>
       </c>
@@ -66687,10 +66958,10 @@
         <v>46244</v>
       </c>
       <c r="C1302" s="56" t="s">
-        <v>1908</v>
+        <v>504</v>
       </c>
       <c r="D1302" s="56" t="s">
-        <v>1909</v>
+        <v>1881</v>
       </c>
       <c r="E1302" s="12" t="s">
         <v>21</v>
@@ -66699,16 +66970,16 @@
         <v>22</v>
       </c>
       <c r="G1302" s="57">
-        <v>61918</v>
+        <v>7606</v>
       </c>
       <c r="H1302" s="15">
-        <v>19939</v>
+        <v>66793</v>
       </c>
       <c r="I1302" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1302" s="15" t="s">
-        <v>46</v>
+        <v>1880</v>
       </c>
       <c r="K1302" s="17" t="s">
         <v>12</v>
@@ -66718,7 +66989,9 @@
       <c r="N1302" s="40"/>
       <c r="O1302" s="18"/>
       <c r="P1302" s="18"/>
-      <c r="Q1302" s="18"/>
+      <c r="Q1302" s="11">
+        <v>501924525</v>
+      </c>
       <c r="R1302" s="20" t="s">
         <v>11</v>
       </c>
@@ -66731,28 +67004,28 @@
         <v>46244</v>
       </c>
       <c r="C1303" s="56" t="s">
-        <v>1910</v>
-      </c>
-      <c r="D1303" s="56" t="s">
-        <v>1911</v>
-      </c>
-      <c r="E1303" s="30" t="s">
-        <v>119</v>
+        <v>906</v>
+      </c>
+      <c r="D1303" s="56">
+        <v>128333109</v>
+      </c>
+      <c r="E1303" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="F1303" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1303" s="57">
-        <v>8490</v>
+        <v>4900</v>
       </c>
       <c r="H1303" s="15">
-        <v>8101</v>
+        <v>-6338</v>
       </c>
       <c r="I1303" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1303" s="15" t="s">
-        <v>202</v>
+        <v>890</v>
       </c>
       <c r="K1303" s="17" t="s">
         <v>12</v>
@@ -66763,13 +67036,13 @@
       <c r="O1303" s="18"/>
       <c r="P1303" s="18"/>
       <c r="Q1303" s="11">
-        <v>98705284</v>
+        <v>95609530</v>
       </c>
       <c r="R1303" s="20" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="1304" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1304" spans="1:18" ht="15" thickBot="1">
       <c r="A1304" s="2">
         <v>1303</v>
       </c>
@@ -66777,28 +67050,28 @@
         <v>46244</v>
       </c>
       <c r="C1304" s="56" t="s">
-        <v>1947</v>
-      </c>
-      <c r="D1304" s="56" t="s">
-        <v>1948</v>
-      </c>
-      <c r="E1304" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="F1304" s="13" t="s">
-        <v>22</v>
+        <v>1894</v>
+      </c>
+      <c r="D1304" s="56">
+        <v>116033629</v>
+      </c>
+      <c r="E1304" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1304" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1304" s="57">
-        <v>18552</v>
+        <v>1702</v>
       </c>
       <c r="H1304" s="15">
-        <v>36476</v>
+        <v>5164</v>
       </c>
       <c r="I1304" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1304" s="15" t="s">
-        <v>49</v>
+        <v>950</v>
       </c>
       <c r="K1304" s="17" t="s">
         <v>12</v>
@@ -66808,12 +67081,14 @@
       <c r="N1304" s="40"/>
       <c r="O1304" s="18"/>
       <c r="P1304" s="18"/>
-      <c r="Q1304" s="18"/>
+      <c r="Q1304" s="11">
+        <v>94250210</v>
+      </c>
       <c r="R1304" s="20" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="1305" spans="1:18" ht="15" thickBot="1">
+    <row r="1305" spans="1:18" ht="27.6" thickBot="1">
       <c r="A1305" s="2">
         <v>1304</v>
       </c>
@@ -66821,28 +67096,28 @@
         <v>46244</v>
       </c>
       <c r="C1305" s="56" t="s">
-        <v>1949</v>
-      </c>
-      <c r="D1305" s="56">
-        <v>132109131</v>
+        <v>1895</v>
+      </c>
+      <c r="D1305" s="56" t="s">
+        <v>1896</v>
       </c>
       <c r="E1305" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1305" s="16" t="s">
-        <v>122</v>
+      <c r="F1305" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1305" s="57">
-        <v>1052</v>
+        <v>21668</v>
       </c>
       <c r="H1305" s="15">
-        <v>2979</v>
+        <v>75184</v>
       </c>
       <c r="I1305" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1305" s="15" t="s">
-        <v>715</v>
+        <v>1897</v>
       </c>
       <c r="K1305" s="17" t="s">
         <v>12</v>
@@ -66852,12 +67127,14 @@
       <c r="N1305" s="40"/>
       <c r="O1305" s="18"/>
       <c r="P1305" s="18"/>
-      <c r="Q1305" s="18"/>
+      <c r="Q1305" s="11">
+        <v>557824163</v>
+      </c>
       <c r="R1305" s="20" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="1306" spans="1:18" ht="15" thickBot="1">
+    <row r="1306" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1306" s="2">
         <v>1305</v>
       </c>
@@ -66865,10 +67142,10 @@
         <v>46244</v>
       </c>
       <c r="C1306" s="56" t="s">
-        <v>1962</v>
+        <v>1898</v>
       </c>
       <c r="D1306" s="56" t="s">
-        <v>1963</v>
+        <v>1899</v>
       </c>
       <c r="E1306" s="12" t="s">
         <v>21</v>
@@ -66877,33 +67154,31 @@
         <v>22</v>
       </c>
       <c r="G1306" s="57">
-        <v>71861</v>
+        <v>9215</v>
       </c>
       <c r="H1306" s="15">
-        <v>38386</v>
+        <v>10278</v>
       </c>
       <c r="I1306" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1306" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="K1306" s="61" t="s">
-        <v>1189</v>
+        <v>49</v>
+      </c>
+      <c r="K1306" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1306" s="18"/>
       <c r="M1306" s="18"/>
       <c r="N1306" s="40"/>
       <c r="O1306" s="18"/>
       <c r="P1306" s="18"/>
-      <c r="Q1306" s="11">
-        <v>77439516</v>
-      </c>
+      <c r="Q1306" s="18"/>
       <c r="R1306" s="20" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="1307" spans="1:18" ht="15" thickBot="1">
+    <row r="1307" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1307" s="2">
         <v>1306</v>
       </c>
@@ -66911,40 +67186,40 @@
         <v>46244</v>
       </c>
       <c r="C1307" s="56" t="s">
-        <v>1998</v>
-      </c>
-      <c r="D1307" s="56">
-        <v>105256785</v>
+        <v>1900</v>
+      </c>
+      <c r="D1307" s="56" t="s">
+        <v>1901</v>
       </c>
       <c r="E1307" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1307" s="16" t="s">
-        <v>122</v>
+      <c r="F1307" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1307" s="57">
-        <v>587</v>
+        <v>53578</v>
       </c>
       <c r="H1307" s="15">
-        <v>-9022</v>
-      </c>
-      <c r="I1307" s="59" t="s">
-        <v>1177</v>
-      </c>
-      <c r="J1307" s="18"/>
+        <v>46411</v>
+      </c>
+      <c r="I1307" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1307" s="15" t="s">
+        <v>49</v>
+      </c>
       <c r="K1307" s="17" t="s">
         <v>12</v>
       </c>
       <c r="L1307" s="18"/>
-      <c r="M1307" s="16" t="s">
-        <v>1999</v>
-      </c>
+      <c r="M1307" s="18"/>
       <c r="N1307" s="40"/>
       <c r="O1307" s="18"/>
       <c r="P1307" s="18"/>
       <c r="Q1307" s="18"/>
-      <c r="R1307" s="16" t="s">
-        <v>1178</v>
+      <c r="R1307" s="20" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="1308" spans="1:18" ht="15" thickBot="1">
@@ -66955,43 +67230,45 @@
         <v>46244</v>
       </c>
       <c r="C1308" s="56" t="s">
-        <v>2000</v>
-      </c>
-      <c r="D1308" s="56">
-        <v>65444142</v>
-      </c>
-      <c r="E1308" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1308" s="16" t="s">
-        <v>122</v>
+        <v>1902</v>
+      </c>
+      <c r="D1308" s="56" t="s">
+        <v>1903</v>
+      </c>
+      <c r="E1308" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1308" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1308" s="57">
-        <v>2227</v>
+        <v>68833</v>
       </c>
       <c r="H1308" s="15">
-        <v>-9283</v>
-      </c>
-      <c r="I1308" s="59" t="s">
-        <v>1177</v>
-      </c>
-      <c r="J1308" s="18"/>
+        <v>78793</v>
+      </c>
+      <c r="I1308" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1308" s="15" t="s">
+        <v>1904</v>
+      </c>
       <c r="K1308" s="17" t="s">
         <v>12</v>
       </c>
       <c r="L1308" s="18"/>
-      <c r="M1308" s="16" t="s">
-        <v>1999</v>
-      </c>
+      <c r="M1308" s="18"/>
       <c r="N1308" s="40"/>
       <c r="O1308" s="18"/>
       <c r="P1308" s="18"/>
-      <c r="Q1308" s="18"/>
-      <c r="R1308" s="16" t="s">
-        <v>1178</v>
-      </c>
-    </row>
-    <row r="1309" spans="1:18" ht="27.6" thickBot="1">
+      <c r="Q1308" s="11">
+        <v>554186760</v>
+      </c>
+      <c r="R1308" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:18" ht="15" thickBot="1">
       <c r="A1309" s="2">
         <v>1308</v>
       </c>
@@ -66999,43 +67276,45 @@
         <v>46244</v>
       </c>
       <c r="C1309" s="56" t="s">
-        <v>2001</v>
-      </c>
-      <c r="D1309" s="56">
-        <v>99086357</v>
-      </c>
-      <c r="E1309" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1309" s="16" t="s">
-        <v>122</v>
+        <v>1905</v>
+      </c>
+      <c r="D1309" s="56" t="s">
+        <v>1906</v>
+      </c>
+      <c r="E1309" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1309" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1309" s="57">
-        <v>9268</v>
-      </c>
-      <c r="H1309" s="15">
-        <v>477</v>
-      </c>
-      <c r="I1309" s="59" t="s">
-        <v>1177</v>
-      </c>
-      <c r="J1309" s="18"/>
+        <v>56757</v>
+      </c>
+      <c r="H1309" s="15" t="s">
+        <v>1907</v>
+      </c>
+      <c r="I1309" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1309" s="15" t="s">
+        <v>1904</v>
+      </c>
       <c r="K1309" s="17" t="s">
         <v>12</v>
       </c>
       <c r="L1309" s="18"/>
-      <c r="M1309" s="16" t="s">
-        <v>1999</v>
-      </c>
+      <c r="M1309" s="18"/>
       <c r="N1309" s="40"/>
       <c r="O1309" s="18"/>
       <c r="P1309" s="18"/>
-      <c r="Q1309" s="18"/>
-      <c r="R1309" s="16" t="s">
-        <v>1178</v>
-      </c>
-    </row>
-    <row r="1310" spans="1:18" ht="15" thickBot="1">
+      <c r="Q1309" s="11">
+        <v>76969759</v>
+      </c>
+      <c r="R1309" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:18" ht="27.6" thickBot="1">
       <c r="A1310" s="2">
         <v>1309</v>
       </c>
@@ -67043,43 +67322,43 @@
         <v>46244</v>
       </c>
       <c r="C1310" s="56" t="s">
-        <v>2002</v>
-      </c>
-      <c r="D1310" s="56">
-        <v>68572777</v>
+        <v>1908</v>
+      </c>
+      <c r="D1310" s="56" t="s">
+        <v>1909</v>
       </c>
       <c r="E1310" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F1310" s="16" t="s">
-        <v>122</v>
+      <c r="F1310" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G1310" s="57">
-        <v>2295</v>
+        <v>61918</v>
       </c>
       <c r="H1310" s="15">
-        <v>970</v>
-      </c>
-      <c r="I1310" s="59" t="s">
-        <v>1177</v>
-      </c>
-      <c r="J1310" s="18"/>
+        <v>19939</v>
+      </c>
+      <c r="I1310" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1310" s="15" t="s">
+        <v>46</v>
+      </c>
       <c r="K1310" s="17" t="s">
         <v>12</v>
       </c>
       <c r="L1310" s="18"/>
-      <c r="M1310" s="16" t="s">
-        <v>1999</v>
-      </c>
+      <c r="M1310" s="18"/>
       <c r="N1310" s="40"/>
       <c r="O1310" s="18"/>
       <c r="P1310" s="18"/>
       <c r="Q1310" s="18"/>
-      <c r="R1310" s="16" t="s">
-        <v>1178</v>
-      </c>
-    </row>
-    <row r="1311" spans="1:18" ht="28.2" thickBot="1">
+      <c r="R1310" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:18" ht="27.6" thickBot="1">
       <c r="A1311" s="2">
         <v>1310</v>
       </c>
@@ -67087,31 +67366,31 @@
         <v>46244</v>
       </c>
       <c r="C1311" s="56" t="s">
-        <v>2003</v>
-      </c>
-      <c r="D1311" s="56">
-        <v>2232021</v>
-      </c>
-      <c r="E1311" s="37" t="s">
-        <v>121</v>
+        <v>1910</v>
+      </c>
+      <c r="D1311" s="56" t="s">
+        <v>1911</v>
+      </c>
+      <c r="E1311" s="30" t="s">
+        <v>119</v>
       </c>
       <c r="F1311" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="G1311" s="75">
-        <v>8606</v>
-      </c>
-      <c r="H1311" s="76">
-        <v>9540</v>
-      </c>
-      <c r="I1311" s="15" t="s">
-        <v>123</v>
+      <c r="G1311" s="57">
+        <v>8490</v>
+      </c>
+      <c r="H1311" s="15">
+        <v>8101</v>
+      </c>
+      <c r="I1311" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="J1311" s="15" t="s">
-        <v>2004</v>
-      </c>
-      <c r="K1311" s="61" t="s">
-        <v>1189</v>
+        <v>202</v>
+      </c>
+      <c r="K1311" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1311" s="18"/>
       <c r="M1311" s="18"/>
@@ -67119,7 +67398,7 @@
       <c r="O1311" s="18"/>
       <c r="P1311" s="18"/>
       <c r="Q1311" s="11">
-        <v>99727424</v>
+        <v>98705284</v>
       </c>
       <c r="R1311" s="20" t="s">
         <v>11</v>
@@ -67133,42 +67412,2124 @@
         <v>46244</v>
       </c>
       <c r="C1312" s="56" t="s">
-        <v>2005</v>
-      </c>
-      <c r="D1312" s="56">
-        <v>75278541</v>
-      </c>
-      <c r="E1312" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1312" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1312" s="75">
-        <v>1802</v>
-      </c>
-      <c r="H1312" s="76">
-        <v>7412</v>
-      </c>
-      <c r="I1312" s="15" t="s">
-        <v>123</v>
+        <v>1947</v>
+      </c>
+      <c r="D1312" s="56" t="s">
+        <v>1948</v>
+      </c>
+      <c r="E1312" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1312" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1312" s="57">
+        <v>18552</v>
+      </c>
+      <c r="H1312" s="15">
+        <v>36476</v>
+      </c>
+      <c r="I1312" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="J1312" s="15" t="s">
-        <v>2004</v>
-      </c>
-      <c r="K1312" s="61" t="s">
-        <v>1189</v>
+        <v>49</v>
+      </c>
+      <c r="K1312" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1312" s="18"/>
       <c r="M1312" s="18"/>
       <c r="N1312" s="40"/>
       <c r="O1312" s="18"/>
       <c r="P1312" s="18"/>
-      <c r="Q1312" s="11">
-        <v>79294748</v>
-      </c>
+      <c r="Q1312" s="18"/>
       <c r="R1312" s="20" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:18" ht="15" thickBot="1">
+      <c r="A1313" s="2">
+        <v>1312</v>
+      </c>
+      <c r="B1313" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1313" s="56" t="s">
+        <v>1949</v>
+      </c>
+      <c r="D1313" s="56">
+        <v>132109131</v>
+      </c>
+      <c r="E1313" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1313" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1313" s="57">
+        <v>1052</v>
+      </c>
+      <c r="H1313" s="15">
+        <v>2979</v>
+      </c>
+      <c r="I1313" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1313" s="15" t="s">
+        <v>715</v>
+      </c>
+      <c r="K1313" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1313" s="18"/>
+      <c r="M1313" s="18"/>
+      <c r="N1313" s="40"/>
+      <c r="O1313" s="18"/>
+      <c r="P1313" s="18"/>
+      <c r="Q1313" s="18"/>
+      <c r="R1313" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:18" ht="15" thickBot="1">
+      <c r="A1314" s="2">
+        <v>1313</v>
+      </c>
+      <c r="B1314" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1314" s="56" t="s">
+        <v>1962</v>
+      </c>
+      <c r="D1314" s="56" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E1314" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1314" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1314" s="57">
+        <v>71861</v>
+      </c>
+      <c r="H1314" s="15">
+        <v>38386</v>
+      </c>
+      <c r="I1314" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1314" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="K1314" s="61" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1314" s="18"/>
+      <c r="M1314" s="18"/>
+      <c r="N1314" s="40"/>
+      <c r="O1314" s="18"/>
+      <c r="P1314" s="18"/>
+      <c r="Q1314" s="11">
+        <v>77439516</v>
+      </c>
+      <c r="R1314" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:18" ht="15" thickBot="1">
+      <c r="A1315" s="2">
+        <v>1314</v>
+      </c>
+      <c r="B1315" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1315" s="56" t="s">
+        <v>1998</v>
+      </c>
+      <c r="D1315" s="56">
+        <v>105256785</v>
+      </c>
+      <c r="E1315" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1315" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1315" s="57">
+        <v>587</v>
+      </c>
+      <c r="H1315" s="15">
+        <v>-9022</v>
+      </c>
+      <c r="I1315" s="59" t="s">
+        <v>1177</v>
+      </c>
+      <c r="J1315" s="18"/>
+      <c r="K1315" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1315" s="18"/>
+      <c r="M1315" s="16" t="s">
+        <v>1999</v>
+      </c>
+      <c r="N1315" s="40"/>
+      <c r="O1315" s="18"/>
+      <c r="P1315" s="18"/>
+      <c r="Q1315" s="18"/>
+      <c r="R1315" s="16" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:18" ht="15" thickBot="1">
+      <c r="A1316" s="2">
+        <v>1315</v>
+      </c>
+      <c r="B1316" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1316" s="56" t="s">
+        <v>2000</v>
+      </c>
+      <c r="D1316" s="56">
+        <v>65444142</v>
+      </c>
+      <c r="E1316" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1316" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1316" s="57">
+        <v>2227</v>
+      </c>
+      <c r="H1316" s="15">
+        <v>-9283</v>
+      </c>
+      <c r="I1316" s="59" t="s">
+        <v>1177</v>
+      </c>
+      <c r="J1316" s="18"/>
+      <c r="K1316" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1316" s="18"/>
+      <c r="M1316" s="16" t="s">
+        <v>1999</v>
+      </c>
+      <c r="N1316" s="40"/>
+      <c r="O1316" s="18"/>
+      <c r="P1316" s="18"/>
+      <c r="Q1316" s="18"/>
+      <c r="R1316" s="16" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1317" s="2">
+        <v>1316</v>
+      </c>
+      <c r="B1317" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1317" s="56" t="s">
+        <v>2001</v>
+      </c>
+      <c r="D1317" s="56">
+        <v>99086357</v>
+      </c>
+      <c r="E1317" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1317" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1317" s="57">
+        <v>9268</v>
+      </c>
+      <c r="H1317" s="15">
+        <v>477</v>
+      </c>
+      <c r="I1317" s="59" t="s">
+        <v>1177</v>
+      </c>
+      <c r="J1317" s="18"/>
+      <c r="K1317" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1317" s="18"/>
+      <c r="M1317" s="16" t="s">
+        <v>1999</v>
+      </c>
+      <c r="N1317" s="40"/>
+      <c r="O1317" s="18"/>
+      <c r="P1317" s="18"/>
+      <c r="Q1317" s="18"/>
+      <c r="R1317" s="16" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:18" ht="15" thickBot="1">
+      <c r="A1318" s="2">
+        <v>1317</v>
+      </c>
+      <c r="B1318" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1318" s="56" t="s">
+        <v>2002</v>
+      </c>
+      <c r="D1318" s="56">
+        <v>68572777</v>
+      </c>
+      <c r="E1318" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1318" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1318" s="57">
+        <v>2295</v>
+      </c>
+      <c r="H1318" s="15">
+        <v>970</v>
+      </c>
+      <c r="I1318" s="59" t="s">
+        <v>1177</v>
+      </c>
+      <c r="J1318" s="18"/>
+      <c r="K1318" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1318" s="18"/>
+      <c r="M1318" s="16" t="s">
+        <v>1999</v>
+      </c>
+      <c r="N1318" s="40"/>
+      <c r="O1318" s="18"/>
+      <c r="P1318" s="18"/>
+      <c r="Q1318" s="18"/>
+      <c r="R1318" s="16" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1319" s="2">
+        <v>1318</v>
+      </c>
+      <c r="B1319" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1319" s="56" t="s">
+        <v>2003</v>
+      </c>
+      <c r="D1319" s="56">
+        <v>2232021</v>
+      </c>
+      <c r="E1319" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1319" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1319" s="75">
+        <v>8606</v>
+      </c>
+      <c r="H1319" s="76">
+        <v>9540</v>
+      </c>
+      <c r="I1319" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1319" s="15" t="s">
+        <v>2004</v>
+      </c>
+      <c r="K1319" s="61" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1319" s="18"/>
+      <c r="M1319" s="18"/>
+      <c r="N1319" s="40"/>
+      <c r="O1319" s="18"/>
+      <c r="P1319" s="18"/>
+      <c r="Q1319" s="11">
+        <v>99727424</v>
+      </c>
+      <c r="R1319" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1320" s="2">
+        <v>1319</v>
+      </c>
+      <c r="B1320" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1320" s="56" t="s">
+        <v>2005</v>
+      </c>
+      <c r="D1320" s="56">
+        <v>75278541</v>
+      </c>
+      <c r="E1320" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1320" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1320" s="75">
+        <v>1802</v>
+      </c>
+      <c r="H1320" s="76">
+        <v>7412</v>
+      </c>
+      <c r="I1320" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1320" s="15" t="s">
+        <v>2004</v>
+      </c>
+      <c r="K1320" s="61" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1320" s="18"/>
+      <c r="M1320" s="18"/>
+      <c r="N1320" s="40"/>
+      <c r="O1320" s="18"/>
+      <c r="P1320" s="18"/>
+      <c r="Q1320" s="11">
+        <v>79294748</v>
+      </c>
+      <c r="R1320" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1321" s="2">
+        <v>1320</v>
+      </c>
+      <c r="B1321" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1321" s="56" t="s">
+        <v>2011</v>
+      </c>
+      <c r="D1321" s="56" t="s">
+        <v>2012</v>
+      </c>
+      <c r="E1321" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1321" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1321" s="75">
+        <v>83932</v>
+      </c>
+      <c r="H1321" s="76">
+        <v>23434</v>
+      </c>
+      <c r="I1321" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1321" s="15" t="s">
+        <v>1880</v>
+      </c>
+      <c r="K1321" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1321" s="18"/>
+      <c r="M1321" s="18"/>
+      <c r="N1321" s="40"/>
+      <c r="O1321" s="18"/>
+      <c r="P1321" s="18"/>
+      <c r="Q1321" s="11">
+        <v>94850550</v>
+      </c>
+      <c r="R1321" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:18" ht="15" thickBot="1">
+      <c r="A1322" s="2">
+        <v>1321</v>
+      </c>
+      <c r="B1322" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1322" s="56" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D1322" s="56" t="s">
+        <v>2014</v>
+      </c>
+      <c r="E1322" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1322" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1322" s="75">
+        <v>28764</v>
+      </c>
+      <c r="H1322" s="76">
+        <v>94819</v>
+      </c>
+      <c r="I1322" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1322" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1322" s="18"/>
+      <c r="L1322" s="18"/>
+      <c r="M1322" s="18"/>
+      <c r="N1322" s="40"/>
+      <c r="O1322" s="18"/>
+      <c r="P1322" s="18"/>
+      <c r="Q1322" s="18"/>
+      <c r="R1322" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:18" ht="15" thickBot="1">
+      <c r="A1323" s="2">
+        <v>1322</v>
+      </c>
+      <c r="B1323" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1323" s="56" t="s">
+        <v>2015</v>
+      </c>
+      <c r="D1323" s="56" t="s">
+        <v>2016</v>
+      </c>
+      <c r="E1323" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1323" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1323" s="75">
+        <v>2709</v>
+      </c>
+      <c r="H1323" s="76" t="s">
+        <v>2017</v>
+      </c>
+      <c r="I1323" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1323" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1323" s="18"/>
+      <c r="L1323" s="18"/>
+      <c r="M1323" s="18"/>
+      <c r="N1323" s="40"/>
+      <c r="O1323" s="18"/>
+      <c r="P1323" s="18"/>
+      <c r="Q1323" s="18"/>
+      <c r="R1323" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:18" ht="15" thickBot="1">
+      <c r="A1324" s="2">
+        <v>1323</v>
+      </c>
+      <c r="B1324" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1324" s="56" t="s">
+        <v>2018</v>
+      </c>
+      <c r="D1324" s="56" t="s">
+        <v>2019</v>
+      </c>
+      <c r="E1324" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1324" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1324" s="75">
+        <v>33942</v>
+      </c>
+      <c r="H1324" s="76">
+        <v>65018</v>
+      </c>
+      <c r="I1324" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1324" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1324" s="18"/>
+      <c r="L1324" s="18"/>
+      <c r="M1324" s="18"/>
+      <c r="N1324" s="40"/>
+      <c r="O1324" s="18"/>
+      <c r="P1324" s="18"/>
+      <c r="Q1324" s="18"/>
+      <c r="R1324" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:18" ht="15" thickBot="1">
+      <c r="A1325" s="2">
+        <v>1324</v>
+      </c>
+      <c r="B1325" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1325" s="56" t="s">
+        <v>2020</v>
+      </c>
+      <c r="D1325" s="56" t="s">
+        <v>2021</v>
+      </c>
+      <c r="E1325" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1325" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1325" s="75">
+        <v>39877</v>
+      </c>
+      <c r="H1325" s="76">
+        <v>39267</v>
+      </c>
+      <c r="I1325" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1325" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1325" s="18"/>
+      <c r="L1325" s="18"/>
+      <c r="M1325" s="18"/>
+      <c r="N1325" s="40"/>
+      <c r="O1325" s="18"/>
+      <c r="P1325" s="18"/>
+      <c r="Q1325" s="18"/>
+      <c r="R1325" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:18" ht="15" thickBot="1">
+      <c r="A1326" s="2">
+        <v>1325</v>
+      </c>
+      <c r="B1326" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1326" s="56" t="s">
+        <v>2022</v>
+      </c>
+      <c r="D1326" s="56">
+        <v>128469614</v>
+      </c>
+      <c r="E1326" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1326" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1326" s="75">
+        <v>9778</v>
+      </c>
+      <c r="H1326" s="76">
+        <v>3878</v>
+      </c>
+      <c r="I1326" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1326" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1326" s="18"/>
+      <c r="L1326" s="18"/>
+      <c r="M1326" s="18"/>
+      <c r="N1326" s="40"/>
+      <c r="O1326" s="18"/>
+      <c r="P1326" s="18"/>
+      <c r="Q1326" s="18"/>
+      <c r="R1326" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:18" ht="15" thickBot="1">
+      <c r="A1327" s="2">
+        <v>1326</v>
+      </c>
+      <c r="B1327" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1327" s="56" t="s">
+        <v>2023</v>
+      </c>
+      <c r="D1327" s="56">
+        <v>127568327</v>
+      </c>
+      <c r="E1327" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1327" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1327" s="75">
+        <v>679</v>
+      </c>
+      <c r="H1327" s="76">
+        <v>8619</v>
+      </c>
+      <c r="I1327" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1327" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1327" s="18"/>
+      <c r="L1327" s="18"/>
+      <c r="M1327" s="18"/>
+      <c r="N1327" s="40"/>
+      <c r="O1327" s="18"/>
+      <c r="P1327" s="18"/>
+      <c r="Q1327" s="18"/>
+      <c r="R1327" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:18" ht="15" thickBot="1">
+      <c r="A1328" s="2">
+        <v>1327</v>
+      </c>
+      <c r="B1328" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1328" s="56" t="s">
+        <v>2024</v>
+      </c>
+      <c r="D1328" s="56">
+        <v>121437439</v>
+      </c>
+      <c r="E1328" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1328" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1328" s="75">
+        <v>1451</v>
+      </c>
+      <c r="H1328" s="76">
+        <v>4867</v>
+      </c>
+      <c r="I1328" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1328" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1328" s="18"/>
+      <c r="L1328" s="18"/>
+      <c r="M1328" s="18"/>
+      <c r="N1328" s="40"/>
+      <c r="O1328" s="18"/>
+      <c r="P1328" s="18"/>
+      <c r="Q1328" s="18"/>
+      <c r="R1328" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:18" ht="15" thickBot="1">
+      <c r="A1329" s="2">
+        <v>1328</v>
+      </c>
+      <c r="B1329" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1329" s="56" t="s">
+        <v>2025</v>
+      </c>
+      <c r="D1329" s="56">
+        <v>107482408</v>
+      </c>
+      <c r="E1329" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1329" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1329" s="75">
+        <v>2481</v>
+      </c>
+      <c r="H1329" s="76">
+        <v>296</v>
+      </c>
+      <c r="I1329" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1329" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1329" s="18"/>
+      <c r="L1329" s="18"/>
+      <c r="M1329" s="18"/>
+      <c r="N1329" s="40"/>
+      <c r="O1329" s="18"/>
+      <c r="P1329" s="18"/>
+      <c r="Q1329" s="18"/>
+      <c r="R1329" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:18" ht="15" thickBot="1">
+      <c r="A1330" s="2">
+        <v>1329</v>
+      </c>
+      <c r="B1330" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1330" s="56" t="s">
+        <v>2026</v>
+      </c>
+      <c r="D1330" s="56">
+        <v>118101831</v>
+      </c>
+      <c r="E1330" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1330" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1330" s="75">
+        <v>2394</v>
+      </c>
+      <c r="H1330" s="76">
+        <v>3469</v>
+      </c>
+      <c r="I1330" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1330" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1330" s="18"/>
+      <c r="L1330" s="18"/>
+      <c r="M1330" s="18"/>
+      <c r="N1330" s="40"/>
+      <c r="O1330" s="18"/>
+      <c r="P1330" s="18"/>
+      <c r="Q1330" s="18"/>
+      <c r="R1330" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:18" ht="15" thickBot="1">
+      <c r="A1331" s="2">
+        <v>1330</v>
+      </c>
+      <c r="B1331" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1331" s="56" t="s">
+        <v>2027</v>
+      </c>
+      <c r="D1331" s="56">
+        <v>132531222</v>
+      </c>
+      <c r="E1331" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1331" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1331" s="75">
+        <v>4525</v>
+      </c>
+      <c r="H1331" s="76" t="s">
+        <v>2028</v>
+      </c>
+      <c r="I1331" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1331" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1331" s="18"/>
+      <c r="L1331" s="18"/>
+      <c r="M1331" s="18"/>
+      <c r="N1331" s="40"/>
+      <c r="O1331" s="18"/>
+      <c r="P1331" s="18"/>
+      <c r="Q1331" s="18"/>
+      <c r="R1331" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:18" ht="15" thickBot="1">
+      <c r="A1332" s="2">
+        <v>1331</v>
+      </c>
+      <c r="B1332" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1332" s="56" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1332" s="56">
+        <v>103453635</v>
+      </c>
+      <c r="E1332" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1332" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1332" s="75">
+        <v>9012</v>
+      </c>
+      <c r="H1332" s="76">
+        <v>2924</v>
+      </c>
+      <c r="I1332" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1332" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1332" s="18"/>
+      <c r="L1332" s="18"/>
+      <c r="M1332" s="18"/>
+      <c r="N1332" s="40"/>
+      <c r="O1332" s="18"/>
+      <c r="P1332" s="18"/>
+      <c r="Q1332" s="18"/>
+      <c r="R1332" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:18" ht="15" thickBot="1">
+      <c r="A1333" s="2">
+        <v>1332</v>
+      </c>
+      <c r="B1333" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1333" s="56" t="s">
+        <v>2029</v>
+      </c>
+      <c r="D1333" s="56" t="s">
+        <v>2030</v>
+      </c>
+      <c r="E1333" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1333" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1333" s="75">
+        <v>22913</v>
+      </c>
+      <c r="H1333" s="76">
+        <v>75303</v>
+      </c>
+      <c r="I1333" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1333" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1333" s="18"/>
+      <c r="L1333" s="18"/>
+      <c r="M1333" s="18"/>
+      <c r="N1333" s="40"/>
+      <c r="O1333" s="18"/>
+      <c r="P1333" s="18"/>
+      <c r="Q1333" s="18"/>
+      <c r="R1333" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:18" ht="15" thickBot="1">
+      <c r="A1334" s="2">
+        <v>1333</v>
+      </c>
+      <c r="B1334" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1334" s="56" t="s">
+        <v>2031</v>
+      </c>
+      <c r="D1334" s="56">
+        <v>122051342</v>
+      </c>
+      <c r="E1334" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1334" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1334" s="75">
+        <v>2191</v>
+      </c>
+      <c r="H1334" s="76">
+        <v>113</v>
+      </c>
+      <c r="I1334" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1334" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1334" s="18"/>
+      <c r="L1334" s="18"/>
+      <c r="M1334" s="18"/>
+      <c r="N1334" s="40"/>
+      <c r="O1334" s="18"/>
+      <c r="P1334" s="18"/>
+      <c r="Q1334" s="18"/>
+      <c r="R1334" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:18" ht="15" thickBot="1">
+      <c r="A1335" s="2">
+        <v>1334</v>
+      </c>
+      <c r="B1335" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1335" s="56" t="s">
+        <v>2032</v>
+      </c>
+      <c r="D1335" s="56" t="s">
+        <v>2033</v>
+      </c>
+      <c r="E1335" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1335" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1335" s="75">
+        <v>65429</v>
+      </c>
+      <c r="H1335" s="76">
+        <v>15184</v>
+      </c>
+      <c r="I1335" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1335" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1335" s="18"/>
+      <c r="L1335" s="18"/>
+      <c r="M1335" s="18"/>
+      <c r="N1335" s="40"/>
+      <c r="O1335" s="18"/>
+      <c r="P1335" s="18"/>
+      <c r="Q1335" s="18"/>
+      <c r="R1335" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:18" ht="15" thickBot="1">
+      <c r="A1336" s="2">
+        <v>1335</v>
+      </c>
+      <c r="B1336" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1336" s="56" t="s">
+        <v>2034</v>
+      </c>
+      <c r="D1336" s="56" t="s">
+        <v>2035</v>
+      </c>
+      <c r="E1336" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1336" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1336" s="75">
+        <v>82948</v>
+      </c>
+      <c r="H1336" s="76">
+        <v>67236</v>
+      </c>
+      <c r="I1336" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1336" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1336" s="18"/>
+      <c r="L1336" s="18"/>
+      <c r="M1336" s="18"/>
+      <c r="N1336" s="40"/>
+      <c r="O1336" s="18"/>
+      <c r="P1336" s="18"/>
+      <c r="Q1336" s="18"/>
+      <c r="R1336" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:18" ht="15" thickBot="1">
+      <c r="A1337" s="2">
+        <v>1336</v>
+      </c>
+      <c r="B1337" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1337" s="56" t="s">
+        <v>305</v>
+      </c>
+      <c r="D1337" s="56">
+        <v>96895153</v>
+      </c>
+      <c r="E1337" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1337" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1337" s="75">
+        <v>1376</v>
+      </c>
+      <c r="H1337" s="76">
+        <v>6502</v>
+      </c>
+      <c r="I1337" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1337" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1337" s="18"/>
+      <c r="L1337" s="18"/>
+      <c r="M1337" s="18"/>
+      <c r="N1337" s="40"/>
+      <c r="O1337" s="18"/>
+      <c r="P1337" s="18"/>
+      <c r="Q1337" s="18"/>
+      <c r="R1337" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:18" ht="15" thickBot="1">
+      <c r="A1338" s="2">
+        <v>1337</v>
+      </c>
+      <c r="B1338" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1338" s="56" t="s">
+        <v>2036</v>
+      </c>
+      <c r="D1338" s="56">
+        <v>86305769</v>
+      </c>
+      <c r="E1338" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1338" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1338" s="75">
+        <v>7494</v>
+      </c>
+      <c r="H1338" s="76">
+        <v>9639</v>
+      </c>
+      <c r="I1338" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1338" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1338" s="18"/>
+      <c r="L1338" s="18"/>
+      <c r="M1338" s="18"/>
+      <c r="N1338" s="40"/>
+      <c r="O1338" s="18"/>
+      <c r="P1338" s="18"/>
+      <c r="Q1338" s="18"/>
+      <c r="R1338" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:18" ht="15" thickBot="1">
+      <c r="A1339" s="2">
+        <v>1338</v>
+      </c>
+      <c r="B1339" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1339" s="56" t="s">
+        <v>2037</v>
+      </c>
+      <c r="D1339" s="56">
+        <v>131509592</v>
+      </c>
+      <c r="E1339" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1339" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1339" s="75">
+        <v>8507</v>
+      </c>
+      <c r="H1339" s="76" t="s">
+        <v>2038</v>
+      </c>
+      <c r="I1339" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1339" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1339" s="18"/>
+      <c r="L1339" s="18"/>
+      <c r="M1339" s="18"/>
+      <c r="N1339" s="40"/>
+      <c r="O1339" s="18"/>
+      <c r="P1339" s="18"/>
+      <c r="Q1339" s="18"/>
+      <c r="R1339" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:18" ht="15" thickBot="1">
+      <c r="A1340" s="2">
+        <v>1339</v>
+      </c>
+      <c r="B1340" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1340" s="56" t="s">
+        <v>2039</v>
+      </c>
+      <c r="D1340" s="56">
+        <v>120247757</v>
+      </c>
+      <c r="E1340" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1340" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1340" s="75">
+        <v>9551</v>
+      </c>
+      <c r="H1340" s="76">
+        <v>9234</v>
+      </c>
+      <c r="I1340" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1340" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1340" s="18"/>
+      <c r="L1340" s="18"/>
+      <c r="M1340" s="18"/>
+      <c r="N1340" s="40"/>
+      <c r="O1340" s="18"/>
+      <c r="P1340" s="18"/>
+      <c r="Q1340" s="18"/>
+      <c r="R1340" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:18" ht="15" thickBot="1">
+      <c r="A1341" s="2">
+        <v>1340</v>
+      </c>
+      <c r="B1341" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1341" s="56" t="s">
+        <v>2040</v>
+      </c>
+      <c r="D1341" s="56">
+        <v>115776722</v>
+      </c>
+      <c r="E1341" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1341" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1341" s="75">
+        <v>8899</v>
+      </c>
+      <c r="H1341" s="76">
+        <v>2991</v>
+      </c>
+      <c r="I1341" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1341" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1341" s="18"/>
+      <c r="L1341" s="18"/>
+      <c r="M1341" s="18"/>
+      <c r="N1341" s="40"/>
+      <c r="O1341" s="18"/>
+      <c r="P1341" s="18"/>
+      <c r="Q1341" s="18"/>
+      <c r="R1341" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:18" ht="15" thickBot="1">
+      <c r="A1342" s="2">
+        <v>1341</v>
+      </c>
+      <c r="B1342" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1342" s="56" t="s">
+        <v>527</v>
+      </c>
+      <c r="D1342" s="56">
+        <v>108708968</v>
+      </c>
+      <c r="E1342" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1342" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1342" s="75">
+        <v>9595</v>
+      </c>
+      <c r="H1342" s="76">
+        <v>1032</v>
+      </c>
+      <c r="I1342" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1342" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1342" s="18"/>
+      <c r="L1342" s="18"/>
+      <c r="M1342" s="18"/>
+      <c r="N1342" s="40"/>
+      <c r="O1342" s="18"/>
+      <c r="P1342" s="18"/>
+      <c r="Q1342" s="18"/>
+      <c r="R1342" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:18" ht="15" thickBot="1">
+      <c r="A1343" s="2">
+        <v>1342</v>
+      </c>
+      <c r="B1343" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1343" s="56" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1343" s="56">
+        <v>125274058</v>
+      </c>
+      <c r="E1343" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1343" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1343" s="75">
+        <v>6013</v>
+      </c>
+      <c r="H1343" s="76">
+        <v>1665</v>
+      </c>
+      <c r="I1343" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1343" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1343" s="18"/>
+      <c r="L1343" s="18"/>
+      <c r="M1343" s="18"/>
+      <c r="N1343" s="40"/>
+      <c r="O1343" s="18"/>
+      <c r="P1343" s="18"/>
+      <c r="Q1343" s="18"/>
+      <c r="R1343" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:18" ht="15" thickBot="1">
+      <c r="A1344" s="2">
+        <v>1343</v>
+      </c>
+      <c r="B1344" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1344" s="56" t="s">
+        <v>2041</v>
+      </c>
+      <c r="D1344" s="56">
+        <v>131629453</v>
+      </c>
+      <c r="E1344" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1344" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1344" s="75">
+        <v>1655</v>
+      </c>
+      <c r="H1344" s="76">
+        <v>7906</v>
+      </c>
+      <c r="I1344" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1344" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1344" s="18"/>
+      <c r="L1344" s="18"/>
+      <c r="M1344" s="18"/>
+      <c r="N1344" s="40"/>
+      <c r="O1344" s="18"/>
+      <c r="P1344" s="18"/>
+      <c r="Q1344" s="18"/>
+      <c r="R1344" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:18" ht="15" thickBot="1">
+      <c r="A1345" s="2">
+        <v>1344</v>
+      </c>
+      <c r="B1345" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1345" s="56" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D1345" s="56">
+        <v>109405367</v>
+      </c>
+      <c r="E1345" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1345" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1345" s="75" t="s">
+        <v>2043</v>
+      </c>
+      <c r="H1345" s="76">
+        <v>1294</v>
+      </c>
+      <c r="I1345" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1345" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1345" s="18"/>
+      <c r="L1345" s="18"/>
+      <c r="M1345" s="18"/>
+      <c r="N1345" s="40"/>
+      <c r="O1345" s="18"/>
+      <c r="P1345" s="18"/>
+      <c r="Q1345" s="18"/>
+      <c r="R1345" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:18" ht="15" thickBot="1">
+      <c r="A1346" s="2">
+        <v>1345</v>
+      </c>
+      <c r="B1346" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1346" s="56" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1346" s="56">
+        <v>116992324</v>
+      </c>
+      <c r="E1346" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1346" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1346" s="75">
+        <v>3001</v>
+      </c>
+      <c r="H1346" s="76">
+        <v>5372</v>
+      </c>
+      <c r="I1346" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1346" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1346" s="18"/>
+      <c r="L1346" s="18"/>
+      <c r="M1346" s="18"/>
+      <c r="N1346" s="40"/>
+      <c r="O1346" s="18"/>
+      <c r="P1346" s="18"/>
+      <c r="Q1346" s="18"/>
+      <c r="R1346" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:18" ht="15" thickBot="1">
+      <c r="A1347" s="2">
+        <v>1346</v>
+      </c>
+      <c r="B1347" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1347" s="56" t="s">
+        <v>2044</v>
+      </c>
+      <c r="D1347" s="56">
+        <v>113906242</v>
+      </c>
+      <c r="E1347" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1347" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1347" s="75">
+        <v>856</v>
+      </c>
+      <c r="H1347" s="76">
+        <v>9488</v>
+      </c>
+      <c r="I1347" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1347" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1347" s="18"/>
+      <c r="L1347" s="18"/>
+      <c r="M1347" s="18"/>
+      <c r="N1347" s="40"/>
+      <c r="O1347" s="18"/>
+      <c r="P1347" s="18"/>
+      <c r="Q1347" s="18"/>
+      <c r="R1347" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:18" ht="15" thickBot="1">
+      <c r="A1348" s="2">
+        <v>1347</v>
+      </c>
+      <c r="B1348" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1348" s="56" t="s">
+        <v>706</v>
+      </c>
+      <c r="D1348" s="56">
+        <v>122783332</v>
+      </c>
+      <c r="E1348" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1348" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1348" s="75">
+        <v>7046</v>
+      </c>
+      <c r="H1348" s="76" t="s">
+        <v>2045</v>
+      </c>
+      <c r="I1348" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1348" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1348" s="18"/>
+      <c r="L1348" s="18"/>
+      <c r="M1348" s="18"/>
+      <c r="N1348" s="40"/>
+      <c r="O1348" s="18"/>
+      <c r="P1348" s="18"/>
+      <c r="Q1348" s="18"/>
+      <c r="R1348" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:18" ht="15" thickBot="1">
+      <c r="A1349" s="2">
+        <v>1348</v>
+      </c>
+      <c r="B1349" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1349" s="56" t="s">
+        <v>2046</v>
+      </c>
+      <c r="D1349" s="56">
+        <v>133408626</v>
+      </c>
+      <c r="E1349" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1349" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1349" s="75">
+        <v>3135</v>
+      </c>
+      <c r="H1349" s="76">
+        <v>1014</v>
+      </c>
+      <c r="I1349" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1349" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1349" s="18"/>
+      <c r="L1349" s="18"/>
+      <c r="M1349" s="18"/>
+      <c r="N1349" s="40"/>
+      <c r="O1349" s="18"/>
+      <c r="P1349" s="18"/>
+      <c r="Q1349" s="18"/>
+      <c r="R1349" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:18" ht="15" thickBot="1">
+      <c r="A1350" s="2">
+        <v>1349</v>
+      </c>
+      <c r="B1350" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1350" s="56" t="s">
+        <v>2020</v>
+      </c>
+      <c r="D1350" s="56">
+        <v>69609874</v>
+      </c>
+      <c r="E1350" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1350" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1350" s="75">
+        <v>8801</v>
+      </c>
+      <c r="H1350" s="76">
+        <v>1222</v>
+      </c>
+      <c r="I1350" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1350" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1350" s="18"/>
+      <c r="L1350" s="18"/>
+      <c r="M1350" s="18"/>
+      <c r="N1350" s="40"/>
+      <c r="O1350" s="18"/>
+      <c r="P1350" s="18"/>
+      <c r="Q1350" s="18"/>
+      <c r="R1350" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:18" ht="15" thickBot="1">
+      <c r="A1351" s="2">
+        <v>1350</v>
+      </c>
+      <c r="B1351" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1351" s="56" t="s">
+        <v>2047</v>
+      </c>
+      <c r="D1351" s="56" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1351" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1351" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1351" s="75">
+        <v>71197</v>
+      </c>
+      <c r="H1351" s="76">
+        <v>40098</v>
+      </c>
+      <c r="I1351" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1351" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1351" s="18"/>
+      <c r="L1351" s="18"/>
+      <c r="M1351" s="18"/>
+      <c r="N1351" s="40"/>
+      <c r="O1351" s="18"/>
+      <c r="P1351" s="18"/>
+      <c r="Q1351" s="18"/>
+      <c r="R1351" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:18" ht="15" thickBot="1">
+      <c r="A1352" s="2">
+        <v>1351</v>
+      </c>
+      <c r="B1352" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1352" s="56" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D1352" s="56" t="s">
+        <v>2050</v>
+      </c>
+      <c r="E1352" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1352" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1352" s="75">
+        <v>51982</v>
+      </c>
+      <c r="H1352" s="76">
+        <v>19100</v>
+      </c>
+      <c r="I1352" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1352" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1352" s="18"/>
+      <c r="L1352" s="18"/>
+      <c r="M1352" s="18"/>
+      <c r="N1352" s="40"/>
+      <c r="O1352" s="18"/>
+      <c r="P1352" s="18"/>
+      <c r="Q1352" s="18"/>
+      <c r="R1352" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:18" ht="15" thickBot="1">
+      <c r="A1353" s="2">
+        <v>1352</v>
+      </c>
+      <c r="B1353" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1353" s="56" t="s">
+        <v>2051</v>
+      </c>
+      <c r="D1353" s="56">
+        <v>70232021</v>
+      </c>
+      <c r="E1353" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1353" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1353" s="75">
+        <v>9461</v>
+      </c>
+      <c r="H1353" s="76">
+        <v>2680</v>
+      </c>
+      <c r="I1353" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1353" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1353" s="18"/>
+      <c r="L1353" s="18"/>
+      <c r="M1353" s="18"/>
+      <c r="N1353" s="40"/>
+      <c r="O1353" s="18"/>
+      <c r="P1353" s="18"/>
+      <c r="Q1353" s="18"/>
+      <c r="R1353" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:18" ht="15" thickBot="1">
+      <c r="A1354" s="2">
+        <v>1353</v>
+      </c>
+      <c r="B1354" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1354" s="56" t="s">
+        <v>2052</v>
+      </c>
+      <c r="D1354" s="56">
+        <v>121609078</v>
+      </c>
+      <c r="E1354" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1354" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1354" s="75">
+        <v>6605</v>
+      </c>
+      <c r="H1354" s="76" t="s">
+        <v>2053</v>
+      </c>
+      <c r="I1354" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1354" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1354" s="18"/>
+      <c r="L1354" s="18"/>
+      <c r="M1354" s="18"/>
+      <c r="N1354" s="40"/>
+      <c r="O1354" s="18"/>
+      <c r="P1354" s="18"/>
+      <c r="Q1354" s="18"/>
+      <c r="R1354" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:18" ht="15" thickBot="1">
+      <c r="A1355" s="2">
+        <v>1354</v>
+      </c>
+      <c r="B1355" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1355" s="56" t="s">
+        <v>2054</v>
+      </c>
+      <c r="D1355" s="56">
+        <v>106823176</v>
+      </c>
+      <c r="E1355" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1355" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1355" s="75">
+        <v>2135</v>
+      </c>
+      <c r="H1355" s="38"/>
+      <c r="I1355" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1355" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1355" s="30" t="s">
+        <v>1596</v>
+      </c>
+      <c r="L1355" s="18"/>
+      <c r="M1355" s="18"/>
+      <c r="N1355" s="40"/>
+      <c r="O1355" s="18"/>
+      <c r="P1355" s="18"/>
+      <c r="Q1355" s="18"/>
+      <c r="R1355" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:18" ht="15" thickBot="1">
+      <c r="A1356" s="2">
+        <v>1355</v>
+      </c>
+      <c r="B1356" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1356" s="56" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D1356" s="56">
+        <v>128958936</v>
+      </c>
+      <c r="E1356" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1356" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1356" s="75">
+        <v>8835</v>
+      </c>
+      <c r="H1356" s="76">
+        <v>1886</v>
+      </c>
+      <c r="I1356" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1356" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1356" s="18"/>
+      <c r="L1356" s="18"/>
+      <c r="M1356" s="18"/>
+      <c r="N1356" s="40"/>
+      <c r="O1356" s="18"/>
+      <c r="P1356" s="18"/>
+      <c r="Q1356" s="18"/>
+      <c r="R1356" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:18" ht="15" thickBot="1">
+      <c r="A1357" s="2">
+        <v>1356</v>
+      </c>
+      <c r="B1357" s="77">
+        <v>46244</v>
+      </c>
+      <c r="C1357" s="78" t="s">
+        <v>2056</v>
+      </c>
+      <c r="D1357" s="78">
+        <v>131199398</v>
+      </c>
+      <c r="E1357" s="79" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1357" s="80" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1357" s="81">
+        <v>7398</v>
+      </c>
+      <c r="H1357" s="82">
+        <v>8171</v>
+      </c>
+      <c r="I1357" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1357" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1357" s="83"/>
+      <c r="L1357" s="83"/>
+      <c r="M1357" s="83"/>
+      <c r="N1357" s="84"/>
+      <c r="O1357" s="83"/>
+      <c r="P1357" s="83"/>
+      <c r="Q1357" s="83"/>
+      <c r="R1357" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:18" ht="15" thickBot="1">
+      <c r="A1358" s="2">
+        <v>1357</v>
+      </c>
+      <c r="B1358" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1358" s="56" t="s">
+        <v>2057</v>
+      </c>
+      <c r="D1358" s="56">
+        <v>121970068</v>
+      </c>
+      <c r="E1358" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1358" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1358" s="75">
+        <v>4090</v>
+      </c>
+      <c r="H1358" s="76">
+        <v>9687</v>
+      </c>
+      <c r="I1358" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1358" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1358" s="18"/>
+      <c r="L1358" s="18"/>
+      <c r="M1358" s="18"/>
+      <c r="N1358" s="40"/>
+      <c r="O1358" s="18"/>
+      <c r="P1358" s="18"/>
+      <c r="Q1358" s="18"/>
+      <c r="R1358" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:18" ht="15" thickBot="1">
+      <c r="A1359" s="2">
+        <v>1358</v>
+      </c>
+      <c r="B1359" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1359" s="56" t="s">
+        <v>2058</v>
+      </c>
+      <c r="D1359" s="56">
+        <v>101430473</v>
+      </c>
+      <c r="E1359" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1359" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1359" s="75">
+        <v>3686</v>
+      </c>
+      <c r="H1359" s="76">
+        <v>2699</v>
+      </c>
+      <c r="I1359" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1359" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1359" s="18"/>
+      <c r="L1359" s="18"/>
+      <c r="M1359" s="18"/>
+      <c r="N1359" s="40"/>
+      <c r="O1359" s="18"/>
+      <c r="P1359" s="18"/>
+      <c r="Q1359" s="18"/>
+      <c r="R1359" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:18" ht="15" thickBot="1">
+      <c r="A1360" s="2">
+        <v>1359</v>
+      </c>
+      <c r="B1360" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1360" s="56" t="s">
+        <v>2059</v>
+      </c>
+      <c r="D1360" s="56">
+        <v>135821521</v>
+      </c>
+      <c r="E1360" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1360" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1360" s="75">
+        <v>4123</v>
+      </c>
+      <c r="H1360" s="76">
+        <v>6467</v>
+      </c>
+      <c r="I1360" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1360" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1360" s="18"/>
+      <c r="L1360" s="18"/>
+      <c r="M1360" s="18"/>
+      <c r="N1360" s="40"/>
+      <c r="O1360" s="18"/>
+      <c r="P1360" s="18"/>
+      <c r="Q1360" s="18"/>
+      <c r="R1360" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:18" ht="15" thickBot="1">
+      <c r="A1361" s="2">
+        <v>1360</v>
+      </c>
+      <c r="B1361" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1361" s="56" t="s">
+        <v>2060</v>
+      </c>
+      <c r="D1361" s="56">
+        <v>85421804</v>
+      </c>
+      <c r="E1361" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1361" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1361" s="75">
+        <v>9497</v>
+      </c>
+      <c r="H1361" s="76">
+        <v>4915</v>
+      </c>
+      <c r="I1361" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1361" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1361" s="18"/>
+      <c r="L1361" s="18"/>
+      <c r="M1361" s="18"/>
+      <c r="N1361" s="40"/>
+      <c r="O1361" s="18"/>
+      <c r="P1361" s="18"/>
+      <c r="Q1361" s="18"/>
+      <c r="R1361" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAAC3FBA-21A9-45E9-BC77-87BCA0849890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18C2165-B019-47F1-AC6E-8AEB977C76A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10058" uniqueCount="2061">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10219" uniqueCount="2089">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -6221,6 +6221,90 @@
   </si>
   <si>
     <t>SADDAM</t>
+  </si>
+  <si>
+    <t>EHTSAM HASSAN</t>
+  </si>
+  <si>
+    <t>BALRAJ SINGH</t>
+  </si>
+  <si>
+    <t>R9434697</t>
+  </si>
+  <si>
+    <t>JARMANJEET SINGH</t>
+  </si>
+  <si>
+    <t>Z6399121</t>
+  </si>
+  <si>
+    <t>DALJEET</t>
+  </si>
+  <si>
+    <t>ZA096374</t>
+  </si>
+  <si>
+    <t>AMANPREET SINGH</t>
+  </si>
+  <si>
+    <t>W4932244</t>
+  </si>
+  <si>
+    <t>FARHAN</t>
+  </si>
+  <si>
+    <t>SHER DIL</t>
+  </si>
+  <si>
+    <t>HUZAIFA SHAHROOZ</t>
+  </si>
+  <si>
+    <t>RIZWAN</t>
+  </si>
+  <si>
+    <t>IBRAR</t>
+  </si>
+  <si>
+    <t>SHAHBAZ KHAN</t>
+  </si>
+  <si>
+    <t>CY0156614</t>
+  </si>
+  <si>
+    <t>REHMAN</t>
+  </si>
+  <si>
+    <t>CA9157055</t>
+  </si>
+  <si>
+    <t>KHURRAM ALI</t>
+  </si>
+  <si>
+    <t>UK1798745</t>
+  </si>
+  <si>
+    <t>KHURRAM IJAZ</t>
+  </si>
+  <si>
+    <t>HABIBULLAH</t>
+  </si>
+  <si>
+    <t>RASHID</t>
+  </si>
+  <si>
+    <t>EZ984923</t>
+  </si>
+  <si>
+    <t>SHAMEER KHALID</t>
+  </si>
+  <si>
+    <t>Z5417539</t>
+  </si>
+  <si>
+    <t>MUBEEN ALI</t>
+  </si>
+  <si>
+    <t>3007-</t>
   </si>
 </sst>
 </file>
@@ -6597,7 +6681,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6850,6 +6934,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7165,7 +7255,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1361"/>
+  <dimension ref="A1:R1386"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -69532,6 +69622,1054 @@
         <v>131</v>
       </c>
     </row>
+    <row r="1362" spans="1:18" ht="15" thickBot="1">
+      <c r="A1362" s="2">
+        <v>1361</v>
+      </c>
+      <c r="B1362" s="77">
+        <v>46244</v>
+      </c>
+      <c r="C1362" s="78" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D1362" s="78">
+        <v>123834056</v>
+      </c>
+      <c r="E1362" s="79" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1362" s="80" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1362" s="81">
+        <v>1179</v>
+      </c>
+      <c r="H1362" s="82">
+        <v>3359</v>
+      </c>
+      <c r="I1362" s="85" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1362" s="86" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1362" s="83"/>
+      <c r="L1362" s="83"/>
+      <c r="M1362" s="83"/>
+      <c r="N1362" s="84"/>
+      <c r="O1362" s="83"/>
+      <c r="P1362" s="83"/>
+      <c r="Q1362" s="83"/>
+      <c r="R1362" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:18" ht="15" thickBot="1">
+      <c r="A1363" s="2">
+        <v>1362</v>
+      </c>
+      <c r="B1363" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1363" s="56" t="s">
+        <v>2061</v>
+      </c>
+      <c r="D1363" s="56">
+        <v>137986597</v>
+      </c>
+      <c r="E1363" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1363" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1363" s="75">
+        <v>3024</v>
+      </c>
+      <c r="H1363" s="76">
+        <v>372</v>
+      </c>
+      <c r="I1363" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1363" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1363" s="18"/>
+      <c r="L1363" s="18"/>
+      <c r="M1363" s="18"/>
+      <c r="N1363" s="40"/>
+      <c r="O1363" s="18"/>
+      <c r="P1363" s="18"/>
+      <c r="Q1363" s="18"/>
+      <c r="R1363" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:18" ht="15" thickBot="1">
+      <c r="A1364" s="2">
+        <v>1363</v>
+      </c>
+      <c r="B1364" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1364" s="56" t="s">
+        <v>2062</v>
+      </c>
+      <c r="D1364" s="56" t="s">
+        <v>2063</v>
+      </c>
+      <c r="E1364" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1364" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1364" s="75">
+        <v>22255</v>
+      </c>
+      <c r="H1364" s="76">
+        <v>94480</v>
+      </c>
+      <c r="I1364" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1364" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1364" s="18"/>
+      <c r="L1364" s="18"/>
+      <c r="M1364" s="18"/>
+      <c r="N1364" s="40"/>
+      <c r="O1364" s="18"/>
+      <c r="P1364" s="18"/>
+      <c r="Q1364" s="18"/>
+      <c r="R1364" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1365" s="2">
+        <v>1364</v>
+      </c>
+      <c r="B1365" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1365" s="56" t="s">
+        <v>2064</v>
+      </c>
+      <c r="D1365" s="56" t="s">
+        <v>2065</v>
+      </c>
+      <c r="E1365" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1365" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1365" s="75">
+        <v>67381</v>
+      </c>
+      <c r="H1365" s="76">
+        <v>33916</v>
+      </c>
+      <c r="I1365" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1365" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1365" s="18"/>
+      <c r="L1365" s="18"/>
+      <c r="M1365" s="18"/>
+      <c r="N1365" s="40"/>
+      <c r="O1365" s="18"/>
+      <c r="P1365" s="18"/>
+      <c r="Q1365" s="18"/>
+      <c r="R1365" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:18" ht="15" thickBot="1">
+      <c r="A1366" s="2">
+        <v>1365</v>
+      </c>
+      <c r="B1366" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1366" s="56" t="s">
+        <v>2066</v>
+      </c>
+      <c r="D1366" s="56" t="s">
+        <v>2067</v>
+      </c>
+      <c r="E1366" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1366" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1366" s="75">
+        <v>61805</v>
+      </c>
+      <c r="H1366" s="38"/>
+      <c r="I1366" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1366" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1366" s="18"/>
+      <c r="L1366" s="18"/>
+      <c r="M1366" s="18"/>
+      <c r="N1366" s="40"/>
+      <c r="O1366" s="18"/>
+      <c r="P1366" s="18"/>
+      <c r="Q1366" s="18"/>
+      <c r="R1366" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1367" s="2">
+        <v>1366</v>
+      </c>
+      <c r="B1367" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1367" s="56" t="s">
+        <v>2068</v>
+      </c>
+      <c r="D1367" s="56" t="s">
+        <v>2069</v>
+      </c>
+      <c r="E1367" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1367" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1367" s="75">
+        <v>70270</v>
+      </c>
+      <c r="H1367" s="76">
+        <v>73889</v>
+      </c>
+      <c r="I1367" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1367" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1367" s="18"/>
+      <c r="L1367" s="18"/>
+      <c r="M1367" s="18"/>
+      <c r="N1367" s="40"/>
+      <c r="O1367" s="18"/>
+      <c r="P1367" s="18"/>
+      <c r="Q1367" s="18"/>
+      <c r="R1367" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:18" ht="15" thickBot="1">
+      <c r="A1368" s="2">
+        <v>1367</v>
+      </c>
+      <c r="B1368" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1368" s="56" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D1368" s="56">
+        <v>10796449</v>
+      </c>
+      <c r="E1368" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1368" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1368" s="75">
+        <v>5474</v>
+      </c>
+      <c r="H1368" s="76">
+        <v>848</v>
+      </c>
+      <c r="I1368" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1368" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1368" s="18"/>
+      <c r="L1368" s="18"/>
+      <c r="M1368" s="18"/>
+      <c r="N1368" s="40"/>
+      <c r="O1368" s="18"/>
+      <c r="P1368" s="18"/>
+      <c r="Q1368" s="18"/>
+      <c r="R1368" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:18" ht="15" thickBot="1">
+      <c r="A1369" s="2">
+        <v>1368</v>
+      </c>
+      <c r="B1369" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1369" s="56" t="s">
+        <v>2070</v>
+      </c>
+      <c r="D1369" s="56">
+        <v>137469576</v>
+      </c>
+      <c r="E1369" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1369" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1369" s="75">
+        <v>6331</v>
+      </c>
+      <c r="H1369" s="76">
+        <v>1144</v>
+      </c>
+      <c r="I1369" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1369" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1369" s="18"/>
+      <c r="L1369" s="18"/>
+      <c r="M1369" s="18"/>
+      <c r="N1369" s="40"/>
+      <c r="O1369" s="18"/>
+      <c r="P1369" s="18"/>
+      <c r="Q1369" s="18"/>
+      <c r="R1369" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:18" ht="15" thickBot="1">
+      <c r="A1370" s="2">
+        <v>1369</v>
+      </c>
+      <c r="B1370" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1370" s="56" t="s">
+        <v>2071</v>
+      </c>
+      <c r="D1370" s="56">
+        <v>113855561</v>
+      </c>
+      <c r="E1370" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1370" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1370" s="75">
+        <v>4686</v>
+      </c>
+      <c r="H1370" s="76">
+        <v>4228</v>
+      </c>
+      <c r="I1370" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1370" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1370" s="18"/>
+      <c r="L1370" s="18"/>
+      <c r="M1370" s="18"/>
+      <c r="N1370" s="40"/>
+      <c r="O1370" s="18"/>
+      <c r="P1370" s="18"/>
+      <c r="Q1370" s="18"/>
+      <c r="R1370" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1371" s="2">
+        <v>1370</v>
+      </c>
+      <c r="B1371" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1371" s="56" t="s">
+        <v>2072</v>
+      </c>
+      <c r="D1371" s="56">
+        <v>123277232</v>
+      </c>
+      <c r="E1371" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1371" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1371" s="75">
+        <v>2262</v>
+      </c>
+      <c r="H1371" s="76">
+        <v>2488</v>
+      </c>
+      <c r="I1371" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1371" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1371" s="18"/>
+      <c r="L1371" s="18"/>
+      <c r="M1371" s="18"/>
+      <c r="N1371" s="40"/>
+      <c r="O1371" s="18"/>
+      <c r="P1371" s="18"/>
+      <c r="Q1371" s="18"/>
+      <c r="R1371" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:18" ht="15" thickBot="1">
+      <c r="A1372" s="2">
+        <v>1371</v>
+      </c>
+      <c r="B1372" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1372" s="56" t="s">
+        <v>832</v>
+      </c>
+      <c r="D1372" s="56">
+        <v>131010155</v>
+      </c>
+      <c r="E1372" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1372" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1372" s="75">
+        <v>653</v>
+      </c>
+      <c r="H1372" s="76">
+        <v>4834</v>
+      </c>
+      <c r="I1372" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1372" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1372" s="18"/>
+      <c r="L1372" s="18"/>
+      <c r="M1372" s="18"/>
+      <c r="N1372" s="40"/>
+      <c r="O1372" s="18"/>
+      <c r="P1372" s="18"/>
+      <c r="Q1372" s="18"/>
+      <c r="R1372" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:18" ht="15" thickBot="1">
+      <c r="A1373" s="2">
+        <v>1372</v>
+      </c>
+      <c r="B1373" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1373" s="56" t="s">
+        <v>2073</v>
+      </c>
+      <c r="D1373" s="56">
+        <v>101432496</v>
+      </c>
+      <c r="E1373" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1373" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1373" s="75">
+        <v>3384</v>
+      </c>
+      <c r="H1373" s="76">
+        <v>4674</v>
+      </c>
+      <c r="I1373" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1373" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1373" s="18"/>
+      <c r="L1373" s="18"/>
+      <c r="M1373" s="18"/>
+      <c r="N1373" s="40"/>
+      <c r="O1373" s="18"/>
+      <c r="P1373" s="18"/>
+      <c r="Q1373" s="18"/>
+      <c r="R1373" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:18" ht="15" thickBot="1">
+      <c r="A1374" s="2">
+        <v>1373</v>
+      </c>
+      <c r="B1374" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1374" s="56" t="s">
+        <v>2074</v>
+      </c>
+      <c r="D1374" s="56">
+        <v>88733109</v>
+      </c>
+      <c r="E1374" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1374" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1374" s="75">
+        <v>7898</v>
+      </c>
+      <c r="H1374" s="76">
+        <v>7496</v>
+      </c>
+      <c r="I1374" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1374" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1374" s="18"/>
+      <c r="L1374" s="18"/>
+      <c r="M1374" s="18"/>
+      <c r="N1374" s="40"/>
+      <c r="O1374" s="18"/>
+      <c r="P1374" s="18"/>
+      <c r="Q1374" s="18"/>
+      <c r="R1374" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:18" ht="15" thickBot="1">
+      <c r="A1375" s="2">
+        <v>1374</v>
+      </c>
+      <c r="B1375" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1375" s="56" t="s">
+        <v>2075</v>
+      </c>
+      <c r="D1375" s="56">
+        <v>95080141</v>
+      </c>
+      <c r="E1375" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1375" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1375" s="75">
+        <v>2874</v>
+      </c>
+      <c r="H1375" s="76">
+        <v>6798</v>
+      </c>
+      <c r="I1375" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1375" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1375" s="18"/>
+      <c r="L1375" s="18"/>
+      <c r="M1375" s="18"/>
+      <c r="N1375" s="40"/>
+      <c r="O1375" s="18"/>
+      <c r="P1375" s="18"/>
+      <c r="Q1375" s="18"/>
+      <c r="R1375" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1376" s="2">
+        <v>1375</v>
+      </c>
+      <c r="B1376" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1376" s="56" t="s">
+        <v>902</v>
+      </c>
+      <c r="D1376" s="56" t="s">
+        <v>2076</v>
+      </c>
+      <c r="E1376" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1376" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1376" s="75">
+        <v>41903</v>
+      </c>
+      <c r="H1376" s="76">
+        <v>15077</v>
+      </c>
+      <c r="I1376" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1376" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1376" s="18"/>
+      <c r="L1376" s="18"/>
+      <c r="M1376" s="18"/>
+      <c r="N1376" s="40"/>
+      <c r="O1376" s="18"/>
+      <c r="P1376" s="18"/>
+      <c r="Q1376" s="18"/>
+      <c r="R1376" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:18" ht="15" thickBot="1">
+      <c r="A1377" s="2">
+        <v>1376</v>
+      </c>
+      <c r="B1377" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1377" s="56" t="s">
+        <v>2077</v>
+      </c>
+      <c r="D1377" s="56" t="s">
+        <v>2078</v>
+      </c>
+      <c r="E1377" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1377" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1377" s="75">
+        <v>27739</v>
+      </c>
+      <c r="H1377" s="76">
+        <v>15360</v>
+      </c>
+      <c r="I1377" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1377" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1377" s="18"/>
+      <c r="L1377" s="18"/>
+      <c r="M1377" s="18"/>
+      <c r="N1377" s="40"/>
+      <c r="O1377" s="18"/>
+      <c r="P1377" s="18"/>
+      <c r="Q1377" s="18"/>
+      <c r="R1377" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:18" ht="15" thickBot="1">
+      <c r="A1378" s="2">
+        <v>1377</v>
+      </c>
+      <c r="B1378" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1378" s="56" t="s">
+        <v>2079</v>
+      </c>
+      <c r="D1378" s="56" t="s">
+        <v>2080</v>
+      </c>
+      <c r="E1378" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1378" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1378" s="75">
+        <v>42905</v>
+      </c>
+      <c r="H1378" s="76">
+        <v>38038</v>
+      </c>
+      <c r="I1378" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1378" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1378" s="18"/>
+      <c r="L1378" s="18"/>
+      <c r="M1378" s="18"/>
+      <c r="N1378" s="40"/>
+      <c r="O1378" s="18"/>
+      <c r="P1378" s="18"/>
+      <c r="Q1378" s="18"/>
+      <c r="R1378" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:18" ht="15" thickBot="1">
+      <c r="A1379" s="2">
+        <v>1378</v>
+      </c>
+      <c r="B1379" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1379" s="56" t="s">
+        <v>2081</v>
+      </c>
+      <c r="D1379" s="56">
+        <v>136758182</v>
+      </c>
+      <c r="E1379" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1379" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1379" s="75">
+        <v>6079</v>
+      </c>
+      <c r="H1379" s="38"/>
+      <c r="I1379" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1379" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1379" s="30" t="s">
+        <v>1596</v>
+      </c>
+      <c r="L1379" s="18"/>
+      <c r="M1379" s="18"/>
+      <c r="N1379" s="40"/>
+      <c r="O1379" s="18"/>
+      <c r="P1379" s="18"/>
+      <c r="Q1379" s="18"/>
+      <c r="R1379" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:18" ht="15" thickBot="1">
+      <c r="A1380" s="2">
+        <v>1379</v>
+      </c>
+      <c r="B1380" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1380" s="56" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D1380" s="56">
+        <v>94284236</v>
+      </c>
+      <c r="E1380" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1380" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1380" s="75">
+        <v>2395</v>
+      </c>
+      <c r="H1380" s="76">
+        <v>3699</v>
+      </c>
+      <c r="I1380" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1380" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1380" s="18"/>
+      <c r="L1380" s="18"/>
+      <c r="M1380" s="18"/>
+      <c r="N1380" s="40"/>
+      <c r="O1380" s="18"/>
+      <c r="P1380" s="18"/>
+      <c r="Q1380" s="18"/>
+      <c r="R1380" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:18" ht="15" thickBot="1">
+      <c r="A1381" s="2">
+        <v>1380</v>
+      </c>
+      <c r="B1381" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1381" s="56" t="s">
+        <v>2082</v>
+      </c>
+      <c r="D1381" s="56">
+        <v>85604949</v>
+      </c>
+      <c r="E1381" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1381" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1381" s="75">
+        <v>7638</v>
+      </c>
+      <c r="H1381" s="76">
+        <v>1996</v>
+      </c>
+      <c r="I1381" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1381" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1381" s="18"/>
+      <c r="L1381" s="18"/>
+      <c r="M1381" s="18"/>
+      <c r="N1381" s="40"/>
+      <c r="O1381" s="18"/>
+      <c r="P1381" s="18"/>
+      <c r="Q1381" s="18"/>
+      <c r="R1381" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:18" ht="15" thickBot="1">
+      <c r="A1382" s="2">
+        <v>1381</v>
+      </c>
+      <c r="B1382" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1382" s="56" t="s">
+        <v>2083</v>
+      </c>
+      <c r="D1382" s="56" t="s">
+        <v>2084</v>
+      </c>
+      <c r="E1382" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1382" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1382" s="75">
+        <v>77612</v>
+      </c>
+      <c r="H1382" s="76">
+        <v>58160</v>
+      </c>
+      <c r="I1382" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1382" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1382" s="18"/>
+      <c r="L1382" s="18"/>
+      <c r="M1382" s="18"/>
+      <c r="N1382" s="40"/>
+      <c r="O1382" s="18"/>
+      <c r="P1382" s="18"/>
+      <c r="Q1382" s="18"/>
+      <c r="R1382" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:18" ht="15" thickBot="1">
+      <c r="A1383" s="2">
+        <v>1382</v>
+      </c>
+      <c r="B1383" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1383" s="56" t="s">
+        <v>2085</v>
+      </c>
+      <c r="D1383" s="56" t="s">
+        <v>2086</v>
+      </c>
+      <c r="E1383" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1383" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1383" s="75">
+        <v>28250</v>
+      </c>
+      <c r="H1383" s="76">
+        <v>96002</v>
+      </c>
+      <c r="I1383" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1383" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1383" s="18"/>
+      <c r="L1383" s="18"/>
+      <c r="M1383" s="18"/>
+      <c r="N1383" s="40"/>
+      <c r="O1383" s="18"/>
+      <c r="P1383" s="18"/>
+      <c r="Q1383" s="18"/>
+      <c r="R1383" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:18" ht="15" thickBot="1">
+      <c r="A1384" s="2">
+        <v>1383</v>
+      </c>
+      <c r="B1384" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1384" s="56" t="s">
+        <v>2087</v>
+      </c>
+      <c r="D1384" s="56">
+        <v>136520749</v>
+      </c>
+      <c r="E1384" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1384" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1384" s="75">
+        <v>6426</v>
+      </c>
+      <c r="H1384" s="76" t="s">
+        <v>2088</v>
+      </c>
+      <c r="I1384" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1384" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1384" s="18"/>
+      <c r="L1384" s="18"/>
+      <c r="M1384" s="18"/>
+      <c r="N1384" s="40"/>
+      <c r="O1384" s="18"/>
+      <c r="P1384" s="18"/>
+      <c r="Q1384" s="18"/>
+      <c r="R1384" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:18" ht="15" thickBot="1">
+      <c r="A1385" s="2">
+        <v>1384</v>
+      </c>
+      <c r="B1385" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1385" s="56" t="s">
+        <v>796</v>
+      </c>
+      <c r="D1385" s="56">
+        <v>137592477</v>
+      </c>
+      <c r="E1385" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1385" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1385" s="75">
+        <v>1682</v>
+      </c>
+      <c r="H1385" s="76">
+        <v>5917</v>
+      </c>
+      <c r="I1385" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1385" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1385" s="18"/>
+      <c r="L1385" s="18"/>
+      <c r="M1385" s="18"/>
+      <c r="N1385" s="40"/>
+      <c r="O1385" s="18"/>
+      <c r="P1385" s="18"/>
+      <c r="Q1385" s="18"/>
+      <c r="R1385" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:18" ht="15" thickBot="1">
+      <c r="A1386" s="2">
+        <v>1385</v>
+      </c>
+      <c r="B1386" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1386" s="56" t="s">
+        <v>613</v>
+      </c>
+      <c r="D1386" s="56">
+        <v>68666526</v>
+      </c>
+      <c r="E1386" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1386" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1386" s="75">
+        <v>2861</v>
+      </c>
+      <c r="H1386" s="76">
+        <v>2723</v>
+      </c>
+      <c r="I1386" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1386" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1386" s="18"/>
+      <c r="L1386" s="18"/>
+      <c r="M1386" s="18"/>
+      <c r="N1386" s="40"/>
+      <c r="O1386" s="18"/>
+      <c r="P1386" s="18"/>
+      <c r="Q1386" s="18"/>
+      <c r="R1386" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18C2165-B019-47F1-AC6E-8AEB977C76A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ECB25FD-F18D-4D80-A097-2E75496E94B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10219" uniqueCount="2089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10400" uniqueCount="2115">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -6305,6 +6305,84 @@
   </si>
   <si>
     <t>3007-</t>
+  </si>
+  <si>
+    <t>ALI HAMZA</t>
+  </si>
+  <si>
+    <t>SAEED AFZAL</t>
+  </si>
+  <si>
+    <t>AFRAZ WARYAM</t>
+  </si>
+  <si>
+    <t>TAHIR ABBAS</t>
+  </si>
+  <si>
+    <t>PERVEZ IQBAL</t>
+  </si>
+  <si>
+    <t>AP4198845</t>
+  </si>
+  <si>
+    <t>MUHAMMED NADEEM</t>
+  </si>
+  <si>
+    <t>9424 3195</t>
+  </si>
+  <si>
+    <t>SUFYAN ALI</t>
+  </si>
+  <si>
+    <t>HAMMAD</t>
+  </si>
+  <si>
+    <t>AFTAB MEHMOOD</t>
+  </si>
+  <si>
+    <t>ABDUL MAJEED</t>
+  </si>
+  <si>
+    <t>SAMAR ABBAS</t>
+  </si>
+  <si>
+    <t>IRFAN ALI</t>
+  </si>
+  <si>
+    <t>FAZAL ABBAS</t>
+  </si>
+  <si>
+    <t>BT1809284</t>
+  </si>
+  <si>
+    <t>AC0410014</t>
+  </si>
+  <si>
+    <t>BASHARAT</t>
+  </si>
+  <si>
+    <t>ABUBAQAR</t>
+  </si>
+  <si>
+    <t>2217*</t>
+  </si>
+  <si>
+    <t>KHAN SAJID</t>
+  </si>
+  <si>
+    <t>CA4135526</t>
+  </si>
+  <si>
+    <t>KALEEM KHAN</t>
+  </si>
+  <si>
+    <t>KHAN ZAFAR ULLAH</t>
+  </si>
+  <si>
+    <t>TE4111965</t>
+  </si>
+  <si>
+    <t>BK1201855</t>
   </si>
 </sst>
 </file>
@@ -6681,7 +6759,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6910,36 +6988,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7255,7 +7303,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1386"/>
+  <dimension ref="A1:R1409"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -7322,7 +7370,9 @@
       <c r="Q1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="4"/>
+      <c r="R1" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2" spans="1:18" ht="28.2" thickBot="1">
       <c r="A2" s="2">
@@ -63739,8 +63789,8 @@
       <c r="J1226" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1226" s="30" t="s">
-        <v>1596</v>
+      <c r="K1226" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1226" s="18"/>
       <c r="M1226" s="18"/>
@@ -66681,23 +66731,33 @@
       <c r="B1293" s="10">
         <v>46244</v>
       </c>
-      <c r="C1293" s="38"/>
-      <c r="D1293" s="38"/>
-      <c r="E1293" s="18"/>
+      <c r="C1293" s="56" t="s">
+        <v>2089</v>
+      </c>
+      <c r="D1293" s="56">
+        <v>137592299</v>
+      </c>
+      <c r="E1293" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="F1293" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1293" s="75">
         <v>4872</v>
       </c>
-      <c r="H1293" s="18"/>
+      <c r="H1293" s="15">
+        <v>7834</v>
+      </c>
       <c r="I1293" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1293" s="52" t="s">
         <v>776</v>
       </c>
-      <c r="K1293" s="18"/>
+      <c r="K1293" s="61" t="s">
+        <v>1189</v>
+      </c>
       <c r="L1293" s="18"/>
       <c r="M1293" s="18"/>
       <c r="N1293" s="40"/>
@@ -66713,23 +66773,33 @@
       <c r="B1294" s="10">
         <v>46244</v>
       </c>
-      <c r="C1294" s="38"/>
-      <c r="D1294" s="38"/>
-      <c r="E1294" s="18"/>
+      <c r="C1294" s="56" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D1294" s="56">
+        <v>138109453</v>
+      </c>
+      <c r="E1294" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="F1294" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1294" s="57">
         <v>7876</v>
       </c>
-      <c r="H1294" s="18"/>
+      <c r="H1294" s="15">
+        <v>4032</v>
+      </c>
       <c r="I1294" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1294" s="52" t="s">
         <v>776</v>
       </c>
-      <c r="K1294" s="18"/>
+      <c r="K1294" s="61" t="s">
+        <v>1189</v>
+      </c>
       <c r="L1294" s="18"/>
       <c r="M1294" s="18"/>
       <c r="N1294" s="40"/>
@@ -66745,23 +66815,33 @@
       <c r="B1295" s="10">
         <v>46244</v>
       </c>
-      <c r="C1295" s="38"/>
-      <c r="D1295" s="38"/>
-      <c r="E1295" s="18"/>
+      <c r="C1295" s="56" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1295" s="56">
+        <v>118946025</v>
+      </c>
+      <c r="E1295" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="F1295" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1295" s="57">
         <v>2328</v>
       </c>
-      <c r="H1295" s="18"/>
+      <c r="H1295" s="15">
+        <v>1004</v>
+      </c>
       <c r="I1295" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1295" s="52" t="s">
         <v>776</v>
       </c>
-      <c r="K1295" s="18"/>
+      <c r="K1295" s="61" t="s">
+        <v>1189</v>
+      </c>
       <c r="L1295" s="18"/>
       <c r="M1295" s="18"/>
       <c r="N1295" s="40"/>
@@ -69065,7 +69145,9 @@
       <c r="J1348" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1348" s="18"/>
+      <c r="K1348" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1348" s="18"/>
       <c r="M1348" s="18"/>
       <c r="N1348" s="40"/>
@@ -69107,7 +69189,9 @@
       <c r="J1349" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1349" s="18"/>
+      <c r="K1349" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1349" s="18"/>
       <c r="M1349" s="18"/>
       <c r="N1349" s="40"/>
@@ -69275,7 +69359,9 @@
       <c r="J1353" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1353" s="18"/>
+      <c r="K1353" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1353" s="18"/>
       <c r="M1353" s="18"/>
       <c r="N1353" s="40"/>
@@ -69416,25 +69502,25 @@
       <c r="A1357" s="2">
         <v>1356</v>
       </c>
-      <c r="B1357" s="77">
+      <c r="B1357" s="10">
         <v>46244</v>
       </c>
-      <c r="C1357" s="78" t="s">
+      <c r="C1357" s="56" t="s">
         <v>2056</v>
       </c>
-      <c r="D1357" s="78">
+      <c r="D1357" s="56">
         <v>131199398</v>
       </c>
-      <c r="E1357" s="79" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1357" s="80" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1357" s="81">
+      <c r="E1357" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1357" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1357" s="75">
         <v>7398</v>
       </c>
-      <c r="H1357" s="82">
+      <c r="H1357" s="76">
         <v>8171</v>
       </c>
       <c r="I1357" s="22" t="s">
@@ -69443,13 +69529,13 @@
       <c r="J1357" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1357" s="83"/>
-      <c r="L1357" s="83"/>
-      <c r="M1357" s="83"/>
-      <c r="N1357" s="84"/>
-      <c r="O1357" s="83"/>
-      <c r="P1357" s="83"/>
-      <c r="Q1357" s="83"/>
+      <c r="K1357" s="18"/>
+      <c r="L1357" s="18"/>
+      <c r="M1357" s="18"/>
+      <c r="N1357" s="40"/>
+      <c r="O1357" s="18"/>
+      <c r="P1357" s="18"/>
+      <c r="Q1357" s="18"/>
       <c r="R1357" s="22" t="s">
         <v>131</v>
       </c>
@@ -69626,40 +69712,42 @@
       <c r="A1362" s="2">
         <v>1361</v>
       </c>
-      <c r="B1362" s="77">
+      <c r="B1362" s="10">
         <v>46244</v>
       </c>
-      <c r="C1362" s="78" t="s">
+      <c r="C1362" s="56" t="s">
         <v>1327</v>
       </c>
-      <c r="D1362" s="78">
+      <c r="D1362" s="56">
         <v>123834056</v>
       </c>
-      <c r="E1362" s="79" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1362" s="80" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1362" s="81">
+      <c r="E1362" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1362" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1362" s="75">
         <v>1179</v>
       </c>
-      <c r="H1362" s="82">
+      <c r="H1362" s="76">
         <v>3359</v>
       </c>
-      <c r="I1362" s="85" t="s">
+      <c r="I1362" s="22" t="s">
         <v>563</v>
       </c>
-      <c r="J1362" s="86" t="s">
+      <c r="J1362" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1362" s="83"/>
-      <c r="L1362" s="83"/>
-      <c r="M1362" s="83"/>
-      <c r="N1362" s="84"/>
-      <c r="O1362" s="83"/>
-      <c r="P1362" s="83"/>
-      <c r="Q1362" s="83"/>
+      <c r="K1362" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1362" s="18"/>
+      <c r="M1362" s="18"/>
+      <c r="N1362" s="40"/>
+      <c r="O1362" s="18"/>
+      <c r="P1362" s="18"/>
+      <c r="Q1362" s="18"/>
       <c r="R1362" s="22" t="s">
         <v>131</v>
       </c>
@@ -70239,7 +70327,9 @@
       <c r="J1376" s="51" t="s">
         <v>564</v>
       </c>
-      <c r="K1376" s="18"/>
+      <c r="K1376" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1376" s="18"/>
       <c r="M1376" s="18"/>
       <c r="N1376" s="40"/>
@@ -70670,6 +70760,1018 @@
         <v>131</v>
       </c>
     </row>
+    <row r="1387" spans="1:18" ht="15" thickBot="1">
+      <c r="A1387" s="2">
+        <v>1386</v>
+      </c>
+      <c r="B1387" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1387" s="56" t="s">
+        <v>2090</v>
+      </c>
+      <c r="D1387" s="56">
+        <v>68666526</v>
+      </c>
+      <c r="E1387" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1387" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1387" s="75">
+        <v>4204</v>
+      </c>
+      <c r="H1387" s="76">
+        <v>4535</v>
+      </c>
+      <c r="I1387" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1387" s="51" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1387" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1387" s="18"/>
+      <c r="M1387" s="18"/>
+      <c r="N1387" s="40"/>
+      <c r="O1387" s="18"/>
+      <c r="P1387" s="18"/>
+      <c r="Q1387" s="18"/>
+      <c r="R1387" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:18" ht="15" thickBot="1">
+      <c r="A1388" s="2">
+        <v>1387</v>
+      </c>
+      <c r="B1388" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1388" s="56" t="s">
+        <v>2091</v>
+      </c>
+      <c r="D1388" s="56">
+        <v>135363378</v>
+      </c>
+      <c r="E1388" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1388" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1388" s="75">
+        <v>2797</v>
+      </c>
+      <c r="H1388" s="76">
+        <v>1411</v>
+      </c>
+      <c r="I1388" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1388" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1388" s="61" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1388" s="18"/>
+      <c r="M1388" s="18"/>
+      <c r="N1388" s="40"/>
+      <c r="O1388" s="18"/>
+      <c r="P1388" s="18"/>
+      <c r="Q1388" s="18"/>
+      <c r="R1388" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:18" ht="15" thickBot="1">
+      <c r="A1389" s="2">
+        <v>1388</v>
+      </c>
+      <c r="B1389" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1389" s="56" t="s">
+        <v>2092</v>
+      </c>
+      <c r="D1389" s="56">
+        <v>135767917</v>
+      </c>
+      <c r="E1389" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1389" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1389" s="75">
+        <v>2692</v>
+      </c>
+      <c r="H1389" s="76">
+        <v>3821</v>
+      </c>
+      <c r="I1389" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1389" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1389" s="61" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1389" s="18"/>
+      <c r="M1389" s="18"/>
+      <c r="N1389" s="40"/>
+      <c r="O1389" s="18"/>
+      <c r="P1389" s="18"/>
+      <c r="Q1389" s="18"/>
+      <c r="R1389" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:18" ht="15" thickBot="1">
+      <c r="A1390" s="2">
+        <v>1389</v>
+      </c>
+      <c r="B1390" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1390" s="56" t="s">
+        <v>2093</v>
+      </c>
+      <c r="D1390" s="56" t="s">
+        <v>2094</v>
+      </c>
+      <c r="E1390" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1390" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1390" s="75">
+        <v>30974</v>
+      </c>
+      <c r="H1390" s="76">
+        <v>38362</v>
+      </c>
+      <c r="I1390" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1390" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1390" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1390" s="18"/>
+      <c r="M1390" s="18"/>
+      <c r="N1390" s="40"/>
+      <c r="O1390" s="18"/>
+      <c r="P1390" s="18"/>
+      <c r="Q1390" s="11">
+        <v>99732006</v>
+      </c>
+      <c r="R1390" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1391" s="2">
+        <v>1390</v>
+      </c>
+      <c r="B1391" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1391" s="56" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D1391" s="56">
+        <v>103663425</v>
+      </c>
+      <c r="E1391" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1391" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1391" s="75">
+        <v>9560</v>
+      </c>
+      <c r="H1391" s="76">
+        <v>1713</v>
+      </c>
+      <c r="I1391" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1391" s="15" t="s">
+        <v>1706</v>
+      </c>
+      <c r="K1391" s="18"/>
+      <c r="L1391" s="18"/>
+      <c r="M1391" s="18"/>
+      <c r="N1391" s="40"/>
+      <c r="O1391" s="18"/>
+      <c r="P1391" s="18"/>
+      <c r="Q1391" s="11">
+        <v>94937118</v>
+      </c>
+      <c r="R1391" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1392" s="2">
+        <v>1391</v>
+      </c>
+      <c r="B1392" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1392" s="56" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D1392" s="56">
+        <v>121392208</v>
+      </c>
+      <c r="E1392" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1392" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1392" s="75">
+        <v>1957</v>
+      </c>
+      <c r="H1392" s="76">
+        <v>5293</v>
+      </c>
+      <c r="I1392" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1392" s="15" t="s">
+        <v>1706</v>
+      </c>
+      <c r="K1392" s="18"/>
+      <c r="L1392" s="18"/>
+      <c r="M1392" s="18"/>
+      <c r="N1392" s="40"/>
+      <c r="O1392" s="18"/>
+      <c r="P1392" s="18"/>
+      <c r="Q1392" s="11" t="s">
+        <v>2096</v>
+      </c>
+      <c r="R1392" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:18" ht="15" thickBot="1">
+      <c r="A1393" s="2">
+        <v>1392</v>
+      </c>
+      <c r="B1393" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1393" s="56" t="s">
+        <v>2097</v>
+      </c>
+      <c r="D1393" s="56">
+        <v>131449685</v>
+      </c>
+      <c r="E1393" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1393" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1393" s="75">
+        <v>5769</v>
+      </c>
+      <c r="H1393" s="76">
+        <v>3254</v>
+      </c>
+      <c r="I1393" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1393" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1393" s="61" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1393" s="18"/>
+      <c r="M1393" s="18"/>
+      <c r="N1393" s="40"/>
+      <c r="O1393" s="18"/>
+      <c r="P1393" s="18"/>
+      <c r="Q1393" s="18"/>
+      <c r="R1393" s="18"/>
+    </row>
+    <row r="1394" spans="1:18" ht="15" thickBot="1">
+      <c r="A1394" s="2">
+        <v>1393</v>
+      </c>
+      <c r="B1394" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1394" s="56" t="s">
+        <v>2098</v>
+      </c>
+      <c r="D1394" s="38"/>
+      <c r="E1394" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1394" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1394" s="75">
+        <v>40407</v>
+      </c>
+      <c r="H1394" s="38"/>
+      <c r="I1394" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1394" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1394" s="61" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1394" s="18"/>
+      <c r="M1394" s="18"/>
+      <c r="N1394" s="40"/>
+      <c r="O1394" s="18"/>
+      <c r="P1394" s="18"/>
+      <c r="Q1394" s="18"/>
+      <c r="R1394" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:18" ht="15" thickBot="1">
+      <c r="A1395" s="2">
+        <v>1394</v>
+      </c>
+      <c r="B1395" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1395" s="56" t="s">
+        <v>743</v>
+      </c>
+      <c r="D1395" s="38"/>
+      <c r="E1395" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1395" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1395" s="75">
+        <v>40405</v>
+      </c>
+      <c r="H1395" s="38"/>
+      <c r="I1395" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1395" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1395" s="61" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1395" s="18"/>
+      <c r="M1395" s="18"/>
+      <c r="N1395" s="40"/>
+      <c r="O1395" s="18"/>
+      <c r="P1395" s="18"/>
+      <c r="Q1395" s="18"/>
+      <c r="R1395" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:18" ht="15" thickBot="1">
+      <c r="A1396" s="2">
+        <v>1395</v>
+      </c>
+      <c r="B1396" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1396" s="56" t="s">
+        <v>2099</v>
+      </c>
+      <c r="D1396" s="38"/>
+      <c r="E1396" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1396" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1396" s="75">
+        <v>5020</v>
+      </c>
+      <c r="H1396" s="38"/>
+      <c r="I1396" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1396" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1396" s="61" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1396" s="18"/>
+      <c r="M1396" s="18"/>
+      <c r="N1396" s="40"/>
+      <c r="O1396" s="18"/>
+      <c r="P1396" s="18"/>
+      <c r="Q1396" s="18"/>
+      <c r="R1396" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:18" ht="15" thickBot="1">
+      <c r="A1397" s="2">
+        <v>1396</v>
+      </c>
+      <c r="B1397" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1397" s="56" t="s">
+        <v>2100</v>
+      </c>
+      <c r="D1397" s="38"/>
+      <c r="E1397" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1397" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1397" s="75">
+        <v>67266</v>
+      </c>
+      <c r="H1397" s="38"/>
+      <c r="I1397" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1397" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1397" s="61" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1397" s="18"/>
+      <c r="M1397" s="18"/>
+      <c r="N1397" s="40"/>
+      <c r="O1397" s="18"/>
+      <c r="P1397" s="18"/>
+      <c r="Q1397" s="18"/>
+      <c r="R1397" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:18" ht="15" thickBot="1">
+      <c r="A1398" s="2">
+        <v>1397</v>
+      </c>
+      <c r="B1398" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1398" s="56" t="s">
+        <v>2101</v>
+      </c>
+      <c r="D1398" s="56">
+        <v>105215777</v>
+      </c>
+      <c r="E1398" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1398" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1398" s="75">
+        <v>9314</v>
+      </c>
+      <c r="H1398" s="76">
+        <v>5845</v>
+      </c>
+      <c r="I1398" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1398" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1398" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1398" s="18"/>
+      <c r="M1398" s="18"/>
+      <c r="N1398" s="40"/>
+      <c r="O1398" s="18"/>
+      <c r="P1398" s="18"/>
+      <c r="Q1398" s="18"/>
+      <c r="R1398" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1399" s="2">
+        <v>1398</v>
+      </c>
+      <c r="B1399" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1399" s="56" t="s">
+        <v>2102</v>
+      </c>
+      <c r="D1399" s="56">
+        <v>134619447</v>
+      </c>
+      <c r="E1399" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1399" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1399" s="75">
+        <v>6222</v>
+      </c>
+      <c r="H1399" s="76">
+        <v>4607</v>
+      </c>
+      <c r="I1399" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1399" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1399" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1399" s="18"/>
+      <c r="M1399" s="18"/>
+      <c r="N1399" s="40"/>
+      <c r="O1399" s="18"/>
+      <c r="P1399" s="18"/>
+      <c r="Q1399" s="15">
+        <v>95432531</v>
+      </c>
+      <c r="R1399" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1400" s="2">
+        <v>1399</v>
+      </c>
+      <c r="B1400" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1400" s="56" t="s">
+        <v>947</v>
+      </c>
+      <c r="D1400" s="56">
+        <v>124239315</v>
+      </c>
+      <c r="E1400" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1400" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1400" s="75">
+        <v>2419</v>
+      </c>
+      <c r="H1400" s="76">
+        <v>2865</v>
+      </c>
+      <c r="I1400" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1400" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1400" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1400" s="18"/>
+      <c r="M1400" s="18"/>
+      <c r="N1400" s="40"/>
+      <c r="O1400" s="18"/>
+      <c r="P1400" s="18"/>
+      <c r="Q1400" s="15">
+        <v>79264044</v>
+      </c>
+      <c r="R1400" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1401" s="2">
+        <v>1400</v>
+      </c>
+      <c r="B1401" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1401" s="56" t="s">
+        <v>2103</v>
+      </c>
+      <c r="D1401" s="56">
+        <v>123436321</v>
+      </c>
+      <c r="E1401" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1401" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1401" s="75">
+        <v>8524</v>
+      </c>
+      <c r="H1401" s="76">
+        <v>5352</v>
+      </c>
+      <c r="I1401" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1401" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1401" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1401" s="18"/>
+      <c r="M1401" s="18"/>
+      <c r="N1401" s="40"/>
+      <c r="O1401" s="18"/>
+      <c r="P1401" s="18"/>
+      <c r="Q1401" s="15">
+        <v>71328155</v>
+      </c>
+      <c r="R1401" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1402" s="2">
+        <v>1401</v>
+      </c>
+      <c r="B1402" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1402" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="D1402" s="56" t="s">
+        <v>2104</v>
+      </c>
+      <c r="E1402" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1402" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1402" s="75">
+        <v>69693</v>
+      </c>
+      <c r="H1402" s="76">
+        <v>7021</v>
+      </c>
+      <c r="I1402" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1402" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1402" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1402" s="18"/>
+      <c r="M1402" s="18"/>
+      <c r="N1402" s="40"/>
+      <c r="O1402" s="18"/>
+      <c r="P1402" s="18"/>
+      <c r="Q1402" s="15">
+        <v>96876021895</v>
+      </c>
+      <c r="R1402" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1403" s="2">
+        <v>1402</v>
+      </c>
+      <c r="B1403" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1403" s="56" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D1403" s="56" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E1403" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1403" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1403" s="75">
+        <v>34507</v>
+      </c>
+      <c r="H1403" s="76">
+        <v>14858</v>
+      </c>
+      <c r="I1403" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1403" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1403" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1403" s="18"/>
+      <c r="M1403" s="18"/>
+      <c r="N1403" s="40"/>
+      <c r="O1403" s="18"/>
+      <c r="P1403" s="18"/>
+      <c r="Q1403" s="15">
+        <v>96895635079</v>
+      </c>
+      <c r="R1403" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1404" s="2">
+        <v>1403</v>
+      </c>
+      <c r="B1404" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1404" s="56" t="s">
+        <v>2106</v>
+      </c>
+      <c r="D1404" s="56">
+        <v>103684737</v>
+      </c>
+      <c r="E1404" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1404" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1404" s="75">
+        <v>9686</v>
+      </c>
+      <c r="H1404" s="76">
+        <v>4665</v>
+      </c>
+      <c r="I1404" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1404" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1404" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1404" s="18"/>
+      <c r="M1404" s="18"/>
+      <c r="N1404" s="40"/>
+      <c r="O1404" s="18"/>
+      <c r="P1404" s="18"/>
+      <c r="Q1404" s="15">
+        <v>90602548</v>
+      </c>
+      <c r="R1404" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1405" s="2">
+        <v>1404</v>
+      </c>
+      <c r="B1405" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1405" s="56" t="s">
+        <v>2107</v>
+      </c>
+      <c r="D1405" s="56">
+        <v>131373463</v>
+      </c>
+      <c r="E1405" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1405" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1405" s="75" t="s">
+        <v>2108</v>
+      </c>
+      <c r="H1405" s="76">
+        <v>5264</v>
+      </c>
+      <c r="I1405" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1405" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1405" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1405" s="18"/>
+      <c r="M1405" s="18"/>
+      <c r="N1405" s="40"/>
+      <c r="O1405" s="18"/>
+      <c r="P1405" s="18"/>
+      <c r="Q1405" s="18"/>
+      <c r="R1405" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1406" s="2">
+        <v>1405</v>
+      </c>
+      <c r="B1406" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1406" s="56" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D1406" s="56">
+        <v>116311615</v>
+      </c>
+      <c r="E1406" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1406" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1406" s="75">
+        <v>5240</v>
+      </c>
+      <c r="H1406" s="76">
+        <v>6053</v>
+      </c>
+      <c r="I1406" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1406" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1406" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1406" s="18"/>
+      <c r="M1406" s="18"/>
+      <c r="N1406" s="40"/>
+      <c r="O1406" s="18"/>
+      <c r="P1406" s="18"/>
+      <c r="Q1406" s="18"/>
+      <c r="R1406" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1407" s="2">
+        <v>1406</v>
+      </c>
+      <c r="B1407" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1407" s="56" t="s">
+        <v>2109</v>
+      </c>
+      <c r="D1407" s="56" t="s">
+        <v>2110</v>
+      </c>
+      <c r="E1407" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1407" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1407" s="75">
+        <v>15555</v>
+      </c>
+      <c r="H1407" s="76">
+        <v>87032</v>
+      </c>
+      <c r="I1407" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1407" s="15" t="s">
+        <v>2111</v>
+      </c>
+      <c r="K1407" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1407" s="18"/>
+      <c r="M1407" s="18"/>
+      <c r="N1407" s="40"/>
+      <c r="O1407" s="18"/>
+      <c r="P1407" s="18"/>
+      <c r="Q1407" s="11">
+        <v>553624302</v>
+      </c>
+      <c r="R1407" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1408" s="2">
+        <v>1407</v>
+      </c>
+      <c r="B1408" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1408" s="56" t="s">
+        <v>2112</v>
+      </c>
+      <c r="D1408" s="56" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E1408" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1408" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1408" s="75">
+        <v>35724</v>
+      </c>
+      <c r="H1408" s="76">
+        <v>68761</v>
+      </c>
+      <c r="I1408" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1408" s="15" t="s">
+        <v>2111</v>
+      </c>
+      <c r="K1408" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1408" s="18"/>
+      <c r="M1408" s="18"/>
+      <c r="N1408" s="40"/>
+      <c r="O1408" s="18"/>
+      <c r="P1408" s="18"/>
+      <c r="Q1408" s="11">
+        <v>971553590824</v>
+      </c>
+      <c r="R1408" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1409" s="2">
+        <v>1408</v>
+      </c>
+      <c r="B1409" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C1409" s="56" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1409" s="56" t="s">
+        <v>2114</v>
+      </c>
+      <c r="E1409" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1409" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1409" s="75">
+        <v>63226</v>
+      </c>
+      <c r="H1409" s="38"/>
+      <c r="I1409" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1409" s="15" t="s">
+        <v>2111</v>
+      </c>
+      <c r="K1409" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1409" s="18"/>
+      <c r="M1409" s="18"/>
+      <c r="N1409" s="40"/>
+      <c r="O1409" s="18"/>
+      <c r="P1409" s="18"/>
+      <c r="Q1409" s="11">
+        <v>527752054</v>
+      </c>
+      <c r="R1409" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F571937-BD4E-498D-A3FC-EFA1DA4576AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{270BE473-7107-4A4E-8E02-334E17055CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10741" uniqueCount="2188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10818" uniqueCount="2199">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -6602,6 +6602,39 @@
   </si>
   <si>
     <t>TH5154222</t>
+  </si>
+  <si>
+    <t>LIAQAT KHAN</t>
+  </si>
+  <si>
+    <t>AHMED HUMAID GHNAM</t>
+  </si>
+  <si>
+    <t>SALEM SHATAYAT KHALFAN</t>
+  </si>
+  <si>
+    <t>JJ1790605</t>
+  </si>
+  <si>
+    <t>SALEM SALEEM</t>
+  </si>
+  <si>
+    <t>HAMDUN ABDALLAH</t>
+  </si>
+  <si>
+    <t>UZAIR ABBAS</t>
+  </si>
+  <si>
+    <t>ALI MURTAZA</t>
+  </si>
+  <si>
+    <t>HAMMAD AKHTAR</t>
+  </si>
+  <si>
+    <t>WASEEM SHAHZAD</t>
+  </si>
+  <si>
+    <t>KR5147635</t>
   </si>
 </sst>
 </file>
@@ -6978,7 +7011,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7210,6 +7243,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7525,7 +7561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1444"/>
+  <dimension ref="A1:R1455"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -7577,7 +7613,7 @@
       <c r="L1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="4" t="s">
         <v>1923</v>
       </c>
       <c r="N1" s="8" t="s">
@@ -15797,10 +15833,12 @@
       <c r="J170" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="K170" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L170" s="18"/>
+      <c r="K170" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L170" s="53">
+        <v>46250</v>
+      </c>
       <c r="M170" s="18"/>
       <c r="N170" s="54">
         <v>214</v>
@@ -15893,10 +15931,12 @@
       <c r="J172" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="K172" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L172" s="18"/>
+      <c r="K172" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L172" s="53">
+        <v>46250</v>
+      </c>
       <c r="M172" s="18"/>
       <c r="N172" s="40"/>
       <c r="O172" s="18"/>
@@ -16779,10 +16819,12 @@
       <c r="J191" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="K191" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L191" s="18"/>
+      <c r="K191" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L191" s="53">
+        <v>46250</v>
+      </c>
       <c r="M191" s="18"/>
       <c r="N191" s="40"/>
       <c r="O191" s="18"/>
@@ -29889,10 +29931,12 @@
       <c r="J466" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="K466" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L466" s="18"/>
+      <c r="K466" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L466" s="53">
+        <v>46250</v>
+      </c>
       <c r="M466" s="18"/>
       <c r="N466" s="40"/>
       <c r="O466" s="18"/>
@@ -29979,10 +30023,12 @@
       <c r="J468" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="K468" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L468" s="18"/>
+      <c r="K468" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L468" s="53">
+        <v>46250</v>
+      </c>
       <c r="M468" s="18"/>
       <c r="N468" s="40"/>
       <c r="O468" s="18"/>
@@ -30065,10 +30111,12 @@
       <c r="J470" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="K470" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L470" s="18"/>
+      <c r="K470" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L470" s="53">
+        <v>46250</v>
+      </c>
       <c r="M470" s="18"/>
       <c r="N470" s="40"/>
       <c r="O470" s="18"/>
@@ -30793,10 +30841,12 @@
       <c r="J486" s="15" t="s">
         <v>923</v>
       </c>
-      <c r="K486" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L486" s="18"/>
+      <c r="K486" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L486" s="53">
+        <v>46250</v>
+      </c>
       <c r="M486" s="18"/>
       <c r="N486" s="40"/>
       <c r="O486" s="18"/>
@@ -32613,10 +32663,12 @@
       <c r="J525" s="15" t="s">
         <v>848</v>
       </c>
-      <c r="K525" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L525" s="18"/>
+      <c r="K525" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L525" s="53">
+        <v>46250</v>
+      </c>
       <c r="M525" s="18"/>
       <c r="N525" s="54">
         <v>797</v>
@@ -32661,10 +32713,12 @@
       <c r="J526" s="15" t="s">
         <v>848</v>
       </c>
-      <c r="K526" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L526" s="18"/>
+      <c r="K526" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L526" s="53">
+        <v>46250</v>
+      </c>
       <c r="M526" s="18"/>
       <c r="N526" s="54">
         <v>2568</v>
@@ -32707,10 +32761,12 @@
       <c r="J527" s="27" t="s">
         <v>890</v>
       </c>
-      <c r="K527" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L527" s="28"/>
+      <c r="K527" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L527" s="53">
+        <v>46250</v>
+      </c>
       <c r="M527" s="28"/>
       <c r="N527" s="27">
         <v>416</v>
@@ -32753,10 +32809,12 @@
       <c r="J528" s="15" t="s">
         <v>1115</v>
       </c>
-      <c r="K528" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L528" s="18"/>
+      <c r="K528" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L528" s="53">
+        <v>46250</v>
+      </c>
       <c r="M528" s="18"/>
       <c r="N528" s="40"/>
       <c r="O528" s="18"/>
@@ -32799,10 +32857,12 @@
       <c r="J529" s="15" t="s">
         <v>1115</v>
       </c>
-      <c r="K529" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L529" s="18"/>
+      <c r="K529" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L529" s="53">
+        <v>46250</v>
+      </c>
       <c r="M529" s="18"/>
       <c r="N529" s="40"/>
       <c r="O529" s="18"/>
@@ -32843,10 +32903,12 @@
       <c r="J530" s="15" t="s">
         <v>1115</v>
       </c>
-      <c r="K530" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L530" s="18"/>
+      <c r="K530" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L530" s="53">
+        <v>46250</v>
+      </c>
       <c r="M530" s="18"/>
       <c r="N530" s="40"/>
       <c r="O530" s="18"/>
@@ -32887,10 +32949,12 @@
       <c r="J531" s="15" t="s">
         <v>1115</v>
       </c>
-      <c r="K531" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L531" s="18"/>
+      <c r="K531" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L531" s="53">
+        <v>46250</v>
+      </c>
       <c r="M531" s="18"/>
       <c r="N531" s="40"/>
       <c r="O531" s="18"/>
@@ -32977,10 +33041,12 @@
       <c r="J533" s="15" t="s">
         <v>562</v>
       </c>
-      <c r="K533" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L533" s="18"/>
+      <c r="K533" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L533" s="53">
+        <v>46250</v>
+      </c>
       <c r="M533" s="18"/>
       <c r="N533" s="40"/>
       <c r="O533" s="18"/>
@@ -33023,10 +33089,12 @@
       <c r="J534" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="K534" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L534" s="18"/>
+      <c r="K534" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L534" s="53">
+        <v>46250</v>
+      </c>
       <c r="M534" s="18"/>
       <c r="N534" s="54">
         <v>706</v>
@@ -33119,10 +33187,12 @@
       <c r="J536" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="K536" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L536" s="18"/>
+      <c r="K536" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L536" s="53">
+        <v>46250</v>
+      </c>
       <c r="M536" s="18"/>
       <c r="N536" s="40"/>
       <c r="O536" s="18"/>
@@ -33163,10 +33233,12 @@
       <c r="J537" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="K537" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L537" s="18"/>
+      <c r="K537" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L537" s="53">
+        <v>46250</v>
+      </c>
       <c r="M537" s="18"/>
       <c r="N537" s="54">
         <v>285</v>
@@ -33209,10 +33281,12 @@
       <c r="J538" s="15" t="s">
         <v>976</v>
       </c>
-      <c r="K538" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L538" s="18"/>
+      <c r="K538" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L538" s="53">
+        <v>46250</v>
+      </c>
       <c r="M538" s="18"/>
       <c r="N538" s="54">
         <v>675</v>
@@ -33255,10 +33329,12 @@
       <c r="J539" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="K539" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L539" s="18"/>
+      <c r="K539" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L539" s="53">
+        <v>46250</v>
+      </c>
       <c r="M539" s="18"/>
       <c r="N539" s="40"/>
       <c r="O539" s="18"/>
@@ -33299,10 +33375,12 @@
       <c r="J540" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="K540" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L540" s="18"/>
+      <c r="K540" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L540" s="53">
+        <v>46250</v>
+      </c>
       <c r="M540" s="18"/>
       <c r="N540" s="40"/>
       <c r="O540" s="18"/>
@@ -33391,10 +33469,12 @@
       <c r="J542" s="15" t="s">
         <v>1140</v>
       </c>
-      <c r="K542" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L542" s="18"/>
+      <c r="K542" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L542" s="53">
+        <v>46250</v>
+      </c>
       <c r="M542" s="18"/>
       <c r="N542" s="54">
         <v>328</v>
@@ -33435,10 +33515,12 @@
       <c r="J543" s="15" t="s">
         <v>1140</v>
       </c>
-      <c r="K543" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L543" s="18"/>
+      <c r="K543" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L543" s="53">
+        <v>46250</v>
+      </c>
       <c r="M543" s="18"/>
       <c r="N543" s="40"/>
       <c r="O543" s="18"/>
@@ -33479,10 +33561,12 @@
       <c r="J544" s="15" t="s">
         <v>1145</v>
       </c>
-      <c r="K544" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L544" s="18"/>
+      <c r="K544" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L544" s="53">
+        <v>46250</v>
+      </c>
       <c r="M544" s="18"/>
       <c r="N544" s="54">
         <v>373</v>
@@ -33527,10 +33611,12 @@
       <c r="J545" s="15" t="s">
         <v>1145</v>
       </c>
-      <c r="K545" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L545" s="18"/>
+      <c r="K545" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L545" s="53">
+        <v>46250</v>
+      </c>
       <c r="M545" s="18"/>
       <c r="N545" s="54">
         <v>561</v>
@@ -33575,10 +33661,12 @@
       <c r="J546" s="15" t="s">
         <v>839</v>
       </c>
-      <c r="K546" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L546" s="18"/>
+      <c r="K546" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L546" s="53">
+        <v>46250</v>
+      </c>
       <c r="M546" s="18"/>
       <c r="N546" s="40"/>
       <c r="O546" s="18"/>
@@ -34319,10 +34407,12 @@
       <c r="J562" s="15" t="s">
         <v>950</v>
       </c>
-      <c r="K562" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L562" s="18"/>
+      <c r="K562" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L562" s="53">
+        <v>46250</v>
+      </c>
       <c r="M562" s="18"/>
       <c r="N562" s="54">
         <v>438</v>
@@ -34415,10 +34505,12 @@
       <c r="J564" s="15" t="s">
         <v>950</v>
       </c>
-      <c r="K564" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L564" s="18"/>
+      <c r="K564" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L564" s="53">
+        <v>46250</v>
+      </c>
       <c r="M564" s="18"/>
       <c r="N564" s="54">
         <v>441</v>
@@ -37657,10 +37749,12 @@
       <c r="J632" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K632" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L632" s="18"/>
+      <c r="K632" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L632" s="53">
+        <v>46250</v>
+      </c>
       <c r="M632" s="18"/>
       <c r="N632" s="40"/>
       <c r="O632" s="18"/>
@@ -37703,10 +37797,12 @@
       <c r="J633" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K633" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L633" s="18"/>
+      <c r="K633" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L633" s="53">
+        <v>46250</v>
+      </c>
       <c r="M633" s="18"/>
       <c r="N633" s="40"/>
       <c r="O633" s="18"/>
@@ -38795,10 +38891,12 @@
       <c r="J656" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K656" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L656" s="18"/>
+      <c r="K656" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L656" s="53">
+        <v>46250</v>
+      </c>
       <c r="M656" s="18"/>
       <c r="N656" s="54">
         <v>807</v>
@@ -44501,10 +44599,12 @@
       <c r="J777" s="15" t="s">
         <v>1207</v>
       </c>
-      <c r="K777" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L777" s="18"/>
+      <c r="K777" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L777" s="53">
+        <v>46250</v>
+      </c>
       <c r="M777" s="18"/>
       <c r="N777" s="40"/>
       <c r="O777" s="18"/>
@@ -44549,10 +44649,12 @@
       <c r="J778" s="15" t="s">
         <v>1207</v>
       </c>
-      <c r="K778" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L778" s="18"/>
+      <c r="K778" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L778" s="53">
+        <v>46250</v>
+      </c>
       <c r="M778" s="18"/>
       <c r="N778" s="40"/>
       <c r="O778" s="18"/>
@@ -44645,10 +44747,12 @@
       <c r="J780" s="15" t="s">
         <v>1207</v>
       </c>
-      <c r="K780" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L780" s="18"/>
+      <c r="K780" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L780" s="53">
+        <v>46250</v>
+      </c>
       <c r="M780" s="18"/>
       <c r="N780" s="40"/>
       <c r="O780" s="18"/>
@@ -44691,10 +44795,12 @@
       <c r="J781" s="15" t="s">
         <v>1207</v>
       </c>
-      <c r="K781" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L781" s="18"/>
+      <c r="K781" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L781" s="53">
+        <v>46250</v>
+      </c>
       <c r="M781" s="18"/>
       <c r="N781" s="54">
         <v>251</v>
@@ -45539,10 +45645,12 @@
       <c r="J799" s="15" t="s">
         <v>1250</v>
       </c>
-      <c r="K799" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L799" s="18"/>
+      <c r="K799" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L799" s="53">
+        <v>46250</v>
+      </c>
       <c r="M799" s="18"/>
       <c r="N799" s="54">
         <v>684</v>
@@ -45587,10 +45695,12 @@
       <c r="J800" s="15" t="s">
         <v>1250</v>
       </c>
-      <c r="K800" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L800" s="18"/>
+      <c r="K800" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L800" s="53">
+        <v>46250</v>
+      </c>
       <c r="M800" s="18"/>
       <c r="N800" s="54">
         <v>699</v>
@@ -45633,10 +45743,12 @@
       <c r="J801" s="15" t="s">
         <v>1250</v>
       </c>
-      <c r="K801" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L801" s="18"/>
+      <c r="K801" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L801" s="53">
+        <v>46250</v>
+      </c>
       <c r="M801" s="18"/>
       <c r="N801" s="54">
         <v>327</v>
@@ -45681,10 +45793,12 @@
       <c r="J802" s="15" t="s">
         <v>1250</v>
       </c>
-      <c r="K802" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L802" s="18"/>
+      <c r="K802" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L802" s="53">
+        <v>46250</v>
+      </c>
       <c r="M802" s="18"/>
       <c r="N802" s="54">
         <v>324</v>
@@ -45729,10 +45843,12 @@
       <c r="J803" s="15" t="s">
         <v>1250</v>
       </c>
-      <c r="K803" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L803" s="18"/>
+      <c r="K803" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L803" s="53">
+        <v>46250</v>
+      </c>
       <c r="M803" s="18"/>
       <c r="N803" s="40"/>
       <c r="O803" s="18"/>
@@ -45775,10 +45891,12 @@
       <c r="J804" s="15" t="s">
         <v>1250</v>
       </c>
-      <c r="K804" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L804" s="18"/>
+      <c r="K804" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L804" s="53">
+        <v>46250</v>
+      </c>
       <c r="M804" s="18"/>
       <c r="N804" s="54">
         <v>711</v>
@@ -45823,10 +45941,12 @@
       <c r="J805" s="15" t="s">
         <v>1250</v>
       </c>
-      <c r="K805" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L805" s="18"/>
+      <c r="K805" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L805" s="53">
+        <v>46250</v>
+      </c>
       <c r="M805" s="18"/>
       <c r="N805" s="40"/>
       <c r="O805" s="18"/>
@@ -45869,10 +45989,12 @@
       <c r="J806" s="15" t="s">
         <v>1250</v>
       </c>
-      <c r="K806" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L806" s="18"/>
+      <c r="K806" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L806" s="53">
+        <v>46250</v>
+      </c>
       <c r="M806" s="18"/>
       <c r="N806" s="54">
         <v>320</v>
@@ -49023,10 +49145,12 @@
       <c r="J875" s="15" t="s">
         <v>1706</v>
       </c>
-      <c r="K875" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L875" s="18"/>
+      <c r="K875" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L875" s="53">
+        <v>46250</v>
+      </c>
       <c r="M875" s="18"/>
       <c r="N875" s="40"/>
       <c r="O875" s="18"/>
@@ -49159,10 +49283,12 @@
       <c r="J878" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="K878" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L878" s="18"/>
+      <c r="K878" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L878" s="53">
+        <v>46250</v>
+      </c>
       <c r="M878" s="18"/>
       <c r="N878" s="54">
         <v>180</v>
@@ -50713,10 +50839,12 @@
       <c r="J912" s="15" t="s">
         <v>1792</v>
       </c>
-      <c r="K912" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L912" s="18"/>
+      <c r="K912" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L912" s="53">
+        <v>46250</v>
+      </c>
       <c r="M912" s="18"/>
       <c r="N912" s="40"/>
       <c r="O912" s="18"/>
@@ -51723,10 +51851,12 @@
       <c r="J934" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K934" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L934" s="18"/>
+      <c r="K934" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L934" s="53">
+        <v>46250</v>
+      </c>
       <c r="M934" s="18"/>
       <c r="N934" s="54">
         <v>272</v>
@@ -51771,10 +51901,12 @@
       <c r="J935" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K935" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L935" s="18"/>
+      <c r="K935" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L935" s="53">
+        <v>46250</v>
+      </c>
       <c r="M935" s="18"/>
       <c r="N935" s="54">
         <v>273</v>
@@ -51819,10 +51951,12 @@
       <c r="J936" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K936" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L936" s="18"/>
+      <c r="K936" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L936" s="53">
+        <v>46250</v>
+      </c>
       <c r="M936" s="18"/>
       <c r="N936" s="54">
         <v>274</v>
@@ -51867,10 +52001,12 @@
       <c r="J937" s="15" t="s">
         <v>382</v>
       </c>
-      <c r="K937" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L937" s="18"/>
+      <c r="K937" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L937" s="53">
+        <v>46250</v>
+      </c>
       <c r="M937" s="18"/>
       <c r="N937" s="40"/>
       <c r="O937" s="18"/>
@@ -61146,10 +61282,10 @@
         <v>122</v>
       </c>
       <c r="G1140" s="71">
+        <v>9381</v>
+      </c>
+      <c r="H1140" s="72">
         <v>7261</v>
-      </c>
-      <c r="H1140" s="72">
-        <v>9381</v>
       </c>
       <c r="I1140" s="22" t="s">
         <v>1736</v>
@@ -64901,10 +65037,12 @@
       <c r="J1226" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1226" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1226" s="18"/>
+      <c r="K1226" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1226" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1226" s="18"/>
       <c r="N1226" s="40"/>
       <c r="O1226" s="18"/>
@@ -70519,10 +70657,12 @@
       <c r="J1349" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1349" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1349" s="18"/>
+      <c r="K1349" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1349" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1349" s="18"/>
       <c r="N1349" s="54">
         <v>704</v>
@@ -74638,7 +74778,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="1442" spans="1:18" ht="15" thickBot="1">
+    <row r="1442" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1442" s="2">
         <v>1441</v>
       </c>
@@ -74646,31 +74786,29 @@
         <v>46245</v>
       </c>
       <c r="C1442" s="55" t="s">
-        <v>1776</v>
+        <v>2188</v>
       </c>
       <c r="D1442" s="55">
-        <v>20703738</v>
-      </c>
-      <c r="E1442" s="37" t="s">
-        <v>121</v>
+        <v>123757652</v>
+      </c>
+      <c r="E1442" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="F1442" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1442" s="74">
-        <v>9420</v>
+        <v>7264</v>
       </c>
       <c r="H1442" s="75">
-        <v>8585</v>
-      </c>
-      <c r="I1442" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1442" s="15" t="s">
-        <v>1207</v>
-      </c>
-      <c r="K1442" s="60" t="s">
-        <v>1189</v>
+        <v>7946</v>
+      </c>
+      <c r="I1442" s="48" t="s">
+        <v>485</v>
+      </c>
+      <c r="J1442" s="18"/>
+      <c r="K1442" s="37" t="s">
+        <v>175</v>
       </c>
       <c r="L1442" s="18"/>
       <c r="M1442" s="18"/>
@@ -74678,11 +74816,11 @@
       <c r="O1442" s="18"/>
       <c r="P1442" s="18"/>
       <c r="Q1442" s="18"/>
-      <c r="R1442" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1443" spans="1:18" ht="15" thickBot="1">
+      <c r="R1442" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1443" s="2">
         <v>1442</v>
       </c>
@@ -74690,10 +74828,10 @@
         <v>46245</v>
       </c>
       <c r="C1443" s="55" t="s">
-        <v>1777</v>
+        <v>2189</v>
       </c>
       <c r="D1443" s="55">
-        <v>24162468</v>
+        <v>10386563</v>
       </c>
       <c r="E1443" s="37" t="s">
         <v>121</v>
@@ -74702,16 +74840,16 @@
         <v>122</v>
       </c>
       <c r="G1443" s="74">
-        <v>7644</v>
+        <v>7380</v>
       </c>
       <c r="H1443" s="75">
-        <v>1748</v>
+        <v>-999</v>
       </c>
       <c r="I1443" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1443" s="15" t="s">
-        <v>1207</v>
+        <v>319</v>
       </c>
       <c r="K1443" s="60" t="s">
         <v>1189</v>
@@ -74722,11 +74860,11 @@
       <c r="O1443" s="18"/>
       <c r="P1443" s="18"/>
       <c r="Q1443" s="18"/>
-      <c r="R1443" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1444" spans="1:18" ht="15" thickBot="1">
+      <c r="R1443" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1444" s="2">
         <v>1443</v>
       </c>
@@ -74734,31 +74872,31 @@
         <v>46245</v>
       </c>
       <c r="C1444" s="55" t="s">
-        <v>2186</v>
-      </c>
-      <c r="D1444" s="55" t="s">
-        <v>2187</v>
-      </c>
-      <c r="E1444" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1444" s="13" t="s">
-        <v>22</v>
+        <v>2190</v>
+      </c>
+      <c r="D1444" s="55">
+        <v>19588434</v>
+      </c>
+      <c r="E1444" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1444" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="G1444" s="74">
-        <v>82098</v>
+        <v>50</v>
       </c>
       <c r="H1444" s="75">
-        <v>70636</v>
-      </c>
-      <c r="I1444" s="22" t="s">
-        <v>563</v>
+        <v>2081</v>
+      </c>
+      <c r="I1444" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="J1444" s="15" t="s">
-        <v>1672</v>
-      </c>
-      <c r="K1444" s="17" t="s">
-        <v>12</v>
+        <v>319</v>
+      </c>
+      <c r="K1444" s="60" t="s">
+        <v>1189</v>
       </c>
       <c r="L1444" s="18"/>
       <c r="M1444" s="18"/>
@@ -74766,7 +74904,507 @@
       <c r="O1444" s="18"/>
       <c r="P1444" s="18"/>
       <c r="Q1444" s="18"/>
-      <c r="R1444" s="22" t="s">
+      <c r="R1444" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1445" s="2">
+        <v>1444</v>
+      </c>
+      <c r="B1445" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1445" s="55" t="s">
+        <v>2102</v>
+      </c>
+      <c r="D1445" s="55" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1445" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1445" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1445" s="74">
+        <v>48738</v>
+      </c>
+      <c r="H1445" s="75">
+        <v>37765</v>
+      </c>
+      <c r="I1445" s="48" t="s">
+        <v>485</v>
+      </c>
+      <c r="J1445" s="18"/>
+      <c r="K1445" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1445" s="18"/>
+      <c r="M1445" s="18"/>
+      <c r="N1445" s="54">
+        <v>817</v>
+      </c>
+      <c r="O1445" s="18"/>
+      <c r="P1445" s="18"/>
+      <c r="Q1445" s="18"/>
+      <c r="R1445" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1446" s="2">
+        <v>1445</v>
+      </c>
+      <c r="B1446" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1446" s="55" t="s">
+        <v>360</v>
+      </c>
+      <c r="D1446" s="55">
+        <v>51644987</v>
+      </c>
+      <c r="E1446" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1446" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1446" s="74">
+        <v>2661</v>
+      </c>
+      <c r="H1446" s="75">
+        <v>8366</v>
+      </c>
+      <c r="I1446" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1446" s="15" t="s">
+        <v>371</v>
+      </c>
+      <c r="K1446" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1446" s="18"/>
+      <c r="M1446" s="18"/>
+      <c r="N1446" s="40"/>
+      <c r="O1446" s="18"/>
+      <c r="P1446" s="18"/>
+      <c r="Q1446" s="11">
+        <v>95520514</v>
+      </c>
+      <c r="R1446" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1447" s="2">
+        <v>1446</v>
+      </c>
+      <c r="B1447" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1447" s="55" t="s">
+        <v>2192</v>
+      </c>
+      <c r="D1447" s="55">
+        <v>9891324</v>
+      </c>
+      <c r="E1447" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1447" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1447" s="74">
+        <v>9393</v>
+      </c>
+      <c r="H1447" s="75">
+        <v>-4320</v>
+      </c>
+      <c r="I1447" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1447" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1447" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1447" s="18"/>
+      <c r="M1447" s="18"/>
+      <c r="N1447" s="40"/>
+      <c r="O1447" s="18"/>
+      <c r="P1447" s="18"/>
+      <c r="Q1447" s="18"/>
+      <c r="R1447" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1448" s="2">
+        <v>1447</v>
+      </c>
+      <c r="B1448" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1448" s="55" t="s">
+        <v>2193</v>
+      </c>
+      <c r="D1448" s="55">
+        <v>132724487</v>
+      </c>
+      <c r="E1448" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1448" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1448" s="74">
+        <v>7397</v>
+      </c>
+      <c r="H1448" s="75">
+        <v>9165</v>
+      </c>
+      <c r="I1448" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1448" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1448" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1448" s="18"/>
+      <c r="M1448" s="18"/>
+      <c r="N1448" s="40"/>
+      <c r="O1448" s="18"/>
+      <c r="P1448" s="18"/>
+      <c r="Q1448" s="18"/>
+      <c r="R1448" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:18" ht="15" thickBot="1">
+      <c r="A1449" s="2">
+        <v>1448</v>
+      </c>
+      <c r="B1449" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1449" s="55" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D1449" s="55">
+        <v>20703738</v>
+      </c>
+      <c r="E1449" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1449" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1449" s="74">
+        <v>9420</v>
+      </c>
+      <c r="H1449" s="75">
+        <v>8585</v>
+      </c>
+      <c r="I1449" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1449" s="15" t="s">
+        <v>1207</v>
+      </c>
+      <c r="K1449" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1449" s="18"/>
+      <c r="M1449" s="18"/>
+      <c r="N1449" s="40"/>
+      <c r="O1449" s="18"/>
+      <c r="P1449" s="18"/>
+      <c r="Q1449" s="18"/>
+      <c r="R1449" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:18" ht="15" thickBot="1">
+      <c r="A1450" s="2">
+        <v>1449</v>
+      </c>
+      <c r="B1450" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1450" s="55" t="s">
+        <v>1777</v>
+      </c>
+      <c r="D1450" s="55">
+        <v>24162468</v>
+      </c>
+      <c r="E1450" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1450" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1450" s="74">
+        <v>7644</v>
+      </c>
+      <c r="H1450" s="75">
+        <v>1748</v>
+      </c>
+      <c r="I1450" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1450" s="15" t="s">
+        <v>1207</v>
+      </c>
+      <c r="K1450" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1450" s="18"/>
+      <c r="M1450" s="18"/>
+      <c r="N1450" s="40"/>
+      <c r="O1450" s="18"/>
+      <c r="P1450" s="18"/>
+      <c r="Q1450" s="18"/>
+      <c r="R1450" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:18" ht="15" thickBot="1">
+      <c r="A1451" s="2">
+        <v>1450</v>
+      </c>
+      <c r="B1451" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1451" s="55" t="s">
+        <v>2194</v>
+      </c>
+      <c r="D1451" s="55">
+        <v>107861342</v>
+      </c>
+      <c r="E1451" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1451" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1451" s="74">
+        <v>5726</v>
+      </c>
+      <c r="H1451" s="75">
+        <v>-8287</v>
+      </c>
+      <c r="I1451" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1451" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K1451" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1451" s="18"/>
+      <c r="M1451" s="18"/>
+      <c r="N1451" s="54">
+        <v>899</v>
+      </c>
+      <c r="O1451" s="18"/>
+      <c r="P1451" s="18"/>
+      <c r="Q1451" s="11">
+        <v>79060959</v>
+      </c>
+      <c r="R1451" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:18" ht="15" thickBot="1">
+      <c r="A1452" s="2">
+        <v>1451</v>
+      </c>
+      <c r="B1452" s="31">
+        <v>46245</v>
+      </c>
+      <c r="C1452" s="68" t="s">
+        <v>2195</v>
+      </c>
+      <c r="D1452" s="68">
+        <v>133986224</v>
+      </c>
+      <c r="E1452" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1452" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1452" s="78">
+        <v>6153</v>
+      </c>
+      <c r="H1452" s="78">
+        <v>5169</v>
+      </c>
+      <c r="I1452" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1452" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="K1452" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1452" s="28"/>
+      <c r="M1452" s="28"/>
+      <c r="N1452" s="27">
+        <v>889</v>
+      </c>
+      <c r="O1452" s="28"/>
+      <c r="P1452" s="28"/>
+      <c r="Q1452" s="24">
+        <v>76843136</v>
+      </c>
+      <c r="R1452" s="29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:18" ht="15" thickBot="1">
+      <c r="A1453" s="2">
+        <v>1452</v>
+      </c>
+      <c r="B1453" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1453" s="55" t="s">
+        <v>2196</v>
+      </c>
+      <c r="D1453" s="55">
+        <v>135954527</v>
+      </c>
+      <c r="E1453" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1453" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1453" s="74">
+        <v>1447</v>
+      </c>
+      <c r="H1453" s="75">
+        <v>3025</v>
+      </c>
+      <c r="I1453" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1453" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K1453" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1453" s="18"/>
+      <c r="M1453" s="18"/>
+      <c r="N1453" s="54">
+        <v>898</v>
+      </c>
+      <c r="O1453" s="18"/>
+      <c r="P1453" s="18"/>
+      <c r="Q1453" s="11">
+        <v>77294508</v>
+      </c>
+      <c r="R1453" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:18" ht="15" thickBot="1">
+      <c r="A1454" s="2">
+        <v>1453</v>
+      </c>
+      <c r="B1454" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1454" s="55" t="s">
+        <v>2186</v>
+      </c>
+      <c r="D1454" s="55" t="s">
+        <v>2187</v>
+      </c>
+      <c r="E1454" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1454" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1454" s="74">
+        <v>82098</v>
+      </c>
+      <c r="H1454" s="75">
+        <v>70636</v>
+      </c>
+      <c r="I1454" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1454" s="15" t="s">
+        <v>1672</v>
+      </c>
+      <c r="K1454" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1454" s="18"/>
+      <c r="M1454" s="18"/>
+      <c r="N1454" s="40"/>
+      <c r="O1454" s="18"/>
+      <c r="P1454" s="18"/>
+      <c r="Q1454" s="18"/>
+      <c r="R1454" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1455" s="2">
+        <v>1454</v>
+      </c>
+      <c r="B1455" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1455" s="55" t="s">
+        <v>2197</v>
+      </c>
+      <c r="D1455" s="55" t="s">
+        <v>2198</v>
+      </c>
+      <c r="E1455" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1455" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1455" s="74">
+        <v>39305</v>
+      </c>
+      <c r="H1455" s="75">
+        <v>94368</v>
+      </c>
+      <c r="I1455" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1455" s="15" t="s">
+        <v>2153</v>
+      </c>
+      <c r="K1455" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1455" s="18"/>
+      <c r="M1455" s="18"/>
+      <c r="N1455" s="40"/>
+      <c r="O1455" s="18"/>
+      <c r="P1455" s="18"/>
+      <c r="Q1455" s="11">
+        <v>77129970</v>
+      </c>
+      <c r="R1455" s="22" t="s">
         <v>131</v>
       </c>
     </row>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5865B93-0B34-455B-8D23-2E5128F57BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{784A7E64-3C82-4F80-B050-46E677F4F2C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10854" uniqueCount="2203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10939" uniqueCount="2217">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -6647,6 +6647,48 @@
   </si>
   <si>
     <t>SAJID IQBAL</t>
+  </si>
+  <si>
+    <t>ASIF SOHAIL</t>
+  </si>
+  <si>
+    <t>FR5191273</t>
+  </si>
+  <si>
+    <t>RAISAT IQBAL</t>
+  </si>
+  <si>
+    <t>SIDDIQUE</t>
+  </si>
+  <si>
+    <t>JAWAD AL HASSAN</t>
+  </si>
+  <si>
+    <t>ASMAT ULLAH</t>
+  </si>
+  <si>
+    <t>TAWAR BOOTA</t>
+  </si>
+  <si>
+    <t>AB6620452</t>
+  </si>
+  <si>
+    <t>62581-</t>
+  </si>
+  <si>
+    <t>AC6311104</t>
+  </si>
+  <si>
+    <t>GATE</t>
+  </si>
+  <si>
+    <t>QAIS ALI RASHID</t>
+  </si>
+  <si>
+    <t>SAMI MOHAMED</t>
+  </si>
+  <si>
+    <t>QE4124614</t>
   </si>
 </sst>
 </file>
@@ -7576,7 +7618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1460"/>
+  <dimension ref="A1:R1471"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -75725,6 +75767,496 @@
         <v>131</v>
       </c>
     </row>
+    <row r="1461" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1461" s="2">
+        <v>50</v>
+      </c>
+      <c r="B1461" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1461" s="55" t="s">
+        <v>2203</v>
+      </c>
+      <c r="D1461" s="55" t="s">
+        <v>2204</v>
+      </c>
+      <c r="E1461" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1461" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1461" s="74">
+        <v>9429</v>
+      </c>
+      <c r="H1461" s="75">
+        <v>5615</v>
+      </c>
+      <c r="I1461" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1461" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="K1461" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1461" s="18"/>
+      <c r="M1461" s="18"/>
+      <c r="N1461" s="40"/>
+      <c r="O1461" s="18"/>
+      <c r="P1461" s="18"/>
+      <c r="Q1461" s="18"/>
+      <c r="R1461" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:18" ht="15" thickBot="1">
+      <c r="A1462" s="2">
+        <v>51</v>
+      </c>
+      <c r="B1462" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1462" s="55" t="s">
+        <v>2205</v>
+      </c>
+      <c r="D1462" s="55">
+        <v>96801698</v>
+      </c>
+      <c r="E1462" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1462" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1462" s="74">
+        <v>7327</v>
+      </c>
+      <c r="H1462" s="75">
+        <v>6326</v>
+      </c>
+      <c r="I1462" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1462" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1462" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1462" s="18"/>
+      <c r="M1462" s="18"/>
+      <c r="N1462" s="40"/>
+      <c r="O1462" s="18"/>
+      <c r="P1462" s="18"/>
+      <c r="Q1462" s="18"/>
+      <c r="R1462" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:18" ht="15" thickBot="1">
+      <c r="A1463" s="2">
+        <v>52</v>
+      </c>
+      <c r="B1463" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1463" s="55" t="s">
+        <v>2206</v>
+      </c>
+      <c r="D1463" s="38"/>
+      <c r="E1463" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1463" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1463" s="74">
+        <v>69588</v>
+      </c>
+      <c r="H1463" s="38"/>
+      <c r="I1463" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1463" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1463" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1463" s="18"/>
+      <c r="M1463" s="18"/>
+      <c r="N1463" s="40"/>
+      <c r="O1463" s="18"/>
+      <c r="P1463" s="18"/>
+      <c r="Q1463" s="18"/>
+      <c r="R1463" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1464" s="2">
+        <v>53</v>
+      </c>
+      <c r="B1464" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1464" s="55" t="s">
+        <v>2207</v>
+      </c>
+      <c r="D1464" s="55">
+        <v>95307809</v>
+      </c>
+      <c r="E1464" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1464" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1464" s="74">
+        <v>6289</v>
+      </c>
+      <c r="H1464" s="75">
+        <v>8289</v>
+      </c>
+      <c r="I1464" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1464" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1464" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1464" s="18"/>
+      <c r="M1464" s="18"/>
+      <c r="N1464" s="40"/>
+      <c r="O1464" s="18"/>
+      <c r="P1464" s="18"/>
+      <c r="Q1464" s="18"/>
+      <c r="R1464" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1465" s="2">
+        <v>54</v>
+      </c>
+      <c r="B1465" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1465" s="55" t="s">
+        <v>2208</v>
+      </c>
+      <c r="D1465" s="55">
+        <v>98434725</v>
+      </c>
+      <c r="E1465" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1465" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1465" s="74">
+        <v>8146</v>
+      </c>
+      <c r="H1465" s="75">
+        <v>7980</v>
+      </c>
+      <c r="I1465" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1465" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1465" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1465" s="15">
+        <v>77450471</v>
+      </c>
+      <c r="M1465" s="18"/>
+      <c r="N1465" s="40"/>
+      <c r="O1465" s="18"/>
+      <c r="P1465" s="18"/>
+      <c r="Q1465" s="18"/>
+      <c r="R1465" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:18" ht="15" thickBot="1">
+      <c r="A1466" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1466" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1466" s="55" t="s">
+        <v>2209</v>
+      </c>
+      <c r="D1466" s="55" t="s">
+        <v>2210</v>
+      </c>
+      <c r="E1466" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1466" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1466" s="74">
+        <v>57994</v>
+      </c>
+      <c r="H1466" s="75" t="s">
+        <v>2211</v>
+      </c>
+      <c r="I1466" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1466" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1466" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1466" s="18"/>
+      <c r="M1466" s="18"/>
+      <c r="N1466" s="40"/>
+      <c r="O1466" s="18"/>
+      <c r="P1466" s="18"/>
+      <c r="Q1466" s="18"/>
+      <c r="R1466" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:18" ht="15" thickBot="1">
+      <c r="A1467" s="2">
+        <v>56</v>
+      </c>
+      <c r="B1467" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1467" s="55" t="s">
+        <v>752</v>
+      </c>
+      <c r="D1467" s="55" t="s">
+        <v>2212</v>
+      </c>
+      <c r="E1467" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1467" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1467" s="74">
+        <v>58269</v>
+      </c>
+      <c r="H1467" s="75">
+        <v>35158</v>
+      </c>
+      <c r="I1467" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1467" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1467" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1467" s="18"/>
+      <c r="M1467" s="18"/>
+      <c r="N1467" s="40"/>
+      <c r="O1467" s="18"/>
+      <c r="P1467" s="18"/>
+      <c r="Q1467" s="18"/>
+      <c r="R1467" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:18" ht="15" thickBot="1">
+      <c r="A1468" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1468" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1468" s="55" t="s">
+        <v>320</v>
+      </c>
+      <c r="D1468" s="55">
+        <v>9025663</v>
+      </c>
+      <c r="E1468" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1468" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1468" s="74">
+        <v>3372</v>
+      </c>
+      <c r="H1468" s="75">
+        <v>-3639</v>
+      </c>
+      <c r="I1468" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1468" s="15" t="s">
+        <v>1207</v>
+      </c>
+      <c r="K1468" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1468" s="18"/>
+      <c r="M1468" s="18"/>
+      <c r="N1468" s="40"/>
+      <c r="O1468" s="18"/>
+      <c r="P1468" s="49" t="s">
+        <v>2213</v>
+      </c>
+      <c r="Q1468" s="18"/>
+      <c r="R1468" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:18" ht="15" thickBot="1">
+      <c r="A1469" s="2">
+        <v>58</v>
+      </c>
+      <c r="B1469" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1469" s="55" t="s">
+        <v>2214</v>
+      </c>
+      <c r="D1469" s="55">
+        <v>20806662</v>
+      </c>
+      <c r="E1469" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1469" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1469" s="74">
+        <v>4936</v>
+      </c>
+      <c r="H1469" s="75">
+        <v>1603</v>
+      </c>
+      <c r="I1469" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1469" s="15" t="s">
+        <v>1207</v>
+      </c>
+      <c r="K1469" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1469" s="18"/>
+      <c r="M1469" s="18"/>
+      <c r="N1469" s="40"/>
+      <c r="O1469" s="18"/>
+      <c r="P1469" s="49" t="s">
+        <v>2213</v>
+      </c>
+      <c r="Q1469" s="18"/>
+      <c r="R1469" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:18" ht="15" thickBot="1">
+      <c r="A1470" s="2">
+        <v>59</v>
+      </c>
+      <c r="B1470" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1470" s="55" t="s">
+        <v>2215</v>
+      </c>
+      <c r="D1470" s="55">
+        <v>7888654</v>
+      </c>
+      <c r="E1470" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1470" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1470" s="74">
+        <v>6376</v>
+      </c>
+      <c r="H1470" s="75">
+        <v>-1603</v>
+      </c>
+      <c r="I1470" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1470" s="15" t="s">
+        <v>1207</v>
+      </c>
+      <c r="K1470" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1470" s="18"/>
+      <c r="M1470" s="18"/>
+      <c r="N1470" s="40"/>
+      <c r="O1470" s="18"/>
+      <c r="P1470" s="49" t="s">
+        <v>2213</v>
+      </c>
+      <c r="Q1470" s="18"/>
+      <c r="R1470" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:18" ht="15" thickBot="1">
+      <c r="A1471" s="2">
+        <v>60</v>
+      </c>
+      <c r="B1471" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1471" s="55" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D1471" s="55" t="s">
+        <v>2216</v>
+      </c>
+      <c r="E1471" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1471" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1471" s="74">
+        <v>56437</v>
+      </c>
+      <c r="H1471" s="75">
+        <v>38484</v>
+      </c>
+      <c r="I1471" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1471" s="15" t="s">
+        <v>562</v>
+      </c>
+      <c r="K1471" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1471" s="18"/>
+      <c r="M1471" s="18"/>
+      <c r="N1471" s="40"/>
+      <c r="O1471" s="18"/>
+      <c r="P1471" s="18"/>
+      <c r="Q1471" s="11">
+        <v>508875771</v>
+      </c>
+      <c r="R1471" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{784A7E64-3C82-4F80-B050-46E677F4F2C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93713358-F0C8-4679-8236-F931D76660AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10939" uniqueCount="2217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11050" uniqueCount="2223">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -6689,6 +6689,24 @@
   </si>
   <si>
     <t>QE4124614</t>
+  </si>
+  <si>
+    <t>FD6800474</t>
+  </si>
+  <si>
+    <t>ABDU LLAH HUMAID</t>
+  </si>
+  <si>
+    <t>SULAIMAN NASSER</t>
+  </si>
+  <si>
+    <t>BADAR HUMAID</t>
+  </si>
+  <si>
+    <t>SAID MOHAMMED</t>
+  </si>
+  <si>
+    <t>FASIAL MAHMOOD</t>
   </si>
 </sst>
 </file>
@@ -7065,7 +7083,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7302,6 +7320,30 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7618,7 +7660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1471"/>
+  <dimension ref="A1:R1490"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -48518,8 +48560,8 @@
       <c r="J859" s="15" t="s">
         <v>1484</v>
       </c>
-      <c r="K859" s="17" t="s">
-        <v>12</v>
+      <c r="K859" s="37" t="s">
+        <v>175</v>
       </c>
       <c r="L859" s="18"/>
       <c r="M859" s="18"/>
@@ -48527,7 +48569,9 @@
         <v>449</v>
       </c>
       <c r="O859" s="18"/>
-      <c r="P859" s="18"/>
+      <c r="P859" s="49" t="s">
+        <v>2126</v>
+      </c>
       <c r="Q859" s="18"/>
       <c r="R859" s="20" t="s">
         <v>11</v>
@@ -53332,10 +53376,12 @@
       <c r="J963" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K963" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L963" s="18"/>
+      <c r="K963" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L963" s="53">
+        <v>46251</v>
+      </c>
       <c r="M963" s="18"/>
       <c r="N963" s="54">
         <v>466</v>
@@ -53380,10 +53426,12 @@
       <c r="J964" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K964" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L964" s="18"/>
+      <c r="K964" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L964" s="53">
+        <v>46251</v>
+      </c>
       <c r="M964" s="18"/>
       <c r="N964" s="40"/>
       <c r="O964" s="18"/>
@@ -54292,10 +54340,12 @@
       <c r="J983" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K983" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L983" s="18"/>
+      <c r="K983" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L983" s="53">
+        <v>46251</v>
+      </c>
       <c r="M983" s="18"/>
       <c r="N983" s="40"/>
       <c r="O983" s="53">
@@ -54340,10 +54390,12 @@
       <c r="J984" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K984" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L984" s="18"/>
+      <c r="K984" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L984" s="53">
+        <v>46251</v>
+      </c>
       <c r="M984" s="18"/>
       <c r="N984" s="40"/>
       <c r="O984" s="53">
@@ -54388,10 +54440,12 @@
       <c r="J985" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K985" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L985" s="18"/>
+      <c r="K985" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L985" s="53">
+        <v>46251</v>
+      </c>
       <c r="M985" s="18"/>
       <c r="N985" s="54">
         <v>161</v>
@@ -75973,14 +76027,14 @@
       <c r="K1465" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="L1465" s="15">
-        <v>77450471</v>
-      </c>
+      <c r="L1465" s="38"/>
       <c r="M1465" s="18"/>
       <c r="N1465" s="40"/>
       <c r="O1465" s="18"/>
       <c r="P1465" s="18"/>
-      <c r="Q1465" s="18"/>
+      <c r="Q1465" s="15">
+        <v>77450471</v>
+      </c>
       <c r="R1465" s="22" t="s">
         <v>131</v>
       </c>
@@ -76257,6 +76311,764 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1472" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1472" s="2">
+        <v>61</v>
+      </c>
+      <c r="B1472" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1472" s="55" t="s">
+        <v>961</v>
+      </c>
+      <c r="D1472" s="55">
+        <v>137911273</v>
+      </c>
+      <c r="E1472" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1472" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1472" s="74">
+        <v>8212</v>
+      </c>
+      <c r="H1472" s="75">
+        <v>1005</v>
+      </c>
+      <c r="I1472" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1472" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1472" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1472" s="18"/>
+      <c r="M1472" s="18"/>
+      <c r="N1472" s="40"/>
+      <c r="O1472" s="18"/>
+      <c r="P1472" s="18"/>
+      <c r="Q1472" s="18"/>
+      <c r="R1472" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1473" s="2">
+        <v>62</v>
+      </c>
+      <c r="B1473" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1473" s="55" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1473" s="55" t="s">
+        <v>2217</v>
+      </c>
+      <c r="E1473" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1473" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1473" s="74">
+        <v>87930</v>
+      </c>
+      <c r="H1473" s="75">
+        <v>54759</v>
+      </c>
+      <c r="I1473" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1473" s="15" t="s">
+        <v>1028</v>
+      </c>
+      <c r="K1473" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1473" s="18"/>
+      <c r="M1473" s="18"/>
+      <c r="N1473" s="40"/>
+      <c r="O1473" s="18"/>
+      <c r="P1473" s="18"/>
+      <c r="Q1473" s="18"/>
+      <c r="R1473" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1474" s="2">
+        <v>63</v>
+      </c>
+      <c r="B1474" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1474" s="55" t="s">
+        <v>1960</v>
+      </c>
+      <c r="D1474" s="55">
+        <v>18471584</v>
+      </c>
+      <c r="E1474" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1474" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1474" s="74">
+        <v>6080</v>
+      </c>
+      <c r="H1474" s="75">
+        <v>8219</v>
+      </c>
+      <c r="I1474" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1474" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1474" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1474" s="18"/>
+      <c r="M1474" s="18"/>
+      <c r="N1474" s="40"/>
+      <c r="O1474" s="18"/>
+      <c r="P1474" s="18"/>
+      <c r="Q1474" s="18"/>
+      <c r="R1474" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1475" s="2">
+        <v>64</v>
+      </c>
+      <c r="B1475" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1475" s="55" t="s">
+        <v>2218</v>
+      </c>
+      <c r="D1475" s="55">
+        <v>19245071</v>
+      </c>
+      <c r="E1475" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1475" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1475" s="74">
+        <v>9742</v>
+      </c>
+      <c r="H1475" s="75">
+        <v>1793</v>
+      </c>
+      <c r="I1475" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1475" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1475" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1475" s="18"/>
+      <c r="M1475" s="18"/>
+      <c r="N1475" s="40"/>
+      <c r="O1475" s="18"/>
+      <c r="P1475" s="18"/>
+      <c r="Q1475" s="18"/>
+      <c r="R1475" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1476" s="2">
+        <v>65</v>
+      </c>
+      <c r="B1476" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1476" s="55" t="s">
+        <v>2219</v>
+      </c>
+      <c r="D1476" s="55">
+        <v>10433156</v>
+      </c>
+      <c r="E1476" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1476" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1476" s="74">
+        <v>5238</v>
+      </c>
+      <c r="H1476" s="75">
+        <v>458</v>
+      </c>
+      <c r="I1476" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1476" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1476" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1476" s="18"/>
+      <c r="M1476" s="18"/>
+      <c r="N1476" s="40"/>
+      <c r="O1476" s="18"/>
+      <c r="P1476" s="18"/>
+      <c r="Q1476" s="18"/>
+      <c r="R1476" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1477" s="2">
+        <v>66</v>
+      </c>
+      <c r="B1477" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1477" s="55" t="s">
+        <v>2220</v>
+      </c>
+      <c r="D1477" s="55">
+        <v>12478178</v>
+      </c>
+      <c r="E1477" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1477" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1477" s="74">
+        <v>255</v>
+      </c>
+      <c r="H1477" s="75">
+        <v>4081</v>
+      </c>
+      <c r="I1477" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1477" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1477" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1477" s="18"/>
+      <c r="M1477" s="18"/>
+      <c r="N1477" s="40"/>
+      <c r="O1477" s="18"/>
+      <c r="P1477" s="18"/>
+      <c r="Q1477" s="18"/>
+      <c r="R1477" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1478" s="2">
+        <v>67</v>
+      </c>
+      <c r="B1478" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1478" s="55" t="s">
+        <v>2221</v>
+      </c>
+      <c r="D1478" s="55">
+        <v>11687823</v>
+      </c>
+      <c r="E1478" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1478" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1478" s="74">
+        <v>1164</v>
+      </c>
+      <c r="H1478" s="75">
+        <v>4807</v>
+      </c>
+      <c r="I1478" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1478" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1478" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1478" s="18"/>
+      <c r="M1478" s="18"/>
+      <c r="N1478" s="40"/>
+      <c r="O1478" s="18"/>
+      <c r="P1478" s="18"/>
+      <c r="Q1478" s="18"/>
+      <c r="R1478" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:18" ht="15" thickBot="1">
+      <c r="A1479" s="2">
+        <v>68</v>
+      </c>
+      <c r="B1479" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1479" s="55" t="s">
+        <v>993</v>
+      </c>
+      <c r="D1479" s="55">
+        <v>137221766</v>
+      </c>
+      <c r="E1479" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1479" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1479" s="74">
+        <v>5865</v>
+      </c>
+      <c r="H1479" s="75">
+        <v>1817</v>
+      </c>
+      <c r="I1479" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1479" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1479" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1479" s="18"/>
+      <c r="M1479" s="18"/>
+      <c r="N1479" s="40"/>
+      <c r="O1479" s="18"/>
+      <c r="P1479" s="18"/>
+      <c r="Q1479" s="11">
+        <v>91382542</v>
+      </c>
+      <c r="R1479" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:18" ht="15" thickBot="1">
+      <c r="A1480" s="2">
+        <v>69</v>
+      </c>
+      <c r="B1480" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1480" s="55" t="s">
+        <v>2222</v>
+      </c>
+      <c r="D1480" s="55">
+        <v>69667313</v>
+      </c>
+      <c r="E1480" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1480" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1480" s="74">
+        <v>3859</v>
+      </c>
+      <c r="H1480" s="75">
+        <v>4713</v>
+      </c>
+      <c r="I1480" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1480" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1480" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1480" s="18"/>
+      <c r="M1480" s="18"/>
+      <c r="N1480" s="40"/>
+      <c r="O1480" s="18"/>
+      <c r="P1480" s="18"/>
+      <c r="Q1480" s="18"/>
+      <c r="R1480" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:18" ht="15" thickBot="1">
+      <c r="A1481" s="2">
+        <v>70</v>
+      </c>
+      <c r="B1481" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1481" s="55" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D1481" s="55">
+        <v>81251502</v>
+      </c>
+      <c r="E1481" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1481" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1481" s="74">
+        <v>7873</v>
+      </c>
+      <c r="H1481" s="75">
+        <v>1336</v>
+      </c>
+      <c r="I1481" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1481" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1481" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1481" s="18"/>
+      <c r="M1481" s="18"/>
+      <c r="N1481" s="40"/>
+      <c r="O1481" s="18"/>
+      <c r="P1481" s="18"/>
+      <c r="Q1481" s="18"/>
+      <c r="R1481" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:18" ht="15" thickBot="1">
+      <c r="A1482" s="2">
+        <v>71</v>
+      </c>
+      <c r="B1482" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1482" s="55" t="s">
+        <v>562</v>
+      </c>
+      <c r="D1482" s="55">
+        <v>96895520514</v>
+      </c>
+      <c r="E1482" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1482" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1482" s="74">
+        <v>8366</v>
+      </c>
+      <c r="H1482" s="75">
+        <v>2661</v>
+      </c>
+      <c r="I1482" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1482" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1482" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1482" s="18"/>
+      <c r="M1482" s="18"/>
+      <c r="N1482" s="40"/>
+      <c r="O1482" s="18"/>
+      <c r="P1482" s="18"/>
+      <c r="Q1482" s="18"/>
+      <c r="R1482" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:18" ht="15" thickBot="1">
+      <c r="A1483" s="2">
+        <v>72</v>
+      </c>
+      <c r="B1483" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1483" s="81"/>
+      <c r="D1483" s="81"/>
+      <c r="E1483" s="80"/>
+      <c r="F1483" s="80"/>
+      <c r="G1483" s="82">
+        <v>9392</v>
+      </c>
+      <c r="H1483" s="81"/>
+      <c r="I1483" s="83" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1483" s="84" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1483" s="85" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1483" s="80"/>
+      <c r="M1483" s="80"/>
+      <c r="N1483" s="86"/>
+      <c r="O1483" s="80"/>
+      <c r="P1483" s="80"/>
+      <c r="Q1483" s="80"/>
+      <c r="R1483" s="87" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:18" ht="15" thickBot="1">
+      <c r="A1484" s="2">
+        <v>73</v>
+      </c>
+      <c r="B1484" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1484" s="38"/>
+      <c r="D1484" s="38"/>
+      <c r="E1484" s="18"/>
+      <c r="F1484" s="18"/>
+      <c r="G1484" s="74">
+        <v>2046</v>
+      </c>
+      <c r="H1484" s="38"/>
+      <c r="I1484" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1484" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1484" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1484" s="18"/>
+      <c r="M1484" s="18"/>
+      <c r="N1484" s="40"/>
+      <c r="O1484" s="18"/>
+      <c r="P1484" s="18"/>
+      <c r="Q1484" s="18"/>
+      <c r="R1484" s="87" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:18" ht="15" thickBot="1">
+      <c r="A1485" s="2">
+        <v>74</v>
+      </c>
+      <c r="B1485" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1485" s="38"/>
+      <c r="D1485" s="38"/>
+      <c r="E1485" s="18"/>
+      <c r="F1485" s="18"/>
+      <c r="G1485" s="74">
+        <v>2258</v>
+      </c>
+      <c r="H1485" s="38"/>
+      <c r="I1485" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1485" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1485" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1485" s="18"/>
+      <c r="M1485" s="18"/>
+      <c r="N1485" s="40"/>
+      <c r="O1485" s="18"/>
+      <c r="P1485" s="18"/>
+      <c r="Q1485" s="18"/>
+      <c r="R1485" s="87" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:18" ht="15" thickBot="1">
+      <c r="A1486" s="2">
+        <v>75</v>
+      </c>
+      <c r="B1486" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1486" s="38"/>
+      <c r="D1486" s="38"/>
+      <c r="E1486" s="18"/>
+      <c r="F1486" s="18"/>
+      <c r="G1486" s="74">
+        <v>60840</v>
+      </c>
+      <c r="H1486" s="38"/>
+      <c r="I1486" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1486" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1486" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1486" s="18"/>
+      <c r="M1486" s="18"/>
+      <c r="N1486" s="40"/>
+      <c r="O1486" s="18"/>
+      <c r="P1486" s="18"/>
+      <c r="Q1486" s="18"/>
+      <c r="R1486" s="87" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:18" ht="15" thickBot="1">
+      <c r="A1487" s="2">
+        <v>76</v>
+      </c>
+      <c r="B1487" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1487" s="38"/>
+      <c r="D1487" s="38"/>
+      <c r="E1487" s="18"/>
+      <c r="F1487" s="18"/>
+      <c r="G1487" s="74">
+        <v>18771</v>
+      </c>
+      <c r="H1487" s="38"/>
+      <c r="I1487" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1487" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1487" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1487" s="18"/>
+      <c r="M1487" s="18"/>
+      <c r="N1487" s="40"/>
+      <c r="O1487" s="18"/>
+      <c r="P1487" s="18"/>
+      <c r="Q1487" s="18"/>
+      <c r="R1487" s="87" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:18" ht="15" thickBot="1">
+      <c r="A1488" s="2">
+        <v>77</v>
+      </c>
+      <c r="B1488" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1488" s="38"/>
+      <c r="D1488" s="38"/>
+      <c r="E1488" s="18"/>
+      <c r="F1488" s="18"/>
+      <c r="G1488" s="74">
+        <v>72527</v>
+      </c>
+      <c r="H1488" s="38"/>
+      <c r="I1488" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1488" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1488" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1488" s="18"/>
+      <c r="M1488" s="18"/>
+      <c r="N1488" s="40"/>
+      <c r="O1488" s="18"/>
+      <c r="P1488" s="18"/>
+      <c r="Q1488" s="18"/>
+      <c r="R1488" s="87" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:18" ht="15" thickBot="1">
+      <c r="A1489" s="2">
+        <v>78</v>
+      </c>
+      <c r="B1489" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1489" s="38"/>
+      <c r="D1489" s="38"/>
+      <c r="E1489" s="18"/>
+      <c r="F1489" s="18"/>
+      <c r="G1489" s="74">
+        <v>1859</v>
+      </c>
+      <c r="H1489" s="38"/>
+      <c r="I1489" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1489" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1489" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1489" s="18"/>
+      <c r="M1489" s="18"/>
+      <c r="N1489" s="40"/>
+      <c r="O1489" s="18"/>
+      <c r="P1489" s="18"/>
+      <c r="Q1489" s="18"/>
+      <c r="R1489" s="87" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:18" ht="15" thickBot="1">
+      <c r="A1490" s="2">
+        <v>79</v>
+      </c>
+      <c r="B1490" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1490" s="38"/>
+      <c r="D1490" s="38"/>
+      <c r="E1490" s="18"/>
+      <c r="F1490" s="18"/>
+      <c r="G1490" s="74">
+        <v>77145</v>
+      </c>
+      <c r="H1490" s="38"/>
+      <c r="I1490" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1490" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1490" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1490" s="18"/>
+      <c r="M1490" s="18"/>
+      <c r="N1490" s="40"/>
+      <c r="O1490" s="18"/>
+      <c r="P1490" s="18"/>
+      <c r="Q1490" s="18"/>
+      <c r="R1490" s="87" t="s">
+        <v>131</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93713358-F0C8-4679-8236-F931D76660AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C7E87F-6357-4ECF-8578-FA645D413D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11050" uniqueCount="2223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11153" uniqueCount="2245">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -6707,13 +6707,79 @@
   </si>
   <si>
     <t>FASIAL MAHMOOD</t>
+  </si>
+  <si>
+    <t>BILAL HUSSAIN</t>
+  </si>
+  <si>
+    <t>ZAIN AKBAR</t>
+  </si>
+  <si>
+    <t>SARFRAZ ALI</t>
+  </si>
+  <si>
+    <t>KJ1793035</t>
+  </si>
+  <si>
+    <t>USMAN SAIL</t>
+  </si>
+  <si>
+    <t>ZULQARNAIN TARAR</t>
+  </si>
+  <si>
+    <t>DHIYAS KHAMIS</t>
+  </si>
+  <si>
+    <t>AHMED SAID</t>
+  </si>
+  <si>
+    <t>YOUNIS ALI</t>
+  </si>
+  <si>
+    <t>AN3704514</t>
+  </si>
+  <si>
+    <t>HARIS MAHMOOD</t>
+  </si>
+  <si>
+    <t>QZ0150146</t>
+  </si>
+  <si>
+    <t>MAMRAZ HUSSAIN</t>
+  </si>
+  <si>
+    <t>NH6892395</t>
+  </si>
+  <si>
+    <t>AS2742367</t>
+  </si>
+  <si>
+    <t>FARHAN LAIQAT</t>
+  </si>
+  <si>
+    <t>DF8963425</t>
+  </si>
+  <si>
+    <t>RAJAB SHAHZAD</t>
+  </si>
+  <si>
+    <t>CQ5159723</t>
+  </si>
+  <si>
+    <t>EY7964742</t>
+  </si>
+  <si>
+    <t>SHOAIB ARIF</t>
+  </si>
+  <si>
+    <t>GR1983915</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="37">
+  <fonts count="38">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6942,6 +7008,11 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Lexend"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -7083,7 +7154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7307,43 +7378,16 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7660,7 +7704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1490"/>
+  <dimension ref="A1:R1500"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -7697,7 +7741,7 @@
       <c r="G1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="78" t="s">
         <v>20</v>
       </c>
       <c r="I1" s="4" t="s">
@@ -7762,10 +7806,12 @@
       <c r="J2" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="K2" s="67" t="s">
-        <v>1285</v>
-      </c>
-      <c r="L2" s="18"/>
+      <c r="K2" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L2" s="53">
+        <v>46245</v>
+      </c>
       <c r="M2" s="18"/>
       <c r="N2" s="54">
         <v>97</v>
@@ -8520,7 +8566,7 @@
       </c>
     </row>
     <row r="18" spans="1:18" ht="15" thickBot="1">
-      <c r="A18" s="79">
+      <c r="A18" s="77">
         <v>17</v>
       </c>
       <c r="B18" s="31">
@@ -14159,7 +14205,7 @@
         <v>46247</v>
       </c>
       <c r="M134" s="18"/>
-      <c r="N134" s="76" t="s">
+      <c r="N134" s="75" t="s">
         <v>2115</v>
       </c>
       <c r="O134" s="53">
@@ -19465,7 +19511,7 @@
         <v>22</v>
       </c>
       <c r="G246" s="14">
-        <v>83597</v>
+        <v>295</v>
       </c>
       <c r="H246" s="15">
         <v>67698</v>
@@ -22285,7 +22331,7 @@
       </c>
       <c r="L305" s="18"/>
       <c r="M305" s="18"/>
-      <c r="N305" s="77" t="s">
+      <c r="N305" s="76" t="s">
         <v>2116</v>
       </c>
       <c r="O305" s="18"/>
@@ -22939,7 +22985,7 @@
         <v>46247</v>
       </c>
       <c r="M318" s="18"/>
-      <c r="N318" s="77" t="s">
+      <c r="N318" s="76" t="s">
         <v>2117</v>
       </c>
       <c r="O318" s="18"/>
@@ -22989,7 +23035,7 @@
         <v>46247</v>
       </c>
       <c r="M319" s="18"/>
-      <c r="N319" s="77" t="s">
+      <c r="N319" s="76" t="s">
         <v>2118</v>
       </c>
       <c r="O319" s="18"/>
@@ -31830,10 +31876,12 @@
       <c r="J505" s="15" t="s">
         <v>950</v>
       </c>
-      <c r="K505" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L505" s="18"/>
+      <c r="K505" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L505" s="53">
+        <v>46250</v>
+      </c>
       <c r="M505" s="18"/>
       <c r="N505" s="54">
         <v>447</v>
@@ -31878,10 +31926,12 @@
       <c r="J506" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K506" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L506" s="18"/>
+      <c r="K506" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L506" s="53">
+        <v>46250</v>
+      </c>
       <c r="M506" s="18"/>
       <c r="N506" s="40"/>
       <c r="O506" s="18"/>
@@ -31924,10 +31974,12 @@
       <c r="J507" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K507" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L507" s="18"/>
+      <c r="K507" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L507" s="53">
+        <v>46250</v>
+      </c>
       <c r="M507" s="18"/>
       <c r="N507" s="54">
         <v>810</v>
@@ -31970,10 +32022,12 @@
       <c r="J508" s="15" t="s">
         <v>953</v>
       </c>
-      <c r="K508" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L508" s="18"/>
+      <c r="K508" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L508" s="53">
+        <v>46250</v>
+      </c>
       <c r="M508" s="18"/>
       <c r="N508" s="54">
         <v>210</v>
@@ -32018,10 +32072,12 @@
       <c r="J509" s="15" t="s">
         <v>953</v>
       </c>
-      <c r="K509" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L509" s="18"/>
+      <c r="K509" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L509" s="53">
+        <v>46250</v>
+      </c>
       <c r="M509" s="18"/>
       <c r="N509" s="40"/>
       <c r="O509" s="18"/>
@@ -32532,10 +32588,12 @@
       <c r="J520" s="15" t="s">
         <v>976</v>
       </c>
-      <c r="K520" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L520" s="18"/>
+      <c r="K520" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L520" s="53">
+        <v>46250</v>
+      </c>
       <c r="M520" s="18"/>
       <c r="N520" s="54">
         <v>478</v>
@@ -32578,10 +32636,12 @@
       <c r="J521" s="15" t="s">
         <v>976</v>
       </c>
-      <c r="K521" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L521" s="18"/>
+      <c r="K521" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L521" s="53">
+        <v>46250</v>
+      </c>
       <c r="M521" s="18"/>
       <c r="N521" s="54">
         <v>477</v>
@@ -32626,10 +32686,12 @@
       <c r="J522" s="15" t="s">
         <v>976</v>
       </c>
-      <c r="K522" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L522" s="18"/>
+      <c r="K522" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L522" s="53">
+        <v>46250</v>
+      </c>
       <c r="M522" s="18"/>
       <c r="N522" s="54">
         <v>676</v>
@@ -32672,10 +32734,12 @@
       <c r="J523" s="15" t="s">
         <v>976</v>
       </c>
-      <c r="K523" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L523" s="18"/>
+      <c r="K523" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L523" s="53">
+        <v>46250</v>
+      </c>
       <c r="M523" s="18"/>
       <c r="N523" s="40"/>
       <c r="O523" s="18"/>
@@ -32716,10 +32780,12 @@
       <c r="J524" s="15" t="s">
         <v>976</v>
       </c>
-      <c r="K524" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L524" s="18"/>
+      <c r="K524" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L524" s="53">
+        <v>46250</v>
+      </c>
       <c r="M524" s="18"/>
       <c r="N524" s="40"/>
       <c r="O524" s="18"/>
@@ -33238,10 +33304,12 @@
       <c r="J535" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="K535" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L535" s="18"/>
+      <c r="K535" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L535" s="53">
+        <v>46250</v>
+      </c>
       <c r="M535" s="18"/>
       <c r="N535" s="54">
         <v>753</v>
@@ -33808,10 +33876,12 @@
       <c r="J547" s="15" t="s">
         <v>839</v>
       </c>
-      <c r="K547" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L547" s="18"/>
+      <c r="K547" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L547" s="53">
+        <v>46250</v>
+      </c>
       <c r="M547" s="18"/>
       <c r="N547" s="40"/>
       <c r="O547" s="18"/>
@@ -33854,10 +33924,12 @@
       <c r="J548" s="15" t="s">
         <v>839</v>
       </c>
-      <c r="K548" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L548" s="18"/>
+      <c r="K548" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L548" s="53">
+        <v>46250</v>
+      </c>
       <c r="M548" s="18"/>
       <c r="N548" s="54">
         <v>575</v>
@@ -33902,10 +33974,12 @@
       <c r="J549" s="15" t="s">
         <v>839</v>
       </c>
-      <c r="K549" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L549" s="18"/>
+      <c r="K549" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L549" s="53">
+        <v>46250</v>
+      </c>
       <c r="M549" s="18"/>
       <c r="N549" s="54">
         <v>583</v>
@@ -33950,10 +34024,12 @@
       <c r="J550" s="15" t="s">
         <v>839</v>
       </c>
-      <c r="K550" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L550" s="18"/>
+      <c r="K550" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L550" s="53">
+        <v>46250</v>
+      </c>
       <c r="M550" s="18"/>
       <c r="N550" s="54">
         <v>584</v>
@@ -33998,10 +34074,12 @@
       <c r="J551" s="15" t="s">
         <v>839</v>
       </c>
-      <c r="K551" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L551" s="18"/>
+      <c r="K551" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L551" s="53">
+        <v>46250</v>
+      </c>
       <c r="M551" s="18"/>
       <c r="N551" s="40"/>
       <c r="O551" s="18"/>
@@ -34042,10 +34120,12 @@
       <c r="J552" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="K552" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L552" s="18"/>
+      <c r="K552" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L552" s="53">
+        <v>46250</v>
+      </c>
       <c r="M552" s="18"/>
       <c r="N552" s="40"/>
       <c r="O552" s="18"/>
@@ -34086,10 +34166,12 @@
       <c r="J553" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="K553" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L553" s="18"/>
+      <c r="K553" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L553" s="53">
+        <v>46250</v>
+      </c>
       <c r="M553" s="18"/>
       <c r="N553" s="40"/>
       <c r="O553" s="18"/>
@@ -34130,10 +34212,12 @@
       <c r="J554" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="K554" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L554" s="18"/>
+      <c r="K554" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L554" s="53">
+        <v>46250</v>
+      </c>
       <c r="M554" s="18"/>
       <c r="N554" s="40"/>
       <c r="O554" s="18"/>
@@ -34176,10 +34260,12 @@
       <c r="J555" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="K555" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L555" s="18"/>
+      <c r="K555" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L555" s="53">
+        <v>46250</v>
+      </c>
       <c r="M555" s="18"/>
       <c r="N555" s="54">
         <v>579</v>
@@ -38753,7 +38839,7 @@
       </c>
       <c r="L651" s="18"/>
       <c r="M651" s="18"/>
-      <c r="N651" s="77" t="s">
+      <c r="N651" s="76" t="s">
         <v>2119</v>
       </c>
       <c r="O651" s="18"/>
@@ -38947,7 +39033,7 @@
       </c>
       <c r="L655" s="18"/>
       <c r="M655" s="18"/>
-      <c r="N655" s="77" t="s">
+      <c r="N655" s="76" t="s">
         <v>2120</v>
       </c>
       <c r="O655" s="18"/>
@@ -43908,10 +43994,12 @@
         <v>1177</v>
       </c>
       <c r="J760" s="18"/>
-      <c r="K760" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L760" s="18"/>
+      <c r="K760" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L760" s="53">
+        <v>46250</v>
+      </c>
       <c r="M760" s="18"/>
       <c r="N760" s="40"/>
       <c r="O760" s="18"/>
@@ -43950,10 +44038,12 @@
         <v>1177</v>
       </c>
       <c r="J761" s="18"/>
-      <c r="K761" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L761" s="18"/>
+      <c r="K761" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L761" s="53">
+        <v>46250</v>
+      </c>
       <c r="M761" s="18"/>
       <c r="N761" s="54">
         <v>77</v>
@@ -43994,10 +44084,12 @@
         <v>1177</v>
       </c>
       <c r="J762" s="18"/>
-      <c r="K762" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L762" s="18"/>
+      <c r="K762" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L762" s="53">
+        <v>46250</v>
+      </c>
       <c r="M762" s="18"/>
       <c r="N762" s="40"/>
       <c r="O762" s="18"/>
@@ -44036,10 +44128,12 @@
         <v>1177</v>
       </c>
       <c r="J763" s="18"/>
-      <c r="K763" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L763" s="18"/>
+      <c r="K763" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L763" s="53">
+        <v>46250</v>
+      </c>
       <c r="M763" s="18"/>
       <c r="N763" s="40"/>
       <c r="O763" s="18"/>
@@ -44078,10 +44172,12 @@
         <v>1177</v>
       </c>
       <c r="J764" s="18"/>
-      <c r="K764" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L764" s="18"/>
+      <c r="K764" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L764" s="53">
+        <v>46250</v>
+      </c>
       <c r="M764" s="18"/>
       <c r="N764" s="40"/>
       <c r="O764" s="18"/>
@@ -44120,10 +44216,12 @@
         <v>1177</v>
       </c>
       <c r="J765" s="18"/>
-      <c r="K765" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L765" s="18"/>
+      <c r="K765" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L765" s="53">
+        <v>46250</v>
+      </c>
       <c r="M765" s="18"/>
       <c r="N765" s="40"/>
       <c r="O765" s="18"/>
@@ -45181,7 +45279,7 @@
         <v>46249</v>
       </c>
       <c r="M787" s="18"/>
-      <c r="N787" s="77" t="s">
+      <c r="N787" s="76" t="s">
         <v>2122</v>
       </c>
       <c r="O787" s="18"/>
@@ -45514,10 +45612,12 @@
       <c r="J794" s="15" t="s">
         <v>1250</v>
       </c>
-      <c r="K794" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L794" s="18"/>
+      <c r="K794" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L794" s="53">
+        <v>46250</v>
+      </c>
       <c r="M794" s="18"/>
       <c r="N794" s="54">
         <v>357</v>
@@ -45562,10 +45662,12 @@
       <c r="J795" s="15" t="s">
         <v>1250</v>
       </c>
-      <c r="K795" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L795" s="18"/>
+      <c r="K795" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L795" s="53">
+        <v>46250</v>
+      </c>
       <c r="M795" s="18"/>
       <c r="N795" s="54">
         <v>325</v>
@@ -45606,10 +45708,12 @@
       <c r="J796" s="15" t="s">
         <v>1250</v>
       </c>
-      <c r="K796" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L796" s="18"/>
+      <c r="K796" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L796" s="53">
+        <v>46250</v>
+      </c>
       <c r="M796" s="18"/>
       <c r="N796" s="54">
         <v>359</v>
@@ -45652,10 +45756,12 @@
       <c r="J797" s="15" t="s">
         <v>1250</v>
       </c>
-      <c r="K797" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L797" s="18"/>
+      <c r="K797" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L797" s="53">
+        <v>46250</v>
+      </c>
       <c r="M797" s="18"/>
       <c r="N797" s="54">
         <v>306</v>
@@ -45698,10 +45804,12 @@
       <c r="J798" s="15" t="s">
         <v>1250</v>
       </c>
-      <c r="K798" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L798" s="18"/>
+      <c r="K798" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L798" s="53">
+        <v>46250</v>
+      </c>
       <c r="M798" s="18"/>
       <c r="N798" s="54">
         <v>330</v>
@@ -46138,10 +46246,12 @@
       <c r="J807" s="15" t="s">
         <v>1250</v>
       </c>
-      <c r="K807" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L807" s="18"/>
+      <c r="K807" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L807" s="53">
+        <v>46250</v>
+      </c>
       <c r="M807" s="18"/>
       <c r="N807" s="54">
         <v>329</v>
@@ -46184,10 +46294,12 @@
       <c r="J808" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="K808" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L808" s="18"/>
+      <c r="K808" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L808" s="53">
+        <v>46250</v>
+      </c>
       <c r="M808" s="18"/>
       <c r="N808" s="40"/>
       <c r="O808" s="53">
@@ -48469,7 +48581,7 @@
       </c>
       <c r="L857" s="18"/>
       <c r="M857" s="18"/>
-      <c r="N857" s="77" t="s">
+      <c r="N857" s="76" t="s">
         <v>2124</v>
       </c>
       <c r="O857" s="18"/>
@@ -48517,7 +48629,7 @@
       </c>
       <c r="L858" s="18"/>
       <c r="M858" s="18"/>
-      <c r="N858" s="77" t="s">
+      <c r="N858" s="76" t="s">
         <v>2125</v>
       </c>
       <c r="O858" s="18"/>
@@ -49614,10 +49726,12 @@
       <c r="J882" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="K882" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L882" s="18"/>
+      <c r="K882" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L882" s="53">
+        <v>46250</v>
+      </c>
       <c r="M882" s="18"/>
       <c r="N882" s="40"/>
       <c r="O882" s="18"/>
@@ -49660,10 +49774,12 @@
       <c r="J883" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="K883" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L883" s="18"/>
+      <c r="K883" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L883" s="53">
+        <v>46250</v>
+      </c>
       <c r="M883" s="18"/>
       <c r="N883" s="40"/>
       <c r="O883" s="18"/>
@@ -49706,10 +49822,12 @@
       <c r="J884" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="K884" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L884" s="18"/>
+      <c r="K884" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L884" s="53">
+        <v>46250</v>
+      </c>
       <c r="M884" s="18"/>
       <c r="N884" s="40"/>
       <c r="O884" s="18"/>
@@ -49752,10 +49870,12 @@
       <c r="J885" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="K885" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L885" s="18"/>
+      <c r="K885" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L885" s="53">
+        <v>46250</v>
+      </c>
       <c r="M885" s="18"/>
       <c r="N885" s="40"/>
       <c r="O885" s="18"/>
@@ -51314,8 +51434,8 @@
       <c r="J919" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K919" s="30" t="s">
-        <v>1596</v>
+      <c r="K919" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L919" s="18"/>
       <c r="M919" s="18"/>
@@ -51340,23 +51460,33 @@
       <c r="B920" s="10">
         <v>46243</v>
       </c>
-      <c r="C920" s="38"/>
-      <c r="D920" s="38"/>
-      <c r="E920" s="18"/>
+      <c r="C920" s="55" t="s">
+        <v>2223</v>
+      </c>
+      <c r="D920" s="55">
+        <v>111924926</v>
+      </c>
+      <c r="E920" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="F920" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G920" s="56">
         <v>5597</v>
       </c>
-      <c r="H920" s="18"/>
+      <c r="H920" s="15">
+        <v>2276</v>
+      </c>
       <c r="I920" s="22" t="s">
         <v>563</v>
       </c>
       <c r="J920" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K920" s="18"/>
+      <c r="K920" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L920" s="18"/>
       <c r="M920" s="18"/>
       <c r="N920" s="54">
@@ -51404,10 +51534,12 @@
       <c r="J921" s="15" t="s">
         <v>1028</v>
       </c>
-      <c r="K921" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L921" s="18"/>
+      <c r="K921" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L921" s="53">
+        <v>46250</v>
+      </c>
       <c r="M921" s="18"/>
       <c r="N921" s="40"/>
       <c r="O921" s="18"/>
@@ -51448,10 +51580,12 @@
       <c r="J922" s="15" t="s">
         <v>1028</v>
       </c>
-      <c r="K922" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L922" s="18"/>
+      <c r="K922" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L922" s="53">
+        <v>46250</v>
+      </c>
       <c r="M922" s="18"/>
       <c r="N922" s="40"/>
       <c r="O922" s="18"/>
@@ -51912,10 +52046,12 @@
       <c r="J932" s="15" t="s">
         <v>1271</v>
       </c>
-      <c r="K932" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L932" s="18"/>
+      <c r="K932" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L932" s="53">
+        <v>46250</v>
+      </c>
       <c r="M932" s="18"/>
       <c r="N932" s="54">
         <v>487</v>
@@ -58215,7 +58351,7 @@
       </c>
       <c r="L1065" s="18"/>
       <c r="M1065" s="18"/>
-      <c r="N1065" s="77" t="s">
+      <c r="N1065" s="76" t="s">
         <v>2130</v>
       </c>
       <c r="O1065" s="18"/>
@@ -58399,7 +58535,7 @@
       </c>
       <c r="L1069" s="18"/>
       <c r="M1069" s="18"/>
-      <c r="N1069" s="77" t="s">
+      <c r="N1069" s="76" t="s">
         <v>2131</v>
       </c>
       <c r="O1069" s="18"/>
@@ -64150,10 +64286,12 @@
       <c r="J1202" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="K1202" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1202" s="18"/>
+      <c r="K1202" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1202" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1202" s="18"/>
       <c r="N1202" s="40"/>
       <c r="O1202" s="18"/>
@@ -67792,10 +67930,12 @@
       <c r="J1282" s="15" t="s">
         <v>1058</v>
       </c>
-      <c r="K1282" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1282" s="18"/>
+      <c r="K1282" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1282" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1282" s="18"/>
       <c r="N1282" s="40"/>
       <c r="O1282" s="18"/>
@@ -69461,7 +69601,7 @@
       <c r="G1319" s="74">
         <v>8606</v>
       </c>
-      <c r="H1319" s="75">
+      <c r="H1319" s="66">
         <v>9540</v>
       </c>
       <c r="I1319" s="15" t="s">
@@ -69509,7 +69649,7 @@
       <c r="G1320" s="74">
         <v>1802</v>
       </c>
-      <c r="H1320" s="75">
+      <c r="H1320" s="66">
         <v>7412</v>
       </c>
       <c r="I1320" s="15" t="s">
@@ -69557,7 +69697,7 @@
       <c r="G1321" s="74">
         <v>83932</v>
       </c>
-      <c r="H1321" s="75">
+      <c r="H1321" s="66">
         <v>23434</v>
       </c>
       <c r="I1321" s="16" t="s">
@@ -69566,10 +69706,12 @@
       <c r="J1321" s="15" t="s">
         <v>1880</v>
       </c>
-      <c r="K1321" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1321" s="18"/>
+      <c r="K1321" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1321" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1321" s="18"/>
       <c r="N1321" s="54">
         <v>677</v>
@@ -69605,7 +69747,7 @@
       <c r="G1322" s="74">
         <v>28764</v>
       </c>
-      <c r="H1322" s="75">
+      <c r="H1322" s="66">
         <v>94819</v>
       </c>
       <c r="I1322" s="22" t="s">
@@ -69651,7 +69793,7 @@
       <c r="G1323" s="74">
         <v>2709</v>
       </c>
-      <c r="H1323" s="75" t="s">
+      <c r="H1323" s="66" t="s">
         <v>2017</v>
       </c>
       <c r="I1323" s="22" t="s">
@@ -69697,7 +69839,7 @@
       <c r="G1324" s="74">
         <v>33942</v>
       </c>
-      <c r="H1324" s="75">
+      <c r="H1324" s="66">
         <v>65018</v>
       </c>
       <c r="I1324" s="22" t="s">
@@ -69741,7 +69883,7 @@
       <c r="G1325" s="74">
         <v>39877</v>
       </c>
-      <c r="H1325" s="75">
+      <c r="H1325" s="66">
         <v>39267</v>
       </c>
       <c r="I1325" s="22" t="s">
@@ -69785,7 +69927,7 @@
       <c r="G1326" s="74">
         <v>9778</v>
       </c>
-      <c r="H1326" s="75">
+      <c r="H1326" s="66">
         <v>3878</v>
       </c>
       <c r="I1326" s="22" t="s">
@@ -69833,7 +69975,7 @@
       <c r="G1327" s="74">
         <v>679</v>
       </c>
-      <c r="H1327" s="75">
+      <c r="H1327" s="66">
         <v>8619</v>
       </c>
       <c r="I1327" s="22" t="s">
@@ -69877,7 +70019,7 @@
       <c r="G1328" s="74">
         <v>1451</v>
       </c>
-      <c r="H1328" s="75">
+      <c r="H1328" s="66">
         <v>4867</v>
       </c>
       <c r="I1328" s="22" t="s">
@@ -69921,7 +70063,7 @@
       <c r="G1329" s="74">
         <v>2481</v>
       </c>
-      <c r="H1329" s="75">
+      <c r="H1329" s="66">
         <v>296</v>
       </c>
       <c r="I1329" s="22" t="s">
@@ -69965,7 +70107,7 @@
       <c r="G1330" s="74">
         <v>2394</v>
       </c>
-      <c r="H1330" s="75">
+      <c r="H1330" s="66">
         <v>3469</v>
       </c>
       <c r="I1330" s="22" t="s">
@@ -70009,7 +70151,7 @@
       <c r="G1331" s="74">
         <v>4525</v>
       </c>
-      <c r="H1331" s="75" t="s">
+      <c r="H1331" s="66" t="s">
         <v>2028</v>
       </c>
       <c r="I1331" s="22" t="s">
@@ -70055,7 +70197,7 @@
       <c r="G1332" s="74">
         <v>9012</v>
       </c>
-      <c r="H1332" s="75">
+      <c r="H1332" s="66">
         <v>2924</v>
       </c>
       <c r="I1332" s="22" t="s">
@@ -70101,7 +70243,7 @@
       <c r="G1333" s="74">
         <v>22913</v>
       </c>
-      <c r="H1333" s="75">
+      <c r="H1333" s="66">
         <v>75303</v>
       </c>
       <c r="I1333" s="22" t="s">
@@ -70147,7 +70289,7 @@
       <c r="G1334" s="74">
         <v>2191</v>
       </c>
-      <c r="H1334" s="75">
+      <c r="H1334" s="66">
         <v>113</v>
       </c>
       <c r="I1334" s="22" t="s">
@@ -70191,7 +70333,7 @@
       <c r="G1335" s="74">
         <v>65429</v>
       </c>
-      <c r="H1335" s="75">
+      <c r="H1335" s="66">
         <v>15184</v>
       </c>
       <c r="I1335" s="22" t="s">
@@ -70237,7 +70379,7 @@
       <c r="G1336" s="74">
         <v>82948</v>
       </c>
-      <c r="H1336" s="75">
+      <c r="H1336" s="66">
         <v>67236</v>
       </c>
       <c r="I1336" s="22" t="s">
@@ -70281,7 +70423,7 @@
       <c r="G1337" s="74">
         <v>1376</v>
       </c>
-      <c r="H1337" s="75">
+      <c r="H1337" s="66">
         <v>6502</v>
       </c>
       <c r="I1337" s="22" t="s">
@@ -70325,7 +70467,7 @@
       <c r="G1338" s="74">
         <v>7494</v>
       </c>
-      <c r="H1338" s="75">
+      <c r="H1338" s="66">
         <v>9639</v>
       </c>
       <c r="I1338" s="22" t="s">
@@ -70373,7 +70515,7 @@
       <c r="G1339" s="74">
         <v>8507</v>
       </c>
-      <c r="H1339" s="75" t="s">
+      <c r="H1339" s="66" t="s">
         <v>2038</v>
       </c>
       <c r="I1339" s="22" t="s">
@@ -70421,7 +70563,7 @@
       <c r="G1340" s="74">
         <v>9551</v>
       </c>
-      <c r="H1340" s="75">
+      <c r="H1340" s="66">
         <v>9234</v>
       </c>
       <c r="I1340" s="22" t="s">
@@ -70469,7 +70611,7 @@
       <c r="G1341" s="74">
         <v>8899</v>
       </c>
-      <c r="H1341" s="75">
+      <c r="H1341" s="66">
         <v>2991</v>
       </c>
       <c r="I1341" s="22" t="s">
@@ -70517,7 +70659,7 @@
       <c r="G1342" s="74">
         <v>9595</v>
       </c>
-      <c r="H1342" s="75">
+      <c r="H1342" s="66">
         <v>1032</v>
       </c>
       <c r="I1342" s="22" t="s">
@@ -70565,7 +70707,7 @@
       <c r="G1343" s="74">
         <v>6013</v>
       </c>
-      <c r="H1343" s="75">
+      <c r="H1343" s="66">
         <v>1665</v>
       </c>
       <c r="I1343" s="22" t="s">
@@ -70609,7 +70751,7 @@
       <c r="G1344" s="74">
         <v>1655</v>
       </c>
-      <c r="H1344" s="75">
+      <c r="H1344" s="66">
         <v>7906</v>
       </c>
       <c r="I1344" s="22" t="s">
@@ -70653,7 +70795,7 @@
       <c r="G1345" s="74" t="s">
         <v>2043</v>
       </c>
-      <c r="H1345" s="75">
+      <c r="H1345" s="66">
         <v>1294</v>
       </c>
       <c r="I1345" s="22" t="s">
@@ -70697,7 +70839,7 @@
       <c r="G1346" s="74">
         <v>3001</v>
       </c>
-      <c r="H1346" s="75">
+      <c r="H1346" s="66">
         <v>5372</v>
       </c>
       <c r="I1346" s="22" t="s">
@@ -70741,7 +70883,7 @@
       <c r="G1347" s="74">
         <v>856</v>
       </c>
-      <c r="H1347" s="75">
+      <c r="H1347" s="66">
         <v>9488</v>
       </c>
       <c r="I1347" s="22" t="s">
@@ -70785,7 +70927,7 @@
       <c r="G1348" s="74">
         <v>7046</v>
       </c>
-      <c r="H1348" s="75" t="s">
+      <c r="H1348" s="66" t="s">
         <v>2045</v>
       </c>
       <c r="I1348" s="22" t="s">
@@ -70831,7 +70973,7 @@
       <c r="G1349" s="74">
         <v>3135</v>
       </c>
-      <c r="H1349" s="75">
+      <c r="H1349" s="66">
         <v>1014</v>
       </c>
       <c r="I1349" s="22" t="s">
@@ -70879,7 +71021,7 @@
       <c r="G1350" s="74">
         <v>8801</v>
       </c>
-      <c r="H1350" s="75">
+      <c r="H1350" s="66">
         <v>1222</v>
       </c>
       <c r="I1350" s="22" t="s">
@@ -70925,7 +71067,7 @@
       <c r="G1351" s="74">
         <v>71197</v>
       </c>
-      <c r="H1351" s="75">
+      <c r="H1351" s="66">
         <v>40098</v>
       </c>
       <c r="I1351" s="22" t="s">
@@ -70971,7 +71113,7 @@
       <c r="G1352" s="74">
         <v>51982</v>
       </c>
-      <c r="H1352" s="75">
+      <c r="H1352" s="66">
         <v>19100</v>
       </c>
       <c r="I1352" s="22" t="s">
@@ -71017,7 +71159,7 @@
       <c r="G1353" s="74">
         <v>9461</v>
       </c>
-      <c r="H1353" s="75">
+      <c r="H1353" s="66">
         <v>2680</v>
       </c>
       <c r="I1353" s="22" t="s">
@@ -71063,7 +71205,7 @@
       <c r="G1354" s="74">
         <v>6605</v>
       </c>
-      <c r="H1354" s="75" t="s">
+      <c r="H1354" s="66" t="s">
         <v>2053</v>
       </c>
       <c r="I1354" s="22" t="s">
@@ -71149,7 +71291,7 @@
       <c r="G1356" s="74">
         <v>8835</v>
       </c>
-      <c r="H1356" s="75">
+      <c r="H1356" s="66">
         <v>1886</v>
       </c>
       <c r="I1356" s="22" t="s">
@@ -71193,7 +71335,7 @@
       <c r="G1357" s="74">
         <v>7398</v>
       </c>
-      <c r="H1357" s="75">
+      <c r="H1357" s="66">
         <v>8171</v>
       </c>
       <c r="I1357" s="22" t="s">
@@ -71237,7 +71379,7 @@
       <c r="G1358" s="74">
         <v>4090</v>
       </c>
-      <c r="H1358" s="75">
+      <c r="H1358" s="66">
         <v>9687</v>
       </c>
       <c r="I1358" s="22" t="s">
@@ -71281,7 +71423,7 @@
       <c r="G1359" s="74">
         <v>3686</v>
       </c>
-      <c r="H1359" s="75">
+      <c r="H1359" s="66">
         <v>2699</v>
       </c>
       <c r="I1359" s="22" t="s">
@@ -71325,7 +71467,7 @@
       <c r="G1360" s="74">
         <v>4123</v>
       </c>
-      <c r="H1360" s="75">
+      <c r="H1360" s="66">
         <v>6467</v>
       </c>
       <c r="I1360" s="22" t="s">
@@ -71369,7 +71511,7 @@
       <c r="G1361" s="74">
         <v>9497</v>
       </c>
-      <c r="H1361" s="75">
+      <c r="H1361" s="66">
         <v>4915</v>
       </c>
       <c r="I1361" s="22" t="s">
@@ -71413,7 +71555,7 @@
       <c r="G1362" s="74">
         <v>1179</v>
       </c>
-      <c r="H1362" s="75">
+      <c r="H1362" s="66">
         <v>3359</v>
       </c>
       <c r="I1362" s="22" t="s">
@@ -71457,7 +71599,7 @@
       <c r="G1363" s="74">
         <v>3024</v>
       </c>
-      <c r="H1363" s="75">
+      <c r="H1363" s="66">
         <v>372</v>
       </c>
       <c r="I1363" s="22" t="s">
@@ -71501,7 +71643,7 @@
       <c r="G1364" s="74">
         <v>22255</v>
       </c>
-      <c r="H1364" s="75">
+      <c r="H1364" s="66">
         <v>94480</v>
       </c>
       <c r="I1364" s="22" t="s">
@@ -71545,7 +71687,7 @@
       <c r="G1365" s="74">
         <v>67381</v>
       </c>
-      <c r="H1365" s="75">
+      <c r="H1365" s="66">
         <v>33916</v>
       </c>
       <c r="I1365" s="22" t="s">
@@ -71635,7 +71777,7 @@
       <c r="G1367" s="74">
         <v>70270</v>
       </c>
-      <c r="H1367" s="75">
+      <c r="H1367" s="66">
         <v>73889</v>
       </c>
       <c r="I1367" s="22" t="s">
@@ -71679,7 +71821,7 @@
       <c r="G1368" s="74">
         <v>5474</v>
       </c>
-      <c r="H1368" s="75">
+      <c r="H1368" s="66">
         <v>848</v>
       </c>
       <c r="I1368" s="22" t="s">
@@ -71723,7 +71865,7 @@
       <c r="G1369" s="74">
         <v>6331</v>
       </c>
-      <c r="H1369" s="75">
+      <c r="H1369" s="66">
         <v>1144</v>
       </c>
       <c r="I1369" s="22" t="s">
@@ -71767,7 +71909,7 @@
       <c r="G1370" s="74">
         <v>4686</v>
       </c>
-      <c r="H1370" s="75">
+      <c r="H1370" s="66">
         <v>4228</v>
       </c>
       <c r="I1370" s="22" t="s">
@@ -71811,7 +71953,7 @@
       <c r="G1371" s="74">
         <v>2262</v>
       </c>
-      <c r="H1371" s="75">
+      <c r="H1371" s="66">
         <v>2488</v>
       </c>
       <c r="I1371" s="22" t="s">
@@ -71855,7 +71997,7 @@
       <c r="G1372" s="74">
         <v>653</v>
       </c>
-      <c r="H1372" s="75">
+      <c r="H1372" s="66">
         <v>4834</v>
       </c>
       <c r="I1372" s="22" t="s">
@@ -71899,7 +72041,7 @@
       <c r="G1373" s="74">
         <v>3384</v>
       </c>
-      <c r="H1373" s="75">
+      <c r="H1373" s="66">
         <v>4674</v>
       </c>
       <c r="I1373" s="22" t="s">
@@ -71943,7 +72085,7 @@
       <c r="G1374" s="74">
         <v>7898</v>
       </c>
-      <c r="H1374" s="75">
+      <c r="H1374" s="66">
         <v>7496</v>
       </c>
       <c r="I1374" s="22" t="s">
@@ -71987,7 +72129,7 @@
       <c r="G1375" s="74">
         <v>2874</v>
       </c>
-      <c r="H1375" s="75">
+      <c r="H1375" s="66">
         <v>6798</v>
       </c>
       <c r="I1375" s="22" t="s">
@@ -72031,7 +72173,7 @@
       <c r="G1376" s="74">
         <v>41903</v>
       </c>
-      <c r="H1376" s="75">
+      <c r="H1376" s="66">
         <v>15077</v>
       </c>
       <c r="I1376" s="22" t="s">
@@ -72077,7 +72219,7 @@
       <c r="G1377" s="74">
         <v>27739</v>
       </c>
-      <c r="H1377" s="75">
+      <c r="H1377" s="66">
         <v>15360</v>
       </c>
       <c r="I1377" s="22" t="s">
@@ -72121,7 +72263,7 @@
       <c r="G1378" s="74">
         <v>42905</v>
       </c>
-      <c r="H1378" s="75">
+      <c r="H1378" s="66">
         <v>38038</v>
       </c>
       <c r="I1378" s="22" t="s">
@@ -72207,7 +72349,7 @@
       <c r="G1380" s="74">
         <v>2395</v>
       </c>
-      <c r="H1380" s="75">
+      <c r="H1380" s="66">
         <v>3699</v>
       </c>
       <c r="I1380" s="22" t="s">
@@ -72251,7 +72393,7 @@
       <c r="G1381" s="74">
         <v>7638</v>
       </c>
-      <c r="H1381" s="75">
+      <c r="H1381" s="66">
         <v>1996</v>
       </c>
       <c r="I1381" s="22" t="s">
@@ -72295,7 +72437,7 @@
       <c r="G1382" s="74">
         <v>77612</v>
       </c>
-      <c r="H1382" s="75">
+      <c r="H1382" s="66">
         <v>58160</v>
       </c>
       <c r="I1382" s="22" t="s">
@@ -72339,7 +72481,7 @@
       <c r="G1383" s="74">
         <v>28250</v>
       </c>
-      <c r="H1383" s="75">
+      <c r="H1383" s="66">
         <v>96002</v>
       </c>
       <c r="I1383" s="22" t="s">
@@ -72383,7 +72525,7 @@
       <c r="G1384" s="74">
         <v>6426</v>
       </c>
-      <c r="H1384" s="75" t="s">
+      <c r="H1384" s="66" t="s">
         <v>2088</v>
       </c>
       <c r="I1384" s="22" t="s">
@@ -72427,7 +72569,7 @@
       <c r="G1385" s="74">
         <v>1682</v>
       </c>
-      <c r="H1385" s="75">
+      <c r="H1385" s="66">
         <v>5917</v>
       </c>
       <c r="I1385" s="22" t="s">
@@ -72475,7 +72617,7 @@
       <c r="G1386" s="74">
         <v>2861</v>
       </c>
-      <c r="H1386" s="75">
+      <c r="H1386" s="66">
         <v>2723</v>
       </c>
       <c r="I1386" s="22" t="s">
@@ -72523,7 +72665,7 @@
       <c r="G1387" s="74">
         <v>4204</v>
       </c>
-      <c r="H1387" s="75">
+      <c r="H1387" s="66">
         <v>4535</v>
       </c>
       <c r="I1387" s="22" t="s">
@@ -72569,7 +72711,7 @@
       <c r="G1388" s="74">
         <v>2797</v>
       </c>
-      <c r="H1388" s="75">
+      <c r="H1388" s="66">
         <v>1411</v>
       </c>
       <c r="I1388" s="16" t="s">
@@ -72617,7 +72759,7 @@
       <c r="G1389" s="74">
         <v>2692</v>
       </c>
-      <c r="H1389" s="75">
+      <c r="H1389" s="66">
         <v>3821</v>
       </c>
       <c r="I1389" s="16" t="s">
@@ -72665,7 +72807,7 @@
       <c r="G1390" s="74">
         <v>30974</v>
       </c>
-      <c r="H1390" s="75">
+      <c r="H1390" s="66">
         <v>38362</v>
       </c>
       <c r="I1390" s="16" t="s">
@@ -72713,7 +72855,7 @@
       <c r="G1391" s="74">
         <v>9560</v>
       </c>
-      <c r="H1391" s="75">
+      <c r="H1391" s="66">
         <v>1713</v>
       </c>
       <c r="I1391" s="15" t="s">
@@ -72759,7 +72901,7 @@
       <c r="G1392" s="74">
         <v>1957</v>
       </c>
-      <c r="H1392" s="75">
+      <c r="H1392" s="66">
         <v>5293</v>
       </c>
       <c r="I1392" s="15" t="s">
@@ -72805,7 +72947,7 @@
       <c r="G1393" s="74">
         <v>5769</v>
       </c>
-      <c r="H1393" s="75">
+      <c r="H1393" s="66">
         <v>3254</v>
       </c>
       <c r="I1393" s="16" t="s">
@@ -73017,7 +73159,7 @@
       <c r="G1398" s="74">
         <v>9314</v>
       </c>
-      <c r="H1398" s="75">
+      <c r="H1398" s="66">
         <v>5845</v>
       </c>
       <c r="I1398" s="16" t="s">
@@ -73061,7 +73203,7 @@
       <c r="G1399" s="74">
         <v>6222</v>
       </c>
-      <c r="H1399" s="75">
+      <c r="H1399" s="66">
         <v>4607</v>
       </c>
       <c r="I1399" s="15" t="s">
@@ -73109,7 +73251,7 @@
       <c r="G1400" s="74">
         <v>2419</v>
       </c>
-      <c r="H1400" s="75">
+      <c r="H1400" s="66">
         <v>2865</v>
       </c>
       <c r="I1400" s="15" t="s">
@@ -73155,7 +73297,7 @@
       <c r="G1401" s="74">
         <v>8524</v>
       </c>
-      <c r="H1401" s="75">
+      <c r="H1401" s="66">
         <v>5352</v>
       </c>
       <c r="I1401" s="15" t="s">
@@ -73201,7 +73343,7 @@
       <c r="G1402" s="74">
         <v>69693</v>
       </c>
-      <c r="H1402" s="75">
+      <c r="H1402" s="66">
         <v>7021</v>
       </c>
       <c r="I1402" s="15" t="s">
@@ -73247,7 +73389,7 @@
       <c r="G1403" s="74">
         <v>34507</v>
       </c>
-      <c r="H1403" s="75">
+      <c r="H1403" s="66">
         <v>14858</v>
       </c>
       <c r="I1403" s="15" t="s">
@@ -73293,7 +73435,7 @@
       <c r="G1404" s="74">
         <v>9686</v>
       </c>
-      <c r="H1404" s="75">
+      <c r="H1404" s="66">
         <v>4665</v>
       </c>
       <c r="I1404" s="15" t="s">
@@ -73339,7 +73481,7 @@
       <c r="G1405" s="74" t="s">
         <v>2108</v>
       </c>
-      <c r="H1405" s="75">
+      <c r="H1405" s="66">
         <v>5264</v>
       </c>
       <c r="I1405" s="15" t="s">
@@ -73383,7 +73525,7 @@
       <c r="G1406" s="74">
         <v>5240</v>
       </c>
-      <c r="H1406" s="75">
+      <c r="H1406" s="66">
         <v>6053</v>
       </c>
       <c r="I1406" s="15" t="s">
@@ -73427,7 +73569,7 @@
       <c r="G1407" s="74">
         <v>15555</v>
       </c>
-      <c r="H1407" s="75">
+      <c r="H1407" s="66">
         <v>87032</v>
       </c>
       <c r="I1407" s="16" t="s">
@@ -73475,7 +73617,7 @@
       <c r="G1408" s="74">
         <v>35724</v>
       </c>
-      <c r="H1408" s="75">
+      <c r="H1408" s="66">
         <v>68761</v>
       </c>
       <c r="I1408" s="16" t="s">
@@ -73523,7 +73665,7 @@
       <c r="G1409" s="74">
         <v>63226</v>
       </c>
-      <c r="H1409" s="75">
+      <c r="H1409" s="66">
         <v>29656</v>
       </c>
       <c r="I1409" s="16" t="s">
@@ -73571,7 +73713,7 @@
       <c r="G1410" s="74">
         <v>2965</v>
       </c>
-      <c r="H1410" s="75">
+      <c r="H1410" s="66">
         <v>1098</v>
       </c>
       <c r="I1410" s="16" t="s">
@@ -73617,7 +73759,7 @@
       <c r="G1411" s="74">
         <v>1353</v>
       </c>
-      <c r="H1411" s="75">
+      <c r="H1411" s="66">
         <v>1962</v>
       </c>
       <c r="I1411" s="15" t="s">
@@ -73663,7 +73805,7 @@
       <c r="G1412" s="74">
         <v>5264</v>
       </c>
-      <c r="H1412" s="75">
+      <c r="H1412" s="66">
         <v>2307</v>
       </c>
       <c r="I1412" s="16" t="s">
@@ -73707,7 +73849,7 @@
       <c r="G1413" s="74">
         <v>83840</v>
       </c>
-      <c r="H1413" s="75">
+      <c r="H1413" s="66">
         <v>99047</v>
       </c>
       <c r="I1413" s="22" t="s">
@@ -73755,7 +73897,7 @@
       <c r="G1414" s="74">
         <v>2972</v>
       </c>
-      <c r="H1414" s="75">
+      <c r="H1414" s="66">
         <v>5857</v>
       </c>
       <c r="I1414" s="15" t="s">
@@ -73803,7 +73945,7 @@
       <c r="G1415" s="74">
         <v>7561</v>
       </c>
-      <c r="H1415" s="75">
+      <c r="H1415" s="66">
         <v>7805</v>
       </c>
       <c r="I1415" s="15" t="s">
@@ -73847,7 +73989,7 @@
       <c r="G1416" s="74">
         <v>281</v>
       </c>
-      <c r="H1416" s="75">
+      <c r="H1416" s="66">
         <v>8429</v>
       </c>
       <c r="I1416" s="15" t="s">
@@ -73891,7 +74033,7 @@
       <c r="G1417" s="74">
         <v>2806</v>
       </c>
-      <c r="H1417" s="75">
+      <c r="H1417" s="66">
         <v>4054</v>
       </c>
       <c r="I1417" s="15" t="s">
@@ -73935,7 +74077,7 @@
       <c r="G1418" s="74">
         <v>67739</v>
       </c>
-      <c r="H1418" s="75">
+      <c r="H1418" s="66">
         <v>24668</v>
       </c>
       <c r="I1418" s="15" t="s">
@@ -73981,7 +74123,7 @@
       <c r="G1419" s="74">
         <v>31989</v>
       </c>
-      <c r="H1419" s="75">
+      <c r="H1419" s="66">
         <v>60425</v>
       </c>
       <c r="I1419" s="15" t="s">
@@ -74027,7 +74169,7 @@
       <c r="G1420" s="74">
         <v>36294</v>
       </c>
-      <c r="H1420" s="75">
+      <c r="H1420" s="66">
         <v>62386</v>
       </c>
       <c r="I1420" s="15" t="s">
@@ -74073,7 +74215,7 @@
       <c r="G1421" s="74">
         <v>60394</v>
       </c>
-      <c r="H1421" s="75">
+      <c r="H1421" s="66">
         <v>35609</v>
       </c>
       <c r="I1421" s="15" t="s">
@@ -74119,7 +74261,7 @@
       <c r="G1422" s="74">
         <v>52161</v>
       </c>
-      <c r="H1422" s="75">
+      <c r="H1422" s="66">
         <v>47033</v>
       </c>
       <c r="I1422" s="15" t="s">
@@ -74165,7 +74307,7 @@
       <c r="G1423" s="74">
         <v>14608</v>
       </c>
-      <c r="H1423" s="75">
+      <c r="H1423" s="66">
         <v>94390</v>
       </c>
       <c r="I1423" s="15" t="s">
@@ -74211,7 +74353,7 @@
       <c r="G1424" s="74">
         <v>53695</v>
       </c>
-      <c r="H1424" s="75">
+      <c r="H1424" s="66">
         <v>47102</v>
       </c>
       <c r="I1424" s="15" t="s">
@@ -74301,7 +74443,7 @@
       <c r="G1426" s="74">
         <v>32453</v>
       </c>
-      <c r="H1426" s="75">
+      <c r="H1426" s="66">
         <v>20937</v>
       </c>
       <c r="I1426" s="15" t="s">
@@ -74347,7 +74489,7 @@
       <c r="G1427" s="74">
         <v>53735</v>
       </c>
-      <c r="H1427" s="75">
+      <c r="H1427" s="66">
         <v>19933</v>
       </c>
       <c r="I1427" s="15" t="s">
@@ -74393,7 +74535,7 @@
       <c r="G1428" s="74">
         <v>45256</v>
       </c>
-      <c r="H1428" s="75">
+      <c r="H1428" s="66">
         <v>85118</v>
       </c>
       <c r="I1428" s="15" t="s">
@@ -74483,7 +74625,7 @@
       <c r="G1430" s="74">
         <v>37577</v>
       </c>
-      <c r="H1430" s="75">
+      <c r="H1430" s="66">
         <v>23001</v>
       </c>
       <c r="I1430" s="15" t="s">
@@ -74569,7 +74711,7 @@
       <c r="G1432" s="74">
         <v>22601</v>
       </c>
-      <c r="H1432" s="75">
+      <c r="H1432" s="66">
         <v>49396</v>
       </c>
       <c r="I1432" s="15" t="s">
@@ -74611,7 +74753,7 @@
       <c r="G1433" s="74">
         <v>10328</v>
       </c>
-      <c r="H1433" s="75">
+      <c r="H1433" s="66">
         <v>76310</v>
       </c>
       <c r="I1433" s="15" t="s">
@@ -74653,7 +74795,7 @@
       <c r="G1434" s="74">
         <v>99081</v>
       </c>
-      <c r="H1434" s="75">
+      <c r="H1434" s="66">
         <v>85770</v>
       </c>
       <c r="I1434" s="15" t="s">
@@ -74695,7 +74837,7 @@
       <c r="G1435" s="74">
         <v>53818</v>
       </c>
-      <c r="H1435" s="75">
+      <c r="H1435" s="66">
         <v>74162</v>
       </c>
       <c r="I1435" s="15" t="s">
@@ -74737,7 +74879,7 @@
       <c r="G1436" s="74">
         <v>39679</v>
       </c>
-      <c r="H1436" s="75">
+      <c r="H1436" s="66">
         <v>90188</v>
       </c>
       <c r="I1436" s="15" t="s">
@@ -74779,7 +74921,7 @@
       <c r="G1437" s="74">
         <v>10686</v>
       </c>
-      <c r="H1437" s="75">
+      <c r="H1437" s="66">
         <v>52299</v>
       </c>
       <c r="I1437" s="15" t="s">
@@ -74861,7 +75003,7 @@
       <c r="G1439" s="74">
         <v>35870</v>
       </c>
-      <c r="H1439" s="75">
+      <c r="H1439" s="66">
         <v>52185</v>
       </c>
       <c r="I1439" s="15" t="s">
@@ -74943,7 +75085,7 @@
       <c r="G1441" s="74">
         <v>9390</v>
       </c>
-      <c r="H1441" s="75">
+      <c r="H1441" s="66">
         <v>4320</v>
       </c>
       <c r="I1441" s="15" t="s">
@@ -74989,7 +75131,7 @@
       <c r="G1442" s="74">
         <v>7264</v>
       </c>
-      <c r="H1442" s="75">
+      <c r="H1442" s="66">
         <v>7946</v>
       </c>
       <c r="I1442" s="48" t="s">
@@ -75031,7 +75173,7 @@
       <c r="G1443" s="74">
         <v>7380</v>
       </c>
-      <c r="H1443" s="75">
+      <c r="H1443" s="66">
         <v>-999</v>
       </c>
       <c r="I1443" s="16" t="s">
@@ -75075,7 +75217,7 @@
       <c r="G1444" s="74">
         <v>50</v>
       </c>
-      <c r="H1444" s="75">
+      <c r="H1444" s="66">
         <v>2081</v>
       </c>
       <c r="I1444" s="16" t="s">
@@ -75119,7 +75261,7 @@
       <c r="G1445" s="74">
         <v>48738</v>
       </c>
-      <c r="H1445" s="75">
+      <c r="H1445" s="66">
         <v>37765</v>
       </c>
       <c r="I1445" s="48" t="s">
@@ -75163,7 +75305,7 @@
       <c r="G1446" s="74">
         <v>2661</v>
       </c>
-      <c r="H1446" s="75">
+      <c r="H1446" s="66">
         <v>8366</v>
       </c>
       <c r="I1446" s="16" t="s">
@@ -75209,7 +75351,7 @@
       <c r="G1447" s="74">
         <v>9393</v>
       </c>
-      <c r="H1447" s="75">
+      <c r="H1447" s="66">
         <v>-4320</v>
       </c>
       <c r="I1447" s="16" t="s">
@@ -75253,7 +75395,7 @@
       <c r="G1448" s="74">
         <v>7397</v>
       </c>
-      <c r="H1448" s="75">
+      <c r="H1448" s="66">
         <v>9165</v>
       </c>
       <c r="I1448" s="16" t="s">
@@ -75297,7 +75439,7 @@
       <c r="G1449" s="74">
         <v>9420</v>
       </c>
-      <c r="H1449" s="75">
+      <c r="H1449" s="66">
         <v>8585</v>
       </c>
       <c r="I1449" s="16" t="s">
@@ -75341,7 +75483,7 @@
       <c r="G1450" s="74">
         <v>7644</v>
       </c>
-      <c r="H1450" s="75">
+      <c r="H1450" s="66">
         <v>1748</v>
       </c>
       <c r="I1450" s="16" t="s">
@@ -75385,7 +75527,7 @@
       <c r="G1451" s="74">
         <v>5726</v>
       </c>
-      <c r="H1451" s="75">
+      <c r="H1451" s="66">
         <v>-8287</v>
       </c>
       <c r="I1451" s="16" t="s">
@@ -75433,7 +75575,7 @@
       <c r="G1452" s="74">
         <v>6153</v>
       </c>
-      <c r="H1452" s="78">
+      <c r="H1452" s="72">
         <v>5169</v>
       </c>
       <c r="I1452" s="26" t="s">
@@ -75481,7 +75623,7 @@
       <c r="G1453" s="74">
         <v>1447</v>
       </c>
-      <c r="H1453" s="75">
+      <c r="H1453" s="66">
         <v>3025</v>
       </c>
       <c r="I1453" s="16" t="s">
@@ -75529,7 +75671,7 @@
       <c r="G1454" s="74">
         <v>82098</v>
       </c>
-      <c r="H1454" s="75">
+      <c r="H1454" s="66">
         <v>70636</v>
       </c>
       <c r="I1454" s="22" t="s">
@@ -75573,7 +75715,7 @@
       <c r="G1455" s="74">
         <v>39305</v>
       </c>
-      <c r="H1455" s="75">
+      <c r="H1455" s="66">
         <v>94368</v>
       </c>
       <c r="I1455" s="15" t="s">
@@ -75619,7 +75761,7 @@
       <c r="G1456" s="74" t="s">
         <v>2199</v>
       </c>
-      <c r="H1456" s="75">
+      <c r="H1456" s="66">
         <v>697</v>
       </c>
       <c r="I1456" s="15" t="s">
@@ -75665,7 +75807,7 @@
       <c r="G1457" s="74">
         <v>9480</v>
       </c>
-      <c r="H1457" s="75">
+      <c r="H1457" s="66">
         <v>6466</v>
       </c>
       <c r="I1457" s="15" t="s">
@@ -75711,7 +75853,7 @@
       <c r="G1458" s="74">
         <v>4901</v>
       </c>
-      <c r="H1458" s="75">
+      <c r="H1458" s="66">
         <v>2258</v>
       </c>
       <c r="I1458" s="15" t="s">
@@ -75755,7 +75897,7 @@
       <c r="G1459" s="74">
         <v>1565</v>
       </c>
-      <c r="H1459" s="75">
+      <c r="H1459" s="66">
         <v>4865</v>
       </c>
       <c r="I1459" s="15" t="s">
@@ -75799,7 +75941,7 @@
       <c r="G1460" s="74">
         <v>3386</v>
       </c>
-      <c r="H1460" s="75">
+      <c r="H1460" s="66">
         <v>1896</v>
       </c>
       <c r="I1460" s="22" t="s">
@@ -75843,7 +75985,7 @@
       <c r="G1461" s="74">
         <v>9429</v>
       </c>
-      <c r="H1461" s="75">
+      <c r="H1461" s="66">
         <v>5615</v>
       </c>
       <c r="I1461" s="15" t="s">
@@ -75887,7 +76029,7 @@
       <c r="G1462" s="74">
         <v>7327</v>
       </c>
-      <c r="H1462" s="75">
+      <c r="H1462" s="66">
         <v>6326</v>
       </c>
       <c r="I1462" s="22" t="s">
@@ -75971,7 +76113,7 @@
       <c r="G1464" s="74">
         <v>6289</v>
       </c>
-      <c r="H1464" s="75">
+      <c r="H1464" s="66">
         <v>8289</v>
       </c>
       <c r="I1464" s="16" t="s">
@@ -76015,7 +76157,7 @@
       <c r="G1465" s="74">
         <v>8146</v>
       </c>
-      <c r="H1465" s="75">
+      <c r="H1465" s="66">
         <v>7980</v>
       </c>
       <c r="I1465" s="15" t="s">
@@ -76061,7 +76203,7 @@
       <c r="G1466" s="74">
         <v>57994</v>
       </c>
-      <c r="H1466" s="75" t="s">
+      <c r="H1466" s="66" t="s">
         <v>2211</v>
       </c>
       <c r="I1466" s="22" t="s">
@@ -76105,7 +76247,7 @@
       <c r="G1467" s="74">
         <v>58269</v>
       </c>
-      <c r="H1467" s="75">
+      <c r="H1467" s="66">
         <v>35158</v>
       </c>
       <c r="I1467" s="22" t="s">
@@ -76149,7 +76291,7 @@
       <c r="G1468" s="74">
         <v>3372</v>
       </c>
-      <c r="H1468" s="75">
+      <c r="H1468" s="66">
         <v>-3639</v>
       </c>
       <c r="I1468" s="16" t="s">
@@ -76195,7 +76337,7 @@
       <c r="G1469" s="74">
         <v>4936</v>
       </c>
-      <c r="H1469" s="75">
+      <c r="H1469" s="66">
         <v>1603</v>
       </c>
       <c r="I1469" s="16" t="s">
@@ -76241,7 +76383,7 @@
       <c r="G1470" s="74">
         <v>6376</v>
       </c>
-      <c r="H1470" s="75">
+      <c r="H1470" s="66">
         <v>-1603</v>
       </c>
       <c r="I1470" s="16" t="s">
@@ -76287,7 +76429,7 @@
       <c r="G1471" s="74">
         <v>56437</v>
       </c>
-      <c r="H1471" s="75">
+      <c r="H1471" s="66">
         <v>38484</v>
       </c>
       <c r="I1471" s="16" t="s">
@@ -76333,7 +76475,7 @@
       <c r="G1472" s="74">
         <v>8212</v>
       </c>
-      <c r="H1472" s="75">
+      <c r="H1472" s="66">
         <v>1005</v>
       </c>
       <c r="I1472" s="15" t="s">
@@ -76377,7 +76519,7 @@
       <c r="G1473" s="74">
         <v>87930</v>
       </c>
-      <c r="H1473" s="75">
+      <c r="H1473" s="66">
         <v>54759</v>
       </c>
       <c r="I1473" s="15" t="s">
@@ -76421,7 +76563,7 @@
       <c r="G1474" s="74">
         <v>6080</v>
       </c>
-      <c r="H1474" s="75">
+      <c r="H1474" s="66">
         <v>8219</v>
       </c>
       <c r="I1474" s="16" t="s">
@@ -76465,7 +76607,7 @@
       <c r="G1475" s="74">
         <v>9742</v>
       </c>
-      <c r="H1475" s="75">
+      <c r="H1475" s="66">
         <v>1793</v>
       </c>
       <c r="I1475" s="16" t="s">
@@ -76509,7 +76651,7 @@
       <c r="G1476" s="74">
         <v>5238</v>
       </c>
-      <c r="H1476" s="75">
+      <c r="H1476" s="66">
         <v>458</v>
       </c>
       <c r="I1476" s="16" t="s">
@@ -76553,7 +76695,7 @@
       <c r="G1477" s="74">
         <v>255</v>
       </c>
-      <c r="H1477" s="75">
+      <c r="H1477" s="66">
         <v>4081</v>
       </c>
       <c r="I1477" s="16" t="s">
@@ -76597,7 +76739,7 @@
       <c r="G1478" s="74">
         <v>1164</v>
       </c>
-      <c r="H1478" s="75">
+      <c r="H1478" s="66">
         <v>4807</v>
       </c>
       <c r="I1478" s="16" t="s">
@@ -76641,7 +76783,7 @@
       <c r="G1479" s="74">
         <v>5865</v>
       </c>
-      <c r="H1479" s="75">
+      <c r="H1479" s="66">
         <v>1817</v>
       </c>
       <c r="I1479" s="22" t="s">
@@ -76687,7 +76829,7 @@
       <c r="G1480" s="74">
         <v>3859</v>
       </c>
-      <c r="H1480" s="75">
+      <c r="H1480" s="66">
         <v>4713</v>
       </c>
       <c r="I1480" s="16" t="s">
@@ -76731,7 +76873,7 @@
       <c r="G1481" s="74">
         <v>7873</v>
       </c>
-      <c r="H1481" s="75">
+      <c r="H1481" s="66">
         <v>1336</v>
       </c>
       <c r="I1481" s="16" t="s">
@@ -76775,7 +76917,7 @@
       <c r="G1482" s="74">
         <v>8366</v>
       </c>
-      <c r="H1482" s="75">
+      <c r="H1482" s="66">
         <v>2661</v>
       </c>
       <c r="I1482" s="16" t="s">
@@ -76804,30 +76946,38 @@
       <c r="B1483" s="10">
         <v>46245</v>
       </c>
-      <c r="C1483" s="81"/>
-      <c r="D1483" s="81"/>
-      <c r="E1483" s="80"/>
-      <c r="F1483" s="80"/>
-      <c r="G1483" s="82">
-        <v>9392</v>
-      </c>
-      <c r="H1483" s="81"/>
-      <c r="I1483" s="83" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1483" s="84" t="s">
+      <c r="C1483" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1483" s="55">
+        <v>131316993</v>
+      </c>
+      <c r="E1483" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1483" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1483" s="74">
+        <v>2046</v>
+      </c>
+      <c r="H1483" s="38"/>
+      <c r="I1483" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1483" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1483" s="85" t="s">
+      <c r="K1483" s="60" t="s">
         <v>1189</v>
       </c>
-      <c r="L1483" s="80"/>
-      <c r="M1483" s="80"/>
-      <c r="N1483" s="86"/>
-      <c r="O1483" s="80"/>
-      <c r="P1483" s="80"/>
-      <c r="Q1483" s="80"/>
-      <c r="R1483" s="87" t="s">
+      <c r="L1483" s="18"/>
+      <c r="M1483" s="18"/>
+      <c r="N1483" s="40"/>
+      <c r="O1483" s="18"/>
+      <c r="P1483" s="18"/>
+      <c r="Q1483" s="18"/>
+      <c r="R1483" s="22" t="s">
         <v>131</v>
       </c>
     </row>
@@ -76838,12 +76988,20 @@
       <c r="B1484" s="10">
         <v>46245</v>
       </c>
-      <c r="C1484" s="38"/>
-      <c r="D1484" s="38"/>
-      <c r="E1484" s="18"/>
-      <c r="F1484" s="18"/>
+      <c r="C1484" s="55" t="s">
+        <v>2224</v>
+      </c>
+      <c r="D1484" s="55">
+        <v>111323605</v>
+      </c>
+      <c r="E1484" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1484" s="16" t="s">
+        <v>122</v>
+      </c>
       <c r="G1484" s="74">
-        <v>2046</v>
+        <v>2258</v>
       </c>
       <c r="H1484" s="38"/>
       <c r="I1484" s="16" t="s">
@@ -76861,7 +77019,7 @@
       <c r="O1484" s="18"/>
       <c r="P1484" s="18"/>
       <c r="Q1484" s="18"/>
-      <c r="R1484" s="87" t="s">
+      <c r="R1484" s="22" t="s">
         <v>131</v>
       </c>
     </row>
@@ -76872,14 +77030,24 @@
       <c r="B1485" s="10">
         <v>46245</v>
       </c>
-      <c r="C1485" s="38"/>
-      <c r="D1485" s="38"/>
-      <c r="E1485" s="18"/>
-      <c r="F1485" s="18"/>
+      <c r="C1485" s="55" t="s">
+        <v>2225</v>
+      </c>
+      <c r="D1485" s="55" t="s">
+        <v>2226</v>
+      </c>
+      <c r="E1485" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1485" s="13" t="s">
+        <v>22</v>
+      </c>
       <c r="G1485" s="74">
-        <v>2258</v>
-      </c>
-      <c r="H1485" s="38"/>
+        <v>60840</v>
+      </c>
+      <c r="H1485" s="66">
+        <v>17043</v>
+      </c>
       <c r="I1485" s="16" t="s">
         <v>10</v>
       </c>
@@ -76895,7 +77063,7 @@
       <c r="O1485" s="18"/>
       <c r="P1485" s="18"/>
       <c r="Q1485" s="18"/>
-      <c r="R1485" s="87" t="s">
+      <c r="R1485" s="22" t="s">
         <v>131</v>
       </c>
     </row>
@@ -76911,7 +77079,7 @@
       <c r="E1486" s="18"/>
       <c r="F1486" s="18"/>
       <c r="G1486" s="74">
-        <v>60840</v>
+        <v>18771</v>
       </c>
       <c r="H1486" s="38"/>
       <c r="I1486" s="16" t="s">
@@ -76929,7 +77097,7 @@
       <c r="O1486" s="18"/>
       <c r="P1486" s="18"/>
       <c r="Q1486" s="18"/>
-      <c r="R1486" s="87" t="s">
+      <c r="R1486" s="22" t="s">
         <v>131</v>
       </c>
     </row>
@@ -76940,12 +77108,18 @@
       <c r="B1487" s="10">
         <v>46245</v>
       </c>
-      <c r="C1487" s="38"/>
+      <c r="C1487" s="55" t="s">
+        <v>2227</v>
+      </c>
       <c r="D1487" s="38"/>
-      <c r="E1487" s="18"/>
-      <c r="F1487" s="18"/>
+      <c r="E1487" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1487" s="13" t="s">
+        <v>22</v>
+      </c>
       <c r="G1487" s="74">
-        <v>18771</v>
+        <v>72527</v>
       </c>
       <c r="H1487" s="38"/>
       <c r="I1487" s="16" t="s">
@@ -76963,25 +77137,35 @@
       <c r="O1487" s="18"/>
       <c r="P1487" s="18"/>
       <c r="Q1487" s="18"/>
-      <c r="R1487" s="87" t="s">
+      <c r="R1487" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1488" spans="1:18" ht="15" thickBot="1">
+    <row r="1488" spans="1:18" ht="27.6" thickBot="1">
       <c r="A1488" s="2">
         <v>77</v>
       </c>
       <c r="B1488" s="10">
         <v>46245</v>
       </c>
-      <c r="C1488" s="38"/>
-      <c r="D1488" s="38"/>
-      <c r="E1488" s="18"/>
-      <c r="F1488" s="18"/>
+      <c r="C1488" s="55" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1488" s="55">
+        <v>134784363</v>
+      </c>
+      <c r="E1488" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1488" s="16" t="s">
+        <v>122</v>
+      </c>
       <c r="G1488" s="74">
-        <v>72527</v>
-      </c>
-      <c r="H1488" s="38"/>
+        <v>1859</v>
+      </c>
+      <c r="H1488" s="66">
+        <v>7337</v>
+      </c>
       <c r="I1488" s="16" t="s">
         <v>10</v>
       </c>
@@ -76997,7 +77181,7 @@
       <c r="O1488" s="18"/>
       <c r="P1488" s="18"/>
       <c r="Q1488" s="18"/>
-      <c r="R1488" s="87" t="s">
+      <c r="R1488" s="22" t="s">
         <v>131</v>
       </c>
     </row>
@@ -77008,12 +77192,18 @@
       <c r="B1489" s="10">
         <v>46245</v>
       </c>
-      <c r="C1489" s="38"/>
+      <c r="C1489" s="55" t="s">
+        <v>1000</v>
+      </c>
       <c r="D1489" s="38"/>
-      <c r="E1489" s="18"/>
-      <c r="F1489" s="18"/>
+      <c r="E1489" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1489" s="13" t="s">
+        <v>22</v>
+      </c>
       <c r="G1489" s="74">
-        <v>1859</v>
+        <v>77145</v>
       </c>
       <c r="H1489" s="38"/>
       <c r="I1489" s="16" t="s">
@@ -77031,30 +77221,40 @@
       <c r="O1489" s="18"/>
       <c r="P1489" s="18"/>
       <c r="Q1489" s="18"/>
-      <c r="R1489" s="87" t="s">
+      <c r="R1489" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="1490" spans="1:18" ht="15" thickBot="1">
+    <row r="1490" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1490" s="2">
         <v>79</v>
       </c>
       <c r="B1490" s="10">
         <v>46245</v>
       </c>
-      <c r="C1490" s="38"/>
-      <c r="D1490" s="38"/>
-      <c r="E1490" s="18"/>
-      <c r="F1490" s="18"/>
+      <c r="C1490" s="55" t="s">
+        <v>2229</v>
+      </c>
+      <c r="D1490" s="55">
+        <v>1265278</v>
+      </c>
+      <c r="E1490" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1490" s="16" t="s">
+        <v>122</v>
+      </c>
       <c r="G1490" s="74">
-        <v>77145</v>
-      </c>
-      <c r="H1490" s="38"/>
+        <v>2452</v>
+      </c>
+      <c r="H1490" s="66">
+        <v>7433</v>
+      </c>
       <c r="I1490" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J1490" s="51" t="s">
-        <v>776</v>
+      <c r="J1490" s="15" t="s">
+        <v>319</v>
       </c>
       <c r="K1490" s="60" t="s">
         <v>1189</v>
@@ -77065,7 +77265,459 @@
       <c r="O1490" s="18"/>
       <c r="P1490" s="18"/>
       <c r="Q1490" s="18"/>
-      <c r="R1490" s="87" t="s">
+      <c r="R1490" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1491" s="2">
+        <v>80</v>
+      </c>
+      <c r="B1491" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1491" s="55" t="s">
+        <v>2230</v>
+      </c>
+      <c r="D1491" s="55">
+        <v>14841106</v>
+      </c>
+      <c r="E1491" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1491" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1491" s="74">
+        <v>9226</v>
+      </c>
+      <c r="H1491" s="66">
+        <v>441</v>
+      </c>
+      <c r="I1491" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1491" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1491" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1491" s="18"/>
+      <c r="M1491" s="18"/>
+      <c r="N1491" s="40"/>
+      <c r="O1491" s="18"/>
+      <c r="P1491" s="18"/>
+      <c r="Q1491" s="18"/>
+      <c r="R1491" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1492" s="2">
+        <v>81</v>
+      </c>
+      <c r="B1492" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1492" s="55" t="s">
+        <v>2231</v>
+      </c>
+      <c r="D1492" s="55">
+        <v>14317685</v>
+      </c>
+      <c r="E1492" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1492" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1492" s="74">
+        <v>5396</v>
+      </c>
+      <c r="H1492" s="66">
+        <v>5135</v>
+      </c>
+      <c r="I1492" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1492" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1492" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1492" s="18"/>
+      <c r="M1492" s="18"/>
+      <c r="N1492" s="40"/>
+      <c r="O1492" s="18"/>
+      <c r="P1492" s="18"/>
+      <c r="Q1492" s="18"/>
+      <c r="R1492" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:18" ht="15" thickBot="1">
+      <c r="A1493" s="2">
+        <v>82</v>
+      </c>
+      <c r="B1493" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1493" s="55" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D1493" s="55" t="s">
+        <v>2232</v>
+      </c>
+      <c r="E1493" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1493" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1493" s="74">
+        <v>76150</v>
+      </c>
+      <c r="H1493" s="66">
+        <v>3686</v>
+      </c>
+      <c r="I1493" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1493" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1493" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1493" s="18"/>
+      <c r="M1493" s="18"/>
+      <c r="N1493" s="40"/>
+      <c r="O1493" s="18"/>
+      <c r="P1493" s="18"/>
+      <c r="Q1493" s="15">
+        <v>95189383</v>
+      </c>
+      <c r="R1493" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:18" ht="15" thickBot="1">
+      <c r="A1494" s="2">
+        <v>83</v>
+      </c>
+      <c r="B1494" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1494" s="55" t="s">
+        <v>2233</v>
+      </c>
+      <c r="D1494" s="55" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1494" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1494" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1494" s="74">
+        <v>65063</v>
+      </c>
+      <c r="H1494" s="66">
+        <v>79901</v>
+      </c>
+      <c r="I1494" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1494" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1494" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1494" s="18"/>
+      <c r="M1494" s="18"/>
+      <c r="N1494" s="40"/>
+      <c r="O1494" s="18"/>
+      <c r="P1494" s="18"/>
+      <c r="Q1494" s="15">
+        <v>90962101</v>
+      </c>
+      <c r="R1494" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:18" ht="15" thickBot="1">
+      <c r="A1495" s="2">
+        <v>84</v>
+      </c>
+      <c r="B1495" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1495" s="55" t="s">
+        <v>2235</v>
+      </c>
+      <c r="D1495" s="55" t="s">
+        <v>2236</v>
+      </c>
+      <c r="E1495" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1495" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1495" s="74">
+        <v>49127</v>
+      </c>
+      <c r="H1495" s="66">
+        <v>80708</v>
+      </c>
+      <c r="I1495" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1495" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1495" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1495" s="18"/>
+      <c r="M1495" s="18"/>
+      <c r="N1495" s="40"/>
+      <c r="O1495" s="18"/>
+      <c r="P1495" s="18"/>
+      <c r="Q1495" s="15">
+        <v>971553475686</v>
+      </c>
+      <c r="R1495" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:18" ht="15" thickBot="1">
+      <c r="A1496" s="2">
+        <v>85</v>
+      </c>
+      <c r="B1496" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1496" s="55" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1496" s="55" t="s">
+        <v>2237</v>
+      </c>
+      <c r="E1496" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1496" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1496" s="74">
+        <v>65132</v>
+      </c>
+      <c r="H1496" s="66">
+        <v>25125</v>
+      </c>
+      <c r="I1496" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1496" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1496" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1496" s="18"/>
+      <c r="M1496" s="18"/>
+      <c r="N1496" s="40"/>
+      <c r="O1496" s="18"/>
+      <c r="P1496" s="18"/>
+      <c r="Q1496" s="15">
+        <v>90952280</v>
+      </c>
+      <c r="R1496" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:18" ht="15" thickBot="1">
+      <c r="A1497" s="2">
+        <v>86</v>
+      </c>
+      <c r="B1497" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1497" s="55" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D1497" s="55" t="s">
+        <v>2239</v>
+      </c>
+      <c r="E1497" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1497" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1497" s="74">
+        <v>95839</v>
+      </c>
+      <c r="H1497" s="66">
+        <v>93661</v>
+      </c>
+      <c r="I1497" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1497" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1497" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1497" s="18"/>
+      <c r="M1497" s="18"/>
+      <c r="N1497" s="40"/>
+      <c r="O1497" s="18"/>
+      <c r="P1497" s="18"/>
+      <c r="Q1497" s="15">
+        <v>95524672</v>
+      </c>
+      <c r="R1497" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:18" ht="15" thickBot="1">
+      <c r="A1498" s="2">
+        <v>87</v>
+      </c>
+      <c r="B1498" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1498" s="55" t="s">
+        <v>2240</v>
+      </c>
+      <c r="D1498" s="55" t="s">
+        <v>2241</v>
+      </c>
+      <c r="E1498" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1498" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1498" s="74">
+        <v>59861</v>
+      </c>
+      <c r="H1498" s="66">
+        <v>60712</v>
+      </c>
+      <c r="I1498" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1498" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1498" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1498" s="18"/>
+      <c r="M1498" s="18"/>
+      <c r="N1498" s="40"/>
+      <c r="O1498" s="18"/>
+      <c r="P1498" s="18"/>
+      <c r="Q1498" s="15">
+        <v>97505908</v>
+      </c>
+      <c r="R1498" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1499" s="2">
+        <v>88</v>
+      </c>
+      <c r="B1499" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1499" s="55" t="s">
+        <v>2172</v>
+      </c>
+      <c r="D1499" s="55" t="s">
+        <v>2242</v>
+      </c>
+      <c r="E1499" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1499" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1499" s="74">
+        <v>67531</v>
+      </c>
+      <c r="H1499" s="66">
+        <v>24295</v>
+      </c>
+      <c r="I1499" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1499" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="K1499" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1499" s="18"/>
+      <c r="M1499" s="18"/>
+      <c r="N1499" s="40"/>
+      <c r="O1499" s="18"/>
+      <c r="P1499" s="18"/>
+      <c r="Q1499" s="18"/>
+      <c r="R1499" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1500" s="2">
+        <v>89</v>
+      </c>
+      <c r="B1500" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1500" s="55" t="s">
+        <v>2243</v>
+      </c>
+      <c r="D1500" s="55" t="s">
+        <v>2244</v>
+      </c>
+      <c r="E1500" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1500" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1500" s="74">
+        <v>15901</v>
+      </c>
+      <c r="H1500" s="66">
+        <v>62943</v>
+      </c>
+      <c r="I1500" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1500" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="K1500" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1500" s="18"/>
+      <c r="M1500" s="18"/>
+      <c r="N1500" s="40"/>
+      <c r="O1500" s="18"/>
+      <c r="P1500" s="18"/>
+      <c r="Q1500" s="18"/>
+      <c r="R1500" s="22" t="s">
         <v>131</v>
       </c>
     </row>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C7E87F-6357-4ECF-8578-FA645D413D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2545A6-7E4B-4A51-9E15-2ED8B89C1B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11153" uniqueCount="2245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11198" uniqueCount="2252">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -6773,6 +6773,27 @@
   </si>
   <si>
     <t>GR1983915</t>
+  </si>
+  <si>
+    <t>ZAYID ABDULLAH</t>
+  </si>
+  <si>
+    <t>WAZIR ZAMAN</t>
+  </si>
+  <si>
+    <t>AV5209626</t>
+  </si>
+  <si>
+    <t>GY4126704</t>
+  </si>
+  <si>
+    <t>KHAI ZADA</t>
+  </si>
+  <si>
+    <t>AMEEN</t>
+  </si>
+  <si>
+    <t>AQ5937573</t>
   </si>
 </sst>
 </file>
@@ -7704,7 +7725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1500"/>
+  <dimension ref="A1:R1506"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -19576,7 +19597,9 @@
       <c r="N247" s="54">
         <v>173</v>
       </c>
-      <c r="O247" s="18"/>
+      <c r="O247" s="53">
+        <v>46244</v>
+      </c>
       <c r="P247" s="18"/>
       <c r="Q247" s="18"/>
       <c r="R247" s="21" t="s">
@@ -19622,7 +19645,9 @@
       <c r="N248" s="54">
         <v>174</v>
       </c>
-      <c r="O248" s="18"/>
+      <c r="O248" s="53">
+        <v>46244</v>
+      </c>
       <c r="P248" s="18"/>
       <c r="Q248" s="18"/>
       <c r="R248" s="21" t="s">
@@ -19668,7 +19693,9 @@
       <c r="N249" s="54">
         <v>153</v>
       </c>
-      <c r="O249" s="18"/>
+      <c r="O249" s="53">
+        <v>46244</v>
+      </c>
       <c r="P249" s="18"/>
       <c r="Q249" s="18"/>
       <c r="R249" s="21" t="s">
@@ -22334,7 +22361,9 @@
       <c r="N305" s="76" t="s">
         <v>2116</v>
       </c>
-      <c r="O305" s="18"/>
+      <c r="O305" s="53">
+        <v>46244</v>
+      </c>
       <c r="P305" s="18"/>
       <c r="Q305" s="11">
         <v>95804838</v>
@@ -28378,7 +28407,9 @@
       <c r="N431" s="54">
         <v>186</v>
       </c>
-      <c r="O431" s="18"/>
+      <c r="O431" s="53">
+        <v>46244</v>
+      </c>
       <c r="P431" s="18"/>
       <c r="Q431" s="11">
         <v>91372233</v>
@@ -35076,7 +35107,9 @@
       <c r="N572" s="54">
         <v>127</v>
       </c>
-      <c r="O572" s="18"/>
+      <c r="O572" s="53">
+        <v>46244</v>
+      </c>
       <c r="P572" s="18"/>
       <c r="Q572" s="15">
         <v>94625143</v>
@@ -43352,10 +43385,12 @@
       <c r="J747" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K747" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L747" s="18"/>
+      <c r="K747" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L747" s="53">
+        <v>46250</v>
+      </c>
       <c r="M747" s="18"/>
       <c r="N747" s="54">
         <v>1</v>
@@ -49778,7 +49813,7 @@
         <v>837</v>
       </c>
       <c r="L883" s="53">
-        <v>46250</v>
+        <v>46245</v>
       </c>
       <c r="M883" s="18"/>
       <c r="N883" s="40"/>
@@ -51633,7 +51668,7 @@
       </c>
       <c r="L923" s="18"/>
       <c r="M923" s="18"/>
-      <c r="N923" s="54" t="s">
+      <c r="N923" s="76" t="s">
         <v>2127</v>
       </c>
       <c r="O923" s="18"/>
@@ -51727,7 +51762,7 @@
       </c>
       <c r="L925" s="18"/>
       <c r="M925" s="18"/>
-      <c r="N925" s="54" t="s">
+      <c r="N925" s="76" t="s">
         <v>2128</v>
       </c>
       <c r="O925" s="18"/>
@@ -54094,10 +54129,12 @@
       <c r="J975" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K975" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L975" s="18"/>
+      <c r="K975" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L975" s="53">
+        <v>46250</v>
+      </c>
       <c r="M975" s="18"/>
       <c r="N975" s="40"/>
       <c r="O975" s="18"/>
@@ -54140,10 +54177,12 @@
       <c r="J976" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K976" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L976" s="18"/>
+      <c r="K976" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L976" s="53">
+        <v>46250</v>
+      </c>
       <c r="M976" s="18"/>
       <c r="N976" s="54">
         <v>619</v>
@@ -54188,10 +54227,12 @@
       <c r="J977" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K977" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L977" s="18"/>
+      <c r="K977" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L977" s="53">
+        <v>46250</v>
+      </c>
       <c r="M977" s="18"/>
       <c r="N977" s="54">
         <v>707</v>
@@ -54236,10 +54277,12 @@
       <c r="J978" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K978" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L978" s="18"/>
+      <c r="K978" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L978" s="53">
+        <v>46250</v>
+      </c>
       <c r="M978" s="18"/>
       <c r="N978" s="40"/>
       <c r="O978" s="18"/>
@@ -54282,10 +54325,12 @@
       <c r="J979" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K979" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L979" s="18"/>
+      <c r="K979" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L979" s="53">
+        <v>46250</v>
+      </c>
       <c r="M979" s="18"/>
       <c r="N979" s="54">
         <v>166</v>
@@ -54332,10 +54377,12 @@
       <c r="J980" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K980" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L980" s="18"/>
+      <c r="K980" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L980" s="53">
+        <v>46250</v>
+      </c>
       <c r="M980" s="18"/>
       <c r="N980" s="40"/>
       <c r="O980" s="53">
@@ -54380,10 +54427,12 @@
       <c r="J981" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K981" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L981" s="18"/>
+      <c r="K981" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L981" s="53">
+        <v>46250</v>
+      </c>
       <c r="M981" s="18"/>
       <c r="N981" s="40"/>
       <c r="O981" s="53">
@@ -54428,10 +54477,12 @@
       <c r="J982" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K982" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L982" s="18"/>
+      <c r="K982" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L982" s="53">
+        <v>46250</v>
+      </c>
       <c r="M982" s="18"/>
       <c r="N982" s="40"/>
       <c r="O982" s="15" t="s">
@@ -63663,7 +63714,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1189" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1189" spans="1:18" ht="15" thickBot="1">
       <c r="A1189" s="2">
         <v>424</v>
       </c>
@@ -63688,11 +63739,11 @@
       <c r="H1189" s="66">
         <v>7019</v>
       </c>
-      <c r="I1189" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="J1189" s="15" t="s">
-        <v>1832</v>
+      <c r="I1189" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1189" s="50" t="s">
+        <v>564</v>
       </c>
       <c r="K1189" s="17" t="s">
         <v>12</v>
@@ -68698,10 +68749,12 @@
       <c r="J1299" s="15" t="s">
         <v>950</v>
       </c>
-      <c r="K1299" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1299" s="18"/>
+      <c r="K1299" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1299" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1299" s="18"/>
       <c r="N1299" s="40"/>
       <c r="O1299" s="18"/>
@@ -77721,6 +77774,272 @@
         <v>131</v>
       </c>
     </row>
+    <row r="1501" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1501" s="2">
+        <v>90</v>
+      </c>
+      <c r="B1501" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1501" s="55" t="s">
+        <v>2245</v>
+      </c>
+      <c r="D1501" s="55">
+        <v>17052525</v>
+      </c>
+      <c r="E1501" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1501" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1501" s="74">
+        <v>8089</v>
+      </c>
+      <c r="H1501" s="66">
+        <v>5193</v>
+      </c>
+      <c r="I1501" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1501" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1501" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1501" s="18"/>
+      <c r="M1501" s="18"/>
+      <c r="N1501" s="40"/>
+      <c r="O1501" s="18"/>
+      <c r="P1501" s="18"/>
+      <c r="Q1501" s="18"/>
+      <c r="R1501" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1502" s="2">
+        <v>91</v>
+      </c>
+      <c r="B1502" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1502" s="55" t="s">
+        <v>2246</v>
+      </c>
+      <c r="D1502" s="55" t="s">
+        <v>2247</v>
+      </c>
+      <c r="E1502" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1502" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1502" s="74">
+        <v>45344</v>
+      </c>
+      <c r="H1502" s="66">
+        <v>83685</v>
+      </c>
+      <c r="I1502" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1502" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1502" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1502" s="18"/>
+      <c r="M1502" s="18"/>
+      <c r="N1502" s="40"/>
+      <c r="O1502" s="18"/>
+      <c r="P1502" s="18"/>
+      <c r="Q1502" s="11">
+        <v>77803735</v>
+      </c>
+      <c r="R1502" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1503" s="2">
+        <v>92</v>
+      </c>
+      <c r="B1503" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1503" s="55" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D1503" s="55" t="s">
+        <v>2248</v>
+      </c>
+      <c r="E1503" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1503" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1503" s="74">
+        <v>89832</v>
+      </c>
+      <c r="H1503" s="66">
+        <v>34088</v>
+      </c>
+      <c r="I1503" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1503" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1503" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1503" s="18"/>
+      <c r="M1503" s="18"/>
+      <c r="N1503" s="40"/>
+      <c r="O1503" s="18"/>
+      <c r="P1503" s="18"/>
+      <c r="Q1503" s="11">
+        <v>77804719</v>
+      </c>
+      <c r="R1503" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:18" ht="15" thickBot="1">
+      <c r="A1504" s="2">
+        <v>93</v>
+      </c>
+      <c r="B1504" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1504" s="55" t="s">
+        <v>2249</v>
+      </c>
+      <c r="D1504" s="55">
+        <v>68793586</v>
+      </c>
+      <c r="E1504" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1504" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1504" s="74">
+        <v>7065</v>
+      </c>
+      <c r="H1504" s="38"/>
+      <c r="I1504" s="73" t="s">
+        <v>1808</v>
+      </c>
+      <c r="J1504" s="18"/>
+      <c r="K1504" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1504" s="18"/>
+      <c r="M1504" s="21" t="s">
+        <v>2185</v>
+      </c>
+      <c r="N1504" s="40"/>
+      <c r="O1504" s="18"/>
+      <c r="P1504" s="18"/>
+      <c r="Q1504" s="18"/>
+      <c r="R1504" s="16" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:18" ht="15" thickBot="1">
+      <c r="A1505" s="2">
+        <v>94</v>
+      </c>
+      <c r="B1505" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1505" s="55" t="s">
+        <v>2250</v>
+      </c>
+      <c r="D1505" s="55">
+        <v>108899597</v>
+      </c>
+      <c r="E1505" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1505" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1505" s="74">
+        <v>6241</v>
+      </c>
+      <c r="H1505" s="66">
+        <v>2381</v>
+      </c>
+      <c r="I1505" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1505" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1505" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1505" s="18"/>
+      <c r="M1505" s="18"/>
+      <c r="N1505" s="40"/>
+      <c r="O1505" s="18"/>
+      <c r="P1505" s="18"/>
+      <c r="Q1505" s="18"/>
+      <c r="R1505" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1506" s="2">
+        <v>95</v>
+      </c>
+      <c r="B1506" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C1506" s="55" t="s">
+        <v>1982</v>
+      </c>
+      <c r="D1506" s="55" t="s">
+        <v>2251</v>
+      </c>
+      <c r="E1506" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1506" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1506" s="74">
+        <v>32363</v>
+      </c>
+      <c r="H1506" s="66">
+        <v>41938</v>
+      </c>
+      <c r="I1506" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1506" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="K1506" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1506" s="18"/>
+      <c r="M1506" s="18"/>
+      <c r="N1506" s="40"/>
+      <c r="O1506" s="18"/>
+      <c r="P1506" s="18"/>
+      <c r="Q1506" s="18"/>
+      <c r="R1506" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2545A6-7E4B-4A51-9E15-2ED8B89C1B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D3C06B-2D65-4CC8-9F40-21CA45920FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11198" uniqueCount="2252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11517" uniqueCount="2333">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -6794,13 +6794,256 @@
   </si>
   <si>
     <t>AQ5937573</t>
+  </si>
+  <si>
+    <t>151/1019</t>
+  </si>
+  <si>
+    <t>185/984</t>
+  </si>
+  <si>
+    <t>777//940</t>
+  </si>
+  <si>
+    <t>397//939</t>
+  </si>
+  <si>
+    <t>743/966</t>
+  </si>
+  <si>
+    <t>748/965/967</t>
+  </si>
+  <si>
+    <t>689//937</t>
+  </si>
+  <si>
+    <t>723/910</t>
+  </si>
+  <si>
+    <t>688//943</t>
+  </si>
+  <si>
+    <t>687//941</t>
+  </si>
+  <si>
+    <t>690//942</t>
+  </si>
+  <si>
+    <t>171//1013</t>
+  </si>
+  <si>
+    <t>245//1014</t>
+  </si>
+  <si>
+    <t>2//844</t>
+  </si>
+  <si>
+    <t>4//919</t>
+  </si>
+  <si>
+    <t>5//920</t>
+  </si>
+  <si>
+    <t>10/8.</t>
+  </si>
+  <si>
+    <t>SUBMITTED ON 12/AUG</t>
+  </si>
+  <si>
+    <t>828/891</t>
+  </si>
+  <si>
+    <t>KAMRAN ABBAS</t>
+  </si>
+  <si>
+    <t>BP1014674</t>
+  </si>
+  <si>
+    <t>UMAIR JAN</t>
+  </si>
+  <si>
+    <t>EV8797494</t>
+  </si>
+  <si>
+    <t>QAISER NADEEM</t>
+  </si>
+  <si>
+    <t>FJ9457882</t>
+  </si>
+  <si>
+    <t>MUDASSAR IMTIAZ</t>
+  </si>
+  <si>
+    <t>AR1274213</t>
+  </si>
+  <si>
+    <t>ALI ZAFAR</t>
+  </si>
+  <si>
+    <t>BL8521401</t>
+  </si>
+  <si>
+    <t>SHAHZAD SAFDAR</t>
+  </si>
+  <si>
+    <t>CQ5577992</t>
+  </si>
+  <si>
+    <t>ATEZAZ AHMED</t>
+  </si>
+  <si>
+    <t>CX1154685</t>
+  </si>
+  <si>
+    <t>52286-</t>
+  </si>
+  <si>
+    <t>EF6807086</t>
+  </si>
+  <si>
+    <t>050 3691704</t>
+  </si>
+  <si>
+    <t>ZAMEER UL HASSAN</t>
+  </si>
+  <si>
+    <t>BA5225014</t>
+  </si>
+  <si>
+    <t>ATIF JAVED</t>
+  </si>
+  <si>
+    <t>EG8672265</t>
+  </si>
+  <si>
+    <t>10642-</t>
+  </si>
+  <si>
+    <t>ZAHEER AHMED</t>
+  </si>
+  <si>
+    <t>QJ1151295</t>
+  </si>
+  <si>
+    <t>SANAWAR ABBS</t>
+  </si>
+  <si>
+    <t>RW1010622</t>
+  </si>
+  <si>
+    <t>ARFAN</t>
+  </si>
+  <si>
+    <t>AS1982464</t>
+  </si>
+  <si>
+    <t>SURESH KUMAR</t>
+  </si>
+  <si>
+    <t>AJ711033</t>
+  </si>
+  <si>
+    <t>SAMOTA CHAUTH MAL</t>
+  </si>
+  <si>
+    <t>ZA060556</t>
+  </si>
+  <si>
+    <t>RAM GOPAL</t>
+  </si>
+  <si>
+    <t>Z5440702</t>
+  </si>
+  <si>
+    <t>AQIB REHMAN</t>
+  </si>
+  <si>
+    <t>CH9150403</t>
+  </si>
+  <si>
+    <t>SULTAN ISSA</t>
+  </si>
+  <si>
+    <t>SAEED AHMAD</t>
+  </si>
+  <si>
+    <t>QZ1160663</t>
+  </si>
+  <si>
+    <t>33150*</t>
+  </si>
+  <si>
+    <t>BABAR HUSSAIN</t>
+  </si>
+  <si>
+    <t>ER6906675</t>
+  </si>
+  <si>
+    <t>AASIR NABEEL</t>
+  </si>
+  <si>
+    <t>AH9005056</t>
+  </si>
+  <si>
+    <t>TOQEER ABBAS</t>
+  </si>
+  <si>
+    <t>GH1013945</t>
+  </si>
+  <si>
+    <t>DQ8672295</t>
+  </si>
+  <si>
+    <t>UMAR</t>
+  </si>
+  <si>
+    <t>AWAIS RAZA</t>
+  </si>
+  <si>
+    <t>FAROOQ AHMAD</t>
+  </si>
+  <si>
+    <t>2264-</t>
+  </si>
+  <si>
+    <t>SAQLAIN MUSHTAQ</t>
+  </si>
+  <si>
+    <t>978--</t>
+  </si>
+  <si>
+    <t>KHALID HUMAID HAMED</t>
+  </si>
+  <si>
+    <t>INTAZAR</t>
+  </si>
+  <si>
+    <t>NS1164163</t>
+  </si>
+  <si>
+    <t>NAVEED AHMED</t>
+  </si>
+  <si>
+    <t>RIZWAN ULLAH KHAN</t>
+  </si>
+  <si>
+    <t>WALEED HAMOOD RASHID</t>
+  </si>
+  <si>
+    <t>Ghanim Salim Said Mohammed Al Malki</t>
+  </si>
+  <si>
+    <t>MAHMOOD ABDALLAH</t>
+  </si>
+  <si>
+    <t>ABDUL MALIK</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="38">
+  <fonts count="39">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7034,8 +7277,14 @@
       <color rgb="FFFFFFFF"/>
       <name val="Lexend"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7099,6 +7348,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBFBFBF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7175,7 +7430,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7410,6 +7665,15 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7725,7 +7989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1506"/>
+  <dimension ref="A1:R1545"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -8328,7 +8592,9 @@
         <v>46247</v>
       </c>
       <c r="M12" s="18"/>
-      <c r="N12" s="40"/>
+      <c r="N12" s="54">
+        <v>832</v>
+      </c>
       <c r="O12" s="18"/>
       <c r="P12" s="18"/>
       <c r="Q12" s="11">
@@ -8526,7 +8792,9 @@
         <v>46247</v>
       </c>
       <c r="M16" s="18"/>
-      <c r="N16" s="40"/>
+      <c r="N16" s="54">
+        <v>847</v>
+      </c>
       <c r="O16" s="18"/>
       <c r="P16" s="18"/>
       <c r="Q16" s="11">
@@ -8625,7 +8893,9 @@
       <c r="N18" s="54">
         <v>331</v>
       </c>
-      <c r="O18" s="28"/>
+      <c r="O18" s="65">
+        <v>46245</v>
+      </c>
       <c r="P18" s="28"/>
       <c r="Q18" s="28"/>
       <c r="R18" s="29" t="s">
@@ -8764,10 +9034,14 @@
         <v>46247</v>
       </c>
       <c r="M21" s="18"/>
-      <c r="N21" s="40"/>
+      <c r="N21" s="54">
+        <v>826</v>
+      </c>
       <c r="O21" s="18"/>
       <c r="P21" s="18"/>
-      <c r="Q21" s="18"/>
+      <c r="Q21" s="11">
+        <v>96405258</v>
+      </c>
       <c r="R21" s="20" t="s">
         <v>11</v>
       </c>
@@ -8810,10 +9084,14 @@
         <v>46247</v>
       </c>
       <c r="M22" s="18"/>
-      <c r="N22" s="40"/>
+      <c r="N22" s="54">
+        <v>827</v>
+      </c>
       <c r="O22" s="18"/>
       <c r="P22" s="18"/>
-      <c r="Q22" s="18"/>
+      <c r="Q22" s="11">
+        <v>94966211</v>
+      </c>
       <c r="R22" s="20" t="s">
         <v>11</v>
       </c>
@@ -9549,7 +9827,9 @@
       <c r="N37" s="54">
         <v>390</v>
       </c>
-      <c r="O37" s="18"/>
+      <c r="O37" s="53">
+        <v>46245</v>
+      </c>
       <c r="P37" s="18"/>
       <c r="Q37" s="11">
         <v>90133939</v>
@@ -9644,7 +9924,9 @@
         <v>46247</v>
       </c>
       <c r="M39" s="18"/>
-      <c r="N39" s="40"/>
+      <c r="N39" s="54">
+        <v>823</v>
+      </c>
       <c r="O39" s="18"/>
       <c r="P39" s="18"/>
       <c r="Q39" s="18"/>
@@ -9988,7 +10270,9 @@
         <v>46247</v>
       </c>
       <c r="M46" s="18"/>
-      <c r="N46" s="40"/>
+      <c r="N46" s="54">
+        <v>949</v>
+      </c>
       <c r="O46" s="18"/>
       <c r="P46" s="18"/>
       <c r="Q46" s="11">
@@ -10228,7 +10512,9 @@
         <v>46247</v>
       </c>
       <c r="M51" s="18"/>
-      <c r="N51" s="40"/>
+      <c r="N51" s="54">
+        <v>840</v>
+      </c>
       <c r="O51" s="18"/>
       <c r="P51" s="18"/>
       <c r="Q51" s="11">
@@ -10324,7 +10610,9 @@
         <v>46247</v>
       </c>
       <c r="M53" s="18"/>
-      <c r="N53" s="40"/>
+      <c r="N53" s="54">
+        <v>904</v>
+      </c>
       <c r="O53" s="18"/>
       <c r="P53" s="18"/>
       <c r="Q53" s="11">
@@ -10468,7 +10756,9 @@
         <v>46247</v>
       </c>
       <c r="M56" s="18"/>
-      <c r="N56" s="40"/>
+      <c r="N56" s="54">
+        <v>912</v>
+      </c>
       <c r="O56" s="18"/>
       <c r="P56" s="18"/>
       <c r="Q56" s="18"/>
@@ -10567,7 +10857,9 @@
       <c r="N58" s="54">
         <v>341</v>
       </c>
-      <c r="O58" s="18"/>
+      <c r="O58" s="53">
+        <v>46245</v>
+      </c>
       <c r="P58" s="18"/>
       <c r="Q58" s="11">
         <v>95626634</v>
@@ -10617,7 +10909,9 @@
       <c r="N59" s="54">
         <v>342</v>
       </c>
-      <c r="O59" s="18"/>
+      <c r="O59" s="53">
+        <v>46245</v>
+      </c>
       <c r="P59" s="18"/>
       <c r="Q59" s="18"/>
       <c r="R59" s="20" t="s">
@@ -10665,7 +10959,9 @@
       <c r="N60" s="54">
         <v>343</v>
       </c>
-      <c r="O60" s="18"/>
+      <c r="O60" s="53">
+        <v>46245</v>
+      </c>
       <c r="P60" s="18"/>
       <c r="Q60" s="18"/>
       <c r="R60" s="20" t="s">
@@ -10713,7 +11009,9 @@
       <c r="N61" s="54">
         <v>344</v>
       </c>
-      <c r="O61" s="18"/>
+      <c r="O61" s="53">
+        <v>46245</v>
+      </c>
       <c r="P61" s="18"/>
       <c r="Q61" s="18"/>
       <c r="R61" s="20" t="s">
@@ -10761,7 +11059,9 @@
       <c r="N62" s="54">
         <v>257</v>
       </c>
-      <c r="O62" s="18"/>
+      <c r="O62" s="53">
+        <v>46244</v>
+      </c>
       <c r="P62" s="18"/>
       <c r="Q62" s="11">
         <v>95549561</v>
@@ -10809,7 +11109,9 @@
       <c r="N63" s="54">
         <v>259</v>
       </c>
-      <c r="O63" s="18"/>
+      <c r="O63" s="53">
+        <v>46244</v>
+      </c>
       <c r="P63" s="18"/>
       <c r="Q63" s="11">
         <v>95804679</v>
@@ -10859,7 +11161,9 @@
       <c r="N64" s="54">
         <v>258</v>
       </c>
-      <c r="O64" s="18"/>
+      <c r="O64" s="53">
+        <v>46244</v>
+      </c>
       <c r="P64" s="18"/>
       <c r="Q64" s="18"/>
       <c r="R64" s="20" t="s">
@@ -10907,7 +11211,9 @@
       <c r="N65" s="54">
         <v>270</v>
       </c>
-      <c r="O65" s="18"/>
+      <c r="O65" s="53">
+        <v>46244</v>
+      </c>
       <c r="P65" s="18"/>
       <c r="Q65" s="11">
         <v>95785835</v>
@@ -10957,7 +11263,9 @@
       <c r="N66" s="54">
         <v>269</v>
       </c>
-      <c r="O66" s="18"/>
+      <c r="O66" s="53">
+        <v>46244</v>
+      </c>
       <c r="P66" s="18"/>
       <c r="Q66" s="18"/>
       <c r="R66" s="20" t="s">
@@ -11008,7 +11316,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="15" thickBot="1">
+    <row r="68" spans="1:18" ht="28.2" thickBot="1">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -11044,8 +11352,8 @@
       </c>
       <c r="L68" s="18"/>
       <c r="M68" s="18"/>
-      <c r="N68" s="54">
-        <v>151</v>
+      <c r="N68" s="76" t="s">
+        <v>2252</v>
       </c>
       <c r="O68" s="53">
         <v>46244</v>
@@ -11186,7 +11494,9 @@
         <v>46247</v>
       </c>
       <c r="M71" s="18"/>
-      <c r="N71" s="40"/>
+      <c r="N71" s="54">
+        <v>885</v>
+      </c>
       <c r="O71" s="18"/>
       <c r="P71" s="18"/>
       <c r="Q71" s="11">
@@ -11234,7 +11544,9 @@
         <v>46247</v>
       </c>
       <c r="M72" s="18"/>
-      <c r="N72" s="40"/>
+      <c r="N72" s="54">
+        <v>887</v>
+      </c>
       <c r="O72" s="18"/>
       <c r="P72" s="18"/>
       <c r="Q72" s="11">
@@ -11328,7 +11640,9 @@
         <v>46247</v>
       </c>
       <c r="M74" s="18"/>
-      <c r="N74" s="40"/>
+      <c r="N74" s="54">
+        <v>883</v>
+      </c>
       <c r="O74" s="18"/>
       <c r="P74" s="18"/>
       <c r="Q74" s="18"/>
@@ -11374,7 +11688,9 @@
         <v>46247</v>
       </c>
       <c r="M75" s="18"/>
-      <c r="N75" s="40"/>
+      <c r="N75" s="54">
+        <v>884</v>
+      </c>
       <c r="O75" s="18"/>
       <c r="P75" s="18"/>
       <c r="Q75" s="18"/>
@@ -11858,7 +12174,9 @@
         <v>46247</v>
       </c>
       <c r="M85" s="18"/>
-      <c r="N85" s="40"/>
+      <c r="N85" s="54">
+        <v>978</v>
+      </c>
       <c r="O85" s="18"/>
       <c r="P85" s="18"/>
       <c r="Q85" s="11">
@@ -12218,7 +12536,9 @@
       </c>
       <c r="L93" s="18"/>
       <c r="M93" s="18"/>
-      <c r="N93" s="40"/>
+      <c r="N93" s="54">
+        <v>1021</v>
+      </c>
       <c r="O93" s="18"/>
       <c r="P93" s="36" t="s">
         <v>322</v>
@@ -12745,7 +13065,9 @@
       <c r="N104" s="54">
         <v>318</v>
       </c>
-      <c r="O104" s="18"/>
+      <c r="O104" s="53">
+        <v>46245</v>
+      </c>
       <c r="P104" s="18"/>
       <c r="Q104" s="11">
         <v>7719527</v>
@@ -12792,7 +13114,9 @@
         <v>46247</v>
       </c>
       <c r="M105" s="18"/>
-      <c r="N105" s="40"/>
+      <c r="N105" s="54">
+        <v>1029</v>
+      </c>
       <c r="O105" s="18"/>
       <c r="P105" s="18"/>
       <c r="Q105" s="11">
@@ -12995,7 +13319,9 @@
       <c r="N109" s="54">
         <v>300</v>
       </c>
-      <c r="O109" s="18"/>
+      <c r="O109" s="53">
+        <v>46245</v>
+      </c>
       <c r="P109" s="18"/>
       <c r="Q109" s="11">
         <v>91347098</v>
@@ -13094,10 +13420,12 @@
         <v>46247</v>
       </c>
       <c r="M111" s="18"/>
-      <c r="N111" s="54">
-        <v>185</v>
-      </c>
-      <c r="O111" s="18"/>
+      <c r="N111" s="76" t="s">
+        <v>2253</v>
+      </c>
+      <c r="O111" s="53">
+        <v>46244</v>
+      </c>
       <c r="P111" s="18"/>
       <c r="Q111" s="11">
         <v>77857868</v>
@@ -13245,7 +13573,9 @@
       <c r="N114" s="54">
         <v>187</v>
       </c>
-      <c r="O114" s="18"/>
+      <c r="O114" s="53">
+        <v>46244</v>
+      </c>
       <c r="P114" s="18"/>
       <c r="Q114" s="11">
         <v>77480470</v>
@@ -13341,7 +13671,9 @@
       <c r="N116" s="54">
         <v>184</v>
       </c>
-      <c r="O116" s="18"/>
+      <c r="O116" s="53">
+        <v>46244</v>
+      </c>
       <c r="P116" s="18"/>
       <c r="Q116" s="11">
         <v>92724546</v>
@@ -13443,7 +13775,9 @@
       <c r="N118" s="54">
         <v>181</v>
       </c>
-      <c r="O118" s="18"/>
+      <c r="O118" s="53">
+        <v>46244</v>
+      </c>
       <c r="P118" s="18"/>
       <c r="Q118" s="11">
         <v>77208876</v>
@@ -13493,7 +13827,9 @@
       <c r="N119" s="54">
         <v>183</v>
       </c>
-      <c r="O119" s="18"/>
+      <c r="O119" s="53">
+        <v>46244</v>
+      </c>
       <c r="P119" s="18"/>
       <c r="Q119" s="11">
         <v>524577680</v>
@@ -14080,7 +14416,9 @@
       </c>
       <c r="L131" s="18"/>
       <c r="M131" s="18"/>
-      <c r="N131" s="40"/>
+      <c r="N131" s="54">
+        <v>908</v>
+      </c>
       <c r="O131" s="18"/>
       <c r="P131" s="18"/>
       <c r="Q131" s="11">
@@ -14178,7 +14516,9 @@
         <v>46247</v>
       </c>
       <c r="M133" s="18"/>
-      <c r="N133" s="40"/>
+      <c r="N133" s="54">
+        <v>906</v>
+      </c>
       <c r="O133" s="18"/>
       <c r="P133" s="18"/>
       <c r="Q133" s="11">
@@ -14634,7 +14974,9 @@
         <v>46247</v>
       </c>
       <c r="M142" s="18"/>
-      <c r="N142" s="40"/>
+      <c r="N142" s="54">
+        <v>956</v>
+      </c>
       <c r="O142" s="18"/>
       <c r="P142" s="18"/>
       <c r="Q142" s="11">
@@ -14732,7 +15074,9 @@
         <v>46247</v>
       </c>
       <c r="M144" s="18"/>
-      <c r="N144" s="40"/>
+      <c r="N144" s="54">
+        <v>954</v>
+      </c>
       <c r="O144" s="18"/>
       <c r="P144" s="18"/>
       <c r="Q144" s="11">
@@ -15174,7 +15518,9 @@
         <v>46247</v>
       </c>
       <c r="M153" s="18"/>
-      <c r="N153" s="40"/>
+      <c r="N153" s="54">
+        <v>932</v>
+      </c>
       <c r="O153" s="18"/>
       <c r="P153" s="18"/>
       <c r="Q153" s="11">
@@ -15275,7 +15621,9 @@
       <c r="N155" s="54">
         <v>232</v>
       </c>
-      <c r="O155" s="18"/>
+      <c r="O155" s="53">
+        <v>46244</v>
+      </c>
       <c r="P155" s="18"/>
       <c r="Q155" s="11">
         <v>79291867</v>
@@ -15322,7 +15670,9 @@
         <v>46247</v>
       </c>
       <c r="M156" s="18"/>
-      <c r="N156" s="40"/>
+      <c r="N156" s="54">
+        <v>1039</v>
+      </c>
       <c r="O156" s="18"/>
       <c r="P156" s="18"/>
       <c r="Q156" s="11">
@@ -15370,7 +15720,9 @@
         <v>46247</v>
       </c>
       <c r="M157" s="18"/>
-      <c r="N157" s="40"/>
+      <c r="N157" s="54">
+        <v>964</v>
+      </c>
       <c r="O157" s="18"/>
       <c r="P157" s="18"/>
       <c r="Q157" s="11">
@@ -15418,7 +15770,9 @@
         <v>46247</v>
       </c>
       <c r="M158" s="18"/>
-      <c r="N158" s="40"/>
+      <c r="N158" s="54">
+        <v>1040</v>
+      </c>
       <c r="O158" s="18"/>
       <c r="P158" s="18"/>
       <c r="Q158" s="11">
@@ -15466,7 +15820,9 @@
         <v>46247</v>
       </c>
       <c r="M159" s="18"/>
-      <c r="N159" s="40"/>
+      <c r="N159" s="54">
+        <v>1038</v>
+      </c>
       <c r="O159" s="18"/>
       <c r="P159" s="18"/>
       <c r="Q159" s="11">
@@ -15514,7 +15870,9 @@
         <v>46247</v>
       </c>
       <c r="M160" s="18"/>
-      <c r="N160" s="40"/>
+      <c r="N160" s="54">
+        <v>1037</v>
+      </c>
       <c r="O160" s="18"/>
       <c r="P160" s="18"/>
       <c r="Q160" s="11">
@@ -15662,7 +16020,9 @@
         <v>46247</v>
       </c>
       <c r="M163" s="18"/>
-      <c r="N163" s="40"/>
+      <c r="N163" s="54">
+        <v>934</v>
+      </c>
       <c r="O163" s="18"/>
       <c r="P163" s="18"/>
       <c r="Q163" s="11">
@@ -15810,7 +16170,9 @@
         <v>46247</v>
       </c>
       <c r="M166" s="18"/>
-      <c r="N166" s="40"/>
+      <c r="N166" s="54">
+        <v>909</v>
+      </c>
       <c r="O166" s="18"/>
       <c r="P166" s="18"/>
       <c r="Q166" s="11">
@@ -16057,7 +16419,9 @@
       <c r="N171" s="54">
         <v>212</v>
       </c>
-      <c r="O171" s="18"/>
+      <c r="O171" s="53">
+        <v>46244</v>
+      </c>
       <c r="P171" s="18"/>
       <c r="Q171" s="11">
         <v>71049872</v>
@@ -16104,7 +16468,9 @@
         <v>46250</v>
       </c>
       <c r="M172" s="18"/>
-      <c r="N172" s="40"/>
+      <c r="N172" s="54">
+        <v>1032</v>
+      </c>
       <c r="O172" s="18"/>
       <c r="P172" s="18"/>
       <c r="Q172" s="11">
@@ -16150,7 +16516,9 @@
       </c>
       <c r="L173" s="18"/>
       <c r="M173" s="18"/>
-      <c r="N173" s="40"/>
+      <c r="N173" s="54">
+        <v>1033</v>
+      </c>
       <c r="O173" s="18"/>
       <c r="P173" s="18"/>
       <c r="Q173" s="11">
@@ -16199,7 +16567,9 @@
       <c r="N174" s="54">
         <v>219</v>
       </c>
-      <c r="O174" s="18"/>
+      <c r="O174" s="53">
+        <v>46244</v>
+      </c>
       <c r="P174" s="18"/>
       <c r="Q174" s="11">
         <v>77552346</v>
@@ -16898,7 +17268,9 @@
       </c>
       <c r="L189" s="18"/>
       <c r="M189" s="18"/>
-      <c r="N189" s="40"/>
+      <c r="N189" s="54">
+        <v>933</v>
+      </c>
       <c r="O189" s="18"/>
       <c r="P189" s="18"/>
       <c r="Q189" s="11">
@@ -16992,7 +17364,9 @@
         <v>46250</v>
       </c>
       <c r="M191" s="18"/>
-      <c r="N191" s="40"/>
+      <c r="N191" s="54">
+        <v>935</v>
+      </c>
       <c r="O191" s="18"/>
       <c r="P191" s="18"/>
       <c r="Q191" s="11">
@@ -17038,7 +17412,9 @@
       </c>
       <c r="L192" s="18"/>
       <c r="M192" s="18"/>
-      <c r="N192" s="40"/>
+      <c r="N192" s="54">
+        <v>935</v>
+      </c>
       <c r="O192" s="18"/>
       <c r="P192" s="18"/>
       <c r="Q192" s="11">
@@ -17644,7 +18020,9 @@
       </c>
       <c r="L205" s="18"/>
       <c r="M205" s="18"/>
-      <c r="N205" s="40"/>
+      <c r="N205" s="54">
+        <v>948</v>
+      </c>
       <c r="O205" s="18"/>
       <c r="P205" s="18"/>
       <c r="Q205" s="11">
@@ -17878,7 +18256,9 @@
       </c>
       <c r="L210" s="18"/>
       <c r="M210" s="18"/>
-      <c r="N210" s="40"/>
+      <c r="N210" s="54">
+        <v>931</v>
+      </c>
       <c r="O210" s="18"/>
       <c r="P210" s="18"/>
       <c r="Q210" s="11">
@@ -17926,7 +18306,9 @@
         <v>46250</v>
       </c>
       <c r="M211" s="18"/>
-      <c r="N211" s="40"/>
+      <c r="N211" s="54">
+        <v>913</v>
+      </c>
       <c r="O211" s="18"/>
       <c r="P211" s="18"/>
       <c r="Q211" s="11">
@@ -17974,7 +18356,9 @@
         <v>46250</v>
       </c>
       <c r="M212" s="18"/>
-      <c r="N212" s="40"/>
+      <c r="N212" s="54">
+        <v>947</v>
+      </c>
       <c r="O212" s="18"/>
       <c r="P212" s="18"/>
       <c r="Q212" s="11">
@@ -18544,7 +18928,9 @@
       </c>
       <c r="L224" s="18"/>
       <c r="M224" s="18"/>
-      <c r="N224" s="40"/>
+      <c r="N224" s="54">
+        <v>1042</v>
+      </c>
       <c r="O224" s="18"/>
       <c r="P224" s="18"/>
       <c r="Q224" s="11">
@@ -18632,7 +19018,9 @@
       </c>
       <c r="L226" s="18"/>
       <c r="M226" s="18"/>
-      <c r="N226" s="40"/>
+      <c r="N226" s="54">
+        <v>1041</v>
+      </c>
       <c r="O226" s="18"/>
       <c r="P226" s="18"/>
       <c r="Q226" s="11">
@@ -18764,7 +19152,9 @@
         <v>46250</v>
       </c>
       <c r="M229" s="18"/>
-      <c r="N229" s="40"/>
+      <c r="N229" s="54">
+        <v>890</v>
+      </c>
       <c r="O229" s="18"/>
       <c r="P229" s="18"/>
       <c r="Q229" s="11">
@@ -19223,7 +19613,9 @@
       <c r="N239" s="54">
         <v>308</v>
       </c>
-      <c r="O239" s="18"/>
+      <c r="O239" s="53">
+        <v>46245</v>
+      </c>
       <c r="P239" s="18"/>
       <c r="Q239" s="11">
         <v>568487207</v>
@@ -19271,7 +19663,9 @@
       <c r="N240" s="54">
         <v>310</v>
       </c>
-      <c r="O240" s="18"/>
+      <c r="O240" s="53">
+        <v>46245</v>
+      </c>
       <c r="P240" s="18"/>
       <c r="Q240" s="11">
         <v>77411027</v>
@@ -19457,7 +19851,9 @@
       <c r="N244" s="54">
         <v>307</v>
       </c>
-      <c r="O244" s="18"/>
+      <c r="O244" s="53">
+        <v>46245</v>
+      </c>
       <c r="P244" s="18"/>
       <c r="Q244" s="11">
         <v>505192986</v>
@@ -19741,7 +20137,9 @@
       <c r="N250" s="54">
         <v>222</v>
       </c>
-      <c r="O250" s="18"/>
+      <c r="O250" s="53">
+        <v>46244</v>
+      </c>
       <c r="P250" s="18"/>
       <c r="Q250" s="18"/>
       <c r="R250" s="21" t="s">
@@ -19787,7 +20185,9 @@
       <c r="N251" s="54">
         <v>369</v>
       </c>
-      <c r="O251" s="18"/>
+      <c r="O251" s="53">
+        <v>46245</v>
+      </c>
       <c r="P251" s="18"/>
       <c r="Q251" s="18"/>
       <c r="R251" s="21" t="s">
@@ -19833,7 +20233,9 @@
       <c r="N252" s="54">
         <v>368</v>
       </c>
-      <c r="O252" s="18"/>
+      <c r="O252" s="53">
+        <v>46245</v>
+      </c>
       <c r="P252" s="18"/>
       <c r="Q252" s="18"/>
       <c r="R252" s="21" t="s">
@@ -19879,7 +20281,9 @@
       <c r="N253" s="54">
         <v>394</v>
       </c>
-      <c r="O253" s="18"/>
+      <c r="O253" s="53">
+        <v>46245</v>
+      </c>
       <c r="P253" s="18"/>
       <c r="Q253" s="11">
         <v>99158798</v>
@@ -19973,7 +20377,9 @@
       <c r="N255" s="54">
         <v>223</v>
       </c>
-      <c r="O255" s="18"/>
+      <c r="O255" s="53">
+        <v>46244</v>
+      </c>
       <c r="P255" s="18"/>
       <c r="Q255" s="18"/>
       <c r="R255" s="21" t="s">
@@ -20019,7 +20425,9 @@
       <c r="N256" s="54">
         <v>235</v>
       </c>
-      <c r="O256" s="18"/>
+      <c r="O256" s="53">
+        <v>46244</v>
+      </c>
       <c r="P256" s="18"/>
       <c r="Q256" s="18"/>
       <c r="R256" s="21" t="s">
@@ -20065,7 +20473,9 @@
       <c r="N257" s="54">
         <v>221</v>
       </c>
-      <c r="O257" s="18"/>
+      <c r="O257" s="53">
+        <v>46244</v>
+      </c>
       <c r="P257" s="18"/>
       <c r="Q257" s="18"/>
       <c r="R257" s="21" t="s">
@@ -20111,7 +20521,9 @@
       <c r="N258" s="54">
         <v>220</v>
       </c>
-      <c r="O258" s="18"/>
+      <c r="O258" s="53">
+        <v>46244</v>
+      </c>
       <c r="P258" s="18"/>
       <c r="Q258" s="11">
         <v>77801925</v>
@@ -20159,7 +20571,9 @@
       <c r="N259" s="54">
         <v>420</v>
       </c>
-      <c r="O259" s="18"/>
+      <c r="O259" s="53">
+        <v>46245</v>
+      </c>
       <c r="P259" s="18"/>
       <c r="Q259" s="11">
         <v>91305005</v>
@@ -20296,7 +20710,9 @@
       </c>
       <c r="L262" s="18"/>
       <c r="M262" s="18"/>
-      <c r="N262" s="40"/>
+      <c r="N262" s="54">
+        <v>829</v>
+      </c>
       <c r="O262" s="18"/>
       <c r="P262" s="18"/>
       <c r="Q262" s="11">
@@ -20669,7 +21085,9 @@
       <c r="N270" s="54">
         <v>23</v>
       </c>
-      <c r="O270" s="18"/>
+      <c r="O270" s="53">
+        <v>46244</v>
+      </c>
       <c r="P270" s="18"/>
       <c r="Q270" s="11">
         <v>99151850</v>
@@ -20760,8 +21178,8 @@
         <v>46247</v>
       </c>
       <c r="M272" s="18"/>
-      <c r="N272" s="54">
-        <v>777</v>
+      <c r="N272" s="76" t="s">
+        <v>2254</v>
       </c>
       <c r="O272" s="18"/>
       <c r="P272" s="18"/>
@@ -20854,8 +21272,8 @@
         <v>46247</v>
       </c>
       <c r="M274" s="18"/>
-      <c r="N274" s="54">
-        <v>397</v>
+      <c r="N274" s="76" t="s">
+        <v>2255</v>
       </c>
       <c r="O274" s="18"/>
       <c r="P274" s="18"/>
@@ -20904,7 +21322,9 @@
         <v>46247</v>
       </c>
       <c r="M275" s="18"/>
-      <c r="N275" s="40"/>
+      <c r="N275" s="54">
+        <v>939</v>
+      </c>
       <c r="O275" s="18"/>
       <c r="P275" s="18"/>
       <c r="Q275" s="18"/>
@@ -21184,8 +21604,8 @@
         <v>46247</v>
       </c>
       <c r="M281" s="18"/>
-      <c r="N281" s="54">
-        <v>743</v>
+      <c r="N281" s="76" t="s">
+        <v>2256</v>
       </c>
       <c r="O281" s="18"/>
       <c r="P281" s="18"/>
@@ -21280,8 +21700,8 @@
         <v>46247</v>
       </c>
       <c r="M283" s="18"/>
-      <c r="N283" s="54">
-        <v>748</v>
+      <c r="N283" s="76" t="s">
+        <v>2257</v>
       </c>
       <c r="O283" s="18"/>
       <c r="P283" s="18"/>
@@ -21379,7 +21799,9 @@
       <c r="N285" s="54">
         <v>209</v>
       </c>
-      <c r="O285" s="18"/>
+      <c r="O285" s="53">
+        <v>46244</v>
+      </c>
       <c r="P285" s="18"/>
       <c r="Q285" s="18"/>
       <c r="R285" s="22" t="s">
@@ -21477,7 +21899,9 @@
       <c r="N287" s="54">
         <v>207</v>
       </c>
-      <c r="O287" s="18"/>
+      <c r="O287" s="53">
+        <v>46244</v>
+      </c>
       <c r="P287" s="18"/>
       <c r="Q287" s="18"/>
       <c r="R287" s="22" t="s">
@@ -21522,7 +21946,9 @@
         <v>46247</v>
       </c>
       <c r="M288" s="18"/>
-      <c r="N288" s="40"/>
+      <c r="N288" s="54">
+        <v>945</v>
+      </c>
       <c r="O288" s="18"/>
       <c r="P288" s="18"/>
       <c r="Q288" s="18"/>
@@ -21568,8 +21994,8 @@
         <v>46247</v>
       </c>
       <c r="M289" s="18"/>
-      <c r="N289" s="54">
-        <v>689</v>
+      <c r="N289" s="76" t="s">
+        <v>2258</v>
       </c>
       <c r="O289" s="18"/>
       <c r="P289" s="18"/>
@@ -21665,7 +22091,9 @@
       <c r="N291" s="54">
         <v>374</v>
       </c>
-      <c r="O291" s="18"/>
+      <c r="O291" s="53">
+        <v>46245</v>
+      </c>
       <c r="P291" s="18"/>
       <c r="Q291" s="11">
         <v>94799278</v>
@@ -21763,7 +22191,9 @@
       <c r="N293" s="54">
         <v>371</v>
       </c>
-      <c r="O293" s="18"/>
+      <c r="O293" s="53">
+        <v>46245</v>
+      </c>
       <c r="P293" s="18"/>
       <c r="Q293" s="11">
         <v>96954720</v>
@@ -21813,7 +22243,9 @@
       <c r="N294" s="54">
         <v>314</v>
       </c>
-      <c r="O294" s="18"/>
+      <c r="O294" s="53">
+        <v>46245</v>
+      </c>
       <c r="P294" s="18"/>
       <c r="Q294" s="11">
         <v>94245786</v>
@@ -22165,7 +22597,9 @@
       <c r="N301" s="54">
         <v>81</v>
       </c>
-      <c r="O301" s="18"/>
+      <c r="O301" s="53">
+        <v>46244</v>
+      </c>
       <c r="P301" s="18"/>
       <c r="Q301" s="11">
         <v>94496988</v>
@@ -22517,7 +22951,9 @@
       <c r="N308" s="54">
         <v>315</v>
       </c>
-      <c r="O308" s="18"/>
+      <c r="O308" s="53">
+        <v>46245</v>
+      </c>
       <c r="P308" s="18"/>
       <c r="Q308" s="11">
         <v>96876643273</v>
@@ -22814,8 +23250,8 @@
         <v>46247</v>
       </c>
       <c r="M314" s="18"/>
-      <c r="N314" s="54">
-        <v>723</v>
+      <c r="N314" s="76" t="s">
+        <v>2259</v>
       </c>
       <c r="O314" s="18"/>
       <c r="P314" s="18"/>
@@ -23164,8 +23600,8 @@
         <v>46247</v>
       </c>
       <c r="M321" s="18"/>
-      <c r="N321" s="54">
-        <v>688</v>
+      <c r="N321" s="76" t="s">
+        <v>2260</v>
       </c>
       <c r="O321" s="18"/>
       <c r="P321" s="18"/>
@@ -23212,8 +23648,8 @@
         <v>46247</v>
       </c>
       <c r="M322" s="18"/>
-      <c r="N322" s="54">
-        <v>687</v>
+      <c r="N322" s="76" t="s">
+        <v>2261</v>
       </c>
       <c r="O322" s="18"/>
       <c r="P322" s="18"/>
@@ -23260,7 +23696,9 @@
         <v>46247</v>
       </c>
       <c r="M323" s="18"/>
-      <c r="N323" s="40"/>
+      <c r="N323" s="54">
+        <v>944</v>
+      </c>
       <c r="O323" s="18"/>
       <c r="P323" s="18"/>
       <c r="Q323" s="18"/>
@@ -23354,8 +23792,8 @@
         <v>46247</v>
       </c>
       <c r="M325" s="18"/>
-      <c r="N325" s="54">
-        <v>690</v>
+      <c r="N325" s="76" t="s">
+        <v>2262</v>
       </c>
       <c r="O325" s="18"/>
       <c r="P325" s="18"/>
@@ -23675,7 +24113,9 @@
       <c r="N332" s="54">
         <v>271</v>
       </c>
-      <c r="O332" s="18"/>
+      <c r="O332" s="53">
+        <v>46244</v>
+      </c>
       <c r="P332" s="18"/>
       <c r="Q332" s="18"/>
       <c r="R332" s="22" t="s">
@@ -23952,7 +24392,9 @@
         <v>46247</v>
       </c>
       <c r="M338" s="18"/>
-      <c r="N338" s="40"/>
+      <c r="N338" s="54">
+        <v>896</v>
+      </c>
       <c r="O338" s="18"/>
       <c r="P338" s="18"/>
       <c r="Q338" s="18"/>
@@ -24801,7 +25243,9 @@
       <c r="N356" s="54">
         <v>215</v>
       </c>
-      <c r="O356" s="18"/>
+      <c r="O356" s="53">
+        <v>46244</v>
+      </c>
       <c r="P356" s="18"/>
       <c r="Q356" s="11">
         <v>78286427</v>
@@ -24849,7 +25293,9 @@
       <c r="N357" s="54">
         <v>164</v>
       </c>
-      <c r="O357" s="18"/>
+      <c r="O357" s="53">
+        <v>46245</v>
+      </c>
       <c r="P357" s="49" t="s">
         <v>1286</v>
       </c>
@@ -24944,7 +25390,9 @@
       </c>
       <c r="L359" s="18"/>
       <c r="M359" s="18"/>
-      <c r="N359" s="40"/>
+      <c r="N359" s="54">
+        <v>998</v>
+      </c>
       <c r="O359" s="18"/>
       <c r="P359" s="18"/>
       <c r="Q359" s="11">
@@ -25004,7 +25452,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="361" spans="1:18" ht="15" thickBot="1">
+    <row r="361" spans="1:18" ht="28.2" thickBot="1">
       <c r="A361" s="2">
         <v>11</v>
       </c>
@@ -25040,8 +25488,8 @@
       </c>
       <c r="L361" s="18"/>
       <c r="M361" s="18"/>
-      <c r="N361" s="54">
-        <v>171</v>
+      <c r="N361" s="79" t="s">
+        <v>2263</v>
       </c>
       <c r="O361" s="53">
         <v>46244</v>
@@ -25188,7 +25636,9 @@
         <v>46247</v>
       </c>
       <c r="M364" s="18"/>
-      <c r="N364" s="40"/>
+      <c r="N364" s="54">
+        <v>975</v>
+      </c>
       <c r="O364" s="18"/>
       <c r="P364" s="18"/>
       <c r="Q364" s="11">
@@ -25237,7 +25687,9 @@
       <c r="N365" s="54">
         <v>297</v>
       </c>
-      <c r="O365" s="18"/>
+      <c r="O365" s="53">
+        <v>46244</v>
+      </c>
       <c r="P365" s="18"/>
       <c r="Q365" s="11">
         <v>98130965</v>
@@ -25246,7 +25698,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="366" spans="1:18" ht="15" thickBot="1">
+    <row r="366" spans="1:18" ht="28.2" thickBot="1">
       <c r="A366" s="2">
         <v>16</v>
       </c>
@@ -25284,10 +25736,12 @@
         <v>46247</v>
       </c>
       <c r="M366" s="18"/>
-      <c r="N366" s="54">
-        <v>245</v>
-      </c>
-      <c r="O366" s="18"/>
+      <c r="N366" s="79" t="s">
+        <v>2264</v>
+      </c>
+      <c r="O366" s="53">
+        <v>46244</v>
+      </c>
       <c r="P366" s="18"/>
       <c r="Q366" s="11">
         <v>97765961</v>
@@ -25434,7 +25888,9 @@
         <v>46250</v>
       </c>
       <c r="M369" s="28"/>
-      <c r="N369" s="28"/>
+      <c r="N369" s="27">
+        <v>907</v>
+      </c>
       <c r="O369" s="28"/>
       <c r="P369" s="28"/>
       <c r="Q369" s="28"/>
@@ -25920,7 +26376,9 @@
         <v>46247</v>
       </c>
       <c r="M379" s="18"/>
-      <c r="N379" s="40"/>
+      <c r="N379" s="54">
+        <v>897</v>
+      </c>
       <c r="O379" s="18"/>
       <c r="P379" s="18"/>
       <c r="Q379" s="18"/>
@@ -25966,7 +26424,9 @@
         <v>46247</v>
       </c>
       <c r="M380" s="18"/>
-      <c r="N380" s="40"/>
+      <c r="N380" s="54">
+        <v>969</v>
+      </c>
       <c r="O380" s="18"/>
       <c r="P380" s="18"/>
       <c r="Q380" s="18"/>
@@ -26067,7 +26527,9 @@
       <c r="N382" s="54">
         <v>323</v>
       </c>
-      <c r="O382" s="18"/>
+      <c r="O382" s="53">
+        <v>46245</v>
+      </c>
       <c r="P382" s="18"/>
       <c r="Q382" s="11">
         <v>95768198</v>
@@ -26169,7 +26631,9 @@
       <c r="N384" s="54">
         <v>224</v>
       </c>
-      <c r="O384" s="18"/>
+      <c r="O384" s="53">
+        <v>46244</v>
+      </c>
       <c r="P384" s="18"/>
       <c r="Q384" s="11">
         <v>92020971</v>
@@ -27558,7 +28022,9 @@
       </c>
       <c r="L413" s="18"/>
       <c r="M413" s="18"/>
-      <c r="N413" s="40"/>
+      <c r="N413" s="54">
+        <v>1000</v>
+      </c>
       <c r="O413" s="18"/>
       <c r="P413" s="18"/>
       <c r="Q413" s="11">
@@ -27786,7 +28252,9 @@
       </c>
       <c r="L418" s="18"/>
       <c r="M418" s="18"/>
-      <c r="N418" s="40"/>
+      <c r="N418" s="54">
+        <v>971</v>
+      </c>
       <c r="O418" s="18"/>
       <c r="P418" s="18"/>
       <c r="Q418" s="11">
@@ -27924,7 +28392,9 @@
       </c>
       <c r="L421" s="18"/>
       <c r="M421" s="18"/>
-      <c r="N421" s="40"/>
+      <c r="N421" s="54">
+        <v>903</v>
+      </c>
       <c r="O421" s="18"/>
       <c r="P421" s="18"/>
       <c r="Q421" s="11">
@@ -28597,7 +29067,9 @@
       <c r="N435" s="54">
         <v>263</v>
       </c>
-      <c r="O435" s="18"/>
+      <c r="O435" s="53">
+        <v>46244</v>
+      </c>
       <c r="P435" s="18"/>
       <c r="Q435" s="11">
         <v>90930841</v>
@@ -30206,7 +30678,9 @@
         <v>46250</v>
       </c>
       <c r="M468" s="18"/>
-      <c r="N468" s="40"/>
+      <c r="N468" s="54">
+        <v>957</v>
+      </c>
       <c r="O468" s="18"/>
       <c r="P468" s="18"/>
       <c r="Q468" s="18"/>
@@ -30250,7 +30724,9 @@
       </c>
       <c r="L469" s="18"/>
       <c r="M469" s="18"/>
-      <c r="N469" s="40"/>
+      <c r="N469" s="54">
+        <v>960</v>
+      </c>
       <c r="O469" s="18"/>
       <c r="P469" s="18"/>
       <c r="Q469" s="18"/>
@@ -30294,7 +30770,9 @@
         <v>46250</v>
       </c>
       <c r="M470" s="18"/>
-      <c r="N470" s="40"/>
+      <c r="N470" s="54">
+        <v>961</v>
+      </c>
       <c r="O470" s="18"/>
       <c r="P470" s="18"/>
       <c r="Q470" s="18"/>
@@ -30384,7 +30862,9 @@
       </c>
       <c r="L472" s="18"/>
       <c r="M472" s="18"/>
-      <c r="N472" s="40"/>
+      <c r="N472" s="54">
+        <v>962</v>
+      </c>
       <c r="O472" s="18"/>
       <c r="P472" s="18"/>
       <c r="Q472" s="18"/>
@@ -31534,7 +32014,9 @@
       </c>
       <c r="L497" s="18"/>
       <c r="M497" s="18"/>
-      <c r="N497" s="40"/>
+      <c r="N497" s="54">
+        <v>1020</v>
+      </c>
       <c r="O497" s="18"/>
       <c r="P497" s="18"/>
       <c r="Q497" s="11">
@@ -31866,7 +32348,9 @@
       </c>
       <c r="L504" s="18"/>
       <c r="M504" s="18"/>
-      <c r="N504" s="40"/>
+      <c r="N504" s="54">
+        <v>1018</v>
+      </c>
       <c r="O504" s="18"/>
       <c r="P504" s="18"/>
       <c r="Q504" s="11">
@@ -32534,10 +33018,14 @@
       </c>
       <c r="L518" s="18"/>
       <c r="M518" s="18"/>
-      <c r="N518" s="40"/>
+      <c r="N518" s="54">
+        <v>992</v>
+      </c>
       <c r="O518" s="18"/>
       <c r="P518" s="18"/>
-      <c r="Q518" s="18"/>
+      <c r="Q518" s="11">
+        <v>77312349</v>
+      </c>
       <c r="R518" s="20" t="s">
         <v>11</v>
       </c>
@@ -33534,7 +34022,9 @@
         <v>46250</v>
       </c>
       <c r="M539" s="18"/>
-      <c r="N539" s="40"/>
+      <c r="N539" s="54">
+        <v>1031</v>
+      </c>
       <c r="O539" s="18"/>
       <c r="P539" s="18"/>
       <c r="Q539" s="18"/>
@@ -33580,7 +34070,9 @@
         <v>46250</v>
       </c>
       <c r="M540" s="18"/>
-      <c r="N540" s="40"/>
+      <c r="N540" s="54">
+        <v>900</v>
+      </c>
       <c r="O540" s="18"/>
       <c r="P540" s="18"/>
       <c r="Q540" s="18"/>
@@ -33769,7 +34261,9 @@
       <c r="N544" s="54">
         <v>373</v>
       </c>
-      <c r="O544" s="18"/>
+      <c r="O544" s="53">
+        <v>46245</v>
+      </c>
       <c r="P544" s="18"/>
       <c r="Q544" s="11">
         <v>95199535</v>
@@ -34204,7 +34698,9 @@
         <v>46250</v>
       </c>
       <c r="M553" s="18"/>
-      <c r="N553" s="40"/>
+      <c r="N553" s="54">
+        <v>911</v>
+      </c>
       <c r="O553" s="18"/>
       <c r="P553" s="18"/>
       <c r="Q553" s="18"/>
@@ -35590,7 +36086,9 @@
       </c>
       <c r="L582" s="18"/>
       <c r="M582" s="18"/>
-      <c r="N582" s="40"/>
+      <c r="N582" s="54">
+        <v>994</v>
+      </c>
       <c r="O582" s="18"/>
       <c r="P582" s="18"/>
       <c r="Q582" s="15">
@@ -35638,7 +36136,9 @@
         <v>46250</v>
       </c>
       <c r="M583" s="18"/>
-      <c r="N583" s="40"/>
+      <c r="N583" s="54">
+        <v>995</v>
+      </c>
       <c r="O583" s="18"/>
       <c r="P583" s="18"/>
       <c r="Q583" s="15">
@@ -35880,7 +36380,9 @@
         <v>46250</v>
       </c>
       <c r="M588" s="18"/>
-      <c r="N588" s="40"/>
+      <c r="N588" s="54">
+        <v>989</v>
+      </c>
       <c r="O588" s="18"/>
       <c r="P588" s="18"/>
       <c r="Q588" s="15">
@@ -35928,7 +36430,9 @@
         <v>46250</v>
       </c>
       <c r="M589" s="18"/>
-      <c r="N589" s="40"/>
+      <c r="N589" s="54">
+        <v>988</v>
+      </c>
       <c r="O589" s="18"/>
       <c r="P589" s="18"/>
       <c r="Q589" s="15">
@@ -35979,7 +36483,9 @@
       <c r="N590" s="54">
         <v>266</v>
       </c>
-      <c r="O590" s="18"/>
+      <c r="O590" s="53">
+        <v>46245</v>
+      </c>
       <c r="P590" s="18"/>
       <c r="Q590" s="15">
         <v>76042698</v>
@@ -36026,7 +36532,9 @@
         <v>46250</v>
       </c>
       <c r="M591" s="18"/>
-      <c r="N591" s="40"/>
+      <c r="N591" s="54">
+        <v>990</v>
+      </c>
       <c r="O591" s="18"/>
       <c r="P591" s="18"/>
       <c r="Q591" s="15">
@@ -36077,7 +36585,9 @@
       <c r="N592" s="54">
         <v>337</v>
       </c>
-      <c r="O592" s="18"/>
+      <c r="O592" s="53">
+        <v>46245</v>
+      </c>
       <c r="P592" s="18"/>
       <c r="Q592" s="15">
         <v>78476249</v>
@@ -36166,7 +36676,9 @@
       </c>
       <c r="L594" s="18"/>
       <c r="M594" s="18"/>
-      <c r="N594" s="40"/>
+      <c r="N594" s="54">
+        <v>917</v>
+      </c>
       <c r="O594" s="18"/>
       <c r="P594" s="18"/>
       <c r="Q594" s="15">
@@ -37787,7 +38299,9 @@
       <c r="N628" s="54">
         <v>275</v>
       </c>
-      <c r="O628" s="18"/>
+      <c r="O628" s="53">
+        <v>46244</v>
+      </c>
       <c r="P628" s="18"/>
       <c r="Q628" s="15">
         <v>94063515</v>
@@ -38406,7 +38920,9 @@
       </c>
       <c r="L641" s="18"/>
       <c r="M641" s="18"/>
-      <c r="N641" s="40"/>
+      <c r="N641" s="54">
+        <v>959</v>
+      </c>
       <c r="O641" s="18"/>
       <c r="P641" s="18"/>
       <c r="Q641" s="15">
@@ -38452,7 +38968,9 @@
       </c>
       <c r="L642" s="18"/>
       <c r="M642" s="18"/>
-      <c r="N642" s="40"/>
+      <c r="N642" s="54">
+        <v>958</v>
+      </c>
       <c r="O642" s="18"/>
       <c r="P642" s="18"/>
       <c r="Q642" s="15">
@@ -38546,7 +39064,9 @@
       </c>
       <c r="L644" s="18"/>
       <c r="M644" s="18"/>
-      <c r="N644" s="40"/>
+      <c r="N644" s="54">
+        <v>991</v>
+      </c>
       <c r="O644" s="18"/>
       <c r="P644" s="18"/>
       <c r="Q644" s="15">
@@ -38732,7 +39252,9 @@
       </c>
       <c r="L648" s="18"/>
       <c r="M648" s="18"/>
-      <c r="N648" s="40"/>
+      <c r="N648" s="54">
+        <v>1001</v>
+      </c>
       <c r="O648" s="18"/>
       <c r="P648" s="18"/>
       <c r="Q648" s="15">
@@ -38827,7 +39349,9 @@
       <c r="N650" s="54">
         <v>265</v>
       </c>
-      <c r="O650" s="18"/>
+      <c r="O650" s="53">
+        <v>46244</v>
+      </c>
       <c r="P650" s="18"/>
       <c r="Q650" s="15">
         <v>79273422</v>
@@ -39676,7 +40200,9 @@
       </c>
       <c r="L668" s="18"/>
       <c r="M668" s="18"/>
-      <c r="N668" s="40"/>
+      <c r="N668" s="54">
+        <v>818</v>
+      </c>
       <c r="O668" s="18"/>
       <c r="P668" s="18"/>
       <c r="Q668" s="11">
@@ -39906,7 +40432,9 @@
       </c>
       <c r="L673" s="18"/>
       <c r="M673" s="18"/>
-      <c r="N673" s="40"/>
+      <c r="N673" s="54">
+        <v>819</v>
+      </c>
       <c r="O673" s="18"/>
       <c r="P673" s="18"/>
       <c r="Q673" s="11">
@@ -40153,7 +40681,9 @@
       <c r="N678" s="54">
         <v>216</v>
       </c>
-      <c r="O678" s="18"/>
+      <c r="O678" s="53">
+        <v>46244</v>
+      </c>
       <c r="P678" s="18"/>
       <c r="Q678" s="11">
         <v>563491256</v>
@@ -40486,7 +41016,9 @@
       </c>
       <c r="L685" s="18"/>
       <c r="M685" s="18"/>
-      <c r="N685" s="40"/>
+      <c r="N685" s="54">
+        <v>839</v>
+      </c>
       <c r="O685" s="18"/>
       <c r="P685" s="18"/>
       <c r="Q685" s="11">
@@ -42487,7 +43019,9 @@
       <c r="N728" s="54">
         <v>241</v>
       </c>
-      <c r="O728" s="18"/>
+      <c r="O728" s="53">
+        <v>46244</v>
+      </c>
       <c r="P728" s="18"/>
       <c r="Q728" s="15">
         <v>77593415</v>
@@ -42535,7 +43069,9 @@
       <c r="N729" s="54">
         <v>242</v>
       </c>
-      <c r="O729" s="18"/>
+      <c r="O729" s="53">
+        <v>46244</v>
+      </c>
       <c r="P729" s="18"/>
       <c r="Q729" s="15">
         <v>76784647</v>
@@ -42631,7 +43167,9 @@
       <c r="N731" s="54">
         <v>236</v>
       </c>
-      <c r="O731" s="18"/>
+      <c r="O731" s="53">
+        <v>46244</v>
+      </c>
       <c r="P731" s="18"/>
       <c r="Q731" s="15">
         <v>527875541</v>
@@ -43442,8 +43980,8 @@
       </c>
       <c r="L748" s="18"/>
       <c r="M748" s="18"/>
-      <c r="N748" s="54">
-        <v>2</v>
+      <c r="N748" s="79" t="s">
+        <v>2265</v>
       </c>
       <c r="O748" s="53">
         <v>46244</v>
@@ -43540,8 +44078,8 @@
       </c>
       <c r="L750" s="18"/>
       <c r="M750" s="18"/>
-      <c r="N750" s="54">
-        <v>4</v>
+      <c r="N750" s="79" t="s">
+        <v>2266</v>
       </c>
       <c r="O750" s="53">
         <v>46244</v>
@@ -43590,8 +44128,8 @@
       </c>
       <c r="L751" s="18"/>
       <c r="M751" s="18"/>
-      <c r="N751" s="54">
-        <v>5</v>
+      <c r="N751" s="79" t="s">
+        <v>2267</v>
       </c>
       <c r="O751" s="53">
         <v>46244</v>
@@ -43989,7 +44527,9 @@
       <c r="N759" s="54" t="s">
         <v>1206</v>
       </c>
-      <c r="O759" s="18"/>
+      <c r="O759" s="53">
+        <v>46244</v>
+      </c>
       <c r="P759" s="62" t="s">
         <v>1204</v>
       </c>
@@ -45657,7 +46197,9 @@
       <c r="N794" s="54">
         <v>357</v>
       </c>
-      <c r="O794" s="18"/>
+      <c r="O794" s="53">
+        <v>46245</v>
+      </c>
       <c r="P794" s="18"/>
       <c r="Q794" s="11">
         <v>95571607</v>
@@ -45707,7 +46249,9 @@
       <c r="N795" s="54">
         <v>325</v>
       </c>
-      <c r="O795" s="18"/>
+      <c r="O795" s="53">
+        <v>46245</v>
+      </c>
       <c r="P795" s="18"/>
       <c r="Q795" s="18"/>
       <c r="R795" s="20" t="s">
@@ -45753,7 +46297,9 @@
       <c r="N796" s="54">
         <v>359</v>
       </c>
-      <c r="O796" s="18"/>
+      <c r="O796" s="53">
+        <v>46244</v>
+      </c>
       <c r="P796" s="18"/>
       <c r="Q796" s="18"/>
       <c r="R796" s="20" t="s">
@@ -45801,7 +46347,9 @@
       <c r="N797" s="54">
         <v>306</v>
       </c>
-      <c r="O797" s="18"/>
+      <c r="O797" s="53">
+        <v>46244</v>
+      </c>
       <c r="P797" s="18"/>
       <c r="Q797" s="18"/>
       <c r="R797" s="20" t="s">
@@ -45849,7 +46397,9 @@
       <c r="N798" s="54">
         <v>330</v>
       </c>
-      <c r="O798" s="18"/>
+      <c r="O798" s="53">
+        <v>46245</v>
+      </c>
       <c r="P798" s="18"/>
       <c r="Q798" s="11">
         <v>95704619</v>
@@ -45997,7 +46547,9 @@
       <c r="N801" s="54">
         <v>327</v>
       </c>
-      <c r="O801" s="18"/>
+      <c r="O801" s="53">
+        <v>46245</v>
+      </c>
       <c r="P801" s="18"/>
       <c r="Q801" s="11" t="s">
         <v>1314</v>
@@ -46047,7 +46599,9 @@
       <c r="N802" s="54">
         <v>324</v>
       </c>
-      <c r="O802" s="18"/>
+      <c r="O802" s="53">
+        <v>46245</v>
+      </c>
       <c r="P802" s="18"/>
       <c r="Q802" s="11">
         <v>77830428</v>
@@ -46243,7 +46797,9 @@
       <c r="N806" s="54">
         <v>320</v>
       </c>
-      <c r="O806" s="18"/>
+      <c r="O806" s="53">
+        <v>46244</v>
+      </c>
       <c r="P806" s="18"/>
       <c r="Q806" s="18"/>
       <c r="R806" s="20" t="s">
@@ -46291,7 +46847,9 @@
       <c r="N807" s="54">
         <v>329</v>
       </c>
-      <c r="O807" s="18"/>
+      <c r="O807" s="53">
+        <v>46244</v>
+      </c>
       <c r="P807" s="18"/>
       <c r="Q807" s="18"/>
       <c r="R807" s="20" t="s">
@@ -46524,7 +47082,7 @@
       </c>
       <c r="L812" s="18"/>
       <c r="M812" s="18"/>
-      <c r="N812" s="54" t="s">
+      <c r="N812" s="76" t="s">
         <v>2123</v>
       </c>
       <c r="O812" s="18"/>
@@ -46660,7 +47218,9 @@
       </c>
       <c r="L815" s="18"/>
       <c r="M815" s="18"/>
-      <c r="N815" s="40"/>
+      <c r="N815" s="54">
+        <v>1043</v>
+      </c>
       <c r="O815" s="18"/>
       <c r="P815" s="18"/>
       <c r="Q815" s="18"/>
@@ -46704,7 +47264,9 @@
       </c>
       <c r="L816" s="18"/>
       <c r="M816" s="18"/>
-      <c r="N816" s="40"/>
+      <c r="N816" s="54">
+        <v>1044</v>
+      </c>
       <c r="O816" s="18"/>
       <c r="P816" s="18"/>
       <c r="Q816" s="11">
@@ -46750,7 +47312,9 @@
       </c>
       <c r="L817" s="18"/>
       <c r="M817" s="18"/>
-      <c r="N817" s="40"/>
+      <c r="N817" s="54">
+        <v>950</v>
+      </c>
       <c r="O817" s="18"/>
       <c r="P817" s="18"/>
       <c r="Q817" s="11">
@@ -46941,7 +47505,9 @@
       <c r="N821" s="54">
         <v>280</v>
       </c>
-      <c r="O821" s="18"/>
+      <c r="O821" s="53">
+        <v>46244</v>
+      </c>
       <c r="P821" s="18"/>
       <c r="Q821" s="18"/>
       <c r="R821" s="20" t="s">
@@ -47081,7 +47647,9 @@
       <c r="N824" s="54">
         <v>294</v>
       </c>
-      <c r="O824" s="18"/>
+      <c r="O824" s="53">
+        <v>46244</v>
+      </c>
       <c r="P824" s="18"/>
       <c r="Q824" s="11">
         <v>77615320</v>
@@ -47129,7 +47697,9 @@
       <c r="N825" s="54">
         <v>295</v>
       </c>
-      <c r="O825" s="18"/>
+      <c r="O825" s="53">
+        <v>46245</v>
+      </c>
       <c r="P825" s="18"/>
       <c r="Q825" s="18"/>
       <c r="R825" s="20" t="s">
@@ -47411,7 +47981,9 @@
       <c r="N831" s="54">
         <v>332</v>
       </c>
-      <c r="O831" s="18"/>
+      <c r="O831" s="53">
+        <v>46245</v>
+      </c>
       <c r="P831" s="18"/>
       <c r="Q831" s="18"/>
       <c r="R831" s="20" t="s">
@@ -47550,7 +48122,9 @@
         <v>46250</v>
       </c>
       <c r="M834" s="18"/>
-      <c r="N834" s="40"/>
+      <c r="N834" s="54">
+        <v>835</v>
+      </c>
       <c r="O834" s="18"/>
       <c r="P834" s="18"/>
       <c r="Q834" s="11" t="s">
@@ -47598,7 +48172,9 @@
         <v>46250</v>
       </c>
       <c r="M835" s="18"/>
-      <c r="N835" s="40"/>
+      <c r="N835" s="54">
+        <v>834</v>
+      </c>
       <c r="O835" s="18"/>
       <c r="P835" s="18"/>
       <c r="Q835" s="11">
@@ -47738,7 +48314,9 @@
         <v>46250</v>
       </c>
       <c r="M838" s="18"/>
-      <c r="N838" s="40"/>
+      <c r="N838" s="54">
+        <v>1007</v>
+      </c>
       <c r="O838" s="18"/>
       <c r="P838" s="18"/>
       <c r="Q838" s="18"/>
@@ -47874,10 +48452,14 @@
         <v>46250</v>
       </c>
       <c r="M841" s="18"/>
-      <c r="N841" s="40"/>
+      <c r="N841" s="54">
+        <v>1010</v>
+      </c>
       <c r="O841" s="18"/>
       <c r="P841" s="18"/>
-      <c r="Q841" s="18"/>
+      <c r="Q841" s="11">
+        <v>90297193</v>
+      </c>
       <c r="R841" s="20" t="s">
         <v>11</v>
       </c>
@@ -48244,7 +48826,9 @@
         <v>46250</v>
       </c>
       <c r="M849" s="18"/>
-      <c r="N849" s="40"/>
+      <c r="N849" s="54">
+        <v>1006</v>
+      </c>
       <c r="O849" s="18"/>
       <c r="P849" s="18"/>
       <c r="Q849" s="18"/>
@@ -48426,7 +49010,9 @@
       </c>
       <c r="L853" s="18"/>
       <c r="M853" s="18"/>
-      <c r="N853" s="40"/>
+      <c r="N853" s="54">
+        <v>836</v>
+      </c>
       <c r="O853" s="18"/>
       <c r="P853" s="18"/>
       <c r="Q853" s="11">
@@ -48900,7 +49486,9 @@
       </c>
       <c r="L863" s="18"/>
       <c r="M863" s="18"/>
-      <c r="N863" s="40"/>
+      <c r="N863" s="54">
+        <v>973</v>
+      </c>
       <c r="O863" s="18"/>
       <c r="P863" s="18"/>
       <c r="Q863" s="11">
@@ -49078,10 +49666,14 @@
       </c>
       <c r="L867" s="18"/>
       <c r="M867" s="18"/>
-      <c r="N867" s="40"/>
+      <c r="N867" s="54">
+        <v>1011</v>
+      </c>
       <c r="O867" s="18"/>
       <c r="P867" s="18"/>
-      <c r="Q867" s="18"/>
+      <c r="Q867" s="11">
+        <v>93880771</v>
+      </c>
       <c r="R867" s="20" t="s">
         <v>11</v>
       </c>
@@ -49356,7 +49948,9 @@
       </c>
       <c r="L873" s="18"/>
       <c r="M873" s="18"/>
-      <c r="N873" s="40"/>
+      <c r="N873" s="54">
+        <v>968</v>
+      </c>
       <c r="O873" s="18"/>
       <c r="P873" s="18"/>
       <c r="Q873" s="11">
@@ -49400,7 +49994,9 @@
       </c>
       <c r="L874" s="18"/>
       <c r="M874" s="18"/>
-      <c r="N874" s="40"/>
+      <c r="N874" s="54">
+        <v>970</v>
+      </c>
       <c r="O874" s="18"/>
       <c r="P874" s="18"/>
       <c r="Q874" s="18"/>
@@ -49720,7 +50316,9 @@
       </c>
       <c r="L881" s="18"/>
       <c r="M881" s="18"/>
-      <c r="N881" s="40"/>
+      <c r="N881" s="54">
+        <v>1030</v>
+      </c>
       <c r="O881" s="18"/>
       <c r="P881" s="18"/>
       <c r="Q881" s="11">
@@ -50615,7 +51213,9 @@
       <c r="L900" s="18"/>
       <c r="M900" s="18"/>
       <c r="N900" s="40"/>
-      <c r="O900" s="18"/>
+      <c r="O900" s="53">
+        <v>46244</v>
+      </c>
       <c r="P900" s="18"/>
       <c r="Q900" s="18"/>
       <c r="R900" s="21" t="s">
@@ -50747,7 +51347,9 @@
       <c r="L903" s="18"/>
       <c r="M903" s="18"/>
       <c r="N903" s="40"/>
-      <c r="O903" s="18"/>
+      <c r="O903" s="15" t="s">
+        <v>2268</v>
+      </c>
       <c r="P903" s="18"/>
       <c r="Q903" s="18"/>
       <c r="R903" s="21" t="s">
@@ -50933,7 +51535,9 @@
       <c r="L907" s="18"/>
       <c r="M907" s="18"/>
       <c r="N907" s="40"/>
-      <c r="O907" s="18"/>
+      <c r="O907" s="53">
+        <v>46245</v>
+      </c>
       <c r="P907" s="18"/>
       <c r="Q907" s="18"/>
       <c r="R907" s="21" t="s">
@@ -50977,7 +51581,9 @@
       <c r="L908" s="18"/>
       <c r="M908" s="18"/>
       <c r="N908" s="40"/>
-      <c r="O908" s="18"/>
+      <c r="O908" s="53">
+        <v>46245</v>
+      </c>
       <c r="P908" s="18"/>
       <c r="Q908" s="18"/>
       <c r="R908" s="21" t="s">
@@ -51021,7 +51627,9 @@
       <c r="L909" s="18"/>
       <c r="M909" s="18"/>
       <c r="N909" s="40"/>
-      <c r="O909" s="18"/>
+      <c r="O909" s="53">
+        <v>46245</v>
+      </c>
       <c r="P909" s="18"/>
       <c r="Q909" s="18"/>
       <c r="R909" s="21" t="s">
@@ -51065,7 +51673,9 @@
       <c r="L910" s="18"/>
       <c r="M910" s="18"/>
       <c r="N910" s="40"/>
-      <c r="O910" s="18"/>
+      <c r="O910" s="53">
+        <v>46245</v>
+      </c>
       <c r="P910" s="18"/>
       <c r="Q910" s="18"/>
       <c r="R910" s="21" t="s">
@@ -51109,7 +51719,9 @@
       <c r="L911" s="18"/>
       <c r="M911" s="18"/>
       <c r="N911" s="40"/>
-      <c r="O911" s="18"/>
+      <c r="O911" s="53">
+        <v>46245</v>
+      </c>
       <c r="P911" s="18"/>
       <c r="Q911" s="18"/>
       <c r="R911" s="21" t="s">
@@ -51430,7 +52042,9 @@
       </c>
       <c r="L918" s="18"/>
       <c r="M918" s="18"/>
-      <c r="N918" s="40"/>
+      <c r="N918" s="54">
+        <v>892</v>
+      </c>
       <c r="O918" s="18"/>
       <c r="P918" s="18"/>
       <c r="Q918" s="18"/>
@@ -51907,7 +52521,9 @@
       <c r="N928" s="54">
         <v>491</v>
       </c>
-      <c r="O928" s="18"/>
+      <c r="O928" s="53">
+        <v>46244</v>
+      </c>
       <c r="P928" s="18"/>
       <c r="Q928" s="18"/>
       <c r="R928" s="22" t="s">
@@ -51999,7 +52615,9 @@
       <c r="N930" s="54">
         <v>488</v>
       </c>
-      <c r="O930" s="18"/>
+      <c r="O930" s="53">
+        <v>46244</v>
+      </c>
       <c r="P930" s="18"/>
       <c r="Q930" s="18"/>
       <c r="R930" s="22" t="s">
@@ -52091,7 +52709,9 @@
       <c r="N932" s="54">
         <v>487</v>
       </c>
-      <c r="O932" s="18"/>
+      <c r="O932" s="53">
+        <v>46244</v>
+      </c>
       <c r="P932" s="18"/>
       <c r="Q932" s="15">
         <v>92041492</v>
@@ -52137,7 +52757,9 @@
       <c r="L933" s="18"/>
       <c r="M933" s="18"/>
       <c r="N933" s="40"/>
-      <c r="O933" s="18"/>
+      <c r="O933" s="53">
+        <v>46244</v>
+      </c>
       <c r="P933" s="18"/>
       <c r="Q933" s="18"/>
       <c r="R933" s="22" t="s">
@@ -52378,7 +53000,9 @@
       </c>
       <c r="L938" s="18"/>
       <c r="M938" s="18"/>
-      <c r="N938" s="40"/>
+      <c r="N938" s="54">
+        <v>1036</v>
+      </c>
       <c r="O938" s="18"/>
       <c r="P938" s="18"/>
       <c r="Q938" s="18"/>
@@ -52422,7 +53046,9 @@
       </c>
       <c r="L939" s="18"/>
       <c r="M939" s="18"/>
-      <c r="N939" s="40"/>
+      <c r="N939" s="54">
+        <v>1035</v>
+      </c>
       <c r="O939" s="18"/>
       <c r="P939" s="18"/>
       <c r="Q939" s="18"/>
@@ -52742,7 +53368,9 @@
       </c>
       <c r="L946" s="18"/>
       <c r="M946" s="18"/>
-      <c r="N946" s="40"/>
+      <c r="N946" s="54">
+        <v>986</v>
+      </c>
       <c r="O946" s="18"/>
       <c r="P946" s="18"/>
       <c r="Q946" s="15">
@@ -52788,7 +53416,9 @@
       </c>
       <c r="L947" s="18"/>
       <c r="M947" s="18"/>
-      <c r="N947" s="40"/>
+      <c r="N947" s="54">
+        <v>987</v>
+      </c>
       <c r="O947" s="18"/>
       <c r="P947" s="18"/>
       <c r="Q947" s="15">
@@ -52885,7 +53515,9 @@
       <c r="N949" s="54">
         <v>385</v>
       </c>
-      <c r="O949" s="18"/>
+      <c r="O949" s="53">
+        <v>46245</v>
+      </c>
       <c r="P949" s="18"/>
       <c r="Q949" s="15">
         <v>92155296</v>
@@ -52983,7 +53615,9 @@
       <c r="N951" s="54">
         <v>393</v>
       </c>
-      <c r="O951" s="18"/>
+      <c r="O951" s="53">
+        <v>46245</v>
+      </c>
       <c r="P951" s="18"/>
       <c r="Q951" s="15">
         <v>95819273</v>
@@ -53077,7 +53711,9 @@
       <c r="N953" s="54">
         <v>386</v>
       </c>
-      <c r="O953" s="18"/>
+      <c r="O953" s="53">
+        <v>46245</v>
+      </c>
       <c r="P953" s="18"/>
       <c r="Q953" s="15">
         <v>99102728</v>
@@ -53992,7 +54628,9 @@
         <v>46250</v>
       </c>
       <c r="M972" s="18"/>
-      <c r="N972" s="40"/>
+      <c r="N972" s="54">
+        <v>1009</v>
+      </c>
       <c r="O972" s="18"/>
       <c r="P972" s="18"/>
       <c r="Q972" s="15">
@@ -54284,7 +54922,9 @@
         <v>46250</v>
       </c>
       <c r="M978" s="18"/>
-      <c r="N978" s="40"/>
+      <c r="N978" s="54">
+        <v>846</v>
+      </c>
       <c r="O978" s="18"/>
       <c r="P978" s="18"/>
       <c r="Q978" s="15">
@@ -55119,7 +55759,9 @@
       <c r="N995" s="54">
         <v>177</v>
       </c>
-      <c r="O995" s="18"/>
+      <c r="O995" s="53">
+        <v>46244</v>
+      </c>
       <c r="P995" s="18"/>
       <c r="Q995" s="15">
         <v>77462308</v>
@@ -55164,7 +55806,9 @@
       </c>
       <c r="L996" s="18"/>
       <c r="M996" s="18"/>
-      <c r="N996" s="40"/>
+      <c r="N996" s="54">
+        <v>916</v>
+      </c>
       <c r="O996" s="18"/>
       <c r="P996" s="18"/>
       <c r="Q996" s="15">
@@ -55537,15 +56181,19 @@
       <c r="J1004" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1004" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1004" s="18"/>
+      <c r="K1004" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1004" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1004" s="18"/>
       <c r="N1004" s="54">
         <v>123</v>
       </c>
-      <c r="O1004" s="18"/>
+      <c r="O1004" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1004" s="18"/>
       <c r="Q1004" s="15">
         <v>95672061</v>
@@ -55585,15 +56233,19 @@
       <c r="J1005" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1005" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1005" s="18"/>
+      <c r="K1005" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1005" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1005" s="18"/>
       <c r="N1005" s="54">
         <v>124</v>
       </c>
-      <c r="O1005" s="18"/>
+      <c r="O1005" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1005" s="18"/>
       <c r="Q1005" s="15">
         <v>78474305</v>
@@ -55641,7 +56293,9 @@
       <c r="N1006" s="54">
         <v>117</v>
       </c>
-      <c r="O1006" s="18"/>
+      <c r="O1006" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1006" s="18"/>
       <c r="Q1006" s="15">
         <v>97179088</v>
@@ -55829,7 +56483,9 @@
       <c r="N1010" s="54">
         <v>288</v>
       </c>
-      <c r="O1010" s="18"/>
+      <c r="O1010" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1010" s="18"/>
       <c r="Q1010" s="15">
         <v>99545249</v>
@@ -55969,7 +56625,9 @@
       <c r="N1013" s="54">
         <v>287</v>
       </c>
-      <c r="O1013" s="18"/>
+      <c r="O1013" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1013" s="18"/>
       <c r="Q1013" s="15">
         <v>77376103</v>
@@ -56057,10 +56715,12 @@
       <c r="J1015" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1015" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1015" s="38"/>
+      <c r="K1015" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1015" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1015" s="18"/>
       <c r="N1015" s="40"/>
       <c r="O1015" s="18"/>
@@ -56103,12 +56763,16 @@
       <c r="J1016" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1016" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1016" s="38"/>
+      <c r="K1016" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1016" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1016" s="18"/>
-      <c r="N1016" s="40"/>
+      <c r="N1016" s="54">
+        <v>848</v>
+      </c>
       <c r="O1016" s="18"/>
       <c r="P1016" s="18"/>
       <c r="Q1016" s="15">
@@ -56149,10 +56813,12 @@
       <c r="J1017" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1017" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1017" s="38"/>
+      <c r="K1017" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1017" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1017" s="18"/>
       <c r="N1017" s="54">
         <v>354</v>
@@ -56195,10 +56861,12 @@
       <c r="J1018" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1018" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1018" s="38"/>
+      <c r="K1018" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1018" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1018" s="18"/>
       <c r="N1018" s="54">
         <v>814</v>
@@ -56243,10 +56911,12 @@
       <c r="J1019" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1019" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1019" s="38"/>
+      <c r="K1019" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1019" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1019" s="18"/>
       <c r="N1019" s="40"/>
       <c r="O1019" s="18"/>
@@ -56289,10 +56959,12 @@
       <c r="J1020" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1020" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1020" s="38"/>
+      <c r="K1020" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1020" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1020" s="18"/>
       <c r="N1020" s="40"/>
       <c r="O1020" s="18"/>
@@ -56335,10 +57007,12 @@
       <c r="J1021" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1021" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1021" s="38"/>
+      <c r="K1021" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1021" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1021" s="18"/>
       <c r="N1021" s="40"/>
       <c r="O1021" s="18"/>
@@ -56381,10 +57055,12 @@
       <c r="J1022" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1022" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1022" s="38"/>
+      <c r="K1022" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1022" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1022" s="18"/>
       <c r="N1022" s="40"/>
       <c r="O1022" s="18"/>
@@ -56427,10 +57103,12 @@
       <c r="J1023" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1023" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1023" s="38"/>
+      <c r="K1023" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1023" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1023" s="18"/>
       <c r="N1023" s="54">
         <v>352</v>
@@ -56475,10 +57153,12 @@
       <c r="J1024" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1024" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1024" s="38"/>
+      <c r="K1024" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1024" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1024" s="18"/>
       <c r="N1024" s="54">
         <v>673</v>
@@ -56862,10 +57542,14 @@
       </c>
       <c r="L1032" s="38"/>
       <c r="M1032" s="18"/>
-      <c r="N1032" s="40"/>
+      <c r="N1032" s="54">
+        <v>838</v>
+      </c>
       <c r="O1032" s="18"/>
       <c r="P1032" s="18"/>
-      <c r="Q1032" s="18"/>
+      <c r="Q1032" s="15">
+        <v>77373859</v>
+      </c>
       <c r="R1032" s="22" t="s">
         <v>131</v>
       </c>
@@ -57284,7 +57968,9 @@
       </c>
       <c r="L1041" s="38"/>
       <c r="M1041" s="18"/>
-      <c r="N1041" s="40"/>
+      <c r="N1041" s="54">
+        <v>837</v>
+      </c>
       <c r="O1041" s="18"/>
       <c r="P1041" s="18"/>
       <c r="Q1041" s="15">
@@ -57333,7 +58019,9 @@
       <c r="N1042" s="54">
         <v>195</v>
       </c>
-      <c r="O1042" s="18"/>
+      <c r="O1042" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1042" s="18"/>
       <c r="Q1042" s="15">
         <v>95285611</v>
@@ -57747,10 +58435,12 @@
       <c r="J1051" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1051" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1051" s="18"/>
+      <c r="K1051" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1051" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1051" s="18"/>
       <c r="N1051" s="54">
         <v>419</v>
@@ -57795,10 +58485,12 @@
       <c r="J1052" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1052" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1052" s="18"/>
+      <c r="K1052" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1052" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1052" s="18"/>
       <c r="N1052" s="54">
         <v>635</v>
@@ -57843,10 +58535,12 @@
       <c r="J1053" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1053" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1053" s="18"/>
+      <c r="K1053" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1053" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1053" s="18"/>
       <c r="N1053" s="54">
         <v>603</v>
@@ -57891,10 +58585,12 @@
       <c r="J1054" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1054" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1054" s="18"/>
+      <c r="K1054" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1054" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1054" s="18"/>
       <c r="N1054" s="54">
         <v>783</v>
@@ -57939,10 +58635,12 @@
       <c r="J1055" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1055" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1055" s="18"/>
+      <c r="K1055" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1055" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1055" s="18"/>
       <c r="N1055" s="54">
         <v>613</v>
@@ -58035,10 +58733,12 @@
       <c r="J1057" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1057" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1057" s="18"/>
+      <c r="K1057" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1057" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1057" s="18"/>
       <c r="N1057" s="54">
         <v>614</v>
@@ -58081,10 +58781,12 @@
       <c r="J1058" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1058" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1058" s="18"/>
+      <c r="K1058" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1058" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1058" s="18"/>
       <c r="N1058" s="54">
         <v>615</v>
@@ -58127,10 +58829,12 @@
       <c r="J1059" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1059" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1059" s="18"/>
+      <c r="K1059" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1059" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1059" s="18"/>
       <c r="N1059" s="40"/>
       <c r="O1059" s="18"/>
@@ -58171,12 +58875,16 @@
       <c r="J1060" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1060" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1060" s="18"/>
+      <c r="K1060" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1060" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1060" s="18"/>
-      <c r="N1060" s="40"/>
+      <c r="N1060" s="54">
+        <v>936</v>
+      </c>
       <c r="O1060" s="18"/>
       <c r="P1060" s="18"/>
       <c r="Q1060" s="18"/>
@@ -58215,10 +58923,12 @@
       <c r="J1061" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1061" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1061" s="18"/>
+      <c r="K1061" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1061" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1061" s="18"/>
       <c r="N1061" s="54">
         <v>589</v>
@@ -58309,10 +59019,12 @@
       <c r="J1063" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1063" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1063" s="18"/>
+      <c r="K1063" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1063" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1063" s="18"/>
       <c r="N1063" s="54">
         <v>782</v>
@@ -58405,7 +59117,9 @@
       <c r="N1065" s="76" t="s">
         <v>2130</v>
       </c>
-      <c r="O1065" s="18"/>
+      <c r="O1065" s="53">
+        <v>46245</v>
+      </c>
       <c r="P1065" s="18"/>
       <c r="Q1065" s="11">
         <v>95889286</v>
@@ -58453,7 +59167,9 @@
       <c r="N1066" s="54">
         <v>348</v>
       </c>
-      <c r="O1066" s="18"/>
+      <c r="O1066" s="53">
+        <v>46245</v>
+      </c>
       <c r="P1066" s="18"/>
       <c r="Q1066" s="11">
         <v>96874108770</v>
@@ -58726,10 +59442,14 @@
       </c>
       <c r="L1072" s="18"/>
       <c r="M1072" s="18"/>
-      <c r="N1072" s="40"/>
+      <c r="N1072" s="54">
+        <v>825</v>
+      </c>
       <c r="O1072" s="18"/>
       <c r="P1072" s="18"/>
-      <c r="Q1072" s="18"/>
+      <c r="Q1072" s="11">
+        <v>95520693</v>
+      </c>
       <c r="R1072" s="22" t="s">
         <v>131</v>
       </c>
@@ -59806,10 +60526,14 @@
       </c>
       <c r="L1096" s="18"/>
       <c r="M1096" s="18"/>
-      <c r="N1096" s="40"/>
+      <c r="N1096" s="54">
+        <v>845</v>
+      </c>
       <c r="O1096" s="18"/>
       <c r="P1096" s="18"/>
-      <c r="Q1096" s="18"/>
+      <c r="Q1096" s="11">
+        <v>77481215</v>
+      </c>
       <c r="R1096" s="22" t="s">
         <v>131</v>
       </c>
@@ -59897,7 +60621,9 @@
       <c r="N1098" s="54">
         <v>302</v>
       </c>
-      <c r="O1098" s="18"/>
+      <c r="O1098" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1098" s="18"/>
       <c r="Q1098" s="18"/>
       <c r="R1098" s="22" t="s">
@@ -59943,7 +60669,9 @@
       <c r="N1099" s="54">
         <v>303</v>
       </c>
-      <c r="O1099" s="18"/>
+      <c r="O1099" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1099" s="18"/>
       <c r="Q1099" s="18"/>
       <c r="R1099" s="22" t="s">
@@ -59989,7 +60717,9 @@
       <c r="N1100" s="54">
         <v>301</v>
       </c>
-      <c r="O1100" s="18"/>
+      <c r="O1100" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1100" s="18"/>
       <c r="Q1100" s="18"/>
       <c r="R1100" s="22" t="s">
@@ -60157,7 +60887,9 @@
       <c r="N1104" s="54" t="s">
         <v>2132</v>
       </c>
-      <c r="O1104" s="18"/>
+      <c r="O1104" s="53">
+        <v>46245</v>
+      </c>
       <c r="P1104" s="18"/>
       <c r="Q1104" s="15">
         <v>97554041</v>
@@ -60205,7 +60937,9 @@
       <c r="N1105" s="54">
         <v>366</v>
       </c>
-      <c r="O1105" s="18"/>
+      <c r="O1105" s="53">
+        <v>46245</v>
+      </c>
       <c r="P1105" s="18"/>
       <c r="Q1105" s="15">
         <v>559595869</v>
@@ -60253,7 +60987,9 @@
       <c r="N1106" s="54">
         <v>367</v>
       </c>
-      <c r="O1106" s="18"/>
+      <c r="O1106" s="53">
+        <v>46245</v>
+      </c>
       <c r="P1106" s="18"/>
       <c r="Q1106" s="15" t="s">
         <v>1701</v>
@@ -60301,7 +61037,9 @@
       <c r="N1107" s="54">
         <v>370</v>
       </c>
-      <c r="O1107" s="18"/>
+      <c r="O1107" s="53">
+        <v>46245</v>
+      </c>
       <c r="P1107" s="18"/>
       <c r="Q1107" s="15">
         <v>76941165</v>
@@ -60578,7 +61316,9 @@
       </c>
       <c r="L1113" s="18"/>
       <c r="M1113" s="18"/>
-      <c r="N1113" s="40"/>
+      <c r="N1113" s="54">
+        <v>1012</v>
+      </c>
       <c r="O1113" s="18"/>
       <c r="P1113" s="18"/>
       <c r="Q1113" s="18"/>
@@ -60620,7 +61360,9 @@
       </c>
       <c r="L1114" s="18"/>
       <c r="M1114" s="18"/>
-      <c r="N1114" s="40"/>
+      <c r="N1114" s="54">
+        <v>946</v>
+      </c>
       <c r="O1114" s="18"/>
       <c r="P1114" s="18"/>
       <c r="Q1114" s="18"/>
@@ -62107,7 +62849,9 @@
       <c r="L1151" s="18"/>
       <c r="M1151" s="18"/>
       <c r="N1151" s="40"/>
-      <c r="O1151" s="18"/>
+      <c r="O1151" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1151" s="18"/>
       <c r="Q1151" s="18"/>
       <c r="R1151" s="22" t="s">
@@ -62307,7 +63051,9 @@
       <c r="L1156" s="18"/>
       <c r="M1156" s="18"/>
       <c r="N1156" s="40"/>
-      <c r="O1156" s="18"/>
+      <c r="O1156" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1156" s="18"/>
       <c r="Q1156" s="18"/>
       <c r="R1156" s="22" t="s">
@@ -62347,7 +63093,9 @@
       <c r="L1157" s="18"/>
       <c r="M1157" s="18"/>
       <c r="N1157" s="40"/>
-      <c r="O1157" s="18"/>
+      <c r="O1157" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1157" s="18"/>
       <c r="Q1157" s="18"/>
       <c r="R1157" s="22" t="s">
@@ -62387,7 +63135,9 @@
       <c r="L1158" s="18"/>
       <c r="M1158" s="18"/>
       <c r="N1158" s="40"/>
-      <c r="O1158" s="18"/>
+      <c r="O1158" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1158" s="18"/>
       <c r="Q1158" s="18"/>
       <c r="R1158" s="22" t="s">
@@ -62863,7 +63613,9 @@
       <c r="L1169" s="18"/>
       <c r="M1169" s="18"/>
       <c r="N1169" s="40"/>
-      <c r="O1169" s="18"/>
+      <c r="O1169" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1169" s="18"/>
       <c r="Q1169" s="55">
         <v>97966106</v>
@@ -62907,7 +63659,9 @@
       <c r="L1170" s="18"/>
       <c r="M1170" s="18"/>
       <c r="N1170" s="40"/>
-      <c r="O1170" s="18"/>
+      <c r="O1170" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1170" s="18"/>
       <c r="Q1170" s="55">
         <v>92315235</v>
@@ -62951,7 +63705,9 @@
       <c r="L1171" s="18"/>
       <c r="M1171" s="18"/>
       <c r="N1171" s="40"/>
-      <c r="O1171" s="18"/>
+      <c r="O1171" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1171" s="18"/>
       <c r="Q1171" s="55">
         <v>93651697</v>
@@ -63039,7 +63795,9 @@
       <c r="L1173" s="18"/>
       <c r="M1173" s="18"/>
       <c r="N1173" s="40"/>
-      <c r="O1173" s="18"/>
+      <c r="O1173" s="53">
+        <v>46245</v>
+      </c>
       <c r="P1173" s="18"/>
       <c r="Q1173" s="55">
         <v>99144513</v>
@@ -63127,7 +63885,9 @@
       <c r="L1175" s="18"/>
       <c r="M1175" s="18"/>
       <c r="N1175" s="40"/>
-      <c r="O1175" s="18"/>
+      <c r="O1175" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1175" s="18"/>
       <c r="Q1175" s="55">
         <v>96690774</v>
@@ -63348,7 +64108,9 @@
       </c>
       <c r="L1180" s="18"/>
       <c r="M1180" s="18"/>
-      <c r="N1180" s="40"/>
+      <c r="N1180" s="54">
+        <v>1022</v>
+      </c>
       <c r="O1180" s="18"/>
       <c r="P1180" s="18"/>
       <c r="Q1180" s="55">
@@ -63436,8 +64198,12 @@
       </c>
       <c r="L1182" s="18"/>
       <c r="M1182" s="18"/>
-      <c r="N1182" s="40"/>
-      <c r="O1182" s="18"/>
+      <c r="N1182" s="54">
+        <v>963</v>
+      </c>
+      <c r="O1182" s="53">
+        <v>46245</v>
+      </c>
       <c r="P1182" s="18"/>
       <c r="Q1182" s="55" t="s">
         <v>1826</v>
@@ -63525,7 +64291,9 @@
       <c r="L1184" s="18"/>
       <c r="M1184" s="18"/>
       <c r="N1184" s="40"/>
-      <c r="O1184" s="18"/>
+      <c r="O1184" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1184" s="18"/>
       <c r="Q1184" s="66">
         <v>97279697</v>
@@ -63568,7 +64336,9 @@
       </c>
       <c r="L1185" s="18"/>
       <c r="M1185" s="18"/>
-      <c r="N1185" s="40"/>
+      <c r="N1185" s="54">
+        <v>982</v>
+      </c>
       <c r="O1185" s="18"/>
       <c r="P1185" s="18"/>
       <c r="Q1185" s="55">
@@ -63656,7 +64426,9 @@
       </c>
       <c r="L1187" s="18"/>
       <c r="M1187" s="18"/>
-      <c r="N1187" s="40"/>
+      <c r="N1187" s="54">
+        <v>981</v>
+      </c>
       <c r="O1187" s="18"/>
       <c r="P1187" s="18"/>
       <c r="Q1187" s="72">
@@ -63933,7 +64705,9 @@
       <c r="L1193" s="18"/>
       <c r="M1193" s="18"/>
       <c r="N1193" s="40"/>
-      <c r="O1193" s="18"/>
+      <c r="O1193" s="53">
+        <v>46245</v>
+      </c>
       <c r="P1193" s="36" t="s">
         <v>1836</v>
       </c>
@@ -63979,7 +64753,9 @@
       <c r="L1194" s="18"/>
       <c r="M1194" s="18"/>
       <c r="N1194" s="40"/>
-      <c r="O1194" s="18"/>
+      <c r="O1194" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1194" s="36" t="s">
         <v>1839</v>
       </c>
@@ -64027,7 +64803,9 @@
       </c>
       <c r="M1195" s="18"/>
       <c r="N1195" s="40"/>
-      <c r="O1195" s="18"/>
+      <c r="O1195" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1195" s="36" t="s">
         <v>1839</v>
       </c>
@@ -64344,7 +65122,9 @@
         <v>46250</v>
       </c>
       <c r="M1202" s="18"/>
-      <c r="N1202" s="40"/>
+      <c r="N1202" s="54">
+        <v>974</v>
+      </c>
       <c r="O1202" s="18"/>
       <c r="P1202" s="18"/>
       <c r="Q1202" s="18"/>
@@ -64389,7 +65169,9 @@
       <c r="L1203" s="18"/>
       <c r="M1203" s="18"/>
       <c r="N1203" s="40"/>
-      <c r="O1203" s="18"/>
+      <c r="O1203" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1203" s="18"/>
       <c r="Q1203" s="18"/>
       <c r="R1203" s="21" t="s">
@@ -64477,7 +65259,9 @@
       <c r="L1205" s="18"/>
       <c r="M1205" s="18"/>
       <c r="N1205" s="40"/>
-      <c r="O1205" s="18"/>
+      <c r="O1205" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1205" s="18"/>
       <c r="Q1205" s="18"/>
       <c r="R1205" s="21" t="s">
@@ -64521,7 +65305,9 @@
       <c r="L1206" s="18"/>
       <c r="M1206" s="18"/>
       <c r="N1206" s="40"/>
-      <c r="O1206" s="18"/>
+      <c r="O1206" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1206" s="18"/>
       <c r="Q1206" s="18"/>
       <c r="R1206" s="21" t="s">
@@ -65330,7 +66116,9 @@
       </c>
       <c r="L1224" s="18"/>
       <c r="M1224" s="18"/>
-      <c r="N1224" s="40"/>
+      <c r="N1224" s="54">
+        <v>1015</v>
+      </c>
       <c r="O1224" s="18"/>
       <c r="P1224" s="18"/>
       <c r="Q1224" s="15">
@@ -65376,7 +66164,9 @@
       </c>
       <c r="L1225" s="18"/>
       <c r="M1225" s="18"/>
-      <c r="N1225" s="40"/>
+      <c r="N1225" s="54">
+        <v>815</v>
+      </c>
       <c r="O1225" s="18"/>
       <c r="P1225" s="18"/>
       <c r="Q1225" s="15">
@@ -65416,7 +66206,9 @@
         <v>46250</v>
       </c>
       <c r="M1226" s="18"/>
-      <c r="N1226" s="40"/>
+      <c r="N1226" s="54">
+        <v>816</v>
+      </c>
       <c r="O1226" s="18"/>
       <c r="P1226" s="18"/>
       <c r="Q1226" s="18"/>
@@ -65649,7 +66441,9 @@
       <c r="N1231" s="54">
         <v>321</v>
       </c>
-      <c r="O1231" s="18"/>
+      <c r="O1231" s="53">
+        <v>46245</v>
+      </c>
       <c r="P1231" s="18"/>
       <c r="Q1231" s="15">
         <v>77245341</v>
@@ -65988,7 +66782,9 @@
       </c>
       <c r="L1239" s="18"/>
       <c r="M1239" s="18"/>
-      <c r="N1239" s="40"/>
+      <c r="N1239" s="54">
+        <v>886</v>
+      </c>
       <c r="O1239" s="18"/>
       <c r="P1239" s="18"/>
       <c r="Q1239" s="18"/>
@@ -66126,7 +66922,9 @@
       </c>
       <c r="L1242" s="18"/>
       <c r="M1242" s="18"/>
-      <c r="N1242" s="40"/>
+      <c r="N1242" s="54">
+        <v>1028</v>
+      </c>
       <c r="O1242" s="18"/>
       <c r="P1242" s="18"/>
       <c r="Q1242" s="15">
@@ -66402,7 +67200,9 @@
       </c>
       <c r="L1248" s="18"/>
       <c r="M1248" s="18"/>
-      <c r="N1248" s="40"/>
+      <c r="N1248" s="54">
+        <v>830</v>
+      </c>
       <c r="O1248" s="18"/>
       <c r="P1248" s="18"/>
       <c r="Q1248" s="15">
@@ -66780,7 +67580,9 @@
       </c>
       <c r="L1256" s="18"/>
       <c r="M1256" s="18"/>
-      <c r="N1256" s="40"/>
+      <c r="N1256" s="54">
+        <v>831</v>
+      </c>
       <c r="O1256" s="18"/>
       <c r="P1256" s="18"/>
       <c r="Q1256" s="15">
@@ -67007,10 +67809,12 @@
       <c r="J1261" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1261" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1261" s="18"/>
+      <c r="K1261" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1261" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1261" s="18"/>
       <c r="N1261" s="40"/>
       <c r="O1261" s="18"/>
@@ -67051,10 +67855,12 @@
       <c r="J1262" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1262" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1262" s="18"/>
+      <c r="K1262" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1262" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1262" s="18"/>
       <c r="N1262" s="54">
         <v>709</v>
@@ -67097,10 +67903,12 @@
       <c r="J1263" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1263" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1263" s="18"/>
+      <c r="K1263" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1263" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1263" s="18"/>
       <c r="N1263" s="54">
         <v>562</v>
@@ -67145,10 +67953,12 @@
       <c r="J1264" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1264" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1264" s="18"/>
+      <c r="K1264" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1264" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1264" s="18"/>
       <c r="N1264" s="54">
         <v>563</v>
@@ -67193,10 +68003,12 @@
       <c r="J1265" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1265" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1265" s="18"/>
+      <c r="K1265" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1265" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1265" s="18"/>
       <c r="N1265" s="54">
         <v>555</v>
@@ -67241,10 +68053,12 @@
       <c r="J1266" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1266" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1266" s="18"/>
+      <c r="K1266" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1266" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1266" s="18"/>
       <c r="N1266" s="54">
         <v>661</v>
@@ -67287,10 +68101,12 @@
       <c r="J1267" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1267" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1267" s="18"/>
+      <c r="K1267" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1267" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1267" s="18"/>
       <c r="N1267" s="54">
         <v>670</v>
@@ -67333,10 +68149,12 @@
       <c r="J1268" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1268" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1268" s="18"/>
+      <c r="K1268" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1268" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1268" s="18"/>
       <c r="N1268" s="54">
         <v>671</v>
@@ -67427,10 +68245,12 @@
       <c r="J1270" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1270" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1270" s="18"/>
+      <c r="K1270" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1270" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1270" s="18"/>
       <c r="N1270" s="54">
         <v>545</v>
@@ -67475,10 +68295,12 @@
       <c r="J1271" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1271" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1271" s="18"/>
+      <c r="K1271" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1271" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1271" s="18"/>
       <c r="N1271" s="54">
         <v>544</v>
@@ -67569,10 +68391,12 @@
       <c r="J1273" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1273" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1273" s="18"/>
+      <c r="K1273" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1273" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1273" s="18"/>
       <c r="N1273" s="54">
         <v>413</v>
@@ -67670,7 +68494,9 @@
       </c>
       <c r="L1275" s="18"/>
       <c r="M1275" s="18"/>
-      <c r="N1275" s="40"/>
+      <c r="N1275" s="54">
+        <v>951</v>
+      </c>
       <c r="O1275" s="18"/>
       <c r="P1275" s="18"/>
       <c r="Q1275" s="18"/>
@@ -67757,10 +68583,12 @@
       <c r="J1277" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1277" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1277" s="18"/>
+      <c r="K1277" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1277" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1277" s="18"/>
       <c r="N1277" s="54">
         <v>569</v>
@@ -68071,10 +68899,12 @@
       <c r="J1284" s="15" t="s">
         <v>1672</v>
       </c>
-      <c r="K1284" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1284" s="18"/>
+      <c r="K1284" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1284" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1284" s="18"/>
       <c r="N1284" s="54">
         <v>574</v>
@@ -68119,10 +68949,12 @@
       <c r="J1285" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1285" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1285" s="18"/>
+      <c r="K1285" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1285" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1285" s="18"/>
       <c r="N1285" s="54">
         <v>767</v>
@@ -68165,10 +68997,12 @@
       <c r="J1286" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1286" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1286" s="18"/>
+      <c r="K1286" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1286" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1286" s="18"/>
       <c r="N1286" s="54">
         <v>624</v>
@@ -68209,10 +69043,12 @@
       <c r="J1287" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1287" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1287" s="18"/>
+      <c r="K1287" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1287" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1287" s="18"/>
       <c r="N1287" s="54">
         <v>623</v>
@@ -68255,10 +69091,12 @@
       <c r="J1288" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1288" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1288" s="18"/>
+      <c r="K1288" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1288" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1288" s="18"/>
       <c r="N1288" s="54">
         <v>621</v>
@@ -68301,10 +69139,12 @@
       <c r="J1289" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1289" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1289" s="18"/>
+      <c r="K1289" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1289" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1289" s="18"/>
       <c r="N1289" s="54">
         <v>620</v>
@@ -68347,10 +69187,12 @@
       <c r="J1290" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1290" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1290" s="18"/>
+      <c r="K1290" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1290" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1290" s="18"/>
       <c r="N1290" s="54">
         <v>622</v>
@@ -68393,10 +69235,12 @@
       <c r="J1291" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1291" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1291" s="18"/>
+      <c r="K1291" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1291" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1291" s="18"/>
       <c r="N1291" s="54">
         <v>458</v>
@@ -68439,12 +69283,16 @@
       <c r="J1292" s="15" t="s">
         <v>1997</v>
       </c>
-      <c r="K1292" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1292" s="18"/>
+      <c r="K1292" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1292" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1292" s="18"/>
-      <c r="N1292" s="40"/>
+      <c r="N1292" s="54">
+        <v>1048</v>
+      </c>
       <c r="O1292" s="18"/>
       <c r="P1292" s="18"/>
       <c r="Q1292" s="11">
@@ -68664,7 +69512,9 @@
       </c>
       <c r="L1297" s="18"/>
       <c r="M1297" s="18"/>
-      <c r="N1297" s="40"/>
+      <c r="N1297" s="54">
+        <v>901</v>
+      </c>
       <c r="O1297" s="18"/>
       <c r="P1297" s="18"/>
       <c r="Q1297" s="11">
@@ -68710,7 +69560,9 @@
       </c>
       <c r="L1298" s="18"/>
       <c r="M1298" s="18"/>
-      <c r="N1298" s="40"/>
+      <c r="N1298" s="54">
+        <v>894</v>
+      </c>
       <c r="O1298" s="18"/>
       <c r="P1298" s="18"/>
       <c r="Q1298" s="18"/>
@@ -68756,7 +69608,9 @@
         <v>46250</v>
       </c>
       <c r="M1299" s="18"/>
-      <c r="N1299" s="40"/>
+      <c r="N1299" s="54">
+        <v>895</v>
+      </c>
       <c r="O1299" s="18"/>
       <c r="P1299" s="18"/>
       <c r="Q1299" s="11" t="s">
@@ -68802,7 +69656,9 @@
       </c>
       <c r="L1300" s="18"/>
       <c r="M1300" s="18"/>
-      <c r="N1300" s="40"/>
+      <c r="N1300" s="54">
+        <v>893</v>
+      </c>
       <c r="O1300" s="18"/>
       <c r="P1300" s="18"/>
       <c r="Q1300" s="18"/>
@@ -68892,7 +69748,9 @@
       </c>
       <c r="L1302" s="18"/>
       <c r="M1302" s="18"/>
-      <c r="N1302" s="40"/>
+      <c r="N1302" s="54">
+        <v>999</v>
+      </c>
       <c r="O1302" s="18"/>
       <c r="P1302" s="18"/>
       <c r="Q1302" s="11">
@@ -70037,12 +70895,16 @@
       <c r="J1327" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1327" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1327" s="18"/>
+      <c r="K1327" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1327" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1327" s="18"/>
-      <c r="N1327" s="40"/>
+      <c r="N1327" s="54">
+        <v>972</v>
+      </c>
       <c r="O1327" s="18"/>
       <c r="P1327" s="18"/>
       <c r="Q1327" s="18"/>
@@ -70081,12 +70943,16 @@
       <c r="J1328" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1328" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1328" s="18"/>
+      <c r="K1328" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1328" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1328" s="18"/>
-      <c r="N1328" s="40"/>
+      <c r="N1328" s="54">
+        <v>1005</v>
+      </c>
       <c r="O1328" s="18"/>
       <c r="P1328" s="18"/>
       <c r="Q1328" s="18"/>
@@ -70130,8 +70996,12 @@
       </c>
       <c r="L1329" s="18"/>
       <c r="M1329" s="18"/>
-      <c r="N1329" s="40"/>
-      <c r="O1329" s="18"/>
+      <c r="N1329" s="54">
+        <v>979</v>
+      </c>
+      <c r="O1329" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1329" s="18"/>
       <c r="Q1329" s="18"/>
       <c r="R1329" s="22" t="s">
@@ -70485,10 +71355,12 @@
       <c r="J1337" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1337" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1337" s="18"/>
+      <c r="K1337" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1337" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1337" s="18"/>
       <c r="N1337" s="40"/>
       <c r="O1337" s="18"/>
@@ -70813,10 +71685,12 @@
       <c r="J1344" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1344" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1344" s="18"/>
+      <c r="K1344" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1344" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1344" s="18"/>
       <c r="N1344" s="40"/>
       <c r="O1344" s="18"/>
@@ -70945,10 +71819,12 @@
       <c r="J1347" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1347" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1347" s="18"/>
+      <c r="K1347" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1347" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1347" s="18"/>
       <c r="N1347" s="40"/>
       <c r="O1347" s="18"/>
@@ -71623,7 +72499,9 @@
       <c r="L1362" s="18"/>
       <c r="M1362" s="18"/>
       <c r="N1362" s="40"/>
-      <c r="O1362" s="18"/>
+      <c r="O1362" s="53">
+        <v>46245</v>
+      </c>
       <c r="P1362" s="18"/>
       <c r="Q1362" s="18"/>
       <c r="R1362" s="22" t="s">
@@ -72015,10 +72893,12 @@
       <c r="J1371" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1371" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1371" s="18"/>
+      <c r="K1371" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1371" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1371" s="18"/>
       <c r="N1371" s="40"/>
       <c r="O1371" s="18"/>
@@ -72059,10 +72939,12 @@
       <c r="J1372" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1372" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1372" s="18"/>
+      <c r="K1372" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1372" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1372" s="18"/>
       <c r="N1372" s="40"/>
       <c r="O1372" s="18"/>
@@ -72294,7 +73176,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1378" spans="1:18" ht="15" thickBot="1">
+    <row r="1378" spans="1:18" ht="21" thickBot="1">
       <c r="A1378" s="2">
         <v>187</v>
       </c>
@@ -72325,14 +73207,16 @@
       <c r="J1378" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1378" s="30" t="s">
-        <v>1596</v>
+      <c r="K1378" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1378" s="18"/>
       <c r="M1378" s="18"/>
       <c r="N1378" s="40"/>
       <c r="O1378" s="18"/>
-      <c r="P1378" s="49"/>
+      <c r="P1378" s="49" t="s">
+        <v>2269</v>
+      </c>
       <c r="Q1378" s="18"/>
       <c r="R1378" s="22" t="s">
         <v>131</v>
@@ -72411,10 +73295,12 @@
       <c r="J1380" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1380" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1380" s="18"/>
+      <c r="K1380" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1380" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1380" s="18"/>
       <c r="N1380" s="40"/>
       <c r="O1380" s="18"/>
@@ -72455,13 +73341,17 @@
       <c r="J1381" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1381" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1381" s="18"/>
+      <c r="K1381" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1381" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1381" s="18"/>
       <c r="N1381" s="40"/>
-      <c r="O1381" s="18"/>
+      <c r="O1381" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1381" s="18"/>
       <c r="Q1381" s="18"/>
       <c r="R1381" s="22" t="s">
@@ -72504,7 +73394,9 @@
       </c>
       <c r="L1382" s="18"/>
       <c r="M1382" s="18"/>
-      <c r="N1382" s="40"/>
+      <c r="N1382" s="54">
+        <v>993</v>
+      </c>
       <c r="O1382" s="18"/>
       <c r="P1382" s="18"/>
       <c r="Q1382" s="18"/>
@@ -72922,7 +73814,9 @@
       </c>
       <c r="L1391" s="18"/>
       <c r="M1391" s="18"/>
-      <c r="N1391" s="40"/>
+      <c r="N1391" s="54">
+        <v>952</v>
+      </c>
       <c r="O1391" s="18"/>
       <c r="P1391" s="18"/>
       <c r="Q1391" s="11">
@@ -72968,7 +73862,9 @@
       </c>
       <c r="L1392" s="18"/>
       <c r="M1392" s="18"/>
-      <c r="N1392" s="40"/>
+      <c r="N1392" s="54">
+        <v>953</v>
+      </c>
       <c r="O1392" s="18"/>
       <c r="P1392" s="18"/>
       <c r="Q1392" s="11" t="s">
@@ -73592,7 +74488,9 @@
       </c>
       <c r="L1406" s="18"/>
       <c r="M1406" s="18"/>
-      <c r="N1406" s="40"/>
+      <c r="N1406" s="54">
+        <v>1024</v>
+      </c>
       <c r="O1406" s="18"/>
       <c r="P1406" s="18"/>
       <c r="Q1406" s="18"/>
@@ -73873,7 +74771,9 @@
       <c r="L1412" s="18"/>
       <c r="M1412" s="18"/>
       <c r="N1412" s="40"/>
-      <c r="O1412" s="18"/>
+      <c r="O1412" s="53">
+        <v>46245</v>
+      </c>
       <c r="P1412" s="18"/>
       <c r="Q1412" s="18"/>
       <c r="R1412" s="21" t="s">
@@ -73918,7 +74818,9 @@
         <v>46250</v>
       </c>
       <c r="M1413" s="18"/>
-      <c r="N1413" s="40"/>
+      <c r="N1413" s="76" t="s">
+        <v>2270</v>
+      </c>
       <c r="O1413" s="18"/>
       <c r="P1413" s="18"/>
       <c r="Q1413" s="11">
@@ -74057,7 +74959,9 @@
       <c r="L1416" s="18"/>
       <c r="M1416" s="18"/>
       <c r="N1416" s="40"/>
-      <c r="O1416" s="18"/>
+      <c r="O1416" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1416" s="18"/>
       <c r="Q1416" s="18"/>
       <c r="R1416" s="22" t="s">
@@ -74101,7 +75005,9 @@
       <c r="L1417" s="18"/>
       <c r="M1417" s="18"/>
       <c r="N1417" s="40"/>
-      <c r="O1417" s="18"/>
+      <c r="O1417" s="53">
+        <v>46244</v>
+      </c>
       <c r="P1417" s="18"/>
       <c r="Q1417" s="18"/>
       <c r="R1417" s="22" t="s">
@@ -74328,7 +75234,9 @@
       </c>
       <c r="L1422" s="18"/>
       <c r="M1422" s="18"/>
-      <c r="N1422" s="40"/>
+      <c r="N1422" s="54">
+        <v>1052</v>
+      </c>
       <c r="O1422" s="18"/>
       <c r="P1422" s="18"/>
       <c r="Q1422" s="15">
@@ -74374,7 +75282,9 @@
       </c>
       <c r="L1423" s="18"/>
       <c r="M1423" s="18"/>
-      <c r="N1423" s="40"/>
+      <c r="N1423" s="54">
+        <v>902</v>
+      </c>
       <c r="O1423" s="18"/>
       <c r="P1423" s="18"/>
       <c r="Q1423" s="15">
@@ -74736,7 +75646,9 @@
       </c>
       <c r="L1431" s="18"/>
       <c r="M1431" s="18"/>
-      <c r="N1431" s="40"/>
+      <c r="N1431" s="54">
+        <v>921</v>
+      </c>
       <c r="O1431" s="18"/>
       <c r="P1431" s="18"/>
       <c r="Q1431" s="18"/>
@@ -74778,7 +75690,9 @@
       </c>
       <c r="L1432" s="18"/>
       <c r="M1432" s="18"/>
-      <c r="N1432" s="40"/>
+      <c r="N1432" s="54">
+        <v>922</v>
+      </c>
       <c r="O1432" s="18"/>
       <c r="P1432" s="18"/>
       <c r="Q1432" s="18"/>
@@ -74820,7 +75734,9 @@
       </c>
       <c r="L1433" s="18"/>
       <c r="M1433" s="18"/>
-      <c r="N1433" s="40"/>
+      <c r="N1433" s="54">
+        <v>923</v>
+      </c>
       <c r="O1433" s="18"/>
       <c r="P1433" s="18"/>
       <c r="Q1433" s="18"/>
@@ -74862,7 +75778,9 @@
       </c>
       <c r="L1434" s="18"/>
       <c r="M1434" s="18"/>
-      <c r="N1434" s="40"/>
+      <c r="N1434" s="54">
+        <v>924</v>
+      </c>
       <c r="O1434" s="18"/>
       <c r="P1434" s="18"/>
       <c r="Q1434" s="18"/>
@@ -74904,7 +75822,9 @@
       </c>
       <c r="L1435" s="18"/>
       <c r="M1435" s="18"/>
-      <c r="N1435" s="40"/>
+      <c r="N1435" s="54">
+        <v>925</v>
+      </c>
       <c r="O1435" s="18"/>
       <c r="P1435" s="18"/>
       <c r="Q1435" s="18"/>
@@ -74946,7 +75866,9 @@
       </c>
       <c r="L1436" s="18"/>
       <c r="M1436" s="18"/>
-      <c r="N1436" s="40"/>
+      <c r="N1436" s="54">
+        <v>926</v>
+      </c>
       <c r="O1436" s="18"/>
       <c r="P1436" s="18"/>
       <c r="Q1436" s="18"/>
@@ -74988,7 +75910,9 @@
       </c>
       <c r="L1437" s="18"/>
       <c r="M1437" s="18"/>
-      <c r="N1437" s="40"/>
+      <c r="N1437" s="54">
+        <v>927</v>
+      </c>
       <c r="O1437" s="18"/>
       <c r="P1437" s="18"/>
       <c r="Q1437" s="18"/>
@@ -75028,7 +75952,9 @@
       </c>
       <c r="L1438" s="18"/>
       <c r="M1438" s="18"/>
-      <c r="N1438" s="40"/>
+      <c r="N1438" s="54">
+        <v>928</v>
+      </c>
       <c r="O1438" s="18"/>
       <c r="P1438" s="18"/>
       <c r="Q1438" s="18"/>
@@ -75070,7 +75996,9 @@
       </c>
       <c r="L1439" s="18"/>
       <c r="M1439" s="18"/>
-      <c r="N1439" s="40"/>
+      <c r="N1439" s="54">
+        <v>929</v>
+      </c>
       <c r="O1439" s="18"/>
       <c r="P1439" s="18"/>
       <c r="Q1439" s="18"/>
@@ -75110,7 +76038,9 @@
       </c>
       <c r="L1440" s="18"/>
       <c r="M1440" s="18"/>
-      <c r="N1440" s="40"/>
+      <c r="N1440" s="54">
+        <v>930</v>
+      </c>
       <c r="O1440" s="18"/>
       <c r="P1440" s="18"/>
       <c r="Q1440" s="18"/>
@@ -75191,10 +76121,12 @@
         <v>485</v>
       </c>
       <c r="J1442" s="18"/>
-      <c r="K1442" s="37" t="s">
-        <v>175</v>
-      </c>
-      <c r="L1442" s="18"/>
+      <c r="K1442" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1442" s="53">
+        <v>46248</v>
+      </c>
       <c r="M1442" s="18"/>
       <c r="N1442" s="40"/>
       <c r="O1442" s="18"/>
@@ -75331,7 +76263,9 @@
       </c>
       <c r="O1445" s="18"/>
       <c r="P1445" s="18"/>
-      <c r="Q1445" s="18"/>
+      <c r="Q1445" s="11">
+        <v>77136032</v>
+      </c>
       <c r="R1445" s="21" t="s">
         <v>14</v>
       </c>
@@ -75738,7 +76672,9 @@
       </c>
       <c r="L1454" s="18"/>
       <c r="M1454" s="18"/>
-      <c r="N1454" s="40"/>
+      <c r="N1454" s="54">
+        <v>905</v>
+      </c>
       <c r="O1454" s="18"/>
       <c r="P1454" s="18"/>
       <c r="Q1454" s="18"/>
@@ -75828,7 +76764,9 @@
       </c>
       <c r="L1456" s="18"/>
       <c r="M1456" s="18"/>
-      <c r="N1456" s="40"/>
+      <c r="N1456" s="54">
+        <v>914</v>
+      </c>
       <c r="O1456" s="18"/>
       <c r="P1456" s="18"/>
       <c r="Q1456" s="11">
@@ -75920,7 +76858,9 @@
       </c>
       <c r="L1458" s="18"/>
       <c r="M1458" s="18"/>
-      <c r="N1458" s="40"/>
+      <c r="N1458" s="54">
+        <v>915</v>
+      </c>
       <c r="O1458" s="18"/>
       <c r="P1458" s="18"/>
       <c r="Q1458" s="18"/>
@@ -75964,7 +76904,9 @@
       </c>
       <c r="L1459" s="18"/>
       <c r="M1459" s="18"/>
-      <c r="N1459" s="40"/>
+      <c r="N1459" s="54">
+        <v>955</v>
+      </c>
       <c r="O1459" s="18"/>
       <c r="P1459" s="18"/>
       <c r="Q1459" s="18"/>
@@ -76008,7 +76950,9 @@
       </c>
       <c r="L1460" s="18"/>
       <c r="M1460" s="18"/>
-      <c r="N1460" s="40"/>
+      <c r="N1460" s="54">
+        <v>1026</v>
+      </c>
       <c r="O1460" s="18"/>
       <c r="P1460" s="18"/>
       <c r="Q1460" s="18"/>
@@ -76052,7 +76996,9 @@
       </c>
       <c r="L1461" s="18"/>
       <c r="M1461" s="18"/>
-      <c r="N1461" s="40"/>
+      <c r="N1461" s="54">
+        <v>985</v>
+      </c>
       <c r="O1461" s="18"/>
       <c r="P1461" s="18"/>
       <c r="Q1461" s="18"/>
@@ -76096,7 +77042,9 @@
       </c>
       <c r="L1462" s="18"/>
       <c r="M1462" s="18"/>
-      <c r="N1462" s="40"/>
+      <c r="N1462" s="54">
+        <v>983</v>
+      </c>
       <c r="O1462" s="18"/>
       <c r="P1462" s="18"/>
       <c r="Q1462" s="18"/>
@@ -76224,7 +77172,9 @@
       </c>
       <c r="L1465" s="38"/>
       <c r="M1465" s="18"/>
-      <c r="N1465" s="40"/>
+      <c r="N1465" s="54">
+        <v>996</v>
+      </c>
       <c r="O1465" s="18"/>
       <c r="P1465" s="18"/>
       <c r="Q1465" s="15">
@@ -76270,7 +77220,9 @@
       </c>
       <c r="L1466" s="18"/>
       <c r="M1466" s="18"/>
-      <c r="N1466" s="40"/>
+      <c r="N1466" s="54">
+        <v>976</v>
+      </c>
       <c r="O1466" s="18"/>
       <c r="P1466" s="18"/>
       <c r="Q1466" s="18"/>
@@ -76314,7 +77266,9 @@
       </c>
       <c r="L1467" s="18"/>
       <c r="M1467" s="18"/>
-      <c r="N1467" s="40"/>
+      <c r="N1467" s="54">
+        <v>980</v>
+      </c>
       <c r="O1467" s="18"/>
       <c r="P1467" s="18"/>
       <c r="Q1467" s="18"/>
@@ -76491,12 +77445,16 @@
       <c r="J1471" s="15" t="s">
         <v>562</v>
       </c>
-      <c r="K1471" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1471" s="18"/>
+      <c r="K1471" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1471" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1471" s="18"/>
-      <c r="N1471" s="40"/>
+      <c r="N1471" s="54">
+        <v>977</v>
+      </c>
       <c r="O1471" s="18"/>
       <c r="P1471" s="18"/>
       <c r="Q1471" s="11">
@@ -76586,7 +77544,9 @@
       </c>
       <c r="L1473" s="18"/>
       <c r="M1473" s="18"/>
-      <c r="N1473" s="40"/>
+      <c r="N1473" s="54">
+        <v>997</v>
+      </c>
       <c r="O1473" s="18"/>
       <c r="P1473" s="18"/>
       <c r="Q1473" s="18"/>
@@ -76850,7 +77810,9 @@
       </c>
       <c r="L1479" s="18"/>
       <c r="M1479" s="18"/>
-      <c r="N1479" s="40"/>
+      <c r="N1479" s="54">
+        <v>1023</v>
+      </c>
       <c r="O1479" s="18"/>
       <c r="P1479" s="18"/>
       <c r="Q1479" s="11">
@@ -77492,7 +78454,9 @@
       </c>
       <c r="L1494" s="18"/>
       <c r="M1494" s="18"/>
-      <c r="N1494" s="40"/>
+      <c r="N1494" s="54">
+        <v>1045</v>
+      </c>
       <c r="O1494" s="18"/>
       <c r="P1494" s="18"/>
       <c r="Q1494" s="15">
@@ -77538,7 +78502,9 @@
       </c>
       <c r="L1495" s="18"/>
       <c r="M1495" s="18"/>
-      <c r="N1495" s="40"/>
+      <c r="N1495" s="54">
+        <v>1046</v>
+      </c>
       <c r="O1495" s="18"/>
       <c r="P1495" s="18"/>
       <c r="Q1495" s="15">
@@ -77584,7 +78550,9 @@
       </c>
       <c r="L1496" s="18"/>
       <c r="M1496" s="18"/>
-      <c r="N1496" s="40"/>
+      <c r="N1496" s="54">
+        <v>1047</v>
+      </c>
       <c r="O1496" s="18"/>
       <c r="P1496" s="18"/>
       <c r="Q1496" s="15">
@@ -77854,7 +78822,9 @@
       </c>
       <c r="L1502" s="18"/>
       <c r="M1502" s="18"/>
-      <c r="N1502" s="40"/>
+      <c r="N1502" s="54">
+        <v>1016</v>
+      </c>
       <c r="O1502" s="18"/>
       <c r="P1502" s="18"/>
       <c r="Q1502" s="11">
@@ -77900,7 +78870,9 @@
       </c>
       <c r="L1503" s="18"/>
       <c r="M1503" s="18"/>
-      <c r="N1503" s="40"/>
+      <c r="N1503" s="54">
+        <v>1017</v>
+      </c>
       <c r="O1503" s="18"/>
       <c r="P1503" s="18"/>
       <c r="Q1503" s="11">
@@ -78031,8 +79003,12 @@
         <v>12</v>
       </c>
       <c r="L1506" s="18"/>
-      <c r="M1506" s="18"/>
-      <c r="N1506" s="40"/>
+      <c r="M1506" s="16" t="s">
+        <v>1999</v>
+      </c>
+      <c r="N1506" s="54">
+        <v>1025</v>
+      </c>
       <c r="O1506" s="18"/>
       <c r="P1506" s="18"/>
       <c r="Q1506" s="18"/>
@@ -78040,6 +79016,1746 @@
         <v>131</v>
       </c>
     </row>
+    <row r="1507" spans="1:18" ht="15" thickBot="1">
+      <c r="A1507" s="2">
+        <v>1</v>
+      </c>
+      <c r="B1507" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1507" s="55" t="s">
+        <v>2271</v>
+      </c>
+      <c r="D1507" s="55" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E1507" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1507" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1507" s="74">
+        <v>52156</v>
+      </c>
+      <c r="H1507" s="66">
+        <v>44011</v>
+      </c>
+      <c r="I1507" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1507" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1507" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1507" s="18"/>
+      <c r="M1507" s="18"/>
+      <c r="N1507" s="54">
+        <v>841</v>
+      </c>
+      <c r="O1507" s="18"/>
+      <c r="P1507" s="18"/>
+      <c r="Q1507" s="11">
+        <v>77683261</v>
+      </c>
+      <c r="R1507" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1508" s="2">
+        <v>2</v>
+      </c>
+      <c r="B1508" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1508" s="55" t="s">
+        <v>2273</v>
+      </c>
+      <c r="D1508" s="55" t="s">
+        <v>2274</v>
+      </c>
+      <c r="E1508" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1508" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1508" s="74">
+        <v>86093</v>
+      </c>
+      <c r="H1508" s="66">
+        <v>46182</v>
+      </c>
+      <c r="I1508" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1508" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="K1508" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1508" s="18"/>
+      <c r="M1508" s="18"/>
+      <c r="N1508" s="40"/>
+      <c r="O1508" s="18"/>
+      <c r="P1508" s="18"/>
+      <c r="Q1508" s="18"/>
+      <c r="R1508" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1509" s="2">
+        <v>3</v>
+      </c>
+      <c r="B1509" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1509" s="55" t="s">
+        <v>2275</v>
+      </c>
+      <c r="D1509" s="55" t="s">
+        <v>2276</v>
+      </c>
+      <c r="E1509" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1509" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1509" s="74">
+        <v>65015</v>
+      </c>
+      <c r="H1509" s="66">
+        <v>14581</v>
+      </c>
+      <c r="I1509" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1509" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1509" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1509" s="18"/>
+      <c r="M1509" s="18"/>
+      <c r="N1509" s="40"/>
+      <c r="O1509" s="18"/>
+      <c r="P1509" s="18"/>
+      <c r="Q1509" s="15">
+        <v>95574816</v>
+      </c>
+      <c r="R1509" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1510" s="2">
+        <v>4</v>
+      </c>
+      <c r="B1510" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1510" s="55" t="s">
+        <v>2277</v>
+      </c>
+      <c r="D1510" s="55" t="s">
+        <v>2278</v>
+      </c>
+      <c r="E1510" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1510" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1510" s="74">
+        <v>77574</v>
+      </c>
+      <c r="H1510" s="66">
+        <v>63261</v>
+      </c>
+      <c r="I1510" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1510" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1510" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1510" s="18"/>
+      <c r="M1510" s="18"/>
+      <c r="N1510" s="40"/>
+      <c r="O1510" s="18"/>
+      <c r="P1510" s="18"/>
+      <c r="Q1510" s="15">
+        <v>95813276</v>
+      </c>
+      <c r="R1510" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1511" s="2">
+        <v>5</v>
+      </c>
+      <c r="B1511" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1511" s="55" t="s">
+        <v>2279</v>
+      </c>
+      <c r="D1511" s="55" t="s">
+        <v>2280</v>
+      </c>
+      <c r="E1511" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1511" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1511" s="74">
+        <v>40541</v>
+      </c>
+      <c r="H1511" s="66">
+        <v>57134</v>
+      </c>
+      <c r="I1511" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1511" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1511" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1511" s="18"/>
+      <c r="M1511" s="18"/>
+      <c r="N1511" s="40"/>
+      <c r="O1511" s="18"/>
+      <c r="P1511" s="18"/>
+      <c r="Q1511" s="15">
+        <v>71012511</v>
+      </c>
+      <c r="R1511" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1512" s="2">
+        <v>6</v>
+      </c>
+      <c r="B1512" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1512" s="55" t="s">
+        <v>2281</v>
+      </c>
+      <c r="D1512" s="55" t="s">
+        <v>2282</v>
+      </c>
+      <c r="E1512" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1512" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1512" s="74">
+        <v>39007</v>
+      </c>
+      <c r="H1512" s="66">
+        <v>61966</v>
+      </c>
+      <c r="I1512" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1512" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1512" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1512" s="18"/>
+      <c r="M1512" s="18"/>
+      <c r="N1512" s="40"/>
+      <c r="O1512" s="18"/>
+      <c r="P1512" s="18"/>
+      <c r="Q1512" s="15">
+        <v>72093508</v>
+      </c>
+      <c r="R1512" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1513" s="2">
+        <v>7</v>
+      </c>
+      <c r="B1513" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1513" s="55" t="s">
+        <v>2283</v>
+      </c>
+      <c r="D1513" s="55" t="s">
+        <v>2284</v>
+      </c>
+      <c r="E1513" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1513" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1513" s="74">
+        <v>40197</v>
+      </c>
+      <c r="H1513" s="66" t="s">
+        <v>2285</v>
+      </c>
+      <c r="I1513" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1513" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1513" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1513" s="18"/>
+      <c r="M1513" s="18"/>
+      <c r="N1513" s="40"/>
+      <c r="O1513" s="18"/>
+      <c r="P1513" s="18"/>
+      <c r="Q1513" s="15">
+        <v>966505424510</v>
+      </c>
+      <c r="R1513" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1514" s="2">
+        <v>8</v>
+      </c>
+      <c r="B1514" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1514" s="55" t="s">
+        <v>1845</v>
+      </c>
+      <c r="D1514" s="55" t="s">
+        <v>2286</v>
+      </c>
+      <c r="E1514" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1514" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1514" s="74">
+        <v>81629</v>
+      </c>
+      <c r="H1514" s="66">
+        <v>33560</v>
+      </c>
+      <c r="I1514" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1514" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1514" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1514" s="18"/>
+      <c r="M1514" s="18"/>
+      <c r="N1514" s="40"/>
+      <c r="O1514" s="18"/>
+      <c r="P1514" s="18"/>
+      <c r="Q1514" s="15" t="s">
+        <v>2287</v>
+      </c>
+      <c r="R1514" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1515" s="2">
+        <v>9</v>
+      </c>
+      <c r="B1515" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1515" s="55" t="s">
+        <v>2288</v>
+      </c>
+      <c r="D1515" s="55" t="s">
+        <v>2289</v>
+      </c>
+      <c r="E1515" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1515" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1515" s="74">
+        <v>33872</v>
+      </c>
+      <c r="H1515" s="66">
+        <v>6238</v>
+      </c>
+      <c r="I1515" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1515" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1515" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1515" s="18"/>
+      <c r="M1515" s="18"/>
+      <c r="N1515" s="40"/>
+      <c r="O1515" s="18"/>
+      <c r="P1515" s="18"/>
+      <c r="Q1515" s="15">
+        <v>95707784</v>
+      </c>
+      <c r="R1515" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1516" s="2">
+        <v>10</v>
+      </c>
+      <c r="B1516" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1516" s="55" t="s">
+        <v>2290</v>
+      </c>
+      <c r="D1516" s="55" t="s">
+        <v>2291</v>
+      </c>
+      <c r="E1516" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1516" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1516" s="74">
+        <v>19555</v>
+      </c>
+      <c r="H1516" s="66" t="s">
+        <v>2292</v>
+      </c>
+      <c r="I1516" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1516" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1516" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1516" s="18"/>
+      <c r="M1516" s="18"/>
+      <c r="N1516" s="40"/>
+      <c r="O1516" s="18"/>
+      <c r="P1516" s="18"/>
+      <c r="Q1516" s="15">
+        <v>525947439</v>
+      </c>
+      <c r="R1516" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1517" s="2">
+        <v>11</v>
+      </c>
+      <c r="B1517" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1517" s="55" t="s">
+        <v>2293</v>
+      </c>
+      <c r="D1517" s="55" t="s">
+        <v>2294</v>
+      </c>
+      <c r="E1517" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1517" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1517" s="74">
+        <v>14693</v>
+      </c>
+      <c r="H1517" s="66">
+        <v>10779</v>
+      </c>
+      <c r="I1517" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1517" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1517" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1517" s="18"/>
+      <c r="M1517" s="18"/>
+      <c r="N1517" s="40"/>
+      <c r="O1517" s="18"/>
+      <c r="P1517" s="18"/>
+      <c r="Q1517" s="15">
+        <v>586767189</v>
+      </c>
+      <c r="R1517" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1518" s="2">
+        <v>12</v>
+      </c>
+      <c r="B1518" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1518" s="55" t="s">
+        <v>2295</v>
+      </c>
+      <c r="D1518" s="55" t="s">
+        <v>2296</v>
+      </c>
+      <c r="E1518" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1518" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1518" s="74">
+        <v>91508</v>
+      </c>
+      <c r="H1518" s="66">
+        <v>24026</v>
+      </c>
+      <c r="I1518" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1518" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1518" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1518" s="18"/>
+      <c r="M1518" s="18"/>
+      <c r="N1518" s="40"/>
+      <c r="O1518" s="18"/>
+      <c r="P1518" s="18"/>
+      <c r="Q1518" s="15">
+        <v>507500864</v>
+      </c>
+      <c r="R1518" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1519" s="2">
+        <v>13</v>
+      </c>
+      <c r="B1519" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1519" s="55" t="s">
+        <v>2297</v>
+      </c>
+      <c r="D1519" s="55" t="s">
+        <v>2298</v>
+      </c>
+      <c r="E1519" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1519" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1519" s="74">
+        <v>32156</v>
+      </c>
+      <c r="H1519" s="66">
+        <v>68298</v>
+      </c>
+      <c r="I1519" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1519" s="15" t="s">
+        <v>2153</v>
+      </c>
+      <c r="K1519" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1519" s="18"/>
+      <c r="M1519" s="18"/>
+      <c r="N1519" s="40"/>
+      <c r="O1519" s="18"/>
+      <c r="P1519" s="18"/>
+      <c r="Q1519" s="15">
+        <v>95610733</v>
+      </c>
+      <c r="R1519" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1520" s="2">
+        <v>14</v>
+      </c>
+      <c r="B1520" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1520" s="55" t="s">
+        <v>2299</v>
+      </c>
+      <c r="D1520" s="55" t="s">
+        <v>2300</v>
+      </c>
+      <c r="E1520" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1520" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1520" s="74">
+        <v>79605</v>
+      </c>
+      <c r="H1520" s="66">
+        <v>97337</v>
+      </c>
+      <c r="I1520" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1520" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1520" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1520" s="18"/>
+      <c r="M1520" s="18"/>
+      <c r="N1520" s="40"/>
+      <c r="O1520" s="18"/>
+      <c r="P1520" s="18"/>
+      <c r="Q1520" s="18"/>
+      <c r="R1520" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1521" s="2">
+        <v>15</v>
+      </c>
+      <c r="B1521" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1521" s="55" t="s">
+        <v>2301</v>
+      </c>
+      <c r="D1521" s="55" t="s">
+        <v>2302</v>
+      </c>
+      <c r="E1521" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1521" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1521" s="74">
+        <v>82007</v>
+      </c>
+      <c r="H1521" s="66">
+        <v>32647</v>
+      </c>
+      <c r="I1521" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1521" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1521" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1521" s="18"/>
+      <c r="M1521" s="18"/>
+      <c r="N1521" s="40"/>
+      <c r="O1521" s="18"/>
+      <c r="P1521" s="18"/>
+      <c r="Q1521" s="18"/>
+      <c r="R1521" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1522" s="2">
+        <v>16</v>
+      </c>
+      <c r="B1522" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1522" s="55" t="s">
+        <v>2303</v>
+      </c>
+      <c r="D1522" s="55" t="s">
+        <v>2304</v>
+      </c>
+      <c r="E1522" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1522" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1522" s="74">
+        <v>29976</v>
+      </c>
+      <c r="H1522" s="66">
+        <v>27279</v>
+      </c>
+      <c r="I1522" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1522" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1522" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1522" s="18"/>
+      <c r="M1522" s="18"/>
+      <c r="N1522" s="40"/>
+      <c r="O1522" s="18"/>
+      <c r="P1522" s="18"/>
+      <c r="Q1522" s="18"/>
+      <c r="R1522" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1523" s="2">
+        <v>17</v>
+      </c>
+      <c r="B1523" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1523" s="55" t="s">
+        <v>2305</v>
+      </c>
+      <c r="D1523" s="55" t="s">
+        <v>2306</v>
+      </c>
+      <c r="E1523" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1523" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1523" s="74">
+        <v>60383</v>
+      </c>
+      <c r="H1523" s="66">
+        <v>56704</v>
+      </c>
+      <c r="I1523" s="48" t="s">
+        <v>485</v>
+      </c>
+      <c r="J1523" s="18"/>
+      <c r="K1523" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1523" s="18"/>
+      <c r="M1523" s="18"/>
+      <c r="N1523" s="40"/>
+      <c r="O1523" s="18"/>
+      <c r="P1523" s="18"/>
+      <c r="Q1523" s="18"/>
+      <c r="R1523" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1524" s="2">
+        <v>18</v>
+      </c>
+      <c r="B1524" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1524" s="55" t="s">
+        <v>2307</v>
+      </c>
+      <c r="D1524" s="55">
+        <v>1962714</v>
+      </c>
+      <c r="E1524" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1524" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1524" s="74">
+        <v>6232</v>
+      </c>
+      <c r="H1524" s="66">
+        <v>8070</v>
+      </c>
+      <c r="I1524" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1524" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1524" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1524" s="18"/>
+      <c r="M1524" s="18"/>
+      <c r="N1524" s="40"/>
+      <c r="O1524" s="18"/>
+      <c r="P1524" s="18"/>
+      <c r="Q1524" s="18"/>
+      <c r="R1524" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:18" ht="15" thickBot="1">
+      <c r="A1525" s="2">
+        <v>19</v>
+      </c>
+      <c r="B1525" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1525" s="55" t="s">
+        <v>2308</v>
+      </c>
+      <c r="D1525" s="55" t="s">
+        <v>2309</v>
+      </c>
+      <c r="E1525" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1525" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1525" s="74">
+        <v>45528</v>
+      </c>
+      <c r="H1525" s="66" t="s">
+        <v>2310</v>
+      </c>
+      <c r="I1525" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1525" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1525" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1525" s="18"/>
+      <c r="M1525" s="18"/>
+      <c r="N1525" s="40"/>
+      <c r="O1525" s="18"/>
+      <c r="P1525" s="18"/>
+      <c r="Q1525" s="18"/>
+      <c r="R1525" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:18" ht="15" thickBot="1">
+      <c r="A1526" s="2">
+        <v>20</v>
+      </c>
+      <c r="B1526" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1526" s="55" t="s">
+        <v>2311</v>
+      </c>
+      <c r="D1526" s="55" t="s">
+        <v>2312</v>
+      </c>
+      <c r="E1526" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1526" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1526" s="74">
+        <v>36430</v>
+      </c>
+      <c r="H1526" s="66">
+        <v>44896</v>
+      </c>
+      <c r="I1526" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1526" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1526" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1526" s="18"/>
+      <c r="M1526" s="18"/>
+      <c r="N1526" s="40"/>
+      <c r="O1526" s="18"/>
+      <c r="P1526" s="18"/>
+      <c r="Q1526" s="15">
+        <v>95924374</v>
+      </c>
+      <c r="R1526" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:18" ht="15" thickBot="1">
+      <c r="A1527" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1527" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1527" s="55" t="s">
+        <v>2313</v>
+      </c>
+      <c r="D1527" s="55" t="s">
+        <v>2314</v>
+      </c>
+      <c r="E1527" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1527" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1527" s="74">
+        <v>82361</v>
+      </c>
+      <c r="H1527" s="66">
+        <v>64816</v>
+      </c>
+      <c r="I1527" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1527" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1527" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1527" s="18"/>
+      <c r="M1527" s="18"/>
+      <c r="N1527" s="40"/>
+      <c r="O1527" s="18"/>
+      <c r="P1527" s="18"/>
+      <c r="Q1527" s="15">
+        <v>95923647</v>
+      </c>
+      <c r="R1527" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:18" ht="15" thickBot="1">
+      <c r="A1528" s="2">
+        <v>22</v>
+      </c>
+      <c r="B1528" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1528" s="55" t="s">
+        <v>2315</v>
+      </c>
+      <c r="D1528" s="55" t="s">
+        <v>2316</v>
+      </c>
+      <c r="E1528" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1528" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1528" s="74">
+        <v>90259</v>
+      </c>
+      <c r="H1528" s="66">
+        <v>30567</v>
+      </c>
+      <c r="I1528" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1528" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1528" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1528" s="18"/>
+      <c r="M1528" s="18"/>
+      <c r="N1528" s="40"/>
+      <c r="O1528" s="18"/>
+      <c r="P1528" s="18"/>
+      <c r="Q1528" s="15">
+        <v>77829741</v>
+      </c>
+      <c r="R1528" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:18" ht="15" thickBot="1">
+      <c r="A1529" s="2">
+        <v>23</v>
+      </c>
+      <c r="B1529" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1529" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1529" s="55" t="s">
+        <v>2317</v>
+      </c>
+      <c r="E1529" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1529" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1529" s="74">
+        <v>36965</v>
+      </c>
+      <c r="H1529" s="38"/>
+      <c r="I1529" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1529" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1529" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1529" s="18"/>
+      <c r="M1529" s="18"/>
+      <c r="N1529" s="40"/>
+      <c r="O1529" s="18"/>
+      <c r="P1529" s="18"/>
+      <c r="Q1529" s="15">
+        <v>95924324</v>
+      </c>
+      <c r="R1529" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1530" s="2">
+        <v>24</v>
+      </c>
+      <c r="B1530" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1530" s="55" t="s">
+        <v>2318</v>
+      </c>
+      <c r="D1530" s="55">
+        <v>103251586</v>
+      </c>
+      <c r="E1530" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1530" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1530" s="74">
+        <v>792</v>
+      </c>
+      <c r="H1530" s="66">
+        <v>9596</v>
+      </c>
+      <c r="I1530" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1530" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="K1530" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1530" s="18"/>
+      <c r="M1530" s="18"/>
+      <c r="N1530" s="40"/>
+      <c r="O1530" s="18"/>
+      <c r="P1530" s="18"/>
+      <c r="Q1530" s="18"/>
+      <c r="R1530" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1531" s="2">
+        <v>25</v>
+      </c>
+      <c r="B1531" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1531" s="55" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D1531" s="55">
+        <v>83262499</v>
+      </c>
+      <c r="E1531" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1531" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1531" s="74">
+        <v>2723</v>
+      </c>
+      <c r="H1531" s="66">
+        <v>4971</v>
+      </c>
+      <c r="I1531" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1531" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="K1531" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1531" s="18"/>
+      <c r="M1531" s="18"/>
+      <c r="N1531" s="40"/>
+      <c r="O1531" s="18"/>
+      <c r="P1531" s="18"/>
+      <c r="Q1531" s="18"/>
+      <c r="R1531" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:18" ht="15" thickBot="1">
+      <c r="A1532" s="2">
+        <v>26</v>
+      </c>
+      <c r="B1532" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1532" s="55" t="s">
+        <v>2319</v>
+      </c>
+      <c r="D1532" s="55">
+        <v>137879144</v>
+      </c>
+      <c r="E1532" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1532" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1532" s="74">
+        <v>4350</v>
+      </c>
+      <c r="H1532" s="66">
+        <v>5586</v>
+      </c>
+      <c r="I1532" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1532" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1532" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1532" s="18"/>
+      <c r="M1532" s="18"/>
+      <c r="N1532" s="40"/>
+      <c r="O1532" s="18"/>
+      <c r="P1532" s="18"/>
+      <c r="Q1532" s="15">
+        <v>79273400</v>
+      </c>
+      <c r="R1532" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:18" ht="15" thickBot="1">
+      <c r="A1533" s="2">
+        <v>27</v>
+      </c>
+      <c r="B1533" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1533" s="55" t="s">
+        <v>2320</v>
+      </c>
+      <c r="D1533" s="55">
+        <v>74621634</v>
+      </c>
+      <c r="E1533" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1533" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1533" s="74">
+        <v>3791</v>
+      </c>
+      <c r="H1533" s="66" t="s">
+        <v>2321</v>
+      </c>
+      <c r="I1533" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1533" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1533" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1533" s="18"/>
+      <c r="M1533" s="18"/>
+      <c r="N1533" s="40"/>
+      <c r="O1533" s="18"/>
+      <c r="P1533" s="18"/>
+      <c r="Q1533" s="15">
+        <v>92406192</v>
+      </c>
+      <c r="R1533" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1534" s="2">
+        <v>28</v>
+      </c>
+      <c r="B1534" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1534" s="55" t="s">
+        <v>2322</v>
+      </c>
+      <c r="D1534" s="55">
+        <v>90961365</v>
+      </c>
+      <c r="E1534" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1534" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1534" s="74">
+        <v>4676</v>
+      </c>
+      <c r="H1534" s="66" t="s">
+        <v>2323</v>
+      </c>
+      <c r="I1534" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1534" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1534" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1534" s="18"/>
+      <c r="M1534" s="18"/>
+      <c r="N1534" s="40"/>
+      <c r="O1534" s="18"/>
+      <c r="P1534" s="18"/>
+      <c r="Q1534" s="15">
+        <v>94398619</v>
+      </c>
+      <c r="R1534" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:18" ht="15" thickBot="1">
+      <c r="A1535" s="2">
+        <v>29</v>
+      </c>
+      <c r="B1535" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1535" s="55" t="s">
+        <v>919</v>
+      </c>
+      <c r="D1535" s="55">
+        <v>130811436</v>
+      </c>
+      <c r="E1535" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1535" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1535" s="74">
+        <v>9200</v>
+      </c>
+      <c r="H1535" s="66">
+        <v>2429</v>
+      </c>
+      <c r="I1535" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1535" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1535" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1535" s="18"/>
+      <c r="M1535" s="18"/>
+      <c r="N1535" s="40"/>
+      <c r="O1535" s="18"/>
+      <c r="P1535" s="18"/>
+      <c r="Q1535" s="15">
+        <v>99861508</v>
+      </c>
+      <c r="R1535" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1536" s="2">
+        <v>30</v>
+      </c>
+      <c r="B1536" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1536" s="55" t="s">
+        <v>2324</v>
+      </c>
+      <c r="D1536" s="55">
+        <v>89666661</v>
+      </c>
+      <c r="E1536" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1536" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1536" s="74">
+        <v>1527</v>
+      </c>
+      <c r="H1536" s="66">
+        <v>2298</v>
+      </c>
+      <c r="I1536" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1536" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1536" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1536" s="18"/>
+      <c r="M1536" s="18"/>
+      <c r="N1536" s="40"/>
+      <c r="O1536" s="18"/>
+      <c r="P1536" s="18"/>
+      <c r="Q1536" s="18"/>
+      <c r="R1536" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:18" ht="15" thickBot="1">
+      <c r="A1537" s="2">
+        <v>31</v>
+      </c>
+      <c r="B1537" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1537" s="55" t="s">
+        <v>2325</v>
+      </c>
+      <c r="D1537" s="55" t="s">
+        <v>2326</v>
+      </c>
+      <c r="E1537" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1537" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1537" s="74">
+        <v>53911</v>
+      </c>
+      <c r="H1537" s="66">
+        <v>24851</v>
+      </c>
+      <c r="I1537" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1537" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1537" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1537" s="18"/>
+      <c r="M1537" s="18"/>
+      <c r="N1537" s="40"/>
+      <c r="O1537" s="18"/>
+      <c r="P1537" s="18"/>
+      <c r="Q1537" s="11">
+        <v>74121421</v>
+      </c>
+      <c r="R1537" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:18" ht="15" thickBot="1">
+      <c r="A1538" s="2">
+        <v>32</v>
+      </c>
+      <c r="B1538" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1538" s="55" t="s">
+        <v>156</v>
+      </c>
+      <c r="D1538" s="55">
+        <v>73851284</v>
+      </c>
+      <c r="E1538" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1538" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1538" s="74">
+        <v>2657</v>
+      </c>
+      <c r="H1538" s="66">
+        <v>1733</v>
+      </c>
+      <c r="I1538" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1538" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1538" s="18"/>
+      <c r="L1538" s="18"/>
+      <c r="M1538" s="18"/>
+      <c r="N1538" s="40"/>
+      <c r="O1538" s="18"/>
+      <c r="P1538" s="18"/>
+      <c r="Q1538" s="11">
+        <v>96551290</v>
+      </c>
+      <c r="R1538" s="18"/>
+    </row>
+    <row r="1539" spans="1:18" ht="15" thickBot="1">
+      <c r="A1539" s="2">
+        <v>33</v>
+      </c>
+      <c r="B1539" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1539" s="80" t="s">
+        <v>2327</v>
+      </c>
+      <c r="D1539" s="80">
+        <v>79883496</v>
+      </c>
+      <c r="E1539" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1539" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1539" s="81">
+        <v>925</v>
+      </c>
+      <c r="H1539" s="38"/>
+      <c r="I1539" s="73" t="s">
+        <v>1808</v>
+      </c>
+      <c r="J1539" s="18"/>
+      <c r="K1539" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1539" s="18"/>
+      <c r="M1539" s="21" t="s">
+        <v>2185</v>
+      </c>
+      <c r="N1539" s="40"/>
+      <c r="O1539" s="18"/>
+      <c r="P1539" s="18"/>
+      <c r="Q1539" s="18"/>
+      <c r="R1539" s="16" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1540" s="2">
+        <v>34</v>
+      </c>
+      <c r="B1540" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1540" s="80" t="s">
+        <v>2328</v>
+      </c>
+      <c r="D1540" s="80">
+        <v>102096078</v>
+      </c>
+      <c r="E1540" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1540" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1540" s="81">
+        <v>2698</v>
+      </c>
+      <c r="H1540" s="38"/>
+      <c r="I1540" s="73" t="s">
+        <v>1808</v>
+      </c>
+      <c r="J1540" s="18"/>
+      <c r="K1540" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1540" s="18"/>
+      <c r="M1540" s="21" t="s">
+        <v>2185</v>
+      </c>
+      <c r="N1540" s="40"/>
+      <c r="O1540" s="18"/>
+      <c r="P1540" s="18"/>
+      <c r="Q1540" s="18"/>
+      <c r="R1540" s="16" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1541" s="2">
+        <v>35</v>
+      </c>
+      <c r="B1541" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1541" s="80" t="s">
+        <v>2329</v>
+      </c>
+      <c r="D1541" s="80">
+        <v>10417783</v>
+      </c>
+      <c r="E1541" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1541" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1541" s="81">
+        <v>9854</v>
+      </c>
+      <c r="H1541" s="38"/>
+      <c r="I1541" s="73" t="s">
+        <v>1808</v>
+      </c>
+      <c r="J1541" s="18"/>
+      <c r="K1541" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1541" s="18"/>
+      <c r="M1541" s="21" t="s">
+        <v>2185</v>
+      </c>
+      <c r="N1541" s="40"/>
+      <c r="O1541" s="18"/>
+      <c r="P1541" s="18"/>
+      <c r="Q1541" s="18"/>
+      <c r="R1541" s="16" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:18" ht="40.799999999999997" thickBot="1">
+      <c r="A1542" s="2">
+        <v>36</v>
+      </c>
+      <c r="B1542" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1542" s="80" t="s">
+        <v>2330</v>
+      </c>
+      <c r="D1542" s="80">
+        <v>24946408</v>
+      </c>
+      <c r="E1542" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1542" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1542" s="81">
+        <v>9965</v>
+      </c>
+      <c r="H1542" s="38"/>
+      <c r="I1542" s="73" t="s">
+        <v>1808</v>
+      </c>
+      <c r="J1542" s="18"/>
+      <c r="K1542" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1542" s="18"/>
+      <c r="M1542" s="21" t="s">
+        <v>2185</v>
+      </c>
+      <c r="N1542" s="40"/>
+      <c r="O1542" s="18"/>
+      <c r="P1542" s="18"/>
+      <c r="Q1542" s="18"/>
+      <c r="R1542" s="16" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1543" s="2">
+        <v>37</v>
+      </c>
+      <c r="B1543" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1543" s="80" t="s">
+        <v>2331</v>
+      </c>
+      <c r="D1543" s="80">
+        <v>23008711</v>
+      </c>
+      <c r="E1543" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1543" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1543" s="81">
+        <v>5671</v>
+      </c>
+      <c r="H1543" s="38"/>
+      <c r="I1543" s="73" t="s">
+        <v>1808</v>
+      </c>
+      <c r="J1543" s="18"/>
+      <c r="K1543" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1543" s="18"/>
+      <c r="M1543" s="21" t="s">
+        <v>2185</v>
+      </c>
+      <c r="N1543" s="40"/>
+      <c r="O1543" s="18"/>
+      <c r="P1543" s="18"/>
+      <c r="Q1543" s="18"/>
+      <c r="R1543" s="16" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:18" ht="15" thickBot="1">
+      <c r="A1544" s="2">
+        <v>38</v>
+      </c>
+      <c r="B1544" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1544" s="80" t="s">
+        <v>2332</v>
+      </c>
+      <c r="D1544" s="80">
+        <v>20790727</v>
+      </c>
+      <c r="E1544" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1544" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1544" s="81">
+        <v>5578</v>
+      </c>
+      <c r="H1544" s="38"/>
+      <c r="I1544" s="73" t="s">
+        <v>1808</v>
+      </c>
+      <c r="J1544" s="18"/>
+      <c r="K1544" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1544" s="18"/>
+      <c r="M1544" s="21" t="s">
+        <v>2185</v>
+      </c>
+      <c r="N1544" s="40"/>
+      <c r="O1544" s="18"/>
+      <c r="P1544" s="18"/>
+      <c r="Q1544" s="18"/>
+      <c r="R1544" s="16" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:18" ht="15" thickBot="1">
+      <c r="A1545" s="2">
+        <v>39</v>
+      </c>
+      <c r="B1545" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1545" s="80" t="s">
+        <v>1736</v>
+      </c>
+      <c r="D1545" s="80">
+        <v>27107582</v>
+      </c>
+      <c r="E1545" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1545" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1545" s="81">
+        <v>2081</v>
+      </c>
+      <c r="H1545" s="38"/>
+      <c r="I1545" s="73" t="s">
+        <v>1808</v>
+      </c>
+      <c r="J1545" s="18"/>
+      <c r="K1545" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1545" s="18"/>
+      <c r="M1545" s="21" t="s">
+        <v>2185</v>
+      </c>
+      <c r="N1545" s="40"/>
+      <c r="O1545" s="18"/>
+      <c r="P1545" s="18"/>
+      <c r="Q1545" s="18"/>
+      <c r="R1545" s="16" t="s">
+        <v>1178</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D3C06B-2D65-4CC8-9F40-21CA45920FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47863C16-6736-45C0-8B35-58917B4CE284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$K$1:$K$1</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11517" uniqueCount="2333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11587" uniqueCount="2354">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -7037,13 +7037,76 @@
   </si>
   <si>
     <t>ABDUL MALIK</t>
+  </si>
+  <si>
+    <t>MANUAL PASS</t>
+  </si>
+  <si>
+    <t>MANUAL PASS(12)</t>
+  </si>
+  <si>
+    <t>629-</t>
+  </si>
+  <si>
+    <t>GHULAM BARI</t>
+  </si>
+  <si>
+    <t>AY1512845</t>
+  </si>
+  <si>
+    <t>2035-</t>
+  </si>
+  <si>
+    <t>ZAHID MEHMOOD</t>
+  </si>
+  <si>
+    <t>CA01558525</t>
+  </si>
+  <si>
+    <t>NADEEM SHAHID</t>
+  </si>
+  <si>
+    <t>JM5157254</t>
+  </si>
+  <si>
+    <t>SHAHID ALI</t>
+  </si>
+  <si>
+    <t>YB1797865</t>
+  </si>
+  <si>
+    <t>MAZHAR RASHID</t>
+  </si>
+  <si>
+    <t>CF9848564</t>
+  </si>
+  <si>
+    <t>ZAHID MAHMOOD</t>
+  </si>
+  <si>
+    <t>NA0156905</t>
+  </si>
+  <si>
+    <t>9257-</t>
+  </si>
+  <si>
+    <t>ABID</t>
+  </si>
+  <si>
+    <t>AU1079424</t>
+  </si>
+  <si>
+    <t>39022-</t>
+  </si>
+  <si>
+    <t>NAEEM IQBAL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="39">
+  <fonts count="41">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7283,6 +7346,22 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="9"/>
+      <color rgb="FFD4EDBC"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="11"/>
+      <color rgb="FF0A53A8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -7430,7 +7509,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7672,8 +7751,41 @@
     <xf numFmtId="0" fontId="38" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7989,7 +8101,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1545"/>
+  <dimension ref="A1:R1553"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -9127,10 +9239,12 @@
       <c r="J23" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="K23" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L23" s="18"/>
+      <c r="K23" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L23" s="53">
+        <v>46246</v>
+      </c>
       <c r="M23" s="18"/>
       <c r="N23" s="54">
         <v>389</v>
@@ -9175,10 +9289,12 @@
       <c r="J24" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="K24" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L24" s="18"/>
+      <c r="K24" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L24" s="53">
+        <v>46246</v>
+      </c>
       <c r="M24" s="18"/>
       <c r="N24" s="54">
         <v>387</v>
@@ -11395,10 +11511,12 @@
       <c r="J69" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="K69" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L69" s="18"/>
+      <c r="K69" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L69" s="53">
+        <v>46246</v>
+      </c>
       <c r="M69" s="18"/>
       <c r="N69" s="54">
         <v>528</v>
@@ -11877,10 +11995,12 @@
       <c r="J79" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="K79" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L79" s="18"/>
+      <c r="K79" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L79" s="53">
+        <v>46246</v>
+      </c>
       <c r="M79" s="18"/>
       <c r="N79" s="54">
         <v>157</v>
@@ -12675,10 +12795,12 @@
       <c r="J96" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="K96" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L96" s="18"/>
+      <c r="K96" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L96" s="53">
+        <v>46246</v>
+      </c>
       <c r="M96" s="18"/>
       <c r="N96" s="54">
         <v>479</v>
@@ -13915,10 +14037,12 @@
       <c r="J121" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="K121" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L121" s="18"/>
+      <c r="K121" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L121" s="53">
+        <v>46246</v>
+      </c>
       <c r="M121" s="18"/>
       <c r="N121" s="54">
         <v>121</v>
@@ -13965,10 +14089,12 @@
       <c r="J122" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="K122" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L122" s="18"/>
+      <c r="K122" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L122" s="53">
+        <v>46246</v>
+      </c>
       <c r="M122" s="18"/>
       <c r="N122" s="54">
         <v>120</v>
@@ -14015,10 +14141,12 @@
       <c r="J123" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="K123" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L123" s="18"/>
+      <c r="K123" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L123" s="53">
+        <v>46246</v>
+      </c>
       <c r="M123" s="18"/>
       <c r="N123" s="54">
         <v>122</v>
@@ -16282,7 +16410,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="169" spans="1:18" ht="15" thickBot="1">
+    <row r="169" spans="1:18" ht="23.4" thickBot="1">
       <c r="A169" s="2">
         <v>168</v>
       </c>
@@ -16313,10 +16441,12 @@
       <c r="J169" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="K169" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L169" s="18"/>
+      <c r="K169" s="11" t="s">
+        <v>2334</v>
+      </c>
+      <c r="L169" s="53">
+        <v>46246</v>
+      </c>
       <c r="M169" s="18"/>
       <c r="N169" s="54">
         <v>333</v>
@@ -16703,10 +16833,12 @@
       <c r="J177" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="K177" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L177" s="18"/>
+      <c r="K177" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L177" s="53">
+        <v>46246</v>
+      </c>
       <c r="M177" s="18"/>
       <c r="N177" s="54">
         <v>233</v>
@@ -16843,10 +16975,12 @@
       <c r="J180" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="K180" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L180" s="18"/>
+      <c r="K180" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L180" s="53">
+        <v>46246</v>
+      </c>
       <c r="M180" s="18"/>
       <c r="N180" s="54">
         <v>448</v>
@@ -17472,7 +17606,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="194" spans="1:18" ht="15" thickBot="1">
+    <row r="194" spans="1:18" ht="23.4" thickBot="1">
       <c r="A194" s="2">
         <v>193</v>
       </c>
@@ -17503,10 +17637,12 @@
       <c r="J194" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="K194" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L194" s="18"/>
+      <c r="K194" s="11" t="s">
+        <v>2334</v>
+      </c>
+      <c r="L194" s="53">
+        <v>46246</v>
+      </c>
       <c r="M194" s="18"/>
       <c r="N194" s="54">
         <v>452</v>
@@ -17919,10 +18055,12 @@
       <c r="J203" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="K203" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L203" s="18"/>
+      <c r="K203" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L203" s="53">
+        <v>46246</v>
+      </c>
       <c r="M203" s="18"/>
       <c r="N203" s="54">
         <v>694</v>
@@ -17967,10 +18105,12 @@
       <c r="J204" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="K204" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L204" s="18"/>
+      <c r="K204" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L204" s="53">
+        <v>46246</v>
+      </c>
       <c r="M204" s="18"/>
       <c r="N204" s="54">
         <v>715</v>
@@ -18468,7 +18608,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="215" spans="1:18" ht="15" thickBot="1">
+    <row r="215" spans="1:18" ht="23.4" thickBot="1">
       <c r="A215" s="2">
         <v>214</v>
       </c>
@@ -18499,10 +18639,12 @@
       <c r="J215" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="K215" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L215" s="18"/>
+      <c r="K215" s="11" t="s">
+        <v>2334</v>
+      </c>
+      <c r="L215" s="53">
+        <v>46246</v>
+      </c>
       <c r="M215" s="18"/>
       <c r="N215" s="54">
         <v>55</v>
@@ -18566,7 +18708,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="217" spans="1:18" ht="15" thickBot="1">
+    <row r="217" spans="1:18" ht="23.4" thickBot="1">
       <c r="A217" s="2">
         <v>216</v>
       </c>
@@ -18597,10 +18739,12 @@
       <c r="J217" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="K217" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L217" s="18"/>
+      <c r="K217" s="11" t="s">
+        <v>2334</v>
+      </c>
+      <c r="L217" s="53">
+        <v>46246</v>
+      </c>
       <c r="M217" s="18"/>
       <c r="N217" s="54">
         <v>56</v>
@@ -18789,10 +18933,12 @@
         <v>485</v>
       </c>
       <c r="J221" s="18"/>
-      <c r="K221" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L221" s="18"/>
+      <c r="K221" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L221" s="53">
+        <v>46249</v>
+      </c>
       <c r="M221" s="18"/>
       <c r="N221" s="54">
         <v>597</v>
@@ -19701,10 +19847,12 @@
         <v>485</v>
       </c>
       <c r="J241" s="18"/>
-      <c r="K241" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L241" s="18"/>
+      <c r="K241" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L241" s="53">
+        <v>46246</v>
+      </c>
       <c r="M241" s="18"/>
       <c r="N241" s="54">
         <v>309</v>
@@ -19795,10 +19943,12 @@
         <v>485</v>
       </c>
       <c r="J243" s="18"/>
-      <c r="K243" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L243" s="18"/>
+      <c r="K243" s="11" t="s">
+        <v>2334</v>
+      </c>
+      <c r="L243" s="53">
+        <v>46246</v>
+      </c>
       <c r="M243" s="18"/>
       <c r="N243" s="54">
         <v>283</v>
@@ -20751,10 +20901,12 @@
         <v>485</v>
       </c>
       <c r="J263" s="18"/>
-      <c r="K263" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L263" s="18"/>
+      <c r="K263" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L263" s="53">
+        <v>46246</v>
+      </c>
       <c r="M263" s="18"/>
       <c r="N263" s="54">
         <v>531</v>
@@ -20797,10 +20949,12 @@
         <v>485</v>
       </c>
       <c r="J264" s="18"/>
-      <c r="K264" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L264" s="18"/>
+      <c r="K264" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L264" s="53">
+        <v>46246</v>
+      </c>
       <c r="M264" s="18"/>
       <c r="N264" s="54">
         <v>566</v>
@@ -20843,10 +20997,12 @@
         <v>485</v>
       </c>
       <c r="J265" s="18"/>
-      <c r="K265" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L265" s="18"/>
+      <c r="K265" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L265" s="53">
+        <v>46246</v>
+      </c>
       <c r="M265" s="18"/>
       <c r="N265" s="54">
         <v>536</v>
@@ -20889,10 +21045,12 @@
         <v>485</v>
       </c>
       <c r="J266" s="18"/>
-      <c r="K266" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L266" s="18"/>
+      <c r="K266" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L266" s="53">
+        <v>46246</v>
+      </c>
       <c r="M266" s="18"/>
       <c r="N266" s="54">
         <v>617</v>
@@ -20935,10 +21093,12 @@
         <v>485</v>
       </c>
       <c r="J267" s="18"/>
-      <c r="K267" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L267" s="18"/>
+      <c r="K267" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L267" s="53">
+        <v>46246</v>
+      </c>
       <c r="M267" s="18"/>
       <c r="N267" s="54">
         <v>422</v>
@@ -24715,10 +24875,12 @@
       <c r="J345" s="15" t="s">
         <v>549</v>
       </c>
-      <c r="K345" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L345" s="18"/>
+      <c r="K345" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L345" s="53">
+        <v>46246</v>
+      </c>
       <c r="M345" s="18"/>
       <c r="N345" s="54">
         <v>484</v>
@@ -24763,10 +24925,12 @@
       <c r="J346" s="15" t="s">
         <v>549</v>
       </c>
-      <c r="K346" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L346" s="18"/>
+      <c r="K346" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L346" s="53">
+        <v>46246</v>
+      </c>
       <c r="M346" s="18"/>
       <c r="N346" s="54">
         <v>431</v>
@@ -24811,10 +24975,12 @@
       <c r="J347" s="15" t="s">
         <v>549</v>
       </c>
-      <c r="K347" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L347" s="18"/>
+      <c r="K347" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L347" s="53">
+        <v>46246</v>
+      </c>
       <c r="M347" s="18"/>
       <c r="N347" s="54">
         <v>432</v>
@@ -24993,10 +25159,12 @@
       <c r="J351" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="K351" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L351" s="18"/>
+      <c r="K351" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L351" s="53">
+        <v>46246</v>
+      </c>
       <c r="M351" s="18"/>
       <c r="N351" s="54">
         <v>473</v>
@@ -25137,10 +25305,12 @@
       <c r="J354" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="K354" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L354" s="18"/>
+      <c r="K354" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L354" s="53">
+        <v>46246</v>
+      </c>
       <c r="M354" s="18"/>
       <c r="N354" s="54">
         <v>148</v>
@@ -25337,10 +25507,12 @@
       <c r="J358" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="K358" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L358" s="18"/>
+      <c r="K358" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L358" s="53">
+        <v>46246</v>
+      </c>
       <c r="M358" s="18"/>
       <c r="N358" s="54">
         <v>163</v>
@@ -27345,10 +27517,12 @@
       <c r="J399" s="15" t="s">
         <v>562</v>
       </c>
-      <c r="K399" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L399" s="18"/>
+      <c r="K399" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L399" s="53">
+        <v>46246</v>
+      </c>
       <c r="M399" s="18"/>
       <c r="N399" s="54">
         <v>459</v>
@@ -27531,10 +27705,12 @@
       <c r="J403" s="15" t="s">
         <v>562</v>
       </c>
-      <c r="K403" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L403" s="18"/>
+      <c r="K403" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L403" s="53">
+        <v>46246</v>
+      </c>
       <c r="M403" s="18"/>
       <c r="N403" s="54">
         <v>395</v>
@@ -29213,10 +29389,12 @@
       <c r="J438" s="15" t="s">
         <v>848</v>
       </c>
-      <c r="K438" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L438" s="18"/>
+      <c r="K438" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L438" s="53">
+        <v>46246</v>
+      </c>
       <c r="M438" s="18"/>
       <c r="N438" s="54">
         <v>464</v>
@@ -29955,10 +30133,12 @@
       <c r="J453" s="15" t="s">
         <v>848</v>
       </c>
-      <c r="K453" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L453" s="18"/>
+      <c r="K453" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L453" s="53">
+        <v>46246</v>
+      </c>
       <c r="M453" s="18"/>
       <c r="N453" s="54">
         <v>435</v>
@@ -30003,10 +30183,12 @@
       <c r="J454" s="15" t="s">
         <v>881</v>
       </c>
-      <c r="K454" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L454" s="18"/>
+      <c r="K454" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L454" s="53">
+        <v>46246</v>
+      </c>
       <c r="M454" s="18"/>
       <c r="N454" s="54">
         <v>199</v>
@@ -30051,10 +30233,12 @@
       <c r="J455" s="15" t="s">
         <v>881</v>
       </c>
-      <c r="K455" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L455" s="18"/>
+      <c r="K455" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L455" s="53">
+        <v>46246</v>
+      </c>
       <c r="M455" s="18"/>
       <c r="N455" s="54">
         <v>197</v>
@@ -30099,10 +30283,12 @@
       <c r="J456" s="15" t="s">
         <v>881</v>
       </c>
-      <c r="K456" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L456" s="18"/>
+      <c r="K456" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L456" s="53">
+        <v>46246</v>
+      </c>
       <c r="M456" s="18"/>
       <c r="N456" s="54">
         <v>196</v>
@@ -30347,10 +30533,12 @@
       <c r="J461" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="K461" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L461" s="18"/>
+      <c r="K461" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L461" s="53">
+        <v>46246</v>
+      </c>
       <c r="M461" s="18"/>
       <c r="N461" s="54">
         <v>415</v>
@@ -30395,10 +30583,12 @@
       <c r="J462" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="K462" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L462" s="18"/>
+      <c r="K462" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L462" s="53">
+        <v>46246</v>
+      </c>
       <c r="M462" s="18"/>
       <c r="N462" s="54">
         <v>403</v>
@@ -30533,10 +30723,12 @@
       <c r="J465" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="K465" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L465" s="18"/>
+      <c r="K465" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L465" s="53">
+        <v>46246</v>
+      </c>
       <c r="M465" s="18"/>
       <c r="N465" s="54">
         <v>267</v>
@@ -30952,8 +31144,8 @@
         <v>46247</v>
       </c>
       <c r="M474" s="18"/>
-      <c r="N474" s="54">
-        <v>629</v>
+      <c r="N474" s="54" t="s">
+        <v>2335</v>
       </c>
       <c r="O474" s="53">
         <v>46244</v>
@@ -31410,7 +31602,9 @@
       </c>
       <c r="L484" s="18"/>
       <c r="M484" s="18"/>
-      <c r="N484" s="40"/>
+      <c r="N484" s="54">
+        <v>95927827</v>
+      </c>
       <c r="O484" s="18"/>
       <c r="P484" s="18"/>
       <c r="Q484" s="11">
@@ -31684,7 +31878,9 @@
       </c>
       <c r="L490" s="18"/>
       <c r="M490" s="18"/>
-      <c r="N490" s="40"/>
+      <c r="N490" s="54">
+        <v>629</v>
+      </c>
       <c r="O490" s="18"/>
       <c r="P490" s="18"/>
       <c r="Q490" s="11">
@@ -31773,10 +31969,12 @@
       <c r="J492" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K492" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L492" s="18"/>
+      <c r="K492" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L492" s="53">
+        <v>46246</v>
+      </c>
       <c r="M492" s="18"/>
       <c r="N492" s="54">
         <v>495</v>
@@ -31867,10 +32065,12 @@
       <c r="J494" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K494" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L494" s="18"/>
+      <c r="K494" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L494" s="53">
+        <v>46246</v>
+      </c>
       <c r="M494" s="18"/>
       <c r="N494" s="54">
         <v>499</v>
@@ -31961,10 +32161,12 @@
       <c r="J496" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K496" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L496" s="18"/>
+      <c r="K496" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L496" s="53">
+        <v>46246</v>
+      </c>
       <c r="M496" s="18"/>
       <c r="N496" s="54">
         <v>494</v>
@@ -32199,10 +32401,12 @@
       <c r="J501" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K501" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L501" s="18"/>
+      <c r="K501" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L501" s="53">
+        <v>46246</v>
+      </c>
       <c r="M501" s="18"/>
       <c r="N501" s="54">
         <v>496</v>
@@ -32635,10 +32839,12 @@
       <c r="J510" s="15" t="s">
         <v>953</v>
       </c>
-      <c r="K510" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L510" s="18"/>
+      <c r="K510" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L510" s="53">
+        <v>46246</v>
+      </c>
       <c r="M510" s="18"/>
       <c r="N510" s="54">
         <v>305</v>
@@ -32731,10 +32937,12 @@
       <c r="J512" s="15" t="s">
         <v>953</v>
       </c>
-      <c r="K512" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L512" s="18"/>
+      <c r="K512" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L512" s="53">
+        <v>46246</v>
+      </c>
       <c r="M512" s="18"/>
       <c r="N512" s="54">
         <v>391</v>
@@ -32917,10 +33125,12 @@
       <c r="J516" s="15" t="s">
         <v>961</v>
       </c>
-      <c r="K516" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L516" s="18"/>
+      <c r="K516" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L516" s="53">
+        <v>46246</v>
+      </c>
       <c r="M516" s="18"/>
       <c r="N516" s="54">
         <v>296</v>
@@ -33059,10 +33269,12 @@
       <c r="J519" s="15" t="s">
         <v>971</v>
       </c>
-      <c r="K519" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L519" s="18"/>
+      <c r="K519" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L519" s="53">
+        <v>46246</v>
+      </c>
       <c r="M519" s="18"/>
       <c r="N519" s="54">
         <v>243</v>
@@ -35169,10 +35381,12 @@
       <c r="J563" s="15" t="s">
         <v>950</v>
       </c>
-      <c r="K563" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L563" s="18"/>
+      <c r="K563" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L563" s="53">
+        <v>46246</v>
+      </c>
       <c r="M563" s="18"/>
       <c r="N563" s="54">
         <v>440</v>
@@ -35451,10 +35665,12 @@
       <c r="J569" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K569" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L569" s="18"/>
+      <c r="K569" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L569" s="53">
+        <v>46246</v>
+      </c>
       <c r="M569" s="18"/>
       <c r="N569" s="54">
         <v>338</v>
@@ -35499,10 +35715,12 @@
       <c r="J570" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K570" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L570" s="18"/>
+      <c r="K570" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L570" s="53">
+        <v>46246</v>
+      </c>
       <c r="M570" s="18"/>
       <c r="N570" s="54">
         <v>339</v>
@@ -35547,10 +35765,12 @@
       <c r="J571" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K571" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L571" s="18"/>
+      <c r="K571" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L571" s="53">
+        <v>46246</v>
+      </c>
       <c r="M571" s="18"/>
       <c r="N571" s="54">
         <v>340</v>
@@ -35645,10 +35865,12 @@
       <c r="J573" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K573" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L573" s="18"/>
+      <c r="K573" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L573" s="53">
+        <v>46246</v>
+      </c>
       <c r="M573" s="18"/>
       <c r="N573" s="54">
         <v>401</v>
@@ -35693,10 +35915,12 @@
       <c r="J574" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K574" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L574" s="18"/>
+      <c r="K574" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L574" s="10">
+        <v>46246</v>
+      </c>
       <c r="M574" s="18"/>
       <c r="N574" s="54">
         <v>246</v>
@@ -35741,10 +35965,12 @@
       <c r="J575" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K575" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L575" s="18"/>
+      <c r="K575" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L575" s="10">
+        <v>46246</v>
+      </c>
       <c r="M575" s="18"/>
       <c r="N575" s="54">
         <v>247</v>
@@ -36179,10 +36405,12 @@
       <c r="J584" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K584" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L584" s="18"/>
+      <c r="K584" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L584" s="53">
+        <v>46246</v>
+      </c>
       <c r="M584" s="18"/>
       <c r="N584" s="54">
         <v>202</v>
@@ -36769,10 +36997,12 @@
       <c r="J596" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K596" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L596" s="18"/>
+      <c r="K596" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L596" s="53">
+        <v>46246</v>
+      </c>
       <c r="M596" s="18"/>
       <c r="N596" s="54">
         <v>59</v>
@@ -36817,10 +37047,12 @@
       <c r="J597" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K597" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L597" s="18"/>
+      <c r="K597" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L597" s="53">
+        <v>46246</v>
+      </c>
       <c r="M597" s="18"/>
       <c r="N597" s="54">
         <v>58</v>
@@ -36865,10 +37097,12 @@
       <c r="J598" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K598" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L598" s="18"/>
+      <c r="K598" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L598" s="53">
+        <v>46246</v>
+      </c>
       <c r="M598" s="18"/>
       <c r="N598" s="54">
         <v>60</v>
@@ -36913,10 +37147,12 @@
       <c r="J599" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K599" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L599" s="18"/>
+      <c r="K599" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L599" s="53">
+        <v>46246</v>
+      </c>
       <c r="M599" s="18"/>
       <c r="N599" s="54">
         <v>316</v>
@@ -36961,10 +37197,12 @@
       <c r="J600" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K600" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L600" s="18"/>
+      <c r="K600" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L600" s="53">
+        <v>46246</v>
+      </c>
       <c r="M600" s="18"/>
       <c r="N600" s="54">
         <v>126</v>
@@ -37105,10 +37343,12 @@
       <c r="J603" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K603" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L603" s="18"/>
+      <c r="K603" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L603" s="53">
+        <v>46246</v>
+      </c>
       <c r="M603" s="18"/>
       <c r="N603" s="54">
         <v>178</v>
@@ -37153,10 +37393,12 @@
       <c r="J604" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K604" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L604" s="18"/>
+      <c r="K604" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L604" s="53">
+        <v>46246</v>
+      </c>
       <c r="M604" s="18"/>
       <c r="N604" s="54">
         <v>179</v>
@@ -37295,10 +37537,12 @@
       <c r="J607" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K607" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L607" s="18"/>
+      <c r="K607" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L607" s="53">
+        <v>46246</v>
+      </c>
       <c r="M607" s="18"/>
       <c r="N607" s="54">
         <v>225</v>
@@ -37343,10 +37587,12 @@
       <c r="J608" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K608" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L608" s="18"/>
+      <c r="K608" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L608" s="53">
+        <v>46246</v>
+      </c>
       <c r="M608" s="18"/>
       <c r="N608" s="54">
         <v>226</v>
@@ -37391,10 +37637,12 @@
       <c r="J609" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K609" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L609" s="18"/>
+      <c r="K609" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L609" s="53">
+        <v>46246</v>
+      </c>
       <c r="M609" s="18"/>
       <c r="N609" s="54">
         <v>203</v>
@@ -37439,10 +37687,12 @@
       <c r="J610" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K610" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L610" s="18"/>
+      <c r="K610" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L610" s="53">
+        <v>46246</v>
+      </c>
       <c r="M610" s="18"/>
       <c r="N610" s="54">
         <v>201</v>
@@ -37487,10 +37737,12 @@
       <c r="J611" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K611" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L611" s="18"/>
+      <c r="K611" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L611" s="53">
+        <v>46246</v>
+      </c>
       <c r="M611" s="18"/>
       <c r="N611" s="54">
         <v>206</v>
@@ -37535,10 +37787,12 @@
       <c r="J612" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K612" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L612" s="18"/>
+      <c r="K612" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L612" s="53">
+        <v>46246</v>
+      </c>
       <c r="M612" s="18"/>
       <c r="N612" s="54">
         <v>139</v>
@@ -37583,10 +37837,12 @@
       <c r="J613" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K613" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L613" s="18"/>
+      <c r="K613" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L613" s="53">
+        <v>46246</v>
+      </c>
       <c r="M613" s="18"/>
       <c r="N613" s="54">
         <v>176</v>
@@ -37631,10 +37887,12 @@
       <c r="J614" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K614" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L614" s="18"/>
+      <c r="K614" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L614" s="53">
+        <v>46246</v>
+      </c>
       <c r="M614" s="18"/>
       <c r="N614" s="54">
         <v>115</v>
@@ -37679,10 +37937,12 @@
       <c r="J615" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K615" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L615" s="18"/>
+      <c r="K615" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L615" s="53">
+        <v>46246</v>
+      </c>
       <c r="M615" s="18"/>
       <c r="N615" s="54">
         <v>49</v>
@@ -37775,10 +38035,12 @@
       <c r="J617" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K617" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L617" s="18"/>
+      <c r="K617" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L617" s="53">
+        <v>46246</v>
+      </c>
       <c r="M617" s="18"/>
       <c r="N617" s="54">
         <v>10</v>
@@ -37823,10 +38085,12 @@
       <c r="J618" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K618" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L618" s="18"/>
+      <c r="K618" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L618" s="53">
+        <v>46246</v>
+      </c>
       <c r="M618" s="18"/>
       <c r="N618" s="54">
         <v>13</v>
@@ -37871,10 +38135,12 @@
       <c r="J619" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K619" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L619" s="18"/>
+      <c r="K619" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L619" s="53">
+        <v>46246</v>
+      </c>
       <c r="M619" s="18"/>
       <c r="N619" s="54">
         <v>11</v>
@@ -37919,10 +38185,12 @@
       <c r="J620" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K620" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L620" s="18"/>
+      <c r="K620" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L620" s="53">
+        <v>46246</v>
+      </c>
       <c r="M620" s="18"/>
       <c r="N620" s="54">
         <v>12</v>
@@ -40475,10 +40743,12 @@
       <c r="J674" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="K674" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L674" s="18"/>
+      <c r="K674" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L674" s="53">
+        <v>46246</v>
+      </c>
       <c r="M674" s="18"/>
       <c r="N674" s="54">
         <v>159</v>
@@ -41057,10 +41327,12 @@
         <v>485</v>
       </c>
       <c r="J686" s="18"/>
-      <c r="K686" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L686" s="18"/>
+      <c r="K686" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L686" s="53">
+        <v>46246</v>
+      </c>
       <c r="M686" s="18"/>
       <c r="N686" s="54">
         <v>714</v>
@@ -41103,10 +41375,12 @@
         <v>485</v>
       </c>
       <c r="J687" s="18"/>
-      <c r="K687" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L687" s="18"/>
+      <c r="K687" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L687" s="53">
+        <v>46246</v>
+      </c>
       <c r="M687" s="18"/>
       <c r="N687" s="54">
         <v>713</v>
@@ -41237,10 +41511,12 @@
         <v>485</v>
       </c>
       <c r="J690" s="18"/>
-      <c r="K690" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L690" s="18"/>
+      <c r="K690" s="11" t="s">
+        <v>2334</v>
+      </c>
+      <c r="L690" s="53">
+        <v>46246</v>
+      </c>
       <c r="M690" s="18"/>
       <c r="N690" s="54">
         <v>417</v>
@@ -41329,10 +41605,12 @@
       <c r="J692" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="K692" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L692" s="18"/>
+      <c r="K692" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L692" s="53">
+        <v>46246</v>
+      </c>
       <c r="M692" s="18"/>
       <c r="N692" s="54">
         <v>227</v>
@@ -41375,10 +41653,12 @@
         <v>485</v>
       </c>
       <c r="J693" s="18"/>
-      <c r="K693" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L693" s="18"/>
+      <c r="K693" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L693" s="53">
+        <v>46246</v>
+      </c>
       <c r="M693" s="18"/>
       <c r="N693" s="54">
         <v>712</v>
@@ -41851,10 +42131,12 @@
       <c r="J703" s="15" t="s">
         <v>1028</v>
       </c>
-      <c r="K703" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L703" s="18"/>
+      <c r="K703" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L703" s="53">
+        <v>46246</v>
+      </c>
       <c r="M703" s="18"/>
       <c r="N703" s="54">
         <v>521</v>
@@ -41899,10 +42181,12 @@
       <c r="J704" s="15" t="s">
         <v>1028</v>
       </c>
-      <c r="K704" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L704" s="18"/>
+      <c r="K704" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L704" s="53">
+        <v>46246</v>
+      </c>
       <c r="M704" s="18"/>
       <c r="N704" s="54">
         <v>519</v>
@@ -41993,10 +42277,12 @@
       <c r="J706" s="15" t="s">
         <v>1028</v>
       </c>
-      <c r="K706" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L706" s="18"/>
+      <c r="K706" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L706" s="53">
+        <v>46246</v>
+      </c>
       <c r="M706" s="18"/>
       <c r="N706" s="54">
         <v>436</v>
@@ -42087,8 +42373,8 @@
       <c r="J708" s="15" t="s">
         <v>1028</v>
       </c>
-      <c r="K708" s="17" t="s">
-        <v>12</v>
+      <c r="K708" s="11" t="s">
+        <v>2333</v>
       </c>
       <c r="L708" s="18"/>
       <c r="M708" s="18"/>
@@ -42271,10 +42557,12 @@
       <c r="J712" s="15" t="s">
         <v>1028</v>
       </c>
-      <c r="K712" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L712" s="18"/>
+      <c r="K712" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L712" s="53">
+        <v>46246</v>
+      </c>
       <c r="M712" s="18"/>
       <c r="N712" s="54">
         <v>469</v>
@@ -42319,10 +42607,12 @@
       <c r="J713" s="15" t="s">
         <v>1028</v>
       </c>
-      <c r="K713" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L713" s="18"/>
+      <c r="K713" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L713" s="53">
+        <v>46246</v>
+      </c>
       <c r="M713" s="18"/>
       <c r="N713" s="54">
         <v>278</v>
@@ -42505,10 +42795,12 @@
       <c r="J717" s="15" t="s">
         <v>1058</v>
       </c>
-      <c r="K717" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L717" s="18"/>
+      <c r="K717" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L717" s="53">
+        <v>46246</v>
+      </c>
       <c r="M717" s="18"/>
       <c r="N717" s="54">
         <v>311</v>
@@ -42551,10 +42843,12 @@
       <c r="J718" s="15" t="s">
         <v>1058</v>
       </c>
-      <c r="K718" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L718" s="18"/>
+      <c r="K718" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L718" s="53">
+        <v>46246</v>
+      </c>
       <c r="M718" s="18"/>
       <c r="N718" s="54">
         <v>312</v>
@@ -42867,10 +43161,12 @@
       <c r="J725" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K725" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L725" s="18"/>
+      <c r="K725" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L725" s="53">
+        <v>46246</v>
+      </c>
       <c r="M725" s="18"/>
       <c r="N725" s="54">
         <v>276</v>
@@ -42915,10 +43211,12 @@
       <c r="J726" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K726" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L726" s="18"/>
+      <c r="K726" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L726" s="53">
+        <v>46246</v>
+      </c>
       <c r="M726" s="18"/>
       <c r="N726" s="54">
         <v>326</v>
@@ -42963,10 +43261,12 @@
       <c r="J727" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K727" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L727" s="18"/>
+      <c r="K727" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L727" s="53">
+        <v>46246</v>
+      </c>
       <c r="M727" s="18"/>
       <c r="N727" s="54">
         <v>268</v>
@@ -43111,10 +43411,12 @@
       <c r="J730" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K730" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L730" s="18"/>
+      <c r="K730" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L730" s="53">
+        <v>46246</v>
+      </c>
       <c r="M730" s="18"/>
       <c r="N730" s="54">
         <v>234</v>
@@ -43209,10 +43511,12 @@
       <c r="J732" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K732" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L732" s="18"/>
+      <c r="K732" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L732" s="53">
+        <v>46246</v>
+      </c>
       <c r="M732" s="18"/>
       <c r="N732" s="54">
         <v>463</v>
@@ -43401,10 +43705,12 @@
       <c r="J736" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K736" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L736" s="18"/>
+      <c r="K736" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L736" s="53">
+        <v>46246</v>
+      </c>
       <c r="M736" s="18"/>
       <c r="N736" s="54">
         <v>462</v>
@@ -43497,10 +43803,12 @@
       <c r="J738" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K738" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L738" s="18"/>
+      <c r="K738" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L738" s="53">
+        <v>46246</v>
+      </c>
       <c r="M738" s="18"/>
       <c r="N738" s="54">
         <v>299</v>
@@ -43545,10 +43853,12 @@
       <c r="J739" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K739" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L739" s="18"/>
+      <c r="K739" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L739" s="53">
+        <v>46246</v>
+      </c>
       <c r="M739" s="18"/>
       <c r="N739" s="54">
         <v>317</v>
@@ -43683,10 +43993,12 @@
       <c r="J742" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K742" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L742" s="18"/>
+      <c r="K742" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L742" s="53">
+        <v>46246</v>
+      </c>
       <c r="M742" s="18"/>
       <c r="N742" s="54">
         <v>404</v>
@@ -43731,10 +44043,12 @@
       <c r="J743" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K743" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L743" s="18"/>
+      <c r="K743" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L743" s="53">
+        <v>46246</v>
+      </c>
       <c r="M743" s="18"/>
       <c r="N743" s="54">
         <v>406</v>
@@ -43779,10 +44093,12 @@
       <c r="J744" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K744" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L744" s="18"/>
+      <c r="K744" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L744" s="53">
+        <v>46246</v>
+      </c>
       <c r="M744" s="18"/>
       <c r="N744" s="54">
         <v>497</v>
@@ -44371,8 +44687,12 @@
       <c r="J756" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K756" s="18"/>
-      <c r="L756" s="18"/>
+      <c r="K756" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L756" s="53">
+        <v>46246</v>
+      </c>
       <c r="M756" s="18"/>
       <c r="N756" s="54">
         <v>20</v>
@@ -45471,10 +45791,12 @@
       <c r="J779" s="15" t="s">
         <v>1207</v>
       </c>
-      <c r="K779" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L779" s="18"/>
+      <c r="K779" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L779" s="53">
+        <v>46246</v>
+      </c>
       <c r="M779" s="18"/>
       <c r="N779" s="54">
         <v>381</v>
@@ -45947,10 +46269,12 @@
       <c r="J789" s="15" t="s">
         <v>1236</v>
       </c>
-      <c r="K789" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L789" s="18"/>
+      <c r="K789" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L789" s="53">
+        <v>46246</v>
+      </c>
       <c r="M789" s="18"/>
       <c r="N789" s="54">
         <v>260</v>
@@ -45995,10 +46319,12 @@
       <c r="J790" s="15" t="s">
         <v>1236</v>
       </c>
-      <c r="K790" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L790" s="18"/>
+      <c r="K790" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L790" s="53">
+        <v>46246</v>
+      </c>
       <c r="M790" s="18"/>
       <c r="N790" s="54">
         <v>252</v>
@@ -46043,10 +46369,12 @@
       <c r="J791" s="15" t="s">
         <v>1236</v>
       </c>
-      <c r="K791" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L791" s="18"/>
+      <c r="K791" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L791" s="53">
+        <v>46246</v>
+      </c>
       <c r="M791" s="18"/>
       <c r="N791" s="54">
         <v>254</v>
@@ -46091,10 +46419,12 @@
       <c r="J792" s="15" t="s">
         <v>1236</v>
       </c>
-      <c r="K792" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L792" s="18"/>
+      <c r="K792" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L792" s="53">
+        <v>46246</v>
+      </c>
       <c r="M792" s="18"/>
       <c r="N792" s="54">
         <v>253</v>
@@ -46935,10 +47265,12 @@
       <c r="J809" s="15" t="s">
         <v>1330</v>
       </c>
-      <c r="K809" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L809" s="18"/>
+      <c r="K809" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L809" s="53">
+        <v>46246</v>
+      </c>
       <c r="M809" s="18"/>
       <c r="N809" s="54">
         <v>218</v>
@@ -46983,10 +47315,12 @@
       <c r="J810" s="15" t="s">
         <v>1330</v>
       </c>
-      <c r="K810" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L810" s="18"/>
+      <c r="K810" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L810" s="53">
+        <v>46246</v>
+      </c>
       <c r="M810" s="18"/>
       <c r="N810" s="54">
         <v>408</v>
@@ -47737,10 +48071,12 @@
       <c r="J826" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="K826" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L826" s="18"/>
+      <c r="K826" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L826" s="53">
+        <v>46246</v>
+      </c>
       <c r="M826" s="18"/>
       <c r="N826" s="54">
         <v>474</v>
@@ -48911,10 +49247,12 @@
       <c r="J851" s="15" t="s">
         <v>968</v>
       </c>
-      <c r="K851" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L851" s="18"/>
+      <c r="K851" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L851" s="53">
+        <v>46246</v>
+      </c>
       <c r="M851" s="18"/>
       <c r="N851" s="54">
         <v>351</v>
@@ -49053,10 +49391,12 @@
       <c r="J854" s="15" t="s">
         <v>950</v>
       </c>
-      <c r="K854" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L854" s="18"/>
+      <c r="K854" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L854" s="53">
+        <v>46246</v>
+      </c>
       <c r="M854" s="18"/>
       <c r="N854" s="54">
         <v>443</v>
@@ -49101,10 +49441,12 @@
       <c r="J855" s="15" t="s">
         <v>950</v>
       </c>
-      <c r="K855" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L855" s="18"/>
+      <c r="K855" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L855" s="53">
+        <v>46246</v>
+      </c>
       <c r="M855" s="18"/>
       <c r="N855" s="54">
         <v>442</v>
@@ -49149,10 +49491,12 @@
       <c r="J856" s="15" t="s">
         <v>950</v>
       </c>
-      <c r="K856" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L856" s="18"/>
+      <c r="K856" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L856" s="53">
+        <v>46246</v>
+      </c>
       <c r="M856" s="18"/>
       <c r="N856" s="54">
         <v>437</v>
@@ -49293,10 +49637,12 @@
       <c r="J859" s="15" t="s">
         <v>1484</v>
       </c>
-      <c r="K859" s="37" t="s">
-        <v>175</v>
-      </c>
-      <c r="L859" s="18"/>
+      <c r="K859" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L859" s="53">
+        <v>46246</v>
+      </c>
       <c r="M859" s="18"/>
       <c r="N859" s="54">
         <v>449</v>
@@ -49341,10 +49687,12 @@
       <c r="J860" s="15" t="s">
         <v>968</v>
       </c>
-      <c r="K860" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L860" s="18"/>
+      <c r="K860" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L860" s="53">
+        <v>46246</v>
+      </c>
       <c r="M860" s="18"/>
       <c r="N860" s="54">
         <v>380</v>
@@ -49433,10 +49781,12 @@
       <c r="J862" s="15" t="s">
         <v>1145</v>
       </c>
-      <c r="K862" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L862" s="18"/>
+      <c r="K862" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L862" s="53">
+        <v>46246</v>
+      </c>
       <c r="M862" s="18"/>
       <c r="N862" s="54">
         <v>510</v>
@@ -50127,10 +50477,12 @@
         <v>485</v>
       </c>
       <c r="J877" s="18"/>
-      <c r="K877" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L877" s="18"/>
+      <c r="K877" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L877" s="53">
+        <v>46246</v>
+      </c>
       <c r="M877" s="18"/>
       <c r="N877" s="54">
         <v>471</v>
@@ -50520,7 +50872,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="886" spans="1:18" ht="15" thickBot="1">
+    <row r="886" spans="1:18" ht="23.4" thickBot="1">
       <c r="A886" s="2">
         <v>121</v>
       </c>
@@ -50551,10 +50903,12 @@
       <c r="J886" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="K886" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L886" s="18"/>
+      <c r="K886" s="11" t="s">
+        <v>2334</v>
+      </c>
+      <c r="L886" s="53">
+        <v>46246</v>
+      </c>
       <c r="M886" s="18"/>
       <c r="N886" s="54">
         <v>334</v>
@@ -50739,10 +51093,12 @@
       <c r="J890" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="K890" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L890" s="18"/>
+      <c r="K890" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L890" s="53">
+        <v>46246</v>
+      </c>
       <c r="M890" s="18"/>
       <c r="N890" s="54">
         <v>363</v>
@@ -51385,10 +51741,12 @@
         <v>485</v>
       </c>
       <c r="J904" s="18"/>
-      <c r="K904" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L904" s="18"/>
+      <c r="K904" s="11" t="s">
+        <v>2334</v>
+      </c>
+      <c r="L904" s="53">
+        <v>46246</v>
+      </c>
       <c r="M904" s="18"/>
       <c r="N904" s="54">
         <v>530</v>
@@ -53803,10 +54161,12 @@
       <c r="J955" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K955" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L955" s="18"/>
+      <c r="K955" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L955" s="53">
+        <v>46246</v>
+      </c>
       <c r="M955" s="18"/>
       <c r="N955" s="54">
         <v>48</v>
@@ -53851,10 +54211,12 @@
       <c r="J956" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K956" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L956" s="18"/>
+      <c r="K956" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L956" s="53">
+        <v>46246</v>
+      </c>
       <c r="M956" s="18"/>
       <c r="N956" s="54">
         <v>47</v>
@@ -53899,10 +54261,12 @@
       <c r="J957" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K957" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L957" s="18"/>
+      <c r="K957" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L957" s="53">
+        <v>46246</v>
+      </c>
       <c r="M957" s="18"/>
       <c r="N957" s="54">
         <v>46</v>
@@ -53947,10 +54311,12 @@
       <c r="J958" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K958" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L958" s="18"/>
+      <c r="K958" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L958" s="53">
+        <v>46246</v>
+      </c>
       <c r="M958" s="18"/>
       <c r="N958" s="54">
         <v>44</v>
@@ -53995,10 +54361,12 @@
       <c r="J959" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K959" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L959" s="18"/>
+      <c r="K959" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L959" s="53">
+        <v>46246</v>
+      </c>
       <c r="M959" s="18"/>
       <c r="N959" s="54">
         <v>45</v>
@@ -54041,10 +54409,12 @@
       <c r="J960" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K960" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L960" s="18"/>
+      <c r="K960" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L960" s="53">
+        <v>46246</v>
+      </c>
       <c r="M960" s="18"/>
       <c r="N960" s="54">
         <v>43</v>
@@ -55319,10 +55689,12 @@
       <c r="J986" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K986" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L986" s="18"/>
+      <c r="K986" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L986" s="53">
+        <v>46246</v>
+      </c>
       <c r="M986" s="18"/>
       <c r="N986" s="54">
         <v>293</v>
@@ -55367,10 +55739,12 @@
       <c r="J987" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K987" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L987" s="18"/>
+      <c r="K987" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L987" s="53">
+        <v>46246</v>
+      </c>
       <c r="M987" s="18"/>
       <c r="N987" s="54">
         <v>291</v>
@@ -55415,10 +55789,12 @@
       <c r="J988" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K988" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L988" s="18"/>
+      <c r="K988" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L988" s="53">
+        <v>46246</v>
+      </c>
       <c r="M988" s="18"/>
       <c r="N988" s="54">
         <v>290</v>
@@ -55463,10 +55839,12 @@
       <c r="J989" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K989" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L989" s="18"/>
+      <c r="K989" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L989" s="53">
+        <v>46246</v>
+      </c>
       <c r="M989" s="18"/>
       <c r="N989" s="54">
         <v>292</v>
@@ -55511,10 +55889,12 @@
       <c r="J990" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K990" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L990" s="18"/>
+      <c r="K990" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L990" s="53">
+        <v>46246</v>
+      </c>
       <c r="M990" s="18"/>
       <c r="N990" s="54">
         <v>280</v>
@@ -55559,10 +55939,12 @@
       <c r="J991" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K991" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L991" s="18"/>
+      <c r="K991" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L991" s="53">
+        <v>46246</v>
+      </c>
       <c r="M991" s="18"/>
       <c r="N991" s="54">
         <v>136</v>
@@ -55607,10 +55989,12 @@
       <c r="J992" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K992" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L992" s="18"/>
+      <c r="K992" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L992" s="53">
+        <v>46246</v>
+      </c>
       <c r="M992" s="18"/>
       <c r="N992" s="54">
         <v>137</v>
@@ -55655,10 +56039,12 @@
       <c r="J993" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K993" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L993" s="18"/>
+      <c r="K993" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L993" s="53">
+        <v>46246</v>
+      </c>
       <c r="M993" s="18"/>
       <c r="N993" s="54">
         <v>138</v>
@@ -55703,10 +56089,12 @@
       <c r="J994" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K994" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L994" s="18"/>
+      <c r="K994" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L994" s="53">
+        <v>46246</v>
+      </c>
       <c r="M994" s="18"/>
       <c r="N994" s="54">
         <v>135</v>
@@ -57206,7 +57594,7 @@
       <c r="K1025" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="L1025" s="38"/>
+      <c r="L1025" s="18"/>
       <c r="M1025" s="18"/>
       <c r="N1025" s="54">
         <v>674</v>
@@ -57251,10 +57639,12 @@
       <c r="J1026" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1026" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1026" s="38"/>
+      <c r="K1026" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1026" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1026" s="18"/>
       <c r="N1026" s="54">
         <v>503</v>
@@ -57299,10 +57689,12 @@
       <c r="J1027" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1027" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1027" s="38"/>
+      <c r="K1027" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1027" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1027" s="18"/>
       <c r="N1027" s="54">
         <v>501</v>
@@ -57350,7 +57742,7 @@
       <c r="K1028" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="L1028" s="38"/>
+      <c r="L1028" s="18"/>
       <c r="M1028" s="18"/>
       <c r="N1028" s="54">
         <v>630</v>
@@ -57395,10 +57787,12 @@
       <c r="J1029" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1029" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1029" s="38"/>
+      <c r="K1029" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1029" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1029" s="18"/>
       <c r="N1029" s="54">
         <v>498</v>
@@ -57443,10 +57837,12 @@
       <c r="J1030" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1030" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1030" s="38"/>
+      <c r="K1030" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1030" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1030" s="18"/>
       <c r="N1030" s="54">
         <v>335</v>
@@ -57494,7 +57890,7 @@
       <c r="K1031" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="L1031" s="38"/>
+      <c r="L1031" s="18"/>
       <c r="M1031" s="18"/>
       <c r="N1031" s="40"/>
       <c r="O1031" s="18"/>
@@ -57540,7 +57936,7 @@
       <c r="K1032" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="L1032" s="38"/>
+      <c r="L1032" s="18"/>
       <c r="M1032" s="18"/>
       <c r="N1032" s="54">
         <v>838</v>
@@ -57585,10 +57981,12 @@
       <c r="J1033" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1033" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1033" s="38"/>
+      <c r="K1033" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1033" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1033" s="18"/>
       <c r="N1033" s="54">
         <v>150</v>
@@ -57633,10 +58031,12 @@
       <c r="J1034" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1034" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1034" s="38"/>
+      <c r="K1034" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1034" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1034" s="18"/>
       <c r="N1034" s="54">
         <v>355</v>
@@ -57681,10 +58081,12 @@
       <c r="J1035" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1035" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1035" s="38"/>
+      <c r="K1035" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1035" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1035" s="18"/>
       <c r="N1035" s="54">
         <v>356</v>
@@ -57730,7 +58132,7 @@
       <c r="K1036" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="L1036" s="38"/>
+      <c r="L1036" s="18"/>
       <c r="M1036" s="18"/>
       <c r="N1036" s="54">
         <v>609</v>
@@ -57775,10 +58177,12 @@
       <c r="J1037" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1037" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1037" s="38"/>
+      <c r="K1037" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1037" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1037" s="18"/>
       <c r="N1037" s="54">
         <v>377</v>
@@ -57826,7 +58230,7 @@
       <c r="K1038" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="L1038" s="38"/>
+      <c r="L1038" s="18"/>
       <c r="M1038" s="18"/>
       <c r="N1038" s="40"/>
       <c r="O1038" s="18"/>
@@ -57872,7 +58276,7 @@
       <c r="K1039" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="L1039" s="38"/>
+      <c r="L1039" s="18"/>
       <c r="M1039" s="18"/>
       <c r="N1039" s="40"/>
       <c r="O1039" s="18"/>
@@ -57915,10 +58319,12 @@
       <c r="J1040" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1040" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1040" s="38"/>
+      <c r="K1040" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1040" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1040" s="18"/>
       <c r="N1040" s="54">
         <v>165</v>
@@ -57966,7 +58372,7 @@
       <c r="K1041" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="L1041" s="38"/>
+      <c r="L1041" s="18"/>
       <c r="M1041" s="18"/>
       <c r="N1041" s="54">
         <v>837</v>
@@ -58014,7 +58420,7 @@
       <c r="K1042" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="L1042" s="38"/>
+      <c r="L1042" s="18"/>
       <c r="M1042" s="18"/>
       <c r="N1042" s="54">
         <v>195</v>
@@ -58061,10 +58467,12 @@
       <c r="J1043" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1043" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1043" s="38"/>
+      <c r="K1043" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1043" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1043" s="18"/>
       <c r="N1043" s="54">
         <v>461</v>
@@ -58112,7 +58520,7 @@
       <c r="K1044" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="L1044" s="38"/>
+      <c r="L1044" s="18"/>
       <c r="M1044" s="18"/>
       <c r="N1044" s="40"/>
       <c r="O1044" s="18"/>
@@ -58158,7 +58566,7 @@
       <c r="K1045" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="L1045" s="38"/>
+      <c r="L1045" s="18"/>
       <c r="M1045" s="18"/>
       <c r="N1045" s="40"/>
       <c r="O1045" s="18"/>
@@ -58204,7 +58612,7 @@
       <c r="K1046" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="L1046" s="38"/>
+      <c r="L1046" s="18"/>
       <c r="M1046" s="18"/>
       <c r="N1046" s="40"/>
       <c r="O1046" s="18"/>
@@ -58250,7 +58658,7 @@
       <c r="K1047" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="L1047" s="38"/>
+      <c r="L1047" s="18"/>
       <c r="M1047" s="18"/>
       <c r="N1047" s="54">
         <v>682</v>
@@ -58298,7 +58706,7 @@
       <c r="K1048" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="L1048" s="38"/>
+      <c r="L1048" s="18"/>
       <c r="M1048" s="18"/>
       <c r="N1048" s="40"/>
       <c r="O1048" s="18"/>
@@ -58685,10 +59093,12 @@
       <c r="J1056" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1056" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1056" s="18"/>
+      <c r="K1056" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1056" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1056" s="18"/>
       <c r="N1056" s="54">
         <v>372</v>
@@ -59529,10 +59939,12 @@
       <c r="J1074" s="15" t="s">
         <v>1672</v>
       </c>
-      <c r="K1074" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1074" s="18"/>
+      <c r="K1074" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1074" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1074" s="18"/>
       <c r="N1074" s="54">
         <v>439</v>
@@ -60749,8 +61161,12 @@
       <c r="J1101" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1101" s="18"/>
-      <c r="L1101" s="18"/>
+      <c r="K1101" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1101" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1101" s="18"/>
       <c r="N1101" s="54">
         <v>434</v>
@@ -61121,10 +61537,12 @@
       <c r="J1109" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1109" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1109" s="18"/>
+      <c r="K1109" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1109" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1109" s="18"/>
       <c r="N1109" s="54">
         <v>502</v>
@@ -61217,10 +61635,12 @@
       <c r="J1111" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1111" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1111" s="18"/>
+      <c r="K1111" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1111" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1111" s="18"/>
       <c r="N1111" s="54">
         <v>375</v>
@@ -61265,10 +61685,12 @@
       <c r="J1112" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1112" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1112" s="18"/>
+      <c r="K1112" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1112" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1112" s="18"/>
       <c r="N1112" s="54">
         <v>376</v>
@@ -65899,10 +66321,12 @@
       <c r="J1219" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1219" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1219" s="18"/>
+      <c r="K1219" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1219" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1219" s="18"/>
       <c r="N1219" s="54">
         <v>322</v>
@@ -65981,10 +66405,12 @@
       <c r="J1221" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1221" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1221" s="18"/>
+      <c r="K1221" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1221" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1221" s="18"/>
       <c r="N1221" s="54">
         <v>455</v>
@@ -68345,10 +68771,12 @@
       <c r="J1272" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1272" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1272" s="18"/>
+      <c r="K1272" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1272" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1272" s="18"/>
       <c r="N1272" s="54">
         <v>412</v>
@@ -72627,10 +73055,12 @@
       <c r="J1365" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1365" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1365" s="18"/>
+      <c r="K1365" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1365" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1365" s="18"/>
       <c r="N1365" s="54">
         <v>520</v>
@@ -76256,7 +76686,9 @@
       <c r="K1445" s="60" t="s">
         <v>1189</v>
       </c>
-      <c r="L1445" s="18"/>
+      <c r="L1445" s="53">
+        <v>46249</v>
+      </c>
       <c r="M1445" s="18"/>
       <c r="N1445" s="54">
         <v>817</v>
@@ -79483,7 +79915,7 @@
       <c r="B1517" s="10">
         <v>46246</v>
       </c>
-      <c r="C1517" s="55" t="s">
+      <c r="C1517" s="66" t="s">
         <v>2293</v>
       </c>
       <c r="D1517" s="55" t="s">
@@ -79529,7 +79961,7 @@
       <c r="B1518" s="10">
         <v>46246</v>
       </c>
-      <c r="C1518" s="55" t="s">
+      <c r="C1518" s="66" t="s">
         <v>2295</v>
       </c>
       <c r="D1518" s="55" t="s">
@@ -79575,7 +80007,7 @@
       <c r="B1519" s="10">
         <v>46246</v>
       </c>
-      <c r="C1519" s="55" t="s">
+      <c r="C1519" s="66" t="s">
         <v>2297</v>
       </c>
       <c r="D1519" s="55" t="s">
@@ -79621,7 +80053,7 @@
       <c r="B1520" s="10">
         <v>46246</v>
       </c>
-      <c r="C1520" s="55" t="s">
+      <c r="C1520" s="66" t="s">
         <v>2299</v>
       </c>
       <c r="D1520" s="55" t="s">
@@ -79658,14 +80090,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1521" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1521" spans="1:18" ht="28.8" thickBot="1">
       <c r="A1521" s="2">
         <v>15</v>
       </c>
       <c r="B1521" s="10">
         <v>46246</v>
       </c>
-      <c r="C1521" s="55" t="s">
+      <c r="C1521" s="66" t="s">
         <v>2301</v>
       </c>
       <c r="D1521" s="55" t="s">
@@ -79709,7 +80141,7 @@
       <c r="B1522" s="10">
         <v>46246</v>
       </c>
-      <c r="C1522" s="55" t="s">
+      <c r="C1522" s="66" t="s">
         <v>2303</v>
       </c>
       <c r="D1522" s="55" t="s">
@@ -79753,7 +80185,7 @@
       <c r="B1523" s="10">
         <v>46246</v>
       </c>
-      <c r="C1523" s="55" t="s">
+      <c r="C1523" s="66" t="s">
         <v>2305</v>
       </c>
       <c r="D1523" s="55" t="s">
@@ -79795,7 +80227,7 @@
       <c r="B1524" s="10">
         <v>46246</v>
       </c>
-      <c r="C1524" s="55" t="s">
+      <c r="C1524" s="66" t="s">
         <v>2307</v>
       </c>
       <c r="D1524" s="55">
@@ -79839,7 +80271,7 @@
       <c r="B1525" s="10">
         <v>46246</v>
       </c>
-      <c r="C1525" s="55" t="s">
+      <c r="C1525" s="66" t="s">
         <v>2308</v>
       </c>
       <c r="D1525" s="55" t="s">
@@ -79883,7 +80315,7 @@
       <c r="B1526" s="10">
         <v>46246</v>
       </c>
-      <c r="C1526" s="55" t="s">
+      <c r="C1526" s="66" t="s">
         <v>2311</v>
       </c>
       <c r="D1526" s="55" t="s">
@@ -79929,7 +80361,7 @@
       <c r="B1527" s="10">
         <v>46246</v>
       </c>
-      <c r="C1527" s="55" t="s">
+      <c r="C1527" s="66" t="s">
         <v>2313</v>
       </c>
       <c r="D1527" s="55" t="s">
@@ -79975,7 +80407,7 @@
       <c r="B1528" s="10">
         <v>46246</v>
       </c>
-      <c r="C1528" s="55" t="s">
+      <c r="C1528" s="66" t="s">
         <v>2315</v>
       </c>
       <c r="D1528" s="55" t="s">
@@ -80021,7 +80453,7 @@
       <c r="B1529" s="10">
         <v>46246</v>
       </c>
-      <c r="C1529" s="55" t="s">
+      <c r="C1529" s="66" t="s">
         <v>27</v>
       </c>
       <c r="D1529" s="55" t="s">
@@ -80060,12 +80492,12 @@
     </row>
     <row r="1530" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1530" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1530" s="10">
         <v>46246</v>
       </c>
-      <c r="C1530" s="55" t="s">
+      <c r="C1530" s="66" t="s">
         <v>2318</v>
       </c>
       <c r="D1530" s="55">
@@ -80104,7 +80536,7 @@
     </row>
     <row r="1531" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1531" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1531" s="10">
         <v>46246</v>
@@ -80148,7 +80580,7 @@
     </row>
     <row r="1532" spans="1:18" ht="15" thickBot="1">
       <c r="A1532" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B1532" s="10">
         <v>46246</v>
@@ -80194,7 +80626,7 @@
     </row>
     <row r="1533" spans="1:18" ht="15" thickBot="1">
       <c r="A1533" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B1533" s="10">
         <v>46246</v>
@@ -80240,7 +80672,7 @@
     </row>
     <row r="1534" spans="1:18" ht="27.6" thickBot="1">
       <c r="A1534" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B1534" s="10">
         <v>46246</v>
@@ -80286,7 +80718,7 @@
     </row>
     <row r="1535" spans="1:18" ht="15" thickBot="1">
       <c r="A1535" s="2">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B1535" s="10">
         <v>46246</v>
@@ -80332,7 +80764,7 @@
     </row>
     <row r="1536" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1536" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B1536" s="10">
         <v>46246</v>
@@ -80376,7 +80808,7 @@
     </row>
     <row r="1537" spans="1:18" ht="15" thickBot="1">
       <c r="A1537" s="2">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B1537" s="10">
         <v>46246</v>
@@ -80422,7 +80854,7 @@
     </row>
     <row r="1538" spans="1:18" ht="15" thickBot="1">
       <c r="A1538" s="2">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B1538" s="10">
         <v>46246</v>
@@ -80451,7 +80883,9 @@
       <c r="J1538" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1538" s="18"/>
+      <c r="K1538" s="30" t="s">
+        <v>1596</v>
+      </c>
       <c r="L1538" s="18"/>
       <c r="M1538" s="18"/>
       <c r="N1538" s="40"/>
@@ -80464,12 +80898,12 @@
     </row>
     <row r="1539" spans="1:18" ht="15" thickBot="1">
       <c r="A1539" s="2">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B1539" s="10">
         <v>46246</v>
       </c>
-      <c r="C1539" s="80" t="s">
+      <c r="C1539" s="81" t="s">
         <v>2327</v>
       </c>
       <c r="D1539" s="80">
@@ -80481,7 +80915,7 @@
       <c r="F1539" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="G1539" s="81">
+      <c r="G1539" s="74">
         <v>925</v>
       </c>
       <c r="H1539" s="38"/>
@@ -80506,12 +80940,12 @@
     </row>
     <row r="1540" spans="1:18" ht="27.6" thickBot="1">
       <c r="A1540" s="2">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B1540" s="10">
         <v>46246</v>
       </c>
-      <c r="C1540" s="80" t="s">
+      <c r="C1540" s="81" t="s">
         <v>2328</v>
       </c>
       <c r="D1540" s="80">
@@ -80523,7 +80957,7 @@
       <c r="F1540" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="G1540" s="81">
+      <c r="G1540" s="74">
         <v>2698</v>
       </c>
       <c r="H1540" s="38"/>
@@ -80548,12 +80982,12 @@
     </row>
     <row r="1541" spans="1:18" ht="27.6" thickBot="1">
       <c r="A1541" s="2">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B1541" s="10">
         <v>46246</v>
       </c>
-      <c r="C1541" s="80" t="s">
+      <c r="C1541" s="81" t="s">
         <v>2329</v>
       </c>
       <c r="D1541" s="80">
@@ -80565,7 +80999,7 @@
       <c r="F1541" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="G1541" s="81">
+      <c r="G1541" s="74">
         <v>9854</v>
       </c>
       <c r="H1541" s="38"/>
@@ -80590,12 +81024,12 @@
     </row>
     <row r="1542" spans="1:18" ht="40.799999999999997" thickBot="1">
       <c r="A1542" s="2">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B1542" s="10">
         <v>46246</v>
       </c>
-      <c r="C1542" s="80" t="s">
+      <c r="C1542" s="81" t="s">
         <v>2330</v>
       </c>
       <c r="D1542" s="80">
@@ -80607,7 +81041,7 @@
       <c r="F1542" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="G1542" s="81">
+      <c r="G1542" s="74">
         <v>9965</v>
       </c>
       <c r="H1542" s="38"/>
@@ -80632,12 +81066,12 @@
     </row>
     <row r="1543" spans="1:18" ht="27.6" thickBot="1">
       <c r="A1543" s="2">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="B1543" s="10">
         <v>46246</v>
       </c>
-      <c r="C1543" s="80" t="s">
+      <c r="C1543" s="81" t="s">
         <v>2331</v>
       </c>
       <c r="D1543" s="80">
@@ -80649,7 +81083,7 @@
       <c r="F1543" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="G1543" s="81">
+      <c r="G1543" s="74">
         <v>5671</v>
       </c>
       <c r="H1543" s="38"/>
@@ -80674,12 +81108,12 @@
     </row>
     <row r="1544" spans="1:18" ht="15" thickBot="1">
       <c r="A1544" s="2">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="B1544" s="10">
         <v>46246</v>
       </c>
-      <c r="C1544" s="80" t="s">
+      <c r="C1544" s="81" t="s">
         <v>2332</v>
       </c>
       <c r="D1544" s="80">
@@ -80691,7 +81125,7 @@
       <c r="F1544" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="G1544" s="81">
+      <c r="G1544" s="74">
         <v>5578</v>
       </c>
       <c r="H1544" s="38"/>
@@ -80716,12 +81150,12 @@
     </row>
     <row r="1545" spans="1:18" ht="15" thickBot="1">
       <c r="A1545" s="2">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="B1545" s="10">
         <v>46246</v>
       </c>
-      <c r="C1545" s="80" t="s">
+      <c r="C1545" s="81" t="s">
         <v>1736</v>
       </c>
       <c r="D1545" s="80">
@@ -80733,7 +81167,7 @@
       <c r="F1545" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="G1545" s="81">
+      <c r="G1545" s="74">
         <v>2081</v>
       </c>
       <c r="H1545" s="38"/>
@@ -80756,6 +81190,370 @@
         <v>1178</v>
       </c>
     </row>
+    <row r="1546" spans="1:18" ht="15" thickBot="1">
+      <c r="A1546" s="2">
+        <v>24</v>
+      </c>
+      <c r="B1546" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1546" s="55" t="s">
+        <v>2336</v>
+      </c>
+      <c r="D1546" s="55" t="s">
+        <v>2337</v>
+      </c>
+      <c r="E1546" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1546" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1546" s="74">
+        <v>68798</v>
+      </c>
+      <c r="H1546" s="66" t="s">
+        <v>2338</v>
+      </c>
+      <c r="I1546" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1546" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1546" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1546" s="18"/>
+      <c r="M1546" s="18"/>
+      <c r="N1546" s="40"/>
+      <c r="O1546" s="18"/>
+      <c r="P1546" s="18"/>
+      <c r="Q1546" s="15">
+        <v>95246598</v>
+      </c>
+      <c r="R1546" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:18" ht="15" thickBot="1">
+      <c r="A1547" s="2">
+        <v>25</v>
+      </c>
+      <c r="B1547" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1547" s="23" t="s">
+        <v>2339</v>
+      </c>
+      <c r="D1547" s="11" t="s">
+        <v>2340</v>
+      </c>
+      <c r="E1547" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1547" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1547" s="56">
+        <v>78025</v>
+      </c>
+      <c r="H1547" s="15">
+        <v>62263</v>
+      </c>
+      <c r="I1547" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1547" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1547" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1547" s="18"/>
+      <c r="M1547" s="18"/>
+      <c r="N1547" s="40"/>
+      <c r="O1547" s="18"/>
+      <c r="P1547" s="18"/>
+      <c r="Q1547" s="15">
+        <v>77504531</v>
+      </c>
+      <c r="R1547" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:18" ht="15" thickBot="1">
+      <c r="A1548" s="2">
+        <v>26</v>
+      </c>
+      <c r="B1548" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1548" s="23" t="s">
+        <v>2341</v>
+      </c>
+      <c r="D1548" s="11" t="s">
+        <v>2342</v>
+      </c>
+      <c r="E1548" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1548" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1548" s="14">
+        <v>38476</v>
+      </c>
+      <c r="H1548" s="15">
+        <v>42440</v>
+      </c>
+      <c r="I1548" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1548" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1548" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1548" s="18"/>
+      <c r="M1548" s="18"/>
+      <c r="N1548" s="40"/>
+      <c r="O1548" s="18"/>
+      <c r="P1548" s="18"/>
+      <c r="Q1548" s="15">
+        <v>77500689</v>
+      </c>
+      <c r="R1548" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:18" ht="15" thickBot="1">
+      <c r="A1549" s="2">
+        <v>27</v>
+      </c>
+      <c r="B1549" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1549" s="23" t="s">
+        <v>2343</v>
+      </c>
+      <c r="D1549" s="11" t="s">
+        <v>2344</v>
+      </c>
+      <c r="E1549" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1549" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1549" s="14">
+        <v>42762</v>
+      </c>
+      <c r="H1549" s="15">
+        <v>45609</v>
+      </c>
+      <c r="I1549" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1549" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1549" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1549" s="18"/>
+      <c r="M1549" s="18"/>
+      <c r="N1549" s="40"/>
+      <c r="O1549" s="18"/>
+      <c r="P1549" s="18"/>
+      <c r="Q1549" s="15">
+        <v>971524009286</v>
+      </c>
+      <c r="R1549" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:18" ht="15" thickBot="1">
+      <c r="A1550" s="2">
+        <v>28</v>
+      </c>
+      <c r="B1550" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1550" s="23" t="s">
+        <v>2345</v>
+      </c>
+      <c r="D1550" s="11" t="s">
+        <v>2346</v>
+      </c>
+      <c r="E1550" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1550" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1550" s="14">
+        <v>52529</v>
+      </c>
+      <c r="H1550" s="15">
+        <v>65404</v>
+      </c>
+      <c r="I1550" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1550" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1550" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1550" s="18"/>
+      <c r="M1550" s="18"/>
+      <c r="N1550" s="40"/>
+      <c r="O1550" s="18"/>
+      <c r="P1550" s="18"/>
+      <c r="Q1550" s="15">
+        <v>971508436604</v>
+      </c>
+      <c r="R1550" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:18" ht="15" thickBot="1">
+      <c r="A1551" s="2">
+        <v>29</v>
+      </c>
+      <c r="B1551" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1551" s="23" t="s">
+        <v>2347</v>
+      </c>
+      <c r="D1551" s="11" t="s">
+        <v>2348</v>
+      </c>
+      <c r="E1551" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1551" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1551" s="14">
+        <v>90498</v>
+      </c>
+      <c r="H1551" s="15" t="s">
+        <v>2349</v>
+      </c>
+      <c r="I1551" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1551" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1551" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1551" s="18"/>
+      <c r="M1551" s="18"/>
+      <c r="N1551" s="40"/>
+      <c r="O1551" s="18"/>
+      <c r="P1551" s="18"/>
+      <c r="Q1551" s="15">
+        <v>501310447</v>
+      </c>
+      <c r="R1551" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:18" ht="15" thickBot="1">
+      <c r="A1552" s="2">
+        <v>30</v>
+      </c>
+      <c r="B1552" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C1552" s="23" t="s">
+        <v>2350</v>
+      </c>
+      <c r="D1552" s="11" t="s">
+        <v>2351</v>
+      </c>
+      <c r="E1552" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1552" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1552" s="14">
+        <v>38386</v>
+      </c>
+      <c r="H1552" s="15" t="s">
+        <v>2352</v>
+      </c>
+      <c r="I1552" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1552" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1552" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1552" s="18"/>
+      <c r="M1552" s="18"/>
+      <c r="N1552" s="40"/>
+      <c r="O1552" s="18"/>
+      <c r="P1552" s="18"/>
+      <c r="Q1552" s="15">
+        <v>502187198</v>
+      </c>
+      <c r="R1552" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:18" ht="24.6" thickBot="1">
+      <c r="A1553" s="2">
+        <v>31</v>
+      </c>
+      <c r="B1553" s="82"/>
+      <c r="C1553" s="83" t="s">
+        <v>2353</v>
+      </c>
+      <c r="D1553" s="84">
+        <v>70549062</v>
+      </c>
+      <c r="E1553" s="85" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1553" s="86" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1553" s="87">
+        <v>8846</v>
+      </c>
+      <c r="H1553" s="88">
+        <v>4252</v>
+      </c>
+      <c r="I1553" s="89" t="s">
+        <v>1177</v>
+      </c>
+      <c r="J1553" s="82"/>
+      <c r="K1553" s="90" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1553" s="82"/>
+      <c r="M1553" s="91" t="s">
+        <v>1999</v>
+      </c>
+      <c r="N1553" s="92"/>
+      <c r="O1553" s="82"/>
+      <c r="P1553" s="82"/>
+      <c r="Q1553" s="82"/>
+      <c r="R1553" s="91" t="s">
+        <v>1178</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47863C16-6736-45C0-8B35-58917B4CE284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772ED5EB-2B84-4DA3-B4C9-51C0D5DE29B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11587" uniqueCount="2354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11652" uniqueCount="2369">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -7042,9 +7042,6 @@
     <t>MANUAL PASS</t>
   </si>
   <si>
-    <t>MANUAL PASS(12)</t>
-  </si>
-  <si>
     <t>629-</t>
   </si>
   <si>
@@ -7100,13 +7097,61 @@
   </si>
   <si>
     <t>NAEEM IQBAL</t>
+  </si>
+  <si>
+    <t>1//862</t>
+  </si>
+  <si>
+    <t>6//859</t>
+  </si>
+  <si>
+    <t>ZAFAR</t>
+  </si>
+  <si>
+    <t>AF5529406</t>
+  </si>
+  <si>
+    <t>DILDAR AHMED</t>
+  </si>
+  <si>
+    <t>MUDASSAR IJAZ</t>
+  </si>
+  <si>
+    <t>CL1514484</t>
+  </si>
+  <si>
+    <t>RASHIID MUNAWAR</t>
+  </si>
+  <si>
+    <t>SYED MUSTANSAR</t>
+  </si>
+  <si>
+    <t>GA1809344</t>
+  </si>
+  <si>
+    <t>NAUMAN ALI</t>
+  </si>
+  <si>
+    <t>VC1797374</t>
+  </si>
+  <si>
+    <t>AMJAD PERVAIZ</t>
+  </si>
+  <si>
+    <t>2500*</t>
+  </si>
+  <si>
+    <t>SHAH FAISAL</t>
+  </si>
+  <si>
+    <t>2317*</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="41">
+  <fonts count="39">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7346,22 +7391,6 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <strike/>
-      <sz val="9"/>
-      <color rgb="FFD4EDBC"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <strike/>
-      <sz val="11"/>
-      <color rgb="FF0A53A8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -7509,7 +7538,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7753,39 +7782,6 @@
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8101,7 +8097,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1553"/>
+  <dimension ref="A1:R1561"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -10776,7 +10772,9 @@
         <v>46247</v>
       </c>
       <c r="M54" s="18"/>
-      <c r="N54" s="40"/>
+      <c r="N54" s="54">
+        <v>872</v>
+      </c>
       <c r="O54" s="18"/>
       <c r="P54" s="18"/>
       <c r="Q54" s="11">
@@ -14241,10 +14239,12 @@
       <c r="J125" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="K125" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L125" s="18"/>
+      <c r="K125" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L125" s="53">
+        <v>46246</v>
+      </c>
       <c r="M125" s="18"/>
       <c r="N125" s="54">
         <v>534</v>
@@ -14296,7 +14296,9 @@
         <v>46247</v>
       </c>
       <c r="M126" s="18"/>
-      <c r="N126" s="40"/>
+      <c r="N126" s="54">
+        <v>854</v>
+      </c>
       <c r="O126" s="18"/>
       <c r="P126" s="18"/>
       <c r="Q126" s="11">
@@ -16410,7 +16412,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="169" spans="1:18" ht="23.4" thickBot="1">
+    <row r="169" spans="1:18" ht="15" thickBot="1">
       <c r="A169" s="2">
         <v>168</v>
       </c>
@@ -16442,7 +16444,7 @@
         <v>124</v>
       </c>
       <c r="K169" s="11" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="L169" s="53">
         <v>46246</v>
@@ -16934,7 +16936,9 @@
       </c>
       <c r="L179" s="18"/>
       <c r="M179" s="18"/>
-      <c r="N179" s="40"/>
+      <c r="N179" s="54">
+        <v>880</v>
+      </c>
       <c r="O179" s="18"/>
       <c r="P179" s="18"/>
       <c r="Q179" s="11">
@@ -17606,7 +17610,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="194" spans="1:18" ht="23.4" thickBot="1">
+    <row r="194" spans="1:18" ht="15" thickBot="1">
       <c r="A194" s="2">
         <v>193</v>
       </c>
@@ -17638,7 +17642,7 @@
         <v>124</v>
       </c>
       <c r="K194" s="11" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="L194" s="53">
         <v>46246</v>
@@ -18608,7 +18612,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="215" spans="1:18" ht="23.4" thickBot="1">
+    <row r="215" spans="1:18" ht="15" thickBot="1">
       <c r="A215" s="2">
         <v>214</v>
       </c>
@@ -18640,7 +18644,7 @@
         <v>124</v>
       </c>
       <c r="K215" s="11" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="L215" s="53">
         <v>46246</v>
@@ -18708,7 +18712,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="217" spans="1:18" ht="23.4" thickBot="1">
+    <row r="217" spans="1:18" ht="15" thickBot="1">
       <c r="A217" s="2">
         <v>216</v>
       </c>
@@ -18740,7 +18744,7 @@
         <v>124</v>
       </c>
       <c r="K217" s="11" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="L217" s="53">
         <v>46246</v>
@@ -19944,7 +19948,7 @@
       </c>
       <c r="J243" s="18"/>
       <c r="K243" s="11" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="L243" s="53">
         <v>46246</v>
@@ -22445,10 +22449,12 @@
       <c r="J295" s="15" t="s">
         <v>382</v>
       </c>
-      <c r="K295" s="67" t="s">
-        <v>1285</v>
-      </c>
-      <c r="L295" s="18"/>
+      <c r="K295" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L295" s="53">
+        <v>46246</v>
+      </c>
       <c r="M295" s="18"/>
       <c r="N295" s="54">
         <v>538</v>
@@ -22799,10 +22805,12 @@
       <c r="J302" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K302" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L302" s="18"/>
+      <c r="K302" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L302" s="53">
+        <v>46246</v>
+      </c>
       <c r="M302" s="18"/>
       <c r="N302" s="54">
         <v>87</v>
@@ -24827,10 +24835,12 @@
       <c r="J344" s="15" t="s">
         <v>549</v>
       </c>
-      <c r="K344" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L344" s="18"/>
+      <c r="K344" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L344" s="53">
+        <v>46246</v>
+      </c>
       <c r="M344" s="18"/>
       <c r="N344" s="54">
         <v>476</v>
@@ -25025,10 +25035,12 @@
       <c r="J348" s="15" t="s">
         <v>549</v>
       </c>
-      <c r="K348" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L348" s="18"/>
+      <c r="K348" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L348" s="53">
+        <v>46246</v>
+      </c>
       <c r="M348" s="18"/>
       <c r="N348" s="54">
         <v>460</v>
@@ -25113,10 +25125,12 @@
       <c r="J350" s="15" t="s">
         <v>549</v>
       </c>
-      <c r="K350" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L350" s="18"/>
+      <c r="K350" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L350" s="53">
+        <v>46246</v>
+      </c>
       <c r="M350" s="18"/>
       <c r="N350" s="54">
         <v>653</v>
@@ -27897,10 +27911,12 @@
       <c r="J407" s="15" t="s">
         <v>562</v>
       </c>
-      <c r="K407" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L407" s="18"/>
+      <c r="K407" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L407" s="53">
+        <v>46246</v>
+      </c>
       <c r="M407" s="18"/>
       <c r="N407" s="54">
         <v>634</v>
@@ -28145,10 +28161,12 @@
       <c r="J412" s="15" t="s">
         <v>562</v>
       </c>
-      <c r="K412" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L412" s="18"/>
+      <c r="K412" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L412" s="53">
+        <v>46246</v>
+      </c>
       <c r="M412" s="18"/>
       <c r="N412" s="54">
         <v>552</v>
@@ -28517,10 +28535,12 @@
       <c r="J420" s="15" t="s">
         <v>562</v>
       </c>
-      <c r="K420" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L420" s="18"/>
+      <c r="K420" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L420" s="53">
+        <v>46246</v>
+      </c>
       <c r="M420" s="18"/>
       <c r="N420" s="54">
         <v>647</v>
@@ -28616,7 +28636,9 @@
       </c>
       <c r="L422" s="18"/>
       <c r="M422" s="18"/>
-      <c r="N422" s="40"/>
+      <c r="N422" s="54">
+        <v>868</v>
+      </c>
       <c r="O422" s="18"/>
       <c r="P422" s="18"/>
       <c r="Q422" s="11">
@@ -28703,10 +28725,12 @@
       <c r="J424" s="15" t="s">
         <v>562</v>
       </c>
-      <c r="K424" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L424" s="18"/>
+      <c r="K424" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L424" s="53">
+        <v>46246</v>
+      </c>
       <c r="M424" s="18"/>
       <c r="N424" s="54">
         <v>556</v>
@@ -28797,10 +28821,12 @@
       <c r="J426" s="15" t="s">
         <v>562</v>
       </c>
-      <c r="K426" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L426" s="18"/>
+      <c r="K426" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L426" s="53">
+        <v>46246</v>
+      </c>
       <c r="M426" s="18"/>
       <c r="N426" s="54">
         <v>654</v>
@@ -29095,10 +29121,12 @@
       <c r="J432" s="15" t="s">
         <v>839</v>
       </c>
-      <c r="K432" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L432" s="18"/>
+      <c r="K432" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L432" s="53">
+        <v>46246</v>
+      </c>
       <c r="M432" s="18"/>
       <c r="N432" s="54">
         <v>540</v>
@@ -31145,7 +31173,7 @@
       </c>
       <c r="M474" s="18"/>
       <c r="N474" s="54" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="O474" s="53">
         <v>46244</v>
@@ -31558,10 +31586,14 @@
       </c>
       <c r="L483" s="18"/>
       <c r="M483" s="18"/>
-      <c r="N483" s="40"/>
+      <c r="N483" s="54">
+        <v>850</v>
+      </c>
       <c r="O483" s="18"/>
       <c r="P483" s="18"/>
-      <c r="Q483" s="18"/>
+      <c r="Q483" s="11">
+        <v>95927827</v>
+      </c>
       <c r="R483" s="20" t="s">
         <v>11</v>
       </c>
@@ -31603,7 +31635,7 @@
       <c r="L484" s="18"/>
       <c r="M484" s="18"/>
       <c r="N484" s="54">
-        <v>95927827</v>
+        <v>849</v>
       </c>
       <c r="O484" s="18"/>
       <c r="P484" s="18"/>
@@ -31650,7 +31682,9 @@
       </c>
       <c r="L485" s="18"/>
       <c r="M485" s="18"/>
-      <c r="N485" s="40"/>
+      <c r="N485" s="54">
+        <v>852</v>
+      </c>
       <c r="O485" s="18"/>
       <c r="P485" s="18"/>
       <c r="Q485" s="11">
@@ -31698,7 +31732,9 @@
         <v>46250</v>
       </c>
       <c r="M486" s="18"/>
-      <c r="N486" s="40"/>
+      <c r="N486" s="54">
+        <v>858</v>
+      </c>
       <c r="O486" s="18"/>
       <c r="P486" s="18"/>
       <c r="Q486" s="11">
@@ -31788,7 +31824,9 @@
       </c>
       <c r="L488" s="18"/>
       <c r="M488" s="18"/>
-      <c r="N488" s="40"/>
+      <c r="N488" s="54">
+        <v>851</v>
+      </c>
       <c r="O488" s="18"/>
       <c r="P488" s="18"/>
       <c r="Q488" s="18"/>
@@ -31921,10 +31959,12 @@
       <c r="J491" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K491" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L491" s="18"/>
+      <c r="K491" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L491" s="53">
+        <v>46246</v>
+      </c>
       <c r="M491" s="18"/>
       <c r="N491" s="54">
         <v>493</v>
@@ -32259,10 +32299,12 @@
       <c r="J498" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K498" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L498" s="18"/>
+      <c r="K498" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L498" s="53">
+        <v>46246</v>
+      </c>
       <c r="M498" s="18"/>
       <c r="N498" s="54">
         <v>806</v>
@@ -32307,10 +32349,12 @@
       <c r="J499" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K499" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L499" s="18"/>
+      <c r="K499" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L499" s="53">
+        <v>46246</v>
+      </c>
       <c r="M499" s="18"/>
       <c r="N499" s="54">
         <v>808</v>
@@ -32451,10 +32495,12 @@
       <c r="J502" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K502" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L502" s="18"/>
+      <c r="K502" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L502" s="53">
+        <v>46246</v>
+      </c>
       <c r="M502" s="18"/>
       <c r="N502" s="54">
         <v>701</v>
@@ -32499,10 +32545,12 @@
       <c r="J503" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K503" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L503" s="18"/>
+      <c r="K503" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L503" s="53">
+        <v>46246</v>
+      </c>
       <c r="M503" s="18"/>
       <c r="N503" s="54">
         <v>809</v>
@@ -33175,10 +33223,12 @@
       <c r="J517" s="15" t="s">
         <v>968</v>
       </c>
-      <c r="K517" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L517" s="18"/>
+      <c r="K517" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L517" s="53">
+        <v>46246</v>
+      </c>
       <c r="M517" s="18"/>
       <c r="N517" s="54">
         <v>754</v>
@@ -33806,7 +33856,9 @@
         <v>46250</v>
       </c>
       <c r="M530" s="18"/>
-      <c r="N530" s="40"/>
+      <c r="N530" s="54">
+        <v>871</v>
+      </c>
       <c r="O530" s="18"/>
       <c r="P530" s="18"/>
       <c r="Q530" s="18"/>
@@ -33852,7 +33904,9 @@
         <v>46250</v>
       </c>
       <c r="M531" s="18"/>
-      <c r="N531" s="40"/>
+      <c r="N531" s="54">
+        <v>879</v>
+      </c>
       <c r="O531" s="18"/>
       <c r="P531" s="18"/>
       <c r="Q531" s="18"/>
@@ -34958,7 +35012,9 @@
         <v>46250</v>
       </c>
       <c r="M554" s="18"/>
-      <c r="N554" s="40"/>
+      <c r="N554" s="54">
+        <v>873</v>
+      </c>
       <c r="O554" s="18"/>
       <c r="P554" s="18"/>
       <c r="Q554" s="11">
@@ -36163,10 +36219,12 @@
       <c r="J579" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K579" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L579" s="18"/>
+      <c r="K579" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L579" s="53">
+        <v>46246</v>
+      </c>
       <c r="M579" s="18"/>
       <c r="N579" s="54">
         <v>644</v>
@@ -36211,10 +36269,12 @@
       <c r="J580" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K580" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L580" s="18"/>
+      <c r="K580" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L580" s="53">
+        <v>46246</v>
+      </c>
       <c r="M580" s="18"/>
       <c r="N580" s="54">
         <v>645</v>
@@ -37247,10 +37307,12 @@
       <c r="J601" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K601" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L601" s="18"/>
+      <c r="K601" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L601" s="53">
+        <v>46246</v>
+      </c>
       <c r="M601" s="18"/>
       <c r="N601" s="54">
         <v>567</v>
@@ -37295,10 +37357,12 @@
       <c r="J602" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K602" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L602" s="18"/>
+      <c r="K602" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L602" s="53">
+        <v>46246</v>
+      </c>
       <c r="M602" s="18"/>
       <c r="N602" s="54">
         <v>568</v>
@@ -37441,10 +37505,12 @@
       <c r="J605" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K605" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L605" s="18"/>
+      <c r="K605" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L605" s="53">
+        <v>46246</v>
+      </c>
       <c r="M605" s="18"/>
       <c r="N605" s="54">
         <v>533</v>
@@ -37489,10 +37555,12 @@
       <c r="J606" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K606" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L606" s="18"/>
+      <c r="K606" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L606" s="53">
+        <v>46246</v>
+      </c>
       <c r="M606" s="18"/>
       <c r="N606" s="54">
         <v>407</v>
@@ -38609,10 +38677,12 @@
       <c r="J629" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K629" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L629" s="18"/>
+      <c r="K629" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L629" s="53">
+        <v>46246</v>
+      </c>
       <c r="M629" s="18"/>
       <c r="N629" s="54">
         <v>632</v>
@@ -38845,10 +38915,12 @@
       <c r="J634" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K634" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L634" s="18"/>
+      <c r="K634" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L634" s="53">
+        <v>46246</v>
+      </c>
       <c r="M634" s="18"/>
       <c r="N634" s="54">
         <v>642</v>
@@ -38943,10 +39015,12 @@
       <c r="J636" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K636" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L636" s="18"/>
+      <c r="K636" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L636" s="53">
+        <v>46246</v>
+      </c>
       <c r="M636" s="18"/>
       <c r="N636" s="54">
         <v>643</v>
@@ -38991,10 +39065,12 @@
       <c r="J637" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K637" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L637" s="18"/>
+      <c r="K637" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L637" s="53">
+        <v>46246</v>
+      </c>
       <c r="M637" s="18"/>
       <c r="N637" s="54">
         <v>641</v>
@@ -39039,10 +39115,12 @@
       <c r="J638" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K638" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L638" s="18"/>
+      <c r="K638" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L638" s="53">
+        <v>46246</v>
+      </c>
       <c r="M638" s="18"/>
       <c r="N638" s="54">
         <v>640</v>
@@ -39087,10 +39165,12 @@
       <c r="J639" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K639" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L639" s="18"/>
+      <c r="K639" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L639" s="53">
+        <v>46246</v>
+      </c>
       <c r="M639" s="18"/>
       <c r="N639" s="54">
         <v>697</v>
@@ -39135,10 +39215,12 @@
       <c r="J640" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K640" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L640" s="18"/>
+      <c r="K640" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L640" s="53">
+        <v>46246</v>
+      </c>
       <c r="M640" s="18"/>
       <c r="N640" s="54">
         <v>696</v>
@@ -39279,10 +39361,12 @@
       <c r="J643" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K643" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L643" s="18"/>
+      <c r="K643" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L643" s="53">
+        <v>46246</v>
+      </c>
       <c r="M643" s="18"/>
       <c r="N643" s="54">
         <v>695</v>
@@ -39467,10 +39551,12 @@
       <c r="J647" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K647" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L647" s="18"/>
+      <c r="K647" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L647" s="53">
+        <v>46246</v>
+      </c>
       <c r="M647" s="18"/>
       <c r="N647" s="54">
         <v>763</v>
@@ -39659,10 +39745,12 @@
       <c r="J651" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K651" s="30" t="s">
-        <v>1596</v>
-      </c>
-      <c r="L651" s="18"/>
+      <c r="K651" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L651" s="53">
+        <v>46246</v>
+      </c>
       <c r="M651" s="18"/>
       <c r="N651" s="76" t="s">
         <v>2119</v>
@@ -39709,10 +39797,12 @@
       <c r="J652" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K652" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L652" s="18"/>
+      <c r="K652" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L652" s="53">
+        <v>46246</v>
+      </c>
       <c r="M652" s="18"/>
       <c r="N652" s="54">
         <v>430</v>
@@ -39757,10 +39847,12 @@
       <c r="J653" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K653" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L653" s="18"/>
+      <c r="K653" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L653" s="53">
+        <v>46246</v>
+      </c>
       <c r="M653" s="18"/>
       <c r="N653" s="54">
         <v>433</v>
@@ -39805,10 +39897,12 @@
       <c r="J654" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K654" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L654" s="18"/>
+      <c r="K654" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L654" s="53">
+        <v>46246</v>
+      </c>
       <c r="M654" s="18"/>
       <c r="N654" s="54">
         <v>444</v>
@@ -39853,10 +39947,12 @@
       <c r="J655" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K655" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L655" s="18"/>
+      <c r="K655" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L655" s="53">
+        <v>46246</v>
+      </c>
       <c r="M655" s="18"/>
       <c r="N655" s="76" t="s">
         <v>2120</v>
@@ -39951,10 +40047,12 @@
       <c r="J657" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K657" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L657" s="18"/>
+      <c r="K657" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L657" s="53">
+        <v>46246</v>
+      </c>
       <c r="M657" s="18"/>
       <c r="N657" s="54">
         <v>663</v>
@@ -39999,10 +40097,12 @@
       <c r="J658" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K658" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L658" s="18"/>
+      <c r="K658" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L658" s="53">
+        <v>46246</v>
+      </c>
       <c r="M658" s="18"/>
       <c r="N658" s="54">
         <v>539</v>
@@ -40277,10 +40377,12 @@
       <c r="J664" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K664" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L664" s="18"/>
+      <c r="K664" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L664" s="53">
+        <v>46246</v>
+      </c>
       <c r="M664" s="18"/>
       <c r="N664" s="54">
         <v>400</v>
@@ -40793,10 +40895,12 @@
       <c r="J675" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="K675" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L675" s="18"/>
+      <c r="K675" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L675" s="53">
+        <v>46246</v>
+      </c>
       <c r="M675" s="18"/>
       <c r="N675" s="54">
         <v>577</v>
@@ -41512,7 +41616,7 @@
       </c>
       <c r="J690" s="18"/>
       <c r="K690" s="11" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="L690" s="53">
         <v>46246</v>
@@ -42376,7 +42480,9 @@
       <c r="K708" s="11" t="s">
         <v>2333</v>
       </c>
-      <c r="L708" s="18"/>
+      <c r="L708" s="53">
+        <v>46246</v>
+      </c>
       <c r="M708" s="18"/>
       <c r="N708" s="54">
         <v>524</v>
@@ -42426,7 +42532,9 @@
       </c>
       <c r="L709" s="18"/>
       <c r="M709" s="18"/>
-      <c r="N709" s="40"/>
+      <c r="N709" s="54">
+        <v>860</v>
+      </c>
       <c r="O709" s="18"/>
       <c r="P709" s="18"/>
       <c r="Q709" s="15">
@@ -42470,7 +42578,9 @@
       </c>
       <c r="L710" s="18"/>
       <c r="M710" s="18"/>
-      <c r="N710" s="40"/>
+      <c r="N710" s="54">
+        <v>863</v>
+      </c>
       <c r="O710" s="18"/>
       <c r="P710" s="18"/>
       <c r="Q710" s="15" t="s">
@@ -42516,7 +42626,9 @@
       </c>
       <c r="L711" s="18"/>
       <c r="M711" s="18"/>
-      <c r="N711" s="40"/>
+      <c r="N711" s="54">
+        <v>865</v>
+      </c>
       <c r="O711" s="18"/>
       <c r="P711" s="18"/>
       <c r="Q711" s="15">
@@ -42662,7 +42774,9 @@
       </c>
       <c r="L714" s="18"/>
       <c r="M714" s="18"/>
-      <c r="N714" s="40"/>
+      <c r="N714" s="54">
+        <v>881</v>
+      </c>
       <c r="O714" s="18"/>
       <c r="P714" s="18"/>
       <c r="Q714" s="11">
@@ -42891,10 +43005,12 @@
       <c r="J719" s="15" t="s">
         <v>1058</v>
       </c>
-      <c r="K719" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L719" s="18"/>
+      <c r="K719" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L719" s="53">
+        <v>46246</v>
+      </c>
       <c r="M719" s="18"/>
       <c r="N719" s="54">
         <v>648</v>
@@ -43120,7 +43236,9 @@
       </c>
       <c r="L724" s="18"/>
       <c r="M724" s="18"/>
-      <c r="N724" s="40"/>
+      <c r="N724" s="54">
+        <v>866</v>
+      </c>
       <c r="O724" s="18"/>
       <c r="P724" s="18"/>
       <c r="Q724" s="11">
@@ -43561,10 +43679,12 @@
       <c r="J733" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K733" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L733" s="18"/>
+      <c r="K733" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L733" s="53">
+        <v>46246</v>
+      </c>
       <c r="M733" s="18"/>
       <c r="N733" s="54">
         <v>631</v>
@@ -43609,10 +43729,12 @@
       <c r="J734" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K734" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L734" s="18"/>
+      <c r="K734" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L734" s="53">
+        <v>46246</v>
+      </c>
       <c r="M734" s="18"/>
       <c r="N734" s="54">
         <v>604</v>
@@ -43657,10 +43779,12 @@
       <c r="J735" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K735" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L735" s="18"/>
+      <c r="K735" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L735" s="53">
+        <v>46246</v>
+      </c>
       <c r="M735" s="18"/>
       <c r="N735" s="54">
         <v>605</v>
@@ -44246,8 +44370,8 @@
         <v>46250</v>
       </c>
       <c r="M747" s="18"/>
-      <c r="N747" s="54">
-        <v>1</v>
+      <c r="N747" s="79" t="s">
+        <v>2353</v>
       </c>
       <c r="O747" s="53">
         <v>46244</v>
@@ -44494,8 +44618,8 @@
       </c>
       <c r="L752" s="18"/>
       <c r="M752" s="18"/>
-      <c r="N752" s="54">
-        <v>6</v>
+      <c r="N752" s="79" t="s">
+        <v>2354</v>
       </c>
       <c r="O752" s="53">
         <v>46244</v>
@@ -44671,16 +44795,24 @@
       <c r="B756" s="10">
         <v>46242</v>
       </c>
-      <c r="C756" s="38"/>
-      <c r="D756" s="38"/>
-      <c r="E756" s="18"/>
+      <c r="C756" s="55" t="s">
+        <v>2355</v>
+      </c>
+      <c r="D756" s="55" t="s">
+        <v>2356</v>
+      </c>
+      <c r="E756" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="F756" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G756" s="56">
         <v>24724</v>
       </c>
-      <c r="H756" s="18"/>
+      <c r="H756" s="15">
+        <v>66226</v>
+      </c>
       <c r="I756" s="22" t="s">
         <v>563</v>
       </c>
@@ -46077,10 +46209,12 @@
       <c r="J785" s="15" t="s">
         <v>968</v>
       </c>
-      <c r="K785" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L785" s="18"/>
+      <c r="K785" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L785" s="53">
+        <v>46246</v>
+      </c>
       <c r="M785" s="18"/>
       <c r="N785" s="54">
         <v>740</v>
@@ -47785,10 +47919,12 @@
       <c r="J820" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="K820" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L820" s="18"/>
+      <c r="K820" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L820" s="53">
+        <v>46246</v>
+      </c>
       <c r="M820" s="18"/>
       <c r="N820" s="54">
         <v>756</v>
@@ -47925,10 +48061,12 @@
       <c r="J823" s="15" t="s">
         <v>562</v>
       </c>
-      <c r="K823" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L823" s="18"/>
+      <c r="K823" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L823" s="53">
+        <v>46246</v>
+      </c>
       <c r="M823" s="18"/>
       <c r="N823" s="54">
         <v>636</v>
@@ -48126,7 +48264,9 @@
         <v>46250</v>
       </c>
       <c r="M827" s="18"/>
-      <c r="N827" s="40"/>
+      <c r="N827" s="54">
+        <v>870</v>
+      </c>
       <c r="O827" s="18"/>
       <c r="P827" s="18"/>
       <c r="Q827" s="18"/>
@@ -48172,7 +48312,9 @@
         <v>46250</v>
       </c>
       <c r="M828" s="18"/>
-      <c r="N828" s="40"/>
+      <c r="N828" s="54">
+        <v>869</v>
+      </c>
       <c r="O828" s="18"/>
       <c r="P828" s="18"/>
       <c r="Q828" s="18"/>
@@ -49972,7 +50114,9 @@
       </c>
       <c r="L866" s="18"/>
       <c r="M866" s="18"/>
-      <c r="N866" s="40"/>
+      <c r="N866" s="54">
+        <v>882</v>
+      </c>
       <c r="O866" s="18"/>
       <c r="P866" s="18"/>
       <c r="Q866" s="18"/>
@@ -50059,10 +50203,12 @@
       <c r="J868" s="15" t="s">
         <v>848</v>
       </c>
-      <c r="K868" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L868" s="18"/>
+      <c r="K868" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L868" s="53">
+        <v>46246</v>
+      </c>
       <c r="M868" s="18"/>
       <c r="N868" s="54">
         <v>570</v>
@@ -50718,7 +50864,9 @@
         <v>46250</v>
       </c>
       <c r="M882" s="18"/>
-      <c r="N882" s="40"/>
+      <c r="N882" s="54">
+        <v>864</v>
+      </c>
       <c r="O882" s="18"/>
       <c r="P882" s="18"/>
       <c r="Q882" s="11">
@@ -50814,7 +50962,9 @@
         <v>46250</v>
       </c>
       <c r="M884" s="18"/>
-      <c r="N884" s="40"/>
+      <c r="N884" s="54">
+        <v>855</v>
+      </c>
       <c r="O884" s="18"/>
       <c r="P884" s="18"/>
       <c r="Q884" s="11">
@@ -50872,7 +51022,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="886" spans="1:18" ht="23.4" thickBot="1">
+    <row r="886" spans="1:18" ht="15" thickBot="1">
       <c r="A886" s="2">
         <v>121</v>
       </c>
@@ -50904,7 +51054,7 @@
         <v>130</v>
       </c>
       <c r="K886" s="11" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="L886" s="53">
         <v>46246</v>
@@ -51742,7 +51892,7 @@
       </c>
       <c r="J904" s="18"/>
       <c r="K904" s="11" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="L904" s="53">
         <v>46246</v>
@@ -52441,10 +52591,12 @@
       <c r="J919" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K919" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L919" s="18"/>
+      <c r="K919" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L919" s="53">
+        <v>46246</v>
+      </c>
       <c r="M919" s="18"/>
       <c r="N919" s="54">
         <v>398</v>
@@ -52491,10 +52643,12 @@
       <c r="J920" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K920" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L920" s="18"/>
+      <c r="K920" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L920" s="53">
+        <v>46246</v>
+      </c>
       <c r="M920" s="18"/>
       <c r="N920" s="54">
         <v>399</v>
@@ -52548,7 +52702,9 @@
         <v>46250</v>
       </c>
       <c r="M921" s="18"/>
-      <c r="N921" s="40"/>
+      <c r="N921" s="54">
+        <v>861</v>
+      </c>
       <c r="O921" s="18"/>
       <c r="P921" s="18"/>
       <c r="Q921" s="15">
@@ -52594,7 +52750,9 @@
         <v>46250</v>
       </c>
       <c r="M922" s="18"/>
-      <c r="N922" s="40"/>
+      <c r="N922" s="54">
+        <v>875</v>
+      </c>
       <c r="O922" s="18"/>
       <c r="P922" s="18"/>
       <c r="Q922" s="15">
@@ -52635,10 +52793,12 @@
       <c r="J923" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K923" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L923" s="18"/>
+      <c r="K923" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L923" s="53">
+        <v>46246</v>
+      </c>
       <c r="M923" s="18"/>
       <c r="N923" s="76" t="s">
         <v>2127</v>
@@ -52729,10 +52889,12 @@
       <c r="J925" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K925" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L925" s="18"/>
+      <c r="K925" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L925" s="53">
+        <v>46246</v>
+      </c>
       <c r="M925" s="18"/>
       <c r="N925" s="76" t="s">
         <v>2128</v>
@@ -52777,10 +52939,12 @@
       <c r="J926" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K926" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L926" s="18"/>
+      <c r="K926" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L926" s="53">
+        <v>46246</v>
+      </c>
       <c r="M926" s="18"/>
       <c r="N926" s="54">
         <v>588</v>
@@ -52823,10 +52987,12 @@
       <c r="J927" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K927" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L927" s="18"/>
+      <c r="K927" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L927" s="53">
+        <v>46246</v>
+      </c>
       <c r="M927" s="18"/>
       <c r="N927" s="54">
         <v>586</v>
@@ -52919,10 +53085,12 @@
       <c r="J929" s="15" t="s">
         <v>1271</v>
       </c>
-      <c r="K929" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L929" s="18"/>
+      <c r="K929" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L929" s="53">
+        <v>46246</v>
+      </c>
       <c r="M929" s="18"/>
       <c r="N929" s="54">
         <v>492</v>
@@ -53542,7 +53710,9 @@
       </c>
       <c r="L942" s="18"/>
       <c r="M942" s="18"/>
-      <c r="N942" s="40"/>
+      <c r="N942" s="54">
+        <v>853</v>
+      </c>
       <c r="O942" s="18"/>
       <c r="P942" s="18"/>
       <c r="Q942" s="15">
@@ -54015,10 +54185,12 @@
       <c r="J952" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K952" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L952" s="18"/>
+      <c r="K952" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L952" s="53">
+        <v>46246</v>
+      </c>
       <c r="M952" s="18"/>
       <c r="N952" s="54">
         <v>426</v>
@@ -54457,10 +54629,12 @@
       <c r="J961" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K961" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L961" s="18"/>
+      <c r="K961" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L961" s="53">
+        <v>46246</v>
+      </c>
       <c r="M961" s="18"/>
       <c r="N961" s="54">
         <v>587</v>
@@ -54505,10 +54679,12 @@
       <c r="J962" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K962" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L962" s="18"/>
+      <c r="K962" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L962" s="53">
+        <v>46246</v>
+      </c>
       <c r="M962" s="18"/>
       <c r="N962" s="54">
         <v>465</v>
@@ -54610,7 +54786,9 @@
         <v>46251</v>
       </c>
       <c r="M964" s="18"/>
-      <c r="N964" s="40"/>
+      <c r="N964" s="54">
+        <v>867</v>
+      </c>
       <c r="O964" s="18"/>
       <c r="P964" s="18"/>
       <c r="Q964" s="15">
@@ -56281,10 +56459,12 @@
       <c r="J998" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K998" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L998" s="18"/>
+      <c r="K998" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L998" s="53">
+        <v>46246</v>
+      </c>
       <c r="M998" s="18"/>
       <c r="N998" s="54">
         <v>602</v>
@@ -56329,10 +56509,12 @@
       <c r="J999" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K999" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L999" s="18"/>
+      <c r="K999" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L999" s="53">
+        <v>46246</v>
+      </c>
       <c r="M999" s="18"/>
       <c r="N999" s="54">
         <v>601</v>
@@ -56377,10 +56559,12 @@
       <c r="J1000" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1000" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1000" s="18"/>
+      <c r="K1000" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1000" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1000" s="18"/>
       <c r="N1000" s="54">
         <v>600</v>
@@ -56425,10 +56609,12 @@
       <c r="J1001" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1001" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1001" s="18"/>
+      <c r="K1001" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1001" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1001" s="18"/>
       <c r="N1001" s="54">
         <v>625</v>
@@ -56473,10 +56659,12 @@
       <c r="J1002" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1002" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1002" s="18"/>
+      <c r="K1002" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1002" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1002" s="18"/>
       <c r="N1002" s="54">
         <v>627</v>
@@ -56521,10 +56709,12 @@
       <c r="J1003" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1003" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1003" s="18"/>
+      <c r="K1003" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1003" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1003" s="18"/>
       <c r="N1003" s="54">
         <v>626</v>
@@ -56723,10 +56913,12 @@
       <c r="J1007" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1007" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1007" s="18"/>
+      <c r="K1007" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1007" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1007" s="18"/>
       <c r="N1007" s="54">
         <v>522</v>
@@ -56817,10 +57009,12 @@
       <c r="J1009" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1009" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1009" s="18"/>
+      <c r="K1009" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1009" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1009" s="18"/>
       <c r="N1009" s="54">
         <v>698</v>
@@ -57055,10 +57249,12 @@
       <c r="J1014" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1014" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1014" s="18"/>
+      <c r="K1014" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1014" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1014" s="18"/>
       <c r="N1014" s="54">
         <v>628</v>
@@ -57739,10 +57935,12 @@
       <c r="J1028" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1028" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1028" s="18"/>
+      <c r="K1028" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1028" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1028" s="18"/>
       <c r="N1028" s="54">
         <v>630</v>
@@ -58129,10 +58327,12 @@
       <c r="J1036" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1036" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1036" s="18"/>
+      <c r="K1036" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1036" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1036" s="18"/>
       <c r="N1036" s="54">
         <v>609</v>
@@ -58795,10 +58995,12 @@
       <c r="J1050" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1050" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1050" s="18"/>
+      <c r="K1050" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1050" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1050" s="18"/>
       <c r="N1050" s="54">
         <v>532</v>
@@ -59383,10 +59585,12 @@
       <c r="J1062" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1062" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1062" s="18"/>
+      <c r="K1062" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1062" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1062" s="18"/>
       <c r="N1062" s="54">
         <v>672</v>
@@ -59707,10 +59911,12 @@
       <c r="J1069" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K1069" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1069" s="18"/>
+      <c r="K1069" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1069" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1069" s="18"/>
       <c r="N1069" s="76" t="s">
         <v>2131</v>
@@ -59755,10 +59961,12 @@
       <c r="J1070" s="15" t="s">
         <v>1349</v>
       </c>
-      <c r="K1070" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1070" s="18"/>
+      <c r="K1070" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1070" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1070" s="18"/>
       <c r="N1070" s="54">
         <v>411</v>
@@ -60077,10 +60285,12 @@
       <c r="J1077" s="15" t="s">
         <v>1672</v>
       </c>
-      <c r="K1077" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1077" s="18"/>
+      <c r="K1077" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1077" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1077" s="18"/>
       <c r="N1077" s="54">
         <v>703</v>
@@ -60655,10 +60865,12 @@
       <c r="J1090" s="15" t="s">
         <v>1672</v>
       </c>
-      <c r="K1090" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1090" s="18"/>
+      <c r="K1090" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1090" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1090" s="18"/>
       <c r="N1090" s="54">
         <v>770</v>
@@ -60745,10 +60957,12 @@
       <c r="J1092" s="15" t="s">
         <v>1672</v>
       </c>
-      <c r="K1092" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1092" s="18"/>
+      <c r="K1092" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1092" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1092" s="18"/>
       <c r="N1092" s="54">
         <v>608</v>
@@ -60793,10 +61007,12 @@
       <c r="J1093" s="15" t="s">
         <v>1672</v>
       </c>
-      <c r="K1093" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1093" s="18"/>
+      <c r="K1093" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1093" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1093" s="18"/>
       <c r="N1093" s="54">
         <v>607</v>
@@ -60841,10 +61057,12 @@
       <c r="J1094" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1094" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1094" s="18"/>
+      <c r="K1094" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1094" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1094" s="18"/>
       <c r="N1094" s="54">
         <v>664</v>
@@ -60887,10 +61105,12 @@
       <c r="J1095" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1095" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1095" s="18"/>
+      <c r="K1095" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1095" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1095" s="18"/>
       <c r="N1095" s="54">
         <v>683</v>
@@ -61824,7 +62044,9 @@
       </c>
       <c r="L1115" s="18"/>
       <c r="M1115" s="18"/>
-      <c r="N1115" s="40"/>
+      <c r="N1115" s="54">
+        <v>874</v>
+      </c>
       <c r="O1115" s="18"/>
       <c r="P1115" s="18"/>
       <c r="Q1115" s="18"/>
@@ -64891,10 +65113,12 @@
       <c r="J1188" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K1188" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1188" s="18"/>
+      <c r="K1188" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1188" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1188" s="18"/>
       <c r="N1188" s="54">
         <v>486</v>
@@ -64983,10 +65207,12 @@
       <c r="J1190" s="15" t="s">
         <v>1832</v>
       </c>
-      <c r="K1190" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1190" s="18"/>
+      <c r="K1190" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1190" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1190" s="18"/>
       <c r="N1190" s="54">
         <v>793</v>
@@ -67534,7 +67760,9 @@
       </c>
       <c r="L1246" s="18"/>
       <c r="M1246" s="18"/>
-      <c r="N1246" s="40"/>
+      <c r="N1246" s="54">
+        <v>878</v>
+      </c>
       <c r="O1246" s="18"/>
       <c r="P1246" s="18"/>
       <c r="Q1246" s="15">
@@ -67717,10 +67945,12 @@
       <c r="J1250" s="15" t="s">
         <v>1913</v>
       </c>
-      <c r="K1250" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1250" s="18"/>
+      <c r="K1250" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1250" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1250" s="18"/>
       <c r="N1250" s="54">
         <v>606</v>
@@ -67765,10 +67995,12 @@
       <c r="J1251" s="15" t="s">
         <v>1913</v>
       </c>
-      <c r="K1251" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1251" s="18"/>
+      <c r="K1251" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1251" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1251" s="18"/>
       <c r="N1251" s="54">
         <v>638</v>
@@ -67813,10 +68045,12 @@
       <c r="J1252" s="15" t="s">
         <v>1913</v>
       </c>
-      <c r="K1252" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1252" s="18"/>
+      <c r="K1252" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1252" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1252" s="18"/>
       <c r="N1252" s="54">
         <v>637</v>
@@ -68623,10 +68857,12 @@
       <c r="J1269" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1269" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1269" s="18"/>
+      <c r="K1269" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1269" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1269" s="18"/>
       <c r="N1269" s="54">
         <v>543</v>
@@ -68869,10 +69105,12 @@
       <c r="J1274" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1274" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1274" s="18"/>
+      <c r="K1274" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1274" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1274" s="18"/>
       <c r="N1274" s="54">
         <v>542</v>
@@ -70548,7 +70786,9 @@
       </c>
       <c r="L1310" s="18"/>
       <c r="M1310" s="18"/>
-      <c r="N1310" s="40"/>
+      <c r="N1310" s="54">
+        <v>388</v>
+      </c>
       <c r="O1310" s="18"/>
       <c r="P1310" s="18"/>
       <c r="Q1310" s="18"/>
@@ -71141,10 +71381,12 @@
       <c r="J1323" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1323" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1323" s="18"/>
+      <c r="K1323" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1323" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1323" s="18"/>
       <c r="N1323" s="54">
         <v>657</v>
@@ -71693,10 +71935,12 @@
       <c r="J1335" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1335" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1335" s="18"/>
+      <c r="K1335" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1335" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1335" s="18"/>
       <c r="N1335" s="54">
         <v>655</v>
@@ -72479,10 +72723,12 @@
       <c r="J1352" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1352" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1352" s="18"/>
+      <c r="K1352" s="11" t="s">
+        <v>2333</v>
+      </c>
+      <c r="L1352" s="53">
+        <v>46246</v>
+      </c>
       <c r="M1352" s="18"/>
       <c r="N1352" s="54">
         <v>656</v>
@@ -74464,7 +74710,9 @@
       </c>
       <c r="L1396" s="18"/>
       <c r="M1396" s="18"/>
-      <c r="N1396" s="40"/>
+      <c r="N1396" s="54">
+        <v>877</v>
+      </c>
       <c r="O1396" s="18"/>
       <c r="P1396" s="18"/>
       <c r="Q1396" s="18"/>
@@ -81198,10 +81446,10 @@
         <v>46246</v>
       </c>
       <c r="C1546" s="55" t="s">
+        <v>2335</v>
+      </c>
+      <c r="D1546" s="55" t="s">
         <v>2336</v>
-      </c>
-      <c r="D1546" s="55" t="s">
-        <v>2337</v>
       </c>
       <c r="E1546" s="12" t="s">
         <v>21</v>
@@ -81213,7 +81461,7 @@
         <v>68798</v>
       </c>
       <c r="H1546" s="66" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
       <c r="I1546" s="16" t="s">
         <v>10</v>
@@ -81244,10 +81492,10 @@
         <v>46246</v>
       </c>
       <c r="C1547" s="23" t="s">
+        <v>2338</v>
+      </c>
+      <c r="D1547" s="11" t="s">
         <v>2339</v>
-      </c>
-      <c r="D1547" s="11" t="s">
-        <v>2340</v>
       </c>
       <c r="E1547" s="12" t="s">
         <v>21</v>
@@ -81290,10 +81538,10 @@
         <v>46246</v>
       </c>
       <c r="C1548" s="23" t="s">
+        <v>2340</v>
+      </c>
+      <c r="D1548" s="11" t="s">
         <v>2341</v>
-      </c>
-      <c r="D1548" s="11" t="s">
-        <v>2342</v>
       </c>
       <c r="E1548" s="12" t="s">
         <v>21</v>
@@ -81336,10 +81584,10 @@
         <v>46246</v>
       </c>
       <c r="C1549" s="23" t="s">
+        <v>2342</v>
+      </c>
+      <c r="D1549" s="11" t="s">
         <v>2343</v>
-      </c>
-      <c r="D1549" s="11" t="s">
-        <v>2344</v>
       </c>
       <c r="E1549" s="12" t="s">
         <v>21</v>
@@ -81382,10 +81630,10 @@
         <v>46246</v>
       </c>
       <c r="C1550" s="23" t="s">
+        <v>2344</v>
+      </c>
+      <c r="D1550" s="11" t="s">
         <v>2345</v>
-      </c>
-      <c r="D1550" s="11" t="s">
-        <v>2346</v>
       </c>
       <c r="E1550" s="12" t="s">
         <v>21</v>
@@ -81428,10 +81676,10 @@
         <v>46246</v>
       </c>
       <c r="C1551" s="23" t="s">
+        <v>2346</v>
+      </c>
+      <c r="D1551" s="11" t="s">
         <v>2347</v>
-      </c>
-      <c r="D1551" s="11" t="s">
-        <v>2348</v>
       </c>
       <c r="E1551" s="12" t="s">
         <v>21</v>
@@ -81443,7 +81691,7 @@
         <v>90498</v>
       </c>
       <c r="H1551" s="15" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="I1551" s="16" t="s">
         <v>10</v>
@@ -81474,10 +81722,10 @@
         <v>46246</v>
       </c>
       <c r="C1552" s="23" t="s">
+        <v>2349</v>
+      </c>
+      <c r="D1552" s="11" t="s">
         <v>2350</v>
-      </c>
-      <c r="D1552" s="11" t="s">
-        <v>2351</v>
       </c>
       <c r="E1552" s="12" t="s">
         <v>21</v>
@@ -81489,7 +81737,7 @@
         <v>38386</v>
       </c>
       <c r="H1552" s="15" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="I1552" s="16" t="s">
         <v>10</v>
@@ -81516,42 +81764,410 @@
       <c r="A1553" s="2">
         <v>31</v>
       </c>
-      <c r="B1553" s="82"/>
-      <c r="C1553" s="83" t="s">
-        <v>2353</v>
-      </c>
-      <c r="D1553" s="84">
+      <c r="B1553" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1553" s="23" t="s">
+        <v>2352</v>
+      </c>
+      <c r="D1553" s="11">
         <v>70549062</v>
       </c>
-      <c r="E1553" s="85" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1553" s="86" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1553" s="87">
+      <c r="E1553" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1553" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1553" s="14">
         <v>8846</v>
       </c>
-      <c r="H1553" s="88">
+      <c r="H1553" s="15">
         <v>4252</v>
       </c>
-      <c r="I1553" s="89" t="s">
+      <c r="I1553" s="58" t="s">
         <v>1177</v>
       </c>
-      <c r="J1553" s="82"/>
-      <c r="K1553" s="90" t="s">
+      <c r="J1553" s="18"/>
+      <c r="K1553" s="60" t="s">
         <v>1189</v>
       </c>
-      <c r="L1553" s="82"/>
-      <c r="M1553" s="91" t="s">
+      <c r="L1553" s="18"/>
+      <c r="M1553" s="16" t="s">
         <v>1999</v>
       </c>
-      <c r="N1553" s="92"/>
-      <c r="O1553" s="82"/>
-      <c r="P1553" s="82"/>
-      <c r="Q1553" s="82"/>
-      <c r="R1553" s="91" t="s">
+      <c r="N1553" s="40"/>
+      <c r="O1553" s="18"/>
+      <c r="P1553" s="18"/>
+      <c r="Q1553" s="18"/>
+      <c r="R1553" s="16" t="s">
         <v>1178</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:18" ht="24.6" thickBot="1">
+      <c r="A1554" s="2">
+        <v>32</v>
+      </c>
+      <c r="B1554" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1554" s="23" t="s">
+        <v>2357</v>
+      </c>
+      <c r="D1554" s="11">
+        <v>128261398</v>
+      </c>
+      <c r="E1554" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1554" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1554" s="14">
+        <v>408</v>
+      </c>
+      <c r="H1554" s="15">
+        <v>5648</v>
+      </c>
+      <c r="I1554" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1554" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1554" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1554" s="18"/>
+      <c r="M1554" s="18"/>
+      <c r="N1554" s="40"/>
+      <c r="O1554" s="18"/>
+      <c r="P1554" s="18"/>
+      <c r="Q1554" s="11">
+        <v>94319252</v>
+      </c>
+      <c r="R1554" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:18" ht="24.6" thickBot="1">
+      <c r="A1555" s="2">
+        <v>33</v>
+      </c>
+      <c r="B1555" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1555" s="23" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D1555" s="11" t="s">
+        <v>2359</v>
+      </c>
+      <c r="E1555" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1555" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1555" s="14">
+        <v>59122</v>
+      </c>
+      <c r="H1555" s="15">
+        <v>76614</v>
+      </c>
+      <c r="I1555" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1555" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1555" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1555" s="18"/>
+      <c r="M1555" s="18"/>
+      <c r="N1555" s="40"/>
+      <c r="O1555" s="18"/>
+      <c r="P1555" s="18"/>
+      <c r="Q1555" s="11">
+        <v>76845076</v>
+      </c>
+      <c r="R1555" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:18" ht="27" thickBot="1">
+      <c r="A1556" s="2">
+        <v>34</v>
+      </c>
+      <c r="B1556" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1556" s="23" t="s">
+        <v>2360</v>
+      </c>
+      <c r="D1556" s="11">
+        <v>128847714</v>
+      </c>
+      <c r="E1556" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1556" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1556" s="14">
+        <v>7383</v>
+      </c>
+      <c r="H1556" s="15">
+        <v>5046</v>
+      </c>
+      <c r="I1556" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1556" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1556" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1556" s="18"/>
+      <c r="M1556" s="18"/>
+      <c r="N1556" s="40"/>
+      <c r="O1556" s="18"/>
+      <c r="P1556" s="18"/>
+      <c r="Q1556" s="11">
+        <v>97342088</v>
+      </c>
+      <c r="R1556" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:18" ht="27" thickBot="1">
+      <c r="A1557" s="2">
+        <v>35</v>
+      </c>
+      <c r="B1557" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1557" s="23" t="s">
+        <v>2361</v>
+      </c>
+      <c r="D1557" s="11">
+        <v>127551765</v>
+      </c>
+      <c r="E1557" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1557" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1557" s="14">
+        <v>756</v>
+      </c>
+      <c r="H1557" s="15">
+        <v>3143</v>
+      </c>
+      <c r="I1557" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1557" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1557" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1557" s="18"/>
+      <c r="M1557" s="18"/>
+      <c r="N1557" s="40"/>
+      <c r="O1557" s="18"/>
+      <c r="P1557" s="18"/>
+      <c r="Q1557" s="11">
+        <v>79822349</v>
+      </c>
+      <c r="R1557" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:18" ht="24.6" thickBot="1">
+      <c r="A1558" s="2">
+        <v>36</v>
+      </c>
+      <c r="B1558" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1558" s="23" t="s">
+        <v>580</v>
+      </c>
+      <c r="D1558" s="11" t="s">
+        <v>2362</v>
+      </c>
+      <c r="E1558" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1558" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1558" s="14">
+        <v>39610</v>
+      </c>
+      <c r="H1558" s="15">
+        <v>71917</v>
+      </c>
+      <c r="I1558" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1558" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1558" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1558" s="18"/>
+      <c r="M1558" s="18"/>
+      <c r="N1558" s="40"/>
+      <c r="O1558" s="18"/>
+      <c r="P1558" s="18"/>
+      <c r="Q1558" s="11">
+        <v>95858017</v>
+      </c>
+      <c r="R1558" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:18" ht="24.6" thickBot="1">
+      <c r="A1559" s="2">
+        <v>37</v>
+      </c>
+      <c r="B1559" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1559" s="23" t="s">
+        <v>2363</v>
+      </c>
+      <c r="D1559" s="11" t="s">
+        <v>2364</v>
+      </c>
+      <c r="E1559" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1559" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1559" s="14">
+        <v>26932</v>
+      </c>
+      <c r="H1559" s="15">
+        <v>62197</v>
+      </c>
+      <c r="I1559" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1559" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1559" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1559" s="18"/>
+      <c r="M1559" s="18"/>
+      <c r="N1559" s="40"/>
+      <c r="O1559" s="18"/>
+      <c r="P1559" s="18"/>
+      <c r="Q1559" s="11">
+        <v>95610171</v>
+      </c>
+      <c r="R1559" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:18" ht="24.6" thickBot="1">
+      <c r="A1560" s="2">
+        <v>38</v>
+      </c>
+      <c r="B1560" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1560" s="23" t="s">
+        <v>2365</v>
+      </c>
+      <c r="D1560" s="11">
+        <v>70409518</v>
+      </c>
+      <c r="E1560" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1560" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1560" s="14" t="s">
+        <v>2366</v>
+      </c>
+      <c r="H1560" s="15">
+        <v>570</v>
+      </c>
+      <c r="I1560" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1560" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1560" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1560" s="18"/>
+      <c r="M1560" s="18"/>
+      <c r="N1560" s="40"/>
+      <c r="O1560" s="18"/>
+      <c r="P1560" s="18"/>
+      <c r="Q1560" s="11">
+        <v>77833715</v>
+      </c>
+      <c r="R1560" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1561" s="2">
+        <v>39</v>
+      </c>
+      <c r="B1561" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1561" s="23" t="s">
+        <v>2367</v>
+      </c>
+      <c r="D1561" s="11">
+        <v>69523302</v>
+      </c>
+      <c r="E1561" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1561" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1561" s="14" t="s">
+        <v>2368</v>
+      </c>
+      <c r="H1561" s="15">
+        <v>8695</v>
+      </c>
+      <c r="I1561" s="48" t="s">
+        <v>485</v>
+      </c>
+      <c r="J1561" s="18"/>
+      <c r="K1561" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1561" s="53">
+        <v>46252</v>
+      </c>
+      <c r="M1561" s="18"/>
+      <c r="N1561" s="40"/>
+      <c r="O1561" s="18"/>
+      <c r="P1561" s="18"/>
+      <c r="Q1561" s="18"/>
+      <c r="R1561" s="21" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57B9655A-06AB-464F-AC70-B2522639B88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E6E316-45E0-4993-97A2-921AE7599C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$K$1:$K$1</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11652" uniqueCount="2368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11703" uniqueCount="2377">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -7142,13 +7142,40 @@
   </si>
   <si>
     <t>ZULFIQAR AHMED</t>
+  </si>
+  <si>
+    <t>FAHAD MOHAMED</t>
+  </si>
+  <si>
+    <t>SHABBIR ABBAS</t>
+  </si>
+  <si>
+    <t>CZ1016355</t>
+  </si>
+  <si>
+    <t>HAMOOD SAID</t>
+  </si>
+  <si>
+    <t>MOHAMMED HAMED</t>
+  </si>
+  <si>
+    <t>DAWOUD SULAIMAN</t>
+  </si>
+  <si>
+    <t>MOHAMMED SULAIMAN</t>
+  </si>
+  <si>
+    <t>TANVEER AHMED</t>
+  </si>
+  <si>
+    <t>NA1173862</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="39">
+  <fonts count="40">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7388,6 +7415,13 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFCFC9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -7535,7 +7569,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7779,6 +7813,9 @@
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8094,7 +8131,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1561"/>
+  <dimension ref="A1:R1568"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -18642,11 +18679,11 @@
       <c r="J215" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="K215" s="11" t="s">
-        <v>2329</v>
+      <c r="K215" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L215" s="53">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="M215" s="18"/>
       <c r="N215" s="54">
@@ -19252,10 +19289,12 @@
         <v>485</v>
       </c>
       <c r="J228" s="18"/>
-      <c r="K228" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L228" s="18"/>
+      <c r="K228" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L228" s="53">
+        <v>46251</v>
+      </c>
       <c r="M228" s="18"/>
       <c r="N228" s="40"/>
       <c r="O228" s="18"/>
@@ -44416,10 +44455,12 @@
       <c r="J748" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K748" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L748" s="18"/>
+      <c r="K748" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L748" s="10">
+        <v>46250</v>
+      </c>
       <c r="M748" s="18"/>
       <c r="N748" s="79" t="s">
         <v>2261</v>
@@ -44871,7 +44912,9 @@
       <c r="K757" s="52" t="s">
         <v>837</v>
       </c>
-      <c r="L757" s="18"/>
+      <c r="L757" s="53">
+        <v>46251</v>
+      </c>
       <c r="M757" s="18"/>
       <c r="N757" s="54" t="s">
         <v>1203</v>
@@ -44923,7 +44966,9 @@
       <c r="K758" s="52" t="s">
         <v>837</v>
       </c>
-      <c r="L758" s="18"/>
+      <c r="L758" s="53">
+        <v>46251</v>
+      </c>
       <c r="M758" s="18"/>
       <c r="N758" s="54" t="s">
         <v>1205</v>
@@ -46210,11 +46255,11 @@
       <c r="J785" s="15" t="s">
         <v>968</v>
       </c>
-      <c r="K785" s="11" t="s">
-        <v>2329</v>
+      <c r="K785" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L785" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M785" s="18"/>
       <c r="N785" s="54">
@@ -46258,10 +46303,12 @@
       <c r="J786" s="15" t="s">
         <v>1653</v>
       </c>
-      <c r="K786" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L786" s="18"/>
+      <c r="K786" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L786" s="53">
+        <v>46251</v>
+      </c>
       <c r="M786" s="18"/>
       <c r="N786" s="40"/>
       <c r="O786" s="18"/>
@@ -50400,10 +50447,12 @@
       <c r="J872" s="15" t="s">
         <v>1145</v>
       </c>
-      <c r="K872" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L872" s="18"/>
+      <c r="K872" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L872" s="53">
+        <v>46250</v>
+      </c>
       <c r="M872" s="18"/>
       <c r="N872" s="40"/>
       <c r="O872" s="18"/>
@@ -50492,10 +50541,12 @@
       <c r="J874" s="15" t="s">
         <v>1145</v>
       </c>
-      <c r="K874" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L874" s="18"/>
+      <c r="K874" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L874" s="53">
+        <v>46250</v>
+      </c>
       <c r="M874" s="18"/>
       <c r="N874" s="54">
         <v>970</v>
@@ -50586,10 +50637,12 @@
       <c r="J876" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="K876" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L876" s="18"/>
+      <c r="K876" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L876" s="53">
+        <v>46250</v>
+      </c>
       <c r="M876" s="18"/>
       <c r="N876" s="40"/>
       <c r="O876" s="18"/>
@@ -52800,11 +52853,11 @@
       <c r="J923" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K923" s="11" t="s">
-        <v>2329</v>
+      <c r="K923" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L923" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M923" s="18"/>
       <c r="N923" s="76" t="s">
@@ -52850,10 +52903,12 @@
       <c r="J924" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K924" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L924" s="18"/>
+      <c r="K924" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L924" s="53">
+        <v>46251</v>
+      </c>
       <c r="M924" s="18"/>
       <c r="N924" s="40"/>
       <c r="O924" s="18"/>
@@ -53994,10 +54049,12 @@
       <c r="J948" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K948" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L948" s="18"/>
+      <c r="K948" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L948" s="53">
+        <v>46250</v>
+      </c>
       <c r="M948" s="18"/>
       <c r="N948" s="54">
         <v>162</v>
@@ -54042,10 +54099,12 @@
       <c r="J949" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K949" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L949" s="18"/>
+      <c r="K949" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L949" s="53">
+        <v>46250</v>
+      </c>
       <c r="M949" s="18"/>
       <c r="N949" s="54">
         <v>385</v>
@@ -54092,10 +54151,12 @@
       <c r="J950" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K950" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L950" s="18"/>
+      <c r="K950" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L950" s="53">
+        <v>46250</v>
+      </c>
       <c r="M950" s="18"/>
       <c r="N950" s="54">
         <v>146</v>
@@ -54142,10 +54203,12 @@
       <c r="J951" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K951" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L951" s="18"/>
+      <c r="K951" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L951" s="53">
+        <v>46250</v>
+      </c>
       <c r="M951" s="18"/>
       <c r="N951" s="54">
         <v>393</v>
@@ -54192,11 +54255,11 @@
       <c r="J952" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K952" s="11" t="s">
-        <v>2329</v>
+      <c r="K952" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L952" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M952" s="18"/>
       <c r="N952" s="54">
@@ -54240,10 +54303,12 @@
       <c r="J953" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K953" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L953" s="18"/>
+      <c r="K953" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L953" s="53">
+        <v>46250</v>
+      </c>
       <c r="M953" s="18"/>
       <c r="N953" s="54">
         <v>386</v>
@@ -54290,10 +54355,12 @@
       <c r="J954" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K954" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L954" s="18"/>
+      <c r="K954" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L954" s="53">
+        <v>46250</v>
+      </c>
       <c r="M954" s="18"/>
       <c r="N954" s="54">
         <v>145</v>
@@ -54340,11 +54407,11 @@
       <c r="J955" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K955" s="11" t="s">
-        <v>2329</v>
+      <c r="K955" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L955" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M955" s="18"/>
       <c r="N955" s="54">
@@ -54390,11 +54457,11 @@
       <c r="J956" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K956" s="11" t="s">
-        <v>2329</v>
+      <c r="K956" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L956" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M956" s="18"/>
       <c r="N956" s="54">
@@ -54686,11 +54753,11 @@
       <c r="J962" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K962" s="11" t="s">
-        <v>2329</v>
+      <c r="K962" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L962" s="53">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="M962" s="18"/>
       <c r="N962" s="54">
@@ -55874,11 +55941,11 @@
       <c r="J986" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K986" s="11" t="s">
-        <v>2329</v>
+      <c r="K986" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L986" s="53">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="M986" s="18"/>
       <c r="N986" s="54">
@@ -55924,11 +55991,11 @@
       <c r="J987" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K987" s="11" t="s">
-        <v>2329</v>
+      <c r="K987" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L987" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M987" s="18"/>
       <c r="N987" s="54">
@@ -55974,11 +56041,11 @@
       <c r="J988" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K988" s="11" t="s">
-        <v>2329</v>
+      <c r="K988" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L988" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M988" s="18"/>
       <c r="N988" s="54">
@@ -56024,11 +56091,11 @@
       <c r="J989" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K989" s="11" t="s">
-        <v>2329</v>
+      <c r="K989" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L989" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M989" s="18"/>
       <c r="N989" s="54">
@@ -56074,11 +56141,11 @@
       <c r="J990" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K990" s="11" t="s">
-        <v>2329</v>
+      <c r="K990" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L990" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M990" s="18"/>
       <c r="N990" s="54">
@@ -56124,11 +56191,11 @@
       <c r="J991" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K991" s="11" t="s">
-        <v>2329</v>
+      <c r="K991" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L991" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M991" s="18"/>
       <c r="N991" s="54">
@@ -56174,11 +56241,11 @@
       <c r="J992" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K992" s="11" t="s">
-        <v>2329</v>
+      <c r="K992" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L992" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M992" s="18"/>
       <c r="N992" s="54">
@@ -56224,11 +56291,11 @@
       <c r="J993" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K993" s="11" t="s">
-        <v>2329</v>
+      <c r="K993" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L993" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M993" s="18"/>
       <c r="N993" s="54">
@@ -56274,11 +56341,11 @@
       <c r="J994" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K994" s="11" t="s">
-        <v>2329</v>
+      <c r="K994" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L994" s="53">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="M994" s="18"/>
       <c r="N994" s="54">
@@ -56324,10 +56391,12 @@
       <c r="J995" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K995" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L995" s="18"/>
+      <c r="K995" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L995" s="53">
+        <v>46250</v>
+      </c>
       <c r="M995" s="18"/>
       <c r="N995" s="54">
         <v>177</v>
@@ -56374,10 +56443,12 @@
       <c r="J996" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K996" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L996" s="18"/>
+      <c r="K996" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L996" s="53">
+        <v>46250</v>
+      </c>
       <c r="M996" s="18"/>
       <c r="N996" s="54">
         <v>916</v>
@@ -56422,10 +56493,12 @@
       <c r="J997" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K997" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L997" s="18"/>
+      <c r="K997" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L997" s="53">
+        <v>46251</v>
+      </c>
       <c r="M997" s="18"/>
       <c r="N997" s="40"/>
       <c r="O997" s="18"/>
@@ -56466,11 +56539,11 @@
       <c r="J998" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K998" s="11" t="s">
-        <v>2329</v>
+      <c r="K998" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L998" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M998" s="18"/>
       <c r="N998" s="54">
@@ -56516,11 +56589,11 @@
       <c r="J999" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K999" s="11" t="s">
-        <v>2329</v>
+      <c r="K999" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L999" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M999" s="18"/>
       <c r="N999" s="54">
@@ -56566,11 +56639,11 @@
       <c r="J1000" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1000" s="11" t="s">
-        <v>2329</v>
+      <c r="K1000" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1000" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1000" s="18"/>
       <c r="N1000" s="54">
@@ -56616,11 +56689,11 @@
       <c r="J1001" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1001" s="11" t="s">
-        <v>2329</v>
+      <c r="K1001" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1001" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1001" s="18"/>
       <c r="N1001" s="54">
@@ -56666,11 +56739,11 @@
       <c r="J1002" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1002" s="11" t="s">
-        <v>2329</v>
+      <c r="K1002" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1002" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1002" s="18"/>
       <c r="N1002" s="54">
@@ -56716,11 +56789,11 @@
       <c r="J1003" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1003" s="11" t="s">
-        <v>2329</v>
+      <c r="K1003" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1003" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1003" s="18"/>
       <c r="N1003" s="54">
@@ -57794,10 +57867,12 @@
       <c r="J1025" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1025" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1025" s="18"/>
+      <c r="K1025" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1025" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1025" s="18"/>
       <c r="N1025" s="54">
         <v>674</v>
@@ -57842,11 +57917,11 @@
       <c r="J1026" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1026" s="11" t="s">
-        <v>2329</v>
+      <c r="K1026" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1026" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1026" s="18"/>
       <c r="N1026" s="54">
@@ -57892,11 +57967,11 @@
       <c r="J1027" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1027" s="11" t="s">
-        <v>2329</v>
+      <c r="K1027" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1027" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1027" s="18"/>
       <c r="N1027" s="54">
@@ -57942,11 +58017,11 @@
       <c r="J1028" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1028" s="11" t="s">
-        <v>2329</v>
+      <c r="K1028" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1028" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1028" s="18"/>
       <c r="N1028" s="54">
@@ -57992,11 +58067,11 @@
       <c r="J1029" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1029" s="11" t="s">
-        <v>2329</v>
+      <c r="K1029" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1029" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1029" s="18"/>
       <c r="N1029" s="54">
@@ -58042,11 +58117,11 @@
       <c r="J1030" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1030" s="11" t="s">
-        <v>2329</v>
+      <c r="K1030" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1030" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1030" s="18"/>
       <c r="N1030" s="54">
@@ -58092,10 +58167,12 @@
       <c r="J1031" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1031" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1031" s="18"/>
+      <c r="K1031" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1031" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1031" s="18"/>
       <c r="N1031" s="40"/>
       <c r="O1031" s="18"/>
@@ -58138,10 +58215,12 @@
       <c r="J1032" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1032" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1032" s="18"/>
+      <c r="K1032" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1032" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1032" s="18"/>
       <c r="N1032" s="54">
         <v>838</v>
@@ -58186,11 +58265,11 @@
       <c r="J1033" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1033" s="11" t="s">
-        <v>2329</v>
+      <c r="K1033" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1033" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1033" s="18"/>
       <c r="N1033" s="54">
@@ -58236,11 +58315,11 @@
       <c r="J1034" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1034" s="11" t="s">
-        <v>2329</v>
+      <c r="K1034" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1034" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1034" s="18"/>
       <c r="N1034" s="54">
@@ -58334,11 +58413,11 @@
       <c r="J1036" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1036" s="11" t="s">
-        <v>2329</v>
+      <c r="K1036" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1036" s="53">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="M1036" s="18"/>
       <c r="N1036" s="54">
@@ -58384,11 +58463,11 @@
       <c r="J1037" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1037" s="11" t="s">
-        <v>2329</v>
+      <c r="K1037" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1037" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1037" s="18"/>
       <c r="N1037" s="54">
@@ -58628,10 +58707,12 @@
       <c r="J1042" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1042" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1042" s="18"/>
+      <c r="K1042" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1042" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1042" s="18"/>
       <c r="N1042" s="54">
         <v>195</v>
@@ -58728,10 +58809,12 @@
       <c r="J1044" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1044" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1044" s="18"/>
+      <c r="K1044" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1044" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1044" s="18"/>
       <c r="N1044" s="40"/>
       <c r="O1044" s="18"/>
@@ -58774,8 +58857,8 @@
       <c r="J1045" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1045" s="17" t="s">
-        <v>12</v>
+      <c r="K1045" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1045" s="18"/>
       <c r="M1045" s="18"/>
@@ -58820,10 +58903,12 @@
       <c r="J1046" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1046" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1046" s="18"/>
+      <c r="K1046" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1046" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1046" s="18"/>
       <c r="N1046" s="40"/>
       <c r="O1046" s="18"/>
@@ -58866,10 +58951,12 @@
       <c r="J1047" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1047" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1047" s="18"/>
+      <c r="K1047" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1047" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1047" s="18"/>
       <c r="N1047" s="54">
         <v>682</v>
@@ -58914,10 +59001,12 @@
       <c r="J1048" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1048" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1048" s="18"/>
+      <c r="K1048" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1048" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1048" s="18"/>
       <c r="N1048" s="40"/>
       <c r="O1048" s="18"/>
@@ -58960,10 +59049,12 @@
       <c r="J1049" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1049" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1049" s="18"/>
+      <c r="K1049" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1049" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1049" s="18"/>
       <c r="N1049" s="40"/>
       <c r="O1049" s="18"/>
@@ -59006,11 +59097,11 @@
       <c r="J1050" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1050" s="11" t="s">
-        <v>2329</v>
+      <c r="K1050" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1050" s="53">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="M1050" s="18"/>
       <c r="N1050" s="54">
@@ -59736,10 +59827,12 @@
       <c r="J1065" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K1065" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1065" s="18"/>
+      <c r="K1065" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1065" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1065" s="18"/>
       <c r="N1065" s="76" t="s">
         <v>2126</v>
@@ -59786,10 +59879,12 @@
       <c r="J1066" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K1066" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1066" s="18"/>
+      <c r="K1066" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1066" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1066" s="18"/>
       <c r="N1066" s="54">
         <v>348</v>
@@ -59880,10 +59975,12 @@
       <c r="J1068" s="15" t="s">
         <v>1648</v>
       </c>
-      <c r="K1068" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1068" s="18"/>
+      <c r="K1068" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1068" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1068" s="18"/>
       <c r="N1068" s="40"/>
       <c r="O1068" s="18"/>
@@ -59924,11 +60021,11 @@
       <c r="J1069" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K1069" s="11" t="s">
-        <v>2329</v>
+      <c r="K1069" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1069" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1069" s="18"/>
       <c r="N1069" s="76" t="s">
@@ -60024,10 +60121,12 @@
       <c r="J1071" s="15" t="s">
         <v>1349</v>
       </c>
-      <c r="K1071" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1071" s="18"/>
+      <c r="K1071" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1071" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1071" s="18"/>
       <c r="N1071" s="40"/>
       <c r="O1071" s="18"/>
@@ -60068,10 +60167,12 @@
       <c r="J1072" s="15" t="s">
         <v>1349</v>
       </c>
-      <c r="K1072" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1072" s="18"/>
+      <c r="K1072" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1072" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1072" s="18"/>
       <c r="N1072" s="54">
         <v>825</v>
@@ -60116,10 +60217,12 @@
       <c r="J1073" s="15" t="s">
         <v>1349</v>
       </c>
-      <c r="K1073" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1073" s="18"/>
+      <c r="K1073" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1073" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1073" s="18"/>
       <c r="N1073" s="40"/>
       <c r="O1073" s="18"/>
@@ -60488,10 +60591,12 @@
       <c r="J1081" s="15" t="s">
         <v>1672</v>
       </c>
-      <c r="K1081" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1081" s="18"/>
+      <c r="K1081" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1081" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1081" s="18"/>
       <c r="N1081" s="40"/>
       <c r="O1081" s="18"/>
@@ -68326,10 +68431,12 @@
       <c r="J1257" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K1257" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1257" s="18"/>
+      <c r="K1257" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1257" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1257" s="18"/>
       <c r="N1257" s="54">
         <v>554</v>
@@ -68760,11 +68867,11 @@
       <c r="J1266" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1266" s="11" t="s">
-        <v>2329</v>
+      <c r="K1266" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1266" s="53">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="M1266" s="18"/>
       <c r="N1266" s="54">
@@ -68910,11 +69017,11 @@
       <c r="J1269" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1269" s="11" t="s">
-        <v>2329</v>
+      <c r="K1269" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1269" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1269" s="18"/>
       <c r="N1269" s="54">
@@ -69008,11 +69115,11 @@
       <c r="J1271" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1271" s="11" t="s">
-        <v>2329</v>
+      <c r="K1271" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1271" s="53">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="M1271" s="18"/>
       <c r="N1271" s="54">
@@ -69058,10 +69165,12 @@
       <c r="J1272" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1272" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1272" s="18"/>
+      <c r="K1272" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1272" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1272" s="18"/>
       <c r="N1272" s="54">
         <v>951</v>
@@ -69104,10 +69213,12 @@
       <c r="J1273" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1273" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1273" s="18"/>
+      <c r="K1273" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1273" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1273" s="18"/>
       <c r="N1273" s="54">
         <v>515</v>
@@ -70032,10 +70143,12 @@
       <c r="J1293" s="15" t="s">
         <v>839</v>
       </c>
-      <c r="K1293" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1293" s="18"/>
+      <c r="K1293" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1293" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1293" s="18"/>
       <c r="N1293" s="40"/>
       <c r="O1293" s="18"/>
@@ -70076,10 +70189,12 @@
       <c r="J1294" s="15" t="s">
         <v>950</v>
       </c>
-      <c r="K1294" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1294" s="18"/>
+      <c r="K1294" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1294" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1294" s="18"/>
       <c r="N1294" s="54">
         <v>901</v>
@@ -70124,10 +70239,12 @@
       <c r="J1295" s="15" t="s">
         <v>950</v>
       </c>
-      <c r="K1295" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1295" s="18"/>
+      <c r="K1295" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1295" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1295" s="18"/>
       <c r="N1295" s="54">
         <v>894</v>
@@ -70220,10 +70337,12 @@
       <c r="J1297" s="15" t="s">
         <v>950</v>
       </c>
-      <c r="K1297" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1297" s="18"/>
+      <c r="K1297" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1297" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1297" s="18"/>
       <c r="N1297" s="54">
         <v>893</v>
@@ -70266,10 +70385,12 @@
       <c r="J1298" s="15" t="s">
         <v>1879</v>
       </c>
-      <c r="K1298" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1298" s="18"/>
+      <c r="K1298" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1298" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1298" s="18"/>
       <c r="N1298" s="40"/>
       <c r="O1298" s="18"/>
@@ -70312,10 +70433,12 @@
       <c r="J1299" s="15" t="s">
         <v>1879</v>
       </c>
-      <c r="K1299" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1299" s="18"/>
+      <c r="K1299" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1299" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1299" s="18"/>
       <c r="N1299" s="54">
         <v>999</v>
@@ -70360,10 +70483,12 @@
       <c r="J1300" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="K1300" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1300" s="18"/>
+      <c r="K1300" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1300" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1300" s="18"/>
       <c r="N1300" s="54">
         <v>585</v>
@@ -70408,10 +70533,12 @@
       <c r="J1301" s="15" t="s">
         <v>950</v>
       </c>
-      <c r="K1301" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1301" s="18"/>
+      <c r="K1301" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1301" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1301" s="18"/>
       <c r="N1301" s="54">
         <v>456</v>
@@ -70456,10 +70583,12 @@
       <c r="J1302" s="15" t="s">
         <v>1893</v>
       </c>
-      <c r="K1302" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1302" s="18"/>
+      <c r="K1302" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1302" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1302" s="18"/>
       <c r="N1302" s="54">
         <v>765</v>
@@ -70504,10 +70633,12 @@
       <c r="J1303" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="K1303" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1303" s="18"/>
+      <c r="K1303" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1303" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1303" s="18"/>
       <c r="N1303" s="40"/>
       <c r="O1303" s="18"/>
@@ -70548,10 +70679,12 @@
       <c r="J1304" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="K1304" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1304" s="18"/>
+      <c r="K1304" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1304" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1304" s="18"/>
       <c r="N1304" s="40"/>
       <c r="O1304" s="18"/>
@@ -70776,10 +70909,12 @@
       <c r="J1309" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="K1309" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1309" s="18"/>
+      <c r="K1309" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1309" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1309" s="18"/>
       <c r="N1309" s="40"/>
       <c r="O1309" s="18"/>
@@ -70820,10 +70955,12 @@
       <c r="J1310" s="15" t="s">
         <v>715</v>
       </c>
-      <c r="K1310" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1310" s="18"/>
+      <c r="K1310" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1310" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1310" s="18"/>
       <c r="N1310" s="54">
         <v>576</v>
@@ -71238,10 +71375,12 @@
       <c r="J1319" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1319" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1319" s="18"/>
+      <c r="K1319" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1319" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1319" s="18"/>
       <c r="N1319" s="54">
         <v>659</v>
@@ -71332,10 +71471,12 @@
       <c r="J1321" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1321" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1321" s="18"/>
+      <c r="K1321" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1321" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1321" s="18"/>
       <c r="N1321" s="40"/>
       <c r="O1321" s="18"/>
@@ -71376,10 +71517,12 @@
       <c r="J1322" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1322" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1322" s="18"/>
+      <c r="K1322" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1322" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1322" s="18"/>
       <c r="N1322" s="40"/>
       <c r="O1322" s="18"/>
@@ -71710,10 +71853,12 @@
       <c r="J1329" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1329" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1329" s="18"/>
+      <c r="K1329" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1329" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1329" s="18"/>
       <c r="N1329" s="40"/>
       <c r="O1329" s="53">
@@ -71756,10 +71901,12 @@
       <c r="J1330" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1330" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1330" s="18"/>
+      <c r="K1330" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1330" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1330" s="18"/>
       <c r="N1330" s="54">
         <v>660</v>
@@ -71846,11 +71993,11 @@
       <c r="J1332" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1332" s="11" t="s">
-        <v>2329</v>
+      <c r="K1332" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1332" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1332" s="18"/>
       <c r="N1332" s="54">
@@ -71894,10 +72041,12 @@
       <c r="J1333" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1333" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1333" s="18"/>
+      <c r="K1333" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1333" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1333" s="18"/>
       <c r="N1333" s="40"/>
       <c r="O1333" s="18"/>
@@ -72084,10 +72233,12 @@
       <c r="J1337" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1337" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1337" s="18"/>
+      <c r="K1337" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1337" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1337" s="18"/>
       <c r="N1337" s="54" t="s">
         <v>2129</v>
@@ -72132,10 +72283,12 @@
       <c r="J1338" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1338" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1338" s="18"/>
+      <c r="K1338" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1338" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1338" s="18"/>
       <c r="N1338" s="54">
         <v>513</v>
@@ -72180,10 +72333,12 @@
       <c r="J1339" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1339" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1339" s="18"/>
+      <c r="K1339" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1339" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1339" s="18"/>
       <c r="N1339" s="54">
         <v>541</v>
@@ -72458,10 +72613,12 @@
       <c r="J1345" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1345" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1345" s="18"/>
+      <c r="K1345" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1345" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1345" s="18"/>
       <c r="N1345" s="54">
         <v>702</v>
@@ -72644,11 +72801,11 @@
       <c r="J1349" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1349" s="11" t="s">
-        <v>2329</v>
+      <c r="K1349" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1349" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1349" s="18"/>
       <c r="N1349" s="54">
@@ -72692,10 +72849,12 @@
       <c r="J1350" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1350" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1350" s="18"/>
+      <c r="K1350" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1350" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1350" s="18"/>
       <c r="N1350" s="54">
         <v>680</v>
@@ -73056,10 +73215,12 @@
       <c r="J1358" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1358" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1358" s="18"/>
+      <c r="K1358" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1358" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1358" s="18"/>
       <c r="N1358" s="40"/>
       <c r="O1358" s="18"/>
@@ -73100,10 +73261,12 @@
       <c r="J1359" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1359" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1359" s="18"/>
+      <c r="K1359" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1359" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1359" s="18"/>
       <c r="N1359" s="40"/>
       <c r="O1359" s="53">
@@ -73192,10 +73355,12 @@
       <c r="J1361" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1361" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1361" s="18"/>
+      <c r="K1361" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1361" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1361" s="18"/>
       <c r="N1361" s="40"/>
       <c r="O1361" s="18"/>
@@ -73236,11 +73401,11 @@
       <c r="J1362" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1362" s="11" t="s">
-        <v>2329</v>
+      <c r="K1362" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1362" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1362" s="18"/>
       <c r="N1362" s="54">
@@ -73284,10 +73449,12 @@
       <c r="J1363" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1363" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1363" s="18"/>
+      <c r="K1363" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1363" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1363" s="18"/>
       <c r="N1363" s="40"/>
       <c r="O1363" s="18"/>
@@ -73328,10 +73495,12 @@
       <c r="J1364" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1364" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1364" s="18"/>
+      <c r="K1364" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1364" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1364" s="18"/>
       <c r="N1364" s="40"/>
       <c r="O1364" s="18"/>
@@ -73740,10 +73909,12 @@
       <c r="J1373" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1373" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1373" s="18"/>
+      <c r="K1373" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1373" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1373" s="18"/>
       <c r="N1373" s="54">
         <v>705</v>
@@ -73786,10 +73957,12 @@
       <c r="J1374" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1374" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1374" s="18"/>
+      <c r="K1374" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1374" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1374" s="18"/>
       <c r="N1374" s="40"/>
       <c r="O1374" s="18"/>
@@ -74058,10 +74231,12 @@
       <c r="J1380" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1380" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1380" s="18"/>
+      <c r="K1380" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1380" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1380" s="18"/>
       <c r="N1380" s="40"/>
       <c r="O1380" s="18"/>
@@ -74102,10 +74277,12 @@
       <c r="J1381" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1381" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1381" s="18"/>
+      <c r="K1381" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1381" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1381" s="18"/>
       <c r="N1381" s="40"/>
       <c r="O1381" s="18"/>
@@ -74146,10 +74323,12 @@
       <c r="J1382" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1382" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1382" s="18"/>
+      <c r="K1382" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1382" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1382" s="18"/>
       <c r="N1382" s="54">
         <v>500</v>
@@ -74194,10 +74373,12 @@
       <c r="J1383" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1383" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1383" s="18"/>
+      <c r="K1383" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1383" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1383" s="18"/>
       <c r="N1383" s="54">
         <v>517</v>
@@ -74242,10 +74423,12 @@
       <c r="J1384" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1384" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1384" s="18"/>
+      <c r="K1384" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1384" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1384" s="18"/>
       <c r="N1384" s="54">
         <v>717</v>
@@ -74384,10 +74567,12 @@
       <c r="J1387" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1387" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1387" s="18"/>
+      <c r="K1387" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1387" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1387" s="18"/>
       <c r="N1387" s="54">
         <v>710</v>
@@ -74742,10 +74927,12 @@
       <c r="J1395" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1395" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1395" s="18"/>
+      <c r="K1395" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1395" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1395" s="18"/>
       <c r="N1395" s="40"/>
       <c r="O1395" s="18"/>
@@ -74880,10 +75067,12 @@
       <c r="J1398" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K1398" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1398" s="18"/>
+      <c r="K1398" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1398" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1398" s="18"/>
       <c r="N1398" s="40"/>
       <c r="O1398" s="18"/>
@@ -74926,10 +75115,12 @@
       <c r="J1399" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K1399" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1399" s="18"/>
+      <c r="K1399" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1399" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1399" s="18"/>
       <c r="N1399" s="40"/>
       <c r="O1399" s="18"/>
@@ -74972,10 +75163,12 @@
       <c r="J1400" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K1400" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1400" s="18"/>
+      <c r="K1400" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1400" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1400" s="18"/>
       <c r="N1400" s="40"/>
       <c r="O1400" s="18"/>
@@ -75018,10 +75211,12 @@
       <c r="J1401" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K1401" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1401" s="18"/>
+      <c r="K1401" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1401" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1401" s="18"/>
       <c r="N1401" s="40"/>
       <c r="O1401" s="18"/>
@@ -75064,10 +75259,12 @@
       <c r="J1402" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K1402" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1402" s="18"/>
+      <c r="K1402" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1402" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1402" s="18"/>
       <c r="N1402" s="40"/>
       <c r="O1402" s="18"/>
@@ -77156,10 +77353,12 @@
       <c r="J1448" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="K1448" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1448" s="18"/>
+      <c r="K1448" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1448" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1448" s="18"/>
       <c r="N1448" s="54">
         <v>899</v>
@@ -77204,10 +77403,12 @@
       <c r="J1449" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="K1449" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1449" s="28"/>
+      <c r="K1449" s="64" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1449" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1449" s="28"/>
       <c r="N1449" s="27">
         <v>889</v>
@@ -77252,10 +77453,12 @@
       <c r="J1450" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="K1450" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1450" s="18"/>
+      <c r="K1450" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1450" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1450" s="18"/>
       <c r="N1450" s="54">
         <v>898</v>
@@ -77578,10 +77781,12 @@
       <c r="J1457" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1457" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1457" s="18"/>
+      <c r="K1457" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1457" s="53">
+        <v>46251</v>
+      </c>
       <c r="M1457" s="18"/>
       <c r="N1457" s="54">
         <v>1026</v>
@@ -79468,10 +79673,12 @@
       <c r="J1499" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K1499" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1499" s="18"/>
+      <c r="K1499" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1499" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1499" s="18"/>
       <c r="N1499" s="54">
         <v>1016</v>
@@ -79516,10 +79723,12 @@
       <c r="J1500" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K1500" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1500" s="18"/>
+      <c r="K1500" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1500" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1500" s="18"/>
       <c r="N1500" s="54">
         <v>1017</v>
@@ -82277,6 +82486,316 @@
         <v>131</v>
       </c>
     </row>
+    <row r="1562" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1562" s="2">
+        <v>43</v>
+      </c>
+      <c r="B1562" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1562" s="23" t="s">
+        <v>2368</v>
+      </c>
+      <c r="D1562" s="11">
+        <v>5563107</v>
+      </c>
+      <c r="E1562" s="82" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1562" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1562" s="14">
+        <v>3672</v>
+      </c>
+      <c r="H1562" s="15">
+        <v>4628</v>
+      </c>
+      <c r="I1562" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1562" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1562" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1562" s="18"/>
+      <c r="M1562" s="18"/>
+      <c r="N1562" s="40"/>
+      <c r="O1562" s="18"/>
+      <c r="P1562" s="18"/>
+      <c r="Q1562" s="18"/>
+      <c r="R1562" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1563" s="2">
+        <v>44</v>
+      </c>
+      <c r="B1563" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1563" s="23" t="s">
+        <v>2369</v>
+      </c>
+      <c r="D1563" s="11" t="s">
+        <v>2370</v>
+      </c>
+      <c r="E1563" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1563" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1563" s="14">
+        <v>22982</v>
+      </c>
+      <c r="H1563" s="15">
+        <v>24633</v>
+      </c>
+      <c r="I1563" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1563" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="K1563" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1563" s="18"/>
+      <c r="M1563" s="18"/>
+      <c r="N1563" s="40"/>
+      <c r="O1563" s="18"/>
+      <c r="P1563" s="18"/>
+      <c r="Q1563" s="18"/>
+      <c r="R1563" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1564" s="2">
+        <v>45</v>
+      </c>
+      <c r="B1564" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1564" s="23" t="s">
+        <v>2371</v>
+      </c>
+      <c r="D1564" s="11">
+        <v>1733157</v>
+      </c>
+      <c r="E1564" s="82" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1564" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1564" s="14">
+        <v>9616</v>
+      </c>
+      <c r="H1564" s="15">
+        <v>5417</v>
+      </c>
+      <c r="I1564" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1564" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1564" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1564" s="18"/>
+      <c r="M1564" s="18"/>
+      <c r="N1564" s="40"/>
+      <c r="O1564" s="18"/>
+      <c r="P1564" s="18"/>
+      <c r="Q1564" s="18"/>
+      <c r="R1564" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1565" s="2">
+        <v>46</v>
+      </c>
+      <c r="B1565" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1565" s="23" t="s">
+        <v>2372</v>
+      </c>
+      <c r="D1565" s="11">
+        <v>15584447</v>
+      </c>
+      <c r="E1565" s="82" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1565" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1565" s="14">
+        <v>6698</v>
+      </c>
+      <c r="H1565" s="15">
+        <v>1400</v>
+      </c>
+      <c r="I1565" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1565" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1565" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1565" s="18"/>
+      <c r="M1565" s="18"/>
+      <c r="N1565" s="40"/>
+      <c r="O1565" s="18"/>
+      <c r="P1565" s="18"/>
+      <c r="Q1565" s="18"/>
+      <c r="R1565" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1566" s="2">
+        <v>47</v>
+      </c>
+      <c r="B1566" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1566" s="23" t="s">
+        <v>2373</v>
+      </c>
+      <c r="D1566" s="11">
+        <v>13076492</v>
+      </c>
+      <c r="E1566" s="82" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1566" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1566" s="14">
+        <v>3025</v>
+      </c>
+      <c r="H1566" s="15">
+        <v>3565</v>
+      </c>
+      <c r="I1566" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1566" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1566" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1566" s="18"/>
+      <c r="M1566" s="18"/>
+      <c r="N1566" s="40"/>
+      <c r="O1566" s="18"/>
+      <c r="P1566" s="18"/>
+      <c r="Q1566" s="18"/>
+      <c r="R1566" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1567" s="2">
+        <v>48</v>
+      </c>
+      <c r="B1567" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1567" s="23" t="s">
+        <v>2374</v>
+      </c>
+      <c r="D1567" s="11">
+        <v>8359317</v>
+      </c>
+      <c r="E1567" s="82" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1567" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1567" s="14">
+        <v>3492</v>
+      </c>
+      <c r="H1567" s="15">
+        <v>7224</v>
+      </c>
+      <c r="I1567" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1567" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1567" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1567" s="18"/>
+      <c r="M1567" s="18"/>
+      <c r="N1567" s="40"/>
+      <c r="O1567" s="18"/>
+      <c r="P1567" s="18"/>
+      <c r="Q1567" s="18"/>
+      <c r="R1567" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:18" ht="24.6" thickBot="1">
+      <c r="A1568" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1568" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1568" s="23" t="s">
+        <v>2375</v>
+      </c>
+      <c r="D1568" s="11" t="s">
+        <v>2376</v>
+      </c>
+      <c r="E1568" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1568" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1568" s="14">
+        <v>19899</v>
+      </c>
+      <c r="H1568" s="15">
+        <v>56711</v>
+      </c>
+      <c r="I1568" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1568" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1568" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1568" s="18"/>
+      <c r="M1568" s="18"/>
+      <c r="N1568" s="40"/>
+      <c r="O1568" s="18"/>
+      <c r="P1568" s="18"/>
+      <c r="Q1568" s="11">
+        <v>76828356</v>
+      </c>
+      <c r="R1568" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E6E316-45E0-4993-97A2-921AE7599C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F09025-B2C9-4E83-9C30-BC4E35C571C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11703" uniqueCount="2377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11741" uniqueCount="2384">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -7169,13 +7169,34 @@
   </si>
   <si>
     <t>NA1173862</t>
+  </si>
+  <si>
+    <t>USAMA</t>
+  </si>
+  <si>
+    <t>DILNAWAR NAZIR</t>
+  </si>
+  <si>
+    <t>YAHYA HARIB</t>
+  </si>
+  <si>
+    <t>3638*</t>
+  </si>
+  <si>
+    <t>BR5305751</t>
+  </si>
+  <si>
+    <t>AZHAR ABBAS</t>
+  </si>
+  <si>
+    <t>CW1014614</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="40">
+  <fonts count="41">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7422,6 +7443,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -7569,7 +7597,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7815,6 +7843,51 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8131,7 +8204,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1568"/>
+  <dimension ref="A1:R1573"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -82796,6 +82869,230 @@
         <v>131</v>
       </c>
     </row>
+    <row r="1569" spans="1:18" ht="24.6" thickBot="1">
+      <c r="A1569" s="83">
+        <v>50</v>
+      </c>
+      <c r="B1569" s="84">
+        <v>46247</v>
+      </c>
+      <c r="C1569" s="85" t="s">
+        <v>2377</v>
+      </c>
+      <c r="D1569" s="86">
+        <v>131424936</v>
+      </c>
+      <c r="E1569" s="87" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1569" s="88" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1569" s="89">
+        <v>2058</v>
+      </c>
+      <c r="H1569" s="90">
+        <v>3009</v>
+      </c>
+      <c r="I1569" s="91" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1569" s="92" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1569" s="93" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1569" s="94"/>
+      <c r="M1569" s="94"/>
+      <c r="N1569" s="95"/>
+      <c r="O1569" s="94"/>
+      <c r="P1569" s="94"/>
+      <c r="Q1569" s="86">
+        <v>97798874</v>
+      </c>
+      <c r="R1569" s="96" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:18" ht="24.6" thickBot="1">
+      <c r="A1570" s="2">
+        <v>51</v>
+      </c>
+      <c r="B1570" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1570" s="23" t="s">
+        <v>2378</v>
+      </c>
+      <c r="D1570" s="11">
+        <v>111354348</v>
+      </c>
+      <c r="E1570" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1570" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1570" s="14">
+        <v>8320</v>
+      </c>
+      <c r="H1570" s="15">
+        <v>7528</v>
+      </c>
+      <c r="I1570" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1570" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1570" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1570" s="18"/>
+      <c r="M1570" s="18"/>
+      <c r="N1570" s="40"/>
+      <c r="O1570" s="18"/>
+      <c r="P1570" s="18"/>
+      <c r="Q1570" s="11">
+        <v>98839150</v>
+      </c>
+      <c r="R1570" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1571" s="2">
+        <v>52</v>
+      </c>
+      <c r="B1571" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1571" s="23" t="s">
+        <v>2379</v>
+      </c>
+      <c r="D1571" s="11">
+        <v>5249316</v>
+      </c>
+      <c r="E1571" s="82" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1571" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1571" s="14" t="s">
+        <v>2380</v>
+      </c>
+      <c r="H1571" s="15">
+        <v>4292</v>
+      </c>
+      <c r="I1571" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1571" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1571" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1571" s="18"/>
+      <c r="M1571" s="18"/>
+      <c r="N1571" s="40"/>
+      <c r="O1571" s="18"/>
+      <c r="P1571" s="18"/>
+      <c r="Q1571" s="18"/>
+      <c r="R1571" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:18" ht="24.6" thickBot="1">
+      <c r="A1572" s="2">
+        <v>54</v>
+      </c>
+      <c r="B1572" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1572" s="23" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D1572" s="11" t="s">
+        <v>2381</v>
+      </c>
+      <c r="E1572" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1572" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1572" s="97">
+        <v>41780</v>
+      </c>
+      <c r="H1572" s="15">
+        <v>95934</v>
+      </c>
+      <c r="I1572" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1572" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1572" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1572" s="18"/>
+      <c r="M1572" s="18"/>
+      <c r="N1572" s="40"/>
+      <c r="O1572" s="18"/>
+      <c r="P1572" s="18"/>
+      <c r="Q1572" s="18"/>
+      <c r="R1572" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:18" ht="24.6" thickBot="1">
+      <c r="A1573" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1573" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1573" s="23" t="s">
+        <v>2382</v>
+      </c>
+      <c r="D1573" s="11" t="s">
+        <v>2383</v>
+      </c>
+      <c r="E1573" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1573" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1573" s="97">
+        <v>8937</v>
+      </c>
+      <c r="H1573" s="15">
+        <v>91809</v>
+      </c>
+      <c r="I1573" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1573" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1573" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1573" s="18"/>
+      <c r="M1573" s="18"/>
+      <c r="N1573" s="40"/>
+      <c r="O1573" s="18"/>
+      <c r="P1573" s="18"/>
+      <c r="Q1573" s="18"/>
+      <c r="R1573" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F09025-B2C9-4E83-9C30-BC4E35C571C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F582F8A-555E-474A-8F3D-3E9C5C3AC4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11741" uniqueCount="2384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11807" uniqueCount="2401">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -7190,6 +7190,57 @@
   </si>
   <si>
     <t>CW1014614</t>
+  </si>
+  <si>
+    <t>HASNAIN</t>
+  </si>
+  <si>
+    <t>JT6806952</t>
+  </si>
+  <si>
+    <t>JAGANGIR AHMAD</t>
+  </si>
+  <si>
+    <t>AF1165884</t>
+  </si>
+  <si>
+    <t>63518-</t>
+  </si>
+  <si>
+    <t>WAQAS AKTHAR</t>
+  </si>
+  <si>
+    <t>FM1343515</t>
+  </si>
+  <si>
+    <t>ALKASHDEEP MASIH</t>
+  </si>
+  <si>
+    <t>U1527301</t>
+  </si>
+  <si>
+    <t>KARANJITH SINGH</t>
+  </si>
+  <si>
+    <t>W9036388</t>
+  </si>
+  <si>
+    <t>PRABHOT SINGH</t>
+  </si>
+  <si>
+    <t>W5616020</t>
+  </si>
+  <si>
+    <t>KW1171681</t>
+  </si>
+  <si>
+    <t>7782 7693</t>
+  </si>
+  <si>
+    <t>MOHSIN RAZA</t>
+  </si>
+  <si>
+    <t>MF9895003</t>
   </si>
 </sst>
 </file>
@@ -7597,7 +7648,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7843,48 +7894,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8204,7 +8213,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1573"/>
+  <dimension ref="A1:R1581"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -8910,7 +8919,9 @@
       <c r="N14" s="54">
         <v>445</v>
       </c>
-      <c r="O14" s="18"/>
+      <c r="O14" s="53">
+        <v>46245</v>
+      </c>
       <c r="P14" s="18"/>
       <c r="Q14" s="11">
         <v>99737154</v>
@@ -8960,7 +8971,9 @@
       <c r="N15" s="54">
         <v>446</v>
       </c>
-      <c r="O15" s="18"/>
+      <c r="O15" s="53">
+        <v>46245</v>
+      </c>
       <c r="P15" s="18"/>
       <c r="Q15" s="11">
         <v>96194409</v>
@@ -14556,7 +14569,9 @@
       <c r="N129" s="54">
         <v>409</v>
       </c>
-      <c r="O129" s="18"/>
+      <c r="O129" s="53">
+        <v>46245</v>
+      </c>
       <c r="P129" s="18"/>
       <c r="Q129" s="11">
         <v>95700385</v>
@@ -14706,7 +14721,9 @@
       <c r="N132" s="54">
         <v>410</v>
       </c>
-      <c r="O132" s="18"/>
+      <c r="O132" s="53">
+        <v>46245</v>
+      </c>
       <c r="P132" s="18"/>
       <c r="Q132" s="11">
         <v>74188218</v>
@@ -15460,7 +15477,9 @@
       <c r="N147" s="54">
         <v>424</v>
       </c>
-      <c r="O147" s="18"/>
+      <c r="O147" s="53">
+        <v>46245</v>
+      </c>
       <c r="P147" s="18"/>
       <c r="Q147" s="11">
         <v>76905359</v>
@@ -18960,7 +18979,9 @@
       <c r="N219" s="54">
         <v>229</v>
       </c>
-      <c r="O219" s="18"/>
+      <c r="O219" s="53">
+        <v>46245</v>
+      </c>
       <c r="P219" s="18"/>
       <c r="Q219" s="11">
         <v>79281667</v>
@@ -19554,7 +19575,9 @@
       <c r="N232" s="54">
         <v>428</v>
       </c>
-      <c r="O232" s="18"/>
+      <c r="O232" s="53">
+        <v>46245</v>
+      </c>
       <c r="P232" s="18"/>
       <c r="Q232" s="11">
         <v>96100705</v>
@@ -20068,7 +20091,9 @@
       <c r="N243" s="54">
         <v>283</v>
       </c>
-      <c r="O243" s="18"/>
+      <c r="O243" s="53">
+        <v>46245</v>
+      </c>
       <c r="P243" s="18"/>
       <c r="Q243" s="11">
         <v>98183017</v>
@@ -20886,7 +20911,9 @@
       <c r="N260" s="54">
         <v>421</v>
       </c>
-      <c r="O260" s="18"/>
+      <c r="O260" s="53">
+        <v>46245</v>
+      </c>
       <c r="P260" s="18"/>
       <c r="Q260" s="11">
         <v>92501330</v>
@@ -22316,7 +22343,9 @@
       <c r="L290" s="18"/>
       <c r="M290" s="18"/>
       <c r="N290" s="40"/>
-      <c r="O290" s="18"/>
+      <c r="O290" s="53">
+        <v>46245</v>
+      </c>
       <c r="P290" s="18"/>
       <c r="Q290" s="11">
         <v>77597558</v>
@@ -25440,7 +25469,9 @@
       <c r="N354" s="54">
         <v>148</v>
       </c>
-      <c r="O354" s="18"/>
+      <c r="O354" s="53">
+        <v>46245</v>
+      </c>
       <c r="P354" s="18"/>
       <c r="Q354" s="11">
         <v>90183385</v>
@@ -25642,7 +25673,9 @@
       <c r="N358" s="54">
         <v>163</v>
       </c>
-      <c r="O358" s="18"/>
+      <c r="O358" s="53">
+        <v>46245</v>
+      </c>
       <c r="P358" s="18"/>
       <c r="Q358" s="11">
         <v>98915192</v>
@@ -27130,7 +27163,9 @@
       <c r="N388" s="54">
         <v>457</v>
       </c>
-      <c r="O388" s="18"/>
+      <c r="O388" s="53">
+        <v>46245</v>
+      </c>
       <c r="P388" s="18"/>
       <c r="Q388" s="11">
         <v>94210084</v>
@@ -27180,7 +27215,9 @@
       <c r="N389" s="54">
         <v>396</v>
       </c>
-      <c r="O389" s="18"/>
+      <c r="O389" s="53">
+        <v>46245</v>
+      </c>
       <c r="P389" s="18"/>
       <c r="Q389" s="11">
         <v>94210084</v>
@@ -27604,7 +27641,9 @@
       <c r="N398" s="54">
         <v>667</v>
       </c>
-      <c r="O398" s="18"/>
+      <c r="O398" s="53">
+        <v>46245</v>
+      </c>
       <c r="P398" s="18"/>
       <c r="Q398" s="11">
         <v>94377988</v>
@@ -27654,7 +27693,9 @@
       <c r="N399" s="54">
         <v>459</v>
       </c>
-      <c r="O399" s="18"/>
+      <c r="O399" s="53">
+        <v>46245</v>
+      </c>
       <c r="P399" s="49" t="s">
         <v>625</v>
       </c>
@@ -29940,7 +29981,9 @@
       <c r="N446" s="54">
         <v>467</v>
       </c>
-      <c r="O446" s="18"/>
+      <c r="O446" s="53">
+        <v>46245</v>
+      </c>
       <c r="P446" s="18"/>
       <c r="Q446" s="11">
         <v>96977860</v>
@@ -39868,7 +39911,9 @@
       <c r="N651" s="76" t="s">
         <v>2115</v>
       </c>
-      <c r="O651" s="18"/>
+      <c r="O651" s="53">
+        <v>46245</v>
+      </c>
       <c r="P651" s="49" t="s">
         <v>1787</v>
       </c>
@@ -54338,7 +54383,9 @@
       <c r="N952" s="54">
         <v>426</v>
       </c>
-      <c r="O952" s="18"/>
+      <c r="O952" s="53">
+        <v>46245</v>
+      </c>
       <c r="P952" s="18"/>
       <c r="Q952" s="15">
         <v>76730900</v>
@@ -58348,7 +58395,9 @@
       <c r="N1033" s="54">
         <v>150</v>
       </c>
-      <c r="O1033" s="18"/>
+      <c r="O1033" s="53">
+        <v>46245</v>
+      </c>
       <c r="P1033" s="18"/>
       <c r="Q1033" s="15">
         <v>76716831</v>
@@ -58842,7 +58891,9 @@
       <c r="N1043" s="54">
         <v>461</v>
       </c>
-      <c r="O1043" s="18"/>
+      <c r="O1043" s="53">
+        <v>46245</v>
+      </c>
       <c r="P1043" s="18"/>
       <c r="Q1043" s="15">
         <v>79289188</v>
@@ -64656,7 +64707,9 @@
       <c r="L1173" s="18"/>
       <c r="M1173" s="18"/>
       <c r="N1173" s="40"/>
-      <c r="O1173" s="18"/>
+      <c r="O1173" s="53">
+        <v>46245</v>
+      </c>
       <c r="P1173" s="18"/>
       <c r="Q1173" s="55">
         <v>94000637</v>
@@ -65340,7 +65393,9 @@
       <c r="L1188" s="18"/>
       <c r="M1188" s="18"/>
       <c r="N1188" s="40"/>
-      <c r="O1188" s="18"/>
+      <c r="O1188" s="53">
+        <v>46245</v>
+      </c>
       <c r="P1188" s="18"/>
       <c r="Q1188" s="18"/>
       <c r="R1188" s="22" t="s">
@@ -70136,7 +70191,9 @@
       <c r="L1291" s="18"/>
       <c r="M1291" s="18"/>
       <c r="N1291" s="40"/>
-      <c r="O1291" s="18"/>
+      <c r="O1291" s="53">
+        <v>46245</v>
+      </c>
       <c r="P1291" s="18"/>
       <c r="Q1291" s="18"/>
       <c r="R1291" s="18"/>
@@ -74552,7 +74609,9 @@
       <c r="N1385" s="54">
         <v>427</v>
       </c>
-      <c r="O1385" s="18"/>
+      <c r="O1385" s="53">
+        <v>46245</v>
+      </c>
       <c r="P1385" s="18"/>
       <c r="Q1385" s="11">
         <v>77032533</v>
@@ -74600,7 +74659,9 @@
       <c r="N1386" s="54">
         <v>429</v>
       </c>
-      <c r="O1386" s="18"/>
+      <c r="O1386" s="53">
+        <v>46245</v>
+      </c>
       <c r="P1386" s="18"/>
       <c r="Q1386" s="11">
         <v>79341622</v>
@@ -74794,7 +74855,9 @@
       <c r="N1390" s="54">
         <v>414</v>
       </c>
-      <c r="O1390" s="18"/>
+      <c r="O1390" s="53">
+        <v>46245</v>
+      </c>
       <c r="P1390" s="18"/>
       <c r="Q1390" s="11">
         <v>96144786</v>
@@ -80801,7 +80864,9 @@
       </c>
       <c r="L1522" s="18"/>
       <c r="M1522" s="18"/>
-      <c r="N1522" s="40"/>
+      <c r="N1522" s="54">
+        <v>71</v>
+      </c>
       <c r="O1522" s="18"/>
       <c r="P1522" s="18"/>
       <c r="Q1522" s="18"/>
@@ -82870,48 +82935,48 @@
       </c>
     </row>
     <row r="1569" spans="1:18" ht="24.6" thickBot="1">
-      <c r="A1569" s="83">
+      <c r="A1569" s="2">
         <v>50</v>
       </c>
-      <c r="B1569" s="84">
+      <c r="B1569" s="10">
         <v>46247</v>
       </c>
-      <c r="C1569" s="85" t="s">
+      <c r="C1569" s="23" t="s">
         <v>2377</v>
       </c>
-      <c r="D1569" s="86">
+      <c r="D1569" s="11">
         <v>131424936</v>
       </c>
-      <c r="E1569" s="87" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1569" s="88" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1569" s="89">
+      <c r="E1569" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1569" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1569" s="14">
         <v>2058</v>
       </c>
-      <c r="H1569" s="90">
+      <c r="H1569" s="15">
         <v>3009</v>
       </c>
-      <c r="I1569" s="91" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1569" s="92" t="s">
+      <c r="I1569" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1569" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1569" s="93" t="s">
+      <c r="K1569" s="60" t="s">
         <v>1189</v>
       </c>
-      <c r="L1569" s="94"/>
-      <c r="M1569" s="94"/>
-      <c r="N1569" s="95"/>
-      <c r="O1569" s="94"/>
-      <c r="P1569" s="94"/>
-      <c r="Q1569" s="86">
+      <c r="L1569" s="18"/>
+      <c r="M1569" s="18"/>
+      <c r="N1569" s="40"/>
+      <c r="O1569" s="18"/>
+      <c r="P1569" s="18"/>
+      <c r="Q1569" s="11">
         <v>97798874</v>
       </c>
-      <c r="R1569" s="96" t="s">
+      <c r="R1569" s="22" t="s">
         <v>131</v>
       </c>
     </row>
@@ -83007,7 +83072,7 @@
     </row>
     <row r="1572" spans="1:18" ht="24.6" thickBot="1">
       <c r="A1572" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B1572" s="10">
         <v>46247</v>
@@ -83024,7 +83089,7 @@
       <c r="F1572" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="G1572" s="97">
+      <c r="G1572" s="83">
         <v>41780</v>
       </c>
       <c r="H1572" s="15">
@@ -83051,7 +83116,7 @@
     </row>
     <row r="1573" spans="1:18" ht="24.6" thickBot="1">
       <c r="A1573" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B1573" s="10">
         <v>46247</v>
@@ -83068,7 +83133,7 @@
       <c r="F1573" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="G1573" s="97">
+      <c r="G1573" s="83">
         <v>8937</v>
       </c>
       <c r="H1573" s="15">
@@ -83093,6 +83158,362 @@
         <v>131</v>
       </c>
     </row>
+    <row r="1574" spans="1:18" ht="24.6" thickBot="1">
+      <c r="A1574" s="2">
+        <v>55</v>
+      </c>
+      <c r="B1574" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1574" s="23" t="s">
+        <v>2384</v>
+      </c>
+      <c r="D1574" s="11" t="s">
+        <v>2385</v>
+      </c>
+      <c r="E1574" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1574" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1574" s="83">
+        <v>70284</v>
+      </c>
+      <c r="H1574" s="15">
+        <v>36263</v>
+      </c>
+      <c r="I1574" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1574" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1574" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1574" s="18"/>
+      <c r="M1574" s="18"/>
+      <c r="N1574" s="40"/>
+      <c r="O1574" s="18"/>
+      <c r="P1574" s="18"/>
+      <c r="Q1574" s="18"/>
+      <c r="R1574" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:18" ht="24.6" thickBot="1">
+      <c r="A1575" s="2">
+        <v>56</v>
+      </c>
+      <c r="B1575" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1575" s="23" t="s">
+        <v>2386</v>
+      </c>
+      <c r="D1575" s="11" t="s">
+        <v>2387</v>
+      </c>
+      <c r="E1575" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1575" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1575" s="83">
+        <v>92178</v>
+      </c>
+      <c r="H1575" s="15" t="s">
+        <v>2388</v>
+      </c>
+      <c r="I1575" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1575" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1575" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1575" s="18"/>
+      <c r="M1575" s="18"/>
+      <c r="N1575" s="40"/>
+      <c r="O1575" s="18"/>
+      <c r="P1575" s="18"/>
+      <c r="Q1575" s="18"/>
+      <c r="R1575" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:18" ht="24.6" thickBot="1">
+      <c r="A1576" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1576" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1576" s="23" t="s">
+        <v>2389</v>
+      </c>
+      <c r="D1576" s="11" t="s">
+        <v>2390</v>
+      </c>
+      <c r="E1576" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1576" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1576" s="83">
+        <v>56091</v>
+      </c>
+      <c r="H1576" s="15">
+        <v>57997</v>
+      </c>
+      <c r="I1576" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1576" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1576" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1576" s="18"/>
+      <c r="M1576" s="18"/>
+      <c r="N1576" s="40"/>
+      <c r="O1576" s="18"/>
+      <c r="P1576" s="18"/>
+      <c r="Q1576" s="18"/>
+      <c r="R1576" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:18" ht="27" thickBot="1">
+      <c r="A1577" s="2">
+        <v>58</v>
+      </c>
+      <c r="B1577" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1577" s="23" t="s">
+        <v>2391</v>
+      </c>
+      <c r="D1577" s="11" t="s">
+        <v>2392</v>
+      </c>
+      <c r="E1577" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1577" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1577" s="83">
+        <v>20201</v>
+      </c>
+      <c r="H1577" s="15">
+        <v>58249</v>
+      </c>
+      <c r="I1577" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1577" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1577" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1577" s="18"/>
+      <c r="M1577" s="18"/>
+      <c r="N1577" s="40"/>
+      <c r="O1577" s="18"/>
+      <c r="P1577" s="18"/>
+      <c r="Q1577" s="18"/>
+      <c r="R1577" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:18" ht="16.2" thickBot="1">
+      <c r="A1578" s="2">
+        <v>59</v>
+      </c>
+      <c r="B1578" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1578" s="23" t="s">
+        <v>2393</v>
+      </c>
+      <c r="D1578" s="11" t="s">
+        <v>2394</v>
+      </c>
+      <c r="E1578" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1578" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1578" s="83">
+        <v>20199</v>
+      </c>
+      <c r="H1578" s="15">
+        <v>58248</v>
+      </c>
+      <c r="I1578" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1578" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1578" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1578" s="18"/>
+      <c r="M1578" s="18"/>
+      <c r="N1578" s="40"/>
+      <c r="O1578" s="18"/>
+      <c r="P1578" s="18"/>
+      <c r="Q1578" s="18"/>
+      <c r="R1578" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:18" ht="16.2" thickBot="1">
+      <c r="A1579" s="2">
+        <v>60</v>
+      </c>
+      <c r="B1579" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1579" s="23" t="s">
+        <v>2395</v>
+      </c>
+      <c r="D1579" s="11" t="s">
+        <v>2396</v>
+      </c>
+      <c r="E1579" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1579" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1579" s="83">
+        <v>61330</v>
+      </c>
+      <c r="H1579" s="15">
+        <v>57299</v>
+      </c>
+      <c r="I1579" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1579" s="51" t="s">
+        <v>776</v>
+      </c>
+      <c r="K1579" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1579" s="18"/>
+      <c r="M1579" s="18"/>
+      <c r="N1579" s="40"/>
+      <c r="O1579" s="18"/>
+      <c r="P1579" s="18"/>
+      <c r="Q1579" s="18"/>
+      <c r="R1579" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1580" s="2">
+        <v>61</v>
+      </c>
+      <c r="B1580" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1580" s="23" t="s">
+        <v>767</v>
+      </c>
+      <c r="D1580" s="11" t="s">
+        <v>2397</v>
+      </c>
+      <c r="E1580" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1580" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1580" s="83">
+        <v>37154</v>
+      </c>
+      <c r="H1580" s="15">
+        <v>60370</v>
+      </c>
+      <c r="I1580" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1580" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="K1580" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1580" s="18"/>
+      <c r="M1580" s="18"/>
+      <c r="N1580" s="40"/>
+      <c r="O1580" s="18"/>
+      <c r="P1580" s="18"/>
+      <c r="Q1580" s="11" t="s">
+        <v>2398</v>
+      </c>
+      <c r="R1580" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1581" s="2">
+        <v>62</v>
+      </c>
+      <c r="B1581" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1581" s="23" t="s">
+        <v>2399</v>
+      </c>
+      <c r="D1581" s="11" t="s">
+        <v>2400</v>
+      </c>
+      <c r="E1581" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1581" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1581" s="83">
+        <v>80208</v>
+      </c>
+      <c r="H1581" s="15">
+        <v>71590</v>
+      </c>
+      <c r="I1581" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1581" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="K1581" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1581" s="18"/>
+      <c r="M1581" s="18"/>
+      <c r="N1581" s="40"/>
+      <c r="O1581" s="18"/>
+      <c r="P1581" s="18"/>
+      <c r="Q1581" s="11">
+        <v>77243948</v>
+      </c>
+      <c r="R1581" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08EFB12-489B-4ADD-8FC7-3601CAAA9740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D829FCC-ABB9-44EB-B09B-0DC5750C1E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12091" uniqueCount="2453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12154" uniqueCount="2491">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -6370,9 +6370,6 @@
     <t>BK1201855</t>
   </si>
   <si>
-    <t>141/764</t>
-  </si>
-  <si>
     <t>82//418</t>
   </si>
   <si>
@@ -7342,9 +7339,6 @@
     <t>5569*</t>
   </si>
   <si>
-    <t>GHULAM</t>
-  </si>
-  <si>
     <t>ABDULLAH NASSER SALIM</t>
   </si>
   <si>
@@ -7397,6 +7391,126 @@
   </si>
   <si>
     <t>CY9843536</t>
+  </si>
+  <si>
+    <t>978/1171</t>
+  </si>
+  <si>
+    <t>794/1170</t>
+  </si>
+  <si>
+    <t>1021/1088</t>
+  </si>
+  <si>
+    <t>854/1178</t>
+  </si>
+  <si>
+    <t>141/764/1101</t>
+  </si>
+  <si>
+    <t>790/1182</t>
+  </si>
+  <si>
+    <t>956/1201</t>
+  </si>
+  <si>
+    <t>931/1181</t>
+  </si>
+  <si>
+    <t>617/1215</t>
+  </si>
+  <si>
+    <t>896/1117</t>
+  </si>
+  <si>
+    <t>485/1143</t>
+  </si>
+  <si>
+    <t>175/1111</t>
+  </si>
+  <si>
+    <t>900/1211</t>
+  </si>
+  <si>
+    <t>328/1219</t>
+  </si>
+  <si>
+    <t>505/1098</t>
+  </si>
+  <si>
+    <t>506/1099</t>
+  </si>
+  <si>
+    <t>646/1123</t>
+  </si>
+  <si>
+    <t>644/1125</t>
+  </si>
+  <si>
+    <t>645/1124</t>
+  </si>
+  <si>
+    <t>1119/1216</t>
+  </si>
+  <si>
+    <t>697/1163</t>
+  </si>
+  <si>
+    <t>696/1164</t>
+  </si>
+  <si>
+    <t>695/1165</t>
+  </si>
+  <si>
+    <t>430/1152</t>
+  </si>
+  <si>
+    <t>444/1105</t>
+  </si>
+  <si>
+    <t>807/1151</t>
+  </si>
+  <si>
+    <t>839/1203</t>
+  </si>
+  <si>
+    <t>714/1206</t>
+  </si>
+  <si>
+    <t>875/1191</t>
+  </si>
+  <si>
+    <t>986/1155</t>
+  </si>
+  <si>
+    <t>987/1154</t>
+  </si>
+  <si>
+    <t>698/1116</t>
+  </si>
+  <si>
+    <t>664/1200</t>
+  </si>
+  <si>
+    <t>455/1120</t>
+  </si>
+  <si>
+    <t>769/1153</t>
+  </si>
+  <si>
+    <t>762/1197</t>
+  </si>
+  <si>
+    <t>922/1140</t>
+  </si>
+  <si>
+    <t>923/1139</t>
+  </si>
+  <si>
+    <t>FAHEEM ABBAS</t>
+  </si>
+  <si>
+    <t>JAMIL AMJAD</t>
   </si>
 </sst>
 </file>
@@ -8369,7 +8483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1619"/>
+  <dimension ref="A1:R1621"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -9518,7 +9632,7 @@
         <v>46</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L23" s="53">
         <v>46246</v>
@@ -9568,7 +9682,7 @@
         <v>46</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L24" s="53">
         <v>46246</v>
@@ -11753,7 +11867,7 @@
       <c r="L68" s="18"/>
       <c r="M68" s="18"/>
       <c r="N68" s="76" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="O68" s="53">
         <v>46244</v>
@@ -11796,7 +11910,7 @@
         <v>128</v>
       </c>
       <c r="K69" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L69" s="53">
         <v>46246</v>
@@ -12280,7 +12394,7 @@
         <v>126</v>
       </c>
       <c r="K79" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L79" s="53">
         <v>46246</v>
@@ -12580,8 +12694,8 @@
         <v>46247</v>
       </c>
       <c r="M85" s="18"/>
-      <c r="N85" s="54">
-        <v>978</v>
+      <c r="N85" s="54" t="s">
+        <v>2451</v>
       </c>
       <c r="O85" s="18"/>
       <c r="P85" s="18"/>
@@ -12630,8 +12744,8 @@
         <v>46247</v>
       </c>
       <c r="M86" s="18"/>
-      <c r="N86" s="54">
-        <v>794</v>
+      <c r="N86" s="54" t="s">
+        <v>2452</v>
       </c>
       <c r="O86" s="18"/>
       <c r="P86" s="18"/>
@@ -12956,8 +13070,8 @@
       </c>
       <c r="L93" s="18"/>
       <c r="M93" s="18"/>
-      <c r="N93" s="54">
-        <v>1021</v>
+      <c r="N93" s="54" t="s">
+        <v>2453</v>
       </c>
       <c r="O93" s="18"/>
       <c r="P93" s="36" t="s">
@@ -13096,7 +13210,7 @@
         <v>319</v>
       </c>
       <c r="K96" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L96" s="53">
         <v>46246</v>
@@ -13849,7 +13963,7 @@
       </c>
       <c r="M111" s="18"/>
       <c r="N111" s="76" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="O111" s="53">
         <v>46244</v>
@@ -14344,7 +14458,7 @@
         <v>319</v>
       </c>
       <c r="K121" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L121" s="53">
         <v>46246</v>
@@ -14398,7 +14512,7 @@
         <v>319</v>
       </c>
       <c r="K122" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L122" s="53">
         <v>46246</v>
@@ -14452,7 +14566,7 @@
         <v>319</v>
       </c>
       <c r="K123" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L123" s="53">
         <v>46246</v>
@@ -14554,7 +14668,7 @@
         <v>319</v>
       </c>
       <c r="K125" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L125" s="53">
         <v>46246</v>
@@ -14574,7 +14688,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="15" thickBot="1">
+    <row r="126" spans="1:18" ht="28.2" thickBot="1">
       <c r="A126" s="2">
         <v>125</v>
       </c>
@@ -14612,8 +14726,8 @@
         <v>46247</v>
       </c>
       <c r="M126" s="18"/>
-      <c r="N126" s="54">
-        <v>854</v>
+      <c r="N126" s="76" t="s">
+        <v>2454</v>
       </c>
       <c r="O126" s="18"/>
       <c r="P126" s="18"/>
@@ -14982,7 +15096,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="15" thickBot="1">
+    <row r="134" spans="1:18" ht="28.2" thickBot="1">
       <c r="A134" s="2">
         <v>133</v>
       </c>
@@ -15021,7 +15135,7 @@
       </c>
       <c r="M134" s="18"/>
       <c r="N134" s="75" t="s">
-        <v>2110</v>
+        <v>2455</v>
       </c>
       <c r="O134" s="53">
         <v>46244</v>
@@ -15342,7 +15456,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="15" thickBot="1">
+    <row r="141" spans="1:18" ht="28.2" thickBot="1">
       <c r="A141" s="2">
         <v>140</v>
       </c>
@@ -15380,8 +15494,8 @@
         <v>46247</v>
       </c>
       <c r="M141" s="18"/>
-      <c r="N141" s="54">
-        <v>790</v>
+      <c r="N141" s="54" t="s">
+        <v>2456</v>
       </c>
       <c r="O141" s="18"/>
       <c r="P141" s="18"/>
@@ -15392,7 +15506,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="15" thickBot="1">
+    <row r="142" spans="1:18" ht="28.2" thickBot="1">
       <c r="A142" s="2">
         <v>141</v>
       </c>
@@ -15430,8 +15544,8 @@
         <v>46247</v>
       </c>
       <c r="M142" s="18"/>
-      <c r="N142" s="54">
-        <v>956</v>
+      <c r="N142" s="54" t="s">
+        <v>2457</v>
       </c>
       <c r="O142" s="18"/>
       <c r="P142" s="18"/>
@@ -15976,7 +16090,7 @@
         <v>46247</v>
       </c>
       <c r="M153" s="21" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="N153" s="54">
         <v>932</v>
@@ -16480,7 +16594,7 @@
         <v>46247</v>
       </c>
       <c r="M163" s="21" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="N163" s="54">
         <v>934</v>
@@ -16776,7 +16890,7 @@
         <v>124</v>
       </c>
       <c r="K169" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L169" s="53">
         <v>46246</v>
@@ -17174,7 +17288,7 @@
         <v>124</v>
       </c>
       <c r="K177" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L177" s="53">
         <v>46246</v>
@@ -17318,7 +17432,7 @@
         <v>124</v>
       </c>
       <c r="K180" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L180" s="53">
         <v>46246</v>
@@ -17746,7 +17860,7 @@
       </c>
       <c r="L189" s="18"/>
       <c r="M189" s="21" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="N189" s="54">
         <v>933</v>
@@ -17984,7 +18098,7 @@
         <v>124</v>
       </c>
       <c r="K194" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L194" s="53">
         <v>46246</v>
@@ -18084,7 +18198,9 @@
       </c>
       <c r="L196" s="18"/>
       <c r="M196" s="18"/>
-      <c r="N196" s="40"/>
+      <c r="N196" s="54">
+        <v>1161</v>
+      </c>
       <c r="O196" s="18"/>
       <c r="P196" s="18"/>
       <c r="Q196" s="11">
@@ -18130,7 +18246,9 @@
       </c>
       <c r="L197" s="18"/>
       <c r="M197" s="18"/>
-      <c r="N197" s="40"/>
+      <c r="N197" s="54">
+        <v>1160</v>
+      </c>
       <c r="O197" s="18"/>
       <c r="P197" s="18"/>
       <c r="Q197" s="11">
@@ -18176,7 +18294,9 @@
       </c>
       <c r="L198" s="18"/>
       <c r="M198" s="18"/>
-      <c r="N198" s="40"/>
+      <c r="N198" s="54">
+        <v>1162</v>
+      </c>
       <c r="O198" s="18"/>
       <c r="P198" s="18"/>
       <c r="Q198" s="11">
@@ -18402,7 +18522,7 @@
         <v>124</v>
       </c>
       <c r="K203" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L203" s="53">
         <v>46246</v>
@@ -18452,7 +18572,7 @@
         <v>124</v>
       </c>
       <c r="K204" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L204" s="53">
         <v>46246</v>
@@ -18556,7 +18676,9 @@
         <v>46248</v>
       </c>
       <c r="M206" s="18"/>
-      <c r="N206" s="40"/>
+      <c r="N206" s="54">
+        <v>1199</v>
+      </c>
       <c r="O206" s="18"/>
       <c r="P206" s="18"/>
       <c r="Q206" s="11" t="s">
@@ -18602,7 +18724,9 @@
       </c>
       <c r="L207" s="18"/>
       <c r="M207" s="18"/>
-      <c r="N207" s="40"/>
+      <c r="N207" s="54">
+        <v>1201</v>
+      </c>
       <c r="O207" s="18"/>
       <c r="P207" s="18"/>
       <c r="Q207" s="11">
@@ -18648,7 +18772,9 @@
       </c>
       <c r="L208" s="18"/>
       <c r="M208" s="18"/>
-      <c r="N208" s="40"/>
+      <c r="N208" s="54">
+        <v>1202</v>
+      </c>
       <c r="O208" s="18"/>
       <c r="P208" s="18"/>
       <c r="Q208" s="11">
@@ -18696,7 +18822,9 @@
         <v>46248</v>
       </c>
       <c r="M209" s="18"/>
-      <c r="N209" s="40"/>
+      <c r="N209" s="54">
+        <v>1198</v>
+      </c>
       <c r="O209" s="18"/>
       <c r="P209" s="18"/>
       <c r="Q209" s="11" t="s">
@@ -18706,7 +18834,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="210" spans="1:18" ht="15" thickBot="1">
+    <row r="210" spans="1:18" ht="28.2" thickBot="1">
       <c r="A210" s="2">
         <v>209</v>
       </c>
@@ -18742,8 +18870,8 @@
       </c>
       <c r="L210" s="18"/>
       <c r="M210" s="18"/>
-      <c r="N210" s="54">
-        <v>931</v>
+      <c r="N210" s="54" t="s">
+        <v>2458</v>
       </c>
       <c r="O210" s="18"/>
       <c r="P210" s="18"/>
@@ -19091,11 +19219,11 @@
       <c r="J217" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="K217" s="11" t="s">
-        <v>2328</v>
+      <c r="K217" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L217" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M217" s="18"/>
       <c r="N217" s="54">
@@ -19932,7 +20060,9 @@
       </c>
       <c r="L235" s="18"/>
       <c r="M235" s="18"/>
-      <c r="N235" s="40"/>
+      <c r="N235" s="54">
+        <v>1090</v>
+      </c>
       <c r="O235" s="18"/>
       <c r="P235" s="18"/>
       <c r="Q235" s="11">
@@ -20214,7 +20344,7 @@
       </c>
       <c r="J241" s="18"/>
       <c r="K241" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L241" s="53">
         <v>46246</v>
@@ -20310,7 +20440,7 @@
       </c>
       <c r="J243" s="18"/>
       <c r="K243" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L243" s="53">
         <v>46246</v>
@@ -21272,7 +21402,7 @@
       </c>
       <c r="J263" s="18"/>
       <c r="K263" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L263" s="53">
         <v>46246</v>
@@ -21320,7 +21450,7 @@
       </c>
       <c r="J264" s="18"/>
       <c r="K264" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L264" s="53">
         <v>46246</v>
@@ -21368,7 +21498,7 @@
       </c>
       <c r="J265" s="18"/>
       <c r="K265" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L265" s="53">
         <v>46246</v>
@@ -21416,14 +21546,14 @@
       </c>
       <c r="J266" s="18"/>
       <c r="K266" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L266" s="53">
         <v>46246</v>
       </c>
       <c r="M266" s="18"/>
-      <c r="N266" s="54">
-        <v>617</v>
+      <c r="N266" s="54" t="s">
+        <v>2459</v>
       </c>
       <c r="O266" s="18"/>
       <c r="P266" s="18"/>
@@ -21464,7 +21594,7 @@
       </c>
       <c r="J267" s="18"/>
       <c r="K267" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L267" s="53">
         <v>46246</v>
@@ -21711,7 +21841,7 @@
       </c>
       <c r="M272" s="18"/>
       <c r="N272" s="76" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="O272" s="18"/>
       <c r="P272" s="18"/>
@@ -21751,10 +21881,12 @@
       <c r="J273" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="K273" s="67" t="s">
-        <v>1285</v>
-      </c>
-      <c r="L273" s="18"/>
+      <c r="K273" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L273" s="53">
+        <v>46250</v>
+      </c>
       <c r="M273" s="18"/>
       <c r="N273" s="40"/>
       <c r="O273" s="18"/>
@@ -21805,7 +21937,7 @@
       </c>
       <c r="M274" s="18"/>
       <c r="N274" s="76" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="O274" s="18"/>
       <c r="P274" s="18"/>
@@ -22137,7 +22269,7 @@
       </c>
       <c r="M281" s="18"/>
       <c r="N281" s="76" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="O281" s="18"/>
       <c r="P281" s="18"/>
@@ -22233,7 +22365,7 @@
       </c>
       <c r="M283" s="18"/>
       <c r="N283" s="76" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="O283" s="18"/>
       <c r="P283" s="18"/>
@@ -22527,7 +22659,7 @@
       </c>
       <c r="M289" s="18"/>
       <c r="N289" s="76" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="O289" s="18"/>
       <c r="P289" s="18"/>
@@ -22820,7 +22952,7 @@
         <v>382</v>
       </c>
       <c r="K295" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L295" s="53">
         <v>46246</v>
@@ -23178,7 +23310,7 @@
         <v>174</v>
       </c>
       <c r="K302" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L302" s="53">
         <v>46246</v>
@@ -23333,7 +23465,7 @@
       <c r="L305" s="18"/>
       <c r="M305" s="18"/>
       <c r="N305" s="76" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="O305" s="53">
         <v>46244</v>
@@ -23793,9 +23925,11 @@
       </c>
       <c r="M314" s="18"/>
       <c r="N314" s="76" t="s">
-        <v>2254</v>
-      </c>
-      <c r="O314" s="18"/>
+        <v>2253</v>
+      </c>
+      <c r="O314" s="53">
+        <v>46246</v>
+      </c>
       <c r="P314" s="18"/>
       <c r="Q314" s="11">
         <v>91254243</v>
@@ -23993,7 +24127,7 @@
       </c>
       <c r="M318" s="18"/>
       <c r="N318" s="76" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="O318" s="18"/>
       <c r="P318" s="18"/>
@@ -24043,7 +24177,7 @@
       </c>
       <c r="M319" s="18"/>
       <c r="N319" s="76" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="O319" s="53">
         <v>46245</v>
@@ -24147,7 +24281,7 @@
       </c>
       <c r="M321" s="18"/>
       <c r="N321" s="76" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
       <c r="O321" s="18"/>
       <c r="P321" s="18"/>
@@ -24195,7 +24329,7 @@
       </c>
       <c r="M322" s="18"/>
       <c r="N322" s="76" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="O322" s="18"/>
       <c r="P322" s="18"/>
@@ -24339,7 +24473,7 @@
       </c>
       <c r="M325" s="18"/>
       <c r="N325" s="76" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="O325" s="18"/>
       <c r="P325" s="18"/>
@@ -24894,7 +25028,9 @@
         <v>46247</v>
       </c>
       <c r="M337" s="18"/>
-      <c r="N337" s="40"/>
+      <c r="N337" s="54">
+        <v>1113</v>
+      </c>
       <c r="O337" s="18"/>
       <c r="P337" s="18"/>
       <c r="Q337" s="18"/>
@@ -24940,8 +25076,8 @@
         <v>46247</v>
       </c>
       <c r="M338" s="18"/>
-      <c r="N338" s="54">
-        <v>896</v>
+      <c r="N338" s="54" t="s">
+        <v>2460</v>
       </c>
       <c r="O338" s="18"/>
       <c r="P338" s="18"/>
@@ -24988,7 +25124,9 @@
         <v>46247</v>
       </c>
       <c r="M339" s="18"/>
-      <c r="N339" s="40"/>
+      <c r="N339" s="54">
+        <v>1114</v>
+      </c>
       <c r="O339" s="18"/>
       <c r="P339" s="18"/>
       <c r="Q339" s="18"/>
@@ -25128,7 +25266,9 @@
         <v>46247</v>
       </c>
       <c r="M342" s="18"/>
-      <c r="N342" s="40"/>
+      <c r="N342" s="54">
+        <v>1115</v>
+      </c>
       <c r="O342" s="18"/>
       <c r="P342" s="18"/>
       <c r="Q342" s="18"/>
@@ -25174,8 +25314,8 @@
         <v>46247</v>
       </c>
       <c r="M343" s="18"/>
-      <c r="N343" s="54">
-        <v>485</v>
+      <c r="N343" s="54" t="s">
+        <v>2461</v>
       </c>
       <c r="O343" s="18"/>
       <c r="P343" s="18"/>
@@ -25218,7 +25358,7 @@
         <v>549</v>
       </c>
       <c r="K344" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L344" s="53">
         <v>46246</v>
@@ -25268,7 +25408,7 @@
         <v>549</v>
       </c>
       <c r="K345" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L345" s="53">
         <v>46246</v>
@@ -25318,7 +25458,7 @@
         <v>549</v>
       </c>
       <c r="K346" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L346" s="53">
         <v>46246</v>
@@ -25368,7 +25508,7 @@
         <v>549</v>
       </c>
       <c r="K347" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L347" s="53">
         <v>46246</v>
@@ -25418,7 +25558,7 @@
         <v>549</v>
       </c>
       <c r="K348" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L348" s="53">
         <v>46246</v>
@@ -25508,7 +25648,7 @@
         <v>549</v>
       </c>
       <c r="K350" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L350" s="53">
         <v>46246</v>
@@ -25556,7 +25696,7 @@
         <v>202</v>
       </c>
       <c r="K351" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L351" s="53">
         <v>46246</v>
@@ -25702,7 +25842,7 @@
         <v>126</v>
       </c>
       <c r="K354" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L354" s="53">
         <v>46246</v>
@@ -25906,7 +26046,7 @@
         <v>126</v>
       </c>
       <c r="K358" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L358" s="53">
         <v>46246</v>
@@ -26061,7 +26201,7 @@
       <c r="L361" s="18"/>
       <c r="M361" s="18"/>
       <c r="N361" s="79" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="O361" s="53">
         <v>46244</v>
@@ -26313,7 +26453,7 @@
       </c>
       <c r="M366" s="18"/>
       <c r="N366" s="79" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="O366" s="53">
         <v>46244</v>
@@ -27610,7 +27750,9 @@
       </c>
       <c r="L392" s="18"/>
       <c r="M392" s="18"/>
-      <c r="N392" s="40"/>
+      <c r="N392" s="54">
+        <v>1172</v>
+      </c>
       <c r="O392" s="18"/>
       <c r="P392" s="18"/>
       <c r="Q392" s="11">
@@ -27656,7 +27798,9 @@
       </c>
       <c r="L393" s="18"/>
       <c r="M393" s="18"/>
-      <c r="N393" s="40"/>
+      <c r="N393" s="54">
+        <v>1142</v>
+      </c>
       <c r="O393" s="18"/>
       <c r="P393" s="18"/>
       <c r="Q393" s="18"/>
@@ -27700,7 +27844,9 @@
       </c>
       <c r="L394" s="18"/>
       <c r="M394" s="18"/>
-      <c r="N394" s="40"/>
+      <c r="N394" s="54">
+        <v>1145</v>
+      </c>
       <c r="O394" s="18"/>
       <c r="P394" s="18"/>
       <c r="Q394" s="11">
@@ -27934,7 +28080,7 @@
         <v>562</v>
       </c>
       <c r="K399" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L399" s="53">
         <v>46246</v>
@@ -28124,7 +28270,7 @@
         <v>562</v>
       </c>
       <c r="K403" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L403" s="53">
         <v>46246</v>
@@ -28316,7 +28462,7 @@
         <v>562</v>
       </c>
       <c r="K407" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L407" s="53">
         <v>46246</v>
@@ -28568,7 +28714,7 @@
         <v>562</v>
       </c>
       <c r="K412" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L412" s="53">
         <v>46246</v>
@@ -28672,7 +28818,9 @@
       </c>
       <c r="L414" s="18"/>
       <c r="M414" s="18"/>
-      <c r="N414" s="40"/>
+      <c r="N414" s="54">
+        <v>1146</v>
+      </c>
       <c r="O414" s="18"/>
       <c r="P414" s="18"/>
       <c r="Q414" s="11" t="s">
@@ -28808,7 +28956,9 @@
       </c>
       <c r="L417" s="18"/>
       <c r="M417" s="18"/>
-      <c r="N417" s="40"/>
+      <c r="N417" s="54">
+        <v>1147</v>
+      </c>
       <c r="O417" s="18"/>
       <c r="P417" s="18"/>
       <c r="Q417" s="11">
@@ -28944,7 +29094,7 @@
         <v>562</v>
       </c>
       <c r="K420" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L420" s="53">
         <v>46246</v>
@@ -29136,7 +29286,7 @@
         <v>562</v>
       </c>
       <c r="K424" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L424" s="53">
         <v>46246</v>
@@ -29234,7 +29384,7 @@
         <v>562</v>
       </c>
       <c r="K426" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L426" s="53">
         <v>46246</v>
@@ -29536,7 +29686,7 @@
         <v>839</v>
       </c>
       <c r="K432" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L432" s="53">
         <v>46246</v>
@@ -29834,7 +29984,7 @@
         <v>848</v>
       </c>
       <c r="K438" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L438" s="53">
         <v>46246</v>
@@ -30054,7 +30204,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="443" spans="1:18" ht="15" thickBot="1">
+    <row r="443" spans="1:18" ht="28.2" thickBot="1">
       <c r="A443" s="2">
         <v>93</v>
       </c>
@@ -30092,8 +30242,8 @@
         <v>46250</v>
       </c>
       <c r="M443" s="18"/>
-      <c r="N443" s="54">
-        <v>175</v>
+      <c r="N443" s="54" t="s">
+        <v>2462</v>
       </c>
       <c r="O443" s="18"/>
       <c r="P443" s="18"/>
@@ -30447,7 +30597,9 @@
       <c r="N450" s="54">
         <v>678</v>
       </c>
-      <c r="O450" s="18"/>
+      <c r="O450" s="53">
+        <v>46246</v>
+      </c>
       <c r="P450" s="18"/>
       <c r="Q450" s="11">
         <v>94054195</v>
@@ -30586,7 +30738,7 @@
         <v>848</v>
       </c>
       <c r="K453" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L453" s="53">
         <v>46246</v>
@@ -30636,7 +30788,7 @@
         <v>881</v>
       </c>
       <c r="K454" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L454" s="53">
         <v>46246</v>
@@ -30686,7 +30838,7 @@
         <v>881</v>
       </c>
       <c r="K455" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L455" s="53">
         <v>46246</v>
@@ -30736,7 +30888,7 @@
         <v>881</v>
       </c>
       <c r="K456" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L456" s="53">
         <v>46246</v>
@@ -30797,7 +30949,7 @@
       </c>
       <c r="O457" s="18"/>
       <c r="P457" s="49" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="Q457" s="11">
         <v>95746105</v>
@@ -30988,7 +31140,7 @@
         <v>890</v>
       </c>
       <c r="K461" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L461" s="53">
         <v>46246</v>
@@ -31038,7 +31190,7 @@
         <v>890</v>
       </c>
       <c r="K462" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L462" s="53">
         <v>46246</v>
@@ -31178,7 +31330,7 @@
         <v>890</v>
       </c>
       <c r="K465" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L465" s="53">
         <v>46246</v>
@@ -31599,7 +31751,7 @@
       </c>
       <c r="M474" s="18"/>
       <c r="N474" s="54" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="O474" s="53">
         <v>46244</v>
@@ -32388,7 +32540,7 @@
         <v>937</v>
       </c>
       <c r="K491" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L491" s="53">
         <v>46246</v>
@@ -32438,7 +32590,7 @@
         <v>937</v>
       </c>
       <c r="K492" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L492" s="53">
         <v>46246</v>
@@ -32534,7 +32686,7 @@
         <v>937</v>
       </c>
       <c r="K494" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L494" s="53">
         <v>46246</v>
@@ -32630,7 +32782,7 @@
         <v>937</v>
       </c>
       <c r="K496" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L496" s="53">
         <v>46246</v>
@@ -32728,7 +32880,7 @@
         <v>937</v>
       </c>
       <c r="K498" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L498" s="53">
         <v>46246</v>
@@ -32778,7 +32930,7 @@
         <v>937</v>
       </c>
       <c r="K499" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L499" s="53">
         <v>46246</v>
@@ -32874,7 +33026,7 @@
         <v>937</v>
       </c>
       <c r="K501" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L501" s="53">
         <v>46246</v>
@@ -32924,7 +33076,7 @@
         <v>937</v>
       </c>
       <c r="K502" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L502" s="53">
         <v>46246</v>
@@ -32974,7 +33126,7 @@
         <v>937</v>
       </c>
       <c r="K503" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L503" s="53">
         <v>46246</v>
@@ -33320,7 +33472,7 @@
         <v>953</v>
       </c>
       <c r="K510" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L510" s="53">
         <v>46246</v>
@@ -33418,7 +33570,7 @@
         <v>953</v>
       </c>
       <c r="K512" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L512" s="53">
         <v>46246</v>
@@ -33608,7 +33760,7 @@
         <v>961</v>
       </c>
       <c r="K516" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L516" s="53">
         <v>46246</v>
@@ -33660,7 +33812,7 @@
         <v>968</v>
       </c>
       <c r="K517" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L517" s="53">
         <v>46246</v>
@@ -33756,7 +33908,7 @@
         <v>971</v>
       </c>
       <c r="K519" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L519" s="53">
         <v>46246</v>
@@ -34392,7 +34544,9 @@
       </c>
       <c r="L532" s="18"/>
       <c r="M532" s="18"/>
-      <c r="N532" s="40"/>
+      <c r="N532" s="54">
+        <v>1157</v>
+      </c>
       <c r="O532" s="18"/>
       <c r="P532" s="18"/>
       <c r="Q532" s="11">
@@ -34440,7 +34594,9 @@
         <v>46250</v>
       </c>
       <c r="M533" s="18"/>
-      <c r="N533" s="40"/>
+      <c r="N533" s="54">
+        <v>1156</v>
+      </c>
       <c r="O533" s="18"/>
       <c r="P533" s="18"/>
       <c r="Q533" s="11">
@@ -34742,7 +34898,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="540" spans="1:18" ht="15" thickBot="1">
+    <row r="540" spans="1:18" ht="28.2" thickBot="1">
       <c r="A540" s="2">
         <v>190</v>
       </c>
@@ -34780,8 +34936,8 @@
         <v>46250</v>
       </c>
       <c r="M540" s="18"/>
-      <c r="N540" s="54">
-        <v>900</v>
+      <c r="N540" s="54" t="s">
+        <v>2463</v>
       </c>
       <c r="O540" s="18"/>
       <c r="P540" s="18"/>
@@ -34838,7 +34994,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="542" spans="1:18" ht="15" thickBot="1">
+    <row r="542" spans="1:18" ht="28.2" thickBot="1">
       <c r="A542" s="2">
         <v>192</v>
       </c>
@@ -34876,8 +35032,8 @@
         <v>46250</v>
       </c>
       <c r="M542" s="18"/>
-      <c r="N542" s="54">
-        <v>328</v>
+      <c r="N542" s="54" t="s">
+        <v>2464</v>
       </c>
       <c r="O542" s="18"/>
       <c r="P542" s="18"/>
@@ -35322,7 +35478,9 @@
         <v>46250</v>
       </c>
       <c r="M551" s="18"/>
-      <c r="N551" s="40"/>
+      <c r="N551" s="54">
+        <v>1166</v>
+      </c>
       <c r="O551" s="18"/>
       <c r="P551" s="18"/>
       <c r="Q551" s="18"/>
@@ -35526,7 +35684,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="556" spans="1:18" ht="15" thickBot="1">
+    <row r="556" spans="1:18" ht="28.2" thickBot="1">
       <c r="A556" s="2">
         <v>206</v>
       </c>
@@ -35562,8 +35720,8 @@
       </c>
       <c r="L556" s="18"/>
       <c r="M556" s="18"/>
-      <c r="N556" s="54">
-        <v>505</v>
+      <c r="N556" s="54" t="s">
+        <v>2465</v>
       </c>
       <c r="O556" s="18"/>
       <c r="P556" s="18"/>
@@ -35574,7 +35732,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="557" spans="1:18" ht="15" thickBot="1">
+    <row r="557" spans="1:18" ht="28.2" thickBot="1">
       <c r="A557" s="2">
         <v>207</v>
       </c>
@@ -35610,8 +35768,8 @@
       </c>
       <c r="L557" s="18"/>
       <c r="M557" s="18"/>
-      <c r="N557" s="54">
-        <v>506</v>
+      <c r="N557" s="54" t="s">
+        <v>2466</v>
       </c>
       <c r="O557" s="18"/>
       <c r="P557" s="18"/>
@@ -35890,7 +36048,7 @@
         <v>950</v>
       </c>
       <c r="K563" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L563" s="53">
         <v>46246</v>
@@ -35994,7 +36152,9 @@
       </c>
       <c r="L565" s="18"/>
       <c r="M565" s="18"/>
-      <c r="N565" s="40"/>
+      <c r="N565" s="54">
+        <v>1122</v>
+      </c>
       <c r="O565" s="18"/>
       <c r="P565" s="18"/>
       <c r="Q565" s="15">
@@ -36174,7 +36334,7 @@
         <v>564</v>
       </c>
       <c r="K569" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L569" s="53">
         <v>46246</v>
@@ -36224,7 +36384,7 @@
         <v>564</v>
       </c>
       <c r="K570" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L570" s="53">
         <v>46246</v>
@@ -36274,7 +36434,7 @@
         <v>564</v>
       </c>
       <c r="K571" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L571" s="53">
         <v>46246</v>
@@ -36374,7 +36534,7 @@
         <v>564</v>
       </c>
       <c r="K573" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L573" s="53">
         <v>46246</v>
@@ -36426,7 +36586,7 @@
         <v>564</v>
       </c>
       <c r="K574" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L574" s="10">
         <v>46246</v>
@@ -36476,7 +36636,7 @@
         <v>564</v>
       </c>
       <c r="K575" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L575" s="10">
         <v>46246</v>
@@ -36592,7 +36752,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="578" spans="1:18" ht="15" thickBot="1">
+    <row r="578" spans="1:18" ht="28.2" thickBot="1">
       <c r="A578" s="2">
         <v>228</v>
       </c>
@@ -36630,8 +36790,8 @@
         <v>46250</v>
       </c>
       <c r="M578" s="18"/>
-      <c r="N578" s="54">
-        <v>646</v>
+      <c r="N578" s="54" t="s">
+        <v>2467</v>
       </c>
       <c r="O578" s="18"/>
       <c r="P578" s="18"/>
@@ -36642,7 +36802,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="579" spans="1:18" ht="15" thickBot="1">
+    <row r="579" spans="1:18" ht="28.2" thickBot="1">
       <c r="A579" s="2">
         <v>229</v>
       </c>
@@ -36674,14 +36834,14 @@
         <v>564</v>
       </c>
       <c r="K579" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L579" s="53">
         <v>46246</v>
       </c>
       <c r="M579" s="18"/>
-      <c r="N579" s="54">
-        <v>644</v>
+      <c r="N579" s="54" t="s">
+        <v>2468</v>
       </c>
       <c r="O579" s="18"/>
       <c r="P579" s="18"/>
@@ -36692,7 +36852,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="580" spans="1:18" ht="15" thickBot="1">
+    <row r="580" spans="1:18" ht="28.2" thickBot="1">
       <c r="A580" s="2">
         <v>230</v>
       </c>
@@ -36724,14 +36884,14 @@
         <v>564</v>
       </c>
       <c r="K580" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L580" s="53">
         <v>46246</v>
       </c>
       <c r="M580" s="18"/>
-      <c r="N580" s="54">
-        <v>645</v>
+      <c r="N580" s="54" t="s">
+        <v>2469</v>
       </c>
       <c r="O580" s="18"/>
       <c r="P580" s="18"/>
@@ -36742,7 +36902,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="581" spans="1:18" ht="15" thickBot="1">
+    <row r="581" spans="1:18" ht="28.2" thickBot="1">
       <c r="A581" s="2">
         <v>231</v>
       </c>
@@ -36780,7 +36940,9 @@
         <v>46250</v>
       </c>
       <c r="M581" s="18"/>
-      <c r="N581" s="40"/>
+      <c r="N581" s="54" t="s">
+        <v>2470</v>
+      </c>
       <c r="O581" s="18"/>
       <c r="P581" s="18"/>
       <c r="Q581" s="15">
@@ -36920,7 +37082,7 @@
         <v>564</v>
       </c>
       <c r="K584" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L584" s="53">
         <v>46246</v>
@@ -37520,7 +37682,7 @@
         <v>564</v>
       </c>
       <c r="K596" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L596" s="53">
         <v>46246</v>
@@ -37572,7 +37734,7 @@
         <v>564</v>
       </c>
       <c r="K597" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L597" s="53">
         <v>46246</v>
@@ -37624,7 +37786,7 @@
         <v>564</v>
       </c>
       <c r="K598" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L598" s="53">
         <v>46246</v>
@@ -37676,7 +37838,7 @@
         <v>564</v>
       </c>
       <c r="K599" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L599" s="53">
         <v>46246</v>
@@ -37726,7 +37888,7 @@
         <v>564</v>
       </c>
       <c r="K600" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L600" s="53">
         <v>46246</v>
@@ -37778,7 +37940,7 @@
         <v>564</v>
       </c>
       <c r="K601" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L601" s="53">
         <v>46246</v>
@@ -37830,7 +37992,7 @@
         <v>564</v>
       </c>
       <c r="K602" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L602" s="53">
         <v>46246</v>
@@ -37882,7 +38044,7 @@
         <v>564</v>
       </c>
       <c r="K603" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L603" s="53">
         <v>46246</v>
@@ -37932,7 +38094,7 @@
         <v>564</v>
       </c>
       <c r="K604" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L604" s="53">
         <v>46246</v>
@@ -37980,7 +38142,7 @@
         <v>564</v>
       </c>
       <c r="K605" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L605" s="53">
         <v>46246</v>
@@ -38030,7 +38192,7 @@
         <v>564</v>
       </c>
       <c r="K606" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L606" s="53">
         <v>46246</v>
@@ -38080,7 +38242,7 @@
         <v>564</v>
       </c>
       <c r="K607" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L607" s="53">
         <v>46246</v>
@@ -38130,7 +38292,7 @@
         <v>564</v>
       </c>
       <c r="K608" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L608" s="53">
         <v>46246</v>
@@ -38180,7 +38342,7 @@
         <v>564</v>
       </c>
       <c r="K609" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L609" s="53">
         <v>46246</v>
@@ -38232,7 +38394,7 @@
         <v>564</v>
       </c>
       <c r="K610" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L610" s="53">
         <v>46246</v>
@@ -38284,7 +38446,7 @@
         <v>564</v>
       </c>
       <c r="K611" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L611" s="53">
         <v>46246</v>
@@ -38334,7 +38496,7 @@
         <v>564</v>
       </c>
       <c r="K612" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L612" s="53">
         <v>46246</v>
@@ -38384,7 +38546,7 @@
         <v>564</v>
       </c>
       <c r="K613" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L613" s="53">
         <v>46246</v>
@@ -38436,7 +38598,7 @@
         <v>564</v>
       </c>
       <c r="K614" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L614" s="53">
         <v>46246</v>
@@ -38486,7 +38648,7 @@
         <v>564</v>
       </c>
       <c r="K615" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L615" s="53">
         <v>46246</v>
@@ -38932,7 +39094,9 @@
       </c>
       <c r="L624" s="18"/>
       <c r="M624" s="18"/>
-      <c r="N624" s="40"/>
+      <c r="N624" s="54">
+        <v>1210</v>
+      </c>
       <c r="O624" s="18"/>
       <c r="P624" s="18"/>
       <c r="Q624" s="15">
@@ -39160,7 +39324,7 @@
         <v>776</v>
       </c>
       <c r="K629" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L629" s="53">
         <v>46246</v>
@@ -39400,7 +39564,7 @@
         <v>776</v>
       </c>
       <c r="K634" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L634" s="53">
         <v>46246</v>
@@ -39502,7 +39666,7 @@
         <v>776</v>
       </c>
       <c r="K636" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L636" s="53">
         <v>46246</v>
@@ -39554,7 +39718,7 @@
         <v>776</v>
       </c>
       <c r="K637" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L637" s="53">
         <v>46246</v>
@@ -39606,7 +39770,7 @@
         <v>776</v>
       </c>
       <c r="K638" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L638" s="53">
         <v>46246</v>
@@ -39626,7 +39790,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="639" spans="1:18" ht="15" thickBot="1">
+    <row r="639" spans="1:18" ht="28.2" thickBot="1">
       <c r="A639" s="2">
         <v>289</v>
       </c>
@@ -39658,14 +39822,14 @@
         <v>776</v>
       </c>
       <c r="K639" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L639" s="53">
         <v>46246</v>
       </c>
       <c r="M639" s="18"/>
-      <c r="N639" s="54">
-        <v>697</v>
+      <c r="N639" s="54" t="s">
+        <v>2471</v>
       </c>
       <c r="O639" s="18"/>
       <c r="P639" s="18"/>
@@ -39676,7 +39840,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="640" spans="1:18" ht="15" thickBot="1">
+    <row r="640" spans="1:18" ht="28.2" thickBot="1">
       <c r="A640" s="2">
         <v>290</v>
       </c>
@@ -39708,14 +39872,14 @@
         <v>776</v>
       </c>
       <c r="K640" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L640" s="53">
         <v>46246</v>
       </c>
       <c r="M640" s="18"/>
-      <c r="N640" s="54">
-        <v>696</v>
+      <c r="N640" s="54" t="s">
+        <v>2472</v>
       </c>
       <c r="O640" s="18"/>
       <c r="P640" s="18"/>
@@ -39822,7 +39986,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="643" spans="1:18" ht="15" thickBot="1">
+    <row r="643" spans="1:18" ht="28.2" thickBot="1">
       <c r="A643" s="2">
         <v>293</v>
       </c>
@@ -39854,14 +40018,14 @@
         <v>776</v>
       </c>
       <c r="K643" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L643" s="53">
         <v>46246</v>
       </c>
       <c r="M643" s="18"/>
-      <c r="N643" s="54">
-        <v>695</v>
+      <c r="N643" s="54" t="s">
+        <v>2473</v>
       </c>
       <c r="O643" s="18"/>
       <c r="P643" s="18"/>
@@ -40044,7 +40208,7 @@
         <v>776</v>
       </c>
       <c r="K647" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L647" s="53">
         <v>46246</v>
@@ -40238,14 +40402,14 @@
         <v>776</v>
       </c>
       <c r="K651" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L651" s="53">
         <v>46246</v>
       </c>
       <c r="M651" s="18"/>
       <c r="N651" s="76" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="O651" s="53">
         <v>46245</v>
@@ -40260,7 +40424,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="652" spans="1:18" ht="15" thickBot="1">
+    <row r="652" spans="1:18" ht="28.2" thickBot="1">
       <c r="A652" s="2">
         <v>302</v>
       </c>
@@ -40292,14 +40456,14 @@
         <v>776</v>
       </c>
       <c r="K652" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L652" s="53">
         <v>46246</v>
       </c>
       <c r="M652" s="18"/>
-      <c r="N652" s="54">
-        <v>430</v>
+      <c r="N652" s="54" t="s">
+        <v>2474</v>
       </c>
       <c r="O652" s="18"/>
       <c r="P652" s="18"/>
@@ -40342,7 +40506,7 @@
         <v>776</v>
       </c>
       <c r="K653" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L653" s="53">
         <v>46246</v>
@@ -40360,7 +40524,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="654" spans="1:18" ht="15" thickBot="1">
+    <row r="654" spans="1:18" ht="28.2" thickBot="1">
       <c r="A654" s="2">
         <v>304</v>
       </c>
@@ -40392,14 +40556,14 @@
         <v>776</v>
       </c>
       <c r="K654" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L654" s="53">
         <v>46246</v>
       </c>
       <c r="M654" s="18"/>
-      <c r="N654" s="54">
-        <v>444</v>
+      <c r="N654" s="54" t="s">
+        <v>2475</v>
       </c>
       <c r="O654" s="18"/>
       <c r="P654" s="18"/>
@@ -40442,14 +40606,14 @@
         <v>776</v>
       </c>
       <c r="K655" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L655" s="53">
         <v>46246</v>
       </c>
       <c r="M655" s="18"/>
       <c r="N655" s="76" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="O655" s="18"/>
       <c r="P655" s="18"/>
@@ -40460,7 +40624,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="656" spans="1:18" ht="15" thickBot="1">
+    <row r="656" spans="1:18" ht="28.2" thickBot="1">
       <c r="A656" s="2">
         <v>306</v>
       </c>
@@ -40498,8 +40662,8 @@
         <v>46250</v>
       </c>
       <c r="M656" s="18"/>
-      <c r="N656" s="54">
-        <v>807</v>
+      <c r="N656" s="54" t="s">
+        <v>2476</v>
       </c>
       <c r="O656" s="18"/>
       <c r="P656" s="18"/>
@@ -40542,7 +40706,7 @@
         <v>776</v>
       </c>
       <c r="K657" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L657" s="53">
         <v>46246</v>
@@ -40592,7 +40756,7 @@
         <v>776</v>
       </c>
       <c r="K658" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L658" s="53">
         <v>46246</v>
@@ -40874,7 +41038,7 @@
         <v>776</v>
       </c>
       <c r="K664" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L664" s="53">
         <v>46246</v>
@@ -40928,7 +41092,9 @@
       </c>
       <c r="L665" s="18"/>
       <c r="M665" s="18"/>
-      <c r="N665" s="40"/>
+      <c r="N665" s="54">
+        <v>1159</v>
+      </c>
       <c r="O665" s="18"/>
       <c r="P665" s="18"/>
       <c r="Q665" s="15">
@@ -40974,7 +41140,9 @@
       </c>
       <c r="L666" s="18"/>
       <c r="M666" s="18"/>
-      <c r="N666" s="40"/>
+      <c r="N666" s="54">
+        <v>1158</v>
+      </c>
       <c r="O666" s="18"/>
       <c r="P666" s="18"/>
       <c r="Q666" s="15">
@@ -41038,7 +41206,7 @@
         <v>46242</v>
       </c>
       <c r="C668" s="11" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="D668" s="11">
         <v>116923547</v>
@@ -41342,7 +41510,7 @@
         <v>130</v>
       </c>
       <c r="K674" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L674" s="53">
         <v>46246</v>
@@ -41392,7 +41560,7 @@
         <v>130</v>
       </c>
       <c r="K675" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L675" s="53">
         <v>46246</v>
@@ -41448,7 +41616,9 @@
         <v>46247</v>
       </c>
       <c r="M676" s="18"/>
-      <c r="N676" s="40"/>
+      <c r="N676" s="54">
+        <v>1177</v>
+      </c>
       <c r="O676" s="18"/>
       <c r="P676" s="36" t="s">
         <v>827</v>
@@ -41498,7 +41668,9 @@
         <v>46247</v>
       </c>
       <c r="M677" s="18"/>
-      <c r="N677" s="40"/>
+      <c r="N677" s="54">
+        <v>1174</v>
+      </c>
       <c r="O677" s="18"/>
       <c r="P677" s="36" t="s">
         <v>827</v>
@@ -41886,8 +42058,8 @@
       </c>
       <c r="L685" s="18"/>
       <c r="M685" s="18"/>
-      <c r="N685" s="54">
-        <v>839</v>
+      <c r="N685" s="54" t="s">
+        <v>2477</v>
       </c>
       <c r="O685" s="18"/>
       <c r="P685" s="18"/>
@@ -41928,14 +42100,14 @@
       </c>
       <c r="J686" s="18"/>
       <c r="K686" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L686" s="53">
         <v>46246</v>
       </c>
       <c r="M686" s="18"/>
-      <c r="N686" s="54">
-        <v>714</v>
+      <c r="N686" s="54" t="s">
+        <v>2478</v>
       </c>
       <c r="O686" s="18"/>
       <c r="P686" s="18"/>
@@ -41976,7 +42148,7 @@
       </c>
       <c r="J687" s="18"/>
       <c r="K687" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L687" s="53">
         <v>46246</v>
@@ -42112,7 +42284,7 @@
       </c>
       <c r="J690" s="18"/>
       <c r="K690" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L690" s="53">
         <v>46246</v>
@@ -42206,7 +42378,7 @@
         <v>130</v>
       </c>
       <c r="K692" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L692" s="53">
         <v>46246</v>
@@ -42254,7 +42426,7 @@
       </c>
       <c r="J693" s="18"/>
       <c r="K693" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L693" s="53">
         <v>46246</v>
@@ -42732,7 +42904,7 @@
         <v>1028</v>
       </c>
       <c r="K703" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L703" s="53">
         <v>46246</v>
@@ -42782,7 +42954,7 @@
         <v>1028</v>
       </c>
       <c r="K704" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L704" s="53">
         <v>46246</v>
@@ -42878,7 +43050,7 @@
         <v>1028</v>
       </c>
       <c r="K706" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L706" s="53">
         <v>46246</v>
@@ -42974,7 +43146,7 @@
         <v>1028</v>
       </c>
       <c r="K708" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L708" s="53">
         <v>46246</v>
@@ -43166,7 +43338,7 @@
         <v>1028</v>
       </c>
       <c r="K712" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L712" s="53">
         <v>46246</v>
@@ -43216,7 +43388,7 @@
         <v>1028</v>
       </c>
       <c r="K713" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L713" s="53">
         <v>46246</v>
@@ -43454,7 +43626,7 @@
         <v>1058</v>
       </c>
       <c r="K718" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L718" s="53">
         <v>46246</v>
@@ -43502,7 +43674,7 @@
         <v>1058</v>
       </c>
       <c r="K719" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L719" s="53">
         <v>46246</v>
@@ -44905,7 +45077,7 @@
       </c>
       <c r="M747" s="18"/>
       <c r="N747" s="79" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="O747" s="53">
         <v>46244</v>
@@ -44957,7 +45129,7 @@
       </c>
       <c r="M748" s="18"/>
       <c r="N748" s="79" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="O748" s="53">
         <v>46244</v>
@@ -45001,10 +45173,12 @@
       <c r="J749" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K749" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L749" s="18"/>
+      <c r="K749" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L749" s="53">
+        <v>46250</v>
+      </c>
       <c r="M749" s="18"/>
       <c r="N749" s="54">
         <v>3</v>
@@ -45049,13 +45223,15 @@
       <c r="J750" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K750" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L750" s="18"/>
+      <c r="K750" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L750" s="53">
+        <v>46250</v>
+      </c>
       <c r="M750" s="18"/>
       <c r="N750" s="79" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="O750" s="53">
         <v>46244</v>
@@ -45099,13 +45275,15 @@
       <c r="J751" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K751" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L751" s="18"/>
+      <c r="K751" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L751" s="53">
+        <v>46250</v>
+      </c>
       <c r="M751" s="18"/>
       <c r="N751" s="79" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="O751" s="53">
         <v>46244</v>
@@ -45149,13 +45327,15 @@
       <c r="J752" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K752" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L752" s="18"/>
+      <c r="K752" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L752" s="53">
+        <v>46250</v>
+      </c>
       <c r="M752" s="18"/>
       <c r="N752" s="79" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="O752" s="53">
         <v>46244</v>
@@ -45199,10 +45379,12 @@
       <c r="J753" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K753" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L753" s="18"/>
+      <c r="K753" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L753" s="53">
+        <v>46250</v>
+      </c>
       <c r="M753" s="18"/>
       <c r="N753" s="54">
         <v>7</v>
@@ -45249,10 +45431,12 @@
       <c r="J754" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K754" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L754" s="18"/>
+      <c r="K754" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L754" s="53">
+        <v>46250</v>
+      </c>
       <c r="M754" s="18"/>
       <c r="N754" s="54" t="s">
         <v>1108</v>
@@ -45332,10 +45516,10 @@
         <v>46242</v>
       </c>
       <c r="C756" s="55" t="s">
+        <v>2349</v>
+      </c>
+      <c r="D756" s="55" t="s">
         <v>2350</v>
-      </c>
-      <c r="D756" s="55" t="s">
-        <v>2351</v>
       </c>
       <c r="E756" s="12" t="s">
         <v>21</v>
@@ -45356,7 +45540,7 @@
         <v>564</v>
       </c>
       <c r="K756" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L756" s="53">
         <v>46246</v>
@@ -46464,7 +46648,7 @@
         <v>1207</v>
       </c>
       <c r="K779" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L779" s="53">
         <v>46246</v>
@@ -46855,7 +47039,7 @@
       </c>
       <c r="M787" s="18"/>
       <c r="N787" s="76" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="O787" s="53">
         <v>46245</v>
@@ -46950,7 +47134,7 @@
         <v>1236</v>
       </c>
       <c r="K789" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L789" s="53">
         <v>46246</v>
@@ -47000,7 +47184,7 @@
         <v>1236</v>
       </c>
       <c r="K790" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L790" s="53">
         <v>46246</v>
@@ -47050,7 +47234,7 @@
         <v>1236</v>
       </c>
       <c r="K791" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L791" s="53">
         <v>46246</v>
@@ -47100,7 +47284,7 @@
         <v>1236</v>
       </c>
       <c r="K792" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L792" s="53">
         <v>46246</v>
@@ -47461,7 +47645,9 @@
       <c r="N799" s="54">
         <v>684</v>
       </c>
-      <c r="O799" s="18"/>
+      <c r="O799" s="53">
+        <v>46246</v>
+      </c>
       <c r="P799" s="18"/>
       <c r="Q799" s="11">
         <v>77810981</v>
@@ -47511,7 +47697,9 @@
       <c r="N800" s="54">
         <v>699</v>
       </c>
-      <c r="O800" s="18"/>
+      <c r="O800" s="53">
+        <v>46246</v>
+      </c>
       <c r="P800" s="18"/>
       <c r="Q800" s="18"/>
       <c r="R800" s="20" t="s">
@@ -47947,11 +48135,11 @@
       <c r="J809" s="15" t="s">
         <v>1330</v>
       </c>
-      <c r="K809" s="11" t="s">
-        <v>2328</v>
+      <c r="K809" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L809" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M809" s="18"/>
       <c r="N809" s="54">
@@ -47997,11 +48185,11 @@
       <c r="J810" s="15" t="s">
         <v>1330</v>
       </c>
-      <c r="K810" s="11" t="s">
-        <v>2328</v>
+      <c r="K810" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L810" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M810" s="18"/>
       <c r="N810" s="54">
@@ -48047,10 +48235,12 @@
       <c r="J811" s="15" t="s">
         <v>993</v>
       </c>
-      <c r="K811" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L811" s="18"/>
+      <c r="K811" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L811" s="53">
+        <v>46250</v>
+      </c>
       <c r="M811" s="18"/>
       <c r="N811" s="40"/>
       <c r="O811" s="18"/>
@@ -48093,13 +48283,15 @@
       <c r="J812" s="15" t="s">
         <v>993</v>
       </c>
-      <c r="K812" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L812" s="18"/>
+      <c r="K812" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L812" s="53">
+        <v>46250</v>
+      </c>
       <c r="M812" s="18"/>
       <c r="N812" s="76" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="O812" s="18"/>
       <c r="P812" s="18"/>
@@ -48185,10 +48377,12 @@
       <c r="J814" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="K814" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L814" s="18"/>
+      <c r="K814" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L814" s="53">
+        <v>46250</v>
+      </c>
       <c r="M814" s="18"/>
       <c r="N814" s="40"/>
       <c r="O814" s="18"/>
@@ -48229,10 +48423,12 @@
       <c r="J815" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="K815" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L815" s="18"/>
+      <c r="K815" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L815" s="53">
+        <v>46250</v>
+      </c>
       <c r="M815" s="18"/>
       <c r="N815" s="54">
         <v>1043</v>
@@ -48275,10 +48471,12 @@
       <c r="J816" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="K816" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L816" s="18"/>
+      <c r="K816" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L816" s="53">
+        <v>46250</v>
+      </c>
       <c r="M816" s="18"/>
       <c r="N816" s="54">
         <v>1044</v>
@@ -48323,10 +48521,12 @@
       <c r="J817" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="K817" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L817" s="18"/>
+      <c r="K817" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L817" s="53">
+        <v>46250</v>
+      </c>
       <c r="M817" s="18"/>
       <c r="N817" s="54">
         <v>950</v>
@@ -48371,10 +48571,12 @@
       <c r="J818" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="K818" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L818" s="18"/>
+      <c r="K818" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L818" s="53">
+        <v>46250</v>
+      </c>
       <c r="M818" s="18"/>
       <c r="N818" s="40"/>
       <c r="O818" s="18"/>
@@ -48467,11 +48669,11 @@
       <c r="J820" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="K820" s="11" t="s">
-        <v>2328</v>
+      <c r="K820" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L820" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M820" s="18"/>
       <c r="N820" s="54">
@@ -48515,10 +48717,12 @@
       <c r="J821" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="K821" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L821" s="18"/>
+      <c r="K821" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L821" s="53">
+        <v>46250</v>
+      </c>
       <c r="M821" s="18"/>
       <c r="N821" s="54">
         <v>280</v>
@@ -48609,17 +48813,19 @@
       <c r="J823" s="15" t="s">
         <v>562</v>
       </c>
-      <c r="K823" s="11" t="s">
-        <v>2328</v>
+      <c r="K823" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L823" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M823" s="18"/>
       <c r="N823" s="54">
         <v>636</v>
       </c>
-      <c r="O823" s="18"/>
+      <c r="O823" s="53">
+        <v>46246</v>
+      </c>
       <c r="P823" s="18"/>
       <c r="Q823" s="11">
         <v>96293172</v>
@@ -48659,10 +48865,12 @@
       <c r="J824" s="15" t="s">
         <v>562</v>
       </c>
-      <c r="K824" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L824" s="18"/>
+      <c r="K824" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L824" s="53">
+        <v>46250</v>
+      </c>
       <c r="M824" s="18"/>
       <c r="N824" s="54">
         <v>294</v>
@@ -48709,10 +48917,12 @@
       <c r="J825" s="15" t="s">
         <v>562</v>
       </c>
-      <c r="K825" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L825" s="18"/>
+      <c r="K825" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L825" s="53">
+        <v>46250</v>
+      </c>
       <c r="M825" s="18"/>
       <c r="N825" s="54">
         <v>295</v>
@@ -49383,10 +49593,12 @@
       <c r="J839" s="15" t="s">
         <v>715</v>
       </c>
-      <c r="K839" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L839" s="18"/>
+      <c r="K839" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L839" s="53">
+        <v>46250</v>
+      </c>
       <c r="M839" s="18"/>
       <c r="N839" s="40"/>
       <c r="O839" s="18"/>
@@ -50247,7 +50459,7 @@
       </c>
       <c r="M857" s="18"/>
       <c r="N857" s="76" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="O857" s="53">
         <v>46245</v>
@@ -50299,7 +50511,7 @@
       </c>
       <c r="M858" s="18"/>
       <c r="N858" s="76" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="O858" s="53">
         <v>46245</v>
@@ -50344,7 +50556,7 @@
         <v>1484</v>
       </c>
       <c r="K859" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L859" s="53">
         <v>46246</v>
@@ -50355,7 +50567,7 @@
       </c>
       <c r="O859" s="18"/>
       <c r="P859" s="49" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="Q859" s="18"/>
       <c r="R859" s="20" t="s">
@@ -50941,7 +51153,7 @@
       <c r="N871" s="40"/>
       <c r="O871" s="18"/>
       <c r="P871" s="49" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="Q871" s="11">
         <v>95742697</v>
@@ -51215,11 +51427,11 @@
         <v>485</v>
       </c>
       <c r="J877" s="18"/>
-      <c r="K877" s="11" t="s">
-        <v>2328</v>
+      <c r="K877" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L877" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M877" s="18"/>
       <c r="N877" s="54">
@@ -51403,10 +51615,12 @@
       <c r="J881" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="K881" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L881" s="18"/>
+      <c r="K881" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L881" s="53">
+        <v>46250</v>
+      </c>
       <c r="M881" s="18"/>
       <c r="N881" s="54">
         <v>1030</v>
@@ -51647,11 +51861,11 @@
       <c r="J886" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="K886" s="11" t="s">
-        <v>2328</v>
+      <c r="K886" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L886" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M886" s="18"/>
       <c r="N886" s="54">
@@ -51837,11 +52051,11 @@
       <c r="J890" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="K890" s="11" t="s">
-        <v>2328</v>
+      <c r="K890" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L890" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M890" s="18"/>
       <c r="N890" s="54">
@@ -52456,7 +52670,7 @@
       <c r="M903" s="18"/>
       <c r="N903" s="40"/>
       <c r="O903" s="15" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="P903" s="18"/>
       <c r="Q903" s="18"/>
@@ -52494,7 +52708,7 @@
       </c>
       <c r="J904" s="18"/>
       <c r="K904" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L904" s="53">
         <v>46246</v>
@@ -52878,7 +53092,9 @@
         <v>46250</v>
       </c>
       <c r="M912" s="18"/>
-      <c r="N912" s="40"/>
+      <c r="N912" s="54">
+        <v>1180</v>
+      </c>
       <c r="O912" s="18"/>
       <c r="P912" s="18"/>
       <c r="Q912" s="11">
@@ -52926,7 +53142,9 @@
         <v>46250</v>
       </c>
       <c r="M913" s="18"/>
-      <c r="N913" s="40"/>
+      <c r="N913" s="54">
+        <v>1175</v>
+      </c>
       <c r="O913" s="18"/>
       <c r="P913" s="18"/>
       <c r="Q913" s="11">
@@ -53153,10 +53371,12 @@
       <c r="J918" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K918" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L918" s="18"/>
+      <c r="K918" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L918" s="53">
+        <v>46250</v>
+      </c>
       <c r="M918" s="18"/>
       <c r="N918" s="54">
         <v>892</v>
@@ -53228,7 +53448,7 @@
         <v>46243</v>
       </c>
       <c r="C920" s="55" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="D920" s="55">
         <v>111924926</v>
@@ -53358,8 +53578,8 @@
         <v>46250</v>
       </c>
       <c r="M922" s="18"/>
-      <c r="N922" s="54">
-        <v>875</v>
+      <c r="N922" s="54" t="s">
+        <v>2479</v>
       </c>
       <c r="O922" s="18"/>
       <c r="P922" s="18"/>
@@ -53409,7 +53629,7 @@
       </c>
       <c r="M923" s="18"/>
       <c r="N923" s="76" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="O923" s="18"/>
       <c r="P923" s="18"/>
@@ -53499,15 +53719,15 @@
       <c r="J925" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K925" s="11" t="s">
-        <v>2328</v>
+      <c r="K925" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L925" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M925" s="18"/>
       <c r="N925" s="76" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="O925" s="18"/>
       <c r="P925" s="18"/>
@@ -53549,11 +53769,11 @@
       <c r="J926" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K926" s="11" t="s">
-        <v>2328</v>
+      <c r="K926" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L926" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M926" s="18"/>
       <c r="N926" s="54">
@@ -53599,11 +53819,11 @@
       <c r="J927" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K927" s="11" t="s">
-        <v>2328</v>
+      <c r="K927" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L927" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M927" s="18"/>
       <c r="N927" s="54">
@@ -53651,10 +53871,12 @@
       <c r="J928" s="15" t="s">
         <v>1271</v>
       </c>
-      <c r="K928" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L928" s="18"/>
+      <c r="K928" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L928" s="53">
+        <v>46250</v>
+      </c>
       <c r="M928" s="18"/>
       <c r="N928" s="54">
         <v>491</v>
@@ -53699,11 +53921,11 @@
       <c r="J929" s="15" t="s">
         <v>1271</v>
       </c>
-      <c r="K929" s="11" t="s">
-        <v>2328</v>
+      <c r="K929" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L929" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M929" s="18"/>
       <c r="N929" s="54">
@@ -53747,10 +53969,12 @@
       <c r="J930" s="15" t="s">
         <v>1271</v>
       </c>
-      <c r="K930" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L930" s="18"/>
+      <c r="K930" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L930" s="53">
+        <v>46250</v>
+      </c>
       <c r="M930" s="18"/>
       <c r="N930" s="54">
         <v>488</v>
@@ -53800,7 +54024,9 @@
       </c>
       <c r="L931" s="18"/>
       <c r="M931" s="18"/>
-      <c r="N931" s="40"/>
+      <c r="N931" s="54">
+        <v>1209</v>
+      </c>
       <c r="O931" s="18"/>
       <c r="P931" s="18"/>
       <c r="Q931" s="18"/>
@@ -54135,10 +54361,12 @@
       <c r="J938" s="15" t="s">
         <v>1349</v>
       </c>
-      <c r="K938" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L938" s="18"/>
+      <c r="K938" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L938" s="53">
+        <v>46250</v>
+      </c>
       <c r="M938" s="18"/>
       <c r="N938" s="54">
         <v>1036</v>
@@ -54181,10 +54409,12 @@
       <c r="J939" s="15" t="s">
         <v>1349</v>
       </c>
-      <c r="K939" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L939" s="18"/>
+      <c r="K939" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L939" s="53">
+        <v>46250</v>
+      </c>
       <c r="M939" s="18"/>
       <c r="N939" s="54">
         <v>1035</v>
@@ -54227,10 +54457,12 @@
       <c r="J940" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K940" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L940" s="18"/>
+      <c r="K940" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L940" s="53">
+        <v>46250</v>
+      </c>
       <c r="M940" s="18"/>
       <c r="N940" s="40"/>
       <c r="O940" s="18"/>
@@ -54273,10 +54505,12 @@
       <c r="J941" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K941" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L941" s="18"/>
+      <c r="K941" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L941" s="53">
+        <v>46250</v>
+      </c>
       <c r="M941" s="18"/>
       <c r="N941" s="40"/>
       <c r="O941" s="18"/>
@@ -54319,10 +54553,12 @@
       <c r="J942" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K942" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L942" s="18"/>
+      <c r="K942" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L942" s="53">
+        <v>46250</v>
+      </c>
       <c r="M942" s="18"/>
       <c r="N942" s="54">
         <v>853</v>
@@ -54367,10 +54603,12 @@
       <c r="J943" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K943" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L943" s="18"/>
+      <c r="K943" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L943" s="53">
+        <v>46250</v>
+      </c>
       <c r="M943" s="18"/>
       <c r="N943" s="40"/>
       <c r="O943" s="18"/>
@@ -54413,10 +54651,12 @@
       <c r="J944" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K944" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L944" s="18"/>
+      <c r="K944" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L944" s="53">
+        <v>46250</v>
+      </c>
       <c r="M944" s="18"/>
       <c r="N944" s="40"/>
       <c r="O944" s="18"/>
@@ -54459,10 +54699,12 @@
       <c r="J945" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K945" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L945" s="18"/>
+      <c r="K945" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L945" s="53">
+        <v>46250</v>
+      </c>
       <c r="M945" s="18"/>
       <c r="N945" s="40"/>
       <c r="O945" s="18"/>
@@ -54474,7 +54716,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="946" spans="1:18" ht="15" thickBot="1">
+    <row r="946" spans="1:18" ht="28.2" thickBot="1">
       <c r="A946" s="2">
         <v>181</v>
       </c>
@@ -54505,13 +54747,15 @@
       <c r="J946" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K946" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L946" s="18"/>
+      <c r="K946" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L946" s="53">
+        <v>46250</v>
+      </c>
       <c r="M946" s="18"/>
-      <c r="N946" s="54">
-        <v>986</v>
+      <c r="N946" s="54" t="s">
+        <v>2480</v>
       </c>
       <c r="O946" s="18"/>
       <c r="P946" s="18"/>
@@ -54522,7 +54766,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="947" spans="1:18" ht="15" thickBot="1">
+    <row r="947" spans="1:18" ht="28.2" thickBot="1">
       <c r="A947" s="2">
         <v>182</v>
       </c>
@@ -54553,13 +54797,15 @@
       <c r="J947" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K947" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L947" s="18"/>
+      <c r="K947" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L947" s="53">
+        <v>46250</v>
+      </c>
       <c r="M947" s="18"/>
-      <c r="N947" s="54">
-        <v>987</v>
+      <c r="N947" s="54" t="s">
+        <v>2481</v>
       </c>
       <c r="O947" s="18"/>
       <c r="P947" s="18"/>
@@ -55061,11 +55307,11 @@
       <c r="J957" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K957" s="11" t="s">
-        <v>2328</v>
+      <c r="K957" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L957" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M957" s="18"/>
       <c r="N957" s="54">
@@ -55111,11 +55357,11 @@
       <c r="J958" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K958" s="11" t="s">
-        <v>2328</v>
+      <c r="K958" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L958" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M958" s="18"/>
       <c r="N958" s="54">
@@ -55161,11 +55407,11 @@
       <c r="J959" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K959" s="11" t="s">
-        <v>2328</v>
+      <c r="K959" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L959" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M959" s="18"/>
       <c r="N959" s="54">
@@ -55209,11 +55455,11 @@
       <c r="J960" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K960" s="11" t="s">
-        <v>2328</v>
+      <c r="K960" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L960" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M960" s="18"/>
       <c r="N960" s="54">
@@ -55257,11 +55503,11 @@
       <c r="J961" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K961" s="11" t="s">
-        <v>2328</v>
+      <c r="K961" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L961" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M961" s="18"/>
       <c r="N961" s="54">
@@ -56306,7 +56552,7 @@
       <c r="M982" s="18"/>
       <c r="N982" s="40"/>
       <c r="O982" s="15" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="P982" s="18"/>
       <c r="Q982" s="15">
@@ -57501,10 +57747,12 @@
       <c r="J1006" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1006" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1006" s="18"/>
+      <c r="K1006" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1006" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1006" s="18"/>
       <c r="N1006" s="54">
         <v>117</v>
@@ -57551,11 +57799,11 @@
       <c r="J1007" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1007" s="11" t="s">
-        <v>2328</v>
+      <c r="K1007" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1007" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1007" s="18"/>
       <c r="N1007" s="54">
@@ -57603,10 +57851,12 @@
       <c r="J1008" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1008" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1008" s="18"/>
+      <c r="K1008" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1008" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1008" s="18"/>
       <c r="N1008" s="40"/>
       <c r="O1008" s="18"/>
@@ -57618,7 +57868,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1009" spans="1:18" ht="15" thickBot="1">
+    <row r="1009" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1009" s="2">
         <v>244</v>
       </c>
@@ -57649,15 +57899,15 @@
       <c r="J1009" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1009" s="11" t="s">
-        <v>2328</v>
+      <c r="K1009" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1009" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1009" s="18"/>
-      <c r="N1009" s="54">
-        <v>698</v>
+      <c r="N1009" s="76" t="s">
+        <v>2482</v>
       </c>
       <c r="O1009" s="18"/>
       <c r="P1009" s="18"/>
@@ -57697,10 +57947,12 @@
       <c r="J1010" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1010" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1010" s="18"/>
+      <c r="K1010" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1010" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1010" s="18"/>
       <c r="N1010" s="54">
         <v>288</v>
@@ -57747,10 +57999,12 @@
       <c r="J1011" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1011" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1011" s="18"/>
+      <c r="K1011" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1011" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1011" s="18"/>
       <c r="N1011" s="40"/>
       <c r="O1011" s="18"/>
@@ -57793,10 +58047,12 @@
       <c r="J1012" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1012" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1012" s="18"/>
+      <c r="K1012" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1012" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1012" s="18"/>
       <c r="N1012" s="40"/>
       <c r="O1012" s="18"/>
@@ -57839,10 +58095,12 @@
       <c r="J1013" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1013" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1013" s="18"/>
+      <c r="K1013" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1013" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1013" s="18"/>
       <c r="N1013" s="54">
         <v>287</v>
@@ -57889,11 +58147,11 @@
       <c r="J1014" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1014" s="11" t="s">
-        <v>2328</v>
+      <c r="K1014" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1014" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1014" s="18"/>
       <c r="N1014" s="54">
@@ -58935,11 +59193,11 @@
       <c r="J1035" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1035" s="11" t="s">
-        <v>2328</v>
+      <c r="K1035" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1035" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1035" s="18"/>
       <c r="N1035" s="54">
@@ -59090,7 +59348,9 @@
         <v>46250</v>
       </c>
       <c r="M1038" s="18"/>
-      <c r="N1038" s="40"/>
+      <c r="N1038" s="54">
+        <v>1213</v>
+      </c>
       <c r="O1038" s="18"/>
       <c r="P1038" s="18"/>
       <c r="Q1038" s="15">
@@ -59332,7 +59592,7 @@
         <v>564</v>
       </c>
       <c r="K1043" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L1043" s="53">
         <v>46246</v>
@@ -59974,7 +60234,7 @@
         <v>564</v>
       </c>
       <c r="K1056" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L1056" s="53">
         <v>46246</v>
@@ -60272,7 +60532,7 @@
         <v>564</v>
       </c>
       <c r="K1062" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L1062" s="53">
         <v>46246</v>
@@ -60421,7 +60681,7 @@
       </c>
       <c r="M1065" s="18"/>
       <c r="N1065" s="76" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
       <c r="O1065" s="53">
         <v>46245</v>
@@ -60615,7 +60875,7 @@
       </c>
       <c r="M1069" s="18"/>
       <c r="N1069" s="76" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O1069" s="18"/>
       <c r="P1069" s="18"/>
@@ -60657,11 +60917,11 @@
       <c r="J1070" s="15" t="s">
         <v>1349</v>
       </c>
-      <c r="K1070" s="11" t="s">
-        <v>2328</v>
+      <c r="K1070" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1070" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1070" s="18"/>
       <c r="N1070" s="54">
@@ -60906,7 +61166,9 @@
         <v>46250</v>
       </c>
       <c r="M1075" s="18"/>
-      <c r="N1075" s="40"/>
+      <c r="N1075" s="54">
+        <v>1091</v>
+      </c>
       <c r="O1075" s="18"/>
       <c r="P1075" s="18"/>
       <c r="Q1075" s="18"/>
@@ -60952,7 +61214,9 @@
         <v>46250</v>
       </c>
       <c r="M1076" s="18"/>
-      <c r="N1076" s="40"/>
+      <c r="N1076" s="54">
+        <v>1092</v>
+      </c>
       <c r="O1076" s="18"/>
       <c r="P1076" s="18"/>
       <c r="Q1076" s="18"/>
@@ -61690,7 +61954,7 @@
         <v>1672</v>
       </c>
       <c r="K1092" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L1092" s="53">
         <v>46246</v>
@@ -61708,7 +61972,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1093" spans="1:18" ht="15" thickBot="1">
+    <row r="1093" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1093" s="2">
         <v>328</v>
       </c>
@@ -61739,15 +62003,15 @@
       <c r="J1093" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1093" s="11" t="s">
-        <v>2328</v>
+      <c r="K1093" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1093" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1093" s="18"/>
-      <c r="N1093" s="54">
-        <v>664</v>
+      <c r="N1093" s="54" t="s">
+        <v>2483</v>
       </c>
       <c r="O1093" s="18"/>
       <c r="P1093" s="18"/>
@@ -61787,11 +62051,11 @@
       <c r="J1094" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1094" s="11" t="s">
-        <v>2328</v>
+      <c r="K1094" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1094" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1094" s="18"/>
       <c r="N1094" s="54">
@@ -61835,10 +62099,12 @@
       <c r="J1095" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1095" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1095" s="18"/>
+      <c r="K1095" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1095" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1095" s="18"/>
       <c r="N1095" s="54">
         <v>845</v>
@@ -61883,10 +62149,12 @@
       <c r="J1096" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1096" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1096" s="18"/>
+      <c r="K1096" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1096" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1096" s="18"/>
       <c r="N1096" s="40"/>
       <c r="O1096" s="18"/>
@@ -61927,10 +62195,12 @@
       <c r="J1097" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1097" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1097" s="18"/>
+      <c r="K1097" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1097" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1097" s="18"/>
       <c r="N1097" s="54">
         <v>302</v>
@@ -61975,10 +62245,12 @@
       <c r="J1098" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1098" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1098" s="18"/>
+      <c r="K1098" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1098" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1098" s="18"/>
       <c r="N1098" s="54">
         <v>303</v>
@@ -62023,10 +62295,12 @@
       <c r="J1099" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1099" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1099" s="18"/>
+      <c r="K1099" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1099" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1099" s="18"/>
       <c r="N1099" s="54">
         <v>301</v>
@@ -62064,7 +62338,7 @@
         <v>564</v>
       </c>
       <c r="K1100" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L1100" s="53">
         <v>46246</v>
@@ -62199,13 +62473,15 @@
       <c r="J1103" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K1103" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1103" s="18"/>
+      <c r="K1103" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1103" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1103" s="18"/>
       <c r="N1103" s="54" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O1103" s="53">
         <v>46245</v>
@@ -62403,10 +62679,12 @@
       <c r="J1107" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1107" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1107" s="18"/>
+      <c r="K1107" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1107" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1107" s="18"/>
       <c r="N1107" s="40"/>
       <c r="O1107" s="18"/>
@@ -62447,11 +62725,11 @@
       <c r="J1108" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1108" s="11" t="s">
-        <v>2328</v>
+      <c r="K1108" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1108" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1108" s="18"/>
       <c r="N1108" s="54">
@@ -62545,11 +62823,11 @@
       <c r="J1110" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1110" s="11" t="s">
-        <v>2328</v>
+      <c r="K1110" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1110" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1110" s="18"/>
       <c r="N1110" s="54">
@@ -62597,11 +62875,11 @@
       <c r="J1111" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1111" s="11" t="s">
-        <v>2328</v>
+      <c r="K1111" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1111" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1111" s="18"/>
       <c r="N1111" s="54">
@@ -62820,7 +63098,9 @@
       </c>
       <c r="L1116" s="18"/>
       <c r="M1116" s="18"/>
-      <c r="N1116" s="40"/>
+      <c r="N1116" s="54">
+        <v>1137</v>
+      </c>
       <c r="O1116" s="18"/>
       <c r="P1116" s="18"/>
       <c r="Q1116" s="18"/>
@@ -62940,7 +63220,9 @@
       </c>
       <c r="L1119" s="18"/>
       <c r="M1119" s="18"/>
-      <c r="N1119" s="40"/>
+      <c r="N1119" s="54">
+        <v>1106</v>
+      </c>
       <c r="O1119" s="18"/>
       <c r="P1119" s="18"/>
       <c r="Q1119" s="18"/>
@@ -63342,7 +63624,9 @@
       </c>
       <c r="L1129" s="18"/>
       <c r="M1129" s="18"/>
-      <c r="N1129" s="40"/>
+      <c r="N1129" s="54">
+        <v>1102</v>
+      </c>
       <c r="O1129" s="18"/>
       <c r="P1129" s="18"/>
       <c r="Q1129" s="18"/>
@@ -64733,10 +65017,12 @@
       <c r="J1163" s="15" t="s">
         <v>1028</v>
       </c>
-      <c r="K1163" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1163" s="18"/>
+      <c r="K1163" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1163" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1163" s="18"/>
       <c r="N1163" s="40"/>
       <c r="O1163" s="18"/>
@@ -64779,10 +65065,12 @@
       <c r="J1164" s="19" t="s">
         <v>1781</v>
       </c>
-      <c r="K1164" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1164" s="18"/>
+      <c r="K1164" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1164" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1164" s="18"/>
       <c r="N1164" s="54">
         <v>194</v>
@@ -64829,10 +65117,12 @@
       <c r="J1165" s="15" t="s">
         <v>1672</v>
       </c>
-      <c r="K1165" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1165" s="18"/>
+      <c r="K1165" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1165" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1165" s="18"/>
       <c r="N1165" s="40"/>
       <c r="O1165" s="18"/>
@@ -64873,10 +65163,12 @@
       <c r="J1166" s="15" t="s">
         <v>1672</v>
       </c>
-      <c r="K1166" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1166" s="18"/>
+      <c r="K1166" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1166" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1166" s="18"/>
       <c r="N1166" s="40"/>
       <c r="O1166" s="18"/>
@@ -65829,11 +66121,11 @@
       <c r="J1187" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K1187" s="11" t="s">
-        <v>2328</v>
+      <c r="K1187" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1187" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1187" s="18"/>
       <c r="N1187" s="54">
@@ -65881,10 +66173,12 @@
       <c r="J1188" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1188" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1188" s="18"/>
+      <c r="K1188" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1188" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1188" s="18"/>
       <c r="N1188" s="40"/>
       <c r="O1188" s="53">
@@ -65927,11 +66221,11 @@
       <c r="J1189" s="15" t="s">
         <v>1830</v>
       </c>
-      <c r="K1189" s="11" t="s">
-        <v>2328</v>
+      <c r="K1189" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1189" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1189" s="18"/>
       <c r="N1189" s="54">
@@ -65975,10 +66269,12 @@
       <c r="J1190" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="K1190" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1190" s="18"/>
+      <c r="K1190" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1190" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1190" s="18"/>
       <c r="N1190" s="40"/>
       <c r="O1190" s="18"/>
@@ -66767,10 +67063,12 @@
       <c r="J1207" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1207" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1207" s="18"/>
+      <c r="K1207" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1207" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1207" s="18"/>
       <c r="N1207" s="54">
         <v>353</v>
@@ -66819,10 +67117,12 @@
       <c r="J1208" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1208" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1208" s="18"/>
+      <c r="K1208" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1208" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1208" s="18"/>
       <c r="N1208" s="40"/>
       <c r="O1208" s="18"/>
@@ -66865,10 +67165,12 @@
       <c r="J1209" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1209" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1209" s="18"/>
+      <c r="K1209" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1209" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1209" s="18"/>
       <c r="N1209" s="40"/>
       <c r="O1209" s="18"/>
@@ -67242,7 +67544,9 @@
       </c>
       <c r="L1217" s="18"/>
       <c r="M1217" s="18"/>
-      <c r="N1217" s="40"/>
+      <c r="N1217" s="54">
+        <v>1104</v>
+      </c>
       <c r="O1217" s="18"/>
       <c r="P1217" s="18"/>
       <c r="Q1217" s="15">
@@ -67283,11 +67587,11 @@
       <c r="J1218" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1218" s="11" t="s">
-        <v>2328</v>
+      <c r="K1218" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1218" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1218" s="18"/>
       <c r="N1218" s="54">
@@ -67336,7 +67640,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1220" spans="1:18" ht="15" thickBot="1">
+    <row r="1220" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1220" s="2">
         <v>30</v>
       </c>
@@ -67367,15 +67671,15 @@
       <c r="J1220" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1220" s="11" t="s">
-        <v>2328</v>
+      <c r="K1220" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1220" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1220" s="18"/>
-      <c r="N1220" s="54">
-        <v>455</v>
+      <c r="N1220" s="54" t="s">
+        <v>2484</v>
       </c>
       <c r="O1220" s="18"/>
       <c r="P1220" s="18"/>
@@ -67417,10 +67721,12 @@
       <c r="J1221" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1221" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1221" s="18"/>
+      <c r="K1221" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1221" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1221" s="18"/>
       <c r="N1221" s="54">
         <v>453</v>
@@ -67499,10 +67805,12 @@
       <c r="J1223" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1223" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1223" s="18"/>
+      <c r="K1223" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1223" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1223" s="18"/>
       <c r="N1223" s="54">
         <v>1015</v>
@@ -67547,10 +67855,12 @@
       <c r="J1224" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1224" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1224" s="18"/>
+      <c r="K1224" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1224" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1224" s="18"/>
       <c r="N1224" s="54">
         <v>815</v>
@@ -67635,12 +67945,16 @@
       <c r="J1226" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1226" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1226" s="18"/>
+      <c r="K1226" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1226" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1226" s="18"/>
-      <c r="N1226" s="40"/>
+      <c r="N1226" s="54">
+        <v>1108</v>
+      </c>
       <c r="O1226" s="18"/>
       <c r="P1226" s="18"/>
       <c r="Q1226" s="15">
@@ -67681,10 +67995,12 @@
       <c r="J1227" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1227" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1227" s="18"/>
+      <c r="K1227" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1227" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1227" s="18"/>
       <c r="N1227" s="40"/>
       <c r="O1227" s="18"/>
@@ -67727,10 +68043,12 @@
       <c r="J1228" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1228" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1228" s="18"/>
+      <c r="K1228" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1228" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1228" s="18"/>
       <c r="N1228" s="40"/>
       <c r="O1228" s="18"/>
@@ -67773,10 +68091,12 @@
       <c r="J1229" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1229" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1229" s="18"/>
+      <c r="K1229" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1229" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1229" s="18"/>
       <c r="N1229" s="54">
         <v>590</v>
@@ -67947,10 +68267,12 @@
       <c r="J1233" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1233" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1233" s="18"/>
+      <c r="K1233" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1233" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1233" s="18"/>
       <c r="N1233" s="54">
         <v>450</v>
@@ -68071,10 +68393,12 @@
       <c r="J1236" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1236" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1236" s="18"/>
+      <c r="K1236" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1236" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1236" s="18"/>
       <c r="N1236" s="40"/>
       <c r="O1236" s="18"/>
@@ -68117,10 +68441,12 @@
       <c r="J1237" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1237" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1237" s="18"/>
+      <c r="K1237" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1237" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1237" s="18"/>
       <c r="N1237" s="54">
         <v>472</v>
@@ -68594,7 +68920,7 @@
         <v>1908</v>
       </c>
       <c r="K1247" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L1247" s="53">
         <v>46246</v>
@@ -68644,7 +68970,7 @@
         <v>1908</v>
       </c>
       <c r="K1248" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L1248" s="53">
         <v>46246</v>
@@ -68696,7 +69022,7 @@
         <v>1908</v>
       </c>
       <c r="K1249" s="11" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="L1249" s="53">
         <v>46246</v>
@@ -72788,7 +73114,9 @@
         <v>46250</v>
       </c>
       <c r="M1334" s="18"/>
-      <c r="N1334" s="40"/>
+      <c r="N1334" s="54">
+        <v>1194</v>
+      </c>
       <c r="O1334" s="18"/>
       <c r="P1334" s="18"/>
       <c r="Q1334" s="18"/>
@@ -72935,7 +73263,7 @@
       </c>
       <c r="M1337" s="18"/>
       <c r="N1337" s="54" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="O1337" s="18"/>
       <c r="P1337" s="18"/>
@@ -73270,7 +73598,9 @@
         <v>46250</v>
       </c>
       <c r="M1344" s="18"/>
-      <c r="N1344" s="40"/>
+      <c r="N1344" s="54">
+        <v>1093</v>
+      </c>
       <c r="O1344" s="53">
         <v>46245</v>
       </c>
@@ -74717,7 +75047,7 @@
       </c>
       <c r="O1375" s="18"/>
       <c r="P1375" s="49" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="Q1375" s="18"/>
       <c r="R1375" s="22" t="s">
@@ -74891,10 +75221,12 @@
       <c r="J1379" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1379" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1379" s="18"/>
+      <c r="K1379" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1379" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1379" s="18"/>
       <c r="N1379" s="54">
         <v>993</v>
@@ -75331,10 +75663,12 @@
       <c r="J1388" s="15" t="s">
         <v>1704</v>
       </c>
-      <c r="K1388" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1388" s="18"/>
+      <c r="K1388" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1388" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1388" s="18"/>
       <c r="N1388" s="54">
         <v>952</v>
@@ -75693,10 +76027,12 @@
       <c r="J1396" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K1396" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1396" s="18"/>
+      <c r="K1396" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1396" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1396" s="18"/>
       <c r="N1396" s="54">
         <v>548</v>
@@ -75741,10 +76077,12 @@
       <c r="J1397" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K1397" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1397" s="18"/>
+      <c r="K1397" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1397" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1397" s="18"/>
       <c r="N1397" s="40"/>
       <c r="O1397" s="18"/>
@@ -76176,8 +76514,8 @@
       </c>
       <c r="L1406" s="18"/>
       <c r="M1406" s="18"/>
-      <c r="N1406" s="54">
-        <v>769</v>
+      <c r="N1406" s="54" t="s">
+        <v>2485</v>
       </c>
       <c r="O1406" s="18"/>
       <c r="P1406" s="18"/>
@@ -76196,7 +76534,7 @@
         <v>46244</v>
       </c>
       <c r="C1407" s="55" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="D1407" s="55">
         <v>123691404</v>
@@ -76242,7 +76580,7 @@
         <v>46244</v>
       </c>
       <c r="C1408" s="55" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="D1408" s="55">
         <v>108920233</v>
@@ -76272,8 +76610,8 @@
         <v>46250</v>
       </c>
       <c r="M1408" s="18"/>
-      <c r="N1408" s="54">
-        <v>762</v>
+      <c r="N1408" s="76" t="s">
+        <v>2486</v>
       </c>
       <c r="O1408" s="18"/>
       <c r="P1408" s="18"/>
@@ -76290,7 +76628,7 @@
         <v>46245</v>
       </c>
       <c r="C1409" s="55" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="D1409" s="55">
         <v>19908438</v>
@@ -76336,10 +76674,10 @@
         <v>46245</v>
       </c>
       <c r="C1410" s="55" t="s">
+        <v>2131</v>
+      </c>
+      <c r="D1410" s="55" t="s">
         <v>2132</v>
-      </c>
-      <c r="D1410" s="55" t="s">
-        <v>2133</v>
       </c>
       <c r="E1410" s="12" t="s">
         <v>21</v>
@@ -76367,7 +76705,7 @@
       </c>
       <c r="M1410" s="18"/>
       <c r="N1410" s="76" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="O1410" s="18"/>
       <c r="P1410" s="18"/>
@@ -76386,7 +76724,7 @@
         <v>46245</v>
       </c>
       <c r="C1411" s="55" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="D1411" s="55">
         <v>95654502</v>
@@ -76407,7 +76745,7 @@
         <v>123</v>
       </c>
       <c r="J1411" s="15" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="K1411" s="52" t="s">
         <v>837</v>
@@ -76434,7 +76772,7 @@
         <v>46245</v>
       </c>
       <c r="C1412" s="55" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="D1412" s="55">
         <v>90614152</v>
@@ -76478,7 +76816,7 @@
         <v>46245</v>
       </c>
       <c r="C1413" s="55" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="D1413" s="55">
         <v>13681821</v>
@@ -76524,7 +76862,7 @@
         <v>46245</v>
       </c>
       <c r="C1414" s="55" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="D1414" s="55">
         <v>8246457</v>
@@ -76573,7 +76911,7 @@
         <v>1327</v>
       </c>
       <c r="D1415" s="55" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="E1415" s="12" t="s">
         <v>21</v>
@@ -76619,7 +76957,7 @@
         <v>1850</v>
       </c>
       <c r="D1416" s="55" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="E1416" s="12" t="s">
         <v>21</v>
@@ -76665,7 +77003,7 @@
         <v>47</v>
       </c>
       <c r="D1417" s="55" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="E1417" s="12" t="s">
         <v>21</v>
@@ -76708,10 +77046,10 @@
         <v>46245</v>
       </c>
       <c r="C1418" s="55" t="s">
+        <v>2141</v>
+      </c>
+      <c r="D1418" s="55" t="s">
         <v>2142</v>
-      </c>
-      <c r="D1418" s="55" t="s">
-        <v>2143</v>
       </c>
       <c r="E1418" s="12" t="s">
         <v>21</v>
@@ -76754,10 +77092,10 @@
         <v>46245</v>
       </c>
       <c r="C1419" s="55" t="s">
+        <v>2143</v>
+      </c>
+      <c r="D1419" s="55" t="s">
         <v>2144</v>
-      </c>
-      <c r="D1419" s="55" t="s">
-        <v>2145</v>
       </c>
       <c r="E1419" s="12" t="s">
         <v>21</v>
@@ -76805,7 +77143,7 @@
         <v>610</v>
       </c>
       <c r="D1420" s="55" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="E1420" s="12" t="s">
         <v>21</v>
@@ -76853,7 +77191,7 @@
         <v>239</v>
       </c>
       <c r="D1421" s="55" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="E1421" s="12" t="s">
         <v>21</v>
@@ -76871,7 +77209,7 @@
         <v>123</v>
       </c>
       <c r="J1421" s="15" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="K1421" s="17" t="s">
         <v>12</v>
@@ -76896,10 +77234,10 @@
         <v>46245</v>
       </c>
       <c r="C1422" s="55" t="s">
+        <v>2148</v>
+      </c>
+      <c r="D1422" s="55" t="s">
         <v>2149</v>
-      </c>
-      <c r="D1422" s="55" t="s">
-        <v>2150</v>
       </c>
       <c r="E1422" s="12" t="s">
         <v>21</v>
@@ -76915,14 +77253,16 @@
         <v>123</v>
       </c>
       <c r="J1422" s="15" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="K1422" s="17" t="s">
         <v>12</v>
       </c>
       <c r="L1422" s="18"/>
       <c r="M1422" s="18"/>
-      <c r="N1422" s="40"/>
+      <c r="N1422" s="54">
+        <v>1204</v>
+      </c>
       <c r="O1422" s="18"/>
       <c r="P1422" s="18"/>
       <c r="Q1422" s="15">
@@ -76940,10 +77280,10 @@
         <v>46245</v>
       </c>
       <c r="C1423" s="55" t="s">
+        <v>2150</v>
+      </c>
+      <c r="D1423" s="55" t="s">
         <v>2151</v>
-      </c>
-      <c r="D1423" s="55" t="s">
-        <v>2152</v>
       </c>
       <c r="E1423" s="12" t="s">
         <v>21</v>
@@ -76961,7 +77301,7 @@
         <v>123</v>
       </c>
       <c r="J1423" s="15" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="K1423" s="17" t="s">
         <v>12</v>
@@ -76989,7 +77329,7 @@
         <v>42</v>
       </c>
       <c r="D1424" s="55" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="E1424" s="12" t="s">
         <v>21</v>
@@ -77007,7 +77347,7 @@
         <v>123</v>
       </c>
       <c r="J1424" s="15" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="K1424" s="17" t="s">
         <v>12</v>
@@ -77035,7 +77375,7 @@
         <v>1359</v>
       </c>
       <c r="D1425" s="55" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="E1425" s="12" t="s">
         <v>21</v>
@@ -77053,7 +77393,7 @@
         <v>123</v>
       </c>
       <c r="J1425" s="15" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="K1425" s="17" t="s">
         <v>12</v>
@@ -77078,10 +77418,10 @@
         <v>46245</v>
       </c>
       <c r="C1426" s="55" t="s">
+        <v>2154</v>
+      </c>
+      <c r="D1426" s="55" t="s">
         <v>2155</v>
-      </c>
-      <c r="D1426" s="55" t="s">
-        <v>2156</v>
       </c>
       <c r="E1426" s="12" t="s">
         <v>21</v>
@@ -77097,7 +77437,7 @@
         <v>123</v>
       </c>
       <c r="J1426" s="15" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="K1426" s="17" t="s">
         <v>12</v>
@@ -77122,10 +77462,10 @@
         <v>46245</v>
       </c>
       <c r="C1427" s="55" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D1427" s="55" t="s">
         <v>2157</v>
-      </c>
-      <c r="D1427" s="55" t="s">
-        <v>2158</v>
       </c>
       <c r="E1427" s="12" t="s">
         <v>21</v>
@@ -77168,10 +77508,10 @@
         <v>46245</v>
       </c>
       <c r="C1428" s="55" t="s">
+        <v>2158</v>
+      </c>
+      <c r="D1428" s="55" t="s">
         <v>2159</v>
-      </c>
-      <c r="D1428" s="55" t="s">
-        <v>2160</v>
       </c>
       <c r="E1428" s="12" t="s">
         <v>21</v>
@@ -77210,10 +77550,10 @@
         <v>46245</v>
       </c>
       <c r="C1429" s="55" t="s">
+        <v>2160</v>
+      </c>
+      <c r="D1429" s="55" t="s">
         <v>2161</v>
-      </c>
-      <c r="D1429" s="55" t="s">
-        <v>2162</v>
       </c>
       <c r="E1429" s="12" t="s">
         <v>21</v>
@@ -77238,8 +77578,8 @@
       </c>
       <c r="L1429" s="18"/>
       <c r="M1429" s="18"/>
-      <c r="N1429" s="54">
-        <v>922</v>
+      <c r="N1429" s="76" t="s">
+        <v>2487</v>
       </c>
       <c r="O1429" s="18"/>
       <c r="P1429" s="18"/>
@@ -77254,10 +77594,10 @@
         <v>46245</v>
       </c>
       <c r="C1430" s="55" t="s">
+        <v>2162</v>
+      </c>
+      <c r="D1430" s="55" t="s">
         <v>2163</v>
-      </c>
-      <c r="D1430" s="55" t="s">
-        <v>2164</v>
       </c>
       <c r="E1430" s="12" t="s">
         <v>21</v>
@@ -77282,8 +77622,8 @@
       </c>
       <c r="L1430" s="18"/>
       <c r="M1430" s="18"/>
-      <c r="N1430" s="54">
-        <v>923</v>
+      <c r="N1430" s="76" t="s">
+        <v>2488</v>
       </c>
       <c r="O1430" s="18"/>
       <c r="P1430" s="18"/>
@@ -77298,10 +77638,10 @@
         <v>46245</v>
       </c>
       <c r="C1431" s="55" t="s">
+        <v>2164</v>
+      </c>
+      <c r="D1431" s="55" t="s">
         <v>2165</v>
-      </c>
-      <c r="D1431" s="55" t="s">
-        <v>2166</v>
       </c>
       <c r="E1431" s="12" t="s">
         <v>21</v>
@@ -77342,10 +77682,10 @@
         <v>46245</v>
       </c>
       <c r="C1432" s="55" t="s">
+        <v>2166</v>
+      </c>
+      <c r="D1432" s="55" t="s">
         <v>2167</v>
-      </c>
-      <c r="D1432" s="55" t="s">
-        <v>2168</v>
       </c>
       <c r="E1432" s="12" t="s">
         <v>21</v>
@@ -77389,7 +77729,7 @@
         <v>562</v>
       </c>
       <c r="D1433" s="55" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="E1433" s="12" t="s">
         <v>21</v>
@@ -77430,10 +77770,10 @@
         <v>46245</v>
       </c>
       <c r="C1434" s="55" t="s">
+        <v>2169</v>
+      </c>
+      <c r="D1434" s="55" t="s">
         <v>2170</v>
-      </c>
-      <c r="D1434" s="55" t="s">
-        <v>2171</v>
       </c>
       <c r="E1434" s="12" t="s">
         <v>21</v>
@@ -77474,10 +77814,10 @@
         <v>46245</v>
       </c>
       <c r="C1435" s="55" t="s">
+        <v>2171</v>
+      </c>
+      <c r="D1435" s="55" t="s">
         <v>2172</v>
-      </c>
-      <c r="D1435" s="55" t="s">
-        <v>2173</v>
       </c>
       <c r="E1435" s="12" t="s">
         <v>21</v>
@@ -77516,10 +77856,10 @@
         <v>46245</v>
       </c>
       <c r="C1436" s="55" t="s">
+        <v>2173</v>
+      </c>
+      <c r="D1436" s="55" t="s">
         <v>2174</v>
-      </c>
-      <c r="D1436" s="55" t="s">
-        <v>2175</v>
       </c>
       <c r="E1436" s="12" t="s">
         <v>21</v>
@@ -77560,10 +77900,10 @@
         <v>46245</v>
       </c>
       <c r="C1437" s="55" t="s">
+        <v>2175</v>
+      </c>
+      <c r="D1437" s="55" t="s">
         <v>2176</v>
-      </c>
-      <c r="D1437" s="55" t="s">
-        <v>2177</v>
       </c>
       <c r="E1437" s="12" t="s">
         <v>21</v>
@@ -77602,7 +77942,7 @@
         <v>46245</v>
       </c>
       <c r="C1438" s="55" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="D1438" s="55">
         <v>9891324</v>
@@ -77623,14 +77963,14 @@
         <v>123</v>
       </c>
       <c r="J1438" s="15" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="K1438" s="60" t="s">
         <v>1189</v>
       </c>
       <c r="L1438" s="18"/>
       <c r="M1438" s="21" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="N1438" s="40"/>
       <c r="O1438" s="18"/>
@@ -77648,7 +77988,7 @@
         <v>46245</v>
       </c>
       <c r="C1439" s="55" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="D1439" s="55">
         <v>123757652</v>
@@ -77692,7 +78032,7 @@
         <v>46245</v>
       </c>
       <c r="C1440" s="55" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
       <c r="D1440" s="55">
         <v>10386563</v>
@@ -77736,7 +78076,7 @@
         <v>46245</v>
       </c>
       <c r="C1441" s="55" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="D1441" s="55">
         <v>19588434</v>
@@ -77785,7 +78125,7 @@
         <v>2097</v>
       </c>
       <c r="D1442" s="55" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="E1442" s="12" t="s">
         <v>21</v>
@@ -77853,10 +78193,12 @@
       <c r="J1443" s="15" t="s">
         <v>371</v>
       </c>
-      <c r="K1443" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1443" s="18"/>
+      <c r="K1443" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1443" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1443" s="18"/>
       <c r="N1443" s="40"/>
       <c r="O1443" s="18"/>
@@ -77876,7 +78218,7 @@
         <v>46245</v>
       </c>
       <c r="C1444" s="55" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="D1444" s="55">
         <v>9891324</v>
@@ -77922,7 +78264,7 @@
         <v>46245</v>
       </c>
       <c r="C1445" s="55" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="D1445" s="55">
         <v>132724487</v>
@@ -78056,7 +78398,7 @@
         <v>46245</v>
       </c>
       <c r="C1448" s="55" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="D1448" s="55">
         <v>107861342</v>
@@ -78106,7 +78448,7 @@
         <v>46245</v>
       </c>
       <c r="C1449" s="68" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="D1449" s="68">
         <v>133986224</v>
@@ -78156,7 +78498,7 @@
         <v>46245</v>
       </c>
       <c r="C1450" s="55" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="D1450" s="55">
         <v>135954527</v>
@@ -78206,10 +78548,10 @@
         <v>46245</v>
       </c>
       <c r="C1451" s="55" t="s">
+        <v>2180</v>
+      </c>
+      <c r="D1451" s="55" t="s">
         <v>2181</v>
-      </c>
-      <c r="D1451" s="55" t="s">
-        <v>2182</v>
       </c>
       <c r="E1451" s="12" t="s">
         <v>21</v>
@@ -78252,10 +78594,10 @@
         <v>46245</v>
       </c>
       <c r="C1452" s="55" t="s">
+        <v>2191</v>
+      </c>
+      <c r="D1452" s="55" t="s">
         <v>2192</v>
-      </c>
-      <c r="D1452" s="55" t="s">
-        <v>2193</v>
       </c>
       <c r="E1452" s="12" t="s">
         <v>21</v>
@@ -78273,7 +78615,7 @@
         <v>123</v>
       </c>
       <c r="J1452" s="15" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="K1452" s="17" t="s">
         <v>12</v>
@@ -78310,7 +78652,7 @@
         <v>122</v>
       </c>
       <c r="G1453" s="74" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="H1453" s="66">
         <v>697</v>
@@ -78346,7 +78688,7 @@
         <v>46245</v>
       </c>
       <c r="C1454" s="55" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="D1454" s="55">
         <v>131696657</v>
@@ -78438,7 +78780,7 @@
         <v>46245</v>
       </c>
       <c r="C1456" s="55" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="D1456" s="55">
         <v>95648925</v>
@@ -78484,7 +78826,7 @@
         <v>46245</v>
       </c>
       <c r="C1457" s="55" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="D1457" s="55">
         <v>88678181</v>
@@ -78532,10 +78874,10 @@
         <v>46245</v>
       </c>
       <c r="C1458" s="55" t="s">
+        <v>2197</v>
+      </c>
+      <c r="D1458" s="55" t="s">
         <v>2198</v>
-      </c>
-      <c r="D1458" s="55" t="s">
-        <v>2199</v>
       </c>
       <c r="E1458" s="12" t="s">
         <v>21</v>
@@ -78578,7 +78920,7 @@
         <v>46245</v>
       </c>
       <c r="C1459" s="55" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="D1459" s="55">
         <v>96801698</v>
@@ -78624,7 +78966,7 @@
         <v>46245</v>
       </c>
       <c r="C1460" s="55" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="D1460" s="38"/>
       <c r="E1460" s="12" t="s">
@@ -78664,7 +79006,7 @@
         <v>46245</v>
       </c>
       <c r="C1461" s="55" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="D1461" s="55">
         <v>95307809</v>
@@ -78708,7 +79050,7 @@
         <v>46245</v>
       </c>
       <c r="C1462" s="55" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="D1462" s="55">
         <v>98434725</v>
@@ -78756,10 +79098,10 @@
         <v>46245</v>
       </c>
       <c r="C1463" s="55" t="s">
+        <v>2203</v>
+      </c>
+      <c r="D1463" s="55" t="s">
         <v>2204</v>
-      </c>
-      <c r="D1463" s="55" t="s">
-        <v>2205</v>
       </c>
       <c r="E1463" s="12" t="s">
         <v>21</v>
@@ -78771,7 +79113,7 @@
         <v>57994</v>
       </c>
       <c r="H1463" s="66" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="I1463" s="22" t="s">
         <v>563</v>
@@ -78784,7 +79126,7 @@
       </c>
       <c r="L1463" s="18"/>
       <c r="M1463" s="21" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="N1463" s="54">
         <v>976</v>
@@ -78807,7 +79149,7 @@
         <v>752</v>
       </c>
       <c r="D1464" s="55" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="E1464" s="12" t="s">
         <v>21</v>
@@ -78883,7 +79225,7 @@
         <v>46245</v>
       </c>
       <c r="P1465" s="49" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="Q1465" s="18"/>
       <c r="R1465" s="20" t="s">
@@ -78898,7 +79240,7 @@
         <v>46245</v>
       </c>
       <c r="C1466" s="55" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="D1466" s="55">
         <v>20806662</v>
@@ -78931,7 +79273,7 @@
         <v>46245</v>
       </c>
       <c r="P1466" s="49" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="Q1466" s="18"/>
       <c r="R1466" s="20" t="s">
@@ -78946,7 +79288,7 @@
         <v>46245</v>
       </c>
       <c r="C1467" s="55" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="D1467" s="55">
         <v>7888654</v>
@@ -78979,7 +79321,7 @@
         <v>46245</v>
       </c>
       <c r="P1467" s="49" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="Q1467" s="18"/>
       <c r="R1467" s="20" t="s">
@@ -78997,7 +79339,7 @@
         <v>1737</v>
       </c>
       <c r="D1468" s="55" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="E1468" s="12" t="s">
         <v>21</v>
@@ -79091,7 +79433,7 @@
         <v>56</v>
       </c>
       <c r="D1470" s="55" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="E1470" s="12" t="s">
         <v>21</v>
@@ -79111,10 +79453,12 @@
       <c r="J1470" s="15" t="s">
         <v>1028</v>
       </c>
-      <c r="K1470" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1470" s="18"/>
+      <c r="K1470" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1470" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1470" s="18"/>
       <c r="N1470" s="54">
         <v>997</v>
@@ -79178,7 +79522,7 @@
         <v>46245</v>
       </c>
       <c r="C1472" s="55" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="D1472" s="55">
         <v>19245071</v>
@@ -79222,7 +79566,7 @@
         <v>46245</v>
       </c>
       <c r="C1473" s="55" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="D1473" s="55">
         <v>10433156</v>
@@ -79266,7 +79610,7 @@
         <v>46245</v>
       </c>
       <c r="C1474" s="55" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="D1474" s="55">
         <v>12478178</v>
@@ -79310,7 +79654,7 @@
         <v>46245</v>
       </c>
       <c r="C1475" s="55" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="D1475" s="55">
         <v>11687823</v>
@@ -79404,7 +79748,7 @@
         <v>46245</v>
       </c>
       <c r="C1477" s="55" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="D1477" s="55">
         <v>69667313</v>
@@ -79578,7 +79922,7 @@
         <v>46245</v>
       </c>
       <c r="C1481" s="55" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="D1481" s="55">
         <v>111323605</v>
@@ -79620,10 +79964,10 @@
         <v>46245</v>
       </c>
       <c r="C1482" s="55" t="s">
+        <v>2219</v>
+      </c>
+      <c r="D1482" s="55" t="s">
         <v>2220</v>
-      </c>
-      <c r="D1482" s="55" t="s">
-        <v>2221</v>
       </c>
       <c r="E1482" s="12" t="s">
         <v>21</v>
@@ -79698,7 +80042,7 @@
         <v>46245</v>
       </c>
       <c r="C1484" s="55" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="D1484" s="38"/>
       <c r="E1484" s="12" t="s">
@@ -79738,7 +80082,7 @@
         <v>46245</v>
       </c>
       <c r="C1485" s="55" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="D1485" s="55">
         <v>134784363</v>
@@ -79822,7 +80166,7 @@
         <v>46245</v>
       </c>
       <c r="C1487" s="55" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="D1487" s="55">
         <v>1265278</v>
@@ -79866,7 +80210,7 @@
         <v>46245</v>
       </c>
       <c r="C1488" s="55" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="D1488" s="55">
         <v>14841106</v>
@@ -79910,7 +80254,7 @@
         <v>46245</v>
       </c>
       <c r="C1489" s="55" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="D1489" s="55">
         <v>14317685</v>
@@ -79957,7 +80301,7 @@
         <v>1149</v>
       </c>
       <c r="D1490" s="55" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="E1490" s="12" t="s">
         <v>21</v>
@@ -80002,10 +80346,10 @@
         <v>46245</v>
       </c>
       <c r="C1491" s="55" t="s">
+        <v>2227</v>
+      </c>
+      <c r="D1491" s="55" t="s">
         <v>2228</v>
-      </c>
-      <c r="D1491" s="55" t="s">
-        <v>2229</v>
       </c>
       <c r="E1491" s="12" t="s">
         <v>21</v>
@@ -80052,10 +80396,10 @@
         <v>46245</v>
       </c>
       <c r="C1492" s="55" t="s">
+        <v>2229</v>
+      </c>
+      <c r="D1492" s="55" t="s">
         <v>2230</v>
-      </c>
-      <c r="D1492" s="55" t="s">
-        <v>2231</v>
       </c>
       <c r="E1492" s="12" t="s">
         <v>21</v>
@@ -80105,7 +80449,7 @@
         <v>632</v>
       </c>
       <c r="D1493" s="55" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="E1493" s="12" t="s">
         <v>21</v>
@@ -80152,10 +80496,10 @@
         <v>46245</v>
       </c>
       <c r="C1494" s="55" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D1494" s="55" t="s">
         <v>2233</v>
-      </c>
-      <c r="D1494" s="55" t="s">
-        <v>2234</v>
       </c>
       <c r="E1494" s="12" t="s">
         <v>21</v>
@@ -80200,10 +80544,10 @@
         <v>46245</v>
       </c>
       <c r="C1495" s="55" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D1495" s="55" t="s">
         <v>2235</v>
-      </c>
-      <c r="D1495" s="55" t="s">
-        <v>2236</v>
       </c>
       <c r="E1495" s="12" t="s">
         <v>21</v>
@@ -80248,10 +80592,10 @@
         <v>46245</v>
       </c>
       <c r="C1496" s="55" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="D1496" s="55" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="E1496" s="12" t="s">
         <v>21</v>
@@ -80294,10 +80638,10 @@
         <v>46245</v>
       </c>
       <c r="C1497" s="55" t="s">
+        <v>2237</v>
+      </c>
+      <c r="D1497" s="55" t="s">
         <v>2238</v>
-      </c>
-      <c r="D1497" s="55" t="s">
-        <v>2239</v>
       </c>
       <c r="E1497" s="12" t="s">
         <v>21</v>
@@ -80340,7 +80684,7 @@
         <v>46245</v>
       </c>
       <c r="C1498" s="55" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="D1498" s="55">
         <v>17052525</v>
@@ -80384,10 +80728,10 @@
         <v>46245</v>
       </c>
       <c r="C1499" s="55" t="s">
+        <v>2240</v>
+      </c>
+      <c r="D1499" s="55" t="s">
         <v>2241</v>
-      </c>
-      <c r="D1499" s="55" t="s">
-        <v>2242</v>
       </c>
       <c r="E1499" s="12" t="s">
         <v>21</v>
@@ -80437,7 +80781,7 @@
         <v>1737</v>
       </c>
       <c r="D1500" s="55" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="E1500" s="12" t="s">
         <v>21</v>
@@ -80484,7 +80828,7 @@
         <v>46245</v>
       </c>
       <c r="C1501" s="55" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="D1501" s="55">
         <v>68793586</v>
@@ -80508,7 +80852,7 @@
       </c>
       <c r="L1501" s="18"/>
       <c r="M1501" s="21" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="N1501" s="40"/>
       <c r="O1501" s="18"/>
@@ -80526,7 +80870,7 @@
         <v>46245</v>
       </c>
       <c r="C1502" s="55" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="D1502" s="55">
         <v>108899597</v>
@@ -80575,7 +80919,7 @@
         <v>1977</v>
       </c>
       <c r="D1503" s="55" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="E1503" s="12" t="s">
         <v>21</v>
@@ -80595,10 +80939,12 @@
       <c r="J1503" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="K1503" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1503" s="18"/>
+      <c r="K1503" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1503" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1503" s="16" t="s">
         <v>1994</v>
       </c>
@@ -80620,10 +80966,10 @@
         <v>46246</v>
       </c>
       <c r="C1504" s="55" t="s">
+        <v>2265</v>
+      </c>
+      <c r="D1504" s="55" t="s">
         <v>2266</v>
-      </c>
-      <c r="D1504" s="55" t="s">
-        <v>2267</v>
       </c>
       <c r="E1504" s="12" t="s">
         <v>21</v>
@@ -80668,10 +81014,10 @@
         <v>46246</v>
       </c>
       <c r="C1505" s="55" t="s">
+        <v>2267</v>
+      </c>
+      <c r="D1505" s="55" t="s">
         <v>2268</v>
-      </c>
-      <c r="D1505" s="55" t="s">
-        <v>2269</v>
       </c>
       <c r="E1505" s="12" t="s">
         <v>21</v>
@@ -80712,10 +81058,10 @@
         <v>46246</v>
       </c>
       <c r="C1506" s="55" t="s">
+        <v>2269</v>
+      </c>
+      <c r="D1506" s="55" t="s">
         <v>2270</v>
-      </c>
-      <c r="D1506" s="55" t="s">
-        <v>2271</v>
       </c>
       <c r="E1506" s="12" t="s">
         <v>21</v>
@@ -80758,10 +81104,10 @@
         <v>46246</v>
       </c>
       <c r="C1507" s="55" t="s">
+        <v>2271</v>
+      </c>
+      <c r="D1507" s="55" t="s">
         <v>2272</v>
-      </c>
-      <c r="D1507" s="55" t="s">
-        <v>2273</v>
       </c>
       <c r="E1507" s="12" t="s">
         <v>21</v>
@@ -80804,10 +81150,10 @@
         <v>46246</v>
       </c>
       <c r="C1508" s="55" t="s">
+        <v>2273</v>
+      </c>
+      <c r="D1508" s="55" t="s">
         <v>2274</v>
-      </c>
-      <c r="D1508" s="55" t="s">
-        <v>2275</v>
       </c>
       <c r="E1508" s="12" t="s">
         <v>21</v>
@@ -80850,10 +81196,10 @@
         <v>46246</v>
       </c>
       <c r="C1509" s="55" t="s">
+        <v>2275</v>
+      </c>
+      <c r="D1509" s="55" t="s">
         <v>2276</v>
-      </c>
-      <c r="D1509" s="55" t="s">
-        <v>2277</v>
       </c>
       <c r="E1509" s="12" t="s">
         <v>21</v>
@@ -80896,10 +81242,10 @@
         <v>46246</v>
       </c>
       <c r="C1510" s="55" t="s">
+        <v>2277</v>
+      </c>
+      <c r="D1510" s="55" t="s">
         <v>2278</v>
-      </c>
-      <c r="D1510" s="55" t="s">
-        <v>2279</v>
       </c>
       <c r="E1510" s="12" t="s">
         <v>21</v>
@@ -80911,7 +81257,7 @@
         <v>40197</v>
       </c>
       <c r="H1510" s="66" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="I1510" s="15" t="s">
         <v>123</v>
@@ -80945,7 +81291,7 @@
         <v>1843</v>
       </c>
       <c r="D1511" s="55" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="E1511" s="12" t="s">
         <v>21</v>
@@ -80974,7 +81320,7 @@
       <c r="O1511" s="18"/>
       <c r="P1511" s="18"/>
       <c r="Q1511" s="15" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="R1511" s="22" t="s">
         <v>131</v>
@@ -80988,10 +81334,10 @@
         <v>46246</v>
       </c>
       <c r="C1512" s="55" t="s">
+        <v>2282</v>
+      </c>
+      <c r="D1512" s="55" t="s">
         <v>2283</v>
-      </c>
-      <c r="D1512" s="55" t="s">
-        <v>2284</v>
       </c>
       <c r="E1512" s="12" t="s">
         <v>21</v>
@@ -81016,7 +81362,9 @@
       </c>
       <c r="L1512" s="18"/>
       <c r="M1512" s="18"/>
-      <c r="N1512" s="40"/>
+      <c r="N1512" s="54">
+        <v>1097</v>
+      </c>
       <c r="O1512" s="18"/>
       <c r="P1512" s="18"/>
       <c r="Q1512" s="15">
@@ -81034,10 +81382,10 @@
         <v>46246</v>
       </c>
       <c r="C1513" s="55" t="s">
+        <v>2284</v>
+      </c>
+      <c r="D1513" s="55" t="s">
         <v>2285</v>
-      </c>
-      <c r="D1513" s="55" t="s">
-        <v>2286</v>
       </c>
       <c r="E1513" s="12" t="s">
         <v>21</v>
@@ -81049,7 +81397,7 @@
         <v>19555</v>
       </c>
       <c r="H1513" s="66" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="I1513" s="15" t="s">
         <v>123</v>
@@ -81080,10 +81428,10 @@
         <v>46246</v>
       </c>
       <c r="C1514" s="66" t="s">
+        <v>2287</v>
+      </c>
+      <c r="D1514" s="55" t="s">
         <v>2288</v>
-      </c>
-      <c r="D1514" s="55" t="s">
-        <v>2289</v>
       </c>
       <c r="E1514" s="12" t="s">
         <v>21</v>
@@ -81108,7 +81456,9 @@
       </c>
       <c r="L1514" s="18"/>
       <c r="M1514" s="18"/>
-      <c r="N1514" s="40"/>
+      <c r="N1514" s="54">
+        <v>1100</v>
+      </c>
       <c r="O1514" s="18"/>
       <c r="P1514" s="18"/>
       <c r="Q1514" s="15">
@@ -81126,10 +81476,10 @@
         <v>46246</v>
       </c>
       <c r="C1515" s="66" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D1515" s="55" t="s">
         <v>2290</v>
-      </c>
-      <c r="D1515" s="55" t="s">
-        <v>2291</v>
       </c>
       <c r="E1515" s="12" t="s">
         <v>21</v>
@@ -81172,10 +81522,10 @@
         <v>46246</v>
       </c>
       <c r="C1516" s="66" t="s">
+        <v>2291</v>
+      </c>
+      <c r="D1516" s="55" t="s">
         <v>2292</v>
-      </c>
-      <c r="D1516" s="55" t="s">
-        <v>2293</v>
       </c>
       <c r="E1516" s="12" t="s">
         <v>21</v>
@@ -81193,7 +81543,7 @@
         <v>123</v>
       </c>
       <c r="J1516" s="15" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="K1516" s="17" t="s">
         <v>12</v>
@@ -81218,10 +81568,10 @@
         <v>46246</v>
       </c>
       <c r="C1517" s="66" t="s">
+        <v>2293</v>
+      </c>
+      <c r="D1517" s="55" t="s">
         <v>2294</v>
-      </c>
-      <c r="D1517" s="55" t="s">
-        <v>2295</v>
       </c>
       <c r="E1517" s="30" t="s">
         <v>119</v>
@@ -81262,10 +81612,10 @@
         <v>46246</v>
       </c>
       <c r="C1518" s="66" t="s">
+        <v>2295</v>
+      </c>
+      <c r="D1518" s="55" t="s">
         <v>2296</v>
-      </c>
-      <c r="D1518" s="55" t="s">
-        <v>2297</v>
       </c>
       <c r="E1518" s="30" t="s">
         <v>119</v>
@@ -81306,10 +81656,10 @@
         <v>46246</v>
       </c>
       <c r="C1519" s="66" t="s">
+        <v>2297</v>
+      </c>
+      <c r="D1519" s="55" t="s">
         <v>2298</v>
-      </c>
-      <c r="D1519" s="55" t="s">
-        <v>2299</v>
       </c>
       <c r="E1519" s="30" t="s">
         <v>119</v>
@@ -81350,10 +81700,10 @@
         <v>46246</v>
       </c>
       <c r="C1520" s="66" t="s">
+        <v>2299</v>
+      </c>
+      <c r="D1520" s="55" t="s">
         <v>2300</v>
-      </c>
-      <c r="D1520" s="55" t="s">
-        <v>2301</v>
       </c>
       <c r="E1520" s="12" t="s">
         <v>21</v>
@@ -81392,7 +81742,7 @@
         <v>46246</v>
       </c>
       <c r="C1521" s="66" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="D1521" s="55">
         <v>1962714</v>
@@ -81436,10 +81786,10 @@
         <v>46246</v>
       </c>
       <c r="C1522" s="66" t="s">
+        <v>2302</v>
+      </c>
+      <c r="D1522" s="55" t="s">
         <v>2303</v>
-      </c>
-      <c r="D1522" s="55" t="s">
-        <v>2304</v>
       </c>
       <c r="E1522" s="12" t="s">
         <v>21</v>
@@ -81451,7 +81801,7 @@
         <v>45528</v>
       </c>
       <c r="H1522" s="66" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="I1522" s="22" t="s">
         <v>563</v>
@@ -81464,7 +81814,7 @@
       </c>
       <c r="L1522" s="18"/>
       <c r="M1522" s="21" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="N1522" s="54">
         <v>71</v>
@@ -81484,10 +81834,10 @@
         <v>46246</v>
       </c>
       <c r="C1523" s="66" t="s">
+        <v>2305</v>
+      </c>
+      <c r="D1523" s="55" t="s">
         <v>2306</v>
-      </c>
-      <c r="D1523" s="55" t="s">
-        <v>2307</v>
       </c>
       <c r="E1523" s="12" t="s">
         <v>21</v>
@@ -81532,10 +81882,10 @@
         <v>46246</v>
       </c>
       <c r="C1524" s="66" t="s">
+        <v>2307</v>
+      </c>
+      <c r="D1524" s="55" t="s">
         <v>2308</v>
-      </c>
-      <c r="D1524" s="55" t="s">
-        <v>2309</v>
       </c>
       <c r="E1524" s="12" t="s">
         <v>21</v>
@@ -81580,10 +81930,10 @@
         <v>46246</v>
       </c>
       <c r="C1525" s="66" t="s">
+        <v>2309</v>
+      </c>
+      <c r="D1525" s="55" t="s">
         <v>2310</v>
-      </c>
-      <c r="D1525" s="55" t="s">
-        <v>2311</v>
       </c>
       <c r="E1525" s="12" t="s">
         <v>21</v>
@@ -81631,7 +81981,7 @@
         <v>27</v>
       </c>
       <c r="D1526" s="55" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="E1526" s="12" t="s">
         <v>21</v>
@@ -81674,7 +82024,7 @@
         <v>46246</v>
       </c>
       <c r="C1527" s="66" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="D1527" s="55">
         <v>103251586</v>
@@ -81762,7 +82112,7 @@
         <v>46246</v>
       </c>
       <c r="C1529" s="55" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="D1529" s="55">
         <v>137879144</v>
@@ -81808,7 +82158,7 @@
         <v>46246</v>
       </c>
       <c r="C1530" s="55" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="D1530" s="55">
         <v>74621634</v>
@@ -81823,7 +82173,7 @@
         <v>3791</v>
       </c>
       <c r="H1530" s="66" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="I1530" s="22" t="s">
         <v>563</v>
@@ -81854,7 +82204,7 @@
         <v>46246</v>
       </c>
       <c r="C1531" s="55" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="D1531" s="55">
         <v>90961365</v>
@@ -81869,7 +82219,7 @@
         <v>4676</v>
       </c>
       <c r="H1531" s="66" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="I1531" s="22" t="s">
         <v>563</v>
@@ -81946,7 +82296,7 @@
         <v>46246</v>
       </c>
       <c r="C1533" s="55" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="D1533" s="55">
         <v>89666661</v>
@@ -81990,10 +82340,10 @@
         <v>46246</v>
       </c>
       <c r="C1534" s="55" t="s">
+        <v>2319</v>
+      </c>
+      <c r="D1534" s="55" t="s">
         <v>2320</v>
-      </c>
-      <c r="D1534" s="55" t="s">
-        <v>2321</v>
       </c>
       <c r="E1534" s="12" t="s">
         <v>21</v>
@@ -82082,7 +82432,7 @@
         <v>46246</v>
       </c>
       <c r="C1536" s="81" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="D1536" s="80">
         <v>79883496</v>
@@ -82106,7 +82456,7 @@
       </c>
       <c r="L1536" s="18"/>
       <c r="M1536" s="21" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="N1536" s="40"/>
       <c r="O1536" s="18"/>
@@ -82124,7 +82474,7 @@
         <v>46246</v>
       </c>
       <c r="C1537" s="81" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="D1537" s="80">
         <v>102096078</v>
@@ -82148,7 +82498,7 @@
       </c>
       <c r="L1537" s="18"/>
       <c r="M1537" s="21" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="N1537" s="40"/>
       <c r="O1537" s="18"/>
@@ -82166,7 +82516,7 @@
         <v>46246</v>
       </c>
       <c r="C1538" s="81" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="D1538" s="80">
         <v>10417783</v>
@@ -82190,7 +82540,7 @@
       </c>
       <c r="L1538" s="18"/>
       <c r="M1538" s="21" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="N1538" s="40"/>
       <c r="O1538" s="18"/>
@@ -82208,7 +82558,7 @@
         <v>46246</v>
       </c>
       <c r="C1539" s="81" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
       <c r="D1539" s="80">
         <v>24946408</v>
@@ -82232,7 +82582,7 @@
       </c>
       <c r="L1539" s="18"/>
       <c r="M1539" s="21" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="N1539" s="40"/>
       <c r="O1539" s="18"/>
@@ -82250,7 +82600,7 @@
         <v>46246</v>
       </c>
       <c r="C1540" s="81" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
       <c r="D1540" s="80">
         <v>23008711</v>
@@ -82274,7 +82624,7 @@
       </c>
       <c r="L1540" s="18"/>
       <c r="M1540" s="21" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="N1540" s="40"/>
       <c r="O1540" s="18"/>
@@ -82292,7 +82642,7 @@
         <v>46246</v>
       </c>
       <c r="C1541" s="81" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="D1541" s="80">
         <v>20790727</v>
@@ -82316,7 +82666,7 @@
       </c>
       <c r="L1541" s="18"/>
       <c r="M1541" s="21" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="N1541" s="40"/>
       <c r="O1541" s="18"/>
@@ -82358,7 +82708,7 @@
       </c>
       <c r="L1542" s="18"/>
       <c r="M1542" s="21" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="N1542" s="40"/>
       <c r="O1542" s="18"/>
@@ -82376,10 +82726,10 @@
         <v>46246</v>
       </c>
       <c r="C1543" s="55" t="s">
+        <v>2329</v>
+      </c>
+      <c r="D1543" s="55" t="s">
         <v>2330</v>
-      </c>
-      <c r="D1543" s="55" t="s">
-        <v>2331</v>
       </c>
       <c r="E1543" s="12" t="s">
         <v>21</v>
@@ -82391,7 +82741,7 @@
         <v>68798</v>
       </c>
       <c r="H1543" s="66" t="s">
-        <v>2332</v>
+        <v>2331</v>
       </c>
       <c r="I1543" s="16" t="s">
         <v>10</v>
@@ -82422,10 +82772,10 @@
         <v>46246</v>
       </c>
       <c r="C1544" s="23" t="s">
+        <v>2332</v>
+      </c>
+      <c r="D1544" s="11" t="s">
         <v>2333</v>
-      </c>
-      <c r="D1544" s="11" t="s">
-        <v>2334</v>
       </c>
       <c r="E1544" s="12" t="s">
         <v>21</v>
@@ -82468,10 +82818,10 @@
         <v>46246</v>
       </c>
       <c r="C1545" s="23" t="s">
+        <v>2334</v>
+      </c>
+      <c r="D1545" s="11" t="s">
         <v>2335</v>
-      </c>
-      <c r="D1545" s="11" t="s">
-        <v>2336</v>
       </c>
       <c r="E1545" s="12" t="s">
         <v>21</v>
@@ -82514,10 +82864,10 @@
         <v>46246</v>
       </c>
       <c r="C1546" s="23" t="s">
+        <v>2336</v>
+      </c>
+      <c r="D1546" s="11" t="s">
         <v>2337</v>
-      </c>
-      <c r="D1546" s="11" t="s">
-        <v>2338</v>
       </c>
       <c r="E1546" s="12" t="s">
         <v>21</v>
@@ -82560,10 +82910,10 @@
         <v>46246</v>
       </c>
       <c r="C1547" s="23" t="s">
+        <v>2338</v>
+      </c>
+      <c r="D1547" s="11" t="s">
         <v>2339</v>
-      </c>
-      <c r="D1547" s="11" t="s">
-        <v>2340</v>
       </c>
       <c r="E1547" s="12" t="s">
         <v>21</v>
@@ -82606,10 +82956,10 @@
         <v>46246</v>
       </c>
       <c r="C1548" s="23" t="s">
+        <v>2340</v>
+      </c>
+      <c r="D1548" s="11" t="s">
         <v>2341</v>
-      </c>
-      <c r="D1548" s="11" t="s">
-        <v>2342</v>
       </c>
       <c r="E1548" s="12" t="s">
         <v>21</v>
@@ -82621,7 +82971,7 @@
         <v>90498</v>
       </c>
       <c r="H1548" s="15" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="I1548" s="16" t="s">
         <v>10</v>
@@ -82652,10 +83002,10 @@
         <v>46246</v>
       </c>
       <c r="C1549" s="23" t="s">
+        <v>2343</v>
+      </c>
+      <c r="D1549" s="11" t="s">
         <v>2344</v>
-      </c>
-      <c r="D1549" s="11" t="s">
-        <v>2345</v>
       </c>
       <c r="E1549" s="12" t="s">
         <v>21</v>
@@ -82667,7 +83017,7 @@
         <v>38386</v>
       </c>
       <c r="H1549" s="15" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="I1549" s="16" t="s">
         <v>10</v>
@@ -82698,7 +83048,7 @@
         <v>46246</v>
       </c>
       <c r="C1550" s="23" t="s">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="D1550" s="11">
         <v>70549062</v>
@@ -82742,7 +83092,7 @@
         <v>46246</v>
       </c>
       <c r="C1551" s="23" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="D1551" s="11">
         <v>128261398</v>
@@ -82788,10 +83138,10 @@
         <v>46246</v>
       </c>
       <c r="C1552" s="23" t="s">
+        <v>2352</v>
+      </c>
+      <c r="D1552" s="11" t="s">
         <v>2353</v>
-      </c>
-      <c r="D1552" s="11" t="s">
-        <v>2354</v>
       </c>
       <c r="E1552" s="46" t="s">
         <v>21</v>
@@ -82834,7 +83184,7 @@
         <v>46246</v>
       </c>
       <c r="C1553" s="23" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="D1553" s="11">
         <v>128847714</v>
@@ -82882,7 +83232,7 @@
         <v>46246</v>
       </c>
       <c r="C1554" s="23" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="D1554" s="11">
         <v>127551765</v>
@@ -82933,7 +83283,7 @@
         <v>580</v>
       </c>
       <c r="D1555" s="11" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="E1555" s="46" t="s">
         <v>21</v>
@@ -82978,10 +83328,10 @@
         <v>46246</v>
       </c>
       <c r="C1556" s="23" t="s">
+        <v>2357</v>
+      </c>
+      <c r="D1556" s="11" t="s">
         <v>2358</v>
-      </c>
-      <c r="D1556" s="11" t="s">
-        <v>2359</v>
       </c>
       <c r="E1556" s="46" t="s">
         <v>21</v>
@@ -83024,7 +83374,7 @@
         <v>46246</v>
       </c>
       <c r="C1557" s="23" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="D1557" s="11">
         <v>70409518</v>
@@ -83036,7 +83386,7 @@
         <v>122</v>
       </c>
       <c r="G1557" s="14" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
       <c r="H1557" s="15">
         <v>570</v>
@@ -83070,7 +83420,7 @@
         <v>46246</v>
       </c>
       <c r="C1558" s="23" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="D1558" s="11">
         <v>69523302</v>
@@ -83082,7 +83432,7 @@
         <v>122</v>
       </c>
       <c r="G1558" s="14" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="H1558" s="15">
         <v>8695</v>
@@ -83160,7 +83510,7 @@
         <v>46246</v>
       </c>
       <c r="C1560" s="23" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="D1560" s="11">
         <v>131870609</v>
@@ -83204,7 +83554,7 @@
         <v>46246</v>
       </c>
       <c r="C1561" s="23" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="D1561" s="11">
         <v>106137387</v>
@@ -83248,7 +83598,7 @@
         <v>46246</v>
       </c>
       <c r="C1562" s="23" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="D1562" s="11">
         <v>5563107</v>
@@ -83292,10 +83642,10 @@
         <v>46246</v>
       </c>
       <c r="C1563" s="23" t="s">
+        <v>2367</v>
+      </c>
+      <c r="D1563" s="11" t="s">
         <v>2368</v>
-      </c>
-      <c r="D1563" s="11" t="s">
-        <v>2369</v>
       </c>
       <c r="E1563" s="46" t="s">
         <v>21</v>
@@ -83338,7 +83688,7 @@
         <v>46246</v>
       </c>
       <c r="C1564" s="23" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="D1564" s="11">
         <v>1733157</v>
@@ -83382,7 +83732,7 @@
         <v>46246</v>
       </c>
       <c r="C1565" s="23" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="D1565" s="11">
         <v>15584447</v>
@@ -83426,7 +83776,7 @@
         <v>46246</v>
       </c>
       <c r="C1566" s="23" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="D1566" s="11">
         <v>13076492</v>
@@ -83470,7 +83820,7 @@
         <v>46246</v>
       </c>
       <c r="C1567" s="23" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="D1567" s="11">
         <v>8359317</v>
@@ -83514,10 +83864,10 @@
         <v>46246</v>
       </c>
       <c r="C1568" s="23" t="s">
+        <v>2373</v>
+      </c>
+      <c r="D1568" s="11" t="s">
         <v>2374</v>
-      </c>
-      <c r="D1568" s="11" t="s">
-        <v>2375</v>
       </c>
       <c r="E1568" s="46" t="s">
         <v>21</v>
@@ -83562,7 +83912,7 @@
         <v>46246</v>
       </c>
       <c r="C1569" s="23" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="D1569" s="11">
         <v>131424936</v>
@@ -83608,7 +83958,7 @@
         <v>46246</v>
       </c>
       <c r="C1570" s="23" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="D1570" s="11">
         <v>111354348</v>
@@ -83654,7 +84004,7 @@
         <v>46246</v>
       </c>
       <c r="C1571" s="23" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="D1571" s="11">
         <v>5249316</v>
@@ -83666,7 +84016,7 @@
         <v>122</v>
       </c>
       <c r="G1571" s="14" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="H1571" s="15">
         <v>4292</v>
@@ -83701,7 +84051,7 @@
         <v>1087</v>
       </c>
       <c r="D1572" s="11" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="E1572" s="46" t="s">
         <v>21</v>
@@ -83742,10 +84092,10 @@
         <v>46246</v>
       </c>
       <c r="C1573" s="23" t="s">
+        <v>2380</v>
+      </c>
+      <c r="D1573" s="11" t="s">
         <v>2381</v>
-      </c>
-      <c r="D1573" s="11" t="s">
-        <v>2382</v>
       </c>
       <c r="E1573" s="46" t="s">
         <v>21</v>
@@ -83786,10 +84136,10 @@
         <v>46246</v>
       </c>
       <c r="C1574" s="23" t="s">
+        <v>2382</v>
+      </c>
+      <c r="D1574" s="11" t="s">
         <v>2383</v>
-      </c>
-      <c r="D1574" s="11" t="s">
-        <v>2384</v>
       </c>
       <c r="E1574" s="46" t="s">
         <v>21</v>
@@ -83830,10 +84180,10 @@
         <v>46246</v>
       </c>
       <c r="C1575" s="23" t="s">
+        <v>2384</v>
+      </c>
+      <c r="D1575" s="11" t="s">
         <v>2385</v>
-      </c>
-      <c r="D1575" s="11" t="s">
-        <v>2386</v>
       </c>
       <c r="E1575" s="46" t="s">
         <v>21</v>
@@ -83845,7 +84195,7 @@
         <v>92178</v>
       </c>
       <c r="H1575" s="15" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="I1575" s="16" t="s">
         <v>10</v>
@@ -83874,10 +84224,10 @@
         <v>46246</v>
       </c>
       <c r="C1576" s="23" t="s">
+        <v>2387</v>
+      </c>
+      <c r="D1576" s="11" t="s">
         <v>2388</v>
-      </c>
-      <c r="D1576" s="11" t="s">
-        <v>2389</v>
       </c>
       <c r="E1576" s="46" t="s">
         <v>21</v>
@@ -83918,10 +84268,10 @@
         <v>46246</v>
       </c>
       <c r="C1577" s="23" t="s">
+        <v>2389</v>
+      </c>
+      <c r="D1577" s="11" t="s">
         <v>2390</v>
-      </c>
-      <c r="D1577" s="11" t="s">
-        <v>2391</v>
       </c>
       <c r="E1577" s="44" t="s">
         <v>119</v>
@@ -83962,10 +84312,10 @@
         <v>46246</v>
       </c>
       <c r="C1578" s="23" t="s">
+        <v>2391</v>
+      </c>
+      <c r="D1578" s="11" t="s">
         <v>2392</v>
-      </c>
-      <c r="D1578" s="11" t="s">
-        <v>2393</v>
       </c>
       <c r="E1578" s="44" t="s">
         <v>119</v>
@@ -84006,10 +84356,10 @@
         <v>46246</v>
       </c>
       <c r="C1579" s="23" t="s">
+        <v>2393</v>
+      </c>
+      <c r="D1579" s="11" t="s">
         <v>2394</v>
-      </c>
-      <c r="D1579" s="11" t="s">
-        <v>2395</v>
       </c>
       <c r="E1579" s="44" t="s">
         <v>119</v>
@@ -84053,7 +84403,7 @@
         <v>767</v>
       </c>
       <c r="D1580" s="11" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="E1580" s="46" t="s">
         <v>21</v>
@@ -84082,7 +84432,7 @@
       <c r="O1580" s="18"/>
       <c r="P1580" s="18"/>
       <c r="Q1580" s="11" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="R1580" s="22" t="s">
         <v>131</v>
@@ -84096,10 +84446,10 @@
         <v>46246</v>
       </c>
       <c r="C1581" s="23" t="s">
+        <v>2397</v>
+      </c>
+      <c r="D1581" s="11" t="s">
         <v>2398</v>
-      </c>
-      <c r="D1581" s="11" t="s">
-        <v>2399</v>
       </c>
       <c r="E1581" s="46" t="s">
         <v>21</v>
@@ -84145,7 +84495,7 @@
         <v>1149</v>
       </c>
       <c r="D1582" s="11" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="E1582" s="46" t="s">
         <v>21</v>
@@ -84189,7 +84539,7 @@
         <v>1960</v>
       </c>
       <c r="D1583" s="11" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="E1583" s="46" t="s">
         <v>21</v>
@@ -84230,10 +84580,10 @@
         <v>46247</v>
       </c>
       <c r="C1584" s="23" t="s">
+        <v>2401</v>
+      </c>
+      <c r="D1584" s="11" t="s">
         <v>2402</v>
-      </c>
-      <c r="D1584" s="11" t="s">
-        <v>2403</v>
       </c>
       <c r="E1584" s="44" t="s">
         <v>119</v>
@@ -84274,10 +84624,10 @@
         <v>46247</v>
       </c>
       <c r="C1585" s="23" t="s">
+        <v>2403</v>
+      </c>
+      <c r="D1585" s="11" t="s">
         <v>2404</v>
-      </c>
-      <c r="D1585" s="11" t="s">
-        <v>2405</v>
       </c>
       <c r="E1585" s="46" t="s">
         <v>21</v>
@@ -84289,7 +84639,7 @@
         <v>87355</v>
       </c>
       <c r="H1585" s="15" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="I1585" s="22" t="s">
         <v>563</v>
@@ -84320,10 +84670,10 @@
         <v>46247</v>
       </c>
       <c r="C1586" s="23" t="s">
+        <v>2406</v>
+      </c>
+      <c r="D1586" s="11" t="s">
         <v>2407</v>
-      </c>
-      <c r="D1586" s="11" t="s">
-        <v>2408</v>
       </c>
       <c r="E1586" s="46" t="s">
         <v>21</v>
@@ -84366,7 +84716,7 @@
         <v>46247</v>
       </c>
       <c r="C1587" s="23" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="D1587" s="11">
         <v>71852247</v>
@@ -84412,10 +84762,10 @@
         <v>46247</v>
       </c>
       <c r="C1588" s="23" t="s">
+        <v>2409</v>
+      </c>
+      <c r="D1588" s="11" t="s">
         <v>2410</v>
-      </c>
-      <c r="D1588" s="11" t="s">
-        <v>2411</v>
       </c>
       <c r="E1588" s="46" t="s">
         <v>21</v>
@@ -84458,10 +84808,10 @@
         <v>46247</v>
       </c>
       <c r="C1589" s="23" t="s">
+        <v>2411</v>
+      </c>
+      <c r="D1589" s="11" t="s">
         <v>2412</v>
-      </c>
-      <c r="D1589" s="11" t="s">
-        <v>2413</v>
       </c>
       <c r="E1589" s="46" t="s">
         <v>21</v>
@@ -84502,7 +84852,7 @@
         <v>46247</v>
       </c>
       <c r="C1590" s="23" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
       <c r="D1590" s="11">
         <v>28240626</v>
@@ -84517,7 +84867,7 @@
         <v>3360</v>
       </c>
       <c r="H1590" s="15" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
       <c r="I1590" s="16" t="s">
         <v>10</v>
@@ -84558,10 +84908,10 @@
         <v>122</v>
       </c>
       <c r="G1591" s="83" t="s">
+        <v>2415</v>
+      </c>
+      <c r="H1591" s="15" t="s">
         <v>2416</v>
-      </c>
-      <c r="H1591" s="15" t="s">
-        <v>2417</v>
       </c>
       <c r="I1591" s="16" t="s">
         <v>10</v>
@@ -84577,7 +84927,7 @@
       <c r="N1591" s="40"/>
       <c r="O1591" s="18"/>
       <c r="P1591" s="49" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="Q1591" s="18"/>
       <c r="R1591" s="21" t="s">
@@ -84592,7 +84942,7 @@
         <v>46247</v>
       </c>
       <c r="C1592" s="23" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="D1592" s="11">
         <v>28330063</v>
@@ -84636,7 +84986,7 @@
         <v>46247</v>
       </c>
       <c r="C1593" s="23" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="D1593" s="11">
         <v>27576027</v>
@@ -84680,7 +85030,7 @@
         <v>46247</v>
       </c>
       <c r="C1594" s="23" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="D1594" s="11">
         <v>25014322</v>
@@ -84692,10 +85042,10 @@
         <v>122</v>
       </c>
       <c r="G1594" s="83" t="s">
+        <v>2421</v>
+      </c>
+      <c r="H1594" s="15" t="s">
         <v>2422</v>
-      </c>
-      <c r="H1594" s="15" t="s">
-        <v>2423</v>
       </c>
       <c r="I1594" s="16" t="s">
         <v>10</v>
@@ -84711,7 +85061,7 @@
       <c r="N1594" s="40"/>
       <c r="O1594" s="18"/>
       <c r="P1594" s="49" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="Q1594" s="18"/>
       <c r="R1594" s="21" t="s">
@@ -84726,7 +85076,7 @@
         <v>46247</v>
       </c>
       <c r="C1595" s="23" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="D1595" s="11">
         <v>18533316</v>
@@ -84770,7 +85120,7 @@
         <v>46247</v>
       </c>
       <c r="C1596" s="23" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="D1596" s="11">
         <v>20362741</v>
@@ -84858,7 +85208,7 @@
         <v>46247</v>
       </c>
       <c r="C1598" s="23" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="D1598" s="11">
         <v>20759159</v>
@@ -84902,7 +85252,7 @@
         <v>46247</v>
       </c>
       <c r="C1599" s="23" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="D1599" s="11">
         <v>113229088</v>
@@ -84948,7 +85298,7 @@
         <v>46247</v>
       </c>
       <c r="C1600" s="23" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="D1600" s="11">
         <v>74737721</v>
@@ -84994,7 +85344,7 @@
         <v>46247</v>
       </c>
       <c r="C1601" s="23" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="D1601" s="11">
         <v>6253321</v>
@@ -85006,10 +85356,10 @@
         <v>122</v>
       </c>
       <c r="G1601" s="83" t="s">
+        <v>2429</v>
+      </c>
+      <c r="H1601" s="15" t="s">
         <v>2430</v>
-      </c>
-      <c r="H1601" s="15" t="s">
-        <v>2431</v>
       </c>
       <c r="I1601" s="16" t="s">
         <v>10</v>
@@ -85025,7 +85375,7 @@
       <c r="N1601" s="40"/>
       <c r="O1601" s="18"/>
       <c r="P1601" s="49" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="Q1601" s="18"/>
       <c r="R1601" s="21" t="s">
@@ -85052,10 +85402,10 @@
         <v>122</v>
       </c>
       <c r="G1602" s="83" t="s">
+        <v>2431</v>
+      </c>
+      <c r="H1602" s="15" t="s">
         <v>2432</v>
-      </c>
-      <c r="H1602" s="15" t="s">
-        <v>2433</v>
       </c>
       <c r="I1602" s="16" t="s">
         <v>10</v>
@@ -85071,7 +85421,7 @@
       <c r="N1602" s="40"/>
       <c r="O1602" s="18"/>
       <c r="P1602" s="49" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="Q1602" s="18"/>
       <c r="R1602" s="21" t="s">
@@ -85122,76 +85472,106 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1604" spans="1:18" ht="16.2" thickBot="1">
+    <row r="1604" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1604" s="2">
-        <v>23</v>
-      </c>
-      <c r="B1604" s="18"/>
+        <v>25</v>
+      </c>
+      <c r="B1604" s="10">
+        <v>46247</v>
+      </c>
       <c r="C1604" s="23" t="s">
-        <v>75</v>
+        <v>2433</v>
       </c>
       <c r="D1604" s="11">
-        <v>90508672</v>
-      </c>
-      <c r="E1604" s="18"/>
-      <c r="F1604" s="18"/>
+        <v>22939425</v>
+      </c>
+      <c r="E1604" s="82" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1604" s="47" t="s">
+        <v>122</v>
+      </c>
       <c r="G1604" s="83">
-        <v>5481</v>
+        <v>6579</v>
       </c>
       <c r="H1604" s="15">
-        <v>4694</v>
-      </c>
-      <c r="I1604" s="18"/>
-      <c r="J1604" s="18"/>
-      <c r="K1604" s="18"/>
+        <v>6039</v>
+      </c>
+      <c r="I1604" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1604" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1604" s="60" t="s">
+        <v>1189</v>
+      </c>
       <c r="L1604" s="18"/>
       <c r="M1604" s="18"/>
       <c r="N1604" s="40"/>
       <c r="O1604" s="18"/>
       <c r="P1604" s="18"/>
       <c r="Q1604" s="18"/>
-      <c r="R1604" s="18"/>
-    </row>
-    <row r="1605" spans="1:18" ht="16.2" thickBot="1">
+      <c r="R1604" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1605" s="2">
-        <v>24</v>
-      </c>
-      <c r="B1605" s="18"/>
+        <v>26</v>
+      </c>
+      <c r="B1605" s="10">
+        <v>46247</v>
+      </c>
       <c r="C1605" s="23" t="s">
         <v>2434</v>
       </c>
       <c r="D1605" s="11">
-        <v>137967312</v>
-      </c>
-      <c r="E1605" s="18"/>
-      <c r="F1605" s="18"/>
+        <v>14995818</v>
+      </c>
+      <c r="E1605" s="82" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1605" s="47" t="s">
+        <v>122</v>
+      </c>
       <c r="G1605" s="83">
-        <v>2761</v>
+        <v>9739</v>
       </c>
       <c r="H1605" s="15">
-        <v>3745</v>
-      </c>
-      <c r="I1605" s="18"/>
-      <c r="J1605" s="18"/>
-      <c r="K1605" s="18"/>
+        <v>4751</v>
+      </c>
+      <c r="I1605" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1605" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1605" s="60" t="s">
+        <v>1189</v>
+      </c>
       <c r="L1605" s="18"/>
       <c r="M1605" s="18"/>
       <c r="N1605" s="40"/>
       <c r="O1605" s="18"/>
       <c r="P1605" s="18"/>
       <c r="Q1605" s="18"/>
-      <c r="R1605" s="18"/>
+      <c r="R1605" s="21" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="1606" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1606" s="2">
-        <v>25</v>
-      </c>
-      <c r="B1606" s="18"/>
+        <v>27</v>
+      </c>
+      <c r="B1606" s="10">
+        <v>46247</v>
+      </c>
       <c r="C1606" s="23" t="s">
         <v>2435</v>
       </c>
       <c r="D1606" s="11">
-        <v>22939425</v>
+        <v>12989448</v>
       </c>
       <c r="E1606" s="82" t="s">
         <v>121</v>
@@ -85200,10 +85580,10 @@
         <v>122</v>
       </c>
       <c r="G1606" s="83">
-        <v>6579</v>
+        <v>1553</v>
       </c>
       <c r="H1606" s="15">
-        <v>6039</v>
+        <v>1292</v>
       </c>
       <c r="I1606" s="16" t="s">
         <v>10</v>
@@ -85226,74 +85606,80 @@
     </row>
     <row r="1607" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1607" s="2">
-        <v>26</v>
-      </c>
-      <c r="B1607" s="18"/>
+        <v>28</v>
+      </c>
+      <c r="B1607" s="10">
+        <v>46247</v>
+      </c>
       <c r="C1607" s="23" t="s">
         <v>2436</v>
       </c>
       <c r="D1607" s="11">
-        <v>14995818</v>
-      </c>
-      <c r="E1607" s="82" t="s">
-        <v>121</v>
+        <v>108564836</v>
+      </c>
+      <c r="E1607" s="46" t="s">
+        <v>21</v>
       </c>
       <c r="F1607" s="47" t="s">
         <v>122</v>
       </c>
       <c r="G1607" s="83">
-        <v>9739</v>
-      </c>
-      <c r="H1607" s="15">
-        <v>4751</v>
-      </c>
-      <c r="I1607" s="16" t="s">
-        <v>10</v>
+        <v>8698</v>
+      </c>
+      <c r="H1607" s="15" t="s">
+        <v>2437</v>
+      </c>
+      <c r="I1607" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="J1607" s="15" t="s">
-        <v>319</v>
-      </c>
-      <c r="K1607" s="60" t="s">
-        <v>1189</v>
+        <v>174</v>
+      </c>
+      <c r="K1607" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1607" s="18"/>
       <c r="M1607" s="18"/>
       <c r="N1607" s="40"/>
       <c r="O1607" s="18"/>
       <c r="P1607" s="18"/>
-      <c r="Q1607" s="18"/>
-      <c r="R1607" s="21" t="s">
-        <v>14</v>
+      <c r="Q1607" s="11">
+        <v>98518183</v>
+      </c>
+      <c r="R1607" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="1608" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1608" s="2">
-        <v>27</v>
-      </c>
-      <c r="B1608" s="18"/>
-      <c r="C1608" s="23" t="s">
-        <v>2437</v>
+        <v>29</v>
+      </c>
+      <c r="B1608" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1608" s="11" t="s">
+        <v>328</v>
       </c>
       <c r="D1608" s="11">
-        <v>12989448</v>
-      </c>
-      <c r="E1608" s="82" t="s">
+        <v>8852091</v>
+      </c>
+      <c r="E1608" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="F1608" s="47" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1608" s="83">
-        <v>1553</v>
+      <c r="F1608" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1608" s="14">
+        <v>8116</v>
       </c>
       <c r="H1608" s="15">
-        <v>1292</v>
-      </c>
-      <c r="I1608" s="16" t="s">
-        <v>10</v>
+        <v>9291</v>
+      </c>
+      <c r="I1608" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="J1608" s="15" t="s">
-        <v>319</v>
+        <v>2438</v>
       </c>
       <c r="K1608" s="60" t="s">
         <v>1189</v>
@@ -85304,86 +85690,84 @@
       <c r="O1608" s="18"/>
       <c r="P1608" s="18"/>
       <c r="Q1608" s="18"/>
-      <c r="R1608" s="21" t="s">
-        <v>14</v>
+      <c r="R1608" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="1609" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1609" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1609" s="10">
         <v>46247</v>
       </c>
-      <c r="C1609" s="23" t="s">
-        <v>2438</v>
+      <c r="C1609" s="11" t="s">
+        <v>2439</v>
       </c>
       <c r="D1609" s="11">
-        <v>108564836</v>
-      </c>
-      <c r="E1609" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1609" s="47" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1609" s="83">
-        <v>8698</v>
-      </c>
-      <c r="H1609" s="15" t="s">
-        <v>2439</v>
+        <v>9018657</v>
+      </c>
+      <c r="E1609" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1609" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1609" s="14">
+        <v>609</v>
+      </c>
+      <c r="H1609" s="15">
+        <v>3428</v>
       </c>
       <c r="I1609" s="15" t="s">
         <v>123</v>
       </c>
       <c r="J1609" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="K1609" s="17" t="s">
-        <v>12</v>
+        <v>2438</v>
+      </c>
+      <c r="K1609" s="60" t="s">
+        <v>1189</v>
       </c>
       <c r="L1609" s="18"/>
       <c r="M1609" s="18"/>
       <c r="N1609" s="40"/>
       <c r="O1609" s="18"/>
       <c r="P1609" s="18"/>
-      <c r="Q1609" s="11">
-        <v>98518183</v>
-      </c>
+      <c r="Q1609" s="18"/>
       <c r="R1609" s="22" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="1610" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1610" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B1610" s="10">
         <v>46247</v>
       </c>
-      <c r="C1610" s="11" t="s">
-        <v>328</v>
+      <c r="C1610" s="23" t="s">
+        <v>2440</v>
       </c>
       <c r="D1610" s="11">
-        <v>8852091</v>
-      </c>
-      <c r="E1610" s="37" t="s">
-        <v>121</v>
+        <v>102928204</v>
+      </c>
+      <c r="E1610" s="46" t="s">
+        <v>21</v>
       </c>
       <c r="F1610" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="G1610" s="14">
-        <v>8116</v>
-      </c>
-      <c r="H1610" s="15">
-        <v>9291</v>
+      <c r="G1610" s="83">
+        <v>9599</v>
+      </c>
+      <c r="H1610" s="15" t="s">
+        <v>2441</v>
       </c>
       <c r="I1610" s="15" t="s">
         <v>123</v>
       </c>
       <c r="J1610" s="15" t="s">
-        <v>2440</v>
+        <v>2438</v>
       </c>
       <c r="K1610" s="60" t="s">
         <v>1189</v>
@@ -85398,36 +85782,36 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1611" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1611" spans="1:18" ht="24.6" thickBot="1">
       <c r="A1611" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B1611" s="10">
         <v>46247</v>
       </c>
-      <c r="C1611" s="11" t="s">
-        <v>2441</v>
-      </c>
-      <c r="D1611" s="11">
-        <v>9018657</v>
-      </c>
-      <c r="E1611" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="F1611" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1611" s="14">
-        <v>609</v>
-      </c>
-      <c r="H1611" s="15">
-        <v>3428</v>
-      </c>
-      <c r="I1611" s="15" t="s">
-        <v>123</v>
+      <c r="C1611" s="23" t="s">
+        <v>601</v>
+      </c>
+      <c r="D1611" s="11" t="s">
+        <v>602</v>
+      </c>
+      <c r="E1611" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1611" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1611" s="83" t="s">
+        <v>2442</v>
+      </c>
+      <c r="H1611" s="15" t="s">
+        <v>2443</v>
+      </c>
+      <c r="I1611" s="22" t="s">
+        <v>563</v>
       </c>
       <c r="J1611" s="15" t="s">
-        <v>2440</v>
+        <v>1672</v>
       </c>
       <c r="K1611" s="60" t="s">
         <v>1189</v>
@@ -85442,36 +85826,36 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1612" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1612" spans="1:18" ht="24.6" thickBot="1">
       <c r="A1612" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B1612" s="10">
         <v>46247</v>
       </c>
       <c r="C1612" s="23" t="s">
-        <v>2442</v>
+        <v>2444</v>
       </c>
       <c r="D1612" s="11">
-        <v>102928204</v>
+        <v>137351063</v>
       </c>
       <c r="E1612" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="F1612" s="16" t="s">
+      <c r="F1612" s="47" t="s">
         <v>122</v>
       </c>
       <c r="G1612" s="83">
-        <v>9599</v>
-      </c>
-      <c r="H1612" s="15" t="s">
-        <v>2443</v>
-      </c>
-      <c r="I1612" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="J1612" s="15" t="s">
-        <v>2440</v>
+        <v>2346</v>
+      </c>
+      <c r="H1612" s="15">
+        <v>547</v>
+      </c>
+      <c r="I1612" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1612" s="51" t="s">
+        <v>776</v>
       </c>
       <c r="K1612" s="60" t="s">
         <v>1189</v>
@@ -85488,34 +85872,34 @@
     </row>
     <row r="1613" spans="1:18" ht="24.6" thickBot="1">
       <c r="A1613" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B1613" s="10">
         <v>46247</v>
       </c>
       <c r="C1613" s="23" t="s">
-        <v>601</v>
-      </c>
-      <c r="D1613" s="11" t="s">
-        <v>602</v>
+        <v>2445</v>
+      </c>
+      <c r="D1613" s="11">
+        <v>135147837</v>
       </c>
       <c r="E1613" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="F1613" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1613" s="83" t="s">
-        <v>2444</v>
-      </c>
-      <c r="H1613" s="15" t="s">
-        <v>2445</v>
-      </c>
-      <c r="I1613" s="22" t="s">
-        <v>563</v>
-      </c>
-      <c r="J1613" s="15" t="s">
-        <v>1672</v>
+      <c r="F1613" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1613" s="83">
+        <v>6164</v>
+      </c>
+      <c r="H1613" s="15">
+        <v>9375</v>
+      </c>
+      <c r="I1613" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1613" s="51" t="s">
+        <v>776</v>
       </c>
       <c r="K1613" s="60" t="s">
         <v>1189</v>
@@ -85532,16 +85916,16 @@
     </row>
     <row r="1614" spans="1:18" ht="24.6" thickBot="1">
       <c r="A1614" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B1614" s="10">
         <v>46247</v>
       </c>
       <c r="C1614" s="23" t="s">
-        <v>2446</v>
+        <v>989</v>
       </c>
       <c r="D1614" s="11">
-        <v>137351063</v>
+        <v>106990709</v>
       </c>
       <c r="E1614" s="46" t="s">
         <v>21</v>
@@ -85550,10 +85934,10 @@
         <v>122</v>
       </c>
       <c r="G1614" s="83">
-        <v>2346</v>
+        <v>5429</v>
       </c>
       <c r="H1614" s="15">
-        <v>547</v>
+        <v>4828</v>
       </c>
       <c r="I1614" s="16" t="s">
         <v>10</v>
@@ -85576,16 +85960,16 @@
     </row>
     <row r="1615" spans="1:18" ht="24.6" thickBot="1">
       <c r="A1615" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1615" s="10">
         <v>46247</v>
       </c>
       <c r="C1615" s="23" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="D1615" s="11">
-        <v>135147837</v>
+        <v>131776588</v>
       </c>
       <c r="E1615" s="46" t="s">
         <v>21</v>
@@ -85594,11 +85978,9 @@
         <v>122</v>
       </c>
       <c r="G1615" s="83">
-        <v>6164</v>
-      </c>
-      <c r="H1615" s="15">
-        <v>9375</v>
-      </c>
+        <v>8934</v>
+      </c>
+      <c r="H1615" s="18"/>
       <c r="I1615" s="16" t="s">
         <v>10</v>
       </c>
@@ -85620,16 +86002,16 @@
     </row>
     <row r="1616" spans="1:18" ht="24.6" thickBot="1">
       <c r="A1616" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1616" s="10">
         <v>46247</v>
       </c>
       <c r="C1616" s="23" t="s">
-        <v>989</v>
+        <v>2489</v>
       </c>
       <c r="D1616" s="11">
-        <v>106990709</v>
+        <v>106002067</v>
       </c>
       <c r="E1616" s="46" t="s">
         <v>21</v>
@@ -85638,10 +86020,10 @@
         <v>122</v>
       </c>
       <c r="G1616" s="83">
-        <v>5429</v>
+        <v>301</v>
       </c>
       <c r="H1616" s="15">
-        <v>4828</v>
+        <v>8384</v>
       </c>
       <c r="I1616" s="16" t="s">
         <v>10</v>
@@ -85664,16 +86046,16 @@
     </row>
     <row r="1617" spans="1:18" ht="24.6" thickBot="1">
       <c r="A1617" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B1617" s="10">
         <v>46247</v>
       </c>
       <c r="C1617" s="23" t="s">
-        <v>2448</v>
+        <v>2490</v>
       </c>
       <c r="D1617" s="11">
-        <v>131776588</v>
+        <v>107885351</v>
       </c>
       <c r="E1617" s="46" t="s">
         <v>21</v>
@@ -85682,14 +86064,16 @@
         <v>122</v>
       </c>
       <c r="G1617" s="83">
-        <v>8934</v>
-      </c>
-      <c r="H1617" s="18"/>
-      <c r="I1617" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1617" s="51" t="s">
-        <v>776</v>
+        <v>7981</v>
+      </c>
+      <c r="H1617" s="15">
+        <v>4420</v>
+      </c>
+      <c r="I1617" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1617" s="50" t="s">
+        <v>564</v>
       </c>
       <c r="K1617" s="60" t="s">
         <v>1189</v>
@@ -85704,56 +86088,62 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1618" spans="1:18" ht="27" thickBot="1">
+    <row r="1618" spans="1:18" ht="24.6" thickBot="1">
       <c r="A1618" s="2">
-        <v>42</v>
-      </c>
-      <c r="B1618" s="18"/>
+        <v>39</v>
+      </c>
+      <c r="B1618" s="10">
+        <v>46247</v>
+      </c>
       <c r="C1618" s="23" t="s">
-        <v>2449</v>
-      </c>
-      <c r="D1618" s="11" t="s">
-        <v>2450</v>
+        <v>1387</v>
+      </c>
+      <c r="D1618" s="11">
+        <v>122181529</v>
       </c>
       <c r="E1618" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="F1618" s="45" t="s">
-        <v>22</v>
+      <c r="F1618" s="47" t="s">
+        <v>122</v>
       </c>
       <c r="G1618" s="83">
-        <v>87989</v>
+        <v>806</v>
       </c>
       <c r="H1618" s="15">
-        <v>24193</v>
-      </c>
-      <c r="I1618" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1618" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1618" s="18"/>
+        <v>6723</v>
+      </c>
+      <c r="I1618" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1618" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1618" s="60" t="s">
+        <v>1189</v>
+      </c>
       <c r="L1618" s="18"/>
       <c r="M1618" s="18"/>
       <c r="N1618" s="40"/>
       <c r="O1618" s="18"/>
       <c r="P1618" s="18"/>
       <c r="Q1618" s="18"/>
-      <c r="R1618" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1619" spans="1:18" ht="24.6" thickBot="1">
+      <c r="R1618" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:18" ht="27" thickBot="1">
       <c r="A1619" s="2">
-        <v>43</v>
-      </c>
-      <c r="B1619" s="18"/>
+        <v>40</v>
+      </c>
+      <c r="B1619" s="10">
+        <v>46247</v>
+      </c>
       <c r="C1619" s="23" t="s">
-        <v>2451</v>
+        <v>2447</v>
       </c>
       <c r="D1619" s="11" t="s">
-        <v>2452</v>
+        <v>2448</v>
       </c>
       <c r="E1619" s="46" t="s">
         <v>21</v>
@@ -85762,10 +86152,10 @@
         <v>22</v>
       </c>
       <c r="G1619" s="83">
-        <v>84815</v>
+        <v>87989</v>
       </c>
       <c r="H1619" s="15">
-        <v>41009</v>
+        <v>24193</v>
       </c>
       <c r="I1619" s="16" t="s">
         <v>10</v>
@@ -85784,6 +86174,92 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1620" spans="1:18" ht="24.6" thickBot="1">
+      <c r="A1620" s="2">
+        <v>41</v>
+      </c>
+      <c r="B1620" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1620" s="23" t="s">
+        <v>2449</v>
+      </c>
+      <c r="D1620" s="11" t="s">
+        <v>2450</v>
+      </c>
+      <c r="E1620" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1620" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1620" s="83">
+        <v>84815</v>
+      </c>
+      <c r="H1620" s="15">
+        <v>41009</v>
+      </c>
+      <c r="I1620" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1620" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1620" s="18"/>
+      <c r="L1620" s="18"/>
+      <c r="M1620" s="18"/>
+      <c r="N1620" s="40"/>
+      <c r="O1620" s="18"/>
+      <c r="P1620" s="18"/>
+      <c r="Q1620" s="18"/>
+      <c r="R1620" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:18" ht="24.6" thickBot="1">
+      <c r="A1621" s="2">
+        <v>42</v>
+      </c>
+      <c r="B1621" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1621" s="23" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D1621" s="11">
+        <v>124529941</v>
+      </c>
+      <c r="E1621" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1621" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1621" s="83">
+        <v>4208</v>
+      </c>
+      <c r="H1621" s="15">
+        <v>8251</v>
+      </c>
+      <c r="I1621" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1621" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1621" s="30" t="s">
+        <v>1596</v>
+      </c>
+      <c r="L1621" s="18"/>
+      <c r="M1621" s="18"/>
+      <c r="N1621" s="40"/>
+      <c r="O1621" s="18"/>
+      <c r="P1621" s="18"/>
+      <c r="Q1621" s="18"/>
+      <c r="R1621" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D829FCC-ABB9-44EB-B09B-0DC5750C1E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E863FB-421D-4B93-8546-9D964DFB0765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12154" uniqueCount="2491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12154" uniqueCount="2492">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -7511,6 +7511,9 @@
   </si>
   <si>
     <t>JAMIL AMJAD</t>
+  </si>
+  <si>
+    <t>SUHAI</t>
   </si>
 </sst>
 </file>
@@ -86257,7 +86260,7 @@
       <c r="P1621" s="18"/>
       <c r="Q1621" s="18"/>
       <c r="R1621" s="22" t="s">
-        <v>131</v>
+        <v>2491</v>
       </c>
     </row>
   </sheetData>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E863FB-421D-4B93-8546-9D964DFB0765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A007545-8AEC-43C4-A13D-8ECF8CD186DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
+    <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12154" uniqueCount="2492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12215" uniqueCount="2505">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -7513,7 +7513,46 @@
     <t>JAMIL AMJAD</t>
   </si>
   <si>
-    <t>SUHAI</t>
+    <t>12/8/</t>
+  </si>
+  <si>
+    <t>GHULAM</t>
+  </si>
+  <si>
+    <t>YASSER JUMA MUBARAK AL SOOLI</t>
+  </si>
+  <si>
+    <t>4544*</t>
+  </si>
+  <si>
+    <t>9197*</t>
+  </si>
+  <si>
+    <t>MUSAAB JUMA</t>
+  </si>
+  <si>
+    <t>SALIM SAID NASSER AL-HARRASI</t>
+  </si>
+  <si>
+    <t>608*</t>
+  </si>
+  <si>
+    <t>1515*</t>
+  </si>
+  <si>
+    <t>ABDUL AZIZ MOHAMMAD</t>
+  </si>
+  <si>
+    <t>7391*</t>
+  </si>
+  <si>
+    <t>8519*</t>
+  </si>
+  <si>
+    <t>FARIS SALIM HAMOOD</t>
+  </si>
+  <si>
+    <t>OBAID SAID SALIM</t>
   </si>
 </sst>
 </file>
@@ -7921,7 +7960,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8170,6 +8209,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8486,7 +8528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1621"/>
+  <dimension ref="A1:R1630"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -9496,7 +9538,9 @@
       <c r="N20" s="54">
         <v>737</v>
       </c>
-      <c r="O20" s="18"/>
+      <c r="O20" s="53">
+        <v>46246</v>
+      </c>
       <c r="P20" s="18"/>
       <c r="Q20" s="18"/>
       <c r="R20" s="20" t="s">
@@ -9644,7 +9688,9 @@
       <c r="N23" s="54">
         <v>389</v>
       </c>
-      <c r="O23" s="18"/>
+      <c r="O23" s="53">
+        <v>46246</v>
+      </c>
       <c r="P23" s="18"/>
       <c r="Q23" s="11">
         <v>95694362</v>
@@ -9694,7 +9740,9 @@
       <c r="N24" s="54">
         <v>387</v>
       </c>
-      <c r="O24" s="18"/>
+      <c r="O24" s="53">
+        <v>46246</v>
+      </c>
       <c r="P24" s="18"/>
       <c r="Q24" s="11">
         <v>77324820</v>
@@ -10588,7 +10636,9 @@
       <c r="N42" s="54">
         <v>211</v>
       </c>
-      <c r="O42" s="18"/>
+      <c r="O42" s="53">
+        <v>46246</v>
+      </c>
       <c r="P42" s="18"/>
       <c r="Q42" s="11">
         <v>92131103</v>
@@ -10638,7 +10688,9 @@
       <c r="N43" s="54">
         <v>264</v>
       </c>
-      <c r="O43" s="18"/>
+      <c r="O43" s="53">
+        <v>46246</v>
+      </c>
       <c r="P43" s="18"/>
       <c r="Q43" s="11">
         <v>99421805</v>
@@ -12106,10 +12158,12 @@
       <c r="J73" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="K73" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L73" s="18"/>
+      <c r="K73" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L73" s="53">
+        <v>46250</v>
+      </c>
       <c r="M73" s="18"/>
       <c r="N73" s="40"/>
       <c r="O73" s="18"/>
@@ -13420,7 +13474,9 @@
       <c r="P100" s="36" t="s">
         <v>331</v>
       </c>
-      <c r="Q100" s="18"/>
+      <c r="Q100" s="84">
+        <v>46246</v>
+      </c>
       <c r="R100" s="21" t="s">
         <v>14</v>
       </c>
@@ -15296,7 +15352,9 @@
       <c r="N137" s="54">
         <v>38</v>
       </c>
-      <c r="O137" s="18"/>
+      <c r="O137" s="53">
+        <v>46246</v>
+      </c>
       <c r="P137" s="18"/>
       <c r="Q137" s="11">
         <v>98581749</v>
@@ -15346,7 +15404,9 @@
       <c r="N138" s="54">
         <v>125</v>
       </c>
-      <c r="O138" s="18"/>
+      <c r="O138" s="53">
+        <v>46246</v>
+      </c>
       <c r="P138" s="18"/>
       <c r="Q138" s="11">
         <v>98202156</v>
@@ -15700,7 +15760,9 @@
       <c r="N145" s="54">
         <v>693</v>
       </c>
-      <c r="O145" s="18"/>
+      <c r="O145" s="53">
+        <v>46246</v>
+      </c>
       <c r="P145" s="18"/>
       <c r="Q145" s="11">
         <v>96004896</v>
@@ -16148,7 +16210,9 @@
       <c r="N154" s="54">
         <v>716</v>
       </c>
-      <c r="O154" s="18"/>
+      <c r="O154" s="53">
+        <v>46246</v>
+      </c>
       <c r="P154" s="18"/>
       <c r="Q154" s="11">
         <v>95823518</v>
@@ -16652,7 +16716,9 @@
       <c r="N164" s="54">
         <v>708</v>
       </c>
-      <c r="O164" s="18"/>
+      <c r="O164" s="53">
+        <v>46246</v>
+      </c>
       <c r="P164" s="18"/>
       <c r="Q164" s="11">
         <v>96170497</v>
@@ -17003,7 +17069,7 @@
         <v>212</v>
       </c>
       <c r="O171" s="53">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="P171" s="18"/>
       <c r="Q171" s="11">
@@ -17250,7 +17316,9 @@
       </c>
       <c r="M176" s="18"/>
       <c r="N176" s="40"/>
-      <c r="O176" s="18"/>
+      <c r="O176" s="53">
+        <v>46246</v>
+      </c>
       <c r="P176" s="18"/>
       <c r="Q176" s="11">
         <v>95734972</v>
@@ -17300,7 +17368,9 @@
       <c r="N177" s="54">
         <v>233</v>
       </c>
-      <c r="O177" s="18"/>
+      <c r="O177" s="53">
+        <v>46246</v>
+      </c>
       <c r="P177" s="18"/>
       <c r="Q177" s="11">
         <v>98054987</v>
@@ -18110,7 +18180,9 @@
       <c r="N194" s="54">
         <v>452</v>
       </c>
-      <c r="O194" s="18"/>
+      <c r="O194" s="53">
+        <v>46246</v>
+      </c>
       <c r="P194" s="18"/>
       <c r="Q194" s="11">
         <v>96907447</v>
@@ -18534,7 +18606,9 @@
       <c r="N203" s="54">
         <v>694</v>
       </c>
-      <c r="O203" s="18"/>
+      <c r="O203" s="53">
+        <v>46246</v>
+      </c>
       <c r="P203" s="18"/>
       <c r="Q203" s="11">
         <v>94919456</v>
@@ -19430,7 +19504,9 @@
       <c r="N221" s="54">
         <v>597</v>
       </c>
-      <c r="O221" s="18"/>
+      <c r="O221" s="53">
+        <v>46246</v>
+      </c>
       <c r="P221" s="18"/>
       <c r="Q221" s="11">
         <v>95451572</v>
@@ -20356,7 +20432,9 @@
       <c r="N241" s="54">
         <v>309</v>
       </c>
-      <c r="O241" s="18"/>
+      <c r="O241" s="53">
+        <v>46246</v>
+      </c>
       <c r="P241" s="18"/>
       <c r="Q241" s="11">
         <v>551713007</v>
@@ -21414,7 +21492,9 @@
       <c r="N263" s="54">
         <v>531</v>
       </c>
-      <c r="O263" s="18"/>
+      <c r="O263" s="53">
+        <v>46246</v>
+      </c>
       <c r="P263" s="18"/>
       <c r="Q263" s="11">
         <v>93953829</v>
@@ -21462,7 +21542,9 @@
       <c r="N264" s="54">
         <v>566</v>
       </c>
-      <c r="O264" s="18"/>
+      <c r="O264" s="53">
+        <v>46246</v>
+      </c>
       <c r="P264" s="18"/>
       <c r="Q264" s="11">
         <v>99649307</v>
@@ -21510,7 +21592,9 @@
       <c r="N265" s="54">
         <v>536</v>
       </c>
-      <c r="O265" s="18"/>
+      <c r="O265" s="53">
+        <v>46246</v>
+      </c>
       <c r="P265" s="18"/>
       <c r="Q265" s="11">
         <v>79046101</v>
@@ -21558,7 +21642,9 @@
       <c r="N266" s="54" t="s">
         <v>2459</v>
       </c>
-      <c r="O266" s="18"/>
+      <c r="O266" s="53">
+        <v>46246</v>
+      </c>
       <c r="P266" s="18"/>
       <c r="Q266" s="11">
         <v>96264258</v>
@@ -22040,7 +22126,9 @@
       <c r="N276" s="54">
         <v>746</v>
       </c>
-      <c r="O276" s="18"/>
+      <c r="O276" s="53">
+        <v>46246</v>
+      </c>
       <c r="P276" s="18"/>
       <c r="Q276" s="18"/>
       <c r="R276" s="22" t="s">
@@ -22088,7 +22176,9 @@
       <c r="N277" s="54">
         <v>747</v>
       </c>
-      <c r="O277" s="18"/>
+      <c r="O277" s="53">
+        <v>46246</v>
+      </c>
       <c r="P277" s="18"/>
       <c r="Q277" s="18"/>
       <c r="R277" s="22" t="s">
@@ -22134,7 +22224,9 @@
       <c r="N278" s="54">
         <v>750</v>
       </c>
-      <c r="O278" s="18"/>
+      <c r="O278" s="53">
+        <v>46246</v>
+      </c>
       <c r="P278" s="18"/>
       <c r="Q278" s="18"/>
       <c r="R278" s="22" t="s">
@@ -22180,7 +22272,9 @@
       <c r="N279" s="54">
         <v>749</v>
       </c>
-      <c r="O279" s="18"/>
+      <c r="O279" s="53">
+        <v>46246</v>
+      </c>
       <c r="P279" s="18"/>
       <c r="Q279" s="18"/>
       <c r="R279" s="22" t="s">
@@ -22226,7 +22320,9 @@
       <c r="N280" s="54">
         <v>752</v>
       </c>
-      <c r="O280" s="18"/>
+      <c r="O280" s="53">
+        <v>46246</v>
+      </c>
       <c r="P280" s="18"/>
       <c r="Q280" s="18"/>
       <c r="R280" s="22" t="s">
@@ -22274,7 +22370,9 @@
       <c r="N281" s="76" t="s">
         <v>2250</v>
       </c>
-      <c r="O281" s="18"/>
+      <c r="O281" s="53">
+        <v>46246</v>
+      </c>
       <c r="P281" s="18"/>
       <c r="Q281" s="18"/>
       <c r="R281" s="22" t="s">
@@ -22322,7 +22420,9 @@
       <c r="N282" s="54">
         <v>738</v>
       </c>
-      <c r="O282" s="18"/>
+      <c r="O282" s="53">
+        <v>46246</v>
+      </c>
       <c r="P282" s="18"/>
       <c r="Q282" s="18"/>
       <c r="R282" s="22" t="s">
@@ -22370,7 +22470,9 @@
       <c r="N283" s="76" t="s">
         <v>2251</v>
       </c>
-      <c r="O283" s="18"/>
+      <c r="O283" s="53">
+        <v>46246</v>
+      </c>
       <c r="P283" s="18"/>
       <c r="Q283" s="18"/>
       <c r="R283" s="22" t="s">
@@ -22418,7 +22520,9 @@
       <c r="N284" s="54">
         <v>739</v>
       </c>
-      <c r="O284" s="18"/>
+      <c r="O284" s="53">
+        <v>46246</v>
+      </c>
       <c r="P284" s="18"/>
       <c r="Q284" s="18"/>
       <c r="R284" s="22" t="s">
@@ -22664,7 +22768,9 @@
       <c r="N289" s="76" t="s">
         <v>2252</v>
       </c>
-      <c r="O289" s="18"/>
+      <c r="O289" s="53">
+        <v>46246</v>
+      </c>
       <c r="P289" s="18"/>
       <c r="Q289" s="18"/>
       <c r="R289" s="22" t="s">
@@ -22954,11 +23060,11 @@
       <c r="J295" s="15" t="s">
         <v>382</v>
       </c>
-      <c r="K295" s="11" t="s">
-        <v>2327</v>
+      <c r="K295" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L295" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M295" s="18"/>
       <c r="N295" s="54">
@@ -23780,7 +23886,9 @@
       <c r="N311" s="54">
         <v>720</v>
       </c>
-      <c r="O311" s="18"/>
+      <c r="O311" s="53">
+        <v>46246</v>
+      </c>
       <c r="P311" s="18"/>
       <c r="Q311" s="11">
         <v>95321343</v>
@@ -23880,7 +23988,9 @@
       <c r="N313" s="54">
         <v>722</v>
       </c>
-      <c r="O313" s="18"/>
+      <c r="O313" s="53">
+        <v>46246</v>
+      </c>
       <c r="P313" s="18"/>
       <c r="Q313" s="11">
         <v>90766013</v>
@@ -23982,7 +24092,9 @@
       <c r="N315" s="54">
         <v>724</v>
       </c>
-      <c r="O315" s="18"/>
+      <c r="O315" s="53">
+        <v>46246</v>
+      </c>
       <c r="P315" s="18"/>
       <c r="Q315" s="11">
         <v>96303751</v>
@@ -24082,7 +24194,9 @@
       <c r="N317" s="54">
         <v>726</v>
       </c>
-      <c r="O317" s="18"/>
+      <c r="O317" s="53">
+        <v>46246</v>
+      </c>
       <c r="P317" s="18"/>
       <c r="Q317" s="11">
         <v>94408241</v>
@@ -24132,7 +24246,9 @@
       <c r="N318" s="76" t="s">
         <v>2111</v>
       </c>
-      <c r="O318" s="18"/>
+      <c r="O318" s="53">
+        <v>46246</v>
+      </c>
       <c r="P318" s="18"/>
       <c r="Q318" s="11">
         <v>95981460</v>
@@ -24286,7 +24402,9 @@
       <c r="N321" s="76" t="s">
         <v>2254</v>
       </c>
-      <c r="O321" s="18"/>
+      <c r="O321" s="53">
+        <v>46246</v>
+      </c>
       <c r="P321" s="18"/>
       <c r="Q321" s="18"/>
       <c r="R321" s="22" t="s">
@@ -24334,7 +24452,9 @@
       <c r="N322" s="76" t="s">
         <v>2255</v>
       </c>
-      <c r="O322" s="18"/>
+      <c r="O322" s="53">
+        <v>46246</v>
+      </c>
       <c r="P322" s="18"/>
       <c r="Q322" s="18"/>
       <c r="R322" s="22" t="s">
@@ -24430,7 +24550,9 @@
       <c r="N324" s="54">
         <v>686</v>
       </c>
-      <c r="O324" s="18"/>
+      <c r="O324" s="53">
+        <v>46246</v>
+      </c>
       <c r="P324" s="18"/>
       <c r="Q324" s="18"/>
       <c r="R324" s="22" t="s">
@@ -24478,7 +24600,9 @@
       <c r="N325" s="76" t="s">
         <v>2256</v>
       </c>
-      <c r="O325" s="18"/>
+      <c r="O325" s="53">
+        <v>46246</v>
+      </c>
       <c r="P325" s="18"/>
       <c r="Q325" s="18"/>
       <c r="R325" s="22" t="s">
@@ -25320,7 +25444,9 @@
       <c r="N343" s="54" t="s">
         <v>2461</v>
       </c>
-      <c r="O343" s="18"/>
+      <c r="O343" s="53">
+        <v>46246</v>
+      </c>
       <c r="P343" s="18"/>
       <c r="Q343" s="11">
         <v>97120936</v>
@@ -25370,7 +25496,9 @@
       <c r="N344" s="54">
         <v>476</v>
       </c>
-      <c r="O344" s="18"/>
+      <c r="O344" s="53">
+        <v>46246</v>
+      </c>
       <c r="P344" s="18"/>
       <c r="Q344" s="11">
         <v>95432591</v>
@@ -25420,7 +25548,9 @@
       <c r="N345" s="54">
         <v>484</v>
       </c>
-      <c r="O345" s="18"/>
+      <c r="O345" s="53">
+        <v>46246</v>
+      </c>
       <c r="P345" s="18"/>
       <c r="Q345" s="11">
         <v>97120936</v>
@@ -25660,7 +25790,9 @@
       <c r="N350" s="54">
         <v>653</v>
       </c>
-      <c r="O350" s="18"/>
+      <c r="O350" s="53">
+        <v>46246</v>
+      </c>
       <c r="P350" s="18"/>
       <c r="Q350" s="18"/>
       <c r="R350" s="22" t="s">
@@ -26860,7 +26992,9 @@
       <c r="N374" s="54">
         <v>364</v>
       </c>
-      <c r="O374" s="18"/>
+      <c r="O374" s="53">
+        <v>46246</v>
+      </c>
       <c r="P374" s="18"/>
       <c r="Q374" s="18"/>
       <c r="R374" s="20" t="s">
@@ -30800,7 +30934,9 @@
       <c r="N454" s="54">
         <v>199</v>
       </c>
-      <c r="O454" s="18"/>
+      <c r="O454" s="53">
+        <v>46247</v>
+      </c>
       <c r="P454" s="18"/>
       <c r="Q454" s="11">
         <v>95781875</v>
@@ -30900,7 +31036,9 @@
       <c r="N456" s="54">
         <v>196</v>
       </c>
-      <c r="O456" s="18"/>
+      <c r="O456" s="53">
+        <v>46246</v>
+      </c>
       <c r="P456" s="18"/>
       <c r="Q456" s="11">
         <v>95781892</v>
@@ -31855,7 +31993,9 @@
       <c r="O476" s="53">
         <v>46244</v>
       </c>
-      <c r="P476" s="18"/>
+      <c r="P476" s="70">
+        <v>46246</v>
+      </c>
       <c r="Q476" s="18"/>
       <c r="R476" s="20" t="s">
         <v>11</v>
@@ -32494,10 +32634,12 @@
       <c r="J490" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K490" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L490" s="18"/>
+      <c r="K490" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L490" s="53">
+        <v>46250</v>
+      </c>
       <c r="M490" s="18"/>
       <c r="N490" s="54">
         <v>629</v>
@@ -32552,7 +32694,9 @@
       <c r="N491" s="54">
         <v>493</v>
       </c>
-      <c r="O491" s="18"/>
+      <c r="O491" s="53">
+        <v>46246</v>
+      </c>
       <c r="P491" s="18"/>
       <c r="Q491" s="11">
         <v>91852979</v>
@@ -32602,7 +32746,9 @@
       <c r="N492" s="54">
         <v>495</v>
       </c>
-      <c r="O492" s="18"/>
+      <c r="O492" s="53">
+        <v>46246</v>
+      </c>
       <c r="P492" s="18"/>
       <c r="Q492" s="11">
         <v>94879541</v>
@@ -32642,8 +32788,8 @@
       <c r="J493" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K493" s="17" t="s">
-        <v>12</v>
+      <c r="K493" s="67" t="s">
+        <v>1285</v>
       </c>
       <c r="L493" s="18"/>
       <c r="M493" s="18"/>
@@ -32698,7 +32844,9 @@
       <c r="N494" s="54">
         <v>499</v>
       </c>
-      <c r="O494" s="18"/>
+      <c r="O494" s="53">
+        <v>46246</v>
+      </c>
       <c r="P494" s="18"/>
       <c r="Q494" s="11">
         <v>98137492</v>
@@ -32738,8 +32886,8 @@
       <c r="J495" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K495" s="17" t="s">
-        <v>12</v>
+      <c r="K495" s="67" t="s">
+        <v>1285</v>
       </c>
       <c r="L495" s="18"/>
       <c r="M495" s="18"/>
@@ -32794,7 +32942,9 @@
       <c r="N496" s="54">
         <v>494</v>
       </c>
-      <c r="O496" s="18"/>
+      <c r="O496" s="53">
+        <v>46246</v>
+      </c>
       <c r="P496" s="18"/>
       <c r="Q496" s="11">
         <v>79487590</v>
@@ -32932,12 +33082,10 @@
       <c r="J499" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K499" s="11" t="s">
-        <v>2327</v>
-      </c>
-      <c r="L499" s="53">
-        <v>46246</v>
-      </c>
+      <c r="K499" s="67" t="s">
+        <v>1285</v>
+      </c>
+      <c r="L499" s="18"/>
       <c r="M499" s="18"/>
       <c r="N499" s="54">
         <v>808</v>
@@ -33038,7 +33186,9 @@
       <c r="N501" s="54">
         <v>496</v>
       </c>
-      <c r="O501" s="18"/>
+      <c r="O501" s="53">
+        <v>46246</v>
+      </c>
       <c r="P501" s="18"/>
       <c r="Q501" s="11">
         <v>71731561</v>
@@ -33128,8 +33278,8 @@
       <c r="J503" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K503" s="11" t="s">
-        <v>2327</v>
+      <c r="K503" s="67" t="s">
+        <v>1285</v>
       </c>
       <c r="L503" s="53">
         <v>46246</v>
@@ -33920,7 +34070,9 @@
       <c r="N519" s="54">
         <v>243</v>
       </c>
-      <c r="O519" s="18"/>
+      <c r="O519" s="53">
+        <v>46246</v>
+      </c>
       <c r="P519" s="18"/>
       <c r="Q519" s="11">
         <v>77297237</v>
@@ -35182,7 +35334,9 @@
       <c r="N545" s="54">
         <v>561</v>
       </c>
-      <c r="O545" s="18"/>
+      <c r="O545" s="53">
+        <v>46246</v>
+      </c>
       <c r="P545" s="18"/>
       <c r="Q545" s="11">
         <v>94609416</v>
@@ -36060,7 +36214,9 @@
       <c r="N563" s="54">
         <v>440</v>
       </c>
-      <c r="O563" s="18"/>
+      <c r="O563" s="53">
+        <v>46246</v>
+      </c>
       <c r="P563" s="18"/>
       <c r="Q563" s="11">
         <v>94535329</v>
@@ -36346,7 +36502,9 @@
       <c r="N569" s="54">
         <v>338</v>
       </c>
-      <c r="O569" s="18"/>
+      <c r="O569" s="53">
+        <v>46246</v>
+      </c>
       <c r="P569" s="18"/>
       <c r="Q569" s="15">
         <v>95670691</v>
@@ -36396,7 +36554,9 @@
       <c r="N570" s="54">
         <v>339</v>
       </c>
-      <c r="O570" s="18"/>
+      <c r="O570" s="53">
+        <v>46246</v>
+      </c>
       <c r="P570" s="18"/>
       <c r="Q570" s="15">
         <v>96892097975</v>
@@ -36446,7 +36606,9 @@
       <c r="N571" s="54">
         <v>340</v>
       </c>
-      <c r="O571" s="18"/>
+      <c r="O571" s="53">
+        <v>46246</v>
+      </c>
       <c r="P571" s="18"/>
       <c r="Q571" s="15">
         <v>76062910</v>
@@ -36746,7 +36908,9 @@
       <c r="N577" s="54">
         <v>128</v>
       </c>
-      <c r="O577" s="18"/>
+      <c r="O577" s="53">
+        <v>46246</v>
+      </c>
       <c r="P577" s="18"/>
       <c r="Q577" s="15">
         <v>75204227</v>
@@ -36796,7 +36960,9 @@
       <c r="N578" s="54" t="s">
         <v>2467</v>
       </c>
-      <c r="O578" s="18"/>
+      <c r="O578" s="53">
+        <v>46246</v>
+      </c>
       <c r="P578" s="18"/>
       <c r="Q578" s="15">
         <v>79404068</v>
@@ -36846,7 +37012,9 @@
       <c r="N579" s="54" t="s">
         <v>2468</v>
       </c>
-      <c r="O579" s="18"/>
+      <c r="O579" s="53">
+        <v>46246</v>
+      </c>
       <c r="P579" s="18"/>
       <c r="Q579" s="15">
         <v>98132836</v>
@@ -37850,7 +38018,9 @@
       <c r="N599" s="54">
         <v>316</v>
       </c>
-      <c r="O599" s="18"/>
+      <c r="O599" s="53">
+        <v>46246</v>
+      </c>
       <c r="P599" s="18"/>
       <c r="Q599" s="15">
         <v>77825073</v>
@@ -38056,7 +38226,9 @@
       <c r="N603" s="54">
         <v>178</v>
       </c>
-      <c r="O603" s="18"/>
+      <c r="O603" s="53">
+        <v>46246</v>
+      </c>
       <c r="P603" s="18"/>
       <c r="Q603" s="15">
         <v>72208912</v>
@@ -38106,7 +38278,9 @@
       <c r="N604" s="54">
         <v>179</v>
       </c>
-      <c r="O604" s="18"/>
+      <c r="O604" s="53">
+        <v>46246</v>
+      </c>
       <c r="P604" s="18"/>
       <c r="Q604" s="15">
         <v>94464618</v>
@@ -38154,7 +38328,9 @@
       <c r="N605" s="54">
         <v>533</v>
       </c>
-      <c r="O605" s="18"/>
+      <c r="O605" s="53">
+        <v>46246</v>
+      </c>
       <c r="P605" s="18"/>
       <c r="Q605" s="15">
         <v>95870468</v>
@@ -38254,7 +38430,9 @@
       <c r="N607" s="54">
         <v>225</v>
       </c>
-      <c r="O607" s="18"/>
+      <c r="O607" s="53">
+        <v>46246</v>
+      </c>
       <c r="P607" s="18"/>
       <c r="Q607" s="15">
         <v>563797821</v>
@@ -38304,7 +38482,9 @@
       <c r="N608" s="54">
         <v>226</v>
       </c>
-      <c r="O608" s="18"/>
+      <c r="O608" s="53">
+        <v>46246</v>
+      </c>
       <c r="P608" s="18"/>
       <c r="Q608" s="15">
         <v>77283364</v>
@@ -38458,7 +38638,9 @@
       <c r="N611" s="54">
         <v>206</v>
       </c>
-      <c r="O611" s="18"/>
+      <c r="O611" s="53">
+        <v>46246</v>
+      </c>
       <c r="P611" s="18"/>
       <c r="Q611" s="15">
         <v>95208325</v>
@@ -38760,7 +38942,9 @@
       <c r="N617" s="54">
         <v>10</v>
       </c>
-      <c r="O617" s="18"/>
+      <c r="O617" s="53">
+        <v>46246</v>
+      </c>
       <c r="P617" s="18"/>
       <c r="Q617" s="15">
         <v>77825127</v>
@@ -38810,7 +38994,9 @@
       <c r="N618" s="54">
         <v>13</v>
       </c>
-      <c r="O618" s="18"/>
+      <c r="O618" s="53">
+        <v>46246</v>
+      </c>
       <c r="P618" s="18"/>
       <c r="Q618" s="15">
         <v>527167527</v>
@@ -38860,7 +39046,9 @@
       <c r="N619" s="54">
         <v>11</v>
       </c>
-      <c r="O619" s="18"/>
+      <c r="O619" s="53">
+        <v>46246</v>
+      </c>
       <c r="P619" s="18"/>
       <c r="Q619" s="15">
         <v>523787624</v>
@@ -38910,7 +39098,9 @@
       <c r="N620" s="54">
         <v>12</v>
       </c>
-      <c r="O620" s="18"/>
+      <c r="O620" s="53">
+        <v>46246</v>
+      </c>
       <c r="P620" s="18"/>
       <c r="Q620" s="15">
         <v>503911434</v>
@@ -39834,7 +40024,9 @@
       <c r="N639" s="54" t="s">
         <v>2471</v>
       </c>
-      <c r="O639" s="18"/>
+      <c r="O639" s="53">
+        <v>46246</v>
+      </c>
       <c r="P639" s="18"/>
       <c r="Q639" s="15">
         <v>79602894</v>
@@ -39884,7 +40076,9 @@
       <c r="N640" s="54" t="s">
         <v>2472</v>
       </c>
-      <c r="O640" s="18"/>
+      <c r="O640" s="53">
+        <v>46246</v>
+      </c>
       <c r="P640" s="18"/>
       <c r="Q640" s="15" t="s">
         <v>811</v>
@@ -40030,7 +40224,9 @@
       <c r="N643" s="54" t="s">
         <v>2473</v>
       </c>
-      <c r="O643" s="18"/>
+      <c r="O643" s="53">
+        <v>46246</v>
+      </c>
       <c r="P643" s="18"/>
       <c r="Q643" s="15">
         <v>97856786</v>
@@ -40468,7 +40664,9 @@
       <c r="N652" s="54" t="s">
         <v>2474</v>
       </c>
-      <c r="O652" s="18"/>
+      <c r="O652" s="53">
+        <v>46246</v>
+      </c>
       <c r="P652" s="18"/>
       <c r="Q652" s="15">
         <v>79400053</v>
@@ -40568,7 +40766,9 @@
       <c r="N654" s="54" t="s">
         <v>2475</v>
       </c>
-      <c r="O654" s="18"/>
+      <c r="O654" s="53">
+        <v>46246</v>
+      </c>
       <c r="P654" s="18"/>
       <c r="Q654" s="15">
         <v>99650350</v>
@@ -40665,7 +40865,7 @@
         <v>46250</v>
       </c>
       <c r="M656" s="18"/>
-      <c r="N656" s="54" t="s">
+      <c r="N656" s="76" t="s">
         <v>2476</v>
       </c>
       <c r="O656" s="18"/>
@@ -41572,7 +41772,9 @@
       <c r="N675" s="54">
         <v>577</v>
       </c>
-      <c r="O675" s="18"/>
+      <c r="O675" s="53">
+        <v>46246</v>
+      </c>
       <c r="P675" s="18"/>
       <c r="Q675" s="11">
         <v>95635586</v>
@@ -42112,7 +42314,9 @@
       <c r="N686" s="54" t="s">
         <v>2478</v>
       </c>
-      <c r="O686" s="18"/>
+      <c r="O686" s="53">
+        <v>46246</v>
+      </c>
       <c r="P686" s="18"/>
       <c r="Q686" s="11">
         <v>96341510</v>
@@ -42160,7 +42364,9 @@
       <c r="N687" s="54">
         <v>713</v>
       </c>
-      <c r="O687" s="18"/>
+      <c r="O687" s="53">
+        <v>46246</v>
+      </c>
       <c r="P687" s="18"/>
       <c r="Q687" s="11">
         <v>96049215</v>
@@ -42438,7 +42644,9 @@
       <c r="N693" s="54">
         <v>712</v>
       </c>
-      <c r="O693" s="18"/>
+      <c r="O693" s="53">
+        <v>46246</v>
+      </c>
       <c r="P693" s="18"/>
       <c r="Q693" s="11">
         <v>99424853</v>
@@ -42682,7 +42890,9 @@
       <c r="P698" s="36" t="s">
         <v>1171</v>
       </c>
-      <c r="Q698" s="18"/>
+      <c r="Q698" s="84">
+        <v>46246</v>
+      </c>
       <c r="R698" s="21" t="s">
         <v>14</v>
       </c>
@@ -42916,7 +43126,9 @@
       <c r="N703" s="54">
         <v>521</v>
       </c>
-      <c r="O703" s="18"/>
+      <c r="O703" s="53">
+        <v>46246</v>
+      </c>
       <c r="P703" s="18"/>
       <c r="Q703" s="15">
         <v>75175379</v>
@@ -42966,7 +43178,9 @@
       <c r="N704" s="54">
         <v>519</v>
       </c>
-      <c r="O704" s="18"/>
+      <c r="O704" s="53">
+        <v>46246</v>
+      </c>
       <c r="P704" s="18"/>
       <c r="Q704" s="15">
         <v>528112551</v>
@@ -43062,7 +43276,9 @@
       <c r="N706" s="54">
         <v>436</v>
       </c>
-      <c r="O706" s="18"/>
+      <c r="O706" s="53">
+        <v>46246</v>
+      </c>
       <c r="P706" s="18"/>
       <c r="Q706" s="15" t="s">
         <v>1036</v>
@@ -43158,7 +43374,9 @@
       <c r="N708" s="54">
         <v>524</v>
       </c>
-      <c r="O708" s="18"/>
+      <c r="O708" s="53">
+        <v>46246</v>
+      </c>
       <c r="P708" s="18"/>
       <c r="Q708" s="15">
         <v>96875175379</v>
@@ -43350,7 +43568,9 @@
       <c r="N712" s="54">
         <v>469</v>
       </c>
-      <c r="O712" s="18"/>
+      <c r="O712" s="53">
+        <v>46246</v>
+      </c>
       <c r="P712" s="18"/>
       <c r="Q712" s="15">
         <v>93825952</v>
@@ -43400,7 +43620,9 @@
       <c r="N713" s="54">
         <v>278</v>
       </c>
-      <c r="O713" s="18"/>
+      <c r="O713" s="53">
+        <v>46246</v>
+      </c>
       <c r="P713" s="18"/>
       <c r="Q713" s="15">
         <v>94063423</v>
@@ -43590,7 +43812,9 @@
       <c r="N717" s="54">
         <v>311</v>
       </c>
-      <c r="O717" s="18"/>
+      <c r="O717" s="53">
+        <v>46246</v>
+      </c>
       <c r="P717" s="18"/>
       <c r="Q717" s="18"/>
       <c r="R717" s="22" t="s">
@@ -43638,7 +43862,9 @@
       <c r="N718" s="54">
         <v>312</v>
       </c>
-      <c r="O718" s="18"/>
+      <c r="O718" s="53">
+        <v>46246</v>
+      </c>
       <c r="P718" s="18"/>
       <c r="Q718" s="18"/>
       <c r="R718" s="22" t="s">
@@ -43686,7 +43912,9 @@
       <c r="N719" s="54">
         <v>648</v>
       </c>
-      <c r="O719" s="18"/>
+      <c r="O719" s="53">
+        <v>46246</v>
+      </c>
       <c r="P719" s="18"/>
       <c r="Q719" s="18"/>
       <c r="R719" s="22" t="s">
@@ -43732,7 +43960,9 @@
       </c>
       <c r="M720" s="18"/>
       <c r="N720" s="40"/>
-      <c r="O720" s="18"/>
+      <c r="O720" s="53">
+        <v>46246</v>
+      </c>
       <c r="P720" s="18"/>
       <c r="Q720" s="18"/>
       <c r="R720" s="22" t="s">
@@ -43822,7 +44052,9 @@
       <c r="L722" s="18"/>
       <c r="M722" s="18"/>
       <c r="N722" s="40"/>
-      <c r="O722" s="18"/>
+      <c r="O722" s="53">
+        <v>46246</v>
+      </c>
       <c r="P722" s="18"/>
       <c r="Q722" s="18"/>
       <c r="R722" s="22" t="s">
@@ -43868,7 +44100,9 @@
       </c>
       <c r="M723" s="18"/>
       <c r="N723" s="40"/>
-      <c r="O723" s="18"/>
+      <c r="O723" s="53">
+        <v>46246</v>
+      </c>
       <c r="P723" s="18"/>
       <c r="Q723" s="18"/>
       <c r="R723" s="22" t="s">
@@ -44688,7 +44922,9 @@
       <c r="N739" s="54">
         <v>317</v>
       </c>
-      <c r="O739" s="18"/>
+      <c r="O739" s="53">
+        <v>46246</v>
+      </c>
       <c r="P739" s="18"/>
       <c r="Q739" s="15">
         <v>95637364</v>
@@ -44882,7 +45118,9 @@
       <c r="N743" s="54">
         <v>406</v>
       </c>
-      <c r="O743" s="18"/>
+      <c r="O743" s="53">
+        <v>46246</v>
+      </c>
       <c r="P743" s="18"/>
       <c r="Q743" s="15">
         <v>79068151</v>
@@ -46116,7 +46354,9 @@
       </c>
       <c r="M768" s="18"/>
       <c r="N768" s="40"/>
-      <c r="O768" s="18"/>
+      <c r="O768" s="53">
+        <v>46246</v>
+      </c>
       <c r="P768" s="63" t="s">
         <v>1208</v>
       </c>
@@ -46368,7 +46608,9 @@
       <c r="P773" s="63" t="s">
         <v>1217</v>
       </c>
-      <c r="Q773" s="18"/>
+      <c r="Q773" s="84">
+        <v>46246</v>
+      </c>
       <c r="R773" s="20" t="s">
         <v>11</v>
       </c>
@@ -47146,7 +47388,9 @@
       <c r="N789" s="54">
         <v>260</v>
       </c>
-      <c r="O789" s="18"/>
+      <c r="O789" s="53">
+        <v>46246</v>
+      </c>
       <c r="P789" s="18"/>
       <c r="Q789" s="11">
         <v>98036001</v>
@@ -47196,7 +47440,9 @@
       <c r="N790" s="54">
         <v>252</v>
       </c>
-      <c r="O790" s="18"/>
+      <c r="O790" s="53">
+        <v>46246</v>
+      </c>
       <c r="P790" s="18"/>
       <c r="Q790" s="11">
         <v>78259563</v>
@@ -47246,7 +47492,9 @@
       <c r="N791" s="54">
         <v>254</v>
       </c>
-      <c r="O791" s="18"/>
+      <c r="O791" s="53">
+        <v>46246</v>
+      </c>
       <c r="P791" s="18"/>
       <c r="Q791" s="11">
         <v>77238933</v>
@@ -47296,7 +47544,9 @@
       <c r="N792" s="54">
         <v>253</v>
       </c>
-      <c r="O792" s="18"/>
+      <c r="O792" s="53">
+        <v>46246</v>
+      </c>
       <c r="P792" s="18"/>
       <c r="Q792" s="11">
         <v>77823455</v>
@@ -47902,7 +48152,9 @@
       <c r="N804" s="54">
         <v>711</v>
       </c>
-      <c r="O804" s="18"/>
+      <c r="O804" s="53">
+        <v>46246</v>
+      </c>
       <c r="P804" s="18"/>
       <c r="Q804" s="11">
         <v>95868227</v>
@@ -48148,7 +48400,9 @@
       <c r="N809" s="54">
         <v>218</v>
       </c>
-      <c r="O809" s="18"/>
+      <c r="O809" s="53">
+        <v>46246</v>
+      </c>
       <c r="P809" s="18"/>
       <c r="Q809" s="11">
         <v>79787847</v>
@@ -48296,7 +48550,9 @@
       <c r="N812" s="76" t="s">
         <v>2117</v>
       </c>
-      <c r="O812" s="18"/>
+      <c r="O812" s="53">
+        <v>46246</v>
+      </c>
       <c r="P812" s="18"/>
       <c r="Q812" s="11">
         <v>94686316</v>
@@ -48682,7 +48938,9 @@
       <c r="N820" s="54">
         <v>756</v>
       </c>
-      <c r="O820" s="18"/>
+      <c r="O820" s="53">
+        <v>46246</v>
+      </c>
       <c r="P820" s="18"/>
       <c r="Q820" s="18"/>
       <c r="R820" s="20" t="s">
@@ -50314,7 +50572,9 @@
       <c r="N854" s="54">
         <v>443</v>
       </c>
-      <c r="O854" s="18"/>
+      <c r="O854" s="53">
+        <v>46247</v>
+      </c>
       <c r="P854" s="18"/>
       <c r="Q854" s="11">
         <v>96963610</v>
@@ -50364,7 +50624,9 @@
       <c r="N855" s="54">
         <v>442</v>
       </c>
-      <c r="O855" s="18"/>
+      <c r="O855" s="53">
+        <v>46246</v>
+      </c>
       <c r="P855" s="18"/>
       <c r="Q855" s="11">
         <v>97310271</v>
@@ -50414,7 +50676,9 @@
       <c r="N856" s="54">
         <v>437</v>
       </c>
-      <c r="O856" s="18"/>
+      <c r="O856" s="53">
+        <v>46246</v>
+      </c>
       <c r="P856" s="18"/>
       <c r="Q856" s="11">
         <v>96511538</v>
@@ -53634,7 +53898,9 @@
       <c r="N923" s="76" t="s">
         <v>2121</v>
       </c>
-      <c r="O923" s="18"/>
+      <c r="O923" s="53">
+        <v>46246</v>
+      </c>
       <c r="P923" s="18"/>
       <c r="Q923" s="15">
         <v>99814942</v>
@@ -53732,7 +53998,9 @@
       <c r="N925" s="76" t="s">
         <v>2122</v>
       </c>
-      <c r="O925" s="18"/>
+      <c r="O925" s="53">
+        <v>46246</v>
+      </c>
       <c r="P925" s="18"/>
       <c r="Q925" s="15" t="s">
         <v>1266</v>
@@ -56304,7 +56572,9 @@
       <c r="N977" s="54">
         <v>707</v>
       </c>
-      <c r="O977" s="18"/>
+      <c r="O977" s="53">
+        <v>46246</v>
+      </c>
       <c r="P977" s="18"/>
       <c r="Q977" s="15">
         <v>71354571</v>
@@ -57506,7 +57776,9 @@
       <c r="N1001" s="54">
         <v>625</v>
       </c>
-      <c r="O1001" s="18"/>
+      <c r="O1001" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1001" s="18"/>
       <c r="Q1001" s="15">
         <v>526793094</v>
@@ -57556,7 +57828,9 @@
       <c r="N1002" s="54">
         <v>627</v>
       </c>
-      <c r="O1002" s="18"/>
+      <c r="O1002" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1002" s="18"/>
       <c r="Q1002" s="15">
         <v>527044855</v>
@@ -57606,7 +57880,9 @@
       <c r="N1003" s="54">
         <v>626</v>
       </c>
-      <c r="O1003" s="18"/>
+      <c r="O1003" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1003" s="18"/>
       <c r="Q1003" s="15">
         <v>502563347</v>
@@ -57912,7 +58188,9 @@
       <c r="N1009" s="76" t="s">
         <v>2482</v>
       </c>
-      <c r="O1009" s="18"/>
+      <c r="O1009" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1009" s="18"/>
       <c r="Q1009" s="18"/>
       <c r="R1009" s="22" t="s">
@@ -58160,7 +58438,9 @@
       <c r="N1014" s="54">
         <v>628</v>
       </c>
-      <c r="O1014" s="18"/>
+      <c r="O1014" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1014" s="18"/>
       <c r="Q1014" s="15">
         <v>95474068</v>
@@ -59944,7 +60224,9 @@
       <c r="N1050" s="54">
         <v>532</v>
       </c>
-      <c r="O1050" s="18"/>
+      <c r="O1050" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1050" s="18"/>
       <c r="Q1050" s="15">
         <v>96092786</v>
@@ -61268,7 +61550,9 @@
       <c r="N1077" s="54">
         <v>703</v>
       </c>
-      <c r="O1077" s="18"/>
+      <c r="O1077" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1077" s="18"/>
       <c r="Q1077" s="18"/>
       <c r="R1077" s="22" t="s">
@@ -61916,7 +62200,9 @@
       <c r="N1091" s="54">
         <v>608</v>
       </c>
-      <c r="O1091" s="18"/>
+      <c r="O1091" s="53">
+        <v>46247</v>
+      </c>
       <c r="P1091" s="18"/>
       <c r="Q1091" s="11">
         <v>77804820</v>
@@ -61966,7 +62252,9 @@
       <c r="N1092" s="54">
         <v>607</v>
       </c>
-      <c r="O1092" s="18"/>
+      <c r="O1092" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1092" s="18"/>
       <c r="Q1092" s="11">
         <v>77204234</v>
@@ -62160,7 +62448,9 @@
       </c>
       <c r="M1096" s="18"/>
       <c r="N1096" s="40"/>
-      <c r="O1096" s="18"/>
+      <c r="O1096" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1096" s="18"/>
       <c r="Q1096" s="18"/>
       <c r="R1096" s="22" t="s">
@@ -64128,7 +64418,9 @@
       <c r="L1141" s="18"/>
       <c r="M1141" s="18"/>
       <c r="N1141" s="40"/>
-      <c r="O1141" s="18"/>
+      <c r="O1141" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1141" s="18"/>
       <c r="Q1141" s="18"/>
       <c r="R1141" s="22" t="s">
@@ -64168,7 +64460,9 @@
       <c r="L1142" s="18"/>
       <c r="M1142" s="18"/>
       <c r="N1142" s="40"/>
-      <c r="O1142" s="18"/>
+      <c r="O1142" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1142" s="18"/>
       <c r="Q1142" s="18"/>
       <c r="R1142" s="22" t="s">
@@ -64208,7 +64502,9 @@
       <c r="L1143" s="18"/>
       <c r="M1143" s="18"/>
       <c r="N1143" s="40"/>
-      <c r="O1143" s="18"/>
+      <c r="O1143" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1143" s="18"/>
       <c r="Q1143" s="18"/>
       <c r="R1143" s="22" t="s">
@@ -64248,7 +64544,9 @@
       <c r="L1144" s="18"/>
       <c r="M1144" s="18"/>
       <c r="N1144" s="40"/>
-      <c r="O1144" s="18"/>
+      <c r="O1144" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1144" s="18"/>
       <c r="Q1144" s="18"/>
       <c r="R1144" s="22" t="s">
@@ -64288,7 +64586,9 @@
       <c r="L1145" s="18"/>
       <c r="M1145" s="18"/>
       <c r="N1145" s="40"/>
-      <c r="O1145" s="18"/>
+      <c r="O1145" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1145" s="18"/>
       <c r="Q1145" s="18"/>
       <c r="R1145" s="22" t="s">
@@ -64328,7 +64628,9 @@
       <c r="L1146" s="18"/>
       <c r="M1146" s="18"/>
       <c r="N1146" s="40"/>
-      <c r="O1146" s="18"/>
+      <c r="O1146" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1146" s="18"/>
       <c r="Q1146" s="18"/>
       <c r="R1146" s="22" t="s">
@@ -64816,7 +65118,9 @@
       <c r="L1158" s="18"/>
       <c r="M1158" s="18"/>
       <c r="N1158" s="40"/>
-      <c r="O1158" s="18"/>
+      <c r="O1158" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1158" s="18"/>
       <c r="Q1158" s="18"/>
       <c r="R1158" s="22" t="s">
@@ -64943,7 +65247,9 @@
       <c r="O1161" s="53">
         <v>46244</v>
       </c>
-      <c r="P1161" s="18"/>
+      <c r="P1161" s="70">
+        <v>46246</v>
+      </c>
       <c r="Q1161" s="18"/>
       <c r="R1161" s="22" t="s">
         <v>131</v>
@@ -65676,7 +65982,9 @@
       <c r="L1177" s="18"/>
       <c r="M1177" s="18"/>
       <c r="N1177" s="40"/>
-      <c r="O1177" s="18"/>
+      <c r="O1177" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1177" s="18"/>
       <c r="Q1177" s="66">
         <v>99077225</v>
@@ -65766,7 +66074,9 @@
       <c r="N1179" s="54">
         <v>1022</v>
       </c>
-      <c r="O1179" s="18"/>
+      <c r="O1179" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1179" s="18"/>
       <c r="Q1179" s="55">
         <v>79258076</v>
@@ -67262,10 +67572,12 @@
       <c r="J1211" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1211" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1211" s="18"/>
+      <c r="K1211" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1211" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1211" s="18"/>
       <c r="N1211" s="40"/>
       <c r="O1211" s="53">
@@ -67310,10 +67622,12 @@
       <c r="J1212" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1212" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1212" s="18"/>
+      <c r="K1212" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1212" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1212" s="18"/>
       <c r="N1212" s="40"/>
       <c r="O1212" s="53">
@@ -67358,10 +67672,12 @@
       <c r="J1213" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1213" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1213" s="18"/>
+      <c r="K1213" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1213" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1213" s="18"/>
       <c r="N1213" s="40"/>
       <c r="O1213" s="18"/>
@@ -67404,10 +67720,12 @@
       <c r="J1214" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1214" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1214" s="18"/>
+      <c r="K1214" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1214" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1214" s="18"/>
       <c r="N1214" s="40"/>
       <c r="O1214" s="18"/>
@@ -67450,10 +67768,12 @@
       <c r="J1215" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1215" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1215" s="18"/>
+      <c r="K1215" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1215" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1215" s="18"/>
       <c r="N1215" s="40"/>
       <c r="O1215" s="18"/>
@@ -67496,10 +67816,12 @@
       <c r="J1216" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1216" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1216" s="18"/>
+      <c r="K1216" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1216" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1216" s="18"/>
       <c r="N1216" s="40"/>
       <c r="O1216" s="18"/>
@@ -67542,10 +67864,12 @@
       <c r="J1217" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K1217" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1217" s="18"/>
+      <c r="K1217" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1217" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1217" s="18"/>
       <c r="N1217" s="54">
         <v>1104</v>
@@ -67684,7 +68008,9 @@
       <c r="N1220" s="54" t="s">
         <v>2484</v>
       </c>
-      <c r="O1220" s="18"/>
+      <c r="O1220" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1220" s="18"/>
       <c r="Q1220" s="15">
         <v>94789315</v>
@@ -68682,10 +69008,12 @@
       <c r="J1242" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K1242" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1242" s="18"/>
+      <c r="K1242" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1242" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1242" s="18"/>
       <c r="N1242" s="54">
         <v>475</v>
@@ -68732,15 +69060,19 @@
       <c r="J1243" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K1243" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1243" s="18"/>
+      <c r="K1243" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1243" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1243" s="18"/>
       <c r="N1243" s="54">
         <v>878</v>
       </c>
-      <c r="O1243" s="18"/>
+      <c r="O1243" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1243" s="18"/>
       <c r="Q1243" s="15">
         <v>78615034</v>
@@ -68780,10 +69112,12 @@
       <c r="J1244" s="15" t="s">
         <v>1908</v>
       </c>
-      <c r="K1244" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1244" s="18"/>
+      <c r="K1244" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1244" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1244" s="18"/>
       <c r="N1244" s="40"/>
       <c r="O1244" s="18"/>
@@ -68826,10 +69160,12 @@
       <c r="J1245" s="15" t="s">
         <v>1908</v>
       </c>
-      <c r="K1245" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1245" s="18"/>
+      <c r="K1245" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1245" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1245" s="18"/>
       <c r="N1245" s="54">
         <v>830</v>
@@ -68883,7 +69219,9 @@
         <v>454</v>
       </c>
       <c r="O1246" s="18"/>
-      <c r="P1246" s="18"/>
+      <c r="P1246" s="70">
+        <v>46246</v>
+      </c>
       <c r="Q1246" s="15">
         <v>98172901</v>
       </c>
@@ -68922,11 +69260,11 @@
       <c r="J1247" s="15" t="s">
         <v>1908</v>
       </c>
-      <c r="K1247" s="11" t="s">
-        <v>2327</v>
+      <c r="K1247" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1247" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1247" s="18"/>
       <c r="N1247" s="54">
@@ -68972,11 +69310,11 @@
       <c r="J1248" s="15" t="s">
         <v>1908</v>
       </c>
-      <c r="K1248" s="11" t="s">
-        <v>2327</v>
+      <c r="K1248" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1248" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1248" s="18"/>
       <c r="N1248" s="54">
@@ -69024,11 +69362,11 @@
       <c r="J1249" s="15" t="s">
         <v>1908</v>
       </c>
-      <c r="K1249" s="11" t="s">
-        <v>2327</v>
+      <c r="K1249" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L1249" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M1249" s="18"/>
       <c r="N1249" s="54">
@@ -69074,15 +69412,19 @@
       <c r="J1250" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K1250" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1250" s="18"/>
+      <c r="K1250" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1250" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1250" s="18"/>
       <c r="N1250" s="54">
         <v>482</v>
       </c>
-      <c r="O1250" s="18"/>
+      <c r="O1250" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1250" s="18"/>
       <c r="Q1250" s="11">
         <v>96877336001</v>
@@ -69122,10 +69464,12 @@
       <c r="J1251" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K1251" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1251" s="18"/>
+      <c r="K1251" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1251" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1251" s="18"/>
       <c r="N1251" s="40"/>
       <c r="O1251" s="18"/>
@@ -69168,10 +69512,12 @@
       <c r="J1252" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K1252" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1252" s="18"/>
+      <c r="K1252" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1252" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1252" s="18"/>
       <c r="N1252" s="40"/>
       <c r="O1252" s="18"/>
@@ -69214,10 +69560,12 @@
       <c r="J1253" s="15" t="s">
         <v>1908</v>
       </c>
-      <c r="K1253" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1253" s="18"/>
+      <c r="K1253" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1253" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1253" s="18"/>
       <c r="N1253" s="54">
         <v>831</v>
@@ -69262,15 +69610,19 @@
       <c r="J1254" s="15" t="s">
         <v>1908</v>
       </c>
-      <c r="K1254" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1254" s="18"/>
+      <c r="K1254" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1254" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1254" s="18"/>
       <c r="N1254" s="54">
         <v>571</v>
       </c>
-      <c r="O1254" s="18"/>
+      <c r="O1254" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1254" s="18"/>
       <c r="Q1254" s="15">
         <v>94526230</v>
@@ -69310,15 +69662,19 @@
       <c r="J1255" s="15" t="s">
         <v>1908</v>
       </c>
-      <c r="K1255" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1255" s="18"/>
+      <c r="K1255" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1255" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1255" s="18"/>
       <c r="N1255" s="54">
         <v>470</v>
       </c>
-      <c r="O1255" s="18"/>
+      <c r="O1255" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1255" s="18"/>
       <c r="Q1255" s="18"/>
       <c r="R1255" s="22" t="s">
@@ -69506,7 +69862,9 @@
       <c r="N1259" s="54">
         <v>709</v>
       </c>
-      <c r="O1259" s="18"/>
+      <c r="O1259" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1259" s="18"/>
       <c r="Q1259" s="18"/>
       <c r="R1259" s="22" t="s">
@@ -69658,7 +70016,9 @@
       <c r="N1262" s="54">
         <v>555</v>
       </c>
-      <c r="O1262" s="18"/>
+      <c r="O1262" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1262" s="18"/>
       <c r="Q1262" s="11">
         <v>77491283</v>
@@ -70002,7 +70362,9 @@
       <c r="N1269" s="54">
         <v>412</v>
       </c>
-      <c r="O1269" s="18"/>
+      <c r="O1269" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1269" s="18"/>
       <c r="Q1269" s="11">
         <v>95722052</v>
@@ -70050,7 +70412,9 @@
       <c r="N1270" s="54">
         <v>413</v>
       </c>
-      <c r="O1270" s="18"/>
+      <c r="O1270" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1270" s="18"/>
       <c r="Q1270" s="11">
         <v>95722052</v>
@@ -70344,7 +70708,9 @@
       </c>
       <c r="M1276" s="18"/>
       <c r="N1276" s="40"/>
-      <c r="O1276" s="18"/>
+      <c r="O1276" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1276" s="18"/>
       <c r="Q1276" s="18"/>
       <c r="R1276" s="22" t="s">
@@ -70390,7 +70756,9 @@
       </c>
       <c r="M1277" s="18"/>
       <c r="N1277" s="40"/>
-      <c r="O1277" s="18"/>
+      <c r="O1277" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1277" s="18"/>
       <c r="Q1277" s="18"/>
       <c r="R1277" s="22" t="s">
@@ -71494,7 +71862,9 @@
       <c r="N1300" s="54">
         <v>585</v>
       </c>
-      <c r="O1300" s="18"/>
+      <c r="O1300" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1300" s="18"/>
       <c r="Q1300" s="11">
         <v>95609530</v>
@@ -72062,10 +72432,12 @@
         <v>1177</v>
       </c>
       <c r="J1312" s="18"/>
-      <c r="K1312" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1312" s="18"/>
+      <c r="K1312" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1312" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1312" s="16" t="s">
         <v>1994</v>
       </c>
@@ -72106,10 +72478,12 @@
         <v>1177</v>
       </c>
       <c r="J1313" s="18"/>
-      <c r="K1313" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1313" s="18"/>
+      <c r="K1313" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1313" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1313" s="16" t="s">
         <v>1994</v>
       </c>
@@ -72150,10 +72524,12 @@
         <v>1177</v>
       </c>
       <c r="J1314" s="18"/>
-      <c r="K1314" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1314" s="18"/>
+      <c r="K1314" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1314" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1314" s="16" t="s">
         <v>1994</v>
       </c>
@@ -72194,10 +72570,12 @@
         <v>1177</v>
       </c>
       <c r="J1315" s="18"/>
-      <c r="K1315" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1315" s="18"/>
+      <c r="K1315" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1315" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1315" s="16" t="s">
         <v>1994</v>
       </c>
@@ -73654,7 +74032,9 @@
       <c r="N1345" s="54">
         <v>702</v>
       </c>
-      <c r="O1345" s="18"/>
+      <c r="O1345" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1345" s="18"/>
       <c r="Q1345" s="18"/>
       <c r="R1345" s="22" t="s">
@@ -75726,7 +76106,9 @@
       <c r="N1389" s="54">
         <v>953</v>
       </c>
-      <c r="O1389" s="18"/>
+      <c r="O1389" s="15" t="s">
+        <v>2491</v>
+      </c>
       <c r="P1389" s="18"/>
       <c r="Q1389" s="11" t="s">
         <v>2091</v>
@@ -76422,7 +76804,9 @@
       <c r="N1404" s="54">
         <v>766</v>
       </c>
-      <c r="O1404" s="18"/>
+      <c r="O1404" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1404" s="18"/>
       <c r="Q1404" s="11">
         <v>553624302</v>
@@ -76616,7 +77000,9 @@
       <c r="N1408" s="76" t="s">
         <v>2486</v>
       </c>
-      <c r="O1408" s="18"/>
+      <c r="O1408" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1408" s="18"/>
       <c r="Q1408" s="18"/>
       <c r="R1408" s="22" t="s">
@@ -78862,7 +79248,9 @@
       <c r="N1457" s="54">
         <v>1026</v>
       </c>
-      <c r="O1457" s="18"/>
+      <c r="O1457" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1457" s="18"/>
       <c r="Q1457" s="18"/>
       <c r="R1457" s="22" t="s">
@@ -78994,7 +79382,9 @@
       <c r="L1460" s="18"/>
       <c r="M1460" s="18"/>
       <c r="N1460" s="40"/>
-      <c r="O1460" s="18"/>
+      <c r="O1460" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1460" s="18"/>
       <c r="Q1460" s="18"/>
       <c r="R1460" s="22" t="s">
@@ -79510,7 +79900,9 @@
       <c r="L1471" s="18"/>
       <c r="M1471" s="18"/>
       <c r="N1471" s="40"/>
-      <c r="O1471" s="18"/>
+      <c r="O1471" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1471" s="18"/>
       <c r="Q1471" s="18"/>
       <c r="R1471" s="21" t="s">
@@ -79554,7 +79946,9 @@
       <c r="L1472" s="18"/>
       <c r="M1472" s="18"/>
       <c r="N1472" s="40"/>
-      <c r="O1472" s="18"/>
+      <c r="O1472" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1472" s="18"/>
       <c r="Q1472" s="18"/>
       <c r="R1472" s="21" t="s">
@@ -79598,7 +79992,9 @@
       <c r="L1473" s="18"/>
       <c r="M1473" s="18"/>
       <c r="N1473" s="40"/>
-      <c r="O1473" s="18"/>
+      <c r="O1473" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1473" s="18"/>
       <c r="Q1473" s="18"/>
       <c r="R1473" s="21" t="s">
@@ -79642,7 +80038,9 @@
       <c r="L1474" s="18"/>
       <c r="M1474" s="18"/>
       <c r="N1474" s="40"/>
-      <c r="O1474" s="18"/>
+      <c r="O1474" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1474" s="18"/>
       <c r="Q1474" s="18"/>
       <c r="R1474" s="21" t="s">
@@ -79686,7 +80084,9 @@
       <c r="L1475" s="18"/>
       <c r="M1475" s="18"/>
       <c r="N1475" s="40"/>
-      <c r="O1475" s="18"/>
+      <c r="O1475" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1475" s="18"/>
       <c r="Q1475" s="18"/>
       <c r="R1475" s="21" t="s">
@@ -80198,7 +80598,9 @@
       <c r="L1487" s="18"/>
       <c r="M1487" s="18"/>
       <c r="N1487" s="40"/>
-      <c r="O1487" s="18"/>
+      <c r="O1487" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1487" s="18"/>
       <c r="Q1487" s="18"/>
       <c r="R1487" s="21" t="s">
@@ -80286,7 +80688,9 @@
       <c r="L1489" s="18"/>
       <c r="M1489" s="18"/>
       <c r="N1489" s="40"/>
-      <c r="O1489" s="18"/>
+      <c r="O1489" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1489" s="18"/>
       <c r="Q1489" s="18"/>
       <c r="R1489" s="21" t="s">
@@ -81774,7 +82178,9 @@
       <c r="L1521" s="18"/>
       <c r="M1521" s="18"/>
       <c r="N1521" s="40"/>
-      <c r="O1521" s="18"/>
+      <c r="O1521" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1521" s="18"/>
       <c r="Q1521" s="18"/>
       <c r="R1521" s="21" t="s">
@@ -82328,7 +82734,9 @@
       <c r="L1533" s="18"/>
       <c r="M1533" s="18"/>
       <c r="N1533" s="40"/>
-      <c r="O1533" s="18"/>
+      <c r="O1533" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1533" s="18"/>
       <c r="Q1533" s="18"/>
       <c r="R1533" s="21" t="s">
@@ -82546,7 +82954,9 @@
         <v>2179</v>
       </c>
       <c r="N1538" s="40"/>
-      <c r="O1538" s="18"/>
+      <c r="O1538" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1538" s="18"/>
       <c r="Q1538" s="18"/>
       <c r="R1538" s="16" t="s">
@@ -82588,7 +82998,9 @@
         <v>2179</v>
       </c>
       <c r="N1539" s="40"/>
-      <c r="O1539" s="18"/>
+      <c r="O1539" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1539" s="18"/>
       <c r="Q1539" s="18"/>
       <c r="R1539" s="16" t="s">
@@ -82630,7 +83042,9 @@
         <v>2179</v>
       </c>
       <c r="N1540" s="40"/>
-      <c r="O1540" s="18"/>
+      <c r="O1540" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1540" s="18"/>
       <c r="Q1540" s="18"/>
       <c r="R1540" s="16" t="s">
@@ -82714,7 +83128,9 @@
         <v>2179</v>
       </c>
       <c r="N1542" s="40"/>
-      <c r="O1542" s="18"/>
+      <c r="O1542" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1542" s="18"/>
       <c r="Q1542" s="18"/>
       <c r="R1542" s="16" t="s">
@@ -85475,106 +85891,82 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1604" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1604" spans="1:18" ht="16.2" thickBot="1">
       <c r="A1604" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1604" s="10">
         <v>46247</v>
       </c>
       <c r="C1604" s="23" t="s">
-        <v>2433</v>
+        <v>75</v>
       </c>
       <c r="D1604" s="11">
-        <v>22939425</v>
-      </c>
-      <c r="E1604" s="82" t="s">
-        <v>121</v>
-      </c>
-      <c r="F1604" s="47" t="s">
-        <v>122</v>
-      </c>
+        <v>90508672</v>
+      </c>
+      <c r="E1604" s="18"/>
+      <c r="F1604" s="18"/>
       <c r="G1604" s="83">
-        <v>6579</v>
+        <v>5481</v>
       </c>
       <c r="H1604" s="15">
-        <v>6039</v>
-      </c>
-      <c r="I1604" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1604" s="15" t="s">
-        <v>319</v>
-      </c>
-      <c r="K1604" s="60" t="s">
-        <v>1189</v>
-      </c>
+        <v>4694</v>
+      </c>
+      <c r="I1604" s="18"/>
+      <c r="J1604" s="18"/>
+      <c r="K1604" s="18"/>
       <c r="L1604" s="18"/>
       <c r="M1604" s="18"/>
       <c r="N1604" s="40"/>
       <c r="O1604" s="18"/>
       <c r="P1604" s="18"/>
       <c r="Q1604" s="18"/>
-      <c r="R1604" s="21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="1605" spans="1:18" ht="28.2" thickBot="1">
+      <c r="R1604" s="18"/>
+    </row>
+    <row r="1605" spans="1:18" ht="16.2" thickBot="1">
       <c r="A1605" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B1605" s="10">
         <v>46247</v>
       </c>
       <c r="C1605" s="23" t="s">
-        <v>2434</v>
+        <v>2492</v>
       </c>
       <c r="D1605" s="11">
-        <v>14995818</v>
-      </c>
-      <c r="E1605" s="82" t="s">
-        <v>121</v>
-      </c>
-      <c r="F1605" s="47" t="s">
-        <v>122</v>
-      </c>
+        <v>137967312</v>
+      </c>
+      <c r="E1605" s="18"/>
+      <c r="F1605" s="18"/>
       <c r="G1605" s="83">
-        <v>9739</v>
+        <v>2761</v>
       </c>
       <c r="H1605" s="15">
-        <v>4751</v>
-      </c>
-      <c r="I1605" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1605" s="15" t="s">
-        <v>319</v>
-      </c>
-      <c r="K1605" s="60" t="s">
-        <v>1189</v>
-      </c>
+        <v>3745</v>
+      </c>
+      <c r="I1605" s="18"/>
+      <c r="J1605" s="18"/>
+      <c r="K1605" s="18"/>
       <c r="L1605" s="18"/>
       <c r="M1605" s="18"/>
       <c r="N1605" s="40"/>
       <c r="O1605" s="18"/>
       <c r="P1605" s="18"/>
       <c r="Q1605" s="18"/>
-      <c r="R1605" s="21" t="s">
-        <v>14</v>
-      </c>
+      <c r="R1605" s="18"/>
     </row>
     <row r="1606" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1606" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B1606" s="10">
         <v>46247</v>
       </c>
       <c r="C1606" s="23" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="D1606" s="11">
-        <v>12989448</v>
+        <v>22939425</v>
       </c>
       <c r="E1606" s="82" t="s">
         <v>121</v>
@@ -85583,10 +85975,10 @@
         <v>122</v>
       </c>
       <c r="G1606" s="83">
-        <v>1553</v>
+        <v>6579</v>
       </c>
       <c r="H1606" s="15">
-        <v>1292</v>
+        <v>6039</v>
       </c>
       <c r="I1606" s="16" t="s">
         <v>10</v>
@@ -85609,80 +86001,78 @@
     </row>
     <row r="1607" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1607" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B1607" s="10">
         <v>46247</v>
       </c>
       <c r="C1607" s="23" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="D1607" s="11">
-        <v>108564836</v>
-      </c>
-      <c r="E1607" s="46" t="s">
-        <v>21</v>
+        <v>14995818</v>
+      </c>
+      <c r="E1607" s="82" t="s">
+        <v>121</v>
       </c>
       <c r="F1607" s="47" t="s">
         <v>122</v>
       </c>
       <c r="G1607" s="83">
-        <v>8698</v>
-      </c>
-      <c r="H1607" s="15" t="s">
-        <v>2437</v>
-      </c>
-      <c r="I1607" s="15" t="s">
-        <v>123</v>
+        <v>9739</v>
+      </c>
+      <c r="H1607" s="15">
+        <v>4751</v>
+      </c>
+      <c r="I1607" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="J1607" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="K1607" s="17" t="s">
-        <v>12</v>
+        <v>319</v>
+      </c>
+      <c r="K1607" s="60" t="s">
+        <v>1189</v>
       </c>
       <c r="L1607" s="18"/>
       <c r="M1607" s="18"/>
       <c r="N1607" s="40"/>
       <c r="O1607" s="18"/>
       <c r="P1607" s="18"/>
-      <c r="Q1607" s="11">
-        <v>98518183</v>
-      </c>
-      <c r="R1607" s="22" t="s">
-        <v>131</v>
+      <c r="Q1607" s="18"/>
+      <c r="R1607" s="21" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="1608" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1608" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B1608" s="10">
         <v>46247</v>
       </c>
-      <c r="C1608" s="11" t="s">
-        <v>328</v>
+      <c r="C1608" s="23" t="s">
+        <v>2435</v>
       </c>
       <c r="D1608" s="11">
-        <v>8852091</v>
-      </c>
-      <c r="E1608" s="37" t="s">
+        <v>12989448</v>
+      </c>
+      <c r="E1608" s="82" t="s">
         <v>121</v>
       </c>
-      <c r="F1608" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1608" s="14">
-        <v>8116</v>
+      <c r="F1608" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1608" s="83">
+        <v>1553</v>
       </c>
       <c r="H1608" s="15">
-        <v>9291</v>
-      </c>
-      <c r="I1608" s="15" t="s">
-        <v>123</v>
+        <v>1292</v>
+      </c>
+      <c r="I1608" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="J1608" s="15" t="s">
-        <v>2438</v>
+        <v>319</v>
       </c>
       <c r="K1608" s="60" t="s">
         <v>1189</v>
@@ -85693,78 +86083,80 @@
       <c r="O1608" s="18"/>
       <c r="P1608" s="18"/>
       <c r="Q1608" s="18"/>
-      <c r="R1608" s="22" t="s">
-        <v>131</v>
+      <c r="R1608" s="21" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="1609" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1609" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B1609" s="10">
         <v>46247</v>
       </c>
-      <c r="C1609" s="11" t="s">
-        <v>2439</v>
+      <c r="C1609" s="23" t="s">
+        <v>2436</v>
       </c>
       <c r="D1609" s="11">
-        <v>9018657</v>
-      </c>
-      <c r="E1609" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="F1609" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1609" s="14">
-        <v>609</v>
-      </c>
-      <c r="H1609" s="15">
-        <v>3428</v>
+        <v>108564836</v>
+      </c>
+      <c r="E1609" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1609" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1609" s="83">
+        <v>8698</v>
+      </c>
+      <c r="H1609" s="15" t="s">
+        <v>2437</v>
       </c>
       <c r="I1609" s="15" t="s">
         <v>123</v>
       </c>
       <c r="J1609" s="15" t="s">
-        <v>2438</v>
-      </c>
-      <c r="K1609" s="60" t="s">
-        <v>1189</v>
+        <v>174</v>
+      </c>
+      <c r="K1609" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1609" s="18"/>
       <c r="M1609" s="18"/>
       <c r="N1609" s="40"/>
       <c r="O1609" s="18"/>
       <c r="P1609" s="18"/>
-      <c r="Q1609" s="18"/>
+      <c r="Q1609" s="11">
+        <v>98518183</v>
+      </c>
       <c r="R1609" s="22" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="1610" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1610" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B1610" s="10">
         <v>46247</v>
       </c>
-      <c r="C1610" s="23" t="s">
-        <v>2440</v>
+      <c r="C1610" s="11" t="s">
+        <v>328</v>
       </c>
       <c r="D1610" s="11">
-        <v>102928204</v>
-      </c>
-      <c r="E1610" s="46" t="s">
-        <v>21</v>
+        <v>8852091</v>
+      </c>
+      <c r="E1610" s="37" t="s">
+        <v>121</v>
       </c>
       <c r="F1610" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="G1610" s="83">
-        <v>9599</v>
-      </c>
-      <c r="H1610" s="15" t="s">
-        <v>2441</v>
+      <c r="G1610" s="14">
+        <v>8116</v>
+      </c>
+      <c r="H1610" s="15">
+        <v>9291</v>
       </c>
       <c r="I1610" s="15" t="s">
         <v>123</v>
@@ -85785,36 +86177,36 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1611" spans="1:18" ht="24.6" thickBot="1">
+    <row r="1611" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1611" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B1611" s="10">
         <v>46247</v>
       </c>
-      <c r="C1611" s="23" t="s">
-        <v>601</v>
-      </c>
-      <c r="D1611" s="11" t="s">
-        <v>602</v>
-      </c>
-      <c r="E1611" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1611" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1611" s="83" t="s">
-        <v>2442</v>
-      </c>
-      <c r="H1611" s="15" t="s">
-        <v>2443</v>
-      </c>
-      <c r="I1611" s="22" t="s">
-        <v>563</v>
+      <c r="C1611" s="11" t="s">
+        <v>2439</v>
+      </c>
+      <c r="D1611" s="11">
+        <v>9018657</v>
+      </c>
+      <c r="E1611" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1611" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1611" s="14">
+        <v>609</v>
+      </c>
+      <c r="H1611" s="15">
+        <v>3428</v>
+      </c>
+      <c r="I1611" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="J1611" s="15" t="s">
-        <v>1672</v>
+        <v>2438</v>
       </c>
       <c r="K1611" s="60" t="s">
         <v>1189</v>
@@ -85829,36 +86221,36 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1612" spans="1:18" ht="24.6" thickBot="1">
+    <row r="1612" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1612" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B1612" s="10">
         <v>46247</v>
       </c>
       <c r="C1612" s="23" t="s">
-        <v>2444</v>
+        <v>2440</v>
       </c>
       <c r="D1612" s="11">
-        <v>137351063</v>
+        <v>102928204</v>
       </c>
       <c r="E1612" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="F1612" s="47" t="s">
+      <c r="F1612" s="16" t="s">
         <v>122</v>
       </c>
       <c r="G1612" s="83">
-        <v>2346</v>
-      </c>
-      <c r="H1612" s="15">
-        <v>547</v>
-      </c>
-      <c r="I1612" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1612" s="51" t="s">
-        <v>776</v>
+        <v>9599</v>
+      </c>
+      <c r="H1612" s="15" t="s">
+        <v>2441</v>
+      </c>
+      <c r="I1612" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1612" s="15" t="s">
+        <v>2438</v>
       </c>
       <c r="K1612" s="60" t="s">
         <v>1189</v>
@@ -85875,34 +86267,34 @@
     </row>
     <row r="1613" spans="1:18" ht="24.6" thickBot="1">
       <c r="A1613" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B1613" s="10">
         <v>46247</v>
       </c>
       <c r="C1613" s="23" t="s">
-        <v>2445</v>
-      </c>
-      <c r="D1613" s="11">
-        <v>135147837</v>
+        <v>601</v>
+      </c>
+      <c r="D1613" s="11" t="s">
+        <v>602</v>
       </c>
       <c r="E1613" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="F1613" s="47" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1613" s="83">
-        <v>6164</v>
-      </c>
-      <c r="H1613" s="15">
-        <v>9375</v>
-      </c>
-      <c r="I1613" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1613" s="51" t="s">
-        <v>776</v>
+      <c r="F1613" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1613" s="83" t="s">
+        <v>2442</v>
+      </c>
+      <c r="H1613" s="15" t="s">
+        <v>2443</v>
+      </c>
+      <c r="I1613" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1613" s="15" t="s">
+        <v>1672</v>
       </c>
       <c r="K1613" s="60" t="s">
         <v>1189</v>
@@ -85919,16 +86311,16 @@
     </row>
     <row r="1614" spans="1:18" ht="24.6" thickBot="1">
       <c r="A1614" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B1614" s="10">
         <v>46247</v>
       </c>
       <c r="C1614" s="23" t="s">
-        <v>989</v>
+        <v>2444</v>
       </c>
       <c r="D1614" s="11">
-        <v>106990709</v>
+        <v>137351063</v>
       </c>
       <c r="E1614" s="46" t="s">
         <v>21</v>
@@ -85937,10 +86329,10 @@
         <v>122</v>
       </c>
       <c r="G1614" s="83">
-        <v>5429</v>
+        <v>2346</v>
       </c>
       <c r="H1614" s="15">
-        <v>4828</v>
+        <v>547</v>
       </c>
       <c r="I1614" s="16" t="s">
         <v>10</v>
@@ -85963,16 +86355,16 @@
     </row>
     <row r="1615" spans="1:18" ht="24.6" thickBot="1">
       <c r="A1615" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B1615" s="10">
         <v>46247</v>
       </c>
       <c r="C1615" s="23" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="D1615" s="11">
-        <v>131776588</v>
+        <v>135147837</v>
       </c>
       <c r="E1615" s="46" t="s">
         <v>21</v>
@@ -85981,9 +86373,11 @@
         <v>122</v>
       </c>
       <c r="G1615" s="83">
-        <v>8934</v>
-      </c>
-      <c r="H1615" s="18"/>
+        <v>6164</v>
+      </c>
+      <c r="H1615" s="15">
+        <v>9375</v>
+      </c>
       <c r="I1615" s="16" t="s">
         <v>10</v>
       </c>
@@ -86005,16 +86399,16 @@
     </row>
     <row r="1616" spans="1:18" ht="24.6" thickBot="1">
       <c r="A1616" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B1616" s="10">
         <v>46247</v>
       </c>
       <c r="C1616" s="23" t="s">
-        <v>2489</v>
+        <v>989</v>
       </c>
       <c r="D1616" s="11">
-        <v>106002067</v>
+        <v>106990709</v>
       </c>
       <c r="E1616" s="46" t="s">
         <v>21</v>
@@ -86023,10 +86417,10 @@
         <v>122</v>
       </c>
       <c r="G1616" s="83">
-        <v>301</v>
+        <v>5429</v>
       </c>
       <c r="H1616" s="15">
-        <v>8384</v>
+        <v>4828</v>
       </c>
       <c r="I1616" s="16" t="s">
         <v>10</v>
@@ -86049,16 +86443,16 @@
     </row>
     <row r="1617" spans="1:18" ht="24.6" thickBot="1">
       <c r="A1617" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B1617" s="10">
         <v>46247</v>
       </c>
       <c r="C1617" s="23" t="s">
-        <v>2490</v>
+        <v>2446</v>
       </c>
       <c r="D1617" s="11">
-        <v>107885351</v>
+        <v>131776588</v>
       </c>
       <c r="E1617" s="46" t="s">
         <v>21</v>
@@ -86067,16 +86461,14 @@
         <v>122</v>
       </c>
       <c r="G1617" s="83">
-        <v>7981</v>
-      </c>
-      <c r="H1617" s="15">
-        <v>4420</v>
-      </c>
-      <c r="I1617" s="22" t="s">
-        <v>563</v>
-      </c>
-      <c r="J1617" s="50" t="s">
-        <v>564</v>
+        <v>8934</v>
+      </c>
+      <c r="H1617" s="18"/>
+      <c r="I1617" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1617" s="51" t="s">
+        <v>776</v>
       </c>
       <c r="K1617" s="60" t="s">
         <v>1189</v>
@@ -86093,16 +86485,16 @@
     </row>
     <row r="1618" spans="1:18" ht="24.6" thickBot="1">
       <c r="A1618" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B1618" s="10">
         <v>46247</v>
       </c>
       <c r="C1618" s="23" t="s">
-        <v>1387</v>
+        <v>2489</v>
       </c>
       <c r="D1618" s="11">
-        <v>122181529</v>
+        <v>106002067</v>
       </c>
       <c r="E1618" s="46" t="s">
         <v>21</v>
@@ -86111,16 +86503,16 @@
         <v>122</v>
       </c>
       <c r="G1618" s="83">
-        <v>806</v>
+        <v>301</v>
       </c>
       <c r="H1618" s="15">
-        <v>6723</v>
-      </c>
-      <c r="I1618" s="22" t="s">
-        <v>563</v>
-      </c>
-      <c r="J1618" s="50" t="s">
-        <v>564</v>
+        <v>8384</v>
+      </c>
+      <c r="I1618" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1618" s="51" t="s">
+        <v>776</v>
       </c>
       <c r="K1618" s="60" t="s">
         <v>1189</v>
@@ -86135,132 +86527,534 @@
         <v>131</v>
       </c>
     </row>
-    <row r="1619" spans="1:18" ht="27" thickBot="1">
+    <row r="1619" spans="1:18" ht="24.6" thickBot="1">
       <c r="A1619" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B1619" s="10">
         <v>46247</v>
       </c>
       <c r="C1619" s="23" t="s">
-        <v>2447</v>
-      </c>
-      <c r="D1619" s="11" t="s">
-        <v>2448</v>
+        <v>2490</v>
+      </c>
+      <c r="D1619" s="11">
+        <v>107885351</v>
       </c>
       <c r="E1619" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="F1619" s="45" t="s">
-        <v>22</v>
+      <c r="F1619" s="47" t="s">
+        <v>122</v>
       </c>
       <c r="G1619" s="83">
-        <v>87989</v>
+        <v>7981</v>
       </c>
       <c r="H1619" s="15">
-        <v>24193</v>
-      </c>
-      <c r="I1619" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1619" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1619" s="18"/>
+        <v>4420</v>
+      </c>
+      <c r="I1619" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1619" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1619" s="60" t="s">
+        <v>1189</v>
+      </c>
       <c r="L1619" s="18"/>
       <c r="M1619" s="18"/>
       <c r="N1619" s="40"/>
       <c r="O1619" s="18"/>
       <c r="P1619" s="18"/>
       <c r="Q1619" s="18"/>
-      <c r="R1619" s="20" t="s">
-        <v>11</v>
+      <c r="R1619" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="1620" spans="1:18" ht="24.6" thickBot="1">
       <c r="A1620" s="2">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B1620" s="10">
         <v>46247</v>
       </c>
       <c r="C1620" s="23" t="s">
-        <v>2449</v>
-      </c>
-      <c r="D1620" s="11" t="s">
-        <v>2450</v>
+        <v>1387</v>
+      </c>
+      <c r="D1620" s="11">
+        <v>122181529</v>
       </c>
       <c r="E1620" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="F1620" s="45" t="s">
-        <v>22</v>
+      <c r="F1620" s="47" t="s">
+        <v>122</v>
       </c>
       <c r="G1620" s="83">
-        <v>84815</v>
+        <v>806</v>
       </c>
       <c r="H1620" s="15">
-        <v>41009</v>
-      </c>
-      <c r="I1620" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1620" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1620" s="18"/>
+        <v>6723</v>
+      </c>
+      <c r="I1620" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1620" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1620" s="60" t="s">
+        <v>1189</v>
+      </c>
       <c r="L1620" s="18"/>
       <c r="M1620" s="18"/>
       <c r="N1620" s="40"/>
       <c r="O1620" s="18"/>
       <c r="P1620" s="18"/>
       <c r="Q1620" s="18"/>
-      <c r="R1620" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1621" spans="1:18" ht="24.6" thickBot="1">
+      <c r="R1620" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:18" ht="27" thickBot="1">
       <c r="A1621" s="2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B1621" s="10">
         <v>46247</v>
       </c>
       <c r="C1621" s="23" t="s">
-        <v>1258</v>
-      </c>
-      <c r="D1621" s="11">
-        <v>124529941</v>
+        <v>2447</v>
+      </c>
+      <c r="D1621" s="11" t="s">
+        <v>2448</v>
       </c>
       <c r="E1621" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="F1621" s="47" t="s">
-        <v>122</v>
+      <c r="F1621" s="45" t="s">
+        <v>22</v>
       </c>
       <c r="G1621" s="83">
-        <v>4208</v>
+        <v>87989</v>
       </c>
       <c r="H1621" s="15">
-        <v>8251</v>
-      </c>
-      <c r="I1621" s="22" t="s">
-        <v>563</v>
-      </c>
-      <c r="J1621" s="50" t="s">
-        <v>564</v>
-      </c>
-      <c r="K1621" s="30" t="s">
-        <v>1596</v>
-      </c>
+        <v>24193</v>
+      </c>
+      <c r="I1621" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1621" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1621" s="18"/>
       <c r="L1621" s="18"/>
       <c r="M1621" s="18"/>
       <c r="N1621" s="40"/>
       <c r="O1621" s="18"/>
       <c r="P1621" s="18"/>
       <c r="Q1621" s="18"/>
-      <c r="R1621" s="22" t="s">
-        <v>2491</v>
+      <c r="R1621" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:18" ht="24.6" thickBot="1">
+      <c r="A1622" s="2">
+        <v>41</v>
+      </c>
+      <c r="B1622" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1622" s="23" t="s">
+        <v>2449</v>
+      </c>
+      <c r="D1622" s="11" t="s">
+        <v>2450</v>
+      </c>
+      <c r="E1622" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1622" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1622" s="83">
+        <v>84815</v>
+      </c>
+      <c r="H1622" s="15">
+        <v>41009</v>
+      </c>
+      <c r="I1622" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1622" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1622" s="18"/>
+      <c r="L1622" s="18"/>
+      <c r="M1622" s="18"/>
+      <c r="N1622" s="40"/>
+      <c r="O1622" s="18"/>
+      <c r="P1622" s="18"/>
+      <c r="Q1622" s="18"/>
+      <c r="R1622" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:18" ht="24.6" thickBot="1">
+      <c r="A1623" s="2">
+        <v>42</v>
+      </c>
+      <c r="B1623" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C1623" s="23" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D1623" s="11">
+        <v>124529941</v>
+      </c>
+      <c r="E1623" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1623" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1623" s="83">
+        <v>4208</v>
+      </c>
+      <c r="H1623" s="15">
+        <v>8251</v>
+      </c>
+      <c r="I1623" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1623" s="50" t="s">
+        <v>564</v>
+      </c>
+      <c r="K1623" s="30" t="s">
+        <v>1596</v>
+      </c>
+      <c r="L1623" s="18"/>
+      <c r="M1623" s="18"/>
+      <c r="N1623" s="40"/>
+      <c r="O1623" s="18"/>
+      <c r="P1623" s="18"/>
+      <c r="Q1623" s="18"/>
+      <c r="R1623" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1624" s="2">
+        <v>1</v>
+      </c>
+      <c r="B1624" s="10">
+        <v>46248</v>
+      </c>
+      <c r="C1624" s="11" t="s">
+        <v>2493</v>
+      </c>
+      <c r="D1624" s="11">
+        <v>12379574</v>
+      </c>
+      <c r="E1624" s="82" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1624" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1624" s="83" t="s">
+        <v>2494</v>
+      </c>
+      <c r="H1624" s="15" t="s">
+        <v>2495</v>
+      </c>
+      <c r="I1624" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1624" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1624" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1624" s="18"/>
+      <c r="M1624" s="18"/>
+      <c r="N1624" s="40"/>
+      <c r="O1624" s="18"/>
+      <c r="P1624" s="49" t="s">
+        <v>2417</v>
+      </c>
+      <c r="Q1624" s="18"/>
+      <c r="R1624" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1625" s="2">
+        <v>2</v>
+      </c>
+      <c r="B1625" s="10">
+        <v>46248</v>
+      </c>
+      <c r="C1625" s="11" t="s">
+        <v>2496</v>
+      </c>
+      <c r="D1625" s="11">
+        <v>17871074</v>
+      </c>
+      <c r="E1625" s="82" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1625" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1625" s="83">
+        <v>7800</v>
+      </c>
+      <c r="H1625" s="15">
+        <v>3262</v>
+      </c>
+      <c r="I1625" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1625" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1625" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1625" s="18"/>
+      <c r="M1625" s="18"/>
+      <c r="N1625" s="40"/>
+      <c r="O1625" s="18"/>
+      <c r="P1625" s="18"/>
+      <c r="Q1625" s="18"/>
+      <c r="R1625" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1626" s="2">
+        <v>3</v>
+      </c>
+      <c r="B1626" s="10">
+        <v>46248</v>
+      </c>
+      <c r="C1626" s="11" t="s">
+        <v>2497</v>
+      </c>
+      <c r="D1626" s="11">
+        <v>8889774</v>
+      </c>
+      <c r="E1626" s="82" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1626" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1626" s="83" t="s">
+        <v>2498</v>
+      </c>
+      <c r="H1626" s="15" t="s">
+        <v>2499</v>
+      </c>
+      <c r="I1626" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1626" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1626" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1626" s="18"/>
+      <c r="M1626" s="18"/>
+      <c r="N1626" s="40"/>
+      <c r="O1626" s="18"/>
+      <c r="P1626" s="49" t="s">
+        <v>2417</v>
+      </c>
+      <c r="Q1626" s="18"/>
+      <c r="R1626" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1627" s="2">
+        <v>4</v>
+      </c>
+      <c r="B1627" s="10">
+        <v>46248</v>
+      </c>
+      <c r="C1627" s="11" t="s">
+        <v>2500</v>
+      </c>
+      <c r="D1627" s="11">
+        <v>20830451</v>
+      </c>
+      <c r="E1627" s="82" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1627" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1627" s="83">
+        <v>9759</v>
+      </c>
+      <c r="H1627" s="15">
+        <v>4920</v>
+      </c>
+      <c r="I1627" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1627" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1627" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1627" s="18"/>
+      <c r="M1627" s="18"/>
+      <c r="N1627" s="40"/>
+      <c r="O1627" s="18"/>
+      <c r="P1627" s="18"/>
+      <c r="Q1627" s="18"/>
+      <c r="R1627" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1628" s="2">
+        <v>5</v>
+      </c>
+      <c r="B1628" s="10">
+        <v>46248</v>
+      </c>
+      <c r="C1628" s="11" t="s">
+        <v>1765</v>
+      </c>
+      <c r="D1628" s="11">
+        <v>19803829</v>
+      </c>
+      <c r="E1628" s="82" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1628" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1628" s="83" t="s">
+        <v>2501</v>
+      </c>
+      <c r="H1628" s="15" t="s">
+        <v>2502</v>
+      </c>
+      <c r="I1628" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1628" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1628" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1628" s="18"/>
+      <c r="M1628" s="18"/>
+      <c r="N1628" s="40"/>
+      <c r="O1628" s="18"/>
+      <c r="P1628" s="49" t="s">
+        <v>2417</v>
+      </c>
+      <c r="Q1628" s="18"/>
+      <c r="R1628" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1629" s="2">
+        <v>6</v>
+      </c>
+      <c r="B1629" s="10">
+        <v>46248</v>
+      </c>
+      <c r="C1629" s="11" t="s">
+        <v>2503</v>
+      </c>
+      <c r="D1629" s="11">
+        <v>18714973</v>
+      </c>
+      <c r="E1629" s="82" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1629" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1629" s="83">
+        <v>1312</v>
+      </c>
+      <c r="H1629" s="15">
+        <v>7124</v>
+      </c>
+      <c r="I1629" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1629" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1629" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1629" s="18"/>
+      <c r="M1629" s="18"/>
+      <c r="N1629" s="40"/>
+      <c r="O1629" s="18"/>
+      <c r="P1629" s="18"/>
+      <c r="Q1629" s="18"/>
+      <c r="R1629" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1630" s="2">
+        <v>7</v>
+      </c>
+      <c r="B1630" s="10">
+        <v>46248</v>
+      </c>
+      <c r="C1630" s="11" t="s">
+        <v>2504</v>
+      </c>
+      <c r="D1630" s="11">
+        <v>12422143</v>
+      </c>
+      <c r="E1630" s="82" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1630" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1630" s="83">
+        <v>9689</v>
+      </c>
+      <c r="H1630" s="15">
+        <v>5365</v>
+      </c>
+      <c r="I1630" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1630" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1630" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1630" s="18"/>
+      <c r="M1630" s="18"/>
+      <c r="N1630" s="40"/>
+      <c r="O1630" s="18"/>
+      <c r="P1630" s="18"/>
+      <c r="Q1630" s="18"/>
+      <c r="R1630" s="21" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A007545-8AEC-43C4-A13D-8ECF8CD186DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C39596D8-9178-42E1-BC4D-F87DEF01C53C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12215" uniqueCount="2505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12298" uniqueCount="2519">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -7553,6 +7553,48 @@
   </si>
   <si>
     <t>OBAID SAID SALIM</t>
+  </si>
+  <si>
+    <t>QASAR IQBAL</t>
+  </si>
+  <si>
+    <t>3536*</t>
+  </si>
+  <si>
+    <t>4535*</t>
+  </si>
+  <si>
+    <t>NADHAL SAID MAAYAUF</t>
+  </si>
+  <si>
+    <t>MAADH KHALIFA RASHID</t>
+  </si>
+  <si>
+    <t>WASEEM</t>
+  </si>
+  <si>
+    <t>NADEEM TALIB</t>
+  </si>
+  <si>
+    <t>BH9455303</t>
+  </si>
+  <si>
+    <t>WILL LOAD ONLY IF CHANCE IS THERE. J</t>
+  </si>
+  <si>
+    <t>SUFYAN</t>
+  </si>
+  <si>
+    <t>AMIR</t>
+  </si>
+  <si>
+    <t>SOYAB KHAN</t>
+  </si>
+  <si>
+    <t>R8013574</t>
+  </si>
+  <si>
+    <t>FAYYAZ MUHAMMAD</t>
   </si>
 </sst>
 </file>
@@ -7960,7 +8002,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8212,6 +8254,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8528,7 +8573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1630"/>
+  <dimension ref="A1:R1641"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -22808,10 +22853,12 @@
       <c r="J290" s="15" t="s">
         <v>382</v>
       </c>
-      <c r="K290" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L290" s="18"/>
+      <c r="K290" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L290" s="53">
+        <v>46250</v>
+      </c>
       <c r="M290" s="18"/>
       <c r="N290" s="40"/>
       <c r="O290" s="53">
@@ -29822,11 +29869,11 @@
       <c r="J432" s="15" t="s">
         <v>839</v>
       </c>
-      <c r="K432" s="11" t="s">
-        <v>2327</v>
+      <c r="K432" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L432" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M432" s="18"/>
       <c r="N432" s="54">
@@ -29874,10 +29921,12 @@
       <c r="J433" s="15" t="s">
         <v>839</v>
       </c>
-      <c r="K433" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L433" s="18"/>
+      <c r="K433" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L433" s="53">
+        <v>46250</v>
+      </c>
       <c r="M433" s="18"/>
       <c r="N433" s="40"/>
       <c r="O433" s="18"/>
@@ -29966,10 +30015,12 @@
       <c r="J435" s="15" t="s">
         <v>848</v>
       </c>
-      <c r="K435" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L435" s="18"/>
+      <c r="K435" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L435" s="53">
+        <v>46250</v>
+      </c>
       <c r="M435" s="18"/>
       <c r="N435" s="54">
         <v>263</v>
@@ -30120,11 +30171,11 @@
       <c r="J438" s="15" t="s">
         <v>848</v>
       </c>
-      <c r="K438" s="11" t="s">
-        <v>2327</v>
+      <c r="K438" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L438" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M438" s="18"/>
       <c r="N438" s="54">
@@ -30874,11 +30925,11 @@
       <c r="J453" s="15" t="s">
         <v>848</v>
       </c>
-      <c r="K453" s="11" t="s">
-        <v>2327</v>
+      <c r="K453" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L453" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M453" s="18"/>
       <c r="N453" s="54">
@@ -30924,11 +30975,11 @@
       <c r="J454" s="15" t="s">
         <v>881</v>
       </c>
-      <c r="K454" s="11" t="s">
-        <v>2327</v>
+      <c r="K454" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L454" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M454" s="18"/>
       <c r="N454" s="54">
@@ -30976,11 +31027,11 @@
       <c r="J455" s="15" t="s">
         <v>881</v>
       </c>
-      <c r="K455" s="11" t="s">
-        <v>2327</v>
+      <c r="K455" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L455" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M455" s="18"/>
       <c r="N455" s="54">
@@ -31026,11 +31077,11 @@
       <c r="J456" s="15" t="s">
         <v>881</v>
       </c>
-      <c r="K456" s="11" t="s">
-        <v>2327</v>
+      <c r="K456" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L456" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M456" s="18"/>
       <c r="N456" s="54">
@@ -31280,11 +31331,11 @@
       <c r="J461" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="K461" s="11" t="s">
-        <v>2327</v>
+      <c r="K461" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L461" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M461" s="18"/>
       <c r="N461" s="54">
@@ -31330,11 +31381,11 @@
       <c r="J462" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="K462" s="11" t="s">
-        <v>2327</v>
+      <c r="K462" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L462" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M462" s="18"/>
       <c r="N462" s="54">
@@ -31380,10 +31431,12 @@
       <c r="J463" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="K463" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L463" s="18"/>
+      <c r="K463" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L463" s="53">
+        <v>46250</v>
+      </c>
       <c r="M463" s="18"/>
       <c r="N463" s="40"/>
       <c r="O463" s="18"/>
@@ -31424,10 +31477,12 @@
       <c r="J464" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="K464" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L464" s="18"/>
+      <c r="K464" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L464" s="53">
+        <v>46250</v>
+      </c>
       <c r="M464" s="18"/>
       <c r="N464" s="40"/>
       <c r="O464" s="18"/>
@@ -31470,11 +31525,11 @@
       <c r="J465" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="K465" s="11" t="s">
-        <v>2327</v>
+      <c r="K465" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L465" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M465" s="18"/>
       <c r="N465" s="54">
@@ -31566,10 +31621,12 @@
       <c r="J467" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="K467" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L467" s="18"/>
+      <c r="K467" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L467" s="53">
+        <v>46250</v>
+      </c>
       <c r="M467" s="18"/>
       <c r="N467" s="40"/>
       <c r="O467" s="18"/>
@@ -31658,10 +31715,12 @@
       <c r="J469" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="K469" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L469" s="18"/>
+      <c r="K469" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L469" s="53">
+        <v>46250</v>
+      </c>
       <c r="M469" s="18"/>
       <c r="N469" s="54">
         <v>960</v>
@@ -31750,10 +31809,12 @@
       <c r="J471" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="K471" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L471" s="18"/>
+      <c r="K471" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L471" s="53">
+        <v>46250</v>
+      </c>
       <c r="M471" s="18"/>
       <c r="N471" s="40"/>
       <c r="O471" s="18"/>
@@ -31796,10 +31857,12 @@
       <c r="J472" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="K472" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L472" s="18"/>
+      <c r="K472" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L472" s="53">
+        <v>46250</v>
+      </c>
       <c r="M472" s="18"/>
       <c r="N472" s="54">
         <v>962</v>
@@ -31840,10 +31903,12 @@
       <c r="J473" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="K473" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L473" s="18"/>
+      <c r="K473" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L473" s="53">
+        <v>46250</v>
+      </c>
       <c r="M473" s="18"/>
       <c r="N473" s="40"/>
       <c r="O473" s="18"/>
@@ -32172,10 +32237,12 @@
       <c r="J480" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="K480" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L480" s="18"/>
+      <c r="K480" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L480" s="53">
+        <v>46250</v>
+      </c>
       <c r="M480" s="18"/>
       <c r="N480" s="40"/>
       <c r="O480" s="18"/>
@@ -32216,10 +32283,12 @@
       <c r="J481" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="K481" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L481" s="18"/>
+      <c r="K481" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L481" s="53">
+        <v>46250</v>
+      </c>
       <c r="M481" s="18"/>
       <c r="N481" s="40"/>
       <c r="O481" s="18"/>
@@ -32260,10 +32329,12 @@
       <c r="J482" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="K482" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L482" s="18"/>
+      <c r="K482" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L482" s="53">
+        <v>46250</v>
+      </c>
       <c r="M482" s="18"/>
       <c r="N482" s="40"/>
       <c r="O482" s="18"/>
@@ -32304,10 +32375,12 @@
       <c r="J483" s="15" t="s">
         <v>923</v>
       </c>
-      <c r="K483" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L483" s="18"/>
+      <c r="K483" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L483" s="53">
+        <v>46250</v>
+      </c>
       <c r="M483" s="18"/>
       <c r="N483" s="54">
         <v>850</v>
@@ -32352,10 +32425,12 @@
       <c r="J484" s="15" t="s">
         <v>923</v>
       </c>
-      <c r="K484" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L484" s="18"/>
+      <c r="K484" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L484" s="53">
+        <v>46250</v>
+      </c>
       <c r="M484" s="18"/>
       <c r="N484" s="54">
         <v>849</v>
@@ -32400,10 +32475,12 @@
       <c r="J485" s="15" t="s">
         <v>923</v>
       </c>
-      <c r="K485" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L485" s="18"/>
+      <c r="K485" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L485" s="53">
+        <v>46250</v>
+      </c>
       <c r="M485" s="18"/>
       <c r="N485" s="54">
         <v>852</v>
@@ -32498,10 +32575,12 @@
       <c r="J487" s="15" t="s">
         <v>923</v>
       </c>
-      <c r="K487" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L487" s="18"/>
+      <c r="K487" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L487" s="53">
+        <v>46250</v>
+      </c>
       <c r="M487" s="18"/>
       <c r="N487" s="40"/>
       <c r="O487" s="18"/>
@@ -32542,10 +32621,12 @@
       <c r="J488" s="15" t="s">
         <v>923</v>
       </c>
-      <c r="K488" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L488" s="18"/>
+      <c r="K488" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L488" s="53">
+        <v>46250</v>
+      </c>
       <c r="M488" s="18"/>
       <c r="N488" s="54">
         <v>851</v>
@@ -32588,10 +32669,12 @@
       <c r="J489" s="15" t="s">
         <v>923</v>
       </c>
-      <c r="K489" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L489" s="18"/>
+      <c r="K489" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L489" s="53">
+        <v>46250</v>
+      </c>
       <c r="M489" s="18"/>
       <c r="N489" s="40"/>
       <c r="O489" s="18"/>
@@ -32684,11 +32767,11 @@
       <c r="J491" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K491" s="11" t="s">
-        <v>2327</v>
+      <c r="K491" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L491" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M491" s="18"/>
       <c r="N491" s="54">
@@ -32736,11 +32819,11 @@
       <c r="J492" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K492" s="11" t="s">
-        <v>2327</v>
+      <c r="K492" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L492" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M492" s="18"/>
       <c r="N492" s="54">
@@ -32788,10 +32871,12 @@
       <c r="J493" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K493" s="67" t="s">
-        <v>1285</v>
-      </c>
-      <c r="L493" s="18"/>
+      <c r="K493" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L493" s="53">
+        <v>46250</v>
+      </c>
       <c r="M493" s="18"/>
       <c r="N493" s="40"/>
       <c r="O493" s="18"/>
@@ -32834,11 +32919,11 @@
       <c r="J494" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K494" s="11" t="s">
-        <v>2327</v>
+      <c r="K494" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L494" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M494" s="18"/>
       <c r="N494" s="54">
@@ -32886,10 +32971,12 @@
       <c r="J495" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K495" s="67" t="s">
-        <v>1285</v>
-      </c>
-      <c r="L495" s="18"/>
+      <c r="K495" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L495" s="53">
+        <v>46250</v>
+      </c>
       <c r="M495" s="18"/>
       <c r="N495" s="40"/>
       <c r="O495" s="18"/>
@@ -32932,11 +33019,11 @@
       <c r="J496" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K496" s="11" t="s">
-        <v>2327</v>
+      <c r="K496" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L496" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M496" s="18"/>
       <c r="N496" s="54">
@@ -32984,10 +33071,12 @@
       <c r="J497" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K497" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L497" s="18"/>
+      <c r="K497" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L497" s="53">
+        <v>46250</v>
+      </c>
       <c r="M497" s="18"/>
       <c r="N497" s="54">
         <v>1020</v>
@@ -33032,11 +33121,11 @@
       <c r="J498" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K498" s="11" t="s">
-        <v>2327</v>
+      <c r="K498" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L498" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M498" s="18"/>
       <c r="N498" s="54">
@@ -33082,10 +33171,12 @@
       <c r="J499" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K499" s="67" t="s">
-        <v>1285</v>
-      </c>
-      <c r="L499" s="18"/>
+      <c r="K499" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L499" s="53">
+        <v>46250</v>
+      </c>
       <c r="M499" s="18"/>
       <c r="N499" s="54">
         <v>808</v>
@@ -33130,10 +33221,12 @@
       <c r="J500" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K500" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L500" s="18"/>
+      <c r="K500" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L500" s="53">
+        <v>46250</v>
+      </c>
       <c r="M500" s="18"/>
       <c r="N500" s="40"/>
       <c r="O500" s="18"/>
@@ -33228,11 +33321,11 @@
       <c r="J502" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K502" s="11" t="s">
-        <v>2327</v>
+      <c r="K502" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L502" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M502" s="18"/>
       <c r="N502" s="54">
@@ -33278,11 +33371,11 @@
       <c r="J503" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K503" s="67" t="s">
-        <v>1285</v>
+      <c r="K503" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L503" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M503" s="18"/>
       <c r="N503" s="54">
@@ -33328,10 +33421,12 @@
       <c r="J504" s="15" t="s">
         <v>937</v>
       </c>
-      <c r="K504" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L504" s="18"/>
+      <c r="K504" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L504" s="53">
+        <v>46250</v>
+      </c>
       <c r="M504" s="18"/>
       <c r="N504" s="54">
         <v>1018</v>
@@ -33964,11 +34059,11 @@
       <c r="J517" s="15" t="s">
         <v>968</v>
       </c>
-      <c r="K517" s="11" t="s">
-        <v>2327</v>
+      <c r="K517" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L517" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M517" s="18"/>
       <c r="N517" s="54">
@@ -34014,10 +34109,12 @@
       <c r="J518" s="15" t="s">
         <v>971</v>
       </c>
-      <c r="K518" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L518" s="18"/>
+      <c r="K518" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L518" s="53">
+        <v>46250</v>
+      </c>
       <c r="M518" s="18"/>
       <c r="N518" s="54">
         <v>992</v>
@@ -34060,11 +34157,11 @@
       <c r="J519" s="15" t="s">
         <v>971</v>
       </c>
-      <c r="K519" s="11" t="s">
-        <v>2327</v>
+      <c r="K519" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L519" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M519" s="18"/>
       <c r="N519" s="54">
@@ -34463,7 +34560,7 @@
         <v>46250</v>
       </c>
       <c r="M527" s="28"/>
-      <c r="N527" s="27">
+      <c r="N527" s="54">
         <v>416</v>
       </c>
       <c r="O527" s="28"/>
@@ -37708,10 +37805,12 @@
       <c r="J593" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K593" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L593" s="18"/>
+      <c r="K593" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L593" s="53">
+        <v>46250</v>
+      </c>
       <c r="M593" s="18"/>
       <c r="N593" s="40"/>
       <c r="O593" s="18"/>
@@ -37752,10 +37851,12 @@
       <c r="J594" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K594" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L594" s="18"/>
+      <c r="K594" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L594" s="53">
+        <v>46250</v>
+      </c>
       <c r="M594" s="18"/>
       <c r="N594" s="54">
         <v>917</v>
@@ -37852,11 +37953,11 @@
       <c r="J596" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K596" s="11" t="s">
-        <v>2327</v>
+      <c r="K596" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L596" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M596" s="18"/>
       <c r="N596" s="54">
@@ -37956,11 +38057,11 @@
       <c r="J598" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K598" s="11" t="s">
-        <v>2327</v>
+      <c r="K598" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L598" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M598" s="18"/>
       <c r="N598" s="54">
@@ -38008,11 +38109,11 @@
       <c r="J599" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K599" s="11" t="s">
-        <v>2327</v>
+      <c r="K599" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L599" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M599" s="18"/>
       <c r="N599" s="54">
@@ -38060,11 +38161,11 @@
       <c r="J600" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K600" s="11" t="s">
-        <v>2327</v>
+      <c r="K600" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L600" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M600" s="18"/>
       <c r="N600" s="54">
@@ -38112,11 +38213,11 @@
       <c r="J601" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K601" s="11" t="s">
-        <v>2327</v>
+      <c r="K601" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L601" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M601" s="18"/>
       <c r="N601" s="54">
@@ -38164,11 +38265,11 @@
       <c r="J602" s="50" t="s">
         <v>564</v>
       </c>
-      <c r="K602" s="11" t="s">
-        <v>2327</v>
+      <c r="K602" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L602" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M602" s="18"/>
       <c r="N602" s="54">
@@ -39140,10 +39241,12 @@
       <c r="J621" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K621" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L621" s="18"/>
+      <c r="K621" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L621" s="53">
+        <v>46250</v>
+      </c>
       <c r="M621" s="18"/>
       <c r="N621" s="40"/>
       <c r="O621" s="18"/>
@@ -39186,10 +39289,12 @@
       <c r="J622" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K622" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L622" s="18"/>
+      <c r="K622" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L622" s="53">
+        <v>46250</v>
+      </c>
       <c r="M622" s="18"/>
       <c r="N622" s="40"/>
       <c r="O622" s="18"/>
@@ -39282,10 +39387,12 @@
       <c r="J624" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K624" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L624" s="18"/>
+      <c r="K624" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L624" s="53">
+        <v>46250</v>
+      </c>
       <c r="M624" s="18"/>
       <c r="N624" s="54">
         <v>1210</v>
@@ -39328,10 +39435,12 @@
       <c r="J625" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K625" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L625" s="18"/>
+      <c r="K625" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L625" s="53">
+        <v>46250</v>
+      </c>
       <c r="M625" s="18"/>
       <c r="N625" s="40"/>
       <c r="O625" s="18"/>
@@ -39374,10 +39483,12 @@
       <c r="J626" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K626" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L626" s="18"/>
+      <c r="K626" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L626" s="53">
+        <v>46250</v>
+      </c>
       <c r="M626" s="18"/>
       <c r="N626" s="40"/>
       <c r="O626" s="18"/>
@@ -39420,10 +39531,12 @@
       <c r="J627" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K627" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L627" s="18"/>
+      <c r="K627" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L627" s="53">
+        <v>46250</v>
+      </c>
       <c r="M627" s="18"/>
       <c r="N627" s="40"/>
       <c r="O627" s="18"/>
@@ -39466,10 +39579,12 @@
       <c r="J628" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K628" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L628" s="18"/>
+      <c r="K628" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L628" s="53">
+        <v>46250</v>
+      </c>
       <c r="M628" s="18"/>
       <c r="N628" s="54">
         <v>275</v>
@@ -39516,11 +39631,11 @@
       <c r="J629" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K629" s="11" t="s">
-        <v>2327</v>
+      <c r="K629" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L629" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M629" s="18"/>
       <c r="N629" s="54">
@@ -39568,10 +39683,12 @@
       <c r="J630" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K630" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L630" s="18"/>
+      <c r="K630" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L630" s="53">
+        <v>46250</v>
+      </c>
       <c r="M630" s="18"/>
       <c r="N630" s="40"/>
       <c r="O630" s="18"/>
@@ -39614,10 +39731,12 @@
       <c r="J631" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K631" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L631" s="18"/>
+      <c r="K631" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L631" s="53">
+        <v>46250</v>
+      </c>
       <c r="M631" s="18"/>
       <c r="N631" s="40"/>
       <c r="O631" s="18"/>
@@ -39756,11 +39875,11 @@
       <c r="J634" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K634" s="11" t="s">
-        <v>2327</v>
+      <c r="K634" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L634" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M634" s="18"/>
       <c r="N634" s="54">
@@ -39808,10 +39927,12 @@
       <c r="J635" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K635" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L635" s="18"/>
+      <c r="K635" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L635" s="53">
+        <v>46250</v>
+      </c>
       <c r="M635" s="18"/>
       <c r="N635" s="54">
         <v>160</v>
@@ -39858,11 +39979,11 @@
       <c r="J636" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K636" s="11" t="s">
-        <v>2327</v>
+      <c r="K636" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L636" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M636" s="18"/>
       <c r="N636" s="54">
@@ -39910,11 +40031,11 @@
       <c r="J637" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K637" s="11" t="s">
-        <v>2327</v>
+      <c r="K637" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L637" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M637" s="18"/>
       <c r="N637" s="54">
@@ -39962,11 +40083,11 @@
       <c r="J638" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K638" s="11" t="s">
-        <v>2327</v>
+      <c r="K638" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L638" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M638" s="18"/>
       <c r="N638" s="54">
@@ -40014,14 +40135,14 @@
       <c r="J639" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K639" s="11" t="s">
-        <v>2327</v>
+      <c r="K639" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L639" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M639" s="18"/>
-      <c r="N639" s="54" t="s">
+      <c r="N639" s="76" t="s">
         <v>2471</v>
       </c>
       <c r="O639" s="53">
@@ -40066,14 +40187,14 @@
       <c r="J640" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K640" s="11" t="s">
-        <v>2327</v>
+      <c r="K640" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L640" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M640" s="18"/>
-      <c r="N640" s="54" t="s">
+      <c r="N640" s="76" t="s">
         <v>2472</v>
       </c>
       <c r="O640" s="53">
@@ -40118,10 +40239,12 @@
       <c r="J641" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K641" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L641" s="18"/>
+      <c r="K641" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L641" s="53">
+        <v>46250</v>
+      </c>
       <c r="M641" s="18"/>
       <c r="N641" s="54">
         <v>959</v>
@@ -40166,10 +40289,12 @@
       <c r="J642" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K642" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L642" s="18"/>
+      <c r="K642" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L642" s="53">
+        <v>46250</v>
+      </c>
       <c r="M642" s="18"/>
       <c r="N642" s="54">
         <v>958</v>
@@ -40214,8 +40339,8 @@
       <c r="J643" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K643" s="11" t="s">
-        <v>2327</v>
+      <c r="K643" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L643" s="53">
         <v>46246</v>
@@ -40266,10 +40391,12 @@
       <c r="J644" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K644" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L644" s="18"/>
+      <c r="K644" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L644" s="53">
+        <v>46250</v>
+      </c>
       <c r="M644" s="18"/>
       <c r="N644" s="54">
         <v>991</v>
@@ -40314,10 +40441,12 @@
       <c r="J645" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K645" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L645" s="18"/>
+      <c r="K645" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L645" s="53">
+        <v>46250</v>
+      </c>
       <c r="M645" s="18"/>
       <c r="N645" s="40"/>
       <c r="O645" s="18"/>
@@ -40360,10 +40489,12 @@
       <c r="J646" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K646" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L646" s="18"/>
+      <c r="K646" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L646" s="53">
+        <v>46250</v>
+      </c>
       <c r="M646" s="18"/>
       <c r="N646" s="40"/>
       <c r="O646" s="18"/>
@@ -40406,11 +40537,11 @@
       <c r="J647" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K647" s="11" t="s">
-        <v>2327</v>
+      <c r="K647" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L647" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M647" s="18"/>
       <c r="N647" s="54">
@@ -40456,10 +40587,12 @@
       <c r="J648" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K648" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L648" s="18"/>
+      <c r="K648" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L648" s="53">
+        <v>46250</v>
+      </c>
       <c r="M648" s="18"/>
       <c r="N648" s="54">
         <v>1001</v>
@@ -40504,10 +40637,12 @@
       <c r="J649" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K649" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L649" s="18"/>
+      <c r="K649" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L649" s="53">
+        <v>46250</v>
+      </c>
       <c r="M649" s="18"/>
       <c r="N649" s="40"/>
       <c r="O649" s="18"/>
@@ -40550,8 +40685,8 @@
       <c r="J650" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K650" s="17" t="s">
-        <v>12</v>
+      <c r="K650" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L650" s="18"/>
       <c r="M650" s="18"/>
@@ -40654,11 +40789,11 @@
       <c r="J652" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K652" s="11" t="s">
-        <v>2327</v>
+      <c r="K652" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L652" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M652" s="18"/>
       <c r="N652" s="54" t="s">
@@ -40706,11 +40841,11 @@
       <c r="J653" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K653" s="11" t="s">
-        <v>2327</v>
+      <c r="K653" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L653" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M653" s="18"/>
       <c r="N653" s="54">
@@ -40756,11 +40891,11 @@
       <c r="J654" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K654" s="11" t="s">
-        <v>2327</v>
+      <c r="K654" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L654" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M654" s="18"/>
       <c r="N654" s="54" t="s">
@@ -40808,11 +40943,11 @@
       <c r="J655" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K655" s="11" t="s">
-        <v>2327</v>
+      <c r="K655" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L655" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M655" s="18"/>
       <c r="N655" s="76" t="s">
@@ -40908,11 +41043,11 @@
       <c r="J657" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K657" s="11" t="s">
-        <v>2327</v>
+      <c r="K657" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L657" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M657" s="18"/>
       <c r="N657" s="54">
@@ -40958,11 +41093,11 @@
       <c r="J658" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K658" s="11" t="s">
-        <v>2327</v>
+      <c r="K658" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L658" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M658" s="18"/>
       <c r="N658" s="54">
@@ -41010,10 +41145,12 @@
       <c r="J659" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K659" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L659" s="18"/>
+      <c r="K659" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L659" s="53">
+        <v>46250</v>
+      </c>
       <c r="M659" s="18"/>
       <c r="N659" s="40"/>
       <c r="O659" s="18"/>
@@ -41056,10 +41193,12 @@
       <c r="J660" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K660" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L660" s="18"/>
+      <c r="K660" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L660" s="53">
+        <v>46250</v>
+      </c>
       <c r="M660" s="18"/>
       <c r="N660" s="40"/>
       <c r="O660" s="18"/>
@@ -41102,10 +41241,12 @@
       <c r="J661" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K661" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L661" s="18"/>
+      <c r="K661" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L661" s="53">
+        <v>46250</v>
+      </c>
       <c r="M661" s="18"/>
       <c r="N661" s="40"/>
       <c r="O661" s="18"/>
@@ -41148,10 +41289,12 @@
       <c r="J662" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K662" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L662" s="18"/>
+      <c r="K662" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L662" s="53">
+        <v>46250</v>
+      </c>
       <c r="M662" s="18"/>
       <c r="N662" s="40"/>
       <c r="O662" s="18"/>
@@ -41194,10 +41337,12 @@
       <c r="J663" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K663" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L663" s="18"/>
+      <c r="K663" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L663" s="53">
+        <v>46250</v>
+      </c>
       <c r="M663" s="18"/>
       <c r="N663" s="40"/>
       <c r="O663" s="18"/>
@@ -41240,11 +41385,11 @@
       <c r="J664" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K664" s="11" t="s">
-        <v>2327</v>
+      <c r="K664" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L664" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M664" s="18"/>
       <c r="N664" s="54">
@@ -41290,10 +41435,12 @@
       <c r="J665" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K665" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L665" s="18"/>
+      <c r="K665" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L665" s="53">
+        <v>46250</v>
+      </c>
       <c r="M665" s="18"/>
       <c r="N665" s="54">
         <v>1159</v>
@@ -41338,10 +41485,12 @@
       <c r="J666" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K666" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L666" s="18"/>
+      <c r="K666" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L666" s="53">
+        <v>46250</v>
+      </c>
       <c r="M666" s="18"/>
       <c r="N666" s="54">
         <v>1158</v>
@@ -41386,10 +41535,12 @@
       <c r="J667" s="51" t="s">
         <v>776</v>
       </c>
-      <c r="K667" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L667" s="18"/>
+      <c r="K667" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L667" s="53">
+        <v>46250</v>
+      </c>
       <c r="M667" s="18"/>
       <c r="N667" s="40"/>
       <c r="O667" s="18"/>
@@ -42066,10 +42217,12 @@
       <c r="J681" s="15" t="s">
         <v>832</v>
       </c>
-      <c r="K681" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L681" s="18"/>
+      <c r="K681" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L681" s="53">
+        <v>46250</v>
+      </c>
       <c r="M681" s="18"/>
       <c r="N681" s="40"/>
       <c r="O681" s="18"/>
@@ -42258,12 +42411,14 @@
         <v>485</v>
       </c>
       <c r="J685" s="18"/>
-      <c r="K685" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L685" s="18"/>
+      <c r="K685" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L685" s="53">
+        <v>46250</v>
+      </c>
       <c r="M685" s="18"/>
-      <c r="N685" s="54" t="s">
+      <c r="N685" s="76" t="s">
         <v>2477</v>
       </c>
       <c r="O685" s="18"/>
@@ -42404,10 +42559,12 @@
         <v>485</v>
       </c>
       <c r="J688" s="18"/>
-      <c r="K688" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L688" s="18"/>
+      <c r="K688" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L688" s="53">
+        <v>46250</v>
+      </c>
       <c r="M688" s="18"/>
       <c r="N688" s="40"/>
       <c r="O688" s="18"/>
@@ -42448,10 +42605,12 @@
         <v>485</v>
       </c>
       <c r="J689" s="18"/>
-      <c r="K689" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L689" s="18"/>
+      <c r="K689" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L689" s="53">
+        <v>46250</v>
+      </c>
       <c r="M689" s="18"/>
       <c r="N689" s="40"/>
       <c r="O689" s="18"/>
@@ -42492,11 +42651,11 @@
         <v>485</v>
       </c>
       <c r="J690" s="18"/>
-      <c r="K690" s="11" t="s">
-        <v>2327</v>
+      <c r="K690" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L690" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M690" s="18"/>
       <c r="N690" s="54">
@@ -42540,10 +42699,12 @@
       <c r="J691" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="K691" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L691" s="18"/>
+      <c r="K691" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L691" s="53">
+        <v>46250</v>
+      </c>
       <c r="M691" s="18"/>
       <c r="N691" s="40"/>
       <c r="O691" s="18"/>
@@ -42586,11 +42747,11 @@
       <c r="J692" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="K692" s="11" t="s">
-        <v>2327</v>
+      <c r="K692" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L692" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M692" s="18"/>
       <c r="N692" s="54">
@@ -42634,11 +42795,11 @@
         <v>485</v>
       </c>
       <c r="J693" s="18"/>
-      <c r="K693" s="11" t="s">
-        <v>2327</v>
+      <c r="K693" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L693" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M693" s="18"/>
       <c r="N693" s="54">
@@ -43072,10 +43233,12 @@
       <c r="J702" s="15" t="s">
         <v>1028</v>
       </c>
-      <c r="K702" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L702" s="18"/>
+      <c r="K702" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L702" s="53">
+        <v>46250</v>
+      </c>
       <c r="M702" s="18"/>
       <c r="N702" s="40"/>
       <c r="O702" s="18"/>
@@ -43116,11 +43279,11 @@
       <c r="J703" s="15" t="s">
         <v>1028</v>
       </c>
-      <c r="K703" s="11" t="s">
-        <v>2327</v>
+      <c r="K703" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L703" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M703" s="18"/>
       <c r="N703" s="54">
@@ -43168,11 +43331,11 @@
       <c r="J704" s="15" t="s">
         <v>1028</v>
       </c>
-      <c r="K704" s="11" t="s">
-        <v>2327</v>
+      <c r="K704" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L704" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M704" s="18"/>
       <c r="N704" s="54">
@@ -43220,10 +43383,12 @@
       <c r="J705" s="15" t="s">
         <v>1028</v>
       </c>
-      <c r="K705" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L705" s="18"/>
+      <c r="K705" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L705" s="53">
+        <v>46250</v>
+      </c>
       <c r="M705" s="18"/>
       <c r="N705" s="40"/>
       <c r="O705" s="18"/>
@@ -43266,11 +43431,11 @@
       <c r="J706" s="15" t="s">
         <v>1028</v>
       </c>
-      <c r="K706" s="11" t="s">
-        <v>2327</v>
+      <c r="K706" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L706" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M706" s="18"/>
       <c r="N706" s="54">
@@ -43318,10 +43483,12 @@
       <c r="J707" s="15" t="s">
         <v>1028</v>
       </c>
-      <c r="K707" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L707" s="18"/>
+      <c r="K707" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L707" s="53">
+        <v>46250</v>
+      </c>
       <c r="M707" s="18"/>
       <c r="N707" s="40"/>
       <c r="O707" s="18"/>
@@ -43364,11 +43531,11 @@
       <c r="J708" s="15" t="s">
         <v>1028</v>
       </c>
-      <c r="K708" s="11" t="s">
-        <v>2327</v>
+      <c r="K708" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L708" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M708" s="18"/>
       <c r="N708" s="54">
@@ -43416,10 +43583,12 @@
       <c r="J709" s="15" t="s">
         <v>1028</v>
       </c>
-      <c r="K709" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L709" s="18"/>
+      <c r="K709" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L709" s="53">
+        <v>46250</v>
+      </c>
       <c r="M709" s="18"/>
       <c r="N709" s="54">
         <v>860</v>
@@ -43462,10 +43631,12 @@
       <c r="J710" s="15" t="s">
         <v>1028</v>
       </c>
-      <c r="K710" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L710" s="18"/>
+      <c r="K710" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L710" s="53">
+        <v>46250</v>
+      </c>
       <c r="M710" s="18"/>
       <c r="N710" s="54">
         <v>863</v>
@@ -43510,10 +43681,12 @@
       <c r="J711" s="15" t="s">
         <v>1028</v>
       </c>
-      <c r="K711" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L711" s="18"/>
+      <c r="K711" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L711" s="53">
+        <v>46250</v>
+      </c>
       <c r="M711" s="18"/>
       <c r="N711" s="54">
         <v>865</v>
@@ -43558,11 +43731,11 @@
       <c r="J712" s="15" t="s">
         <v>1028</v>
       </c>
-      <c r="K712" s="11" t="s">
-        <v>2327</v>
+      <c r="K712" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L712" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M712" s="18"/>
       <c r="N712" s="54">
@@ -43610,11 +43783,11 @@
       <c r="J713" s="15" t="s">
         <v>1028</v>
       </c>
-      <c r="K713" s="11" t="s">
-        <v>2327</v>
+      <c r="K713" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L713" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M713" s="18"/>
       <c r="N713" s="54">
@@ -43662,10 +43835,12 @@
       <c r="J714" s="15" t="s">
         <v>1028</v>
       </c>
-      <c r="K714" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L714" s="18"/>
+      <c r="K714" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L714" s="53">
+        <v>46250</v>
+      </c>
       <c r="M714" s="18"/>
       <c r="N714" s="54">
         <v>881</v>
@@ -43710,10 +43885,12 @@
       <c r="J715" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K715" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L715" s="18"/>
+      <c r="K715" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L715" s="53">
+        <v>46250</v>
+      </c>
       <c r="M715" s="18"/>
       <c r="N715" s="40"/>
       <c r="O715" s="18"/>
@@ -43756,10 +43933,12 @@
       <c r="J716" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="K716" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L716" s="18"/>
+      <c r="K716" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L716" s="53">
+        <v>46250</v>
+      </c>
       <c r="M716" s="18"/>
       <c r="N716" s="40"/>
       <c r="O716" s="18"/>
@@ -43852,11 +44031,11 @@
       <c r="J718" s="15" t="s">
         <v>1058</v>
       </c>
-      <c r="K718" s="11" t="s">
-        <v>2327</v>
+      <c r="K718" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L718" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M718" s="18"/>
       <c r="N718" s="54">
@@ -43902,11 +44081,11 @@
       <c r="J719" s="15" t="s">
         <v>1058</v>
       </c>
-      <c r="K719" s="11" t="s">
-        <v>2327</v>
+      <c r="K719" s="52" t="s">
+        <v>837</v>
       </c>
       <c r="L719" s="53">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="M719" s="18"/>
       <c r="N719" s="54">
@@ -51366,10 +51545,12 @@
       <c r="J870" s="15" t="s">
         <v>1704</v>
       </c>
-      <c r="K870" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L870" s="18"/>
+      <c r="K870" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L870" s="53">
+        <v>46250</v>
+      </c>
       <c r="M870" s="18"/>
       <c r="N870" s="40"/>
       <c r="O870" s="18"/>
@@ -53544,10 +53725,12 @@
       <c r="J916" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="K916" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L916" s="18"/>
+      <c r="K916" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L916" s="53">
+        <v>46250</v>
+      </c>
       <c r="M916" s="18"/>
       <c r="N916" s="40"/>
       <c r="O916" s="18"/>
@@ -61682,10 +61865,12 @@
       <c r="J1080" s="15" t="s">
         <v>1672</v>
       </c>
-      <c r="K1080" s="67" t="s">
-        <v>1285</v>
-      </c>
-      <c r="L1080" s="18"/>
+      <c r="K1080" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1080" s="53">
+        <v>46250</v>
+      </c>
       <c r="M1080" s="18"/>
       <c r="N1080" s="40"/>
       <c r="O1080" s="18"/>
@@ -63838,7 +64023,9 @@
       <c r="L1127" s="18"/>
       <c r="M1127" s="18"/>
       <c r="N1127" s="40"/>
-      <c r="O1127" s="18"/>
+      <c r="O1127" s="53">
+        <v>46246</v>
+      </c>
       <c r="P1127" s="18"/>
       <c r="Q1127" s="18"/>
       <c r="R1127" s="22" t="s">
@@ -63940,7 +64127,9 @@
       <c r="D1130" s="68">
         <v>5884668</v>
       </c>
-      <c r="E1130" s="18"/>
+      <c r="E1130" s="37" t="s">
+        <v>121</v>
+      </c>
       <c r="F1130" s="16" t="s">
         <v>122</v>
       </c>
@@ -87057,6 +87246,498 @@
         <v>14</v>
       </c>
     </row>
+    <row r="1631" spans="1:18" ht="24.6" thickBot="1">
+      <c r="A1631" s="2">
+        <v>8</v>
+      </c>
+      <c r="B1631" s="10">
+        <v>46248</v>
+      </c>
+      <c r="C1631" s="11" t="s">
+        <v>2505</v>
+      </c>
+      <c r="D1631" s="11">
+        <v>116631958</v>
+      </c>
+      <c r="E1631" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1631" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1631" s="83" t="s">
+        <v>2506</v>
+      </c>
+      <c r="H1631" s="15" t="s">
+        <v>2507</v>
+      </c>
+      <c r="I1631" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1631" s="19" t="s">
+        <v>1672</v>
+      </c>
+      <c r="K1631" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1631" s="18"/>
+      <c r="M1631" s="18"/>
+      <c r="N1631" s="40"/>
+      <c r="O1631" s="18"/>
+      <c r="P1631" s="18"/>
+      <c r="Q1631" s="18"/>
+      <c r="R1631" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1632" s="2">
+        <v>9</v>
+      </c>
+      <c r="B1632" s="10">
+        <v>46248</v>
+      </c>
+      <c r="C1632" s="11" t="s">
+        <v>2508</v>
+      </c>
+      <c r="D1632" s="11">
+        <v>2540146</v>
+      </c>
+      <c r="E1632" s="82" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1632" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1632" s="83">
+        <v>2704</v>
+      </c>
+      <c r="H1632" s="15">
+        <v>3177</v>
+      </c>
+      <c r="I1632" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1632" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1632" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1632" s="18"/>
+      <c r="M1632" s="18"/>
+      <c r="N1632" s="40"/>
+      <c r="O1632" s="18"/>
+      <c r="P1632" s="18"/>
+      <c r="Q1632" s="18"/>
+      <c r="R1632" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1633" s="2">
+        <v>10</v>
+      </c>
+      <c r="B1633" s="10">
+        <v>46248</v>
+      </c>
+      <c r="C1633" s="11" t="s">
+        <v>2509</v>
+      </c>
+      <c r="D1633" s="11">
+        <v>13938921</v>
+      </c>
+      <c r="E1633" s="82" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1633" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1633" s="83">
+        <v>4427</v>
+      </c>
+      <c r="H1633" s="15">
+        <v>7368</v>
+      </c>
+      <c r="I1633" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1633" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1633" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1633" s="18"/>
+      <c r="M1633" s="18"/>
+      <c r="N1633" s="40"/>
+      <c r="O1633" s="18"/>
+      <c r="P1633" s="18"/>
+      <c r="Q1633" s="18"/>
+      <c r="R1633" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1634" s="2">
+        <v>11</v>
+      </c>
+      <c r="B1634" s="10">
+        <v>46248</v>
+      </c>
+      <c r="C1634" s="11" t="s">
+        <v>2510</v>
+      </c>
+      <c r="D1634" s="11">
+        <v>137677624</v>
+      </c>
+      <c r="E1634" s="82" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1634" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1634" s="83">
+        <v>1310</v>
+      </c>
+      <c r="H1634" s="15">
+        <v>3014</v>
+      </c>
+      <c r="I1634" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1634" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="K1634" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1634" s="18"/>
+      <c r="M1634" s="18"/>
+      <c r="N1634" s="40"/>
+      <c r="O1634" s="18"/>
+      <c r="P1634" s="18"/>
+      <c r="Q1634" s="18"/>
+      <c r="R1634" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:18" ht="41.4" thickBot="1">
+      <c r="A1635" s="2">
+        <v>12</v>
+      </c>
+      <c r="B1635" s="10">
+        <v>46248</v>
+      </c>
+      <c r="C1635" s="11" t="s">
+        <v>2511</v>
+      </c>
+      <c r="D1635" s="11" t="s">
+        <v>2512</v>
+      </c>
+      <c r="E1635" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1635" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1635" s="83">
+        <v>13662</v>
+      </c>
+      <c r="H1635" s="15">
+        <v>92600</v>
+      </c>
+      <c r="I1635" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1635" s="15" t="s">
+        <v>961</v>
+      </c>
+      <c r="K1635" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1635" s="18"/>
+      <c r="M1635" s="18"/>
+      <c r="N1635" s="40"/>
+      <c r="O1635" s="18"/>
+      <c r="P1635" s="49" t="s">
+        <v>2513</v>
+      </c>
+      <c r="Q1635" s="18"/>
+      <c r="R1635" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1636" s="2">
+        <v>13</v>
+      </c>
+      <c r="B1636" s="10">
+        <v>46248</v>
+      </c>
+      <c r="C1636" s="11" t="s">
+        <v>2514</v>
+      </c>
+      <c r="D1636" s="11">
+        <v>131268366</v>
+      </c>
+      <c r="E1636" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1636" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1636" s="83">
+        <v>6030</v>
+      </c>
+      <c r="H1636" s="15">
+        <v>6055</v>
+      </c>
+      <c r="I1636" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1636" s="15" t="s">
+        <v>2438</v>
+      </c>
+      <c r="K1636" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1636" s="18"/>
+      <c r="M1636" s="18"/>
+      <c r="N1636" s="40"/>
+      <c r="O1636" s="18"/>
+      <c r="P1636" s="18"/>
+      <c r="Q1636" s="18"/>
+      <c r="R1636" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:18" ht="24.6" thickBot="1">
+      <c r="A1637" s="2">
+        <v>14</v>
+      </c>
+      <c r="B1637" s="10">
+        <v>46248</v>
+      </c>
+      <c r="C1637" s="11" t="s">
+        <v>2515</v>
+      </c>
+      <c r="D1637" s="11">
+        <v>85817633</v>
+      </c>
+      <c r="E1637" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1637" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1637" s="83">
+        <v>9082</v>
+      </c>
+      <c r="H1637" s="15">
+        <v>3546</v>
+      </c>
+      <c r="I1637" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1637" s="15" t="s">
+        <v>1672</v>
+      </c>
+      <c r="K1637" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1637" s="53">
+        <v>46250</v>
+      </c>
+      <c r="M1637" s="18"/>
+      <c r="N1637" s="40"/>
+      <c r="O1637" s="18"/>
+      <c r="P1637" s="18"/>
+      <c r="Q1637" s="18"/>
+      <c r="R1637" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:18" ht="16.2" thickBot="1">
+      <c r="A1638" s="2">
+        <v>15</v>
+      </c>
+      <c r="B1638" s="10">
+        <v>46248</v>
+      </c>
+      <c r="C1638" s="11" t="s">
+        <v>2516</v>
+      </c>
+      <c r="D1638" s="11" t="s">
+        <v>2517</v>
+      </c>
+      <c r="E1638" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1638" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1638" s="83">
+        <v>81144</v>
+      </c>
+      <c r="H1638" s="15">
+        <v>55344</v>
+      </c>
+      <c r="I1638" s="22" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1638" s="15" t="s">
+        <v>1672</v>
+      </c>
+      <c r="K1638" s="52" t="s">
+        <v>837</v>
+      </c>
+      <c r="L1638" s="53">
+        <v>46250</v>
+      </c>
+      <c r="M1638" s="18"/>
+      <c r="N1638" s="40"/>
+      <c r="O1638" s="18"/>
+      <c r="P1638" s="18"/>
+      <c r="Q1638" s="18"/>
+      <c r="R1638" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1639" s="2">
+        <v>16</v>
+      </c>
+      <c r="B1639" s="10">
+        <v>46248</v>
+      </c>
+      <c r="C1639" s="55" t="s">
+        <v>1748</v>
+      </c>
+      <c r="D1639" s="68">
+        <v>5884668</v>
+      </c>
+      <c r="E1639" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1639" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1639" s="71">
+        <v>1275</v>
+      </c>
+      <c r="H1639" s="72">
+        <v>4441</v>
+      </c>
+      <c r="I1639" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1639" s="15" t="s">
+        <v>2438</v>
+      </c>
+      <c r="K1639" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1639" s="18"/>
+      <c r="M1639" s="18"/>
+      <c r="N1639" s="40"/>
+      <c r="O1639" s="18"/>
+      <c r="P1639" s="18"/>
+      <c r="Q1639" s="18"/>
+      <c r="R1639" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1640" s="2">
+        <v>17</v>
+      </c>
+      <c r="B1640" s="10">
+        <v>46248</v>
+      </c>
+      <c r="C1640" s="11" t="s">
+        <v>993</v>
+      </c>
+      <c r="D1640" s="11">
+        <v>137332303</v>
+      </c>
+      <c r="E1640" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1640" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1640" s="83">
+        <v>3418</v>
+      </c>
+      <c r="H1640" s="15">
+        <v>934</v>
+      </c>
+      <c r="I1640" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1640" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1640" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1640" s="18"/>
+      <c r="M1640" s="18"/>
+      <c r="N1640" s="40"/>
+      <c r="O1640" s="18"/>
+      <c r="P1640" s="18"/>
+      <c r="Q1640" s="11">
+        <v>97919951</v>
+      </c>
+      <c r="R1640" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:18" ht="24.6" thickBot="1">
+      <c r="A1641" s="85">
+        <v>18</v>
+      </c>
+      <c r="B1641" s="10">
+        <v>46248</v>
+      </c>
+      <c r="C1641" s="11" t="s">
+        <v>2518</v>
+      </c>
+      <c r="D1641" s="11">
+        <v>87794825</v>
+      </c>
+      <c r="E1641" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1641" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1641" s="83">
+        <v>7650</v>
+      </c>
+      <c r="H1641" s="15">
+        <v>2748</v>
+      </c>
+      <c r="I1641" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1641" s="15" t="s">
+        <v>1457</v>
+      </c>
+      <c r="K1641" s="60" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L1641" s="18"/>
+      <c r="M1641" s="18"/>
+      <c r="N1641" s="40"/>
+      <c r="O1641" s="18"/>
+      <c r="P1641" s="18"/>
+      <c r="Q1641" s="18"/>
+      <c r="R1641" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BD31CA-36C2-4BF8-9E4D-C055C3169BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5320678F-7E9C-4726-95B3-2C4A3CAD3FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9922" uniqueCount="2004">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10114" uniqueCount="2045">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -5866,9 +5866,6 @@
     <t>BJ5778993</t>
   </si>
   <si>
-    <t>25 EXP</t>
-  </si>
-  <si>
     <t>12/173</t>
   </si>
   <si>
@@ -6050,13 +6047,139 @@
   </si>
   <si>
     <t>JABAR MUHAMMAD HUSSAIN</t>
+  </si>
+  <si>
+    <t>NADEEM AKRAM</t>
+  </si>
+  <si>
+    <t>JM1328820</t>
+  </si>
+  <si>
+    <t>SARFRAZ AHMED</t>
+  </si>
+  <si>
+    <t>NAUMAN ALI</t>
+  </si>
+  <si>
+    <t>VC1797374</t>
+  </si>
+  <si>
+    <t>SAEED HASSAN</t>
+  </si>
+  <si>
+    <t>MX6800462</t>
+  </si>
+  <si>
+    <t>AZAM ASGHAR</t>
+  </si>
+  <si>
+    <t>FADHIL SAID</t>
+  </si>
+  <si>
+    <t>BAH/EMPIRE</t>
+  </si>
+  <si>
+    <t>AHSAN ALI AZHAR</t>
+  </si>
+  <si>
+    <t>6956*</t>
+  </si>
+  <si>
+    <t>9754*</t>
+  </si>
+  <si>
+    <t>Basharat Ali</t>
+  </si>
+  <si>
+    <t>SABEEL</t>
+  </si>
+  <si>
+    <t>NIHAL</t>
+  </si>
+  <si>
+    <t>ZUBAIR HUSSAIN</t>
+  </si>
+  <si>
+    <t>ARSLAN AFZAL</t>
+  </si>
+  <si>
+    <t>4393-</t>
+  </si>
+  <si>
+    <t>MUHAMMED SHAFIQUE</t>
+  </si>
+  <si>
+    <t>Aamir Hussain</t>
+  </si>
+  <si>
+    <t>Ahmad Raza</t>
+  </si>
+  <si>
+    <t>7734-</t>
+  </si>
+  <si>
+    <t>FAHAD ZAYID</t>
+  </si>
+  <si>
+    <t>HILAL SALIM</t>
+  </si>
+  <si>
+    <t>AHMED OTHMAN</t>
+  </si>
+  <si>
+    <t>RASHID MOHAMMED</t>
+  </si>
+  <si>
+    <t>1636-</t>
+  </si>
+  <si>
+    <t>6972-</t>
+  </si>
+  <si>
+    <t>RASHID HASHIL</t>
+  </si>
+  <si>
+    <t>SALIM HAMED</t>
+  </si>
+  <si>
+    <t>ABDALLAH AHMED</t>
+  </si>
+  <si>
+    <t>8827-</t>
+  </si>
+  <si>
+    <t>SAID SAIF</t>
+  </si>
+  <si>
+    <t>KHALID RASHID</t>
+  </si>
+  <si>
+    <t>MUHAMMAD AZAM</t>
+  </si>
+  <si>
+    <t>MATTAR SULAIMAN</t>
+  </si>
+  <si>
+    <t>Al HABSHI</t>
+  </si>
+  <si>
+    <t>Am BIKA</t>
+  </si>
+  <si>
+    <t>8489-</t>
+  </si>
+  <si>
+    <t>NASSER SALIM</t>
+  </si>
+  <si>
+    <t>SAIF SALIM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="33">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6263,8 +6386,27 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF215A6C"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6310,6 +6452,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7B7B7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -6386,7 +6534,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6597,6 +6745,21 @@
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6912,7 +7075,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1307"/>
+  <dimension ref="A1:R1336"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -7611,7 +7774,9 @@
       </c>
       <c r="L15" s="18"/>
       <c r="M15" s="18"/>
-      <c r="N15" s="53"/>
+      <c r="N15" s="65">
+        <v>299</v>
+      </c>
       <c r="O15" s="18"/>
       <c r="P15" s="18"/>
       <c r="Q15" s="11">
@@ -7797,7 +7962,9 @@
       </c>
       <c r="L19" s="18"/>
       <c r="M19" s="18"/>
-      <c r="N19" s="53"/>
+      <c r="N19" s="65">
+        <v>300</v>
+      </c>
       <c r="O19" s="18"/>
       <c r="P19" s="18"/>
       <c r="Q19" s="18"/>
@@ -19763,7 +19930,9 @@
       </c>
       <c r="L279" s="18"/>
       <c r="M279" s="18"/>
-      <c r="N279" s="53"/>
+      <c r="N279" s="65">
+        <v>284</v>
+      </c>
       <c r="O279" s="18"/>
       <c r="P279" s="18"/>
       <c r="Q279" s="18"/>
@@ -22947,7 +23116,9 @@
       </c>
       <c r="L349" s="18"/>
       <c r="M349" s="18"/>
-      <c r="N349" s="53"/>
+      <c r="N349" s="65">
+        <v>278</v>
+      </c>
       <c r="O349" s="18"/>
       <c r="P349" s="18"/>
       <c r="Q349" s="11">
@@ -23759,7 +23930,9 @@
       </c>
       <c r="L367" s="18"/>
       <c r="M367" s="18"/>
-      <c r="N367" s="53"/>
+      <c r="N367" s="65">
+        <v>289</v>
+      </c>
       <c r="O367" s="18"/>
       <c r="P367" s="18"/>
       <c r="Q367" s="11">
@@ -29629,7 +29802,9 @@
       </c>
       <c r="L495" s="18"/>
       <c r="M495" s="18"/>
-      <c r="N495" s="53"/>
+      <c r="N495" s="65">
+        <v>275</v>
+      </c>
       <c r="O495" s="18"/>
       <c r="P495" s="18"/>
       <c r="Q495" s="11">
@@ -30173,7 +30348,9 @@
       </c>
       <c r="L507" s="18"/>
       <c r="M507" s="18"/>
-      <c r="N507" s="53"/>
+      <c r="N507" s="65">
+        <v>276</v>
+      </c>
       <c r="O507" s="18"/>
       <c r="P507" s="18"/>
       <c r="Q507" s="11">
@@ -33105,7 +33282,9 @@
       </c>
       <c r="L571" s="18"/>
       <c r="M571" s="18"/>
-      <c r="N571" s="53"/>
+      <c r="N571" s="65">
+        <v>285</v>
+      </c>
       <c r="O571" s="18"/>
       <c r="P571" s="18"/>
       <c r="Q571" s="18"/>
@@ -33149,7 +33328,9 @@
       </c>
       <c r="L572" s="18"/>
       <c r="M572" s="18"/>
-      <c r="N572" s="53"/>
+      <c r="N572" s="65">
+        <v>292</v>
+      </c>
       <c r="O572" s="18"/>
       <c r="P572" s="18"/>
       <c r="Q572" s="18"/>
@@ -33237,7 +33418,9 @@
       </c>
       <c r="L574" s="18"/>
       <c r="M574" s="18"/>
-      <c r="N574" s="53"/>
+      <c r="N574" s="65">
+        <v>286</v>
+      </c>
       <c r="O574" s="18"/>
       <c r="P574" s="18"/>
       <c r="Q574" s="18"/>
@@ -33281,7 +33464,9 @@
       </c>
       <c r="L575" s="18"/>
       <c r="M575" s="18"/>
-      <c r="N575" s="53"/>
+      <c r="N575" s="65">
+        <v>293</v>
+      </c>
       <c r="O575" s="18"/>
       <c r="P575" s="18"/>
       <c r="Q575" s="11">
@@ -35219,7 +35404,9 @@
       </c>
       <c r="L618" s="18"/>
       <c r="M618" s="18"/>
-      <c r="N618" s="53"/>
+      <c r="N618" s="65">
+        <v>279</v>
+      </c>
       <c r="O618" s="18"/>
       <c r="P618" s="18"/>
       <c r="Q618" s="18"/>
@@ -36639,7 +36826,9 @@
       </c>
       <c r="L648" s="18"/>
       <c r="M648" s="18"/>
-      <c r="N648" s="53"/>
+      <c r="N648" s="65">
+        <v>290</v>
+      </c>
       <c r="O648" s="18"/>
       <c r="P648" s="18"/>
       <c r="Q648" s="15">
@@ -36685,7 +36874,9 @@
       </c>
       <c r="L649" s="18"/>
       <c r="M649" s="18"/>
-      <c r="N649" s="53"/>
+      <c r="N649" s="65">
+        <v>288</v>
+      </c>
       <c r="O649" s="18"/>
       <c r="P649" s="18"/>
       <c r="Q649" s="15">
@@ -36915,7 +37106,9 @@
       </c>
       <c r="L654" s="18"/>
       <c r="M654" s="18"/>
-      <c r="N654" s="53"/>
+      <c r="N654" s="65">
+        <v>295</v>
+      </c>
       <c r="O654" s="18"/>
       <c r="P654" s="18"/>
       <c r="Q654" s="15">
@@ -37789,7 +37982,9 @@
       </c>
       <c r="L673" s="18"/>
       <c r="M673" s="18"/>
-      <c r="N673" s="53"/>
+      <c r="N673" s="65">
+        <v>280</v>
+      </c>
       <c r="O673" s="18"/>
       <c r="P673" s="18"/>
       <c r="Q673" s="15">
@@ -37835,7 +38030,9 @@
       </c>
       <c r="L674" s="18"/>
       <c r="M674" s="18"/>
-      <c r="N674" s="53"/>
+      <c r="N674" s="65">
+        <v>283</v>
+      </c>
       <c r="O674" s="18"/>
       <c r="P674" s="18"/>
       <c r="Q674" s="15">
@@ -42263,7 +42460,9 @@
       </c>
       <c r="L770" s="18"/>
       <c r="M770" s="18"/>
-      <c r="N770" s="53"/>
+      <c r="N770" s="65">
+        <v>291</v>
+      </c>
       <c r="O770" s="18"/>
       <c r="P770" s="18"/>
       <c r="Q770" s="48">
@@ -43045,7 +43244,9 @@
       </c>
       <c r="L787" s="18"/>
       <c r="M787" s="18"/>
-      <c r="N787" s="53"/>
+      <c r="N787" s="65">
+        <v>282</v>
+      </c>
       <c r="O787" s="18"/>
       <c r="P787" s="18"/>
       <c r="Q787" s="11">
@@ -43091,7 +43292,9 @@
       </c>
       <c r="L788" s="18"/>
       <c r="M788" s="18"/>
-      <c r="N788" s="53"/>
+      <c r="N788" s="65">
+        <v>2814</v>
+      </c>
       <c r="O788" s="18"/>
       <c r="P788" s="18"/>
       <c r="Q788" s="11">
@@ -53736,16 +53939,14 @@
       <c r="J1022" s="15" t="s">
         <v>825</v>
       </c>
-      <c r="K1022" s="30" t="s">
-        <v>638</v>
+      <c r="K1022" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1022" s="18"/>
       <c r="M1022" s="18"/>
       <c r="N1022" s="53"/>
       <c r="O1022" s="18"/>
-      <c r="P1022" s="43" t="s">
-        <v>1942</v>
-      </c>
+      <c r="P1022" s="18"/>
       <c r="Q1022" s="18"/>
       <c r="R1022" s="20" t="s">
         <v>11</v>
@@ -54284,7 +54485,7 @@
       <c r="L1034" s="18"/>
       <c r="M1034" s="18"/>
       <c r="N1034" s="65" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="O1034" s="18"/>
       <c r="P1034" s="18"/>
@@ -54883,7 +55084,9 @@
       </c>
       <c r="L1047" s="18"/>
       <c r="M1047" s="18"/>
-      <c r="N1047" s="53"/>
+      <c r="N1047" s="65">
+        <v>270</v>
+      </c>
       <c r="O1047" s="18"/>
       <c r="P1047" s="18"/>
       <c r="Q1047" s="15">
@@ -56743,7 +56946,9 @@
       </c>
       <c r="L1087" s="18"/>
       <c r="M1087" s="18"/>
-      <c r="N1087" s="53"/>
+      <c r="N1087" s="65">
+        <v>294</v>
+      </c>
       <c r="O1087" s="18"/>
       <c r="P1087" s="18"/>
       <c r="Q1087" s="48">
@@ -57936,7 +58141,7 @@
       <c r="L1113" s="18"/>
       <c r="M1113" s="18"/>
       <c r="N1113" s="65" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="O1113" s="18"/>
       <c r="P1113" s="18"/>
@@ -59497,7 +59702,9 @@
       </c>
       <c r="L1147" s="18"/>
       <c r="M1147" s="18"/>
-      <c r="N1147" s="53"/>
+      <c r="N1147" s="65">
+        <v>296</v>
+      </c>
       <c r="O1147" s="18"/>
       <c r="P1147" s="18"/>
       <c r="Q1147" s="48">
@@ -60141,7 +60348,9 @@
       </c>
       <c r="L1161" s="18"/>
       <c r="M1161" s="18"/>
-      <c r="N1161" s="53"/>
+      <c r="N1161" s="65">
+        <v>267</v>
+      </c>
       <c r="O1161" s="18"/>
       <c r="P1161" s="18"/>
       <c r="Q1161" s="48">
@@ -60329,7 +60538,9 @@
       </c>
       <c r="L1165" s="18"/>
       <c r="M1165" s="18"/>
-      <c r="N1165" s="53"/>
+      <c r="N1165" s="65">
+        <v>268</v>
+      </c>
       <c r="O1165" s="18"/>
       <c r="P1165" s="18"/>
       <c r="Q1165" s="48">
@@ -61707,7 +61918,9 @@
       </c>
       <c r="L1195" s="18"/>
       <c r="M1195" s="18"/>
-      <c r="N1195" s="53"/>
+      <c r="N1195" s="65">
+        <v>298</v>
+      </c>
       <c r="O1195" s="18"/>
       <c r="P1195" s="18"/>
       <c r="Q1195" s="15">
@@ -61753,7 +61966,9 @@
       </c>
       <c r="L1196" s="18"/>
       <c r="M1196" s="18"/>
-      <c r="N1196" s="53"/>
+      <c r="N1196" s="65">
+        <v>297</v>
+      </c>
       <c r="O1196" s="18"/>
       <c r="P1196" s="18"/>
       <c r="Q1196" s="15">
@@ -61817,7 +62032,7 @@
         <v>46253</v>
       </c>
       <c r="C1198" s="11" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="D1198" s="11">
         <v>91699995</v>
@@ -61861,7 +62076,7 @@
         <v>46253</v>
       </c>
       <c r="C1199" s="11" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="D1199" s="11">
         <v>137973128</v>
@@ -61920,7 +62135,7 @@
         <v>4683</v>
       </c>
       <c r="H1200" s="15" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="I1200" s="15" t="s">
         <v>82</v>
@@ -62041,10 +62256,10 @@
         <v>46253</v>
       </c>
       <c r="C1203" s="11" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D1203" s="11" t="s">
         <v>1948</v>
-      </c>
-      <c r="D1203" s="11" t="s">
-        <v>1949</v>
       </c>
       <c r="E1203" s="12" t="s">
         <v>20</v>
@@ -62073,7 +62288,7 @@
       <c r="O1203" s="18"/>
       <c r="P1203" s="18"/>
       <c r="Q1203" s="15" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="R1203" s="22" t="s">
         <v>87</v>
@@ -62090,7 +62305,7 @@
         <v>1597</v>
       </c>
       <c r="D1204" s="11" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="E1204" s="12" t="s">
         <v>20</v>
@@ -62133,7 +62348,7 @@
         <v>46253</v>
       </c>
       <c r="C1205" s="11" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="D1205" s="11">
         <v>116086677</v>
@@ -62177,10 +62392,10 @@
         <v>46253</v>
       </c>
       <c r="C1206" s="11" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D1206" s="11" t="s">
         <v>1953</v>
-      </c>
-      <c r="D1206" s="11" t="s">
-        <v>1954</v>
       </c>
       <c r="E1206" s="12" t="s">
         <v>20</v>
@@ -62223,7 +62438,7 @@
         <v>46253</v>
       </c>
       <c r="C1207" s="11" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="D1207" s="11">
         <v>68078299</v>
@@ -62267,7 +62482,7 @@
         <v>46253</v>
       </c>
       <c r="C1208" s="11" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="D1208" s="11">
         <v>128203171</v>
@@ -62288,7 +62503,7 @@
         <v>82</v>
       </c>
       <c r="J1208" s="15" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="K1208" s="17" t="s">
         <v>12</v>
@@ -62311,10 +62526,10 @@
         <v>46253</v>
       </c>
       <c r="C1209" s="11" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D1209" s="11" t="s">
         <v>1958</v>
-      </c>
-      <c r="D1209" s="11" t="s">
-        <v>1959</v>
       </c>
       <c r="E1209" s="12" t="s">
         <v>20</v>
@@ -62357,10 +62572,10 @@
         <v>46253</v>
       </c>
       <c r="C1210" s="11" t="s">
-        <v>1516</v>
+        <v>2003</v>
       </c>
       <c r="D1210" s="11" t="s">
-        <v>1517</v>
+        <v>2004</v>
       </c>
       <c r="E1210" s="12" t="s">
         <v>20</v>
@@ -62369,16 +62584,16 @@
         <v>21</v>
       </c>
       <c r="G1210" s="14">
-        <v>63609</v>
+        <v>83900</v>
       </c>
       <c r="H1210" s="15">
-        <v>19699</v>
-      </c>
-      <c r="I1210" s="22" t="s">
-        <v>274</v>
-      </c>
-      <c r="J1210" s="15" t="s">
-        <v>374</v>
+        <v>69373</v>
+      </c>
+      <c r="I1210" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1210" s="45" t="s">
+        <v>377</v>
       </c>
       <c r="K1210" s="17" t="s">
         <v>12</v>
@@ -62388,12 +62603,14 @@
       <c r="N1210" s="53"/>
       <c r="O1210" s="18"/>
       <c r="P1210" s="18"/>
-      <c r="Q1210" s="18"/>
-      <c r="R1210" s="21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="1211" spans="1:18" ht="15" thickBot="1">
+      <c r="Q1210" s="15">
+        <v>98904562</v>
+      </c>
+      <c r="R1210" s="22" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1211" s="2">
         <v>319</v>
       </c>
@@ -62401,28 +62618,28 @@
         <v>46253</v>
       </c>
       <c r="C1211" s="11" t="s">
-        <v>1518</v>
-      </c>
-      <c r="D1211" s="11" t="s">
-        <v>1519</v>
+        <v>2005</v>
+      </c>
+      <c r="D1211" s="11">
+        <v>136540764</v>
       </c>
       <c r="E1211" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1211" s="13" t="s">
-        <v>21</v>
+      <c r="F1211" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1211" s="14">
-        <v>90966</v>
+        <v>5155</v>
       </c>
       <c r="H1211" s="15">
-        <v>7537</v>
-      </c>
-      <c r="I1211" s="16" t="s">
-        <v>10</v>
+        <v>199</v>
+      </c>
+      <c r="I1211" s="15" t="s">
+        <v>82</v>
       </c>
       <c r="J1211" s="15" t="s">
-        <v>83</v>
+        <v>682</v>
       </c>
       <c r="K1211" s="17" t="s">
         <v>12</v>
@@ -62432,11 +62649,9 @@
       <c r="N1211" s="53"/>
       <c r="O1211" s="18"/>
       <c r="P1211" s="18"/>
-      <c r="Q1211" s="15">
-        <v>98972785</v>
-      </c>
-      <c r="R1211" s="21" t="s">
-        <v>14</v>
+      <c r="Q1211" s="18"/>
+      <c r="R1211" s="22" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="1212" spans="1:18" ht="15" thickBot="1">
@@ -62447,10 +62662,10 @@
         <v>46253</v>
       </c>
       <c r="C1212" s="11" t="s">
-        <v>1520</v>
+        <v>2006</v>
       </c>
       <c r="D1212" s="11" t="s">
-        <v>1521</v>
+        <v>2007</v>
       </c>
       <c r="E1212" s="12" t="s">
         <v>20</v>
@@ -62459,16 +62674,16 @@
         <v>21</v>
       </c>
       <c r="G1212" s="14">
-        <v>96938</v>
+        <v>26932</v>
       </c>
       <c r="H1212" s="15">
-        <v>7358</v>
-      </c>
-      <c r="I1212" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1212" s="15" t="s">
-        <v>83</v>
+        <v>62197</v>
+      </c>
+      <c r="I1212" s="22" t="s">
+        <v>274</v>
+      </c>
+      <c r="J1212" s="44" t="s">
+        <v>275</v>
       </c>
       <c r="K1212" s="17" t="s">
         <v>12</v>
@@ -62479,13 +62694,13 @@
       <c r="O1212" s="18"/>
       <c r="P1212" s="18"/>
       <c r="Q1212" s="15">
-        <v>99514847</v>
-      </c>
-      <c r="R1212" s="21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="1213" spans="1:18" ht="23.4" thickBot="1">
+        <v>95610171</v>
+      </c>
+      <c r="R1212" s="22" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:18" ht="15" thickBot="1">
       <c r="A1213" s="2">
         <v>321</v>
       </c>
@@ -62493,10 +62708,10 @@
         <v>46253</v>
       </c>
       <c r="C1213" s="11" t="s">
-        <v>1522</v>
+        <v>2008</v>
       </c>
       <c r="D1213" s="11" t="s">
-        <v>1523</v>
+        <v>2009</v>
       </c>
       <c r="E1213" s="12" t="s">
         <v>20</v>
@@ -62505,16 +62720,16 @@
         <v>21</v>
       </c>
       <c r="G1213" s="14">
-        <v>34507</v>
+        <v>50401</v>
       </c>
       <c r="H1213" s="15">
-        <v>14858</v>
-      </c>
-      <c r="I1213" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1213" s="15" t="s">
-        <v>83</v>
+        <v>96818</v>
+      </c>
+      <c r="I1213" s="22" t="s">
+        <v>274</v>
+      </c>
+      <c r="J1213" s="44" t="s">
+        <v>275</v>
       </c>
       <c r="K1213" s="17" t="s">
         <v>12</v>
@@ -62525,13 +62740,13 @@
       <c r="O1213" s="18"/>
       <c r="P1213" s="18"/>
       <c r="Q1213" s="15">
-        <v>95635079</v>
-      </c>
-      <c r="R1213" s="21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="1214" spans="1:18" ht="15" thickBot="1">
+        <v>79071017</v>
+      </c>
+      <c r="R1213" s="22" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1214" s="2">
         <v>322</v>
       </c>
@@ -62539,28 +62754,28 @@
         <v>46253</v>
       </c>
       <c r="C1214" s="11" t="s">
-        <v>1524</v>
-      </c>
-      <c r="D1214" s="11" t="s">
-        <v>1525</v>
+        <v>2010</v>
+      </c>
+      <c r="D1214" s="11">
+        <v>109901938</v>
       </c>
       <c r="E1214" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1214" s="13" t="s">
-        <v>21</v>
+      <c r="F1214" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1214" s="14">
-        <v>70307</v>
+        <v>162</v>
       </c>
       <c r="H1214" s="15">
-        <v>40184</v>
-      </c>
-      <c r="I1214" s="16" t="s">
-        <v>10</v>
+        <v>4464</v>
+      </c>
+      <c r="I1214" s="15" t="s">
+        <v>82</v>
       </c>
       <c r="J1214" s="15" t="s">
-        <v>83</v>
+        <v>1489</v>
       </c>
       <c r="K1214" s="17" t="s">
         <v>12</v>
@@ -62571,13 +62786,13 @@
       <c r="O1214" s="18"/>
       <c r="P1214" s="18"/>
       <c r="Q1214" s="15">
-        <v>92538037</v>
-      </c>
-      <c r="R1214" s="21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="1215" spans="1:18" ht="15" thickBot="1">
+        <v>91458244</v>
+      </c>
+      <c r="R1214" s="22" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1215" s="2">
         <v>323</v>
       </c>
@@ -62585,28 +62800,28 @@
         <v>46253</v>
       </c>
       <c r="C1215" s="11" t="s">
-        <v>1526</v>
-      </c>
-      <c r="D1215" s="11" t="s">
-        <v>1527</v>
+        <v>2011</v>
+      </c>
+      <c r="D1215" s="11">
+        <v>74622655</v>
       </c>
       <c r="E1215" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1215" s="13" t="s">
-        <v>21</v>
+      <c r="F1215" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1215" s="14">
-        <v>17274</v>
+        <v>6465</v>
       </c>
       <c r="H1215" s="15">
-        <v>10058</v>
-      </c>
-      <c r="I1215" s="16" t="s">
-        <v>10</v>
+        <v>7346</v>
+      </c>
+      <c r="I1215" s="15" t="s">
+        <v>82</v>
       </c>
       <c r="J1215" s="15" t="s">
-        <v>83</v>
+        <v>2012</v>
       </c>
       <c r="K1215" s="17" t="s">
         <v>12</v>
@@ -62616,14 +62831,12 @@
       <c r="N1215" s="53"/>
       <c r="O1215" s="18"/>
       <c r="P1215" s="18"/>
-      <c r="Q1215" s="15">
-        <v>95986250</v>
-      </c>
-      <c r="R1215" s="21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="1216" spans="1:18" ht="15" thickBot="1">
+      <c r="Q1215" s="18"/>
+      <c r="R1215" s="22" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1216" s="2">
         <v>324</v>
       </c>
@@ -62631,28 +62844,28 @@
         <v>46253</v>
       </c>
       <c r="C1216" s="11" t="s">
-        <v>1528</v>
-      </c>
-      <c r="D1216" s="11" t="s">
-        <v>1529</v>
+        <v>2013</v>
+      </c>
+      <c r="D1216" s="11">
+        <v>88446789</v>
       </c>
       <c r="E1216" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1216" s="13" t="s">
-        <v>21</v>
+      <c r="F1216" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1216" s="14">
-        <v>75622</v>
-      </c>
-      <c r="H1216" s="15">
-        <v>34163</v>
-      </c>
-      <c r="I1216" s="16" t="s">
-        <v>10</v>
+        <v>6160</v>
+      </c>
+      <c r="H1216" s="15" t="s">
+        <v>2014</v>
+      </c>
+      <c r="I1216" s="15" t="s">
+        <v>82</v>
       </c>
       <c r="J1216" s="15" t="s">
-        <v>83</v>
+        <v>1471</v>
       </c>
       <c r="K1216" s="17" t="s">
         <v>12</v>
@@ -62663,13 +62876,13 @@
       <c r="O1216" s="18"/>
       <c r="P1216" s="18"/>
       <c r="Q1216" s="15">
-        <v>95960758</v>
-      </c>
-      <c r="R1216" s="21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="1217" spans="1:18" ht="15" thickBot="1">
+        <v>94312524</v>
+      </c>
+      <c r="R1216" s="22" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1217" s="2">
         <v>325</v>
       </c>
@@ -62677,28 +62890,28 @@
         <v>46253</v>
       </c>
       <c r="C1217" s="11" t="s">
-        <v>1530</v>
-      </c>
-      <c r="D1217" s="11" t="s">
-        <v>1531</v>
+        <v>392</v>
+      </c>
+      <c r="D1217" s="11">
+        <v>85639447</v>
       </c>
       <c r="E1217" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1217" s="13" t="s">
-        <v>21</v>
+      <c r="F1217" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1217" s="14">
-        <v>82139</v>
-      </c>
-      <c r="H1217" s="15">
-        <v>66091</v>
-      </c>
-      <c r="I1217" s="16" t="s">
-        <v>10</v>
+        <v>2860</v>
+      </c>
+      <c r="H1217" s="15" t="s">
+        <v>2015</v>
+      </c>
+      <c r="I1217" s="15" t="s">
+        <v>82</v>
       </c>
       <c r="J1217" s="15" t="s">
-        <v>83</v>
+        <v>1471</v>
       </c>
       <c r="K1217" s="17" t="s">
         <v>12</v>
@@ -62709,10 +62922,10 @@
       <c r="O1217" s="18"/>
       <c r="P1217" s="18"/>
       <c r="Q1217" s="15">
-        <v>95975136</v>
-      </c>
-      <c r="R1217" s="21" t="s">
-        <v>14</v>
+        <v>98918818</v>
+      </c>
+      <c r="R1217" s="22" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="1218" spans="1:18" ht="15" thickBot="1">
@@ -62723,10 +62936,10 @@
         <v>46253</v>
       </c>
       <c r="C1218" s="11" t="s">
-        <v>786</v>
+        <v>1516</v>
       </c>
       <c r="D1218" s="11" t="s">
-        <v>1532</v>
+        <v>1517</v>
       </c>
       <c r="E1218" s="12" t="s">
         <v>20</v>
@@ -62735,16 +62948,16 @@
         <v>21</v>
       </c>
       <c r="G1218" s="14">
-        <v>65207</v>
+        <v>63609</v>
       </c>
       <c r="H1218" s="15">
-        <v>77688</v>
-      </c>
-      <c r="I1218" s="16" t="s">
-        <v>10</v>
+        <v>19699</v>
+      </c>
+      <c r="I1218" s="22" t="s">
+        <v>274</v>
       </c>
       <c r="J1218" s="15" t="s">
-        <v>83</v>
+        <v>374</v>
       </c>
       <c r="K1218" s="17" t="s">
         <v>12</v>
@@ -62754,9 +62967,7 @@
       <c r="N1218" s="53"/>
       <c r="O1218" s="18"/>
       <c r="P1218" s="18"/>
-      <c r="Q1218" s="15">
-        <v>95981935</v>
-      </c>
+      <c r="Q1218" s="18"/>
       <c r="R1218" s="21" t="s">
         <v>14</v>
       </c>
@@ -62769,10 +62980,10 @@
         <v>46253</v>
       </c>
       <c r="C1219" s="11" t="s">
-        <v>1533</v>
+        <v>1518</v>
       </c>
       <c r="D1219" s="11" t="s">
-        <v>1534</v>
+        <v>1519</v>
       </c>
       <c r="E1219" s="12" t="s">
         <v>20</v>
@@ -62781,10 +62992,10 @@
         <v>21</v>
       </c>
       <c r="G1219" s="14">
-        <v>19658</v>
+        <v>90966</v>
       </c>
       <c r="H1219" s="15">
-        <v>79940</v>
+        <v>7537</v>
       </c>
       <c r="I1219" s="16" t="s">
         <v>10</v>
@@ -62801,7 +63012,7 @@
       <c r="O1219" s="18"/>
       <c r="P1219" s="18"/>
       <c r="Q1219" s="15">
-        <v>95948127</v>
+        <v>98972785</v>
       </c>
       <c r="R1219" s="21" t="s">
         <v>14</v>
@@ -62815,10 +63026,10 @@
         <v>46253</v>
       </c>
       <c r="C1220" s="11" t="s">
-        <v>1535</v>
+        <v>1520</v>
       </c>
       <c r="D1220" s="11" t="s">
-        <v>1536</v>
+        <v>1521</v>
       </c>
       <c r="E1220" s="12" t="s">
         <v>20</v>
@@ -62827,10 +63038,10 @@
         <v>21</v>
       </c>
       <c r="G1220" s="14">
-        <v>24609</v>
+        <v>96938</v>
       </c>
       <c r="H1220" s="15">
-        <v>48453</v>
+        <v>7358</v>
       </c>
       <c r="I1220" s="16" t="s">
         <v>10</v>
@@ -62847,13 +63058,13 @@
       <c r="O1220" s="18"/>
       <c r="P1220" s="18"/>
       <c r="Q1220" s="15">
-        <v>95985321</v>
+        <v>99514847</v>
       </c>
       <c r="R1220" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1221" spans="1:18" ht="15" thickBot="1">
+    <row r="1221" spans="1:18" ht="23.4" thickBot="1">
       <c r="A1221" s="2">
         <v>329</v>
       </c>
@@ -62861,10 +63072,10 @@
         <v>46253</v>
       </c>
       <c r="C1221" s="11" t="s">
-        <v>1537</v>
+        <v>1522</v>
       </c>
       <c r="D1221" s="11" t="s">
-        <v>1538</v>
+        <v>1523</v>
       </c>
       <c r="E1221" s="12" t="s">
         <v>20</v>
@@ -62873,10 +63084,10 @@
         <v>21</v>
       </c>
       <c r="G1221" s="14">
-        <v>14724</v>
+        <v>34507</v>
       </c>
       <c r="H1221" s="15">
-        <v>68375</v>
+        <v>14858</v>
       </c>
       <c r="I1221" s="16" t="s">
         <v>10</v>
@@ -62893,7 +63104,7 @@
       <c r="O1221" s="18"/>
       <c r="P1221" s="18"/>
       <c r="Q1221" s="15">
-        <v>503264142</v>
+        <v>95635079</v>
       </c>
       <c r="R1221" s="21" t="s">
         <v>14</v>
@@ -62907,10 +63118,10 @@
         <v>46253</v>
       </c>
       <c r="C1222" s="11" t="s">
-        <v>1539</v>
+        <v>1524</v>
       </c>
       <c r="D1222" s="11" t="s">
-        <v>1540</v>
+        <v>1525</v>
       </c>
       <c r="E1222" s="12" t="s">
         <v>20</v>
@@ -62919,10 +63130,10 @@
         <v>21</v>
       </c>
       <c r="G1222" s="14">
-        <v>27529</v>
+        <v>70307</v>
       </c>
       <c r="H1222" s="15">
-        <v>81779</v>
+        <v>40184</v>
       </c>
       <c r="I1222" s="16" t="s">
         <v>10</v>
@@ -62938,8 +63149,8 @@
       <c r="N1222" s="53"/>
       <c r="O1222" s="18"/>
       <c r="P1222" s="18"/>
-      <c r="Q1222" s="11">
-        <v>562272457</v>
+      <c r="Q1222" s="15">
+        <v>92538037</v>
       </c>
       <c r="R1222" s="21" t="s">
         <v>14</v>
@@ -62953,22 +63164,22 @@
         <v>46253</v>
       </c>
       <c r="C1223" s="11" t="s">
-        <v>1541</v>
-      </c>
-      <c r="D1223" s="11">
-        <v>128847714</v>
+        <v>1526</v>
+      </c>
+      <c r="D1223" s="11" t="s">
+        <v>1527</v>
       </c>
       <c r="E1223" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1223" s="16" t="s">
-        <v>81</v>
+      <c r="F1223" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G1223" s="14">
-        <v>7383</v>
+        <v>17274</v>
       </c>
       <c r="H1223" s="15">
-        <v>5046</v>
+        <v>10058</v>
       </c>
       <c r="I1223" s="16" t="s">
         <v>10</v>
@@ -62984,8 +63195,8 @@
       <c r="N1223" s="53"/>
       <c r="O1223" s="18"/>
       <c r="P1223" s="18"/>
-      <c r="Q1223" s="11">
-        <v>97342088</v>
+      <c r="Q1223" s="15">
+        <v>95986250</v>
       </c>
       <c r="R1223" s="21" t="s">
         <v>14</v>
@@ -62999,22 +63210,22 @@
         <v>46253</v>
       </c>
       <c r="C1224" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="D1224" s="11">
-        <v>87323682</v>
+        <v>1528</v>
+      </c>
+      <c r="D1224" s="11" t="s">
+        <v>1529</v>
       </c>
       <c r="E1224" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1224" s="16" t="s">
-        <v>81</v>
+      <c r="F1224" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G1224" s="14">
-        <v>2910</v>
+        <v>75622</v>
       </c>
       <c r="H1224" s="15">
-        <v>3008</v>
+        <v>34163</v>
       </c>
       <c r="I1224" s="16" t="s">
         <v>10</v>
@@ -63030,14 +63241,14 @@
       <c r="N1224" s="53"/>
       <c r="O1224" s="18"/>
       <c r="P1224" s="18"/>
-      <c r="Q1224" s="11">
-        <v>97450915</v>
+      <c r="Q1224" s="15">
+        <v>95960758</v>
       </c>
       <c r="R1224" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1225" spans="1:18" ht="23.4" thickBot="1">
+    <row r="1225" spans="1:18" ht="15" thickBot="1">
       <c r="A1225" s="2">
         <v>333</v>
       </c>
@@ -63045,22 +63256,22 @@
         <v>46253</v>
       </c>
       <c r="C1225" s="11" t="s">
-        <v>1542</v>
-      </c>
-      <c r="D1225" s="11">
-        <v>131373463</v>
+        <v>1530</v>
+      </c>
+      <c r="D1225" s="11" t="s">
+        <v>1531</v>
       </c>
       <c r="E1225" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1225" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="G1225" s="14" t="s">
-        <v>1543</v>
+      <c r="F1225" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1225" s="14">
+        <v>82139</v>
       </c>
       <c r="H1225" s="15">
-        <v>5264</v>
+        <v>66091</v>
       </c>
       <c r="I1225" s="16" t="s">
         <v>10</v>
@@ -63076,14 +63287,14 @@
       <c r="N1225" s="53"/>
       <c r="O1225" s="18"/>
       <c r="P1225" s="18"/>
-      <c r="Q1225" s="11">
-        <v>76028112</v>
+      <c r="Q1225" s="15">
+        <v>95975136</v>
       </c>
       <c r="R1225" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1226" spans="1:18" ht="23.4" thickBot="1">
+    <row r="1226" spans="1:18" ht="15" thickBot="1">
       <c r="A1226" s="2">
         <v>334</v>
       </c>
@@ -63091,22 +63302,22 @@
         <v>46253</v>
       </c>
       <c r="C1226" s="11" t="s">
-        <v>1544</v>
-      </c>
-      <c r="D1226" s="11">
-        <v>73860148</v>
+        <v>786</v>
+      </c>
+      <c r="D1226" s="11" t="s">
+        <v>1532</v>
       </c>
       <c r="E1226" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1226" s="16" t="s">
-        <v>81</v>
+      <c r="F1226" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G1226" s="14">
-        <v>4278</v>
+        <v>65207</v>
       </c>
       <c r="H1226" s="15">
-        <v>6749</v>
+        <v>77688</v>
       </c>
       <c r="I1226" s="16" t="s">
         <v>10</v>
@@ -63122,14 +63333,14 @@
       <c r="N1226" s="53"/>
       <c r="O1226" s="18"/>
       <c r="P1226" s="18"/>
-      <c r="Q1226" s="11">
-        <v>92218612</v>
+      <c r="Q1226" s="15">
+        <v>95981935</v>
       </c>
       <c r="R1226" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1227" spans="1:18" ht="23.4" thickBot="1">
+    <row r="1227" spans="1:18" ht="15" thickBot="1">
       <c r="A1227" s="2">
         <v>335</v>
       </c>
@@ -63137,22 +63348,22 @@
         <v>46253</v>
       </c>
       <c r="C1227" s="11" t="s">
-        <v>1545</v>
-      </c>
-      <c r="D1227" s="11">
-        <v>137512475</v>
+        <v>1533</v>
+      </c>
+      <c r="D1227" s="11" t="s">
+        <v>1534</v>
       </c>
       <c r="E1227" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1227" s="16" t="s">
-        <v>81</v>
+      <c r="F1227" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G1227" s="14">
-        <v>1424</v>
+        <v>19658</v>
       </c>
       <c r="H1227" s="15">
-        <v>3163</v>
+        <v>79940</v>
       </c>
       <c r="I1227" s="16" t="s">
         <v>10</v>
@@ -63168,8 +63379,8 @@
       <c r="N1227" s="53"/>
       <c r="O1227" s="18"/>
       <c r="P1227" s="18"/>
-      <c r="Q1227" s="11">
-        <v>77391836</v>
+      <c r="Q1227" s="15">
+        <v>95948127</v>
       </c>
       <c r="R1227" s="21" t="s">
         <v>14</v>
@@ -63183,22 +63394,22 @@
         <v>46253</v>
       </c>
       <c r="C1228" s="11" t="s">
-        <v>1546</v>
-      </c>
-      <c r="D1228" s="11">
-        <v>134317916</v>
+        <v>1535</v>
+      </c>
+      <c r="D1228" s="11" t="s">
+        <v>1536</v>
       </c>
       <c r="E1228" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1228" s="16" t="s">
-        <v>81</v>
+      <c r="F1228" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G1228" s="14">
-        <v>2372</v>
+        <v>24609</v>
       </c>
       <c r="H1228" s="15">
-        <v>2609</v>
+        <v>48453</v>
       </c>
       <c r="I1228" s="16" t="s">
         <v>10</v>
@@ -63214,8 +63425,8 @@
       <c r="N1228" s="53"/>
       <c r="O1228" s="18"/>
       <c r="P1228" s="18"/>
-      <c r="Q1228" s="11">
-        <v>77182970</v>
+      <c r="Q1228" s="15">
+        <v>95985321</v>
       </c>
       <c r="R1228" s="21" t="s">
         <v>14</v>
@@ -63229,22 +63440,22 @@
         <v>46253</v>
       </c>
       <c r="C1229" s="11" t="s">
-        <v>403</v>
-      </c>
-      <c r="D1229" s="11">
-        <v>135298498</v>
+        <v>1537</v>
+      </c>
+      <c r="D1229" s="11" t="s">
+        <v>1538</v>
       </c>
       <c r="E1229" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1229" s="16" t="s">
-        <v>81</v>
+      <c r="F1229" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G1229" s="14">
-        <v>3581</v>
+        <v>14724</v>
       </c>
       <c r="H1229" s="15">
-        <v>7167</v>
+        <v>68375</v>
       </c>
       <c r="I1229" s="16" t="s">
         <v>10</v>
@@ -63260,14 +63471,14 @@
       <c r="N1229" s="53"/>
       <c r="O1229" s="18"/>
       <c r="P1229" s="18"/>
-      <c r="Q1229" s="11">
-        <v>76855071</v>
+      <c r="Q1229" s="15">
+        <v>503264142</v>
       </c>
       <c r="R1229" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1230" spans="1:18" ht="23.4" thickBot="1">
+    <row r="1230" spans="1:18" ht="15" thickBot="1">
       <c r="A1230" s="2">
         <v>338</v>
       </c>
@@ -63275,10 +63486,10 @@
         <v>46253</v>
       </c>
       <c r="C1230" s="11" t="s">
-        <v>1547</v>
+        <v>1539</v>
       </c>
       <c r="D1230" s="11" t="s">
-        <v>1548</v>
+        <v>1540</v>
       </c>
       <c r="E1230" s="12" t="s">
         <v>20</v>
@@ -63287,10 +63498,10 @@
         <v>21</v>
       </c>
       <c r="G1230" s="14">
-        <v>40452</v>
+        <v>27529</v>
       </c>
       <c r="H1230" s="15">
-        <v>7949</v>
+        <v>81779</v>
       </c>
       <c r="I1230" s="16" t="s">
         <v>10</v>
@@ -63307,7 +63518,7 @@
       <c r="O1230" s="18"/>
       <c r="P1230" s="18"/>
       <c r="Q1230" s="11">
-        <v>95982837</v>
+        <v>562272457</v>
       </c>
       <c r="R1230" s="21" t="s">
         <v>14</v>
@@ -63321,22 +63532,22 @@
         <v>46253</v>
       </c>
       <c r="C1231" s="11" t="s">
-        <v>1549</v>
-      </c>
-      <c r="D1231" s="11" t="s">
-        <v>1550</v>
+        <v>1541</v>
+      </c>
+      <c r="D1231" s="11">
+        <v>128847714</v>
       </c>
       <c r="E1231" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1231" s="13" t="s">
-        <v>21</v>
+      <c r="F1231" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1231" s="14">
-        <v>58181</v>
+        <v>7383</v>
       </c>
       <c r="H1231" s="15">
-        <v>95151</v>
+        <v>5046</v>
       </c>
       <c r="I1231" s="16" t="s">
         <v>10</v>
@@ -63353,13 +63564,13 @@
       <c r="O1231" s="18"/>
       <c r="P1231" s="18"/>
       <c r="Q1231" s="11">
-        <v>95907496</v>
+        <v>97342088</v>
       </c>
       <c r="R1231" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1232" spans="1:18" ht="23.4" thickBot="1">
+    <row r="1232" spans="1:18" ht="15" thickBot="1">
       <c r="A1232" s="2">
         <v>340</v>
       </c>
@@ -63367,10 +63578,10 @@
         <v>46253</v>
       </c>
       <c r="C1232" s="11" t="s">
-        <v>1551</v>
+        <v>353</v>
       </c>
       <c r="D1232" s="11">
-        <v>126935488</v>
+        <v>87323682</v>
       </c>
       <c r="E1232" s="12" t="s">
         <v>20</v>
@@ -63379,10 +63590,10 @@
         <v>81</v>
       </c>
       <c r="G1232" s="14">
-        <v>1810</v>
+        <v>2910</v>
       </c>
       <c r="H1232" s="15">
-        <v>9636</v>
+        <v>3008</v>
       </c>
       <c r="I1232" s="16" t="s">
         <v>10</v>
@@ -63399,13 +63610,13 @@
       <c r="O1232" s="18"/>
       <c r="P1232" s="18"/>
       <c r="Q1232" s="11">
-        <v>92114381</v>
+        <v>97450915</v>
       </c>
       <c r="R1232" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1233" spans="1:18" ht="15" thickBot="1">
+    <row r="1233" spans="1:18" ht="23.4" thickBot="1">
       <c r="A1233" s="2">
         <v>341</v>
       </c>
@@ -63413,10 +63624,10 @@
         <v>46253</v>
       </c>
       <c r="C1233" s="11" t="s">
-        <v>1813</v>
+        <v>1542</v>
       </c>
       <c r="D1233" s="11">
-        <v>72821533</v>
+        <v>131373463</v>
       </c>
       <c r="E1233" s="12" t="s">
         <v>20</v>
@@ -63425,10 +63636,10 @@
         <v>81</v>
       </c>
       <c r="G1233" s="14" t="s">
-        <v>1814</v>
+        <v>1543</v>
       </c>
       <c r="H1233" s="15">
-        <v>4243</v>
+        <v>5264</v>
       </c>
       <c r="I1233" s="16" t="s">
         <v>10</v>
@@ -63445,13 +63656,13 @@
       <c r="O1233" s="18"/>
       <c r="P1233" s="18"/>
       <c r="Q1233" s="11">
-        <v>99117472</v>
+        <v>76028112</v>
       </c>
       <c r="R1233" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1234" spans="1:18" ht="15" thickBot="1">
+    <row r="1234" spans="1:18" ht="23.4" thickBot="1">
       <c r="A1234" s="2">
         <v>342</v>
       </c>
@@ -63459,10 +63670,10 @@
         <v>46253</v>
       </c>
       <c r="C1234" s="11" t="s">
-        <v>1781</v>
+        <v>1544</v>
       </c>
       <c r="D1234" s="11">
-        <v>123092514</v>
+        <v>73860148</v>
       </c>
       <c r="E1234" s="12" t="s">
         <v>20</v>
@@ -63471,10 +63682,10 @@
         <v>81</v>
       </c>
       <c r="G1234" s="14">
-        <v>9791</v>
+        <v>4278</v>
       </c>
       <c r="H1234" s="15">
-        <v>7897</v>
+        <v>6749</v>
       </c>
       <c r="I1234" s="16" t="s">
         <v>10</v>
@@ -63491,13 +63702,13 @@
       <c r="O1234" s="18"/>
       <c r="P1234" s="18"/>
       <c r="Q1234" s="11">
-        <v>98843190</v>
+        <v>92218612</v>
       </c>
       <c r="R1234" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1235" spans="1:18" ht="15" thickBot="1">
+    <row r="1235" spans="1:18" ht="23.4" thickBot="1">
       <c r="A1235" s="2">
         <v>343</v>
       </c>
@@ -63505,10 +63716,10 @@
         <v>46253</v>
       </c>
       <c r="C1235" s="11" t="s">
-        <v>1815</v>
+        <v>1545</v>
       </c>
       <c r="D1235" s="11">
-        <v>61922846</v>
+        <v>137512475</v>
       </c>
       <c r="E1235" s="12" t="s">
         <v>20</v>
@@ -63517,10 +63728,10 @@
         <v>81</v>
       </c>
       <c r="G1235" s="14">
-        <v>9035</v>
+        <v>1424</v>
       </c>
       <c r="H1235" s="15">
-        <v>9132</v>
+        <v>3163</v>
       </c>
       <c r="I1235" s="16" t="s">
         <v>10</v>
@@ -63537,7 +63748,7 @@
       <c r="O1235" s="18"/>
       <c r="P1235" s="18"/>
       <c r="Q1235" s="11">
-        <v>98576849</v>
+        <v>77391836</v>
       </c>
       <c r="R1235" s="21" t="s">
         <v>14</v>
@@ -63551,10 +63762,10 @@
         <v>46253</v>
       </c>
       <c r="C1236" s="11" t="s">
-        <v>1816</v>
+        <v>1546</v>
       </c>
       <c r="D1236" s="11">
-        <v>129434826</v>
+        <v>134317916</v>
       </c>
       <c r="E1236" s="12" t="s">
         <v>20</v>
@@ -63563,10 +63774,10 @@
         <v>81</v>
       </c>
       <c r="G1236" s="14">
-        <v>4307</v>
+        <v>2372</v>
       </c>
       <c r="H1236" s="15">
-        <v>1076</v>
+        <v>2609</v>
       </c>
       <c r="I1236" s="16" t="s">
         <v>10</v>
@@ -63583,7 +63794,7 @@
       <c r="O1236" s="18"/>
       <c r="P1236" s="18"/>
       <c r="Q1236" s="11">
-        <v>79315040</v>
+        <v>77182970</v>
       </c>
       <c r="R1236" s="21" t="s">
         <v>14</v>
@@ -63597,22 +63808,22 @@
         <v>46253</v>
       </c>
       <c r="C1237" s="11" t="s">
-        <v>1558</v>
-      </c>
-      <c r="D1237" s="11" t="s">
-        <v>1817</v>
+        <v>403</v>
+      </c>
+      <c r="D1237" s="11">
+        <v>135298498</v>
       </c>
       <c r="E1237" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1237" s="13" t="s">
-        <v>21</v>
+      <c r="F1237" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1237" s="14">
-        <v>68478</v>
+        <v>3581</v>
       </c>
       <c r="H1237" s="15">
-        <v>23855</v>
+        <v>7167</v>
       </c>
       <c r="I1237" s="16" t="s">
         <v>10</v>
@@ -63625,19 +63836,17 @@
       </c>
       <c r="L1237" s="18"/>
       <c r="M1237" s="18"/>
-      <c r="N1237" s="65">
-        <v>1</v>
-      </c>
+      <c r="N1237" s="53"/>
       <c r="O1237" s="18"/>
       <c r="P1237" s="18"/>
       <c r="Q1237" s="11">
-        <v>557218014</v>
+        <v>76855071</v>
       </c>
       <c r="R1237" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1238" spans="1:18" ht="15" thickBot="1">
+    <row r="1238" spans="1:18" ht="23.4" thickBot="1">
       <c r="A1238" s="2">
         <v>346</v>
       </c>
@@ -63645,10 +63854,10 @@
         <v>46253</v>
       </c>
       <c r="C1238" s="11" t="s">
-        <v>181</v>
+        <v>1547</v>
       </c>
       <c r="D1238" s="11" t="s">
-        <v>1818</v>
+        <v>1548</v>
       </c>
       <c r="E1238" s="12" t="s">
         <v>20</v>
@@ -63657,10 +63866,10 @@
         <v>21</v>
       </c>
       <c r="G1238" s="14">
-        <v>49072</v>
+        <v>40452</v>
       </c>
       <c r="H1238" s="15">
-        <v>70610</v>
+        <v>7949</v>
       </c>
       <c r="I1238" s="16" t="s">
         <v>10</v>
@@ -63677,7 +63886,7 @@
       <c r="O1238" s="18"/>
       <c r="P1238" s="18"/>
       <c r="Q1238" s="11">
-        <v>91647358</v>
+        <v>95982837</v>
       </c>
       <c r="R1238" s="21" t="s">
         <v>14</v>
@@ -63691,10 +63900,10 @@
         <v>46253</v>
       </c>
       <c r="C1239" s="11" t="s">
-        <v>1819</v>
+        <v>1549</v>
       </c>
       <c r="D1239" s="11" t="s">
-        <v>1820</v>
+        <v>1550</v>
       </c>
       <c r="E1239" s="12" t="s">
         <v>20</v>
@@ -63703,10 +63912,10 @@
         <v>21</v>
       </c>
       <c r="G1239" s="14">
-        <v>97033</v>
-      </c>
-      <c r="H1239" s="15" t="s">
-        <v>1821</v>
+        <v>58181</v>
+      </c>
+      <c r="H1239" s="15">
+        <v>95151</v>
       </c>
       <c r="I1239" s="16" t="s">
         <v>10</v>
@@ -63723,13 +63932,13 @@
       <c r="O1239" s="18"/>
       <c r="P1239" s="18"/>
       <c r="Q1239" s="11">
-        <v>95616942</v>
+        <v>95907496</v>
       </c>
       <c r="R1239" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1240" spans="1:18" ht="15" thickBot="1">
+    <row r="1240" spans="1:18" ht="23.4" thickBot="1">
       <c r="A1240" s="2">
         <v>348</v>
       </c>
@@ -63737,10 +63946,10 @@
         <v>46253</v>
       </c>
       <c r="C1240" s="11" t="s">
-        <v>1822</v>
+        <v>1551</v>
       </c>
       <c r="D1240" s="11">
-        <v>73013105</v>
+        <v>126935488</v>
       </c>
       <c r="E1240" s="12" t="s">
         <v>20</v>
@@ -63749,10 +63958,10 @@
         <v>81</v>
       </c>
       <c r="G1240" s="14">
-        <v>3004</v>
+        <v>1810</v>
       </c>
       <c r="H1240" s="15">
-        <v>3288</v>
+        <v>9636</v>
       </c>
       <c r="I1240" s="16" t="s">
         <v>10</v>
@@ -63769,7 +63978,7 @@
       <c r="O1240" s="18"/>
       <c r="P1240" s="18"/>
       <c r="Q1240" s="11">
-        <v>92803718</v>
+        <v>92114381</v>
       </c>
       <c r="R1240" s="21" t="s">
         <v>14</v>
@@ -63783,22 +63992,22 @@
         <v>46253</v>
       </c>
       <c r="C1241" s="11" t="s">
-        <v>1823</v>
-      </c>
-      <c r="D1241" s="11" t="s">
-        <v>1824</v>
+        <v>1813</v>
+      </c>
+      <c r="D1241" s="11">
+        <v>72821533</v>
       </c>
       <c r="E1241" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1241" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1241" s="14">
-        <v>90681</v>
+      <c r="F1241" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1241" s="14" t="s">
+        <v>1814</v>
       </c>
       <c r="H1241" s="15">
-        <v>66900</v>
+        <v>4243</v>
       </c>
       <c r="I1241" s="16" t="s">
         <v>10</v>
@@ -63815,7 +64024,7 @@
       <c r="O1241" s="18"/>
       <c r="P1241" s="18"/>
       <c r="Q1241" s="11">
-        <v>502502279</v>
+        <v>99117472</v>
       </c>
       <c r="R1241" s="21" t="s">
         <v>14</v>
@@ -63829,22 +64038,22 @@
         <v>46253</v>
       </c>
       <c r="C1242" s="11" t="s">
-        <v>1825</v>
-      </c>
-      <c r="D1242" s="11" t="s">
-        <v>1826</v>
+        <v>1781</v>
+      </c>
+      <c r="D1242" s="11">
+        <v>123092514</v>
       </c>
       <c r="E1242" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1242" s="13" t="s">
-        <v>21</v>
+      <c r="F1242" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1242" s="14">
-        <v>69249</v>
+        <v>9791</v>
       </c>
       <c r="H1242" s="15">
-        <v>51480</v>
+        <v>7897</v>
       </c>
       <c r="I1242" s="16" t="s">
         <v>10</v>
@@ -63861,7 +64070,7 @@
       <c r="O1242" s="18"/>
       <c r="P1242" s="18"/>
       <c r="Q1242" s="11">
-        <v>77552346</v>
+        <v>98843190</v>
       </c>
       <c r="R1242" s="21" t="s">
         <v>14</v>
@@ -63875,22 +64084,22 @@
         <v>46253</v>
       </c>
       <c r="C1243" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="D1243" s="11" t="s">
-        <v>1827</v>
+        <v>1815</v>
+      </c>
+      <c r="D1243" s="11">
+        <v>61922846</v>
       </c>
       <c r="E1243" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1243" s="13" t="s">
-        <v>21</v>
+      <c r="F1243" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1243" s="14">
-        <v>67322</v>
+        <v>9035</v>
       </c>
       <c r="H1243" s="15">
-        <v>52063</v>
+        <v>9132</v>
       </c>
       <c r="I1243" s="16" t="s">
         <v>10</v>
@@ -63907,7 +64116,7 @@
       <c r="O1243" s="18"/>
       <c r="P1243" s="18"/>
       <c r="Q1243" s="11">
-        <v>77339514</v>
+        <v>98576849</v>
       </c>
       <c r="R1243" s="21" t="s">
         <v>14</v>
@@ -63921,22 +64130,22 @@
         <v>46253</v>
       </c>
       <c r="C1244" s="11" t="s">
-        <v>273</v>
+        <v>1816</v>
       </c>
       <c r="D1244" s="11">
-        <v>79960031</v>
+        <v>129434826</v>
       </c>
       <c r="E1244" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1244" s="13" t="s">
-        <v>21</v>
+      <c r="F1244" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1244" s="14">
-        <v>7375</v>
+        <v>4307</v>
       </c>
       <c r="H1244" s="15">
-        <v>9681</v>
+        <v>1076</v>
       </c>
       <c r="I1244" s="16" t="s">
         <v>10</v>
@@ -63953,7 +64162,7 @@
       <c r="O1244" s="18"/>
       <c r="P1244" s="18"/>
       <c r="Q1244" s="11">
-        <v>90634045</v>
+        <v>79315040</v>
       </c>
       <c r="R1244" s="21" t="s">
         <v>14</v>
@@ -63967,22 +64176,22 @@
         <v>46253</v>
       </c>
       <c r="C1245" s="11" t="s">
-        <v>1828</v>
-      </c>
-      <c r="D1245" s="11">
-        <v>137249793</v>
+        <v>1558</v>
+      </c>
+      <c r="D1245" s="11" t="s">
+        <v>1817</v>
       </c>
       <c r="E1245" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1245" s="16" t="s">
-        <v>81</v>
+      <c r="F1245" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G1245" s="14">
-        <v>7244</v>
+        <v>68478</v>
       </c>
       <c r="H1245" s="15">
-        <v>5873</v>
+        <v>23855</v>
       </c>
       <c r="I1245" s="16" t="s">
         <v>10</v>
@@ -63995,11 +64204,13 @@
       </c>
       <c r="L1245" s="18"/>
       <c r="M1245" s="18"/>
-      <c r="N1245" s="53"/>
+      <c r="N1245" s="65">
+        <v>1</v>
+      </c>
       <c r="O1245" s="18"/>
       <c r="P1245" s="18"/>
       <c r="Q1245" s="11">
-        <v>79409596</v>
+        <v>557218014</v>
       </c>
       <c r="R1245" s="21" t="s">
         <v>14</v>
@@ -64013,22 +64224,22 @@
         <v>46253</v>
       </c>
       <c r="C1246" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="D1246" s="11">
-        <v>70102616</v>
+        <v>181</v>
+      </c>
+      <c r="D1246" s="11" t="s">
+        <v>1818</v>
       </c>
       <c r="E1246" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1246" s="16" t="s">
-        <v>81</v>
+      <c r="F1246" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G1246" s="14">
-        <v>828</v>
+        <v>49072</v>
       </c>
       <c r="H1246" s="15">
-        <v>5601</v>
+        <v>70610</v>
       </c>
       <c r="I1246" s="16" t="s">
         <v>10</v>
@@ -64045,7 +64256,7 @@
       <c r="O1246" s="18"/>
       <c r="P1246" s="18"/>
       <c r="Q1246" s="11">
-        <v>99560807</v>
+        <v>91647358</v>
       </c>
       <c r="R1246" s="21" t="s">
         <v>14</v>
@@ -64059,22 +64270,22 @@
         <v>46253</v>
       </c>
       <c r="C1247" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="D1247" s="11">
-        <v>123876366</v>
+        <v>1819</v>
+      </c>
+      <c r="D1247" s="11" t="s">
+        <v>1820</v>
       </c>
       <c r="E1247" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1247" s="16" t="s">
-        <v>81</v>
+      <c r="F1247" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G1247" s="14">
-        <v>5285</v>
-      </c>
-      <c r="H1247" s="15">
-        <v>3319</v>
+        <v>97033</v>
+      </c>
+      <c r="H1247" s="15" t="s">
+        <v>1821</v>
       </c>
       <c r="I1247" s="16" t="s">
         <v>10</v>
@@ -64091,13 +64302,13 @@
       <c r="O1247" s="18"/>
       <c r="P1247" s="18"/>
       <c r="Q1247" s="11">
-        <v>78467731</v>
+        <v>95616942</v>
       </c>
       <c r="R1247" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1248" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1248" spans="1:18" ht="15" thickBot="1">
       <c r="A1248" s="2">
         <v>356</v>
       </c>
@@ -64105,28 +64316,28 @@
         <v>46253</v>
       </c>
       <c r="C1248" s="11" t="s">
-        <v>1552</v>
-      </c>
-      <c r="D1248" s="11" t="s">
-        <v>1553</v>
+        <v>1822</v>
+      </c>
+      <c r="D1248" s="11">
+        <v>73013105</v>
       </c>
       <c r="E1248" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1248" s="13" t="s">
-        <v>21</v>
+      <c r="F1248" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1248" s="14">
-        <v>15680</v>
+        <v>3004</v>
       </c>
       <c r="H1248" s="15">
-        <v>14556</v>
+        <v>3288</v>
       </c>
       <c r="I1248" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1248" s="15" t="s">
-        <v>170</v>
+        <v>83</v>
       </c>
       <c r="K1248" s="17" t="s">
         <v>12</v>
@@ -64135,17 +64346,15 @@
       <c r="M1248" s="18"/>
       <c r="N1248" s="53"/>
       <c r="O1248" s="18"/>
-      <c r="P1248" s="33" t="s">
-        <v>1554</v>
-      </c>
+      <c r="P1248" s="18"/>
       <c r="Q1248" s="11">
-        <v>562442983</v>
+        <v>92803718</v>
       </c>
       <c r="R1248" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1249" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1249" spans="1:18" ht="15" thickBot="1">
       <c r="A1249" s="2">
         <v>357</v>
       </c>
@@ -64153,28 +64362,28 @@
         <v>46253</v>
       </c>
       <c r="C1249" s="11" t="s">
-        <v>1555</v>
-      </c>
-      <c r="D1249" s="11">
-        <v>87794825</v>
+        <v>1823</v>
+      </c>
+      <c r="D1249" s="11" t="s">
+        <v>1824</v>
       </c>
       <c r="E1249" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1249" s="16" t="s">
-        <v>81</v>
+      <c r="F1249" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G1249" s="14">
-        <v>7650</v>
+        <v>90681</v>
       </c>
       <c r="H1249" s="15">
-        <v>2748</v>
+        <v>66900</v>
       </c>
       <c r="I1249" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1249" s="15" t="s">
-        <v>170</v>
+        <v>83</v>
       </c>
       <c r="K1249" s="17" t="s">
         <v>12</v>
@@ -64185,13 +64394,13 @@
       <c r="O1249" s="18"/>
       <c r="P1249" s="18"/>
       <c r="Q1249" s="11">
-        <v>98532219</v>
+        <v>502502279</v>
       </c>
       <c r="R1249" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1250" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1250" spans="1:18" ht="15" thickBot="1">
       <c r="A1250" s="2">
         <v>358</v>
       </c>
@@ -64199,45 +64408,45 @@
         <v>46253</v>
       </c>
       <c r="C1250" s="11" t="s">
-        <v>1829</v>
-      </c>
-      <c r="D1250" s="11">
-        <v>19020155</v>
-      </c>
-      <c r="E1250" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="F1250" s="16" t="s">
-        <v>81</v>
+        <v>1825</v>
+      </c>
+      <c r="D1250" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="E1250" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1250" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G1250" s="14">
-        <v>86</v>
+        <v>69249</v>
       </c>
       <c r="H1250" s="15">
-        <v>3406</v>
+        <v>51480</v>
       </c>
       <c r="I1250" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1250" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="K1250" s="47" t="s">
-        <v>511</v>
+        <v>83</v>
+      </c>
+      <c r="K1250" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1250" s="18"/>
       <c r="M1250" s="18"/>
       <c r="N1250" s="53"/>
       <c r="O1250" s="18"/>
-      <c r="P1250" s="33" t="s">
-        <v>1830</v>
-      </c>
-      <c r="Q1250" s="18"/>
+      <c r="P1250" s="18"/>
+      <c r="Q1250" s="11">
+        <v>77552346</v>
+      </c>
       <c r="R1250" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1251" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1251" spans="1:18" ht="15" thickBot="1">
       <c r="A1251" s="2">
         <v>359</v>
       </c>
@@ -64245,45 +64454,45 @@
         <v>46253</v>
       </c>
       <c r="C1251" s="11" t="s">
-        <v>1831</v>
-      </c>
-      <c r="D1251" s="11">
-        <v>23978191</v>
-      </c>
-      <c r="E1251" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="F1251" s="16" t="s">
-        <v>81</v>
+        <v>265</v>
+      </c>
+      <c r="D1251" s="11" t="s">
+        <v>1827</v>
+      </c>
+      <c r="E1251" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1251" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G1251" s="14">
-        <v>3526</v>
+        <v>67322</v>
       </c>
       <c r="H1251" s="15">
-        <v>9327</v>
+        <v>52063</v>
       </c>
       <c r="I1251" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1251" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="K1251" s="47" t="s">
-        <v>511</v>
+        <v>83</v>
+      </c>
+      <c r="K1251" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1251" s="18"/>
       <c r="M1251" s="18"/>
       <c r="N1251" s="53"/>
       <c r="O1251" s="18"/>
-      <c r="P1251" s="33" t="s">
-        <v>1830</v>
-      </c>
-      <c r="Q1251" s="18"/>
+      <c r="P1251" s="18"/>
+      <c r="Q1251" s="11">
+        <v>77339514</v>
+      </c>
       <c r="R1251" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1252" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1252" spans="1:18" ht="15" thickBot="1">
       <c r="A1252" s="2">
         <v>360</v>
       </c>
@@ -64291,45 +64500,45 @@
         <v>46253</v>
       </c>
       <c r="C1252" s="11" t="s">
-        <v>1832</v>
+        <v>273</v>
       </c>
       <c r="D1252" s="11">
-        <v>19030172</v>
-      </c>
-      <c r="E1252" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="F1252" s="16" t="s">
-        <v>81</v>
+        <v>79960031</v>
+      </c>
+      <c r="E1252" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1252" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G1252" s="14">
-        <v>8611</v>
+        <v>7375</v>
       </c>
       <c r="H1252" s="15">
-        <v>6847</v>
+        <v>9681</v>
       </c>
       <c r="I1252" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1252" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="K1252" s="47" t="s">
-        <v>511</v>
+        <v>83</v>
+      </c>
+      <c r="K1252" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1252" s="18"/>
       <c r="M1252" s="18"/>
       <c r="N1252" s="53"/>
       <c r="O1252" s="18"/>
-      <c r="P1252" s="33" t="s">
-        <v>1830</v>
-      </c>
-      <c r="Q1252" s="18"/>
+      <c r="P1252" s="18"/>
+      <c r="Q1252" s="11">
+        <v>90634045</v>
+      </c>
       <c r="R1252" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1253" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1253" spans="1:18" ht="15" thickBot="1">
       <c r="A1253" s="2">
         <v>361</v>
       </c>
@@ -64337,45 +64546,45 @@
         <v>46253</v>
       </c>
       <c r="C1253" s="11" t="s">
-        <v>1833</v>
+        <v>1828</v>
       </c>
       <c r="D1253" s="11">
-        <v>19020141</v>
-      </c>
-      <c r="E1253" s="34" t="s">
-        <v>80</v>
+        <v>137249793</v>
+      </c>
+      <c r="E1253" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="F1253" s="16" t="s">
         <v>81</v>
       </c>
       <c r="G1253" s="14">
-        <v>2897</v>
+        <v>7244</v>
       </c>
       <c r="H1253" s="15">
-        <v>6097</v>
+        <v>5873</v>
       </c>
       <c r="I1253" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1253" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="K1253" s="47" t="s">
-        <v>511</v>
+        <v>83</v>
+      </c>
+      <c r="K1253" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1253" s="18"/>
       <c r="M1253" s="18"/>
       <c r="N1253" s="53"/>
       <c r="O1253" s="18"/>
-      <c r="P1253" s="33" t="s">
-        <v>1830</v>
-      </c>
-      <c r="Q1253" s="18"/>
+      <c r="P1253" s="18"/>
+      <c r="Q1253" s="11">
+        <v>79409596</v>
+      </c>
       <c r="R1253" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1254" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1254" spans="1:18" ht="15" thickBot="1">
       <c r="A1254" s="2">
         <v>362</v>
       </c>
@@ -64383,45 +64592,45 @@
         <v>46253</v>
       </c>
       <c r="C1254" s="11" t="s">
-        <v>1834</v>
+        <v>222</v>
       </c>
       <c r="D1254" s="11">
-        <v>13275863</v>
-      </c>
-      <c r="E1254" s="34" t="s">
-        <v>80</v>
+        <v>70102616</v>
+      </c>
+      <c r="E1254" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="F1254" s="16" t="s">
         <v>81</v>
       </c>
       <c r="G1254" s="14">
-        <v>4047</v>
+        <v>828</v>
       </c>
       <c r="H1254" s="15">
-        <v>5022</v>
+        <v>5601</v>
       </c>
       <c r="I1254" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1254" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="K1254" s="47" t="s">
-        <v>511</v>
+        <v>83</v>
+      </c>
+      <c r="K1254" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1254" s="18"/>
       <c r="M1254" s="18"/>
       <c r="N1254" s="53"/>
       <c r="O1254" s="18"/>
-      <c r="P1254" s="33" t="s">
-        <v>1835</v>
-      </c>
-      <c r="Q1254" s="18"/>
+      <c r="P1254" s="18"/>
+      <c r="Q1254" s="11">
+        <v>99560807</v>
+      </c>
       <c r="R1254" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1255" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1255" spans="1:18" ht="15" thickBot="1">
       <c r="A1255" s="2">
         <v>363</v>
       </c>
@@ -64429,40 +64638,40 @@
         <v>46253</v>
       </c>
       <c r="C1255" s="11" t="s">
-        <v>1836</v>
+        <v>213</v>
       </c>
       <c r="D1255" s="11">
-        <v>5684951</v>
-      </c>
-      <c r="E1255" s="34" t="s">
-        <v>80</v>
+        <v>123876366</v>
+      </c>
+      <c r="E1255" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="F1255" s="16" t="s">
         <v>81</v>
       </c>
       <c r="G1255" s="14">
-        <v>8942</v>
+        <v>5285</v>
       </c>
       <c r="H1255" s="15">
-        <v>5035</v>
+        <v>3319</v>
       </c>
       <c r="I1255" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1255" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="K1255" s="47" t="s">
-        <v>511</v>
+        <v>83</v>
+      </c>
+      <c r="K1255" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1255" s="18"/>
       <c r="M1255" s="18"/>
       <c r="N1255" s="53"/>
       <c r="O1255" s="18"/>
-      <c r="P1255" s="33" t="s">
-        <v>1835</v>
-      </c>
-      <c r="Q1255" s="18"/>
+      <c r="P1255" s="18"/>
+      <c r="Q1255" s="11">
+        <v>78467731</v>
+      </c>
       <c r="R1255" s="21" t="s">
         <v>14</v>
       </c>
@@ -64475,22 +64684,22 @@
         <v>46253</v>
       </c>
       <c r="C1256" s="11" t="s">
-        <v>1837</v>
-      </c>
-      <c r="D1256" s="11">
-        <v>13488401</v>
-      </c>
-      <c r="E1256" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="F1256" s="16" t="s">
-        <v>81</v>
+        <v>1552</v>
+      </c>
+      <c r="D1256" s="11" t="s">
+        <v>1553</v>
+      </c>
+      <c r="E1256" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1256" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G1256" s="14">
-        <v>8419</v>
+        <v>15680</v>
       </c>
       <c r="H1256" s="15">
-        <v>3542</v>
+        <v>14556</v>
       </c>
       <c r="I1256" s="16" t="s">
         <v>10</v>
@@ -64498,17 +64707,19 @@
       <c r="J1256" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="K1256" s="47" t="s">
-        <v>511</v>
+      <c r="K1256" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1256" s="18"/>
       <c r="M1256" s="18"/>
       <c r="N1256" s="53"/>
       <c r="O1256" s="18"/>
       <c r="P1256" s="33" t="s">
-        <v>1835</v>
-      </c>
-      <c r="Q1256" s="18"/>
+        <v>1554</v>
+      </c>
+      <c r="Q1256" s="11">
+        <v>562442983</v>
+      </c>
       <c r="R1256" s="21" t="s">
         <v>14</v>
       </c>
@@ -64521,22 +64732,22 @@
         <v>46253</v>
       </c>
       <c r="C1257" s="11" t="s">
-        <v>1838</v>
+        <v>1555</v>
       </c>
       <c r="D1257" s="11">
-        <v>6881512</v>
-      </c>
-      <c r="E1257" s="34" t="s">
-        <v>80</v>
+        <v>87794825</v>
+      </c>
+      <c r="E1257" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="F1257" s="16" t="s">
         <v>81</v>
       </c>
       <c r="G1257" s="14">
-        <v>998</v>
+        <v>7650</v>
       </c>
       <c r="H1257" s="15">
-        <v>8555</v>
+        <v>2748</v>
       </c>
       <c r="I1257" s="16" t="s">
         <v>10</v>
@@ -64544,17 +64755,17 @@
       <c r="J1257" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="K1257" s="47" t="s">
-        <v>511</v>
+      <c r="K1257" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1257" s="18"/>
       <c r="M1257" s="18"/>
       <c r="N1257" s="53"/>
       <c r="O1257" s="18"/>
-      <c r="P1257" s="33" t="s">
-        <v>1835</v>
-      </c>
-      <c r="Q1257" s="18"/>
+      <c r="P1257" s="18"/>
+      <c r="Q1257" s="11">
+        <v>98532219</v>
+      </c>
       <c r="R1257" s="21" t="s">
         <v>14</v>
       </c>
@@ -64567,10 +64778,10 @@
         <v>46253</v>
       </c>
       <c r="C1258" s="11" t="s">
-        <v>1839</v>
+        <v>1829</v>
       </c>
       <c r="D1258" s="11">
-        <v>9664605</v>
+        <v>19020155</v>
       </c>
       <c r="E1258" s="34" t="s">
         <v>80</v>
@@ -64579,10 +64790,10 @@
         <v>81</v>
       </c>
       <c r="G1258" s="14">
-        <v>1101</v>
+        <v>86</v>
       </c>
       <c r="H1258" s="15">
-        <v>6148</v>
+        <v>3406</v>
       </c>
       <c r="I1258" s="16" t="s">
         <v>10</v>
@@ -64598,7 +64809,7 @@
       <c r="N1258" s="53"/>
       <c r="O1258" s="18"/>
       <c r="P1258" s="33" t="s">
-        <v>1835</v>
+        <v>1830</v>
       </c>
       <c r="Q1258" s="18"/>
       <c r="R1258" s="21" t="s">
@@ -64613,10 +64824,10 @@
         <v>46253</v>
       </c>
       <c r="C1259" s="11" t="s">
-        <v>1840</v>
+        <v>1831</v>
       </c>
       <c r="D1259" s="11">
-        <v>11514952</v>
+        <v>23978191</v>
       </c>
       <c r="E1259" s="34" t="s">
         <v>80</v>
@@ -64625,10 +64836,10 @@
         <v>81</v>
       </c>
       <c r="G1259" s="14">
-        <v>8018</v>
-      </c>
-      <c r="H1259" s="15" t="s">
-        <v>1841</v>
+        <v>3526</v>
+      </c>
+      <c r="H1259" s="15">
+        <v>9327</v>
       </c>
       <c r="I1259" s="16" t="s">
         <v>10</v>
@@ -64644,7 +64855,7 @@
       <c r="N1259" s="53"/>
       <c r="O1259" s="18"/>
       <c r="P1259" s="33" t="s">
-        <v>1835</v>
+        <v>1830</v>
       </c>
       <c r="Q1259" s="18"/>
       <c r="R1259" s="21" t="s">
@@ -64659,22 +64870,22 @@
         <v>46253</v>
       </c>
       <c r="C1260" s="11" t="s">
-        <v>1842</v>
+        <v>1832</v>
       </c>
       <c r="D1260" s="11">
-        <v>74772805</v>
-      </c>
-      <c r="E1260" s="12" t="s">
-        <v>20</v>
+        <v>19030172</v>
+      </c>
+      <c r="E1260" s="34" t="s">
+        <v>80</v>
       </c>
       <c r="F1260" s="16" t="s">
         <v>81</v>
       </c>
       <c r="G1260" s="14">
-        <v>8387</v>
+        <v>8611</v>
       </c>
       <c r="H1260" s="15">
-        <v>9332</v>
+        <v>6847</v>
       </c>
       <c r="I1260" s="16" t="s">
         <v>10</v>
@@ -64689,10 +64900,10 @@
       <c r="M1260" s="18"/>
       <c r="N1260" s="53"/>
       <c r="O1260" s="18"/>
-      <c r="P1260" s="18"/>
-      <c r="Q1260" s="11">
-        <v>97653458</v>
-      </c>
+      <c r="P1260" s="33" t="s">
+        <v>1830</v>
+      </c>
+      <c r="Q1260" s="18"/>
       <c r="R1260" s="21" t="s">
         <v>14</v>
       </c>
@@ -64705,22 +64916,22 @@
         <v>46253</v>
       </c>
       <c r="C1261" s="11" t="s">
-        <v>1960</v>
-      </c>
-      <c r="D1261" s="11" t="s">
-        <v>1961</v>
-      </c>
-      <c r="E1261" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1261" s="13" t="s">
-        <v>21</v>
+        <v>1833</v>
+      </c>
+      <c r="D1261" s="11">
+        <v>19020141</v>
+      </c>
+      <c r="E1261" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1261" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1261" s="14">
-        <v>27816</v>
+        <v>2897</v>
       </c>
       <c r="H1261" s="15">
-        <v>47083</v>
+        <v>6097</v>
       </c>
       <c r="I1261" s="16" t="s">
         <v>10</v>
@@ -64728,19 +64939,17 @@
       <c r="J1261" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="K1261" s="17" t="s">
-        <v>12</v>
+      <c r="K1261" s="47" t="s">
+        <v>511</v>
       </c>
       <c r="L1261" s="18"/>
       <c r="M1261" s="18"/>
       <c r="N1261" s="53"/>
       <c r="O1261" s="18"/>
       <c r="P1261" s="33" t="s">
-        <v>1962</v>
-      </c>
-      <c r="Q1261" s="11">
-        <v>77162034</v>
-      </c>
+        <v>1830</v>
+      </c>
+      <c r="Q1261" s="18"/>
       <c r="R1261" s="21" t="s">
         <v>14</v>
       </c>
@@ -64753,22 +64962,22 @@
         <v>46253</v>
       </c>
       <c r="C1262" s="11" t="s">
-        <v>1963</v>
-      </c>
-      <c r="D1262" s="11" t="s">
-        <v>1964</v>
-      </c>
-      <c r="E1262" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1262" s="13" t="s">
-        <v>21</v>
+        <v>1834</v>
+      </c>
+      <c r="D1262" s="11">
+        <v>13275863</v>
+      </c>
+      <c r="E1262" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1262" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1262" s="14">
-        <v>59394</v>
+        <v>4047</v>
       </c>
       <c r="H1262" s="15">
-        <v>10407</v>
+        <v>5022</v>
       </c>
       <c r="I1262" s="16" t="s">
         <v>10</v>
@@ -64776,19 +64985,17 @@
       <c r="J1262" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="K1262" s="17" t="s">
-        <v>12</v>
+      <c r="K1262" s="47" t="s">
+        <v>511</v>
       </c>
       <c r="L1262" s="18"/>
       <c r="M1262" s="18"/>
       <c r="N1262" s="53"/>
       <c r="O1262" s="18"/>
       <c r="P1262" s="33" t="s">
-        <v>1962</v>
-      </c>
-      <c r="Q1262" s="11">
-        <v>502455280</v>
-      </c>
+        <v>1835</v>
+      </c>
+      <c r="Q1262" s="18"/>
       <c r="R1262" s="21" t="s">
         <v>14</v>
       </c>
@@ -64801,22 +65008,22 @@
         <v>46253</v>
       </c>
       <c r="C1263" s="11" t="s">
-        <v>1965</v>
-      </c>
-      <c r="D1263" s="11" t="s">
-        <v>1966</v>
-      </c>
-      <c r="E1263" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1263" s="13" t="s">
-        <v>21</v>
+        <v>1836</v>
+      </c>
+      <c r="D1263" s="11">
+        <v>5684951</v>
+      </c>
+      <c r="E1263" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1263" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1263" s="14">
-        <v>48853</v>
-      </c>
-      <c r="H1263" s="15" t="s">
-        <v>1967</v>
+        <v>8942</v>
+      </c>
+      <c r="H1263" s="15">
+        <v>5035</v>
       </c>
       <c r="I1263" s="16" t="s">
         <v>10</v>
@@ -64824,19 +65031,17 @@
       <c r="J1263" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="K1263" s="17" t="s">
-        <v>12</v>
+      <c r="K1263" s="47" t="s">
+        <v>511</v>
       </c>
       <c r="L1263" s="18"/>
       <c r="M1263" s="18"/>
       <c r="N1263" s="53"/>
       <c r="O1263" s="18"/>
       <c r="P1263" s="33" t="s">
-        <v>1962</v>
-      </c>
-      <c r="Q1263" s="11">
-        <v>521141691</v>
-      </c>
+        <v>1835</v>
+      </c>
+      <c r="Q1263" s="18"/>
       <c r="R1263" s="21" t="s">
         <v>14</v>
       </c>
@@ -64849,22 +65054,22 @@
         <v>46253</v>
       </c>
       <c r="C1264" s="11" t="s">
-        <v>726</v>
-      </c>
-      <c r="D1264" s="11" t="s">
-        <v>1968</v>
-      </c>
-      <c r="E1264" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1264" s="13" t="s">
-        <v>21</v>
+        <v>1837</v>
+      </c>
+      <c r="D1264" s="11">
+        <v>13488401</v>
+      </c>
+      <c r="E1264" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1264" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1264" s="14">
-        <v>53285</v>
+        <v>8419</v>
       </c>
       <c r="H1264" s="15">
-        <v>10458</v>
+        <v>3542</v>
       </c>
       <c r="I1264" s="16" t="s">
         <v>10</v>
@@ -64872,19 +65077,17 @@
       <c r="J1264" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="K1264" s="17" t="s">
-        <v>12</v>
+      <c r="K1264" s="47" t="s">
+        <v>511</v>
       </c>
       <c r="L1264" s="18"/>
       <c r="M1264" s="18"/>
       <c r="N1264" s="53"/>
       <c r="O1264" s="18"/>
       <c r="P1264" s="33" t="s">
-        <v>1962</v>
-      </c>
-      <c r="Q1264" s="11">
-        <v>588611305</v>
-      </c>
+        <v>1835</v>
+      </c>
+      <c r="Q1264" s="18"/>
       <c r="R1264" s="21" t="s">
         <v>14</v>
       </c>
@@ -64897,22 +65100,22 @@
         <v>46253</v>
       </c>
       <c r="C1265" s="11" t="s">
-        <v>1969</v>
-      </c>
-      <c r="D1265" s="11" t="s">
-        <v>1970</v>
-      </c>
-      <c r="E1265" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1265" s="13" t="s">
-        <v>21</v>
+        <v>1838</v>
+      </c>
+      <c r="D1265" s="11">
+        <v>6881512</v>
+      </c>
+      <c r="E1265" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1265" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1265" s="14">
-        <v>80623</v>
+        <v>998</v>
       </c>
       <c r="H1265" s="15">
-        <v>19522</v>
+        <v>8555</v>
       </c>
       <c r="I1265" s="16" t="s">
         <v>10</v>
@@ -64920,19 +65123,17 @@
       <c r="J1265" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="K1265" s="17" t="s">
-        <v>12</v>
+      <c r="K1265" s="47" t="s">
+        <v>511</v>
       </c>
       <c r="L1265" s="18"/>
       <c r="M1265" s="18"/>
       <c r="N1265" s="53"/>
       <c r="O1265" s="18"/>
       <c r="P1265" s="33" t="s">
-        <v>1962</v>
-      </c>
-      <c r="Q1265" s="11">
-        <v>524074068</v>
-      </c>
+        <v>1835</v>
+      </c>
+      <c r="Q1265" s="18"/>
       <c r="R1265" s="21" t="s">
         <v>14</v>
       </c>
@@ -64945,40 +65146,40 @@
         <v>46253</v>
       </c>
       <c r="C1266" s="11" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D1266" s="11" t="s">
-        <v>1972</v>
-      </c>
-      <c r="E1266" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1266" s="13" t="s">
-        <v>21</v>
+        <v>1839</v>
+      </c>
+      <c r="D1266" s="11">
+        <v>9664605</v>
+      </c>
+      <c r="E1266" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1266" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1266" s="14">
-        <v>79279</v>
-      </c>
-      <c r="H1266" s="18"/>
+        <v>1101</v>
+      </c>
+      <c r="H1266" s="15">
+        <v>6148</v>
+      </c>
       <c r="I1266" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1266" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="K1266" s="17" t="s">
-        <v>12</v>
+      <c r="K1266" s="47" t="s">
+        <v>511</v>
       </c>
       <c r="L1266" s="18"/>
       <c r="M1266" s="18"/>
       <c r="N1266" s="53"/>
       <c r="O1266" s="18"/>
       <c r="P1266" s="33" t="s">
-        <v>1962</v>
-      </c>
-      <c r="Q1266" s="11">
-        <v>555466775</v>
-      </c>
+        <v>1835</v>
+      </c>
+      <c r="Q1266" s="18"/>
       <c r="R1266" s="21" t="s">
         <v>14</v>
       </c>
@@ -64991,22 +65192,22 @@
         <v>46253</v>
       </c>
       <c r="C1267" s="11" t="s">
-        <v>1973</v>
-      </c>
-      <c r="D1267" s="11" t="s">
-        <v>1974</v>
-      </c>
-      <c r="E1267" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1267" s="13" t="s">
-        <v>21</v>
+        <v>1840</v>
+      </c>
+      <c r="D1267" s="11">
+        <v>11514952</v>
+      </c>
+      <c r="E1267" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1267" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1267" s="14">
-        <v>35298</v>
-      </c>
-      <c r="H1267" s="15">
-        <v>7509</v>
+        <v>8018</v>
+      </c>
+      <c r="H1267" s="15" t="s">
+        <v>1841</v>
       </c>
       <c r="I1267" s="16" t="s">
         <v>10</v>
@@ -65014,19 +65215,17 @@
       <c r="J1267" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="K1267" s="17" t="s">
-        <v>12</v>
+      <c r="K1267" s="47" t="s">
+        <v>511</v>
       </c>
       <c r="L1267" s="18"/>
       <c r="M1267" s="18"/>
       <c r="N1267" s="53"/>
       <c r="O1267" s="18"/>
       <c r="P1267" s="33" t="s">
-        <v>1975</v>
-      </c>
-      <c r="Q1267" s="11">
-        <v>543442645</v>
-      </c>
+        <v>1835</v>
+      </c>
+      <c r="Q1267" s="18"/>
       <c r="R1267" s="21" t="s">
         <v>14</v>
       </c>
@@ -65039,22 +65238,22 @@
         <v>46253</v>
       </c>
       <c r="C1268" s="11" t="s">
-        <v>1976</v>
-      </c>
-      <c r="D1268" s="11" t="s">
-        <v>1977</v>
-      </c>
-      <c r="E1268" s="70" t="s">
-        <v>1195</v>
-      </c>
-      <c r="F1268" s="13" t="s">
-        <v>21</v>
+        <v>1842</v>
+      </c>
+      <c r="D1268" s="11">
+        <v>74772805</v>
+      </c>
+      <c r="E1268" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1268" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1268" s="14">
-        <v>40646</v>
+        <v>8387</v>
       </c>
       <c r="H1268" s="15">
-        <v>31517</v>
+        <v>9332</v>
       </c>
       <c r="I1268" s="16" t="s">
         <v>10</v>
@@ -65070,7 +65269,9 @@
       <c r="N1268" s="53"/>
       <c r="O1268" s="18"/>
       <c r="P1268" s="18"/>
-      <c r="Q1268" s="18"/>
+      <c r="Q1268" s="11">
+        <v>97653458</v>
+      </c>
       <c r="R1268" s="21" t="s">
         <v>14</v>
       </c>
@@ -65083,22 +65284,22 @@
         <v>46253</v>
       </c>
       <c r="C1269" s="11" t="s">
-        <v>1978</v>
+        <v>1959</v>
       </c>
       <c r="D1269" s="11" t="s">
-        <v>1979</v>
-      </c>
-      <c r="E1269" s="70" t="s">
-        <v>1195</v>
+        <v>1960</v>
+      </c>
+      <c r="E1269" s="30" t="s">
+        <v>78</v>
       </c>
       <c r="F1269" s="13" t="s">
         <v>21</v>
       </c>
       <c r="G1269" s="14">
-        <v>44018</v>
+        <v>27816</v>
       </c>
       <c r="H1269" s="15">
-        <v>29029</v>
+        <v>47083</v>
       </c>
       <c r="I1269" s="16" t="s">
         <v>10</v>
@@ -65106,15 +65307,19 @@
       <c r="J1269" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="K1269" s="47" t="s">
-        <v>511</v>
+      <c r="K1269" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1269" s="18"/>
       <c r="M1269" s="18"/>
       <c r="N1269" s="53"/>
       <c r="O1269" s="18"/>
-      <c r="P1269" s="18"/>
-      <c r="Q1269" s="18"/>
+      <c r="P1269" s="33" t="s">
+        <v>1961</v>
+      </c>
+      <c r="Q1269" s="11">
+        <v>77162034</v>
+      </c>
       <c r="R1269" s="21" t="s">
         <v>14</v>
       </c>
@@ -65127,22 +65332,22 @@
         <v>46253</v>
       </c>
       <c r="C1270" s="11" t="s">
-        <v>1980</v>
+        <v>1962</v>
       </c>
       <c r="D1270" s="11" t="s">
-        <v>1981</v>
-      </c>
-      <c r="E1270" s="70" t="s">
-        <v>1195</v>
+        <v>1963</v>
+      </c>
+      <c r="E1270" s="30" t="s">
+        <v>78</v>
       </c>
       <c r="F1270" s="13" t="s">
         <v>21</v>
       </c>
       <c r="G1270" s="14">
-        <v>62386</v>
+        <v>59394</v>
       </c>
       <c r="H1270" s="15">
-        <v>60239</v>
+        <v>10407</v>
       </c>
       <c r="I1270" s="16" t="s">
         <v>10</v>
@@ -65150,20 +65355,24 @@
       <c r="J1270" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="K1270" s="47" t="s">
-        <v>511</v>
+      <c r="K1270" s="17" t="s">
+        <v>12</v>
       </c>
       <c r="L1270" s="18"/>
       <c r="M1270" s="18"/>
       <c r="N1270" s="53"/>
       <c r="O1270" s="18"/>
-      <c r="P1270" s="18"/>
-      <c r="Q1270" s="18"/>
+      <c r="P1270" s="33" t="s">
+        <v>1961</v>
+      </c>
+      <c r="Q1270" s="11">
+        <v>502455280</v>
+      </c>
       <c r="R1270" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1271" spans="1:18" ht="15" thickBot="1">
+    <row r="1271" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1271" s="2">
         <v>379</v>
       </c>
@@ -65171,28 +65380,28 @@
         <v>46253</v>
       </c>
       <c r="C1271" s="11" t="s">
-        <v>1556</v>
+        <v>1964</v>
       </c>
       <c r="D1271" s="11" t="s">
-        <v>1557</v>
-      </c>
-      <c r="E1271" s="12" t="s">
-        <v>20</v>
+        <v>1965</v>
+      </c>
+      <c r="E1271" s="30" t="s">
+        <v>78</v>
       </c>
       <c r="F1271" s="13" t="s">
         <v>21</v>
       </c>
       <c r="G1271" s="14">
-        <v>40509</v>
-      </c>
-      <c r="H1271" s="15">
-        <v>64464</v>
+        <v>48853</v>
+      </c>
+      <c r="H1271" s="15" t="s">
+        <v>1966</v>
       </c>
       <c r="I1271" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1271" s="15" t="s">
-        <v>902</v>
+        <v>170</v>
       </c>
       <c r="K1271" s="17" t="s">
         <v>12</v>
@@ -65201,15 +65410,17 @@
       <c r="M1271" s="18"/>
       <c r="N1271" s="53"/>
       <c r="O1271" s="18"/>
-      <c r="P1271" s="18"/>
+      <c r="P1271" s="33" t="s">
+        <v>1961</v>
+      </c>
       <c r="Q1271" s="11">
-        <v>94576946</v>
+        <v>521141691</v>
       </c>
       <c r="R1271" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1272" spans="1:18" ht="15" thickBot="1">
+    <row r="1272" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1272" s="2">
         <v>380</v>
       </c>
@@ -65217,28 +65428,28 @@
         <v>46253</v>
       </c>
       <c r="C1272" s="11" t="s">
-        <v>1558</v>
+        <v>726</v>
       </c>
       <c r="D1272" s="11" t="s">
-        <v>1559</v>
-      </c>
-      <c r="E1272" s="12" t="s">
-        <v>20</v>
+        <v>1967</v>
+      </c>
+      <c r="E1272" s="30" t="s">
+        <v>78</v>
       </c>
       <c r="F1272" s="13" t="s">
         <v>21</v>
       </c>
       <c r="G1272" s="14">
-        <v>31118</v>
+        <v>53285</v>
       </c>
       <c r="H1272" s="15">
-        <v>52207</v>
+        <v>10458</v>
       </c>
       <c r="I1272" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1272" s="15" t="s">
-        <v>902</v>
+        <v>170</v>
       </c>
       <c r="K1272" s="17" t="s">
         <v>12</v>
@@ -65247,15 +65458,17 @@
       <c r="M1272" s="18"/>
       <c r="N1272" s="53"/>
       <c r="O1272" s="18"/>
-      <c r="P1272" s="18"/>
+      <c r="P1272" s="33" t="s">
+        <v>1961</v>
+      </c>
       <c r="Q1272" s="11">
-        <v>97640553</v>
+        <v>588611305</v>
       </c>
       <c r="R1272" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1273" spans="1:18" ht="23.4" thickBot="1">
+    <row r="1273" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1273" s="2">
         <v>381</v>
       </c>
@@ -65263,28 +65476,28 @@
         <v>46253</v>
       </c>
       <c r="C1273" s="11" t="s">
-        <v>1560</v>
-      </c>
-      <c r="D1273" s="11">
-        <v>137911273</v>
-      </c>
-      <c r="E1273" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1273" s="16" t="s">
-        <v>81</v>
+        <v>1968</v>
+      </c>
+      <c r="D1273" s="11" t="s">
+        <v>1969</v>
+      </c>
+      <c r="E1273" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1273" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G1273" s="14">
-        <v>8212</v>
+        <v>80623</v>
       </c>
       <c r="H1273" s="15">
-        <v>1005</v>
-      </c>
-      <c r="I1273" s="22" t="s">
-        <v>274</v>
+        <v>19522</v>
+      </c>
+      <c r="I1273" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="J1273" s="15" t="s">
-        <v>1015</v>
+        <v>170</v>
       </c>
       <c r="K1273" s="17" t="s">
         <v>12</v>
@@ -65293,15 +65506,17 @@
       <c r="M1273" s="18"/>
       <c r="N1273" s="53"/>
       <c r="O1273" s="18"/>
-      <c r="P1273" s="18"/>
+      <c r="P1273" s="33" t="s">
+        <v>1961</v>
+      </c>
       <c r="Q1273" s="11">
-        <v>94067496</v>
+        <v>524074068</v>
       </c>
       <c r="R1273" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1274" spans="1:18" ht="15" thickBot="1">
+    <row r="1274" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1274" s="2">
         <v>382</v>
       </c>
@@ -65309,28 +65524,26 @@
         <v>46253</v>
       </c>
       <c r="C1274" s="11" t="s">
-        <v>1843</v>
+        <v>1970</v>
       </c>
       <c r="D1274" s="11" t="s">
-        <v>1844</v>
-      </c>
-      <c r="E1274" s="12" t="s">
-        <v>20</v>
+        <v>1971</v>
+      </c>
+      <c r="E1274" s="30" t="s">
+        <v>78</v>
       </c>
       <c r="F1274" s="13" t="s">
         <v>21</v>
       </c>
       <c r="G1274" s="14">
-        <v>30431</v>
-      </c>
-      <c r="H1274" s="15">
-        <v>38650</v>
-      </c>
+        <v>79279</v>
+      </c>
+      <c r="H1274" s="18"/>
       <c r="I1274" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1274" s="15" t="s">
-        <v>1845</v>
+        <v>170</v>
       </c>
       <c r="K1274" s="17" t="s">
         <v>12</v>
@@ -65339,15 +65552,17 @@
       <c r="M1274" s="18"/>
       <c r="N1274" s="53"/>
       <c r="O1274" s="18"/>
-      <c r="P1274" s="18"/>
+      <c r="P1274" s="33" t="s">
+        <v>1961</v>
+      </c>
       <c r="Q1274" s="11">
-        <v>94426460</v>
+        <v>555466775</v>
       </c>
       <c r="R1274" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1275" spans="1:18" ht="15" thickBot="1">
+    <row r="1275" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1275" s="2">
         <v>383</v>
       </c>
@@ -65355,10 +65570,10 @@
         <v>46253</v>
       </c>
       <c r="C1275" s="11" t="s">
-        <v>1846</v>
+        <v>1972</v>
       </c>
       <c r="D1275" s="11" t="s">
-        <v>1847</v>
+        <v>1973</v>
       </c>
       <c r="E1275" s="12" t="s">
         <v>20</v>
@@ -65367,16 +65582,16 @@
         <v>21</v>
       </c>
       <c r="G1275" s="14">
-        <v>98897</v>
+        <v>35298</v>
       </c>
       <c r="H1275" s="15">
-        <v>79394</v>
+        <v>7509</v>
       </c>
       <c r="I1275" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1275" s="15" t="s">
-        <v>1845</v>
+        <v>170</v>
       </c>
       <c r="K1275" s="17" t="s">
         <v>12</v>
@@ -65385,15 +65600,17 @@
       <c r="M1275" s="18"/>
       <c r="N1275" s="53"/>
       <c r="O1275" s="18"/>
-      <c r="P1275" s="18"/>
+      <c r="P1275" s="33" t="s">
+        <v>1974</v>
+      </c>
       <c r="Q1275" s="11">
-        <v>76710125</v>
+        <v>543442645</v>
       </c>
       <c r="R1275" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1276" spans="1:18" ht="15" thickBot="1">
+    <row r="1276" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1276" s="2">
         <v>384</v>
       </c>
@@ -65401,45 +65618,43 @@
         <v>46253</v>
       </c>
       <c r="C1276" s="11" t="s">
-        <v>1848</v>
+        <v>1975</v>
       </c>
       <c r="D1276" s="11" t="s">
-        <v>1849</v>
-      </c>
-      <c r="E1276" s="12" t="s">
-        <v>20</v>
+        <v>1976</v>
+      </c>
+      <c r="E1276" s="70" t="s">
+        <v>1195</v>
       </c>
       <c r="F1276" s="13" t="s">
         <v>21</v>
       </c>
       <c r="G1276" s="14">
-        <v>84116</v>
+        <v>40646</v>
       </c>
       <c r="H1276" s="15">
-        <v>81840</v>
+        <v>31517</v>
       </c>
       <c r="I1276" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1276" s="15" t="s">
-        <v>1845</v>
-      </c>
-      <c r="K1276" s="17" t="s">
-        <v>12</v>
+        <v>170</v>
+      </c>
+      <c r="K1276" s="47" t="s">
+        <v>511</v>
       </c>
       <c r="L1276" s="18"/>
       <c r="M1276" s="18"/>
       <c r="N1276" s="53"/>
       <c r="O1276" s="18"/>
       <c r="P1276" s="18"/>
-      <c r="Q1276" s="11">
-        <v>77843137</v>
-      </c>
+      <c r="Q1276" s="18"/>
       <c r="R1276" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1277" spans="1:18" ht="15" thickBot="1">
+    <row r="1277" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1277" s="2">
         <v>385</v>
       </c>
@@ -65447,45 +65662,43 @@
         <v>46253</v>
       </c>
       <c r="C1277" s="11" t="s">
-        <v>1850</v>
-      </c>
-      <c r="D1277" s="11">
-        <v>121628418</v>
-      </c>
-      <c r="E1277" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1277" s="16" t="s">
-        <v>81</v>
+        <v>1977</v>
+      </c>
+      <c r="D1277" s="11" t="s">
+        <v>1978</v>
+      </c>
+      <c r="E1277" s="70" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F1277" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G1277" s="14">
-        <v>1190</v>
+        <v>44018</v>
       </c>
       <c r="H1277" s="15">
-        <v>2955</v>
+        <v>29029</v>
       </c>
       <c r="I1277" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1277" s="15" t="s">
-        <v>1845</v>
-      </c>
-      <c r="K1277" s="17" t="s">
-        <v>12</v>
+        <v>170</v>
+      </c>
+      <c r="K1277" s="47" t="s">
+        <v>511</v>
       </c>
       <c r="L1277" s="18"/>
       <c r="M1277" s="18"/>
       <c r="N1277" s="53"/>
       <c r="O1277" s="18"/>
       <c r="P1277" s="18"/>
-      <c r="Q1277" s="11" t="s">
-        <v>1851</v>
-      </c>
+      <c r="Q1277" s="18"/>
       <c r="R1277" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1278" spans="1:18" ht="15" thickBot="1">
+    <row r="1278" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1278" s="2">
         <v>386</v>
       </c>
@@ -65493,40 +65706,38 @@
         <v>46253</v>
       </c>
       <c r="C1278" s="11" t="s">
-        <v>1852</v>
-      </c>
-      <c r="D1278" s="11">
-        <v>10400768</v>
-      </c>
-      <c r="E1278" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1278" s="16" t="s">
-        <v>81</v>
+        <v>1979</v>
+      </c>
+      <c r="D1278" s="11" t="s">
+        <v>1980</v>
+      </c>
+      <c r="E1278" s="70" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F1278" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G1278" s="14">
-        <v>8472</v>
+        <v>62386</v>
       </c>
       <c r="H1278" s="15">
-        <v>8481</v>
+        <v>60239</v>
       </c>
       <c r="I1278" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1278" s="15" t="s">
-        <v>1845</v>
-      </c>
-      <c r="K1278" s="17" t="s">
-        <v>12</v>
+        <v>170</v>
+      </c>
+      <c r="K1278" s="47" t="s">
+        <v>511</v>
       </c>
       <c r="L1278" s="18"/>
       <c r="M1278" s="18"/>
       <c r="N1278" s="53"/>
       <c r="O1278" s="18"/>
       <c r="P1278" s="18"/>
-      <c r="Q1278" s="11" t="s">
-        <v>1853</v>
-      </c>
+      <c r="Q1278" s="18"/>
       <c r="R1278" s="21" t="s">
         <v>14</v>
       </c>
@@ -65539,28 +65750,28 @@
         <v>46253</v>
       </c>
       <c r="C1279" s="11" t="s">
-        <v>1854</v>
-      </c>
-      <c r="D1279" s="11">
-        <v>138047837</v>
+        <v>1556</v>
+      </c>
+      <c r="D1279" s="11" t="s">
+        <v>1557</v>
       </c>
       <c r="E1279" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1279" s="16" t="s">
-        <v>81</v>
+      <c r="F1279" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G1279" s="14">
-        <v>2301</v>
+        <v>40509</v>
       </c>
       <c r="H1279" s="15">
-        <v>997</v>
+        <v>64464</v>
       </c>
       <c r="I1279" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1279" s="15" t="s">
-        <v>1845</v>
+        <v>902</v>
       </c>
       <c r="K1279" s="17" t="s">
         <v>12</v>
@@ -65570,8 +65781,8 @@
       <c r="N1279" s="53"/>
       <c r="O1279" s="18"/>
       <c r="P1279" s="18"/>
-      <c r="Q1279" s="11" t="s">
-        <v>1855</v>
+      <c r="Q1279" s="11">
+        <v>94576946</v>
       </c>
       <c r="R1279" s="21" t="s">
         <v>14</v>
@@ -65585,28 +65796,28 @@
         <v>46253</v>
       </c>
       <c r="C1280" s="11" t="s">
-        <v>1856</v>
-      </c>
-      <c r="D1280" s="11">
-        <v>124185553</v>
+        <v>1558</v>
+      </c>
+      <c r="D1280" s="11" t="s">
+        <v>1559</v>
       </c>
       <c r="E1280" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1280" s="16" t="s">
-        <v>81</v>
+      <c r="F1280" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G1280" s="14">
-        <v>2230</v>
+        <v>31118</v>
       </c>
       <c r="H1280" s="15">
-        <v>3342</v>
+        <v>52207</v>
       </c>
       <c r="I1280" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1280" s="15" t="s">
-        <v>1845</v>
+        <v>902</v>
       </c>
       <c r="K1280" s="17" t="s">
         <v>12</v>
@@ -65617,13 +65828,13 @@
       <c r="O1280" s="18"/>
       <c r="P1280" s="18"/>
       <c r="Q1280" s="11">
-        <v>71265800</v>
+        <v>97640553</v>
       </c>
       <c r="R1280" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1281" spans="1:18" ht="15" thickBot="1">
+    <row r="1281" spans="1:18" ht="23.4" thickBot="1">
       <c r="A1281" s="2">
         <v>389</v>
       </c>
@@ -65631,10 +65842,10 @@
         <v>46253</v>
       </c>
       <c r="C1281" s="11" t="s">
-        <v>1857</v>
+        <v>1560</v>
       </c>
       <c r="D1281" s="11">
-        <v>120435809</v>
+        <v>137911273</v>
       </c>
       <c r="E1281" s="12" t="s">
         <v>20</v>
@@ -65643,16 +65854,16 @@
         <v>81</v>
       </c>
       <c r="G1281" s="14">
-        <v>5221</v>
+        <v>8212</v>
       </c>
       <c r="H1281" s="15">
-        <v>4698</v>
-      </c>
-      <c r="I1281" s="16" t="s">
-        <v>10</v>
+        <v>1005</v>
+      </c>
+      <c r="I1281" s="22" t="s">
+        <v>274</v>
       </c>
       <c r="J1281" s="15" t="s">
-        <v>1845</v>
+        <v>1015</v>
       </c>
       <c r="K1281" s="17" t="s">
         <v>12</v>
@@ -65662,8 +65873,8 @@
       <c r="N1281" s="53"/>
       <c r="O1281" s="18"/>
       <c r="P1281" s="18"/>
-      <c r="Q1281" s="11" t="s">
-        <v>1858</v>
+      <c r="Q1281" s="11">
+        <v>94067496</v>
       </c>
       <c r="R1281" s="21" t="s">
         <v>14</v>
@@ -65677,22 +65888,22 @@
         <v>46253</v>
       </c>
       <c r="C1282" s="11" t="s">
-        <v>1859</v>
-      </c>
-      <c r="D1282" s="11">
-        <v>125366206</v>
+        <v>1843</v>
+      </c>
+      <c r="D1282" s="11" t="s">
+        <v>1844</v>
       </c>
       <c r="E1282" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1282" s="16" t="s">
-        <v>81</v>
+      <c r="F1282" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G1282" s="14">
-        <v>8626</v>
+        <v>30431</v>
       </c>
       <c r="H1282" s="15">
-        <v>682</v>
+        <v>38650</v>
       </c>
       <c r="I1282" s="16" t="s">
         <v>10</v>
@@ -65708,8 +65919,8 @@
       <c r="N1282" s="53"/>
       <c r="O1282" s="18"/>
       <c r="P1282" s="18"/>
-      <c r="Q1282" s="11" t="s">
-        <v>1860</v>
+      <c r="Q1282" s="11">
+        <v>94426460</v>
       </c>
       <c r="R1282" s="21" t="s">
         <v>14</v>
@@ -65723,28 +65934,28 @@
         <v>46253</v>
       </c>
       <c r="C1283" s="11" t="s">
-        <v>1861</v>
-      </c>
-      <c r="D1283" s="11">
-        <v>138404841</v>
+        <v>1846</v>
+      </c>
+      <c r="D1283" s="11" t="s">
+        <v>1847</v>
       </c>
       <c r="E1283" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1283" s="16" t="s">
-        <v>81</v>
+      <c r="F1283" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G1283" s="14">
-        <v>2462</v>
+        <v>98897</v>
       </c>
       <c r="H1283" s="15">
-        <v>4504</v>
+        <v>79394</v>
       </c>
       <c r="I1283" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1283" s="15" t="s">
-        <v>13</v>
+        <v>1845</v>
       </c>
       <c r="K1283" s="17" t="s">
         <v>12</v>
@@ -65755,7 +65966,7 @@
       <c r="O1283" s="18"/>
       <c r="P1283" s="18"/>
       <c r="Q1283" s="11">
-        <v>71084512</v>
+        <v>76710125</v>
       </c>
       <c r="R1283" s="21" t="s">
         <v>14</v>
@@ -65769,28 +65980,28 @@
         <v>46253</v>
       </c>
       <c r="C1284" s="11" t="s">
-        <v>1862</v>
-      </c>
-      <c r="D1284" s="11">
-        <v>118606535</v>
+        <v>1848</v>
+      </c>
+      <c r="D1284" s="11" t="s">
+        <v>1849</v>
       </c>
       <c r="E1284" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1284" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="G1284" s="14" t="s">
-        <v>1863</v>
+      <c r="F1284" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1284" s="14">
+        <v>84116</v>
       </c>
       <c r="H1284" s="15">
-        <v>8868</v>
+        <v>81840</v>
       </c>
       <c r="I1284" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1284" s="15" t="s">
-        <v>13</v>
+        <v>1845</v>
       </c>
       <c r="K1284" s="17" t="s">
         <v>12</v>
@@ -65801,13 +66012,13 @@
       <c r="O1284" s="18"/>
       <c r="P1284" s="18"/>
       <c r="Q1284" s="11">
-        <v>72325874</v>
+        <v>77843137</v>
       </c>
       <c r="R1284" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1285" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1285" spans="1:18" ht="15" thickBot="1">
       <c r="A1285" s="2">
         <v>393</v>
       </c>
@@ -65815,28 +66026,28 @@
         <v>46253</v>
       </c>
       <c r="C1285" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="D1285" s="11" t="s">
-        <v>1864</v>
+        <v>1850</v>
+      </c>
+      <c r="D1285" s="11">
+        <v>121628418</v>
       </c>
       <c r="E1285" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1285" s="13" t="s">
-        <v>21</v>
+      <c r="F1285" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1285" s="14">
-        <v>50077</v>
+        <v>1190</v>
       </c>
       <c r="H1285" s="15">
-        <v>69726</v>
+        <v>2955</v>
       </c>
       <c r="I1285" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1285" s="15" t="s">
-        <v>169</v>
+        <v>1845</v>
       </c>
       <c r="K1285" s="17" t="s">
         <v>12</v>
@@ -65846,8 +66057,8 @@
       <c r="N1285" s="53"/>
       <c r="O1285" s="18"/>
       <c r="P1285" s="18"/>
-      <c r="Q1285" s="11">
-        <v>95767531</v>
+      <c r="Q1285" s="11" t="s">
+        <v>1851</v>
       </c>
       <c r="R1285" s="21" t="s">
         <v>14</v>
@@ -65861,28 +66072,28 @@
         <v>46253</v>
       </c>
       <c r="C1286" s="11" t="s">
-        <v>1865</v>
-      </c>
-      <c r="D1286" s="11" t="s">
-        <v>1866</v>
+        <v>1852</v>
+      </c>
+      <c r="D1286" s="11">
+        <v>10400768</v>
       </c>
       <c r="E1286" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1286" s="13" t="s">
-        <v>21</v>
+      <c r="F1286" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1286" s="14">
-        <v>60622</v>
+        <v>8472</v>
       </c>
       <c r="H1286" s="15">
-        <v>91454</v>
+        <v>8481</v>
       </c>
       <c r="I1286" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1286" s="15" t="s">
-        <v>908</v>
+        <v>1845</v>
       </c>
       <c r="K1286" s="17" t="s">
         <v>12</v>
@@ -65892,8 +66103,8 @@
       <c r="N1286" s="53"/>
       <c r="O1286" s="18"/>
       <c r="P1286" s="18"/>
-      <c r="Q1286" s="11">
-        <v>553738457</v>
+      <c r="Q1286" s="11" t="s">
+        <v>1853</v>
       </c>
       <c r="R1286" s="21" t="s">
         <v>14</v>
@@ -65907,28 +66118,28 @@
         <v>46253</v>
       </c>
       <c r="C1287" s="11" t="s">
-        <v>1867</v>
-      </c>
-      <c r="D1287" s="11" t="s">
-        <v>1868</v>
+        <v>1854</v>
+      </c>
+      <c r="D1287" s="11">
+        <v>138047837</v>
       </c>
       <c r="E1287" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1287" s="13" t="s">
-        <v>21</v>
+      <c r="F1287" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1287" s="14">
-        <v>40994</v>
+        <v>2301</v>
       </c>
       <c r="H1287" s="15">
-        <v>25765</v>
+        <v>997</v>
       </c>
       <c r="I1287" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1287" s="15" t="s">
-        <v>908</v>
+        <v>1845</v>
       </c>
       <c r="K1287" s="17" t="s">
         <v>12</v>
@@ -65938,8 +66149,8 @@
       <c r="N1287" s="53"/>
       <c r="O1287" s="18"/>
       <c r="P1287" s="18"/>
-      <c r="Q1287" s="11">
-        <v>521610897</v>
+      <c r="Q1287" s="11" t="s">
+        <v>1855</v>
       </c>
       <c r="R1287" s="21" t="s">
         <v>14</v>
@@ -65953,28 +66164,28 @@
         <v>46253</v>
       </c>
       <c r="C1288" s="11" t="s">
-        <v>1869</v>
-      </c>
-      <c r="D1288" s="11" t="s">
-        <v>1870</v>
+        <v>1856</v>
+      </c>
+      <c r="D1288" s="11">
+        <v>124185553</v>
       </c>
       <c r="E1288" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1288" s="13" t="s">
-        <v>21</v>
+      <c r="F1288" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1288" s="14">
-        <v>76180</v>
+        <v>2230</v>
       </c>
       <c r="H1288" s="15">
-        <v>18192</v>
+        <v>3342</v>
       </c>
       <c r="I1288" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1288" s="15" t="s">
-        <v>908</v>
+        <v>1845</v>
       </c>
       <c r="K1288" s="17" t="s">
         <v>12</v>
@@ -65985,7 +66196,7 @@
       <c r="O1288" s="18"/>
       <c r="P1288" s="18"/>
       <c r="Q1288" s="11">
-        <v>507620859</v>
+        <v>71265800</v>
       </c>
       <c r="R1288" s="21" t="s">
         <v>14</v>
@@ -65999,10 +66210,10 @@
         <v>46253</v>
       </c>
       <c r="C1289" s="11" t="s">
-        <v>658</v>
+        <v>1857</v>
       </c>
       <c r="D1289" s="11">
-        <v>113856103</v>
+        <v>120435809</v>
       </c>
       <c r="E1289" s="12" t="s">
         <v>20</v>
@@ -66011,16 +66222,16 @@
         <v>81</v>
       </c>
       <c r="G1289" s="14">
-        <v>8299</v>
+        <v>5221</v>
       </c>
       <c r="H1289" s="15">
-        <v>9559</v>
+        <v>4698</v>
       </c>
       <c r="I1289" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1289" s="15" t="s">
-        <v>908</v>
+        <v>1845</v>
       </c>
       <c r="K1289" s="17" t="s">
         <v>12</v>
@@ -66030,8 +66241,8 @@
       <c r="N1289" s="53"/>
       <c r="O1289" s="18"/>
       <c r="P1289" s="18"/>
-      <c r="Q1289" s="11">
-        <v>94984520</v>
+      <c r="Q1289" s="11" t="s">
+        <v>1858</v>
       </c>
       <c r="R1289" s="21" t="s">
         <v>14</v>
@@ -66045,10 +66256,10 @@
         <v>46253</v>
       </c>
       <c r="C1290" s="11" t="s">
-        <v>1871</v>
+        <v>1859</v>
       </c>
       <c r="D1290" s="11">
-        <v>121317564</v>
+        <v>125366206</v>
       </c>
       <c r="E1290" s="12" t="s">
         <v>20</v>
@@ -66057,16 +66268,16 @@
         <v>81</v>
       </c>
       <c r="G1290" s="14">
-        <v>1910</v>
+        <v>8626</v>
       </c>
       <c r="H1290" s="15">
-        <v>6638</v>
+        <v>682</v>
       </c>
       <c r="I1290" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1290" s="15" t="s">
-        <v>908</v>
+        <v>1845</v>
       </c>
       <c r="K1290" s="17" t="s">
         <v>12</v>
@@ -66076,8 +66287,8 @@
       <c r="N1290" s="53"/>
       <c r="O1290" s="18"/>
       <c r="P1290" s="18"/>
-      <c r="Q1290" s="11">
-        <v>95159561</v>
+      <c r="Q1290" s="11" t="s">
+        <v>1860</v>
       </c>
       <c r="R1290" s="21" t="s">
         <v>14</v>
@@ -66091,10 +66302,10 @@
         <v>46253</v>
       </c>
       <c r="C1291" s="11" t="s">
-        <v>1872</v>
+        <v>1861</v>
       </c>
       <c r="D1291" s="11">
-        <v>80693513</v>
+        <v>138404841</v>
       </c>
       <c r="E1291" s="12" t="s">
         <v>20</v>
@@ -66103,16 +66314,16 @@
         <v>81</v>
       </c>
       <c r="G1291" s="14">
-        <v>9343</v>
+        <v>2462</v>
       </c>
       <c r="H1291" s="15">
-        <v>4998</v>
+        <v>4504</v>
       </c>
       <c r="I1291" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1291" s="15" t="s">
-        <v>908</v>
+        <v>13</v>
       </c>
       <c r="K1291" s="17" t="s">
         <v>12</v>
@@ -66123,7 +66334,7 @@
       <c r="O1291" s="18"/>
       <c r="P1291" s="18"/>
       <c r="Q1291" s="11">
-        <v>79269317</v>
+        <v>71084512</v>
       </c>
       <c r="R1291" s="21" t="s">
         <v>14</v>
@@ -66137,10 +66348,10 @@
         <v>46253</v>
       </c>
       <c r="C1292" s="11" t="s">
-        <v>1982</v>
+        <v>1862</v>
       </c>
       <c r="D1292" s="11">
-        <v>13584541</v>
+        <v>118606535</v>
       </c>
       <c r="E1292" s="12" t="s">
         <v>20</v>
@@ -66148,17 +66359,17 @@
       <c r="F1292" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="G1292" s="14">
-        <v>9439</v>
+      <c r="G1292" s="14" t="s">
+        <v>1863</v>
       </c>
       <c r="H1292" s="15">
-        <v>1909</v>
+        <v>8868</v>
       </c>
       <c r="I1292" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1292" s="15" t="s">
-        <v>908</v>
+        <v>13</v>
       </c>
       <c r="K1292" s="17" t="s">
         <v>12</v>
@@ -66169,13 +66380,13 @@
       <c r="O1292" s="18"/>
       <c r="P1292" s="18"/>
       <c r="Q1292" s="11">
-        <v>78365894</v>
+        <v>72325874</v>
       </c>
       <c r="R1292" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1293" spans="1:18" ht="15" thickBot="1">
+    <row r="1293" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1293" s="2">
         <v>401</v>
       </c>
@@ -66183,28 +66394,28 @@
         <v>46253</v>
       </c>
       <c r="C1293" s="11" t="s">
-        <v>1983</v>
-      </c>
-      <c r="D1293" s="11">
-        <v>79408446</v>
+        <v>124</v>
+      </c>
+      <c r="D1293" s="11" t="s">
+        <v>1864</v>
       </c>
       <c r="E1293" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1293" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="G1293" s="14" t="s">
-        <v>1984</v>
+      <c r="F1293" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1293" s="14">
+        <v>50077</v>
       </c>
       <c r="H1293" s="15">
-        <v>7339</v>
+        <v>69726</v>
       </c>
       <c r="I1293" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J1293" s="15" t="s">
-        <v>908</v>
+        <v>169</v>
       </c>
       <c r="K1293" s="17" t="s">
         <v>12</v>
@@ -66215,7 +66426,7 @@
       <c r="O1293" s="18"/>
       <c r="P1293" s="18"/>
       <c r="Q1293" s="11">
-        <v>76922904</v>
+        <v>95767531</v>
       </c>
       <c r="R1293" s="21" t="s">
         <v>14</v>
@@ -66229,22 +66440,22 @@
         <v>46253</v>
       </c>
       <c r="C1294" s="11" t="s">
-        <v>1985</v>
+        <v>1865</v>
       </c>
       <c r="D1294" s="11" t="s">
-        <v>1986</v>
-      </c>
-      <c r="E1294" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1294" s="16" t="s">
-        <v>81</v>
+        <v>1866</v>
+      </c>
+      <c r="E1294" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1294" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G1294" s="14">
-        <v>52732</v>
+        <v>60622</v>
       </c>
       <c r="H1294" s="15">
-        <v>51388</v>
+        <v>91454</v>
       </c>
       <c r="I1294" s="16" t="s">
         <v>10</v>
@@ -66261,7 +66472,7 @@
       <c r="O1294" s="18"/>
       <c r="P1294" s="18"/>
       <c r="Q1294" s="11">
-        <v>95520693</v>
+        <v>553738457</v>
       </c>
       <c r="R1294" s="21" t="s">
         <v>14</v>
@@ -66275,10 +66486,10 @@
         <v>46253</v>
       </c>
       <c r="C1295" s="11" t="s">
-        <v>1873</v>
+        <v>1867</v>
       </c>
       <c r="D1295" s="11" t="s">
-        <v>1874</v>
+        <v>1868</v>
       </c>
       <c r="E1295" s="12" t="s">
         <v>20</v>
@@ -66287,16 +66498,16 @@
         <v>21</v>
       </c>
       <c r="G1295" s="14">
-        <v>33319</v>
+        <v>40994</v>
       </c>
       <c r="H1295" s="15">
-        <v>32943</v>
-      </c>
-      <c r="I1295" s="22" t="s">
-        <v>274</v>
+        <v>25765</v>
+      </c>
+      <c r="I1295" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="J1295" s="15" t="s">
-        <v>374</v>
+        <v>908</v>
       </c>
       <c r="K1295" s="17" t="s">
         <v>12</v>
@@ -66306,7 +66517,9 @@
       <c r="N1295" s="53"/>
       <c r="O1295" s="18"/>
       <c r="P1295" s="18"/>
-      <c r="Q1295" s="18"/>
+      <c r="Q1295" s="11">
+        <v>521610897</v>
+      </c>
       <c r="R1295" s="21" t="s">
         <v>14</v>
       </c>
@@ -66319,10 +66532,10 @@
         <v>46253</v>
       </c>
       <c r="C1296" s="11" t="s">
-        <v>1987</v>
+        <v>1869</v>
       </c>
       <c r="D1296" s="11" t="s">
-        <v>1988</v>
+        <v>1870</v>
       </c>
       <c r="E1296" s="12" t="s">
         <v>20</v>
@@ -66331,16 +66544,16 @@
         <v>21</v>
       </c>
       <c r="G1296" s="14">
-        <v>13272</v>
+        <v>76180</v>
       </c>
       <c r="H1296" s="15">
-        <v>98118</v>
-      </c>
-      <c r="I1296" s="22" t="s">
-        <v>274</v>
+        <v>18192</v>
+      </c>
+      <c r="I1296" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="J1296" s="15" t="s">
-        <v>1376</v>
+        <v>908</v>
       </c>
       <c r="K1296" s="17" t="s">
         <v>12</v>
@@ -66351,13 +66564,13 @@
       <c r="O1296" s="18"/>
       <c r="P1296" s="18"/>
       <c r="Q1296" s="11">
-        <v>94609416</v>
+        <v>507620859</v>
       </c>
       <c r="R1296" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1297" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1297" spans="1:18" ht="15" thickBot="1">
       <c r="A1297" s="2">
         <v>405</v>
       </c>
@@ -66365,10 +66578,10 @@
         <v>46253</v>
       </c>
       <c r="C1297" s="11" t="s">
-        <v>1989</v>
+        <v>658</v>
       </c>
       <c r="D1297" s="11">
-        <v>101540233</v>
+        <v>113856103</v>
       </c>
       <c r="E1297" s="12" t="s">
         <v>20</v>
@@ -66377,16 +66590,16 @@
         <v>81</v>
       </c>
       <c r="G1297" s="14">
-        <v>5126</v>
+        <v>8299</v>
       </c>
       <c r="H1297" s="15">
-        <v>3767</v>
-      </c>
-      <c r="I1297" s="15" t="s">
-        <v>82</v>
+        <v>9559</v>
+      </c>
+      <c r="I1297" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="J1297" s="15" t="s">
-        <v>465</v>
+        <v>908</v>
       </c>
       <c r="K1297" s="17" t="s">
         <v>12</v>
@@ -66397,42 +66610,42 @@
       <c r="O1297" s="18"/>
       <c r="P1297" s="18"/>
       <c r="Q1297" s="11">
-        <v>97066171</v>
+        <v>94984520</v>
       </c>
       <c r="R1297" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1298" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1298" spans="1:18" ht="15" thickBot="1">
       <c r="A1298" s="2">
         <v>406</v>
       </c>
       <c r="B1298" s="10">
         <v>46253</v>
       </c>
-      <c r="C1298" s="46" t="s">
-        <v>1990</v>
-      </c>
-      <c r="D1298" s="46" t="s">
-        <v>1991</v>
+      <c r="C1298" s="11" t="s">
+        <v>1871</v>
+      </c>
+      <c r="D1298" s="11">
+        <v>121317564</v>
       </c>
       <c r="E1298" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1298" s="13" t="s">
-        <v>21</v>
+      <c r="F1298" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1298" s="14">
-        <v>24788</v>
+        <v>1910</v>
       </c>
       <c r="H1298" s="15">
-        <v>81726</v>
-      </c>
-      <c r="I1298" s="15" t="s">
-        <v>82</v>
+        <v>6638</v>
+      </c>
+      <c r="I1298" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="J1298" s="15" t="s">
-        <v>465</v>
+        <v>908</v>
       </c>
       <c r="K1298" s="17" t="s">
         <v>12</v>
@@ -66442,41 +66655,43 @@
       <c r="N1298" s="53"/>
       <c r="O1298" s="18"/>
       <c r="P1298" s="18"/>
-      <c r="Q1298" s="18"/>
+      <c r="Q1298" s="11">
+        <v>95159561</v>
+      </c>
       <c r="R1298" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1299" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1299" spans="1:18" ht="15" thickBot="1">
       <c r="A1299" s="2">
         <v>407</v>
       </c>
       <c r="B1299" s="10">
         <v>46253</v>
       </c>
-      <c r="C1299" s="46" t="s">
-        <v>1992</v>
-      </c>
-      <c r="D1299" s="46" t="s">
-        <v>1993</v>
+      <c r="C1299" s="11" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D1299" s="11">
+        <v>80693513</v>
       </c>
       <c r="E1299" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1299" s="13" t="s">
-        <v>21</v>
+      <c r="F1299" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1299" s="14">
-        <v>90011</v>
+        <v>9343</v>
       </c>
       <c r="H1299" s="15">
-        <v>44326</v>
-      </c>
-      <c r="I1299" s="15" t="s">
-        <v>82</v>
+        <v>4998</v>
+      </c>
+      <c r="I1299" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="J1299" s="15" t="s">
-        <v>465</v>
+        <v>908</v>
       </c>
       <c r="K1299" s="17" t="s">
         <v>12</v>
@@ -66487,42 +66702,42 @@
       <c r="O1299" s="18"/>
       <c r="P1299" s="18"/>
       <c r="Q1299" s="11">
-        <v>77124080</v>
+        <v>79269317</v>
       </c>
       <c r="R1299" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1300" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1300" spans="1:18" ht="15" thickBot="1">
       <c r="A1300" s="2">
         <v>408</v>
       </c>
       <c r="B1300" s="10">
         <v>46253</v>
       </c>
-      <c r="C1300" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1300" s="46" t="s">
-        <v>1994</v>
+      <c r="C1300" s="11" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D1300" s="11">
+        <v>13584541</v>
       </c>
       <c r="E1300" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1300" s="13" t="s">
-        <v>21</v>
+      <c r="F1300" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1300" s="14">
-        <v>81708</v>
+        <v>9439</v>
       </c>
       <c r="H1300" s="15">
-        <v>44992</v>
-      </c>
-      <c r="I1300" s="15" t="s">
-        <v>82</v>
+        <v>1909</v>
+      </c>
+      <c r="I1300" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="J1300" s="15" t="s">
-        <v>465</v>
+        <v>908</v>
       </c>
       <c r="K1300" s="17" t="s">
         <v>12</v>
@@ -66533,42 +66748,42 @@
       <c r="O1300" s="18"/>
       <c r="P1300" s="18"/>
       <c r="Q1300" s="11">
-        <v>77659893</v>
+        <v>78365894</v>
       </c>
       <c r="R1300" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1301" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1301" spans="1:18" ht="15" thickBot="1">
       <c r="A1301" s="2">
         <v>409</v>
       </c>
       <c r="B1301" s="10">
         <v>46253</v>
       </c>
-      <c r="C1301" s="46" t="s">
-        <v>468</v>
-      </c>
-      <c r="D1301" s="46" t="s">
-        <v>1995</v>
+      <c r="C1301" s="11" t="s">
+        <v>1982</v>
+      </c>
+      <c r="D1301" s="11">
+        <v>79408446</v>
       </c>
       <c r="E1301" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1301" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1301" s="14">
-        <v>33746</v>
+      <c r="F1301" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1301" s="14" t="s">
+        <v>1983</v>
       </c>
       <c r="H1301" s="15">
-        <v>33830</v>
-      </c>
-      <c r="I1301" s="15" t="s">
-        <v>82</v>
+        <v>7339</v>
+      </c>
+      <c r="I1301" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="J1301" s="15" t="s">
-        <v>465</v>
+        <v>908</v>
       </c>
       <c r="K1301" s="17" t="s">
         <v>12</v>
@@ -66579,42 +66794,42 @@
       <c r="O1301" s="18"/>
       <c r="P1301" s="18"/>
       <c r="Q1301" s="11">
-        <v>528112551</v>
+        <v>76922904</v>
       </c>
       <c r="R1301" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1302" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1302" spans="1:18" ht="15" thickBot="1">
       <c r="A1302" s="2">
         <v>410</v>
       </c>
       <c r="B1302" s="10">
         <v>46253</v>
       </c>
-      <c r="C1302" s="46" t="s">
-        <v>1996</v>
-      </c>
-      <c r="D1302" s="46" t="s">
-        <v>1997</v>
-      </c>
-      <c r="E1302" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1302" s="13" t="s">
-        <v>21</v>
+      <c r="C1302" s="11" t="s">
+        <v>1984</v>
+      </c>
+      <c r="D1302" s="11" t="s">
+        <v>1985</v>
+      </c>
+      <c r="E1302" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1302" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="G1302" s="14">
-        <v>52254</v>
+        <v>52732</v>
       </c>
       <c r="H1302" s="15">
-        <v>43013</v>
-      </c>
-      <c r="I1302" s="15" t="s">
-        <v>82</v>
+        <v>51388</v>
+      </c>
+      <c r="I1302" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="J1302" s="15" t="s">
-        <v>465</v>
+        <v>908</v>
       </c>
       <c r="K1302" s="17" t="s">
         <v>12</v>
@@ -66625,24 +66840,24 @@
       <c r="O1302" s="18"/>
       <c r="P1302" s="18"/>
       <c r="Q1302" s="11">
-        <v>589798596</v>
+        <v>95520693</v>
       </c>
       <c r="R1302" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1303" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1303" spans="1:18" ht="15" thickBot="1">
       <c r="A1303" s="2">
         <v>411</v>
       </c>
       <c r="B1303" s="10">
         <v>46253</v>
       </c>
-      <c r="C1303" s="46" t="s">
-        <v>1998</v>
-      </c>
-      <c r="D1303" s="46" t="s">
-        <v>1999</v>
+      <c r="C1303" s="11" t="s">
+        <v>1873</v>
+      </c>
+      <c r="D1303" s="11" t="s">
+        <v>1874</v>
       </c>
       <c r="E1303" s="12" t="s">
         <v>20</v>
@@ -66651,16 +66866,16 @@
         <v>21</v>
       </c>
       <c r="G1303" s="14">
-        <v>74899</v>
+        <v>33319</v>
       </c>
       <c r="H1303" s="15">
-        <v>92269</v>
-      </c>
-      <c r="I1303" s="15" t="s">
-        <v>82</v>
+        <v>32943</v>
+      </c>
+      <c r="I1303" s="22" t="s">
+        <v>274</v>
       </c>
       <c r="J1303" s="15" t="s">
-        <v>465</v>
+        <v>374</v>
       </c>
       <c r="K1303" s="17" t="s">
         <v>12</v>
@@ -66670,25 +66885,23 @@
       <c r="N1303" s="53"/>
       <c r="O1303" s="18"/>
       <c r="P1303" s="18"/>
-      <c r="Q1303" s="11">
-        <v>75175379</v>
-      </c>
+      <c r="Q1303" s="18"/>
       <c r="R1303" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1304" spans="1:18" ht="28.2" thickBot="1">
+    <row r="1304" spans="1:18" ht="15" thickBot="1">
       <c r="A1304" s="2">
         <v>412</v>
       </c>
       <c r="B1304" s="10">
         <v>46253</v>
       </c>
-      <c r="C1304" s="46" t="s">
-        <v>2000</v>
-      </c>
-      <c r="D1304" s="46" t="s">
-        <v>2001</v>
+      <c r="C1304" s="11" t="s">
+        <v>1986</v>
+      </c>
+      <c r="D1304" s="11" t="s">
+        <v>1987</v>
       </c>
       <c r="E1304" s="12" t="s">
         <v>20</v>
@@ -66697,16 +66910,16 @@
         <v>21</v>
       </c>
       <c r="G1304" s="14">
-        <v>55729</v>
+        <v>13272</v>
       </c>
       <c r="H1304" s="15">
-        <v>21874</v>
-      </c>
-      <c r="I1304" s="15" t="s">
-        <v>82</v>
+        <v>98118</v>
+      </c>
+      <c r="I1304" s="22" t="s">
+        <v>274</v>
       </c>
       <c r="J1304" s="15" t="s">
-        <v>465</v>
+        <v>1376</v>
       </c>
       <c r="K1304" s="17" t="s">
         <v>12</v>
@@ -66716,8 +66929,8 @@
       <c r="N1304" s="53"/>
       <c r="O1304" s="18"/>
       <c r="P1304" s="18"/>
-      <c r="Q1304" s="15">
-        <v>77821958</v>
+      <c r="Q1304" s="11">
+        <v>94609416</v>
       </c>
       <c r="R1304" s="21" t="s">
         <v>14</v>
@@ -66730,11 +66943,11 @@
       <c r="B1305" s="10">
         <v>46253</v>
       </c>
-      <c r="C1305" s="46" t="s">
-        <v>2002</v>
-      </c>
-      <c r="D1305" s="46">
-        <v>107129497</v>
+      <c r="C1305" s="11" t="s">
+        <v>1988</v>
+      </c>
+      <c r="D1305" s="11">
+        <v>101540233</v>
       </c>
       <c r="E1305" s="12" t="s">
         <v>20</v>
@@ -66743,10 +66956,10 @@
         <v>81</v>
       </c>
       <c r="G1305" s="14">
-        <v>9340</v>
+        <v>5126</v>
       </c>
       <c r="H1305" s="15">
-        <v>3757</v>
+        <v>3767</v>
       </c>
       <c r="I1305" s="15" t="s">
         <v>82</v>
@@ -66762,14 +66975,14 @@
       <c r="N1305" s="53"/>
       <c r="O1305" s="18"/>
       <c r="P1305" s="18"/>
-      <c r="Q1305" s="15">
-        <v>94088182</v>
+      <c r="Q1305" s="11">
+        <v>97066171</v>
       </c>
       <c r="R1305" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1306" spans="1:18" ht="40.799999999999997" thickBot="1">
+    <row r="1306" spans="1:18" ht="28.2" thickBot="1">
       <c r="A1306" s="2">
         <v>414</v>
       </c>
@@ -66777,22 +66990,22 @@
         <v>46253</v>
       </c>
       <c r="C1306" s="46" t="s">
-        <v>2003</v>
-      </c>
-      <c r="D1306" s="46">
-        <v>110877972</v>
+        <v>1989</v>
+      </c>
+      <c r="D1306" s="46" t="s">
+        <v>1990</v>
       </c>
       <c r="E1306" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1306" s="16" t="s">
-        <v>81</v>
+      <c r="F1306" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G1306" s="14">
-        <v>5734</v>
+        <v>24788</v>
       </c>
       <c r="H1306" s="15">
-        <v>235</v>
+        <v>81726</v>
       </c>
       <c r="I1306" s="15" t="s">
         <v>82</v>
@@ -66808,9 +67021,7 @@
       <c r="N1306" s="53"/>
       <c r="O1306" s="18"/>
       <c r="P1306" s="18"/>
-      <c r="Q1306" s="15">
-        <v>79031527</v>
-      </c>
+      <c r="Q1306" s="18"/>
       <c r="R1306" s="21" t="s">
         <v>14</v>
       </c>
@@ -66823,22 +67034,22 @@
         <v>46253</v>
       </c>
       <c r="C1307" s="46" t="s">
-        <v>685</v>
-      </c>
-      <c r="D1307" s="46">
-        <v>138838184</v>
+        <v>1991</v>
+      </c>
+      <c r="D1307" s="46" t="s">
+        <v>1992</v>
       </c>
       <c r="E1307" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1307" s="16" t="s">
-        <v>81</v>
+      <c r="F1307" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G1307" s="14">
-        <v>2233</v>
+        <v>90011</v>
       </c>
       <c r="H1307" s="15">
-        <v>198</v>
+        <v>44326</v>
       </c>
       <c r="I1307" s="15" t="s">
         <v>82</v>
@@ -66854,11 +67065,1303 @@
       <c r="N1307" s="53"/>
       <c r="O1307" s="18"/>
       <c r="P1307" s="18"/>
-      <c r="Q1307" s="15">
-        <v>76249681</v>
+      <c r="Q1307" s="11">
+        <v>77124080</v>
       </c>
       <c r="R1307" s="21" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1308" s="2">
+        <v>416</v>
+      </c>
+      <c r="B1308" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1308" s="46" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1308" s="46" t="s">
+        <v>1993</v>
+      </c>
+      <c r="E1308" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1308" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1308" s="14">
+        <v>81708</v>
+      </c>
+      <c r="H1308" s="15">
+        <v>44992</v>
+      </c>
+      <c r="I1308" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="J1308" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="K1308" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1308" s="18"/>
+      <c r="M1308" s="18"/>
+      <c r="N1308" s="53"/>
+      <c r="O1308" s="18"/>
+      <c r="P1308" s="18"/>
+      <c r="Q1308" s="11">
+        <v>77659893</v>
+      </c>
+      <c r="R1308" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1309" s="2">
+        <v>417</v>
+      </c>
+      <c r="B1309" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1309" s="46" t="s">
+        <v>468</v>
+      </c>
+      <c r="D1309" s="46" t="s">
+        <v>1994</v>
+      </c>
+      <c r="E1309" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1309" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1309" s="14">
+        <v>33746</v>
+      </c>
+      <c r="H1309" s="15">
+        <v>33830</v>
+      </c>
+      <c r="I1309" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="J1309" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="K1309" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1309" s="18"/>
+      <c r="M1309" s="18"/>
+      <c r="N1309" s="53"/>
+      <c r="O1309" s="18"/>
+      <c r="P1309" s="18"/>
+      <c r="Q1309" s="11">
+        <v>528112551</v>
+      </c>
+      <c r="R1309" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1310" s="2">
+        <v>418</v>
+      </c>
+      <c r="B1310" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1310" s="46" t="s">
+        <v>1995</v>
+      </c>
+      <c r="D1310" s="46" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E1310" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1310" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1310" s="14">
+        <v>52254</v>
+      </c>
+      <c r="H1310" s="15">
+        <v>43013</v>
+      </c>
+      <c r="I1310" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="J1310" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="K1310" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1310" s="18"/>
+      <c r="M1310" s="18"/>
+      <c r="N1310" s="53"/>
+      <c r="O1310" s="18"/>
+      <c r="P1310" s="18"/>
+      <c r="Q1310" s="11">
+        <v>589798596</v>
+      </c>
+      <c r="R1310" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1311" s="2">
+        <v>419</v>
+      </c>
+      <c r="B1311" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1311" s="46" t="s">
+        <v>1997</v>
+      </c>
+      <c r="D1311" s="46" t="s">
+        <v>1998</v>
+      </c>
+      <c r="E1311" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1311" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1311" s="14">
+        <v>74899</v>
+      </c>
+      <c r="H1311" s="15">
+        <v>92269</v>
+      </c>
+      <c r="I1311" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="J1311" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="K1311" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1311" s="18"/>
+      <c r="M1311" s="18"/>
+      <c r="N1311" s="53"/>
+      <c r="O1311" s="18"/>
+      <c r="P1311" s="18"/>
+      <c r="Q1311" s="11">
+        <v>75175379</v>
+      </c>
+      <c r="R1311" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1312" s="2">
+        <v>420</v>
+      </c>
+      <c r="B1312" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1312" s="46" t="s">
+        <v>1999</v>
+      </c>
+      <c r="D1312" s="46" t="s">
+        <v>2000</v>
+      </c>
+      <c r="E1312" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1312" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1312" s="14">
+        <v>55729</v>
+      </c>
+      <c r="H1312" s="15">
+        <v>21874</v>
+      </c>
+      <c r="I1312" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="J1312" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="K1312" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1312" s="18"/>
+      <c r="M1312" s="18"/>
+      <c r="N1312" s="53"/>
+      <c r="O1312" s="18"/>
+      <c r="P1312" s="18"/>
+      <c r="Q1312" s="15">
+        <v>77821958</v>
+      </c>
+      <c r="R1312" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1313" s="2">
+        <v>421</v>
+      </c>
+      <c r="B1313" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1313" s="46" t="s">
+        <v>2001</v>
+      </c>
+      <c r="D1313" s="46">
+        <v>107129497</v>
+      </c>
+      <c r="E1313" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1313" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1313" s="14">
+        <v>9340</v>
+      </c>
+      <c r="H1313" s="15">
+        <v>3757</v>
+      </c>
+      <c r="I1313" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="J1313" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="K1313" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1313" s="18"/>
+      <c r="M1313" s="18"/>
+      <c r="N1313" s="53"/>
+      <c r="O1313" s="18"/>
+      <c r="P1313" s="18"/>
+      <c r="Q1313" s="15">
+        <v>94088182</v>
+      </c>
+      <c r="R1313" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:18" ht="40.799999999999997" thickBot="1">
+      <c r="A1314" s="2">
+        <v>422</v>
+      </c>
+      <c r="B1314" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1314" s="46" t="s">
+        <v>2002</v>
+      </c>
+      <c r="D1314" s="46">
+        <v>110877972</v>
+      </c>
+      <c r="E1314" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1314" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1314" s="14">
+        <v>5734</v>
+      </c>
+      <c r="H1314" s="15">
+        <v>235</v>
+      </c>
+      <c r="I1314" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="J1314" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="K1314" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1314" s="18"/>
+      <c r="M1314" s="18"/>
+      <c r="N1314" s="53"/>
+      <c r="O1314" s="18"/>
+      <c r="P1314" s="18"/>
+      <c r="Q1314" s="15">
+        <v>79031527</v>
+      </c>
+      <c r="R1314" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:18" ht="28.2" thickBot="1">
+      <c r="A1315" s="2">
+        <v>423</v>
+      </c>
+      <c r="B1315" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1315" s="46" t="s">
+        <v>685</v>
+      </c>
+      <c r="D1315" s="46">
+        <v>138838184</v>
+      </c>
+      <c r="E1315" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1315" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1315" s="14">
+        <v>2233</v>
+      </c>
+      <c r="H1315" s="15">
+        <v>198</v>
+      </c>
+      <c r="I1315" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="J1315" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="K1315" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1315" s="18"/>
+      <c r="M1315" s="18"/>
+      <c r="N1315" s="53"/>
+      <c r="O1315" s="18"/>
+      <c r="P1315" s="18"/>
+      <c r="Q1315" s="15">
+        <v>76249681</v>
+      </c>
+      <c r="R1315" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:18" ht="15" thickBot="1">
+      <c r="A1316" s="2">
+        <v>424</v>
+      </c>
+      <c r="B1316" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1316" s="71" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D1316" s="71">
+        <v>91662311</v>
+      </c>
+      <c r="E1316" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1316" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1316" s="72">
+        <v>4473</v>
+      </c>
+      <c r="H1316" s="71">
+        <v>4502</v>
+      </c>
+      <c r="I1316" s="73" t="s">
+        <v>2017</v>
+      </c>
+      <c r="J1316" s="18"/>
+      <c r="K1316" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="L1316" s="18"/>
+      <c r="M1316" s="18"/>
+      <c r="N1316" s="53"/>
+      <c r="O1316" s="18"/>
+      <c r="P1316" s="18"/>
+      <c r="Q1316" s="71">
+        <v>93953829</v>
+      </c>
+      <c r="R1316" s="16" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:18" ht="15" thickBot="1">
+      <c r="A1317" s="2">
+        <v>425</v>
+      </c>
+      <c r="B1317" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1317" s="71" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D1317" s="71">
+        <v>79101863</v>
+      </c>
+      <c r="E1317" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1317" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1317" s="72">
+        <v>5194</v>
+      </c>
+      <c r="H1317" s="71">
+        <v>9766</v>
+      </c>
+      <c r="I1317" s="73" t="s">
+        <v>2017</v>
+      </c>
+      <c r="J1317" s="18"/>
+      <c r="K1317" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="L1317" s="18"/>
+      <c r="M1317" s="18"/>
+      <c r="N1317" s="53"/>
+      <c r="O1317" s="18"/>
+      <c r="P1317" s="18"/>
+      <c r="Q1317" s="71">
+        <v>99649307</v>
+      </c>
+      <c r="R1317" s="16" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:18" ht="15" thickBot="1">
+      <c r="A1318" s="2">
+        <v>426</v>
+      </c>
+      <c r="B1318" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1318" s="71" t="s">
+        <v>2020</v>
+      </c>
+      <c r="D1318" s="71">
+        <v>84862551</v>
+      </c>
+      <c r="E1318" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1318" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1318" s="72" t="s">
+        <v>2021</v>
+      </c>
+      <c r="H1318" s="71">
+        <v>9185</v>
+      </c>
+      <c r="I1318" s="73" t="s">
+        <v>2017</v>
+      </c>
+      <c r="J1318" s="18"/>
+      <c r="K1318" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="L1318" s="18"/>
+      <c r="M1318" s="18"/>
+      <c r="N1318" s="53"/>
+      <c r="O1318" s="18"/>
+      <c r="P1318" s="18"/>
+      <c r="Q1318" s="71">
+        <v>96264258</v>
+      </c>
+      <c r="R1318" s="16" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1319" s="2">
+        <v>427</v>
+      </c>
+      <c r="B1319" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1319" s="71" t="s">
+        <v>2022</v>
+      </c>
+      <c r="D1319" s="71">
+        <v>65919668</v>
+      </c>
+      <c r="E1319" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1319" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1319" s="72">
+        <v>8319</v>
+      </c>
+      <c r="H1319" s="71">
+        <v>2816</v>
+      </c>
+      <c r="I1319" s="73" t="s">
+        <v>2017</v>
+      </c>
+      <c r="J1319" s="18"/>
+      <c r="K1319" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="L1319" s="18"/>
+      <c r="M1319" s="18"/>
+      <c r="N1319" s="53"/>
+      <c r="O1319" s="18"/>
+      <c r="P1319" s="18"/>
+      <c r="Q1319" s="71">
+        <v>94421839</v>
+      </c>
+      <c r="R1319" s="16" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:18" ht="15" thickBot="1">
+      <c r="A1320" s="2">
+        <v>428</v>
+      </c>
+      <c r="B1320" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1320" s="71" t="s">
+        <v>2023</v>
+      </c>
+      <c r="D1320" s="71">
+        <v>113593131</v>
+      </c>
+      <c r="E1320" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1320" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1320" s="72">
+        <v>1250</v>
+      </c>
+      <c r="H1320" s="71">
+        <v>6962</v>
+      </c>
+      <c r="I1320" s="73" t="s">
+        <v>2017</v>
+      </c>
+      <c r="J1320" s="18"/>
+      <c r="K1320" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="L1320" s="18"/>
+      <c r="M1320" s="18"/>
+      <c r="N1320" s="53"/>
+      <c r="O1320" s="18"/>
+      <c r="P1320" s="18"/>
+      <c r="Q1320" s="71">
+        <v>79046101</v>
+      </c>
+      <c r="R1320" s="16" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:18" ht="15" thickBot="1">
+      <c r="A1321" s="2">
+        <v>429</v>
+      </c>
+      <c r="B1321" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1321" s="71" t="s">
+        <v>2024</v>
+      </c>
+      <c r="D1321" s="71">
+        <v>99308589</v>
+      </c>
+      <c r="E1321" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1321" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1321" s="72">
+        <v>9400</v>
+      </c>
+      <c r="H1321" s="71" t="s">
+        <v>2025</v>
+      </c>
+      <c r="I1321" s="73" t="s">
+        <v>2017</v>
+      </c>
+      <c r="J1321" s="18"/>
+      <c r="K1321" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="L1321" s="18"/>
+      <c r="M1321" s="18"/>
+      <c r="N1321" s="53"/>
+      <c r="O1321" s="18"/>
+      <c r="P1321" s="18"/>
+      <c r="Q1321" s="71">
+        <v>96341510</v>
+      </c>
+      <c r="R1321" s="16" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:18" ht="15" thickBot="1">
+      <c r="A1322" s="2">
+        <v>430</v>
+      </c>
+      <c r="B1322" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1322" s="71" t="s">
+        <v>2026</v>
+      </c>
+      <c r="D1322" s="71">
+        <v>8726371</v>
+      </c>
+      <c r="E1322" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1322" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1322" s="72">
+        <v>3551</v>
+      </c>
+      <c r="H1322" s="71">
+        <v>9761</v>
+      </c>
+      <c r="I1322" s="73" t="s">
+        <v>2017</v>
+      </c>
+      <c r="J1322" s="18"/>
+      <c r="K1322" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="L1322" s="18"/>
+      <c r="M1322" s="18"/>
+      <c r="N1322" s="53"/>
+      <c r="O1322" s="18"/>
+      <c r="P1322" s="18"/>
+      <c r="Q1322" s="71">
+        <v>92315235</v>
+      </c>
+      <c r="R1322" s="16" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:18" ht="15" thickBot="1">
+      <c r="A1323" s="2">
+        <v>431</v>
+      </c>
+      <c r="B1323" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1323" s="71" t="s">
+        <v>2027</v>
+      </c>
+      <c r="D1323" s="71">
+        <v>6735848</v>
+      </c>
+      <c r="E1323" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1323" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1323" s="72">
+        <v>955</v>
+      </c>
+      <c r="H1323" s="71">
+        <v>3915</v>
+      </c>
+      <c r="I1323" s="73" t="s">
+        <v>2017</v>
+      </c>
+      <c r="J1323" s="18"/>
+      <c r="K1323" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="L1323" s="18"/>
+      <c r="M1323" s="18"/>
+      <c r="N1323" s="53"/>
+      <c r="O1323" s="18"/>
+      <c r="P1323" s="18"/>
+      <c r="Q1323" s="71">
+        <v>98912658</v>
+      </c>
+      <c r="R1323" s="16" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:18" ht="15" thickBot="1">
+      <c r="A1324" s="2">
+        <v>432</v>
+      </c>
+      <c r="B1324" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1324" s="71" t="s">
+        <v>2028</v>
+      </c>
+      <c r="D1324" s="71">
+        <v>37041662</v>
+      </c>
+      <c r="E1324" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1324" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1324" s="72">
+        <v>6644</v>
+      </c>
+      <c r="H1324" s="71">
+        <v>1118</v>
+      </c>
+      <c r="I1324" s="73" t="s">
+        <v>2017</v>
+      </c>
+      <c r="J1324" s="18"/>
+      <c r="K1324" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="L1324" s="18"/>
+      <c r="M1324" s="18"/>
+      <c r="N1324" s="53"/>
+      <c r="O1324" s="18"/>
+      <c r="P1324" s="18"/>
+      <c r="Q1324" s="71">
+        <v>97966106</v>
+      </c>
+      <c r="R1324" s="16" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1325" s="2">
+        <v>433</v>
+      </c>
+      <c r="B1325" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1325" s="71" t="s">
+        <v>2029</v>
+      </c>
+      <c r="D1325" s="71">
+        <v>14964987</v>
+      </c>
+      <c r="E1325" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1325" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1325" s="72" t="s">
+        <v>2030</v>
+      </c>
+      <c r="H1325" s="71" t="s">
+        <v>2031</v>
+      </c>
+      <c r="I1325" s="73" t="s">
+        <v>2017</v>
+      </c>
+      <c r="J1325" s="18"/>
+      <c r="K1325" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="L1325" s="18"/>
+      <c r="M1325" s="18"/>
+      <c r="N1325" s="53"/>
+      <c r="O1325" s="18"/>
+      <c r="P1325" s="18"/>
+      <c r="Q1325" s="71">
+        <v>92558941</v>
+      </c>
+      <c r="R1325" s="16" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:18" ht="15" thickBot="1">
+      <c r="A1326" s="2">
+        <v>434</v>
+      </c>
+      <c r="B1326" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1326" s="74" t="s">
+        <v>2032</v>
+      </c>
+      <c r="D1326" s="74">
+        <v>8852091</v>
+      </c>
+      <c r="E1326" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1326" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1326" s="72">
+        <v>8116</v>
+      </c>
+      <c r="H1326" s="71">
+        <v>9291</v>
+      </c>
+      <c r="I1326" s="73" t="s">
+        <v>2017</v>
+      </c>
+      <c r="J1326" s="18"/>
+      <c r="K1326" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="L1326" s="18"/>
+      <c r="M1326" s="18"/>
+      <c r="N1326" s="53"/>
+      <c r="O1326" s="18"/>
+      <c r="P1326" s="18"/>
+      <c r="Q1326" s="74">
+        <v>91123225</v>
+      </c>
+      <c r="R1326" s="16" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:18" ht="15" thickBot="1">
+      <c r="A1327" s="2">
+        <v>435</v>
+      </c>
+      <c r="B1327" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1327" s="71" t="s">
+        <v>2033</v>
+      </c>
+      <c r="D1327" s="71">
+        <v>8348336</v>
+      </c>
+      <c r="E1327" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1327" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1327" s="72">
+        <v>4475</v>
+      </c>
+      <c r="H1327" s="71">
+        <v>4844</v>
+      </c>
+      <c r="I1327" s="73" t="s">
+        <v>2017</v>
+      </c>
+      <c r="J1327" s="18"/>
+      <c r="K1327" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="L1327" s="18"/>
+      <c r="M1327" s="18"/>
+      <c r="N1327" s="53"/>
+      <c r="O1327" s="18"/>
+      <c r="P1327" s="18"/>
+      <c r="Q1327" s="71">
+        <v>96690774</v>
+      </c>
+      <c r="R1327" s="16" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:18" ht="15" thickBot="1">
+      <c r="A1328" s="2">
+        <v>436</v>
+      </c>
+      <c r="B1328" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1328" s="71" t="s">
+        <v>2034</v>
+      </c>
+      <c r="D1328" s="71">
+        <v>23743806</v>
+      </c>
+      <c r="E1328" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1328" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1328" s="72">
+        <v>414</v>
+      </c>
+      <c r="H1328" s="71" t="s">
+        <v>2035</v>
+      </c>
+      <c r="I1328" s="73" t="s">
+        <v>2017</v>
+      </c>
+      <c r="J1328" s="18"/>
+      <c r="K1328" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="L1328" s="18"/>
+      <c r="M1328" s="18"/>
+      <c r="N1328" s="53"/>
+      <c r="O1328" s="18"/>
+      <c r="P1328" s="18"/>
+      <c r="Q1328" s="71">
+        <v>94000637</v>
+      </c>
+      <c r="R1328" s="16" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:18" ht="15" thickBot="1">
+      <c r="A1329" s="2">
+        <v>437</v>
+      </c>
+      <c r="B1329" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1329" s="71" t="s">
+        <v>2036</v>
+      </c>
+      <c r="D1329" s="71">
+        <v>6253321</v>
+      </c>
+      <c r="E1329" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1329" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1329" s="72">
+        <v>668</v>
+      </c>
+      <c r="H1329" s="71">
+        <v>4282</v>
+      </c>
+      <c r="I1329" s="73" t="s">
+        <v>2017</v>
+      </c>
+      <c r="J1329" s="18"/>
+      <c r="K1329" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="L1329" s="18"/>
+      <c r="M1329" s="18"/>
+      <c r="N1329" s="53"/>
+      <c r="O1329" s="18"/>
+      <c r="P1329" s="18"/>
+      <c r="Q1329" s="71">
+        <v>79022588</v>
+      </c>
+      <c r="R1329" s="16" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:18" ht="15" thickBot="1">
+      <c r="A1330" s="2">
+        <v>438</v>
+      </c>
+      <c r="B1330" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1330" s="71" t="s">
+        <v>2037</v>
+      </c>
+      <c r="D1330" s="71">
+        <v>13050614</v>
+      </c>
+      <c r="E1330" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1330" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1330" s="72">
+        <v>609</v>
+      </c>
+      <c r="H1330" s="71">
+        <v>3428</v>
+      </c>
+      <c r="I1330" s="73" t="s">
+        <v>2017</v>
+      </c>
+      <c r="J1330" s="18"/>
+      <c r="K1330" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="L1330" s="18"/>
+      <c r="M1330" s="18"/>
+      <c r="N1330" s="53"/>
+      <c r="O1330" s="18"/>
+      <c r="P1330" s="18"/>
+      <c r="Q1330" s="71">
+        <v>92533410</v>
+      </c>
+      <c r="R1330" s="16" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:18" ht="15" thickBot="1">
+      <c r="A1331" s="2">
+        <v>439</v>
+      </c>
+      <c r="B1331" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1331" s="71" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D1331" s="71">
+        <v>124900323</v>
+      </c>
+      <c r="E1331" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1331" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1331" s="72">
+        <v>1796</v>
+      </c>
+      <c r="H1331" s="71">
+        <v>7734</v>
+      </c>
+      <c r="I1331" s="73" t="s">
+        <v>2017</v>
+      </c>
+      <c r="J1331" s="18"/>
+      <c r="K1331" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="L1331" s="18"/>
+      <c r="M1331" s="18"/>
+      <c r="N1331" s="53"/>
+      <c r="O1331" s="18"/>
+      <c r="P1331" s="18"/>
+      <c r="Q1331" s="71">
+        <v>99424853</v>
+      </c>
+      <c r="R1331" s="16" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:18" ht="27.6" thickBot="1">
+      <c r="A1332" s="2">
+        <v>440</v>
+      </c>
+      <c r="B1332" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1332" s="71" t="s">
+        <v>2039</v>
+      </c>
+      <c r="D1332" s="71">
+        <v>11270537</v>
+      </c>
+      <c r="E1332" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1332" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1332" s="72">
+        <v>9536</v>
+      </c>
+      <c r="H1332" s="71">
+        <v>6892</v>
+      </c>
+      <c r="I1332" s="73" t="s">
+        <v>2017</v>
+      </c>
+      <c r="J1332" s="18"/>
+      <c r="K1332" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="L1332" s="18"/>
+      <c r="M1332" s="18"/>
+      <c r="N1332" s="53"/>
+      <c r="O1332" s="18"/>
+      <c r="P1332" s="18"/>
+      <c r="Q1332" s="75">
+        <v>93599901</v>
+      </c>
+      <c r="R1332" s="16" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:18" ht="15" thickBot="1">
+      <c r="A1333" s="2">
+        <v>441</v>
+      </c>
+      <c r="B1333" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1333" s="71" t="s">
+        <v>2040</v>
+      </c>
+      <c r="D1333" s="71">
+        <v>1366798</v>
+      </c>
+      <c r="E1333" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1333" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1333" s="72">
+        <v>5669</v>
+      </c>
+      <c r="H1333" s="71">
+        <v>3860</v>
+      </c>
+      <c r="I1333" s="73" t="s">
+        <v>2017</v>
+      </c>
+      <c r="J1333" s="18"/>
+      <c r="K1333" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="L1333" s="18"/>
+      <c r="M1333" s="18"/>
+      <c r="N1333" s="53"/>
+      <c r="O1333" s="18"/>
+      <c r="P1333" s="18"/>
+      <c r="Q1333" s="71">
+        <v>99638638</v>
+      </c>
+      <c r="R1333" s="16" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:18" ht="15" thickBot="1">
+      <c r="A1334" s="2">
+        <v>442</v>
+      </c>
+      <c r="B1334" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1334" s="71" t="s">
+        <v>2041</v>
+      </c>
+      <c r="D1334" s="71">
+        <v>111632104</v>
+      </c>
+      <c r="E1334" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1334" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1334" s="72">
+        <v>5170</v>
+      </c>
+      <c r="H1334" s="71" t="s">
+        <v>2042</v>
+      </c>
+      <c r="I1334" s="73" t="s">
+        <v>2017</v>
+      </c>
+      <c r="J1334" s="18"/>
+      <c r="K1334" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="L1334" s="18"/>
+      <c r="M1334" s="18"/>
+      <c r="N1334" s="53"/>
+      <c r="O1334" s="18"/>
+      <c r="P1334" s="18"/>
+      <c r="Q1334" s="71">
+        <v>90288230</v>
+      </c>
+      <c r="R1334" s="16" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:18" ht="15" thickBot="1">
+      <c r="A1335" s="2">
+        <v>443</v>
+      </c>
+      <c r="B1335" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1335" s="71" t="s">
+        <v>2043</v>
+      </c>
+      <c r="D1335" s="71">
+        <v>22866674</v>
+      </c>
+      <c r="E1335" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1335" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1335" s="72">
+        <v>569</v>
+      </c>
+      <c r="H1335" s="71">
+        <v>6226</v>
+      </c>
+      <c r="I1335" s="73" t="s">
+        <v>2017</v>
+      </c>
+      <c r="J1335" s="18"/>
+      <c r="K1335" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="L1335" s="18"/>
+      <c r="M1335" s="18"/>
+      <c r="N1335" s="53"/>
+      <c r="O1335" s="18"/>
+      <c r="P1335" s="18"/>
+      <c r="Q1335" s="75">
+        <v>92498584</v>
+      </c>
+      <c r="R1335" s="16" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:18" ht="15" thickBot="1">
+      <c r="A1336" s="2">
+        <v>444</v>
+      </c>
+      <c r="B1336" s="10">
+        <v>46253</v>
+      </c>
+      <c r="C1336" s="71" t="s">
+        <v>2044</v>
+      </c>
+      <c r="D1336" s="71">
+        <v>29264612</v>
+      </c>
+      <c r="E1336" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1336" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1336" s="72">
+        <v>1569</v>
+      </c>
+      <c r="H1336" s="71">
+        <v>3635</v>
+      </c>
+      <c r="I1336" s="73" t="s">
+        <v>2017</v>
+      </c>
+      <c r="J1336" s="18"/>
+      <c r="K1336" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="L1336" s="18"/>
+      <c r="M1336" s="18"/>
+      <c r="N1336" s="53"/>
+      <c r="O1336" s="18"/>
+      <c r="P1336" s="18"/>
+      <c r="Q1336" s="71">
+        <v>94499680</v>
+      </c>
+      <c r="R1336" s="16" t="s">
+        <v>2018</v>
       </c>
     </row>
   </sheetData>

--- a/data/sampledata.xlsx
+++ b/data/sampledata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46D8854-89C8-49D3-BCDD-BE52F9CA32CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D848F2FE-4910-4A37-BA12-07303FB0589A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9E2596D9-E4D7-4F61-9C92-3191B68C1938}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10885" uniqueCount="2206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11318" uniqueCount="2299">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -6656,13 +6656,292 @@
   </si>
   <si>
     <t>EQ0159587</t>
+  </si>
+  <si>
+    <t>220//426</t>
+  </si>
+  <si>
+    <t>BAHADUR JUNAID</t>
+  </si>
+  <si>
+    <t>BN3171503</t>
+  </si>
+  <si>
+    <t>NAWAZ NOMAN</t>
+  </si>
+  <si>
+    <t>AR9615703</t>
+  </si>
+  <si>
+    <t>MANZOOR HUSSAIN</t>
+  </si>
+  <si>
+    <t>SL6890285</t>
+  </si>
+  <si>
+    <t>ASIF RANA</t>
+  </si>
+  <si>
+    <t>AL1887385</t>
+  </si>
+  <si>
+    <t>SHAH SYED ADIL</t>
+  </si>
+  <si>
+    <t>PH5149428</t>
+  </si>
+  <si>
+    <t>MK5140557</t>
+  </si>
+  <si>
+    <t>TARIQ HASSAN</t>
+  </si>
+  <si>
+    <t>EW7961973</t>
+  </si>
+  <si>
+    <t>ALI FAISAL</t>
+  </si>
+  <si>
+    <t>VU1804564</t>
+  </si>
+  <si>
+    <t>ALI BASHARAT</t>
+  </si>
+  <si>
+    <t>BISHRAT</t>
+  </si>
+  <si>
+    <t>SHAHZAD AKBAR</t>
+  </si>
+  <si>
+    <t>IJAZ AHMED</t>
+  </si>
+  <si>
+    <t>KASHIF MUHAMMAD</t>
+  </si>
+  <si>
+    <t>ABDUL LATTIFF REDHA</t>
+  </si>
+  <si>
+    <t>JAGMINDER SINGH</t>
+  </si>
+  <si>
+    <t>ZA637173</t>
+  </si>
+  <si>
+    <t>ZIA UL HUSSAIN</t>
+  </si>
+  <si>
+    <t>ZA362128</t>
+  </si>
+  <si>
+    <t>WAHAB FAZAL</t>
+  </si>
+  <si>
+    <t>AC6135758</t>
+  </si>
+  <si>
+    <t>TANSEER RAHMAN</t>
+  </si>
+  <si>
+    <t>ISRAR RAZAQ</t>
+  </si>
+  <si>
+    <t>AHMAD NASEER</t>
+  </si>
+  <si>
+    <t>RASOOL FAZAL</t>
+  </si>
+  <si>
+    <t>BB9803692</t>
+  </si>
+  <si>
+    <t>SAMEER HASSAN</t>
+  </si>
+  <si>
+    <t>MQ6803522</t>
+  </si>
+  <si>
+    <t>AKTHAR ZEESHAN</t>
+  </si>
+  <si>
+    <t>NH1341752</t>
+  </si>
+  <si>
+    <t>TRAILER NOT VALID IN DOC</t>
+  </si>
+  <si>
+    <t>FARRUKH ABBAS</t>
+  </si>
+  <si>
+    <t>ARSLAN HAFIZ</t>
+  </si>
+  <si>
+    <t>DE1911373</t>
+  </si>
+  <si>
+    <t>18106257*</t>
+  </si>
+  <si>
+    <t>R/SUBHAN</t>
+  </si>
+  <si>
+    <t>MAJID SULAIMAN</t>
+  </si>
+  <si>
+    <t>4751*</t>
+  </si>
+  <si>
+    <t>ASAAD SULAIMAN</t>
+  </si>
+  <si>
+    <t>KHALIFA SAIF</t>
+  </si>
+  <si>
+    <t>OMER SALIM</t>
+  </si>
+  <si>
+    <t>4907*</t>
+  </si>
+  <si>
+    <t>HELAL HUMAID</t>
+  </si>
+  <si>
+    <t>639*</t>
+  </si>
+  <si>
+    <t>UMAIR ALI</t>
+  </si>
+  <si>
+    <t>7267*</t>
+  </si>
+  <si>
+    <t>IRFAN</t>
+  </si>
+  <si>
+    <t>HABIB</t>
+  </si>
+  <si>
+    <t>BV6038662</t>
+  </si>
+  <si>
+    <t>ZOHAIB</t>
+  </si>
+  <si>
+    <t>JN5193492</t>
+  </si>
+  <si>
+    <t>SHAHZAIB</t>
+  </si>
+  <si>
+    <t>QK6805812</t>
+  </si>
+  <si>
+    <t>EQ1511204</t>
+  </si>
+  <si>
+    <t>HAMMAD ASIF</t>
+  </si>
+  <si>
+    <t>FW1886122</t>
+  </si>
+  <si>
+    <t>052 6226554</t>
+  </si>
+  <si>
+    <t>JN6894876</t>
+  </si>
+  <si>
+    <t>055 4210211</t>
+  </si>
+  <si>
+    <t>SHAHID REASHEED</t>
+  </si>
+  <si>
+    <t>DE9848444</t>
+  </si>
+  <si>
+    <t>AKMAL SHAHZAD</t>
+  </si>
+  <si>
+    <t>DV5149326</t>
+  </si>
+  <si>
+    <t>YASIF ADNAN</t>
+  </si>
+  <si>
+    <t>CC1400363</t>
+  </si>
+  <si>
+    <t>SAJID ALI SABIR</t>
+  </si>
+  <si>
+    <t>SYED TAIMOUR</t>
+  </si>
+  <si>
+    <t>NADEEM AKHTAR</t>
+  </si>
+  <si>
+    <t>VIJAY BAHADUR</t>
+  </si>
+  <si>
+    <t>ZA381173</t>
+  </si>
+  <si>
+    <t>KAMAR ALI</t>
+  </si>
+  <si>
+    <t>ZA452510</t>
+  </si>
+  <si>
+    <t>SHAHIDA HUSEN</t>
+  </si>
+  <si>
+    <t>ZA452427</t>
+  </si>
+  <si>
+    <t>Z5435261</t>
+  </si>
+  <si>
+    <t>FAZAL ABBAS</t>
+  </si>
+  <si>
+    <t>GHULAM GHOUS</t>
+  </si>
+  <si>
+    <t>NH6802303</t>
+  </si>
+  <si>
+    <t>74319-</t>
+  </si>
+  <si>
+    <t>ADNAN AHMED</t>
+  </si>
+  <si>
+    <t>HG1168414</t>
+  </si>
+  <si>
+    <t>C/O Adnan</t>
+  </si>
+  <si>
+    <t>ZAIN MUSHTAQ</t>
+  </si>
+  <si>
+    <t>BS0843834</t>
+  </si>
+  <si>
+    <t>C/O Zain</t>
+  </si>
+  <si>
+    <t>KJ1155196</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="37">
+  <fonts count="38">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6894,6 +7173,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -7023,7 +7309,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7254,6 +7540,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7570,7 +7859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549975ED-4350-4707-9ED8-0DD8ADBE5296}">
-  <dimension ref="A1:R1442"/>
+  <dimension ref="A1:R1505"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -12589,7 +12878,9 @@
       </c>
       <c r="L109" s="18"/>
       <c r="M109" s="18"/>
-      <c r="N109" s="53"/>
+      <c r="N109" s="65">
+        <v>477</v>
+      </c>
       <c r="O109" s="18"/>
       <c r="P109" s="18"/>
       <c r="Q109" s="11">
@@ -14269,7 +14560,9 @@
       </c>
       <c r="L145" s="18"/>
       <c r="M145" s="18"/>
-      <c r="N145" s="53"/>
+      <c r="N145" s="65">
+        <v>467</v>
+      </c>
       <c r="O145" s="18"/>
       <c r="P145" s="18"/>
       <c r="Q145" s="11">
@@ -14411,7 +14704,9 @@
       </c>
       <c r="L148" s="18"/>
       <c r="M148" s="18"/>
-      <c r="N148" s="53"/>
+      <c r="N148" s="65">
+        <v>470</v>
+      </c>
       <c r="O148" s="18"/>
       <c r="P148" s="18"/>
       <c r="Q148" s="11">
@@ -14457,7 +14752,9 @@
       </c>
       <c r="L149" s="18"/>
       <c r="M149" s="18"/>
-      <c r="N149" s="53"/>
+      <c r="N149" s="65">
+        <v>449</v>
+      </c>
       <c r="O149" s="18"/>
       <c r="P149" s="18"/>
       <c r="Q149" s="11">
@@ -15605,8 +15902,8 @@
       </c>
       <c r="L174" s="18"/>
       <c r="M174" s="18"/>
-      <c r="N174" s="65">
-        <v>220</v>
+      <c r="N174" s="65" t="s">
+        <v>2206</v>
       </c>
       <c r="O174" s="18"/>
       <c r="P174" s="18"/>
@@ -18801,7 +19098,9 @@
       </c>
       <c r="L243" s="18"/>
       <c r="M243" s="18"/>
-      <c r="N243" s="53"/>
+      <c r="N243" s="65">
+        <v>471</v>
+      </c>
       <c r="O243" s="18"/>
       <c r="P243" s="18"/>
       <c r="Q243" s="11">
@@ -19627,7 +19926,9 @@
       </c>
       <c r="L261" s="18"/>
       <c r="M261" s="18"/>
-      <c r="N261" s="53"/>
+      <c r="N261" s="65">
+        <v>446</v>
+      </c>
       <c r="O261" s="18"/>
       <c r="P261" s="18"/>
       <c r="Q261" s="18"/>
@@ -19717,7 +20018,9 @@
       </c>
       <c r="L263" s="18"/>
       <c r="M263" s="18"/>
-      <c r="N263" s="53"/>
+      <c r="N263" s="65">
+        <v>447</v>
+      </c>
       <c r="O263" s="18"/>
       <c r="P263" s="18"/>
       <c r="Q263" s="11">
@@ -21429,7 +21732,9 @@
       </c>
       <c r="L302" s="18"/>
       <c r="M302" s="18"/>
-      <c r="N302" s="53"/>
+      <c r="N302" s="65">
+        <v>450</v>
+      </c>
       <c r="O302" s="18"/>
       <c r="P302" s="35"/>
       <c r="Q302" s="15">
@@ -21763,7 +22068,9 @@
       </c>
       <c r="L309" s="18"/>
       <c r="M309" s="18"/>
-      <c r="N309" s="53"/>
+      <c r="N309" s="65">
+        <v>457</v>
+      </c>
       <c r="O309" s="18"/>
       <c r="P309" s="18"/>
       <c r="Q309" s="15">
@@ -22369,7 +22676,9 @@
       </c>
       <c r="L322" s="18"/>
       <c r="M322" s="18"/>
-      <c r="N322" s="53"/>
+      <c r="N322" s="65">
+        <v>448</v>
+      </c>
       <c r="O322" s="18"/>
       <c r="P322" s="18"/>
       <c r="Q322" s="15">
@@ -25085,7 +25394,9 @@
       </c>
       <c r="L381" s="18"/>
       <c r="M381" s="18"/>
-      <c r="N381" s="53"/>
+      <c r="N381" s="65">
+        <v>473</v>
+      </c>
       <c r="O381" s="18"/>
       <c r="P381" s="18"/>
       <c r="Q381" s="11">
@@ -25131,7 +25442,9 @@
       </c>
       <c r="L382" s="18"/>
       <c r="M382" s="18"/>
-      <c r="N382" s="53"/>
+      <c r="N382" s="65">
+        <v>472</v>
+      </c>
       <c r="O382" s="18"/>
       <c r="P382" s="18"/>
       <c r="Q382" s="11">
@@ -29103,10 +29416,14 @@
       </c>
       <c r="L469" s="18"/>
       <c r="M469" s="18"/>
-      <c r="N469" s="53"/>
+      <c r="N469" s="65">
+        <v>462</v>
+      </c>
       <c r="O469" s="18"/>
       <c r="P469" s="18"/>
-      <c r="Q469" s="18"/>
+      <c r="Q469" s="11">
+        <v>77634818</v>
+      </c>
       <c r="R469" s="20" t="s">
         <v>11</v>
       </c>
@@ -30801,7 +31118,9 @@
       </c>
       <c r="L506" s="18"/>
       <c r="M506" s="18"/>
-      <c r="N506" s="53"/>
+      <c r="N506" s="65">
+        <v>428</v>
+      </c>
       <c r="O506" s="18"/>
       <c r="P506" s="18"/>
       <c r="Q506" s="11">
@@ -32099,7 +32418,9 @@
       </c>
       <c r="L534" s="18"/>
       <c r="M534" s="18"/>
-      <c r="N534" s="53"/>
+      <c r="N534" s="65">
+        <v>475</v>
+      </c>
       <c r="O534" s="18"/>
       <c r="P534" s="18"/>
       <c r="Q534" s="11">
@@ -32145,7 +32466,9 @@
       </c>
       <c r="L535" s="18"/>
       <c r="M535" s="18"/>
-      <c r="N535" s="53"/>
+      <c r="N535" s="65">
+        <v>474</v>
+      </c>
       <c r="O535" s="18"/>
       <c r="P535" s="18"/>
       <c r="Q535" s="11">
@@ -32643,7 +32966,9 @@
       </c>
       <c r="L546" s="18"/>
       <c r="M546" s="18"/>
-      <c r="N546" s="53"/>
+      <c r="N546" s="65">
+        <v>476</v>
+      </c>
       <c r="O546" s="18"/>
       <c r="P546" s="18"/>
       <c r="Q546" s="11">
@@ -35669,7 +35994,9 @@
       </c>
       <c r="L613" s="18"/>
       <c r="M613" s="18"/>
-      <c r="N613" s="53"/>
+      <c r="N613" s="65">
+        <v>429</v>
+      </c>
       <c r="O613" s="18"/>
       <c r="P613" s="18"/>
       <c r="Q613" s="11">
@@ -37511,7 +37838,9 @@
       </c>
       <c r="L652" s="18"/>
       <c r="M652" s="18"/>
-      <c r="N652" s="53"/>
+      <c r="N652" s="65">
+        <v>459</v>
+      </c>
       <c r="O652" s="18"/>
       <c r="P652" s="18"/>
       <c r="Q652" s="15">
@@ -38249,7 +38578,9 @@
       </c>
       <c r="L668" s="18"/>
       <c r="M668" s="18"/>
-      <c r="N668" s="53"/>
+      <c r="N668" s="65">
+        <v>452</v>
+      </c>
       <c r="O668" s="18"/>
       <c r="P668" s="18"/>
       <c r="Q668" s="15">
@@ -38295,7 +38626,9 @@
       </c>
       <c r="L669" s="18"/>
       <c r="M669" s="18"/>
-      <c r="N669" s="53"/>
+      <c r="N669" s="65">
+        <v>451</v>
+      </c>
       <c r="O669" s="18"/>
       <c r="P669" s="18"/>
       <c r="Q669" s="15">
@@ -41979,7 +42312,9 @@
       </c>
       <c r="L749" s="18"/>
       <c r="M749" s="18"/>
-      <c r="N749" s="53"/>
+      <c r="N749" s="65">
+        <v>432</v>
+      </c>
       <c r="O749" s="18"/>
       <c r="P749" s="18"/>
       <c r="Q749" s="48" t="s">
@@ -42311,7 +42646,9 @@
       </c>
       <c r="L756" s="18"/>
       <c r="M756" s="18"/>
-      <c r="N756" s="53"/>
+      <c r="N756" s="65">
+        <v>434</v>
+      </c>
       <c r="O756" s="18"/>
       <c r="P756" s="18"/>
       <c r="Q756" s="48">
@@ -42497,7 +42834,9 @@
       </c>
       <c r="L760" s="18"/>
       <c r="M760" s="18"/>
-      <c r="N760" s="53"/>
+      <c r="N760" s="65">
+        <v>427</v>
+      </c>
       <c r="O760" s="18"/>
       <c r="P760" s="18"/>
       <c r="Q760" s="48">
@@ -42681,7 +43020,9 @@
       </c>
       <c r="L764" s="18"/>
       <c r="M764" s="18"/>
-      <c r="N764" s="53"/>
+      <c r="N764" s="65">
+        <v>437</v>
+      </c>
       <c r="O764" s="18"/>
       <c r="P764" s="18"/>
       <c r="Q764" s="48">
@@ -48417,7 +48758,9 @@
       </c>
       <c r="L890" s="18"/>
       <c r="M890" s="18"/>
-      <c r="N890" s="53"/>
+      <c r="N890" s="65">
+        <v>430</v>
+      </c>
       <c r="O890" s="18"/>
       <c r="P890" s="18"/>
       <c r="Q890" s="11">
@@ -48509,7 +48852,9 @@
       </c>
       <c r="L892" s="18"/>
       <c r="M892" s="18"/>
-      <c r="N892" s="53"/>
+      <c r="N892" s="65">
+        <v>431</v>
+      </c>
       <c r="O892" s="18"/>
       <c r="P892" s="18"/>
       <c r="Q892" s="11">
@@ -51533,10 +51878,14 @@
       </c>
       <c r="L958" s="18"/>
       <c r="M958" s="18"/>
-      <c r="N958" s="53"/>
+      <c r="N958" s="65">
+        <v>466</v>
+      </c>
       <c r="O958" s="18"/>
       <c r="P958" s="18"/>
-      <c r="Q958" s="18"/>
+      <c r="Q958" s="15">
+        <v>77237461</v>
+      </c>
       <c r="R958" s="20" t="s">
         <v>11</v>
       </c>
@@ -53305,7 +53654,9 @@
       </c>
       <c r="L997" s="18"/>
       <c r="M997" s="18"/>
-      <c r="N997" s="53"/>
+      <c r="N997" s="65">
+        <v>468</v>
+      </c>
       <c r="O997" s="18"/>
       <c r="P997" s="18"/>
       <c r="Q997" s="15">
@@ -57725,7 +58076,9 @@
       </c>
       <c r="L1093" s="18"/>
       <c r="M1093" s="18"/>
-      <c r="N1093" s="53"/>
+      <c r="N1093" s="65">
+        <v>458</v>
+      </c>
       <c r="O1093" s="18"/>
       <c r="P1093" s="18"/>
       <c r="Q1093" s="48">
@@ -57953,7 +58306,9 @@
       </c>
       <c r="L1098" s="18"/>
       <c r="M1098" s="18"/>
-      <c r="N1098" s="53"/>
+      <c r="N1098" s="65">
+        <v>433</v>
+      </c>
       <c r="O1098" s="18"/>
       <c r="P1098" s="18"/>
       <c r="Q1098" s="48">
@@ -57999,7 +58354,9 @@
       </c>
       <c r="L1099" s="18"/>
       <c r="M1099" s="18"/>
-      <c r="N1099" s="53"/>
+      <c r="N1099" s="65">
+        <v>435</v>
+      </c>
       <c r="O1099" s="18"/>
       <c r="P1099" s="18"/>
       <c r="Q1099" s="48">
@@ -58045,7 +58402,9 @@
       </c>
       <c r="L1100" s="18"/>
       <c r="M1100" s="18"/>
-      <c r="N1100" s="53"/>
+      <c r="N1100" s="65">
+        <v>454</v>
+      </c>
       <c r="O1100" s="18"/>
       <c r="P1100" s="18"/>
       <c r="Q1100" s="48">
@@ -58091,7 +58450,9 @@
       </c>
       <c r="L1101" s="18"/>
       <c r="M1101" s="18"/>
-      <c r="N1101" s="53"/>
+      <c r="N1101" s="65">
+        <v>455</v>
+      </c>
       <c r="O1101" s="18"/>
       <c r="P1101" s="18"/>
       <c r="Q1101" s="48">
@@ -58137,7 +58498,9 @@
       </c>
       <c r="L1102" s="18"/>
       <c r="M1102" s="18"/>
-      <c r="N1102" s="53"/>
+      <c r="N1102" s="65">
+        <v>453</v>
+      </c>
       <c r="O1102" s="18"/>
       <c r="P1102" s="18"/>
       <c r="Q1102" s="48">
@@ -61733,7 +62096,9 @@
       </c>
       <c r="L1180" s="18"/>
       <c r="M1180" s="18"/>
-      <c r="N1180" s="53"/>
+      <c r="N1180" s="65">
+        <v>421</v>
+      </c>
       <c r="O1180" s="18"/>
       <c r="P1180" s="18"/>
       <c r="Q1180" s="48">
@@ -63505,7 +63870,9 @@
       </c>
       <c r="L1219" s="18"/>
       <c r="M1219" s="18"/>
-      <c r="N1219" s="53"/>
+      <c r="N1219" s="65">
+        <v>422</v>
+      </c>
       <c r="O1219" s="18"/>
       <c r="P1219" s="18"/>
       <c r="Q1219" s="15">
@@ -63551,7 +63918,9 @@
       </c>
       <c r="L1220" s="18"/>
       <c r="M1220" s="18"/>
-      <c r="N1220" s="53"/>
+      <c r="N1220" s="65">
+        <v>423</v>
+      </c>
       <c r="O1220" s="18"/>
       <c r="P1220" s="18"/>
       <c r="Q1220" s="15">
@@ -64379,7 +64748,9 @@
       </c>
       <c r="L1238" s="18"/>
       <c r="M1238" s="18"/>
-      <c r="N1238" s="53"/>
+      <c r="N1238" s="65">
+        <v>436</v>
+      </c>
       <c r="O1238" s="18"/>
       <c r="P1238" s="18"/>
       <c r="Q1238" s="11">
@@ -69580,7 +69951,9 @@
       <c r="J1352" s="15" t="s">
         <v>1405</v>
       </c>
-      <c r="K1352" s="18"/>
+      <c r="K1352" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1352" s="18"/>
       <c r="M1352" s="18"/>
       <c r="N1352" s="53"/>
@@ -69622,7 +69995,9 @@
       <c r="J1353" s="15" t="s">
         <v>1406</v>
       </c>
-      <c r="K1353" s="18"/>
+      <c r="K1353" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1353" s="18"/>
       <c r="M1353" s="18"/>
       <c r="N1353" s="53"/>
@@ -69666,7 +70041,9 @@
       <c r="J1354" s="15" t="s">
         <v>1406</v>
       </c>
-      <c r="K1354" s="18"/>
+      <c r="K1354" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1354" s="18"/>
       <c r="M1354" s="18"/>
       <c r="N1354" s="53"/>
@@ -69758,7 +70135,9 @@
       <c r="J1356" s="15" t="s">
         <v>405</v>
       </c>
-      <c r="K1356" s="18"/>
+      <c r="K1356" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1356" s="18"/>
       <c r="M1356" s="18"/>
       <c r="N1356" s="53"/>
@@ -69848,7 +70227,9 @@
       <c r="J1358" s="15" t="s">
         <v>1429</v>
       </c>
-      <c r="K1358" s="18"/>
+      <c r="K1358" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1358" s="18"/>
       <c r="M1358" s="18"/>
       <c r="N1358" s="53"/>
@@ -69890,7 +70271,9 @@
       <c r="J1359" s="15" t="s">
         <v>1429</v>
       </c>
-      <c r="K1359" s="18"/>
+      <c r="K1359" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1359" s="18"/>
       <c r="M1359" s="18"/>
       <c r="N1359" s="53"/>
@@ -69932,7 +70315,9 @@
       <c r="J1360" s="15" t="s">
         <v>1429</v>
       </c>
-      <c r="K1360" s="18"/>
+      <c r="K1360" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1360" s="18"/>
       <c r="M1360" s="18"/>
       <c r="N1360" s="53"/>
@@ -69976,7 +70361,9 @@
       <c r="J1361" s="15" t="s">
         <v>825</v>
       </c>
-      <c r="K1361" s="18"/>
+      <c r="K1361" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1361" s="18"/>
       <c r="M1361" s="18"/>
       <c r="N1361" s="53"/>
@@ -69989,7 +70376,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1362" spans="1:18" ht="27.6" thickBot="1">
+    <row r="1362" spans="1:18" ht="15" thickBot="1">
       <c r="A1362" s="2">
         <v>25</v>
       </c>
@@ -70020,7 +70407,9 @@
       <c r="J1362" s="15" t="s">
         <v>825</v>
       </c>
-      <c r="K1362" s="18"/>
+      <c r="K1362" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1362" s="18"/>
       <c r="M1362" s="18"/>
       <c r="N1362" s="53"/>
@@ -70037,7 +70426,9 @@
       <c r="A1363" s="2">
         <v>26</v>
       </c>
-      <c r="B1363" s="18"/>
+      <c r="B1363" s="10">
+        <v>46254</v>
+      </c>
       <c r="C1363" s="46" t="s">
         <v>2090</v>
       </c>
@@ -70062,7 +70453,9 @@
       <c r="J1363" s="15" t="s">
         <v>825</v>
       </c>
-      <c r="K1363" s="18"/>
+      <c r="K1363" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1363" s="18"/>
       <c r="M1363" s="18"/>
       <c r="N1363" s="53"/>
@@ -70079,7 +70472,9 @@
       <c r="A1364" s="2">
         <v>27</v>
       </c>
-      <c r="B1364" s="18"/>
+      <c r="B1364" s="10">
+        <v>46254</v>
+      </c>
       <c r="C1364" s="46" t="s">
         <v>2092</v>
       </c>
@@ -70104,7 +70499,9 @@
       <c r="J1364" s="15" t="s">
         <v>825</v>
       </c>
-      <c r="K1364" s="18"/>
+      <c r="K1364" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1364" s="18"/>
       <c r="M1364" s="18"/>
       <c r="N1364" s="53"/>
@@ -70121,7 +70518,9 @@
       <c r="A1365" s="2">
         <v>28</v>
       </c>
-      <c r="B1365" s="18"/>
+      <c r="B1365" s="10">
+        <v>46254</v>
+      </c>
       <c r="C1365" s="46" t="s">
         <v>2094</v>
       </c>
@@ -70146,7 +70545,9 @@
       <c r="J1365" s="15" t="s">
         <v>825</v>
       </c>
-      <c r="K1365" s="18"/>
+      <c r="K1365" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1365" s="18"/>
       <c r="M1365" s="18"/>
       <c r="N1365" s="53"/>
@@ -70161,7 +70562,9 @@
       <c r="A1366" s="2">
         <v>29</v>
       </c>
-      <c r="B1366" s="18"/>
+      <c r="B1366" s="10">
+        <v>46254</v>
+      </c>
       <c r="C1366" s="46" t="s">
         <v>2096</v>
       </c>
@@ -70186,7 +70589,9 @@
       <c r="J1366" s="15" t="s">
         <v>825</v>
       </c>
-      <c r="K1366" s="18"/>
+      <c r="K1366" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1366" s="18"/>
       <c r="M1366" s="18"/>
       <c r="N1366" s="53"/>
@@ -70201,7 +70606,9 @@
       <c r="A1367" s="2">
         <v>30</v>
       </c>
-      <c r="B1367" s="18"/>
+      <c r="B1367" s="10">
+        <v>46254</v>
+      </c>
       <c r="C1367" s="46" t="s">
         <v>2098</v>
       </c>
@@ -70226,7 +70633,9 @@
       <c r="J1367" s="15" t="s">
         <v>825</v>
       </c>
-      <c r="K1367" s="18"/>
+      <c r="K1367" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1367" s="18"/>
       <c r="M1367" s="18"/>
       <c r="N1367" s="53"/>
@@ -70243,7 +70652,9 @@
       <c r="A1368" s="2">
         <v>31</v>
       </c>
-      <c r="B1368" s="18"/>
+      <c r="B1368" s="10">
+        <v>46254</v>
+      </c>
       <c r="C1368" s="46" t="s">
         <v>2099</v>
       </c>
@@ -70268,7 +70679,9 @@
       <c r="J1368" s="15" t="s">
         <v>825</v>
       </c>
-      <c r="K1368" s="18"/>
+      <c r="K1368" s="17" t="s">
+        <v>12</v>
+      </c>
       <c r="L1368" s="18"/>
       <c r="M1368" s="18"/>
       <c r="N1368" s="53"/>
@@ -70287,10 +70700,10 @@
         <v>46254</v>
       </c>
       <c r="C1369" s="46" t="s">
-        <v>2100</v>
+        <v>465</v>
       </c>
       <c r="D1369" s="46">
-        <v>135610387</v>
+        <v>137221766</v>
       </c>
       <c r="E1369" s="12" t="s">
         <v>20</v>
@@ -70299,16 +70712,16 @@
         <v>81</v>
       </c>
       <c r="G1369" s="14">
-        <v>9474</v>
+        <v>5865</v>
       </c>
       <c r="H1369" s="15">
-        <v>2128</v>
+        <v>1817</v>
       </c>
       <c r="I1369" s="22" t="s">
         <v>274</v>
       </c>
-      <c r="J1369" s="44" t="s">
-        <v>275</v>
+      <c r="J1369" s="15" t="s">
+        <v>825</v>
       </c>
       <c r="K1369" s="17" t="s">
         <v>12</v>
@@ -70318,11 +70731,11 @@
       <c r="N1369" s="53"/>
       <c r="O1369" s="18"/>
       <c r="P1369" s="18"/>
-      <c r="Q1369" s="15">
-        <v>77291147</v>
-      </c>
-      <c r="R1369" s="22" t="s">
-        <v>87</v>
+      <c r="Q1369" s="11">
+        <v>91382542</v>
+      </c>
+      <c r="R1369" s="20" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="1370" spans="1:18" ht="15" thickBot="1">
@@ -70333,42 +70746,40 @@
         <v>46254</v>
       </c>
       <c r="C1370" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1370" s="46">
-        <v>85334357</v>
+        <v>2207</v>
+      </c>
+      <c r="D1370" s="46" t="s">
+        <v>2208</v>
       </c>
       <c r="E1370" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1370" s="16" t="s">
-        <v>81</v>
+      <c r="F1370" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G1370" s="14">
-        <v>2471</v>
-      </c>
-      <c r="H1370" s="15" t="s">
-        <v>2101</v>
+        <v>79505</v>
+      </c>
+      <c r="H1370" s="15">
+        <v>29599</v>
       </c>
       <c r="I1370" s="22" t="s">
         <v>274</v>
       </c>
-      <c r="J1370" s="44" t="s">
-        <v>275</v>
-      </c>
-      <c r="K1370" s="17" t="s">
-        <v>12</v>
+      <c r="J1370" s="15" t="s">
+        <v>825</v>
+      </c>
+      <c r="K1370" s="30" t="s">
+        <v>638</v>
       </c>
       <c r="L1370" s="18"/>
       <c r="M1370" s="18"/>
       <c r="N1370" s="53"/>
       <c r="O1370" s="18"/>
       <c r="P1370" s="18"/>
-      <c r="Q1370" s="15">
-        <v>79694547</v>
-      </c>
-      <c r="R1370" s="22" t="s">
-        <v>87</v>
+      <c r="Q1370" s="18"/>
+      <c r="R1370" s="20" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="1371" spans="1:18" ht="15" thickBot="1">
@@ -70379,10 +70790,10 @@
         <v>46254</v>
       </c>
       <c r="C1371" s="46" t="s">
-        <v>2102</v>
+        <v>2209</v>
       </c>
       <c r="D1371" s="46" t="s">
-        <v>2103</v>
+        <v>2210</v>
       </c>
       <c r="E1371" s="12" t="s">
         <v>20</v>
@@ -70391,16 +70802,16 @@
         <v>21</v>
       </c>
       <c r="G1371" s="14">
-        <v>67481</v>
+        <v>23875</v>
       </c>
       <c r="H1371" s="15">
-        <v>23664</v>
+        <v>53385</v>
       </c>
       <c r="I1371" s="22" t="s">
         <v>274</v>
       </c>
-      <c r="J1371" s="44" t="s">
-        <v>275</v>
+      <c r="J1371" s="15" t="s">
+        <v>825</v>
       </c>
       <c r="K1371" s="17" t="s">
         <v>12</v>
@@ -70410,14 +70821,14 @@
       <c r="N1371" s="53"/>
       <c r="O1371" s="18"/>
       <c r="P1371" s="18"/>
-      <c r="Q1371" s="15">
-        <v>95643738</v>
-      </c>
-      <c r="R1371" s="22" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="1372" spans="1:18" ht="15" thickBot="1">
+      <c r="Q1371" s="11">
+        <v>96890683052</v>
+      </c>
+      <c r="R1371" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:18" ht="27.6" thickBot="1">
       <c r="A1372" s="2">
         <v>35</v>
       </c>
@@ -70425,10 +70836,10 @@
         <v>46254</v>
       </c>
       <c r="C1372" s="46" t="s">
-        <v>2104</v>
+        <v>2211</v>
       </c>
       <c r="D1372" s="46" t="s">
-        <v>2105</v>
+        <v>2212</v>
       </c>
       <c r="E1372" s="12" t="s">
         <v>20</v>
@@ -70437,14 +70848,16 @@
         <v>21</v>
       </c>
       <c r="G1372" s="14">
-        <v>87381</v>
-      </c>
-      <c r="H1372" s="18"/>
+        <v>31663</v>
+      </c>
+      <c r="H1372" s="15">
+        <v>66670</v>
+      </c>
       <c r="I1372" s="22" t="s">
         <v>274</v>
       </c>
-      <c r="J1372" s="44" t="s">
-        <v>275</v>
+      <c r="J1372" s="15" t="s">
+        <v>825</v>
       </c>
       <c r="K1372" s="17" t="s">
         <v>12</v>
@@ -70454,11 +70867,11 @@
       <c r="N1372" s="53"/>
       <c r="O1372" s="18"/>
       <c r="P1372" s="18"/>
-      <c r="Q1372" s="15">
-        <v>956463027</v>
-      </c>
-      <c r="R1372" s="22" t="s">
-        <v>87</v>
+      <c r="Q1372" s="11">
+        <v>96876789204</v>
+      </c>
+      <c r="R1372" s="20" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="1373" spans="1:18" ht="15" thickBot="1">
@@ -70469,10 +70882,10 @@
         <v>46254</v>
       </c>
       <c r="C1373" s="46" t="s">
-        <v>41</v>
+        <v>2213</v>
       </c>
       <c r="D1373" s="46" t="s">
-        <v>2106</v>
+        <v>2214</v>
       </c>
       <c r="E1373" s="12" t="s">
         <v>20</v>
@@ -70481,14 +70894,16 @@
         <v>21</v>
       </c>
       <c r="G1373" s="14">
-        <v>33404</v>
-      </c>
-      <c r="H1373" s="18"/>
+        <v>28100</v>
+      </c>
+      <c r="H1373" s="15">
+        <v>36508</v>
+      </c>
       <c r="I1373" s="22" t="s">
         <v>274</v>
       </c>
-      <c r="J1373" s="44" t="s">
-        <v>275</v>
+      <c r="J1373" s="15" t="s">
+        <v>825</v>
       </c>
       <c r="K1373" s="17" t="s">
         <v>12</v>
@@ -70498,11 +70913,11 @@
       <c r="N1373" s="53"/>
       <c r="O1373" s="18"/>
       <c r="P1373" s="18"/>
-      <c r="Q1373" s="15">
-        <v>95643750</v>
-      </c>
-      <c r="R1373" s="22" t="s">
-        <v>87</v>
+      <c r="Q1373" s="11">
+        <v>93963066</v>
+      </c>
+      <c r="R1373" s="20" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="1374" spans="1:18" ht="15" thickBot="1">
@@ -70513,10 +70928,10 @@
         <v>46254</v>
       </c>
       <c r="C1374" s="46" t="s">
-        <v>2107</v>
+        <v>2215</v>
       </c>
       <c r="D1374" s="46" t="s">
-        <v>2108</v>
+        <v>2216</v>
       </c>
       <c r="E1374" s="12" t="s">
         <v>20</v>
@@ -70525,16 +70940,16 @@
         <v>21</v>
       </c>
       <c r="G1374" s="14">
-        <v>73947</v>
+        <v>95098</v>
       </c>
       <c r="H1374" s="15">
-        <v>37518</v>
+        <v>76771</v>
       </c>
       <c r="I1374" s="22" t="s">
         <v>274</v>
       </c>
-      <c r="J1374" s="44" t="s">
-        <v>275</v>
+      <c r="J1374" s="15" t="s">
+        <v>825</v>
       </c>
       <c r="K1374" s="17" t="s">
         <v>12</v>
@@ -70544,14 +70959,14 @@
       <c r="N1374" s="53"/>
       <c r="O1374" s="18"/>
       <c r="P1374" s="18"/>
-      <c r="Q1374" s="15">
-        <v>971568487207</v>
-      </c>
-      <c r="R1374" s="22" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="1375" spans="1:18" ht="15" thickBot="1">
+      <c r="Q1374" s="11">
+        <v>78941465</v>
+      </c>
+      <c r="R1374" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:18" ht="27.6" thickBot="1">
       <c r="A1375" s="2">
         <v>38</v>
       </c>
@@ -70559,10 +70974,10 @@
         <v>46254</v>
       </c>
       <c r="C1375" s="46" t="s">
-        <v>2109</v>
+        <v>577</v>
       </c>
       <c r="D1375" s="46" t="s">
-        <v>2110</v>
+        <v>2217</v>
       </c>
       <c r="E1375" s="12" t="s">
         <v>20</v>
@@ -70571,30 +70986,28 @@
         <v>21</v>
       </c>
       <c r="G1375" s="14">
-        <v>71946</v>
+        <v>56846</v>
       </c>
       <c r="H1375" s="15">
-        <v>99468</v>
+        <v>74554</v>
       </c>
       <c r="I1375" s="22" t="s">
         <v>274</v>
       </c>
-      <c r="J1375" s="44" t="s">
-        <v>275</v>
-      </c>
-      <c r="K1375" s="17" t="s">
-        <v>12</v>
+      <c r="J1375" s="15" t="s">
+        <v>825</v>
+      </c>
+      <c r="K1375" s="30" t="s">
+        <v>638</v>
       </c>
       <c r="L1375" s="18"/>
       <c r="M1375" s="18"/>
       <c r="N1375" s="53"/>
       <c r="O1375" s="18"/>
       <c r="P1375" s="18"/>
-      <c r="Q1375" s="15">
-        <v>77411027</v>
-      </c>
-      <c r="R1375" s="22" t="s">
-        <v>87</v>
+      <c r="Q1375" s="18"/>
+      <c r="R1375" s="20" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="1376" spans="1:18" ht="15" thickBot="1">
@@ -70605,28 +71018,28 @@
         <v>46254</v>
       </c>
       <c r="C1376" s="46" t="s">
-        <v>2111</v>
-      </c>
-      <c r="D1376" s="46">
-        <v>111924926</v>
+        <v>2218</v>
+      </c>
+      <c r="D1376" s="46" t="s">
+        <v>2219</v>
       </c>
       <c r="E1376" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1376" s="16" t="s">
-        <v>81</v>
+      <c r="F1376" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="G1376" s="14">
-        <v>5597</v>
+        <v>23687</v>
       </c>
       <c r="H1376" s="15">
-        <v>2276</v>
+        <v>-53385</v>
       </c>
       <c r="I1376" s="22" t="s">
         <v>274</v>
       </c>
-      <c r="J1376" s="44" t="s">
-        <v>275</v>
+      <c r="J1376" s="15" t="s">
+        <v>825</v>
       </c>
       <c r="K1376" s="17" t="s">
         <v>12</v>
@@ -70636,11 +71049,9 @@
       <c r="N1376" s="53"/>
       <c r="O1376" s="18"/>
       <c r="P1376" s="18"/>
-      <c r="Q1376" s="15">
-        <v>94182149</v>
-      </c>
-      <c r="R1376" s="22" t="s">
-        <v>87</v>
+      <c r="Q1376" s="18"/>
+      <c r="R1376" s="20" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="1377" spans="1:18" ht="15" thickBot="1">
@@ -70651,45 +71062,43 @@
         <v>46254</v>
       </c>
       <c r="C1377" s="46" t="s">
-        <v>2112</v>
-      </c>
-      <c r="D1377" s="46">
-        <v>82569082</v>
+        <v>2220</v>
+      </c>
+      <c r="D1377" s="46" t="s">
+    